--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -1,126 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
-  <si>
-    <t>teacher_name</t>
-  </si>
-  <si>
-    <t>department</t>
-  </si>
-  <si>
-    <t>position</t>
-  </si>
-  <si>
-    <t>trios_url</t>
-  </si>
-  <si>
-    <t>trios_status</t>
-  </si>
-  <si>
-    <t>trios_topics</t>
-  </si>
-  <si>
-    <t>trios_topics_text</t>
-  </si>
-  <si>
-    <t>trios_papers</t>
-  </si>
-  <si>
-    <t>trios_papers_text</t>
-  </si>
-  <si>
-    <t>past_thesis_titles</t>
-  </si>
-  <si>
-    <t>past_thesis_titles_text</t>
-  </si>
-  <si>
-    <t>research_fields</t>
-  </si>
-  <si>
-    <t>research_fields_text</t>
-  </si>
-  <si>
-    <t>山田太郎</t>
-  </si>
-  <si>
-    <t>鈴木花子</t>
-  </si>
-  <si>
-    <t>社会工学学位プログラム</t>
-  </si>
-  <si>
-    <t>教授</t>
-  </si>
-  <si>
-    <t>准教授</t>
-  </si>
-  <si>
-    <t>nan</t>
-  </si>
-  <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>公共施設配置問題に対する組合せ最適化手法の研究 ; 交通流制御における数理最適化モデルの構築</t>
-  </si>
-  <si>
-    <t>物流ネットワーク再設計のための需要予測手法</t>
-  </si>
-  <si>
-    <t>公共施設配置問題に対する組合せ最適化手法の研究 / 交通流制御における数理最適化モデルの構築</t>
-  </si>
-  <si>
-    <t>最適化 ; 意思決定支援 ; 組合せ最適化 ; 数理最適化</t>
-  </si>
-  <si>
-    <t>需要予測 ; 物流最適化 ; ネットワーク科学 ; 社会ネットワーク分析</t>
-  </si>
-  <si>
-    <t>最適化 / 意思決定支援 / 組合せ最適化 / 数理最適化</t>
-  </si>
-  <si>
-    <t>需要予測 / 物流最適化 / ネットワーク科学 / 社会ネットワーク分析</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -135,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -451,110 +420,1414 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" t="s">
-        <v>26</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>teacher_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>trios_url</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>trios_status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>trios_topics</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>trios_topics_text</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>trios_papers</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>trios_papers_text</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>past_thesis_titles</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>past_thesis_titles_text</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>research_fields</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>research_fields_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>吉瀬章子</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000855</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>リーマン多様体上の制約付き最適化問題に対する汎用アルゴリズムの理論と実装 ; リーマン多様体上の最適化理論に基づく新たなデータコラボレーション手法の開発 ; ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発 ; コネクティッドカーのサービス開発を目的とした走行データのデータクレンジング手法に係る研究 ; 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 ; ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発 ; 半正定値基を用いた錐最適化問題の近似解法の開発 ; 地域未来創生共同研究講座 ; 次世代社会システムとモビリティの新価値研究 ; 購買データに基づく顧客行動分析</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>リーマン多様体上の制約付き最適化問題に対する汎用アルゴリズムの理論と実装 / リーマン多様体上の最適化理論に基づく新たなデータコラボレーション手法の開発 / ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発 / コネクティッドカーのサービス開発を目的とした走行データのデータクレンジング手法に係る研究 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発 / 半正定値基を用いた錐最適化問題の近似解法の開発 / 地域未来創生共同研究講座 / 次世代社会システムとモビリティの新価値研究 / 購買データに基づく顧客行動分析</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Data Collaboration Analysis with Orthonormal Basis Selection and Alignment ; Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning ; 正循環制約を考慮したナーススケジューリング ; Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices ; Post-Processing with Projection and Rescaling Algorithms for Semidefinite Programming ; Riemannian Interior Point Methods for Constrained Optimization on Manifolds ; A new extension of Chubanov's method to symmetric cones ; 射影- 再スケーリング法を用いた 対称錐計画問題に対する後処理アルゴリズム ; Riemannian Interior Point Methods for Constrained Optimization on Manifolds ; On the Global Convergence of Riemannian Interior Point Method ; Completely positive factorization by a Riemannian smoothing method ; Evaluating approximations of the semidefinite cone with trace normalized distance ; Evaluating approximations of the semidefinite cone with trace normalized distance ; A New Extension of Chubanov's Method to Symmetric Cones ; Riemannian Interior Point Methods for Constrained Optimization on Manifolds ; Completely Positive Factorization in Orthogonality Optimization via Smoothing Method ; Scenario-based CVaR Approach to Strategic Decision Support in One-way Station-based Carsharing Systems ; Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach ; Polyhedral approximations of the semidefinite cone and their application ; Centering ADMM for the Semidefinite Relaxation of the QAP ; QAPの半正定値緩和問題を解くためのセンタリングADMM ; SD基に基づく半正定値行列錐の凸多面錐近似 ; ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― ; Centering ADMM for the Semidefinite Relaxation of the QAP ; Polyhedral approximations of the semidefinite cone and their application</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Data Collaboration Analysis with Orthonormal Basis Selection and Alignment / Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning / 正循環制約を考慮したナーススケジューリング / Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices / Post-Processing with Projection and Rescaling Algorithms for Semidefinite Programming / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / A new extension of Chubanov's method to symmetric cones / 射影- 再スケーリング法を用いた 対称錐計画問題に対する後処理アルゴリズム / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / On the Global Convergence of Riemannian Interior Point Method / Completely positive factorization by a Riemannian smoothing method / Evaluating approximations of the semidefinite cone with trace normalized distance / Evaluating approximations of the semidefinite cone with trace normalized distance / A New Extension of Chubanov's Method to Symmetric Cones / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / Completely Positive Factorization in Orthogonality Optimization via Smoothing Method / Scenario-based CVaR Approach to Strategic Decision Support in One-way Station-based Carsharing Systems / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach / Polyhedral approximations of the semidefinite cone and their application / Centering ADMM for the Semidefinite Relaxation of the QAP / QAPの半正定値緩和問題を解くためのセンタリングADMM / SD基に基づく半正定値行列錐の凸多面錐近似 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― / Centering ADMM for the Semidefinite Relaxation of the QAP / Polyhedral approximations of the semidefinite cone and their application</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>数理最適化 ; 組合せ最適化 ; 物流最適化 ; 学習分析 ; 社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>数理最適化 / 組合せ最適化 / 物流最適化 / 学習分析 / 社会ネットワーク分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>小西葉子</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000005040</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>サービス業における顧客行動と経営者の価格・立地戦略に関する統計解析 ; 構造計量モデリングによるサービス産業の生産性の計測 ; 経済主体間の異質性に起因する内生性を含むセミパラメトリックモデルの計量経済分析 ; 生産性の識別と推定のためのミクロ計量理論とその応用 研究課題 ; 大規模データを使った因果推論のためのミクロ計量経済分析とEBPMへの応用 ; データ駆動パラメータが統計的機械学習に与える影響の高次漸近特性の理論的解明と応用</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>サービス業における顧客行動と経営者の価格・立地戦略に関する統計解析 / 構造計量モデリングによるサービス産業の生産性の計測 / 経済主体間の異質性に起因する内生性を含むセミパラメトリックモデルの計量経済分析 / 生産性の識別と推定のためのミクロ計量理論とその応用 研究課題 / 大規模データを使った因果推論のためのミクロ計量経済分析とEBPMへの応用 / データ駆動パラメータが統計的機械学習に与える影響の高次漸近特性の理論的解明と応用</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>学習分析 ; マーケティング分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 統計学</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>学習分析 / マーケティング分析 / 行政データ分析 / 社会ネットワーク分析 / 統計学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>高野祐一</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000004075</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>大規模な両面市場に対する公平性を考慮した取引促進施策の包括的最適化 ; 混合整数最適化による次元縮約法の最良スパース推定 ; 混合整数最適化を用いた制約付き変数選択による高精度パラメータ推定 ; ノンパラメトリック推定に基づくテスト理論モデルの研究 ; カーネル法と制御ポリシーを用いた中長期的投資戦略最適化 ; 取引コストを考慮した多期間ポートフォリオの最適化</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>大規模な両面市場に対する公平性を考慮した取引促進施策の包括的最適化 / 混合整数最適化による次元縮約法の最良スパース推定 / 混合整数最適化を用いた制約付き変数選択による高精度パラメータ推定 / ノンパラメトリック推定に基づくテスト理論モデルの研究 / カーネル法と制御ポリシーを用いた中長期的投資戦略最適化 / 取引コストを考慮した多期間ポートフォリオの最適化</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>数理最適化 ; 物流最適化 ; 組合せ最適化 ; 最適化 ; マーケティング分析</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>数理最適化 / 物流最適化 / 組合せ最適化 / 最適化 / マーケティング分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>繆瑩</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000867</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>不正者追跡アルゴリズムの開発とその応用 ; デジタル指紋符号、多重接続通信路、及び組合せ探索問題 ; スパースな結合行列を持つ組合せ的構造の分析と構成 ; デジタル指紋及びグループ検査に共通する組合せ構造とアルゴリズムに関する研究 ; 組合せ論的マルチメディア指紋符号とその不正者追跡アルゴリズムの研究 ; 完全差集合族とそのレーダー配列への応用に関する研究 ; 組合せ的デザイン理論を用いた周波数ホッピング系列の構成に関する研究 ; 組合せ的デザイン理論を用いた光直交符号の構成に関する研究 ; 組合せ的デザインとその符号・暗号への応用</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不正者追跡アルゴリズムの開発とその応用 / デジタル指紋符号、多重接続通信路、及び組合せ探索問題 / スパースな結合行列を持つ組合せ的構造の分析と構成 / デジタル指紋及びグループ検査に共通する組合せ構造とアルゴリズムに関する研究 / 組合せ論的マルチメディア指紋符号とその不正者追跡アルゴリズムの研究 / 完全差集合族とそのレーダー配列への応用に関する研究 / 組合せ的デザイン理論を用いた周波数ホッピング系列の構成に関する研究 / 組合せ的デザイン理論を用いた光直交符号の構成に関する研究 / 組合せ的デザインとその符号・暗号への応用</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) ; A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) ; Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) ; Repairing Schemes for Tamo-Barg Codes ; A Construction of Optimal One-Coincidence Frequency-Hopping Sequences via Generalized Cyclotomy ; Secure Codes With List Decoding ; Codes for Exact Support Recovery of Sparse Vectors from Inaccurate Linear Measurements and Their Decoding ; Optimal Locally Repairable Codes: An Improved Bound and Constructions ; On the Information-Theoretic Security of Combinatorial All-or-Nothing Transforms ; A Construction of Maximally Recoverable Codes With Order-Optimal Field Size ; Capacity-Achieving Private Information Retrieval Schemes From Uncoded Storage Constrained Servers With Low Sub-Packetization ; BCH codes with minimum distance proportional to code length ; Existence and Construction of Complete Traceability Multimedia Fingerprinting Codes Resistant to Averaging Attack and Adversarial Noise ; Strongly separable matrices for nonadaptive combinatorial group testing ; Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting ; Algebraic manipulation detection codes via highly nonlinear functions ; On Optimal Locally Repairable Codes With Super-Linear Length ; On optimal weak algebraic manipulation detection codes and weighted external difference families ; On Optimal Locally Repairable Codes With Multiple Disjoint Repair Sets ; Improved Bounds for Separable Codes and B-2 Codes ; Probabilistic Existence Results for Parent-Identifying Schemes ; Non-adaptive group testing on graphs with connectivity ; Bounds on Traceability Schemes ; New Bounds for Frameproof Codes ; Zero-difference balanced functions with new parameters and their applications</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) / A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) / Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) / Repairing Schemes for Tamo-Barg Codes / A Construction of Optimal One-Coincidence Frequency-Hopping Sequences via Generalized Cyclotomy / Secure Codes With List Decoding / Codes for Exact Support Recovery of Sparse Vectors from Inaccurate Linear Measurements and Their Decoding / Optimal Locally Repairable Codes: An Improved Bound and Constructions / On the Information-Theoretic Security of Combinatorial All-or-Nothing Transforms / A Construction of Maximally Recoverable Codes With Order-Optimal Field Size / Capacity-Achieving Private Information Retrieval Schemes From Uncoded Storage Constrained Servers With Low Sub-Packetization / BCH codes with minimum distance proportional to code length / Existence and Construction of Complete Traceability Multimedia Fingerprinting Codes Resistant to Averaging Attack and Adversarial Noise / Strongly separable matrices for nonadaptive combinatorial group testing / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting / Algebraic manipulation detection codes via highly nonlinear functions / On Optimal Locally Repairable Codes With Super-Linear Length / On optimal weak algebraic manipulation detection codes and weighted external difference families / On Optimal Locally Repairable Codes With Multiple Disjoint Repair Sets / Improved Bounds for Separable Codes and B-2 Codes / Probabilistic Existence Results for Parent-Identifying Schemes / Non-adaptive group testing on graphs with connectivity / Bounds on Traceability Schemes / New Bounds for Frameproof Codes / Zero-difference balanced functions with new parameters and their applications</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>組合せ最適化 ; 数理最適化 ; 自然言語処理 ; 災害分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>組合せ最適化 / 数理最適化 / 自然言語処理 / 災害分析 / 学習分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>有馬澄佳</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000810</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化 ; ワークライフバランスに貢献するサイバー・フィジカル製造業 ; 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配 ; 半導体・液晶製造の良品スループット向上とコスト低減の両立を目指してQ-time制約の遵守と装置の生産性向上とを同時に実現する実時間最適オペレーション管理手法の研究 ; ＱＣＤＲモデルに基づいて革新的な総合設備効率の向上と生産期間の短縮を実現する工場・設備の運用管理システム ; ＱＣＤモデルに基づくマルチチャンバ装置および生産ラインの運用・設計方法 ; 共創ビジョンに基づく半導体産業のビジネスモデル進化と、知財・人材の組織的流動化</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化 / ワークライフバランスに貢献するサイバー・フィジカル製造業 / 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配 / 半導体・液晶製造の良品スループット向上とコスト低減の両立を目指してQ-time制約の遵守と装置の生産性向上とを同時に実現する実時間最適オペレーション管理手法の研究 / ＱＣＤＲモデルに基づいて革新的な総合設備効率の向上と生産期間の短縮を実現する工場・設備の運用管理システム / ＱＣＤモデルに基づくマルチチャンバ装置および生産ラインの運用・設計方法 / 共創ビジョンに基づく半導体産業のビジネスモデル進化と、知財・人材の組織的流動化</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>"INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH ; Robust Classifications of WBM Defect Patterns ; Due dates assignment based on customer changeability classifications in Make-to-order productoins ; Pipeline production model and sensitivity analysis of Engineering-to-Order products using system dynamics ; PRODUCTION AND JOB ROTATION PLANNING CONSIDERING DISABILITIES AND HEALTH CONDITIONS ; Classification of Multivariate Time Series Signals Using Self-Supervised Representation Learning ; Multi-factory Scheduling Considering the Trade-offs between Production Efficiency and Risks ; Analysis of Resilience Factors and Satisfaction in Life-line Charts for Life Career Developments ; Interaction Modeling for High-Dimensional Mixed Data with Numerical and Categorical Features ; Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL ; MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION ; Mixed-type Defect Pattern Classifications ; Interaction Modelling of High Dimensional Production Data ; DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS ; MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN ; Data-driven Modeling for Production Dynamics ; Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption ; MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - ; Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - ; Interaction Modelings for Industrial Data - for final quality estimation and proess integration ; スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 ; スマートフォンアプリの起動順序に着目したユーザーセグメント分析 ; 従属需要の予測手法の構築と検証 ; スマートフォンアプリの起動順序に着目したユーザーセグメント分析 ; Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>"INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH / Robust Classifications of WBM Defect Patterns / Due dates assignment based on customer changeability classifications in Make-to-order productoins / Pipeline production model and sensitivity analysis of Engineering-to-Order products using system dynamics / PRODUCTION AND JOB ROTATION PLANNING CONSIDERING DISABILITIES AND HEALTH CONDITIONS / Classification of Multivariate Time Series Signals Using Self-Supervised Representation Learning / Multi-factory Scheduling Considering the Trade-offs between Production Efficiency and Risks / Analysis of Resilience Factors and Satisfaction in Life-line Charts for Life Career Developments / Interaction Modeling for High-Dimensional Mixed Data with Numerical and Categorical Features / Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL / MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION / Mixed-type Defect Pattern Classifications / Interaction Modelling of High Dimensional Production Data / DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS / MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN / Data-driven Modeling for Production Dynamics / Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption / MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - / Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - / Interaction Modelings for Industrial Data - for final quality estimation and proess integration / スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 / 従属需要の予測手法の構築と検証 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 / Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>物流最適化 ; 品質管理 ; 大規模言語モデル ; 組合せ最適化 ; 需要予測</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>物流最適化 / 品質管理 / 大規模言語モデル / 組合せ最適化 / 需要予測</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>イリチュ美佳</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000881</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>人工知能に基づく非線形高次元小標本データ解析とその社会的応用 ; ３元型時系列高次元小標本データの解析とその社会的応用 ; 高次計量による高次元小標本型ビックデータ解析とその社会的応用 ; 多次元クラスター尺度構成法によるビックデータ解析とその社会的応用 ; 高次シンボリックデータに対するクラスターワイズ手法の開発とその応用 ; Data Mining and Machine Learning Techniques ; Development of Decision Fusion Architecture for Complex Scenarios ; 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 ; 高次元データの理論と方法論の総合的研究 ; 高次Aggregation Operatorの開発とクラスタリングモデルへの適用</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>人工知能に基づく非線形高次元小標本データ解析とその社会的応用 / ３元型時系列高次元小標本データの解析とその社会的応用 / 高次計量による高次元小標本型ビックデータ解析とその社会的応用 / 多次元クラスター尺度構成法によるビックデータ解析とその社会的応用 / 高次シンボリックデータに対するクラスターワイズ手法の開発とその応用 / Data Mining and Machine Learning Techniques / Development of Decision Fusion Architecture for Complex Scenarios / 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 / 高次元データの理論と方法論の総合的研究 / 高次Aggregation Operatorの開発とクラスタリングモデルへの適用</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Simultaneous visualization method for mixed HDLSS data and its application for education ; Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design ; Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey ; Difference on Evaluation Scores Considering Image Descriptions for Autocoding ; ファジィクラスタリングの信頼度について ; Hierarchical Support Vector Machine based Classifier for Autocoding ; Fuzzy Cluster-Scaled Principal Component Analysis for Mixed Data and Its Application of Educational Effect based on Device Selection ; A Fuzzy Cluster-Scaled Principal Component Analysis for Mixed High-Dimension and Low-Sample Size Data ; Principal component analysis for mixed high-dimension low-sample size data based on fuzzy-cluster scale ; Improvement of Training Data for Autocoding on "The National Survey of Family Income, Consumption and Wealth" and "The Family Income and Expenditure Survey" ; Fuzzy Clustering based Autocoding Methods for Family Income and Expenditure Surveys ; Improvement of Model Construction based on Reliability Scores of Objects for Autocoding ; Fuzzy Clustering based Classifier for Extraction of Individualities from High Dimension Low Sample Size Data ; Individuality-based Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data ; Improvement of Model Construction based on Reliability Scores of Objects for Autocoding ; Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results ; Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling ; Cluster-based Analysis for Discrimination of Individuality （招待講演） ; クラスター尺度に基づくデータ間差異の検出と市場データへの応用 ; ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 ; Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data ; Clustering and Multidimensional Scaling for Individual Difference Extraction ; 多次元尺度法による計算効率を考慮したディープラーニング手法 ; Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means ; 区間組成データに対する重み付き回帰分析</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Simultaneous visualization method for mixed HDLSS data and its application for education / Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design / Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey / Difference on Evaluation Scores Considering Image Descriptions for Autocoding / ファジィクラスタリングの信頼度について / Hierarchical Support Vector Machine based Classifier for Autocoding / Fuzzy Cluster-Scaled Principal Component Analysis for Mixed Data and Its Application of Educational Effect based on Device Selection / A Fuzzy Cluster-Scaled Principal Component Analysis for Mixed High-Dimension and Low-Sample Size Data / Principal component analysis for mixed high-dimension low-sample size data based on fuzzy-cluster scale / Improvement of Training Data for Autocoding on "The National Survey of Family Income, Consumption and Wealth" and "The Family Income and Expenditure Survey" / Fuzzy Clustering based Autocoding Methods for Family Income and Expenditure Surveys / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding / Fuzzy Clustering based Classifier for Extraction of Individualities from High Dimension Low Sample Size Data / Individuality-based Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding / Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results / Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling / Cluster-based Analysis for Discrimination of Individuality （招待講演） / クラスター尺度に基づくデータ間差異の検出と市場データへの応用 / ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 / Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Clustering and Multidimensional Scaling for Individual Difference Extraction / 多次元尺度法による計算効率を考慮したディープラーニング手法 / Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means / 区間組成データに対する重み付き回帰分析</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>学習分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 知識グラフ ; 計算社会科学</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>学習分析 / 行政データ分析 / 社会ネットワーク分析 / 知識グラフ / 計算社会科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>志田洋平</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000004728</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>プライバシー配慮型人流データの高度化と応用可能性の検討 ; 効率的な人的制御を実現する歩行者の空間理解に応じた音響的な能動的介入 ; スマホ GPS データに基づく大都市圏人 流モデルの災害事故評価への応用 ; GPSデータに基づく大都市周辺のマクロ人流モデリングの基盤構築</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>プライバシー配慮型人流データの高度化と応用可能性の検討 / 効率的な人的制御を実現する歩行者の空間理解に応じた音響的な能動的介入 / スマホ GPS データに基づく大都市圏人 流モデルの災害事故評価への応用 / GPSデータに基づく大都市周辺のマクロ人流モデリングの基盤構築</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Enhancing the gravity model for commuters: Time-and-spatial-structure-based improvements in Japan’s metropolitan areas ; Data-Driven Approaches to Detecting Misdeliveries in Truck Logistics using GPS Data ; Direct modelling from GPS data reveals daily-activity-dependency of effective reproduction number in COVID-19 pandemic ; Potential fields and fluctuation-dissipation relations derived from human flow in urban areas modeled by a network of electric circuits ; Universal scaling of human flow remain unchanged during the COVID-19 pandemic ; Universal scaling laws of collective human flow patterns in urban regions</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Enhancing the gravity model for commuters: Time-and-spatial-structure-based improvements in Japan’s metropolitan areas / Data-Driven Approaches to Detecting Misdeliveries in Truck Logistics using GPS Data / Direct modelling from GPS data reveals daily-activity-dependency of effective reproduction number in COVID-19 pandemic / Potential fields and fluctuation-dissipation relations derived from human flow in urban areas modeled by a network of electric circuits / Universal scaling of human flow remain unchanged during the COVID-19 pandemic / Universal scaling laws of collective human flow patterns in urban regions</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>災害分析 ; 物流最適化 ; 人間中心設計 ; 社会ネットワーク分析 ; 行政データ分析</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>災害分析 / 物流最適化 / 人間中心設計 / 社会ネットワーク分析 / 行政データ分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>大久保正勝</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000806</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>マクロ経済モデルにおけるモデル不確実性の定量的・計量経済学的分析 ; モデル不確実性を考慮したマクロ経済モデルの実証的評価と分析手法の開発 ; モデル不確実性と経済厚生の国際比較分析 ; モデル不確実性回避度の計測と異質性の国際比較 ; 選好の異質性と消費保険のミクロデータ分析 ; 個票データによる労働所得変動の推定 ; マクロ金融分析における弱操作変数問題と予測可能性の検定 ; 家計の選好パラメータの推定とその規定要因に関する実証研究</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>マクロ経済モデルにおけるモデル不確実性の定量的・計量経済学的分析 / モデル不確実性を考慮したマクロ経済モデルの実証的評価と分析手法の開発 / モデル不確実性と経済厚生の国際比較分析 / モデル不確実性回避度の計測と異質性の国際比較 / 選好の異質性と消費保険のミクロデータ分析 / 個票データによる労働所得変動の推定 / マクロ金融分析における弱操作変数問題と予測可能性の検定 / 家計の選好パラメータの推定とその規定要因に関する実証研究</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Model uncertainty, economic development, and welfare costs of business cycles ; The moment restrictions for the durable consumption model with recursive utility revisited ; On the Computation of Detection Error Probabilities under Normality Assumptions ; 政府支出と民間消費の代替・補完関係－展望とパネル分析－ ; EARNINGS DYNAMICS AND PROFILE HETEROGENEITY: ESTIMATES FROM JAPANESE PANEL DATA ; The Intertemporal Elasticity of Substitution: An Analysis Based on Japanese Data ; DYNAMIC WELFARE COST OF STAGNATION: AN ALTERNATIVE MEASURE TO THE LUCAS-OBSTFELD MODEL ; Dynamic welfare costs of the 1997 Asian crisis ; On the intertemporal elasticity of substitution under nonhomothetic utility ; Public capital and productivity: a nonstationary panel analysis ; Intertemporal Substitution and Nonhomothetic Preferences ; Intratemporal Substitution between Private and Government Consumption: the Case of Japan ; Long-Run Relationship between Consumption and Income in Japan: Tests of the Deterministic Cointegration Restriction</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Model uncertainty, economic development, and welfare costs of business cycles / The moment restrictions for the durable consumption model with recursive utility revisited / On the Computation of Detection Error Probabilities under Normality Assumptions / 政府支出と民間消費の代替・補完関係－展望とパネル分析－ / EARNINGS DYNAMICS AND PROFILE HETEROGENEITY: ESTIMATES FROM JAPANESE PANEL DATA / The Intertemporal Elasticity of Substitution: An Analysis Based on Japanese Data / DYNAMIC WELFARE COST OF STAGNATION: AN ALTERNATIVE MEASURE TO THE LUCAS-OBSTFELD MODEL / Dynamic welfare costs of the 1997 Asian crisis / On the intertemporal elasticity of substitution under nonhomothetic utility / Public capital and productivity: a nonstationary panel analysis / Intertemporal Substitution and Nonhomothetic Preferences / Intratemporal Substitution between Private and Government Consumption: the Case of Japan / Long-Run Relationship between Consumption and Income in Japan: Tests of the Deterministic Cointegration Restriction</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>行政データ分析 ; 社会ネットワーク分析 ; 学習分析 ; 需要予測 ; 災害分析</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>行政データ分析 / 社会ネットワーク分析 / 学習分析 / 需要予測 / 災害分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Phung-DucTuan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>需要予測 ; 推薦システム ; 強化学習 ; 大規模言語モデル ; 人間中心設計</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>需要予測 / 推薦システム / 強化学習 / 大規模言語モデル / 人間中心設計</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>張勇兵</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000822</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>次世代無線通信網での高速データ通信手法と適応能力をもつネットワーク構築手法の開発 ; 次世代情報通信ネットワークにおける経路制御方式に関する研究 ; 広帯域無線ネットワークにおけるサービス品質保証の研究 ; 次世代情報通信ネットワークにおける経路制御方式に関する研究 ; Web技術に基づくWi-Fiタグを用いた大規模位置検知システムの開発 ; 文理融合型サービス・イノベーション研究教育拠点形成のための研究ネットワーク基盤構築 ; 産学連携による実践型人材育成事業―サービス・イノベーション人材育成― ; 準天頂衛星および無線メッシュLANを利用した被災情報伝送法の開発 ; Optimal routing in power-aware senor networks ; WDM光通信ネットワークにおけるルーティング方式</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>次世代無線通信網での高速データ通信手法と適応能力をもつネットワーク構築手法の開発 / 次世代情報通信ネットワークにおける経路制御方式に関する研究 / 広帯域無線ネットワークにおけるサービス品質保証の研究 / 次世代情報通信ネットワークにおける経路制御方式に関する研究 / Web技術に基づくWi-Fiタグを用いた大規模位置検知システムの開発 / 文理融合型サービス・イノベーション研究教育拠点形成のための研究ネットワーク基盤構築 / 産学連携による実践型人材育成事業―サービス・イノベーション人材育成― / 準天頂衛星および無線メッシュLANを利用した被災情報伝送法の開発 / Optimal routing in power-aware senor networks / WDM光通信ネットワークにおけるルーティング方式</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Joint routing, band, and spectrum assignment in C+L band elastic optical network towards ultra-broadband era ; Shared Rerouting Backup Path Protection (SRBPP) Technology Based on Elastic Optical Networks ; Efficient Optical Line Terminal Placement for Passive Optical Network Deployment ; Improved ILP Models and Heuristics for Solving Routing and Resource Allocation Problems in Optical Networks ; Transaction scheduling with temporal data in real-time database systems ; Dynamic Routing, Spatial Channel, and Spectrum Assignment (RSCSA) in Spatial Channel Networks (SCNs) based on Granularity Switching Threshold ; Optimizing Spatial Channel Networks (SCNs) in Hierarchical Optical Cross-Connect (HOXC) Architectures: Impact of Wavelength Switching Granularity on Performance ; Cost-effective joint establishment of fronthaul and virtual base stations in a stochastic C-RAN ; Dynamic Routing, Spatial Channel and Spectrum Assignment (RSCSA) in Spatial Channel Networks (SCNs) ; Toward Increasing User Capacity through Application of Loopback-enabled Architecture and an Adaptive Caching Strategy in Mobile Cellular Networks ; An accelerated benders decomposition approach for virtual base station formation in stochastic cloud-RANs ; Evaluation of Optical Transport Unit Line-card Integration in Spatially and Spectrally Flexible O2ptical Networks in terms of Device Cost and Network Performance ; JIRA: Joint incentive design and resource allocation for edge-based real-time video streaming systems ; Robust design against network failures of shared backup path protected SDM-EONs ; Blockchain based Public Auditing Outsourcing for Cloud Storage ; Time-Aware Machine Learning-based Traffic QoS Classification ; Routing and Spectrum Assignment in MCF-SDM Networks ; Application‑aware QoS routing in SDNs using machine learning techniques ; Reliability-Aware VNF Placement Using a Probability-Based Approach ; Analysis of wavelength deployment schemes in terms of optical network unit cost and upstream transmission performance in NG-EPONs ; Freshness-Optimal Caching for Information Updating Systems with Limited Cache Storage Capacity ; DCVP: Distributed Collaborative Video Stream Processing in Edge Computing ; Comparison of Switching Policies in Terms of Switching Cost and Network Performance in Static SDM-EONs ; Hierarchical Routing and Resource Assignment in Spatial Channel Networks (SCNs): Oriented Toward the Massive SDM Era ; Evaluation of Device Cost, Power Consumption and Network Performance in Spatially and Spectrally Flexible SDM Optical Networks</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Joint routing, band, and spectrum assignment in C+L band elastic optical network towards ultra-broadband era / Shared Rerouting Backup Path Protection (SRBPP) Technology Based on Elastic Optical Networks / Efficient Optical Line Terminal Placement for Passive Optical Network Deployment / Improved ILP Models and Heuristics for Solving Routing and Resource Allocation Problems in Optical Networks / Transaction scheduling with temporal data in real-time database systems / Dynamic Routing, Spatial Channel, and Spectrum Assignment (RSCSA) in Spatial Channel Networks (SCNs) based on Granularity Switching Threshold / Optimizing Spatial Channel Networks (SCNs) in Hierarchical Optical Cross-Connect (HOXC) Architectures: Impact of Wavelength Switching Granularity on Performance / Cost-effective joint establishment of fronthaul and virtual base stations in a stochastic C-RAN / Dynamic Routing, Spatial Channel and Spectrum Assignment (RSCSA) in Spatial Channel Networks (SCNs) / Toward Increasing User Capacity through Application of Loopback-enabled Architecture and an Adaptive Caching Strategy in Mobile Cellular Networks / An accelerated benders decomposition approach for virtual base station formation in stochastic cloud-RANs / Evaluation of Optical Transport Unit Line-card Integration in Spatially and Spectrally Flexible O2ptical Networks in terms of Device Cost and Network Performance / JIRA: Joint incentive design and resource allocation for edge-based real-time video streaming systems / Robust design against network failures of shared backup path protected SDM-EONs / Blockchain based Public Auditing Outsourcing for Cloud Storage / Time-Aware Machine Learning-based Traffic QoS Classification / Routing and Spectrum Assignment in MCF-SDM Networks / Application‑aware QoS routing in SDNs using machine learning techniques / Reliability-Aware VNF Placement Using a Probability-Based Approach / Analysis of wavelength deployment schemes in terms of optical network unit cost and upstream transmission performance in NG-EPONs / Freshness-Optimal Caching for Information Updating Systems with Limited Cache Storage Capacity / DCVP: Distributed Collaborative Video Stream Processing in Edge Computing / Comparison of Switching Policies in Terms of Switching Cost and Network Performance in Static SDM-EONs / Hierarchical Routing and Resource Assignment in Spatial Channel Networks (SCNs): Oriented Toward the Massive SDM Era / Evaluation of Device Cost, Power Consumption and Network Performance in Spatially and Spectrally Flexible SDM Optical Networks</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; ネットワーク科学 ; 災害分析 ; 物流最適化 ; 農業情報学</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 / ネットワーク科学 / 災害分析 / 物流最適化 / 農業情報学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>岡田幸彦</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000865</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>KPI工学教育研究の推進 ; 包摂的コミュニティプラットフォームの構築 ; 健康にやさしいまちづくりのための環境整備に係る実証事業 ; 統合型ヘルスケアシステムの構築 ; 文書生成AIサービス工学に関する研究 ; 文書生成AIの企業内利活用における最適化の研究 ; 統合型ヘルスケアシステムの構築 ; 健康にやさしいまちづくりのための環境整備に係る実証事業 ; 包摂的コミュニティプラットフォームの構築 ; 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KPI工学教育研究の推進 / 包摂的コミュニティプラットフォームの構築 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 統合型ヘルスケアシステムの構築 / 文書生成AIサービス工学に関する研究 / 文書生成AIの企業内利活用における最適化の研究 / 統合型ヘルスケアシステムの構築 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 包摂的コミュニティプラットフォームの構築 / 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment ; Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach ; Estimation of conditional average treatment effects on distributed confidential data ; Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support ; Data collaboration for causal inference from limited medical testing and medication data ; Generating Synthetic Journal-Entry Data Using Variational Autoencoder ; Anomaly Detection in Double-entry Bookkeeping Data by Federated Learning System with Non-model Sharing Approach ; Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data ; An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises ; Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data ; 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 ; pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis ; 会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 ; Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data ; 分散機密データを想定した 処置効果の推定手法の開発 ; 英文学術雑誌における近年の簿記研究 ; Collaborative causal inference on distributed data ; Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach ; Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation ; Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data ; Knowledge sharing among coaches: expert power and social cognitive theory perspectives ; Positive effect of proactive personality on customer orientation in service context ; Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data ; Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis ; Does Double-entry Bookkeeping Information Generated Using node2vec Contribute to Forecasting Future Performance?</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment / Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach / Estimation of conditional average treatment effects on distributed confidential data / Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support / Data collaboration for causal inference from limited medical testing and medication data / Generating Synthetic Journal-Entry Data Using Variational Autoencoder / Anomaly Detection in Double-entry Bookkeeping Data by Federated Learning System with Non-model Sharing Approach / Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data / An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises / Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 / pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis / 会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 / Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data / 分散機密データを想定した 処置効果の推定手法の開発 / 英文学術雑誌における近年の簿記研究 / Collaborative causal inference on distributed data / Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach / Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation / Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data / Knowledge sharing among coaches: expert power and social cognitive theory perspectives / Positive effect of proactive personality on customer orientation in service context / Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data / Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis / Does Double-entry Bookkeeping Information Generated Using node2vec Contribute to Forecasting Future Performance?</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; 学習分析 ; 行政データ分析 ; 災害分析 ; 需要予測</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 / 学習分析 / 行政データ分析 / 災害分析 / 需要予測</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>上市秀雄</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000821</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として― ; 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討 ; リアルタイム場面におけるサービス・インタラクション理論の構築と実証 ; 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 ; 慢性ストレスがヒトの生理心理状態に与える影響とその対処法 ; 犯罪不安に関する認知・感情プロセスのモデル化とその応用 ; 逸脱行動が生起するプロセスと矯正方法に関する研究 ; 進路意思決定における認知・感情過程のモデル化 ; 教師教育教材を事例としたマルチメディア教材設計・評価手法の開発</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として― / 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討 / リアルタイム場面におけるサービス・インタラクション理論の構築と実証 / 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 / 慢性ストレスがヒトの生理心理状態に与える影響とその対処法 / 犯罪不安に関する認知・感情プロセスのモデル化とその応用 / 逸脱行動が生起するプロセスと矯正方法に関する研究 / 進路意思決定における認知・感情過程のモデル化 / 教師教育教材を事例としたマルチメディア教材設計・評価手法の開発</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan ; 後悔を力に変える ; Exploring the Relationship Between Different Consumer Behaviors and Subjective Well-Being in Japan: A Focus on Prosocial, Sustainable, Experiential, and Conspicuous Consumption ; Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan ; The Effect of General Trust on Willingness to Communicate in English among Japanese individuals across various situations. ; Factors influencing behavioral intentions in livestream shopping: A cross-cultural study ; Does macro-level general trust influence second language communication? :targeting prefectural capitals. ; The influence of online multiplayer games on social capital and interdependent well-being in Japan ; オンライン入試の実施と問題点 ; 一般市民の更生支援に対する認知および参加意向の向上にむけた検討 ; Understanding confidence in the human papillomavirus vaccine in Japan: a web-based survey of mothers, female adolescents, and healthcare professionals ; Simulation of Outpatient Flow at the University of Tsukuba Hospital ; Frequency of grooming the eyebrows and cosmetic consciousness in men. ; The relationship between quantity of information contact and public evaluation of volunteer probation officers to promote understanding for social reintegration support. ; Factors influencing differences between useful and useless regret. ; The relationships between a metacognition scale and adaptive behavior in the regret situations: A comparison between junior high-school and university students. ; Understanding confidence in human papillomavirus vaccine in Japan: A web-based questionnaire survey of mothers, female adolescents, and health care professionals. ; 裁判員参加意向を規定する要因および意思決定プロセスの差異：制度施行前後の比較 ; 市民の生態系サービスへの認知が保全行動意図に及ぼす影響：全国アンケートを用いた社会心理学的分析 ; どのようにリスクを伝えればよいか：よりよいリスクコミュニケーションのために必要なこと ; 意思決定から見たギャンブル行動 ; Change of decision-making processes in repeated risk-taking behavior in a complex dynamic situation ; The neural networks model of decision-making including feedback processes ; Research on the gaps between students' expectation and satisfaction for universities ; Analogical decision making in career choice</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan / 後悔を力に変える / Exploring the Relationship Between Different Consumer Behaviors and Subjective Well-Being in Japan: A Focus on Prosocial, Sustainable, Experiential, and Conspicuous Consumption / Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan / The Effect of General Trust on Willingness to Communicate in English among Japanese individuals across various situations. / Factors influencing behavioral intentions in livestream shopping: A cross-cultural study / Does macro-level general trust influence second language communication? :targeting prefectural capitals. / The influence of online multiplayer games on social capital and interdependent well-being in Japan / オンライン入試の実施と問題点 / 一般市民の更生支援に対する認知および参加意向の向上にむけた検討 / Understanding confidence in the human papillomavirus vaccine in Japan: a web-based survey of mothers, female adolescents, and healthcare professionals / Simulation of Outpatient Flow at the University of Tsukuba Hospital / Frequency of grooming the eyebrows and cosmetic consciousness in men. / The relationship between quantity of information contact and public evaluation of volunteer probation officers to promote understanding for social reintegration support. / Factors influencing differences between useful and useless regret. / The relationships between a metacognition scale and adaptive behavior in the regret situations: A comparison between junior high-school and university students. / Understanding confidence in human papillomavirus vaccine in Japan: A web-based questionnaire survey of mothers, female adolescents, and health care professionals. / 裁判員参加意向を規定する要因および意思決定プロセスの差異：制度施行前後の比較 / 市民の生態系サービスへの認知が保全行動意図に及ぼす影響：全国アンケートを用いた社会心理学的分析 / どのようにリスクを伝えればよいか：よりよいリスクコミュニケーションのために必要なこと / 意思決定から見たギャンブル行動 / Change of decision-making processes in repeated risk-taking behavior in a complex dynamic situation / The neural networks model of decision-making including feedback processes / Research on the gaps between students' expectation and satisfaction for universities / Analogical decision making in career choice</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; マーケティング分析 ; 人間中心設計 ; 学習分析 ; 行動科学</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 / マーケティング分析 / 人間中心設計 / 学習分析 / 行動科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>黒瀬雄大</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000004077</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>非線形・非正規状態空間モデルと多変量・高次元経済金融時系列分析 ; 統計的学習を用いた非線形計量経済モデルの新展開と金融・経済リスク評価への応用 ; 多変量／高次元の潜在変数をもつ時系列モデルの効率的ベイズ推測 ; 高次元データモデリングの新展開と統計的リスク分析 ; 経済・金融多変量データのベイズモデリングと政策・行動の確率的評価</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>非線形・非正規状態空間モデルと多変量・高次元経済金融時系列分析 / 統計的学習を用いた非線形計量経済モデルの新展開と金融・経済リスク評価への応用 / 多変量／高次元の潜在変数をもつ時系列モデルの効率的ベイズ推測 / 高次元データモデリングの新展開と統計的リスク分析 / 経済・金融多変量データのベイズモデリングと政策・行動の確率的評価</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Simulation of truncated and unimodal gamma distributions ; Bayesian GARCH modeling for return and range ; 時間変動する相関と確率的ボラティリティモデル ; Multiple-block dynamic equicorrelations with realized measures, leverage and endogeneity ; Dynamic equicorrelation stochastic volatility ; Bayesian Analysis of Time-Varying Quantiles Using a Smoothing Spline</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Simulation of truncated and unimodal gamma distributions / Bayesian GARCH modeling for return and range / 時間変動する相関と確率的ボラティリティモデル / Multiple-block dynamic equicorrelations with realized measures, leverage and endogeneity / Dynamic equicorrelation stochastic volatility / Bayesian Analysis of Time-Varying Quantiles Using a Smoothing Spline</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>学習分析 ; 行政データ分析 ; 災害分析 ; センサデータ解析 ; 数理最適化</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>学習分析 / 行政データ分析 / 災害分析 / センサデータ解析 / 数理最適化</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>佐野幸恵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000003544</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究 ; アカウンティング・インフォマティクス（会計情報科学）の基盤研究 ; 学際的エビデンスに基づく超高齢社会のモビリティ支援とアクティブ・エイジングの推進 ; 多層ネットワークを用いたワクチン忌避に対する実証的研究 ; 想起効果を内在する集合的記憶モデルの開発 ; International School and Conference on Network Science (NetSciX 2020) ; 勤労世代における風疹ワクチン接種の決定要因に関する研究 ; 乳幼児の活動量を測定するウェアラブル機器の開発 ; 乳幼児の活動量を測定するウェアラブルデバイスの開発 ; サイバー社会ネットワークにおける噂の伝播の検出と制御</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究 / アカウンティング・インフォマティクス（会計情報科学）の基盤研究 / 学際的エビデンスに基づく超高齢社会のモビリティ支援とアクティブ・エイジングの推進 / 多層ネットワークを用いたワクチン忌避に対する実証的研究 / 想起効果を内在する集合的記憶モデルの開発 / International School and Conference on Network Science (NetSciX 2020) / 勤労世代における風疹ワクチン接種の決定要因に関する研究 / 乳幼児の活動量を測定するウェアラブル機器の開発 / 乳幼児の活動量を測定するウェアラブルデバイスの開発 / サイバー社会ネットワークにおける噂の伝播の検出と制御</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis ; コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 ; 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 ; Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan ; Quantifying Collective Emotions: Japan’s Societal Trends Through Enhanced Sentiment Index Using POMS2 and SNS ; Quantifying collective attention and fan engagement: a case study of the Japanese professional baseball league ; News coverage of older drivers' fatal car crashes: is it over-represented? ; Burstiness of human physical activities and their characterisation ; 12-year observation of tweets about rubella in Japan: A retrospective infodemiology study ; A two-phase model of collective memory decay with a dynamical switching point ; SNSデータを用いた情報拡散シミュレーション ; SNSにおける情報伝播ネットワークの構造 ; Music Roles Affect the Selection of Consumption Means: A Questionnaire Survey of People’s Expectations for Music and Exploratory Factor Analysis ; Dataset of identified scholars mentioned in acknowledgement statements ; Classification of endogenous and exogenous bursts in collective emotions based on Weibo comments during COVID-19 ; 日本におけるオンライン・ハラスメントの現状と対策：Twitterでの女性記者のツイート「炎上」を例に ; 日本における自治体報道発表のCOVID-19発生状況を用いた感染者遷移状況の記録と可視化 ; Simulation of information spreading on Twitter concerning radiation after the Fukushima nuclear power plant accident ; 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― ; サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して ; Fake news propagates differently from real news even at early stages of spreading ; 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 ; Identifying long-term periodic cycles and memories of collective emotion in online social media ; Correlations and fluctuations in the word sets of collective emotions ; Configuration model for correlation matrices preserving the node strength</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis / コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 / Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan / Quantifying Collective Emotions: Japan’s Societal Trends Through Enhanced Sentiment Index Using POMS2 and SNS / Quantifying collective attention and fan engagement: a case study of the Japanese professional baseball league / News coverage of older drivers' fatal car crashes: is it over-represented? / Burstiness of human physical activities and their characterisation / 12-year observation of tweets about rubella in Japan: A retrospective infodemiology study / A two-phase model of collective memory decay with a dynamical switching point / SNSデータを用いた情報拡散シミュレーション / SNSにおける情報伝播ネットワークの構造 / Music Roles Affect the Selection of Consumption Means: A Questionnaire Survey of People’s Expectations for Music and Exploratory Factor Analysis / Dataset of identified scholars mentioned in acknowledgement statements / Classification of endogenous and exogenous bursts in collective emotions based on Weibo comments during COVID-19 / 日本におけるオンライン・ハラスメントの現状と対策：Twitterでの女性記者のツイート「炎上」を例に / 日本における自治体報道発表のCOVID-19発生状況を用いた感染者遷移状況の記録と可視化 / Simulation of information spreading on Twitter concerning radiation after the Fukushima nuclear power plant accident / 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― / サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して / Fake news propagates differently from real news even at early stages of spreading / 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 / Identifying long-term periodic cycles and memories of collective emotion in online social media / Correlations and fluctuations in the word sets of collective emotions / Configuration model for correlation matrices preserving the node strength</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; 災害分析 ; 学習分析 ; 知識グラフ ; 計算社会科学</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 / 災害分析 / 学習分析 / 知識グラフ / 計算社会科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>秋山英三</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000823</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析 ; 新規投資家の継続的な参入が価格形成・価格変動に与える影響 ; ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響 ; 信用スコア社会に対応可能な評判管理システムの設計 ; 験財消費のための情報収集行動とその支援情報提供システム ; 市場参加者の価格予測の異質性と市場の振る舞いの関係について ; 情報の非対称性と多様な期待形成がもたらす金融市場への影響とその安定化政策について ; 国家の規模とガバナンスの学際的分析 ; 情報コストゼロ社会における過剰懲罰とリスク軽減のための社会制度設計 ; 新しい肺移植制度の構築と評価：ドナー交換移植の可能性</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析 / 新規投資家の継続的な参入が価格形成・価格変動に与える影響 / ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響 / 信用スコア社会に対応可能な評判管理システムの設計 / 験財消費のための情報収集行動とその支援情報提供システム / 市場参加者の価格予測の異質性と市場の振る舞いの関係について / 情報の非対称性と多様な期待形成がもたらす金融市場への影響とその安定化政策について / 国家の規模とガバナンスの学際的分析 / 情報コストゼロ社会における過剰懲罰とリスク軽減のための社会制度設計 / 新しい肺移植制度の構築と評価：ドナー交換移植の可能性</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>検索連動型広告における循環的な入札額変動の発生機構の解明 ; ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 ; Bubbles in Asset Markets and the Heterogeneity of Beliefs. ; 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 ; 進化ゲーム理論の進化 — マルチエージェントシミュレーション，実験室実験と，LLM の行動経済学— ; 発話量と発話内容に基づく集団間のコミュニケーション円滑化システムの提案 ; ソーシャルメディア上のアジェンダ設定がエコーチェンバーの発生に与える影響について ; Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. ; Emergence of echo chambers in social media communication involving multiple topics ; 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 ; 進化ゲーム理論の進化：マルチエージェントシミュレーション, 実験室実験と，LLMの行動経済学 ; 重みが動的なネットワークにおいてネットワーク構造が協力の進化に与える影響 ; 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ ; Individuals reciprocate negative actions revealing negative upstream reciprocity ; SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. ; Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement ; Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim ; パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 ; 群淘汰状況下における罰則・報酬の進化 ; Self-organized Speculation Game for the spontaneous emergence of financial stylized facts ; 情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ ; 時間制約を導入したゴミ箱モデル ; Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment ; 協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 ; A quantitative easing experiment</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>検索連動型広告における循環的な入札額変動の発生機構の解明 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Bubbles in Asset Markets and the Heterogeneity of Beliefs. / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 / 進化ゲーム理論の進化 — マルチエージェントシミュレーション，実験室実験と，LLM の行動経済学— / 発話量と発話内容に基づく集団間のコミュニケーション円滑化システムの提案 / ソーシャルメディア上のアジェンダ設定がエコーチェンバーの発生に与える影響について / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. / Emergence of echo chambers in social media communication involving multiple topics / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 / 進化ゲーム理論の進化：マルチエージェントシミュレーション, 実験室実験と，LLMの行動経済学 / 重みが動的なネットワークにおいてネットワーク構造が協力の進化に与える影響 / 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ / Individuals reciprocate negative actions revealing negative upstream reciprocity / SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. / Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement / Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim / パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 / 群淘汰状況下における罰則・報酬の進化 / Self-organized Speculation Game for the spontaneous emergence of financial stylized facts / 情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ / 時間制約を導入したゴミ箱モデル / Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment / 協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 / A quantitative easing experiment</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; 学習分析 ; マーケティング分析 ; 災害分析 ; 計算社会科学</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 / 学習分析 / マーケティング分析 / 災害分析 / 計算社会科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TranLamAnhDuong</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>需要予測 ; 社会ネットワーク分析 ; 人間中心設計 ; 災害分析 ; テキストマイニング</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>需要予測 / 社会ネットワーク分析 / 人間中心設計 / 災害分析 / テキストマイニング</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LiuTianxiang</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>医用画像 ; 時系列解析 ; 需要予測 ; 人間中心設計 ; 物流最適化</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>医用画像 / 時系列解析 / 需要予測 / 人間中心設計 / 物流最適化</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>奥島真一郎</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000872</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>十分なエネルギーをすべての人へ：家庭部門の公正な移行を実現するために ; 包摂的な低炭素化・エネルギー転換に関する研究 ; 低炭素化・エネルギー転換の包摂性評価：基本的エネルギーニーズの観点から ; 環境・エネルギーに関する多次元貧困指標の開発と政策分析 ; 地球温暖化とエネルギー貧困 ; 東日本大震災後の地球温暖化政策を考える ; モラルモチベーションと環境政策 ; 人々の環境モラルに基づく自発的行動と望ましい環境政策 ; 「環境政策における経済的手法」再検討 ; 応用一般均衡モデルによる環境政策の社会経済学的分析</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>十分なエネルギーをすべての人へ：家庭部門の公正な移行を実現するために / 包摂的な低炭素化・エネルギー転換に関する研究 / 低炭素化・エネルギー転換の包摂性評価：基本的エネルギーニーズの観点から / 環境・エネルギーに関する多次元貧困指標の開発と政策分析 / 地球温暖化とエネルギー貧困 / 東日本大震災後の地球温暖化政策を考える / モラルモチベーションと環境政策 / 人々の環境モラルに基づく自発的行動と望ましい環境政策 / 「環境政策における経済的手法」再検討 / 応用一般均衡モデルによる環境政策の社会経済学的分析</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>エネルギー貧困からエネルギー充足へ ; Aging alone: a twin threat to decarbonisation and energy vulnerability in Japan and UK ; Reevaluating fair carbon emissions for households in Japan: basic energy needs and subsistence CO2 emissions ; Double energy vulnerability in Japan ; Double energy vulnerability in Japan: a first assessment ; Measuring energy sufficiency: A state of being neither in energy poverty nor energy extravagance ; What can be done with one tonne of CO2 emissions?: Reconsidering fair carbon emissions for households in relation to the use of domestic energy services ; Measuring energy sufficiency: A state of being in neither energy poverty nor energy extravagance ; How to evaluate energy sufficiency: A direct measurement approach ; Energy Poverty in Japan: Current Trends and Future Challenges ; 公平なエネルギー転換：気候正義とエネルギー正義の観点から ; Regional energy poverty reevaluated: A direct measurement approach applied to France and Japan ; Energy poor need more energy, but do they need more carbon?: Evaluation of people’s basic carbon needs ; Prevalence of energy poverty in Japan: A comprehensive analysis of energy poverty vulnerabilities ; Prevalence of energy poverty in Japan: A comprehensive analysis of energy poverty vulnerabilities ; Energy poor need more energy, but do they need more carbon? ; Engendering an inclusive low-carbon energy transition in Japan: Considering the perspectives and awareness of the energy poor ; Understanding regional energy poverty in Japan: a direct measurement approach ; Engendering an inclusive low-carbon energy transition in Japan: considering the perspectives and awareness of the energy poor ; Measuring Energy Poverty via Energy Service Usage: The Japanese case ; 「エネルギー貧困」・「エネルギー脆弱性」・「エネルギー正義」：日本における現状と課題 ; 「エネルギー正義」について ; Gauging Energy Poverty: A Multidimensional Approach ; Measuring Energy Poverty in Japan, 2004-2013 ; How Can We Gauge Energy Poverty? A Multidimensional Approach</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>エネルギー貧困からエネルギー充足へ / Aging alone: a twin threat to decarbonisation and energy vulnerability in Japan and UK / Reevaluating fair carbon emissions for households in Japan: basic energy needs and subsistence CO2 emissions / Double energy vulnerability in Japan / Double energy vulnerability in Japan: a first assessment / Measuring energy sufficiency: A state of being neither in energy poverty nor energy extravagance / What can be done with one tonne of CO2 emissions?: Reconsidering fair carbon emissions for households in relation to the use of domestic energy services / Measuring energy sufficiency: A state of being in neither energy poverty nor energy extravagance / How to evaluate energy sufficiency: A direct measurement approach / Energy Poverty in Japan: Current Trends and Future Challenges / 公平なエネルギー転換：気候正義とエネルギー正義の観点から / Regional energy poverty reevaluated: A direct measurement approach applied to France and Japan / Energy poor need more energy, but do they need more carbon?: Evaluation of people’s basic carbon needs / Prevalence of energy poverty in Japan: A comprehensive analysis of energy poverty vulnerabilities / Prevalence of energy poverty in Japan: A comprehensive analysis of energy poverty vulnerabilities / Energy poor need more energy, but do they need more carbon? / Engendering an inclusive low-carbon energy transition in Japan: Considering the perspectives and awareness of the energy poor / Understanding regional energy poverty in Japan: a direct measurement approach / Engendering an inclusive low-carbon energy transition in Japan: considering the perspectives and awareness of the energy poor / Measuring Energy Poverty via Energy Service Usage: The Japanese case / 「エネルギー貧困」・「エネルギー脆弱性」・「エネルギー正義」：日本における現状と課題 / 「エネルギー正義」について / Gauging Energy Poverty: A Multidimensional Approach / Measuring Energy Poverty in Japan, 2004-2013 / How Can We Gauge Energy Poverty? A Multidimensional Approach</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>災害分析 ; 社会ネットワーク分析 ; エネルギーシステム ; 需要予測 ; 環境工学</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>災害分析 / 社会ネットワーク分析 / エネルギーシステム / 需要予測 / 環境工学</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>八森正泰</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000871</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>トポロジー的組合せ論と組合せ論におけるトポロジー的手法 ; 組合せ的構造に関する研究 ; Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求 ; デジタル指紋符号、多重接続通信路、及び組合せ探索問題 ; 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 ; 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 ; 部分構造への等質性を基軸とする単体的複体の構造解析 ; ネットワーク上の時間軸をもった最適化問題とその応用 ; 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化 ; 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>トポロジー的組合せ論と組合せ論におけるトポロジー的手法 / 組合せ的構造に関する研究 / Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求 / デジタル指紋符号、多重接続通信路、及び組合せ探索問題 / 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / 部分構造への等質性を基軸とする単体的複体の構造解析 / ネットワーク上の時間軸をもった最適化問題とその応用 / 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化 / 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>The average expected value of a rooted graph, Monte Carlo calculation, and a power index for the voting game ; Coloring zonotopal quadrangulations of the projective space ; Several minimality concepts related to Frankl's conjecture ; Some computational studies of the root distribution of Ehrhart polynomials ; The root distributions of Ehrhart polynomials of free sums of reflexive polytopes ; Sequential Partitions of Nonpure Simplicial Complexes ; Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting ; Pure-strategy Nash equilibria on competitive diffusion games ; Hereditary properties and obstructions of simplicial complexes ; A comment on pure-strategy Nash equilibria in competitive diffusion games ; Obstructions to shellability, partitionability, and sequential Cohen-Macaulayness ; Decompositions of two-dimensional simplicial complexes ; A note on shellability and acyclic orientations ; On the topology of the free complexes of convex geometries ; A factorization theorem of characteristic polynomials of convex geometries ; The max-flow min-cut property of two-dimensional affine convex geometries ; h-Assignments of simplicial complexes and reverse search ; Tangle sum and constructible spheres ; Deciding constructibility of 3-balls with at most two interior vertices ; Non-constructible complexes and the bridge index ; Decompositions of balls and spheres with knots consisting of few edges ; Nonconstructible balls and a way of testing constructibility ; Constructible complexes and recursive division of posets ; セル複体に付随するグラフの向き付けとその最適解 ; 核付アフィン点配置の根付サーキット系の性質について</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>The average expected value of a rooted graph, Monte Carlo calculation, and a power index for the voting game / Coloring zonotopal quadrangulations of the projective space / Several minimality concepts related to Frankl's conjecture / Some computational studies of the root distribution of Ehrhart polynomials / The root distributions of Ehrhart polynomials of free sums of reflexive polytopes / Sequential Partitions of Nonpure Simplicial Complexes / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting / Pure-strategy Nash equilibria on competitive diffusion games / Hereditary properties and obstructions of simplicial complexes / A comment on pure-strategy Nash equilibria in competitive diffusion games / Obstructions to shellability, partitionability, and sequential Cohen-Macaulayness / Decompositions of two-dimensional simplicial complexes / A note on shellability and acyclic orientations / On the topology of the free complexes of convex geometries / A factorization theorem of characteristic polynomials of convex geometries / The max-flow min-cut property of two-dimensional affine convex geometries / h-Assignments of simplicial complexes and reverse search / Tangle sum and constructible spheres / Deciding constructibility of 3-balls with at most two interior vertices / Non-constructible complexes and the bridge index / Decompositions of balls and spheres with knots consisting of few edges / Nonconstructible balls and a way of testing constructibility / Constructible complexes and recursive division of posets / セル複体に付随するグラフの向き付けとその最適解 / 核付アフィン点配置の根付サーキット系の性質について</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>数理最適化 ; 社会ネットワーク分析 ; 組合せ最適化 ; 学習分析 ; 自然言語処理</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>数理最適化 / 社会ネットワーク分析 / 組合せ最適化 / 学習分析 / 自然言語処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>原田信行</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000836</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>中小企業の雇用・技術と日本経済の再生 ; 経済環境の激変と中小企業の役割 ; 縮小経済のもとでの中小企業と企業家活動 ; 中小企業の資金調達環境と政策のあり方</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>中小企業の雇用・技術と日本経済の再生 / 経済環境の激変と中小企業の役割 / 縮小経済のもとでの中小企業と企業家活動 / 中小企業の資金調達環境と政策のあり方</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Number of positive lymph nodes and lymphatic invasion are significant prognostic factors after pancreaticoduodenectomy for distal cholangiocarcinoma. ; 開業と廃業 ; 中小企業の知的財産 ; Bankruptcy dynamics in Japan ; 開業のダイナミクス－開業研究の展望と法人設立登記にもとづく実証分析－ ; Which firms exit and why? An analysis of small firm exits in Japan ; Video game demand in Japan: a household data analysis ; 新企業の人材確保--事業所・企業統計調査と新企業調査の個票分析 ; SME policy, financial structure and firm growth: Evidence from japan ; Does the creative business promotion law enhance SMEs' capital investments? Evidence from a panel dataset of unlisted SMEs in Japan ; Potential entrepreneurship in Japan ; Consumption-leisure preference structure: A new explanation of the Evans-Jovanovic results for entrepreneurial choice ; Consumption-Leisure Preference Structure: A New Explanation of the Evans-Jovanovic Results for Entrepreneurial Choice(Erratum, 24, 423-427, 2005) ; Does the Creative Business Promotion Law Enhance SMEs' Capital Investment? Evidence from a Panel Dataset of Unlisted SMEs in Japan ; The IT revolution and productivity growth in Japan ; Small Business Owner-Managers as Latent Informal Investors in Japan: Evidence from a Country with a Bank-based Financial System ; 企業家の労働時間－実証分析－ ; 景況感とアンケート調査－変化方向と水準は異曲同工か？－ ; Productivity and Entrepreneurial Characteristics in New Japanese Firms ; Who Succeeds as an Entrepreneur? An Analysis of the Post-Entry Performance of New Firms in Japan ; 少子・高齢化と日本の消費フロンティア ; SNA統計を用いた「トービンのｑ」の計測結果の違いについて ; 潜在的開業者の実証分析 ; 起業の意思決定における所得・余暇の代替と流動性制約 ; SNA統計を用いた民間法人企業ベースの「トービンのｑ」と投資関数</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Number of positive lymph nodes and lymphatic invasion are significant prognostic factors after pancreaticoduodenectomy for distal cholangiocarcinoma. / 開業と廃業 / 中小企業の知的財産 / Bankruptcy dynamics in Japan / 開業のダイナミクス－開業研究の展望と法人設立登記にもとづく実証分析－ / Which firms exit and why? An analysis of small firm exits in Japan / Video game demand in Japan: a household data analysis / 新企業の人材確保--事業所・企業統計調査と新企業調査の個票分析 / SME policy, financial structure and firm growth: Evidence from japan / Does the creative business promotion law enhance SMEs' capital investments? Evidence from a panel dataset of unlisted SMEs in Japan / Potential entrepreneurship in Japan / Consumption-leisure preference structure: A new explanation of the Evans-Jovanovic results for entrepreneurial choice / Consumption-Leisure Preference Structure: A New Explanation of the Evans-Jovanovic Results for Entrepreneurial Choice(Erratum, 24, 423-427, 2005) / Does the Creative Business Promotion Law Enhance SMEs' Capital Investment? Evidence from a Panel Dataset of Unlisted SMEs in Japan / The IT revolution and productivity growth in Japan / Small Business Owner-Managers as Latent Informal Investors in Japan: Evidence from a Country with a Bank-based Financial System / 企業家の労働時間－実証分析－ / 景況感とアンケート調査－変化方向と水準は異曲同工か？－ / Productivity and Entrepreneurial Characteristics in New Japanese Firms / Who Succeeds as an Entrepreneur? An Analysis of the Post-Entry Performance of New Firms in Japan / 少子・高齢化と日本の消費フロンティア / SNA統計を用いた「トービンのｑ」の計測結果の違いについて / 潜在的開業者の実証分析 / 起業の意思決定における所得・余暇の代替と流動性制約 / SNA統計を用いた民間法人企業ベースの「トービンのｑ」と投資関数</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; 行政データ分析 ; マーケティング分析 ; 需要予測 ; 経営工学</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 / 行政データ分析 / マーケティング分析 / 需要予測 / 経営工学</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>藤井さやか</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000809</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>まちづくりを含む不動産開発に関する指導 ; 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究 ; 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 ; 超高層住宅の二重の老いの潜在的課題に関する研究 ; 社会的孤独の解消モデル事例のプロセス分析及び検証手法の検討 ; つくば市みどりの分譲地のまちづくり提案について ; 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 ; 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 ; スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築 ; 超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>まちづくりを含む不動産開発に関する指導 / 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 超高層住宅の二重の老いの潜在的課題に関する研究 / 社会的孤独の解消モデル事例のプロセス分析及び検証手法の検討 / つくば市みどりの分譲地のまちづくり提案について / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築 / 超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 ; 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として ; わがまちのSDGs ; 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ ; 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 ; 京都市東松ノ木市営住宅 ; 国勢調査分析からみる外国人集住団地の実態 ; 増加する外国人の受け皿としての住宅団地 ; 住宅団地の外国人集住：特集の趣旨 ; 住宅地における地区計画や認可協定の今後 ; 区分所有マンションを含む市街地再開発事業の有効空地を考える ; 社会的包摂とデザイン─「つながる場」15事例の実践から ; 外国人住民との共存・共生: 海外の事例からの示唆 ; 首都圏郊外におけるリノベーションまちづくりの成果と課題に関する研究 ; 住宅建替えと一体的に再整備された街区公園の維持管理活動を通じたコミュニティ形成に関する研究 ; 計画的戸建住宅地における駐車場シェアの導入意向と活用可能性に関する研究 ; 多様な主体が関わる出産祝いプロジェクトの成立経緯と参加主体にもたらす変化に関する研究 ; 職員の活躍を願う市長の思いと取り組み ; 今後の地域づくりへの期待 ; Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea ; 転換期にある筑波研究学園都市の地区計画が空間資源継承に果たす役割と課題 ; 1980年以降、40年の「つくば」の変化と現状 ; Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea, Urban Planning ; Living Lab Participants’ Knowledge Change about Inclusive Smart Cities: An Urban Living Lab in Seongdaegol, Seoul, South Korea ; 地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として / わがまちのSDGs / 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ / 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 / 京都市東松ノ木市営住宅 / 国勢調査分析からみる外国人集住団地の実態 / 増加する外国人の受け皿としての住宅団地 / 住宅団地の外国人集住：特集の趣旨 / 住宅地における地区計画や認可協定の今後 / 区分所有マンションを含む市街地再開発事業の有効空地を考える / 社会的包摂とデザイン─「つながる場」15事例の実践から / 外国人住民との共存・共生: 海外の事例からの示唆 / 首都圏郊外におけるリノベーションまちづくりの成果と課題に関する研究 / 住宅建替えと一体的に再整備された街区公園の維持管理活動を通じたコミュニティ形成に関する研究 / 計画的戸建住宅地における駐車場シェアの導入意向と活用可能性に関する研究 / 多様な主体が関わる出産祝いプロジェクトの成立経緯と参加主体にもたらす変化に関する研究 / 職員の活躍を願う市長の思いと取り組み / 今後の地域づくりへの期待 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea / 転換期にある筑波研究学園都市の地区計画が空間資源継承に果たす役割と課題 / 1980年以降、40年の「つくば」の変化と現状 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea, Urban Planning / Living Lab Participants’ Knowledge Change about Inclusive Smart Cities: An Urban Living Lab in Seongdaegol, Seoul, South Korea / 地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>都市計画 ; 社会ネットワーク分析 ; 人間中心設計 ; 環境工学 ; 行政データ分析</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>都市計画 / 社会ネットワーク分析 / 人間中心設計 / 環境工学 / 行政データ分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>繁野麻衣子</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000846</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 ; ネットワーク上の時間軸をもった最適化問題とその応用 ; スタッフスケジューリングに関する研究 ; 組合せ最適化，ネットワーク最適化のアルゴリズム開発 ; ネットワーク構造解析アルゴリズムの開発とネットワークアルゴリズムの総合的展開 ; ネットワーク理論の基盤整備と伸張 ; データの精度を考慮した組合せ最適化問題に対する問題構造とアルゴリズムの研究 ; 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 / ネットワーク上の時間軸をもった最適化問題とその応用 / スタッフスケジューリングに関する研究 / 組合せ最適化，ネットワーク最適化のアルゴリズム開発 / ネットワーク構造解析アルゴリズムの開発とネットワークアルゴリズムの総合的展開 / ネットワーク理論の基盤整備と伸張 / データの精度を考慮した組合せ最適化問題に対する問題構造とアルゴリズムの研究 / 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs ; Break maximization for round-robin tournaments without consecutive breaks ; Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm ; Height Estimation for Abrasive Grain of Synthetic Diamonds on Microscope Images by Conditional Adversarial Networks ; Designing of OTN/WDM networks withrecovery methods for multiple failures ; Restaurant Sales forecasting with feature interaction-learning mechanism based neural network model,IEEE International Conference on Big Data ; A Discrete JAYA Algorithm for Long-Term Carpooling Problem ; Carry-over Effect Values Minimization under Circle Method and Binary Factorization Based on Jaya Algorithm ; Application of Data Anonymization to Smartphone Apps Usage Logs ; 数理最適化を用いたサービス工学の事例―通勤カープールの実証実験― ; Four-level knowledge graph contrastive learning structure for smart-phone application recommendation ; A New Approach to Market Segmentation Based on 2-Dimensional Tables ; Challenges of commuter carpooling with adapting to Japanese customs and regulations: A pilot study ; Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model ; Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan ; Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament ; 交換移植制度におけるドミナントマッチングの適用可能性 ; Network Design Models with Partial Protection Schemes against Multiple Failures under Optical- Channel Data Unit Constraints ; ILP models and improved methods for the problem of routing and spectrum allocation ; A novel channel-based model for the problem of routing, space, and spectrum assignment ; NASH EQUILIBRIA FOR INFORMATION DIFFUSION GAMES ON WEIGHTED CYCLES AND PATHS ; Strongly separable matrices for nonadaptive combinatorial group testing ; Modeling and Evaluating Taxi Ride-sharing for Event Trips ; 不均衡データに対する多段階学習を用いた アンサンブルモデルによる2 クラス分類アルゴリズムの提案 ; A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs / Break maximization for round-robin tournaments without consecutive breaks / Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm / Height Estimation for Abrasive Grain of Synthetic Diamonds on Microscope Images by Conditional Adversarial Networks / Designing of OTN/WDM networks withrecovery methods for multiple failures / Restaurant Sales forecasting with feature interaction-learning mechanism based neural network model,IEEE International Conference on Big Data / A Discrete JAYA Algorithm for Long-Term Carpooling Problem / Carry-over Effect Values Minimization under Circle Method and Binary Factorization Based on Jaya Algorithm / Application of Data Anonymization to Smartphone Apps Usage Logs / 数理最適化を用いたサービス工学の事例―通勤カープールの実証実験― / Four-level knowledge graph contrastive learning structure for smart-phone application recommendation / A New Approach to Market Segmentation Based on 2-Dimensional Tables / Challenges of commuter carpooling with adapting to Japanese customs and regulations: A pilot study / Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model / Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan / Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament / 交換移植制度におけるドミナントマッチングの適用可能性 / Network Design Models with Partial Protection Schemes against Multiple Failures under Optical- Channel Data Unit Constraints / ILP models and improved methods for the problem of routing and spectrum allocation / A novel channel-based model for the problem of routing, space, and spectrum assignment / NASH EQUILIBRIA FOR INFORMATION DIFFUSION GAMES ON WEIGHTED CYCLES AND PATHS / Strongly separable matrices for nonadaptive combinatorial group testing / Modeling and Evaluating Taxi Ride-sharing for Event Trips / 不均衡データに対する多段階学習を用いた アンサンブルモデルによる2 クラス分類アルゴリズムの提案 / A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; 組合せ最適化 ; 数理最適化 ; 学習分析 ; 物流最適化</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 / 組合せ最適化 / 数理最適化 / 学習分析 / 物流最適化</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>木下陽平</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000004260</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>干渉SAR時系列解析を用いた地殻変動モニタリングに関する研究 ; 極端降水現象と超稠密GNSS観測網による水蒸気の動態解明 ; 異常検知手法と大気ノイズ補正を併用したInSAR時系列による未知のSSE検出手法の確立 ; RESTEC 2023年度研究助成「中央構造線で地震は起こるか? -高精度InSAR解析による中央構造線断層帯の運動様式の解明-」 ; JAXA委託研究「2023年度 ALOS-4データ利用検討のための時系列干渉SAR解析の高度化等に関する研究」 ; 2023 年 5 月 5 日の地震を含む能登半島北東部陸海域で継続する地震と災害の総合調査 ; 能登半島北東部において継続する地震活動に関する総合調査 ; GNSS観測と気象モデリングの融合による先進的InSAR大気補正手法の開発 ; SAR気象学 : InSARデータからの気象情報の抽出と地殻変動研究への応用</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>干渉SAR時系列解析を用いた地殻変動モニタリングに関する研究 / 極端降水現象と超稠密GNSS観測網による水蒸気の動態解明 / 異常検知手法と大気ノイズ補正を併用したInSAR時系列による未知のSSE検出手法の確立 / RESTEC 2023年度研究助成「中央構造線で地震は起こるか? -高精度InSAR解析による中央構造線断層帯の運動様式の解明-」 / JAXA委託研究「2023年度 ALOS-4データ利用検討のための時系列干渉SAR解析の高度化等に関する研究」 / 2023 年 5 月 5 日の地震を含む能登半島北東部陸海域で継続する地震と災害の総合調査 / 能登半島北東部において継続する地震活動に関する総合調査 / GNSS観測と気象モデリングの融合による先進的InSAR大気補正手法の開発 / SAR気象学 : InSARデータからの気象情報の抽出と地殻変動研究への応用</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Estimation of the fault geometry of the Median Tectonic Line (MTL) in Eastern Shikoku, Southwestern Japan, via GNSS and InSAR time series analysis ; InSAR-based observations of the 2020-2021 transient deformation and the 2023 earthquake in Noto Peninsula, Japan ; Coseismic slip distribution of the 2024 Noto Peninsula earthquake deduced from dense global navigation satellite system network and interferometric synthetic aperture radar data: effect of assumed dip angle ; Slow slip event displacement on 2018 offshore Boso peninsula detected by Sentinel-1 InSAR time series analysis with numerical weather model assistance ; Atmospheric noise mitigation in SAR interferometry: current state of progress ; Development of InSAR neutral atmospheric delay correction model by use of GNSS ZTD and its horizontal gradient ; Error Evaluation of L-Band InSAR Precipitable Water Vapor Measurements by Comparison with GNSS Observations in Japan ; Quantifying the effect of autonomous adaptation to global river flood projection: Applications to future flood risk assessments ; Detections and simulations of tropospheric water vapor fluctuations due to trapped lee waves by ALOS-2/PALSAR-2 ScanSAR interferometry ; Localized Delay Signals Detected by Synthetic Aperture Radar Interferometry and Their Simulation by WRF 4DVAR ; InSAR observation and numerical modeling of the water vapor signal during a heavy rain: A case study of the 2008 Seino event, central Japan ; Are numerical weather model outputs helpful to reduce tropospheric delay signals in InSAR data? ; On the importance of accurately ray-traced troposphere corrections for Interferometric SAR data ; WACCA virtual laboratory 2020年度活動報告 ; WACCA meeting 10「水文・水資源学Beyond2030 ワークショップ」会議報告 ; 合成開口レーダー研究の現状とリスク・レジリエンス社会 ; 誰もしていないことを楽しむ ; WACCA meeting 06 会議報告 「水関連研究の現状と課題」 ; 水文学若手会 水関連分野次世代研究探索ワークショップ（WACCA meeting 02） 会議報告 「水関連分野における分野融合の可能性と意義」 ; ESA Living Planet Symposium 2013参加報告</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Estimation of the fault geometry of the Median Tectonic Line (MTL) in Eastern Shikoku, Southwestern Japan, via GNSS and InSAR time series analysis / InSAR-based observations of the 2020-2021 transient deformation and the 2023 earthquake in Noto Peninsula, Japan / Coseismic slip distribution of the 2024 Noto Peninsula earthquake deduced from dense global navigation satellite system network and interferometric synthetic aperture radar data: effect of assumed dip angle / Slow slip event displacement on 2018 offshore Boso peninsula detected by Sentinel-1 InSAR time series analysis with numerical weather model assistance / Atmospheric noise mitigation in SAR interferometry: current state of progress / Development of InSAR neutral atmospheric delay correction model by use of GNSS ZTD and its horizontal gradient / Error Evaluation of L-Band InSAR Precipitable Water Vapor Measurements by Comparison with GNSS Observations in Japan / Quantifying the effect of autonomous adaptation to global river flood projection: Applications to future flood risk assessments / Detections and simulations of tropospheric water vapor fluctuations due to trapped lee waves by ALOS-2/PALSAR-2 ScanSAR interferometry / Localized Delay Signals Detected by Synthetic Aperture Radar Interferometry and Their Simulation by WRF 4DVAR / InSAR observation and numerical modeling of the water vapor signal during a heavy rain: A case study of the 2008 Seino event, central Japan / Are numerical weather model outputs helpful to reduce tropospheric delay signals in InSAR data? / On the importance of accurately ray-traced troposphere corrections for Interferometric SAR data / WACCA virtual laboratory 2020年度活動報告 / WACCA meeting 10「水文・水資源学Beyond2030 ワークショップ」会議報告 / 合成開口レーダー研究の現状とリスク・レジリエンス社会 / 誰もしていないことを楽しむ / WACCA meeting 06 会議報告 「水関連研究の現状と課題」 / 水文学若手会 水関連分野次世代研究探索ワークショップ（WACCA meeting 02） 会議報告 「水関連分野における分野融合の可能性と意義」 / ESA Living Planet Symposium 2013参加報告</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>災害分析 ; 需要予測 ; センサデータ解析 ; 社会ネットワーク分析 ; 深層学習</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>災害分析 / 需要予測 / センサデータ解析 / 社会ネットワーク分析 / 深層学習</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>讃井知</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000004603</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>情報提供と環境手がかりによる行動変容：ナッジ犯罪予防の定式化とその効果検証 ; 高齢者の情報通信機器利用とコミュニティ意識の関連：地域参加の促進にむけた検討 ; 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 ; 異文化背景をもつ若者の犯罪リスク要因とそれを踏まえた総合的対応策の検討 ; 高齢者の犯罪被害防止にむけた自助・共助を促進する情報の活用方策</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>情報提供と環境手がかりによる行動変容：ナッジ犯罪予防の定式化とその効果検証 / 高齢者の情報通信機器利用とコミュニティ意識の関連：地域参加の促進にむけた検討 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / 異文化背景をもつ若者の犯罪リスク要因とそれを踏まえた総合的対応策の検討 / 高齢者の犯罪被害防止にむけた自助・共助を促進する情報の活用方策</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>メディア・システムと現実感の関係 ; Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan ; Police confidence attitude formation dynamics in Japan, South Korea and Taiwan ; The role of social capital in a super-aged society: Focus on transformation of "network" ; 子供の前兆事案被害における保護者の警察・学校への連絡意図の形成要因 ; コミュニティ・ポリーシングが警察への信頼に与える影響 : 日本の警察を事例に ; 高齢者によるウェアラブル型健康情報機器の主体的利用可能性： 2つの評価次元からの検討 ; 異文化背景をもつ犯罪者の特性と犯罪化の規定因 ; 高齢者家庭における固定電話の受信への対応についての観察研究 ; 警察の施策の認知が信頼に与える影響 : 伝統的信頼モデル,正統性モデル,主要価値類似性モデルの統合 ; インクルーシブな視点に基づく「みんなの学会」の検討と実践 -科学への市民参加促進にむけての試み ; インクルーシブな視点に基づく「みんなの学会」の検討と実践 -科学への市民参加促進にむけての試み ; 三大都市圏居住者の地方部への地域愛着と貢献行動意図の関連：非三大都市圏の大学在学時に親元を離れて大学周辺に居住した者に着目して ; 自主防犯団体の協働ネットワーク構造と活動の活発さ ; 詐欺電話接触時の夫婦間における相談行動意図の規定因 ; 詐欺電話接触時の夫婦間における相談行動意図の規定因 ; 防犯ボランティア団体の活動継続の規定因:支援の内容と主体による差異 ; 特殊詐欺抑止のための情報提供行動の促進：平時の地域および夫婦の関わりに焦点をあてて ; 環境に対する行動・心理・生理 : エビデンスに基づく環境設計と新しい「環境」研究にむけて (特集 論文レビューの方向を探る) ; 英国の警察関連ボランティアに関する調査報告 ; 高齢者の犯罪被害を防ぐ共助を促進する情報の活用方策 ; みんなの学会:ユニバーサルな学びに向けた挑戦 ; 一般市民の更生支援に対する認知および参加意向の向上にむけた検討 ; 加害者の処遇に対する有効性認知と更生支援活動参加意向の関係 ; 高齢者の犯罪被害を防ぐ共助を促進する情報の活用方策：住民に対するニーズ調査の結果と展望</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>メディア・システムと現実感の関係 / Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan / Police confidence attitude formation dynamics in Japan, South Korea and Taiwan / The role of social capital in a super-aged society: Focus on transformation of "network" / 子供の前兆事案被害における保護者の警察・学校への連絡意図の形成要因 / コミュニティ・ポリーシングが警察への信頼に与える影響 : 日本の警察を事例に / 高齢者によるウェアラブル型健康情報機器の主体的利用可能性： 2つの評価次元からの検討 / 異文化背景をもつ犯罪者の特性と犯罪化の規定因 / 高齢者家庭における固定電話の受信への対応についての観察研究 / 警察の施策の認知が信頼に与える影響 : 伝統的信頼モデル,正統性モデル,主要価値類似性モデルの統合 / インクルーシブな視点に基づく「みんなの学会」の検討と実践 -科学への市民参加促進にむけての試み / インクルーシブな視点に基づく「みんなの学会」の検討と実践 -科学への市民参加促進にむけての試み / 三大都市圏居住者の地方部への地域愛着と貢献行動意図の関連：非三大都市圏の大学在学時に親元を離れて大学周辺に居住した者に着目して / 自主防犯団体の協働ネットワーク構造と活動の活発さ / 詐欺電話接触時の夫婦間における相談行動意図の規定因 / 詐欺電話接触時の夫婦間における相談行動意図の規定因 / 防犯ボランティア団体の活動継続の規定因:支援の内容と主体による差異 / 特殊詐欺抑止のための情報提供行動の促進：平時の地域および夫婦の関わりに焦点をあてて / 環境に対する行動・心理・生理 : エビデンスに基づく環境設計と新しい「環境」研究にむけて (特集 論文レビューの方向を探る) / 英国の警察関連ボランティアに関する調査報告 / 高齢者の犯罪被害を防ぐ共助を促進する情報の活用方策 / みんなの学会:ユニバーサルな学びに向けた挑戦 / 一般市民の更生支援に対する認知および参加意向の向上にむけた検討 / 加害者の処遇に対する有効性認知と更生支援活動参加意向の関係 / 高齢者の犯罪被害を防ぐ共助を促進する情報の活用方策：住民に対するニーズ調査の結果と展望</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; 行政データ分析 ; 人間中心設計 ; 情報検索 ; 意思決定支援</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 / 行政データ分析 / 人間中心設計 / 情報検索 / 意思決定支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>作道真理</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000004255</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ESG、開示とパフォーマンス：ノンパラメトリック手法を用いて ; CSRの実証研究：ノンパラメトリック推計アプローチ ; 社会的責任活動の実証研究：企業のミクロ経済学的行動と政策分析</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ESG、開示とパフォーマンス：ノンパラメトリック手法を用いて / CSRの実証研究：ノンパラメトリック推計アプローチ / 社会的責任活動の実証研究：企業のミクロ経済学的行動と政策分析</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Subjective probabilistic expectations, household air pollution, and health: Evidence from cooking fuel use patterns in West Bengal, India ; Seemingly Unrelated Interventions: Environmental Management Systems in the Workplace and Energy Saving Practices at Home ; Cooking Fuel Choices --Analysis of Socio-economic and Demographic Factors in Rural India-- ; Another Bias Correction for Asymmetric Kernel Density Estimation with a Parametric Start ; Functional-Coefficient Cointegration Models in the Presence of Deterministic Trends ; Do Social Norms Matter to Energy Saving Behavior?: Endogenous Social and Correlated Effects ; Testing Symmetry of Unknown Densities via Smoothing with the Generalized Gamma Kernels ; Family of the Generalised Gamma Kernels: A Generator of Asymmetric Kernels for Nonnegative Data ; Nonnegative Bias Reduction Methods for Density Estimation Using Asymmetric Kernels</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Subjective probabilistic expectations, household air pollution, and health: Evidence from cooking fuel use patterns in West Bengal, India / Seemingly Unrelated Interventions: Environmental Management Systems in the Workplace and Energy Saving Practices at Home / Cooking Fuel Choices --Analysis of Socio-economic and Demographic Factors in Rural India-- / Another Bias Correction for Asymmetric Kernel Density Estimation with a Parametric Start / Functional-Coefficient Cointegration Models in the Presence of Deterministic Trends / Do Social Norms Matter to Energy Saving Behavior?: Endogenous Social and Correlated Effects / Testing Symmetry of Unknown Densities via Smoothing with the Generalized Gamma Kernels / Family of the Generalised Gamma Kernels: A Generator of Asymmetric Kernels for Nonnegative Data / Nonnegative Bias Reduction Methods for Density Estimation Using Asymmetric Kernels</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; 災害分析 ; 計算社会科学 ; 学習分析 ; 行政データ分析</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 / 災害分析 / 計算社会科学 / 学習分析 / 行政データ分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>髙橋裕紀</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000004726</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発 ; 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発 / 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 ; What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews ; Mystery shopping considering lifestyle heterogeneity ; 経験効用モデルに基づくサービス継続利用を促すリマインダーの最適間隔 ; Effects of Incentivized Fake Reviews on E-commerce Markets ; Platform in manufacturing for enhancement of product value by sharing ; Interpreting value creation model by case-based decision theory ; Service switching in case-based decisions following bad experiences: Online reviews data of Japanese hairdressing salons ; Multi-agent simulation for the manufacturer’s decision making in sharing markets ; Manufacturer’s strategy in a sharing economy</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 / What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews / Mystery shopping considering lifestyle heterogeneity / 経験効用モデルに基づくサービス継続利用を促すリマインダーの最適間隔 / Effects of Incentivized Fake Reviews on E-commerce Markets / Platform in manufacturing for enhancement of product value by sharing / Interpreting value creation model by case-based decision theory / Service switching in case-based decisions following bad experiences: Online reviews data of Japanese hairdressing salons / Multi-agent simulation for the manufacturer’s decision making in sharing markets / Manufacturer’s strategy in a sharing economy</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>マーケティング分析 ; 学習分析 ; 社会ネットワーク分析 ; 推薦システム ; 意思決定支援</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>マーケティング分析 / 学習分析 / 社会ネットワーク分析 / 推薦システム / 意思決定支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>大西正輝</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>防災 ; 人間中心設計 ; 医用画像 ; スポーツ科学 ; 行動科学</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>防災 / 人間中心設計 / 医用画像 / スポーツ科学 / 行動科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>岡本直久</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000000834</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>持続可能な観光のための戦略的オーバーツーリズム対処療法の構築 ; 持続可能な観光地形成に向けた複雑系モデルとそれを用いた合意形成ツールの開発 ; 意識分析にもとづく国外旅行意向の国際比較研究 ; 観光振興のためのマーケットデザインに関する研究－効果的な日本型DMO構築に向けて ; 複数の観光交通データの融合的活用方法の開発と政策評価への展開 ; 道路インフラマネジメントサイクルの展開と国内外への実装を目指した統括的研究 ; 交通関連調査体系の再構築と政策評価への展開 ; 道路パフォーマンス指標の開発 ; コンテナ港湾機能配分に関する研究 ; 観光交通の需要分析</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>持続可能な観光のための戦略的オーバーツーリズム対処療法の構築 / 持続可能な観光地形成に向けた複雑系モデルとそれを用いた合意形成ツールの開発 / 意識分析にもとづく国外旅行意向の国際比較研究 / 観光振興のためのマーケットデザインに関する研究－効果的な日本型DMO構築に向けて / 複数の観光交通データの融合的活用方法の開発と政策評価への展開 / 道路インフラマネジメントサイクルの展開と国内外への実装を目指した統括的研究 / 交通関連調査体系の再構築と政策評価への展開 / 道路パフォーマンス指標の開発 / コンテナ港湾機能配分に関する研究 / 観光交通の需要分析</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>人口分布とネットワークを考慮したコミュニティバス運営負担に関する実証分析 ～茨城県の自治体を対象として～ ; Analysis of Changes in Demand before and after the Restructuring of “Tsukubus” ; Simulation Analysis of Tsunami Evacuation Behavior for Residents and Seabathers Under Mixed Pedestrian-Automobile ; A Study of Recovery from Shocks Lead by Crisis in the Field of Tourism ; Examination of A Risk Management Through Technical Transitions in The Railway ATS System ; バス利用に影響を与える要因の検討－利用者意識調査とマクロ分析に基づいて－ ; Consciousness Analysis on Travel Behavior and Intention of People in Mainland China ; 道路ネットワーク上の交通荷重情報収集を目的とした車重計の配置方法 ; つくば市における宅配便の利用実態と再配達依頼の規定因―配達人とのコミュニケーションに着目してー ; 渡航回数に着目した中国人の旅行意向形成に関する研究 ; 観光流行現象の変遷に関する基礎的考察 ; 茨城県内の市町村における橋梁維持管理の実態に関する研究 ; 英国を事例とした我が国の空港運営政策に関する一考察 ; GPSログデータを用いた訪日外国人旅行者の訪問パターンの分析手法の開発 ; 東京近郊観光地におけるインバウンド観光プロモーション施策の考察 ; 人口分布統計データを活用した観光地の特性把握 ; 高齢者の交通環境改善に向けた新たな交通手段の利用可能性に関する研究 ; ガソリンスタンドの経営収支と需要を考慮した存続可能性に関する研究 ; ガソリンスタンドの経営収支と需要を考慮した存続可能性に関する研究 ; 効果的な鉄道の安全対策が新たな課題を惹起する―「安全の 4M」と「リスク」の体系化による考察とマネジメントの重要性― ; 地域鉄道の維持に関する考察-時 系列データによる検討- ; 都市高速道路における交通状態推定問題およびセンサー配置問題に対するデータ同化アプローチ ; 橋梁および高速道路上の横断構造物に対する維持管理の実態と課題 ; 国内旅行におけるリピーターの行動特性及び醸成要因に関する研究 ; 観光地における地域ブランド構築の内部関係者による資源活用パターンと課題構造に関する研究 - 関東・甲信越地域の市町村を対象として -</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>人口分布とネットワークを考慮したコミュニティバス運営負担に関する実証分析 ～茨城県の自治体を対象として～ / Analysis of Changes in Demand before and after the Restructuring of “Tsukubus” / Simulation Analysis of Tsunami Evacuation Behavior for Residents and Seabathers Under Mixed Pedestrian-Automobile / A Study of Recovery from Shocks Lead by Crisis in the Field of Tourism / Examination of A Risk Management Through Technical Transitions in The Railway ATS System / バス利用に影響を与える要因の検討－利用者意識調査とマクロ分析に基づいて－ / Consciousness Analysis on Travel Behavior and Intention of People in Mainland China / 道路ネットワーク上の交通荷重情報収集を目的とした車重計の配置方法 / つくば市における宅配便の利用実態と再配達依頼の規定因―配達人とのコミュニケーションに着目してー / 渡航回数に着目した中国人の旅行意向形成に関する研究 / 観光流行現象の変遷に関する基礎的考察 / 茨城県内の市町村における橋梁維持管理の実態に関する研究 / 英国を事例とした我が国の空港運営政策に関する一考察 / GPSログデータを用いた訪日外国人旅行者の訪問パターンの分析手法の開発 / 東京近郊観光地におけるインバウンド観光プロモーション施策の考察 / 人口分布統計データを活用した観光地の特性把握 / 高齢者の交通環境改善に向けた新たな交通手段の利用可能性に関する研究 / ガソリンスタンドの経営収支と需要を考慮した存続可能性に関する研究 / ガソリンスタンドの経営収支と需要を考慮した存続可能性に関する研究 / 効果的な鉄道の安全対策が新たな課題を惹起する―「安全の 4M」と「リスク」の体系化による考察とマネジメントの重要性― / 地域鉄道の維持に関する考察-時 系列データによる検討- / 都市高速道路における交通状態推定問題およびセンサー配置問題に対するデータ同化アプローチ / 橋梁および高速道路上の横断構造物に対する維持管理の実態と課題 / 国内旅行におけるリピーターの行動特性及び醸成要因に関する研究 / 観光地における地域ブランド構築の内部関係者による資源活用パターンと課題構造に関する研究 - 関東・甲信越地域の市町村を対象として -</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>災害分析 ; 観光情報学 ; 社会ネットワーク分析 ; マーケティング分析 ; 行政データ分析</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>災害分析 / 観光情報学 / 社会ネットワーク分析 / マーケティング分析 / 行政データ分析</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -890,7 +890,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Phung-DucTuan</t>
+          <t>Phung DucTuan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -909,12 +909,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>需要予測 ; 推薦システム ; 強化学習 ; 大規模言語モデル ; 人間中心設計</t>
+          <t>需要予測 ; 推薦システム ; 強化学習 ; 社会ネットワーク分析 ; 人間中心設計</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>需要予測 / 推薦システム / 強化学習 / 大規模言語モデル / 人間中心設計</t>
+          <t>需要予測 / 推薦システム / 強化学習 / 社会ネットワーク分析 / 人間中心設計</t>
         </is>
       </c>
     </row>
@@ -1227,62 +1227,102 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>Tran Lam Anh Duong</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000003869</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>グローバル・バリュー・チェーンの形成と経済発展：理論と実証 ; グローバル・バリュー・チェーンの形成メカニズムに関する分析 ; 経済のグローバル化が市場の不完全性を通じて所得の不平等に与える影響の分析 ; 貿易のネットワーク構造が技術の波及を通じ経済成長に与える影響の分析</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>グローバル・バリュー・チェーンの形成と経済発展：理論と実証 / グローバル・バリュー・チェーンの形成メカニズムに関する分析 / 経済のグローバル化が市場の不完全性を通じて所得の不平等に与える影響の分析 / 貿易のネットワーク構造が技術の波及を通じ経済成長に与える影響の分析</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Technology Level and the Global Value Chain ; Effect of International Trade on Wage Inequality with Endogenous Technology Choice ; International Trade and Income Inequality ; Optimal Infant Industry Protection during Transition to World Trade Organization Membership – A Numerical Analysis for the Vietnamese Motorcycle Industry</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Technology Level and the Global Value Chain / Effect of International Trade on Wage Inequality with Endogenous Technology Choice / International Trade and Income Inequality / Optimal Infant Industry Protection during Transition to World Trade Organization Membership – A Numerical Analysis for the Vietnamese Motorcycle Industry</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>需要予測 ; 社会ネットワーク分析 ; 人間中心設計 ; 災害分析 ; テキストマイニング</t>
+          <t>社会ネットワーク分析 ; マーケティング分析 ; 物流最適化 ; 学習分析 ; 行政データ分析</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>需要予測 / 社会ネットワーク分析 / 人間中心設計 / 災害分析 / テキストマイニング</t>
+          <t>社会ネットワーク分析 / マーケティング分析 / 物流最適化 / 学習分析 / 行政データ分析</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LiuTianxiang</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000005094</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>構造化制約付き最適化問題の効率的な解法の開発と機械学習への応用 ; 一般的な非凸非平滑最適化のための効率的解法の開発と機械学習への応用 ; Fast numerical methods for nonconvex nonsmooth problems without global Lipschitz gradients and applications to machine learning</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>構造化制約付き最適化問題の効率的な解法の開発と機械学習への応用 / 一般的な非凸非平滑最適化のための効率的解法の開発と機械学習への応用 / Fast numerical methods for nonconvex nonsmooth problems without global Lipschitz gradients and applications to machine learning</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Convergence analysis under consistent error bounds ; Doubly majorized algorithm for sparsity-inducing optimization problems with regularizer-compatible constraints ; An inexact successive quadratic approximation method for a class of difference-of-convex optimization problems ; Data-Driven Structured Noise Filtering via Common Dynamics Estimation ; A Hybrid Penalty Method for a Class of Optimization Problems with Multiple Rank Constraints ; An exact penalty method for semidefinite-box-constrained low-rank matrix optimization problems ; A successive difference-of-convex approximation method for a class of nonconvex nonsmooth optimization problems ; A refined convergence analysis of pDCAe with applications to simultaneous sparse recovery and outlier detection ; Peaceman–Rachford splitting for a class of nonconvex optimization problems ; Further properties of the forward–backward envelope with applications to difference-of-convex programming</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Convergence analysis under consistent error bounds / Doubly majorized algorithm for sparsity-inducing optimization problems with regularizer-compatible constraints / An inexact successive quadratic approximation method for a class of difference-of-convex optimization problems / Data-Driven Structured Noise Filtering via Common Dynamics Estimation / A Hybrid Penalty Method for a Class of Optimization Problems with Multiple Rank Constraints / An exact penalty method for semidefinite-box-constrained low-rank matrix optimization problems / A successive difference-of-convex approximation method for a class of nonconvex nonsmooth optimization problems / A refined convergence analysis of pDCAe with applications to simultaneous sparse recovery and outlier detection / Peaceman–Rachford splitting for a class of nonconvex optimization problems / Further properties of the forward–backward envelope with applications to difference-of-convex programming</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>医用画像 ; 時系列解析 ; 需要予測 ; 人間中心設計 ; 物流最適化</t>
+          <t>数理最適化 ; 学習分析 ; 組合せ最適化 ; 物流最適化 ; 最適化</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>医用画像 / 時系列解析 / 需要予測 / 人間中心設計 / 物流最適化</t>
+          <t>数理最適化 / 学習分析 / 組合せ最適化 / 物流最適化 / 最適化</t>
         </is>
       </c>
     </row>

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -890,7 +890,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Phung DucTuan</t>
+          <t>Phung-DucTuan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -909,12 +909,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>需要予測 ; 推薦システム ; 強化学習 ; 社会ネットワーク分析 ; 人間中心設計</t>
+          <t>需要予測 ; 推薦システム ; 強化学習 ; 大規模言語モデル ; 人間中心設計</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>需要予測 / 推薦システム / 強化学習 / 社会ネットワーク分析 / 人間中心設計</t>
+          <t>需要予測 / 推薦システム / 強化学習 / 大規模言語モデル / 人間中心設計</t>
         </is>
       </c>
     </row>
@@ -1227,102 +1227,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tran Lam Anh Duong</t>
+          <t>TranLamAnhDuong</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://trios.tsukuba.ac.jp/researcher/0000003869</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>グローバル・バリュー・チェーンの形成と経済発展：理論と実証 ; グローバル・バリュー・チェーンの形成メカニズムに関する分析 ; 経済のグローバル化が市場の不完全性を通じて所得の不平等に与える影響の分析 ; 貿易のネットワーク構造が技術の波及を通じ経済成長に与える影響の分析</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>グローバル・バリュー・チェーンの形成と経済発展：理論と実証 / グローバル・バリュー・チェーンの形成メカニズムに関する分析 / 経済のグローバル化が市場の不完全性を通じて所得の不平等に与える影響の分析 / 貿易のネットワーク構造が技術の波及を通じ経済成長に与える影響の分析</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Technology Level and the Global Value Chain ; Effect of International Trade on Wage Inequality with Endogenous Technology Choice ; International Trade and Income Inequality ; Optimal Infant Industry Protection during Transition to World Trade Organization Membership – A Numerical Analysis for the Vietnamese Motorcycle Industry</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Technology Level and the Global Value Chain / Effect of International Trade on Wage Inequality with Endogenous Technology Choice / International Trade and Income Inequality / Optimal Infant Industry Protection during Transition to World Trade Organization Membership – A Numerical Analysis for the Vietnamese Motorcycle Industry</t>
-        </is>
-      </c>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>社会ネットワーク分析 ; マーケティング分析 ; 物流最適化 ; 学習分析 ; 行政データ分析</t>
+          <t>需要予測 ; 社会ネットワーク分析 ; 人間中心設計 ; 災害分析 ; テキストマイニング</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>社会ネットワーク分析 / マーケティング分析 / 物流最適化 / 学習分析 / 行政データ分析</t>
+          <t>需要予測 / 社会ネットワーク分析 / 人間中心設計 / 災害分析 / テキストマイニング</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>LiuTianxiang</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://trios.tsukuba.ac.jp/researcher/0000005094</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>構造化制約付き最適化問題の効率的な解法の開発と機械学習への応用 ; 一般的な非凸非平滑最適化のための効率的解法の開発と機械学習への応用 ; Fast numerical methods for nonconvex nonsmooth problems without global Lipschitz gradients and applications to machine learning</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>構造化制約付き最適化問題の効率的な解法の開発と機械学習への応用 / 一般的な非凸非平滑最適化のための効率的解法の開発と機械学習への応用 / Fast numerical methods for nonconvex nonsmooth problems without global Lipschitz gradients and applications to machine learning</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Convergence analysis under consistent error bounds ; Doubly majorized algorithm for sparsity-inducing optimization problems with regularizer-compatible constraints ; An inexact successive quadratic approximation method for a class of difference-of-convex optimization problems ; Data-Driven Structured Noise Filtering via Common Dynamics Estimation ; A Hybrid Penalty Method for a Class of Optimization Problems with Multiple Rank Constraints ; An exact penalty method for semidefinite-box-constrained low-rank matrix optimization problems ; A successive difference-of-convex approximation method for a class of nonconvex nonsmooth optimization problems ; A refined convergence analysis of pDCAe with applications to simultaneous sparse recovery and outlier detection ; Peaceman–Rachford splitting for a class of nonconvex optimization problems ; Further properties of the forward–backward envelope with applications to difference-of-convex programming</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Convergence analysis under consistent error bounds / Doubly majorized algorithm for sparsity-inducing optimization problems with regularizer-compatible constraints / An inexact successive quadratic approximation method for a class of difference-of-convex optimization problems / Data-Driven Structured Noise Filtering via Common Dynamics Estimation / A Hybrid Penalty Method for a Class of Optimization Problems with Multiple Rank Constraints / An exact penalty method for semidefinite-box-constrained low-rank matrix optimization problems / A successive difference-of-convex approximation method for a class of nonconvex nonsmooth optimization problems / A refined convergence analysis of pDCAe with applications to simultaneous sparse recovery and outlier detection / Peaceman–Rachford splitting for a class of nonconvex optimization problems / Further properties of the forward–backward envelope with applications to difference-of-convex programming</t>
-        </is>
-      </c>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>数理最適化 ; 学習分析 ; 組合せ最適化 ; 物流最適化 ; 最適化</t>
+          <t>医用画像 ; 時系列解析 ; 需要予測 ; 人間中心設計 ; 物流最適化</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>数理最適化 / 学習分析 / 組合せ最適化 / 物流最適化 / 最適化</t>
+          <t>医用画像 / 時系列解析 / 需要予測 / 人間中心設計 / 物流最適化</t>
         </is>
       </c>
     </row>

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -890,31 +890,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Phung-DucTuan</t>
+          <t>Phung Duc Tuan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000003872</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>省電力サーバ群の性能評価と負荷分散に関する数理モデル ; 処理能力可変型待ち行列モデルの理論的発展と大規模省エネデータセンターへの応用 ; 複数車両・複数道路橋を対象とした移動センシング技術の基盤的研究 ; 処理能力可変型待ち行列システムの理論的深化と省エネデータセンターへの応用 ; 起動時間を有するシステムの理論解析と省エネ型データセンター性能評価への応用 ; 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化 ; 顧客の再試行と途中放棄を考慮したコールセンターのモデル化と性能解析 ; 再試行型待ち行列によるコールセンターの性能解析とサービス科学への応用 ; 再試行型複数サーバ待ち行列の解析と情報ネットワークへの応用</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>省電力サーバ群の性能評価と負荷分散に関する数理モデル / 処理能力可変型待ち行列モデルの理論的発展と大規模省エネデータセンターへの応用 / 複数車両・複数道路橋を対象とした移動センシング技術の基盤的研究 / 処理能力可変型待ち行列システムの理論的深化と省エネデータセンターへの応用 / 起動時間を有するシステムの理論解析と省エネ型データセンター性能評価への応用 / 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化 / 顧客の再試行と途中放棄を考慮したコールセンターのモデル化と性能解析 / 再試行型待ち行列によるコールセンターの性能解析とサービス科学への応用 / 再試行型複数サーバ待ち行列の解析と情報ネットワークへの応用</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>A simulation study of the sojourn time in queueing systems with stochastically delayed information ; Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers ; Performance Analysis of Blockchain with Rollups ; Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times ; Analysis of a Batch Arrival Queue with Power Saving Mode ; Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes ; A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes ; Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory ; Analytical Modelling of Asymmetric Multi-core Servers ; Energy-performance tradeoffs in server farms with batch services and setup times ; Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers ; Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers ; Queueing Analysis of an Ensemble Machine Learning System ; Performance analysis of a collision channel with abandonments ; Empirical architecture comparison of two-input machine learning systems for vision tasks ; Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes ; Modeling and performance analysis of hybrid systems by queues with setup time ; Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis ; Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing ; To wait or not to wait: Strategic behaviors in an observable batch-service queueing system ; A Two-Population Game in Observable Double-Ended Queueing Systems ; Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems ; Analysis of a Batch Arrival Queue with Power Saving Mode ; Analyzing Vertical and Horizontal Offloading in Federated Cloud and Edge Computing Systems ; Queueing analysis of a Car/Ride-Share system</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>A simulation study of the sojourn time in queueing systems with stochastically delayed information / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers / Performance Analysis of Blockchain with Rollups / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times / Analysis of a Batch Arrival Queue with Power Saving Mode / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory / Analytical Modelling of Asymmetric Multi-core Servers / Energy-performance tradeoffs in server farms with batch services and setup times / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers / Queueing Analysis of an Ensemble Machine Learning System / Performance analysis of a collision channel with abandonments / Empirical architecture comparison of two-input machine learning systems for vision tasks / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes / Modeling and performance analysis of hybrid systems by queues with setup time / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing / To wait or not to wait: Strategic behaviors in an observable batch-service queueing system / A Two-Population Game in Observable Double-Ended Queueing Systems / Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems / Analysis of a Batch Arrival Queue with Power Saving Mode / Analyzing Vertical and Horizontal Offloading in Federated Cloud and Edge Computing Systems / Queueing analysis of a Car/Ride-Share system</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>需要予測 ; 推薦システム ; 強化学習 ; 大規模言語モデル ; 人間中心設計</t>
+          <t>物流最適化 ; 社会ネットワーク分析 ; 大規模言語モデル ; 組合せ最適化 ; 数理最適化</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>需要予測 / 推薦システム / 強化学習 / 大規模言語モデル / 人間中心設計</t>
+          <t>物流最適化 / 社会ネットワーク分析 / 大規模言語モデル / 組合せ最適化 / 数理最適化</t>
         </is>
       </c>
     </row>
@@ -1227,62 +1247,102 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>Tran Lam Anh Duong</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000003869</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>グローバル・バリュー・チェーンの形成と経済発展：理論と実証 ; グローバル・バリュー・チェーンの形成メカニズムに関する分析 ; 経済のグローバル化が市場の不完全性を通じて所得の不平等に与える影響の分析 ; 貿易のネットワーク構造が技術の波及を通じ経済成長に与える影響の分析</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>グローバル・バリュー・チェーンの形成と経済発展：理論と実証 / グローバル・バリュー・チェーンの形成メカニズムに関する分析 / 経済のグローバル化が市場の不完全性を通じて所得の不平等に与える影響の分析 / 貿易のネットワーク構造が技術の波及を通じ経済成長に与える影響の分析</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Technology Level and the Global Value Chain ; Effect of International Trade on Wage Inequality with Endogenous Technology Choice ; International Trade and Income Inequality ; Optimal Infant Industry Protection during Transition to World Trade Organization Membership – A Numerical Analysis for the Vietnamese Motorcycle Industry</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Technology Level and the Global Value Chain / Effect of International Trade on Wage Inequality with Endogenous Technology Choice / International Trade and Income Inequality / Optimal Infant Industry Protection during Transition to World Trade Organization Membership – A Numerical Analysis for the Vietnamese Motorcycle Industry</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>需要予測 ; 社会ネットワーク分析 ; 人間中心設計 ; 災害分析 ; テキストマイニング</t>
+          <t>社会ネットワーク分析 ; マーケティング分析 ; 物流最適化 ; 学習分析 ; 行政データ分析</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>需要予測 / 社会ネットワーク分析 / 人間中心設計 / 災害分析 / テキストマイニング</t>
+          <t>社会ネットワーク分析 / マーケティング分析 / 物流最適化 / 学習分析 / 行政データ分析</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LiuTianxiang</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://trios.tsukuba.ac.jp/researcher/0000005094</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>構造化制約付き最適化問題の効率的な解法の開発と機械学習への応用 ; 一般的な非凸非平滑最適化のための効率的解法の開発と機械学習への応用 ; Fast numerical methods for nonconvex nonsmooth problems without global Lipschitz gradients and applications to machine learning</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>構造化制約付き最適化問題の効率的な解法の開発と機械学習への応用 / 一般的な非凸非平滑最適化のための効率的解法の開発と機械学習への応用 / Fast numerical methods for nonconvex nonsmooth problems without global Lipschitz gradients and applications to machine learning</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Convergence analysis under consistent error bounds ; Doubly majorized algorithm for sparsity-inducing optimization problems with regularizer-compatible constraints ; An inexact successive quadratic approximation method for a class of difference-of-convex optimization problems ; Data-Driven Structured Noise Filtering via Common Dynamics Estimation ; A Hybrid Penalty Method for a Class of Optimization Problems with Multiple Rank Constraints ; An exact penalty method for semidefinite-box-constrained low-rank matrix optimization problems ; A successive difference-of-convex approximation method for a class of nonconvex nonsmooth optimization problems ; A refined convergence analysis of pDCAe with applications to simultaneous sparse recovery and outlier detection ; Peaceman–Rachford splitting for a class of nonconvex optimization problems ; Further properties of the forward–backward envelope with applications to difference-of-convex programming</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Convergence analysis under consistent error bounds / Doubly majorized algorithm for sparsity-inducing optimization problems with regularizer-compatible constraints / An inexact successive quadratic approximation method for a class of difference-of-convex optimization problems / Data-Driven Structured Noise Filtering via Common Dynamics Estimation / A Hybrid Penalty Method for a Class of Optimization Problems with Multiple Rank Constraints / An exact penalty method for semidefinite-box-constrained low-rank matrix optimization problems / A successive difference-of-convex approximation method for a class of nonconvex nonsmooth optimization problems / A refined convergence analysis of pDCAe with applications to simultaneous sparse recovery and outlier detection / Peaceman–Rachford splitting for a class of nonconvex optimization problems / Further properties of the forward–backward envelope with applications to difference-of-convex programming</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>医用画像 ; 時系列解析 ; 需要予測 ; 人間中心設計 ; 物流最適化</t>
+          <t>数理最適化 ; 学習分析 ; 組合せ最適化 ; 物流最適化 ; 最適化</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>医用画像 / 時系列解析 / 需要予測 / 人間中心設計 / 物流最適化</t>
+          <t>数理最適化 / 学習分析 / 組合せ最適化 / 物流最適化 / 最適化</t>
         </is>
       </c>
     </row>

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,30 +467,40 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>trios_research_fields_text</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>trios_research_keywords_text</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>trios_papers_text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>master_title_text</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>coarse_research_field</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>detailed_research_field</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>field_text</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>content_text</t>
         </is>
@@ -534,6 +544,15 @@
 人々の環境モラルに基づく自発的行動と望ましい環境政策
 「環境政策における経済的手法」再検討
 応用一般均衡モデルによる環境政策の社会経済学的分析
+経済政策
+環境政策・環境社会システム
+環境経済学
+エネルギー経済学
+政策分析
+不平等分析
+貧困分析
+分解手法の開発
+エネルギー貧困、エネルギー脆弱性
 エネルギー貧困からエネルギー充足へ
 Aging alone: a twin threat to decarbonisation and energy vulnerability in Japan and UK
 Reevaluating fair carbon emissions for households in Japan: basic energy needs and subsistence CO2 emissions
@@ -566,58 +585,76 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>エネルギー貧困からエネルギー充足へ / Aging alone: a twin threat to decarbonisation and energy vulnerability in Japan and UK / Reevaluating fair carbon emissions for households in Japan: basic energy needs and subsistence CO2 emissions / Double energy vulnerability in Japan / Double energy vulnerability in Japan: a first assessment / Measuring energy sufficiency: A state of being neither in energy poverty nor energy extravagance / What can be done with one tonne of CO2 emissions?: Reconsidering fair carbon emissions for households in relation to the use of domestic energy services / Measuring energy sufficiency: A state of being in neither energy poverty nor energy extravagance / How to evaluate energy sufficiency: A direct measurement approach / Energy Poverty in Japan: Current Trends and Future Challenges / 公平なエネルギー転換：気候正義とエネルギー正義の観点から / Regional energy poverty reevaluated: A direct measurement approach applied to France and Japan / Energy poor need more energy, but do they need more carbon?: Evaluation of people’s basic carbon needs / Prevalence of energy poverty in Japan: A comprehensive analysis of energy poverty vulnerabilities / Prevalence of energy poverty in Japan: A comprehensive analysis of energy poverty vulnerabilities / Energy poor need more energy, but do they need more carbon? / Engendering an inclusive low-carbon energy transition in Japan: Considering the perspectives and awareness of the energy poor / Understanding regional energy poverty in Japan: a direct measurement approach / Engendering an inclusive low-carbon energy transition in Japan: considering the perspectives and awareness of the energy poor / Measuring Energy Poverty via Energy Service Usage: The Japanese case / 「エネルギー貧困」・「エネルギー脆弱性」・「エネルギー正義」：日本における現状と課題 / 「エネルギー正義」について / Gauging Energy Poverty: A Multidimensional Approach / Measuring Energy Poverty in Japan, 2004-2013 / How Can We Gauge Energy Poverty? A Multidimensional Approach</t>
+          <t>経済政策 / 環境政策・環境社会システム</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>環境経済学 / エネルギー経済学 / 政策分析 / 不平等分析 / 貧困分析 / 分解手法の開発 / エネルギー貧困、エネルギー脆弱性</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>エネルギー貧困からエネルギー充足へ / Aging alone: a twin threat to decarbonisation and energy vulnerability in Japan and UK / Reevaluating fair carbon emissions for households in Japan: basic energy needs and subsistence CO2 emissions / Double energy vulnerability in Japan / Double energy vulnerability in Japan: a first assessment / Measuring energy sufficiency: A state of being neither in energy poverty nor energy extravagance / What can be done with one tonne of CO2 emissions?: Reconsidering fair carbon emissions for households in relation to the use of domestic energy services / Measuring energy sufficiency: A state of being in neither energy poverty nor energy extravagance / How to evaluate energy sufficiency: A direct measurement approach / Energy Poverty in Japan: Current Trends and Future Challenges / 公平なエネルギー転換：気候正義とエネルギー正義の観点から / Regional energy poverty reevaluated: A direct measurement approach applied to France and Japan / Energy poor need more energy, but do they need more carbon?: Evaluation of people’s basic carbon needs / Prevalence of energy poverty in Japan: A comprehensive analysis of energy poverty vulnerabilities / Energy poor need more energy, but do they need more carbon? / Engendering an inclusive low-carbon energy transition in Japan: Considering the perspectives and awareness of the energy poor / Understanding regional energy poverty in Japan: a direct measurement approach / Measuring Energy Poverty via Energy Service Usage: The Japanese case / 「エネルギー貧困」・「エネルギー脆弱性」・「エネルギー正義」：日本における現状と課題 / 「エネルギー正義」について / Gauging Energy Poverty: A Multidimensional Approach / Measuring Energy Poverty in Japan, 2004-2013 / How Can We Gauge Energy Poverty? A Multidimensional Approach</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>中国の排出量取引制度がグリーン投資に与える影響 / 再生可能エネルギー促進のための課題ー全国トラブル発生データを用いた考察ー / 中国の「費改税」が製造業に与える影響</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>保険・金融行動 ; マッチング理論・ゲーム理論 ; オペレーションズリサーチ ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>保険・金融行動
+          <t>経済政策 ; 環境政策・環境社会システム ; マッチング理論・ゲーム理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 環境工学 ; 社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>経済政策
+環境政策・環境社会システム
+環境経済学
+エネルギー経済学
+政策分析
+不平等分析
+貧困分析
+分解手法の開発
+エネルギー貧困、エネルギー脆弱性
 マッチング理論・ゲーム理論
-オペレーションズリサーチ
 災害・防災研究
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
 AI・データサイエンス
-環境・エネルギー
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
 安定マッチング
 資源配分
 メカニズムデザイン
 協力ゲーム・非協力ゲーム
-数理最適化
-組合せ最適化
-計画・スケジューリング
 災害社会学
 防災政策
 リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>中国の排出量取引制度がグリーン投資に与える影響 / 再生可能エネルギー促進のための課題ー全国トラブル発生データを用いた考察ー / 中国の「費改税」が製造業に与える影響
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+環境工学
+社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>中国の排出量取引制度がグリーン投資に与える影響
+再生可能エネルギー促進のための課題ー全国トラブル発生データを用いた考察ー
+中国の「費改税」が製造業に与える影響
 十分なエネルギーをすべての人へ：家庭部門の公正な移行を実現するために
 包摂的な低炭素化・エネルギー転換に関する研究
 低炭素化・エネルギー転換の包摂性評価：基本的エネルギーニーズの観点から
@@ -691,6 +728,8 @@
 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年
 都市における環境リスクの軽減の経済効果に関する研究
 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―
+経済政策
+開発経済学、教育の経済学、健康の経済学、応用計量経済学
 Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone
 Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone
 The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand
@@ -719,49 +758,53 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>民主主義における利益誘導と経済発展への影響 / 民主主義における利益誘導と経済発展への影響 / 政策立案のための衛星データ利用法の探索：社会工学的アプローチ / 社会工学分野での衛星画像の利用促進に向けた探索的研究 / 衛星情報を利用した物流における大気環境改善の評価 / 反実仮想で測る公的資源配分の依怙贔屓と非効率 / 交通と環境に関する新経済地理学的基盤研究 / 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年 / 都市における環境リスクの軽減の経済効果に関する研究 / 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―</t>
+          <t>民主主義における利益誘導と経済発展への影響 / 政策立案のための衛星データ利用法の探索：社会工学的アプローチ / 社会工学分野での衛星画像の利用促進に向けた探索的研究 / 衛星情報を利用した物流における大気環境改善の評価 / 反実仮想で測る公的資源配分の依怙贔屓と非効率 / 交通と環境に関する新経済地理学的基盤研究 / 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年 / 都市における環境リスクの軽減の経済効果に関する研究 / 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand / The Impact of a High-speed Railway on Residential Land Prices / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan / School Choice and Student Sorting: Evidence from Adachi Ward in Japan / オリンピック・パラリンピックにはどんな経済効果があるのか / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward / Building an Administrative Database of Children / 高速鉄道の建設が居住地価格に与えた影響 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 / 学校の質と地価－足立区の地価データを用いた検証 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ / 子どもについての行政データベースの構築 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から / 区立小学校での補習の効果：足立区のケース / ヘドニック・アプローチにおける因果識別 / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 / The Impact of a High-speed Railway on Residential Land Prices / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand / School Choice and Student Sorting: Evidence from Adachi City in Japan</t>
+          <t>経済政策</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>開発経済学、教育の経済学、健康の経済学、応用計量経済学</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand / The Impact of a High-speed Railway on Residential Land Prices / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan / School Choice and Student Sorting: Evidence from Adachi Ward in Japan / オリンピック・パラリンピックにはどんな経済効果があるのか / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward / Building an Administrative Database of Children / 高速鉄道の建設が居住地価格に与えた影響 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 / 学校の質と地価－足立区の地価データを用いた検証 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ / 子どもについての行政データベースの構築 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から / 区立小学校での補習の効果：足立区のケース / ヘドニック・アプローチにおける因果識別 / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand / School Choice and Student Sorting: Evidence from Adachi City in Japan</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>選挙制度と資源配分のゆがみ－昭和前期の事例－ / 都市の住みやすさランキングによる居住地選択への影響 / 個人競技における チームメイトの影響 / 農産物直売所が​地域農業に与える影響 / 夜間光リモートセンシング画像を用いた​高速鉄道建設の四川省経済発展に対する影響 / エネルギー会社に対する省エネ基準が、エネルギー消費に与える影響の分析 / 有名作品の舞台地になることによる地方創生への可能性 / 新型農村協同医療制度が中国農村女性の健康格差に与える影響</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>保険・金融行動 ; 都市・地域政策 ; 交通・モビリティ ; 建築・空間設計 ; 機械学習 ; 画像・視覚情報処理 ; スポーツデータ分析 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>保険・金融行動
+          <t>経済政策 ; 都市・地域政策 ; 交通・モビリティ ; 機械学習 ; 画像・視覚情報処理 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>経済政策
+開発経済学、教育の経済学、健康の経済学、応用計量経済学
 都市・地域政策
 交通・モビリティ
-建築・空間設計
 機械学習
 画像・視覚情報処理
-スポーツデータ分析
-災害・防災研究
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
 都市経済
 地域政策
 土地利用
@@ -770,10 +813,6 @@
 モビリティ設計
 交通需要分析
 ネットワーク設計
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
 統計的学習
 予測モデリング
 表現学習
@@ -781,21 +820,29 @@
 画像認識
 行動認識
 マルチモーダル解析
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
-災害社会学
-防災政策
-リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>選挙制度と資源配分のゆがみ－昭和前期の事例－ / 都市の住みやすさランキングによる居住地選択への影響 / 個人競技における チームメイトの影響 / 農産物直売所が​地域農業に与える影響 / 夜間光リモートセンシング画像を用いた​高速鉄道建設の四川省経済発展に対する影響 / エネルギー会社に対する省エネ基準が、エネルギー消費に与える影響の分析 / 有名作品の舞台地になることによる地方創生への可能性 / 新型農村協同医療制度が中国農村女性の健康格差に与える影響
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+社会ネットワーク分析
+行政データ分析
+学習分析</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>選挙制度と資源配分のゆがみ－昭和前期の事例－
+都市の住みやすさランキングによる居住地選択への影響
+個人競技における チームメイトの影響
+農産物直売所が​地域農業に与える影響
+夜間光リモートセンシング画像を用いた​高速鉄道建設の四川省経済発展に対する影響
+エネルギー会社に対する省エネ基準が、エネルギー消費に与える影響の分析
+有名作品の舞台地になることによる地方創生への可能性
+新型農村協同医療制度が中国農村女性の健康格差に与える影響
 民主主義における利益誘導と経済発展への影響
 政策立案のための衛星データ利用法の探索：社会工学的アプローチ
 社会工学分野での衛星画像の利用促進に向けた探索的研究
@@ -863,6 +910,9 @@
           <t>行動経済学の知見を利用した進化ゲーム理論による均衡選択分析
 社会選択問題への進化ゲーム理論的アプローチ
 マルチタスク環境および協力ゲームにおける進化ゲーム理論の研究
+理論経済学
+社会システム工学・安全システム
+ゲーム理論; 進化ゲーム理論;
 The evolution of collective choice under majority rules
 Statistical inference in evolutionary dynamics
 研究室の選好と学生の成績を考慮した研究室配属法の分析
@@ -890,60 +940,73 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>理論経済学 / 社会システム工学・安全システム</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ゲーム理論; 進化ゲーム理論;</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>The evolution of collective choice under majority rules / Statistical inference in evolutionary dynamics / 研究室の選好と学生の成績を考慮した研究室配属法の分析 / 有限オートマトンを用いた私的観測繰り返しゲームにおける進化的安定戦略分析 / A stochastic stability analysis with observation errors in normal form games / Stochastic stability in the large population and small mutation limits for coordination games / oTreeを用いた配属システムの設計・構築とその運用 / A prospect theory Nash bargaining solution and its stochastic stability / 複利型強化学習を用いたポートフォリオ選択手法についての研究 / Evolutionary dynamics in multitasking environments / Stochastic stability under logit choice in coalitional bargaining problems / Prospect dynamics and loss dominance / Reference-dependent preferences, super-dominance and stochastic stability / A one-shot deviation principle for stability in matching problems / Evolutionary imitative dynamics with population-varying aspiration levels / Coalitional stochastic stability in games, networks and markets / Mutation rates and equilibrium selection under stochastic evolutionary dynamics / CG を用いたマシンの3 次元構造進化システム</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>不完全観測下における損失回避性が均衡の安定性に及ぼす影響 / 不確実性の存在する公共財提供問題における近視眼的プレイヤーによる持続的協力行動の進化分析 / 品質選択がクラウドファンディングを行う企業の資金募集形式および利潤に与える影響の分析 / 企業の不祥事における隠蔽のゲーム理論 / 就活市場における企業の内定通知がマッチングの安定性に与える影響の分析 / 非線形公共財ゲームにおけるプレイヤーの関係性を利用したグループ形成手法の考察 / Stochastic stability analysis on the tragedy of climate change via agents’ psychological dynamics / ソーシャルメディア上の炎上現象の分析と対策 / 感情表現と表現に対する反応の共進化 / 通貨競争モデルによる仮想通貨の普及に関する分析 / 多数決による準公益施設の立地分析 / プロ野球現役ドラフト制度における改善 / オークションモデルによる官製談合の分析</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 意思決定分析 ; マッチング理論・ゲーム理論 ; オペレーションズリサーチ ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-意思決定分析
+          <t>理論経済学 ; 社会システム工学・安全システム ; マッチング理論・ゲーム理論 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 学習分析 ; 計算社会科学 ; 行動科学</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>理論経済学
+社会システム工学・安全システム
+ゲーム理論; 進化ゲーム理論;
 マッチング理論・ゲーム理論
-オペレーションズリサーチ
-政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
-AI・データサイエンス
-環境・エネルギー
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-行動意思決定
-実験・行動分析
-ナッジ
-意思決定支援
 安定マッチング
 資源配分
 メカニズムデザイン
 協力ゲーム・非協力ゲーム
-数理最適化
-組合せ最適化
-計画・スケジューリング
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>不完全観測下における損失回避性が均衡の安定性に及ぼす影響 / 不確実性の存在する公共財提供問題における近視眼的プレイヤーによる持続的協力行動の進化分析 / 品質選択がクラウドファンディングを行う企業の資金募集形式および利潤に与える影響の分析 / 企業の不祥事における隠蔽のゲーム理論 / 就活市場における企業の内定通知がマッチングの安定性に与える影響の分析 / 非線形公共財ゲームにおけるプレイヤーの関係性を利用したグループ形成手法の考察 / Stochastic stability analysis on the tragedy of climate change via agents’ psychological dynamics / ソーシャルメディア上の炎上現象の分析と対策 / 感情表現と表現に対する反応の共進化 / 通貨競争モデルによる仮想通貨の普及に関する分析 / 多数決による準公益施設の立地分析 / プロ野球現役ドラフト制度における改善 / オークションモデルによる官製談合の分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+社会ネットワーク分析
+学習分析
+計算社会科学
+行動科学</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>不完全観測下における損失回避性が均衡の安定性に及ぼす影響
+不確実性の存在する公共財提供問題における近視眼的プレイヤーによる持続的協力行動の進化分析
+品質選択がクラウドファンディングを行う企業の資金募集形式および利潤に与える影響の分析
+企業の不祥事における隠蔽のゲーム理論
+就活市場における企業の内定通知がマッチングの安定性に与える影響の分析
+非線形公共財ゲームにおけるプレイヤーの関係性を利用したグループ形成手法の考察
+Stochastic stability analysis on the tragedy of climate change via agents’ psychological dynamics
+ソーシャルメディア上の炎上現象の分析と対策
+感情表現と表現に対する反応の共進化
+通貨競争モデルによる仮想通貨の普及に関する分析
+多数決による準公益施設の立地分析
+プロ野球現役ドラフト制度における改善
+オークションモデルによる官製談合の分析
 行動経済学の知見を利用した進化ゲーム理論による均衡選択分析
 社会選択問題への進化ゲーム理論的アプローチ
 マルチタスク環境および協力ゲームにおける進化ゲーム理論の研究
@@ -993,49 +1056,26 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>オペレーションズリサーチ ; 交通・モビリティ ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>オペレーションズリサーチ
-交通・モビリティ
-ネットワーク・グラフ理論
-政策評価・計量分析
-数理最適化・OR
-AI・データサイエンス
-数理最適化
-組合せ最適化
-計画・スケジューリング
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
+グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築
+中断時系列デザインを用いた人流抑制の効果推定
+実世界への応用のためのNeural Architecture Searchの多目的最適化
+大規模イベントにおける歩行者モデルの拡張と群集制御最適化
+多目的最適化による地下動線を活用した避難誘導効果の検証
+実時間で動作する音響イベント検出の大規模事前学習
+超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
     </row>
@@ -1076,6 +1116,14 @@
 地域未来創生共同研究講座
 次世代社会システムとモビリティの新価値研究
 購買データに基づく顧客行動分析
+数理情報学
+数学基礎・応用数学
+社会システム工学・安全システム
+計算科学
+数理最適化
+数理計画
+オペレーションズ・リサーチ
+サービス工学
 Data Collaboration Analysis with Orthonormal Basis Selection and Alignment
 Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning
 正循環制約を考慮したナーススケジューリング
@@ -1099,37 +1147,51 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>リーマン多様体上の制約付き最適化問題に対する汎用アルゴリズムの理論と実装 / リーマン多様体上の最適化理論に基づく新たなデータコラボレーション手法の開発 / ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発 / コネクティッドカーのサービス開発を目的とした走行データのデータクレンジング手法に係る研究 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発 / 半正定値基を用いた錐最適化問題の近似解法の開発 / 地域未来創生共同研究講座 / 次世代社会システムとモビリティの新価値研究 / 購買データに基づく顧客行動分析</t>
+          <t>リーマン多様体上の制約付き最適化問題に対する汎用アルゴリズムの理論と実装 / リーマン多様体上の最適化理論に基づく新たなデータコラボレーション手法の開発 / ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発 / コネクティッドカーのサービス開発を目的とした走行データのデータクレンジング手法に係る研究 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / 半正定値基を用いた錐最適化問題の近似解法の開発 / 地域未来創生共同研究講座 / 次世代社会システムとモビリティの新価値研究 / 購買データに基づく顧客行動分析</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Data Collaboration Analysis with Orthonormal Basis Selection and Alignment / Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning / 正循環制約を考慮したナーススケジューリング / Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices / Post-Processing with Projection and Rescaling Algorithms for Semidefinite Programming / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / A new extension of Chubanov's method to symmetric cones / 射影- 再スケーリング法を用いた 対称錐計画問題に対する後処理アルゴリズム / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / On the Global Convergence of Riemannian Interior Point Method / Completely positive factorization by a Riemannian smoothing method / Evaluating approximations of the semidefinite cone with trace normalized distance / Evaluating approximations of the semidefinite cone with trace normalized distance / A New Extension of Chubanov's Method to Symmetric Cones / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / Completely Positive Factorization in Orthogonality Optimization via Smoothing Method / Scenario-based CVaR Approach to Strategic Decision Support in One-way Station-based Carsharing Systems / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach / Polyhedral approximations of the semidefinite cone and their application / Centering ADMM for the Semidefinite Relaxation of the QAP / QAPの半正定値緩和問題を解くためのセンタリングADMM / SD基に基づく半正定値行列錐の凸多面錐近似 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― / Centering ADMM for the Semidefinite Relaxation of the QAP / Polyhedral approximations of the semidefinite cone and their application</t>
+          <t>数理情報学 / 数学基礎・応用数学 / 社会システム工学・安全システム / 計算科学</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>数理最適化 / 数理計画 / オペレーションズ・リサーチ / サービス工学</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Data Collaboration Analysis with Orthonormal Basis Selection and Alignment / Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning / 正循環制約を考慮したナーススケジューリング / Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices / Post-Processing with Projection and Rescaling Algorithms for Semidefinite Programming / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / A new extension of Chubanov's method to symmetric cones / 射影- 再スケーリング法を用いた 対称錐計画問題に対する後処理アルゴリズム / On the Global Convergence of Riemannian Interior Point Method / Completely positive factorization by a Riemannian smoothing method / Evaluating approximations of the semidefinite cone with trace normalized distance / Completely Positive Factorization in Orthogonality Optimization via Smoothing Method / Scenario-based CVaR Approach to Strategic Decision Support in One-way Station-based Carsharing Systems / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach / Polyhedral approximations of the semidefinite cone and their application / Centering ADMM for the Semidefinite Relaxation of the QAP / QAPの半正定値緩和問題を解くためのセンタリングADMM / SD基に基づく半正定値行列錐の凸多面錐近似 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成―</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>ロード・プライシング政策を考慮したNLSUEモデルとその解法の提案 / 未達率指標を用いた生産計画手法のSC能力設計への応用の研究 / 予約制乗合タクシーのルート最適化 / スマートキャンパスバス運行計画 / 救急医療サービスの効率化に向けた患者の医療機関割り当てに関するオフラインアルゴリズムの開発 / 一般消費財業界における未達率指標を用いた生産計画手法のSC能力設計への応用の研究 / 多死社会における在宅看取りに関する一考察 －茨城県の医療・介護に関する地域分析と実際の看取りをふまえて－ / バックトゥバック数を考慮したNBAの2018-2019シーズンスケジュールの作成 / 健康診断センターの勤務表作成におけるスケジューリング問題 / メタヒューリスティクスを用いた予約制乗合タクシーの配車スケジュール作成 / 乗客満足度を考慮した乗合タクシーの路線最適化モデル / ファストフード店の勤務スケジュールの作成 / リーマン多様体上の統合解析関数最適化 / 社会工学学位プログラムにおける修論発表会のスケジューリングについて / Traveling umpire problem におけるチーム間の公平性が高い解の探求 / 多要素ランキング法の上で正確性と多様性のトレードオフを考慮したモデルによる推薦システム / A Modification of Representing Linear Programs by Graph Neural Network / つくば市における予約制乗合タクシーの配車スケジューリング作成 / マイクログリッドにおける災害対策を考慮した最適化シミュレーション / 大学入試における屋内連絡員の人員配置最適化ツール開発 / 実運用を考慮した予約制乗合タクシーの配車スケジューリング作成</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>都市・地域政策 ; 社会政策・福祉 ; オペレーションズリサーチ ; 機械学習 ; スポーツデータ分析 ; 災害・防災研究 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 災害社会学 ; 防災政策 ; リスク評価</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>都市・地域政策
-社会政策・福祉
+          <t>数理情報学 ; 数学基礎・応用数学 ; 社会システム工学・安全システム ; 計算科学 ; 都市・地域政策 ; オペレーションズリサーチ ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 学習分析 ; 物流最適化</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>数理情報学
+数学基礎・応用数学
+社会システム工学・安全システム
+計算科学
+数理最適化
+数理計画
+オペレーションズ・リサーチ
+サービス工学
+都市・地域政策
 オペレーションズリサーチ
-機械学習
-スポーツデータ分析
-災害・防災研究
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
@@ -1137,27 +1199,35 @@
 地域政策
 土地利用
 公共政策評価
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
-数理最適化
 組合せ最適化
 計画・スケジューリング
-統計的学習
-予測モデリング
-表現学習
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
-災害社会学
-防災政策
-リスク評価</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ロード・プライシング政策を考慮したNLSUEモデルとその解法の提案 / 未達率指標を用いた生産計画手法のSC能力設計への応用の研究 / 予約制乗合タクシーのルート最適化 / スマートキャンパスバス運行計画 / 救急医療サービスの効率化に向けた患者の医療機関割り当てに関するオフラインアルゴリズムの開発 / 一般消費財業界における未達率指標を用いた生産計画手法のSC能力設計への応用の研究 / 多死社会における在宅看取りに関する一考察 －茨城県の医療・介護に関する地域分析と実際の看取りをふまえて－ / バックトゥバック数を考慮したNBAの2018-2019シーズンスケジュールの作成 / 健康診断センターの勤務表作成におけるスケジューリング問題 / メタヒューリスティクスを用いた予約制乗合タクシーの配車スケジュール作成 / 乗客満足度を考慮した乗合タクシーの路線最適化モデル / ファストフード店の勤務スケジュールの作成 / リーマン多様体上の統合解析関数最適化 / 社会工学学位プログラムにおける修論発表会のスケジューリングについて / Traveling umpire problem におけるチーム間の公平性が高い解の探求 / 多要素ランキング法の上で正確性と多様性のトレードオフを考慮したモデルによる推薦システム / A Modification of Representing Linear Programs by Graph Neural Network / つくば市における予約制乗合タクシーの配車スケジューリング作成 / マイクログリッドにおける災害対策を考慮した最適化シミュレーション / 大学入試における屋内連絡員の人員配置最適化ツール開発 / 実運用を考慮した予約制乗合タクシーの配車スケジューリング作成
+学習分析
+物流最適化</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ロード・プライシング政策を考慮したNLSUEモデルとその解法の提案
+未達率指標を用いた生産計画手法のSC能力設計への応用の研究
+予約制乗合タクシーのルート最適化
+スマートキャンパスバス運行計画
+救急医療サービスの効率化に向けた患者の医療機関割り当てに関するオフラインアルゴリズムの開発
+一般消費財業界における未達率指標を用いた生産計画手法のSC能力設計への応用の研究
+多死社会における在宅看取りに関する一考察 －茨城県の医療・介護に関する地域分析と実際の看取りをふまえて－
+バックトゥバック数を考慮したNBAの2018-2019シーズンスケジュールの作成
+健康診断センターの勤務表作成におけるスケジューリング問題
+メタヒューリスティクスを用いた予約制乗合タクシーの配車スケジュール作成
+乗客満足度を考慮した乗合タクシーの路線最適化モデル
+ファストフード店の勤務スケジュールの作成
+リーマン多様体上の統合解析関数最適化
+社会工学学位プログラムにおける修論発表会のスケジューリングについて
+Traveling umpire problem におけるチーム間の公平性が高い解の探求
+多要素ランキング法の上で正確性と多様性のトレードオフを考慮したモデルによる推薦システム
+A Modification of Representing Linear Programs by Graph Neural Network
+つくば市における予約制乗合タクシーの配車スケジューリング作成
+マイクログリッドにおける災害対策を考慮した最適化シミュレーション
+大学入試における屋内連絡員の人員配置最適化ツール開発
+実運用を考慮した予約制乗合タクシーの配車スケジューリング作成
 リーマン多様体上の制約付き最適化問題に対する汎用アルゴリズムの理論と実装
 リーマン多様体上の最適化理論に基づく新たなデータコラボレーション手法の開発
 ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発
@@ -1227,6 +1297,10 @@
 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学
 高次元データの理論と方法論の総合的研究
 高次Aggregation Operatorの開発とクラスタリングモデルへの適用
+統計科学
+ソフトコンピューティング
+データマイニング
+多次元データ解析
 Simultaneous visualization method for mixed HDLSS data and its application for education
 Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design
 Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey
@@ -1260,32 +1334,45 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Simultaneous visualization method for mixed HDLSS data and its application for education / Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design / Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey / Difference on Evaluation Scores Considering Image Descriptions for Autocoding / ファジィクラスタリングの信頼度について / Hierarchical Support Vector Machine based Classifier for Autocoding / Fuzzy Cluster-Scaled Principal Component Analysis for Mixed Data and Its Application of Educational Effect based on Device Selection / A Fuzzy Cluster-Scaled Principal Component Analysis for Mixed High-Dimension and Low-Sample Size Data / Principal component analysis for mixed high-dimension low-sample size data based on fuzzy-cluster scale / Improvement of Training Data for Autocoding on "The National Survey of Family Income, Consumption and Wealth" and "The Family Income and Expenditure Survey" / Fuzzy Clustering based Autocoding Methods for Family Income and Expenditure Surveys / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding / Fuzzy Clustering based Classifier for Extraction of Individualities from High Dimension Low Sample Size Data / Individuality-based Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding / Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results / Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling / Cluster-based Analysis for Discrimination of Individuality （招待講演） / クラスター尺度に基づくデータ間差異の検出と市場データへの応用 / ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 / Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Clustering and Multidimensional Scaling for Individual Difference Extraction / 多次元尺度法による計算効率を考慮したディープラーニング手法 / Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means / 区間組成データに対する重み付き回帰分析</t>
+          <t>統計科学 / ソフトコンピューティング</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>統計科学 / ソフトコンピューティング / データマイニング / 多次元データ解析</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Simultaneous visualization method for mixed HDLSS data and its application for education / Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design / Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey / Difference on Evaluation Scores Considering Image Descriptions for Autocoding / ファジィクラスタリングの信頼度について / Hierarchical Support Vector Machine based Classifier for Autocoding / Fuzzy Cluster-Scaled Principal Component Analysis for Mixed Data and Its Application of Educational Effect based on Device Selection / A Fuzzy Cluster-Scaled Principal Component Analysis for Mixed High-Dimension and Low-Sample Size Data / Principal component analysis for mixed high-dimension low-sample size data based on fuzzy-cluster scale / Improvement of Training Data for Autocoding on "The National Survey of Family Income, Consumption and Wealth" and "The Family Income and Expenditure Survey" / Fuzzy Clustering based Autocoding Methods for Family Income and Expenditure Surveys / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding / Fuzzy Clustering based Classifier for Extraction of Individualities from High Dimension Low Sample Size Data / Individuality-based Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results / Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling / Cluster-based Analysis for Discrimination of Individuality （招待講演） / クラスター尺度に基づくデータ間差異の検出と市場データへの応用 / ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 / Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Clustering and Multidimensional Scaling for Individual Difference Extraction / 多次元尺度法による計算効率を考慮したディープラーニング手法 / Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means / 区間組成データに対する重み付き回帰分析</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>TLPCMの評価および欠損値処理手法 / 区間組成データに対する 回帰分析 / 歌詞テキストデータの感情分類 / 区間データに対するPCA手法の提案と従来法との比較 / ファジィクラスタリングを用いた欠損値補完法について / T-normを用いたクラスター尺度による顧客分類法</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 都市・地域政策 ; オペレーションズリサーチ ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
+          <t>統計科学 ; ソフトコンピューティング ; 労働経済・就職マッチング ; 都市・地域政策 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 公共政策・社会工学 ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 行政データ分析 ; センサデータ解析 ; 社会ネットワーク分析 ; 計算社会科学</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>統計科学
+ソフトコンピューティング
+データマイニング
+多次元データ解析
+労働経済・就職マッチング
 都市・地域政策
-オペレーションズリサーチ
 政策評価・計量分析
+医療・ヘルスデータ
 公共政策・社会工学
-経済・ファイナンス
 AI・データサイエンス
 労働経済
 人的資本
@@ -1295,18 +1382,28 @@
 地域政策
 土地利用
 公共政策評価
-数理最適化
-組合せ最適化
-計画・スケジューリング
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>TLPCMの評価および欠損値処理手法 / 区間組成データに対する 回帰分析 / 歌詞テキストデータの感情分類 / 区間データに対するPCA手法の提案と従来法との比較 / ファジィクラスタリングを用いた欠損値補完法について / T-normを用いたクラスター尺度による顧客分類法
+実証分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+行政データ分析
+センサデータ解析
+社会ネットワーク分析
+計算社会科学</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>TLPCMの評価および欠損値処理手法
+区間組成データに対する 回帰分析
+歌詞テキストデータの感情分類
+区間データに対するPCA手法の提案と従来法との比較
+ファジィクラスタリングを用いた欠損値補完法について
+T-normを用いたクラスター尺度による顧客分類法
 人工知能に基づく非線形高次元小標本データ解析とその社会的応用
 ３元型時系列高次元小標本データの解析とその社会的応用
 高次計量による高次元小標本型ビックデータ解析とその社会的応用
@@ -1382,6 +1479,14 @@
 乳幼児の活動量を測定するウェアラブル機器の開発
 乳幼児の活動量を測定するウェアラブルデバイスの開発
 サイバー社会ネットワークにおける噂の伝播の検出と制御
+数理物理・物性基礎
+ウェブ情報学・サービス情報学
+経済物理学
+ネットワーク科学
+社会物理学
+計算社会科学
+ウェブサイエンス
+ビッグデータ
 Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis
 コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析
 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析
@@ -1416,58 +1521,58 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>数理物理・物性基礎 / ウェブ情報学・サービス情報学</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>経済物理学 / ネットワーク科学 / 社会物理学 / 計算社会科学 / ウェブサイエンス / ビッグデータ</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis / コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 / Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan / Quantifying Collective Emotions: Japan’s Societal Trends Through Enhanced Sentiment Index Using POMS2 and SNS / Quantifying collective attention and fan engagement: a case study of the Japanese professional baseball league / News coverage of older drivers' fatal car crashes: is it over-represented? / Burstiness of human physical activities and their characterisation / 12-year observation of tweets about rubella in Japan: A retrospective infodemiology study / A two-phase model of collective memory decay with a dynamical switching point / SNSデータを用いた情報拡散シミュレーション / SNSにおける情報伝播ネットワークの構造 / Music Roles Affect the Selection of Consumption Means: A Questionnaire Survey of People’s Expectations for Music and Exploratory Factor Analysis / Dataset of identified scholars mentioned in acknowledgement statements / Classification of endogenous and exogenous bursts in collective emotions based on Weibo comments during COVID-19 / 日本におけるオンライン・ハラスメントの現状と対策：Twitterでの女性記者のツイート「炎上」を例に / 日本における自治体報道発表のCOVID-19発生状況を用いた感染者遷移状況の記録と可視化 / Simulation of information spreading on Twitter concerning radiation after the Fukushima nuclear power plant accident / 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― / サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して / Fake news propagates differently from real news even at early stages of spreading / 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 / Identifying long-term periodic cycles and memories of collective emotion in online social media / Correlations and fluctuations in the word sets of collective emotions / Configuration model for correlation matrices preserving the node strength</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>高齢運転者に関する報道とウェブ上の世論の可視化 / SNSから抽出した感情と実社会の関連性に関する研究 / Wikipedia閲覧数を用いた集合的記憶の減衰モデル / 保育現場への顔認証システム導入と運用の実証研究 / The identification of acknowledged scholars and their interdisciplinarity / Empirical studies on user-generated content and behavior of Southeast Asia community in Reddit / 日本プロ野球における集合的熱狂とファンの関与 / 仲値決定時近傍における板情報の非対称性の定量化 / 福島原発事故後のSNSにおける情報拡散シミュレーション / インターネットテレビにおけるコンテンツカテゴリ間の視聴数流動予測 / SNSを用いた新型コロナ禍における日本の空気感分析 / ソーシャルメディアを通した日本の高齢運転者に対する言論の定量化 / シラバスのテキストマイニングによる学生の主体性を育む科目の研究 / Wikipedia閲覧数を用いた集合的記憶の想起</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>保険・金融行動 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>保険・金融行動
-都市・地域政策
-GIS・空間分析
+          <t>数理物理・物性基礎 ; ウェブ情報学・サービス情報学 ; 社会政策・福祉 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 会計・ファイナンス ; テキスト分析・NLP ; 医療・ヘルスデータ ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 社会ネットワーク分析 ; 計算社会科学 ; 行政データ分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>数理物理・物性基礎
+ウェブ情報学・サービス情報学
+経済物理学
+ネットワーク科学
+社会物理学
+計算社会科学
+ウェブサイエンス
+ビッグデータ
 社会政策・福祉
-建築・空間設計
 ネットワーク・グラフ理論
 災害・防災研究
 政策評価・計量分析
+会計・ファイナンス
+テキスト分析・NLP
+医療・ヘルスデータ
 公共政策・社会工学
-経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
-都市経済
-地域政策
-土地利用
-公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
 社会福祉政策
 地域福祉
 子育て支援
 非営利組織論
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
 グラフ理論
 離散数学
 ネットワーク最適化
@@ -1478,12 +1583,40 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>高齢運転者に関する報道とウェブ上の世論の可視化 / SNSから抽出した感情と実社会の関連性に関する研究 / Wikipedia閲覧数を用いた集合的記憶の減衰モデル / 保育現場への顔認証システム導入と運用の実証研究 / The identification of acknowledged scholars and their interdisciplinarity / Empirical studies on user-generated content and behavior of Southeast Asia community in Reddit / 日本プロ野球における集合的熱狂とファンの関与 / 仲値決定時近傍における板情報の非対称性の定量化 / 福島原発事故後のSNSにおける情報拡散シミュレーション / インターネットテレビにおけるコンテンツカテゴリ間の視聴数流動予測 / SNSを用いた新型コロナ禍における日本の空気感分析 / ソーシャルメディアを通した日本の高齢運転者に対する言論の定量化 / シラバスのテキストマイニングによる学生の主体性を育む科目の研究 / Wikipedia閲覧数を用いた集合的記憶の想起
+実証分析
+会計データ分析
+財務会計
+管理会計
+会計情報システム
+テキストマイニング
+自然言語処理
+感情分析
+社会データ分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+社会ネットワーク分析
+行政データ分析
+学習分析</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>高齢運転者に関する報道とウェブ上の世論の可視化
+SNSから抽出した感情と実社会の関連性に関する研究
+Wikipedia閲覧数を用いた集合的記憶の減衰モデル
+保育現場への顔認証システム導入と運用の実証研究
+The identification of acknowledged scholars and their interdisciplinarity
+Empirical studies on user-generated content and behavior of Southeast Asia community in Reddit
+日本プロ野球における集合的熱狂とファンの関与
+仲値決定時近傍における板情報の非対称性の定量化
+福島原発事故後のSNSにおける情報拡散シミュレーション
+インターネットテレビにおけるコンテンツカテゴリ間の視聴数流動予測
+SNSを用いた新型コロナ禍における日本の空気感分析
+ソーシャルメディアを通した日本の高齢運転者に対する言論の定量化
+シラバスのテキストマイニングによる学生の主体性を育む科目の研究
+Wikipedia閲覧数を用いた集合的記憶の想起
 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究
 アカウンティング・インフォマティクス（会計情報科学）の基盤研究
 学際的エビデンスに基づく超高齢社会のモビリティ支援とアクティブ・エイジングの推進
@@ -1554,6 +1687,9 @@
 経済環境の激変と中小企業の役割
 縮小経済のもとでの中小企業と企業家活動
 中小企業の資金調達環境と政策のあり方
+経済政策
+財政・公共経済
+経済統計
 Number of positive lymph nodes and lymphatic invasion are significant prognostic factors after pancreaticoduodenectomy for distal cholangiocarcinoma.
 開業と廃業
 中小企業の知的財産
@@ -1588,54 +1724,52 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>経済政策 / 財政・公共経済 / 経済統計</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Number of positive lymph nodes and lymphatic invasion are significant prognostic factors after pancreaticoduodenectomy for distal cholangiocarcinoma. / 開業と廃業 / 中小企業の知的財産 / Bankruptcy dynamics in Japan / 開業のダイナミクス－開業研究の展望と法人設立登記にもとづく実証分析－ / Which firms exit and why? An analysis of small firm exits in Japan / Video game demand in Japan: a household data analysis / 新企業の人材確保--事業所・企業統計調査と新企業調査の個票分析 / SME policy, financial structure and firm growth: Evidence from japan / Does the creative business promotion law enhance SMEs' capital investments? Evidence from a panel dataset of unlisted SMEs in Japan / Potential entrepreneurship in Japan / Consumption-leisure preference structure: A new explanation of the Evans-Jovanovic results for entrepreneurial choice / Consumption-Leisure Preference Structure: A New Explanation of the Evans-Jovanovic Results for Entrepreneurial Choice(Erratum, 24, 423-427, 2005) / Does the Creative Business Promotion Law Enhance SMEs' Capital Investment? Evidence from a Panel Dataset of Unlisted SMEs in Japan / The IT revolution and productivity growth in Japan / Small Business Owner-Managers as Latent Informal Investors in Japan: Evidence from a Country with a Bank-based Financial System / 企業家の労働時間－実証分析－ / 景況感とアンケート調査－変化方向と水準は異曲同工か？－ / Productivity and Entrepreneurial Characteristics in New Japanese Firms / Who Succeeds as an Entrepreneur? An Analysis of the Post-Entry Performance of New Firms in Japan / 少子・高齢化と日本の消費フロンティア / SNA統計を用いた「トービンのｑ」の計測結果の違いについて / 潜在的開業者の実証分析 / 起業の意思決定における所得・余暇の代替と流動性制約 / SNA統計を用いた民間法人企業ベースの「トービンのｑ」と投資関数</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>中小企業における労働力の質的不足の影響要因 / 企業の情報開示と株価</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 保険・金融行動 ; 意思決定分析 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-保険・金融行動
-意思決定分析
-政策評価・計量分析
+          <t>経済政策 ; 財政・公共経済 ; 経済統計 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 経営工学 ; 行政データ分析 ; 政策評価 ; マーケティング分析</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>経済政策
+財政・公共経済
+経済統計
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
-環境・エネルギー
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
-行動意思決定
-実験・行動分析
-ナッジ
-意思決定支援
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+経営工学
+行政データ分析
 政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>中小企業における労働力の質的不足の影響要因 / 企業の情報開示と株価
+マーケティング分析</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>中小企業における労働力の質的不足の影響要因
+企業の情報開示と株価
 中小企業の雇用・技術と日本経済の再生
 経済環境の激変と中小企業の役割
 縮小経済のもとでの中小企業と企業家活動
@@ -1701,7 +1835,64 @@
 混合整数最適化を用いた制約付き変数選択による高精度パラメータ推定
 ノンパラメトリック推定に基づくテスト理論モデルの研究
 カーネル法と制御ポリシーを用いた中長期的投資戦略最適化
-取引コストを考慮した多期間ポートフォリオの最適化</t>
+取引コストを考慮した多期間ポートフォリオの最適化
+社会システム工学・安全システム
+数理情報学
+統計科学
+知能情報学
+数理最適化
+金融工学
+機械学習
+Robust personalized pricing under uncertainty of purchase probabilities
+Privacy-preserving recommender system using the data collaboration analysis for distributed datasets
+最適モデル多分木による価格需要曲線の推定
+Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times
+DC algorithm for estimation of sparse Gaussian graphical models
+Robust Portfolio Optimization for Recommender Systems Considering Uncertainty of Estimated Statistics
+Fast Solution to the Fair Ranking Problem Using the Sinkhorn Algorithm
+Mixed-Integer Linear Optimization Formulations for Feature Subset Selection in Kernel SVM Classification
+Robust portfolio optimization model for electronic coupon allocation
+混合整数最適化による相続工程の長期化リスク採点システム
+ECサイトにおける利用者属性データの欠損値補完
+Prescriptive price optimization using optimal regression trees
+構造的正則化処方分析による旅行パックの価格最適化
+Predicting Online Item-Choice Behavior: A Shape-Restricted Regression Approach
+Cardinality-constrained distributionally robust portfolio optimization
+Cutting-plane algorithm for estimation of sparse Cox proportional hazards models
+Branch-and-bound algorithm for optimal sparse canonical correlation analysis
+Dynamic portfolio selection with linear control policies for coherent risk minimization
+Linear control policies for online vehicle relocation in shared mobility systems
+出産前後の情報検索の分析：数理最適化による検索日の確率分布推定
+ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析)
+Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization
+Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach
+Sparse Poisson regression via mixed-integer optimization
+時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析
+データコラボレーション解析における統合関数の最適化
+A Design Method of the Joint Venture Formation in EPC Projects
+形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待)
+サポートベクトルマシンとカーネル法 (特集 機械学習の手法と役割期待)
+Smoothness-constrained model for nonparametric item response theory
+ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成―
+LDPC符号に対するタブー探索法に基づく勾配降下ビット反転復号法
+A Resource Flow Based Multistage Dynamic Scheduling Method for the State-Dependent Work
+数理最適化による学生のプロジェクト配属の決定
+整数最適化復号法の性能評価
+多重共線性を考慮した回帰式の変数選択問題の定式化
+A Simulation-Based Dynamic Scheduling Method in Project Cost Estimation Process
+キークレーン間干渉を考慮したコンテナ事前配列問題
+混合整数最適化による階層的変数選択を用いた店舗選択要因の分析
+ZIMPL言語とSCIPによる数理最適化
+複数の販売チャネルでの購入を促進するための商品推薦手法
+Mathematical Optimization Models for Nonparametric Item Response Theory
+時系列モデルによる商品販促効果の分析
+整数計画法による変数選択を用いた店舗選択モデル
+競争入札戦略と決定理論モデル
+アドネットワークにおけるバナー広告入札戦略決定フレームワークの有効性の検証
+確率計画法の理論と応用
+ECサイトの商品特性を考慮した2次元確率表による購買予測
+A Heuristic Bidding Price Decision Algorithm Based on Cost Estimation Accuracy under Limited Engineering Man-Hours in EPC Projects
+混合整数2次錐計画法による回帰式の変数選択</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1709,62 +1900,142 @@
           <t>大規模な両面市場に対する公平性を考慮した取引促進施策の包括的最適化 / 混合整数最適化による次元縮約法の最良スパース推定 / 混合整数最適化を用いた制約付き変数選択による高精度パラメータ推定 / ノンパラメトリック推定に基づくテスト理論モデルの研究 / カーネル法と制御ポリシーを用いた中長期的投資戦略最適化 / 取引コストを考慮した多期間ポートフォリオの最適化</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>社会システム工学・安全システム / 数理情報学 / 統計科学 / 知能情報学</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>数理最適化 / 金融工学 / 機械学習</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Robust personalized pricing under uncertainty of purchase probabilities / Privacy-preserving recommender system using the data collaboration analysis for distributed datasets / 最適モデル多分木による価格需要曲線の推定 / Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times / DC algorithm for estimation of sparse Gaussian graphical models / Robust Portfolio Optimization for Recommender Systems Considering Uncertainty of Estimated Statistics / Fast Solution to the Fair Ranking Problem Using the Sinkhorn Algorithm / Mixed-Integer Linear Optimization Formulations for Feature Subset Selection in Kernel SVM Classification / Robust portfolio optimization model for electronic coupon allocation / 混合整数最適化による相続工程の長期化リスク採点システム / ECサイトにおける利用者属性データの欠損値補完 / Prescriptive price optimization using optimal regression trees / 構造的正則化処方分析による旅行パックの価格最適化 / Predicting Online Item-Choice Behavior: A Shape-Restricted Regression Approach / Cardinality-constrained distributionally robust portfolio optimization / Cutting-plane algorithm for estimation of sparse Cox proportional hazards models / Branch-and-bound algorithm for optimal sparse canonical correlation analysis / Dynamic portfolio selection with linear control policies for coherent risk minimization / Linear control policies for online vehicle relocation in shared mobility systems / 出産前後の情報検索の分析：数理最適化による検索日の確率分布推定 / ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析) / Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach / Sparse Poisson regression via mixed-integer optimization / 時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析 / データコラボレーション解析における統合関数の最適化 / A Design Method of the Joint Venture Formation in EPC Projects / 形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待) / サポートベクトルマシンとカーネル法 (特集 機械学習の手法と役割期待) / Smoothness-constrained model for nonparametric item response theory / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― / LDPC符号に対するタブー探索法に基づく勾配降下ビット反転復号法 / A Resource Flow Based Multistage Dynamic Scheduling Method for the State-Dependent Work / 数理最適化による学生のプロジェクト配属の決定 / 整数最適化復号法の性能評価 / 多重共線性を考慮した回帰式の変数選択問題の定式化 / A Simulation-Based Dynamic Scheduling Method in Project Cost Estimation Process / キークレーン間干渉を考慮したコンテナ事前配列問題 / 混合整数最適化による階層的変数選択を用いた店舗選択要因の分析 / ZIMPL言語とSCIPによる数理最適化 / 複数の販売チャネルでの購入を促進するための商品推薦手法 / Mathematical Optimization Models for Nonparametric Item Response Theory / 時系列モデルによる商品販促効果の分析 / 整数計画法による変数選択を用いた店舗選択モデル / 競争入札戦略と決定理論モデル / アドネットワークにおけるバナー広告入札戦略決定フレームワークの有効性の検証 / 確率計画法の理論と応用 / ECサイトの商品特性を考慮した2次元確率表による購買予測 / A Heuristic Bidding Price Decision Algorithm Based on Cost Estimation Accuracy under Limited Engineering Man-Hours in EPC Projects / 混合整数2次錐計画法による回帰式の変数選択</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>データ統合解析におけるアンカーデータ作成方法の提案 / 切除平面法による比例ハザードモデルの特徴選択 / 線形制御政策によるロング・ショートポートフォリオ最適化 / データコラボレーション解析における統合関数最適化問題の定式化と解法 / 多値型ノンパラメトリック項目反応理論の形状制約推定モデル / 最適化手法を用いた事例・変数統合型の欠損値補完 / 縮小推定を用いた平均・分散モデルによる推薦システム / 多重共線性を考慮した変数選択問題に対する切除平面法 / 2値分類の採点システムに対するbAUC最大化 / ロバスト平均・分散モデルを用いた推薦アルゴリズム / 確率制約付き最適化問題に対するDCアルゴリズム / シンクホーンアルゴリズムを用いた公平ランキング問題の高速求解 / 多重共線性を考慮した変数選択問題に対する高速厳密解法 / 深層学習を用いた巡回セールスマン問題の高速求解 / 強化学習を用いた競争入札戦略 / 予測評価値の不確実性を考慮した推薦商品集合の分布的ロバスト最適化 / 複数クーポンの効果推定と配布最適化 / コールセンターにおける会話データの分析 / 出産・子育てQ&amp;Aサイトにおける検索クエリの予測と分析 / 疎なWEB解答データの多次元項目反応理論分析</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 保険・金融行動 ; オペレーションズリサーチ ; 機械学習 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>家族・人口政策
+          <t>社会システム工学・安全システム ; 数理情報学 ; 統計科学 ; 知能情報学 ; 保険・金融行動 ; オペレーションズリサーチ ; 機械学習 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 物流最適化 ; 最適化</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>社会システム工学・安全システム
+数理情報学
+統計科学
+知能情報学
+数理最適化
+金融工学
+機械学習
 保険・金融行動
 オペレーションズリサーチ
-機械学習
-政策評価・計量分析
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 行動ファイナンス
 金融市場分析
 ESG投資
 企業財務
-数理最適化
 組合せ最適化
 計画・スケジューリング
 統計的学習
 予測モデリング
 表現学習
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>データ統合解析におけるアンカーデータ作成方法の提案 / 切除平面法による比例ハザードモデルの特徴選択 / 線形制御政策によるロング・ショートポートフォリオ最適化 / データコラボレーション解析における統合関数最適化問題の定式化と解法 / 多値型ノンパラメトリック項目反応理論の形状制約推定モデル / 最適化手法を用いた事例・変数統合型の欠損値補完 / 縮小推定を用いた平均・分散モデルによる推薦システム / 多重共線性を考慮した変数選択問題に対する切除平面法 / 2値分類の採点システムに対するbAUC最大化 / ロバスト平均・分散モデルを用いた推薦アルゴリズム / 確率制約付き最適化問題に対するDCアルゴリズム / シンクホーンアルゴリズムを用いた公平ランキング問題の高速求解 / 多重共線性を考慮した変数選択問題に対する高速厳密解法 / 深層学習を用いた巡回セールスマン問題の高速求解 / 強化学習を用いた競争入札戦略 / 予測評価値の不確実性を考慮した推薦商品集合の分布的ロバスト最適化 / 複数クーポンの効果推定と配布最適化 / コールセンターにおける会話データの分析 / 出産・子育てQ&amp;Aサイトにおける検索クエリの予測と分析 / 疎なWEB解答データの多次元項目反応理論分析
+物流最適化
+最適化</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>データ統合解析におけるアンカーデータ作成方法の提案
+切除平面法による比例ハザードモデルの特徴選択
+線形制御政策によるロング・ショートポートフォリオ最適化
+データコラボレーション解析における統合関数最適化問題の定式化と解法
+多値型ノンパラメトリック項目反応理論の形状制約推定モデル
+最適化手法を用いた事例・変数統合型の欠損値補完
+縮小推定を用いた平均・分散モデルによる推薦システム
+多重共線性を考慮した変数選択問題に対する切除平面法
+2値分類の採点システムに対するbAUC最大化
+ロバスト平均・分散モデルを用いた推薦アルゴリズム
+確率制約付き最適化問題に対するDCアルゴリズム
+シンクホーンアルゴリズムを用いた公平ランキング問題の高速求解
+多重共線性を考慮した変数選択問題に対する高速厳密解法
+深層学習を用いた巡回セールスマン問題の高速求解
+強化学習を用いた競争入札戦略
+予測評価値の不確実性を考慮した推薦商品集合の分布的ロバスト最適化
+複数クーポンの効果推定と配布最適化
+コールセンターにおける会話データの分析
+出産・子育てQ&amp;Aサイトにおける検索クエリの予測と分析
+疎なWEB解答データの多次元項目反応理論分析
 大規模な両面市場に対する公平性を考慮した取引促進施策の包括的最適化
 混合整数最適化による次元縮約法の最良スパース推定
 混合整数最適化を用いた制約付き変数選択による高精度パラメータ推定
 ノンパラメトリック推定に基づくテスト理論モデルの研究
 カーネル法と制御ポリシーを用いた中長期的投資戦略最適化
-取引コストを考慮した多期間ポートフォリオの最適化</t>
+取引コストを考慮した多期間ポートフォリオの最適化
+Robust personalized pricing under uncertainty of purchase probabilities
+Privacy-preserving recommender system using the data collaboration analysis for distributed datasets
+最適モデル多分木による価格需要曲線の推定
+Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times
+DC algorithm for estimation of sparse Gaussian graphical models
+Robust Portfolio Optimization for Recommender Systems Considering Uncertainty of Estimated Statistics
+Fast Solution to the Fair Ranking Problem Using the Sinkhorn Algorithm
+Mixed-Integer Linear Optimization Formulations for Feature Subset Selection in Kernel SVM Classification
+Robust portfolio optimization model for electronic coupon allocation
+混合整数最適化による相続工程の長期化リスク採点システム
+ECサイトにおける利用者属性データの欠損値補完
+Prescriptive price optimization using optimal regression trees
+構造的正則化処方分析による旅行パックの価格最適化
+Predicting Online Item-Choice Behavior: A Shape-Restricted Regression Approach
+Cardinality-constrained distributionally robust portfolio optimization
+Cutting-plane algorithm for estimation of sparse Cox proportional hazards models
+Branch-and-bound algorithm for optimal sparse canonical correlation analysis
+Dynamic portfolio selection with linear control policies for coherent risk minimization
+Linear control policies for online vehicle relocation in shared mobility systems
+出産前後の情報検索の分析：数理最適化による検索日の確率分布推定
+ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析)
+Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization
+Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach
+Sparse Poisson regression via mixed-integer optimization
+時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析
+データコラボレーション解析における統合関数の最適化
+A Design Method of the Joint Venture Formation in EPC Projects
+形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待)
+サポートベクトルマシンとカーネル法 (特集 機械学習の手法と役割期待)
+Smoothness-constrained model for nonparametric item response theory
+ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成―
+LDPC符号に対するタブー探索法に基づく勾配降下ビット反転復号法
+A Resource Flow Based Multistage Dynamic Scheduling Method for the State-Dependent Work
+数理最適化による学生のプロジェクト配属の決定
+整数最適化復号法の性能評価
+多重共線性を考慮した回帰式の変数選択問題の定式化
+A Simulation-Based Dynamic Scheduling Method in Project Cost Estimation Process
+キークレーン間干渉を考慮したコンテナ事前配列問題
+混合整数最適化による階層的変数選択を用いた店舗選択要因の分析
+ZIMPL言語とSCIPによる数理最適化
+複数の販売チャネルでの購入を促進するための商品推薦手法
+Mathematical Optimization Models for Nonparametric Item Response Theory
+時系列モデルによる商品販促効果の分析
+整数計画法による変数選択を用いた店舗選択モデル
+競争入札戦略と決定理論モデル
+アドネットワークにおけるバナー広告入札戦略決定フレームワークの有効性の検証
+確率計画法の理論と応用
+ECサイトの商品特性を考慮した2次元確率表による購買予測
+A Heuristic Bidding Price Decision Algorithm Based on Cost Estimation Accuracy under Limited Engineering Man-Hours in EPC Projects
+混合整数2次錐計画法による回帰式の変数選択</t>
         </is>
       </c>
     </row>
@@ -1803,6 +2074,16 @@
 文書生成AIサービス工学に関する研究
 文書生成AIの企業内利活用における最適化の研究
 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究
+会計学
+ウェブ情報学・サービス情報学
+社会システム工学・安全システム
+経営学
+商学
+ビジネスインテリジェンス
+会計情報科学
+サービス工学
+ソーシャル・データサイエンス
+社会工学
 Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment
 Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients
 Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach
@@ -1831,58 +2112,61 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>KPI工学教育研究の推進 / 包摂的コミュニティプラットフォームの構築 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 統合型ヘルスケアシステムの構築 / 文書生成AIサービス工学に関する研究 / 文書生成AIの企業内利活用における最適化の研究 / 統合型ヘルスケアシステムの構築 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 包摂的コミュニティプラットフォームの構築 / 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究</t>
+          <t>KPI工学教育研究の推進 / 包摂的コミュニティプラットフォームの構築 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 統合型ヘルスケアシステムの構築 / 文書生成AIサービス工学に関する研究 / 文書生成AIの企業内利活用における最適化の研究 / 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment / Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients / Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach / Estimation of conditional average treatment effects on distributed confidential data / Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support / Data collaboration for causal inference from limited medical testing and medication data / Generating Synthetic Journal-Entry Data Using Variational Autoencoder / Anomaly Detection in Double-entry Bookkeeping Data by Federated Learning System with Non-model Sharing Approach / Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data / An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises / Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 / pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis / 会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 / Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data / 分散機密データを想定した 処置効果の推定手法の開発 / 英文学術雑誌における近年の簿記研究 / Collaborative causal inference on distributed data / Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach / Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation / Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data / Knowledge sharing among coaches: expert power and social cognitive theory perspectives / Positive effect of proactive personality on customer orientation in service context / Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data / Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis</t>
+          <t>会計学 / ウェブ情報学・サービス情報学 / 社会システム工学・安全システム / 経営学 / 商学</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>ビジネスインテリジェンス / 会計情報科学 / サービス工学 / ソーシャル・データサイエンス / 社会工学</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment / Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients / Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach / Estimation of conditional average treatment effects on distributed confidential data / Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support / Data collaboration for causal inference from limited medical testing and medication data / Generating Synthetic Journal-Entry Data Using Variational Autoencoder / Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data / An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises / Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 / pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis / 会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 / Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data / 分散機密データを想定した 処置効果の推定手法の開発 / 英文学術雑誌における近年の簿記研究 / Collaborative causal inference on distributed data / Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach / Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation / Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data / Knowledge sharing among coaches: expert power and social cognitive theory perspectives / Positive effect of proactive personality on customer orientation in service context / Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data / Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>個人の能動的先手行動がチームに与える影響に関する時系列分析 / 若者のエシカル消費の阻害要因に関する実証分析 / チーム全体の能動的先手行動を強化するチーム構成の実証分析 / 中小サービス企業における業績管理会計の効果的な実践に関する実証分析 / 地域健康政策のためのベイジアンネットワークを用いた推論モデルの研究 / シングルサイロを想定した解釈可能なデータコラボレーション解析の応用研究 / 傾向スコアを用いた特定健診・特定保健指導の効果検証 / 価値共創を活性化する店員の音声模倣スキルに関する実験的研究 / 糖尿病の予防政策のためのデータコラボレーション解析の応用可能性 / ベイジアンネットワークを用いたフレイルの発症予測モデリング：健康関心度の違いに着目して / マルチレベルモデルを用いたフレイルの地域および個人要因分析 / 糖尿病の因果構造の推定におけるLingamの応用可能性 / 営業部門の上司と部下の顧客意識が提案行動に与える影響 / 小売店の接客サービス中に生じる頷きの模倣に関する実験的研究 / データコラボレーション解析による地域中小企業の資金ニーズ予測 / NavigatorⅢの開発と実証分析 / 分散データに対する統合的クラスタリングの提案 / 営業チームにおける人事異動が能動的先手行動に与える影響 / 非接触呼吸識別技術によるコンサート観客の呼吸同期分析 / 若者の選挙投票に着目したアカウンタビリティの実験的研究 / 確率的潜在意味解析による擬人情報作成方法の提案 / 社会参加が主観的幸福感に及ぼす効果の疑似実験による検証 / GPSデータを用いた陸運の誤配送検知手法の提案 / 仕訳とビジネスプロセスの月次変化とキャッシュフローに関する研究 / 複式簿記の相互参照性情報を学習した業績予測モデルに関する研究 / 高齢者の運動習慣とメンタルヘルスとの関係の実証分析 / 中小企業の財務難予測モデルを解釈する反事実的説明手法の研究 / 非接触計測による生理指標を用いた患者のマルチモーダル感情認識の研究 / 孤独の選好と身体的・精神的健康状態との関係の実証分析 / 分散生存時間データに対するDC因果推論の拡張 / 能動的先手行動の形成プロセスについての縦断的研究 / 標準年限卒業予測における大学間転移学習の研究 / NavigatorIIIのパイロット企業における実証実験</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>保険・金融行動 ; 意思決定分析 ; 都市・地域政策 ; 社会政策・福祉 ; オペレーションズリサーチ ; 機械学習 ; 画像・視覚情報処理 ; ネットワーク・グラフ理論 ; スポーツデータ分析 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>保険・金融行動
-意思決定分析
-都市・地域政策
+          <t>会計学 ; ウェブ情報学・サービス情報学 ; 社会システム工学・安全システム ; 経営学 ; 商学 ; 社会政策・福祉 ; オペレーションズリサーチ ; 政策評価・計量分析 ; 会計・ファイナンス ; 医療・ヘルスデータ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 経営工学 ; 環境工学 ; 社会ネットワーク分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>会計学
+ウェブ情報学・サービス情報学
+社会システム工学・安全システム
+経営学
+商学
+ビジネスインテリジェンス
+会計情報科学
+サービス工学
+ソーシャル・データサイエンス
+社会工学
 社会政策・福祉
 オペレーションズリサーチ
-機械学習
-画像・視覚情報処理
-ネットワーク・グラフ理論
-スポーツデータ分析
 政策評価・計量分析
+会計・ファイナンス
+医療・ヘルスデータ
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
-環境・エネルギー
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
-行動意思決定
-実験・行動分析
-ナッジ
-意思決定支援
-都市経済
-地域政策
-土地利用
-公共政策評価
 社会福祉政策
 地域福祉
 子育て支援
@@ -1890,29 +2174,63 @@
 数理最適化
 組合せ最適化
 計画・スケジューリング
-統計的学習
-予測モデリング
-表現学習
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>個人の能動的先手行動がチームに与える影響に関する時系列分析 / 若者のエシカル消費の阻害要因に関する実証分析 / チーム全体の能動的先手行動を強化するチーム構成の実証分析 / 中小サービス企業における業績管理会計の効果的な実践に関する実証分析 / 地域健康政策のためのベイジアンネットワークを用いた推論モデルの研究 / シングルサイロを想定した解釈可能なデータコラボレーション解析の応用研究 / 傾向スコアを用いた特定健診・特定保健指導の効果検証 / 価値共創を活性化する店員の音声模倣スキルに関する実験的研究 / 糖尿病の予防政策のためのデータコラボレーション解析の応用可能性 / ベイジアンネットワークを用いたフレイルの発症予測モデリング：健康関心度の違いに着目して / マルチレベルモデルを用いたフレイルの地域および個人要因分析 / 糖尿病の因果構造の推定におけるLingamの応用可能性 / 営業部門の上司と部下の顧客意識が提案行動に与える影響 / 小売店の接客サービス中に生じる頷きの模倣に関する実験的研究 / データコラボレーション解析による地域中小企業の資金ニーズ予測 / NavigatorⅢの開発と実証分析 / 分散データに対する統合的クラスタリングの提案 / 営業チームにおける人事異動が能動的先手行動に与える影響 / 非接触呼吸識別技術によるコンサート観客の呼吸同期分析 / 若者の選挙投票に着目したアカウンタビリティの実験的研究 / 確率的潜在意味解析による擬人情報作成方法の提案 / 社会参加が主観的幸福感に及ぼす効果の疑似実験による検証 / GPSデータを用いた陸運の誤配送検知手法の提案 / 仕訳とビジネスプロセスの月次変化とキャッシュフローに関する研究 / 複式簿記の相互参照性情報を学習した業績予測モデルに関する研究 / 高齢者の運動習慣とメンタルヘルスとの関係の実証分析 / 中小企業の財務難予測モデルを解釈する反事実的説明手法の研究 / 非接触計測による生理指標を用いた患者のマルチモーダル感情認識の研究 / 孤独の選好と身体的・精神的健康状態との関係の実証分析 / 分散生存時間データに対するDC因果推論の拡張 / 能動的先手行動の形成プロセスについての縦断的研究 / 標準年限卒業予測における大学間転移学習の研究 / NavigatorIIIのパイロット企業における実証実験
+実証分析
+会計データ分析
+財務会計
+管理会計
+会計情報システム
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+経営工学
+環境工学
+社会ネットワーク分析
+学習分析</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>個人の能動的先手行動がチームに与える影響に関する時系列分析
+若者のエシカル消費の阻害要因に関する実証分析
+チーム全体の能動的先手行動を強化するチーム構成の実証分析
+中小サービス企業における業績管理会計の効果的な実践に関する実証分析
+地域健康政策のためのベイジアンネットワークを用いた推論モデルの研究
+シングルサイロを想定した解釈可能なデータコラボレーション解析の応用研究
+傾向スコアを用いた特定健診・特定保健指導の効果検証
+価値共創を活性化する店員の音声模倣スキルに関する実験的研究
+糖尿病の予防政策のためのデータコラボレーション解析の応用可能性
+ベイジアンネットワークを用いたフレイルの発症予測モデリング：健康関心度の違いに着目して
+マルチレベルモデルを用いたフレイルの地域および個人要因分析
+糖尿病の因果構造の推定におけるLingamの応用可能性
+営業部門の上司と部下の顧客意識が提案行動に与える影響
+小売店の接客サービス中に生じる頷きの模倣に関する実験的研究
+データコラボレーション解析による地域中小企業の資金ニーズ予測
+NavigatorⅢの開発と実証分析
+分散データに対する統合的クラスタリングの提案
+営業チームにおける人事異動が能動的先手行動に与える影響
+非接触呼吸識別技術によるコンサート観客の呼吸同期分析
+若者の選挙投票に着目したアカウンタビリティの実験的研究
+確率的潜在意味解析による擬人情報作成方法の提案
+社会参加が主観的幸福感に及ぼす効果の疑似実験による検証
+GPSデータを用いた陸運の誤配送検知手法の提案
+仕訳とビジネスプロセスの月次変化とキャッシュフローに関する研究
+複式簿記の相互参照性情報を学習した業績予測モデルに関する研究
+高齢者の運動習慣とメンタルヘルスとの関係の実証分析
+中小企業の財務難予測モデルを解釈する反事実的説明手法の研究
+非接触計測による生理指標を用いた患者のマルチモーダル感情認識の研究
+孤独の選好と身体的・精神的健康状態との関係の実証分析
+分散生存時間データに対するDC因果推論の拡張
+能動的先手行動の形成プロセスについての縦断的研究
+標準年限卒業予測における大学間転移学習の研究
+NavigatorIIIのパイロット企業における実証実験
 KPI工学教育研究の推進
 包摂的コミュニティプラットフォームの構築
 健康にやさしいまちづくりのための環境整備に係る実証事業
@@ -1994,72 +2312,54 @@
           <t>ESG、開示とパフォーマンス：ノンパラメトリック手法を用いて / CSRの実証研究：ノンパラメトリック推計アプローチ / 社会的責任活動の実証研究：企業のミクロ経済学的行動と政策分析</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Subjective probabilistic expectations, household air pollution, and health: Evidence from cooking fuel use patterns in West Bengal, India / Seemingly Unrelated Interventions: Environmental Management Systems in the Workplace and Energy Saving Practices at Home / Cooking Fuel Choices --Analysis of Socio-economic and Demographic Factors in Rural India-- / Another Bias Correction for Asymmetric Kernel Density Estimation with a Parametric Start / Functional-Coefficient Cointegration Models in the Presence of Deterministic Trends / Do Social Norms Matter to Energy Saving Behavior?: Endogenous Social and Correlated Effects / Testing Symmetry of Unknown Densities via Smoothing with the Generalized Gamma Kernels / Family of the Generalised Gamma Kernels: A Generator of Asymmetric Kernels for Nonnegative Data / Nonnegative Bias Reduction Methods for Density Estimation Using Asymmetric Kernels</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>交通ネットワークと都市の成長ー西日本における高速道路建設が地方都市に与えた影響ー / 中国における結婚が健康に及ぼす影響 / 日本の賃金分布に対する反実仮想的要因分解 / ESGに関するSNS上での評判と企業パフォーマンス / 駅の開業が大気汚染に与えた影響の分析</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 家族・人口政策 ; 保険・金融行動 ; 都市・地域政策 ; 交通・モビリティ ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-家族・人口政策
-保険・金融行動
-都市・地域政策
-交通・モビリティ
-ネットワーク・グラフ理論
+          <t>保険・金融行動 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; マーケティング分析 ; 社会ネットワーク分析 ; 経営工学</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>保険・金融行動
 政策評価・計量分析
 公共政策・社会工学
 経済・ファイナンス
-数理最適化・OR
-都市・空間・交通
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 行動ファイナンス
 金融市場分析
 ESG投資
 企業財務
-都市経済
-地域政策
-土地利用
-公共政策評価
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>交通ネットワークと都市の成長ー西日本における高速道路建設が地方都市に与えた影響ー / 中国における結婚が健康に及ぼす影響 / 日本の賃金分布に対する反実仮想的要因分解 / ESGに関するSNS上での評判と企業パフォーマンス / 駅の開業が大気汚染に与えた影響の分析
+実証分析
+マーケティング分析
+社会ネットワーク分析
+経営工学</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>交通ネットワークと都市の成長ー西日本における高速道路建設が地方都市に与えた影響ー
+中国における結婚が健康に及ぼす影響
+日本の賃金分布に対する反実仮想的要因分解
+ESGに関するSNS上での評判と企業パフォーマンス
+駅の開業が大気汚染に与えた影響の分析
 ESG、開示とパフォーマンス：ノンパラメトリック手法を用いて
 CSRの実証研究：ノンパラメトリック推計アプローチ
 社会的責任活動の実証研究：企業のミクロ経済学的行動と政策分析
@@ -2113,6 +2413,8 @@
 国家の規模とガバナンスの学際的分析
 情報コストゼロ社会における過剰懲罰とリスク軽減のための社会制度設計
 新しい肺移植制度の構築と評価：ドナー交換移植の可能性
+社会システム工学・安全システム
+社会的ジレンマ、資産市場実験
 検索連動型広告における循環的な入札額変動の発生機構の解明
 ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析
 Bubbles in Asset Markets and the Heterogeneity of Beliefs.
@@ -2146,40 +2448,45 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>検索連動型広告における循環的な入札額変動の発生機構の解明 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Bubbles in Asset Markets and the Heterogeneity of Beliefs. / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 / 進化ゲーム理論の進化 — マルチエージェントシミュレーション，実験室実験と，LLM の行動経済学— / 発話量と発話内容に基づく集団間のコミュニケーション円滑化システムの提案 / ソーシャルメディア上のアジェンダ設定がエコーチェンバーの発生に与える影響について / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. / Emergence of echo chambers in social media communication involving multiple topics / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 / 進化ゲーム理論の進化：マルチエージェントシミュレーション, 実験室実験と，LLMの行動経済学 / 重みが動的なネットワークにおいてネットワーク構造が協力の進化に与える影響 / 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ / Individuals reciprocate negative actions revealing negative upstream reciprocity / SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. / Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement / Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim / パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 / 群淘汰状況下における罰則・報酬の進化 / Self-organized Speculation Game for the spontaneous emergence of financial stylized facts / 情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ / 時間制約を導入したゴミ箱モデル / Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment / 協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 / A quantitative easing experiment</t>
+          <t>社会システム工学・安全システム</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>社会的ジレンマ、資産市場実験</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>検索連動型広告における循環的な入札額変動の発生機構の解明 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Bubbles in Asset Markets and the Heterogeneity of Beliefs. / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 / 進化ゲーム理論の進化 — マルチエージェントシミュレーション，実験室実験と，LLM の行動経済学— / 発話量と発話内容に基づく集団間のコミュニケーション円滑化システムの提案 / ソーシャルメディア上のアジェンダ設定がエコーチェンバーの発生に与える影響について / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. / Emergence of echo chambers in social media communication involving multiple topics / 進化ゲーム理論の進化：マルチエージェントシミュレーション, 実験室実験と，LLMの行動経済学 / 重みが動的なネットワークにおいてネットワーク構造が協力の進化に与える影響 / 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ / Individuals reciprocate negative actions revealing negative upstream reciprocity / SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. / Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement / Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim / パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 / 群淘汰状況下における罰則・報酬の進化 / Self-organized Speculation Game for the spontaneous emergence of financial stylized facts / 情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ / 時間制約を導入したゴミ箱モデル / Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment / 協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 / A quantitative easing experiment</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>条件付き協力のためのコストの存在が、ネットワーク上での協力の進化に与える影響 / 自動運転配車サービスが東京中心部の交通形態に与える影響の分析 / 問題の難易度と意思決定数の関係に双曲志向が与える影響-ゴミ箱モデルによるアプローチ- / 多重ネットワーク上での協力の進化 〜相互作用ネットワークと戦略更新ネットワークの非対称性が協力の進化に与える影響〜 / 重みが動的なネットワークにおいてネットワークトポロジーが協力の進化に与える影響 / リンク重みの異質性と情報開示率が協力の進化に与える影響 / ソーシャルメディア上での複数のトピックにわたるコミュニケーションが意見の分極化とエコーチェンバーの発生に与える影響 / 純粋リスク下において他者の選択がリスク態度に与える影響：経済実験によるアプローチ / 間接互恵による協力進化に記憶の減衰が与える影響 / 歩行者ラウンドアバウトによる整流効果-駅構内の混雑緩和- / 投機的リスク下でのピア効果がリスク態度に与える影響 / 懲罰に関する社会規範が間接互恵の進化に与える影響について:シミュレーションによるアプローチ</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>保険・金融行動 ; 意思決定分析 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; オペレーションズリサーチ ; 交通・モビリティ ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>保険・金融行動
+          <t>社会システム工学・安全システム ; 保険・金融行動 ; 意思決定分析 ; マッチング理論・ゲーム理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 学習分析 ; マーケティング分析</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>社会システム工学・安全システム
+社会的ジレンマ、資産市場実験
+保険・金融行動
 意思決定分析
 マッチング理論・ゲーム理論
-都市・地域政策
-オペレーションズリサーチ
-交通・モビリティ
-ネットワーク・グラフ理論
-災害・防災研究
 政策評価・計量分析
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
-AI・データサイエンス
-都市・空間・交通
 行動ファイナンス
 金融市場分析
 ESG投資
@@ -2192,33 +2499,29 @@
 資源配分
 メカニズムデザイン
 協力ゲーム・非協力ゲーム
-都市経済
-地域政策
-土地利用
-公共政策評価
-数理最適化
-組合せ最適化
-計画・スケジューリング
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-災害社会学
-防災政策
-リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>条件付き協力のためのコストの存在が、ネットワーク上での協力の進化に与える影響 / 自動運転配車サービスが東京中心部の交通形態に与える影響の分析 / 問題の難易度と意思決定数の関係に双曲志向が与える影響-ゴミ箱モデルによるアプローチ- / 多重ネットワーク上での協力の進化 〜相互作用ネットワークと戦略更新ネットワークの非対称性が協力の進化に与える影響〜 / 重みが動的なネットワークにおいてネットワークトポロジーが協力の進化に与える影響 / リンク重みの異質性と情報開示率が協力の進化に与える影響 / ソーシャルメディア上での複数のトピックにわたるコミュニケーションが意見の分極化とエコーチェンバーの発生に与える影響 / 純粋リスク下において他者の選択がリスク態度に与える影響：経済実験によるアプローチ / 間接互恵による協力進化に記憶の減衰が与える影響 / 歩行者ラウンドアバウトによる整流効果-駅構内の混雑緩和- / 投機的リスク下でのピア効果がリスク態度に与える影響 / 懲罰に関する社会規範が間接互恵の進化に与える影響について:シミュレーションによるアプローチ
+実証分析
+社会ネットワーク分析
+学習分析
+マーケティング分析</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>条件付き協力のためのコストの存在が、ネットワーク上での協力の進化に与える影響
+自動運転配車サービスが東京中心部の交通形態に与える影響の分析
+問題の難易度と意思決定数の関係に双曲志向が与える影響-ゴミ箱モデルによるアプローチ-
+多重ネットワーク上での協力の進化 〜相互作用ネットワークと戦略更新ネットワークの非対称性が協力の進化に与える影響〜
+重みが動的なネットワークにおいてネットワークトポロジーが協力の進化に与える影響
+リンク重みの異質性と情報開示率が協力の進化に与える影響
+ソーシャルメディア上での複数のトピックにわたるコミュニケーションが意見の分極化とエコーチェンバーの発生に与える影響
+純粋リスク下において他者の選択がリスク態度に与える影響：経済実験によるアプローチ
+間接互恵による協力進化に記憶の減衰が与える影響
+歩行者ラウンドアバウトによる整流効果-駅構内の混雑緩和-
+投機的リスク下でのピア効果がリスク態度に与える影響
+懲罰に関する社会規範が間接互恵の進化に与える影響について:シミュレーションによるアプローチ
 人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析
 新規投資家の継続的な参入が価格形成・価格変動に与える影響
 ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響
@@ -2294,6 +2597,15 @@
 国際交流を背景とした中東都市計画史研究と都市保全プロジェクトへの還元
 モロッコの歴史都市 フェスの保全と近代化
 現代イスラーム都市の多元的成り立ちに関する研究
+都市計画・建築計画
+建築史・意匠
+地域研究
+建築・都市計画史
+地中海都市
+ヘレニズム基盤
+歴史文化保全
+国際協力
+中東・北アフリカ
 Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers”
 フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から―
 吉田正春使節団が見た19世紀テヘラン都市改造
@@ -2328,33 +2640,48 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>都市計画・建築計画 / 建築史・意匠 / 地域研究</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>建築・都市計画史 / 地中海都市 / ヘレニズム基盤 / 歴史文化保全 / 国際協力 / 中東・北アフリカ</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” / フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― / 吉田正春使節団が見た19世紀テヘラン都市改造 / ジスカール・デスタン政権下のパリ歩行者空間整備 / 1960 年アガディール地震とその震災復興都市計画に関する研究 / フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 / フェルナン・プイヨンのベルカステル村修復に関する研究 ─城と村の一体性に着目して─ / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス / 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 / フェス 積み重なる寄進が形成した迷宮都市 / ガルダイア 丘の上の城塞とオアシス渓谷の集落 / Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development / The Urban Forming History of Dubrovnik During the 12th Until 17th Century / Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning / Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration / カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- / Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris / Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille / The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel / アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 / 19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 / 商業都市カサブランカにおけるトラム導入による社会空間変容 / ビルマ王都マンダレーの城内および城外市街地の空間構造に関する研究</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>ポルトガル植民地期におけるリオ・デ・ジャネイロの都市空間変容 / 戦後パリ郊外におけるフェルナン・プイヨンの住宅地計画 -アルジェ及びマルセイユの作品との比較から- / 中国・杭州市における近代宗教建築の展開 –1840〜1949年に建設されたキリスト教建築を対象に– / メキシコシティ旧水路空間の変遷に見る水都空間の重層性 / アンナバ新市街における伝統的商業空間の形成 / カイロ中心市街地の都市空間変容-イギリス統治下から共和制移行期に着目して / 乾燥地域における伝統的水利システムの洪水抑制効果―アルジェリア国ガルダイア県の事例― / 現チェコ共和国の諸地域におけるカミロ・ジッテの都市計画実作 / フェルナン・プイヨンのベルカステル村修復に関する研究-城と村の一体性に着目して- / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス / 上海・上生新所の都市イノベーション-歴史保全と現代的開発の融合- / 海上シルクロード都市ザイトゥーン（中国・泉州）における遺産の保全と活用 / A Historical Survey of Spatial Customisation in the Modern Planned City of Abuja, Nigeria</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>都市・地域政策
+          <t>都市計画・建築計画 ; 建築史・意匠 ; 地域研究 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 都市計画 ; 社会ネットワーク分析 ; 人間中心設計 ; 災害分析</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>都市計画・建築計画
+建築史・意匠
+地域研究
+建築・都市計画史
+地中海都市
+ヘレニズム基盤
+歴史文化保全
+国際協力
+中東・北アフリカ
+都市・地域政策
 GIS・空間分析
-オペレーションズリサーチ
-交通・モビリティ
 建築・空間設計
-災害・防災研究
-政策評価・計量分析
 公共政策・社会工学
 数理最適化・OR
 都市・空間・交通
@@ -2366,29 +2693,31 @@
 空間計量
 地理情報分析
 立地分析
-数理最適化
-組合せ最適化
-計画・スケジューリング
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
 建築計画
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
-災害社会学
-防災政策
-リスク評価
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ポルトガル植民地期におけるリオ・デ・ジャネイロの都市空間変容 / 戦後パリ郊外におけるフェルナン・プイヨンの住宅地計画 -アルジェ及びマルセイユの作品との比較から- / 中国・杭州市における近代宗教建築の展開 –1840〜1949年に建設されたキリスト教建築を対象に– / メキシコシティ旧水路空間の変遷に見る水都空間の重層性 / アンナバ新市街における伝統的商業空間の形成 / カイロ中心市街地の都市空間変容-イギリス統治下から共和制移行期に着目して / 乾燥地域における伝統的水利システムの洪水抑制効果―アルジェリア国ガルダイア県の事例― / 現チェコ共和国の諸地域におけるカミロ・ジッテの都市計画実作 / フェルナン・プイヨンのベルカステル村修復に関する研究-城と村の一体性に着目して- / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス / 上海・上生新所の都市イノベーション-歴史保全と現代的開発の融合- / 海上シルクロード都市ザイトゥーン（中国・泉州）における遺産の保全と活用 / A Historical Survey of Spatial Customisation in the Modern Planned City of Abuja, Nigeria
+都市計画
+社会ネットワーク分析
+人間中心設計
+災害分析</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ポルトガル植民地期におけるリオ・デ・ジャネイロの都市空間変容
+戦後パリ郊外におけるフェルナン・プイヨンの住宅地計画 -アルジェ及びマルセイユの作品との比較から-
+中国・杭州市における近代宗教建築の展開 –1840〜1949年に建設されたキリスト教建築を対象に–
+メキシコシティ旧水路空間の変遷に見る水都空間の重層性
+アンナバ新市街における伝統的商業空間の形成
+カイロ中心市街地の都市空間変容-イギリス統治下から共和制移行期に着目して
+乾燥地域における伝統的水利システムの洪水抑制効果―アルジェリア国ガルダイア県の事例―
+現チェコ共和国の諸地域におけるカミロ・ジッテの都市計画実作
+フェルナン・プイヨンのベルカステル村修復に関する研究-城と村の一体性に着目して-
+フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス
+上海・上生新所の都市イノベーション-歴史保全と現代的開発の融合-
+海上シルクロード都市ザイトゥーン（中国・泉州）における遺産の保全と活用
+A Historical Survey of Spatial Customisation in the Modern Planned City of Abuja, Nigeria
 「もう一つのモダニズム」による地域性の再構築 フェルナン・プイヨンの生涯業績
 中東・北アフリカ地域におけるヘレニズム基盤の継承に関する都市文献史的研究
 西アジア地域の都市空間の重層性に関する計画論的研究
@@ -2406,7 +2735,6 @@
 1960 年アガディール地震とその震災復興都市計画に関する研究
 フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告
 フェルナン・プイヨンのベルカステル村修復に関する研究 ─城と村の一体性に着目して─
-フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス
 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史
 フェス 積み重なる寄進が形成した迷宮都市
 ガルダイア 丘の上の城塞とオアシス渓谷の集落
@@ -2465,6 +2793,9 @@
 海外における中間財生産による国内都市空間構造の変化に関する研究
 都市内立地の内生的決定に関する数値計算的アプローチ
 都市内情報流を考慮した空間構造の自己組織化
+経済政策
+理論経済学
+都市構造
 Dual Chalcogen-Bonding Interactions for the Conformational Control of Urea
 Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone
 Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone
@@ -2496,51 +2827,50 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Dual Chalcogen-Bonding Interactions for the Conformational Control of Urea / Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Life Cycle Analysis and Cost–Benefit Assessment of the Waste Collection System in Anyama, Cote d’Ivoire / Green Markets, Free Riders, and Monopolistic Competition / Relationship between urban population growth and utility level of workers with heterogeneity of labor efficiency / Environmental offsets and production externalities under monopolistic competition / Environmental offsets and production externalities under monopolistic competition / Implications of urbanization and Impact of Population Growth on Abidjan City, Cote d’Ivoire / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― / 通信技術革新と企業内立地行動の変化に関する研究-通信の固定費用を考慮して- / 通信技術革新と企業内立地行動の変化に関する研究 / Communication technologies and spatial organization of multi-unit firms in metropolitan areas / 企業の分離立地にともなう副都心成立の均衡土地利用分析 / The Influence of the Great Hanshin-Awaji Earthquake on Housing Market of the Area / 東京大都市圏の効用分布の推計と住居選択モデルの応用可能性に関する研究 / テレコミューティングの普及と都市構造に関する研究 / 複数都心を持つ都市構造の動的安定性に関する研究 / 首都圏における通勤家計の居住地選択モデル / 2種類の企業による都市の均衡形状に関する研究 / 大都市圏における近年のテレコミューティング（在宅勤務）と都市構造の均衡分析 / 首都圏における通勤家計の居住地選択モデル / 東京都心部における賃貸集合住宅価格の付加価値要因に関する研究</t>
+          <t>経済政策 / 理論経済学</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>都市構造</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Dual Chalcogen-Bonding Interactions for the Conformational Control of Urea / Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Life Cycle Analysis and Cost–Benefit Assessment of the Waste Collection System in Anyama, Cote d’Ivoire / Green Markets, Free Riders, and Monopolistic Competition / Relationship between urban population growth and utility level of workers with heterogeneity of labor efficiency / Environmental offsets and production externalities under monopolistic competition / Implications of urbanization and Impact of Population Growth on Abidjan City, Cote d’Ivoire / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― / 通信技術革新と企業内立地行動の変化に関する研究-通信の固定費用を考慮して- / 通信技術革新と企業内立地行動の変化に関する研究 / Communication technologies and spatial organization of multi-unit firms in metropolitan areas / 企業の分離立地にともなう副都心成立の均衡土地利用分析 / The Influence of the Great Hanshin-Awaji Earthquake on Housing Market of the Area / 東京大都市圏の効用分布の推計と住居選択モデルの応用可能性に関する研究 / テレコミューティングの普及と都市構造に関する研究 / 複数都心を持つ都市構造の動的安定性に関する研究 / 首都圏における通勤家計の居住地選択モデル / 2種類の企業による都市の均衡形状に関する研究 / 大都市圏における近年のテレコミューティング（在宅勤務）と都市構造の均衡分析 / 東京都心部における賃貸集合住宅価格の付加価値要因に関する研究</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>広域行政が自治体の財政に与える影響 / 長時間労働が中国人の健康に与える影響に関する研究 / 中国・広州市における高齢者施設の空間的アクセシビリティ評価 / 羽田空港の新飛行経路の騒音は周辺住宅価格への影響 / 中国の住宅資産と負債が高等教育進学率への影響と性別差異 / ネット・口コミが消費者行動に与える影響に関する研究～丸亀製麵を例として～ / 地方都市の駅まち空間再構築事業による地価変化の計量分析 / 地方都市におけるスマートシティ事業の実装が地価に与える影響 / 鉄道廃線敷のBRT化が地域に与える影響について / 中国における農村金融の格差に関する影響要因分析及び政策分析。ー中国“十二五”計画を中心に / 「国立公園満喫プロジェクト」が関連地域の地価に与える影響ー先行８公園を対象としてー / ハイテク企業のイノベーションが地価に与える影響 / 中国におけるライブコマースが農村振興に与える影響に関する分析 / 国際スポーツ大会の開催決定がスタジアム周辺地域に与える影響についての研究―地価の変化に注目して― / Park-PFIによる公園整備が商業地域の地価に与える影響 / ウォーカブル向上による関連地域の地価変化に関する研究 / 水害についてのリスク認識の変化が地価に及ぼす影響 / 高速鉄道が沿線地域に与える影響の実証研究―徐蘭高速鉄道を例として― / 中国における子供性別が家計の資産配分に与える影響―不動産を研究対象として― / LRT導入による地価への影響―宇都宮ライトレールを事例として―</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 保険・金融行動 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; 画像・視覚情報処理 ; スポーツデータ分析 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-保険・金融行動
+          <t>経済政策 ; 理論経済学 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 画像・視覚情報処理 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 物流最適化 ; 災害分析 ; 社会ネットワーク分析 ; 行政データ分析</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>経済政策
+理論経済学
+都市構造
 マッチング理論・ゲーム理論
 都市・地域政策
 GIS・空間分析
-オペレーションズリサーチ
-交通・モビリティ
 建築・空間設計
 画像・視覚情報処理
-スポーツデータ分析
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
-数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
 安定マッチング
 資源配分
 メカニズムデザイン
@@ -2553,13 +2883,6 @@
 空間計量
 地理情報分析
 立地分析
-数理最適化
-組合せ最適化
-計画・スケジューリング
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
 建築計画
 空間レイアウト生成
 居住空間設計
@@ -2568,18 +2891,42 @@
 画像認識
 行動認識
 マルチモーダル解析
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>広域行政が自治体の財政に与える影響 / 長時間労働が中国人の健康に与える影響に関する研究 / 中国・広州市における高齢者施設の空間的アクセシビリティ評価 / 羽田空港の新飛行経路の騒音は周辺住宅価格への影響 / 中国の住宅資産と負債が高等教育進学率への影響と性別差異 / ネット・口コミが消費者行動に与える影響に関する研究～丸亀製麵を例として～ / 地方都市の駅まち空間再構築事業による地価変化の計量分析 / 地方都市におけるスマートシティ事業の実装が地価に与える影響 / 鉄道廃線敷のBRT化が地域に与える影響について / 中国における農村金融の格差に関する影響要因分析及び政策分析。ー中国“十二五”計画を中心に / 「国立公園満喫プロジェクト」が関連地域の地価に与える影響ー先行８公園を対象としてー / ハイテク企業のイノベーションが地価に与える影響 / 中国におけるライブコマースが農村振興に与える影響に関する分析 / 国際スポーツ大会の開催決定がスタジアム周辺地域に与える影響についての研究―地価の変化に注目して― / Park-PFIによる公園整備が商業地域の地価に与える影響 / ウォーカブル向上による関連地域の地価変化に関する研究 / 水害についてのリスク認識の変化が地価に及ぼす影響 / 高速鉄道が沿線地域に与える影響の実証研究―徐蘭高速鉄道を例として― / 中国における子供性別が家計の資産配分に与える影響―不動産を研究対象として― / LRT導入による地価への影響―宇都宮ライトレールを事例として―
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+物流最適化
+災害分析
+社会ネットワーク分析
+行政データ分析</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>広域行政が自治体の財政に与える影響
+長時間労働が中国人の健康に与える影響に関する研究
+中国・広州市における高齢者施設の空間的アクセシビリティ評価
+羽田空港の新飛行経路の騒音は周辺住宅価格への影響
+中国の住宅資産と負債が高等教育進学率への影響と性別差異
+ネット・口コミが消費者行動に与える影響に関する研究～丸亀製麵を例として～
+地方都市の駅まち空間再構築事業による地価変化の計量分析
+地方都市におけるスマートシティ事業の実装が地価に与える影響
+鉄道廃線敷のBRT化が地域に与える影響について
+中国における農村金融の格差に関する影響要因分析及び政策分析。ー中国“十二五”計画を中心に
+「国立公園満喫プロジェクト」が関連地域の地価に与える影響ー先行８公園を対象としてー
+ハイテク企業のイノベーションが地価に与える影響
+中国におけるライブコマースが農村振興に与える影響に関する分析
+国際スポーツ大会の開催決定がスタジアム周辺地域に与える影響についての研究―地価の変化に注目して―
+Park-PFIによる公園整備が商業地域の地価に与える影響
+ウォーカブル向上による関連地域の地価変化に関する研究
+水害についてのリスク認識の変化が地価に及ぼす影響
+高速鉄道が沿線地域に与える影響の実証研究―徐蘭高速鉄道を例として―
+中国における子供性別が家計の資産配分に与える影響―不動産を研究対象として―
+LRT導入による地価への影響―宇都宮ライトレールを事例として―
 衛星情報を利用した物流における大気環境改善の評価
 独占的競争下での環境オフセットの自発的供給に関する研究
 都市における環境リスクの軽減の経済効果に関する研究
@@ -2653,6 +3000,9 @@
 「建築情報モデラーに関する研究」に対する
 ポスト定住化社会における時空を超えたアクティビティの流動化実態に関する実証的研究
 拡張現実技術を利用した実空間景観シミュレーションシステムの開発
+都市計画・建築計画
+社会システム工学・安全システム
+情報化・ネットワーク社会における建築計画・都市計画
 歩行者の空間学習を支援するナビゲーション手法に関する研究
 超一線都市の若者向けマンションの立地分析：広州を例にして
 街路網の広がりから見た城下町の空間構成の変容に関する研究
@@ -2686,45 +3036,47 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>歩行者の空間学習を支援するナビゲーション手法に関する研究 / 超一線都市の若者向けマンションの立地分析：広州を例にして / 街路網の広がりから見た城下町の空間構成の変容に関する研究 / 総合設計制度による建築物が街路景観の印象に与える影響に関する研究 ―3D都市モデルPLATEAU及びVR を用いて― / 都市の集約化が分散型エネルギーシステム導入に与える影響について / 街路網の広がりから見た城下町の空間構成の変容に関する研究 / デザイン共創環境を用いた集合住宅設計支援ツールの開発 / An analysis on urban shrinkage trends of all Japanese cities by detecting relative densely inhabited districts - Changes in urban form of Japanese cities in an era of shrinking population, part 2 / モビリティ技術活用による新しい児童通学スタイルの検証 / デザインパターンの列挙に関する一考察 / 相対的な人口集中地区の抽出を通じた全国市町村の都市縮小傾向の分析 －人口減少時代を迎えるわが国の都市圏の形態変化に関する研究（その2）－ / Exploring the Panel Exercises in the Modulor as presented by Le Corbusier / 歩行空間ネットワークを用いた駅周辺の回遊性に関する研究 －埼玉県大宮駅周辺を事例として－ / ル・コルビュジエが提示したモデュロールによる羽目板遊びの探求 / 中国安慶市の敬老院における整備実態の居住者の満足度に関する研究 / BIMと修繕記録を用いた既存建物の部位等の更新間隔算出 / 共育 ～ともに育て、ともに育つ保育園～ / ソーシャルメディアの投稿写真からみた地域特性に関する考察 / 媒介中心性を用いた歩行者の回遊行動に関する検討 - Walkability 指標の計測へ向けて - / 情報量損失最小化法を応用した相対的人口集中地区の抽出; 都市縮小・拡大市町村数の経年変化分析 / 上海中心市街地におけるGated Communityが飲食店への徒歩到達アクセシ ビリティに与える影響 / デジタル・モデュロール３ / AN ANALYSIS OF MIXED LAND USE TOWARD DESIGNING THE COMPACT CITY / 都市のWalkabilityに関する研究 ―Urban Network Analysisを用いた評価指標計算に向けて― / 土地利用の混在指標を用いたわが国の都市圏の形態分析 ―埼玉県東部を対象としたMetropolitan Form Analysis― Land-Use Mixの適用―</t>
+          <t>都市計画・建築計画 / 社会システム工学・安全システム</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>情報化・ネットワーク社会における建築計画・都市計画</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>歩行者の空間学習を支援するナビゲーション手法に関する研究 / 超一線都市の若者向けマンションの立地分析：広州を例にして / 街路網の広がりから見た城下町の空間構成の変容に関する研究 / 総合設計制度による建築物が街路景観の印象に与える影響に関する研究 ―3D都市モデルPLATEAU及びVR を用いて― / 都市の集約化が分散型エネルギーシステム導入に与える影響について / デザイン共創環境を用いた集合住宅設計支援ツールの開発 / An analysis on urban shrinkage trends of all Japanese cities by detecting relative densely inhabited districts - Changes in urban form of Japanese cities in an era of shrinking population, part 2 / モビリティ技術活用による新しい児童通学スタイルの検証 / デザインパターンの列挙に関する一考察 / 相対的な人口集中地区の抽出を通じた全国市町村の都市縮小傾向の分析 －人口減少時代を迎えるわが国の都市圏の形態変化に関する研究（その2）－ / Exploring the Panel Exercises in the Modulor as presented by Le Corbusier / 歩行空間ネットワークを用いた駅周辺の回遊性に関する研究 －埼玉県大宮駅周辺を事例として－ / ル・コルビュジエが提示したモデュロールによる羽目板遊びの探求 / 中国安慶市の敬老院における整備実態の居住者の満足度に関する研究 / BIMと修繕記録を用いた既存建物の部位等の更新間隔算出 / 共育 ～ともに育て、ともに育つ保育園～ / ソーシャルメディアの投稿写真からみた地域特性に関する考察 / 媒介中心性を用いた歩行者の回遊行動に関する検討 - Walkability 指標の計測へ向けて - / 情報量損失最小化法を応用した相対的人口集中地区の抽出; 都市縮小・拡大市町村数の経年変化分析 / 上海中心市街地におけるGated Communityが飲食店への徒歩到達アクセシ ビリティに与える影響 / デジタル・モデュロール３ / AN ANALYSIS OF MIXED LAND USE TOWARD DESIGNING THE COMPACT CITY / 都市のWalkabilityに関する研究 ―Urban Network Analysisを用いた評価指標計算に向けて― / 土地利用の混在指標を用いたわが国の都市圏の形態分析 ―埼玉県東部を対象としたMetropolitan Form Analysis― Land-Use Mixの適用―</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>市民の屋外公共空間活用に対する自治体の支援実態とその在り方ー市民の屋外空間における音楽活動支援に着目してー / 景観計画下での屋外広告物等の実態と伝統的都市景観に対する若者の景観認識—京都市を事例に— / 発達障害者の空間認知からみたナビゲーションのあり方に関する研究 / 中国における大学城の土地用途変遷と利用者の満足度について—呼蘭、下沙、広州大学城を対象にして— / デザイン共創環境を用いた集合住宅設計支援ツールの提案 / 中国旧市街地のゲーテッドコミュニティの再生に関する研究 ー河南省鄭州市を事例としてー / 都市の集約化と分散型エネルギーの導入適性に関する研究 / 総合設計制度による建築物が都市空間に与える圧迫感に関する研究-3D都市モデルPLATEAU及びVRを用いて- / 歩行者の空間学習に関する研究－ナビゲーション手法と環境的特徴に着目して－ / 超一線都市の若者向けマンションの立地分析と最適化－広州を例にして－</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; 画像・視覚情報処理 ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>家族・人口政策
+          <t>都市計画・建築計画 ; 社会システム工学・安全システム ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 都市計画 ; 数理最適化 ; 環境工学 ; 強化学習</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>都市計画・建築計画
+社会システム工学・安全システム
+情報化・ネットワーク社会における建築計画・都市計画
 都市・地域政策
 GIS・空間分析
-社会政策・福祉
-オペレーションズリサーチ
-交通・モビリティ
 建築・空間設計
-画像・視覚情報処理
-ネットワーク・グラフ理論
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 数理最適化・OR
-AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 都市経済
 地域政策
 土地利用
@@ -2733,38 +3085,36 @@
 空間計量
 地理情報分析
 立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
-数理最適化
-組合せ最適化
-計画・スケジューリング
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
 建築計画
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>市民の屋外公共空間活用に対する自治体の支援実態とその在り方ー市民の屋外空間における音楽活動支援に着目してー / 景観計画下での屋外広告物等の実態と伝統的都市景観に対する若者の景観認識—京都市を事例に— / 発達障害者の空間認知からみたナビゲーションのあり方に関する研究 / 中国における大学城の土地用途変遷と利用者の満足度について—呼蘭、下沙、広州大学城を対象にして— / デザイン共創環境を用いた集合住宅設計支援ツールの提案 / 中国旧市街地のゲーテッドコミュニティの再生に関する研究 ー河南省鄭州市を事例としてー / 都市の集約化と分散型エネルギーの導入適性に関する研究 / 総合設計制度による建築物が都市空間に与える圧迫感に関する研究-3D都市モデルPLATEAU及びVRを用いて- / 歩行者の空間学習に関する研究－ナビゲーション手法と環境的特徴に着目して－ / 超一線都市の若者向けマンションの立地分析と最適化－広州を例にして－
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+都市計画
+数理最適化
+環境工学
+強化学習</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>市民の屋外公共空間活用に対する自治体の支援実態とその在り方ー市民の屋外空間における音楽活動支援に着目してー
+景観計画下での屋外広告物等の実態と伝統的都市景観に対する若者の景観認識—京都市を事例に—
+発達障害者の空間認知からみたナビゲーションのあり方に関する研究
+中国における大学城の土地用途変遷と利用者の満足度について—呼蘭、下沙、広州大学城を対象にして—
+デザイン共創環境を用いた集合住宅設計支援ツールの提案
+中国旧市街地のゲーテッドコミュニティの再生に関する研究 ー河南省鄭州市を事例としてー
+都市の集約化と分散型エネルギーの導入適性に関する研究
+総合設計制度による建築物が都市空間に与える圧迫感に関する研究-3D都市モデルPLATEAU及びVRを用いて-
+歩行者の空間学習に関する研究－ナビゲーション手法と環境的特徴に着目して－
+超一線都市の若者向けマンションの立地分析と最適化－広州を例にして－
 ジェネレーティブデザインを通じて敷地計画における創造力はどこまで拡張できるか
 創造性の論理的・ 技術的探求に基づくデザイン共創環境の構築と教育プログラムの開発
 コンパクトシティを目指した都市デザイン戦略のための都市構造評価指標の探究
@@ -2839,6 +3189,16 @@
 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性
 スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築
 超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究
+都市計画・建築計画
+都市計画
+地区計画
+まちづくり
+カナダの都市計画
+団地再生
+住環境整備
+産官学民連携
+地域活性化
+コミュニティビジネス
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告
 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として
 わがまちのSDGs
@@ -2868,46 +3228,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>まちづくりを含む不動産開発に関する指導 / 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 超高層住宅の二重の老いの潜在的課題に関する研究 / 社会的孤独の解消モデル事例のプロセス分析及び検証手法の検討 / つくば市みどりの分譲地のまちづくり提案について / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築 / 超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究</t>
+          <t>まちづくりを含む不動産開発に関する指導 / 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 超高層住宅の二重の老いの潜在的課題に関する研究 / 社会的孤独の解消モデル事例のプロセス分析及び検証手法の検討 / つくば市みどりの分譲地のまちづくり提案について / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築 / 超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>都市計画・建築計画</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>都市計画 / 地区計画 / まちづくり / カナダの都市計画 / 団地再生 / 住環境整備 / 産官学民連携 / 地域活性化 / コミュニティビジネス</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として / わがまちのSDGs / 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ / 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 / 京都市東松ノ木市営住宅 / 国勢調査分析からみる外国人集住団地の実態 / 増加する外国人の受け皿としての住宅団地 / 住宅団地の外国人集住：特集の趣旨 / 住宅地における地区計画や認可協定の今後 / 区分所有マンションを含む市街地再開発事業の有効空地を考える / 社会的包摂とデザイン─「つながる場」15事例の実践から / 外国人住民との共存・共生: 海外の事例からの示唆 / 首都圏郊外におけるリノベーションまちづくりの成果と課題に関する研究 / 住宅建替えと一体的に再整備された街区公園の維持管理活動を通じたコミュニティ形成に関する研究 / 計画的戸建住宅地における駐車場シェアの導入意向と活用可能性に関する研究 / 多様な主体が関わる出産祝いプロジェクトの成立経緯と参加主体にもたらす変化に関する研究 / 職員の活躍を願う市長の思いと取り組み / 今後の地域づくりへの期待 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea / 転換期にある筑波研究学園都市の地区計画が空間資源継承に果たす役割と課題 / 1980年以降、40年の「つくば」の変化と現状 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea, Urban Planning / Living Lab Participants’ Knowledge Change about Inclusive Smart Cities: An Urban Living Lab in Seongdaegol, Seoul, South Korea / 地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>計画的戸建住宅地におけるスペース・シェアリングの展開可能性と受け入れ条件の検討 / 転換期にある筑波研究学園都市の地区計画が地域資源継承に果たす役割と実態 / 地域課題解決に取り組む空き家の活用過程の課題に関する研究―茨城県常総市水海道地区を対象にー / 筑波研究学園都市における市民に向けたサイエンスコミュニケーションの実態と課題 / 絶対高さ型高度地区導入後の展開と課題 / 高齢者情報格差の実態と対応策の検討：つくば市スーパーシティモデル地区を対象に / 民俗芸能の継承と観光活用意向に関する研究―岩手県北上市に着目してー / スペースシェアリングを活用した計画的戸建住宅団地の再生方策に関する研究 / 人材育成事業を契機とした地域活動拡大に関する研究 / 大都市郊外住宅団地における多世代交流活動の展開に関する研究 / 工業地帯の土地利用転換による知識集約型産業集積の実態と課題 －スペイン・バルセロナ市22＠プロジェクトを対象として－ / ごちゃまぜを理念とする多機能型福祉拠点の成立要因と意義に関する研究 －石川県社会福祉法人佛子園「三草二木 西圓寺」を対象として－ / 移住増加地域における遊休不動産を活用した新規事業の成立要因に関する研究 －長野県小諸市中心市街地を対象として－ / 超高層住宅集積地における利活用・維持管理の実態を踏まえた公開空地等の課題に関する研究 －東京都中央区第3ゾーンを対象として－</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>家族・人口政策
+          <t>都市計画・建築計画 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 都市計画 ; 社会ネットワーク分析 ; 人間中心設計 ; 行政データ分析</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>都市計画・建築計画
+都市計画
+地区計画
+まちづくり
+カナダの都市計画
+団地再生
+住環境整備
+産官学民連携
+地域活性化
+コミュニティビジネス
 都市・地域政策
 GIS・空間分析
-社会政策・福祉
 建築・空間設計
-政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 都市経済
 地域政策
 土地利用
@@ -2916,23 +3289,35 @@
 空間計量
 地理情報分析
 立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
 建築計画
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>計画的戸建住宅地におけるスペース・シェアリングの展開可能性と受け入れ条件の検討 / 転換期にある筑波研究学園都市の地区計画が地域資源継承に果たす役割と実態 / 地域課題解決に取り組む空き家の活用過程の課題に関する研究―茨城県常総市水海道地区を対象にー / 筑波研究学園都市における市民に向けたサイエンスコミュニケーションの実態と課題 / 絶対高さ型高度地区導入後の展開と課題 / 高齢者情報格差の実態と対応策の検討：つくば市スーパーシティモデル地区を対象に / 民俗芸能の継承と観光活用意向に関する研究―岩手県北上市に着目してー / スペースシェアリングを活用した計画的戸建住宅団地の再生方策に関する研究 / 人材育成事業を契機とした地域活動拡大に関する研究 / 大都市郊外住宅団地における多世代交流活動の展開に関する研究 / 工業地帯の土地利用転換による知識集約型産業集積の実態と課題 －スペイン・バルセロナ市22＠プロジェクトを対象として－ / ごちゃまぜを理念とする多機能型福祉拠点の成立要因と意義に関する研究 －石川県社会福祉法人佛子園「三草二木 西圓寺」を対象として－ / 移住増加地域における遊休不動産を活用した新規事業の成立要因に関する研究 －長野県小諸市中心市街地を対象として－ / 超高層住宅集積地における利活用・維持管理の実態を踏まえた公開空地等の課題に関する研究 －東京都中央区第3ゾーンを対象として－
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+社会ネットワーク分析
+人間中心設計
+行政データ分析</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>計画的戸建住宅地におけるスペース・シェアリングの展開可能性と受け入れ条件の検討
+転換期にある筑波研究学園都市の地区計画が地域資源継承に果たす役割と実態
+地域課題解決に取り組む空き家の活用過程の課題に関する研究―茨城県常総市水海道地区を対象にー
+筑波研究学園都市における市民に向けたサイエンスコミュニケーションの実態と課題
+絶対高さ型高度地区導入後の展開と課題
+高齢者情報格差の実態と対応策の検討：つくば市スーパーシティモデル地区を対象に
+民俗芸能の継承と観光活用意向に関する研究―岩手県北上市に着目してー
+スペースシェアリングを活用した計画的戸建住宅団地の再生方策に関する研究
+人材育成事業を契機とした地域活動拡大に関する研究
+大都市郊外住宅団地における多世代交流活動の展開に関する研究
+工業地帯の土地利用転換による知識集約型産業集積の実態と課題 －スペイン・バルセロナ市22＠プロジェクトを対象として－
+ごちゃまぜを理念とする多機能型福祉拠点の成立要因と意義に関する研究 －石川県社会福祉法人佛子園「三草二木 西圓寺」を対象として－
+移住増加地域における遊休不動産を活用した新規事業の成立要因に関する研究 －長野県小諸市中心市街地を対象として－
+超高層住宅集積地における利活用・維持管理の実態を踏まえた公開空地等の課題に関する研究 －東京都中央区第3ゾーンを対象として－
 まちづくりを含む不動産開発に関する指導
 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究
 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会
@@ -3007,6 +3392,14 @@
 茨城版ＳＤＧｓを推進する産学研究
 次世代の茅葺きの再生・導入に関する共同研究拠点の形成
 相続工学に関する共同研究
+都市計画・建築計画
+過疎地域
+農村地域
+移住・定住
+古民家
+空き家
+廃校
+地域組織
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告
 農山村地域に立地するゲストハウスの地域活性化に向けた取り組み 九州・中国・四国地方の基礎調査
 地域おこし協力隊の任期終了後の定住率と進路及び地域特性との関連分析 全国の自治体データを対象として
@@ -3036,81 +3429,88 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>つくば茅ラブプロジェクト：環境保全に資する茅葺きの持続利用技術および社会教育システムの開発 / 地域連携による新たな戸建て活用型住宅セーフティネットシステムの提案 / かすみがうら市の歴史的建築物活用にかかわる調査研究 / 石岡市看板建築及び里山景観等調査研究 / 地球規模的課題解決のための全学的広域分野横断型研究推進プラットフォームの構築 / 石岡市看板建築及び里山景観等調査研究 / 農村移住者の宿泊滞在施設運営と地域交流活動による新たな都市農村交流の展開可能性 / 茨城版ＳＤＧｓを推進する産学研究 / 次世代の茅葺きの再生・導入に関する共同研究拠点の形成 / 相続工学に関する共同研究</t>
+          <t>つくば茅ラブプロジェクト：環境保全に資する茅葺きの持続利用技術および社会教育システムの開発 / 地域連携による新たな戸建て活用型住宅セーフティネットシステムの提案 / かすみがうら市の歴史的建築物活用にかかわる調査研究 / 石岡市看板建築及び里山景観等調査研究 / 地球規模的課題解決のための全学的広域分野横断型研究推進プラットフォームの構築 / 農村移住者の宿泊滞在施設運営と地域交流活動による新たな都市農村交流の展開可能性 / 茨城版ＳＤＧｓを推進する産学研究 / 次世代の茅葺きの再生・導入に関する共同研究拠点の形成 / 相続工学に関する共同研究</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>都市計画・建築計画</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>過疎地域 / 農村地域 / 移住・定住 / 古民家 / 空き家 / 廃校 / 地域組織</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 農山村地域に立地するゲストハウスの地域活性化に向けた取り組み 九州・中国・四国地方の基礎調査 / 地域おこし協力隊の任期終了後の定住率と進路及び地域特性との関連分析 全国の自治体データを対象として / 農地における規模別の太陽光パネル設置要因の分析 / 自治体担当課による地域コミュニティ活動のフォローアップと施策立案に関する研究 都市的地域と農村地域が合併した自治体を対象として / 北関東地域における高齢者通所介護サービスの需給構造と将来推計(その2)：市場均衡条件を組込んだ需要供給量推計（2020～2045） / 木造板倉仮設住宅の再利用事例における平面構成の変化と住まい方 / 移住者主体による交流の場の形成過程と効果−茨城県石岡市八郷地域を事例として− / 農村地域の宿泊滞在施設における地域交流活動の実態調査−九州・中国・四国地方のシェアハウスを対象として− / 北関東地域における高齢者通所介護サービスの需給構造と将来推計（その1）：利用者数と供給量の推移を指標とした県別市場特性分析（2000～2019） / 農村集落の電力オフグリッド化の可能性に関する研究―石岡市上山集落を対象として― / 市町村合併により生じた旧市街地の振興における行政支援の手法について－つくば市周辺市街地振興における地域運営組織と外部人材との協働支援を事例として－ / 関係人口の居住地と訪問先との距離が地域とのかかわり方に与える影響－茨城県を対象として－ / 多様な主体が連携する「新しい内発的発展」を支える地方自治体の取り組みについて－つくば市周辺市街地振興を事例として－ / 木造民家を活用した高齢者通所介護施設の空間用途構成に関する研究（その1）：民家の平面構成と主用途の空間配置 / 現代建築への茅葺きの導入可能性に関する研究 / 木造公共建築の用途と建築規模による特徴把握と実現手法の分析 新建築掲載事例を対象として / 現代の茅葺き構法に関する研究−兵庫県神戸市の事例を対象として− / 既存建築を活用した自立高齢者地域支援拠点の運営形態と平面構成—土浦市「生きがい対応型デイサービス事業」を対象として— / 大規模高齢者通所介護施設における主室の用途構成と使われ方 / 萩市における医療法人による高齢者福祉施設の整備運営に関する事例研究（その２）：木造民家を改修した通所介護・介護予防施設の使われ方 / 食堂兼機能訓練室と和室が一体的に構成された小規模高齢者通所介護施設の使われ方 / 社会福祉協議会による中山間地域における高齢者福祉施設の整備運営の取組み（その２）：下関市社会福祉協議会による中山間地域における高齢者福祉施設の整備プロセス / 農村系長屋門の利用の変遷と利活用実態 茨城県つくば市桜地区を対象として / 既存建築ストックを活用したサテライトオフィスの誘致プロセスとその実態 福井県鯖江市を対象として</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>中国・四国地方の過疎市町村における​若年層の移住要因に関する研究​ / 地域組織による移住者受け入れ体制と​定着支援に関する研究​ー中国・四国地方を対象としてー​ / 自治体内における中心部と周縁集落間の往来による集落維持に関する研究ーつくば市筑波地区を対象としてー / 長屋門の利用の変遷と屋敷の利活用実態に関する研究ーつくば市を対象としてー / 外国人経営者による古民家活用に関する研究​ー京町家を宿泊施設に転用した事例を対象としてー / 要介護認定者数推計を基にした高齢者福祉介護施設の充足率推計ー茨城県を対象としてー / 介護保険制度の導入と改正が高齢者通所介護施設供給に及ぼした影響ー北関東三県における運営主体に着目した分析ー / 個人や団体による空き家活用の手法に関する研究 −茨城県内の活用事例を対象として− / 立地・建物の条件不利な廃校の​活用実態と民間活用手法に関する研究​ ​−関東地方の過疎地域を対象として−​ / 現代板倉構法の普及実態と木材生産供給体制に関する研究​ / 地域おこし協力隊の任期終了後における地域定住要因の分析 / 地域連携・協働運営による小規模小学校の存続意義に関する研究ー1自治体1校を対象にー / 外国人留学生の共同住宅としての空き家活用の効果と地域との関わりー茨城県利根町の日本語学校留学生を対象としてー</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 保険・金融行動 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>家族・人口政策
-保険・金融行動
-マッチング理論・ゲーム理論
+          <t>都市計画・建築計画 ; 都市・地域政策 ; 建築・空間設計 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 環境工学 ; 社会ネットワーク分析 ; 政策評価 ; 都市計画</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>都市計画・建築計画
+過疎地域
+農村地域
+移住・定住
+古民家
+空き家
+廃校
+地域組織
 都市・地域政策
-GIS・空間分析
-社会政策・福祉
 建築・空間設計
-政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
-経済・ファイナンス
-AI・データサイエンス
+数理最適化・OR
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
 都市経済
 地域政策
 土地利用
 公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
 建築計画
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+環境工学
+社会ネットワーク分析
 政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>中国・四国地方の過疎市町村における​若年層の移住要因に関する研究​ / 地域組織による移住者受け入れ体制と​定着支援に関する研究​ー中国・四国地方を対象としてー​ / 自治体内における中心部と周縁集落間の往来による集落維持に関する研究ーつくば市筑波地区を対象としてー / 長屋門の利用の変遷と屋敷の利活用実態に関する研究ーつくば市を対象としてー / 外国人経営者による古民家活用に関する研究​ー京町家を宿泊施設に転用した事例を対象としてー / 要介護認定者数推計を基にした高齢者福祉介護施設の充足率推計ー茨城県を対象としてー / 介護保険制度の導入と改正が高齢者通所介護施設供給に及ぼした影響ー北関東三県における運営主体に着目した分析ー / 個人や団体による空き家活用の手法に関する研究 −茨城県内の活用事例を対象として− / 立地・建物の条件不利な廃校の​活用実態と民間活用手法に関する研究​ ​−関東地方の過疎地域を対象として−​ / 現代板倉構法の普及実態と木材生産供給体制に関する研究​ / 地域おこし協力隊の任期終了後における地域定住要因の分析 / 地域連携・協働運営による小規模小学校の存続意義に関する研究ー1自治体1校を対象にー / 外国人留学生の共同住宅としての空き家活用の効果と地域との関わりー茨城県利根町の日本語学校留学生を対象としてー
+都市計画</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>中国・四国地方の過疎市町村における​若年層の移住要因に関する研究​
+地域組織による移住者受け入れ体制と​定着支援に関する研究​ー中国・四国地方を対象としてー​
+自治体内における中心部と周縁集落間の往来による集落維持に関する研究ーつくば市筑波地区を対象としてー
+長屋門の利用の変遷と屋敷の利活用実態に関する研究ーつくば市を対象としてー
+外国人経営者による古民家活用に関する研究​ー京町家を宿泊施設に転用した事例を対象としてー
+要介護認定者数推計を基にした高齢者福祉介護施設の充足率推計ー茨城県を対象としてー
+介護保険制度の導入と改正が高齢者通所介護施設供給に及ぼした影響ー北関東三県における運営主体に着目した分析ー
+個人や団体による空き家活用の手法に関する研究 −茨城県内の活用事例を対象として−
+立地・建物の条件不利な廃校の​活用実態と民間活用手法に関する研究​ ​−関東地方の過疎地域を対象として−​
+現代板倉構法の普及実態と木材生産供給体制に関する研究​
+地域おこし協力隊の任期終了後における地域定住要因の分析
+地域連携・協働運営による小規模小学校の存続意義に関する研究ー1自治体1校を対象にー
+外国人留学生の共同住宅としての空き家活用の効果と地域との関わりー茨城県利根町の日本語学校留学生を対象としてー
 つくば茅ラブプロジェクト：環境保全に資する茅葺きの持続利用技術および社会教育システムの開発
 地域連携による新たな戸建て活用型住宅セーフティネットシステムの提案
 かすみがうら市の歴史的建築物活用にかかわる調査研究
@@ -3184,6 +3584,9 @@
 ネットワーク理論の基盤整備と伸張
 データの精度を考慮した組合せ最適化問題に対する問題構造とアルゴリズムの研究
 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開
+最適化
+組合せ最適化
+アルゴリズム
 A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs
 Break maximization for round-robin tournaments without consecutive breaks
 Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm
@@ -3216,89 +3619,95 @@
           <t>大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 / ネットワーク上の時間軸をもった最適化問題とその応用 / スタッフスケジューリングに関する研究 / 組合せ最適化，ネットワーク最適化のアルゴリズム開発 / ネットワーク構造解析アルゴリズムの開発とネットワークアルゴリズムの総合的展開 / ネットワーク理論の基盤整備と伸張 / データの精度を考慮した組合せ最適化問題に対する問題構造とアルゴリズムの研究 / 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>最適化 / 組合せ最適化 / アルゴリズム</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs / Break maximization for round-robin tournaments without consecutive breaks / Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm / Height Estimation for Abrasive Grain of Synthetic Diamonds on Microscope Images by Conditional Adversarial Networks / Designing of OTN/WDM networks withrecovery methods for multiple failures / Restaurant Sales forecasting with feature interaction-learning mechanism based neural network model,IEEE International Conference on Big Data / A Discrete JAYA Algorithm for Long-Term Carpooling Problem / Carry-over Effect Values Minimization under Circle Method and Binary Factorization Based on Jaya Algorithm / Application of Data Anonymization to Smartphone Apps Usage Logs / 数理最適化を用いたサービス工学の事例―通勤カープールの実証実験― / Four-level knowledge graph contrastive learning structure for smart-phone application recommendation / A New Approach to Market Segmentation Based on 2-Dimensional Tables / Challenges of commuter carpooling with adapting to Japanese customs and regulations: A pilot study / Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model / Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan / Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament / 交換移植制度におけるドミナントマッチングの適用可能性 / Network Design Models with Partial Protection Schemes against Multiple Failures under Optical- Channel Data Unit Constraints / ILP models and improved methods for the problem of routing and spectrum allocation / A novel channel-based model for the problem of routing, space, and spectrum assignment / NASH EQUILIBRIA FOR INFORMATION DIFFUSION GAMES ON WEIGHTED CYCLES AND PATHS / Strongly separable matrices for nonadaptive combinatorial group testing / Modeling and Evaluating Taxi Ride-sharing for Event Trips / 不均衡データに対する多段階学習を用いた アンサンブルモデルによる2 クラス分類アルゴリズムの提案 / A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>外国人居住者向けWebサイトのアクセスログ解析による主要な遷移の特定 / 並列機械バッチスケジューチング問題に対するヒューリスティックアルゴリズム / ネットワーク拡張ゲームの均衡解を求める一解法 / 市場分析における遺伝的アルゴリズムを用いたサンプルデータ抽出 / 光通信ネットワークの耐故障二層モデルの比較と評価 / 深層学習を用いた平面画像上の物体の高さ推定 / ブレークに関する公平性を考慮した総当たり戦スケジューリング / プラスチック製部品製造工場における成形工程の生産スケジューリングモデル化と実応用 / 実応用にむけた多品種少量生産スケジューリング / byesを用いたスポーツスケジューリングの移動距離に関する検討 / ジョブショップスケジューリングの実応用へ向けた二つのアプローチ / 欠勤者を考慮した通勤カープールモデルの提案 / 2部グラフ上のポピュラーマッチングの要素数に着目した特徴づけ / スポーツ競技のスケジュール作成における Carry-Over Effect 値最小化に関する検討 / 次世代光伝送網における資源割り当てIPモデルとヒューリスティックアルゴリズム / 深層学習を用いたレストラン売り上げの予測モデルの構築と実応用 / 安全性と日本の法規制を考慮した通勤カープールモデルの提案と評価 / テクスチャ解析手法による2次元画像の砥粒群の形状分類 / 飲食店におけるスタッフのスキルを考慮したシフト作成のモデル構築と自動化 / 耐故障性を持つ二層光ネットワーク設計問題 / 飲食店の業務標準化に向けた最適な調理手順モデリング / 並列機械スケジューリング問題における多様な解の生成 / 空間分割多重光伝送網における通信保護を考慮した資源割当問題の効率的計算方法の検討 / ジョブショップスケジューリング問題に対する深層学習を用いたヒューリスティックアルゴリズム / A Contrastive Learning Structure for Prediction of smartphone applications to use next / 知識グラフの対照学習におけるグラフサンプリング手法の検討 / 大規模なカープーリング問題に対するK-medoidsクラスタリングを用いた二段階アルゴリズム / データ匿名加工手法のスマートフォンアプリ利用ログへの適用可能性 / 光通信ネットワークにおけるスプリットスペクトルを取り入れた資源割当モデルの提案 / ネットワーク上の耐故障性のある centdian 配置問題 / スマホアプリデータにおける推薦システムの活用 / 動的最短経路阻止モデルの拡張と観察 / 総当たり戦における試合間隔差の最小化問題 / 双曲空間とグラフニューラルネットワークを用いたCross-Domain推薦システムモデル / 高次元データに対するクラスタリングアプローチ / 高齢者通所介護施設における訪問時刻幅を持つ送迎サービスモデル / 訪問介護における訪問順序の最適化 / 待ち時間を考慮した通勤カープールモデル / 試合間隔の公平性を考慮した同時制約を持つ対戦表作成 / 飲食店の調理スケジューリング問題に対するメタヒューリスティクスの適用 / 光ネットワーク上の資源割当問題における候補パスの選択 / Pointer Networksを用いた飲食店における調理スケジューリング</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; オペレーションズリサーチ ; 建築・空間設計 ; 機械学習 ; 画像・視覚情報処理 ; ネットワーク・グラフ理論 ; スポーツデータ分析 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>マッチング理論・ゲーム理論
-都市・地域政策
-GIS・空間分析
-社会政策・福祉
+          <t>オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 社会ネットワーク分析 ; ネットワーク科学</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>最適化
+組合せ最適化
+アルゴリズム
 オペレーションズリサーチ
-建築・空間設計
-機械学習
-画像・視覚情報処理
 ネットワーク・グラフ理論
-スポーツデータ分析
-政策評価・計量分析
-公共政策・社会工学
-経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
-都市経済
-地域政策
-土地利用
-公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
 数理最適化
-組合せ最適化
 計画・スケジューリング
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-統計的学習
-予測モデリング
-表現学習
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
 グラフ理論
 離散数学
 ネットワーク最適化
 組合せ構造
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>外国人居住者向けWebサイトのアクセスログ解析による主要な遷移の特定 / 並列機械バッチスケジューチング問題に対するヒューリスティックアルゴリズム / ネットワーク拡張ゲームの均衡解を求める一解法 / 市場分析における遺伝的アルゴリズムを用いたサンプルデータ抽出 / 光通信ネットワークの耐故障二層モデルの比較と評価 / 深層学習を用いた平面画像上の物体の高さ推定 / ブレークに関する公平性を考慮した総当たり戦スケジューリング / プラスチック製部品製造工場における成形工程の生産スケジューリングモデル化と実応用 / 実応用にむけた多品種少量生産スケジューリング / byesを用いたスポーツスケジューリングの移動距離に関する検討 / ジョブショップスケジューリングの実応用へ向けた二つのアプローチ / 欠勤者を考慮した通勤カープールモデルの提案 / 2部グラフ上のポピュラーマッチングの要素数に着目した特徴づけ / スポーツ競技のスケジュール作成における Carry-Over Effect 値最小化に関する検討 / 次世代光伝送網における資源割り当てIPモデルとヒューリスティックアルゴリズム / 深層学習を用いたレストラン売り上げの予測モデルの構築と実応用 / 安全性と日本の法規制を考慮した通勤カープールモデルの提案と評価 / テクスチャ解析手法による2次元画像の砥粒群の形状分類 / 飲食店におけるスタッフのスキルを考慮したシフト作成のモデル構築と自動化 / 耐故障性を持つ二層光ネットワーク設計問題 / 飲食店の業務標準化に向けた最適な調理手順モデリング / 並列機械スケジューリング問題における多様な解の生成 / 空間分割多重光伝送網における通信保護を考慮した資源割当問題の効率的計算方法の検討 / ジョブショップスケジューリング問題に対する深層学習を用いたヒューリスティックアルゴリズム / A Contrastive Learning Structure for Prediction of smartphone applications to use next / 知識グラフの対照学習におけるグラフサンプリング手法の検討 / 大規模なカープーリング問題に対するK-medoidsクラスタリングを用いた二段階アルゴリズム / データ匿名加工手法のスマートフォンアプリ利用ログへの適用可能性 / 光通信ネットワークにおけるスプリットスペクトルを取り入れた資源割当モデルの提案 / ネットワーク上の耐故障性のある centdian 配置問題 / スマホアプリデータにおける推薦システムの活用 / 動的最短経路阻止モデルの拡張と観察 / 総当たり戦における試合間隔差の最小化問題 / 双曲空間とグラフニューラルネットワークを用いたCross-Domain推薦システムモデル / 高次元データに対するクラスタリングアプローチ / 高齢者通所介護施設における訪問時刻幅を持つ送迎サービスモデル / 訪問介護における訪問順序の最適化 / 待ち時間を考慮した通勤カープールモデル / 試合間隔の公平性を考慮した同時制約を持つ対戦表作成 / 飲食店の調理スケジューリング問題に対するメタヒューリスティクスの適用 / 光ネットワーク上の資源割当問題における候補パスの選択 / Pointer Networksを用いた飲食店における調理スケジューリング
+社会ネットワーク分析
+ネットワーク科学</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>外国人居住者向けWebサイトのアクセスログ解析による主要な遷移の特定
+並列機械バッチスケジューチング問題に対するヒューリスティックアルゴリズム
+ネットワーク拡張ゲームの均衡解を求める一解法
+市場分析における遺伝的アルゴリズムを用いたサンプルデータ抽出
+光通信ネットワークの耐故障二層モデルの比較と評価
+深層学習を用いた平面画像上の物体の高さ推定
+ブレークに関する公平性を考慮した総当たり戦スケジューリング
+プラスチック製部品製造工場における成形工程の生産スケジューリングモデル化と実応用
+実応用にむけた多品種少量生産スケジューリング
+byesを用いたスポーツスケジューリングの移動距離に関する検討
+ジョブショップスケジューリングの実応用へ向けた二つのアプローチ
+欠勤者を考慮した通勤カープールモデルの提案
+2部グラフ上のポピュラーマッチングの要素数に着目した特徴づけ
+スポーツ競技のスケジュール作成における Carry-Over Effect 値最小化に関する検討
+次世代光伝送網における資源割り当てIPモデルとヒューリスティックアルゴリズム
+深層学習を用いたレストラン売り上げの予測モデルの構築と実応用
+安全性と日本の法規制を考慮した通勤カープールモデルの提案と評価
+テクスチャ解析手法による2次元画像の砥粒群の形状分類
+飲食店におけるスタッフのスキルを考慮したシフト作成のモデル構築と自動化
+耐故障性を持つ二層光ネットワーク設計問題
+飲食店の業務標準化に向けた最適な調理手順モデリング
+並列機械スケジューリング問題における多様な解の生成
+空間分割多重光伝送網における通信保護を考慮した資源割当問題の効率的計算方法の検討
+ジョブショップスケジューリング問題に対する深層学習を用いたヒューリスティックアルゴリズム
+A Contrastive Learning Structure for Prediction of smartphone applications to use next
+知識グラフの対照学習におけるグラフサンプリング手法の検討
+大規模なカープーリング問題に対するK-medoidsクラスタリングを用いた二段階アルゴリズム
+データ匿名加工手法のスマートフォンアプリ利用ログへの適用可能性
+光通信ネットワークにおけるスプリットスペクトルを取り入れた資源割当モデルの提案
+ネットワーク上の耐故障性のある centdian 配置問題
+スマホアプリデータにおける推薦システムの活用
+動的最短経路阻止モデルの拡張と観察
+総当たり戦における試合間隔差の最小化問題
+双曲空間とグラフニューラルネットワークを用いたCross-Domain推薦システムモデル
+高次元データに対するクラスタリングアプローチ
+高齢者通所介護施設における訪問時刻幅を持つ送迎サービスモデル
+訪問介護における訪問順序の最適化
+待ち時間を考慮した通勤カープールモデル
+試合間隔の公平性を考慮した同時制約を持つ対戦表作成
+飲食店の調理スケジューリング問題に対するメタヒューリスティクスの適用
+光ネットワーク上の資源割当問題における候補パスの選択
+Pointer Networksを用いた飲食店における調理スケジューリング
 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発
 ネットワーク上の時間軸をもった最適化問題とその応用
 スタッフスケジューリングに関する研究
@@ -3373,6 +3782,13 @@
 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究
 集合住宅における子ども・女性に対する犯罪の実態分析と対策立案
 地理的犯罪予測の手法構築‐学際研究と産官学連携による学術基盤の確立とシステム開発
+社会システム工学・安全システム
+都市計画・建築計画
+環境農学（含ランドスケープ科学）
+都市計画
+犯罪科学
+空間情報科学
+環境心理学
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告
 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて
 都市公園における逸脱行為に関する縦断的研究
@@ -3407,46 +3823,54 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>社会システム工学・安全システム / 都市計画・建築計画 / 環境農学（含ランドスケープ科学）</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>都市計画 / 犯罪科学 / 空間情報科学 / 環境心理学</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて / 都市公園における逸脱行為に関する縦断的研究 / 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 / Mechanisms contributing to road network growth in volunteered street view imagery data / 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して / 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として / 人口低密度地域における人々の活動から見た「都市の活力」の計測 / 全国のJAを対象とする果物盗被害に関するアンケート調査報告 / Regional variations in key factors of children's independent mobility across Japan / 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 / Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives / Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) / Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning / 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 / GPSロガーを用いた官民による果樹盗パトロールの計測 / 子供の前兆事案被害情報の主体間共有の実態 / 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 / Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) / 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して / GPSログに基づく行動推定データを用いた人々の社会的接触可能性の時空間的把握 / サイバー・フィジカル空間上の社会的交流と居住地の近隣環境</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>COVID-19緊急事態宣言に伴う社会変化と犯罪の関連 / 小規模公園の廃止プロセスの実態と評価：社会受容と地域活性化の視点から / Methodology for applying a crowdsourced street view imagery data to evaluate street-level greenness / 留学生の帯同家族におけるソーシャルサポートの実態 / 子供を対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因 / 余暇歩行と近隣の土地利用の配置及び道路構成パターンとの関連 - GULPデータを用いて - / 地方部におけるSNSを介した観光関連情報の授受と観光行動や旅行地に対する愛着の関係 / 子どもを対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因 / 自主防犯行動促進の観点から見た警察SNSの評価 / 新たな防犯活動としての「ながら見守り」の実態と評価 / 多拠点生活者の特徴からみた地域への参入可能性の解明 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 / 刑務所出所者の地域生活定着に向けた訪問支援制度の実態と評価 / 若年層のサイバー・フィジカル空間におけるパーソナルネットワークと個人・居住地特性 / 筑波研究学園都市における公務員宿舎の廃止・再開発が人口移動・住民構成・コミュニティ活動に与える影響 / 人々の社会的接触可能性の時空間的把握とその要因：人口低密地域での検討 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 意思決定分析 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>家族・人口政策
+          <t>社会システム工学・安全システム ; 都市計画・建築計画 ; 環境農学（含ランドスケープ科学） ; 意思決定分析 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 建築・空間設計 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 農業情報学 ; 災害分析 ; 環境工学</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>社会システム工学・安全システム
+都市計画・建築計画
+環境農学（含ランドスケープ科学）
+都市計画
+犯罪科学
+空間情報科学
+環境心理学
 意思決定分析
 都市・地域政策
 GIS・空間分析
-社会政策・福祉
 オペレーションズリサーチ
-交通・モビリティ
 建築・空間設計
-ネットワーク・グラフ理論
-災害・防災研究
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 行動意思決定
 実験・行動分析
 ナッジ
@@ -3459,37 +3883,46 @@
 空間計量
 地理情報分析
 立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
 数理最適化
 組合せ最適化
 計画・スケジューリング
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
 建築計画
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-災害社会学
-防災政策
-リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>COVID-19緊急事態宣言に伴う社会変化と犯罪の関連 / 小規模公園の廃止プロセスの実態と評価：社会受容と地域活性化の視点から / Methodology for applying a crowdsourced street view imagery data to evaluate street-level greenness / 留学生の帯同家族におけるソーシャルサポートの実態 / 子供を対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因 / 余暇歩行と近隣の土地利用の配置及び道路構成パターンとの関連 - GULPデータを用いて - / 地方部におけるSNSを介した観光関連情報の授受と観光行動や旅行地に対する愛着の関係 / 子どもを対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因 / 自主防犯行動促進の観点から見た警察SNSの評価 / 新たな防犯活動としての「ながら見守り」の実態と評価 / 多拠点生活者の特徴からみた地域への参入可能性の解明 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 / 刑務所出所者の地域生活定着に向けた訪問支援制度の実態と評価 / 若年層のサイバー・フィジカル空間におけるパーソナルネットワークと個人・居住地特性 / 筑波研究学園都市における公務員宿舎の廃止・再開発が人口移動・住民構成・コミュニティ活動に与える影響 / 人々の社会的接触可能性の時空間的把握とその要因：人口低密地域での検討 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+社会ネットワーク分析
+農業情報学
+災害分析
+環境工学</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>COVID-19緊急事態宣言に伴う社会変化と犯罪の関連
+小規模公園の廃止プロセスの実態と評価：社会受容と地域活性化の視点から
+Methodology for applying a crowdsourced street view imagery data to evaluate street-level greenness
+留学生の帯同家族におけるソーシャルサポートの実態
+子供を対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因
+余暇歩行と近隣の土地利用の配置及び道路構成パターンとの関連 - GULPデータを用いて -
+地方部におけるSNSを介した観光関連情報の授受と観光行動や旅行地に対する愛着の関係
+子どもを対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因
+自主防犯行動促進の観点から見た警察SNSの評価
+新たな防犯活動としての「ながら見守り」の実態と評価
+多拠点生活者の特徴からみた地域への参入可能性の解明
+留学生の帯同家族におけるソーシャル・サポートの実態に関する研究
+刑務所出所者の地域生活定着に向けた訪問支援制度の実態と評価
+若年層のサイバー・フィジカル空間におけるパーソナルネットワークと個人・居住地特性
+筑波研究学園都市における公務員宿舎の廃止・再開発が人口移動・住民構成・コミュニティ活動に与える影響
+人々の社会的接触可能性の時空間的把握とその要因：人口低密地域での検討
+Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning
 特殊詐欺に「騙されても被害に至らない」社会システムの構築に向けた実証研究
 情報提供と環境手がかりによる行動変容：ナッジ犯罪予防の定式化とその効果検証
 日本における農村犯罪学の創成に向けた萌芽研究：窃盗犯を事例とする実態分析
@@ -3512,11 +3945,9 @@
 全国のJAを対象とする果物盗被害に関するアンケート調査報告
 Regional variations in key factors of children's independent mobility across Japan
 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析
-留学生の帯同家族におけるソーシャル・サポートの実態に関する研究
 Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives
 Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI)
 Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits
-Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning
 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査
 GPSロガーを用いた官民による果樹盗パトロールの計測
 子供の前兆事案被害情報の主体間共有の実態
@@ -3565,6 +3996,11 @@
 逸脱行動が生起するプロセスと矯正方法に関する研究
 進路意思決定における認知・感情過程のモデル化
 教師教育教材を事例としたマルチメディア教材設計・評価手法の開発
+社会心理学
+実験心理学
+意思決定
+認知心理学
+感情
 Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan
 後悔を力に変える
 Exploring the Relationship Between Different Consumer Behaviors and Subjective Well-Being in Japan: A Focus on Prosocial, Sustainable, Experiential, and Conspicuous Consumption
@@ -3598,35 +4034,49 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan / 後悔を力に変える / Exploring the Relationship Between Different Consumer Behaviors and Subjective Well-Being in Japan: A Focus on Prosocial, Sustainable, Experiential, and Conspicuous Consumption / Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan / The Effect of General Trust on Willingness to Communicate in English among Japanese individuals across various situations. / Factors influencing behavioral intentions in livestream shopping: A cross-cultural study / Does macro-level general trust influence second language communication? :targeting prefectural capitals. / The influence of online multiplayer games on social capital and interdependent well-being in Japan / オンライン入試の実施と問題点 / 一般市民の更生支援に対する認知および参加意向の向上にむけた検討 / Understanding confidence in the human papillomavirus vaccine in Japan: a web-based survey of mothers, female adolescents, and healthcare professionals / Simulation of Outpatient Flow at the University of Tsukuba Hospital / Frequency of grooming the eyebrows and cosmetic consciousness in men. / The relationship between quantity of information contact and public evaluation of volunteer probation officers to promote understanding for social reintegration support. / Factors influencing differences between useful and useless regret. / The relationships between a metacognition scale and adaptive behavior in the regret situations: A comparison between junior high-school and university students. / Understanding confidence in human papillomavirus vaccine in Japan: A web-based questionnaire survey of mothers, female adolescents, and health care professionals. / 裁判員参加意向を規定する要因および意思決定プロセスの差異：制度施行前後の比較 / 市民の生態系サービスへの認知が保全行動意図に及ぼす影響：全国アンケートを用いた社会心理学的分析 / どのようにリスクを伝えればよいか：よりよいリスクコミュニケーションのために必要なこと / 意思決定から見たギャンブル行動 / Change of decision-making processes in repeated risk-taking behavior in a complex dynamic situation / The neural networks model of decision-making including feedback processes / Research on the gaps between students' expectation and satisfaction for universities / Analogical decision making in career choice</t>
+          <t>社会心理学 / 実験心理学</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>意思決定 / 認知心理学 / 社会心理学 / 感情</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan / 後悔を力に変える / Exploring the Relationship Between Different Consumer Behaviors and Subjective Well-Being in Japan: A Focus on Prosocial, Sustainable, Experiential, and Conspicuous Consumption / The Effect of General Trust on Willingness to Communicate in English among Japanese individuals across various situations. / Factors influencing behavioral intentions in livestream shopping: A cross-cultural study / Does macro-level general trust influence second language communication? :targeting prefectural capitals. / The influence of online multiplayer games on social capital and interdependent well-being in Japan / オンライン入試の実施と問題点 / 一般市民の更生支援に対する認知および参加意向の向上にむけた検討 / Understanding confidence in the human papillomavirus vaccine in Japan: a web-based survey of mothers, female adolescents, and healthcare professionals / Simulation of Outpatient Flow at the University of Tsukuba Hospital / Frequency of grooming the eyebrows and cosmetic consciousness in men. / The relationship between quantity of information contact and public evaluation of volunteer probation officers to promote understanding for social reintegration support. / Factors influencing differences between useful and useless regret. / The relationships between a metacognition scale and adaptive behavior in the regret situations: A comparison between junior high-school and university students. / Understanding confidence in human papillomavirus vaccine in Japan: A web-based questionnaire survey of mothers, female adolescents, and health care professionals. / 裁判員参加意向を規定する要因および意思決定プロセスの差異：制度施行前後の比較 / 市民の生態系サービスへの認知が保全行動意図に及ぼす影響：全国アンケートを用いた社会心理学的分析 / どのようにリスクを伝えればよいか：よりよいリスクコミュニケーションのために必要なこと / 意思決定から見たギャンブル行動 / Change of decision-making processes in repeated risk-taking behavior in a complex dynamic situation / The neural networks model of decision-making including feedback processes / Research on the gaps between students' expectation and satisfaction for universities / Analogical decision making in career choice</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>中学生の達成目標志向が学業成績に影響を及ぼすプロセスの検討：社会的比較感情・行動を媒介にして / ブランドのSNS活動における製品カテゴリが消費者のSNS使用に与える影響 / 中国人大学生におけるダイエット行動に関連する心理・社会的要因についての検討ー身体不満足感とやせ願望に着目してー / ユーザー生成コンテンツがアプリの粘着性と消費者の購買意図に与える影響に関する研究 / 在日中国人留学生の異文化適応に関する研究 / 個人差要因およびマンガ作品内の表現がマンガ読書行動に与える影響 / 福祉・介護サービス従事者のコミュニティ感覚とメンタルヘルスの関連性について / 新しいメディア環境におけるライブコマースが消費者心理と行動に影響を及ぼす要因の検討 / 中国人大学生のとりあえず進学に関する研究―個人差要因と学校適応感に着目して / 看護師支援における共感疲労に影響を及ぼす要因 / 読書状況が変えるネタバレ選好 / グリーン購入における他者の影響 / An Investigation of the Factors Influencing college student Volunteering motivation - In Perspectives on prosocial behaviour</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 意思決定分析 ; 都市・地域政策 ; 社会政策・福祉 ; オペレーションズリサーチ ; 政策評価・計量分析 ; 公共政策・社会工学 ; AI・データサイエンス ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
+          <t>社会心理学 ; 実験心理学 ; 労働経済・就職マッチング ; 意思決定分析 ; 都市・地域政策 ; 政策評価・計量分析 ; テキスト分析・NLP ; 医療・ヘルスデータ ; 公共政策・社会工学 ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 社会ネットワーク分析 ; マーケティング分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>社会心理学
+実験心理学
+意思決定
+認知心理学
+感情
+労働経済・就職マッチング
 意思決定分析
 都市・地域政策
-社会政策・福祉
-オペレーションズリサーチ
 政策評価・計量分析
+テキスト分析・NLP
+医療・ヘルスデータ
 公共政策・社会工学
 AI・データサイエンス
-環境・エネルギー
 労働経済
 人的資本
 就職マッチング
@@ -3639,22 +4089,38 @@
 地域政策
 土地利用
 公共政策評価
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
-数理最適化
-組合せ最適化
-計画・スケジューリング
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>中学生の達成目標志向が学業成績に影響を及ぼすプロセスの検討：社会的比較感情・行動を媒介にして / ブランドのSNS活動における製品カテゴリが消費者のSNS使用に与える影響 / 中国人大学生におけるダイエット行動に関連する心理・社会的要因についての検討ー身体不満足感とやせ願望に着目してー / ユーザー生成コンテンツがアプリの粘着性と消費者の購買意図に与える影響に関する研究 / 在日中国人留学生の異文化適応に関する研究 / 個人差要因およびマンガ作品内の表現がマンガ読書行動に与える影響 / 福祉・介護サービス従事者のコミュニティ感覚とメンタルヘルスの関連性について / 新しいメディア環境におけるライブコマースが消費者心理と行動に影響を及ぼす要因の検討 / 中国人大学生のとりあえず進学に関する研究―個人差要因と学校適応感に着目して / 看護師支援における共感疲労に影響を及ぼす要因 / 読書状況が変えるネタバレ選好 / グリーン購入における他者の影響 / An Investigation of the Factors Influencing college student Volunteering motivation - In Perspectives on prosocial behaviour
+実証分析
+テキストマイニング
+自然言語処理
+感情分析
+社会データ分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+社会ネットワーク分析
+マーケティング分析
+学習分析</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>中学生の達成目標志向が学業成績に影響を及ぼすプロセスの検討：社会的比較感情・行動を媒介にして
+ブランドのSNS活動における製品カテゴリが消費者のSNS使用に与える影響
+中国人大学生におけるダイエット行動に関連する心理・社会的要因についての検討ー身体不満足感とやせ願望に着目してー
+ユーザー生成コンテンツがアプリの粘着性と消費者の購買意図に与える影響に関する研究
+在日中国人留学生の異文化適応に関する研究
+個人差要因およびマンガ作品内の表現がマンガ読書行動に与える影響
+福祉・介護サービス従事者のコミュニティ感覚とメンタルヘルスの関連性について
+新しいメディア環境におけるライブコマースが消費者心理と行動に影響を及ぼす要因の検討
+中国人大学生のとりあえず進学に関する研究―個人差要因と学校適応感に着目して
+看護師支援における共感疲労に影響を及ぼす要因
+読書状況が変えるネタバレ選好
+グリーン購入における他者の影響
+An Investigation of the Factors Influencing college student Volunteering motivation - In Perspectives on prosocial behaviour
 過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として―
 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討
 リアルタイム場面におけるサービス・インタラクション理論の構築と実証
@@ -3729,6 +4195,17 @@
 道路パフォーマンス指標の開発
 コンテナ港湾機能配分に関する研究
 観光交通の需要分析
+土木計画学・交通工学
+観光学
+交通
+観光
+社会資本
+プロジェクト評価
+港湾
+物流
+オーバーツーリズム
+都市計画
+費用便益分析
 人口分布とネットワークを考慮したコミュニティバス運営負担に関する実証分析 ～茨城県の自治体を対象として～
 Analysis of Changes in Demand before and after the Restructuring of “Tsukubus”
 Simulation Analysis of Tsunami Evacuation Behavior for Residents and Seabathers Under Mixed Pedestrian-Automobile
@@ -3762,72 +4239,83 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>人口分布とネットワークを考慮したコミュニティバス運営負担に関する実証分析 ～茨城県の自治体を対象として～ / Analysis of Changes in Demand before and after the Restructuring of “Tsukubus” / Simulation Analysis of Tsunami Evacuation Behavior for Residents and Seabathers Under Mixed Pedestrian-Automobile / A Study of Recovery from Shocks Lead by Crisis in the Field of Tourism / Examination of A Risk Management Through Technical Transitions in The Railway ATS System / バス利用に影響を与える要因の検討－利用者意識調査とマクロ分析に基づいて－ / Consciousness Analysis on Travel Behavior and Intention of People in Mainland China / 道路ネットワーク上の交通荷重情報収集を目的とした車重計の配置方法 / つくば市における宅配便の利用実態と再配達依頼の規定因―配達人とのコミュニケーションに着目してー / 渡航回数に着目した中国人の旅行意向形成に関する研究 / 観光流行現象の変遷に関する基礎的考察 / 茨城県内の市町村における橋梁維持管理の実態に関する研究 / 英国を事例とした我が国の空港運営政策に関する一考察 / GPSログデータを用いた訪日外国人旅行者の訪問パターンの分析手法の開発 / 東京近郊観光地におけるインバウンド観光プロモーション施策の考察 / 人口分布統計データを活用した観光地の特性把握 / 高齢者の交通環境改善に向けた新たな交通手段の利用可能性に関する研究 / ガソリンスタンドの経営収支と需要を考慮した存続可能性に関する研究 / ガソリンスタンドの経営収支と需要を考慮した存続可能性に関する研究 / 効果的な鉄道の安全対策が新たな課題を惹起する―「安全の 4M」と「リスク」の体系化による考察とマネジメントの重要性― / 地域鉄道の維持に関する考察-時 系列データによる検討- / 都市高速道路における交通状態推定問題およびセンサー配置問題に対するデータ同化アプローチ / 橋梁および高速道路上の横断構造物に対する維持管理の実態と課題 / 国内旅行におけるリピーターの行動特性及び醸成要因に関する研究 / 観光地における地域ブランド構築の内部関係者による資源活用パターンと課題構造に関する研究 - 関東・甲信越地域の市町村を対象として -</t>
+          <t>土木計画学・交通工学 / 観光学</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>交通 / 観光 / 社会資本 / プロジェクト評価 / 港湾 / 物流 / オーバーツーリズム / 都市計画 / 費用便益分析</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>人口分布とネットワークを考慮したコミュニティバス運営負担に関する実証分析 ～茨城県の自治体を対象として～ / Analysis of Changes in Demand before and after the Restructuring of “Tsukubus” / Simulation Analysis of Tsunami Evacuation Behavior for Residents and Seabathers Under Mixed Pedestrian-Automobile / A Study of Recovery from Shocks Lead by Crisis in the Field of Tourism / Examination of A Risk Management Through Technical Transitions in The Railway ATS System / バス利用に影響を与える要因の検討－利用者意識調査とマクロ分析に基づいて－ / Consciousness Analysis on Travel Behavior and Intention of People in Mainland China / 道路ネットワーク上の交通荷重情報収集を目的とした車重計の配置方法 / つくば市における宅配便の利用実態と再配達依頼の規定因―配達人とのコミュニケーションに着目してー / 渡航回数に着目した中国人の旅行意向形成に関する研究 / 観光流行現象の変遷に関する基礎的考察 / 茨城県内の市町村における橋梁維持管理の実態に関する研究 / 英国を事例とした我が国の空港運営政策に関する一考察 / GPSログデータを用いた訪日外国人旅行者の訪問パターンの分析手法の開発 / 東京近郊観光地におけるインバウンド観光プロモーション施策の考察 / 人口分布統計データを活用した観光地の特性把握 / 高齢者の交通環境改善に向けた新たな交通手段の利用可能性に関する研究 / ガソリンスタンドの経営収支と需要を考慮した存続可能性に関する研究 / 効果的な鉄道の安全対策が新たな課題を惹起する―「安全の 4M」と「リスク」の体系化による考察とマネジメントの重要性― / 地域鉄道の維持に関する考察-時 系列データによる検討- / 都市高速道路における交通状態推定問題およびセンサー配置問題に対するデータ同化アプローチ / 橋梁および高速道路上の横断構造物に対する維持管理の実態と課題 / 国内旅行におけるリピーターの行動特性及び醸成要因に関する研究 / 観光地における地域ブランド構築の内部関係者による資源活用パターンと課題構造に関する研究 - 関東・甲信越地域の市町村を対象として -</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>鉄道の運行支障時における駅周辺道路の交通実態に関する研究 / 自動車の走行距離課税制度に対する社会的受容性に関する研究 / 公共交通のネットワーク形態が自治体の負担に与える影響に関する研究 / 高速交通ネットワークの発展に伴う基幹交通の組合せ利用に関する研究 / つくば市における公共交通に対する住民満足度の要因分析 / 地方誘導型インバウンド政策がもたらす経済的影響に関する研究 / 国内旅行実態の経年的変化に関する基礎的研究 / 津波避難シミュレーションを用いた海水浴場の危険性評価 / 地域公共交通に関する利用者意識調査の活用方法の検討 / Difference of tourists‘ behavior by transportation mode in Kamakura City / TX開通による沿線エリアの交通需要とアクセシビリティ変化に関する研究</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 交通・モビリティ ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>家族・人口政策
-都市・地域政策
-GIS・空間分析
-社会政策・福祉
+          <t>土木計画学・交通工学 ; 観光学 ; 交通・モビリティ ; 政策評価・計量分析 ; 観光・マーケティング ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 観光情報学 ; 社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>土木計画学・交通工学
+観光学
+交通
+観光
+社会資本
+プロジェクト評価
+港湾
+物流
+オーバーツーリズム
+都市計画
+費用便益分析
 交通・モビリティ
-ネットワーク・グラフ理論
 政策評価・計量分析
+観光・マーケティング
 公共政策・社会工学
-経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
-都市経済
-地域政策
-土地利用
-公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
 交通工学
 モビリティ設計
 交通需要分析
 ネットワーク設計
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>鉄道の運行支障時における駅周辺道路の交通実態に関する研究 / 自動車の走行距離課税制度に対する社会的受容性に関する研究 / 公共交通のネットワーク形態が自治体の負担に与える影響に関する研究 / 高速交通ネットワークの発展に伴う基幹交通の組合せ利用に関する研究 / つくば市における公共交通に対する住民満足度の要因分析 / 地方誘導型インバウンド政策がもたらす経済的影響に関する研究 / 国内旅行実態の経年的変化に関する基礎的研究 / 津波避難シミュレーションを用いた海水浴場の危険性評価 / 地域公共交通に関する利用者意識調査の活用方法の検討 / Difference of tourists‘ behavior by transportation mode in Kamakura City / TX開通による沿線エリアの交通需要とアクセシビリティ変化に関する研究
+実証分析
+観光データ分析
+マーケティング分析
+クラスタリング
+需要予測
+観光情報学
+社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>鉄道の運行支障時における駅周辺道路の交通実態に関する研究
+自動車の走行距離課税制度に対する社会的受容性に関する研究
+公共交通のネットワーク形態が自治体の負担に与える影響に関する研究
+高速交通ネットワークの発展に伴う基幹交通の組合せ利用に関する研究
+つくば市における公共交通に対する住民満足度の要因分析
+地方誘導型インバウンド政策がもたらす経済的影響に関する研究
+国内旅行実態の経年的変化に関する基礎的研究
+津波避難シミュレーションを用いた海水浴場の危険性評価
+地域公共交通に関する利用者意識調査の活用方法の検討
+Difference of tourists‘ behavior by transportation mode in Kamakura City
+TX開通による沿線エリアの交通需要とアクセシビリティ変化に関する研究
 持続可能な観光のための戦略的オーバーツーリズム対処療法の構築
 持続可能な観光地形成に向けた複雑系モデルとそれを用いた合意形成ツールの開発
 意識分析にもとづく国外旅行意向の国際比較研究
@@ -3899,6 +4387,8 @@
 量から質へのシフトを実現するための緑地の計画制度・設計手法・運用方法の研究
 樹冠表面温度を利用した都市気温分布図の作成と緑地の気候緩和機能の分析
 リモートセンシングを活用した生物季節学図の作成と都市微気候の評価
+都市農村計画
+緑地計画
 グリーンインフラ整備を支える緑化技術研究
 熱的快適性が屋外空間における滞在状態に与える影響に関する研究
 グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例
@@ -3931,42 +4421,48 @@
           <t>津波で失われた景観の再現による記憶の抽出と日常生活に結びついた場の解析 / 低環境負荷型住まい方の実践とソーシャル・キャピタル向上の相乗効果を誘発する都市デザイン－インドネシア・ジャカルタの中層住宅における建築空間・住民行動・コミュニティの関係分析 / 津波で失われた景観のデジタル再現と記憶の分析によるコミュニティが共有する場の解析 / 量から質へのシフトを実現するための緑地の計画制度・設計手法・運用方法の研究 / 樹冠表面温度を利用した都市気温分布図の作成と緑地の気候緩和機能の分析 / リモートセンシングを活用した生物季節学図の作成と都市微気候の評価</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>都市農村計画 / 緑地計画</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>グリーンインフラ整備を支える緑化技術研究 / 熱的快適性が屋外空間における滞在状態に与える影響に関する研究 / グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例 / 2023年度一般公開シンポジウム開催報告 / 座談会 「緑の基本計画」のこれからを考える座談会 : 制度創設30年目を迎えて / 量から質への転換 / 人と土地の関係を創造するよろこび / 「働くクルマと社会」特集にあたって / GPSデータを用いたスポーツイベント来場者の行動分析 / 企業のIR情報に見る都市緑地に関する第三者認証制度の取り扱いに関する研究 / 熱赤外域リモートセンシングデータを活用した市街地の土地被覆に関する研究 / 熱的快適性が屋外空間における滞在に与える影響に関する研究 / 可視化された温熱環境情報が屋外空間の利用に与える影響に関する研究 / An Empirical Study on Using Green Spaces Around an Office as Workplace in Summer: Considerations Based on Office Employees’ Trait Anxiety Tendencies / グリーンインフラと緑の基本計画 / これからの自律的な民間緑地整備に関する考察 / ノルウェーにおける地表面での雨水管理策に関する法改正における議論の特徴 / ランドスケープ分野におけるDX / グリーンインフラとしての平地林による防災機能 －災害現場で確認された農業気象災害軽減事例－ / 移動の体験と景観 / 企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ / 屋外空間利用がオフィスワーカーに与える心理・生理的影響とその要因に関する研究 / 人流ビッグデータを用いた「Natural Cities」と温熱環境の関係分析についての研究 / 季節の違いが緑化に対する支払意思額に与える影響 / 地域・土地との関係性の希薄化</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>温熱環境がランナーの深部体温に及ぼす影響の把握と都市緑道の暑熱対策の検討 / 屋外温熱環境の違いが来訪者の空間利用に与える影響に関する研究 / 地域の持続可能性に資する非住宅木造建築の実現における関係主体の役割と課題 〜大崎市鳴子こども園を事例として〜 / 温熱環境情報の提示が空間利用に与える影響に関する研究 / 総合設計制度により創出された公開空地の緑化の実態に関する研究 / 北京市におけるヒートアイランド現象の時空間特性の分析 / オフィス街における来街者の滞留行動の季節変化に関する研究ー丸の内仲通りを対象としてー / 屋外空間利用がオフィスワーカーに与える心理的・生理的影響とその要因に関する研究 / 都市住民と農家の都市農地保全に対する意識の乖離とその要因に関する研究 / GPSログデータを用いたCOVID-19流行下の都市公園利用と公園利用前後の行動パターンに関する研究 / 日常の生活行動と温熱環境が深部体温に与える影響に関する基礎的研究 / 歩行時の空間認識と歩行の快適性の関係に関する研究</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; スポーツデータ分析 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>都市・地域政策
+          <t>都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 災害分析 ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>都市農村計画
+緑地計画
+都市・地域政策
 GIS・空間分析
 社会政策・福祉
 建築・空間設計
 画像・視覚情報処理
-スポーツデータ分析
 災害・防災研究
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
-経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
 都市経済
 地域政策
 土地利用
@@ -3987,21 +4483,37 @@
 画像認識
 行動認識
 マルチモーダル解析
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
 災害社会学
 防災政策
 リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>温熱環境がランナーの深部体温に及ぼす影響の把握と都市緑道の暑熱対策の検討 / 屋外温熱環境の違いが来訪者の空間利用に与える影響に関する研究 / 地域の持続可能性に資する非住宅木造建築の実現における関係主体の役割と課題 〜大崎市鳴子こども園を事例として〜 / 温熱環境情報の提示が空間利用に与える影響に関する研究 / 総合設計制度により創出された公開空地の緑化の実態に関する研究 / 北京市におけるヒートアイランド現象の時空間特性の分析 / オフィス街における来街者の滞留行動の季節変化に関する研究ー丸の内仲通りを対象としてー / 屋外空間利用がオフィスワーカーに与える心理的・生理的影響とその要因に関する研究 / 都市住民と農家の都市農地保全に対する意識の乖離とその要因に関する研究 / GPSログデータを用いたCOVID-19流行下の都市公園利用と公園利用前後の行動パターンに関する研究 / 日常の生活行動と温熱環境が深部体温に与える影響に関する基礎的研究 / 歩行時の空間認識と歩行の快適性の関係に関する研究
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+災害分析
+社会ネットワーク分析
+行政データ分析
+学習分析</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>温熱環境がランナーの深部体温に及ぼす影響の把握と都市緑道の暑熱対策の検討
+屋外温熱環境の違いが来訪者の空間利用に与える影響に関する研究
+地域の持続可能性に資する非住宅木造建築の実現における関係主体の役割と課題 〜大崎市鳴子こども園を事例として〜
+温熱環境情報の提示が空間利用に与える影響に関する研究
+総合設計制度により創出された公開空地の緑化の実態に関する研究
+北京市におけるヒートアイランド現象の時空間特性の分析
+オフィス街における来街者の滞留行動の季節変化に関する研究ー丸の内仲通りを対象としてー
+屋外空間利用がオフィスワーカーに与える心理的・生理的影響とその要因に関する研究
+都市住民と農家の都市農地保全に対する意識の乖離とその要因に関する研究
+GPSログデータを用いたCOVID-19流行下の都市公園利用と公園利用前後の行動パターンに関する研究
+日常の生活行動と温熱環境が深部体温に与える影響に関する基礎的研究
+歩行時の空間認識と歩行の快適性の関係に関する研究
 津波で失われた景観の再現による記憶の抽出と日常生活に結びついた場の解析
 低環境負荷型住まい方の実践とソーシャル・キャピタル向上の相乗効果を誘発する都市デザイン－インドネシア・ジャカルタの中層住宅における建築空間・住民行動・コミュニティの関係分析
 津波で失われた景観のデジタル再現と記憶の分析によるコミュニティが共有する場の解析
@@ -4074,6 +4586,9 @@
 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化
 顧客の再試行と途中放棄を考慮したコールセンターのモデル化と性能解析
 再試行型待ち行列によるコールセンターの性能解析とサービス科学への応用
+数理情報学
+社会システム工学・安全システム
+応用確率論、 確率モデル、 待ち行列理論、 性能評価、 オペレーションズ・リサーチ、確率システム
 Performance Analysis of Energy-efficient Reliable AIoT System Architectures
 Queueing Model with Alternating Service for Zipper Merging
 A simulation study of the sojourn time in queueing systems with stochastically delayed information
@@ -4107,39 +4622,45 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Performance Analysis of Energy-efficient Reliable AIoT System Architectures / Queueing Model with Alternating Service for Zipper Merging / A simulation study of the sojourn time in queueing systems with stochastically delayed information / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers / Performance Analysis of Blockchain with Rollups / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times / Analysis of a Batch Arrival Queue with Power Saving Mode / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory / Analytical Modelling of Asymmetric Multi-core Servers / Energy-performance tradeoffs in server farms with batch services and setup times / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers / Queueing Analysis of an Ensemble Machine Learning System / Performance analysis of a collision channel with abandonments / Empirical architecture comparison of two-input machine learning systems for vision tasks / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes / Modeling and performance analysis of hybrid systems by queues with setup time / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing / To wait or not to wait: Strategic behaviors in an observable batch-service queueing system / A Two-Population Game in Observable Double-Ended Queueing Systems / Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems / Analysis of a Batch Arrival Queue with Power Saving Mode</t>
+          <t>数理情報学 / 社会システム工学・安全システム</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>応用確率論、 確率モデル、 待ち行列理論、 性能評価、 オペレーションズ・リサーチ、確率システム</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Performance Analysis of Energy-efficient Reliable AIoT System Architectures / Queueing Model with Alternating Service for Zipper Merging / A simulation study of the sojourn time in queueing systems with stochastically delayed information / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers / Performance Analysis of Blockchain with Rollups / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times / Analysis of a Batch Arrival Queue with Power Saving Mode / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory / Analytical Modelling of Asymmetric Multi-core Servers / Energy-performance tradeoffs in server farms with batch services and setup times / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers / Queueing Analysis of an Ensemble Machine Learning System / Performance analysis of a collision channel with abandonments / Empirical architecture comparison of two-input machine learning systems for vision tasks / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes / Modeling and performance analysis of hybrid systems by queues with setup time / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing / To wait or not to wait: Strategic behaviors in an observable batch-service queueing system / A Two-Population Game in Observable Double-Ended Queueing Systems / Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>集団サービス型無限サーバ待ち行列の解析 / 客とサーバの性質が異なるシステムにおける待ち現象の解析 / Modelling social media load through a birth-death-batch-immigration process / マルコフ連鎖を用いたレンタカーとオンデマンド交通の融合システムの性能評価 / 混雑度に依存するサービス速度変化を考慮した待ち行列モデルの分析と交通流への応用 / Sojourn time analysis for m/m/c/setup queues / 異なる省電力モードを導入した集団到着型複数サーバモデルの解析 / Retrial queues with two-way communication for cognitive networks</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>マッチング理論・ゲーム理論 ; オペレーションズリサーチ ; 交通・モビリティ ; 画像・視覚情報処理 ; サービス・待ち行列 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 待ち行列理論 ; サービス工学 ; システム性能評価</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>マッチング理論・ゲーム理論
+          <t>数理情報学 ; 社会システム工学・安全システム ; オペレーションズリサーチ ; 交通・モビリティ ; サービス・待ち行列 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 待ち行列理論 ; サービス工学 ; システム性能評価 ; 学習分析 ; 物流最適化</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>数理情報学
+社会システム工学・安全システム
+応用確率論、 確率モデル、 待ち行列理論、 性能評価、 オペレーションズ・リサーチ、確率システム
 オペレーションズリサーチ
 交通・モビリティ
-画像・視覚情報処理
 サービス・待ち行列
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
-都市・空間・交通
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
 数理最適化
 組合せ最適化
 計画・スケジューリング
@@ -4147,18 +4668,23 @@
 モビリティ設計
 交通需要分析
 ネットワーク設計
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
 待ち行列理論
 サービス工学
-システム性能評価</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>集団サービス型無限サーバ待ち行列の解析 / 客とサーバの性質が異なるシステムにおける待ち現象の解析 / Modelling social media load through a birth-death-batch-immigration process / マルコフ連鎖を用いたレンタカーとオンデマンド交通の融合システムの性能評価 / 混雑度に依存するサービス速度変化を考慮した待ち行列モデルの分析と交通流への応用 / Sojourn time analysis for m/m/c/setup queues / 異なる省電力モードを導入した集団到着型複数サーバモデルの解析 / Retrial queues with two-way communication for cognitive networks
+システム性能評価
+学習分析
+物流最適化</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>集団サービス型無限サーバ待ち行列の解析
+客とサーバの性質が異なるシステムにおける待ち現象の解析
+Modelling social media load through a birth-death-batch-immigration process
+マルコフ連鎖を用いたレンタカーとオンデマンド交通の融合システムの性能評価
+混雑度に依存するサービス速度変化を考慮した待ち行列モデルの分析と交通流への応用
+Sojourn time analysis for m/m/c/setup queues
+異なる省電力モードを導入した集団到着型複数サーバモデルの解析
+Retrial queues with two-way communication for cognitive networks
 AI時代の省エネ型データセンター性能の数理的解明
 省電力データセンターの協調機構の性能評価
 省電力サーバ群の性能評価と負荷分散に関する数理モデル
@@ -4233,6 +4759,12 @@
 イギリスの都市計画プランナーの職能団体による実務研修等を支えるシステムに関する研究
 オープンデータを踏まえた市民セクター主体のICT協働まちづくりに関する研究
 豪雨災害から避難弱者を守る共助的な避難行動計画づくりシステムに関する学際的研究
+都市計画・建築計画
+経済政策
+Industrial Location
+産業集積
+都市・地域政策
+都市計画制度
 土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで
 新しい時代の都市再生と公共貢献のあり方
 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題
@@ -4261,48 +4793,55 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>「協働型都市開発と公共貢献手法に係る今後の展開可能性に関する研究」に対する研究助成 / 「今後の都市再生におけるインセンティヴ制度のあり方に関連する研究」に対する研究助成 / 自治体保有資産の有効活用を目的とした公民共創プロセスに関する研究 / 公的不動産の有効活用実現のための公民連携促進策とアセットマネジメント戦略のあり方 / 公的不動産の有効活用実現のための公民連携促進策とアセットマネジメント戦略のあり方 / 中古住宅市場における空き家・空き地の流通促進のための公民連携体制のあり方に関する研究 / 既成市街地における不動産流通促進を通じた地域再生に資する土地利用制度に関する研究 / イギリスの都市計画プランナーの職能団体による実務研修等を支えるシステムに関する研究 / オープンデータを踏まえた市民セクター主体のICT協働まちづくりに関する研究 / 豪雨災害から避難弱者を守る共助的な避難行動計画づくりシステムに関する学際的研究</t>
+          <t>「協働型都市開発と公共貢献手法に係る今後の展開可能性に関する研究」に対する研究助成 / 「今後の都市再生におけるインセンティヴ制度のあり方に関連する研究」に対する研究助成 / 自治体保有資産の有効活用を目的とした公民共創プロセスに関する研究 / 公的不動産の有効活用実現のための公民連携促進策とアセットマネジメント戦略のあり方 / 中古住宅市場における空き家・空き地の流通促進のための公民連携体制のあり方に関する研究 / 既成市街地における不動産流通促進を通じた地域再生に資する土地利用制度に関する研究 / イギリスの都市計画プランナーの職能団体による実務研修等を支えるシステムに関する研究 / オープンデータを踏まえた市民セクター主体のICT協働まちづくりに関する研究 / 豪雨災害から避難弱者を守る共助的な避難行動計画づくりシステムに関する学際的研究</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで / 新しい時代の都市再生と公共貢献のあり方 / 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 / 都市再開発のこれからの「必要性」と「可能性」 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 / 農村集落における区域区分制度を前提とした土地利用調整手法の実態と活用可能性に関する研究 / 土地建物一体型市街地整備の「必要性」と「可能性」 : これまでとこれから / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に / つくば市による心肺停止傷病者発生位置情報の最寄AED管理者との共有が生み出す協働による救命効果に関する研究 / 地方自治体におけるオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 / 東京都区部における開発実態の評価を踏まえた開発拠点誘導政策の課題に関する研究 / 公民連携による空き家・空き地対策組織の展開と運営実態 / 避難行動要支援者名簿活用に向けた制度設計・運用プロセスにおける課題に関する研究 / オープンデータ施策に総合的に取り組む地方自治体の動因に関する研究 / 地方都市中心市街地における商店街の連続性を踏まえた空間整備の変遷と課題に関する研究 / 地方自治体のオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 / 世界からみた銀座のルールとガバナンス (特集 銀座と都市計画) -- (都市計画と銀座のルール) / 11027 地区スケールの賑わい空間構造の定量分析に関する研究 歩行空間と周辺土地利用に着目して / “Planning transparency and public involvement in pre-application discussions,” / 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 / 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) / 集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ / マイナンバー導入に伴う自治体業務情報システム改修事例に見るオープン化・標準化及び共同化の現状に関する研究 / マイナンバー導入事例に見る政府情報システム調達の現状に関する研究</t>
+          <t>都市計画・建築計画 / 経済政策</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>Industrial Location / 産業集積 / 都市・地域政策 / 都市計画制度</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで / 新しい時代の都市再生と公共貢献のあり方 / 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 / 都市再開発のこれからの「必要性」と「可能性」 / 農村集落における区域区分制度を前提とした土地利用調整手法の実態と活用可能性に関する研究 / 土地建物一体型市街地整備の「必要性」と「可能性」 : これまでとこれから / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に / つくば市による心肺停止傷病者発生位置情報の最寄AED管理者との共有が生み出す協働による救命効果に関する研究 / 地方自治体におけるオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 / 東京都区部における開発実態の評価を踏まえた開発拠点誘導政策の課題に関する研究 / 公民連携による空き家・空き地対策組織の展開と運営実態 / 避難行動要支援者名簿活用に向けた制度設計・運用プロセスにおける課題に関する研究 / オープンデータ施策に総合的に取り組む地方自治体の動因に関する研究 / 地方都市中心市街地における商店街の連続性を踏まえた空間整備の変遷と課題に関する研究 / 地方自治体のオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 / 世界からみた銀座のルールとガバナンス (特集 銀座と都市計画) -- (都市計画と銀座のルール) / 11027 地区スケールの賑わい空間構造の定量分析に関する研究 歩行空間と周辺土地利用に着目して / “Planning transparency and public involvement in pre-application discussions,” / 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 / 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) / 集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ / マイナンバー導入に伴う自治体業務情報システム改修事例に見るオープン化・標準化及び共同化の現状に関する研究 / マイナンバー導入事例に見る政府情報システム調達の現状に関する研究</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>地方都市の法定再開発における持続的運営の課題に関する研究ー権利変換手法に着目してー / 改正個人情報保護法を受けた避難行動要支援者名簿情報の提供方策に関する研究 / 管理型まちづくりへの転換における公民連携の地域管理体制に関する研究-組織の成立プロセスに着目して- / 民間業務範囲を拡大させた PFI 事業における事業実現過程の課題に関する研究 / 人口減少社会における土地利用調整手法の実態と活用可能性に関する研究 －茨城県桜川市を事例として－ / 都市公園における官民連携事業の課題に関する研究 / 公的不動産の有効活用を促進する民間提案プラットフォームにおける課題に関する研究 / 実効性のある個別避難計画に向けた作成プロセスについて / 外国資本による国内不動産投資の増加が周辺地域に与える影響についての考察 / 公的不動産の利活用に向けた情報発信と官民の対話に関する研究 / 公的不動産の有効活用に関する研究 ―自治体に着目して― / 神社更新に伴う分譲マンション開発の実態と課題に関する研究ー東京都区部の神社を対象としてー</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 保険・金融行動 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>家族・人口政策
+          <t>都市計画・建築計画 ; 経済政策 ; 保険・金融行動 ; 都市・地域政策 ; 建築・空間設計 ; 災害・防災研究 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 行政データ分析 ; 都市計画 ; 意思決定支援 ; 社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>都市計画・建築計画
+経済政策
+Industrial Location
+産業集積
+都市・地域政策
+都市計画制度
 保険・金融行動
-都市・地域政策
-GIS・空間分析
 建築・空間設計
 災害・防災研究
-政策評価・計量分析
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 行動ファイナンス
 金融市場分析
 ESG投資
@@ -4311,10 +4850,6 @@
 地域政策
 土地利用
 公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
 建築計画
 空間レイアウト生成
 居住空間設計
@@ -4322,15 +4857,26 @@
 災害社会学
 防災政策
 リスク評価
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>地方都市の法定再開発における持続的運営の課題に関する研究ー権利変換手法に着目してー / 改正個人情報保護法を受けた避難行動要支援者名簿情報の提供方策に関する研究 / 管理型まちづくりへの転換における公民連携の地域管理体制に関する研究-組織の成立プロセスに着目して- / 民間業務範囲を拡大させた PFI 事業における事業実現過程の課題に関する研究 / 人口減少社会における土地利用調整手法の実態と活用可能性に関する研究 －茨城県桜川市を事例として－ / 都市公園における官民連携事業の課題に関する研究 / 公的不動産の有効活用を促進する民間提案プラットフォームにおける課題に関する研究 / 実効性のある個別避難計画に向けた作成プロセスについて / 外国資本による国内不動産投資の増加が周辺地域に与える影響についての考察 / 公的不動産の利活用に向けた情報発信と官民の対話に関する研究 / 公的不動産の有効活用に関する研究 ―自治体に着目して― / 神社更新に伴う分譲マンション開発の実態と課題に関する研究ー東京都区部の神社を対象としてー
+行政データ分析
+都市計画
+意思決定支援
+社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>地方都市の法定再開発における持続的運営の課題に関する研究ー権利変換手法に着目してー
+改正個人情報保護法を受けた避難行動要支援者名簿情報の提供方策に関する研究
+管理型まちづくりへの転換における公民連携の地域管理体制に関する研究-組織の成立プロセスに着目して-
+民間業務範囲を拡大させた PFI 事業における事業実現過程の課題に関する研究
+人口減少社会における土地利用調整手法の実態と活用可能性に関する研究 －茨城県桜川市を事例として－
+都市公園における官民連携事業の課題に関する研究
+公的不動産の有効活用を促進する民間提案プラットフォームにおける課題に関する研究
+実効性のある個別避難計画に向けた作成プロセスについて
+外国資本による国内不動産投資の増加が周辺地域に与える影響についての考察
+公的不動産の利活用に向けた情報発信と官民の対話に関する研究
+公的不動産の有効活用に関する研究 ―自治体に着目して―
+神社更新に伴う分譲マンション開発の実態と課題に関する研究ー東京都区部の神社を対象としてー
 「協働型都市開発と公共貢献手法に係る今後の展開可能性に関する研究」に対する研究助成
 「今後の都市再生におけるインセンティヴ制度のあり方に関連する研究」に対する研究助成
 自治体保有資産の有効活用を目的とした公民共創プロセスに関する研究
@@ -4405,6 +4951,13 @@
 江戸武家地の空間変容に関する文理統合的研究
 北関東の町並みの建築的構成とその展開過程に関する研究
 常陸太田市鯨が丘歴史的建造物調査
+建築史・意匠
+都市計画・建築計画
+日本史
+建築史
+都市史
+保全型都市計画
+居住環境史
 近代中国青島市における「雑院一覧表 二十四年夏季」について
 五台山行宮座落地盤圖 からみた清代白雲寺行宮
 嵩山史跡群における建物の空間構成および登封県の建立の経緯
@@ -4439,48 +4992,49 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>建築史・意匠 / 都市計画・建築計画 / 日本史</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>建築史 / 都市史 / 保全型都市計画 / 居住環境史</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>近代中国青島市における「雑院一覧表 二十四年夏季」について / 五台山行宮座落地盤圖 からみた清代白雲寺行宮 / 嵩山史跡群における建物の空間構成および登封県の建立の経緯 / 近代の町並み景観の多様性：大火からの復興を通してみた近代の町並みに関する研究 その 1 / 戦後昭和期の横浜中華街における商住空間の分布と特徴：中区明細地図の考察から / 清代福州における住宅の類型とその特徴 古絵図 De Stud Hockzieuw en de stad Nanta を中心とした分析 / 明清時代漕運と大運河沿いの都市空間特性との関係 その 2： 済寧を例として / 「白川郷における駐車空間の分布と交通整備の経緯：重要伝統的建造物群保存地区における駐車空間に関する研究」 / 『大日本職業別明細図之内』の空間表現 千葉県北部の地図を対象に / 観光開発を目的とした窯業集落の保全の実態とその課題： 中国陝西省澄城県の伝統村落・堯頭村を事例に / 「清代蘇州の屋外空間における商人達の「自発的な居場所」 のパターン： 「姑蘇繁華図」の分析」 / 新刊紹介『リスボン』 / 明清時代における漕河沿い城・鎮の空間構成に関する研究（その1）：漕運システムと漕河沿岸空間の構成要素との関係 / 清代福州における住宅の三類型 / 大正期から戦前までの山下町における中国系事業所と公共施設の立地と特徴–Japan Directory、商工案内の分析から– / 清代福建省における「舗」の分布とその特性－連江県城を事例として－ / 清代五台山顕通寺の火災と修復工程 / 明清時代漕運と京杭大運河沿い都市の空間特性との関係－臨清を例として－ / 中国における団地構内の小規模野菜市場の空間利用－街商と住民の共存モデル－ / 新刊紹介『明暦の大火』 / 五台山塔院寺の建築の構成とその変容 / 「奈良県橿原市今井町における駐車場の出現パターン：重要伝統的建造物群保存地区の駐車空間に関する研究 その2」 / 「真壁のこれから：過去・現在・未来」 / 「商店街アーケードの空間の変容:十条銀座商店街を対象に」 / 「清代新疆の地域構造と都市群の立地 -軍政中心地イリを対象に- 」</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>東京都区部における銭湯の存続要因とその周辺環境に関する研究－江東区を事例として－ / 幕末の海防に伴う都市空間の変容-江戸沿岸部地域に着目して- / 旧軍用地が地域空間形成に与えた影響について―茨城県ひたちなか市を対象として― / 中国鉄鋼業の発達が都市空間に与えた影響ー近代の武漢を事例にー / 近代中国における鉄道交通基盤の導入と歴史的都市空間との関係—1888〜1958年の京津・津浦鉄道沿線都市を対象に— / 清代駅道の変遷と沿道集落・駅建築の特徴－山東省済南府地域を事例として / 華僑の投資・建設活動が新たな都市空間の形成に果たした役割ー清末〜民国期の広州市東山区を例としてー / 戦後における商店街の業態と空間の変容—高円寺、北千住、巣鴨を事例として— / 観光開発を目的とした窯業集落の保全・修景に関する研究—中国陝西省澄城県の伝統村落・堯頭村を事例に— / 近代中国における民間主導の計画的市街地「漢口模範区」の形成と変容 / 明清期陝西省における都市時報建築の立地と形態 / 近代の繊維都市の形成に模範撚糸工事が果たした役割 / 中国の近代化において交通システムの変容が在郷町の機能・空間に与えた影響 ～四川省資中県を事例として～ / 建設時期・地域による相違に着目した清代満城の都市形態に関する研究 / 農村地域における短路型集落の特徴と近代以降の変容ー茨城県の集落を対象にー / 中国天童寺の寺域及び構成施設の変遷：晋代の創建から近現代の保護まで / 明清時代の役人住宅における職階制度と建築様式の関係—陳氏の住宅を例に / 北京市歴史文化保護区におけるジェントリフィケーションの実態とメカニズム―南鑼鼓巷を事例に</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 保険・金融行動 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 交通・モビリティ ; 建築・空間設計 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-保険・金融行動
+          <t>建築史・意匠 ; 都市計画・建築計画 ; 日本史 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 都市計画 ; 人間中心設計 ; 社会ネットワーク分析 ; 環境工学</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>建築史・意匠
+都市計画・建築計画
+日本史
+建築史
+都市史
+保全型都市計画
+居住環境史
 都市・地域政策
 GIS・空間分析
-社会政策・福祉
-交通・モビリティ
 建築・空間設計
-政策評価・計量分析
 公共政策・社会工学
-経済・ファイナンス
 数理最適化・OR
-AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
 都市経済
 地域政策
 土地利用
@@ -4489,27 +5043,36 @@
 空間計量
 地理情報分析
 立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
 建築計画
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>東京都区部における銭湯の存続要因とその周辺環境に関する研究－江東区を事例として－ / 幕末の海防に伴う都市空間の変容-江戸沿岸部地域に着目して- / 旧軍用地が地域空間形成に与えた影響について―茨城県ひたちなか市を対象として― / 中国鉄鋼業の発達が都市空間に与えた影響ー近代の武漢を事例にー / 近代中国における鉄道交通基盤の導入と歴史的都市空間との関係—1888〜1958年の京津・津浦鉄道沿線都市を対象に— / 清代駅道の変遷と沿道集落・駅建築の特徴－山東省済南府地域を事例として / 華僑の投資・建設活動が新たな都市空間の形成に果たした役割ー清末〜民国期の広州市東山区を例としてー / 戦後における商店街の業態と空間の変容—高円寺、北千住、巣鴨を事例として— / 観光開発を目的とした窯業集落の保全・修景に関する研究—中国陝西省澄城県の伝統村落・堯頭村を事例に— / 近代中国における民間主導の計画的市街地「漢口模範区」の形成と変容 / 明清期陝西省における都市時報建築の立地と形態 / 近代の繊維都市の形成に模範撚糸工事が果たした役割 / 中国の近代化において交通システムの変容が在郷町の機能・空間に与えた影響 ～四川省資中県を事例として～ / 建設時期・地域による相違に着目した清代満城の都市形態に関する研究 / 農村地域における短路型集落の特徴と近代以降の変容ー茨城県の集落を対象にー / 中国天童寺の寺域及び構成施設の変遷：晋代の創建から近現代の保護まで / 明清時代の役人住宅における職階制度と建築様式の関係—陳氏の住宅を例に / 北京市歴史文化保護区におけるジェントリフィケーションの実態とメカニズム―南鑼鼓巷を事例に
+都市計画
+人間中心設計
+社会ネットワーク分析
+環境工学</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>東京都区部における銭湯の存続要因とその周辺環境に関する研究－江東区を事例として－
+幕末の海防に伴う都市空間の変容-江戸沿岸部地域に着目して-
+旧軍用地が地域空間形成に与えた影響について―茨城県ひたちなか市を対象として―
+中国鉄鋼業の発達が都市空間に与えた影響ー近代の武漢を事例にー
+近代中国における鉄道交通基盤の導入と歴史的都市空間との関係—1888〜1958年の京津・津浦鉄道沿線都市を対象に—
+清代駅道の変遷と沿道集落・駅建築の特徴－山東省済南府地域を事例として
+華僑の投資・建設活動が新たな都市空間の形成に果たした役割ー清末〜民国期の広州市東山区を例としてー
+戦後における商店街の業態と空間の変容—高円寺、北千住、巣鴨を事例として—
+観光開発を目的とした窯業集落の保全・修景に関する研究—中国陝西省澄城県の伝統村落・堯頭村を事例に—
+近代中国における民間主導の計画的市街地「漢口模範区」の形成と変容
+明清期陝西省における都市時報建築の立地と形態
+近代の繊維都市の形成に模範撚糸工事が果たした役割
+中国の近代化において交通システムの変容が在郷町の機能・空間に与えた影響 ～四川省資中県を事例として～
+建設時期・地域による相違に着目した清代満城の都市形態に関する研究
+農村地域における短路型集落の特徴と近代以降の変容ー茨城県の集落を対象にー
+中国天童寺の寺域及び構成施設の変遷：晋代の創建から近現代の保護まで
+明清時代の役人住宅における職階制度と建築様式の関係—陳氏の住宅を例に
+北京市歴史文化保護区におけるジェントリフィケーションの実態とメカニズム―南鑼鼓巷を事例に
 形態・材料に着目した近代町家の地域性とその形成要因
 モビリティーイノベーションの社会応用と未来社会工学研究5
 モビリティーイノベーションの社会応用と未来社会工学研究3
@@ -4583,6 +5146,10 @@
 ＱＣＤＲモデルに基づいて革新的な総合設備効率の向上と生産期間の短縮を実現する工場・設備の運用管理システム
 ＱＣＤモデルに基づくマルチチャンバ装置および生産ラインの運用・設計方法
 共創ビジョンに基づく半導体産業のビジネスモデル進化と、知財・人材の組織的流動化
+制御・システム工学
+生産システム工学
+オペレーション管理
+地域活性化
 "INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH
 Robust Classifications of WBM Defect Patterns
 Due dates assignment based on customer changeability classifications in Make-to-order productoins
@@ -4616,79 +5183,92 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>"INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH / Robust Classifications of WBM Defect Patterns / Due dates assignment based on customer changeability classifications in Make-to-order productoins / Pipeline production model and sensitivity analysis of Engineering-to-Order products using system dynamics / PRODUCTION AND JOB ROTATION PLANNING CONSIDERING DISABILITIES AND HEALTH CONDITIONS / Classification of Multivariate Time Series Signals Using Self-Supervised Representation Learning / Multi-factory Scheduling Considering the Trade-offs between Production Efficiency and Risks / Analysis of Resilience Factors and Satisfaction in Life-line Charts for Life Career Developments / Interaction Modeling for High-Dimensional Mixed Data with Numerical and Categorical Features / Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL / MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION / Mixed-type Defect Pattern Classifications / Interaction Modelling of High Dimensional Production Data / DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS / MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN / Data-driven Modeling for Production Dynamics / Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption / MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - / Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - / Interaction Modelings for Industrial Data - for final quality estimation and proess integration / スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 / 従属需要の予測手法の構築と検証 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 / Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling</t>
+          <t>制御・システム工学</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>生産システム工学 / オペレーション管理 / 地域活性化</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>"INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH / Robust Classifications of WBM Defect Patterns / Due dates assignment based on customer changeability classifications in Make-to-order productoins / Pipeline production model and sensitivity analysis of Engineering-to-Order products using system dynamics / PRODUCTION AND JOB ROTATION PLANNING CONSIDERING DISABILITIES AND HEALTH CONDITIONS / Classification of Multivariate Time Series Signals Using Self-Supervised Representation Learning / Multi-factory Scheduling Considering the Trade-offs between Production Efficiency and Risks / Analysis of Resilience Factors and Satisfaction in Life-line Charts for Life Career Developments / Interaction Modeling for High-Dimensional Mixed Data with Numerical and Categorical Features / Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL / MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION / Mixed-type Defect Pattern Classifications / Interaction Modelling of High Dimensional Production Data / DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS / MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN / Data-driven Modeling for Production Dynamics / Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption / MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - / Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - / Interaction Modelings for Industrial Data - for final quality estimation and proess integration / スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 / 従属需要の予測手法の構築と検証 / Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>多目的ハイブリッドフローショップスケジューリングの実証研究 / QR決済ヘビーユーザーの内外特徴の分析と活用 ～ キャンペーンと多種アプリ利用状況を考慮して / 保全時間を考慮した自律搬送ロボットのスケジューリング / n工程・多目的ハイブリッドフローショップスケジューリングの高速化～タブーリストと解構造の活用 / 生産リスクと段取りを考慮したMulti-factoryスケジューリング / 高次元交互作用モデリングにおける構造導入アプローチの効果検証 / 上流工場と処理単位の変化を考慮した投入制御ルールと多目的スケジューリングの融合 / 大規模データに対する変化検出と因果分析 / 多重共線性と因子効果ギャップを考慮した高次元交互作用モデリング / エネルギー消費量と納期遅れペナルティのトレードオフを考慮したセルフチューニングバッチ編成と多目的スケジューリング / 建設現場の多様性への対応する360度撮像と画像認識技術 / データ駆動プロセスインテグレーションのための高相関高次元データモデリング / ネットワーク理論に基づく高齢者福祉施設の最適化配置計画～茨城県通所型高齢者福祉施設の事例 / 相関関係を内包した多次元時系列データの予測モデリング / 高相関データの高因子効果比モデル推定 / 多品種繰り返し大規模生産システムのモデリングと最適スケジューリング～半導体Testbedを対象として / 自己教師あり学習を用いた多変量時系列信号の状態分類 / 料理アプリに着目したスマホ起動履歴の解析と情報推薦 / 高次元混合データの交互作用モデリング / 生産効率・人間工学リスク・エネルギーを考慮したジョブローテーションスケジューリング / 工場間搬送を考慮した並列分散型マルチファクトリー・スケジューリング / 営業コストを考慮したサプライチェーンにおける企業間多段階納期交渉 / エネルギー消費と待ち時間制約のトレードオフを考慮したサプライチェーン・スケジューリング / 画像マルチモーダル学習による半導体不良パターンの解析 / 時空間情報を用いた画像マルチモーダル学習による半導体不良パターンの高精度分類 / 資源・エネルギーロスを最小化する生産フロー制御つきマルチファクトリー・スケジューリング / 因果推論と機械学習による車載半導体需要予測 / 推薦システムによる多様なアプリの利用促進 / 高次元データの交互作用モデリング-Adaptive SFMとSafe Pruningによる高精度化 / 多様な建設現場の部材の検出と分類</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; オペレーションズリサーチ ; 建築・空間設計 ; 機械学習 ; 画像・視覚情報処理 ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>都市・地域政策
-GIS・空間分析
-社会政策・福祉
+          <t>制御・システム工学 ; 都市・地域政策 ; オペレーションズリサーチ ; 機械学習 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 物流最適化 ; 最適化</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>制御・システム工学
+生産システム工学
+オペレーション管理
+地域活性化
+都市・地域政策
 オペレーションズリサーチ
-建築・空間設計
 機械学習
-画像・視覚情報処理
-ネットワーク・グラフ理論
-政策評価・計量分析
 公共政策・社会工学
-経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
-環境・エネルギー
 都市経済
 地域政策
 土地利用
 公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
 数理最適化
 組合せ最適化
 計画・スケジューリング
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
 統計的学習
 予測モデリング
 表現学習
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>多目的ハイブリッドフローショップスケジューリングの実証研究 / QR決済ヘビーユーザーの内外特徴の分析と活用 ～ キャンペーンと多種アプリ利用状況を考慮して / 保全時間を考慮した自律搬送ロボットのスケジューリング / n工程・多目的ハイブリッドフローショップスケジューリングの高速化～タブーリストと解構造の活用 / 生産リスクと段取りを考慮したMulti-factoryスケジューリング / 高次元交互作用モデリングにおける構造導入アプローチの効果検証 / 上流工場と処理単位の変化を考慮した投入制御ルールと多目的スケジューリングの融合 / 大規模データに対する変化検出と因果分析 / 多重共線性と因子効果ギャップを考慮した高次元交互作用モデリング / エネルギー消費量と納期遅れペナルティのトレードオフを考慮したセルフチューニングバッチ編成と多目的スケジューリング / 建設現場の多様性への対応する360度撮像と画像認識技術 / データ駆動プロセスインテグレーションのための高相関高次元データモデリング / ネットワーク理論に基づく高齢者福祉施設の最適化配置計画～茨城県通所型高齢者福祉施設の事例 / 相関関係を内包した多次元時系列データの予測モデリング / 高相関データの高因子効果比モデル推定 / 多品種繰り返し大規模生産システムのモデリングと最適スケジューリング～半導体Testbedを対象として / 自己教師あり学習を用いた多変量時系列信号の状態分類 / 料理アプリに着目したスマホ起動履歴の解析と情報推薦 / 高次元混合データの交互作用モデリング / 生産効率・人間工学リスク・エネルギーを考慮したジョブローテーションスケジューリング / 工場間搬送を考慮した並列分散型マルチファクトリー・スケジューリング / 営業コストを考慮したサプライチェーンにおける企業間多段階納期交渉 / エネルギー消費と待ち時間制約のトレードオフを考慮したサプライチェーン・スケジューリング / 画像マルチモーダル学習による半導体不良パターンの解析 / 時空間情報を用いた画像マルチモーダル学習による半導体不良パターンの高精度分類 / 資源・エネルギーロスを最小化する生産フロー制御つきマルチファクトリー・スケジューリング / 因果推論と機械学習による車載半導体需要予測 / 推薦システムによる多様なアプリの利用促進 / 高次元データの交互作用モデリング-Adaptive SFMとSafe Pruningによる高精度化 / 多様な建設現場の部材の検出と分類
+物流最適化
+最適化</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>多目的ハイブリッドフローショップスケジューリングの実証研究
+QR決済ヘビーユーザーの内外特徴の分析と活用 ～ キャンペーンと多種アプリ利用状況を考慮して
+保全時間を考慮した自律搬送ロボットのスケジューリング
+n工程・多目的ハイブリッドフローショップスケジューリングの高速化～タブーリストと解構造の活用
+生産リスクと段取りを考慮したMulti-factoryスケジューリング
+高次元交互作用モデリングにおける構造導入アプローチの効果検証
+上流工場と処理単位の変化を考慮した投入制御ルールと多目的スケジューリングの融合
+大規模データに対する変化検出と因果分析
+多重共線性と因子効果ギャップを考慮した高次元交互作用モデリング
+エネルギー消費量と納期遅れペナルティのトレードオフを考慮したセルフチューニングバッチ編成と多目的スケジューリング
+建設現場の多様性への対応する360度撮像と画像認識技術
+データ駆動プロセスインテグレーションのための高相関高次元データモデリング
+ネットワーク理論に基づく高齢者福祉施設の最適化配置計画～茨城県通所型高齢者福祉施設の事例
+相関関係を内包した多次元時系列データの予測モデリング
+高相関データの高因子効果比モデル推定
+多品種繰り返し大規模生産システムのモデリングと最適スケジューリング～半導体Testbedを対象として
+自己教師あり学習を用いた多変量時系列信号の状態分類
+料理アプリに着目したスマホ起動履歴の解析と情報推薦
+高次元混合データの交互作用モデリング
+生産効率・人間工学リスク・エネルギーを考慮したジョブローテーションスケジューリング
+工場間搬送を考慮した並列分散型マルチファクトリー・スケジューリング
+営業コストを考慮したサプライチェーンにおける企業間多段階納期交渉
+エネルギー消費と待ち時間制約のトレードオフを考慮したサプライチェーン・スケジューリング
+画像マルチモーダル学習による半導体不良パターンの解析
+時空間情報を用いた画像マルチモーダル学習による半導体不良パターンの高精度分類
+資源・エネルギーロスを最小化する生産フロー制御つきマルチファクトリー・スケジューリング
+因果推論と機械学習による車載半導体需要予測
+推薦システムによる多様なアプリの利用促進
+高次元データの交互作用モデリング-Adaptive SFMとSafe Pruningによる高精度化
+多様な建設現場の部材の検出と分類
 遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化
 ワークライフバランスに貢献するサイバー・フィジカル製造業
 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配
@@ -4761,6 +5341,16 @@
 公共サービスの革新に関する研究
 医療相談アプリ「LEBER」を用いた医療費削減効果のデータ解析に関する学術指導
 日本政府のオープンデータ政策評価
+社会システム工学・安全システム
+都市計画・建築計画
+ウェブ情報学・サービス情報学
+図書館情報学・人文社会情報学
+財政・公共経済
+持続可能システム
+経営学
+地域研究
+環境影響評価
+オープンデータ、公共データ分析、自治体経営、地域情報化政策、国際協力
 在宅医療におけるD to P with Nの臨床的役割：訪問診療との比較による診療内容および受療パターンのケーススタディ
 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に
 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究
@@ -4795,31 +5385,53 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>社会システム工学・安全システム / 都市計画・建築計画 / ウェブ情報学・サービス情報学 / 図書館情報学・人文社会情報学 / 財政・公共経済 / 持続可能システム / 経営学 / 地域研究 / 環境影響評価</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>オープンデータ、公共データ分析、自治体経営、地域情報化政策、国際協力</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>在宅医療におけるD to P with Nの臨床的役割：訪問診療との比較による診療内容および受療パターンのケーススタディ / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 / 筑波大学理工学群におけるデータサイエンス応用基礎教育 / 水害時における市民の避難行動に関する意識の分析 / Asian Cities Connecting through Communities / 排水再利用設備に係る建築行政の現状と今後の動向 / 建設省--インテリジェントビルへの構図 / ペンシルバニア通り2121番地(第1便)「世界銀行」ってどんなところ? / 世界銀行の都市開発分野における日本の情報発信の方向性 / CIOの視点/INTERVIEW 人と人をつなげて進む川島流地域活性化のビジョン / 地方自治体における業務改革と情報システム構築の実際--佐賀県を事例として / 佐賀県 台帳記録管理システムによる業務改革 / 大きな社会システムのアーキテクチャ再構築を / 世界の潮流 : オープンデータ : エンドユーザーの視点に立ち便益が明確な事業の推進を / 事実証拠を根拠とした政策策定 : オープンデータ推進の効果 / オープンデータの最新動向と公共データ市場に関する考察 / 電子自治体と公共イノベーション / オープンデータの5W1H : 今、自治体は「オープンデータ」にどのように取り組むべきか / オープンデータからソーシャルイノベーションへ : 公共データ×ICT×市民力で社会課題を自ら解決する社会ヘ / 自治体がオープンデータに取り組む際の留意点 オープンデータの活用において自治体が成果を出すための5原則 / Society 5.0実現に向けて必要となる教育の方向性 / オープンガバナンス推進に求められる政府・自治体職員の能力 / VUCA時代の政策形成にデジタルをどう活かすか / 自治体会計情報のオープンデータ化の促進―国際基準COFOGによる費目分類に着目して―</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>地方自治体・企業におけるワーケーション関連の取り組み実態に関する研究 / 個別避難計画の作成促進方策に関する研究～常総市・つくばみらい市を対象として～ / 現代における茅葺き屋根保存に関する課題と適切な支援施策に関する研究 ―茨城県石岡市を事例として― / 避難支援関係主体の参画に着目した実効性のある個別避難計画作成プロセスに関する研究 ―令和２年７月豪雨による球磨川氾濫周辺地区を対象として― / ナッジメッセージを用いた地震に対する世帯備蓄促進に向けた社会実験 ―茨城県つくば市内の世帯を対象として― / 医療過疎地域におけるD to P with Nと訪問診療との代替・補完可能性に関する研究 ~ 長野県伊那市のモバイルクリニック運用を例に ~ / 認知症等行方不明者の発生記録を用いた捜索時間の短縮効果に関する研究 / 最寄AED急搬送システムの社会実装過程における不確実性を考慮したAED選定モデル / 地方の先進社会課題の解決に取り組んでいる若者起業家の成功要因に関する研究～修正エフェクチュエーション・モデルの検証～ / 高経年区分所有住宅の耐震性能を向上する建替え推進に向けた法制度設計上の課題に関する研究 ー台湾と日本の法制度の比較を通じてー</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>都市・地域政策
+          <t>社会システム工学・安全システム ; 都市計画・建築計画 ; ウェブ情報学・サービス情報学 ; 図書館情報学・人文社会情報学 ; 財政・公共経済 ; 持続可能システム ; 経営学 ; 地域研究 ; 環境影響評価 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 災害・防災研究 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 行政データ分析 ; 災害分析 ; 推薦システム ; 社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>社会システム工学・安全システム
+都市計画・建築計画
+ウェブ情報学・サービス情報学
+図書館情報学・人文社会情報学
+財政・公共経済
+持続可能システム
+経営学
+地域研究
+環境影響評価
+オープンデータ、公共データ分析、自治体経営、地域情報化政策、国際協力
+都市・地域政策
 GIS・空間分析
 建築・空間設計
 災害・防災研究
 政策評価・計量分析
+医療・ヘルスデータ
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
@@ -4843,12 +5455,33 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>地方自治体・企業におけるワーケーション関連の取り組み実態に関する研究 / 個別避難計画の作成促進方策に関する研究～常総市・つくばみらい市を対象として～ / 現代における茅葺き屋根保存に関する課題と適切な支援施策に関する研究 ―茨城県石岡市を事例として― / 避難支援関係主体の参画に着目した実効性のある個別避難計画作成プロセスに関する研究 ―令和２年７月豪雨による球磨川氾濫周辺地区を対象として― / ナッジメッセージを用いた地震に対する世帯備蓄促進に向けた社会実験 ―茨城県つくば市内の世帯を対象として― / 医療過疎地域におけるD to P with Nと訪問診療との代替・補完可能性に関する研究 ~ 長野県伊那市のモバイルクリニック運用を例に ~ / 認知症等行方不明者の発生記録を用いた捜索時間の短縮効果に関する研究 / 最寄AED急搬送システムの社会実装過程における不確実性を考慮したAED選定モデル / 地方の先進社会課題の解決に取り組んでいる若者起業家の成功要因に関する研究～修正エフェクチュエーション・モデルの検証～ / 高経年区分所有住宅の耐震性能を向上する建替え推進に向けた法制度設計上の課題に関する研究 ー台湾と日本の法制度の比較を通じてー
+実証分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+行政データ分析
+災害分析
+推薦システム
+社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>地方自治体・企業におけるワーケーション関連の取り組み実態に関する研究
+個別避難計画の作成促進方策に関する研究～常総市・つくばみらい市を対象として～
+現代における茅葺き屋根保存に関する課題と適切な支援施策に関する研究 ―茨城県石岡市を事例として―
+避難支援関係主体の参画に着目した実効性のある個別避難計画作成プロセスに関する研究 ―令和２年７月豪雨による球磨川氾濫周辺地区を対象として―
+ナッジメッセージを用いた地震に対する世帯備蓄促進に向けた社会実験 ―茨城県つくば市内の世帯を対象として―
+医療過疎地域におけるD to P with Nと訪問診療との代替・補完可能性に関する研究 ~ 長野県伊那市のモバイルクリニック運用を例に ~
+認知症等行方不明者の発生記録を用いた捜索時間の短縮効果に関する研究
+最寄AED急搬送システムの社会実装過程における不確実性を考慮したAED選定モデル
+地方の先進社会課題の解決に取り組んでいる若者起業家の成功要因に関する研究～修正エフェクチュエーション・モデルの検証～
+高経年区分所有住宅の耐震性能を向上する建替え推進に向けた法制度設計上の課題に関する研究 ー台湾と日本の法制度の比較を通じてー
 地方での生活空間データ連携
 Hack My Tsukuba 2018
 Hack My Tsukuba 2019
@@ -4921,6 +5554,17 @@
 地方自治体における道路維持管理業務のため
 空間計量経済学における最重要課題への挑戦と新たな展開
 道路台帳を活かした道路アセットマネジメントに関する研究
+土木計画学・交通工学
+道路維持管理
+空間計量経済学
+地理情報システム
+空間データ
+空間統計
+不動産
+不動産価格
+不動産賃料
+土地利用
+立地分析
 立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～
 東京23区における賃貸オフィスビルストックの地域性と経年変化
 The Impact of the Flight to Quality on Office Rents and Vacancy
@@ -4948,65 +5592,68 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>オルタナティブデータを用いたオフィス不動産市場分析の可能性 / オフィス賃貸マーケットに関する研究 / オフィス賃貸マーケットに関する研究 / オフィス賃貸マーケットに関する研究 / オフィス賃貸マーケットに関する研究 / 地方自治体における情報の利活用方策の導入 / 地方自治体における道路維持管理業務のため / 地方自治体における情報の利活用方策の導入 / 空間計量経済学における最重要課題への挑戦と新たな展開 / 道路台帳を活かした道路アセットマネジメントに関する研究</t>
+          <t>オルタナティブデータを用いたオフィス不動産市場分析の可能性 / オフィス賃貸マーケットに関する研究 / 地方自治体における情報の利活用方策の導入 / 地方自治体における道路維持管理業務のため / 空間計量経済学における最重要課題への挑戦と新たな展開 / 道路台帳を活かした道路アセットマネジメントに関する研究</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ / 東京23区における賃貸オフィスビルストックの地域性と経年変化 / The Impact of the Flight to Quality on Office Rents and Vacancy / Spillover Effect of Large Building Construction on Neighborhood Office Rents / 地域属性と産業振興政策に着目した新設会社の立地に関する考察 / 実用性を考慮したローカルな不動産価格指数の理論と実証. / デジタル化と立地がコロナ禍における私立中学校選択に与える影響. / 大規模オフィスビルの竣工が近隣のオフィス賃料に与える影響：アメニティ効果 vs 供給効果. / 東京オフィス市場における 集積の経済・不経済とその時間的変化 / Spillover Effect of Large Building Construction on Neighborhood Office Rents / Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics / Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market / ビッグデータのためのローカルなオフィス賃料指数の開発 / オフィス空室率の時空間変動に関する探索的小地域分析 / 東京オフィス市場における 集積の経済・不経済とその時間的変化 / 北陸新幹線開通による大学選択への影響に関する実証的研究 / 計量テキスト分析による道路橋を維持管理する技術力の解明の試み / 土木技術者の経験と学習 ―地方整備局職員の研究所出向と道路構造物を維持管理する技術力に着目して― / 空室率データで見る東京オフィス市場の空間的特性 / インフラの維持管理に関する研修による技術力向上効果の評価 ―道路橋の点検に着目して― / 東京オフィス市場における集積の経済・不経済とその時間的変化 / 携帯位置情報データを用いた東京23区内における“オフィス出社”の時空間分析 / 改訂版ブルーム・タキソノミーを用いた道路橋を維持管理する技術力の解明の試み / 交通アクセシビリティの変化が 中学受験における学校選択に与える影響 / モバイル端末の活用による地方自治体の道路維持業務支援の検討</t>
+          <t>土木計画学・交通工学</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>道路維持管理 / 空間計量経済学 / 地理情報システム / 空間データ / 空間統計 / 不動産 / 不動産価格 / 不動産賃料 / 土地利用 / 立地分析</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ / 東京23区における賃貸オフィスビルストックの地域性と経年変化 / The Impact of the Flight to Quality on Office Rents and Vacancy / Spillover Effect of Large Building Construction on Neighborhood Office Rents / 地域属性と産業振興政策に着目した新設会社の立地に関する考察 / 実用性を考慮したローカルな不動産価格指数の理論と実証. / デジタル化と立地がコロナ禍における私立中学校選択に与える影響. / 大規模オフィスビルの竣工が近隣のオフィス賃料に与える影響：アメニティ効果 vs 供給効果. / 東京オフィス市場における 集積の経済・不経済とその時間的変化 / Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics / Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market / ビッグデータのためのローカルなオフィス賃料指数の開発 / オフィス空室率の時空間変動に関する探索的小地域分析 / 北陸新幹線開通による大学選択への影響に関する実証的研究 / 計量テキスト分析による道路橋を維持管理する技術力の解明の試み / 土木技術者の経験と学習 ―地方整備局職員の研究所出向と道路構造物を維持管理する技術力に着目して― / 空室率データで見る東京オフィス市場の空間的特性 / インフラの維持管理に関する研修による技術力向上効果の評価 ―道路橋の点検に着目して― / 東京オフィス市場における集積の経済・不経済とその時間的変化 / 携帯位置情報データを用いた東京23区内における“オフィス出社”の時空間分析 / 改訂版ブルーム・タキソノミーを用いた道路橋を維持管理する技術力の解明の試み / 交通アクセシビリティの変化が 中学受験における学校選択に与える影響 / モバイル端末の活用による地方自治体の道路維持業務支援の検討</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>自然災害発生による学校選択行動への影響ー首都圏私立中学を対象としてー / 東京オフィス市場における賃料調整過程の異質性と非対称性 / 非労働環境におけるライフキャリア形成プロセス / The Effect of the Housing Prices on the Household Savings in Urban China Under the Trend of Aging Society / The Determinants of China’s crude birth rate and regional difference ——Under the effect of two child policy / 中国における個人用固定資産税改革の効果分析 / 物流企業を考慮した応用都市経済モデルの開発に向けて / 国内政策の普及の実態 ～マイナンバーカードを事例として～ / 地域おこし協力隊の受け入れをめぐる自治体間競争に関する考察 / 大阪市における学力テストスコアと賃料の関係 ～小学校学校選択制の導入から～ / サービス付き高齢者向け住宅の賃料と立地選択の影響要因に関する研究</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 保険・金融行動 ; 意思決定分析 ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-保険・金融行動
-意思決定分析
+          <t>土木計画学・交通工学 ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; マーケティング分析 ; 災害分析 ; 都市計画</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>土木計画学・交通工学
+道路維持管理
+空間計量経済学
+地理情報システム
+空間データ
+空間統計
+不動産
+不動産価格
+不動産賃料
+土地利用
+立地分析
 都市・地域政策
 GIS・空間分析
 交通・モビリティ
 建築・空間設計
-災害・防災研究
 政策評価・計量分析
 公共政策・社会工学
 経済・ファイナンス
+数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
-行動意思決定
-実験・行動分析
-ナッジ
-意思決定支援
 都市経済
 地域政策
-土地利用
 公共政策評価
 GIS
 空間計量
 地理情報分析
-立地分析
 交通工学
 モビリティ設計
 交通需要分析
@@ -5015,18 +5662,29 @@
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
-災害社会学
-防災政策
-リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>自然災害発生による学校選択行動への影響ー首都圏私立中学を対象としてー / 東京オフィス市場における賃料調整過程の異質性と非対称性 / 非労働環境におけるライフキャリア形成プロセス / The Effect of the Housing Prices on the Household Savings in Urban China Under the Trend of Aging Society / The Determinants of China’s crude birth rate and regional difference ——Under the effect of two child policy / 中国における個人用固定資産税改革の効果分析 / 物流企業を考慮した応用都市経済モデルの開発に向けて / 国内政策の普及の実態 ～マイナンバーカードを事例として～ / 地域おこし協力隊の受け入れをめぐる自治体間競争に関する考察 / 大阪市における学力テストスコアと賃料の関係 ～小学校学校選択制の導入から～ / サービス付き高齢者向け住宅の賃料と立地選択の影響要因に関する研究
+実証分析
+行政データ分析
+マーケティング分析
+災害分析
+都市計画</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>自然災害発生による学校選択行動への影響ー首都圏私立中学を対象としてー
+東京オフィス市場における賃料調整過程の異質性と非対称性
+非労働環境におけるライフキャリア形成プロセス
+The Effect of the Housing Prices on the Household Savings in Urban China Under the Trend of Aging Society
+The Determinants of China’s crude birth rate and regional difference ——Under the effect of two child policy
+中国における個人用固定資産税改革の効果分析
+物流企業を考慮した応用都市経済モデルの開発に向けて
+国内政策の普及の実態 ～マイナンバーカードを事例として～
+地域おこし協力隊の受け入れをめぐる自治体間競争に関する考察
+大阪市における学力テストスコアと賃料の関係 ～小学校学校選択制の導入から～
+サービス付き高齢者向け住宅の賃料と立地選択の影響要因に関する研究
 オルタナティブデータを用いたオフィス不動産市場分析の可能性
 オフィス賃貸マーケットに関する研究
 地方自治体における情報の利活用方策の導入
@@ -5095,6 +5753,16 @@
 環境配慮行動と充足感のポジティブな連鎖に関する縦断的研究
 環境政策が市民の環境意識と省エネルギー行動に及ぼす波及効果
 新たな持続的開発指標にもとづく国際環境協力政策評価に関する研究
+環境政策・環境社会システム
+持続可能システム
+土木環境システム
+社会心理学
+環境心理学
+人間と環境の相互作用
+環境価値観・意識
+環境配慮行動
+気候関連行動
+場所愛着
 Validating the dragons of inaction psychological barriers (DIPB) scale in Japan and China: cross-cultural insights on climate change mitigation behaviors
 Potentials of No Single-Use Plastic Initiatives for Plastic Waste Management in Island Communities in Central Vietnam: Insights from Local Stakeholder Interviews
 Drivers of plastic waste reduction in island communities in Central Vietnam: An application of the extended theory of planned behavior
@@ -5128,35 +5796,52 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Validating the dragons of inaction psychological barriers (DIPB) scale in Japan and China: cross-cultural insights on climate change mitigation behaviors / Potentials of No Single-Use Plastic Initiatives for Plastic Waste Management in Island Communities in Central Vietnam: Insights from Local Stakeholder Interviews / Drivers of plastic waste reduction in island communities in Central Vietnam: An application of the extended theory of planned behavior / 景観特性と心理的要因が回復環境形成に与える影響：都市・歴史文化・自然環境の比較 / 航空移動に対する環境負荷認識と相殺行動・主観的幸福感の関係性：日本国内航空会社マイレージ会員調査にもとづく検証 / 騒音源公共施設の受容促進における情報提示の効果：質問紙実験による検証 / Children’s Pro-Environmental Attitudes and Behaviors in Climate Change Mitigation: Findings from Japan and China / Parent-Child Intergenerational Associations of Environmental Attitudes, Psychological Barriers, and Pro-Environmental Behaviors in Japan and China / The function of REM and NREM sleep on memory distortion and consolidation / Health versus environment in alternative meat adoption: An experiment of communication strategies / Relevance of faith and its positive associations with plastic pollution mitigation behaviors : Findings from Japan and Malaysia / Psychological determinants of waste-related pro-environmental behavior by recreational anglers in inland waters in the Kanto region, Japan / Opportunities and challenges for circular economy in the Maldives: A stakeholder analysis of informal E-waste management in the Greater Malé Region / 肉類消費抑制と代替肉普及のためのコミュニケーション方策の効果検証 / The function of REM and NREM sleep on memory distortion and consolidation / Associations of Positive and Negative Perceptions of Outdoor Artificial Light at Night with Nighttime Outdoor Behaviors and Health: Self-Reported Data Analyses on Urban and Suburban Residents in Japan / 容器包装プラスチック分別の社会的受容性：住民の納得感に着目して / Memory load of information encoded amplifies the magnitude of hindsight bias / Effects of outdoor artificial light at night on human health and behavior: A literature review / 環境問題を意識し始めた過去のきっかけと現在の環境配慮行動の関係：大学生を対象に / 路上ポイ捨ての理由と解決方策に関する認識比較分析：日本・マレーシア大学生を対象に / Linking environmental knowledge, attitude, and behavior with place: a case study for strategic environmental education planning in Saint Lucia / 環境問題を意識し始める契機と環境配慮行動の関係：大学生を対象に / 夜間屋外光環境に対する主観的評価と屋外行動の関係 / Discrepancies between beliefs and practices on sleep as a factor of insomnia and negative feelings</t>
+          <t>環境政策・環境社会システム / 持続可能システム / 土木環境システム / 社会心理学</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>環境心理学 / 人間と環境の相互作用 / 環境価値観・意識 / 環境配慮行動 / 気候関連行動 / 場所愛着</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Validating the dragons of inaction psychological barriers (DIPB) scale in Japan and China: cross-cultural insights on climate change mitigation behaviors / Potentials of No Single-Use Plastic Initiatives for Plastic Waste Management in Island Communities in Central Vietnam: Insights from Local Stakeholder Interviews / Drivers of plastic waste reduction in island communities in Central Vietnam: An application of the extended theory of planned behavior / 景観特性と心理的要因が回復環境形成に与える影響：都市・歴史文化・自然環境の比較 / 航空移動に対する環境負荷認識と相殺行動・主観的幸福感の関係性：日本国内航空会社マイレージ会員調査にもとづく検証 / 騒音源公共施設の受容促進における情報提示の効果：質問紙実験による検証 / Children’s Pro-Environmental Attitudes and Behaviors in Climate Change Mitigation: Findings from Japan and China / Parent-Child Intergenerational Associations of Environmental Attitudes, Psychological Barriers, and Pro-Environmental Behaviors in Japan and China / The function of REM and NREM sleep on memory distortion and consolidation / Health versus environment in alternative meat adoption: An experiment of communication strategies / Relevance of faith and its positive associations with plastic pollution mitigation behaviors : Findings from Japan and Malaysia / Psychological determinants of waste-related pro-environmental behavior by recreational anglers in inland waters in the Kanto region, Japan / Opportunities and challenges for circular economy in the Maldives: A stakeholder analysis of informal E-waste management in the Greater Malé Region / 肉類消費抑制と代替肉普及のためのコミュニケーション方策の効果検証 / Associations of Positive and Negative Perceptions of Outdoor Artificial Light at Night with Nighttime Outdoor Behaviors and Health: Self-Reported Data Analyses on Urban and Suburban Residents in Japan / 容器包装プラスチック分別の社会的受容性：住民の納得感に着目して / Memory load of information encoded amplifies the magnitude of hindsight bias / Effects of outdoor artificial light at night on human health and behavior: A literature review / 環境問題を意識し始めた過去のきっかけと現在の環境配慮行動の関係：大学生を対象に / 路上ポイ捨ての理由と解決方策に関する認識比較分析：日本・マレーシア大学生を対象に / Linking environmental knowledge, attitude, and behavior with place: a case study for strategic environmental education planning in Saint Lucia / 環境問題を意識し始める契機と環境配慮行動の関係：大学生を対象に / 夜間屋外光環境に対する主観的評価と屋外行動の関係 / Discrepancies between beliefs and practices on sleep as a factor of insomnia and negative feelings</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>河川に対する地域住民の評価及び印象による水害防災意識・行動の差異 / 容器包装プラスチック分別の社会的受容性：納得感に着目して / 環境配慮型製品のオンライン購買における効果的な情報提供の探索：アイトラッキングを用いた実証研究 / Effects of e-taxi usage on citizens’ willingness to purchase electric vehicles in Shenzhen, China / 成果情報提示による家庭ごみ減量の意図促進効果：地域と個人の関係に着目して / 都市地域環境の変化が現在の環境配慮行動に与える影響：つくば市住民に着目して / 航空移動の心理的価値評価：幸福感と相殺行動に着目して</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>意思決定分析 ; 都市・地域政策 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>意思決定分析
+          <t>環境政策・環境社会システム ; 持続可能システム ; 土木環境システム ; 社会心理学 ; 意思決定分析 ; 都市・地域政策 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 環境工学 ; 災害分析 ; 社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>環境政策・環境社会システム
+持続可能システム
+土木環境システム
+社会心理学
+環境心理学
+人間と環境の相互作用
+環境価値観・意識
+環境配慮行動
+気候関連行動
+場所愛着
+意思決定分析
 都市・地域政策
-画像・視覚情報処理
-災害・防災研究
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 AI・データサイエンス
-都市・空間・交通
-環境・エネルギー
 行動意思決定
 実験・行動分析
 ナッジ
@@ -5165,22 +5850,28 @@
 地域政策
 土地利用
 公共政策評価
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
-災害社会学
-防災政策
-リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>河川に対する地域住民の評価及び印象による水害防災意識・行動の差異 / 容器包装プラスチック分別の社会的受容性：納得感に着目して / 環境配慮型製品のオンライン購買における効果的な情報提供の探索：アイトラッキングを用いた実証研究 / Effects of e-taxi usage on citizens’ willingness to purchase electric vehicles in Shenzhen, China / 成果情報提示による家庭ごみ減量の意図促進効果：地域と個人の関係に着目して / 都市地域環境の変化が現在の環境配慮行動に与える影響：つくば市住民に着目して / 航空移動の心理的価値評価：幸福感と相殺行動に着目して
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+環境工学
+災害分析
+社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>河川に対する地域住民の評価及び印象による水害防災意識・行動の差異
+容器包装プラスチック分別の社会的受容性：納得感に着目して
+環境配慮型製品のオンライン購買における効果的な情報提供の探索：アイトラッキングを用いた実証研究
+Effects of e-taxi usage on citizens’ willingness to purchase electric vehicles in Shenzhen, China
+成果情報提示による家庭ごみ減量の意図促進効果：地域と個人の関係に着目して
+都市地域環境の変化が現在の環境配慮行動に与える影響：つくば市住民に着目して
+航空移動の心理的価値評価：幸福感と相殺行動に着目して
 環境配慮行動の心理的障壁を形成・緩和する「きっかけ」体験の地域横断研究
 気候変動緩和行動に対する心理的障壁軽減方策のための日中比較実験研究
 分布型水土流出モデルの長期解析に基づく流木被害軽減のための森林管理手法の検討
@@ -5254,6 +5945,10 @@
 ASEAN諸国におけるモビリティ・マネジメントの実行可能性に関する実証分析
 道路上の異モード間コミュニケーションの生起と社会的受容
 健康に配慮した交通行動誘発のための学際的研究
+土木計画学・交通工学
+交通計画
+都市計画における態度・行動変容研究
+リスク･コミュニケーション
 ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析
 Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo
 Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt
@@ -5286,45 +5981,48 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo / Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo / 高齢運転者向け認知機能検査における制度変更の影響評価 / Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour / おつかい行動に見る子どもの移動自由性の世代変化と要因分析 / 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 / 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 / 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― / 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― / モビリティのイノベーションに，モビリティ･マネジメントをどう活かすか？ / モビリティ・マネジメントと健康福祉・教育 / 日米の車両生成データ制作の現状とEUのData Actの波及可能性 / SWC首長研究会への加盟有無(健康都市づくりに対する首長の意識)と公共交通分担率が住民の心身の健康に与える影響 / 「報復の空白」と「運」が交通事故時の道徳的判断に与える影響－自動運転と手動運転の比較分析－ / 東京都区部の電動キックボードシェア利用実態と利用体験・交通手段別視点による比較分析 / 米国における自動運転タクシーの社会的受容とその要因分析－人身事故経験を有する二都市に着目して / おつかい行動に見る子どもの移動自由性の世代変化とその要因分析，最近の調査研究から / 新たなモビリティの規制緩和－思考停止の日本人，大丈夫？ / モビリティ・マネジメントとの出会いと今後 / 基礎自治体における電動キックボードビジネス のガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― / 高齢運転者向け認知機能検査における制度変更の影響評価 / 米国の自動運転車両の事故発生後の 社会的受容の比較分析 / 奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討</t>
+          <t>土木計画学・交通工学</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>交通計画 / 都市計画における態度・行動変容研究 / リスク･コミュニケーション</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo / Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt / 高齢運転者向け認知機能検査における制度変更の影響評価 / Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour / おつかい行動に見る子どもの移動自由性の世代変化と要因分析 / 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 / 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 / 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― / 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― / モビリティのイノベーションに，モビリティ･マネジメントをどう活かすか？ / モビリティ・マネジメントと健康福祉・教育 / 日米の車両生成データ制作の現状とEUのData Actの波及可能性 / SWC首長研究会への加盟有無(健康都市づくりに対する首長の意識)と公共交通分担率が住民の心身の健康に与える影響 / 「報復の空白」と「運」が交通事故時の道徳的判断に与える影響－自動運転と手動運転の比較分析－ / 東京都区部の電動キックボードシェア利用実態と利用体験・交通手段別視点による比較分析 / 米国における自動運転タクシーの社会的受容とその要因分析－人身事故経験を有する二都市に着目して / おつかい行動に見る子どもの移動自由性の世代変化とその要因分析，最近の調査研究から / 新たなモビリティの規制緩和－思考停止の日本人，大丈夫？ / モビリティ・マネジメントとの出会いと今後 / 基礎自治体における電動キックボードビジネス のガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― / 米国の自動運転車両の事故発生後の 社会的受容の比較分析 / 奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>電動キックボードの社会的受容 －国内外専門家の懸念と東京都区部への影響 / EUデータ政策を事例にしたわが国の自動車産業における課題の調査研究 / 高速道路での渋滞吸収走行普及に向けた情報提供と先導車種によるドライバーの心理変化 / 俯瞰的整理を通じた「地域の公共交通向上の担い手人材」育成に向けた取組みの現状と課題</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; 社会政策・福祉 ; 交通・モビリティ ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-マッチング理論・ゲーム理論
+          <t>土木計画学・交通工学 ; 都市・地域政策 ; 社会政策・福祉 ; 交通・モビリティ ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 計算社会科学 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>土木計画学・交通工学
+交通計画
+都市計画における態度・行動変容研究
+リスク･コミュニケーション
 都市・地域政策
 社会政策・福祉
 交通・モビリティ
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 数理最適化・OR
-AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
 都市経済
 地域政策
 土地利用
@@ -5340,12 +6038,22 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>電動キックボードの社会的受容 －国内外専門家の懸念と東京都区部への影響 / EUデータ政策を事例にしたわが国の自動車産業における課題の調査研究 / 高速道路での渋滞吸収走行普及に向けた情報提供と先導車種によるドライバーの心理変化 / 俯瞰的整理を通じた「地域の公共交通向上の担い手人材」育成に向けた取組みの現状と課題
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+社会ネットワーク分析
+計算社会科学
+学習分析</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>電動キックボードの社会的受容 －国内外専門家の懸念と東京都区部への影響
+EUデータ政策を事例にしたわが国の自動車産業における課題の調査研究
+高速道路での渋滞吸収走行普及に向けた情報提供と先導車種によるドライバーの心理変化
+俯瞰的整理を通じた「地域の公共交通向上の担い手人材」育成に向けた取組みの現状と課題
 「クルマ」と「自動化するクルマ」の社会的受容の包括的理解に向けた学際研究
 ナラティブで編まれる地域交通コミュニティ形成と人材プログラムの研究開発
 健康にやさしい環境整備に係る実証事業
@@ -5420,6 +6128,13 @@
 ネットワーク上の時間軸をもった最適化問題とその応用
 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化
 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開
+数学基礎・応用数学
+組合せ論
+トポロジー的組合せ論
+シェラビリティー
+単体的複体
+離散構造
+離散幾何
 The average expected value of a rooted graph, Monte Carlo calculation, and a power index for the voting game
 Coloring zonotopal quadrangulations of the projective space
 Several minimality concepts related to Frankl's conjecture
@@ -5454,62 +6169,67 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t>数学基礎・応用数学</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>組合せ論 / トポロジー的組合せ論 / シェラビリティー / 単体的複体 / 離散構造 / 離散幾何</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>The average expected value of a rooted graph, Monte Carlo calculation, and a power index for the voting game / Coloring zonotopal quadrangulations of the projective space / Several minimality concepts related to Frankl's conjecture / Some computational studies of the root distribution of Ehrhart polynomials / The root distributions of Ehrhart polynomials of free sums of reflexive polytopes / Sequential Partitions of Nonpure Simplicial Complexes / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting / Pure-strategy Nash equilibria on competitive diffusion games / Hereditary properties and obstructions of simplicial complexes / A comment on pure-strategy Nash equilibria in competitive diffusion games / Obstructions to shellability, partitionability, and sequential Cohen-Macaulayness / Decompositions of two-dimensional simplicial complexes / A note on shellability and acyclic orientations / On the topology of the free complexes of convex geometries / A factorization theorem of characteristic polynomials of convex geometries / The max-flow min-cut property of two-dimensional affine convex geometries / h-Assignments of simplicial complexes and reverse search / Tangle sum and constructible spheres / Deciding constructibility of 3-balls with at most two interior vertices / Non-constructible complexes and the bridge index / Decompositions of balls and spheres with knots consisting of few edges / Nonconstructible balls and a way of testing constructibility / Constructible complexes and recursive division of posets / セル複体に付随するグラフの向き付けとその最適解 / 核付アフィン点配置の根付サーキット系の性質について</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>飛行禁止空域のある空間におけるドローンを用いた監視経路決定 / グラフ理論における再構成問題及び再構成数に関する一考察 / 最大次数が4以下のグラフにおける1-2 Conjectureについて / 低discrepancy点集合の構成における数独超方格の応用 / 繰り返し離散ボロノイゲームのヒューリスティック解法の検討 / 特定の形をした直径が6の木グラフに対するGraceful Labeling</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>GIS・空間分析 ; オペレーションズリサーチ ; 建築・空間設計 ; 機械学習 ; 画像・視覚情報処理 ; ネットワーク・グラフ理論 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>GIS・空間分析
+          <t>数学基礎・応用数学 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; ネットワーク科学 ; 社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>数学基礎・応用数学
+組合せ論
+トポロジー的組合せ論
+シェラビリティー
+単体的複体
+離散構造
+離散幾何
 オペレーションズリサーチ
-建築・空間設計
-機械学習
-画像・視覚情報処理
 ネットワーク・グラフ理論
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
-GIS
-空間計量
-地理情報分析
-立地分析
 数理最適化
 組合せ最適化
 計画・スケジューリング
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-統計的学習
-予測モデリング
-表現学習
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
 グラフ理論
 離散数学
 ネットワーク最適化
-組合せ構造</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>飛行禁止空域のある空間におけるドローンを用いた監視経路決定 / グラフ理論における再構成問題及び再構成数に関する一考察 / 最大次数が4以下のグラフにおける1-2 Conjectureについて / 低discrepancy点集合の構成における数独超方格の応用 / 繰り返し離散ボロノイゲームのヒューリスティック解法の検討 / 特定の形をした直径が6の木グラフに対するGraceful Labeling
+組合せ構造
+ネットワーク科学
+社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>飛行禁止空域のある空間におけるドローンを用いた監視経路決定
+グラフ理論における再構成問題及び再構成数に関する一考察
+最大次数が4以下のグラフにおける1-2 Conjectureについて
+低discrepancy点集合の構成における数独超方格の応用
+繰り返し離散ボロノイゲームのヒューリスティック解法の検討
+特定の形をした直径が6の木グラフに対するGraceful Labeling
 トポロジー的組合せ論と組合せ論におけるトポロジー的手法
 組合せ的構造に関する研究
 Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求
@@ -5585,6 +6305,11 @@
 組合せ的デザイン理論を用いた周波数ホッピング系列の構成に関する研究
 組合せ的デザイン理論を用いた光直交符号の構成に関する研究
 組合せ的デザインとその符号・暗号への応用
+数学基礎・応用数学
+組合せ論
+符号理論
+情報セキュリティ
+グループ検査
 版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹)
 A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao)
 Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao)
@@ -5619,39 +6344,55 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
+          <t>数学基礎・応用数学</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>組合せ論 / 符号理論 / 情報セキュリティ / グループ検査</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) / A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) / Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) / Repairing Schemes for Tamo-Barg Codes / A Construction of Optimal One-Coincidence Frequency-Hopping Sequences via Generalized Cyclotomy / Secure Codes With List Decoding / Codes for Exact Support Recovery of Sparse Vectors from Inaccurate Linear Measurements and Their Decoding / Optimal Locally Repairable Codes: An Improved Bound and Constructions / On the Information-Theoretic Security of Combinatorial All-or-Nothing Transforms / A Construction of Maximally Recoverable Codes With Order-Optimal Field Size / Capacity-Achieving Private Information Retrieval Schemes From Uncoded Storage Constrained Servers With Low Sub-Packetization / BCH codes with minimum distance proportional to code length / Existence and Construction of Complete Traceability Multimedia Fingerprinting Codes Resistant to Averaging Attack and Adversarial Noise / Strongly separable matrices for nonadaptive combinatorial group testing / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting / Algebraic manipulation detection codes via highly nonlinear functions / On Optimal Locally Repairable Codes With Super-Linear Length / On optimal weak algebraic manipulation detection codes and weighted external difference families / On Optimal Locally Repairable Codes With Multiple Disjoint Repair Sets / Improved Bounds for Separable Codes and B-2 Codes / Probabilistic Existence Results for Parent-Identifying Schemes / Non-adaptive group testing on graphs with connectivity / Bounds on Traceability Schemes / New Bounds for Frameproof Codes / Zero-difference balanced functions with new parameters and their applications</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>An improved algorithm to identify the cardinality of a coalition in multimedia fingerprinting / Group Testing with List Decoding</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>オペレーションズリサーチ ; 機械学習</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>オペレーションズリサーチ
+          <t>数学基礎・応用数学 ; 機械学習</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 組合せ最適化 ; 社会ネットワーク分析 ; 学習分析 ; 数理最適化</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>数学基礎・応用数学
+組合せ論
+符号理論
+情報セキュリティ
+グループ検査
 機械学習
-数理最適化
-組合せ最適化
-計画・スケジューリング
 統計的学習
 予測モデリング
-表現学習</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>An improved algorithm to identify the cardinality of a coalition in multimedia fingerprinting / Group Testing with List Decoding
+表現学習
+組合せ最適化
+社会ネットワーク分析
+学習分析
+数理最適化</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>An improved algorithm to identify the cardinality of a coalition in multimedia fingerprinting
+Group Testing with List Decoding
 不正者追跡アルゴリズムの開発とその応用
 デジタル指紋符号、多重接続通信路、及び組合せ探索問題
 スパースな結合行列を持つ組合せ的構造の分析と構成
@@ -5726,7 +6467,34 @@
 交通渋滞マネジメントのためのビリーフデザインアプローチ
 バイオミメティックスに学ぶスマートな都市退化マネジメント
 AI計算リソースとしての実交通ダイナミクスの活用技術の開発
-走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー</t>
+走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー
+土木計画学・交通工学
+交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム
+Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks
+A second order model of capacity drop at expressway lane-drop bottlenecks
+都市鉄道整備推進に向けた事業制度に関する研究
+Stability analysis of a departure time choice problem with atomic vehicle models
+自動運転車両の速度制御を考慮した系統信号制御に関する考察
+追従モデルによる高速道路サグ部のCapacity Drop現象の再現
+連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析
+テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル
+Predicting traffic breakdown in expressways using linear combination of vehicle detector data
+Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals
+音声による速度回復情報提供の交通性能改善メカニズムの実証分析
+連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析
+Dynamic traffic assignment in a corridor network: Optimum versus equilibrium
+高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム
+需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡
+Fundamental diagram of urban rail transit considering train-passenger interaction
+高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム
+高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動
+Dynamic system optimal traffic assignment with atomic users: Convergence and stability
+A new look at departure time choice equilibrium models with heterogeneous users
+動的交通均衡配分理論の近年の進展
+Continuum car-following model of capacity drop at sag and tunnel bottlenecks
+Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach"
+Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach
+Trading mechanisms for bottleneck permits with multiple purchase opportunities</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5734,40 +6502,49 @@
           <t>気候変動緩和に貢献する新興大都市におけるデータ駆動型の動的交通マネジメントに関する研究 / 高速車両連結技術を前提とした都市鉄道の近未来型運行スキーム / 高速道路単路部の交通流理論の検証と交通制御システムの戦略的デザイン / 限定合理的個人を仮定した大規模社会システムの動的制度設計 / 交通・物流システム効率化のための市場型マッチング・システムの設計・評価法構築 / MaaS＋CV時代の次世代交通システムに向けたインフラと制度の設計 / 交通渋滞マネジメントのためのビリーフデザインアプローチ / バイオミメティックスに学ぶスマートな都市退化マネジメント / AI計算リソースとしての実交通ダイナミクスの活用技術の開発 / 走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>土木計画学・交通工学</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks / A second order model of capacity drop at expressway lane-drop bottlenecks / 都市鉄道整備推進に向けた事業制度に関する研究 / Stability analysis of a departure time choice problem with atomic vehicle models / 自動運転車両の速度制御を考慮した系統信号制御に関する考察 / 追従モデルによる高速道路サグ部のCapacity Drop現象の再現 / 連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析 / テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル / Predicting traffic breakdown in expressways using linear combination of vehicle detector data / Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 / 連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析 / Dynamic traffic assignment in a corridor network: Optimum versus equilibrium / 高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム / 需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡 / Fundamental diagram of urban rail transit considering train-passenger interaction / 高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム / 高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動 / Dynamic system optimal traffic assignment with atomic users: Convergence and stability / A new look at departure time choice equilibrium models with heterogeneous users / 動的交通均衡配分理論の近年の進展 / Continuum car-following model of capacity drop at sag and tunnel bottlenecks / Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" / Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach / Trading mechanisms for bottleneck permits with multiple purchase opportunities</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>ボトルネック渋滞と都市人口分布の相互依存関係の解析 / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 / 多種別連結運行スキームにおける鉄道システムの安定性解析 / 市場型混雑管理システム下における自動運転サービスの運用方法 / 需要の時間的・空間的異質性を考慮した多種別連結運行スキームの分析 / 路線分割に基づく系統制御評価とオフセット設計 / 小規模シェアサイクルにおける再配置の効果分析と改善策の提案―茨城県つくば市「つくチャリ」を対象として―</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>家族・人口政策
+          <t>土木計画学・交通工学 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; 交通・モビリティ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 学習分析 ; 災害分析</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>土木計画学・交通工学
+交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム
 マッチング理論・ゲーム理論
 都市・地域政策
-GIS・空間分析
 交通・モビリティ
-建築・空間設計
-政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
+数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 安定マッチング
 資源配分
 メカニズムデザイン
@@ -5776,27 +6553,28 @@
 地域政策
 土地利用
 公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
 交通工学
 モビリティ設計
 交通需要分析
 ネットワーク設計
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>ボトルネック渋滞と都市人口分布の相互依存関係の解析 / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 / 多種別連結運行スキームにおける鉄道システムの安定性解析 / 市場型混雑管理システム下における自動運転サービスの運用方法 / 需要の時間的・空間的異質性を考慮した多種別連結運行スキームの分析 / 路線分割に基づく系統制御評価とオフセット設計 / 小規模シェアサイクルにおける再配置の効果分析と改善策の提案―茨城県つくば市「つくチャリ」を対象として―
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+社会ネットワーク分析
+学習分析
+災害分析</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>ボトルネック渋滞と都市人口分布の相互依存関係の解析
+音声による速度回復情報提供の交通性能改善メカニズムの実証分析
+多種別連結運行スキームにおける鉄道システムの安定性解析
+市場型混雑管理システム下における自動運転サービスの運用方法
+需要の時間的・空間的異質性を考慮した多種別連結運行スキームの分析
+路線分割に基づく系統制御評価とオフセット設計
+小規模シェアサイクルにおける再配置の効果分析と改善策の提案―茨城県つくば市「つくチャリ」を対象として―
 気候変動緩和に貢献する新興大都市におけるデータ駆動型の動的交通マネジメントに関する研究
 高速車両連結技術を前提とした都市鉄道の近未来型運行スキーム
 高速道路単路部の交通流理論の検証と交通制御システムの戦略的デザイン
@@ -5806,7 +6584,31 @@
 交通渋滞マネジメントのためのビリーフデザインアプローチ
 バイオミメティックスに学ぶスマートな都市退化マネジメント
 AI計算リソースとしての実交通ダイナミクスの活用技術の開発
-走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー</t>
+走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー
+Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks
+A second order model of capacity drop at expressway lane-drop bottlenecks
+都市鉄道整備推進に向けた事業制度に関する研究
+Stability analysis of a departure time choice problem with atomic vehicle models
+自動運転車両の速度制御を考慮した系統信号制御に関する考察
+追従モデルによる高速道路サグ部のCapacity Drop現象の再現
+連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析
+テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル
+Predicting traffic breakdown in expressways using linear combination of vehicle detector data
+Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals
+連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析
+Dynamic traffic assignment in a corridor network: Optimum versus equilibrium
+高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム
+需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡
+Fundamental diagram of urban rail transit considering train-passenger interaction
+高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム
+高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動
+Dynamic system optimal traffic assignment with atomic users: Convergence and stability
+A new look at departure time choice equilibrium models with heterogeneous users
+動的交通均衡配分理論の近年の進展
+Continuum car-following model of capacity drop at sag and tunnel bottlenecks
+Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach"
+Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach
+Trading mechanisms for bottleneck permits with multiple purchase opportunities</t>
         </is>
       </c>
     </row>
@@ -5843,6 +6645,9 @@
 多変量／高次元の潜在変数をもつ時系列モデルの効率的ベイズ推測
 高次元データモデリングの新展開と統計的リスク分析
 経済・金融多変量データのベイズモデリングと政策・行動の確率的評価
+統計科学
+経済統計
+ベイズ統計学, 状態空間モデル
 Simulation of truncated and unimodal gamma distributions
 Bayesian GARCH modeling for return and range
 時間変動する相関と確率的ボラティリティモデル
@@ -5858,29 +6663,41 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
+          <t>統計科学 / 経済統計</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ベイズ統計学, 状態空間モデル</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>Simulation of truncated and unimodal gamma distributions / Bayesian GARCH modeling for return and range / 時間変動する相関と確率的ボラティリティモデル / Multiple-block dynamic equicorrelations with realized measures, leverage and endogeneity / Dynamic equicorrelation stochastic volatility / Bayesian Analysis of Time-Varying Quantiles Using a Smoothing Spline</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>階層ディリクレ多項モデルの効率的な変分推論</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>保険・金融行動 ; GIS・空間分析 ; オペレーションズリサーチ ; 建築・空間設計 ; 機械学習 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>保険・金融行動
+          <t>統計科学 ; 経済統計 ; 保険・金融行動 ; GIS・空間分析 ; 建築・空間設計 ; 機械学習 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 学習分析 ; 統計学 ; 行政データ分析 ; 数理最適化</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>統計科学
+経済統計
+ベイズ統計学, 状態空間モデル
+保険・金融行動
 GIS・空間分析
-オペレーションズリサーチ
 建築・空間設計
 機械学習
 政策評価・計量分析
@@ -5895,9 +6712,6 @@
 空間計量
 地理情報分析
 立地分析
-数理最適化
-組合せ最適化
-計画・スケジューリング
 建築計画
 空間レイアウト生成
 居住空間設計
@@ -5908,10 +6722,14 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
+実証分析
+学習分析
+統計学
+行政データ分析
+数理最適化</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>階層ディリクレ多項モデルの効率的な変分推論
 非線形・非正規状態空間モデルと多変量・高次元経済金融時系列分析
@@ -5965,6 +6783,17 @@
 水害時の住民避難をより安全にする広域避難対策の社会的実装を図る計画技術の構築
 都市の拠点集約と拠点間ネットワークの空間分析
 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究
+都市計画・建築計画
+社会システム工学・安全システム
+人文地理学
+地理学
+土木計画学・交通工学
+都市解析
+地域施設計画
+立地科学
+地域公共交通
+地理情報科学
+都市リスク分析
 起伏を考慮した低炭素都市交通施策の評価
 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関
 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析
@@ -5994,33 +6823,53 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>歩行からみた都市空間の評価とインフラ適正配置に関する数理的・実証的研究 / 輸送モードの多様化と地域性・広域性を両立する公共交通網設計 / 人口の年齢構成の変遷パターンと市街地構造・生活利便施設アクセシビリティとの関連性分析 / 位置情報ビッグデータを活用した人の移動パターンと都市施設・土地利用・交通網の関係性の分析 / 都市拠点の人流パターン解析と市街地構造変容の モデル分析研究 / デジタル時代の施設配置の理論－自己完結，個人情報保護，民主的決定による非効率性－ / 水害時の住民避難をより安全にする広域避難対策の社会的実装を図る計画技術の構築 / 都市の拠点集約と拠点間ネットワークの空間分析 / 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究 / 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究</t>
+          <t>歩行からみた都市空間の評価とインフラ適正配置に関する数理的・実証的研究 / 輸送モードの多様化と地域性・広域性を両立する公共交通網設計 / 人口の年齢構成の変遷パターンと市街地構造・生活利便施設アクセシビリティとの関連性分析 / 位置情報ビッグデータを活用した人の移動パターンと都市施設・土地利用・交通網の関係性の分析 / 都市拠点の人流パターン解析と市街地構造変容の モデル分析研究 / デジタル時代の施設配置の理論－自己完結，個人情報保護，民主的決定による非効率性－ / 水害時の住民避難をより安全にする広域避難対策の社会的実装を図る計画技術の構築 / 都市の拠点集約と拠点間ネットワークの空間分析 / 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
+          <t>都市計画・建築計画 / 社会システム工学・安全システム / 人文地理学 / 地理学 / 土木計画学・交通工学</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>都市解析 / 地域施設計画 / 立地科学 / 地域公共交通 / 地理情報科学 / 都市リスク分析</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>起伏を考慮した低炭素都市交通施策の評価 / 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関 / 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析 / 東京区部における年齢構成類型の変化と生活利便施設へのアクシセビリティ分析 / 電柱広告の空間的配置に関する研究―筑波研究学園都市中心部を対象に― / Exploring Network Scale Separation Strategies for Car-Bicycle Integration / 都市条件に応じた複数公共交通モード併用によるネットワーク設計 / 全国鉄道駅周辺地域における地域分断による移動制約の定量評価 / 小地域人口の年齢構成類型とその遷移から見た安定性分析 / 東京区部における業種構成・滞在パターンに基づく商業集積地の類型化と滞在移動特性の分析 / 東京区部におけるGPSデータに基づく街区レベル発生集中・滞在移動特性と建物用途構成 / 人口分布の集積性と鉄道網との連携度の変化動向に関する研究 / 東京区部における人口年齢構成と土地利用遷移の関連性分析 / 東京区部における交通量密度・移動速度に基づく交通軸と移動効率性評価 / 鉄道網による移動時間短縮を考慮した都市の人口分布の集積性の評価 / 人流データによる滞在者平均年齢の時空間分析 ―昼や休日に若返る自治体はどこか？― / 通学距離最小化と安定マッチングによる学校割当 / Preference-based jogging route selection in Downtown Tokyo / Effect of Speed Control for Travel Time and Emission Reduction in Connected Vehicle Environment / Exploring Separation Strategies for Car-Bicycle Integration / アジア地域の都市における鉄道・道路と人口分布構造 / 建物主要用途・トリップチェーンに着目した人流データによる街区間トリップ特性 / 人流データによる街区レベル時間帯別発生集中の時空間分布 / 人口重心に着目した人流分析 / 沿道電柱密度の地域別・道路種別比較</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>人口の年齢構成遷移と市街地構造・生活利便施設アクセシビリティとの関連性分析</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>家族・人口政策
-マッチング理論・ゲーム理論
+          <t>都市計画・建築計画 ; 社会システム工学・安全システム ; 人文地理学 ; 地理学 ; 土木計画学・交通工学 ; 家族・人口政策 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析 ; 都市計画</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>都市計画・建築計画
+社会システム工学・安全システム
+人文地理学
+地理学
+土木計画学・交通工学
+都市解析
+地域施設計画
+立地科学
+地域公共交通
+地理情報科学
+都市リスク分析
+家族・人口政策
 都市・地域政策
 GIS・空間分析
 オペレーションズリサーチ
@@ -6036,10 +6885,6 @@
 少子化対策
 人口政策
 家計意思決定
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
 都市経済
 地域政策
 土地利用
@@ -6066,10 +6911,14 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
+実証分析
+社会ネットワーク分析
+行政データ分析
+災害分析
+都市計画</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>人口の年齢構成遷移と市街地構造・生活利便施設アクセシビリティとの関連性分析
 歩行からみた都市空間の評価とインフラ適正配置に関する数理的・実証的研究
@@ -6142,6 +6991,16 @@
 測地基準系の座標変換
 地下水位と地盤上下変動に関する研究
 地殻変動解析
+測地学
+空間情報科学
+測量学
+地球観測
+リモートセンシング
+宇宙測地学
+合成開口レーダー
+干渉法
+データサイエンス
+基準座標系
 2011年東北地方太平洋沖地震後の余効変動の時空間関数モデリング
 Spatiotemporal functional modeling of postseismic deformations after the 2011 Tohoku-Oki earthquake
 Ground deformation in the Kobe-Osaka area during 22 years after the Kobe earthquake
@@ -6174,47 +7033,43 @@
           <t>世界測地系の構築 / 合成開口レーダー解析ソフトウェアの開発 / 測地基準系の座標変換 / 地下水位と地盤上下変動に関する研究 / 地殻変動解析</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>測地学 / 空間情報科学 / 測量学 / 地球観測 / リモートセンシング / 宇宙測地学 / 合成開口レーダー / 干渉法 / データサイエンス / 基準座標系</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>2011年東北地方太平洋沖地震後の余効変動の時空間関数モデリング / Spatiotemporal functional modeling of postseismic deformations after the 2011 Tohoku-Oki earthquake / Ground deformation in the Kobe-Osaka area during 22 years after the Kobe earthquake / 兵庫県南部地震以後の22年間の京阪神の地盤変動 / JERS-1/InSAR再解析：1995年兵庫県南部地震後の地殻変動の検出 / 兵庫県南部地震以降，六甲山は高くなったのか？ / Volcanic deformation of Atosanupuri volcanic complex in the Kussharo caldera, Japan, from 1993 to 2016 revealed by JERS-1, ALOS, and ALOS-2 radar interferometry / 宇宙測地技術により検出された1995年兵庫県南部地震の余効変動 / A possible restart of an interplate slow slip adjacent to the Tokai seismic gap in Japan / Combined logarithmic and exponential function model for fitting postseismic GNSS time series after 2011 Tohoku-Oki earthquake / だいち2号SAR干渉解析により捉えられた平成26年（2014年）長野県北部の地震に伴う地殻変動と地表変形 / だいち2号SAR干渉解析による御嶽山噴火に伴う地表変位の検出 (小特集 御嶽山噴火への対応) / P47 ALOS-2干渉SARにより捉えられた2015年箱根山・大涌谷火山活動に伴う地殻変動(ポスターセッション) / 2014年11月22日長野県北部の地震におけるSAR干渉画像に基づく地表変形現地調査結果 / 干渉SARで捉えた2014年11月22日長野県北部を震源とする地震に伴う地表変位 / Continuous gps observations on mindanao / 無人航空機(UAV)による西之島の空中写真撮影と高精度地形計測 / SAR干渉解析のための数値気象モデルを用いた大気遅延誤差の低減処理ツールの開発 / 無人航空機による西之島空中写真の撮影とその分析 / 無人機による西之島地形計測の高精度化 / Landform Monitoring in Active Volcano by UAV and SFM-MVS Technique / Spatial and temporal evolution of the long-term slow slip in the Bungo Channel, Japan / InSAR-derived Coseismic Deformation of the 2010 Southeastern Iran Earthquake (M6.5) and its Relationship with the Tectonic Background in the South of Lut Block / 新潟—神戸ひずみ集中帯越後平野付近の詳細地殻変動分布 / Preceding, coseismic, and postseismic slips of the 2011 Tohoku earthquake, Japan</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>GIS・空間分析 ; 建築・空間設計 ; 機械学習 ; 画像・視覚情報処理 ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>GIS・空間分析
-建築・空間設計
-機械学習
-画像・視覚情報処理
-AI・データサイエンス
-GIS
-空間計量
-地理情報分析
-立地分析
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-統計的学習
-予測モデリング
-表現学習
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
+        <is>
+          <t>センサデータ解析 ; 災害分析 ; 環境工学 ; 行政データ分析</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>測地学
+空間情報科学
+測量学
+地球観測
+リモートセンシング
+宇宙測地学
+合成開口レーダー
+干渉法
+データサイエンス
+基準座標系
+センサデータ解析
+災害分析
+環境工学
+行政データ分析</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>世界測地系の構築
 合成開口レーダー解析ソフトウェアの開発
@@ -6287,6 +7142,11 @@
 マルチスケールな拠点空間計画のための新たな行動モデル研究
 災害時都市継続計画にむけた即応型需要予測の信頼性向上のためのデータフロー
 災害時都市活動支援のためのsoftware2.0型シミュレータの構築
+避難行動
+交通需要
+交通シミュレーション
+災害復旧
+相互作用
 通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～
 EVユーザーの充電場所選択問題に対するゲーム理論的考察
 災害復旧期における個々人の移動パターン変化の特徴分析
@@ -6314,40 +7174,46 @@
           <t>災害時交通網の動学的設計にむけた不確かさ回避行動の評価手法の構築 / ネットワークリスクの動的変化と避難行動チェインの解明 / 次世代モビリティ導入を想定した交通・土地利用モデルの開発とその不確実性分析 / 災害時の他者支援行動を考慮した動的制御シミュレータの開発 / MaaS＋CV時代の次世代交通システムに向けたインフラと制度の設計 / 相乗型豪雨災害時の交通マネジメントの理論再構築と社会への実装 / 量子コンピューティングによる他者相互作用型の行動モデルの発展 / マルチスケールな拠点空間計画のための新たな行動モデル研究 / 災害時都市継続計画にむけた即応型需要予測の信頼性向上のためのデータフロー / 災害時都市活動支援のためのsoftware2.0型シミュレータの構築</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ / EVユーザーの充電場所選択問題に対するゲーム理論的考察 / 災害復旧期における個々人の移動パターン変化の特徴分析 / メタ分析による災害時の避難開始選択要因の評価 / メタ分析による災害時の避難開始選択要因の評価 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 相互作用下での多肢選択行動の量子計算による求解 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— / Object-oriented Bayesian Networks for Activity-based Model with deep generative graph averaging / 筑波大学理工学群におけるデータサイエンス応用基礎教育 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 / 選択肢の不確実性を考慮した動的離散選択モデル / LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること / 日本の復興計画の研究動向と今後の展望 -1995年以降の建築・都市・土木の計画分野を中心に- / 選択肢の不確実性を考慮した動的離散選択モデル / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 / LET'S GO ABROAD!(第77回)シンガポール、パキスタン、アフガニスタン、ベトナム、カンボジア 地域建設業の海外展開と見据える未来—A regional construction company looks to overseas expansion and their future—特集 土木と地政学 / 「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>避難行動 / 交通需要 / 交通シミュレーション / 災害復旧 / 相互作用</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価</t>
-        </is>
-      </c>
+          <t>通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ / EVユーザーの充電場所選択問題に対するゲーム理論的考察 / 災害復旧期における個々人の移動パターン変化の特徴分析 / メタ分析による災害時の避難開始選択要因の評価 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 相互作用下での多肢選択行動の量子計算による求解 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— / 筑波大学理工学群におけるデータサイエンス応用基礎教育 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 / 選択肢の不確実性を考慮した動的離散選択モデル / LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること / 日本の復興計画の研究動向と今後の展望 -1995年以降の建築・都市・土木の計画分野を中心に- / LET'S GO ABROAD!(第77回)シンガポール、パキスタン、アフガニスタン、ベトナム、カンボジア 地域建設業の海外展開と見据える未来—A regional construction company looks to overseas expansion and their future—特集 土木と地政学 / 「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>マッチング理論・ゲーム理論
+          <t>都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 観光・マーケティング ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 災害分析 ; 社会ネットワーク分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>避難行動
+交通需要
+交通シミュレーション
+災害復旧
+相互作用
 都市・地域政策
 GIS・空間分析
-オペレーションズリサーチ
 交通・モビリティ
 建築・空間設計
 ネットワーク・グラフ理論
 災害・防災研究
+観光・マーケティング
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
 都市経済
 地域政策
 土地利用
@@ -6356,9 +7222,6 @@
 空間計量
 地理情報分析
 立地分析
-数理最適化
-組合せ最適化
-計画・スケジューリング
 交通工学
 モビリティ設計
 交通需要分析
@@ -6373,10 +7236,17 @@
 組合せ構造
 災害社会学
 防災政策
-リスク評価</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
+リスク評価
+観光データ分析
+マーケティング分析
+クラスタリング
+需要予測
+災害分析
+社会ネットワーク分析
+学習分析</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>災害時交通網の動学的設計にむけた不確かさ回避行動の評価手法の構築
 ネットワークリスクの動的変化と避難行動チェインの解明
@@ -6441,6 +7311,8 @@
         <is>
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発
 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証
+Service Engineering
+Experimental economics
 主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案
 What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews
 Mystery shopping considering lifestyle heterogeneity
@@ -6458,37 +7330,44 @@
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発 / 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Service Engineering / Experimental economics</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 / What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews / Mystery shopping considering lifestyle heterogeneity / 経験効用モデルに基づくサービス継続利用を促すリマインダーの最適間隔 / Effects of Incentivized Fake Reviews on E-commerce Markets / Platform in manufacturing for enhancement of product value by sharing / Interpreting value creation model by case-based decision theory / Service switching in case-based decisions following bad experiences: Online reviews data of Japanese hairdressing salons / Multi-agent simulation for the manufacturer’s decision making in sharing markets / Manufacturer’s strategy in a sharing economy</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>意思決定分析 ; オペレーションズリサーチ ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>意思決定分析
-オペレーションズリサーチ
+          <t>意思決定分析 ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 推薦システム ; 政策評価 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Service Engineering
+Experimental economics
+意思決定分析
 AI・データサイエンス
 行動意思決定
 実験・行動分析
 ナッジ
 意思決定支援
-数理最適化
-組合せ最適化
-計画・スケジューリング</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
+推薦システム
+政策評価
+学習分析</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発
 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証
@@ -6516,7 +7395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6557,30 +7436,40 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>trios_research_fields_text</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>trios_research_keywords_text</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>trios_papers_text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>master_title_text</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>coarse_research_field</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>detailed_research_field</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>field_text</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>content_text</t>
         </is>
@@ -6624,6 +7513,15 @@
 人々の環境モラルに基づく自発的行動と望ましい環境政策
 「環境政策における経済的手法」再検討
 応用一般均衡モデルによる環境政策の社会経済学的分析
+経済政策
+環境政策・環境社会システム
+環境経済学
+エネルギー経済学
+政策分析
+不平等分析
+貧困分析
+分解手法の開発
+エネルギー貧困、エネルギー脆弱性
 エネルギー貧困からエネルギー充足へ
 Aging alone: a twin threat to decarbonisation and energy vulnerability in Japan and UK
 Reevaluating fair carbon emissions for households in Japan: basic energy needs and subsistence CO2 emissions
@@ -6656,58 +7554,76 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>エネルギー貧困からエネルギー充足へ / Aging alone: a twin threat to decarbonisation and energy vulnerability in Japan and UK / Reevaluating fair carbon emissions for households in Japan: basic energy needs and subsistence CO2 emissions / Double energy vulnerability in Japan / Double energy vulnerability in Japan: a first assessment / Measuring energy sufficiency: A state of being neither in energy poverty nor energy extravagance / What can be done with one tonne of CO2 emissions?: Reconsidering fair carbon emissions for households in relation to the use of domestic energy services / Measuring energy sufficiency: A state of being in neither energy poverty nor energy extravagance / How to evaluate energy sufficiency: A direct measurement approach / Energy Poverty in Japan: Current Trends and Future Challenges / 公平なエネルギー転換：気候正義とエネルギー正義の観点から / Regional energy poverty reevaluated: A direct measurement approach applied to France and Japan / Energy poor need more energy, but do they need more carbon?: Evaluation of people’s basic carbon needs / Prevalence of energy poverty in Japan: A comprehensive analysis of energy poverty vulnerabilities / Prevalence of energy poverty in Japan: A comprehensive analysis of energy poverty vulnerabilities / Energy poor need more energy, but do they need more carbon? / Engendering an inclusive low-carbon energy transition in Japan: Considering the perspectives and awareness of the energy poor / Understanding regional energy poverty in Japan: a direct measurement approach / Engendering an inclusive low-carbon energy transition in Japan: considering the perspectives and awareness of the energy poor / Measuring Energy Poverty via Energy Service Usage: The Japanese case / 「エネルギー貧困」・「エネルギー脆弱性」・「エネルギー正義」：日本における現状と課題 / 「エネルギー正義」について / Gauging Energy Poverty: A Multidimensional Approach / Measuring Energy Poverty in Japan, 2004-2013 / How Can We Gauge Energy Poverty? A Multidimensional Approach</t>
+          <t>経済政策 / 環境政策・環境社会システム</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>環境経済学 / エネルギー経済学 / 政策分析 / 不平等分析 / 貧困分析 / 分解手法の開発 / エネルギー貧困、エネルギー脆弱性</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>エネルギー貧困からエネルギー充足へ / Aging alone: a twin threat to decarbonisation and energy vulnerability in Japan and UK / Reevaluating fair carbon emissions for households in Japan: basic energy needs and subsistence CO2 emissions / Double energy vulnerability in Japan / Double energy vulnerability in Japan: a first assessment / Measuring energy sufficiency: A state of being neither in energy poverty nor energy extravagance / What can be done with one tonne of CO2 emissions?: Reconsidering fair carbon emissions for households in relation to the use of domestic energy services / Measuring energy sufficiency: A state of being in neither energy poverty nor energy extravagance / How to evaluate energy sufficiency: A direct measurement approach / Energy Poverty in Japan: Current Trends and Future Challenges / 公平なエネルギー転換：気候正義とエネルギー正義の観点から / Regional energy poverty reevaluated: A direct measurement approach applied to France and Japan / Energy poor need more energy, but do they need more carbon?: Evaluation of people’s basic carbon needs / Prevalence of energy poverty in Japan: A comprehensive analysis of energy poverty vulnerabilities / Energy poor need more energy, but do they need more carbon? / Engendering an inclusive low-carbon energy transition in Japan: Considering the perspectives and awareness of the energy poor / Understanding regional energy poverty in Japan: a direct measurement approach / Measuring Energy Poverty via Energy Service Usage: The Japanese case / 「エネルギー貧困」・「エネルギー脆弱性」・「エネルギー正義」：日本における現状と課題 / 「エネルギー正義」について / Gauging Energy Poverty: A Multidimensional Approach / Measuring Energy Poverty in Japan, 2004-2013 / How Can We Gauge Energy Poverty? A Multidimensional Approach</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>中国の排出量取引制度がグリーン投資に与える影響 / 再生可能エネルギー促進のための課題ー全国トラブル発生データを用いた考察ー / 中国の「費改税」が製造業に与える影響</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>保険・金融行動 ; マッチング理論・ゲーム理論 ; オペレーションズリサーチ ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>保険・金融行動
+          <t>経済政策 ; 環境政策・環境社会システム ; マッチング理論・ゲーム理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 環境工学 ; 社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>経済政策
+環境政策・環境社会システム
+環境経済学
+エネルギー経済学
+政策分析
+不平等分析
+貧困分析
+分解手法の開発
+エネルギー貧困、エネルギー脆弱性
 マッチング理論・ゲーム理論
-オペレーションズリサーチ
 災害・防災研究
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
 AI・データサイエンス
-環境・エネルギー
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
 安定マッチング
 資源配分
 メカニズムデザイン
 協力ゲーム・非協力ゲーム
-数理最適化
-組合せ最適化
-計画・スケジューリング
 災害社会学
 防災政策
 リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>中国の排出量取引制度がグリーン投資に与える影響 / 再生可能エネルギー促進のための課題ー全国トラブル発生データを用いた考察ー / 中国の「費改税」が製造業に与える影響
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+環境工学
+社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>中国の排出量取引制度がグリーン投資に与える影響
+再生可能エネルギー促進のための課題ー全国トラブル発生データを用いた考察ー
+中国の「費改税」が製造業に与える影響
 十分なエネルギーをすべての人へ：家庭部門の公正な移行を実現するために
 包摂的な低炭素化・エネルギー転換に関する研究
 低炭素化・エネルギー転換の包摂性評価：基本的エネルギーニーズの観点から
@@ -6781,6 +7697,8 @@
 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年
 都市における環境リスクの軽減の経済効果に関する研究
 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―
+経済政策
+開発経済学、教育の経済学、健康の経済学、応用計量経済学
 Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone
 Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone
 The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand
@@ -6809,49 +7727,53 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>民主主義における利益誘導と経済発展への影響 / 民主主義における利益誘導と経済発展への影響 / 政策立案のための衛星データ利用法の探索：社会工学的アプローチ / 社会工学分野での衛星画像の利用促進に向けた探索的研究 / 衛星情報を利用した物流における大気環境改善の評価 / 反実仮想で測る公的資源配分の依怙贔屓と非効率 / 交通と環境に関する新経済地理学的基盤研究 / 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年 / 都市における環境リスクの軽減の経済効果に関する研究 / 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―</t>
+          <t>民主主義における利益誘導と経済発展への影響 / 政策立案のための衛星データ利用法の探索：社会工学的アプローチ / 社会工学分野での衛星画像の利用促進に向けた探索的研究 / 衛星情報を利用した物流における大気環境改善の評価 / 反実仮想で測る公的資源配分の依怙贔屓と非効率 / 交通と環境に関する新経済地理学的基盤研究 / 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年 / 都市における環境リスクの軽減の経済効果に関する研究 / 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand / The Impact of a High-speed Railway on Residential Land Prices / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan / School Choice and Student Sorting: Evidence from Adachi Ward in Japan / オリンピック・パラリンピックにはどんな経済効果があるのか / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward / Building an Administrative Database of Children / 高速鉄道の建設が居住地価格に与えた影響 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 / 学校の質と地価－足立区の地価データを用いた検証 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ / 子どもについての行政データベースの構築 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から / 区立小学校での補習の効果：足立区のケース / ヘドニック・アプローチにおける因果識別 / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 / The Impact of a High-speed Railway on Residential Land Prices / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand / School Choice and Student Sorting: Evidence from Adachi City in Japan</t>
+          <t>経済政策</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>開発経済学、教育の経済学、健康の経済学、応用計量経済学</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand / The Impact of a High-speed Railway on Residential Land Prices / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan / School Choice and Student Sorting: Evidence from Adachi Ward in Japan / オリンピック・パラリンピックにはどんな経済効果があるのか / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward / Building an Administrative Database of Children / 高速鉄道の建設が居住地価格に与えた影響 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 / 学校の質と地価－足立区の地価データを用いた検証 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ / 子どもについての行政データベースの構築 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から / 区立小学校での補習の効果：足立区のケース / ヘドニック・アプローチにおける因果識別 / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand / School Choice and Student Sorting: Evidence from Adachi City in Japan</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>選挙制度と資源配分のゆがみ－昭和前期の事例－ / 都市の住みやすさランキングによる居住地選択への影響 / 個人競技における チームメイトの影響 / 農産物直売所が​地域農業に与える影響 / 夜間光リモートセンシング画像を用いた​高速鉄道建設の四川省経済発展に対する影響 / エネルギー会社に対する省エネ基準が、エネルギー消費に与える影響の分析 / 有名作品の舞台地になることによる地方創生への可能性 / 新型農村協同医療制度が中国農村女性の健康格差に与える影響</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>保険・金融行動 ; 都市・地域政策 ; 交通・モビリティ ; 建築・空間設計 ; 機械学習 ; 画像・視覚情報処理 ; スポーツデータ分析 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>保険・金融行動
+          <t>経済政策 ; 都市・地域政策 ; 交通・モビリティ ; 機械学習 ; 画像・視覚情報処理 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>経済政策
+開発経済学、教育の経済学、健康の経済学、応用計量経済学
 都市・地域政策
 交通・モビリティ
-建築・空間設計
 機械学習
 画像・視覚情報処理
-スポーツデータ分析
-災害・防災研究
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
 都市経済
 地域政策
 土地利用
@@ -6860,10 +7782,6 @@
 モビリティ設計
 交通需要分析
 ネットワーク設計
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
 統計的学習
 予測モデリング
 表現学習
@@ -6871,21 +7789,29 @@
 画像認識
 行動認識
 マルチモーダル解析
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
-災害社会学
-防災政策
-リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>選挙制度と資源配分のゆがみ－昭和前期の事例－ / 都市の住みやすさランキングによる居住地選択への影響 / 個人競技における チームメイトの影響 / 農産物直売所が​地域農業に与える影響 / 夜間光リモートセンシング画像を用いた​高速鉄道建設の四川省経済発展に対する影響 / エネルギー会社に対する省エネ基準が、エネルギー消費に与える影響の分析 / 有名作品の舞台地になることによる地方創生への可能性 / 新型農村協同医療制度が中国農村女性の健康格差に与える影響
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+社会ネットワーク分析
+行政データ分析
+学習分析</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>選挙制度と資源配分のゆがみ－昭和前期の事例－
+都市の住みやすさランキングによる居住地選択への影響
+個人競技における チームメイトの影響
+農産物直売所が​地域農業に与える影響
+夜間光リモートセンシング画像を用いた​高速鉄道建設の四川省経済発展に対する影響
+エネルギー会社に対する省エネ基準が、エネルギー消費に与える影響の分析
+有名作品の舞台地になることによる地方創生への可能性
+新型農村協同医療制度が中国農村女性の健康格差に与える影響
 民主主義における利益誘導と経済発展への影響
 政策立案のための衛星データ利用法の探索：社会工学的アプローチ
 社会工学分野での衛星画像の利用促進に向けた探索的研究
@@ -6953,6 +7879,9 @@
           <t>行動経済学の知見を利用した進化ゲーム理論による均衡選択分析
 社会選択問題への進化ゲーム理論的アプローチ
 マルチタスク環境および協力ゲームにおける進化ゲーム理論の研究
+理論経済学
+社会システム工学・安全システム
+ゲーム理論; 進化ゲーム理論;
 The evolution of collective choice under majority rules
 Statistical inference in evolutionary dynamics
 研究室の選好と学生の成績を考慮した研究室配属法の分析
@@ -6980,60 +7909,73 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>理論経済学 / 社会システム工学・安全システム</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ゲーム理論; 進化ゲーム理論;</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>The evolution of collective choice under majority rules / Statistical inference in evolutionary dynamics / 研究室の選好と学生の成績を考慮した研究室配属法の分析 / 有限オートマトンを用いた私的観測繰り返しゲームにおける進化的安定戦略分析 / A stochastic stability analysis with observation errors in normal form games / Stochastic stability in the large population and small mutation limits for coordination games / oTreeを用いた配属システムの設計・構築とその運用 / A prospect theory Nash bargaining solution and its stochastic stability / 複利型強化学習を用いたポートフォリオ選択手法についての研究 / Evolutionary dynamics in multitasking environments / Stochastic stability under logit choice in coalitional bargaining problems / Prospect dynamics and loss dominance / Reference-dependent preferences, super-dominance and stochastic stability / A one-shot deviation principle for stability in matching problems / Evolutionary imitative dynamics with population-varying aspiration levels / Coalitional stochastic stability in games, networks and markets / Mutation rates and equilibrium selection under stochastic evolutionary dynamics / CG を用いたマシンの3 次元構造進化システム</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>不完全観測下における損失回避性が均衡の安定性に及ぼす影響 / 不確実性の存在する公共財提供問題における近視眼的プレイヤーによる持続的協力行動の進化分析 / 品質選択がクラウドファンディングを行う企業の資金募集形式および利潤に与える影響の分析 / 企業の不祥事における隠蔽のゲーム理論 / 就活市場における企業の内定通知がマッチングの安定性に与える影響の分析 / 非線形公共財ゲームにおけるプレイヤーの関係性を利用したグループ形成手法の考察 / Stochastic stability analysis on the tragedy of climate change via agents’ psychological dynamics / ソーシャルメディア上の炎上現象の分析と対策 / 感情表現と表現に対する反応の共進化 / 通貨競争モデルによる仮想通貨の普及に関する分析 / 多数決による準公益施設の立地分析 / プロ野球現役ドラフト制度における改善 / オークションモデルによる官製談合の分析</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 意思決定分析 ; マッチング理論・ゲーム理論 ; オペレーションズリサーチ ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-意思決定分析
+          <t>理論経済学 ; 社会システム工学・安全システム ; マッチング理論・ゲーム理論 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 学習分析 ; 計算社会科学 ; 行動科学</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>理論経済学
+社会システム工学・安全システム
+ゲーム理論; 進化ゲーム理論;
 マッチング理論・ゲーム理論
-オペレーションズリサーチ
-政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
-AI・データサイエンス
-環境・エネルギー
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-行動意思決定
-実験・行動分析
-ナッジ
-意思決定支援
 安定マッチング
 資源配分
 メカニズムデザイン
 協力ゲーム・非協力ゲーム
-数理最適化
-組合せ最適化
-計画・スケジューリング
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>不完全観測下における損失回避性が均衡の安定性に及ぼす影響 / 不確実性の存在する公共財提供問題における近視眼的プレイヤーによる持続的協力行動の進化分析 / 品質選択がクラウドファンディングを行う企業の資金募集形式および利潤に与える影響の分析 / 企業の不祥事における隠蔽のゲーム理論 / 就活市場における企業の内定通知がマッチングの安定性に与える影響の分析 / 非線形公共財ゲームにおけるプレイヤーの関係性を利用したグループ形成手法の考察 / Stochastic stability analysis on the tragedy of climate change via agents’ psychological dynamics / ソーシャルメディア上の炎上現象の分析と対策 / 感情表現と表現に対する反応の共進化 / 通貨競争モデルによる仮想通貨の普及に関する分析 / 多数決による準公益施設の立地分析 / プロ野球現役ドラフト制度における改善 / オークションモデルによる官製談合の分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+社会ネットワーク分析
+学習分析
+計算社会科学
+行動科学</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>不完全観測下における損失回避性が均衡の安定性に及ぼす影響
+不確実性の存在する公共財提供問題における近視眼的プレイヤーによる持続的協力行動の進化分析
+品質選択がクラウドファンディングを行う企業の資金募集形式および利潤に与える影響の分析
+企業の不祥事における隠蔽のゲーム理論
+就活市場における企業の内定通知がマッチングの安定性に与える影響の分析
+非線形公共財ゲームにおけるプレイヤーの関係性を利用したグループ形成手法の考察
+Stochastic stability analysis on the tragedy of climate change via agents’ psychological dynamics
+ソーシャルメディア上の炎上現象の分析と対策
+感情表現と表現に対する反応の共進化
+通貨競争モデルによる仮想通貨の普及に関する分析
+多数決による準公益施設の立地分析
+プロ野球現役ドラフト制度における改善
+オークションモデルによる官製談合の分析
 行動経済学の知見を利用した進化ゲーム理論による均衡選択分析
 社会選択問題への進化ゲーム理論的アプローチ
 マルチタスク環境および協力ゲームにおける進化ゲーム理論の研究
@@ -7083,49 +8025,26 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>オペレーションズリサーチ ; 交通・モビリティ ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>オペレーションズリサーチ
-交通・モビリティ
-ネットワーク・グラフ理論
-政策評価・計量分析
-数理最適化・OR
-AI・データサイエンス
-数理最適化
-組合せ最適化
-計画・スケジューリング
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
+グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築
+中断時系列デザインを用いた人流抑制の効果推定
+実世界への応用のためのNeural Architecture Searchの多目的最適化
+大規模イベントにおける歩行者モデルの拡張と群集制御最適化
+多目的最適化による地下動線を活用した避難誘導効果の検証
+実時間で動作する音響イベント検出の大規模事前学習
+超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
     </row>
@@ -7166,6 +8085,14 @@
 地域未来創生共同研究講座
 次世代社会システムとモビリティの新価値研究
 購買データに基づく顧客行動分析
+数理情報学
+数学基礎・応用数学
+社会システム工学・安全システム
+計算科学
+数理最適化
+数理計画
+オペレーションズ・リサーチ
+サービス工学
 Data Collaboration Analysis with Orthonormal Basis Selection and Alignment
 Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning
 正循環制約を考慮したナーススケジューリング
@@ -7189,37 +8116,51 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>リーマン多様体上の制約付き最適化問題に対する汎用アルゴリズムの理論と実装 / リーマン多様体上の最適化理論に基づく新たなデータコラボレーション手法の開発 / ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発 / コネクティッドカーのサービス開発を目的とした走行データのデータクレンジング手法に係る研究 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発 / 半正定値基を用いた錐最適化問題の近似解法の開発 / 地域未来創生共同研究講座 / 次世代社会システムとモビリティの新価値研究 / 購買データに基づく顧客行動分析</t>
+          <t>リーマン多様体上の制約付き最適化問題に対する汎用アルゴリズムの理論と実装 / リーマン多様体上の最適化理論に基づく新たなデータコラボレーション手法の開発 / ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発 / コネクティッドカーのサービス開発を目的とした走行データのデータクレンジング手法に係る研究 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / 半正定値基を用いた錐最適化問題の近似解法の開発 / 地域未来創生共同研究講座 / 次世代社会システムとモビリティの新価値研究 / 購買データに基づく顧客行動分析</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Data Collaboration Analysis with Orthonormal Basis Selection and Alignment / Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning / 正循環制約を考慮したナーススケジューリング / Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices / Post-Processing with Projection and Rescaling Algorithms for Semidefinite Programming / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / A new extension of Chubanov's method to symmetric cones / 射影- 再スケーリング法を用いた 対称錐計画問題に対する後処理アルゴリズム / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / On the Global Convergence of Riemannian Interior Point Method / Completely positive factorization by a Riemannian smoothing method / Evaluating approximations of the semidefinite cone with trace normalized distance / Evaluating approximations of the semidefinite cone with trace normalized distance / A New Extension of Chubanov's Method to Symmetric Cones / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / Completely Positive Factorization in Orthogonality Optimization via Smoothing Method / Scenario-based CVaR Approach to Strategic Decision Support in One-way Station-based Carsharing Systems / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach / Polyhedral approximations of the semidefinite cone and their application / Centering ADMM for the Semidefinite Relaxation of the QAP / QAPの半正定値緩和問題を解くためのセンタリングADMM / SD基に基づく半正定値行列錐の凸多面錐近似 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― / Centering ADMM for the Semidefinite Relaxation of the QAP / Polyhedral approximations of the semidefinite cone and their application</t>
+          <t>数理情報学 / 数学基礎・応用数学 / 社会システム工学・安全システム / 計算科学</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>数理最適化 / 数理計画 / オペレーションズ・リサーチ / サービス工学</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Data Collaboration Analysis with Orthonormal Basis Selection and Alignment / Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning / 正循環制約を考慮したナーススケジューリング / Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices / Post-Processing with Projection and Rescaling Algorithms for Semidefinite Programming / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / A new extension of Chubanov's method to symmetric cones / 射影- 再スケーリング法を用いた 対称錐計画問題に対する後処理アルゴリズム / On the Global Convergence of Riemannian Interior Point Method / Completely positive factorization by a Riemannian smoothing method / Evaluating approximations of the semidefinite cone with trace normalized distance / Completely Positive Factorization in Orthogonality Optimization via Smoothing Method / Scenario-based CVaR Approach to Strategic Decision Support in One-way Station-based Carsharing Systems / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach / Polyhedral approximations of the semidefinite cone and their application / Centering ADMM for the Semidefinite Relaxation of the QAP / QAPの半正定値緩和問題を解くためのセンタリングADMM / SD基に基づく半正定値行列錐の凸多面錐近似 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成―</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>ロード・プライシング政策を考慮したNLSUEモデルとその解法の提案 / 未達率指標を用いた生産計画手法のSC能力設計への応用の研究 / 予約制乗合タクシーのルート最適化 / スマートキャンパスバス運行計画 / 救急医療サービスの効率化に向けた患者の医療機関割り当てに関するオフラインアルゴリズムの開発 / 一般消費財業界における未達率指標を用いた生産計画手法のSC能力設計への応用の研究 / 多死社会における在宅看取りに関する一考察 －茨城県の医療・介護に関する地域分析と実際の看取りをふまえて－ / バックトゥバック数を考慮したNBAの2018-2019シーズンスケジュールの作成 / 健康診断センターの勤務表作成におけるスケジューリング問題 / メタヒューリスティクスを用いた予約制乗合タクシーの配車スケジュール作成 / 乗客満足度を考慮した乗合タクシーの路線最適化モデル / ファストフード店の勤務スケジュールの作成 / リーマン多様体上の統合解析関数最適化 / 社会工学学位プログラムにおける修論発表会のスケジューリングについて / Traveling umpire problem におけるチーム間の公平性が高い解の探求 / 多要素ランキング法の上で正確性と多様性のトレードオフを考慮したモデルによる推薦システム / A Modification of Representing Linear Programs by Graph Neural Network / つくば市における予約制乗合タクシーの配車スケジューリング作成 / マイクログリッドにおける災害対策を考慮した最適化シミュレーション / 大学入試における屋内連絡員の人員配置最適化ツール開発 / 実運用を考慮した予約制乗合タクシーの配車スケジューリング作成</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>都市・地域政策 ; 社会政策・福祉 ; オペレーションズリサーチ ; 機械学習 ; スポーツデータ分析 ; 災害・防災研究 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 災害社会学 ; 防災政策 ; リスク評価</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>都市・地域政策
-社会政策・福祉
+          <t>数理情報学 ; 数学基礎・応用数学 ; 社会システム工学・安全システム ; 計算科学 ; 都市・地域政策 ; オペレーションズリサーチ ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 学習分析 ; 物流最適化</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>数理情報学
+数学基礎・応用数学
+社会システム工学・安全システム
+計算科学
+数理最適化
+数理計画
+オペレーションズ・リサーチ
+サービス工学
+都市・地域政策
 オペレーションズリサーチ
-機械学習
-スポーツデータ分析
-災害・防災研究
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
@@ -7227,27 +8168,35 @@
 地域政策
 土地利用
 公共政策評価
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
-数理最適化
 組合せ最適化
 計画・スケジューリング
-統計的学習
-予測モデリング
-表現学習
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
-災害社会学
-防災政策
-リスク評価</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ロード・プライシング政策を考慮したNLSUEモデルとその解法の提案 / 未達率指標を用いた生産計画手法のSC能力設計への応用の研究 / 予約制乗合タクシーのルート最適化 / スマートキャンパスバス運行計画 / 救急医療サービスの効率化に向けた患者の医療機関割り当てに関するオフラインアルゴリズムの開発 / 一般消費財業界における未達率指標を用いた生産計画手法のSC能力設計への応用の研究 / 多死社会における在宅看取りに関する一考察 －茨城県の医療・介護に関する地域分析と実際の看取りをふまえて－ / バックトゥバック数を考慮したNBAの2018-2019シーズンスケジュールの作成 / 健康診断センターの勤務表作成におけるスケジューリング問題 / メタヒューリスティクスを用いた予約制乗合タクシーの配車スケジュール作成 / 乗客満足度を考慮した乗合タクシーの路線最適化モデル / ファストフード店の勤務スケジュールの作成 / リーマン多様体上の統合解析関数最適化 / 社会工学学位プログラムにおける修論発表会のスケジューリングについて / Traveling umpire problem におけるチーム間の公平性が高い解の探求 / 多要素ランキング法の上で正確性と多様性のトレードオフを考慮したモデルによる推薦システム / A Modification of Representing Linear Programs by Graph Neural Network / つくば市における予約制乗合タクシーの配車スケジューリング作成 / マイクログリッドにおける災害対策を考慮した最適化シミュレーション / 大学入試における屋内連絡員の人員配置最適化ツール開発 / 実運用を考慮した予約制乗合タクシーの配車スケジューリング作成
+学習分析
+物流最適化</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ロード・プライシング政策を考慮したNLSUEモデルとその解法の提案
+未達率指標を用いた生産計画手法のSC能力設計への応用の研究
+予約制乗合タクシーのルート最適化
+スマートキャンパスバス運行計画
+救急医療サービスの効率化に向けた患者の医療機関割り当てに関するオフラインアルゴリズムの開発
+一般消費財業界における未達率指標を用いた生産計画手法のSC能力設計への応用の研究
+多死社会における在宅看取りに関する一考察 －茨城県の医療・介護に関する地域分析と実際の看取りをふまえて－
+バックトゥバック数を考慮したNBAの2018-2019シーズンスケジュールの作成
+健康診断センターの勤務表作成におけるスケジューリング問題
+メタヒューリスティクスを用いた予約制乗合タクシーの配車スケジュール作成
+乗客満足度を考慮した乗合タクシーの路線最適化モデル
+ファストフード店の勤務スケジュールの作成
+リーマン多様体上の統合解析関数最適化
+社会工学学位プログラムにおける修論発表会のスケジューリングについて
+Traveling umpire problem におけるチーム間の公平性が高い解の探求
+多要素ランキング法の上で正確性と多様性のトレードオフを考慮したモデルによる推薦システム
+A Modification of Representing Linear Programs by Graph Neural Network
+つくば市における予約制乗合タクシーの配車スケジューリング作成
+マイクログリッドにおける災害対策を考慮した最適化シミュレーション
+大学入試における屋内連絡員の人員配置最適化ツール開発
+実運用を考慮した予約制乗合タクシーの配車スケジューリング作成
 リーマン多様体上の制約付き最適化問題に対する汎用アルゴリズムの理論と実装
 リーマン多様体上の最適化理論に基づく新たなデータコラボレーション手法の開発
 ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発
@@ -7317,6 +8266,10 @@
 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学
 高次元データの理論と方法論の総合的研究
 高次Aggregation Operatorの開発とクラスタリングモデルへの適用
+統計科学
+ソフトコンピューティング
+データマイニング
+多次元データ解析
 Simultaneous visualization method for mixed HDLSS data and its application for education
 Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design
 Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey
@@ -7350,32 +8303,45 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Simultaneous visualization method for mixed HDLSS data and its application for education / Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design / Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey / Difference on Evaluation Scores Considering Image Descriptions for Autocoding / ファジィクラスタリングの信頼度について / Hierarchical Support Vector Machine based Classifier for Autocoding / Fuzzy Cluster-Scaled Principal Component Analysis for Mixed Data and Its Application of Educational Effect based on Device Selection / A Fuzzy Cluster-Scaled Principal Component Analysis for Mixed High-Dimension and Low-Sample Size Data / Principal component analysis for mixed high-dimension low-sample size data based on fuzzy-cluster scale / Improvement of Training Data for Autocoding on "The National Survey of Family Income, Consumption and Wealth" and "The Family Income and Expenditure Survey" / Fuzzy Clustering based Autocoding Methods for Family Income and Expenditure Surveys / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding / Fuzzy Clustering based Classifier for Extraction of Individualities from High Dimension Low Sample Size Data / Individuality-based Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding / Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results / Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling / Cluster-based Analysis for Discrimination of Individuality （招待講演） / クラスター尺度に基づくデータ間差異の検出と市場データへの応用 / ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 / Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Clustering and Multidimensional Scaling for Individual Difference Extraction / 多次元尺度法による計算効率を考慮したディープラーニング手法 / Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means / 区間組成データに対する重み付き回帰分析</t>
+          <t>統計科学 / ソフトコンピューティング</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>統計科学 / ソフトコンピューティング / データマイニング / 多次元データ解析</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Simultaneous visualization method for mixed HDLSS data and its application for education / Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design / Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey / Difference on Evaluation Scores Considering Image Descriptions for Autocoding / ファジィクラスタリングの信頼度について / Hierarchical Support Vector Machine based Classifier for Autocoding / Fuzzy Cluster-Scaled Principal Component Analysis for Mixed Data and Its Application of Educational Effect based on Device Selection / A Fuzzy Cluster-Scaled Principal Component Analysis for Mixed High-Dimension and Low-Sample Size Data / Principal component analysis for mixed high-dimension low-sample size data based on fuzzy-cluster scale / Improvement of Training Data for Autocoding on "The National Survey of Family Income, Consumption and Wealth" and "The Family Income and Expenditure Survey" / Fuzzy Clustering based Autocoding Methods for Family Income and Expenditure Surveys / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding / Fuzzy Clustering based Classifier for Extraction of Individualities from High Dimension Low Sample Size Data / Individuality-based Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results / Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling / Cluster-based Analysis for Discrimination of Individuality （招待講演） / クラスター尺度に基づくデータ間差異の検出と市場データへの応用 / ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 / Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Clustering and Multidimensional Scaling for Individual Difference Extraction / 多次元尺度法による計算効率を考慮したディープラーニング手法 / Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means / 区間組成データに対する重み付き回帰分析</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>TLPCMの評価および欠損値処理手法 / 区間組成データに対する 回帰分析 / 歌詞テキストデータの感情分類 / 区間データに対するPCA手法の提案と従来法との比較 / ファジィクラスタリングを用いた欠損値補完法について / T-normを用いたクラスター尺度による顧客分類法</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 都市・地域政策 ; オペレーションズリサーチ ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
+          <t>統計科学 ; ソフトコンピューティング ; 労働経済・就職マッチング ; 都市・地域政策 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 公共政策・社会工学 ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 行政データ分析 ; センサデータ解析 ; 社会ネットワーク分析 ; 計算社会科学</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>統計科学
+ソフトコンピューティング
+データマイニング
+多次元データ解析
+労働経済・就職マッチング
 都市・地域政策
-オペレーションズリサーチ
 政策評価・計量分析
+医療・ヘルスデータ
 公共政策・社会工学
-経済・ファイナンス
 AI・データサイエンス
 労働経済
 人的資本
@@ -7385,18 +8351,28 @@
 地域政策
 土地利用
 公共政策評価
-数理最適化
-組合せ最適化
-計画・スケジューリング
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>TLPCMの評価および欠損値処理手法 / 区間組成データに対する 回帰分析 / 歌詞テキストデータの感情分類 / 区間データに対するPCA手法の提案と従来法との比較 / ファジィクラスタリングを用いた欠損値補完法について / T-normを用いたクラスター尺度による顧客分類法
+実証分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+行政データ分析
+センサデータ解析
+社会ネットワーク分析
+計算社会科学</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>TLPCMの評価および欠損値処理手法
+区間組成データに対する 回帰分析
+歌詞テキストデータの感情分類
+区間データに対するPCA手法の提案と従来法との比較
+ファジィクラスタリングを用いた欠損値補完法について
+T-normを用いたクラスター尺度による顧客分類法
 人工知能に基づく非線形高次元小標本データ解析とその社会的応用
 ３元型時系列高次元小標本データの解析とその社会的応用
 高次計量による高次元小標本型ビックデータ解析とその社会的応用
@@ -7472,6 +8448,14 @@
 乳幼児の活動量を測定するウェアラブル機器の開発
 乳幼児の活動量を測定するウェアラブルデバイスの開発
 サイバー社会ネットワークにおける噂の伝播の検出と制御
+数理物理・物性基礎
+ウェブ情報学・サービス情報学
+経済物理学
+ネットワーク科学
+社会物理学
+計算社会科学
+ウェブサイエンス
+ビッグデータ
 Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis
 コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析
 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析
@@ -7506,58 +8490,58 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>数理物理・物性基礎 / ウェブ情報学・サービス情報学</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>経済物理学 / ネットワーク科学 / 社会物理学 / 計算社会科学 / ウェブサイエンス / ビッグデータ</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis / コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 / Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan / Quantifying Collective Emotions: Japan’s Societal Trends Through Enhanced Sentiment Index Using POMS2 and SNS / Quantifying collective attention and fan engagement: a case study of the Japanese professional baseball league / News coverage of older drivers' fatal car crashes: is it over-represented? / Burstiness of human physical activities and their characterisation / 12-year observation of tweets about rubella in Japan: A retrospective infodemiology study / A two-phase model of collective memory decay with a dynamical switching point / SNSデータを用いた情報拡散シミュレーション / SNSにおける情報伝播ネットワークの構造 / Music Roles Affect the Selection of Consumption Means: A Questionnaire Survey of People’s Expectations for Music and Exploratory Factor Analysis / Dataset of identified scholars mentioned in acknowledgement statements / Classification of endogenous and exogenous bursts in collective emotions based on Weibo comments during COVID-19 / 日本におけるオンライン・ハラスメントの現状と対策：Twitterでの女性記者のツイート「炎上」を例に / 日本における自治体報道発表のCOVID-19発生状況を用いた感染者遷移状況の記録と可視化 / Simulation of information spreading on Twitter concerning radiation after the Fukushima nuclear power plant accident / 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― / サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して / Fake news propagates differently from real news even at early stages of spreading / 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 / Identifying long-term periodic cycles and memories of collective emotion in online social media / Correlations and fluctuations in the word sets of collective emotions / Configuration model for correlation matrices preserving the node strength</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>高齢運転者に関する報道とウェブ上の世論の可視化 / SNSから抽出した感情と実社会の関連性に関する研究 / Wikipedia閲覧数を用いた集合的記憶の減衰モデル / 保育現場への顔認証システム導入と運用の実証研究 / The identification of acknowledged scholars and their interdisciplinarity / Empirical studies on user-generated content and behavior of Southeast Asia community in Reddit / 日本プロ野球における集合的熱狂とファンの関与 / 仲値決定時近傍における板情報の非対称性の定量化 / 福島原発事故後のSNSにおける情報拡散シミュレーション / インターネットテレビにおけるコンテンツカテゴリ間の視聴数流動予測 / SNSを用いた新型コロナ禍における日本の空気感分析 / ソーシャルメディアを通した日本の高齢運転者に対する言論の定量化 / シラバスのテキストマイニングによる学生の主体性を育む科目の研究 / Wikipedia閲覧数を用いた集合的記憶の想起</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>保険・金融行動 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>保険・金融行動
-都市・地域政策
-GIS・空間分析
+          <t>数理物理・物性基礎 ; ウェブ情報学・サービス情報学 ; 社会政策・福祉 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 会計・ファイナンス ; テキスト分析・NLP ; 医療・ヘルスデータ ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 社会ネットワーク分析 ; 計算社会科学 ; 行政データ分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>数理物理・物性基礎
+ウェブ情報学・サービス情報学
+経済物理学
+ネットワーク科学
+社会物理学
+計算社会科学
+ウェブサイエンス
+ビッグデータ
 社会政策・福祉
-建築・空間設計
 ネットワーク・グラフ理論
 災害・防災研究
 政策評価・計量分析
+会計・ファイナンス
+テキスト分析・NLP
+医療・ヘルスデータ
 公共政策・社会工学
-経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
-都市経済
-地域政策
-土地利用
-公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
 社会福祉政策
 地域福祉
 子育て支援
 非営利組織論
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
 グラフ理論
 離散数学
 ネットワーク最適化
@@ -7568,12 +8552,40 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>高齢運転者に関する報道とウェブ上の世論の可視化 / SNSから抽出した感情と実社会の関連性に関する研究 / Wikipedia閲覧数を用いた集合的記憶の減衰モデル / 保育現場への顔認証システム導入と運用の実証研究 / The identification of acknowledged scholars and their interdisciplinarity / Empirical studies on user-generated content and behavior of Southeast Asia community in Reddit / 日本プロ野球における集合的熱狂とファンの関与 / 仲値決定時近傍における板情報の非対称性の定量化 / 福島原発事故後のSNSにおける情報拡散シミュレーション / インターネットテレビにおけるコンテンツカテゴリ間の視聴数流動予測 / SNSを用いた新型コロナ禍における日本の空気感分析 / ソーシャルメディアを通した日本の高齢運転者に対する言論の定量化 / シラバスのテキストマイニングによる学生の主体性を育む科目の研究 / Wikipedia閲覧数を用いた集合的記憶の想起
+実証分析
+会計データ分析
+財務会計
+管理会計
+会計情報システム
+テキストマイニング
+自然言語処理
+感情分析
+社会データ分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+社会ネットワーク分析
+行政データ分析
+学習分析</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>高齢運転者に関する報道とウェブ上の世論の可視化
+SNSから抽出した感情と実社会の関連性に関する研究
+Wikipedia閲覧数を用いた集合的記憶の減衰モデル
+保育現場への顔認証システム導入と運用の実証研究
+The identification of acknowledged scholars and their interdisciplinarity
+Empirical studies on user-generated content and behavior of Southeast Asia community in Reddit
+日本プロ野球における集合的熱狂とファンの関与
+仲値決定時近傍における板情報の非対称性の定量化
+福島原発事故後のSNSにおける情報拡散シミュレーション
+インターネットテレビにおけるコンテンツカテゴリ間の視聴数流動予測
+SNSを用いた新型コロナ禍における日本の空気感分析
+ソーシャルメディアを通した日本の高齢運転者に対する言論の定量化
+シラバスのテキストマイニングによる学生の主体性を育む科目の研究
+Wikipedia閲覧数を用いた集合的記憶の想起
 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究
 アカウンティング・インフォマティクス（会計情報科学）の基盤研究
 学際的エビデンスに基づく超高齢社会のモビリティ支援とアクティブ・エイジングの推進
@@ -7644,6 +8656,9 @@
 経済環境の激変と中小企業の役割
 縮小経済のもとでの中小企業と企業家活動
 中小企業の資金調達環境と政策のあり方
+経済政策
+財政・公共経済
+経済統計
 Number of positive lymph nodes and lymphatic invasion are significant prognostic factors after pancreaticoduodenectomy for distal cholangiocarcinoma.
 開業と廃業
 中小企業の知的財産
@@ -7678,54 +8693,52 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>経済政策 / 財政・公共経済 / 経済統計</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Number of positive lymph nodes and lymphatic invasion are significant prognostic factors after pancreaticoduodenectomy for distal cholangiocarcinoma. / 開業と廃業 / 中小企業の知的財産 / Bankruptcy dynamics in Japan / 開業のダイナミクス－開業研究の展望と法人設立登記にもとづく実証分析－ / Which firms exit and why? An analysis of small firm exits in Japan / Video game demand in Japan: a household data analysis / 新企業の人材確保--事業所・企業統計調査と新企業調査の個票分析 / SME policy, financial structure and firm growth: Evidence from japan / Does the creative business promotion law enhance SMEs' capital investments? Evidence from a panel dataset of unlisted SMEs in Japan / Potential entrepreneurship in Japan / Consumption-leisure preference structure: A new explanation of the Evans-Jovanovic results for entrepreneurial choice / Consumption-Leisure Preference Structure: A New Explanation of the Evans-Jovanovic Results for Entrepreneurial Choice(Erratum, 24, 423-427, 2005) / Does the Creative Business Promotion Law Enhance SMEs' Capital Investment? Evidence from a Panel Dataset of Unlisted SMEs in Japan / The IT revolution and productivity growth in Japan / Small Business Owner-Managers as Latent Informal Investors in Japan: Evidence from a Country with a Bank-based Financial System / 企業家の労働時間－実証分析－ / 景況感とアンケート調査－変化方向と水準は異曲同工か？－ / Productivity and Entrepreneurial Characteristics in New Japanese Firms / Who Succeeds as an Entrepreneur? An Analysis of the Post-Entry Performance of New Firms in Japan / 少子・高齢化と日本の消費フロンティア / SNA統計を用いた「トービンのｑ」の計測結果の違いについて / 潜在的開業者の実証分析 / 起業の意思決定における所得・余暇の代替と流動性制約 / SNA統計を用いた民間法人企業ベースの「トービンのｑ」と投資関数</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>中小企業における労働力の質的不足の影響要因 / 企業の情報開示と株価</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 保険・金融行動 ; 意思決定分析 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-保険・金融行動
-意思決定分析
-政策評価・計量分析
+          <t>経済政策 ; 財政・公共経済 ; 経済統計 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 経営工学 ; 行政データ分析 ; 政策評価 ; マーケティング分析</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>経済政策
+財政・公共経済
+経済統計
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
-環境・エネルギー
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
-行動意思決定
-実験・行動分析
-ナッジ
-意思決定支援
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+経営工学
+行政データ分析
 政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>中小企業における労働力の質的不足の影響要因 / 企業の情報開示と株価
+マーケティング分析</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>中小企業における労働力の質的不足の影響要因
+企業の情報開示と株価
 中小企業の雇用・技術と日本経済の再生
 経済環境の激変と中小企業の役割
 縮小経済のもとでの中小企業と企業家活動
@@ -7791,7 +8804,64 @@
 混合整数最適化を用いた制約付き変数選択による高精度パラメータ推定
 ノンパラメトリック推定に基づくテスト理論モデルの研究
 カーネル法と制御ポリシーを用いた中長期的投資戦略最適化
-取引コストを考慮した多期間ポートフォリオの最適化</t>
+取引コストを考慮した多期間ポートフォリオの最適化
+社会システム工学・安全システム
+数理情報学
+統計科学
+知能情報学
+数理最適化
+金融工学
+機械学習
+Robust personalized pricing under uncertainty of purchase probabilities
+Privacy-preserving recommender system using the data collaboration analysis for distributed datasets
+最適モデル多分木による価格需要曲線の推定
+Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times
+DC algorithm for estimation of sparse Gaussian graphical models
+Robust Portfolio Optimization for Recommender Systems Considering Uncertainty of Estimated Statistics
+Fast Solution to the Fair Ranking Problem Using the Sinkhorn Algorithm
+Mixed-Integer Linear Optimization Formulations for Feature Subset Selection in Kernel SVM Classification
+Robust portfolio optimization model for electronic coupon allocation
+混合整数最適化による相続工程の長期化リスク採点システム
+ECサイトにおける利用者属性データの欠損値補完
+Prescriptive price optimization using optimal regression trees
+構造的正則化処方分析による旅行パックの価格最適化
+Predicting Online Item-Choice Behavior: A Shape-Restricted Regression Approach
+Cardinality-constrained distributionally robust portfolio optimization
+Cutting-plane algorithm for estimation of sparse Cox proportional hazards models
+Branch-and-bound algorithm for optimal sparse canonical correlation analysis
+Dynamic portfolio selection with linear control policies for coherent risk minimization
+Linear control policies for online vehicle relocation in shared mobility systems
+出産前後の情報検索の分析：数理最適化による検索日の確率分布推定
+ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析)
+Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization
+Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach
+Sparse Poisson regression via mixed-integer optimization
+時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析
+データコラボレーション解析における統合関数の最適化
+A Design Method of the Joint Venture Formation in EPC Projects
+形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待)
+サポートベクトルマシンとカーネル法 (特集 機械学習の手法と役割期待)
+Smoothness-constrained model for nonparametric item response theory
+ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成―
+LDPC符号に対するタブー探索法に基づく勾配降下ビット反転復号法
+A Resource Flow Based Multistage Dynamic Scheduling Method for the State-Dependent Work
+数理最適化による学生のプロジェクト配属の決定
+整数最適化復号法の性能評価
+多重共線性を考慮した回帰式の変数選択問題の定式化
+A Simulation-Based Dynamic Scheduling Method in Project Cost Estimation Process
+キークレーン間干渉を考慮したコンテナ事前配列問題
+混合整数最適化による階層的変数選択を用いた店舗選択要因の分析
+ZIMPL言語とSCIPによる数理最適化
+複数の販売チャネルでの購入を促進するための商品推薦手法
+Mathematical Optimization Models for Nonparametric Item Response Theory
+時系列モデルによる商品販促効果の分析
+整数計画法による変数選択を用いた店舗選択モデル
+競争入札戦略と決定理論モデル
+アドネットワークにおけるバナー広告入札戦略決定フレームワークの有効性の検証
+確率計画法の理論と応用
+ECサイトの商品特性を考慮した2次元確率表による購買予測
+A Heuristic Bidding Price Decision Algorithm Based on Cost Estimation Accuracy under Limited Engineering Man-Hours in EPC Projects
+混合整数2次錐計画法による回帰式の変数選択</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -7799,62 +8869,142 @@
           <t>大規模な両面市場に対する公平性を考慮した取引促進施策の包括的最適化 / 混合整数最適化による次元縮約法の最良スパース推定 / 混合整数最適化を用いた制約付き変数選択による高精度パラメータ推定 / ノンパラメトリック推定に基づくテスト理論モデルの研究 / カーネル法と制御ポリシーを用いた中長期的投資戦略最適化 / 取引コストを考慮した多期間ポートフォリオの最適化</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>社会システム工学・安全システム / 数理情報学 / 統計科学 / 知能情報学</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>数理最適化 / 金融工学 / 機械学習</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Robust personalized pricing under uncertainty of purchase probabilities / Privacy-preserving recommender system using the data collaboration analysis for distributed datasets / 最適モデル多分木による価格需要曲線の推定 / Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times / DC algorithm for estimation of sparse Gaussian graphical models / Robust Portfolio Optimization for Recommender Systems Considering Uncertainty of Estimated Statistics / Fast Solution to the Fair Ranking Problem Using the Sinkhorn Algorithm / Mixed-Integer Linear Optimization Formulations for Feature Subset Selection in Kernel SVM Classification / Robust portfolio optimization model for electronic coupon allocation / 混合整数最適化による相続工程の長期化リスク採点システム / ECサイトにおける利用者属性データの欠損値補完 / Prescriptive price optimization using optimal regression trees / 構造的正則化処方分析による旅行パックの価格最適化 / Predicting Online Item-Choice Behavior: A Shape-Restricted Regression Approach / Cardinality-constrained distributionally robust portfolio optimization / Cutting-plane algorithm for estimation of sparse Cox proportional hazards models / Branch-and-bound algorithm for optimal sparse canonical correlation analysis / Dynamic portfolio selection with linear control policies for coherent risk minimization / Linear control policies for online vehicle relocation in shared mobility systems / 出産前後の情報検索の分析：数理最適化による検索日の確率分布推定 / ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析) / Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach / Sparse Poisson regression via mixed-integer optimization / 時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析 / データコラボレーション解析における統合関数の最適化 / A Design Method of the Joint Venture Formation in EPC Projects / 形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待) / サポートベクトルマシンとカーネル法 (特集 機械学習の手法と役割期待) / Smoothness-constrained model for nonparametric item response theory / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― / LDPC符号に対するタブー探索法に基づく勾配降下ビット反転復号法 / A Resource Flow Based Multistage Dynamic Scheduling Method for the State-Dependent Work / 数理最適化による学生のプロジェクト配属の決定 / 整数最適化復号法の性能評価 / 多重共線性を考慮した回帰式の変数選択問題の定式化 / A Simulation-Based Dynamic Scheduling Method in Project Cost Estimation Process / キークレーン間干渉を考慮したコンテナ事前配列問題 / 混合整数最適化による階層的変数選択を用いた店舗選択要因の分析 / ZIMPL言語とSCIPによる数理最適化 / 複数の販売チャネルでの購入を促進するための商品推薦手法 / Mathematical Optimization Models for Nonparametric Item Response Theory / 時系列モデルによる商品販促効果の分析 / 整数計画法による変数選択を用いた店舗選択モデル / 競争入札戦略と決定理論モデル / アドネットワークにおけるバナー広告入札戦略決定フレームワークの有効性の検証 / 確率計画法の理論と応用 / ECサイトの商品特性を考慮した2次元確率表による購買予測 / A Heuristic Bidding Price Decision Algorithm Based on Cost Estimation Accuracy under Limited Engineering Man-Hours in EPC Projects / 混合整数2次錐計画法による回帰式の変数選択</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>データ統合解析におけるアンカーデータ作成方法の提案 / 切除平面法による比例ハザードモデルの特徴選択 / 線形制御政策によるロング・ショートポートフォリオ最適化 / データコラボレーション解析における統合関数最適化問題の定式化と解法 / 多値型ノンパラメトリック項目反応理論の形状制約推定モデル / 最適化手法を用いた事例・変数統合型の欠損値補完 / 縮小推定を用いた平均・分散モデルによる推薦システム / 多重共線性を考慮した変数選択問題に対する切除平面法 / 2値分類の採点システムに対するbAUC最大化 / ロバスト平均・分散モデルを用いた推薦アルゴリズム / 確率制約付き最適化問題に対するDCアルゴリズム / シンクホーンアルゴリズムを用いた公平ランキング問題の高速求解 / 多重共線性を考慮した変数選択問題に対する高速厳密解法 / 深層学習を用いた巡回セールスマン問題の高速求解 / 強化学習を用いた競争入札戦略 / 予測評価値の不確実性を考慮した推薦商品集合の分布的ロバスト最適化 / 複数クーポンの効果推定と配布最適化 / コールセンターにおける会話データの分析 / 出産・子育てQ&amp;Aサイトにおける検索クエリの予測と分析 / 疎なWEB解答データの多次元項目反応理論分析</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 保険・金融行動 ; オペレーションズリサーチ ; 機械学習 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>家族・人口政策
+          <t>社会システム工学・安全システム ; 数理情報学 ; 統計科学 ; 知能情報学 ; 保険・金融行動 ; オペレーションズリサーチ ; 機械学習 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 物流最適化 ; 最適化</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>社会システム工学・安全システム
+数理情報学
+統計科学
+知能情報学
+数理最適化
+金融工学
+機械学習
 保険・金融行動
 オペレーションズリサーチ
-機械学習
-政策評価・計量分析
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 行動ファイナンス
 金融市場分析
 ESG投資
 企業財務
-数理最適化
 組合せ最適化
 計画・スケジューリング
 統計的学習
 予測モデリング
 表現学習
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>データ統合解析におけるアンカーデータ作成方法の提案 / 切除平面法による比例ハザードモデルの特徴選択 / 線形制御政策によるロング・ショートポートフォリオ最適化 / データコラボレーション解析における統合関数最適化問題の定式化と解法 / 多値型ノンパラメトリック項目反応理論の形状制約推定モデル / 最適化手法を用いた事例・変数統合型の欠損値補完 / 縮小推定を用いた平均・分散モデルによる推薦システム / 多重共線性を考慮した変数選択問題に対する切除平面法 / 2値分類の採点システムに対するbAUC最大化 / ロバスト平均・分散モデルを用いた推薦アルゴリズム / 確率制約付き最適化問題に対するDCアルゴリズム / シンクホーンアルゴリズムを用いた公平ランキング問題の高速求解 / 多重共線性を考慮した変数選択問題に対する高速厳密解法 / 深層学習を用いた巡回セールスマン問題の高速求解 / 強化学習を用いた競争入札戦略 / 予測評価値の不確実性を考慮した推薦商品集合の分布的ロバスト最適化 / 複数クーポンの効果推定と配布最適化 / コールセンターにおける会話データの分析 / 出産・子育てQ&amp;Aサイトにおける検索クエリの予測と分析 / 疎なWEB解答データの多次元項目反応理論分析
+物流最適化
+最適化</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>データ統合解析におけるアンカーデータ作成方法の提案
+切除平面法による比例ハザードモデルの特徴選択
+線形制御政策によるロング・ショートポートフォリオ最適化
+データコラボレーション解析における統合関数最適化問題の定式化と解法
+多値型ノンパラメトリック項目反応理論の形状制約推定モデル
+最適化手法を用いた事例・変数統合型の欠損値補完
+縮小推定を用いた平均・分散モデルによる推薦システム
+多重共線性を考慮した変数選択問題に対する切除平面法
+2値分類の採点システムに対するbAUC最大化
+ロバスト平均・分散モデルを用いた推薦アルゴリズム
+確率制約付き最適化問題に対するDCアルゴリズム
+シンクホーンアルゴリズムを用いた公平ランキング問題の高速求解
+多重共線性を考慮した変数選択問題に対する高速厳密解法
+深層学習を用いた巡回セールスマン問題の高速求解
+強化学習を用いた競争入札戦略
+予測評価値の不確実性を考慮した推薦商品集合の分布的ロバスト最適化
+複数クーポンの効果推定と配布最適化
+コールセンターにおける会話データの分析
+出産・子育てQ&amp;Aサイトにおける検索クエリの予測と分析
+疎なWEB解答データの多次元項目反応理論分析
 大規模な両面市場に対する公平性を考慮した取引促進施策の包括的最適化
 混合整数最適化による次元縮約法の最良スパース推定
 混合整数最適化を用いた制約付き変数選択による高精度パラメータ推定
 ノンパラメトリック推定に基づくテスト理論モデルの研究
 カーネル法と制御ポリシーを用いた中長期的投資戦略最適化
-取引コストを考慮した多期間ポートフォリオの最適化</t>
+取引コストを考慮した多期間ポートフォリオの最適化
+Robust personalized pricing under uncertainty of purchase probabilities
+Privacy-preserving recommender system using the data collaboration analysis for distributed datasets
+最適モデル多分木による価格需要曲線の推定
+Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times
+DC algorithm for estimation of sparse Gaussian graphical models
+Robust Portfolio Optimization for Recommender Systems Considering Uncertainty of Estimated Statistics
+Fast Solution to the Fair Ranking Problem Using the Sinkhorn Algorithm
+Mixed-Integer Linear Optimization Formulations for Feature Subset Selection in Kernel SVM Classification
+Robust portfolio optimization model for electronic coupon allocation
+混合整数最適化による相続工程の長期化リスク採点システム
+ECサイトにおける利用者属性データの欠損値補完
+Prescriptive price optimization using optimal regression trees
+構造的正則化処方分析による旅行パックの価格最適化
+Predicting Online Item-Choice Behavior: A Shape-Restricted Regression Approach
+Cardinality-constrained distributionally robust portfolio optimization
+Cutting-plane algorithm for estimation of sparse Cox proportional hazards models
+Branch-and-bound algorithm for optimal sparse canonical correlation analysis
+Dynamic portfolio selection with linear control policies for coherent risk minimization
+Linear control policies for online vehicle relocation in shared mobility systems
+出産前後の情報検索の分析：数理最適化による検索日の確率分布推定
+ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析)
+Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization
+Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach
+Sparse Poisson regression via mixed-integer optimization
+時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析
+データコラボレーション解析における統合関数の最適化
+A Design Method of the Joint Venture Formation in EPC Projects
+形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待)
+サポートベクトルマシンとカーネル法 (特集 機械学習の手法と役割期待)
+Smoothness-constrained model for nonparametric item response theory
+ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成―
+LDPC符号に対するタブー探索法に基づく勾配降下ビット反転復号法
+A Resource Flow Based Multistage Dynamic Scheduling Method for the State-Dependent Work
+数理最適化による学生のプロジェクト配属の決定
+整数最適化復号法の性能評価
+多重共線性を考慮した回帰式の変数選択問題の定式化
+A Simulation-Based Dynamic Scheduling Method in Project Cost Estimation Process
+キークレーン間干渉を考慮したコンテナ事前配列問題
+混合整数最適化による階層的変数選択を用いた店舗選択要因の分析
+ZIMPL言語とSCIPによる数理最適化
+複数の販売チャネルでの購入を促進するための商品推薦手法
+Mathematical Optimization Models for Nonparametric Item Response Theory
+時系列モデルによる商品販促効果の分析
+整数計画法による変数選択を用いた店舗選択モデル
+競争入札戦略と決定理論モデル
+アドネットワークにおけるバナー広告入札戦略決定フレームワークの有効性の検証
+確率計画法の理論と応用
+ECサイトの商品特性を考慮した2次元確率表による購買予測
+A Heuristic Bidding Price Decision Algorithm Based on Cost Estimation Accuracy under Limited Engineering Man-Hours in EPC Projects
+混合整数2次錐計画法による回帰式の変数選択</t>
         </is>
       </c>
     </row>
@@ -7893,6 +9043,16 @@
 文書生成AIサービス工学に関する研究
 文書生成AIの企業内利活用における最適化の研究
 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究
+会計学
+ウェブ情報学・サービス情報学
+社会システム工学・安全システム
+経営学
+商学
+ビジネスインテリジェンス
+会計情報科学
+サービス工学
+ソーシャル・データサイエンス
+社会工学
 Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment
 Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients
 Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach
@@ -7921,58 +9081,61 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>KPI工学教育研究の推進 / 包摂的コミュニティプラットフォームの構築 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 統合型ヘルスケアシステムの構築 / 文書生成AIサービス工学に関する研究 / 文書生成AIの企業内利活用における最適化の研究 / 統合型ヘルスケアシステムの構築 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 包摂的コミュニティプラットフォームの構築 / 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究</t>
+          <t>KPI工学教育研究の推進 / 包摂的コミュニティプラットフォームの構築 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 統合型ヘルスケアシステムの構築 / 文書生成AIサービス工学に関する研究 / 文書生成AIの企業内利活用における最適化の研究 / 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment / Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients / Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach / Estimation of conditional average treatment effects on distributed confidential data / Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support / Data collaboration for causal inference from limited medical testing and medication data / Generating Synthetic Journal-Entry Data Using Variational Autoencoder / Anomaly Detection in Double-entry Bookkeeping Data by Federated Learning System with Non-model Sharing Approach / Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data / An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises / Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 / pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis / 会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 / Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data / 分散機密データを想定した 処置効果の推定手法の開発 / 英文学術雑誌における近年の簿記研究 / Collaborative causal inference on distributed data / Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach / Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation / Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data / Knowledge sharing among coaches: expert power and social cognitive theory perspectives / Positive effect of proactive personality on customer orientation in service context / Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data / Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis</t>
+          <t>会計学 / ウェブ情報学・サービス情報学 / 社会システム工学・安全システム / 経営学 / 商学</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>ビジネスインテリジェンス / 会計情報科学 / サービス工学 / ソーシャル・データサイエンス / 社会工学</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment / Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients / Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach / Estimation of conditional average treatment effects on distributed confidential data / Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support / Data collaboration for causal inference from limited medical testing and medication data / Generating Synthetic Journal-Entry Data Using Variational Autoencoder / Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data / An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises / Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 / pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis / 会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 / Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data / 分散機密データを想定した 処置効果の推定手法の開発 / 英文学術雑誌における近年の簿記研究 / Collaborative causal inference on distributed data / Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach / Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation / Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data / Knowledge sharing among coaches: expert power and social cognitive theory perspectives / Positive effect of proactive personality on customer orientation in service context / Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data / Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>個人の能動的先手行動がチームに与える影響に関する時系列分析 / 若者のエシカル消費の阻害要因に関する実証分析 / チーム全体の能動的先手行動を強化するチーム構成の実証分析 / 中小サービス企業における業績管理会計の効果的な実践に関する実証分析 / 地域健康政策のためのベイジアンネットワークを用いた推論モデルの研究 / シングルサイロを想定した解釈可能なデータコラボレーション解析の応用研究 / 傾向スコアを用いた特定健診・特定保健指導の効果検証 / 価値共創を活性化する店員の音声模倣スキルに関する実験的研究 / 糖尿病の予防政策のためのデータコラボレーション解析の応用可能性 / ベイジアンネットワークを用いたフレイルの発症予測モデリング：健康関心度の違いに着目して / マルチレベルモデルを用いたフレイルの地域および個人要因分析 / 糖尿病の因果構造の推定におけるLingamの応用可能性 / 営業部門の上司と部下の顧客意識が提案行動に与える影響 / 小売店の接客サービス中に生じる頷きの模倣に関する実験的研究 / データコラボレーション解析による地域中小企業の資金ニーズ予測 / NavigatorⅢの開発と実証分析 / 分散データに対する統合的クラスタリングの提案 / 営業チームにおける人事異動が能動的先手行動に与える影響 / 非接触呼吸識別技術によるコンサート観客の呼吸同期分析 / 若者の選挙投票に着目したアカウンタビリティの実験的研究 / 確率的潜在意味解析による擬人情報作成方法の提案 / 社会参加が主観的幸福感に及ぼす効果の疑似実験による検証 / GPSデータを用いた陸運の誤配送検知手法の提案 / 仕訳とビジネスプロセスの月次変化とキャッシュフローに関する研究 / 複式簿記の相互参照性情報を学習した業績予測モデルに関する研究 / 高齢者の運動習慣とメンタルヘルスとの関係の実証分析 / 中小企業の財務難予測モデルを解釈する反事実的説明手法の研究 / 非接触計測による生理指標を用いた患者のマルチモーダル感情認識の研究 / 孤独の選好と身体的・精神的健康状態との関係の実証分析 / 分散生存時間データに対するDC因果推論の拡張 / 能動的先手行動の形成プロセスについての縦断的研究 / 標準年限卒業予測における大学間転移学習の研究 / NavigatorIIIのパイロット企業における実証実験</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>保険・金融行動 ; 意思決定分析 ; 都市・地域政策 ; 社会政策・福祉 ; オペレーションズリサーチ ; 機械学習 ; 画像・視覚情報処理 ; ネットワーク・グラフ理論 ; スポーツデータ分析 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>保険・金融行動
-意思決定分析
-都市・地域政策
+          <t>会計学 ; ウェブ情報学・サービス情報学 ; 社会システム工学・安全システム ; 経営学 ; 商学 ; 社会政策・福祉 ; オペレーションズリサーチ ; 政策評価・計量分析 ; 会計・ファイナンス ; 医療・ヘルスデータ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 経営工学 ; 環境工学 ; 社会ネットワーク分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>会計学
+ウェブ情報学・サービス情報学
+社会システム工学・安全システム
+経営学
+商学
+ビジネスインテリジェンス
+会計情報科学
+サービス工学
+ソーシャル・データサイエンス
+社会工学
 社会政策・福祉
 オペレーションズリサーチ
-機械学習
-画像・視覚情報処理
-ネットワーク・グラフ理論
-スポーツデータ分析
 政策評価・計量分析
+会計・ファイナンス
+医療・ヘルスデータ
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
-環境・エネルギー
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
-行動意思決定
-実験・行動分析
-ナッジ
-意思決定支援
-都市経済
-地域政策
-土地利用
-公共政策評価
 社会福祉政策
 地域福祉
 子育て支援
@@ -7980,29 +9143,63 @@
 数理最適化
 組合せ最適化
 計画・スケジューリング
-統計的学習
-予測モデリング
-表現学習
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>個人の能動的先手行動がチームに与える影響に関する時系列分析 / 若者のエシカル消費の阻害要因に関する実証分析 / チーム全体の能動的先手行動を強化するチーム構成の実証分析 / 中小サービス企業における業績管理会計の効果的な実践に関する実証分析 / 地域健康政策のためのベイジアンネットワークを用いた推論モデルの研究 / シングルサイロを想定した解釈可能なデータコラボレーション解析の応用研究 / 傾向スコアを用いた特定健診・特定保健指導の効果検証 / 価値共創を活性化する店員の音声模倣スキルに関する実験的研究 / 糖尿病の予防政策のためのデータコラボレーション解析の応用可能性 / ベイジアンネットワークを用いたフレイルの発症予測モデリング：健康関心度の違いに着目して / マルチレベルモデルを用いたフレイルの地域および個人要因分析 / 糖尿病の因果構造の推定におけるLingamの応用可能性 / 営業部門の上司と部下の顧客意識が提案行動に与える影響 / 小売店の接客サービス中に生じる頷きの模倣に関する実験的研究 / データコラボレーション解析による地域中小企業の資金ニーズ予測 / NavigatorⅢの開発と実証分析 / 分散データに対する統合的クラスタリングの提案 / 営業チームにおける人事異動が能動的先手行動に与える影響 / 非接触呼吸識別技術によるコンサート観客の呼吸同期分析 / 若者の選挙投票に着目したアカウンタビリティの実験的研究 / 確率的潜在意味解析による擬人情報作成方法の提案 / 社会参加が主観的幸福感に及ぼす効果の疑似実験による検証 / GPSデータを用いた陸運の誤配送検知手法の提案 / 仕訳とビジネスプロセスの月次変化とキャッシュフローに関する研究 / 複式簿記の相互参照性情報を学習した業績予測モデルに関する研究 / 高齢者の運動習慣とメンタルヘルスとの関係の実証分析 / 中小企業の財務難予測モデルを解釈する反事実的説明手法の研究 / 非接触計測による生理指標を用いた患者のマルチモーダル感情認識の研究 / 孤独の選好と身体的・精神的健康状態との関係の実証分析 / 分散生存時間データに対するDC因果推論の拡張 / 能動的先手行動の形成プロセスについての縦断的研究 / 標準年限卒業予測における大学間転移学習の研究 / NavigatorIIIのパイロット企業における実証実験
+実証分析
+会計データ分析
+財務会計
+管理会計
+会計情報システム
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+経営工学
+環境工学
+社会ネットワーク分析
+学習分析</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>個人の能動的先手行動がチームに与える影響に関する時系列分析
+若者のエシカル消費の阻害要因に関する実証分析
+チーム全体の能動的先手行動を強化するチーム構成の実証分析
+中小サービス企業における業績管理会計の効果的な実践に関する実証分析
+地域健康政策のためのベイジアンネットワークを用いた推論モデルの研究
+シングルサイロを想定した解釈可能なデータコラボレーション解析の応用研究
+傾向スコアを用いた特定健診・特定保健指導の効果検証
+価値共創を活性化する店員の音声模倣スキルに関する実験的研究
+糖尿病の予防政策のためのデータコラボレーション解析の応用可能性
+ベイジアンネットワークを用いたフレイルの発症予測モデリング：健康関心度の違いに着目して
+マルチレベルモデルを用いたフレイルの地域および個人要因分析
+糖尿病の因果構造の推定におけるLingamの応用可能性
+営業部門の上司と部下の顧客意識が提案行動に与える影響
+小売店の接客サービス中に生じる頷きの模倣に関する実験的研究
+データコラボレーション解析による地域中小企業の資金ニーズ予測
+NavigatorⅢの開発と実証分析
+分散データに対する統合的クラスタリングの提案
+営業チームにおける人事異動が能動的先手行動に与える影響
+非接触呼吸識別技術によるコンサート観客の呼吸同期分析
+若者の選挙投票に着目したアカウンタビリティの実験的研究
+確率的潜在意味解析による擬人情報作成方法の提案
+社会参加が主観的幸福感に及ぼす効果の疑似実験による検証
+GPSデータを用いた陸運の誤配送検知手法の提案
+仕訳とビジネスプロセスの月次変化とキャッシュフローに関する研究
+複式簿記の相互参照性情報を学習した業績予測モデルに関する研究
+高齢者の運動習慣とメンタルヘルスとの関係の実証分析
+中小企業の財務難予測モデルを解釈する反事実的説明手法の研究
+非接触計測による生理指標を用いた患者のマルチモーダル感情認識の研究
+孤独の選好と身体的・精神的健康状態との関係の実証分析
+分散生存時間データに対するDC因果推論の拡張
+能動的先手行動の形成プロセスについての縦断的研究
+標準年限卒業予測における大学間転移学習の研究
+NavigatorIIIのパイロット企業における実証実験
 KPI工学教育研究の推進
 包摂的コミュニティプラットフォームの構築
 健康にやさしいまちづくりのための環境整備に係る実証事業
@@ -8084,72 +9281,54 @@
           <t>ESG、開示とパフォーマンス：ノンパラメトリック手法を用いて / CSRの実証研究：ノンパラメトリック推計アプローチ / 社会的責任活動の実証研究：企業のミクロ経済学的行動と政策分析</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Subjective probabilistic expectations, household air pollution, and health: Evidence from cooking fuel use patterns in West Bengal, India / Seemingly Unrelated Interventions: Environmental Management Systems in the Workplace and Energy Saving Practices at Home / Cooking Fuel Choices --Analysis of Socio-economic and Demographic Factors in Rural India-- / Another Bias Correction for Asymmetric Kernel Density Estimation with a Parametric Start / Functional-Coefficient Cointegration Models in the Presence of Deterministic Trends / Do Social Norms Matter to Energy Saving Behavior?: Endogenous Social and Correlated Effects / Testing Symmetry of Unknown Densities via Smoothing with the Generalized Gamma Kernels / Family of the Generalised Gamma Kernels: A Generator of Asymmetric Kernels for Nonnegative Data / Nonnegative Bias Reduction Methods for Density Estimation Using Asymmetric Kernels</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>交通ネットワークと都市の成長ー西日本における高速道路建設が地方都市に与えた影響ー / 中国における結婚が健康に及ぼす影響 / 日本の賃金分布に対する反実仮想的要因分解 / ESGに関するSNS上での評判と企業パフォーマンス / 駅の開業が大気汚染に与えた影響の分析</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 家族・人口政策 ; 保険・金融行動 ; 都市・地域政策 ; 交通・モビリティ ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-家族・人口政策
-保険・金融行動
-都市・地域政策
-交通・モビリティ
-ネットワーク・グラフ理論
+          <t>保険・金融行動 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; マーケティング分析 ; 社会ネットワーク分析 ; 経営工学</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>保険・金融行動
 政策評価・計量分析
 公共政策・社会工学
 経済・ファイナンス
-数理最適化・OR
-都市・空間・交通
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 行動ファイナンス
 金融市場分析
 ESG投資
 企業財務
-都市経済
-地域政策
-土地利用
-公共政策評価
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>交通ネットワークと都市の成長ー西日本における高速道路建設が地方都市に与えた影響ー / 中国における結婚が健康に及ぼす影響 / 日本の賃金分布に対する反実仮想的要因分解 / ESGに関するSNS上での評判と企業パフォーマンス / 駅の開業が大気汚染に与えた影響の分析
+実証分析
+マーケティング分析
+社会ネットワーク分析
+経営工学</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>交通ネットワークと都市の成長ー西日本における高速道路建設が地方都市に与えた影響ー
+中国における結婚が健康に及ぼす影響
+日本の賃金分布に対する反実仮想的要因分解
+ESGに関するSNS上での評判と企業パフォーマンス
+駅の開業が大気汚染に与えた影響の分析
 ESG、開示とパフォーマンス：ノンパラメトリック手法を用いて
 CSRの実証研究：ノンパラメトリック推計アプローチ
 社会的責任活動の実証研究：企業のミクロ経済学的行動と政策分析
@@ -8203,6 +9382,8 @@
 国家の規模とガバナンスの学際的分析
 情報コストゼロ社会における過剰懲罰とリスク軽減のための社会制度設計
 新しい肺移植制度の構築と評価：ドナー交換移植の可能性
+社会システム工学・安全システム
+社会的ジレンマ、資産市場実験
 検索連動型広告における循環的な入札額変動の発生機構の解明
 ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析
 Bubbles in Asset Markets and the Heterogeneity of Beliefs.
@@ -8236,40 +9417,45 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>検索連動型広告における循環的な入札額変動の発生機構の解明 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Bubbles in Asset Markets and the Heterogeneity of Beliefs. / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 / 進化ゲーム理論の進化 — マルチエージェントシミュレーション，実験室実験と，LLM の行動経済学— / 発話量と発話内容に基づく集団間のコミュニケーション円滑化システムの提案 / ソーシャルメディア上のアジェンダ設定がエコーチェンバーの発生に与える影響について / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. / Emergence of echo chambers in social media communication involving multiple topics / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 / 進化ゲーム理論の進化：マルチエージェントシミュレーション, 実験室実験と，LLMの行動経済学 / 重みが動的なネットワークにおいてネットワーク構造が協力の進化に与える影響 / 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ / Individuals reciprocate negative actions revealing negative upstream reciprocity / SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. / Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement / Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim / パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 / 群淘汰状況下における罰則・報酬の進化 / Self-organized Speculation Game for the spontaneous emergence of financial stylized facts / 情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ / 時間制約を導入したゴミ箱モデル / Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment / 協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 / A quantitative easing experiment</t>
+          <t>社会システム工学・安全システム</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>社会的ジレンマ、資産市場実験</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>検索連動型広告における循環的な入札額変動の発生機構の解明 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Bubbles in Asset Markets and the Heterogeneity of Beliefs. / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 / 進化ゲーム理論の進化 — マルチエージェントシミュレーション，実験室実験と，LLM の行動経済学— / 発話量と発話内容に基づく集団間のコミュニケーション円滑化システムの提案 / ソーシャルメディア上のアジェンダ設定がエコーチェンバーの発生に与える影響について / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. / Emergence of echo chambers in social media communication involving multiple topics / 進化ゲーム理論の進化：マルチエージェントシミュレーション, 実験室実験と，LLMの行動経済学 / 重みが動的なネットワークにおいてネットワーク構造が協力の進化に与える影響 / 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ / Individuals reciprocate negative actions revealing negative upstream reciprocity / SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. / Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement / Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim / パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 / 群淘汰状況下における罰則・報酬の進化 / Self-organized Speculation Game for the spontaneous emergence of financial stylized facts / 情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ / 時間制約を導入したゴミ箱モデル / Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment / 協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 / A quantitative easing experiment</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>条件付き協力のためのコストの存在が、ネットワーク上での協力の進化に与える影響 / 自動運転配車サービスが東京中心部の交通形態に与える影響の分析 / 問題の難易度と意思決定数の関係に双曲志向が与える影響-ゴミ箱モデルによるアプローチ- / 多重ネットワーク上での協力の進化 〜相互作用ネットワークと戦略更新ネットワークの非対称性が協力の進化に与える影響〜 / 重みが動的なネットワークにおいてネットワークトポロジーが協力の進化に与える影響 / リンク重みの異質性と情報開示率が協力の進化に与える影響 / ソーシャルメディア上での複数のトピックにわたるコミュニケーションが意見の分極化とエコーチェンバーの発生に与える影響 / 純粋リスク下において他者の選択がリスク態度に与える影響：経済実験によるアプローチ / 間接互恵による協力進化に記憶の減衰が与える影響 / 歩行者ラウンドアバウトによる整流効果-駅構内の混雑緩和- / 投機的リスク下でのピア効果がリスク態度に与える影響 / 懲罰に関する社会規範が間接互恵の進化に与える影響について:シミュレーションによるアプローチ</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>保険・金融行動 ; 意思決定分析 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; オペレーションズリサーチ ; 交通・モビリティ ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>保険・金融行動
+          <t>社会システム工学・安全システム ; 保険・金融行動 ; 意思決定分析 ; マッチング理論・ゲーム理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 学習分析 ; マーケティング分析</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>社会システム工学・安全システム
+社会的ジレンマ、資産市場実験
+保険・金融行動
 意思決定分析
 マッチング理論・ゲーム理論
-都市・地域政策
-オペレーションズリサーチ
-交通・モビリティ
-ネットワーク・グラフ理論
-災害・防災研究
 政策評価・計量分析
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
-AI・データサイエンス
-都市・空間・交通
 行動ファイナンス
 金融市場分析
 ESG投資
@@ -8282,33 +9468,29 @@
 資源配分
 メカニズムデザイン
 協力ゲーム・非協力ゲーム
-都市経済
-地域政策
-土地利用
-公共政策評価
-数理最適化
-組合せ最適化
-計画・スケジューリング
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-災害社会学
-防災政策
-リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>条件付き協力のためのコストの存在が、ネットワーク上での協力の進化に与える影響 / 自動運転配車サービスが東京中心部の交通形態に与える影響の分析 / 問題の難易度と意思決定数の関係に双曲志向が与える影響-ゴミ箱モデルによるアプローチ- / 多重ネットワーク上での協力の進化 〜相互作用ネットワークと戦略更新ネットワークの非対称性が協力の進化に与える影響〜 / 重みが動的なネットワークにおいてネットワークトポロジーが協力の進化に与える影響 / リンク重みの異質性と情報開示率が協力の進化に与える影響 / ソーシャルメディア上での複数のトピックにわたるコミュニケーションが意見の分極化とエコーチェンバーの発生に与える影響 / 純粋リスク下において他者の選択がリスク態度に与える影響：経済実験によるアプローチ / 間接互恵による協力進化に記憶の減衰が与える影響 / 歩行者ラウンドアバウトによる整流効果-駅構内の混雑緩和- / 投機的リスク下でのピア効果がリスク態度に与える影響 / 懲罰に関する社会規範が間接互恵の進化に与える影響について:シミュレーションによるアプローチ
+実証分析
+社会ネットワーク分析
+学習分析
+マーケティング分析</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>条件付き協力のためのコストの存在が、ネットワーク上での協力の進化に与える影響
+自動運転配車サービスが東京中心部の交通形態に与える影響の分析
+問題の難易度と意思決定数の関係に双曲志向が与える影響-ゴミ箱モデルによるアプローチ-
+多重ネットワーク上での協力の進化 〜相互作用ネットワークと戦略更新ネットワークの非対称性が協力の進化に与える影響〜
+重みが動的なネットワークにおいてネットワークトポロジーが協力の進化に与える影響
+リンク重みの異質性と情報開示率が協力の進化に与える影響
+ソーシャルメディア上での複数のトピックにわたるコミュニケーションが意見の分極化とエコーチェンバーの発生に与える影響
+純粋リスク下において他者の選択がリスク態度に与える影響：経済実験によるアプローチ
+間接互恵による協力進化に記憶の減衰が与える影響
+歩行者ラウンドアバウトによる整流効果-駅構内の混雑緩和-
+投機的リスク下でのピア効果がリスク態度に与える影響
+懲罰に関する社会規範が間接互恵の進化に与える影響について:シミュレーションによるアプローチ
 人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析
 新規投資家の継続的な参入が価格形成・価格変動に与える影響
 ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響
@@ -8384,6 +9566,15 @@
 国際交流を背景とした中東都市計画史研究と都市保全プロジェクトへの還元
 モロッコの歴史都市 フェスの保全と近代化
 現代イスラーム都市の多元的成り立ちに関する研究
+都市計画・建築計画
+建築史・意匠
+地域研究
+建築・都市計画史
+地中海都市
+ヘレニズム基盤
+歴史文化保全
+国際協力
+中東・北アフリカ
 Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers”
 フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から―
 吉田正春使節団が見た19世紀テヘラン都市改造
@@ -8418,33 +9609,48 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>都市計画・建築計画 / 建築史・意匠 / 地域研究</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>建築・都市計画史 / 地中海都市 / ヘレニズム基盤 / 歴史文化保全 / 国際協力 / 中東・北アフリカ</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” / フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― / 吉田正春使節団が見た19世紀テヘラン都市改造 / ジスカール・デスタン政権下のパリ歩行者空間整備 / 1960 年アガディール地震とその震災復興都市計画に関する研究 / フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 / フェルナン・プイヨンのベルカステル村修復に関する研究 ─城と村の一体性に着目して─ / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス / 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 / フェス 積み重なる寄進が形成した迷宮都市 / ガルダイア 丘の上の城塞とオアシス渓谷の集落 / Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development / The Urban Forming History of Dubrovnik During the 12th Until 17th Century / Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning / Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration / カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- / Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris / Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille / The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel / アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 / 19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 / 商業都市カサブランカにおけるトラム導入による社会空間変容 / ビルマ王都マンダレーの城内および城外市街地の空間構造に関する研究</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>ポルトガル植民地期におけるリオ・デ・ジャネイロの都市空間変容 / 戦後パリ郊外におけるフェルナン・プイヨンの住宅地計画 -アルジェ及びマルセイユの作品との比較から- / 中国・杭州市における近代宗教建築の展開 –1840〜1949年に建設されたキリスト教建築を対象に– / メキシコシティ旧水路空間の変遷に見る水都空間の重層性 / アンナバ新市街における伝統的商業空間の形成 / カイロ中心市街地の都市空間変容-イギリス統治下から共和制移行期に着目して / 乾燥地域における伝統的水利システムの洪水抑制効果―アルジェリア国ガルダイア県の事例― / 現チェコ共和国の諸地域におけるカミロ・ジッテの都市計画実作 / フェルナン・プイヨンのベルカステル村修復に関する研究-城と村の一体性に着目して- / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス / 上海・上生新所の都市イノベーション-歴史保全と現代的開発の融合- / 海上シルクロード都市ザイトゥーン（中国・泉州）における遺産の保全と活用 / A Historical Survey of Spatial Customisation in the Modern Planned City of Abuja, Nigeria</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>都市・地域政策
+          <t>都市計画・建築計画 ; 建築史・意匠 ; 地域研究 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 都市計画 ; 社会ネットワーク分析 ; 人間中心設計 ; 災害分析</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>都市計画・建築計画
+建築史・意匠
+地域研究
+建築・都市計画史
+地中海都市
+ヘレニズム基盤
+歴史文化保全
+国際協力
+中東・北アフリカ
+都市・地域政策
 GIS・空間分析
-オペレーションズリサーチ
-交通・モビリティ
 建築・空間設計
-災害・防災研究
-政策評価・計量分析
 公共政策・社会工学
 数理最適化・OR
 都市・空間・交通
@@ -8456,29 +9662,31 @@
 空間計量
 地理情報分析
 立地分析
-数理最適化
-組合せ最適化
-計画・スケジューリング
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
 建築計画
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
-災害社会学
-防災政策
-リスク評価
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ポルトガル植民地期におけるリオ・デ・ジャネイロの都市空間変容 / 戦後パリ郊外におけるフェルナン・プイヨンの住宅地計画 -アルジェ及びマルセイユの作品との比較から- / 中国・杭州市における近代宗教建築の展開 –1840〜1949年に建設されたキリスト教建築を対象に– / メキシコシティ旧水路空間の変遷に見る水都空間の重層性 / アンナバ新市街における伝統的商業空間の形成 / カイロ中心市街地の都市空間変容-イギリス統治下から共和制移行期に着目して / 乾燥地域における伝統的水利システムの洪水抑制効果―アルジェリア国ガルダイア県の事例― / 現チェコ共和国の諸地域におけるカミロ・ジッテの都市計画実作 / フェルナン・プイヨンのベルカステル村修復に関する研究-城と村の一体性に着目して- / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス / 上海・上生新所の都市イノベーション-歴史保全と現代的開発の融合- / 海上シルクロード都市ザイトゥーン（中国・泉州）における遺産の保全と活用 / A Historical Survey of Spatial Customisation in the Modern Planned City of Abuja, Nigeria
+都市計画
+社会ネットワーク分析
+人間中心設計
+災害分析</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ポルトガル植民地期におけるリオ・デ・ジャネイロの都市空間変容
+戦後パリ郊外におけるフェルナン・プイヨンの住宅地計画 -アルジェ及びマルセイユの作品との比較から-
+中国・杭州市における近代宗教建築の展開 –1840〜1949年に建設されたキリスト教建築を対象に–
+メキシコシティ旧水路空間の変遷に見る水都空間の重層性
+アンナバ新市街における伝統的商業空間の形成
+カイロ中心市街地の都市空間変容-イギリス統治下から共和制移行期に着目して
+乾燥地域における伝統的水利システムの洪水抑制効果―アルジェリア国ガルダイア県の事例―
+現チェコ共和国の諸地域におけるカミロ・ジッテの都市計画実作
+フェルナン・プイヨンのベルカステル村修復に関する研究-城と村の一体性に着目して-
+フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス
+上海・上生新所の都市イノベーション-歴史保全と現代的開発の融合-
+海上シルクロード都市ザイトゥーン（中国・泉州）における遺産の保全と活用
+A Historical Survey of Spatial Customisation in the Modern Planned City of Abuja, Nigeria
 「もう一つのモダニズム」による地域性の再構築 フェルナン・プイヨンの生涯業績
 中東・北アフリカ地域におけるヘレニズム基盤の継承に関する都市文献史的研究
 西アジア地域の都市空間の重層性に関する計画論的研究
@@ -8496,7 +9704,6 @@
 1960 年アガディール地震とその震災復興都市計画に関する研究
 フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告
 フェルナン・プイヨンのベルカステル村修復に関する研究 ─城と村の一体性に着目して─
-フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス
 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史
 フェス 積み重なる寄進が形成した迷宮都市
 ガルダイア 丘の上の城塞とオアシス渓谷の集落
@@ -8555,6 +9762,9 @@
 海外における中間財生産による国内都市空間構造の変化に関する研究
 都市内立地の内生的決定に関する数値計算的アプローチ
 都市内情報流を考慮した空間構造の自己組織化
+経済政策
+理論経済学
+都市構造
 Dual Chalcogen-Bonding Interactions for the Conformational Control of Urea
 Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone
 Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone
@@ -8586,51 +9796,50 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Dual Chalcogen-Bonding Interactions for the Conformational Control of Urea / Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Life Cycle Analysis and Cost–Benefit Assessment of the Waste Collection System in Anyama, Cote d’Ivoire / Green Markets, Free Riders, and Monopolistic Competition / Relationship between urban population growth and utility level of workers with heterogeneity of labor efficiency / Environmental offsets and production externalities under monopolistic competition / Environmental offsets and production externalities under monopolistic competition / Implications of urbanization and Impact of Population Growth on Abidjan City, Cote d’Ivoire / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― / 通信技術革新と企業内立地行動の変化に関する研究-通信の固定費用を考慮して- / 通信技術革新と企業内立地行動の変化に関する研究 / Communication technologies and spatial organization of multi-unit firms in metropolitan areas / 企業の分離立地にともなう副都心成立の均衡土地利用分析 / The Influence of the Great Hanshin-Awaji Earthquake on Housing Market of the Area / 東京大都市圏の効用分布の推計と住居選択モデルの応用可能性に関する研究 / テレコミューティングの普及と都市構造に関する研究 / 複数都心を持つ都市構造の動的安定性に関する研究 / 首都圏における通勤家計の居住地選択モデル / 2種類の企業による都市の均衡形状に関する研究 / 大都市圏における近年のテレコミューティング（在宅勤務）と都市構造の均衡分析 / 首都圏における通勤家計の居住地選択モデル / 東京都心部における賃貸集合住宅価格の付加価値要因に関する研究</t>
+          <t>経済政策 / 理論経済学</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>都市構造</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Dual Chalcogen-Bonding Interactions for the Conformational Control of Urea / Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Life Cycle Analysis and Cost–Benefit Assessment of the Waste Collection System in Anyama, Cote d’Ivoire / Green Markets, Free Riders, and Monopolistic Competition / Relationship between urban population growth and utility level of workers with heterogeneity of labor efficiency / Environmental offsets and production externalities under monopolistic competition / Implications of urbanization and Impact of Population Growth on Abidjan City, Cote d’Ivoire / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― / 通信技術革新と企業内立地行動の変化に関する研究-通信の固定費用を考慮して- / 通信技術革新と企業内立地行動の変化に関する研究 / Communication technologies and spatial organization of multi-unit firms in metropolitan areas / 企業の分離立地にともなう副都心成立の均衡土地利用分析 / The Influence of the Great Hanshin-Awaji Earthquake on Housing Market of the Area / 東京大都市圏の効用分布の推計と住居選択モデルの応用可能性に関する研究 / テレコミューティングの普及と都市構造に関する研究 / 複数都心を持つ都市構造の動的安定性に関する研究 / 首都圏における通勤家計の居住地選択モデル / 2種類の企業による都市の均衡形状に関する研究 / 大都市圏における近年のテレコミューティング（在宅勤務）と都市構造の均衡分析 / 東京都心部における賃貸集合住宅価格の付加価値要因に関する研究</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>広域行政が自治体の財政に与える影響 / 長時間労働が中国人の健康に与える影響に関する研究 / 中国・広州市における高齢者施設の空間的アクセシビリティ評価 / 羽田空港の新飛行経路の騒音は周辺住宅価格への影響 / 中国の住宅資産と負債が高等教育進学率への影響と性別差異 / ネット・口コミが消費者行動に与える影響に関する研究～丸亀製麵を例として～ / 地方都市の駅まち空間再構築事業による地価変化の計量分析 / 地方都市におけるスマートシティ事業の実装が地価に与える影響 / 鉄道廃線敷のBRT化が地域に与える影響について / 中国における農村金融の格差に関する影響要因分析及び政策分析。ー中国“十二五”計画を中心に / 「国立公園満喫プロジェクト」が関連地域の地価に与える影響ー先行８公園を対象としてー / ハイテク企業のイノベーションが地価に与える影響 / 中国におけるライブコマースが農村振興に与える影響に関する分析 / 国際スポーツ大会の開催決定がスタジアム周辺地域に与える影響についての研究―地価の変化に注目して― / Park-PFIによる公園整備が商業地域の地価に与える影響 / ウォーカブル向上による関連地域の地価変化に関する研究 / 水害についてのリスク認識の変化が地価に及ぼす影響 / 高速鉄道が沿線地域に与える影響の実証研究―徐蘭高速鉄道を例として― / 中国における子供性別が家計の資産配分に与える影響―不動産を研究対象として― / LRT導入による地価への影響―宇都宮ライトレールを事例として―</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 保険・金融行動 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; 画像・視覚情報処理 ; スポーツデータ分析 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-保険・金融行動
+          <t>経済政策 ; 理論経済学 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 画像・視覚情報処理 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 物流最適化 ; 災害分析 ; 社会ネットワーク分析 ; 行政データ分析</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>経済政策
+理論経済学
+都市構造
 マッチング理論・ゲーム理論
 都市・地域政策
 GIS・空間分析
-オペレーションズリサーチ
-交通・モビリティ
 建築・空間設計
 画像・視覚情報処理
-スポーツデータ分析
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
-数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
 安定マッチング
 資源配分
 メカニズムデザイン
@@ -8643,13 +9852,6 @@
 空間計量
 地理情報分析
 立地分析
-数理最適化
-組合せ最適化
-計画・スケジューリング
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
 建築計画
 空間レイアウト生成
 居住空間設計
@@ -8658,18 +9860,42 @@
 画像認識
 行動認識
 マルチモーダル解析
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>広域行政が自治体の財政に与える影響 / 長時間労働が中国人の健康に与える影響に関する研究 / 中国・広州市における高齢者施設の空間的アクセシビリティ評価 / 羽田空港の新飛行経路の騒音は周辺住宅価格への影響 / 中国の住宅資産と負債が高等教育進学率への影響と性別差異 / ネット・口コミが消費者行動に与える影響に関する研究～丸亀製麵を例として～ / 地方都市の駅まち空間再構築事業による地価変化の計量分析 / 地方都市におけるスマートシティ事業の実装が地価に与える影響 / 鉄道廃線敷のBRT化が地域に与える影響について / 中国における農村金融の格差に関する影響要因分析及び政策分析。ー中国“十二五”計画を中心に / 「国立公園満喫プロジェクト」が関連地域の地価に与える影響ー先行８公園を対象としてー / ハイテク企業のイノベーションが地価に与える影響 / 中国におけるライブコマースが農村振興に与える影響に関する分析 / 国際スポーツ大会の開催決定がスタジアム周辺地域に与える影響についての研究―地価の変化に注目して― / Park-PFIによる公園整備が商業地域の地価に与える影響 / ウォーカブル向上による関連地域の地価変化に関する研究 / 水害についてのリスク認識の変化が地価に及ぼす影響 / 高速鉄道が沿線地域に与える影響の実証研究―徐蘭高速鉄道を例として― / 中国における子供性別が家計の資産配分に与える影響―不動産を研究対象として― / LRT導入による地価への影響―宇都宮ライトレールを事例として―
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+物流最適化
+災害分析
+社会ネットワーク分析
+行政データ分析</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>広域行政が自治体の財政に与える影響
+長時間労働が中国人の健康に与える影響に関する研究
+中国・広州市における高齢者施設の空間的アクセシビリティ評価
+羽田空港の新飛行経路の騒音は周辺住宅価格への影響
+中国の住宅資産と負債が高等教育進学率への影響と性別差異
+ネット・口コミが消費者行動に与える影響に関する研究～丸亀製麵を例として～
+地方都市の駅まち空間再構築事業による地価変化の計量分析
+地方都市におけるスマートシティ事業の実装が地価に与える影響
+鉄道廃線敷のBRT化が地域に与える影響について
+中国における農村金融の格差に関する影響要因分析及び政策分析。ー中国“十二五”計画を中心に
+「国立公園満喫プロジェクト」が関連地域の地価に与える影響ー先行８公園を対象としてー
+ハイテク企業のイノベーションが地価に与える影響
+中国におけるライブコマースが農村振興に与える影響に関する分析
+国際スポーツ大会の開催決定がスタジアム周辺地域に与える影響についての研究―地価の変化に注目して―
+Park-PFIによる公園整備が商業地域の地価に与える影響
+ウォーカブル向上による関連地域の地価変化に関する研究
+水害についてのリスク認識の変化が地価に及ぼす影響
+高速鉄道が沿線地域に与える影響の実証研究―徐蘭高速鉄道を例として―
+中国における子供性別が家計の資産配分に与える影響―不動産を研究対象として―
+LRT導入による地価への影響―宇都宮ライトレールを事例として―
 衛星情報を利用した物流における大気環境改善の評価
 独占的競争下での環境オフセットの自発的供給に関する研究
 都市における環境リスクの軽減の経済効果に関する研究
@@ -8743,6 +9969,9 @@
 「建築情報モデラーに関する研究」に対する
 ポスト定住化社会における時空を超えたアクティビティの流動化実態に関する実証的研究
 拡張現実技術を利用した実空間景観シミュレーションシステムの開発
+都市計画・建築計画
+社会システム工学・安全システム
+情報化・ネットワーク社会における建築計画・都市計画
 歩行者の空間学習を支援するナビゲーション手法に関する研究
 超一線都市の若者向けマンションの立地分析：広州を例にして
 街路網の広がりから見た城下町の空間構成の変容に関する研究
@@ -8776,45 +10005,47 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>歩行者の空間学習を支援するナビゲーション手法に関する研究 / 超一線都市の若者向けマンションの立地分析：広州を例にして / 街路網の広がりから見た城下町の空間構成の変容に関する研究 / 総合設計制度による建築物が街路景観の印象に与える影響に関する研究 ―3D都市モデルPLATEAU及びVR を用いて― / 都市の集約化が分散型エネルギーシステム導入に与える影響について / 街路網の広がりから見た城下町の空間構成の変容に関する研究 / デザイン共創環境を用いた集合住宅設計支援ツールの開発 / An analysis on urban shrinkage trends of all Japanese cities by detecting relative densely inhabited districts - Changes in urban form of Japanese cities in an era of shrinking population, part 2 / モビリティ技術活用による新しい児童通学スタイルの検証 / デザインパターンの列挙に関する一考察 / 相対的な人口集中地区の抽出を通じた全国市町村の都市縮小傾向の分析 －人口減少時代を迎えるわが国の都市圏の形態変化に関する研究（その2）－ / Exploring the Panel Exercises in the Modulor as presented by Le Corbusier / 歩行空間ネットワークを用いた駅周辺の回遊性に関する研究 －埼玉県大宮駅周辺を事例として－ / ル・コルビュジエが提示したモデュロールによる羽目板遊びの探求 / 中国安慶市の敬老院における整備実態の居住者の満足度に関する研究 / BIMと修繕記録を用いた既存建物の部位等の更新間隔算出 / 共育 ～ともに育て、ともに育つ保育園～ / ソーシャルメディアの投稿写真からみた地域特性に関する考察 / 媒介中心性を用いた歩行者の回遊行動に関する検討 - Walkability 指標の計測へ向けて - / 情報量損失最小化法を応用した相対的人口集中地区の抽出; 都市縮小・拡大市町村数の経年変化分析 / 上海中心市街地におけるGated Communityが飲食店への徒歩到達アクセシ ビリティに与える影響 / デジタル・モデュロール３ / AN ANALYSIS OF MIXED LAND USE TOWARD DESIGNING THE COMPACT CITY / 都市のWalkabilityに関する研究 ―Urban Network Analysisを用いた評価指標計算に向けて― / 土地利用の混在指標を用いたわが国の都市圏の形態分析 ―埼玉県東部を対象としたMetropolitan Form Analysis― Land-Use Mixの適用―</t>
+          <t>都市計画・建築計画 / 社会システム工学・安全システム</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>情報化・ネットワーク社会における建築計画・都市計画</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>歩行者の空間学習を支援するナビゲーション手法に関する研究 / 超一線都市の若者向けマンションの立地分析：広州を例にして / 街路網の広がりから見た城下町の空間構成の変容に関する研究 / 総合設計制度による建築物が街路景観の印象に与える影響に関する研究 ―3D都市モデルPLATEAU及びVR を用いて― / 都市の集約化が分散型エネルギーシステム導入に与える影響について / デザイン共創環境を用いた集合住宅設計支援ツールの開発 / An analysis on urban shrinkage trends of all Japanese cities by detecting relative densely inhabited districts - Changes in urban form of Japanese cities in an era of shrinking population, part 2 / モビリティ技術活用による新しい児童通学スタイルの検証 / デザインパターンの列挙に関する一考察 / 相対的な人口集中地区の抽出を通じた全国市町村の都市縮小傾向の分析 －人口減少時代を迎えるわが国の都市圏の形態変化に関する研究（その2）－ / Exploring the Panel Exercises in the Modulor as presented by Le Corbusier / 歩行空間ネットワークを用いた駅周辺の回遊性に関する研究 －埼玉県大宮駅周辺を事例として－ / ル・コルビュジエが提示したモデュロールによる羽目板遊びの探求 / 中国安慶市の敬老院における整備実態の居住者の満足度に関する研究 / BIMと修繕記録を用いた既存建物の部位等の更新間隔算出 / 共育 ～ともに育て、ともに育つ保育園～ / ソーシャルメディアの投稿写真からみた地域特性に関する考察 / 媒介中心性を用いた歩行者の回遊行動に関する検討 - Walkability 指標の計測へ向けて - / 情報量損失最小化法を応用した相対的人口集中地区の抽出; 都市縮小・拡大市町村数の経年変化分析 / 上海中心市街地におけるGated Communityが飲食店への徒歩到達アクセシ ビリティに与える影響 / デジタル・モデュロール３ / AN ANALYSIS OF MIXED LAND USE TOWARD DESIGNING THE COMPACT CITY / 都市のWalkabilityに関する研究 ―Urban Network Analysisを用いた評価指標計算に向けて― / 土地利用の混在指標を用いたわが国の都市圏の形態分析 ―埼玉県東部を対象としたMetropolitan Form Analysis― Land-Use Mixの適用―</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>市民の屋外公共空間活用に対する自治体の支援実態とその在り方ー市民の屋外空間における音楽活動支援に着目してー / 景観計画下での屋外広告物等の実態と伝統的都市景観に対する若者の景観認識—京都市を事例に— / 発達障害者の空間認知からみたナビゲーションのあり方に関する研究 / 中国における大学城の土地用途変遷と利用者の満足度について—呼蘭、下沙、広州大学城を対象にして— / デザイン共創環境を用いた集合住宅設計支援ツールの提案 / 中国旧市街地のゲーテッドコミュニティの再生に関する研究 ー河南省鄭州市を事例としてー / 都市の集約化と分散型エネルギーの導入適性に関する研究 / 総合設計制度による建築物が都市空間に与える圧迫感に関する研究-3D都市モデルPLATEAU及びVRを用いて- / 歩行者の空間学習に関する研究－ナビゲーション手法と環境的特徴に着目して－ / 超一線都市の若者向けマンションの立地分析と最適化－広州を例にして－</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; 画像・視覚情報処理 ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>家族・人口政策
+          <t>都市計画・建築計画 ; 社会システム工学・安全システム ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 都市計画 ; 数理最適化 ; 環境工学 ; 強化学習</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>都市計画・建築計画
+社会システム工学・安全システム
+情報化・ネットワーク社会における建築計画・都市計画
 都市・地域政策
 GIS・空間分析
-社会政策・福祉
-オペレーションズリサーチ
-交通・モビリティ
 建築・空間設計
-画像・視覚情報処理
-ネットワーク・グラフ理論
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 数理最適化・OR
-AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 都市経済
 地域政策
 土地利用
@@ -8823,38 +10054,36 @@
 空間計量
 地理情報分析
 立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
-数理最適化
-組合せ最適化
-計画・スケジューリング
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
 建築計画
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>市民の屋外公共空間活用に対する自治体の支援実態とその在り方ー市民の屋外空間における音楽活動支援に着目してー / 景観計画下での屋外広告物等の実態と伝統的都市景観に対する若者の景観認識—京都市を事例に— / 発達障害者の空間認知からみたナビゲーションのあり方に関する研究 / 中国における大学城の土地用途変遷と利用者の満足度について—呼蘭、下沙、広州大学城を対象にして— / デザイン共創環境を用いた集合住宅設計支援ツールの提案 / 中国旧市街地のゲーテッドコミュニティの再生に関する研究 ー河南省鄭州市を事例としてー / 都市の集約化と分散型エネルギーの導入適性に関する研究 / 総合設計制度による建築物が都市空間に与える圧迫感に関する研究-3D都市モデルPLATEAU及びVRを用いて- / 歩行者の空間学習に関する研究－ナビゲーション手法と環境的特徴に着目して－ / 超一線都市の若者向けマンションの立地分析と最適化－広州を例にして－
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+都市計画
+数理最適化
+環境工学
+強化学習</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>市民の屋外公共空間活用に対する自治体の支援実態とその在り方ー市民の屋外空間における音楽活動支援に着目してー
+景観計画下での屋外広告物等の実態と伝統的都市景観に対する若者の景観認識—京都市を事例に—
+発達障害者の空間認知からみたナビゲーションのあり方に関する研究
+中国における大学城の土地用途変遷と利用者の満足度について—呼蘭、下沙、広州大学城を対象にして—
+デザイン共創環境を用いた集合住宅設計支援ツールの提案
+中国旧市街地のゲーテッドコミュニティの再生に関する研究 ー河南省鄭州市を事例としてー
+都市の集約化と分散型エネルギーの導入適性に関する研究
+総合設計制度による建築物が都市空間に与える圧迫感に関する研究-3D都市モデルPLATEAU及びVRを用いて-
+歩行者の空間学習に関する研究－ナビゲーション手法と環境的特徴に着目して－
+超一線都市の若者向けマンションの立地分析と最適化－広州を例にして－
 ジェネレーティブデザインを通じて敷地計画における創造力はどこまで拡張できるか
 創造性の論理的・ 技術的探求に基づくデザイン共創環境の構築と教育プログラムの開発
 コンパクトシティを目指した都市デザイン戦略のための都市構造評価指標の探究
@@ -8929,6 +10158,16 @@
 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性
 スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築
 超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究
+都市計画・建築計画
+都市計画
+地区計画
+まちづくり
+カナダの都市計画
+団地再生
+住環境整備
+産官学民連携
+地域活性化
+コミュニティビジネス
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告
 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として
 わがまちのSDGs
@@ -8958,46 +10197,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>まちづくりを含む不動産開発に関する指導 / 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 超高層住宅の二重の老いの潜在的課題に関する研究 / 社会的孤独の解消モデル事例のプロセス分析及び検証手法の検討 / つくば市みどりの分譲地のまちづくり提案について / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築 / 超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究</t>
+          <t>まちづくりを含む不動産開発に関する指導 / 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 超高層住宅の二重の老いの潜在的課題に関する研究 / 社会的孤独の解消モデル事例のプロセス分析及び検証手法の検討 / つくば市みどりの分譲地のまちづくり提案について / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築 / 超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>都市計画・建築計画</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>都市計画 / 地区計画 / まちづくり / カナダの都市計画 / 団地再生 / 住環境整備 / 産官学民連携 / 地域活性化 / コミュニティビジネス</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として / わがまちのSDGs / 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ / 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 / 京都市東松ノ木市営住宅 / 国勢調査分析からみる外国人集住団地の実態 / 増加する外国人の受け皿としての住宅団地 / 住宅団地の外国人集住：特集の趣旨 / 住宅地における地区計画や認可協定の今後 / 区分所有マンションを含む市街地再開発事業の有効空地を考える / 社会的包摂とデザイン─「つながる場」15事例の実践から / 外国人住民との共存・共生: 海外の事例からの示唆 / 首都圏郊外におけるリノベーションまちづくりの成果と課題に関する研究 / 住宅建替えと一体的に再整備された街区公園の維持管理活動を通じたコミュニティ形成に関する研究 / 計画的戸建住宅地における駐車場シェアの導入意向と活用可能性に関する研究 / 多様な主体が関わる出産祝いプロジェクトの成立経緯と参加主体にもたらす変化に関する研究 / 職員の活躍を願う市長の思いと取り組み / 今後の地域づくりへの期待 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea / 転換期にある筑波研究学園都市の地区計画が空間資源継承に果たす役割と課題 / 1980年以降、40年の「つくば」の変化と現状 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea, Urban Planning / Living Lab Participants’ Knowledge Change about Inclusive Smart Cities: An Urban Living Lab in Seongdaegol, Seoul, South Korea / 地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>計画的戸建住宅地におけるスペース・シェアリングの展開可能性と受け入れ条件の検討 / 転換期にある筑波研究学園都市の地区計画が地域資源継承に果たす役割と実態 / 地域課題解決に取り組む空き家の活用過程の課題に関する研究―茨城県常総市水海道地区を対象にー / 筑波研究学園都市における市民に向けたサイエンスコミュニケーションの実態と課題 / 絶対高さ型高度地区導入後の展開と課題 / 高齢者情報格差の実態と対応策の検討：つくば市スーパーシティモデル地区を対象に / 民俗芸能の継承と観光活用意向に関する研究―岩手県北上市に着目してー / スペースシェアリングを活用した計画的戸建住宅団地の再生方策に関する研究 / 人材育成事業を契機とした地域活動拡大に関する研究 / 大都市郊外住宅団地における多世代交流活動の展開に関する研究 / 工業地帯の土地利用転換による知識集約型産業集積の実態と課題 －スペイン・バルセロナ市22＠プロジェクトを対象として－ / ごちゃまぜを理念とする多機能型福祉拠点の成立要因と意義に関する研究 －石川県社会福祉法人佛子園「三草二木 西圓寺」を対象として－ / 移住増加地域における遊休不動産を活用した新規事業の成立要因に関する研究 －長野県小諸市中心市街地を対象として－ / 超高層住宅集積地における利活用・維持管理の実態を踏まえた公開空地等の課題に関する研究 －東京都中央区第3ゾーンを対象として－</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>家族・人口政策
+          <t>都市計画・建築計画 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 都市計画 ; 社会ネットワーク分析 ; 人間中心設計 ; 行政データ分析</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>都市計画・建築計画
+都市計画
+地区計画
+まちづくり
+カナダの都市計画
+団地再生
+住環境整備
+産官学民連携
+地域活性化
+コミュニティビジネス
 都市・地域政策
 GIS・空間分析
-社会政策・福祉
 建築・空間設計
-政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 都市経済
 地域政策
 土地利用
@@ -9006,23 +10258,35 @@
 空間計量
 地理情報分析
 立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
 建築計画
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>計画的戸建住宅地におけるスペース・シェアリングの展開可能性と受け入れ条件の検討 / 転換期にある筑波研究学園都市の地区計画が地域資源継承に果たす役割と実態 / 地域課題解決に取り組む空き家の活用過程の課題に関する研究―茨城県常総市水海道地区を対象にー / 筑波研究学園都市における市民に向けたサイエンスコミュニケーションの実態と課題 / 絶対高さ型高度地区導入後の展開と課題 / 高齢者情報格差の実態と対応策の検討：つくば市スーパーシティモデル地区を対象に / 民俗芸能の継承と観光活用意向に関する研究―岩手県北上市に着目してー / スペースシェアリングを活用した計画的戸建住宅団地の再生方策に関する研究 / 人材育成事業を契機とした地域活動拡大に関する研究 / 大都市郊外住宅団地における多世代交流活動の展開に関する研究 / 工業地帯の土地利用転換による知識集約型産業集積の実態と課題 －スペイン・バルセロナ市22＠プロジェクトを対象として－ / ごちゃまぜを理念とする多機能型福祉拠点の成立要因と意義に関する研究 －石川県社会福祉法人佛子園「三草二木 西圓寺」を対象として－ / 移住増加地域における遊休不動産を活用した新規事業の成立要因に関する研究 －長野県小諸市中心市街地を対象として－ / 超高層住宅集積地における利活用・維持管理の実態を踏まえた公開空地等の課題に関する研究 －東京都中央区第3ゾーンを対象として－
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+社会ネットワーク分析
+人間中心設計
+行政データ分析</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>計画的戸建住宅地におけるスペース・シェアリングの展開可能性と受け入れ条件の検討
+転換期にある筑波研究学園都市の地区計画が地域資源継承に果たす役割と実態
+地域課題解決に取り組む空き家の活用過程の課題に関する研究―茨城県常総市水海道地区を対象にー
+筑波研究学園都市における市民に向けたサイエンスコミュニケーションの実態と課題
+絶対高さ型高度地区導入後の展開と課題
+高齢者情報格差の実態と対応策の検討：つくば市スーパーシティモデル地区を対象に
+民俗芸能の継承と観光活用意向に関する研究―岩手県北上市に着目してー
+スペースシェアリングを活用した計画的戸建住宅団地の再生方策に関する研究
+人材育成事業を契機とした地域活動拡大に関する研究
+大都市郊外住宅団地における多世代交流活動の展開に関する研究
+工業地帯の土地利用転換による知識集約型産業集積の実態と課題 －スペイン・バルセロナ市22＠プロジェクトを対象として－
+ごちゃまぜを理念とする多機能型福祉拠点の成立要因と意義に関する研究 －石川県社会福祉法人佛子園「三草二木 西圓寺」を対象として－
+移住増加地域における遊休不動産を活用した新規事業の成立要因に関する研究 －長野県小諸市中心市街地を対象として－
+超高層住宅集積地における利活用・維持管理の実態を踏まえた公開空地等の課題に関する研究 －東京都中央区第3ゾーンを対象として－
 まちづくりを含む不動産開発に関する指導
 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究
 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会
@@ -9096,6 +10360,9 @@
 ネットワーク理論の基盤整備と伸張
 データの精度を考慮した組合せ最適化問題に対する問題構造とアルゴリズムの研究
 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開
+最適化
+組合せ最適化
+アルゴリズム
 A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs
 Break maximization for round-robin tournaments without consecutive breaks
 Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm
@@ -9128,89 +10395,95 @@
           <t>大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 / ネットワーク上の時間軸をもった最適化問題とその応用 / スタッフスケジューリングに関する研究 / 組合せ最適化，ネットワーク最適化のアルゴリズム開発 / ネットワーク構造解析アルゴリズムの開発とネットワークアルゴリズムの総合的展開 / ネットワーク理論の基盤整備と伸張 / データの精度を考慮した組合せ最適化問題に対する問題構造とアルゴリズムの研究 / 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>最適化 / 組合せ最適化 / アルゴリズム</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs / Break maximization for round-robin tournaments without consecutive breaks / Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm / Height Estimation for Abrasive Grain of Synthetic Diamonds on Microscope Images by Conditional Adversarial Networks / Designing of OTN/WDM networks withrecovery methods for multiple failures / Restaurant Sales forecasting with feature interaction-learning mechanism based neural network model,IEEE International Conference on Big Data / A Discrete JAYA Algorithm for Long-Term Carpooling Problem / Carry-over Effect Values Minimization under Circle Method and Binary Factorization Based on Jaya Algorithm / Application of Data Anonymization to Smartphone Apps Usage Logs / 数理最適化を用いたサービス工学の事例―通勤カープールの実証実験― / Four-level knowledge graph contrastive learning structure for smart-phone application recommendation / A New Approach to Market Segmentation Based on 2-Dimensional Tables / Challenges of commuter carpooling with adapting to Japanese customs and regulations: A pilot study / Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model / Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan / Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament / 交換移植制度におけるドミナントマッチングの適用可能性 / Network Design Models with Partial Protection Schemes against Multiple Failures under Optical- Channel Data Unit Constraints / ILP models and improved methods for the problem of routing and spectrum allocation / A novel channel-based model for the problem of routing, space, and spectrum assignment / NASH EQUILIBRIA FOR INFORMATION DIFFUSION GAMES ON WEIGHTED CYCLES AND PATHS / Strongly separable matrices for nonadaptive combinatorial group testing / Modeling and Evaluating Taxi Ride-sharing for Event Trips / 不均衡データに対する多段階学習を用いた アンサンブルモデルによる2 クラス分類アルゴリズムの提案 / A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>外国人居住者向けWebサイトのアクセスログ解析による主要な遷移の特定 / 並列機械バッチスケジューチング問題に対するヒューリスティックアルゴリズム / ネットワーク拡張ゲームの均衡解を求める一解法 / 市場分析における遺伝的アルゴリズムを用いたサンプルデータ抽出 / 光通信ネットワークの耐故障二層モデルの比較と評価 / 深層学習を用いた平面画像上の物体の高さ推定 / ブレークに関する公平性を考慮した総当たり戦スケジューリング / プラスチック製部品製造工場における成形工程の生産スケジューリングモデル化と実応用 / 実応用にむけた多品種少量生産スケジューリング / byesを用いたスポーツスケジューリングの移動距離に関する検討 / ジョブショップスケジューリングの実応用へ向けた二つのアプローチ / 欠勤者を考慮した通勤カープールモデルの提案 / 2部グラフ上のポピュラーマッチングの要素数に着目した特徴づけ / スポーツ競技のスケジュール作成における Carry-Over Effect 値最小化に関する検討 / 次世代光伝送網における資源割り当てIPモデルとヒューリスティックアルゴリズム / 深層学習を用いたレストラン売り上げの予測モデルの構築と実応用 / 安全性と日本の法規制を考慮した通勤カープールモデルの提案と評価 / テクスチャ解析手法による2次元画像の砥粒群の形状分類 / 飲食店におけるスタッフのスキルを考慮したシフト作成のモデル構築と自動化 / 耐故障性を持つ二層光ネットワーク設計問題 / 飲食店の業務標準化に向けた最適な調理手順モデリング / 並列機械スケジューリング問題における多様な解の生成 / 空間分割多重光伝送網における通信保護を考慮した資源割当問題の効率的計算方法の検討 / ジョブショップスケジューリング問題に対する深層学習を用いたヒューリスティックアルゴリズム / A Contrastive Learning Structure for Prediction of smartphone applications to use next / 知識グラフの対照学習におけるグラフサンプリング手法の検討 / 大規模なカープーリング問題に対するK-medoidsクラスタリングを用いた二段階アルゴリズム / データ匿名加工手法のスマートフォンアプリ利用ログへの適用可能性 / 光通信ネットワークにおけるスプリットスペクトルを取り入れた資源割当モデルの提案 / ネットワーク上の耐故障性のある centdian 配置問題 / スマホアプリデータにおける推薦システムの活用 / 動的最短経路阻止モデルの拡張と観察 / 総当たり戦における試合間隔差の最小化問題 / 双曲空間とグラフニューラルネットワークを用いたCross-Domain推薦システムモデル / 高次元データに対するクラスタリングアプローチ / 高齢者通所介護施設における訪問時刻幅を持つ送迎サービスモデル / 訪問介護における訪問順序の最適化 / 待ち時間を考慮した通勤カープールモデル / 試合間隔の公平性を考慮した同時制約を持つ対戦表作成 / 飲食店の調理スケジューリング問題に対するメタヒューリスティクスの適用 / 光ネットワーク上の資源割当問題における候補パスの選択 / Pointer Networksを用いた飲食店における調理スケジューリング</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; オペレーションズリサーチ ; 建築・空間設計 ; 機械学習 ; 画像・視覚情報処理 ; ネットワーク・グラフ理論 ; スポーツデータ分析 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>マッチング理論・ゲーム理論
-都市・地域政策
-GIS・空間分析
-社会政策・福祉
+          <t>オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 社会ネットワーク分析 ; ネットワーク科学</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>最適化
+組合せ最適化
+アルゴリズム
 オペレーションズリサーチ
-建築・空間設計
-機械学習
-画像・視覚情報処理
 ネットワーク・グラフ理論
-スポーツデータ分析
-政策評価・計量分析
-公共政策・社会工学
-経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
-都市経済
-地域政策
-土地利用
-公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
 数理最適化
-組合せ最適化
 計画・スケジューリング
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-統計的学習
-予測モデリング
-表現学習
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
 グラフ理論
 離散数学
 ネットワーク最適化
 組合せ構造
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>外国人居住者向けWebサイトのアクセスログ解析による主要な遷移の特定 / 並列機械バッチスケジューチング問題に対するヒューリスティックアルゴリズム / ネットワーク拡張ゲームの均衡解を求める一解法 / 市場分析における遺伝的アルゴリズムを用いたサンプルデータ抽出 / 光通信ネットワークの耐故障二層モデルの比較と評価 / 深層学習を用いた平面画像上の物体の高さ推定 / ブレークに関する公平性を考慮した総当たり戦スケジューリング / プラスチック製部品製造工場における成形工程の生産スケジューリングモデル化と実応用 / 実応用にむけた多品種少量生産スケジューリング / byesを用いたスポーツスケジューリングの移動距離に関する検討 / ジョブショップスケジューリングの実応用へ向けた二つのアプローチ / 欠勤者を考慮した通勤カープールモデルの提案 / 2部グラフ上のポピュラーマッチングの要素数に着目した特徴づけ / スポーツ競技のスケジュール作成における Carry-Over Effect 値最小化に関する検討 / 次世代光伝送網における資源割り当てIPモデルとヒューリスティックアルゴリズム / 深層学習を用いたレストラン売り上げの予測モデルの構築と実応用 / 安全性と日本の法規制を考慮した通勤カープールモデルの提案と評価 / テクスチャ解析手法による2次元画像の砥粒群の形状分類 / 飲食店におけるスタッフのスキルを考慮したシフト作成のモデル構築と自動化 / 耐故障性を持つ二層光ネットワーク設計問題 / 飲食店の業務標準化に向けた最適な調理手順モデリング / 並列機械スケジューリング問題における多様な解の生成 / 空間分割多重光伝送網における通信保護を考慮した資源割当問題の効率的計算方法の検討 / ジョブショップスケジューリング問題に対する深層学習を用いたヒューリスティックアルゴリズム / A Contrastive Learning Structure for Prediction of smartphone applications to use next / 知識グラフの対照学習におけるグラフサンプリング手法の検討 / 大規模なカープーリング問題に対するK-medoidsクラスタリングを用いた二段階アルゴリズム / データ匿名加工手法のスマートフォンアプリ利用ログへの適用可能性 / 光通信ネットワークにおけるスプリットスペクトルを取り入れた資源割当モデルの提案 / ネットワーク上の耐故障性のある centdian 配置問題 / スマホアプリデータにおける推薦システムの活用 / 動的最短経路阻止モデルの拡張と観察 / 総当たり戦における試合間隔差の最小化問題 / 双曲空間とグラフニューラルネットワークを用いたCross-Domain推薦システムモデル / 高次元データに対するクラスタリングアプローチ / 高齢者通所介護施設における訪問時刻幅を持つ送迎サービスモデル / 訪問介護における訪問順序の最適化 / 待ち時間を考慮した通勤カープールモデル / 試合間隔の公平性を考慮した同時制約を持つ対戦表作成 / 飲食店の調理スケジューリング問題に対するメタヒューリスティクスの適用 / 光ネットワーク上の資源割当問題における候補パスの選択 / Pointer Networksを用いた飲食店における調理スケジューリング
+社会ネットワーク分析
+ネットワーク科学</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>外国人居住者向けWebサイトのアクセスログ解析による主要な遷移の特定
+並列機械バッチスケジューチング問題に対するヒューリスティックアルゴリズム
+ネットワーク拡張ゲームの均衡解を求める一解法
+市場分析における遺伝的アルゴリズムを用いたサンプルデータ抽出
+光通信ネットワークの耐故障二層モデルの比較と評価
+深層学習を用いた平面画像上の物体の高さ推定
+ブレークに関する公平性を考慮した総当たり戦スケジューリング
+プラスチック製部品製造工場における成形工程の生産スケジューリングモデル化と実応用
+実応用にむけた多品種少量生産スケジューリング
+byesを用いたスポーツスケジューリングの移動距離に関する検討
+ジョブショップスケジューリングの実応用へ向けた二つのアプローチ
+欠勤者を考慮した通勤カープールモデルの提案
+2部グラフ上のポピュラーマッチングの要素数に着目した特徴づけ
+スポーツ競技のスケジュール作成における Carry-Over Effect 値最小化に関する検討
+次世代光伝送網における資源割り当てIPモデルとヒューリスティックアルゴリズム
+深層学習を用いたレストラン売り上げの予測モデルの構築と実応用
+安全性と日本の法規制を考慮した通勤カープールモデルの提案と評価
+テクスチャ解析手法による2次元画像の砥粒群の形状分類
+飲食店におけるスタッフのスキルを考慮したシフト作成のモデル構築と自動化
+耐故障性を持つ二層光ネットワーク設計問題
+飲食店の業務標準化に向けた最適な調理手順モデリング
+並列機械スケジューリング問題における多様な解の生成
+空間分割多重光伝送網における通信保護を考慮した資源割当問題の効率的計算方法の検討
+ジョブショップスケジューリング問題に対する深層学習を用いたヒューリスティックアルゴリズム
+A Contrastive Learning Structure for Prediction of smartphone applications to use next
+知識グラフの対照学習におけるグラフサンプリング手法の検討
+大規模なカープーリング問題に対するK-medoidsクラスタリングを用いた二段階アルゴリズム
+データ匿名加工手法のスマートフォンアプリ利用ログへの適用可能性
+光通信ネットワークにおけるスプリットスペクトルを取り入れた資源割当モデルの提案
+ネットワーク上の耐故障性のある centdian 配置問題
+スマホアプリデータにおける推薦システムの活用
+動的最短経路阻止モデルの拡張と観察
+総当たり戦における試合間隔差の最小化問題
+双曲空間とグラフニューラルネットワークを用いたCross-Domain推薦システムモデル
+高次元データに対するクラスタリングアプローチ
+高齢者通所介護施設における訪問時刻幅を持つ送迎サービスモデル
+訪問介護における訪問順序の最適化
+待ち時間を考慮した通勤カープールモデル
+試合間隔の公平性を考慮した同時制約を持つ対戦表作成
+飲食店の調理スケジューリング問題に対するメタヒューリスティクスの適用
+光ネットワーク上の資源割当問題における候補パスの選択
+Pointer Networksを用いた飲食店における調理スケジューリング
 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発
 ネットワーク上の時間軸をもった最適化問題とその応用
 スタッフスケジューリングに関する研究
@@ -9285,6 +10558,13 @@
 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究
 集合住宅における子ども・女性に対する犯罪の実態分析と対策立案
 地理的犯罪予測の手法構築‐学際研究と産官学連携による学術基盤の確立とシステム開発
+社会システム工学・安全システム
+都市計画・建築計画
+環境農学（含ランドスケープ科学）
+都市計画
+犯罪科学
+空間情報科学
+環境心理学
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告
 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて
 都市公園における逸脱行為に関する縦断的研究
@@ -9319,46 +10599,54 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>社会システム工学・安全システム / 都市計画・建築計画 / 環境農学（含ランドスケープ科学）</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>都市計画 / 犯罪科学 / 空間情報科学 / 環境心理学</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて / 都市公園における逸脱行為に関する縦断的研究 / 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 / Mechanisms contributing to road network growth in volunteered street view imagery data / 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して / 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として / 人口低密度地域における人々の活動から見た「都市の活力」の計測 / 全国のJAを対象とする果物盗被害に関するアンケート調査報告 / Regional variations in key factors of children's independent mobility across Japan / 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 / Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives / Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) / Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning / 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 / GPSロガーを用いた官民による果樹盗パトロールの計測 / 子供の前兆事案被害情報の主体間共有の実態 / 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 / Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) / 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して / GPSログに基づく行動推定データを用いた人々の社会的接触可能性の時空間的把握 / サイバー・フィジカル空間上の社会的交流と居住地の近隣環境</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>COVID-19緊急事態宣言に伴う社会変化と犯罪の関連 / 小規模公園の廃止プロセスの実態と評価：社会受容と地域活性化の視点から / Methodology for applying a crowdsourced street view imagery data to evaluate street-level greenness / 留学生の帯同家族におけるソーシャルサポートの実態 / 子供を対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因 / 余暇歩行と近隣の土地利用の配置及び道路構成パターンとの関連 - GULPデータを用いて - / 地方部におけるSNSを介した観光関連情報の授受と観光行動や旅行地に対する愛着の関係 / 子どもを対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因 / 自主防犯行動促進の観点から見た警察SNSの評価 / 新たな防犯活動としての「ながら見守り」の実態と評価 / 多拠点生活者の特徴からみた地域への参入可能性の解明 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 / 刑務所出所者の地域生活定着に向けた訪問支援制度の実態と評価 / 若年層のサイバー・フィジカル空間におけるパーソナルネットワークと個人・居住地特性 / 筑波研究学園都市における公務員宿舎の廃止・再開発が人口移動・住民構成・コミュニティ活動に与える影響 / 人々の社会的接触可能性の時空間的把握とその要因：人口低密地域での検討 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 意思決定分析 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>家族・人口政策
+          <t>社会システム工学・安全システム ; 都市計画・建築計画 ; 環境農学（含ランドスケープ科学） ; 意思決定分析 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 建築・空間設計 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 農業情報学 ; 災害分析 ; 環境工学</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>社会システム工学・安全システム
+都市計画・建築計画
+環境農学（含ランドスケープ科学）
+都市計画
+犯罪科学
+空間情報科学
+環境心理学
 意思決定分析
 都市・地域政策
 GIS・空間分析
-社会政策・福祉
 オペレーションズリサーチ
-交通・モビリティ
 建築・空間設計
-ネットワーク・グラフ理論
-災害・防災研究
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 行動意思決定
 実験・行動分析
 ナッジ
@@ -9371,37 +10659,46 @@
 空間計量
 地理情報分析
 立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
 数理最適化
 組合せ最適化
 計画・スケジューリング
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
 建築計画
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-災害社会学
-防災政策
-リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>COVID-19緊急事態宣言に伴う社会変化と犯罪の関連 / 小規模公園の廃止プロセスの実態と評価：社会受容と地域活性化の視点から / Methodology for applying a crowdsourced street view imagery data to evaluate street-level greenness / 留学生の帯同家族におけるソーシャルサポートの実態 / 子供を対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因 / 余暇歩行と近隣の土地利用の配置及び道路構成パターンとの関連 - GULPデータを用いて - / 地方部におけるSNSを介した観光関連情報の授受と観光行動や旅行地に対する愛着の関係 / 子どもを対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因 / 自主防犯行動促進の観点から見た警察SNSの評価 / 新たな防犯活動としての「ながら見守り」の実態と評価 / 多拠点生活者の特徴からみた地域への参入可能性の解明 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 / 刑務所出所者の地域生活定着に向けた訪問支援制度の実態と評価 / 若年層のサイバー・フィジカル空間におけるパーソナルネットワークと個人・居住地特性 / 筑波研究学園都市における公務員宿舎の廃止・再開発が人口移動・住民構成・コミュニティ活動に与える影響 / 人々の社会的接触可能性の時空間的把握とその要因：人口低密地域での検討 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+社会ネットワーク分析
+農業情報学
+災害分析
+環境工学</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>COVID-19緊急事態宣言に伴う社会変化と犯罪の関連
+小規模公園の廃止プロセスの実態と評価：社会受容と地域活性化の視点から
+Methodology for applying a crowdsourced street view imagery data to evaluate street-level greenness
+留学生の帯同家族におけるソーシャルサポートの実態
+子供を対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因
+余暇歩行と近隣の土地利用の配置及び道路構成パターンとの関連 - GULPデータを用いて -
+地方部におけるSNSを介した観光関連情報の授受と観光行動や旅行地に対する愛着の関係
+子どもを対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因
+自主防犯行動促進の観点から見た警察SNSの評価
+新たな防犯活動としての「ながら見守り」の実態と評価
+多拠点生活者の特徴からみた地域への参入可能性の解明
+留学生の帯同家族におけるソーシャル・サポートの実態に関する研究
+刑務所出所者の地域生活定着に向けた訪問支援制度の実態と評価
+若年層のサイバー・フィジカル空間におけるパーソナルネットワークと個人・居住地特性
+筑波研究学園都市における公務員宿舎の廃止・再開発が人口移動・住民構成・コミュニティ活動に与える影響
+人々の社会的接触可能性の時空間的把握とその要因：人口低密地域での検討
+Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning
 特殊詐欺に「騙されても被害に至らない」社会システムの構築に向けた実証研究
 情報提供と環境手がかりによる行動変容：ナッジ犯罪予防の定式化とその効果検証
 日本における農村犯罪学の創成に向けた萌芽研究：窃盗犯を事例とする実態分析
@@ -9424,11 +10721,9 @@
 全国のJAを対象とする果物盗被害に関するアンケート調査報告
 Regional variations in key factors of children's independent mobility across Japan
 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析
-留学生の帯同家族におけるソーシャル・サポートの実態に関する研究
 Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives
 Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI)
 Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits
-Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning
 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査
 GPSロガーを用いた官民による果樹盗パトロールの計測
 子供の前兆事案被害情報の主体間共有の実態
@@ -9477,6 +10772,11 @@
 逸脱行動が生起するプロセスと矯正方法に関する研究
 進路意思決定における認知・感情過程のモデル化
 教師教育教材を事例としたマルチメディア教材設計・評価手法の開発
+社会心理学
+実験心理学
+意思決定
+認知心理学
+感情
 Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan
 後悔を力に変える
 Exploring the Relationship Between Different Consumer Behaviors and Subjective Well-Being in Japan: A Focus on Prosocial, Sustainable, Experiential, and Conspicuous Consumption
@@ -9510,35 +10810,49 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan / 後悔を力に変える / Exploring the Relationship Between Different Consumer Behaviors and Subjective Well-Being in Japan: A Focus on Prosocial, Sustainable, Experiential, and Conspicuous Consumption / Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan / The Effect of General Trust on Willingness to Communicate in English among Japanese individuals across various situations. / Factors influencing behavioral intentions in livestream shopping: A cross-cultural study / Does macro-level general trust influence second language communication? :targeting prefectural capitals. / The influence of online multiplayer games on social capital and interdependent well-being in Japan / オンライン入試の実施と問題点 / 一般市民の更生支援に対する認知および参加意向の向上にむけた検討 / Understanding confidence in the human papillomavirus vaccine in Japan: a web-based survey of mothers, female adolescents, and healthcare professionals / Simulation of Outpatient Flow at the University of Tsukuba Hospital / Frequency of grooming the eyebrows and cosmetic consciousness in men. / The relationship between quantity of information contact and public evaluation of volunteer probation officers to promote understanding for social reintegration support. / Factors influencing differences between useful and useless regret. / The relationships between a metacognition scale and adaptive behavior in the regret situations: A comparison between junior high-school and university students. / Understanding confidence in human papillomavirus vaccine in Japan: A web-based questionnaire survey of mothers, female adolescents, and health care professionals. / 裁判員参加意向を規定する要因および意思決定プロセスの差異：制度施行前後の比較 / 市民の生態系サービスへの認知が保全行動意図に及ぼす影響：全国アンケートを用いた社会心理学的分析 / どのようにリスクを伝えればよいか：よりよいリスクコミュニケーションのために必要なこと / 意思決定から見たギャンブル行動 / Change of decision-making processes in repeated risk-taking behavior in a complex dynamic situation / The neural networks model of decision-making including feedback processes / Research on the gaps between students' expectation and satisfaction for universities / Analogical decision making in career choice</t>
+          <t>社会心理学 / 実験心理学</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>意思決定 / 認知心理学 / 社会心理学 / 感情</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan / 後悔を力に変える / Exploring the Relationship Between Different Consumer Behaviors and Subjective Well-Being in Japan: A Focus on Prosocial, Sustainable, Experiential, and Conspicuous Consumption / The Effect of General Trust on Willingness to Communicate in English among Japanese individuals across various situations. / Factors influencing behavioral intentions in livestream shopping: A cross-cultural study / Does macro-level general trust influence second language communication? :targeting prefectural capitals. / The influence of online multiplayer games on social capital and interdependent well-being in Japan / オンライン入試の実施と問題点 / 一般市民の更生支援に対する認知および参加意向の向上にむけた検討 / Understanding confidence in the human papillomavirus vaccine in Japan: a web-based survey of mothers, female adolescents, and healthcare professionals / Simulation of Outpatient Flow at the University of Tsukuba Hospital / Frequency of grooming the eyebrows and cosmetic consciousness in men. / The relationship between quantity of information contact and public evaluation of volunteer probation officers to promote understanding for social reintegration support. / Factors influencing differences between useful and useless regret. / The relationships between a metacognition scale and adaptive behavior in the regret situations: A comparison between junior high-school and university students. / Understanding confidence in human papillomavirus vaccine in Japan: A web-based questionnaire survey of mothers, female adolescents, and health care professionals. / 裁判員参加意向を規定する要因および意思決定プロセスの差異：制度施行前後の比較 / 市民の生態系サービスへの認知が保全行動意図に及ぼす影響：全国アンケートを用いた社会心理学的分析 / どのようにリスクを伝えればよいか：よりよいリスクコミュニケーションのために必要なこと / 意思決定から見たギャンブル行動 / Change of decision-making processes in repeated risk-taking behavior in a complex dynamic situation / The neural networks model of decision-making including feedback processes / Research on the gaps between students' expectation and satisfaction for universities / Analogical decision making in career choice</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>中学生の達成目標志向が学業成績に影響を及ぼすプロセスの検討：社会的比較感情・行動を媒介にして / ブランドのSNS活動における製品カテゴリが消費者のSNS使用に与える影響 / 中国人大学生におけるダイエット行動に関連する心理・社会的要因についての検討ー身体不満足感とやせ願望に着目してー / ユーザー生成コンテンツがアプリの粘着性と消費者の購買意図に与える影響に関する研究 / 在日中国人留学生の異文化適応に関する研究 / 個人差要因およびマンガ作品内の表現がマンガ読書行動に与える影響 / 福祉・介護サービス従事者のコミュニティ感覚とメンタルヘルスの関連性について / 新しいメディア環境におけるライブコマースが消費者心理と行動に影響を及ぼす要因の検討 / 中国人大学生のとりあえず進学に関する研究―個人差要因と学校適応感に着目して / 看護師支援における共感疲労に影響を及ぼす要因 / 読書状況が変えるネタバレ選好 / グリーン購入における他者の影響 / An Investigation of the Factors Influencing college student Volunteering motivation - In Perspectives on prosocial behaviour</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 意思決定分析 ; 都市・地域政策 ; 社会政策・福祉 ; オペレーションズリサーチ ; 政策評価・計量分析 ; 公共政策・社会工学 ; AI・データサイエンス ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
+          <t>社会心理学 ; 実験心理学 ; 労働経済・就職マッチング ; 意思決定分析 ; 都市・地域政策 ; 政策評価・計量分析 ; テキスト分析・NLP ; 医療・ヘルスデータ ; 公共政策・社会工学 ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 社会ネットワーク分析 ; マーケティング分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>社会心理学
+実験心理学
+意思決定
+認知心理学
+感情
+労働経済・就職マッチング
 意思決定分析
 都市・地域政策
-社会政策・福祉
-オペレーションズリサーチ
 政策評価・計量分析
+テキスト分析・NLP
+医療・ヘルスデータ
 公共政策・社会工学
 AI・データサイエンス
-環境・エネルギー
 労働経済
 人的資本
 就職マッチング
@@ -9551,22 +10865,38 @@
 地域政策
 土地利用
 公共政策評価
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
-数理最適化
-組合せ最適化
-計画・スケジューリング
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>中学生の達成目標志向が学業成績に影響を及ぼすプロセスの検討：社会的比較感情・行動を媒介にして / ブランドのSNS活動における製品カテゴリが消費者のSNS使用に与える影響 / 中国人大学生におけるダイエット行動に関連する心理・社会的要因についての検討ー身体不満足感とやせ願望に着目してー / ユーザー生成コンテンツがアプリの粘着性と消費者の購買意図に与える影響に関する研究 / 在日中国人留学生の異文化適応に関する研究 / 個人差要因およびマンガ作品内の表現がマンガ読書行動に与える影響 / 福祉・介護サービス従事者のコミュニティ感覚とメンタルヘルスの関連性について / 新しいメディア環境におけるライブコマースが消費者心理と行動に影響を及ぼす要因の検討 / 中国人大学生のとりあえず進学に関する研究―個人差要因と学校適応感に着目して / 看護師支援における共感疲労に影響を及ぼす要因 / 読書状況が変えるネタバレ選好 / グリーン購入における他者の影響 / An Investigation of the Factors Influencing college student Volunteering motivation - In Perspectives on prosocial behaviour
+実証分析
+テキストマイニング
+自然言語処理
+感情分析
+社会データ分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+社会ネットワーク分析
+マーケティング分析
+学習分析</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>中学生の達成目標志向が学業成績に影響を及ぼすプロセスの検討：社会的比較感情・行動を媒介にして
+ブランドのSNS活動における製品カテゴリが消費者のSNS使用に与える影響
+中国人大学生におけるダイエット行動に関連する心理・社会的要因についての検討ー身体不満足感とやせ願望に着目してー
+ユーザー生成コンテンツがアプリの粘着性と消費者の購買意図に与える影響に関する研究
+在日中国人留学生の異文化適応に関する研究
+個人差要因およびマンガ作品内の表現がマンガ読書行動に与える影響
+福祉・介護サービス従事者のコミュニティ感覚とメンタルヘルスの関連性について
+新しいメディア環境におけるライブコマースが消費者心理と行動に影響を及ぼす要因の検討
+中国人大学生のとりあえず進学に関する研究―個人差要因と学校適応感に着目して
+看護師支援における共感疲労に影響を及ぼす要因
+読書状況が変えるネタバレ選好
+グリーン購入における他者の影響
+An Investigation of the Factors Influencing college student Volunteering motivation - In Perspectives on prosocial behaviour
 過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として―
 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討
 リアルタイム場面におけるサービス・インタラクション理論の構築と実証
@@ -9641,6 +10971,17 @@
 道路パフォーマンス指標の開発
 コンテナ港湾機能配分に関する研究
 観光交通の需要分析
+土木計画学・交通工学
+観光学
+交通
+観光
+社会資本
+プロジェクト評価
+港湾
+物流
+オーバーツーリズム
+都市計画
+費用便益分析
 人口分布とネットワークを考慮したコミュニティバス運営負担に関する実証分析 ～茨城県の自治体を対象として～
 Analysis of Changes in Demand before and after the Restructuring of “Tsukubus”
 Simulation Analysis of Tsunami Evacuation Behavior for Residents and Seabathers Under Mixed Pedestrian-Automobile
@@ -9674,72 +11015,83 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>人口分布とネットワークを考慮したコミュニティバス運営負担に関する実証分析 ～茨城県の自治体を対象として～ / Analysis of Changes in Demand before and after the Restructuring of “Tsukubus” / Simulation Analysis of Tsunami Evacuation Behavior for Residents and Seabathers Under Mixed Pedestrian-Automobile / A Study of Recovery from Shocks Lead by Crisis in the Field of Tourism / Examination of A Risk Management Through Technical Transitions in The Railway ATS System / バス利用に影響を与える要因の検討－利用者意識調査とマクロ分析に基づいて－ / Consciousness Analysis on Travel Behavior and Intention of People in Mainland China / 道路ネットワーク上の交通荷重情報収集を目的とした車重計の配置方法 / つくば市における宅配便の利用実態と再配達依頼の規定因―配達人とのコミュニケーションに着目してー / 渡航回数に着目した中国人の旅行意向形成に関する研究 / 観光流行現象の変遷に関する基礎的考察 / 茨城県内の市町村における橋梁維持管理の実態に関する研究 / 英国を事例とした我が国の空港運営政策に関する一考察 / GPSログデータを用いた訪日外国人旅行者の訪問パターンの分析手法の開発 / 東京近郊観光地におけるインバウンド観光プロモーション施策の考察 / 人口分布統計データを活用した観光地の特性把握 / 高齢者の交通環境改善に向けた新たな交通手段の利用可能性に関する研究 / ガソリンスタンドの経営収支と需要を考慮した存続可能性に関する研究 / ガソリンスタンドの経営収支と需要を考慮した存続可能性に関する研究 / 効果的な鉄道の安全対策が新たな課題を惹起する―「安全の 4M」と「リスク」の体系化による考察とマネジメントの重要性― / 地域鉄道の維持に関する考察-時 系列データによる検討- / 都市高速道路における交通状態推定問題およびセンサー配置問題に対するデータ同化アプローチ / 橋梁および高速道路上の横断構造物に対する維持管理の実態と課題 / 国内旅行におけるリピーターの行動特性及び醸成要因に関する研究 / 観光地における地域ブランド構築の内部関係者による資源活用パターンと課題構造に関する研究 - 関東・甲信越地域の市町村を対象として -</t>
+          <t>土木計画学・交通工学 / 観光学</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>交通 / 観光 / 社会資本 / プロジェクト評価 / 港湾 / 物流 / オーバーツーリズム / 都市計画 / 費用便益分析</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>人口分布とネットワークを考慮したコミュニティバス運営負担に関する実証分析 ～茨城県の自治体を対象として～ / Analysis of Changes in Demand before and after the Restructuring of “Tsukubus” / Simulation Analysis of Tsunami Evacuation Behavior for Residents and Seabathers Under Mixed Pedestrian-Automobile / A Study of Recovery from Shocks Lead by Crisis in the Field of Tourism / Examination of A Risk Management Through Technical Transitions in The Railway ATS System / バス利用に影響を与える要因の検討－利用者意識調査とマクロ分析に基づいて－ / Consciousness Analysis on Travel Behavior and Intention of People in Mainland China / 道路ネットワーク上の交通荷重情報収集を目的とした車重計の配置方法 / つくば市における宅配便の利用実態と再配達依頼の規定因―配達人とのコミュニケーションに着目してー / 渡航回数に着目した中国人の旅行意向形成に関する研究 / 観光流行現象の変遷に関する基礎的考察 / 茨城県内の市町村における橋梁維持管理の実態に関する研究 / 英国を事例とした我が国の空港運営政策に関する一考察 / GPSログデータを用いた訪日外国人旅行者の訪問パターンの分析手法の開発 / 東京近郊観光地におけるインバウンド観光プロモーション施策の考察 / 人口分布統計データを活用した観光地の特性把握 / 高齢者の交通環境改善に向けた新たな交通手段の利用可能性に関する研究 / ガソリンスタンドの経営収支と需要を考慮した存続可能性に関する研究 / 効果的な鉄道の安全対策が新たな課題を惹起する―「安全の 4M」と「リスク」の体系化による考察とマネジメントの重要性― / 地域鉄道の維持に関する考察-時 系列データによる検討- / 都市高速道路における交通状態推定問題およびセンサー配置問題に対するデータ同化アプローチ / 橋梁および高速道路上の横断構造物に対する維持管理の実態と課題 / 国内旅行におけるリピーターの行動特性及び醸成要因に関する研究 / 観光地における地域ブランド構築の内部関係者による資源活用パターンと課題構造に関する研究 - 関東・甲信越地域の市町村を対象として -</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>鉄道の運行支障時における駅周辺道路の交通実態に関する研究 / 自動車の走行距離課税制度に対する社会的受容性に関する研究 / 公共交通のネットワーク形態が自治体の負担に与える影響に関する研究 / 高速交通ネットワークの発展に伴う基幹交通の組合せ利用に関する研究 / つくば市における公共交通に対する住民満足度の要因分析 / 地方誘導型インバウンド政策がもたらす経済的影響に関する研究 / 国内旅行実態の経年的変化に関する基礎的研究 / 津波避難シミュレーションを用いた海水浴場の危険性評価 / 地域公共交通に関する利用者意識調査の活用方法の検討 / Difference of tourists‘ behavior by transportation mode in Kamakura City / TX開通による沿線エリアの交通需要とアクセシビリティ変化に関する研究</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 交通・モビリティ ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>家族・人口政策
-都市・地域政策
-GIS・空間分析
-社会政策・福祉
+          <t>土木計画学・交通工学 ; 観光学 ; 交通・モビリティ ; 政策評価・計量分析 ; 観光・マーケティング ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 観光情報学 ; 社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>土木計画学・交通工学
+観光学
+交通
+観光
+社会資本
+プロジェクト評価
+港湾
+物流
+オーバーツーリズム
+都市計画
+費用便益分析
 交通・モビリティ
-ネットワーク・グラフ理論
 政策評価・計量分析
+観光・マーケティング
 公共政策・社会工学
-経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
-都市経済
-地域政策
-土地利用
-公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
 交通工学
 モビリティ設計
 交通需要分析
 ネットワーク設計
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>鉄道の運行支障時における駅周辺道路の交通実態に関する研究 / 自動車の走行距離課税制度に対する社会的受容性に関する研究 / 公共交通のネットワーク形態が自治体の負担に与える影響に関する研究 / 高速交通ネットワークの発展に伴う基幹交通の組合せ利用に関する研究 / つくば市における公共交通に対する住民満足度の要因分析 / 地方誘導型インバウンド政策がもたらす経済的影響に関する研究 / 国内旅行実態の経年的変化に関する基礎的研究 / 津波避難シミュレーションを用いた海水浴場の危険性評価 / 地域公共交通に関する利用者意識調査の活用方法の検討 / Difference of tourists‘ behavior by transportation mode in Kamakura City / TX開通による沿線エリアの交通需要とアクセシビリティ変化に関する研究
+実証分析
+観光データ分析
+マーケティング分析
+クラスタリング
+需要予測
+観光情報学
+社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>鉄道の運行支障時における駅周辺道路の交通実態に関する研究
+自動車の走行距離課税制度に対する社会的受容性に関する研究
+公共交通のネットワーク形態が自治体の負担に与える影響に関する研究
+高速交通ネットワークの発展に伴う基幹交通の組合せ利用に関する研究
+つくば市における公共交通に対する住民満足度の要因分析
+地方誘導型インバウンド政策がもたらす経済的影響に関する研究
+国内旅行実態の経年的変化に関する基礎的研究
+津波避難シミュレーションを用いた海水浴場の危険性評価
+地域公共交通に関する利用者意識調査の活用方法の検討
+Difference of tourists‘ behavior by transportation mode in Kamakura City
+TX開通による沿線エリアの交通需要とアクセシビリティ変化に関する研究
 持続可能な観光のための戦略的オーバーツーリズム対処療法の構築
 持続可能な観光地形成に向けた複雑系モデルとそれを用いた合意形成ツールの開発
 意識分析にもとづく国外旅行意向の国際比較研究
@@ -9811,6 +11163,8 @@
 量から質へのシフトを実現するための緑地の計画制度・設計手法・運用方法の研究
 樹冠表面温度を利用した都市気温分布図の作成と緑地の気候緩和機能の分析
 リモートセンシングを活用した生物季節学図の作成と都市微気候の評価
+都市農村計画
+緑地計画
 グリーンインフラ整備を支える緑化技術研究
 熱的快適性が屋外空間における滞在状態に与える影響に関する研究
 グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例
@@ -9843,42 +11197,48 @@
           <t>津波で失われた景観の再現による記憶の抽出と日常生活に結びついた場の解析 / 低環境負荷型住まい方の実践とソーシャル・キャピタル向上の相乗効果を誘発する都市デザイン－インドネシア・ジャカルタの中層住宅における建築空間・住民行動・コミュニティの関係分析 / 津波で失われた景観のデジタル再現と記憶の分析によるコミュニティが共有する場の解析 / 量から質へのシフトを実現するための緑地の計画制度・設計手法・運用方法の研究 / 樹冠表面温度を利用した都市気温分布図の作成と緑地の気候緩和機能の分析 / リモートセンシングを活用した生物季節学図の作成と都市微気候の評価</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>都市農村計画 / 緑地計画</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>グリーンインフラ整備を支える緑化技術研究 / 熱的快適性が屋外空間における滞在状態に与える影響に関する研究 / グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例 / 2023年度一般公開シンポジウム開催報告 / 座談会 「緑の基本計画」のこれからを考える座談会 : 制度創設30年目を迎えて / 量から質への転換 / 人と土地の関係を創造するよろこび / 「働くクルマと社会」特集にあたって / GPSデータを用いたスポーツイベント来場者の行動分析 / 企業のIR情報に見る都市緑地に関する第三者認証制度の取り扱いに関する研究 / 熱赤外域リモートセンシングデータを活用した市街地の土地被覆に関する研究 / 熱的快適性が屋外空間における滞在に与える影響に関する研究 / 可視化された温熱環境情報が屋外空間の利用に与える影響に関する研究 / An Empirical Study on Using Green Spaces Around an Office as Workplace in Summer: Considerations Based on Office Employees’ Trait Anxiety Tendencies / グリーンインフラと緑の基本計画 / これからの自律的な民間緑地整備に関する考察 / ノルウェーにおける地表面での雨水管理策に関する法改正における議論の特徴 / ランドスケープ分野におけるDX / グリーンインフラとしての平地林による防災機能 －災害現場で確認された農業気象災害軽減事例－ / 移動の体験と景観 / 企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ / 屋外空間利用がオフィスワーカーに与える心理・生理的影響とその要因に関する研究 / 人流ビッグデータを用いた「Natural Cities」と温熱環境の関係分析についての研究 / 季節の違いが緑化に対する支払意思額に与える影響 / 地域・土地との関係性の希薄化</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>温熱環境がランナーの深部体温に及ぼす影響の把握と都市緑道の暑熱対策の検討 / 屋外温熱環境の違いが来訪者の空間利用に与える影響に関する研究 / 地域の持続可能性に資する非住宅木造建築の実現における関係主体の役割と課題 〜大崎市鳴子こども園を事例として〜 / 温熱環境情報の提示が空間利用に与える影響に関する研究 / 総合設計制度により創出された公開空地の緑化の実態に関する研究 / 北京市におけるヒートアイランド現象の時空間特性の分析 / オフィス街における来街者の滞留行動の季節変化に関する研究ー丸の内仲通りを対象としてー / 屋外空間利用がオフィスワーカーに与える心理的・生理的影響とその要因に関する研究 / 都市住民と農家の都市農地保全に対する意識の乖離とその要因に関する研究 / GPSログデータを用いたCOVID-19流行下の都市公園利用と公園利用前後の行動パターンに関する研究 / 日常の生活行動と温熱環境が深部体温に与える影響に関する基礎的研究 / 歩行時の空間認識と歩行の快適性の関係に関する研究</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; スポーツデータ分析 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>都市・地域政策
+          <t>都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 災害分析 ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>都市農村計画
+緑地計画
+都市・地域政策
 GIS・空間分析
 社会政策・福祉
 建築・空間設計
 画像・視覚情報処理
-スポーツデータ分析
 災害・防災研究
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
-経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
 都市経済
 地域政策
 土地利用
@@ -9899,21 +11259,37 @@
 画像認識
 行動認識
 マルチモーダル解析
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
 災害社会学
 防災政策
 リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>温熱環境がランナーの深部体温に及ぼす影響の把握と都市緑道の暑熱対策の検討 / 屋外温熱環境の違いが来訪者の空間利用に与える影響に関する研究 / 地域の持続可能性に資する非住宅木造建築の実現における関係主体の役割と課題 〜大崎市鳴子こども園を事例として〜 / 温熱環境情報の提示が空間利用に与える影響に関する研究 / 総合設計制度により創出された公開空地の緑化の実態に関する研究 / 北京市におけるヒートアイランド現象の時空間特性の分析 / オフィス街における来街者の滞留行動の季節変化に関する研究ー丸の内仲通りを対象としてー / 屋外空間利用がオフィスワーカーに与える心理的・生理的影響とその要因に関する研究 / 都市住民と農家の都市農地保全に対する意識の乖離とその要因に関する研究 / GPSログデータを用いたCOVID-19流行下の都市公園利用と公園利用前後の行動パターンに関する研究 / 日常の生活行動と温熱環境が深部体温に与える影響に関する基礎的研究 / 歩行時の空間認識と歩行の快適性の関係に関する研究
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+災害分析
+社会ネットワーク分析
+行政データ分析
+学習分析</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>温熱環境がランナーの深部体温に及ぼす影響の把握と都市緑道の暑熱対策の検討
+屋外温熱環境の違いが来訪者の空間利用に与える影響に関する研究
+地域の持続可能性に資する非住宅木造建築の実現における関係主体の役割と課題 〜大崎市鳴子こども園を事例として〜
+温熱環境情報の提示が空間利用に与える影響に関する研究
+総合設計制度により創出された公開空地の緑化の実態に関する研究
+北京市におけるヒートアイランド現象の時空間特性の分析
+オフィス街における来街者の滞留行動の季節変化に関する研究ー丸の内仲通りを対象としてー
+屋外空間利用がオフィスワーカーに与える心理的・生理的影響とその要因に関する研究
+都市住民と農家の都市農地保全に対する意識の乖離とその要因に関する研究
+GPSログデータを用いたCOVID-19流行下の都市公園利用と公園利用前後の行動パターンに関する研究
+日常の生活行動と温熱環境が深部体温に与える影響に関する基礎的研究
+歩行時の空間認識と歩行の快適性の関係に関する研究
 津波で失われた景観の再現による記憶の抽出と日常生活に結びついた場の解析
 低環境負荷型住まい方の実践とソーシャル・キャピタル向上の相乗効果を誘発する都市デザイン－インドネシア・ジャカルタの中層住宅における建築空間・住民行動・コミュニティの関係分析
 津波で失われた景観のデジタル再現と記憶の分析によるコミュニティが共有する場の解析
@@ -9986,6 +11362,9 @@
 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化
 顧客の再試行と途中放棄を考慮したコールセンターのモデル化と性能解析
 再試行型待ち行列によるコールセンターの性能解析とサービス科学への応用
+数理情報学
+社会システム工学・安全システム
+応用確率論、 確率モデル、 待ち行列理論、 性能評価、 オペレーションズ・リサーチ、確率システム
 Performance Analysis of Energy-efficient Reliable AIoT System Architectures
 Queueing Model with Alternating Service for Zipper Merging
 A simulation study of the sojourn time in queueing systems with stochastically delayed information
@@ -10019,39 +11398,45 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Performance Analysis of Energy-efficient Reliable AIoT System Architectures / Queueing Model with Alternating Service for Zipper Merging / A simulation study of the sojourn time in queueing systems with stochastically delayed information / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers / Performance Analysis of Blockchain with Rollups / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times / Analysis of a Batch Arrival Queue with Power Saving Mode / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory / Analytical Modelling of Asymmetric Multi-core Servers / Energy-performance tradeoffs in server farms with batch services and setup times / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers / Queueing Analysis of an Ensemble Machine Learning System / Performance analysis of a collision channel with abandonments / Empirical architecture comparison of two-input machine learning systems for vision tasks / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes / Modeling and performance analysis of hybrid systems by queues with setup time / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing / To wait or not to wait: Strategic behaviors in an observable batch-service queueing system / A Two-Population Game in Observable Double-Ended Queueing Systems / Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems / Analysis of a Batch Arrival Queue with Power Saving Mode</t>
+          <t>数理情報学 / 社会システム工学・安全システム</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>応用確率論、 確率モデル、 待ち行列理論、 性能評価、 オペレーションズ・リサーチ、確率システム</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Performance Analysis of Energy-efficient Reliable AIoT System Architectures / Queueing Model with Alternating Service for Zipper Merging / A simulation study of the sojourn time in queueing systems with stochastically delayed information / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers / Performance Analysis of Blockchain with Rollups / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times / Analysis of a Batch Arrival Queue with Power Saving Mode / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory / Analytical Modelling of Asymmetric Multi-core Servers / Energy-performance tradeoffs in server farms with batch services and setup times / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers / Queueing Analysis of an Ensemble Machine Learning System / Performance analysis of a collision channel with abandonments / Empirical architecture comparison of two-input machine learning systems for vision tasks / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes / Modeling and performance analysis of hybrid systems by queues with setup time / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing / To wait or not to wait: Strategic behaviors in an observable batch-service queueing system / A Two-Population Game in Observable Double-Ended Queueing Systems / Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>集団サービス型無限サーバ待ち行列の解析 / 客とサーバの性質が異なるシステムにおける待ち現象の解析 / Modelling social media load through a birth-death-batch-immigration process / マルコフ連鎖を用いたレンタカーとオンデマンド交通の融合システムの性能評価 / 混雑度に依存するサービス速度変化を考慮した待ち行列モデルの分析と交通流への応用 / Sojourn time analysis for m/m/c/setup queues / 異なる省電力モードを導入した集団到着型複数サーバモデルの解析 / Retrial queues with two-way communication for cognitive networks</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>マッチング理論・ゲーム理論 ; オペレーションズリサーチ ; 交通・モビリティ ; 画像・視覚情報処理 ; サービス・待ち行列 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 待ち行列理論 ; サービス工学 ; システム性能評価</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>マッチング理論・ゲーム理論
+          <t>数理情報学 ; 社会システム工学・安全システム ; オペレーションズリサーチ ; 交通・モビリティ ; サービス・待ち行列 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 待ち行列理論 ; サービス工学 ; システム性能評価 ; 学習分析 ; 物流最適化</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>数理情報学
+社会システム工学・安全システム
+応用確率論、 確率モデル、 待ち行列理論、 性能評価、 オペレーションズ・リサーチ、確率システム
 オペレーションズリサーチ
 交通・モビリティ
-画像・視覚情報処理
 サービス・待ち行列
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
-都市・空間・交通
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
 数理最適化
 組合せ最適化
 計画・スケジューリング
@@ -10059,18 +11444,23 @@
 モビリティ設計
 交通需要分析
 ネットワーク設計
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
 待ち行列理論
 サービス工学
-システム性能評価</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>集団サービス型無限サーバ待ち行列の解析 / 客とサーバの性質が異なるシステムにおける待ち現象の解析 / Modelling social media load through a birth-death-batch-immigration process / マルコフ連鎖を用いたレンタカーとオンデマンド交通の融合システムの性能評価 / 混雑度に依存するサービス速度変化を考慮した待ち行列モデルの分析と交通流への応用 / Sojourn time analysis for m/m/c/setup queues / 異なる省電力モードを導入した集団到着型複数サーバモデルの解析 / Retrial queues with two-way communication for cognitive networks
+システム性能評価
+学習分析
+物流最適化</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>集団サービス型無限サーバ待ち行列の解析
+客とサーバの性質が異なるシステムにおける待ち現象の解析
+Modelling social media load through a birth-death-batch-immigration process
+マルコフ連鎖を用いたレンタカーとオンデマンド交通の融合システムの性能評価
+混雑度に依存するサービス速度変化を考慮した待ち行列モデルの分析と交通流への応用
+Sojourn time analysis for m/m/c/setup queues
+異なる省電力モードを導入した集団到着型複数サーバモデルの解析
+Retrial queues with two-way communication for cognitive networks
 AI時代の省エネ型データセンター性能の数理的解明
 省電力データセンターの協調機構の性能評価
 省電力サーバ群の性能評価と負荷分散に関する数理モデル
@@ -10145,6 +11535,12 @@
 イギリスの都市計画プランナーの職能団体による実務研修等を支えるシステムに関する研究
 オープンデータを踏まえた市民セクター主体のICT協働まちづくりに関する研究
 豪雨災害から避難弱者を守る共助的な避難行動計画づくりシステムに関する学際的研究
+都市計画・建築計画
+経済政策
+Industrial Location
+産業集積
+都市・地域政策
+都市計画制度
 土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで
 新しい時代の都市再生と公共貢献のあり方
 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題
@@ -10173,48 +11569,55 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>「協働型都市開発と公共貢献手法に係る今後の展開可能性に関する研究」に対する研究助成 / 「今後の都市再生におけるインセンティヴ制度のあり方に関連する研究」に対する研究助成 / 自治体保有資産の有効活用を目的とした公民共創プロセスに関する研究 / 公的不動産の有効活用実現のための公民連携促進策とアセットマネジメント戦略のあり方 / 公的不動産の有効活用実現のための公民連携促進策とアセットマネジメント戦略のあり方 / 中古住宅市場における空き家・空き地の流通促進のための公民連携体制のあり方に関する研究 / 既成市街地における不動産流通促進を通じた地域再生に資する土地利用制度に関する研究 / イギリスの都市計画プランナーの職能団体による実務研修等を支えるシステムに関する研究 / オープンデータを踏まえた市民セクター主体のICT協働まちづくりに関する研究 / 豪雨災害から避難弱者を守る共助的な避難行動計画づくりシステムに関する学際的研究</t>
+          <t>「協働型都市開発と公共貢献手法に係る今後の展開可能性に関する研究」に対する研究助成 / 「今後の都市再生におけるインセンティヴ制度のあり方に関連する研究」に対する研究助成 / 自治体保有資産の有効活用を目的とした公民共創プロセスに関する研究 / 公的不動産の有効活用実現のための公民連携促進策とアセットマネジメント戦略のあり方 / 中古住宅市場における空き家・空き地の流通促進のための公民連携体制のあり方に関する研究 / 既成市街地における不動産流通促進を通じた地域再生に資する土地利用制度に関する研究 / イギリスの都市計画プランナーの職能団体による実務研修等を支えるシステムに関する研究 / オープンデータを踏まえた市民セクター主体のICT協働まちづくりに関する研究 / 豪雨災害から避難弱者を守る共助的な避難行動計画づくりシステムに関する学際的研究</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで / 新しい時代の都市再生と公共貢献のあり方 / 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 / 都市再開発のこれからの「必要性」と「可能性」 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 / 農村集落における区域区分制度を前提とした土地利用調整手法の実態と活用可能性に関する研究 / 土地建物一体型市街地整備の「必要性」と「可能性」 : これまでとこれから / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に / つくば市による心肺停止傷病者発生位置情報の最寄AED管理者との共有が生み出す協働による救命効果に関する研究 / 地方自治体におけるオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 / 東京都区部における開発実態の評価を踏まえた開発拠点誘導政策の課題に関する研究 / 公民連携による空き家・空き地対策組織の展開と運営実態 / 避難行動要支援者名簿活用に向けた制度設計・運用プロセスにおける課題に関する研究 / オープンデータ施策に総合的に取り組む地方自治体の動因に関する研究 / 地方都市中心市街地における商店街の連続性を踏まえた空間整備の変遷と課題に関する研究 / 地方自治体のオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 / 世界からみた銀座のルールとガバナンス (特集 銀座と都市計画) -- (都市計画と銀座のルール) / 11027 地区スケールの賑わい空間構造の定量分析に関する研究 歩行空間と周辺土地利用に着目して / “Planning transparency and public involvement in pre-application discussions,” / 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 / 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) / 集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ / マイナンバー導入に伴う自治体業務情報システム改修事例に見るオープン化・標準化及び共同化の現状に関する研究 / マイナンバー導入事例に見る政府情報システム調達の現状に関する研究</t>
+          <t>都市計画・建築計画 / 経済政策</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>Industrial Location / 産業集積 / 都市・地域政策 / 都市計画制度</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで / 新しい時代の都市再生と公共貢献のあり方 / 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 / 都市再開発のこれからの「必要性」と「可能性」 / 農村集落における区域区分制度を前提とした土地利用調整手法の実態と活用可能性に関する研究 / 土地建物一体型市街地整備の「必要性」と「可能性」 : これまでとこれから / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に / つくば市による心肺停止傷病者発生位置情報の最寄AED管理者との共有が生み出す協働による救命効果に関する研究 / 地方自治体におけるオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 / 東京都区部における開発実態の評価を踏まえた開発拠点誘導政策の課題に関する研究 / 公民連携による空き家・空き地対策組織の展開と運営実態 / 避難行動要支援者名簿活用に向けた制度設計・運用プロセスにおける課題に関する研究 / オープンデータ施策に総合的に取り組む地方自治体の動因に関する研究 / 地方都市中心市街地における商店街の連続性を踏まえた空間整備の変遷と課題に関する研究 / 地方自治体のオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 / 世界からみた銀座のルールとガバナンス (特集 銀座と都市計画) -- (都市計画と銀座のルール) / 11027 地区スケールの賑わい空間構造の定量分析に関する研究 歩行空間と周辺土地利用に着目して / “Planning transparency and public involvement in pre-application discussions,” / 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 / 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) / 集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ / マイナンバー導入に伴う自治体業務情報システム改修事例に見るオープン化・標準化及び共同化の現状に関する研究 / マイナンバー導入事例に見る政府情報システム調達の現状に関する研究</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>地方都市の法定再開発における持続的運営の課題に関する研究ー権利変換手法に着目してー / 改正個人情報保護法を受けた避難行動要支援者名簿情報の提供方策に関する研究 / 管理型まちづくりへの転換における公民連携の地域管理体制に関する研究-組織の成立プロセスに着目して- / 民間業務範囲を拡大させた PFI 事業における事業実現過程の課題に関する研究 / 人口減少社会における土地利用調整手法の実態と活用可能性に関する研究 －茨城県桜川市を事例として－ / 都市公園における官民連携事業の課題に関する研究 / 公的不動産の有効活用を促進する民間提案プラットフォームにおける課題に関する研究 / 実効性のある個別避難計画に向けた作成プロセスについて / 外国資本による国内不動産投資の増加が周辺地域に与える影響についての考察 / 公的不動産の利活用に向けた情報発信と官民の対話に関する研究 / 公的不動産の有効活用に関する研究 ―自治体に着目して― / 神社更新に伴う分譲マンション開発の実態と課題に関する研究ー東京都区部の神社を対象としてー</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; 保険・金融行動 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>家族・人口政策
+          <t>都市計画・建築計画 ; 経済政策 ; 保険・金融行動 ; 都市・地域政策 ; 建築・空間設計 ; 災害・防災研究 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 行政データ分析 ; 都市計画 ; 意思決定支援 ; 社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>都市計画・建築計画
+経済政策
+Industrial Location
+産業集積
+都市・地域政策
+都市計画制度
 保険・金融行動
-都市・地域政策
-GIS・空間分析
 建築・空間設計
 災害・防災研究
-政策評価・計量分析
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 行動ファイナンス
 金融市場分析
 ESG投資
@@ -10223,10 +11626,6 @@
 地域政策
 土地利用
 公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
 建築計画
 空間レイアウト生成
 居住空間設計
@@ -10234,15 +11633,26 @@
 災害社会学
 防災政策
 リスク評価
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>地方都市の法定再開発における持続的運営の課題に関する研究ー権利変換手法に着目してー / 改正個人情報保護法を受けた避難行動要支援者名簿情報の提供方策に関する研究 / 管理型まちづくりへの転換における公民連携の地域管理体制に関する研究-組織の成立プロセスに着目して- / 民間業務範囲を拡大させた PFI 事業における事業実現過程の課題に関する研究 / 人口減少社会における土地利用調整手法の実態と活用可能性に関する研究 －茨城県桜川市を事例として－ / 都市公園における官民連携事業の課題に関する研究 / 公的不動産の有効活用を促進する民間提案プラットフォームにおける課題に関する研究 / 実効性のある個別避難計画に向けた作成プロセスについて / 外国資本による国内不動産投資の増加が周辺地域に与える影響についての考察 / 公的不動産の利活用に向けた情報発信と官民の対話に関する研究 / 公的不動産の有効活用に関する研究 ―自治体に着目して― / 神社更新に伴う分譲マンション開発の実態と課題に関する研究ー東京都区部の神社を対象としてー
+行政データ分析
+都市計画
+意思決定支援
+社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>地方都市の法定再開発における持続的運営の課題に関する研究ー権利変換手法に着目してー
+改正個人情報保護法を受けた避難行動要支援者名簿情報の提供方策に関する研究
+管理型まちづくりへの転換における公民連携の地域管理体制に関する研究-組織の成立プロセスに着目して-
+民間業務範囲を拡大させた PFI 事業における事業実現過程の課題に関する研究
+人口減少社会における土地利用調整手法の実態と活用可能性に関する研究 －茨城県桜川市を事例として－
+都市公園における官民連携事業の課題に関する研究
+公的不動産の有効活用を促進する民間提案プラットフォームにおける課題に関する研究
+実効性のある個別避難計画に向けた作成プロセスについて
+外国資本による国内不動産投資の増加が周辺地域に与える影響についての考察
+公的不動産の利活用に向けた情報発信と官民の対話に関する研究
+公的不動産の有効活用に関する研究 ―自治体に着目して―
+神社更新に伴う分譲マンション開発の実態と課題に関する研究ー東京都区部の神社を対象としてー
 「協働型都市開発と公共貢献手法に係る今後の展開可能性に関する研究」に対する研究助成
 「今後の都市再生におけるインセンティヴ制度のあり方に関連する研究」に対する研究助成
 自治体保有資産の有効活用を目的とした公民共創プロセスに関する研究
@@ -10317,6 +11727,13 @@
 江戸武家地の空間変容に関する文理統合的研究
 北関東の町並みの建築的構成とその展開過程に関する研究
 常陸太田市鯨が丘歴史的建造物調査
+建築史・意匠
+都市計画・建築計画
+日本史
+建築史
+都市史
+保全型都市計画
+居住環境史
 近代中国青島市における「雑院一覧表 二十四年夏季」について
 五台山行宮座落地盤圖 からみた清代白雲寺行宮
 嵩山史跡群における建物の空間構成および登封県の建立の経緯
@@ -10351,48 +11768,49 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>建築史・意匠 / 都市計画・建築計画 / 日本史</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>建築史 / 都市史 / 保全型都市計画 / 居住環境史</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>近代中国青島市における「雑院一覧表 二十四年夏季」について / 五台山行宮座落地盤圖 からみた清代白雲寺行宮 / 嵩山史跡群における建物の空間構成および登封県の建立の経緯 / 近代の町並み景観の多様性：大火からの復興を通してみた近代の町並みに関する研究 その 1 / 戦後昭和期の横浜中華街における商住空間の分布と特徴：中区明細地図の考察から / 清代福州における住宅の類型とその特徴 古絵図 De Stud Hockzieuw en de stad Nanta を中心とした分析 / 明清時代漕運と大運河沿いの都市空間特性との関係 その 2： 済寧を例として / 「白川郷における駐車空間の分布と交通整備の経緯：重要伝統的建造物群保存地区における駐車空間に関する研究」 / 『大日本職業別明細図之内』の空間表現 千葉県北部の地図を対象に / 観光開発を目的とした窯業集落の保全の実態とその課題： 中国陝西省澄城県の伝統村落・堯頭村を事例に / 「清代蘇州の屋外空間における商人達の「自発的な居場所」 のパターン： 「姑蘇繁華図」の分析」 / 新刊紹介『リスボン』 / 明清時代における漕河沿い城・鎮の空間構成に関する研究（その1）：漕運システムと漕河沿岸空間の構成要素との関係 / 清代福州における住宅の三類型 / 大正期から戦前までの山下町における中国系事業所と公共施設の立地と特徴–Japan Directory、商工案内の分析から– / 清代福建省における「舗」の分布とその特性－連江県城を事例として－ / 清代五台山顕通寺の火災と修復工程 / 明清時代漕運と京杭大運河沿い都市の空間特性との関係－臨清を例として－ / 中国における団地構内の小規模野菜市場の空間利用－街商と住民の共存モデル－ / 新刊紹介『明暦の大火』 / 五台山塔院寺の建築の構成とその変容 / 「奈良県橿原市今井町における駐車場の出現パターン：重要伝統的建造物群保存地区の駐車空間に関する研究 その2」 / 「真壁のこれから：過去・現在・未来」 / 「商店街アーケードの空間の変容:十条銀座商店街を対象に」 / 「清代新疆の地域構造と都市群の立地 -軍政中心地イリを対象に- 」</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>東京都区部における銭湯の存続要因とその周辺環境に関する研究－江東区を事例として－ / 幕末の海防に伴う都市空間の変容-江戸沿岸部地域に着目して- / 旧軍用地が地域空間形成に与えた影響について―茨城県ひたちなか市を対象として― / 中国鉄鋼業の発達が都市空間に与えた影響ー近代の武漢を事例にー / 近代中国における鉄道交通基盤の導入と歴史的都市空間との関係—1888〜1958年の京津・津浦鉄道沿線都市を対象に— / 清代駅道の変遷と沿道集落・駅建築の特徴－山東省済南府地域を事例として / 華僑の投資・建設活動が新たな都市空間の形成に果たした役割ー清末〜民国期の広州市東山区を例としてー / 戦後における商店街の業態と空間の変容—高円寺、北千住、巣鴨を事例として— / 観光開発を目的とした窯業集落の保全・修景に関する研究—中国陝西省澄城県の伝統村落・堯頭村を事例に— / 近代中国における民間主導の計画的市街地「漢口模範区」の形成と変容 / 明清期陝西省における都市時報建築の立地と形態 / 近代の繊維都市の形成に模範撚糸工事が果たした役割 / 中国の近代化において交通システムの変容が在郷町の機能・空間に与えた影響 ～四川省資中県を事例として～ / 建設時期・地域による相違に着目した清代満城の都市形態に関する研究 / 農村地域における短路型集落の特徴と近代以降の変容ー茨城県の集落を対象にー / 中国天童寺の寺域及び構成施設の変遷：晋代の創建から近現代の保護まで / 明清時代の役人住宅における職階制度と建築様式の関係—陳氏の住宅を例に / 北京市歴史文化保護区におけるジェントリフィケーションの実態とメカニズム―南鑼鼓巷を事例に</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 保険・金融行動 ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 交通・モビリティ ; 建築・空間設計 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-保険・金融行動
+          <t>建築史・意匠 ; 都市計画・建築計画 ; 日本史 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 都市計画 ; 人間中心設計 ; 社会ネットワーク分析 ; 環境工学</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>建築史・意匠
+都市計画・建築計画
+日本史
+建築史
+都市史
+保全型都市計画
+居住環境史
 都市・地域政策
 GIS・空間分析
-社会政策・福祉
-交通・モビリティ
 建築・空間設計
-政策評価・計量分析
 公共政策・社会工学
-経済・ファイナンス
 数理最適化・OR
-AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
 都市経済
 地域政策
 土地利用
@@ -10401,27 +11819,36 @@
 空間計量
 地理情報分析
 立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
-交通工学
-モビリティ設計
-交通需要分析
-ネットワーク設計
 建築計画
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>東京都区部における銭湯の存続要因とその周辺環境に関する研究－江東区を事例として－ / 幕末の海防に伴う都市空間の変容-江戸沿岸部地域に着目して- / 旧軍用地が地域空間形成に与えた影響について―茨城県ひたちなか市を対象として― / 中国鉄鋼業の発達が都市空間に与えた影響ー近代の武漢を事例にー / 近代中国における鉄道交通基盤の導入と歴史的都市空間との関係—1888〜1958年の京津・津浦鉄道沿線都市を対象に— / 清代駅道の変遷と沿道集落・駅建築の特徴－山東省済南府地域を事例として / 華僑の投資・建設活動が新たな都市空間の形成に果たした役割ー清末〜民国期の広州市東山区を例としてー / 戦後における商店街の業態と空間の変容—高円寺、北千住、巣鴨を事例として— / 観光開発を目的とした窯業集落の保全・修景に関する研究—中国陝西省澄城県の伝統村落・堯頭村を事例に— / 近代中国における民間主導の計画的市街地「漢口模範区」の形成と変容 / 明清期陝西省における都市時報建築の立地と形態 / 近代の繊維都市の形成に模範撚糸工事が果たした役割 / 中国の近代化において交通システムの変容が在郷町の機能・空間に与えた影響 ～四川省資中県を事例として～ / 建設時期・地域による相違に着目した清代満城の都市形態に関する研究 / 農村地域における短路型集落の特徴と近代以降の変容ー茨城県の集落を対象にー / 中国天童寺の寺域及び構成施設の変遷：晋代の創建から近現代の保護まで / 明清時代の役人住宅における職階制度と建築様式の関係—陳氏の住宅を例に / 北京市歴史文化保護区におけるジェントリフィケーションの実態とメカニズム―南鑼鼓巷を事例に
+都市計画
+人間中心設計
+社会ネットワーク分析
+環境工学</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>東京都区部における銭湯の存続要因とその周辺環境に関する研究－江東区を事例として－
+幕末の海防に伴う都市空間の変容-江戸沿岸部地域に着目して-
+旧軍用地が地域空間形成に与えた影響について―茨城県ひたちなか市を対象として―
+中国鉄鋼業の発達が都市空間に与えた影響ー近代の武漢を事例にー
+近代中国における鉄道交通基盤の導入と歴史的都市空間との関係—1888〜1958年の京津・津浦鉄道沿線都市を対象に—
+清代駅道の変遷と沿道集落・駅建築の特徴－山東省済南府地域を事例として
+華僑の投資・建設活動が新たな都市空間の形成に果たした役割ー清末〜民国期の広州市東山区を例としてー
+戦後における商店街の業態と空間の変容—高円寺、北千住、巣鴨を事例として—
+観光開発を目的とした窯業集落の保全・修景に関する研究—中国陝西省澄城県の伝統村落・堯頭村を事例に—
+近代中国における民間主導の計画的市街地「漢口模範区」の形成と変容
+明清期陝西省における都市時報建築の立地と形態
+近代の繊維都市の形成に模範撚糸工事が果たした役割
+中国の近代化において交通システムの変容が在郷町の機能・空間に与えた影響 ～四川省資中県を事例として～
+建設時期・地域による相違に着目した清代満城の都市形態に関する研究
+農村地域における短路型集落の特徴と近代以降の変容ー茨城県の集落を対象にー
+中国天童寺の寺域及び構成施設の変遷：晋代の創建から近現代の保護まで
+明清時代の役人住宅における職階制度と建築様式の関係—陳氏の住宅を例に
+北京市歴史文化保護区におけるジェントリフィケーションの実態とメカニズム―南鑼鼓巷を事例に
 形態・材料に着目した近代町家の地域性とその形成要因
 モビリティーイノベーションの社会応用と未来社会工学研究5
 モビリティーイノベーションの社会応用と未来社会工学研究3
@@ -10495,6 +11922,10 @@
 ＱＣＤＲモデルに基づいて革新的な総合設備効率の向上と生産期間の短縮を実現する工場・設備の運用管理システム
 ＱＣＤモデルに基づくマルチチャンバ装置および生産ラインの運用・設計方法
 共創ビジョンに基づく半導体産業のビジネスモデル進化と、知財・人材の組織的流動化
+制御・システム工学
+生産システム工学
+オペレーション管理
+地域活性化
 "INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH
 Robust Classifications of WBM Defect Patterns
 Due dates assignment based on customer changeability classifications in Make-to-order productoins
@@ -10528,79 +11959,92 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>"INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH / Robust Classifications of WBM Defect Patterns / Due dates assignment based on customer changeability classifications in Make-to-order productoins / Pipeline production model and sensitivity analysis of Engineering-to-Order products using system dynamics / PRODUCTION AND JOB ROTATION PLANNING CONSIDERING DISABILITIES AND HEALTH CONDITIONS / Classification of Multivariate Time Series Signals Using Self-Supervised Representation Learning / Multi-factory Scheduling Considering the Trade-offs between Production Efficiency and Risks / Analysis of Resilience Factors and Satisfaction in Life-line Charts for Life Career Developments / Interaction Modeling for High-Dimensional Mixed Data with Numerical and Categorical Features / Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL / MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION / Mixed-type Defect Pattern Classifications / Interaction Modelling of High Dimensional Production Data / DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS / MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN / Data-driven Modeling for Production Dynamics / Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption / MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - / Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - / Interaction Modelings for Industrial Data - for final quality estimation and proess integration / スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 / 従属需要の予測手法の構築と検証 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 / Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling</t>
+          <t>制御・システム工学</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>生産システム工学 / オペレーション管理 / 地域活性化</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>"INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH / Robust Classifications of WBM Defect Patterns / Due dates assignment based on customer changeability classifications in Make-to-order productoins / Pipeline production model and sensitivity analysis of Engineering-to-Order products using system dynamics / PRODUCTION AND JOB ROTATION PLANNING CONSIDERING DISABILITIES AND HEALTH CONDITIONS / Classification of Multivariate Time Series Signals Using Self-Supervised Representation Learning / Multi-factory Scheduling Considering the Trade-offs between Production Efficiency and Risks / Analysis of Resilience Factors and Satisfaction in Life-line Charts for Life Career Developments / Interaction Modeling for High-Dimensional Mixed Data with Numerical and Categorical Features / Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL / MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION / Mixed-type Defect Pattern Classifications / Interaction Modelling of High Dimensional Production Data / DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS / MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN / Data-driven Modeling for Production Dynamics / Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption / MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - / Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - / Interaction Modelings for Industrial Data - for final quality estimation and proess integration / スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 / 従属需要の予測手法の構築と検証 / Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>多目的ハイブリッドフローショップスケジューリングの実証研究 / QR決済ヘビーユーザーの内外特徴の分析と活用 ～ キャンペーンと多種アプリ利用状況を考慮して / 保全時間を考慮した自律搬送ロボットのスケジューリング / n工程・多目的ハイブリッドフローショップスケジューリングの高速化～タブーリストと解構造の活用 / 生産リスクと段取りを考慮したMulti-factoryスケジューリング / 高次元交互作用モデリングにおける構造導入アプローチの効果検証 / 上流工場と処理単位の変化を考慮した投入制御ルールと多目的スケジューリングの融合 / 大規模データに対する変化検出と因果分析 / 多重共線性と因子効果ギャップを考慮した高次元交互作用モデリング / エネルギー消費量と納期遅れペナルティのトレードオフを考慮したセルフチューニングバッチ編成と多目的スケジューリング / 建設現場の多様性への対応する360度撮像と画像認識技術 / データ駆動プロセスインテグレーションのための高相関高次元データモデリング / ネットワーク理論に基づく高齢者福祉施設の最適化配置計画～茨城県通所型高齢者福祉施設の事例 / 相関関係を内包した多次元時系列データの予測モデリング / 高相関データの高因子効果比モデル推定 / 多品種繰り返し大規模生産システムのモデリングと最適スケジューリング～半導体Testbedを対象として / 自己教師あり学習を用いた多変量時系列信号の状態分類 / 料理アプリに着目したスマホ起動履歴の解析と情報推薦 / 高次元混合データの交互作用モデリング / 生産効率・人間工学リスク・エネルギーを考慮したジョブローテーションスケジューリング / 工場間搬送を考慮した並列分散型マルチファクトリー・スケジューリング / 営業コストを考慮したサプライチェーンにおける企業間多段階納期交渉 / エネルギー消費と待ち時間制約のトレードオフを考慮したサプライチェーン・スケジューリング / 画像マルチモーダル学習による半導体不良パターンの解析 / 時空間情報を用いた画像マルチモーダル学習による半導体不良パターンの高精度分類 / 資源・エネルギーロスを最小化する生産フロー制御つきマルチファクトリー・スケジューリング / 因果推論と機械学習による車載半導体需要予測 / 推薦システムによる多様なアプリの利用促進 / 高次元データの交互作用モデリング-Adaptive SFMとSafe Pruningによる高精度化 / 多様な建設現場の部材の検出と分類</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; オペレーションズリサーチ ; 建築・空間設計 ; 機械学習 ; 画像・視覚情報処理 ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>都市・地域政策
-GIS・空間分析
-社会政策・福祉
+          <t>制御・システム工学 ; 都市・地域政策 ; オペレーションズリサーチ ; 機械学習 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 物流最適化 ; 最適化</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>制御・システム工学
+生産システム工学
+オペレーション管理
+地域活性化
+都市・地域政策
 オペレーションズリサーチ
-建築・空間設計
 機械学習
-画像・視覚情報処理
-ネットワーク・グラフ理論
-政策評価・計量分析
 公共政策・社会工学
-経済・ファイナンス
 数理最適化・OR
 AI・データサイエンス
-環境・エネルギー
 都市経済
 地域政策
 土地利用
 公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
-社会福祉政策
-地域福祉
-子育て支援
-非営利組織論
 数理最適化
 組合せ最適化
 計画・スケジューリング
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
 統計的学習
 予測モデリング
 表現学習
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>多目的ハイブリッドフローショップスケジューリングの実証研究 / QR決済ヘビーユーザーの内外特徴の分析と活用 ～ キャンペーンと多種アプリ利用状況を考慮して / 保全時間を考慮した自律搬送ロボットのスケジューリング / n工程・多目的ハイブリッドフローショップスケジューリングの高速化～タブーリストと解構造の活用 / 生産リスクと段取りを考慮したMulti-factoryスケジューリング / 高次元交互作用モデリングにおける構造導入アプローチの効果検証 / 上流工場と処理単位の変化を考慮した投入制御ルールと多目的スケジューリングの融合 / 大規模データに対する変化検出と因果分析 / 多重共線性と因子効果ギャップを考慮した高次元交互作用モデリング / エネルギー消費量と納期遅れペナルティのトレードオフを考慮したセルフチューニングバッチ編成と多目的スケジューリング / 建設現場の多様性への対応する360度撮像と画像認識技術 / データ駆動プロセスインテグレーションのための高相関高次元データモデリング / ネットワーク理論に基づく高齢者福祉施設の最適化配置計画～茨城県通所型高齢者福祉施設の事例 / 相関関係を内包した多次元時系列データの予測モデリング / 高相関データの高因子効果比モデル推定 / 多品種繰り返し大規模生産システムのモデリングと最適スケジューリング～半導体Testbedを対象として / 自己教師あり学習を用いた多変量時系列信号の状態分類 / 料理アプリに着目したスマホ起動履歴の解析と情報推薦 / 高次元混合データの交互作用モデリング / 生産効率・人間工学リスク・エネルギーを考慮したジョブローテーションスケジューリング / 工場間搬送を考慮した並列分散型マルチファクトリー・スケジューリング / 営業コストを考慮したサプライチェーンにおける企業間多段階納期交渉 / エネルギー消費と待ち時間制約のトレードオフを考慮したサプライチェーン・スケジューリング / 画像マルチモーダル学習による半導体不良パターンの解析 / 時空間情報を用いた画像マルチモーダル学習による半導体不良パターンの高精度分類 / 資源・エネルギーロスを最小化する生産フロー制御つきマルチファクトリー・スケジューリング / 因果推論と機械学習による車載半導体需要予測 / 推薦システムによる多様なアプリの利用促進 / 高次元データの交互作用モデリング-Adaptive SFMとSafe Pruningによる高精度化 / 多様な建設現場の部材の検出と分類
+物流最適化
+最適化</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>多目的ハイブリッドフローショップスケジューリングの実証研究
+QR決済ヘビーユーザーの内外特徴の分析と活用 ～ キャンペーンと多種アプリ利用状況を考慮して
+保全時間を考慮した自律搬送ロボットのスケジューリング
+n工程・多目的ハイブリッドフローショップスケジューリングの高速化～タブーリストと解構造の活用
+生産リスクと段取りを考慮したMulti-factoryスケジューリング
+高次元交互作用モデリングにおける構造導入アプローチの効果検証
+上流工場と処理単位の変化を考慮した投入制御ルールと多目的スケジューリングの融合
+大規模データに対する変化検出と因果分析
+多重共線性と因子効果ギャップを考慮した高次元交互作用モデリング
+エネルギー消費量と納期遅れペナルティのトレードオフを考慮したセルフチューニングバッチ編成と多目的スケジューリング
+建設現場の多様性への対応する360度撮像と画像認識技術
+データ駆動プロセスインテグレーションのための高相関高次元データモデリング
+ネットワーク理論に基づく高齢者福祉施設の最適化配置計画～茨城県通所型高齢者福祉施設の事例
+相関関係を内包した多次元時系列データの予測モデリング
+高相関データの高因子効果比モデル推定
+多品種繰り返し大規模生産システムのモデリングと最適スケジューリング～半導体Testbedを対象として
+自己教師あり学習を用いた多変量時系列信号の状態分類
+料理アプリに着目したスマホ起動履歴の解析と情報推薦
+高次元混合データの交互作用モデリング
+生産効率・人間工学リスク・エネルギーを考慮したジョブローテーションスケジューリング
+工場間搬送を考慮した並列分散型マルチファクトリー・スケジューリング
+営業コストを考慮したサプライチェーンにおける企業間多段階納期交渉
+エネルギー消費と待ち時間制約のトレードオフを考慮したサプライチェーン・スケジューリング
+画像マルチモーダル学習による半導体不良パターンの解析
+時空間情報を用いた画像マルチモーダル学習による半導体不良パターンの高精度分類
+資源・エネルギーロスを最小化する生産フロー制御つきマルチファクトリー・スケジューリング
+因果推論と機械学習による車載半導体需要予測
+推薦システムによる多様なアプリの利用促進
+高次元データの交互作用モデリング-Adaptive SFMとSafe Pruningによる高精度化
+多様な建設現場の部材の検出と分類
 遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化
 ワークライフバランスに貢献するサイバー・フィジカル製造業
 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配
@@ -10673,6 +12117,16 @@
 公共サービスの革新に関する研究
 医療相談アプリ「LEBER」を用いた医療費削減効果のデータ解析に関する学術指導
 日本政府のオープンデータ政策評価
+社会システム工学・安全システム
+都市計画・建築計画
+ウェブ情報学・サービス情報学
+図書館情報学・人文社会情報学
+財政・公共経済
+持続可能システム
+経営学
+地域研究
+環境影響評価
+オープンデータ、公共データ分析、自治体経営、地域情報化政策、国際協力
 在宅医療におけるD to P with Nの臨床的役割：訪問診療との比較による診療内容および受療パターンのケーススタディ
 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に
 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究
@@ -10707,31 +12161,53 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
+          <t>社会システム工学・安全システム / 都市計画・建築計画 / ウェブ情報学・サービス情報学 / 図書館情報学・人文社会情報学 / 財政・公共経済 / 持続可能システム / 経営学 / 地域研究 / 環境影響評価</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>オープンデータ、公共データ分析、自治体経営、地域情報化政策、国際協力</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>在宅医療におけるD to P with Nの臨床的役割：訪問診療との比較による診療内容および受療パターンのケーススタディ / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 / 筑波大学理工学群におけるデータサイエンス応用基礎教育 / 水害時における市民の避難行動に関する意識の分析 / Asian Cities Connecting through Communities / 排水再利用設備に係る建築行政の現状と今後の動向 / 建設省--インテリジェントビルへの構図 / ペンシルバニア通り2121番地(第1便)「世界銀行」ってどんなところ? / 世界銀行の都市開発分野における日本の情報発信の方向性 / CIOの視点/INTERVIEW 人と人をつなげて進む川島流地域活性化のビジョン / 地方自治体における業務改革と情報システム構築の実際--佐賀県を事例として / 佐賀県 台帳記録管理システムによる業務改革 / 大きな社会システムのアーキテクチャ再構築を / 世界の潮流 : オープンデータ : エンドユーザーの視点に立ち便益が明確な事業の推進を / 事実証拠を根拠とした政策策定 : オープンデータ推進の効果 / オープンデータの最新動向と公共データ市場に関する考察 / 電子自治体と公共イノベーション / オープンデータの5W1H : 今、自治体は「オープンデータ」にどのように取り組むべきか / オープンデータからソーシャルイノベーションへ : 公共データ×ICT×市民力で社会課題を自ら解決する社会ヘ / 自治体がオープンデータに取り組む際の留意点 オープンデータの活用において自治体が成果を出すための5原則 / Society 5.0実現に向けて必要となる教育の方向性 / オープンガバナンス推進に求められる政府・自治体職員の能力 / VUCA時代の政策形成にデジタルをどう活かすか / 自治体会計情報のオープンデータ化の促進―国際基準COFOGによる費目分類に着目して―</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>地方自治体・企業におけるワーケーション関連の取り組み実態に関する研究 / 個別避難計画の作成促進方策に関する研究～常総市・つくばみらい市を対象として～ / 現代における茅葺き屋根保存に関する課題と適切な支援施策に関する研究 ―茨城県石岡市を事例として― / 避難支援関係主体の参画に着目した実効性のある個別避難計画作成プロセスに関する研究 ―令和２年７月豪雨による球磨川氾濫周辺地区を対象として― / ナッジメッセージを用いた地震に対する世帯備蓄促進に向けた社会実験 ―茨城県つくば市内の世帯を対象として― / 医療過疎地域におけるD to P with Nと訪問診療との代替・補完可能性に関する研究 ~ 長野県伊那市のモバイルクリニック運用を例に ~ / 認知症等行方不明者の発生記録を用いた捜索時間の短縮効果に関する研究 / 最寄AED急搬送システムの社会実装過程における不確実性を考慮したAED選定モデル / 地方の先進社会課題の解決に取り組んでいる若者起業家の成功要因に関する研究～修正エフェクチュエーション・モデルの検証～ / 高経年区分所有住宅の耐震性能を向上する建替え推進に向けた法制度設計上の課題に関する研究 ー台湾と日本の法制度の比較を通じてー</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>都市・地域政策
+          <t>社会システム工学・安全システム ; 都市計画・建築計画 ; ウェブ情報学・サービス情報学 ; 図書館情報学・人文社会情報学 ; 財政・公共経済 ; 持続可能システム ; 経営学 ; 地域研究 ; 環境影響評価 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 災害・防災研究 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 行政データ分析 ; 災害分析 ; 推薦システム ; 社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>社会システム工学・安全システム
+都市計画・建築計画
+ウェブ情報学・サービス情報学
+図書館情報学・人文社会情報学
+財政・公共経済
+持続可能システム
+経営学
+地域研究
+環境影響評価
+オープンデータ、公共データ分析、自治体経営、地域情報化政策、国際協力
+都市・地域政策
 GIS・空間分析
 建築・空間設計
 災害・防災研究
 政策評価・計量分析
+医療・ヘルスデータ
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
@@ -10755,12 +12231,33 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>地方自治体・企業におけるワーケーション関連の取り組み実態に関する研究 / 個別避難計画の作成促進方策に関する研究～常総市・つくばみらい市を対象として～ / 現代における茅葺き屋根保存に関する課題と適切な支援施策に関する研究 ―茨城県石岡市を事例として― / 避難支援関係主体の参画に着目した実効性のある個別避難計画作成プロセスに関する研究 ―令和２年７月豪雨による球磨川氾濫周辺地区を対象として― / ナッジメッセージを用いた地震に対する世帯備蓄促進に向けた社会実験 ―茨城県つくば市内の世帯を対象として― / 医療過疎地域におけるD to P with Nと訪問診療との代替・補完可能性に関する研究 ~ 長野県伊那市のモバイルクリニック運用を例に ~ / 認知症等行方不明者の発生記録を用いた捜索時間の短縮効果に関する研究 / 最寄AED急搬送システムの社会実装過程における不確実性を考慮したAED選定モデル / 地方の先進社会課題の解決に取り組んでいる若者起業家の成功要因に関する研究～修正エフェクチュエーション・モデルの検証～ / 高経年区分所有住宅の耐震性能を向上する建替え推進に向けた法制度設計上の課題に関する研究 ー台湾と日本の法制度の比較を通じてー
+実証分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+行政データ分析
+災害分析
+推薦システム
+社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>地方自治体・企業におけるワーケーション関連の取り組み実態に関する研究
+個別避難計画の作成促進方策に関する研究～常総市・つくばみらい市を対象として～
+現代における茅葺き屋根保存に関する課題と適切な支援施策に関する研究 ―茨城県石岡市を事例として―
+避難支援関係主体の参画に着目した実効性のある個別避難計画作成プロセスに関する研究 ―令和２年７月豪雨による球磨川氾濫周辺地区を対象として―
+ナッジメッセージを用いた地震に対する世帯備蓄促進に向けた社会実験 ―茨城県つくば市内の世帯を対象として―
+医療過疎地域におけるD to P with Nと訪問診療との代替・補完可能性に関する研究 ~ 長野県伊那市のモバイルクリニック運用を例に ~
+認知症等行方不明者の発生記録を用いた捜索時間の短縮効果に関する研究
+最寄AED急搬送システムの社会実装過程における不確実性を考慮したAED選定モデル
+地方の先進社会課題の解決に取り組んでいる若者起業家の成功要因に関する研究～修正エフェクチュエーション・モデルの検証～
+高経年区分所有住宅の耐震性能を向上する建替え推進に向けた法制度設計上の課題に関する研究 ー台湾と日本の法制度の比較を通じてー
 地方での生活空間データ連携
 Hack My Tsukuba 2018
 Hack My Tsukuba 2019
@@ -10833,6 +12330,17 @@
 地方自治体における道路維持管理業務のため
 空間計量経済学における最重要課題への挑戦と新たな展開
 道路台帳を活かした道路アセットマネジメントに関する研究
+土木計画学・交通工学
+道路維持管理
+空間計量経済学
+地理情報システム
+空間データ
+空間統計
+不動産
+不動産価格
+不動産賃料
+土地利用
+立地分析
 立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～
 東京23区における賃貸オフィスビルストックの地域性と経年変化
 The Impact of the Flight to Quality on Office Rents and Vacancy
@@ -10860,65 +12368,68 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>オルタナティブデータを用いたオフィス不動産市場分析の可能性 / オフィス賃貸マーケットに関する研究 / オフィス賃貸マーケットに関する研究 / オフィス賃貸マーケットに関する研究 / オフィス賃貸マーケットに関する研究 / 地方自治体における情報の利活用方策の導入 / 地方自治体における道路維持管理業務のため / 地方自治体における情報の利活用方策の導入 / 空間計量経済学における最重要課題への挑戦と新たな展開 / 道路台帳を活かした道路アセットマネジメントに関する研究</t>
+          <t>オルタナティブデータを用いたオフィス不動産市場分析の可能性 / オフィス賃貸マーケットに関する研究 / 地方自治体における情報の利活用方策の導入 / 地方自治体における道路維持管理業務のため / 空間計量経済学における最重要課題への挑戦と新たな展開 / 道路台帳を活かした道路アセットマネジメントに関する研究</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ / 東京23区における賃貸オフィスビルストックの地域性と経年変化 / The Impact of the Flight to Quality on Office Rents and Vacancy / Spillover Effect of Large Building Construction on Neighborhood Office Rents / 地域属性と産業振興政策に着目した新設会社の立地に関する考察 / 実用性を考慮したローカルな不動産価格指数の理論と実証. / デジタル化と立地がコロナ禍における私立中学校選択に与える影響. / 大規模オフィスビルの竣工が近隣のオフィス賃料に与える影響：アメニティ効果 vs 供給効果. / 東京オフィス市場における 集積の経済・不経済とその時間的変化 / Spillover Effect of Large Building Construction on Neighborhood Office Rents / Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics / Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market / ビッグデータのためのローカルなオフィス賃料指数の開発 / オフィス空室率の時空間変動に関する探索的小地域分析 / 東京オフィス市場における 集積の経済・不経済とその時間的変化 / 北陸新幹線開通による大学選択への影響に関する実証的研究 / 計量テキスト分析による道路橋を維持管理する技術力の解明の試み / 土木技術者の経験と学習 ―地方整備局職員の研究所出向と道路構造物を維持管理する技術力に着目して― / 空室率データで見る東京オフィス市場の空間的特性 / インフラの維持管理に関する研修による技術力向上効果の評価 ―道路橋の点検に着目して― / 東京オフィス市場における集積の経済・不経済とその時間的変化 / 携帯位置情報データを用いた東京23区内における“オフィス出社”の時空間分析 / 改訂版ブルーム・タキソノミーを用いた道路橋を維持管理する技術力の解明の試み / 交通アクセシビリティの変化が 中学受験における学校選択に与える影響 / モバイル端末の活用による地方自治体の道路維持業務支援の検討</t>
+          <t>土木計画学・交通工学</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>道路維持管理 / 空間計量経済学 / 地理情報システム / 空間データ / 空間統計 / 不動産 / 不動産価格 / 不動産賃料 / 土地利用 / 立地分析</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ / 東京23区における賃貸オフィスビルストックの地域性と経年変化 / The Impact of the Flight to Quality on Office Rents and Vacancy / Spillover Effect of Large Building Construction on Neighborhood Office Rents / 地域属性と産業振興政策に着目した新設会社の立地に関する考察 / 実用性を考慮したローカルな不動産価格指数の理論と実証. / デジタル化と立地がコロナ禍における私立中学校選択に与える影響. / 大規模オフィスビルの竣工が近隣のオフィス賃料に与える影響：アメニティ効果 vs 供給効果. / 東京オフィス市場における 集積の経済・不経済とその時間的変化 / Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics / Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market / ビッグデータのためのローカルなオフィス賃料指数の開発 / オフィス空室率の時空間変動に関する探索的小地域分析 / 北陸新幹線開通による大学選択への影響に関する実証的研究 / 計量テキスト分析による道路橋を維持管理する技術力の解明の試み / 土木技術者の経験と学習 ―地方整備局職員の研究所出向と道路構造物を維持管理する技術力に着目して― / 空室率データで見る東京オフィス市場の空間的特性 / インフラの維持管理に関する研修による技術力向上効果の評価 ―道路橋の点検に着目して― / 東京オフィス市場における集積の経済・不経済とその時間的変化 / 携帯位置情報データを用いた東京23区内における“オフィス出社”の時空間分析 / 改訂版ブルーム・タキソノミーを用いた道路橋を維持管理する技術力の解明の試み / 交通アクセシビリティの変化が 中学受験における学校選択に与える影響 / モバイル端末の活用による地方自治体の道路維持業務支援の検討</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>自然災害発生による学校選択行動への影響ー首都圏私立中学を対象としてー / 東京オフィス市場における賃料調整過程の異質性と非対称性 / 非労働環境におけるライフキャリア形成プロセス / The Effect of the Housing Prices on the Household Savings in Urban China Under the Trend of Aging Society / The Determinants of China’s crude birth rate and regional difference ——Under the effect of two child policy / 中国における個人用固定資産税改革の効果分析 / 物流企業を考慮した応用都市経済モデルの開発に向けて / 国内政策の普及の実態 ～マイナンバーカードを事例として～ / 地域おこし協力隊の受け入れをめぐる自治体間競争に関する考察 / 大阪市における学力テストスコアと賃料の関係 ～小学校学校選択制の導入から～ / サービス付き高齢者向け住宅の賃料と立地選択の影響要因に関する研究</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; 保険・金融行動 ; 意思決定分析 ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; 災害・防災研究 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-保険・金融行動
-意思決定分析
+          <t>土木計画学・交通工学 ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; マーケティング分析 ; 災害分析 ; 都市計画</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>土木計画学・交通工学
+道路維持管理
+空間計量経済学
+地理情報システム
+空間データ
+空間統計
+不動産
+不動産価格
+不動産賃料
+土地利用
+立地分析
 都市・地域政策
 GIS・空間分析
 交通・モビリティ
 建築・空間設計
-災害・防災研究
 政策評価・計量分析
 公共政策・社会工学
 経済・ファイナンス
+数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-行動ファイナンス
-金融市場分析
-ESG投資
-企業財務
-行動意思決定
-実験・行動分析
-ナッジ
-意思決定支援
 都市経済
 地域政策
-土地利用
 公共政策評価
 GIS
 空間計量
 地理情報分析
-立地分析
 交通工学
 モビリティ設計
 交通需要分析
@@ -10927,18 +12438,29 @@
 空間レイアウト生成
 居住空間設計
 都市空間デザイン
-災害社会学
-防災政策
-リスク評価
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>自然災害発生による学校選択行動への影響ー首都圏私立中学を対象としてー / 東京オフィス市場における賃料調整過程の異質性と非対称性 / 非労働環境におけるライフキャリア形成プロセス / The Effect of the Housing Prices on the Household Savings in Urban China Under the Trend of Aging Society / The Determinants of China’s crude birth rate and regional difference ——Under the effect of two child policy / 中国における個人用固定資産税改革の効果分析 / 物流企業を考慮した応用都市経済モデルの開発に向けて / 国内政策の普及の実態 ～マイナンバーカードを事例として～ / 地域おこし協力隊の受け入れをめぐる自治体間競争に関する考察 / 大阪市における学力テストスコアと賃料の関係 ～小学校学校選択制の導入から～ / サービス付き高齢者向け住宅の賃料と立地選択の影響要因に関する研究
+実証分析
+行政データ分析
+マーケティング分析
+災害分析
+都市計画</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>自然災害発生による学校選択行動への影響ー首都圏私立中学を対象としてー
+東京オフィス市場における賃料調整過程の異質性と非対称性
+非労働環境におけるライフキャリア形成プロセス
+The Effect of the Housing Prices on the Household Savings in Urban China Under the Trend of Aging Society
+The Determinants of China’s crude birth rate and regional difference ——Under the effect of two child policy
+中国における個人用固定資産税改革の効果分析
+物流企業を考慮した応用都市経済モデルの開発に向けて
+国内政策の普及の実態 ～マイナンバーカードを事例として～
+地域おこし協力隊の受け入れをめぐる自治体間競争に関する考察
+大阪市における学力テストスコアと賃料の関係 ～小学校学校選択制の導入から～
+サービス付き高齢者向け住宅の賃料と立地選択の影響要因に関する研究
 オルタナティブデータを用いたオフィス不動産市場分析の可能性
 オフィス賃貸マーケットに関する研究
 地方自治体における情報の利活用方策の導入
@@ -11009,6 +12531,10 @@
 ASEAN諸国におけるモビリティ・マネジメントの実行可能性に関する実証分析
 道路上の異モード間コミュニケーションの生起と社会的受容
 健康に配慮した交通行動誘発のための学際的研究
+土木計画学・交通工学
+交通計画
+都市計画における態度・行動変容研究
+リスク･コミュニケーション
 ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析
 Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo
 Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt
@@ -11041,45 +12567,48 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo / Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo / 高齢運転者向け認知機能検査における制度変更の影響評価 / Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour / おつかい行動に見る子どもの移動自由性の世代変化と要因分析 / 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 / 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 / 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― / 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― / モビリティのイノベーションに，モビリティ･マネジメントをどう活かすか？ / モビリティ・マネジメントと健康福祉・教育 / 日米の車両生成データ制作の現状とEUのData Actの波及可能性 / SWC首長研究会への加盟有無(健康都市づくりに対する首長の意識)と公共交通分担率が住民の心身の健康に与える影響 / 「報復の空白」と「運」が交通事故時の道徳的判断に与える影響－自動運転と手動運転の比較分析－ / 東京都区部の電動キックボードシェア利用実態と利用体験・交通手段別視点による比較分析 / 米国における自動運転タクシーの社会的受容とその要因分析－人身事故経験を有する二都市に着目して / おつかい行動に見る子どもの移動自由性の世代変化とその要因分析，最近の調査研究から / 新たなモビリティの規制緩和－思考停止の日本人，大丈夫？ / モビリティ・マネジメントとの出会いと今後 / 基礎自治体における電動キックボードビジネス のガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― / 高齢運転者向け認知機能検査における制度変更の影響評価 / 米国の自動運転車両の事故発生後の 社会的受容の比較分析 / 奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討</t>
+          <t>土木計画学・交通工学</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>交通計画 / 都市計画における態度・行動変容研究 / リスク･コミュニケーション</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo / Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt / 高齢運転者向け認知機能検査における制度変更の影響評価 / Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour / おつかい行動に見る子どもの移動自由性の世代変化と要因分析 / 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 / 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 / 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― / 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― / モビリティのイノベーションに，モビリティ･マネジメントをどう活かすか？ / モビリティ・マネジメントと健康福祉・教育 / 日米の車両生成データ制作の現状とEUのData Actの波及可能性 / SWC首長研究会への加盟有無(健康都市づくりに対する首長の意識)と公共交通分担率が住民の心身の健康に与える影響 / 「報復の空白」と「運」が交通事故時の道徳的判断に与える影響－自動運転と手動運転の比較分析－ / 東京都区部の電動キックボードシェア利用実態と利用体験・交通手段別視点による比較分析 / 米国における自動運転タクシーの社会的受容とその要因分析－人身事故経験を有する二都市に着目して / おつかい行動に見る子どもの移動自由性の世代変化とその要因分析，最近の調査研究から / 新たなモビリティの規制緩和－思考停止の日本人，大丈夫？ / モビリティ・マネジメントとの出会いと今後 / 基礎自治体における電動キックボードビジネス のガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― / 米国の自動運転車両の事故発生後の 社会的受容の比較分析 / 奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>電動キックボードの社会的受容 －国内外専門家の懸念と東京都区部への影響 / EUデータ政策を事例にしたわが国の自動車産業における課題の調査研究 / 高速道路での渋滞吸収走行普及に向けた情報提供と先導車種によるドライバーの心理変化 / 俯瞰的整理を通じた「地域の公共交通向上の担い手人材」育成に向けた取組みの現状と課題</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>労働経済・就職マッチング ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; 社会政策・福祉 ; 交通・モビリティ ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>労働経済・就職マッチング
-マッチング理論・ゲーム理論
+          <t>土木計画学・交通工学 ; 都市・地域政策 ; 社会政策・福祉 ; 交通・モビリティ ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 計算社会科学 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>土木計画学・交通工学
+交通計画
+都市計画における態度・行動変容研究
+リスク･コミュニケーション
 都市・地域政策
 社会政策・福祉
 交通・モビリティ
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 数理最適化・OR
-AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
 都市経済
 地域政策
 土地利用
@@ -11095,12 +12624,22 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>電動キックボードの社会的受容 －国内外専門家の懸念と東京都区部への影響 / EUデータ政策を事例にしたわが国の自動車産業における課題の調査研究 / 高速道路での渋滞吸収走行普及に向けた情報提供と先導車種によるドライバーの心理変化 / 俯瞰的整理を通じた「地域の公共交通向上の担い手人材」育成に向けた取組みの現状と課題
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+社会ネットワーク分析
+計算社会科学
+学習分析</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>電動キックボードの社会的受容 －国内外専門家の懸念と東京都区部への影響
+EUデータ政策を事例にしたわが国の自動車産業における課題の調査研究
+高速道路での渋滞吸収走行普及に向けた情報提供と先導車種によるドライバーの心理変化
+俯瞰的整理を通じた「地域の公共交通向上の担い手人材」育成に向けた取組みの現状と課題
 「クルマ」と「自動化するクルマ」の社会的受容の包括的理解に向けた学際研究
 ナラティブで編まれる地域交通コミュニティ形成と人材プログラムの研究開発
 健康にやさしい環境整備に係る実証事業
@@ -11175,6 +12714,13 @@
 ネットワーク上の時間軸をもった最適化問題とその応用
 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化
 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開
+数学基礎・応用数学
+組合せ論
+トポロジー的組合せ論
+シェラビリティー
+単体的複体
+離散構造
+離散幾何
 The average expected value of a rooted graph, Monte Carlo calculation, and a power index for the voting game
 Coloring zonotopal quadrangulations of the projective space
 Several minimality concepts related to Frankl's conjecture
@@ -11209,62 +12755,67 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
+          <t>数学基礎・応用数学</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>組合せ論 / トポロジー的組合せ論 / シェラビリティー / 単体的複体 / 離散構造 / 離散幾何</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>The average expected value of a rooted graph, Monte Carlo calculation, and a power index for the voting game / Coloring zonotopal quadrangulations of the projective space / Several minimality concepts related to Frankl's conjecture / Some computational studies of the root distribution of Ehrhart polynomials / The root distributions of Ehrhart polynomials of free sums of reflexive polytopes / Sequential Partitions of Nonpure Simplicial Complexes / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting / Pure-strategy Nash equilibria on competitive diffusion games / Hereditary properties and obstructions of simplicial complexes / A comment on pure-strategy Nash equilibria in competitive diffusion games / Obstructions to shellability, partitionability, and sequential Cohen-Macaulayness / Decompositions of two-dimensional simplicial complexes / A note on shellability and acyclic orientations / On the topology of the free complexes of convex geometries / A factorization theorem of characteristic polynomials of convex geometries / The max-flow min-cut property of two-dimensional affine convex geometries / h-Assignments of simplicial complexes and reverse search / Tangle sum and constructible spheres / Deciding constructibility of 3-balls with at most two interior vertices / Non-constructible complexes and the bridge index / Decompositions of balls and spheres with knots consisting of few edges / Nonconstructible balls and a way of testing constructibility / Constructible complexes and recursive division of posets / セル複体に付随するグラフの向き付けとその最適解 / 核付アフィン点配置の根付サーキット系の性質について</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>飛行禁止空域のある空間におけるドローンを用いた監視経路決定 / グラフ理論における再構成問題及び再構成数に関する一考察 / 最大次数が4以下のグラフにおける1-2 Conjectureについて / 低discrepancy点集合の構成における数独超方格の応用 / 繰り返し離散ボロノイゲームのヒューリスティック解法の検討 / 特定の形をした直径が6の木グラフに対するGraceful Labeling</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>GIS・空間分析 ; オペレーションズリサーチ ; 建築・空間設計 ; 機械学習 ; 画像・視覚情報処理 ; ネットワーク・グラフ理論 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>GIS・空間分析
+          <t>数学基礎・応用数学 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; ネットワーク科学 ; 社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>数学基礎・応用数学
+組合せ論
+トポロジー的組合せ論
+シェラビリティー
+単体的複体
+離散構造
+離散幾何
 オペレーションズリサーチ
-建築・空間設計
-機械学習
-画像・視覚情報処理
 ネットワーク・グラフ理論
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
-GIS
-空間計量
-地理情報分析
-立地分析
 数理最適化
 組合せ最適化
 計画・スケジューリング
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-統計的学習
-予測モデリング
-表現学習
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
 グラフ理論
 離散数学
 ネットワーク最適化
-組合せ構造</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>飛行禁止空域のある空間におけるドローンを用いた監視経路決定 / グラフ理論における再構成問題及び再構成数に関する一考察 / 最大次数が4以下のグラフにおける1-2 Conjectureについて / 低discrepancy点集合の構成における数独超方格の応用 / 繰り返し離散ボロノイゲームのヒューリスティック解法の検討 / 特定の形をした直径が6の木グラフに対するGraceful Labeling
+組合せ構造
+ネットワーク科学
+社会ネットワーク分析</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>飛行禁止空域のある空間におけるドローンを用いた監視経路決定
+グラフ理論における再構成問題及び再構成数に関する一考察
+最大次数が4以下のグラフにおける1-2 Conjectureについて
+低discrepancy点集合の構成における数独超方格の応用
+繰り返し離散ボロノイゲームのヒューリスティック解法の検討
+特定の形をした直径が6の木グラフに対するGraceful Labeling
 トポロジー的組合せ論と組合せ論におけるトポロジー的手法
 組合せ的構造に関する研究
 Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求
@@ -11340,6 +12891,11 @@
 組合せ的デザイン理論を用いた周波数ホッピング系列の構成に関する研究
 組合せ的デザイン理論を用いた光直交符号の構成に関する研究
 組合せ的デザインとその符号・暗号への応用
+数学基礎・応用数学
+組合せ論
+符号理論
+情報セキュリティ
+グループ検査
 版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹)
 A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao)
 Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao)
@@ -11374,39 +12930,55 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>数学基礎・応用数学</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>組合せ論 / 符号理論 / 情報セキュリティ / グループ検査</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) / A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) / Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) / Repairing Schemes for Tamo-Barg Codes / A Construction of Optimal One-Coincidence Frequency-Hopping Sequences via Generalized Cyclotomy / Secure Codes With List Decoding / Codes for Exact Support Recovery of Sparse Vectors from Inaccurate Linear Measurements and Their Decoding / Optimal Locally Repairable Codes: An Improved Bound and Constructions / On the Information-Theoretic Security of Combinatorial All-or-Nothing Transforms / A Construction of Maximally Recoverable Codes With Order-Optimal Field Size / Capacity-Achieving Private Information Retrieval Schemes From Uncoded Storage Constrained Servers With Low Sub-Packetization / BCH codes with minimum distance proportional to code length / Existence and Construction of Complete Traceability Multimedia Fingerprinting Codes Resistant to Averaging Attack and Adversarial Noise / Strongly separable matrices for nonadaptive combinatorial group testing / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting / Algebraic manipulation detection codes via highly nonlinear functions / On Optimal Locally Repairable Codes With Super-Linear Length / On optimal weak algebraic manipulation detection codes and weighted external difference families / On Optimal Locally Repairable Codes With Multiple Disjoint Repair Sets / Improved Bounds for Separable Codes and B-2 Codes / Probabilistic Existence Results for Parent-Identifying Schemes / Non-adaptive group testing on graphs with connectivity / Bounds on Traceability Schemes / New Bounds for Frameproof Codes / Zero-difference balanced functions with new parameters and their applications</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>An improved algorithm to identify the cardinality of a coalition in multimedia fingerprinting / Group Testing with List Decoding</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>オペレーションズリサーチ ; 機械学習</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>オペレーションズリサーチ
+          <t>数学基礎・応用数学 ; 機械学習</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 組合せ最適化 ; 社会ネットワーク分析 ; 学習分析 ; 数理最適化</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>数学基礎・応用数学
+組合せ論
+符号理論
+情報セキュリティ
+グループ検査
 機械学習
-数理最適化
-組合せ最適化
-計画・スケジューリング
 統計的学習
 予測モデリング
-表現学習</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>An improved algorithm to identify the cardinality of a coalition in multimedia fingerprinting / Group Testing with List Decoding
+表現学習
+組合せ最適化
+社会ネットワーク分析
+学習分析
+数理最適化</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>An improved algorithm to identify the cardinality of a coalition in multimedia fingerprinting
+Group Testing with List Decoding
 不正者追跡アルゴリズムの開発とその応用
 デジタル指紋符号、多重接続通信路、及び組合せ探索問題
 スパースな結合行列を持つ組合せ的構造の分析と構成
@@ -11481,7 +13053,34 @@
 交通渋滞マネジメントのためのビリーフデザインアプローチ
 バイオミメティックスに学ぶスマートな都市退化マネジメント
 AI計算リソースとしての実交通ダイナミクスの活用技術の開発
-走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー</t>
+走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー
+土木計画学・交通工学
+交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム
+Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks
+A second order model of capacity drop at expressway lane-drop bottlenecks
+都市鉄道整備推進に向けた事業制度に関する研究
+Stability analysis of a departure time choice problem with atomic vehicle models
+自動運転車両の速度制御を考慮した系統信号制御に関する考察
+追従モデルによる高速道路サグ部のCapacity Drop現象の再現
+連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析
+テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル
+Predicting traffic breakdown in expressways using linear combination of vehicle detector data
+Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals
+音声による速度回復情報提供の交通性能改善メカニズムの実証分析
+連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析
+Dynamic traffic assignment in a corridor network: Optimum versus equilibrium
+高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム
+需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡
+Fundamental diagram of urban rail transit considering train-passenger interaction
+高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム
+高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動
+Dynamic system optimal traffic assignment with atomic users: Convergence and stability
+A new look at departure time choice equilibrium models with heterogeneous users
+動的交通均衡配分理論の近年の進展
+Continuum car-following model of capacity drop at sag and tunnel bottlenecks
+Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach"
+Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach
+Trading mechanisms for bottleneck permits with multiple purchase opportunities</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -11489,40 +13088,49 @@
           <t>気候変動緩和に貢献する新興大都市におけるデータ駆動型の動的交通マネジメントに関する研究 / 高速車両連結技術を前提とした都市鉄道の近未来型運行スキーム / 高速道路単路部の交通流理論の検証と交通制御システムの戦略的デザイン / 限定合理的個人を仮定した大規模社会システムの動的制度設計 / 交通・物流システム効率化のための市場型マッチング・システムの設計・評価法構築 / MaaS＋CV時代の次世代交通システムに向けたインフラと制度の設計 / 交通渋滞マネジメントのためのビリーフデザインアプローチ / バイオミメティックスに学ぶスマートな都市退化マネジメント / AI計算リソースとしての実交通ダイナミクスの活用技術の開発 / 走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>土木計画学・交通工学</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks / A second order model of capacity drop at expressway lane-drop bottlenecks / 都市鉄道整備推進に向けた事業制度に関する研究 / Stability analysis of a departure time choice problem with atomic vehicle models / 自動運転車両の速度制御を考慮した系統信号制御に関する考察 / 追従モデルによる高速道路サグ部のCapacity Drop現象の再現 / 連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析 / テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル / Predicting traffic breakdown in expressways using linear combination of vehicle detector data / Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 / 連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析 / Dynamic traffic assignment in a corridor network: Optimum versus equilibrium / 高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム / 需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡 / Fundamental diagram of urban rail transit considering train-passenger interaction / 高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム / 高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動 / Dynamic system optimal traffic assignment with atomic users: Convergence and stability / A new look at departure time choice equilibrium models with heterogeneous users / 動的交通均衡配分理論の近年の進展 / Continuum car-following model of capacity drop at sag and tunnel bottlenecks / Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" / Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach / Trading mechanisms for bottleneck permits with multiple purchase opportunities</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>ボトルネック渋滞と都市人口分布の相互依存関係の解析 / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 / 多種別連結運行スキームにおける鉄道システムの安定性解析 / 市場型混雑管理システム下における自動運転サービスの運用方法 / 需要の時間的・空間的異質性を考慮した多種別連結運行スキームの分析 / 路線分割に基づく系統制御評価とオフセット設計 / 小規模シェアサイクルにおける再配置の効果分析と改善策の提案―茨城県つくば市「つくチャリ」を対象として―</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通 ; 環境・エネルギー</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>家族・人口政策
+          <t>土木計画学・交通工学 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; 交通・モビリティ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 学習分析 ; 災害分析</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>土木計画学・交通工学
+交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム
 マッチング理論・ゲーム理論
 都市・地域政策
-GIS・空間分析
 交通・モビリティ
-建築・空間設計
-政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
+数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-環境・エネルギー
-家族の経済学
-少子化対策
-人口政策
-家計意思決定
 安定マッチング
 資源配分
 メカニズムデザイン
@@ -11531,27 +13139,28 @@
 地域政策
 土地利用
 公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
 交通工学
 モビリティ設計
 交通需要分析
 ネットワーク設計
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-政策評価
-計量経済学
-統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>ボトルネック渋滞と都市人口分布の相互依存関係の解析 / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 / 多種別連結運行スキームにおける鉄道システムの安定性解析 / 市場型混雑管理システム下における自動運転サービスの運用方法 / 需要の時間的・空間的異質性を考慮した多種別連結運行スキームの分析 / 路線分割に基づく系統制御評価とオフセット設計 / 小規模シェアサイクルにおける再配置の効果分析と改善策の提案―茨城県つくば市「つくチャリ」を対象として―
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+社会ネットワーク分析
+学習分析
+災害分析</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>ボトルネック渋滞と都市人口分布の相互依存関係の解析
+音声による速度回復情報提供の交通性能改善メカニズムの実証分析
+多種別連結運行スキームにおける鉄道システムの安定性解析
+市場型混雑管理システム下における自動運転サービスの運用方法
+需要の時間的・空間的異質性を考慮した多種別連結運行スキームの分析
+路線分割に基づく系統制御評価とオフセット設計
+小規模シェアサイクルにおける再配置の効果分析と改善策の提案―茨城県つくば市「つくチャリ」を対象として―
 気候変動緩和に貢献する新興大都市におけるデータ駆動型の動的交通マネジメントに関する研究
 高速車両連結技術を前提とした都市鉄道の近未来型運行スキーム
 高速道路単路部の交通流理論の検証と交通制御システムの戦略的デザイン
@@ -11561,7 +13170,31 @@
 交通渋滞マネジメントのためのビリーフデザインアプローチ
 バイオミメティックスに学ぶスマートな都市退化マネジメント
 AI計算リソースとしての実交通ダイナミクスの活用技術の開発
-走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー</t>
+走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー
+Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks
+A second order model of capacity drop at expressway lane-drop bottlenecks
+都市鉄道整備推進に向けた事業制度に関する研究
+Stability analysis of a departure time choice problem with atomic vehicle models
+自動運転車両の速度制御を考慮した系統信号制御に関する考察
+追従モデルによる高速道路サグ部のCapacity Drop現象の再現
+連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析
+テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル
+Predicting traffic breakdown in expressways using linear combination of vehicle detector data
+Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals
+連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析
+Dynamic traffic assignment in a corridor network: Optimum versus equilibrium
+高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム
+需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡
+Fundamental diagram of urban rail transit considering train-passenger interaction
+高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム
+高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動
+Dynamic system optimal traffic assignment with atomic users: Convergence and stability
+A new look at departure time choice equilibrium models with heterogeneous users
+動的交通均衡配分理論の近年の進展
+Continuum car-following model of capacity drop at sag and tunnel bottlenecks
+Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach"
+Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach
+Trading mechanisms for bottleneck permits with multiple purchase opportunities</t>
         </is>
       </c>
     </row>
@@ -11598,6 +13231,9 @@
 多変量／高次元の潜在変数をもつ時系列モデルの効率的ベイズ推測
 高次元データモデリングの新展開と統計的リスク分析
 経済・金融多変量データのベイズモデリングと政策・行動の確率的評価
+統計科学
+経済統計
+ベイズ統計学, 状態空間モデル
 Simulation of truncated and unimodal gamma distributions
 Bayesian GARCH modeling for return and range
 時間変動する相関と確率的ボラティリティモデル
@@ -11613,29 +13249,41 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
+          <t>統計科学 / 経済統計</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ベイズ統計学, 状態空間モデル</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>Simulation of truncated and unimodal gamma distributions / Bayesian GARCH modeling for return and range / 時間変動する相関と確率的ボラティリティモデル / Multiple-block dynamic equicorrelations with realized measures, leverage and endogeneity / Dynamic equicorrelation stochastic volatility / Bayesian Analysis of Time-Varying Quantiles Using a Smoothing Spline</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>階層ディリクレ多項モデルの効率的な変分推論</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>保険・金融行動 ; GIS・空間分析 ; オペレーションズリサーチ ; 建築・空間設計 ; 機械学習 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>保険・金融行動
+          <t>統計科学 ; 経済統計 ; 保険・金融行動 ; GIS・空間分析 ; 建築・空間設計 ; 機械学習 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 学習分析 ; 統計学 ; 行政データ分析 ; 数理最適化</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>統計科学
+経済統計
+ベイズ統計学, 状態空間モデル
+保険・金融行動
 GIS・空間分析
-オペレーションズリサーチ
 建築・空間設計
 機械学習
 政策評価・計量分析
@@ -11650,9 +13298,6 @@
 空間計量
 地理情報分析
 立地分析
-数理最適化
-組合せ最適化
-計画・スケジューリング
 建築計画
 空間レイアウト生成
 居住空間設計
@@ -11663,10 +13308,14 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
+実証分析
+学習分析
+統計学
+行政データ分析
+数理最適化</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>階層ディリクレ多項モデルの効率的な変分推論
 非線形・非正規状態空間モデルと多変量・高次元経済金融時系列分析
@@ -11720,6 +13369,17 @@
 水害時の住民避難をより安全にする広域避難対策の社会的実装を図る計画技術の構築
 都市の拠点集約と拠点間ネットワークの空間分析
 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究
+都市計画・建築計画
+社会システム工学・安全システム
+人文地理学
+地理学
+土木計画学・交通工学
+都市解析
+地域施設計画
+立地科学
+地域公共交通
+地理情報科学
+都市リスク分析
 起伏を考慮した低炭素都市交通施策の評価
 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関
 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析
@@ -11749,33 +13409,53 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>歩行からみた都市空間の評価とインフラ適正配置に関する数理的・実証的研究 / 輸送モードの多様化と地域性・広域性を両立する公共交通網設計 / 人口の年齢構成の変遷パターンと市街地構造・生活利便施設アクセシビリティとの関連性分析 / 位置情報ビッグデータを活用した人の移動パターンと都市施設・土地利用・交通網の関係性の分析 / 都市拠点の人流パターン解析と市街地構造変容の モデル分析研究 / デジタル時代の施設配置の理論－自己完結，個人情報保護，民主的決定による非効率性－ / 水害時の住民避難をより安全にする広域避難対策の社会的実装を図る計画技術の構築 / 都市の拠点集約と拠点間ネットワークの空間分析 / 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究 / 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究</t>
+          <t>歩行からみた都市空間の評価とインフラ適正配置に関する数理的・実証的研究 / 輸送モードの多様化と地域性・広域性を両立する公共交通網設計 / 人口の年齢構成の変遷パターンと市街地構造・生活利便施設アクセシビリティとの関連性分析 / 位置情報ビッグデータを活用した人の移動パターンと都市施設・土地利用・交通網の関係性の分析 / 都市拠点の人流パターン解析と市街地構造変容の モデル分析研究 / デジタル時代の施設配置の理論－自己完結，個人情報保護，民主的決定による非効率性－ / 水害時の住民避難をより安全にする広域避難対策の社会的実装を図る計画技術の構築 / 都市の拠点集約と拠点間ネットワークの空間分析 / 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
+          <t>都市計画・建築計画 / 社会システム工学・安全システム / 人文地理学 / 地理学 / 土木計画学・交通工学</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>都市解析 / 地域施設計画 / 立地科学 / 地域公共交通 / 地理情報科学 / 都市リスク分析</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>起伏を考慮した低炭素都市交通施策の評価 / 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関 / 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析 / 東京区部における年齢構成類型の変化と生活利便施設へのアクシセビリティ分析 / 電柱広告の空間的配置に関する研究―筑波研究学園都市中心部を対象に― / Exploring Network Scale Separation Strategies for Car-Bicycle Integration / 都市条件に応じた複数公共交通モード併用によるネットワーク設計 / 全国鉄道駅周辺地域における地域分断による移動制約の定量評価 / 小地域人口の年齢構成類型とその遷移から見た安定性分析 / 東京区部における業種構成・滞在パターンに基づく商業集積地の類型化と滞在移動特性の分析 / 東京区部におけるGPSデータに基づく街区レベル発生集中・滞在移動特性と建物用途構成 / 人口分布の集積性と鉄道網との連携度の変化動向に関する研究 / 東京区部における人口年齢構成と土地利用遷移の関連性分析 / 東京区部における交通量密度・移動速度に基づく交通軸と移動効率性評価 / 鉄道網による移動時間短縮を考慮した都市の人口分布の集積性の評価 / 人流データによる滞在者平均年齢の時空間分析 ―昼や休日に若返る自治体はどこか？― / 通学距離最小化と安定マッチングによる学校割当 / Preference-based jogging route selection in Downtown Tokyo / Effect of Speed Control for Travel Time and Emission Reduction in Connected Vehicle Environment / Exploring Separation Strategies for Car-Bicycle Integration / アジア地域の都市における鉄道・道路と人口分布構造 / 建物主要用途・トリップチェーンに着目した人流データによる街区間トリップ特性 / 人流データによる街区レベル時間帯別発生集中の時空間分布 / 人口重心に着目した人流分析 / 沿道電柱密度の地域別・道路種別比較</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>人口の年齢構成遷移と市街地構造・生活利便施設アクセシビリティとの関連性分析</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>家族・人口政策 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>家族・人口政策
-マッチング理論・ゲーム理論
+          <t>都市計画・建築計画 ; 社会システム工学・安全システム ; 人文地理学 ; 地理学 ; 土木計画学・交通工学 ; 家族・人口政策 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析 ; 都市計画</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>都市計画・建築計画
+社会システム工学・安全システム
+人文地理学
+地理学
+土木計画学・交通工学
+都市解析
+地域施設計画
+立地科学
+地域公共交通
+地理情報科学
+都市リスク分析
+家族・人口政策
 都市・地域政策
 GIS・空間分析
 オペレーションズリサーチ
@@ -11791,10 +13471,6 @@
 少子化対策
 人口政策
 家計意思決定
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
 都市経済
 地域政策
 土地利用
@@ -11821,10 +13497,14 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
+実証分析
+社会ネットワーク分析
+行政データ分析
+災害分析
+都市計画</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>人口の年齢構成遷移と市街地構造・生活利便施設アクセシビリティとの関連性分析
 歩行からみた都市空間の評価とインフラ適正配置に関する数理的・実証的研究
@@ -11897,6 +13577,16 @@
 測地基準系の座標変換
 地下水位と地盤上下変動に関する研究
 地殻変動解析
+測地学
+空間情報科学
+測量学
+地球観測
+リモートセンシング
+宇宙測地学
+合成開口レーダー
+干渉法
+データサイエンス
+基準座標系
 2011年東北地方太平洋沖地震後の余効変動の時空間関数モデリング
 Spatiotemporal functional modeling of postseismic deformations after the 2011 Tohoku-Oki earthquake
 Ground deformation in the Kobe-Osaka area during 22 years after the Kobe earthquake
@@ -11929,47 +13619,43 @@
           <t>世界測地系の構築 / 合成開口レーダー解析ソフトウェアの開発 / 測地基準系の座標変換 / 地下水位と地盤上下変動に関する研究 / 地殻変動解析</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>測地学 / 空間情報科学 / 測量学 / 地球観測 / リモートセンシング / 宇宙測地学 / 合成開口レーダー / 干渉法 / データサイエンス / 基準座標系</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>2011年東北地方太平洋沖地震後の余効変動の時空間関数モデリング / Spatiotemporal functional modeling of postseismic deformations after the 2011 Tohoku-Oki earthquake / Ground deformation in the Kobe-Osaka area during 22 years after the Kobe earthquake / 兵庫県南部地震以後の22年間の京阪神の地盤変動 / JERS-1/InSAR再解析：1995年兵庫県南部地震後の地殻変動の検出 / 兵庫県南部地震以降，六甲山は高くなったのか？ / Volcanic deformation of Atosanupuri volcanic complex in the Kussharo caldera, Japan, from 1993 to 2016 revealed by JERS-1, ALOS, and ALOS-2 radar interferometry / 宇宙測地技術により検出された1995年兵庫県南部地震の余効変動 / A possible restart of an interplate slow slip adjacent to the Tokai seismic gap in Japan / Combined logarithmic and exponential function model for fitting postseismic GNSS time series after 2011 Tohoku-Oki earthquake / だいち2号SAR干渉解析により捉えられた平成26年（2014年）長野県北部の地震に伴う地殻変動と地表変形 / だいち2号SAR干渉解析による御嶽山噴火に伴う地表変位の検出 (小特集 御嶽山噴火への対応) / P47 ALOS-2干渉SARにより捉えられた2015年箱根山・大涌谷火山活動に伴う地殻変動(ポスターセッション) / 2014年11月22日長野県北部の地震におけるSAR干渉画像に基づく地表変形現地調査結果 / 干渉SARで捉えた2014年11月22日長野県北部を震源とする地震に伴う地表変位 / Continuous gps observations on mindanao / 無人航空機(UAV)による西之島の空中写真撮影と高精度地形計測 / SAR干渉解析のための数値気象モデルを用いた大気遅延誤差の低減処理ツールの開発 / 無人航空機による西之島空中写真の撮影とその分析 / 無人機による西之島地形計測の高精度化 / Landform Monitoring in Active Volcano by UAV and SFM-MVS Technique / Spatial and temporal evolution of the long-term slow slip in the Bungo Channel, Japan / InSAR-derived Coseismic Deformation of the 2010 Southeastern Iran Earthquake (M6.5) and its Relationship with the Tectonic Background in the South of Lut Block / 新潟—神戸ひずみ集中帯越後平野付近の詳細地殻変動分布 / Preceding, coseismic, and postseismic slips of the 2011 Tohoku earthquake, Japan</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>GIS・空間分析 ; 建築・空間設計 ; 機械学習 ; 画像・視覚情報処理 ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>GIS・空間分析
-建築・空間設計
-機械学習
-画像・視覚情報処理
-AI・データサイエンス
-GIS
-空間計量
-地理情報分析
-立地分析
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-統計的学習
-予測モデリング
-表現学習
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
+        <is>
+          <t>センサデータ解析 ; 災害分析 ; 環境工学 ; 行政データ分析</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>測地学
+空間情報科学
+測量学
+地球観測
+リモートセンシング
+宇宙測地学
+合成開口レーダー
+干渉法
+データサイエンス
+基準座標系
+センサデータ解析
+災害分析
+環境工学
+行政データ分析</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>世界測地系の構築
 合成開口レーダー解析ソフトウェアの開発
@@ -12042,6 +13728,11 @@
 マルチスケールな拠点空間計画のための新たな行動モデル研究
 災害時都市継続計画にむけた即応型需要予測の信頼性向上のためのデータフロー
 災害時都市活動支援のためのsoftware2.0型シミュレータの構築
+避難行動
+交通需要
+交通シミュレーション
+災害復旧
+相互作用
 通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～
 EVユーザーの充電場所選択問題に対するゲーム理論的考察
 災害復旧期における個々人の移動パターン変化の特徴分析
@@ -12069,40 +13760,46 @@
           <t>災害時交通網の動学的設計にむけた不確かさ回避行動の評価手法の構築 / ネットワークリスクの動的変化と避難行動チェインの解明 / 次世代モビリティ導入を想定した交通・土地利用モデルの開発とその不確実性分析 / 災害時の他者支援行動を考慮した動的制御シミュレータの開発 / MaaS＋CV時代の次世代交通システムに向けたインフラと制度の設計 / 相乗型豪雨災害時の交通マネジメントの理論再構築と社会への実装 / 量子コンピューティングによる他者相互作用型の行動モデルの発展 / マルチスケールな拠点空間計画のための新たな行動モデル研究 / 災害時都市継続計画にむけた即応型需要予測の信頼性向上のためのデータフロー / 災害時都市活動支援のためのsoftware2.0型シミュレータの構築</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ / EVユーザーの充電場所選択問題に対するゲーム理論的考察 / 災害復旧期における個々人の移動パターン変化の特徴分析 / メタ分析による災害時の避難開始選択要因の評価 / メタ分析による災害時の避難開始選択要因の評価 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 相互作用下での多肢選択行動の量子計算による求解 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— / Object-oriented Bayesian Networks for Activity-based Model with deep generative graph averaging / 筑波大学理工学群におけるデータサイエンス応用基礎教育 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 / 選択肢の不確実性を考慮した動的離散選択モデル / LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること / 日本の復興計画の研究動向と今後の展望 -1995年以降の建築・都市・土木の計画分野を中心に- / 選択肢の不確実性を考慮した動的離散選択モデル / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 / LET'S GO ABROAD!(第77回)シンガポール、パキスタン、アフガニスタン、ベトナム、カンボジア 地域建設業の海外展開と見据える未来—A regional construction company looks to overseas expansion and their future—特集 土木と地政学 / 「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>避難行動 / 交通需要 / 交通シミュレーション / 災害復旧 / 相互作用</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価</t>
-        </is>
-      </c>
+          <t>通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ / EVユーザーの充電場所選択問題に対するゲーム理論的考察 / 災害復旧期における個々人の移動パターン変化の特徴分析 / メタ分析による災害時の避難開始選択要因の評価 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 相互作用下での多肢選択行動の量子計算による求解 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— / 筑波大学理工学群におけるデータサイエンス応用基礎教育 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 / 選択肢の不確実性を考慮した動的離散選択モデル / LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること / 日本の復興計画の研究動向と今後の展望 -1995年以降の建築・都市・土木の計画分野を中心に- / LET'S GO ABROAD!(第77回)シンガポール、パキスタン、アフガニスタン、ベトナム、カンボジア 地域建設業の海外展開と見据える未来—A regional construction company looks to overseas expansion and their future—特集 土木と地政学 / 「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>マッチング理論・ゲーム理論
+          <t>都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 観光・マーケティング ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 災害分析 ; 社会ネットワーク分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>避難行動
+交通需要
+交通シミュレーション
+災害復旧
+相互作用
 都市・地域政策
 GIS・空間分析
-オペレーションズリサーチ
 交通・モビリティ
 建築・空間設計
 ネットワーク・グラフ理論
 災害・防災研究
+観光・マーケティング
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
 都市経済
 地域政策
 土地利用
@@ -12111,9 +13808,6 @@
 空間計量
 地理情報分析
 立地分析
-数理最適化
-組合せ最適化
-計画・スケジューリング
 交通工学
 モビリティ設計
 交通需要分析
@@ -12128,10 +13822,17 @@
 組合せ構造
 災害社会学
 防災政策
-リスク評価</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
+リスク評価
+観光データ分析
+マーケティング分析
+クラスタリング
+需要予測
+災害分析
+社会ネットワーク分析
+学習分析</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>災害時交通網の動学的設計にむけた不確かさ回避行動の評価手法の構築
 ネットワークリスクの動的変化と避難行動チェインの解明
@@ -12196,6 +13897,8 @@
         <is>
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発
 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証
+Service Engineering
+Experimental economics
 主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案
 What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews
 Mystery shopping considering lifestyle heterogeneity
@@ -12213,37 +13916,44 @@
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発 / 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Service Engineering / Experimental economics</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 / What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews / Mystery shopping considering lifestyle heterogeneity / 経験効用モデルに基づくサービス継続利用を促すリマインダーの最適間隔 / Effects of Incentivized Fake Reviews on E-commerce Markets / Platform in manufacturing for enhancement of product value by sharing / Interpreting value creation model by case-based decision theory / Service switching in case-based decisions following bad experiences: Online reviews data of Japanese hairdressing salons / Multi-agent simulation for the manufacturer’s decision making in sharing markets / Manufacturer’s strategy in a sharing economy</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>意思決定分析 ; オペレーションズリサーチ ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>意思決定分析
-オペレーションズリサーチ
+          <t>意思決定分析 ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 推薦システム ; 政策評価 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Service Engineering
+Experimental economics
+意思決定分析
 AI・データサイエンス
 行動意思決定
 実験・行動分析
 ナッジ
 意思決定支援
-数理最適化
-組合せ最適化
-計画・スケジューリング</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
+推薦システム
+政策評価
+学習分析</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発
 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,50 +457,55 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>profile_source</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>trios_info</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>trios_topics_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>trios_research_fields_text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>trios_research_keywords_text</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>trios_papers_text</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>master_title_text</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>coarse_research_field</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>detailed_research_field</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>field_text</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>content_text</t>
         </is>
@@ -533,6 +538,11 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>十分なエネルギーをすべての人へ：家庭部門の公正な移行を実現するために
 包摂的な低炭素化・エネルギー転換に関する研究
@@ -578,42 +588,42 @@
 How Can We Gauge Energy Poverty? A Multidimensional Approach</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>十分なエネルギーをすべての人へ：家庭部門の公正な移行を実現するために / 包摂的な低炭素化・エネルギー転換に関する研究 / 低炭素化・エネルギー転換の包摂性評価：基本的エネルギーニーズの観点から / 環境・エネルギーに関する多次元貧困指標の開発と政策分析 / 地球温暖化とエネルギー貧困 / 東日本大震災後の地球温暖化政策を考える / モラルモチベーションと環境政策 / 人々の環境モラルに基づく自発的行動と望ましい環境政策 / 「環境政策における経済的手法」再検討 / 応用一般均衡モデルによる環境政策の社会経済学的分析</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>経済政策 / 環境政策・環境社会システム</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>環境経済学 / エネルギー経済学 / 政策分析 / 不平等分析 / 貧困分析 / 分解手法の開発 / エネルギー貧困、エネルギー脆弱性</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>エネルギー貧困からエネルギー充足へ / Aging alone: a twin threat to decarbonisation and energy vulnerability in Japan and UK / Reevaluating fair carbon emissions for households in Japan: basic energy needs and subsistence CO2 emissions / Double energy vulnerability in Japan / Double energy vulnerability in Japan: a first assessment / Measuring energy sufficiency: A state of being neither in energy poverty nor energy extravagance / What can be done with one tonne of CO2 emissions?: Reconsidering fair carbon emissions for households in relation to the use of domestic energy services / Measuring energy sufficiency: A state of being in neither energy poverty nor energy extravagance / How to evaluate energy sufficiency: A direct measurement approach / Energy Poverty in Japan: Current Trends and Future Challenges / 公平なエネルギー転換：気候正義とエネルギー正義の観点から / Regional energy poverty reevaluated: A direct measurement approach applied to France and Japan / Energy poor need more energy, but do they need more carbon?: Evaluation of people’s basic carbon needs / Prevalence of energy poverty in Japan: A comprehensive analysis of energy poverty vulnerabilities / Energy poor need more energy, but do they need more carbon? / Engendering an inclusive low-carbon energy transition in Japan: Considering the perspectives and awareness of the energy poor / Understanding regional energy poverty in Japan: a direct measurement approach / Measuring Energy Poverty via Energy Service Usage: The Japanese case / 「エネルギー貧困」・「エネルギー脆弱性」・「エネルギー正義」：日本における現状と課題 / 「エネルギー正義」について / Gauging Energy Poverty: A Multidimensional Approach / Measuring Energy Poverty in Japan, 2004-2013 / How Can We Gauge Energy Poverty? A Multidimensional Approach</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>中国の排出量取引制度がグリーン投資に与える影響 / 再生可能エネルギー促進のための課題ー全国トラブル発生データを用いた考察ー / 中国の「費改税」が製造業に与える影響</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>経済政策 ; 環境政策・環境社会システム ; マッチング理論・ゲーム理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 環境工学 ; 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>経済政策
 環境政策・環境社会システム
@@ -650,7 +660,7 @@
 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>中国の排出量取引制度がグリーン投資に与える影響
 再生可能エネルギー促進のための課題ー全国トラブル発生データを用いた考察ー
@@ -719,6 +729,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>民主主義における利益誘導と経済発展への影響
 政策立案のための衛星データ利用法の探索：社会工学的アプローチ
 社会工学分野での衛星画像の利用促進に向けた探索的研究
@@ -756,42 +771,42 @@
 School Choice and Student Sorting: Evidence from Adachi City in Japan</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>民主主義における利益誘導と経済発展への影響 / 政策立案のための衛星データ利用法の探索：社会工学的アプローチ / 社会工学分野での衛星画像の利用促進に向けた探索的研究 / 衛星情報を利用した物流における大気環境改善の評価 / 反実仮想で測る公的資源配分の依怙贔屓と非効率 / 交通と環境に関する新経済地理学的基盤研究 / 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年 / 都市における環境リスクの軽減の経済効果に関する研究 / 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>経済政策</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>開発経済学、教育の経済学、健康の経済学、応用計量経済学</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand / The Impact of a High-speed Railway on Residential Land Prices / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan / School Choice and Student Sorting: Evidence from Adachi Ward in Japan / オリンピック・パラリンピックにはどんな経済効果があるのか / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward / Building an Administrative Database of Children / 高速鉄道の建設が居住地価格に与えた影響 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 / 学校の質と地価－足立区の地価データを用いた検証 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ / 子どもについての行政データベースの構築 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から / 区立小学校での補習の効果：足立区のケース / ヘドニック・アプローチにおける因果識別 / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand / School Choice and Student Sorting: Evidence from Adachi City in Japan</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>選挙制度と資源配分のゆがみ－昭和前期の事例－ / 都市の住みやすさランキングによる居住地選択への影響 / 個人競技における チームメイトの影響 / 農産物直売所が​地域農業に与える影響 / 夜間光リモートセンシング画像を用いた​高速鉄道建設の四川省経済発展に対する影響 / エネルギー会社に対する省エネ基準が、エネルギー消費に与える影響の分析 / 有名作品の舞台地になることによる地方創生への可能性 / 新型農村協同医療制度が中国農村女性の健康格差に与える影響</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>経済政策 ; 都市・地域政策 ; 交通・モビリティ ; 機械学習 ; 画像・視覚情報処理 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>経済政策
 開発経済学、教育の経済学、健康の経済学、応用計量経済学
@@ -833,7 +848,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>選挙制度と資源配分のゆがみ－昭和前期の事例－
 都市の住みやすさランキングによる居住地選択への影響
@@ -907,6 +922,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>行動経済学の知見を利用した進化ゲーム理論による均衡選択分析
 社会選択問題への進化ゲーム理論的アプローチ
 マルチタスク環境および協力ゲームにおける進化ゲーム理論の研究
@@ -933,42 +953,42 @@
 CG を用いたマシンの3 次元構造進化システム</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>行動経済学の知見を利用した進化ゲーム理論による均衡選択分析 / 社会選択問題への進化ゲーム理論的アプローチ / マルチタスク環境および協力ゲームにおける進化ゲーム理論の研究</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>理論経済学 / 社会システム工学・安全システム</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>ゲーム理論; 進化ゲーム理論;</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>The evolution of collective choice under majority rules / Statistical inference in evolutionary dynamics / 研究室の選好と学生の成績を考慮した研究室配属法の分析 / 有限オートマトンを用いた私的観測繰り返しゲームにおける進化的安定戦略分析 / A stochastic stability analysis with observation errors in normal form games / Stochastic stability in the large population and small mutation limits for coordination games / oTreeを用いた配属システムの設計・構築とその運用 / A prospect theory Nash bargaining solution and its stochastic stability / 複利型強化学習を用いたポートフォリオ選択手法についての研究 / Evolutionary dynamics in multitasking environments / Stochastic stability under logit choice in coalitional bargaining problems / Prospect dynamics and loss dominance / Reference-dependent preferences, super-dominance and stochastic stability / A one-shot deviation principle for stability in matching problems / Evolutionary imitative dynamics with population-varying aspiration levels / Coalitional stochastic stability in games, networks and markets / Mutation rates and equilibrium selection under stochastic evolutionary dynamics / CG を用いたマシンの3 次元構造進化システム</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>不完全観測下における損失回避性が均衡の安定性に及ぼす影響 / 不確実性の存在する公共財提供問題における近視眼的プレイヤーによる持続的協力行動の進化分析 / 品質選択がクラウドファンディングを行う企業の資金募集形式および利潤に与える影響の分析 / 企業の不祥事における隠蔽のゲーム理論 / 就活市場における企業の内定通知がマッチングの安定性に与える影響の分析 / 非線形公共財ゲームにおけるプレイヤーの関係性を利用したグループ形成手法の考察 / Stochastic stability analysis on the tragedy of climate change via agents’ psychological dynamics / ソーシャルメディア上の炎上現象の分析と対策 / 感情表現と表現に対する反応の共進化 / 通貨競争モデルによる仮想通貨の普及に関する分析 / 多数決による準公益施設の立地分析 / プロ野球現役ドラフト制度における改善 / オークションモデルによる官製談合の分析</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>理論経済学 ; 社会システム工学・安全システム ; マッチング理論・ゲーム理論 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 学習分析 ; 計算社会科学 ; 行動科学</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>理論経済学
 社会システム工学・安全システム
@@ -992,7 +1012,7 @@
 行動科学</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>不完全観測下における損失回避性が均衡の安定性に及ぼす影響
 不確実性の存在する公共財提供問題における近視眼的プレイヤーによる持続的協力行動の進化分析
@@ -1050,23 +1070,28 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>researchmap_not_found</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>researchmap</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
 グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築
@@ -1106,6 +1131,11 @@
         </is>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>リーマン多様体上の制約付き最適化問題に対する汎用アルゴリズムの理論と実装
 リーマン多様体上の最適化理論に基づく新たなデータコラボレーション手法の開発
@@ -1145,42 +1175,42 @@
 ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成―</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>リーマン多様体上の制約付き最適化問題に対する汎用アルゴリズムの理論と実装 / リーマン多様体上の最適化理論に基づく新たなデータコラボレーション手法の開発 / ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発 / コネクティッドカーのサービス開発を目的とした走行データのデータクレンジング手法に係る研究 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / 半正定値基を用いた錐最適化問題の近似解法の開発 / 地域未来創生共同研究講座 / 次世代社会システムとモビリティの新価値研究 / 購買データに基づく顧客行動分析</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>数理情報学 / 数学基礎・応用数学 / 社会システム工学・安全システム / 計算科学</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>数理最適化 / 数理計画 / オペレーションズ・リサーチ / サービス工学</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Data Collaboration Analysis with Orthonormal Basis Selection and Alignment / Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning / 正循環制約を考慮したナーススケジューリング / Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices / Post-Processing with Projection and Rescaling Algorithms for Semidefinite Programming / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / A new extension of Chubanov's method to symmetric cones / 射影- 再スケーリング法を用いた 対称錐計画問題に対する後処理アルゴリズム / On the Global Convergence of Riemannian Interior Point Method / Completely positive factorization by a Riemannian smoothing method / Evaluating approximations of the semidefinite cone with trace normalized distance / Completely Positive Factorization in Orthogonality Optimization via Smoothing Method / Scenario-based CVaR Approach to Strategic Decision Support in One-way Station-based Carsharing Systems / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach / Polyhedral approximations of the semidefinite cone and their application / Centering ADMM for the Semidefinite Relaxation of the QAP / QAPの半正定値緩和問題を解くためのセンタリングADMM / SD基に基づく半正定値行列錐の凸多面錐近似 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成―</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>ロード・プライシング政策を考慮したNLSUEモデルとその解法の提案 / 未達率指標を用いた生産計画手法のSC能力設計への応用の研究 / 予約制乗合タクシーのルート最適化 / スマートキャンパスバス運行計画 / 救急医療サービスの効率化に向けた患者の医療機関割り当てに関するオフラインアルゴリズムの開発 / 一般消費財業界における未達率指標を用いた生産計画手法のSC能力設計への応用の研究 / 多死社会における在宅看取りに関する一考察 －茨城県の医療・介護に関する地域分析と実際の看取りをふまえて－ / バックトゥバック数を考慮したNBAの2018-2019シーズンスケジュールの作成 / 健康診断センターの勤務表作成におけるスケジューリング問題 / メタヒューリスティクスを用いた予約制乗合タクシーの配車スケジュール作成 / 乗客満足度を考慮した乗合タクシーの路線最適化モデル / ファストフード店の勤務スケジュールの作成 / リーマン多様体上の統合解析関数最適化 / 社会工学学位プログラムにおける修論発表会のスケジューリングについて / Traveling umpire problem におけるチーム間の公平性が高い解の探求 / 多要素ランキング法の上で正確性と多様性のトレードオフを考慮したモデルによる推薦システム / A Modification of Representing Linear Programs by Graph Neural Network / つくば市における予約制乗合タクシーの配車スケジューリング作成 / マイクログリッドにおける災害対策を考慮した最適化シミュレーション / 大学入試における屋内連絡員の人員配置最適化ツール開発 / 実運用を考慮した予約制乗合タクシーの配車スケジューリング作成</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>数理情報学 ; 数学基礎・応用数学 ; 社会システム工学・安全システム ; 計算科学 ; 都市・地域政策 ; オペレーションズリサーチ ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 学習分析 ; 物流最適化</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>数理情報学
 数学基礎・応用数学
@@ -1205,7 +1235,7 @@
 物流最適化</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>ロード・プライシング政策を考慮したNLSUEモデルとその解法の提案
 未達率指標を用いた生産計画手法のSC能力設計への応用の研究
@@ -1287,6 +1317,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>人工知能に基づく非線形高次元小標本データ解析とその社会的応用
 ３元型時系列高次元小標本データの解析とその社会的応用
 高次計量による高次元小標本型ビックデータ解析とその社会的応用
@@ -1327,42 +1362,42 @@
 区間組成データに対する重み付き回帰分析</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>人工知能に基づく非線形高次元小標本データ解析とその社会的応用 / ３元型時系列高次元小標本データの解析とその社会的応用 / 高次計量による高次元小標本型ビックデータ解析とその社会的応用 / 多次元クラスター尺度構成法によるビックデータ解析とその社会的応用 / 高次シンボリックデータに対するクラスターワイズ手法の開発とその応用 / Data Mining and Machine Learning Techniques / Development of Decision Fusion Architecture for Complex Scenarios / 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 / 高次元データの理論と方法論の総合的研究 / 高次Aggregation Operatorの開発とクラスタリングモデルへの適用</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>統計科学 / ソフトコンピューティング</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>統計科学 / ソフトコンピューティング / データマイニング / 多次元データ解析</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Simultaneous visualization method for mixed HDLSS data and its application for education / Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design / Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey / Difference on Evaluation Scores Considering Image Descriptions for Autocoding / ファジィクラスタリングの信頼度について / Hierarchical Support Vector Machine based Classifier for Autocoding / Fuzzy Cluster-Scaled Principal Component Analysis for Mixed Data and Its Application of Educational Effect based on Device Selection / A Fuzzy Cluster-Scaled Principal Component Analysis for Mixed High-Dimension and Low-Sample Size Data / Principal component analysis for mixed high-dimension low-sample size data based on fuzzy-cluster scale / Improvement of Training Data for Autocoding on "The National Survey of Family Income, Consumption and Wealth" and "The Family Income and Expenditure Survey" / Fuzzy Clustering based Autocoding Methods for Family Income and Expenditure Surveys / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding / Fuzzy Clustering based Classifier for Extraction of Individualities from High Dimension Low Sample Size Data / Individuality-based Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results / Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling / Cluster-based Analysis for Discrimination of Individuality （招待講演） / クラスター尺度に基づくデータ間差異の検出と市場データへの応用 / ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 / Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Clustering and Multidimensional Scaling for Individual Difference Extraction / 多次元尺度法による計算効率を考慮したディープラーニング手法 / Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means / 区間組成データに対する重み付き回帰分析</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>TLPCMの評価および欠損値処理手法 / 区間組成データに対する 回帰分析 / 歌詞テキストデータの感情分類 / 区間データに対するPCA手法の提案と従来法との比較 / ファジィクラスタリングを用いた欠損値補完法について / T-normを用いたクラスター尺度による顧客分類法</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>統計科学 ; ソフトコンピューティング ; 労働経済・就職マッチング ; 都市・地域政策 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 公共政策・社会工学 ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 行政データ分析 ; センサデータ解析 ; 社会ネットワーク分析 ; 計算社会科学</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>統計科学
 ソフトコンピューティング
@@ -1396,7 +1431,7 @@
 計算社会科学</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>TLPCMの評価および欠損値処理手法
 区間組成データに対する 回帰分析
@@ -1468,6 +1503,11 @@
         </is>
       </c>
       <c r="F8" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究
 アカウンティング・インフォマティクス（会計情報科学）の基盤研究
@@ -1514,42 +1554,42 @@
 Configuration model for correlation matrices preserving the node strength</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究 / アカウンティング・インフォマティクス（会計情報科学）の基盤研究 / 学際的エビデンスに基づく超高齢社会のモビリティ支援とアクティブ・エイジングの推進 / 多層ネットワークを用いたワクチン忌避に対する実証的研究 / 想起効果を内在する集合的記憶モデルの開発 / International School and Conference on Network Science (NetSciX 2020) / 勤労世代における風疹ワクチン接種の決定要因に関する研究 / 乳幼児の活動量を測定するウェアラブル機器の開発 / 乳幼児の活動量を測定するウェアラブルデバイスの開発 / サイバー社会ネットワークにおける噂の伝播の検出と制御</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>数理物理・物性基礎 / ウェブ情報学・サービス情報学</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>経済物理学 / ネットワーク科学 / 社会物理学 / 計算社会科学 / ウェブサイエンス / ビッグデータ</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis / コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 / Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan / Quantifying Collective Emotions: Japan’s Societal Trends Through Enhanced Sentiment Index Using POMS2 and SNS / Quantifying collective attention and fan engagement: a case study of the Japanese professional baseball league / News coverage of older drivers' fatal car crashes: is it over-represented? / Burstiness of human physical activities and their characterisation / 12-year observation of tweets about rubella in Japan: A retrospective infodemiology study / A two-phase model of collective memory decay with a dynamical switching point / SNSデータを用いた情報拡散シミュレーション / SNSにおける情報伝播ネットワークの構造 / Music Roles Affect the Selection of Consumption Means: A Questionnaire Survey of People’s Expectations for Music and Exploratory Factor Analysis / Dataset of identified scholars mentioned in acknowledgement statements / Classification of endogenous and exogenous bursts in collective emotions based on Weibo comments during COVID-19 / 日本におけるオンライン・ハラスメントの現状と対策：Twitterでの女性記者のツイート「炎上」を例に / 日本における自治体報道発表のCOVID-19発生状況を用いた感染者遷移状況の記録と可視化 / Simulation of information spreading on Twitter concerning radiation after the Fukushima nuclear power plant accident / 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― / サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して / Fake news propagates differently from real news even at early stages of spreading / 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 / Identifying long-term periodic cycles and memories of collective emotion in online social media / Correlations and fluctuations in the word sets of collective emotions / Configuration model for correlation matrices preserving the node strength</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>高齢運転者に関する報道とウェブ上の世論の可視化 / SNSから抽出した感情と実社会の関連性に関する研究 / Wikipedia閲覧数を用いた集合的記憶の減衰モデル / 保育現場への顔認証システム導入と運用の実証研究 / The identification of acknowledged scholars and their interdisciplinarity / Empirical studies on user-generated content and behavior of Southeast Asia community in Reddit / 日本プロ野球における集合的熱狂とファンの関与 / 仲値決定時近傍における板情報の非対称性の定量化 / 福島原発事故後のSNSにおける情報拡散シミュレーション / インターネットテレビにおけるコンテンツカテゴリ間の視聴数流動予測 / SNSを用いた新型コロナ禍における日本の空気感分析 / ソーシャルメディアを通した日本の高齢運転者に対する言論の定量化 / シラバスのテキストマイニングによる学生の主体性を育む科目の研究 / Wikipedia閲覧数を用いた集合的記憶の想起</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>数理物理・物性基礎 ; ウェブ情報学・サービス情報学 ; 社会政策・福祉 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 会計・ファイナンス ; テキスト分析・NLP ; 医療・ヘルスデータ ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 社会ネットワーク分析 ; 計算社会科学 ; 行政データ分析 ; 学習分析</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>数理物理・物性基礎
 ウェブ情報学・サービス情報学
@@ -1601,7 +1641,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>高齢運転者に関する報道とウェブ上の世論の可視化
 SNSから抽出した感情と実社会の関連性に関する研究
@@ -1683,6 +1723,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>中小企業の雇用・技術と日本経済の再生
 経済環境の激変と中小企業の役割
 縮小経済のもとでの中小企業と企業家活動
@@ -1717,38 +1762,38 @@
 SNA統計を用いた民間法人企業ベースの「トービンのｑ」と投資関数</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>中小企業の雇用・技術と日本経済の再生 / 経済環境の激変と中小企業の役割 / 縮小経済のもとでの中小企業と企業家活動 / 中小企業の資金調達環境と政策のあり方</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>経済政策 / 財政・公共経済 / 経済統計</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Number of positive lymph nodes and lymphatic invasion are significant prognostic factors after pancreaticoduodenectomy for distal cholangiocarcinoma. / 開業と廃業 / 中小企業の知的財産 / Bankruptcy dynamics in Japan / 開業のダイナミクス－開業研究の展望と法人設立登記にもとづく実証分析－ / Which firms exit and why? An analysis of small firm exits in Japan / Video game demand in Japan: a household data analysis / 新企業の人材確保--事業所・企業統計調査と新企業調査の個票分析 / SME policy, financial structure and firm growth: Evidence from japan / Does the creative business promotion law enhance SMEs' capital investments? Evidence from a panel dataset of unlisted SMEs in Japan / Potential entrepreneurship in Japan / Consumption-leisure preference structure: A new explanation of the Evans-Jovanovic results for entrepreneurial choice / Consumption-Leisure Preference Structure: A New Explanation of the Evans-Jovanovic Results for Entrepreneurial Choice(Erratum, 24, 423-427, 2005) / Does the Creative Business Promotion Law Enhance SMEs' Capital Investment? Evidence from a Panel Dataset of Unlisted SMEs in Japan / The IT revolution and productivity growth in Japan / Small Business Owner-Managers as Latent Informal Investors in Japan: Evidence from a Country with a Bank-based Financial System / 企業家の労働時間－実証分析－ / 景況感とアンケート調査－変化方向と水準は異曲同工か？－ / Productivity and Entrepreneurial Characteristics in New Japanese Firms / Who Succeeds as an Entrepreneur? An Analysis of the Post-Entry Performance of New Firms in Japan / 少子・高齢化と日本の消費フロンティア / SNA統計を用いた「トービンのｑ」の計測結果の違いについて / 潜在的開業者の実証分析 / 起業の意思決定における所得・余暇の代替と流動性制約 / SNA統計を用いた民間法人企業ベースの「トービンのｑ」と投資関数</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>中小企業における労働力の質的不足の影響要因 / 企業の情報開示と株価</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>経済政策 ; 財政・公共経済 ; 経済統計 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 経営工学 ; 行政データ分析 ; 政策評価 ; マーケティング分析</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>経済政策
 財政・公共経済
@@ -1766,7 +1811,7 @@
 マーケティング分析</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>中小企業における労働力の質的不足の影響要因
 企業の情報開示と株価
@@ -1829,6 +1874,11 @@
         </is>
       </c>
       <c r="F10" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>大規模な両面市場に対する公平性を考慮した取引促進施策の包括的最適化
 混合整数最適化による次元縮約法の最良スパース推定
@@ -1895,42 +1945,42 @@
 混合整数2次錐計画法による回帰式の変数選択</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>大規模な両面市場に対する公平性を考慮した取引促進施策の包括的最適化 / 混合整数最適化による次元縮約法の最良スパース推定 / 混合整数最適化を用いた制約付き変数選択による高精度パラメータ推定 / ノンパラメトリック推定に基づくテスト理論モデルの研究 / カーネル法と制御ポリシーを用いた中長期的投資戦略最適化 / 取引コストを考慮した多期間ポートフォリオの最適化</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム / 数理情報学 / 統計科学 / 知能情報学</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>数理最適化 / 金融工学 / 機械学習</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Robust personalized pricing under uncertainty of purchase probabilities / Privacy-preserving recommender system using the data collaboration analysis for distributed datasets / 最適モデル多分木による価格需要曲線の推定 / Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times / DC algorithm for estimation of sparse Gaussian graphical models / Robust Portfolio Optimization for Recommender Systems Considering Uncertainty of Estimated Statistics / Fast Solution to the Fair Ranking Problem Using the Sinkhorn Algorithm / Mixed-Integer Linear Optimization Formulations for Feature Subset Selection in Kernel SVM Classification / Robust portfolio optimization model for electronic coupon allocation / 混合整数最適化による相続工程の長期化リスク採点システム / ECサイトにおける利用者属性データの欠損値補完 / Prescriptive price optimization using optimal regression trees / 構造的正則化処方分析による旅行パックの価格最適化 / Predicting Online Item-Choice Behavior: A Shape-Restricted Regression Approach / Cardinality-constrained distributionally robust portfolio optimization / Cutting-plane algorithm for estimation of sparse Cox proportional hazards models / Branch-and-bound algorithm for optimal sparse canonical correlation analysis / Dynamic portfolio selection with linear control policies for coherent risk minimization / Linear control policies for online vehicle relocation in shared mobility systems / 出産前後の情報検索の分析：数理最適化による検索日の確率分布推定 / ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析) / Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach / Sparse Poisson regression via mixed-integer optimization / 時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析 / データコラボレーション解析における統合関数の最適化 / A Design Method of the Joint Venture Formation in EPC Projects / 形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待) / サポートベクトルマシンとカーネル法 (特集 機械学習の手法と役割期待) / Smoothness-constrained model for nonparametric item response theory / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― / LDPC符号に対するタブー探索法に基づく勾配降下ビット反転復号法 / A Resource Flow Based Multistage Dynamic Scheduling Method for the State-Dependent Work / 数理最適化による学生のプロジェクト配属の決定 / 整数最適化復号法の性能評価 / 多重共線性を考慮した回帰式の変数選択問題の定式化 / A Simulation-Based Dynamic Scheduling Method in Project Cost Estimation Process / キークレーン間干渉を考慮したコンテナ事前配列問題 / 混合整数最適化による階層的変数選択を用いた店舗選択要因の分析 / ZIMPL言語とSCIPによる数理最適化 / 複数の販売チャネルでの購入を促進するための商品推薦手法 / Mathematical Optimization Models for Nonparametric Item Response Theory / 時系列モデルによる商品販促効果の分析 / 整数計画法による変数選択を用いた店舗選択モデル / 競争入札戦略と決定理論モデル / アドネットワークにおけるバナー広告入札戦略決定フレームワークの有効性の検証 / 確率計画法の理論と応用 / ECサイトの商品特性を考慮した2次元確率表による購買予測 / A Heuristic Bidding Price Decision Algorithm Based on Cost Estimation Accuracy under Limited Engineering Man-Hours in EPC Projects / 混合整数2次錐計画法による回帰式の変数選択</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>データ統合解析におけるアンカーデータ作成方法の提案 / 切除平面法による比例ハザードモデルの特徴選択 / 線形制御政策によるロング・ショートポートフォリオ最適化 / データコラボレーション解析における統合関数最適化問題の定式化と解法 / 多値型ノンパラメトリック項目反応理論の形状制約推定モデル / 最適化手法を用いた事例・変数統合型の欠損値補完 / 縮小推定を用いた平均・分散モデルによる推薦システム / 多重共線性を考慮した変数選択問題に対する切除平面法 / 2値分類の採点システムに対するbAUC最大化 / ロバスト平均・分散モデルを用いた推薦アルゴリズム / 確率制約付き最適化問題に対するDCアルゴリズム / シンクホーンアルゴリズムを用いた公平ランキング問題の高速求解 / 多重共線性を考慮した変数選択問題に対する高速厳密解法 / 深層学習を用いた巡回セールスマン問題の高速求解 / 強化学習を用いた競争入札戦略 / 予測評価値の不確実性を考慮した推薦商品集合の分布的ロバスト最適化 / 複数クーポンの効果推定と配布最適化 / コールセンターにおける会話データの分析 / 出産・子育てQ&amp;Aサイトにおける検索クエリの予測と分析 / 疎なWEB解答データの多次元項目反応理論分析</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム ; 数理情報学 ; 統計科学 ; 知能情報学 ; 保険・金融行動 ; オペレーションズリサーチ ; 機械学習 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 物流最適化 ; 最適化</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム
 数理情報学
@@ -1958,7 +2008,7 @@
 最適化</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>データ統合解析におけるアンカーデータ作成方法の提案
 切除平面法による比例ハザードモデルの特徴選択
@@ -2067,6 +2117,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>KPI工学教育研究の推進
 包摂的コミュニティプラットフォームの構築
 健康にやさしいまちづくりのための環境整備に係る実証事業
@@ -2110,42 +2165,42 @@
 Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>KPI工学教育研究の推進 / 包摂的コミュニティプラットフォームの構築 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 統合型ヘルスケアシステムの構築 / 文書生成AIサービス工学に関する研究 / 文書生成AIの企業内利活用における最適化の研究 / 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>会計学 / ウェブ情報学・サービス情報学 / 社会システム工学・安全システム / 経営学 / 商学</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>ビジネスインテリジェンス / 会計情報科学 / サービス工学 / ソーシャル・データサイエンス / 社会工学</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment / Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients / Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach / Estimation of conditional average treatment effects on distributed confidential data / Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support / Data collaboration for causal inference from limited medical testing and medication data / Generating Synthetic Journal-Entry Data Using Variational Autoencoder / Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data / An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises / Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 / pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis / 会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 / Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data / 分散機密データを想定した 処置効果の推定手法の開発 / 英文学術雑誌における近年の簿記研究 / Collaborative causal inference on distributed data / Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach / Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation / Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data / Knowledge sharing among coaches: expert power and social cognitive theory perspectives / Positive effect of proactive personality on customer orientation in service context / Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data / Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>個人の能動的先手行動がチームに与える影響に関する時系列分析 / 若者のエシカル消費の阻害要因に関する実証分析 / チーム全体の能動的先手行動を強化するチーム構成の実証分析 / 中小サービス企業における業績管理会計の効果的な実践に関する実証分析 / 地域健康政策のためのベイジアンネットワークを用いた推論モデルの研究 / シングルサイロを想定した解釈可能なデータコラボレーション解析の応用研究 / 傾向スコアを用いた特定健診・特定保健指導の効果検証 / 価値共創を活性化する店員の音声模倣スキルに関する実験的研究 / 糖尿病の予防政策のためのデータコラボレーション解析の応用可能性 / ベイジアンネットワークを用いたフレイルの発症予測モデリング：健康関心度の違いに着目して / マルチレベルモデルを用いたフレイルの地域および個人要因分析 / 糖尿病の因果構造の推定におけるLingamの応用可能性 / 営業部門の上司と部下の顧客意識が提案行動に与える影響 / 小売店の接客サービス中に生じる頷きの模倣に関する実験的研究 / データコラボレーション解析による地域中小企業の資金ニーズ予測 / NavigatorⅢの開発と実証分析 / 分散データに対する統合的クラスタリングの提案 / 営業チームにおける人事異動が能動的先手行動に与える影響 / 非接触呼吸識別技術によるコンサート観客の呼吸同期分析 / 若者の選挙投票に着目したアカウンタビリティの実験的研究 / 確率的潜在意味解析による擬人情報作成方法の提案 / 社会参加が主観的幸福感に及ぼす効果の疑似実験による検証 / GPSデータを用いた陸運の誤配送検知手法の提案 / 仕訳とビジネスプロセスの月次変化とキャッシュフローに関する研究 / 複式簿記の相互参照性情報を学習した業績予測モデルに関する研究 / 高齢者の運動習慣とメンタルヘルスとの関係の実証分析 / 中小企業の財務難予測モデルを解釈する反事実的説明手法の研究 / 非接触計測による生理指標を用いた患者のマルチモーダル感情認識の研究 / 孤独の選好と身体的・精神的健康状態との関係の実証分析 / 分散生存時間データに対するDC因果推論の拡張 / 能動的先手行動の形成プロセスについての縦断的研究 / 標準年限卒業予測における大学間転移学習の研究 / NavigatorIIIのパイロット企業における実証実験</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>会計学 ; ウェブ情報学・サービス情報学 ; 社会システム工学・安全システム ; 経営学 ; 商学 ; 社会政策・福祉 ; オペレーションズリサーチ ; 政策評価・計量分析 ; 会計・ファイナンス ; 医療・ヘルスデータ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 経営工学 ; 環境工学 ; 社会ネットワーク分析 ; 学習分析</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>会計学
 ウェブ情報学・サービス情報学
@@ -2196,7 +2251,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>個人の能動的先手行動がチームに与える影響に関する時系列分析
 若者のエシカル消費の阻害要因に関する実証分析
@@ -2293,6 +2348,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>ESG、開示とパフォーマンス：ノンパラメトリック手法を用いて
 CSRの実証研究：ノンパラメトリック推計アプローチ
 社会的責任活動の実証研究：企業のミクロ経済学的行動と政策分析
@@ -2307,34 +2367,34 @@
 Nonnegative Bias Reduction Methods for Density Estimation Using Asymmetric Kernels</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>ESG、開示とパフォーマンス：ノンパラメトリック手法を用いて / CSRの実証研究：ノンパラメトリック推計アプローチ / 社会的責任活動の実証研究：企業のミクロ経済学的行動と政策分析</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Subjective probabilistic expectations, household air pollution, and health: Evidence from cooking fuel use patterns in West Bengal, India / Seemingly Unrelated Interventions: Environmental Management Systems in the Workplace and Energy Saving Practices at Home / Cooking Fuel Choices --Analysis of Socio-economic and Demographic Factors in Rural India-- / Another Bias Correction for Asymmetric Kernel Density Estimation with a Parametric Start / Functional-Coefficient Cointegration Models in the Presence of Deterministic Trends / Do Social Norms Matter to Energy Saving Behavior?: Endogenous Social and Correlated Effects / Testing Symmetry of Unknown Densities via Smoothing with the Generalized Gamma Kernels / Family of the Generalised Gamma Kernels: A Generator of Asymmetric Kernels for Nonnegative Data / Nonnegative Bias Reduction Methods for Density Estimation Using Asymmetric Kernels</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>交通ネットワークと都市の成長ー西日本における高速道路建設が地方都市に与えた影響ー / 中国における結婚が健康に及ぼす影響 / 日本の賃金分布に対する反実仮想的要因分解 / ESGに関するSNS上での評判と企業パフォーマンス / 駅の開業が大気汚染に与えた影響の分析</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>保険・金融行動 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; マーケティング分析 ; 社会ネットワーク分析 ; 経営工学</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>保険・金融行動
 政策評価・計量分析
@@ -2353,7 +2413,7 @@
 経営工学</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>交通ネットワークと都市の成長ー西日本における高速道路建設が地方都市に与えた影響ー
 中国における結婚が健康に及ぼす影響
@@ -2402,6 +2462,11 @@
         </is>
       </c>
       <c r="F13" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析
 新規投資家の継続的な参入が価格形成・価格変動に与える影響
@@ -2441,42 +2506,42 @@
 A quantitative easing experiment</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析 / 新規投資家の継続的な参入が価格形成・価格変動に与える影響 / ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響 / 信用スコア社会に対応可能な評判管理システムの設計 / 験財消費のための情報収集行動とその支援情報提供システム / 市場参加者の価格予測の異質性と市場の振る舞いの関係について / 情報の非対称性と多様な期待形成がもたらす金融市場への影響とその安定化政策について / 国家の規模とガバナンスの学際的分析 / 情報コストゼロ社会における過剰懲罰とリスク軽減のための社会制度設計 / 新しい肺移植制度の構築と評価：ドナー交換移植の可能性</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>社会的ジレンマ、資産市場実験</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>検索連動型広告における循環的な入札額変動の発生機構の解明 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Bubbles in Asset Markets and the Heterogeneity of Beliefs. / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 / 進化ゲーム理論の進化 — マルチエージェントシミュレーション，実験室実験と，LLM の行動経済学— / 発話量と発話内容に基づく集団間のコミュニケーション円滑化システムの提案 / ソーシャルメディア上のアジェンダ設定がエコーチェンバーの発生に与える影響について / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. / Emergence of echo chambers in social media communication involving multiple topics / 進化ゲーム理論の進化：マルチエージェントシミュレーション, 実験室実験と，LLMの行動経済学 / 重みが動的なネットワークにおいてネットワーク構造が協力の進化に与える影響 / 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ / Individuals reciprocate negative actions revealing negative upstream reciprocity / SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. / Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement / Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim / パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 / 群淘汰状況下における罰則・報酬の進化 / Self-organized Speculation Game for the spontaneous emergence of financial stylized facts / 情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ / 時間制約を導入したゴミ箱モデル / Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment / 協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 / A quantitative easing experiment</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>条件付き協力のためのコストの存在が、ネットワーク上での協力の進化に与える影響 / 自動運転配車サービスが東京中心部の交通形態に与える影響の分析 / 問題の難易度と意思決定数の関係に双曲志向が与える影響-ゴミ箱モデルによるアプローチ- / 多重ネットワーク上での協力の進化 〜相互作用ネットワークと戦略更新ネットワークの非対称性が協力の進化に与える影響〜 / 重みが動的なネットワークにおいてネットワークトポロジーが協力の進化に与える影響 / リンク重みの異質性と情報開示率が協力の進化に与える影響 / ソーシャルメディア上での複数のトピックにわたるコミュニケーションが意見の分極化とエコーチェンバーの発生に与える影響 / 純粋リスク下において他者の選択がリスク態度に与える影響：経済実験によるアプローチ / 間接互恵による協力進化に記憶の減衰が与える影響 / 歩行者ラウンドアバウトによる整流効果-駅構内の混雑緩和- / 投機的リスク下でのピア効果がリスク態度に与える影響 / 懲罰に関する社会規範が間接互恵の進化に与える影響について:シミュレーションによるアプローチ</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム ; 保険・金融行動 ; 意思決定分析 ; マッチング理論・ゲーム理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 学習分析 ; マーケティング分析</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム
 社会的ジレンマ、資産市場実験
@@ -2508,7 +2573,7 @@
 マーケティング分析</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>条件付き協力のためのコストの存在が、ネットワーク上での協力の進化に与える影響
 自動運転配車サービスが東京中心部の交通形態に与える影響の分析
@@ -2587,6 +2652,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>「もう一つのモダニズム」による地域性の再構築 フェルナン・プイヨンの生涯業績
 中東・北アフリカ地域におけるヘレニズム基盤の継承に関する都市文献史的研究
 西アジア地域の都市空間の重層性に関する計画論的研究
@@ -2633,42 +2703,42 @@
 ビルマ王都マンダレーの城内および城外市街地の空間構造に関する研究</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>「もう一つのモダニズム」による地域性の再構築 フェルナン・プイヨンの生涯業績 / 中東・北アフリカ地域におけるヘレニズム基盤の継承に関する都市文献史的研究 / 西アジア地域の都市空間の重層性に関する計画論的研究 / 日本の貢献を踏まえた中東・北アフリカ地域の都市計画史-「イスラム都市」論を越えて / チュニジア－日本シンポジウム「イノベーティブ社会構築に向けたマネジメント戦略」 / アレッポの戦災状況調査と戦災復興都市計画原案の策定 / 多様性と共生の知恵を育む中東・北アフリカ地域の都市計画史 / 国際交流を背景とした中東都市計画史研究と都市保全プロジェクトへの還元 / モロッコの歴史都市 フェスの保全と近代化 / 現代イスラーム都市の多元的成り立ちに関する研究</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>都市計画・建築計画 / 建築史・意匠 / 地域研究</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>建築・都市計画史 / 地中海都市 / ヘレニズム基盤 / 歴史文化保全 / 国際協力 / 中東・北アフリカ</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” / フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― / 吉田正春使節団が見た19世紀テヘラン都市改造 / ジスカール・デスタン政権下のパリ歩行者空間整備 / 1960 年アガディール地震とその震災復興都市計画に関する研究 / フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 / フェルナン・プイヨンのベルカステル村修復に関する研究 ─城と村の一体性に着目して─ / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス / 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 / フェス 積み重なる寄進が形成した迷宮都市 / ガルダイア 丘の上の城塞とオアシス渓谷の集落 / Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development / The Urban Forming History of Dubrovnik During the 12th Until 17th Century / Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning / Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration / カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- / Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris / Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille / The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel / アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 / 19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 / 商業都市カサブランカにおけるトラム導入による社会空間変容 / ビルマ王都マンダレーの城内および城外市街地の空間構造に関する研究</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>ポルトガル植民地期におけるリオ・デ・ジャネイロの都市空間変容 / 戦後パリ郊外におけるフェルナン・プイヨンの住宅地計画 -アルジェ及びマルセイユの作品との比較から- / 中国・杭州市における近代宗教建築の展開 –1840〜1949年に建設されたキリスト教建築を対象に– / メキシコシティ旧水路空間の変遷に見る水都空間の重層性 / アンナバ新市街における伝統的商業空間の形成 / カイロ中心市街地の都市空間変容-イギリス統治下から共和制移行期に着目して / 乾燥地域における伝統的水利システムの洪水抑制効果―アルジェリア国ガルダイア県の事例― / 現チェコ共和国の諸地域におけるカミロ・ジッテの都市計画実作 / フェルナン・プイヨンのベルカステル村修復に関する研究-城と村の一体性に着目して- / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス / 上海・上生新所の都市イノベーション-歴史保全と現代的開発の融合- / 海上シルクロード都市ザイトゥーン（中国・泉州）における遺産の保全と活用 / A Historical Survey of Spatial Customisation in the Modern Planned City of Abuja, Nigeria</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>都市計画・建築計画 ; 建築史・意匠 ; 地域研究 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 都市計画 ; 社会ネットワーク分析 ; 人間中心設計 ; 災害分析</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>都市計画・建築計画
 建築史・意匠
@@ -2703,7 +2773,7 @@
 災害分析</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>ポルトガル植民地期におけるリオ・デ・ジャネイロの都市空間変容
 戦後パリ郊外におけるフェルナン・プイヨンの住宅地計画 -アルジェ及びマルセイユの作品との比較から-
@@ -2783,6 +2853,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>衛星情報を利用した物流における大気環境改善の評価
 独占的競争下での環境オフセットの自発的供給に関する研究
 都市における環境リスクの軽減の経済効果に関する研究
@@ -2820,42 +2895,42 @@
 東京都心部における賃貸集合住宅価格の付加価値要因に関する研究</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>衛星情報を利用した物流における大気環境改善の評価 / 独占的競争下での環境オフセットの自発的供給に関する研究 / 都市における環境リスクの軽減の経済効果に関する研究 / Radon測度上の動的システムの研究と都市構造遷移モデルへの応用 / 新たな集積効果関数を用いた都市一般均衡モデルの構築 / 通信技術の発達と住宅地地価の都市経済的分析 / 通信技術革新と都市空間構造の自己組織化 / 海外における中間財生産による国内都市空間構造の変化に関する研究 / 都市内立地の内生的決定に関する数値計算的アプローチ / 都市内情報流を考慮した空間構造の自己組織化</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>経済政策 / 理論経済学</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>都市構造</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Dual Chalcogen-Bonding Interactions for the Conformational Control of Urea / Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Life Cycle Analysis and Cost–Benefit Assessment of the Waste Collection System in Anyama, Cote d’Ivoire / Green Markets, Free Riders, and Monopolistic Competition / Relationship between urban population growth and utility level of workers with heterogeneity of labor efficiency / Environmental offsets and production externalities under monopolistic competition / Implications of urbanization and Impact of Population Growth on Abidjan City, Cote d’Ivoire / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― / 通信技術革新と企業内立地行動の変化に関する研究-通信の固定費用を考慮して- / 通信技術革新と企業内立地行動の変化に関する研究 / Communication technologies and spatial organization of multi-unit firms in metropolitan areas / 企業の分離立地にともなう副都心成立の均衡土地利用分析 / The Influence of the Great Hanshin-Awaji Earthquake on Housing Market of the Area / 東京大都市圏の効用分布の推計と住居選択モデルの応用可能性に関する研究 / テレコミューティングの普及と都市構造に関する研究 / 複数都心を持つ都市構造の動的安定性に関する研究 / 首都圏における通勤家計の居住地選択モデル / 2種類の企業による都市の均衡形状に関する研究 / 大都市圏における近年のテレコミューティング（在宅勤務）と都市構造の均衡分析 / 東京都心部における賃貸集合住宅価格の付加価値要因に関する研究</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>広域行政が自治体の財政に与える影響 / 長時間労働が中国人の健康に与える影響に関する研究 / 中国・広州市における高齢者施設の空間的アクセシビリティ評価 / 羽田空港の新飛行経路の騒音は周辺住宅価格への影響 / 中国の住宅資産と負債が高等教育進学率への影響と性別差異 / ネット・口コミが消費者行動に与える影響に関する研究～丸亀製麵を例として～ / 地方都市の駅まち空間再構築事業による地価変化の計量分析 / 地方都市におけるスマートシティ事業の実装が地価に与える影響 / 鉄道廃線敷のBRT化が地域に与える影響について / 中国における農村金融の格差に関する影響要因分析及び政策分析。ー中国“十二五”計画を中心に / 「国立公園満喫プロジェクト」が関連地域の地価に与える影響ー先行８公園を対象としてー / ハイテク企業のイノベーションが地価に与える影響 / 中国におけるライブコマースが農村振興に与える影響に関する分析 / 国際スポーツ大会の開催決定がスタジアム周辺地域に与える影響についての研究―地価の変化に注目して― / Park-PFIによる公園整備が商業地域の地価に与える影響 / ウォーカブル向上による関連地域の地価変化に関する研究 / 水害についてのリスク認識の変化が地価に及ぼす影響 / 高速鉄道が沿線地域に与える影響の実証研究―徐蘭高速鉄道を例として― / 中国における子供性別が家計の資産配分に与える影響―不動産を研究対象として― / LRT導入による地価への影響―宇都宮ライトレールを事例として―</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>経済政策 ; 理論経済学 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 画像・視覚情報処理 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 物流最適化 ; 災害分析 ; 社会ネットワーク分析 ; 行政データ分析</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>経済政策
 理論経済学
@@ -2905,7 +2980,7 @@
 行政データ分析</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>広域行政が自治体の財政に与える影響
 長時間労働が中国人の健康に与える影響に関する研究
@@ -2990,6 +3065,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>ジェネレーティブデザインを通じて敷地計画における創造力はどこまで拡張できるか
 創造性の論理的・ 技術的探求に基づくデザイン共創環境の構築と教育プログラムの開発
 コンパクトシティを目指した都市デザイン戦略のための都市構造評価指標の探究
@@ -3029,42 +3109,42 @@
 土地利用の混在指標を用いたわが国の都市圏の形態分析 ―埼玉県東部を対象としたMetropolitan Form Analysis― Land-Use Mixの適用―</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>ジェネレーティブデザインを通じて敷地計画における創造力はどこまで拡張できるか / 創造性の論理的・ 技術的探求に基づくデザイン共創環境の構築と教育プログラムの開発 / コンパクトシティを目指した都市デザイン戦略のための都市構造評価指標の探究 / 伝統的市街地の景観形成支援手法の研究 / 博士課程「短期在学コース」の創設に関わる課題等に関する調査研究 / 伝統的都市の現代化における空間制御を支援する情報技術の開発 / 伝統的都市の現代化における空間制御技術に関する研究 / 「建築情報モデラーに関する研究」に対する / ポスト定住化社会における時空を超えたアクティビティの流動化実態に関する実証的研究 / 拡張現実技術を利用した実空間景観シミュレーションシステムの開発</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>都市計画・建築計画 / 社会システム工学・安全システム</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>情報化・ネットワーク社会における建築計画・都市計画</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>歩行者の空間学習を支援するナビゲーション手法に関する研究 / 超一線都市の若者向けマンションの立地分析：広州を例にして / 街路網の広がりから見た城下町の空間構成の変容に関する研究 / 総合設計制度による建築物が街路景観の印象に与える影響に関する研究 ―3D都市モデルPLATEAU及びVR を用いて― / 都市の集約化が分散型エネルギーシステム導入に与える影響について / デザイン共創環境を用いた集合住宅設計支援ツールの開発 / An analysis on urban shrinkage trends of all Japanese cities by detecting relative densely inhabited districts - Changes in urban form of Japanese cities in an era of shrinking population, part 2 / モビリティ技術活用による新しい児童通学スタイルの検証 / デザインパターンの列挙に関する一考察 / 相対的な人口集中地区の抽出を通じた全国市町村の都市縮小傾向の分析 －人口減少時代を迎えるわが国の都市圏の形態変化に関する研究（その2）－ / Exploring the Panel Exercises in the Modulor as presented by Le Corbusier / 歩行空間ネットワークを用いた駅周辺の回遊性に関する研究 －埼玉県大宮駅周辺を事例として－ / ル・コルビュジエが提示したモデュロールによる羽目板遊びの探求 / 中国安慶市の敬老院における整備実態の居住者の満足度に関する研究 / BIMと修繕記録を用いた既存建物の部位等の更新間隔算出 / 共育 ～ともに育て、ともに育つ保育園～ / ソーシャルメディアの投稿写真からみた地域特性に関する考察 / 媒介中心性を用いた歩行者の回遊行動に関する検討 - Walkability 指標の計測へ向けて - / 情報量損失最小化法を応用した相対的人口集中地区の抽出; 都市縮小・拡大市町村数の経年変化分析 / 上海中心市街地におけるGated Communityが飲食店への徒歩到達アクセシ ビリティに与える影響 / デジタル・モデュロール３ / AN ANALYSIS OF MIXED LAND USE TOWARD DESIGNING THE COMPACT CITY / 都市のWalkabilityに関する研究 ―Urban Network Analysisを用いた評価指標計算に向けて― / 土地利用の混在指標を用いたわが国の都市圏の形態分析 ―埼玉県東部を対象としたMetropolitan Form Analysis― Land-Use Mixの適用―</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>市民の屋外公共空間活用に対する自治体の支援実態とその在り方ー市民の屋外空間における音楽活動支援に着目してー / 景観計画下での屋外広告物等の実態と伝統的都市景観に対する若者の景観認識—京都市を事例に— / 発達障害者の空間認知からみたナビゲーションのあり方に関する研究 / 中国における大学城の土地用途変遷と利用者の満足度について—呼蘭、下沙、広州大学城を対象にして— / デザイン共創環境を用いた集合住宅設計支援ツールの提案 / 中国旧市街地のゲーテッドコミュニティの再生に関する研究 ー河南省鄭州市を事例としてー / 都市の集約化と分散型エネルギーの導入適性に関する研究 / 総合設計制度による建築物が都市空間に与える圧迫感に関する研究-3D都市モデルPLATEAU及びVRを用いて- / 歩行者の空間学習に関する研究－ナビゲーション手法と環境的特徴に着目して－ / 超一線都市の若者向けマンションの立地分析と最適化－広州を例にして－</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>都市計画・建築計画 ; 社会システム工学・安全システム ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 都市計画 ; 数理最適化 ; 環境工学 ; 強化学習</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>都市計画・建築計画
 社会システム工学・安全システム
@@ -3103,7 +3183,7 @@
 強化学習</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>市民の屋外公共空間活用に対する自治体の支援実態とその在り方ー市民の屋外空間における音楽活動支援に着目してー
 景観計画下での屋外広告物等の実態と伝統的都市景観に対する若者の景観認識—京都市を事例に—
@@ -3180,6 +3260,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>まちづくりを含む不動産開発に関する指導
 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究
 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会
@@ -3226,42 +3311,42 @@
 地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>まちづくりを含む不動産開発に関する指導 / 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 超高層住宅の二重の老いの潜在的課題に関する研究 / 社会的孤独の解消モデル事例のプロセス分析及び検証手法の検討 / つくば市みどりの分譲地のまちづくり提案について / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築 / 超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>都市計画・建築計画</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>都市計画 / 地区計画 / まちづくり / カナダの都市計画 / 団地再生 / 住環境整備 / 産官学民連携 / 地域活性化 / コミュニティビジネス</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として / わがまちのSDGs / 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ / 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 / 京都市東松ノ木市営住宅 / 国勢調査分析からみる外国人集住団地の実態 / 増加する外国人の受け皿としての住宅団地 / 住宅団地の外国人集住：特集の趣旨 / 住宅地における地区計画や認可協定の今後 / 区分所有マンションを含む市街地再開発事業の有効空地を考える / 社会的包摂とデザイン─「つながる場」15事例の実践から / 外国人住民との共存・共生: 海外の事例からの示唆 / 首都圏郊外におけるリノベーションまちづくりの成果と課題に関する研究 / 住宅建替えと一体的に再整備された街区公園の維持管理活動を通じたコミュニティ形成に関する研究 / 計画的戸建住宅地における駐車場シェアの導入意向と活用可能性に関する研究 / 多様な主体が関わる出産祝いプロジェクトの成立経緯と参加主体にもたらす変化に関する研究 / 職員の活躍を願う市長の思いと取り組み / 今後の地域づくりへの期待 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea / 転換期にある筑波研究学園都市の地区計画が空間資源継承に果たす役割と課題 / 1980年以降、40年の「つくば」の変化と現状 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea, Urban Planning / Living Lab Participants’ Knowledge Change about Inclusive Smart Cities: An Urban Living Lab in Seongdaegol, Seoul, South Korea / 地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>計画的戸建住宅地におけるスペース・シェアリングの展開可能性と受け入れ条件の検討 / 転換期にある筑波研究学園都市の地区計画が地域資源継承に果たす役割と実態 / 地域課題解決に取り組む空き家の活用過程の課題に関する研究―茨城県常総市水海道地区を対象にー / 筑波研究学園都市における市民に向けたサイエンスコミュニケーションの実態と課題 / 絶対高さ型高度地区導入後の展開と課題 / 高齢者情報格差の実態と対応策の検討：つくば市スーパーシティモデル地区を対象に / 民俗芸能の継承と観光活用意向に関する研究―岩手県北上市に着目してー / スペースシェアリングを活用した計画的戸建住宅団地の再生方策に関する研究 / 人材育成事業を契機とした地域活動拡大に関する研究 / 大都市郊外住宅団地における多世代交流活動の展開に関する研究 / 工業地帯の土地利用転換による知識集約型産業集積の実態と課題 －スペイン・バルセロナ市22＠プロジェクトを対象として－ / ごちゃまぜを理念とする多機能型福祉拠点の成立要因と意義に関する研究 －石川県社会福祉法人佛子園「三草二木 西圓寺」を対象として－ / 移住増加地域における遊休不動産を活用した新規事業の成立要因に関する研究 －長野県小諸市中心市街地を対象として－ / 超高層住宅集積地における利活用・維持管理の実態を踏まえた公開空地等の課題に関する研究 －東京都中央区第3ゾーンを対象として－</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>都市計画・建築計画 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 都市計画 ; 社会ネットワーク分析 ; 人間中心設計 ; 行政データ分析</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>都市計画・建築計画
 都市計画
@@ -3302,7 +3387,7 @@
 行政データ分析</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>計画的戸建住宅地におけるスペース・シェアリングの展開可能性と受け入れ条件の検討
 転換期にある筑波研究学園都市の地区計画が地域資源継承に果たす役割と実態
@@ -3383,6 +3468,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>つくば茅ラブプロジェクト：環境保全に資する茅葺きの持続利用技術および社会教育システムの開発
 地域連携による新たな戸建て活用型住宅セーフティネットシステムの提案
 かすみがうら市の歴史的建築物活用にかかわる調査研究
@@ -3427,42 +3517,42 @@
 既存建築ストックを活用したサテライトオフィスの誘致プロセスとその実態 福井県鯖江市を対象として</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>つくば茅ラブプロジェクト：環境保全に資する茅葺きの持続利用技術および社会教育システムの開発 / 地域連携による新たな戸建て活用型住宅セーフティネットシステムの提案 / かすみがうら市の歴史的建築物活用にかかわる調査研究 / 石岡市看板建築及び里山景観等調査研究 / 地球規模的課題解決のための全学的広域分野横断型研究推進プラットフォームの構築 / 農村移住者の宿泊滞在施設運営と地域交流活動による新たな都市農村交流の展開可能性 / 茨城版ＳＤＧｓを推進する産学研究 / 次世代の茅葺きの再生・導入に関する共同研究拠点の形成 / 相続工学に関する共同研究</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>都市計画・建築計画</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>過疎地域 / 農村地域 / 移住・定住 / 古民家 / 空き家 / 廃校 / 地域組織</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 農山村地域に立地するゲストハウスの地域活性化に向けた取り組み 九州・中国・四国地方の基礎調査 / 地域おこし協力隊の任期終了後の定住率と進路及び地域特性との関連分析 全国の自治体データを対象として / 農地における規模別の太陽光パネル設置要因の分析 / 自治体担当課による地域コミュニティ活動のフォローアップと施策立案に関する研究 都市的地域と農村地域が合併した自治体を対象として / 北関東地域における高齢者通所介護サービスの需給構造と将来推計(その2)：市場均衡条件を組込んだ需要供給量推計（2020～2045） / 木造板倉仮設住宅の再利用事例における平面構成の変化と住まい方 / 移住者主体による交流の場の形成過程と効果−茨城県石岡市八郷地域を事例として− / 農村地域の宿泊滞在施設における地域交流活動の実態調査−九州・中国・四国地方のシェアハウスを対象として− / 北関東地域における高齢者通所介護サービスの需給構造と将来推計（その1）：利用者数と供給量の推移を指標とした県別市場特性分析（2000～2019） / 農村集落の電力オフグリッド化の可能性に関する研究―石岡市上山集落を対象として― / 市町村合併により生じた旧市街地の振興における行政支援の手法について－つくば市周辺市街地振興における地域運営組織と外部人材との協働支援を事例として－ / 関係人口の居住地と訪問先との距離が地域とのかかわり方に与える影響－茨城県を対象として－ / 多様な主体が連携する「新しい内発的発展」を支える地方自治体の取り組みについて－つくば市周辺市街地振興を事例として－ / 木造民家を活用した高齢者通所介護施設の空間用途構成に関する研究（その1）：民家の平面構成と主用途の空間配置 / 現代建築への茅葺きの導入可能性に関する研究 / 木造公共建築の用途と建築規模による特徴把握と実現手法の分析 新建築掲載事例を対象として / 現代の茅葺き構法に関する研究−兵庫県神戸市の事例を対象として− / 既存建築を活用した自立高齢者地域支援拠点の運営形態と平面構成—土浦市「生きがい対応型デイサービス事業」を対象として— / 大規模高齢者通所介護施設における主室の用途構成と使われ方 / 萩市における医療法人による高齢者福祉施設の整備運営に関する事例研究（その２）：木造民家を改修した通所介護・介護予防施設の使われ方 / 食堂兼機能訓練室と和室が一体的に構成された小規模高齢者通所介護施設の使われ方 / 社会福祉協議会による中山間地域における高齢者福祉施設の整備運営の取組み（その２）：下関市社会福祉協議会による中山間地域における高齢者福祉施設の整備プロセス / 農村系長屋門の利用の変遷と利活用実態 茨城県つくば市桜地区を対象として / 既存建築ストックを活用したサテライトオフィスの誘致プロセスとその実態 福井県鯖江市を対象として</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>中国・四国地方の過疎市町村における​若年層の移住要因に関する研究​ / 地域組織による移住者受け入れ体制と​定着支援に関する研究​ー中国・四国地方を対象としてー​ / 自治体内における中心部と周縁集落間の往来による集落維持に関する研究ーつくば市筑波地区を対象としてー / 長屋門の利用の変遷と屋敷の利活用実態に関する研究ーつくば市を対象としてー / 外国人経営者による古民家活用に関する研究​ー京町家を宿泊施設に転用した事例を対象としてー / 要介護認定者数推計を基にした高齢者福祉介護施設の充足率推計ー茨城県を対象としてー / 介護保険制度の導入と改正が高齢者通所介護施設供給に及ぼした影響ー北関東三県における運営主体に着目した分析ー / 個人や団体による空き家活用の手法に関する研究 −茨城県内の活用事例を対象として− / 立地・建物の条件不利な廃校の​活用実態と民間活用手法に関する研究​ ​−関東地方の過疎地域を対象として−​ / 現代板倉構法の普及実態と木材生産供給体制に関する研究​ / 地域おこし協力隊の任期終了後における地域定住要因の分析 / 地域連携・協働運営による小規模小学校の存続意義に関する研究ー1自治体1校を対象にー / 外国人留学生の共同住宅としての空き家活用の効果と地域との関わりー茨城県利根町の日本語学校留学生を対象としてー</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>都市計画・建築計画 ; 都市・地域政策 ; 建築・空間設計 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 環境工学 ; 社会ネットワーク分析 ; 政策評価 ; 都市計画</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>都市計画・建築計画
 過疎地域
@@ -3496,7 +3586,7 @@
 都市計画</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>中国・四国地方の過疎市町村における​若年層の移住要因に関する研究​
 地域組織による移住者受け入れ体制と​定着支援に関する研究​ー中国・四国地方を対象としてー​
@@ -3576,6 +3666,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発
 ネットワーク上の時間軸をもった最適化問題とその応用
 スタッフスケジューリングに関する研究
@@ -3614,38 +3709,38 @@
 A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 / ネットワーク上の時間軸をもった最適化問題とその応用 / スタッフスケジューリングに関する研究 / 組合せ最適化，ネットワーク最適化のアルゴリズム開発 / ネットワーク構造解析アルゴリズムの開発とネットワークアルゴリズムの総合的展開 / ネットワーク理論の基盤整備と伸張 / データの精度を考慮した組合せ最適化問題に対する問題構造とアルゴリズムの研究 / 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>最適化 / 組合せ最適化 / アルゴリズム</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs / Break maximization for round-robin tournaments without consecutive breaks / Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm / Height Estimation for Abrasive Grain of Synthetic Diamonds on Microscope Images by Conditional Adversarial Networks / Designing of OTN/WDM networks withrecovery methods for multiple failures / Restaurant Sales forecasting with feature interaction-learning mechanism based neural network model,IEEE International Conference on Big Data / A Discrete JAYA Algorithm for Long-Term Carpooling Problem / Carry-over Effect Values Minimization under Circle Method and Binary Factorization Based on Jaya Algorithm / Application of Data Anonymization to Smartphone Apps Usage Logs / 数理最適化を用いたサービス工学の事例―通勤カープールの実証実験― / Four-level knowledge graph contrastive learning structure for smart-phone application recommendation / A New Approach to Market Segmentation Based on 2-Dimensional Tables / Challenges of commuter carpooling with adapting to Japanese customs and regulations: A pilot study / Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model / Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan / Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament / 交換移植制度におけるドミナントマッチングの適用可能性 / Network Design Models with Partial Protection Schemes against Multiple Failures under Optical- Channel Data Unit Constraints / ILP models and improved methods for the problem of routing and spectrum allocation / A novel channel-based model for the problem of routing, space, and spectrum assignment / NASH EQUILIBRIA FOR INFORMATION DIFFUSION GAMES ON WEIGHTED CYCLES AND PATHS / Strongly separable matrices for nonadaptive combinatorial group testing / Modeling and Evaluating Taxi Ride-sharing for Event Trips / 不均衡データに対する多段階学習を用いた アンサンブルモデルによる2 クラス分類アルゴリズムの提案 / A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>外国人居住者向けWebサイトのアクセスログ解析による主要な遷移の特定 / 並列機械バッチスケジューチング問題に対するヒューリスティックアルゴリズム / ネットワーク拡張ゲームの均衡解を求める一解法 / 市場分析における遺伝的アルゴリズムを用いたサンプルデータ抽出 / 光通信ネットワークの耐故障二層モデルの比較と評価 / 深層学習を用いた平面画像上の物体の高さ推定 / ブレークに関する公平性を考慮した総当たり戦スケジューリング / プラスチック製部品製造工場における成形工程の生産スケジューリングモデル化と実応用 / 実応用にむけた多品種少量生産スケジューリング / byesを用いたスポーツスケジューリングの移動距離に関する検討 / ジョブショップスケジューリングの実応用へ向けた二つのアプローチ / 欠勤者を考慮した通勤カープールモデルの提案 / 2部グラフ上のポピュラーマッチングの要素数に着目した特徴づけ / スポーツ競技のスケジュール作成における Carry-Over Effect 値最小化に関する検討 / 次世代光伝送網における資源割り当てIPモデルとヒューリスティックアルゴリズム / 深層学習を用いたレストラン売り上げの予測モデルの構築と実応用 / 安全性と日本の法規制を考慮した通勤カープールモデルの提案と評価 / テクスチャ解析手法による2次元画像の砥粒群の形状分類 / 飲食店におけるスタッフのスキルを考慮したシフト作成のモデル構築と自動化 / 耐故障性を持つ二層光ネットワーク設計問題 / 飲食店の業務標準化に向けた最適な調理手順モデリング / 並列機械スケジューリング問題における多様な解の生成 / 空間分割多重光伝送網における通信保護を考慮した資源割当問題の効率的計算方法の検討 / ジョブショップスケジューリング問題に対する深層学習を用いたヒューリスティックアルゴリズム / A Contrastive Learning Structure for Prediction of smartphone applications to use next / 知識グラフの対照学習におけるグラフサンプリング手法の検討 / 大規模なカープーリング問題に対するK-medoidsクラスタリングを用いた二段階アルゴリズム / データ匿名加工手法のスマートフォンアプリ利用ログへの適用可能性 / 光通信ネットワークにおけるスプリットスペクトルを取り入れた資源割当モデルの提案 / ネットワーク上の耐故障性のある centdian 配置問題 / スマホアプリデータにおける推薦システムの活用 / 動的最短経路阻止モデルの拡張と観察 / 総当たり戦における試合間隔差の最小化問題 / 双曲空間とグラフニューラルネットワークを用いたCross-Domain推薦システムモデル / 高次元データに対するクラスタリングアプローチ / 高齢者通所介護施設における訪問時刻幅を持つ送迎サービスモデル / 訪問介護における訪問順序の最適化 / 待ち時間を考慮した通勤カープールモデル / 試合間隔の公平性を考慮した同時制約を持つ対戦表作成 / 飲食店の調理スケジューリング問題に対するメタヒューリスティクスの適用 / 光ネットワーク上の資源割当問題における候補パスの選択 / Pointer Networksを用いた飲食店における調理スケジューリング</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 社会ネットワーク分析 ; ネットワーク科学</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>最適化
 組合せ最適化
@@ -3664,7 +3759,7 @@
 ネットワーク科学</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>外国人居住者向けWebサイトのアクセスログ解析による主要な遷移の特定
 並列機械バッチスケジューチング問題に対するヒューリスティックアルゴリズム
@@ -3772,6 +3867,11 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>特殊詐欺に「騙されても被害に至らない」社会システムの構築に向けた実証研究
 情報提供と環境手がかりによる行動変容：ナッジ犯罪予防の定式化とその効果検証
 日本における農村犯罪学の創成に向けた萌芽研究：窃盗犯を事例とする実態分析
@@ -3816,42 +3916,42 @@
 サイバー・フィジカル空間上の社会的交流と居住地の近隣環境</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>特殊詐欺に「騙されても被害に至らない」社会システムの構築に向けた実証研究 / 情報提供と環境手がかりによる行動変容：ナッジ犯罪予防の定式化とその効果検証 / 日本における農村犯罪学の創成に向けた萌芽研究：窃盗犯を事例とする実態分析 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / 安全と身体活動を両立するActive School Travelの探究と都市計画・デザイン手法の確立 / 地理空間ビッグデータを用いた犯罪の時空間分析と社会実験への展開 / 警察の情報発信における「信頼」－行動科学・倫理学・政策科学からの学際的問題解決 / 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究 / 集合住宅における子ども・女性に対する犯罪の実態分析と対策立案 / 地理的犯罪予測の手法構築‐学際研究と産官学連携による学術基盤の確立とシステム開発</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム / 都市計画・建築計画 / 環境農学（含ランドスケープ科学）</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>都市計画 / 犯罪科学 / 空間情報科学 / 環境心理学</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて / 都市公園における逸脱行為に関する縦断的研究 / 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 / Mechanisms contributing to road network growth in volunteered street view imagery data / 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して / 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として / 人口低密度地域における人々の活動から見た「都市の活力」の計測 / 全国のJAを対象とする果物盗被害に関するアンケート調査報告 / Regional variations in key factors of children's independent mobility across Japan / 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 / Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives / Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) / Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning / 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 / GPSロガーを用いた官民による果樹盗パトロールの計測 / 子供の前兆事案被害情報の主体間共有の実態 / 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 / Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) / 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して / GPSログに基づく行動推定データを用いた人々の社会的接触可能性の時空間的把握 / サイバー・フィジカル空間上の社会的交流と居住地の近隣環境</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>COVID-19緊急事態宣言に伴う社会変化と犯罪の関連 / 小規模公園の廃止プロセスの実態と評価：社会受容と地域活性化の視点から / Methodology for applying a crowdsourced street view imagery data to evaluate street-level greenness / 留学生の帯同家族におけるソーシャルサポートの実態 / 子供を対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因 / 余暇歩行と近隣の土地利用の配置及び道路構成パターンとの関連 - GULPデータを用いて - / 地方部におけるSNSを介した観光関連情報の授受と観光行動や旅行地に対する愛着の関係 / 子どもを対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因 / 自主防犯行動促進の観点から見た警察SNSの評価 / 新たな防犯活動としての「ながら見守り」の実態と評価 / 多拠点生活者の特徴からみた地域への参入可能性の解明 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 / 刑務所出所者の地域生活定着に向けた訪問支援制度の実態と評価 / 若年層のサイバー・フィジカル空間におけるパーソナルネットワークと個人・居住地特性 / 筑波研究学園都市における公務員宿舎の廃止・再開発が人口移動・住民構成・コミュニティ活動に与える影響 / 人々の社会的接触可能性の時空間的把握とその要因：人口低密地域での検討 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム ; 都市計画・建築計画 ; 環境農学（含ランドスケープ科学） ; 意思決定分析 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 建築・空間設計 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 農業情報学 ; 災害分析 ; 環境工学</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム
 都市計画・建築計画
@@ -3904,7 +4004,7 @@
 環境工学</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>COVID-19緊急事態宣言に伴う社会変化と犯罪の関連
 小規模公園の廃止プロセスの実態と評価：社会受容と地域活性化の視点から
@@ -3987,6 +4087,11 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として―
 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討
 リアルタイム場面におけるサービス・インタラクション理論の構築と実証
@@ -4027,42 +4132,42 @@
 Analogical decision making in career choice</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として― / 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討 / リアルタイム場面におけるサービス・インタラクション理論の構築と実証 / 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 / 慢性ストレスがヒトの生理心理状態に与える影響とその対処法 / 犯罪不安に関する認知・感情プロセスのモデル化とその応用 / 逸脱行動が生起するプロセスと矯正方法に関する研究 / 進路意思決定における認知・感情過程のモデル化 / 教師教育教材を事例としたマルチメディア教材設計・評価手法の開発</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>社会心理学 / 実験心理学</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>意思決定 / 認知心理学 / 社会心理学 / 感情</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan / 後悔を力に変える / Exploring the Relationship Between Different Consumer Behaviors and Subjective Well-Being in Japan: A Focus on Prosocial, Sustainable, Experiential, and Conspicuous Consumption / The Effect of General Trust on Willingness to Communicate in English among Japanese individuals across various situations. / Factors influencing behavioral intentions in livestream shopping: A cross-cultural study / Does macro-level general trust influence second language communication? :targeting prefectural capitals. / The influence of online multiplayer games on social capital and interdependent well-being in Japan / オンライン入試の実施と問題点 / 一般市民の更生支援に対する認知および参加意向の向上にむけた検討 / Understanding confidence in the human papillomavirus vaccine in Japan: a web-based survey of mothers, female adolescents, and healthcare professionals / Simulation of Outpatient Flow at the University of Tsukuba Hospital / Frequency of grooming the eyebrows and cosmetic consciousness in men. / The relationship between quantity of information contact and public evaluation of volunteer probation officers to promote understanding for social reintegration support. / Factors influencing differences between useful and useless regret. / The relationships between a metacognition scale and adaptive behavior in the regret situations: A comparison between junior high-school and university students. / Understanding confidence in human papillomavirus vaccine in Japan: A web-based questionnaire survey of mothers, female adolescents, and health care professionals. / 裁判員参加意向を規定する要因および意思決定プロセスの差異：制度施行前後の比較 / 市民の生態系サービスへの認知が保全行動意図に及ぼす影響：全国アンケートを用いた社会心理学的分析 / どのようにリスクを伝えればよいか：よりよいリスクコミュニケーションのために必要なこと / 意思決定から見たギャンブル行動 / Change of decision-making processes in repeated risk-taking behavior in a complex dynamic situation / The neural networks model of decision-making including feedback processes / Research on the gaps between students' expectation and satisfaction for universities / Analogical decision making in career choice</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>中学生の達成目標志向が学業成績に影響を及ぼすプロセスの検討：社会的比較感情・行動を媒介にして / ブランドのSNS活動における製品カテゴリが消費者のSNS使用に与える影響 / 中国人大学生におけるダイエット行動に関連する心理・社会的要因についての検討ー身体不満足感とやせ願望に着目してー / ユーザー生成コンテンツがアプリの粘着性と消費者の購買意図に与える影響に関する研究 / 在日中国人留学生の異文化適応に関する研究 / 個人差要因およびマンガ作品内の表現がマンガ読書行動に与える影響 / 福祉・介護サービス従事者のコミュニティ感覚とメンタルヘルスの関連性について / 新しいメディア環境におけるライブコマースが消費者心理と行動に影響を及ぼす要因の検討 / 中国人大学生のとりあえず進学に関する研究―個人差要因と学校適応感に着目して / 看護師支援における共感疲労に影響を及ぼす要因 / 読書状況が変えるネタバレ選好 / グリーン購入における他者の影響 / An Investigation of the Factors Influencing college student Volunteering motivation - In Perspectives on prosocial behaviour</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>社会心理学 ; 実験心理学 ; 労働経済・就職マッチング ; 意思決定分析 ; 都市・地域政策 ; 政策評価・計量分析 ; テキスト分析・NLP ; 医療・ヘルスデータ ; 公共政策・社会工学 ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 社会ネットワーク分析 ; マーケティング分析 ; 学習分析</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>社会心理学
 実験心理学
@@ -4106,7 +4211,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>中学生の達成目標志向が学業成績に影響を及ぼすプロセスの検討：社会的比較感情・行動を媒介にして
 ブランドのSNS活動における製品カテゴリが消費者のSNS使用に与える影響
@@ -4185,6 +4290,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>持続可能な観光のための戦略的オーバーツーリズム対処療法の構築
 持続可能な観光地形成に向けた複雑系モデルとそれを用いた合意形成ツールの開発
 意識分析にもとづく国外旅行意向の国際比較研究
@@ -4232,42 +4342,42 @@
 観光地における地域ブランド構築の内部関係者による資源活用パターンと課題構造に関する研究 - 関東・甲信越地域の市町村を対象として -</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>持続可能な観光のための戦略的オーバーツーリズム対処療法の構築 / 持続可能な観光地形成に向けた複雑系モデルとそれを用いた合意形成ツールの開発 / 意識分析にもとづく国外旅行意向の国際比較研究 / 観光振興のためのマーケットデザインに関する研究－効果的な日本型DMO構築に向けて / 複数の観光交通データの融合的活用方法の開発と政策評価への展開 / 道路インフラマネジメントサイクルの展開と国内外への実装を目指した統括的研究 / 交通関連調査体系の再構築と政策評価への展開 / 道路パフォーマンス指標の開発 / コンテナ港湾機能配分に関する研究 / 観光交通の需要分析</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>土木計画学・交通工学 / 観光学</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>交通 / 観光 / 社会資本 / プロジェクト評価 / 港湾 / 物流 / オーバーツーリズム / 都市計画 / 費用便益分析</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>人口分布とネットワークを考慮したコミュニティバス運営負担に関する実証分析 ～茨城県の自治体を対象として～ / Analysis of Changes in Demand before and after the Restructuring of “Tsukubus” / Simulation Analysis of Tsunami Evacuation Behavior for Residents and Seabathers Under Mixed Pedestrian-Automobile / A Study of Recovery from Shocks Lead by Crisis in the Field of Tourism / Examination of A Risk Management Through Technical Transitions in The Railway ATS System / バス利用に影響を与える要因の検討－利用者意識調査とマクロ分析に基づいて－ / Consciousness Analysis on Travel Behavior and Intention of People in Mainland China / 道路ネットワーク上の交通荷重情報収集を目的とした車重計の配置方法 / つくば市における宅配便の利用実態と再配達依頼の規定因―配達人とのコミュニケーションに着目してー / 渡航回数に着目した中国人の旅行意向形成に関する研究 / 観光流行現象の変遷に関する基礎的考察 / 茨城県内の市町村における橋梁維持管理の実態に関する研究 / 英国を事例とした我が国の空港運営政策に関する一考察 / GPSログデータを用いた訪日外国人旅行者の訪問パターンの分析手法の開発 / 東京近郊観光地におけるインバウンド観光プロモーション施策の考察 / 人口分布統計データを活用した観光地の特性把握 / 高齢者の交通環境改善に向けた新たな交通手段の利用可能性に関する研究 / ガソリンスタンドの経営収支と需要を考慮した存続可能性に関する研究 / 効果的な鉄道の安全対策が新たな課題を惹起する―「安全の 4M」と「リスク」の体系化による考察とマネジメントの重要性― / 地域鉄道の維持に関する考察-時 系列データによる検討- / 都市高速道路における交通状態推定問題およびセンサー配置問題に対するデータ同化アプローチ / 橋梁および高速道路上の横断構造物に対する維持管理の実態と課題 / 国内旅行におけるリピーターの行動特性及び醸成要因に関する研究 / 観光地における地域ブランド構築の内部関係者による資源活用パターンと課題構造に関する研究 - 関東・甲信越地域の市町村を対象として -</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>鉄道の運行支障時における駅周辺道路の交通実態に関する研究 / 自動車の走行距離課税制度に対する社会的受容性に関する研究 / 公共交通のネットワーク形態が自治体の負担に与える影響に関する研究 / 高速交通ネットワークの発展に伴う基幹交通の組合せ利用に関する研究 / つくば市における公共交通に対する住民満足度の要因分析 / 地方誘導型インバウンド政策がもたらす経済的影響に関する研究 / 国内旅行実態の経年的変化に関する基礎的研究 / 津波避難シミュレーションを用いた海水浴場の危険性評価 / 地域公共交通に関する利用者意識調査の活用方法の検討 / Difference of tourists‘ behavior by transportation mode in Kamakura City / TX開通による沿線エリアの交通需要とアクセシビリティ変化に関する研究</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>土木計画学・交通工学 ; 観光学 ; 交通・モビリティ ; 政策評価・計量分析 ; 観光・マーケティング ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 観光情報学 ; 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>土木計画学・交通工学
 観光学
@@ -4303,7 +4413,7 @@
 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>鉄道の運行支障時における駅周辺道路の交通実態に関する研究
 自動車の走行距離課税制度に対する社会的受容性に関する研究
@@ -4381,6 +4491,11 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>津波で失われた景観の再現による記憶の抽出と日常生活に結びついた場の解析
 低環境負荷型住まい方の実践とソーシャル・キャピタル向上の相乗効果を誘発する都市デザイン－インドネシア・ジャカルタの中層住宅における建築空間・住民行動・コミュニティの関係分析
 津波で失われた景観のデジタル再現と記憶の分析によるコミュニティが共有する場の解析
@@ -4416,38 +4531,38 @@
 地域・土地との関係性の希薄化</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>津波で失われた景観の再現による記憶の抽出と日常生活に結びついた場の解析 / 低環境負荷型住まい方の実践とソーシャル・キャピタル向上の相乗効果を誘発する都市デザイン－インドネシア・ジャカルタの中層住宅における建築空間・住民行動・コミュニティの関係分析 / 津波で失われた景観のデジタル再現と記憶の分析によるコミュニティが共有する場の解析 / 量から質へのシフトを実現するための緑地の計画制度・設計手法・運用方法の研究 / 樹冠表面温度を利用した都市気温分布図の作成と緑地の気候緩和機能の分析 / リモートセンシングを活用した生物季節学図の作成と都市微気候の評価</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>都市農村計画 / 緑地計画</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>グリーンインフラ整備を支える緑化技術研究 / 熱的快適性が屋外空間における滞在状態に与える影響に関する研究 / グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例 / 2023年度一般公開シンポジウム開催報告 / 座談会 「緑の基本計画」のこれからを考える座談会 : 制度創設30年目を迎えて / 量から質への転換 / 人と土地の関係を創造するよろこび / 「働くクルマと社会」特集にあたって / GPSデータを用いたスポーツイベント来場者の行動分析 / 企業のIR情報に見る都市緑地に関する第三者認証制度の取り扱いに関する研究 / 熱赤外域リモートセンシングデータを活用した市街地の土地被覆に関する研究 / 熱的快適性が屋外空間における滞在に与える影響に関する研究 / 可視化された温熱環境情報が屋外空間の利用に与える影響に関する研究 / An Empirical Study on Using Green Spaces Around an Office as Workplace in Summer: Considerations Based on Office Employees’ Trait Anxiety Tendencies / グリーンインフラと緑の基本計画 / これからの自律的な民間緑地整備に関する考察 / ノルウェーにおける地表面での雨水管理策に関する法改正における議論の特徴 / ランドスケープ分野におけるDX / グリーンインフラとしての平地林による防災機能 －災害現場で確認された農業気象災害軽減事例－ / 移動の体験と景観 / 企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ / 屋外空間利用がオフィスワーカーに与える心理・生理的影響とその要因に関する研究 / 人流ビッグデータを用いた「Natural Cities」と温熱環境の関係分析についての研究 / 季節の違いが緑化に対する支払意思額に与える影響 / 地域・土地との関係性の希薄化</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>温熱環境がランナーの深部体温に及ぼす影響の把握と都市緑道の暑熱対策の検討 / 屋外温熱環境の違いが来訪者の空間利用に与える影響に関する研究 / 地域の持続可能性に資する非住宅木造建築の実現における関係主体の役割と課題 〜大崎市鳴子こども園を事例として〜 / 温熱環境情報の提示が空間利用に与える影響に関する研究 / 総合設計制度により創出された公開空地の緑化の実態に関する研究 / 北京市におけるヒートアイランド現象の時空間特性の分析 / オフィス街における来街者の滞留行動の季節変化に関する研究ー丸の内仲通りを対象としてー / 屋外空間利用がオフィスワーカーに与える心理的・生理的影響とその要因に関する研究 / 都市住民と農家の都市農地保全に対する意識の乖離とその要因に関する研究 / GPSログデータを用いたCOVID-19流行下の都市公園利用と公園利用前後の行動パターンに関する研究 / 日常の生活行動と温熱環境が深部体温に与える影響に関する基礎的研究 / 歩行時の空間認識と歩行の快適性の関係に関する研究</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 災害分析 ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>都市農村計画
 緑地計画
@@ -4500,7 +4615,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>温熱環境がランナーの深部体温に及ぼす影響の把握と都市緑道の暑熱対策の検討
 屋外温熱環境の違いが来訪者の空間利用に与える影響に関する研究
@@ -4576,6 +4691,11 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>AI時代の省エネ型データセンター性能の数理的解明
 省電力データセンターの協調機構の性能評価
 省電力サーバ群の性能評価と負荷分散に関する数理モデル
@@ -4615,42 +4735,42 @@
 Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>AI時代の省エネ型データセンター性能の数理的解明 / 省電力データセンターの協調機構の性能評価 / 省電力サーバ群の性能評価と負荷分散に関する数理モデル / 処理能力可変型待ち行列モデルの理論的発展と大規模省エネデータセンターへの応用 / 複数車両・複数道路橋を対象とした移動センシング技術の基盤的研究 / 処理能力可変型待ち行列システムの理論的深化と省エネデータセンターへの応用 / 起動時間を有するシステムの理論解析と省エネ型データセンター性能評価への応用 / 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化 / 顧客の再試行と途中放棄を考慮したコールセンターのモデル化と性能解析 / 再試行型待ち行列によるコールセンターの性能解析とサービス科学への応用</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>数理情報学 / 社会システム工学・安全システム</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>応用確率論、 確率モデル、 待ち行列理論、 性能評価、 オペレーションズ・リサーチ、確率システム</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Performance Analysis of Energy-efficient Reliable AIoT System Architectures / Queueing Model with Alternating Service for Zipper Merging / A simulation study of the sojourn time in queueing systems with stochastically delayed information / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers / Performance Analysis of Blockchain with Rollups / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times / Analysis of a Batch Arrival Queue with Power Saving Mode / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory / Analytical Modelling of Asymmetric Multi-core Servers / Energy-performance tradeoffs in server farms with batch services and setup times / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers / Queueing Analysis of an Ensemble Machine Learning System / Performance analysis of a collision channel with abandonments / Empirical architecture comparison of two-input machine learning systems for vision tasks / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes / Modeling and performance analysis of hybrid systems by queues with setup time / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing / To wait or not to wait: Strategic behaviors in an observable batch-service queueing system / A Two-Population Game in Observable Double-Ended Queueing Systems / Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>集団サービス型無限サーバ待ち行列の解析 / 客とサーバの性質が異なるシステムにおける待ち現象の解析 / Modelling social media load through a birth-death-batch-immigration process / マルコフ連鎖を用いたレンタカーとオンデマンド交通の融合システムの性能評価 / 混雑度に依存するサービス速度変化を考慮した待ち行列モデルの分析と交通流への応用 / Sojourn time analysis for m/m/c/setup queues / 異なる省電力モードを導入した集団到着型複数サーバモデルの解析 / Retrial queues with two-way communication for cognitive networks</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>数理情報学 ; 社会システム工学・安全システム ; オペレーションズリサーチ ; 交通・モビリティ ; サービス・待ち行列 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 待ち行列理論 ; サービス工学 ; システム性能評価 ; 学習分析 ; 物流最適化</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>数理情報学
 社会システム工学・安全システム
@@ -4675,7 +4795,7 @@
 物流最適化</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>集団サービス型無限サーバ待ち行列の解析
 客とサーバの性質が異なるシステムにおける待ち現象の解析
@@ -4750,6 +4870,11 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>「協働型都市開発と公共貢献手法に係る今後の展開可能性に関する研究」に対する研究助成
 「今後の都市再生におけるインセンティヴ制度のあり方に関連する研究」に対する研究助成
 自治体保有資産の有効活用を目的とした公民共創プロセスに関する研究
@@ -4791,42 +4916,42 @@
 マイナンバー導入事例に見る政府情報システム調達の現状に関する研究</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>「協働型都市開発と公共貢献手法に係る今後の展開可能性に関する研究」に対する研究助成 / 「今後の都市再生におけるインセンティヴ制度のあり方に関連する研究」に対する研究助成 / 自治体保有資産の有効活用を目的とした公民共創プロセスに関する研究 / 公的不動産の有効活用実現のための公民連携促進策とアセットマネジメント戦略のあり方 / 中古住宅市場における空き家・空き地の流通促進のための公民連携体制のあり方に関する研究 / 既成市街地における不動産流通促進を通じた地域再生に資する土地利用制度に関する研究 / イギリスの都市計画プランナーの職能団体による実務研修等を支えるシステムに関する研究 / オープンデータを踏まえた市民セクター主体のICT協働まちづくりに関する研究 / 豪雨災害から避難弱者を守る共助的な避難行動計画づくりシステムに関する学際的研究</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>都市計画・建築計画 / 経済政策</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Industrial Location / 産業集積 / 都市・地域政策 / 都市計画制度</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで / 新しい時代の都市再生と公共貢献のあり方 / 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 / 都市再開発のこれからの「必要性」と「可能性」 / 農村集落における区域区分制度を前提とした土地利用調整手法の実態と活用可能性に関する研究 / 土地建物一体型市街地整備の「必要性」と「可能性」 : これまでとこれから / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に / つくば市による心肺停止傷病者発生位置情報の最寄AED管理者との共有が生み出す協働による救命効果に関する研究 / 地方自治体におけるオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 / 東京都区部における開発実態の評価を踏まえた開発拠点誘導政策の課題に関する研究 / 公民連携による空き家・空き地対策組織の展開と運営実態 / 避難行動要支援者名簿活用に向けた制度設計・運用プロセスにおける課題に関する研究 / オープンデータ施策に総合的に取り組む地方自治体の動因に関する研究 / 地方都市中心市街地における商店街の連続性を踏まえた空間整備の変遷と課題に関する研究 / 地方自治体のオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 / 世界からみた銀座のルールとガバナンス (特集 銀座と都市計画) -- (都市計画と銀座のルール) / 11027 地区スケールの賑わい空間構造の定量分析に関する研究 歩行空間と周辺土地利用に着目して / “Planning transparency and public involvement in pre-application discussions,” / 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 / 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) / 集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ / マイナンバー導入に伴う自治体業務情報システム改修事例に見るオープン化・標準化及び共同化の現状に関する研究 / マイナンバー導入事例に見る政府情報システム調達の現状に関する研究</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>地方都市の法定再開発における持続的運営の課題に関する研究ー権利変換手法に着目してー / 改正個人情報保護法を受けた避難行動要支援者名簿情報の提供方策に関する研究 / 管理型まちづくりへの転換における公民連携の地域管理体制に関する研究-組織の成立プロセスに着目して- / 民間業務範囲を拡大させた PFI 事業における事業実現過程の課題に関する研究 / 人口減少社会における土地利用調整手法の実態と活用可能性に関する研究 －茨城県桜川市を事例として－ / 都市公園における官民連携事業の課題に関する研究 / 公的不動産の有効活用を促進する民間提案プラットフォームにおける課題に関する研究 / 実効性のある個別避難計画に向けた作成プロセスについて / 外国資本による国内不動産投資の増加が周辺地域に与える影響についての考察 / 公的不動産の利活用に向けた情報発信と官民の対話に関する研究 / 公的不動産の有効活用に関する研究 ―自治体に着目して― / 神社更新に伴う分譲マンション開発の実態と課題に関する研究ー東京都区部の神社を対象としてー</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>都市計画・建築計画 ; 経済政策 ; 保険・金融行動 ; 都市・地域政策 ; 建築・空間設計 ; 災害・防災研究 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 行政データ分析 ; 都市計画 ; 意思決定支援 ; 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>都市計画・建築計画
 経済政策
@@ -4863,7 +4988,7 @@
 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>地方都市の法定再開発における持続的運営の課題に関する研究ー権利変換手法に着目してー
 改正個人情報保護法を受けた避難行動要支援者名簿情報の提供方策に関する研究
@@ -4941,6 +5066,11 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>形態・材料に着目した近代町家の地域性とその形成要因
 モビリティーイノベーションの社会応用と未来社会工学研究5
 モビリティーイノベーションの社会応用と未来社会工学研究3
@@ -4985,42 +5115,42 @@
 「清代新疆の地域構造と都市群の立地 -軍政中心地イリを対象に- 」</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>形態・材料に着目した近代町家の地域性とその形成要因 / モビリティーイノベーションの社会応用と未来社会工学研究5 / モビリティーイノベーションの社会応用と未来社会工学研究3 / モビリティーイノベーションの社会応用と未来社会工学研究4 / 石岡市歴史的景観及び里山景観調査研究 / 大火からの復興を通してみた近代の町並みの再評価 / 江戸武家地の成熟過程に関する建築史・都市史的研究 / 江戸武家地の空間変容に関する文理統合的研究 / 北関東の町並みの建築的構成とその展開過程に関する研究 / 常陸太田市鯨が丘歴史的建造物調査</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>建築史・意匠 / 都市計画・建築計画 / 日本史</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>建築史 / 都市史 / 保全型都市計画 / 居住環境史</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>近代中国青島市における「雑院一覧表 二十四年夏季」について / 五台山行宮座落地盤圖 からみた清代白雲寺行宮 / 嵩山史跡群における建物の空間構成および登封県の建立の経緯 / 近代の町並み景観の多様性：大火からの復興を通してみた近代の町並みに関する研究 その 1 / 戦後昭和期の横浜中華街における商住空間の分布と特徴：中区明細地図の考察から / 清代福州における住宅の類型とその特徴 古絵図 De Stud Hockzieuw en de stad Nanta を中心とした分析 / 明清時代漕運と大運河沿いの都市空間特性との関係 その 2： 済寧を例として / 「白川郷における駐車空間の分布と交通整備の経緯：重要伝統的建造物群保存地区における駐車空間に関する研究」 / 『大日本職業別明細図之内』の空間表現 千葉県北部の地図を対象に / 観光開発を目的とした窯業集落の保全の実態とその課題： 中国陝西省澄城県の伝統村落・堯頭村を事例に / 「清代蘇州の屋外空間における商人達の「自発的な居場所」 のパターン： 「姑蘇繁華図」の分析」 / 新刊紹介『リスボン』 / 明清時代における漕河沿い城・鎮の空間構成に関する研究（その1）：漕運システムと漕河沿岸空間の構成要素との関係 / 清代福州における住宅の三類型 / 大正期から戦前までの山下町における中国系事業所と公共施設の立地と特徴–Japan Directory、商工案内の分析から– / 清代福建省における「舗」の分布とその特性－連江県城を事例として－ / 清代五台山顕通寺の火災と修復工程 / 明清時代漕運と京杭大運河沿い都市の空間特性との関係－臨清を例として－ / 中国における団地構内の小規模野菜市場の空間利用－街商と住民の共存モデル－ / 新刊紹介『明暦の大火』 / 五台山塔院寺の建築の構成とその変容 / 「奈良県橿原市今井町における駐車場の出現パターン：重要伝統的建造物群保存地区の駐車空間に関する研究 その2」 / 「真壁のこれから：過去・現在・未来」 / 「商店街アーケードの空間の変容:十条銀座商店街を対象に」 / 「清代新疆の地域構造と都市群の立地 -軍政中心地イリを対象に- 」</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>東京都区部における銭湯の存続要因とその周辺環境に関する研究－江東区を事例として－ / 幕末の海防に伴う都市空間の変容-江戸沿岸部地域に着目して- / 旧軍用地が地域空間形成に与えた影響について―茨城県ひたちなか市を対象として― / 中国鉄鋼業の発達が都市空間に与えた影響ー近代の武漢を事例にー / 近代中国における鉄道交通基盤の導入と歴史的都市空間との関係—1888〜1958年の京津・津浦鉄道沿線都市を対象に— / 清代駅道の変遷と沿道集落・駅建築の特徴－山東省済南府地域を事例として / 華僑の投資・建設活動が新たな都市空間の形成に果たした役割ー清末〜民国期の広州市東山区を例としてー / 戦後における商店街の業態と空間の変容—高円寺、北千住、巣鴨を事例として— / 観光開発を目的とした窯業集落の保全・修景に関する研究—中国陝西省澄城県の伝統村落・堯頭村を事例に— / 近代中国における民間主導の計画的市街地「漢口模範区」の形成と変容 / 明清期陝西省における都市時報建築の立地と形態 / 近代の繊維都市の形成に模範撚糸工事が果たした役割 / 中国の近代化において交通システムの変容が在郷町の機能・空間に与えた影響 ～四川省資中県を事例として～ / 建設時期・地域による相違に着目した清代満城の都市形態に関する研究 / 農村地域における短路型集落の特徴と近代以降の変容ー茨城県の集落を対象にー / 中国天童寺の寺域及び構成施設の変遷：晋代の創建から近現代の保護まで / 明清時代の役人住宅における職階制度と建築様式の関係—陳氏の住宅を例に / 北京市歴史文化保護区におけるジェントリフィケーションの実態とメカニズム―南鑼鼓巷を事例に</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>建築史・意匠 ; 都市計画・建築計画 ; 日本史 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 都市計画 ; 人間中心設計 ; 社会ネットワーク分析 ; 環境工学</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>建築史・意匠
 都市計画・建築計画
@@ -5053,7 +5183,7 @@
 環境工学</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>東京都区部における銭湯の存続要因とその周辺環境に関する研究－江東区を事例として－
 幕末の海防に伴う都市空間の変容-江戸沿岸部地域に着目して-
@@ -5139,6 +5269,11 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化
 ワークライフバランスに貢献するサイバー・フィジカル製造業
 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配
@@ -5176,42 +5311,42 @@
 Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化 / ワークライフバランスに貢献するサイバー・フィジカル製造業 / 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配 / 半導体・液晶製造の良品スループット向上とコスト低減の両立を目指してQ-time制約の遵守と装置の生産性向上とを同時に実現する実時間最適オペレーション管理手法の研究 / ＱＣＤＲモデルに基づいて革新的な総合設備効率の向上と生産期間の短縮を実現する工場・設備の運用管理システム / ＱＣＤモデルに基づくマルチチャンバ装置および生産ラインの運用・設計方法 / 共創ビジョンに基づく半導体産業のビジネスモデル進化と、知財・人材の組織的流動化</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>制御・システム工学</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>生産システム工学 / オペレーション管理 / 地域活性化</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>"INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH / Robust Classifications of WBM Defect Patterns / Due dates assignment based on customer changeability classifications in Make-to-order productoins / Pipeline production model and sensitivity analysis of Engineering-to-Order products using system dynamics / PRODUCTION AND JOB ROTATION PLANNING CONSIDERING DISABILITIES AND HEALTH CONDITIONS / Classification of Multivariate Time Series Signals Using Self-Supervised Representation Learning / Multi-factory Scheduling Considering the Trade-offs between Production Efficiency and Risks / Analysis of Resilience Factors and Satisfaction in Life-line Charts for Life Career Developments / Interaction Modeling for High-Dimensional Mixed Data with Numerical and Categorical Features / Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL / MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION / Mixed-type Defect Pattern Classifications / Interaction Modelling of High Dimensional Production Data / DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS / MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN / Data-driven Modeling for Production Dynamics / Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption / MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - / Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - / Interaction Modelings for Industrial Data - for final quality estimation and proess integration / スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 / 従属需要の予測手法の構築と検証 / Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>多目的ハイブリッドフローショップスケジューリングの実証研究 / QR決済ヘビーユーザーの内外特徴の分析と活用 ～ キャンペーンと多種アプリ利用状況を考慮して / 保全時間を考慮した自律搬送ロボットのスケジューリング / n工程・多目的ハイブリッドフローショップスケジューリングの高速化～タブーリストと解構造の活用 / 生産リスクと段取りを考慮したMulti-factoryスケジューリング / 高次元交互作用モデリングにおける構造導入アプローチの効果検証 / 上流工場と処理単位の変化を考慮した投入制御ルールと多目的スケジューリングの融合 / 大規模データに対する変化検出と因果分析 / 多重共線性と因子効果ギャップを考慮した高次元交互作用モデリング / エネルギー消費量と納期遅れペナルティのトレードオフを考慮したセルフチューニングバッチ編成と多目的スケジューリング / 建設現場の多様性への対応する360度撮像と画像認識技術 / データ駆動プロセスインテグレーションのための高相関高次元データモデリング / ネットワーク理論に基づく高齢者福祉施設の最適化配置計画～茨城県通所型高齢者福祉施設の事例 / 相関関係を内包した多次元時系列データの予測モデリング / 高相関データの高因子効果比モデル推定 / 多品種繰り返し大規模生産システムのモデリングと最適スケジューリング～半導体Testbedを対象として / 自己教師あり学習を用いた多変量時系列信号の状態分類 / 料理アプリに着目したスマホ起動履歴の解析と情報推薦 / 高次元混合データの交互作用モデリング / 生産効率・人間工学リスク・エネルギーを考慮したジョブローテーションスケジューリング / 工場間搬送を考慮した並列分散型マルチファクトリー・スケジューリング / 営業コストを考慮したサプライチェーンにおける企業間多段階納期交渉 / エネルギー消費と待ち時間制約のトレードオフを考慮したサプライチェーン・スケジューリング / 画像マルチモーダル学習による半導体不良パターンの解析 / 時空間情報を用いた画像マルチモーダル学習による半導体不良パターンの高精度分類 / 資源・エネルギーロスを最小化する生産フロー制御つきマルチファクトリー・スケジューリング / 因果推論と機械学習による車載半導体需要予測 / 推薦システムによる多様なアプリの利用促進 / 高次元データの交互作用モデリング-Adaptive SFMとSafe Pruningによる高精度化 / 多様な建設現場の部材の検出と分類</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>制御・システム工学 ; 都市・地域政策 ; オペレーションズリサーチ ; 機械学習 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 物流最適化 ; 最適化</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>制御・システム工学
 生産システム工学
@@ -5237,7 +5372,7 @@
 最適化</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>多目的ハイブリッドフローショップスケジューリングの実証研究
 QR決済ヘビーユーザーの内外特徴の分析と活用 ～ キャンペーンと多種アプリ利用状況を考慮して
@@ -5331,6 +5466,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>地方での生活空間データ連携
 Hack My Tsukuba 2018
 Hack My Tsukuba 2019
@@ -5378,42 +5518,42 @@
 自治体会計情報のオープンデータ化の促進―国際基準COFOGによる費目分類に着目して―</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>地方での生活空間データ連携 / Hack My Tsukuba 2018 / Hack My Tsukuba 2019 / 豪雨災害から避難弱者を守る共助的な避難行動計画づくりシステムに関する学際的研究 / 茨城県AEDデータベース / 犯罪情報オープン化の犯罪抑止効果研究 / つくば市AEDデータベース / 公共サービスの革新に関する研究 / 医療相談アプリ「LEBER」を用いた医療費削減効果のデータ解析に関する学術指導 / 日本政府のオープンデータ政策評価</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム / 都市計画・建築計画 / ウェブ情報学・サービス情報学 / 図書館情報学・人文社会情報学 / 財政・公共経済 / 持続可能システム / 経営学 / 地域研究 / 環境影響評価</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>オープンデータ、公共データ分析、自治体経営、地域情報化政策、国際協力</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>在宅医療におけるD to P with Nの臨床的役割：訪問診療との比較による診療内容および受療パターンのケーススタディ / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 / 筑波大学理工学群におけるデータサイエンス応用基礎教育 / 水害時における市民の避難行動に関する意識の分析 / Asian Cities Connecting through Communities / 排水再利用設備に係る建築行政の現状と今後の動向 / 建設省--インテリジェントビルへの構図 / ペンシルバニア通り2121番地(第1便)「世界銀行」ってどんなところ? / 世界銀行の都市開発分野における日本の情報発信の方向性 / CIOの視点/INTERVIEW 人と人をつなげて進む川島流地域活性化のビジョン / 地方自治体における業務改革と情報システム構築の実際--佐賀県を事例として / 佐賀県 台帳記録管理システムによる業務改革 / 大きな社会システムのアーキテクチャ再構築を / 世界の潮流 : オープンデータ : エンドユーザーの視点に立ち便益が明確な事業の推進を / 事実証拠を根拠とした政策策定 : オープンデータ推進の効果 / オープンデータの最新動向と公共データ市場に関する考察 / 電子自治体と公共イノベーション / オープンデータの5W1H : 今、自治体は「オープンデータ」にどのように取り組むべきか / オープンデータからソーシャルイノベーションへ : 公共データ×ICT×市民力で社会課題を自ら解決する社会ヘ / 自治体がオープンデータに取り組む際の留意点 オープンデータの活用において自治体が成果を出すための5原則 / Society 5.0実現に向けて必要となる教育の方向性 / オープンガバナンス推進に求められる政府・自治体職員の能力 / VUCA時代の政策形成にデジタルをどう活かすか / 自治体会計情報のオープンデータ化の促進―国際基準COFOGによる費目分類に着目して―</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>地方自治体・企業におけるワーケーション関連の取り組み実態に関する研究 / 個別避難計画の作成促進方策に関する研究～常総市・つくばみらい市を対象として～ / 現代における茅葺き屋根保存に関する課題と適切な支援施策に関する研究 ―茨城県石岡市を事例として― / 避難支援関係主体の参画に着目した実効性のある個別避難計画作成プロセスに関する研究 ―令和２年７月豪雨による球磨川氾濫周辺地区を対象として― / ナッジメッセージを用いた地震に対する世帯備蓄促進に向けた社会実験 ―茨城県つくば市内の世帯を対象として― / 医療過疎地域におけるD to P with Nと訪問診療との代替・補完可能性に関する研究 ~ 長野県伊那市のモバイルクリニック運用を例に ~ / 認知症等行方不明者の発生記録を用いた捜索時間の短縮効果に関する研究 / 最寄AED急搬送システムの社会実装過程における不確実性を考慮したAED選定モデル / 地方の先進社会課題の解決に取り組んでいる若者起業家の成功要因に関する研究～修正エフェクチュエーション・モデルの検証～ / 高経年区分所有住宅の耐震性能を向上する建替え推進に向けた法制度設計上の課題に関する研究 ー台湾と日本の法制度の比較を通じてー</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム ; 都市計画・建築計画 ; ウェブ情報学・サービス情報学 ; 図書館情報学・人文社会情報学 ; 財政・公共経済 ; 持続可能システム ; 経営学 ; 地域研究 ; 環境影響評価 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 災害・防災研究 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 行政データ分析 ; 災害分析 ; 推薦システム ; 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム
 都市計画・建築計画
@@ -5470,7 +5610,7 @@
 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>地方自治体・企業におけるワーケーション関連の取り組み実態に関する研究
 個別避難計画の作成促進方策に関する研究～常総市・つくばみらい市を対象として～
@@ -5548,6 +5688,11 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>オルタナティブデータを用いたオフィス不動産市場分析の可能性
 オフィス賃貸マーケットに関する研究
 地方自治体における情報の利活用方策の導入
@@ -5590,42 +5735,42 @@
 モバイル端末の活用による地方自治体の道路維持業務支援の検討</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>オルタナティブデータを用いたオフィス不動産市場分析の可能性 / オフィス賃貸マーケットに関する研究 / 地方自治体における情報の利活用方策の導入 / 地方自治体における道路維持管理業務のため / 空間計量経済学における最重要課題への挑戦と新たな展開 / 道路台帳を活かした道路アセットマネジメントに関する研究</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>土木計画学・交通工学</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>道路維持管理 / 空間計量経済学 / 地理情報システム / 空間データ / 空間統計 / 不動産 / 不動産価格 / 不動産賃料 / 土地利用 / 立地分析</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ / 東京23区における賃貸オフィスビルストックの地域性と経年変化 / The Impact of the Flight to Quality on Office Rents and Vacancy / Spillover Effect of Large Building Construction on Neighborhood Office Rents / 地域属性と産業振興政策に着目した新設会社の立地に関する考察 / 実用性を考慮したローカルな不動産価格指数の理論と実証. / デジタル化と立地がコロナ禍における私立中学校選択に与える影響. / 大規模オフィスビルの竣工が近隣のオフィス賃料に与える影響：アメニティ効果 vs 供給効果. / 東京オフィス市場における 集積の経済・不経済とその時間的変化 / Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics / Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market / ビッグデータのためのローカルなオフィス賃料指数の開発 / オフィス空室率の時空間変動に関する探索的小地域分析 / 北陸新幹線開通による大学選択への影響に関する実証的研究 / 計量テキスト分析による道路橋を維持管理する技術力の解明の試み / 土木技術者の経験と学習 ―地方整備局職員の研究所出向と道路構造物を維持管理する技術力に着目して― / 空室率データで見る東京オフィス市場の空間的特性 / インフラの維持管理に関する研修による技術力向上効果の評価 ―道路橋の点検に着目して― / 東京オフィス市場における集積の経済・不経済とその時間的変化 / 携帯位置情報データを用いた東京23区内における“オフィス出社”の時空間分析 / 改訂版ブルーム・タキソノミーを用いた道路橋を維持管理する技術力の解明の試み / 交通アクセシビリティの変化が 中学受験における学校選択に与える影響 / モバイル端末の活用による地方自治体の道路維持業務支援の検討</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>自然災害発生による学校選択行動への影響ー首都圏私立中学を対象としてー / 東京オフィス市場における賃料調整過程の異質性と非対称性 / 非労働環境におけるライフキャリア形成プロセス / The Effect of the Housing Prices on the Household Savings in Urban China Under the Trend of Aging Society / The Determinants of China’s crude birth rate and regional difference ——Under the effect of two child policy / 中国における個人用固定資産税改革の効果分析 / 物流企業を考慮した応用都市経済モデルの開発に向けて / 国内政策の普及の実態 ～マイナンバーカードを事例として～ / 地域おこし協力隊の受け入れをめぐる自治体間競争に関する考察 / 大阪市における学力テストスコアと賃料の関係 ～小学校学校選択制の導入から～ / サービス付き高齢者向け住宅の賃料と立地選択の影響要因に関する研究</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>土木計画学・交通工学 ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; マーケティング分析 ; 災害分析 ; 都市計画</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>土木計画学・交通工学
 道路維持管理
@@ -5672,7 +5817,7 @@
 都市計画</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>自然災害発生による学校選択行動への影響ー首都圏私立中学を対象としてー
 東京オフィス市場における賃料調整過程の異質性と非対称性
@@ -5744,6 +5889,11 @@
         </is>
       </c>
       <c r="F30" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>環境配慮行動の心理的障壁を形成・緩和する「きっかけ」体験の地域横断研究
 気候変動緩和行動に対する心理的障壁軽減方策のための日中比較実験研究
@@ -5789,42 +5939,42 @@
 Discrepancies between beliefs and practices on sleep as a factor of insomnia and negative feelings</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>環境配慮行動の心理的障壁を形成・緩和する「きっかけ」体験の地域横断研究 / 気候変動緩和行動に対する心理的障壁軽減方策のための日中比較実験研究 / 分布型水土流出モデルの長期解析に基づく流木被害軽減のための森林管理手法の検討 / 宗教的信念に寄り添った食品廃棄減量プログラムの実践 / 価値観に根ざした環境配慮行動促進策の提案：東洋・西洋社会における横断・縦断研究 / 環境配慮行動と充足感のポジティブな連鎖に関する縦断的研究 / 環境政策が市民の環境意識と省エネルギー行動に及ぼす波及効果 / 新たな持続的開発指標にもとづく国際環境協力政策評価に関する研究</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>環境政策・環境社会システム / 持続可能システム / 土木環境システム / 社会心理学</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>環境心理学 / 人間と環境の相互作用 / 環境価値観・意識 / 環境配慮行動 / 気候関連行動 / 場所愛着</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Validating the dragons of inaction psychological barriers (DIPB) scale in Japan and China: cross-cultural insights on climate change mitigation behaviors / Potentials of No Single-Use Plastic Initiatives for Plastic Waste Management in Island Communities in Central Vietnam: Insights from Local Stakeholder Interviews / Drivers of plastic waste reduction in island communities in Central Vietnam: An application of the extended theory of planned behavior / 景観特性と心理的要因が回復環境形成に与える影響：都市・歴史文化・自然環境の比較 / 航空移動に対する環境負荷認識と相殺行動・主観的幸福感の関係性：日本国内航空会社マイレージ会員調査にもとづく検証 / 騒音源公共施設の受容促進における情報提示の効果：質問紙実験による検証 / Children’s Pro-Environmental Attitudes and Behaviors in Climate Change Mitigation: Findings from Japan and China / Parent-Child Intergenerational Associations of Environmental Attitudes, Psychological Barriers, and Pro-Environmental Behaviors in Japan and China / The function of REM and NREM sleep on memory distortion and consolidation / Health versus environment in alternative meat adoption: An experiment of communication strategies / Relevance of faith and its positive associations with plastic pollution mitigation behaviors : Findings from Japan and Malaysia / Psychological determinants of waste-related pro-environmental behavior by recreational anglers in inland waters in the Kanto region, Japan / Opportunities and challenges for circular economy in the Maldives: A stakeholder analysis of informal E-waste management in the Greater Malé Region / 肉類消費抑制と代替肉普及のためのコミュニケーション方策の効果検証 / Associations of Positive and Negative Perceptions of Outdoor Artificial Light at Night with Nighttime Outdoor Behaviors and Health: Self-Reported Data Analyses on Urban and Suburban Residents in Japan / 容器包装プラスチック分別の社会的受容性：住民の納得感に着目して / Memory load of information encoded amplifies the magnitude of hindsight bias / Effects of outdoor artificial light at night on human health and behavior: A literature review / 環境問題を意識し始めた過去のきっかけと現在の環境配慮行動の関係：大学生を対象に / 路上ポイ捨ての理由と解決方策に関する認識比較分析：日本・マレーシア大学生を対象に / Linking environmental knowledge, attitude, and behavior with place: a case study for strategic environmental education planning in Saint Lucia / 環境問題を意識し始める契機と環境配慮行動の関係：大学生を対象に / 夜間屋外光環境に対する主観的評価と屋外行動の関係 / Discrepancies between beliefs and practices on sleep as a factor of insomnia and negative feelings</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>河川に対する地域住民の評価及び印象による水害防災意識・行動の差異 / 容器包装プラスチック分別の社会的受容性：納得感に着目して / 環境配慮型製品のオンライン購買における効果的な情報提供の探索：アイトラッキングを用いた実証研究 / Effects of e-taxi usage on citizens’ willingness to purchase electric vehicles in Shenzhen, China / 成果情報提示による家庭ごみ減量の意図促進効果：地域と個人の関係に着目して / 都市地域環境の変化が現在の環境配慮行動に与える影響：つくば市住民に着目して / 航空移動の心理的価値評価：幸福感と相殺行動に着目して</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>環境政策・環境社会システム ; 持続可能システム ; 土木環境システム ; 社会心理学 ; 意思決定分析 ; 都市・地域政策 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 環境工学 ; 災害分析 ; 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>環境政策・環境社会システム
 持続可能システム
@@ -5863,7 +6013,7 @@
 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>河川に対する地域住民の評価及び印象による水害防災意識・行動の差異
 容器包装プラスチック分別の社会的受容性：納得感に着目して
@@ -5935,6 +6085,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>「クルマ」と「自動化するクルマ」の社会的受容の包括的理解に向けた学際研究
 ナラティブで編まれる地域交通コミュニティ形成と人材プログラムの研究開発
 健康にやさしい環境整備に係る実証事業
@@ -5974,42 +6129,42 @@
 奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>「クルマ」と「自動化するクルマ」の社会的受容の包括的理解に向けた学際研究 / ナラティブで編まれる地域交通コミュニティ形成と人材プログラムの研究開発 / 健康にやさしい環境整備に係る実証事業 / 高速道路における渋滞吸収走行の社会的受容に関する研究 / 技術の倫理的・法制度的・社会的課題(ELSI)への包括的実線研究開発プログラム / 「クルマ」と「自動化するクルマ」に対する社会的受容の包括的理解に向けた学際研究 / 「高齢運転者向け認知機能検査の負の効用とその緩和策の検討」 / ASEAN諸国におけるモビリティ・マネジメントの実行可能性に関する実証分析 / 道路上の異モード間コミュニケーションの生起と社会的受容 / 健康に配慮した交通行動誘発のための学際的研究</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>土木計画学・交通工学</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>交通計画 / 都市計画における態度・行動変容研究 / リスク･コミュニケーション</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo / Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt / 高齢運転者向け認知機能検査における制度変更の影響評価 / Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour / おつかい行動に見る子どもの移動自由性の世代変化と要因分析 / 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 / 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 / 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― / 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― / モビリティのイノベーションに，モビリティ･マネジメントをどう活かすか？ / モビリティ・マネジメントと健康福祉・教育 / 日米の車両生成データ制作の現状とEUのData Actの波及可能性 / SWC首長研究会への加盟有無(健康都市づくりに対する首長の意識)と公共交通分担率が住民の心身の健康に与える影響 / 「報復の空白」と「運」が交通事故時の道徳的判断に与える影響－自動運転と手動運転の比較分析－ / 東京都区部の電動キックボードシェア利用実態と利用体験・交通手段別視点による比較分析 / 米国における自動運転タクシーの社会的受容とその要因分析－人身事故経験を有する二都市に着目して / おつかい行動に見る子どもの移動自由性の世代変化とその要因分析，最近の調査研究から / 新たなモビリティの規制緩和－思考停止の日本人，大丈夫？ / モビリティ・マネジメントとの出会いと今後 / 基礎自治体における電動キックボードビジネス のガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― / 米国の自動運転車両の事故発生後の 社会的受容の比較分析 / 奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>電動キックボードの社会的受容 －国内外専門家の懸念と東京都区部への影響 / EUデータ政策を事例にしたわが国の自動車産業における課題の調査研究 / 高速道路での渋滞吸収走行普及に向けた情報提供と先導車種によるドライバーの心理変化 / 俯瞰的整理を通じた「地域の公共交通向上の担い手人材」育成に向けた取組みの現状と課題</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>土木計画学・交通工学 ; 都市・地域政策 ; 社会政策・福祉 ; 交通・モビリティ ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 計算社会科学 ; 学習分析</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>土木計画学・交通工学
 交通計画
@@ -6048,7 +6203,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>電動キックボードの社会的受容 －国内外専門家の懸念と東京都区部への影響
 EUデータ政策を事例にしたわが国の自動車産業における課題の調査研究
@@ -6117,6 +6272,11 @@
         </is>
       </c>
       <c r="F32" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>トポロジー的組合せ論と組合せ論におけるトポロジー的手法
 組合せ的構造に関する研究
@@ -6162,42 +6322,42 @@
 核付アフィン点配置の根付サーキット系の性質について</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>トポロジー的組合せ論と組合せ論におけるトポロジー的手法 / 組合せ的構造に関する研究 / Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求 / デジタル指紋符号、多重接続通信路、及び組合せ探索問題 / 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / 部分構造への等質性を基軸とする単体的複体の構造解析 / ネットワーク上の時間軸をもった最適化問題とその応用 / 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化 / 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>数学基礎・応用数学</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>組合せ論 / トポロジー的組合せ論 / シェラビリティー / 単体的複体 / 離散構造 / 離散幾何</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>The average expected value of a rooted graph, Monte Carlo calculation, and a power index for the voting game / Coloring zonotopal quadrangulations of the projective space / Several minimality concepts related to Frankl's conjecture / Some computational studies of the root distribution of Ehrhart polynomials / The root distributions of Ehrhart polynomials of free sums of reflexive polytopes / Sequential Partitions of Nonpure Simplicial Complexes / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting / Pure-strategy Nash equilibria on competitive diffusion games / Hereditary properties and obstructions of simplicial complexes / A comment on pure-strategy Nash equilibria in competitive diffusion games / Obstructions to shellability, partitionability, and sequential Cohen-Macaulayness / Decompositions of two-dimensional simplicial complexes / A note on shellability and acyclic orientations / On the topology of the free complexes of convex geometries / A factorization theorem of characteristic polynomials of convex geometries / The max-flow min-cut property of two-dimensional affine convex geometries / h-Assignments of simplicial complexes and reverse search / Tangle sum and constructible spheres / Deciding constructibility of 3-balls with at most two interior vertices / Non-constructible complexes and the bridge index / Decompositions of balls and spheres with knots consisting of few edges / Nonconstructible balls and a way of testing constructibility / Constructible complexes and recursive division of posets / セル複体に付随するグラフの向き付けとその最適解 / 核付アフィン点配置の根付サーキット系の性質について</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>飛行禁止空域のある空間におけるドローンを用いた監視経路決定 / グラフ理論における再構成問題及び再構成数に関する一考察 / 最大次数が4以下のグラフにおける1-2 Conjectureについて / 低discrepancy点集合の構成における数独超方格の応用 / 繰り返し離散ボロノイゲームのヒューリスティック解法の検討 / 特定の形をした直径が6の木グラフに対するGraceful Labeling</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>数学基礎・応用数学 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; ネットワーク科学 ; 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>数学基礎・応用数学
 組合せ論
@@ -6222,7 +6382,7 @@
 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>飛行禁止空域のある空間におけるドローンを用いた監視経路決定
 グラフ理論における再構成問題及び再構成数に関する一考察
@@ -6296,6 +6456,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>不正者追跡アルゴリズムの開発とその応用
 デジタル指紋符号、多重接続通信路、及び組合せ探索問題
 スパースな結合行列を持つ組合せ的構造の分析と構成
@@ -6337,42 +6502,42 @@
 Zero-difference balanced functions with new parameters and their applications</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>不正者追跡アルゴリズムの開発とその応用 / デジタル指紋符号、多重接続通信路、及び組合せ探索問題 / スパースな結合行列を持つ組合せ的構造の分析と構成 / デジタル指紋及びグループ検査に共通する組合せ構造とアルゴリズムに関する研究 / 組合せ論的マルチメディア指紋符号とその不正者追跡アルゴリズムの研究 / 完全差集合族とそのレーダー配列への応用に関する研究 / 組合せ的デザイン理論を用いた周波数ホッピング系列の構成に関する研究 / 組合せ的デザイン理論を用いた光直交符号の構成に関する研究 / 組合せ的デザインとその符号・暗号への応用</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>数学基礎・応用数学</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>組合せ論 / 符号理論 / 情報セキュリティ / グループ検査</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) / A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) / Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) / Repairing Schemes for Tamo-Barg Codes / A Construction of Optimal One-Coincidence Frequency-Hopping Sequences via Generalized Cyclotomy / Secure Codes With List Decoding / Codes for Exact Support Recovery of Sparse Vectors from Inaccurate Linear Measurements and Their Decoding / Optimal Locally Repairable Codes: An Improved Bound and Constructions / On the Information-Theoretic Security of Combinatorial All-or-Nothing Transforms / A Construction of Maximally Recoverable Codes With Order-Optimal Field Size / Capacity-Achieving Private Information Retrieval Schemes From Uncoded Storage Constrained Servers With Low Sub-Packetization / BCH codes with minimum distance proportional to code length / Existence and Construction of Complete Traceability Multimedia Fingerprinting Codes Resistant to Averaging Attack and Adversarial Noise / Strongly separable matrices for nonadaptive combinatorial group testing / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting / Algebraic manipulation detection codes via highly nonlinear functions / On Optimal Locally Repairable Codes With Super-Linear Length / On optimal weak algebraic manipulation detection codes and weighted external difference families / On Optimal Locally Repairable Codes With Multiple Disjoint Repair Sets / Improved Bounds for Separable Codes and B-2 Codes / Probabilistic Existence Results for Parent-Identifying Schemes / Non-adaptive group testing on graphs with connectivity / Bounds on Traceability Schemes / New Bounds for Frameproof Codes / Zero-difference balanced functions with new parameters and their applications</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>An improved algorithm to identify the cardinality of a coalition in multimedia fingerprinting / Group Testing with List Decoding</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>数学基礎・応用数学 ; 機械学習</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 組合せ最適化 ; 社会ネットワーク分析 ; 学習分析 ; 数理最適化</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>数学基礎・応用数学
 組合せ論
@@ -6389,7 +6554,7 @@
 数理最適化</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>An improved algorithm to identify the cardinality of a coalition in multimedia fingerprinting
 Group Testing with List Decoding
@@ -6457,6 +6622,11 @@
         </is>
       </c>
       <c r="F34" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>気候変動緩和に貢献する新興大都市におけるデータ駆動型の動的交通マネジメントに関する研究
 高速車両連結技術を前提とした都市鉄道の近未来型運行スキーム
@@ -6497,42 +6667,42 @@
 Trading mechanisms for bottleneck permits with multiple purchase opportunities</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>気候変動緩和に貢献する新興大都市におけるデータ駆動型の動的交通マネジメントに関する研究 / 高速車両連結技術を前提とした都市鉄道の近未来型運行スキーム / 高速道路単路部の交通流理論の検証と交通制御システムの戦略的デザイン / 限定合理的個人を仮定した大規模社会システムの動的制度設計 / 交通・物流システム効率化のための市場型マッチング・システムの設計・評価法構築 / MaaS＋CV時代の次世代交通システムに向けたインフラと制度の設計 / 交通渋滞マネジメントのためのビリーフデザインアプローチ / バイオミメティックスに学ぶスマートな都市退化マネジメント / AI計算リソースとしての実交通ダイナミクスの活用技術の開発 / 走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>土木計画学・交通工学</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks / A second order model of capacity drop at expressway lane-drop bottlenecks / 都市鉄道整備推進に向けた事業制度に関する研究 / Stability analysis of a departure time choice problem with atomic vehicle models / 自動運転車両の速度制御を考慮した系統信号制御に関する考察 / 追従モデルによる高速道路サグ部のCapacity Drop現象の再現 / 連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析 / テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル / Predicting traffic breakdown in expressways using linear combination of vehicle detector data / Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 / 連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析 / Dynamic traffic assignment in a corridor network: Optimum versus equilibrium / 高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム / 需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡 / Fundamental diagram of urban rail transit considering train-passenger interaction / 高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム / 高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動 / Dynamic system optimal traffic assignment with atomic users: Convergence and stability / A new look at departure time choice equilibrium models with heterogeneous users / 動的交通均衡配分理論の近年の進展 / Continuum car-following model of capacity drop at sag and tunnel bottlenecks / Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" / Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach / Trading mechanisms for bottleneck permits with multiple purchase opportunities</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>ボトルネック渋滞と都市人口分布の相互依存関係の解析 / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 / 多種別連結運行スキームにおける鉄道システムの安定性解析 / 市場型混雑管理システム下における自動運転サービスの運用方法 / 需要の時間的・空間的異質性を考慮した多種別連結運行スキームの分析 / 路線分割に基づく系統制御評価とオフセット設計 / 小規模シェアサイクルにおける再配置の効果分析と改善策の提案―茨城県つくば市「つくチャリ」を対象として―</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>土木計画学・交通工学 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; 交通・モビリティ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 学習分析 ; 災害分析</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>土木計画学・交通工学
 交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム
@@ -6566,7 +6736,7 @@
 災害分析</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>ボトルネック渋滞と都市人口分布の相互依存関係の解析
 音声による速度回復情報提供の交通性能改善メカニズムの実証分析
@@ -6640,6 +6810,11 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>非線形・非正規状態空間モデルと多変量・高次元経済金融時系列分析
 統計的学習を用いた非線形計量経済モデルの新展開と金融・経済リスク評価への応用
 多変量／高次元の潜在変数をもつ時系列モデルの効率的ベイズ推測
@@ -6656,42 +6831,42 @@
 Bayesian Analysis of Time-Varying Quantiles Using a Smoothing Spline</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>非線形・非正規状態空間モデルと多変量・高次元経済金融時系列分析 / 統計的学習を用いた非線形計量経済モデルの新展開と金融・経済リスク評価への応用 / 多変量／高次元の潜在変数をもつ時系列モデルの効率的ベイズ推測 / 高次元データモデリングの新展開と統計的リスク分析 / 経済・金融多変量データのベイズモデリングと政策・行動の確率的評価</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>統計科学 / 経済統計</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>ベイズ統計学, 状態空間モデル</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Simulation of truncated and unimodal gamma distributions / Bayesian GARCH modeling for return and range / 時間変動する相関と確率的ボラティリティモデル / Multiple-block dynamic equicorrelations with realized measures, leverage and endogeneity / Dynamic equicorrelation stochastic volatility / Bayesian Analysis of Time-Varying Quantiles Using a Smoothing Spline</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>階層ディリクレ多項モデルの効率的な変分推論</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>統計科学 ; 経済統計 ; 保険・金融行動 ; GIS・空間分析 ; 建築・空間設計 ; 機械学習 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 学習分析 ; 統計学 ; 行政データ分析 ; 数理最適化</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>統計科学
 経済統計
@@ -6729,7 +6904,7 @@
 数理最適化</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>階層ディリクレ多項モデルの効率的な変分推論
 非線形・非正規状態空間モデルと多変量・高次元経済金融時系列分析
@@ -6773,6 +6948,11 @@
         </is>
       </c>
       <c r="F36" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>歩行からみた都市空間の評価とインフラ適正配置に関する数理的・実証的研究
 輸送モードの多様化と地域性・広域性を両立する公共交通網設計
@@ -6821,42 +7001,42 @@
 沿道電柱密度の地域別・道路種別比較</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>歩行からみた都市空間の評価とインフラ適正配置に関する数理的・実証的研究 / 輸送モードの多様化と地域性・広域性を両立する公共交通網設計 / 人口の年齢構成の変遷パターンと市街地構造・生活利便施設アクセシビリティとの関連性分析 / 位置情報ビッグデータを活用した人の移動パターンと都市施設・土地利用・交通網の関係性の分析 / 都市拠点の人流パターン解析と市街地構造変容の モデル分析研究 / デジタル時代の施設配置の理論－自己完結，個人情報保護，民主的決定による非効率性－ / 水害時の住民避難をより安全にする広域避難対策の社会的実装を図る計画技術の構築 / 都市の拠点集約と拠点間ネットワークの空間分析 / 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>都市計画・建築計画 / 社会システム工学・安全システム / 人文地理学 / 地理学 / 土木計画学・交通工学</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>都市解析 / 地域施設計画 / 立地科学 / 地域公共交通 / 地理情報科学 / 都市リスク分析</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>起伏を考慮した低炭素都市交通施策の評価 / 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関 / 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析 / 東京区部における年齢構成類型の変化と生活利便施設へのアクシセビリティ分析 / 電柱広告の空間的配置に関する研究―筑波研究学園都市中心部を対象に― / Exploring Network Scale Separation Strategies for Car-Bicycle Integration / 都市条件に応じた複数公共交通モード併用によるネットワーク設計 / 全国鉄道駅周辺地域における地域分断による移動制約の定量評価 / 小地域人口の年齢構成類型とその遷移から見た安定性分析 / 東京区部における業種構成・滞在パターンに基づく商業集積地の類型化と滞在移動特性の分析 / 東京区部におけるGPSデータに基づく街区レベル発生集中・滞在移動特性と建物用途構成 / 人口分布の集積性と鉄道網との連携度の変化動向に関する研究 / 東京区部における人口年齢構成と土地利用遷移の関連性分析 / 東京区部における交通量密度・移動速度に基づく交通軸と移動効率性評価 / 鉄道網による移動時間短縮を考慮した都市の人口分布の集積性の評価 / 人流データによる滞在者平均年齢の時空間分析 ―昼や休日に若返る自治体はどこか？― / 通学距離最小化と安定マッチングによる学校割当 / Preference-based jogging route selection in Downtown Tokyo / Effect of Speed Control for Travel Time and Emission Reduction in Connected Vehicle Environment / Exploring Separation Strategies for Car-Bicycle Integration / アジア地域の都市における鉄道・道路と人口分布構造 / 建物主要用途・トリップチェーンに着目した人流データによる街区間トリップ特性 / 人流データによる街区レベル時間帯別発生集中の時空間分布 / 人口重心に着目した人流分析 / 沿道電柱密度の地域別・道路種別比較</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>人口の年齢構成遷移と市街地構造・生活利便施設アクセシビリティとの関連性分析</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>都市計画・建築計画 ; 社会システム工学・安全システム ; 人文地理学 ; 地理学 ; 土木計画学・交通工学 ; 家族・人口政策 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析 ; 都市計画</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>都市計画・建築計画
 社会システム工学・安全システム
@@ -6918,7 +7098,7 @@
 都市計画</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>人口の年齢構成遷移と市街地構造・生活利便施設アクセシビリティとの関連性分析
 歩行からみた都市空間の評価とインフラ適正配置に関する数理的・実証的研究
@@ -6985,6 +7165,11 @@
         </is>
       </c>
       <c r="F37" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>世界測地系の構築
 合成開口レーダー解析ソフトウェアの開発
@@ -7028,30 +7213,30 @@
 Preceding, coseismic, and postseismic slips of the 2011 Tohoku earthquake, Japan</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>世界測地系の構築 / 合成開口レーダー解析ソフトウェアの開発 / 測地基準系の座標変換 / 地下水位と地盤上下変動に関する研究 / 地殻変動解析</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
         <is>
           <t>測地学 / 空間情報科学 / 測量学 / 地球観測 / リモートセンシング / 宇宙測地学 / 合成開口レーダー / 干渉法 / データサイエンス / 基準座標系</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>2011年東北地方太平洋沖地震後の余効変動の時空間関数モデリング / Spatiotemporal functional modeling of postseismic deformations after the 2011 Tohoku-Oki earthquake / Ground deformation in the Kobe-Osaka area during 22 years after the Kobe earthquake / 兵庫県南部地震以後の22年間の京阪神の地盤変動 / JERS-1/InSAR再解析：1995年兵庫県南部地震後の地殻変動の検出 / 兵庫県南部地震以降，六甲山は高くなったのか？ / Volcanic deformation of Atosanupuri volcanic complex in the Kussharo caldera, Japan, from 1993 to 2016 revealed by JERS-1, ALOS, and ALOS-2 radar interferometry / 宇宙測地技術により検出された1995年兵庫県南部地震の余効変動 / A possible restart of an interplate slow slip adjacent to the Tokai seismic gap in Japan / Combined logarithmic and exponential function model for fitting postseismic GNSS time series after 2011 Tohoku-Oki earthquake / だいち2号SAR干渉解析により捉えられた平成26年（2014年）長野県北部の地震に伴う地殻変動と地表変形 / だいち2号SAR干渉解析による御嶽山噴火に伴う地表変位の検出 (小特集 御嶽山噴火への対応) / P47 ALOS-2干渉SARにより捉えられた2015年箱根山・大涌谷火山活動に伴う地殻変動(ポスターセッション) / 2014年11月22日長野県北部の地震におけるSAR干渉画像に基づく地表変形現地調査結果 / 干渉SARで捉えた2014年11月22日長野県北部を震源とする地震に伴う地表変位 / Continuous gps observations on mindanao / 無人航空機(UAV)による西之島の空中写真撮影と高精度地形計測 / SAR干渉解析のための数値気象モデルを用いた大気遅延誤差の低減処理ツールの開発 / 無人航空機による西之島空中写真の撮影とその分析 / 無人機による西之島地形計測の高精度化 / Landform Monitoring in Active Volcano by UAV and SFM-MVS Technique / Spatial and temporal evolution of the long-term slow slip in the Bungo Channel, Japan / InSAR-derived Coseismic Deformation of the 2010 Southeastern Iran Earthquake (M6.5) and its Relationship with the Tectonic Background in the South of Lut Block / 新潟—神戸ひずみ集中帯越後平野付近の詳細地殻変動分布 / Preceding, coseismic, and postseismic slips of the 2011 Tohoku earthquake, Japan</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
         <is>
           <t>センサデータ解析 ; 災害分析 ; 環境工学 ; 行政データ分析</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>測地学
 空間情報科学
@@ -7069,7 +7254,7 @@
 行政データ分析</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>世界測地系の構築
 合成開口レーダー解析ソフトウェアの開発
@@ -7131,6 +7316,11 @@
         </is>
       </c>
       <c r="F38" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>災害時交通網の動学的設計にむけた不確かさ回避行動の評価手法の構築
 ネットワークリスクの動的変化と避難行動チェインの解明
@@ -7169,34 +7359,34 @@
 「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>災害時交通網の動学的設計にむけた不確かさ回避行動の評価手法の構築 / ネットワークリスクの動的変化と避難行動チェインの解明 / 次世代モビリティ導入を想定した交通・土地利用モデルの開発とその不確実性分析 / 災害時の他者支援行動を考慮した動的制御シミュレータの開発 / MaaS＋CV時代の次世代交通システムに向けたインフラと制度の設計 / 相乗型豪雨災害時の交通マネジメントの理論再構築と社会への実装 / 量子コンピューティングによる他者相互作用型の行動モデルの発展 / マルチスケールな拠点空間計画のための新たな行動モデル研究 / 災害時都市継続計画にむけた即応型需要予測の信頼性向上のためのデータフロー / 災害時都市活動支援のためのsoftware2.0型シミュレータの構築</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
         <is>
           <t>避難行動 / 交通需要 / 交通シミュレーション / 災害復旧 / 相互作用</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ / EVユーザーの充電場所選択問題に対するゲーム理論的考察 / 災害復旧期における個々人の移動パターン変化の特徴分析 / メタ分析による災害時の避難開始選択要因の評価 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 相互作用下での多肢選択行動の量子計算による求解 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— / 筑波大学理工学群におけるデータサイエンス応用基礎教育 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 / 選択肢の不確実性を考慮した動的離散選択モデル / LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること / 日本の復興計画の研究動向と今後の展望 -1995年以降の建築・都市・土木の計画分野を中心に- / LET'S GO ABROAD!(第77回)シンガポール、パキスタン、アフガニスタン、ベトナム、カンボジア 地域建設業の海外展開と見据える未来—A regional construction company looks to overseas expansion and their future—特集 土木と地政学 / 「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
         <is>
           <t>都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 観光・マーケティング ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 災害分析 ; 社会ネットワーク分析 ; 学習分析</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>避難行動
 交通需要
@@ -7246,7 +7436,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>災害時交通網の動学的設計にむけた不確かさ回避行動の評価手法の構築
 ネットワークリスクの動的変化と避難行動チェインの解明
@@ -7309,6 +7499,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発
 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証
 Service Engineering
@@ -7325,34 +7520,34 @@
 Manufacturer’s strategy in a sharing economy</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発 / 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
         <is>
           <t>Service Engineering / Experimental economics</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 / What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews / Mystery shopping considering lifestyle heterogeneity / 経験効用モデルに基づくサービス継続利用を促すリマインダーの最適間隔 / Effects of Incentivized Fake Reviews on E-commerce Markets / Platform in manufacturing for enhancement of product value by sharing / Interpreting value creation model by case-based decision theory / Service switching in case-based decisions following bad experiences: Online reviews data of Japanese hairdressing salons / Multi-agent simulation for the manufacturer’s decision making in sharing markets / Manufacturer’s strategy in a sharing economy</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
         <is>
           <t>意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 推薦システム ; 政策評価 ; 学習分析</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Service Engineering
 Experimental economics
@@ -7367,7 +7562,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発
 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証
@@ -7395,7 +7590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7426,50 +7621,55 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>profile_source</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>trios_info</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>trios_topics_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>trios_research_fields_text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>trios_research_keywords_text</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>trios_papers_text</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>master_title_text</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>coarse_research_field</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>detailed_research_field</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>field_text</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>content_text</t>
         </is>
@@ -7502,6 +7702,11 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>十分なエネルギーをすべての人へ：家庭部門の公正な移行を実現するために
 包摂的な低炭素化・エネルギー転換に関する研究
@@ -7547,42 +7752,42 @@
 How Can We Gauge Energy Poverty? A Multidimensional Approach</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>十分なエネルギーをすべての人へ：家庭部門の公正な移行を実現するために / 包摂的な低炭素化・エネルギー転換に関する研究 / 低炭素化・エネルギー転換の包摂性評価：基本的エネルギーニーズの観点から / 環境・エネルギーに関する多次元貧困指標の開発と政策分析 / 地球温暖化とエネルギー貧困 / 東日本大震災後の地球温暖化政策を考える / モラルモチベーションと環境政策 / 人々の環境モラルに基づく自発的行動と望ましい環境政策 / 「環境政策における経済的手法」再検討 / 応用一般均衡モデルによる環境政策の社会経済学的分析</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>経済政策 / 環境政策・環境社会システム</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>環境経済学 / エネルギー経済学 / 政策分析 / 不平等分析 / 貧困分析 / 分解手法の開発 / エネルギー貧困、エネルギー脆弱性</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>エネルギー貧困からエネルギー充足へ / Aging alone: a twin threat to decarbonisation and energy vulnerability in Japan and UK / Reevaluating fair carbon emissions for households in Japan: basic energy needs and subsistence CO2 emissions / Double energy vulnerability in Japan / Double energy vulnerability in Japan: a first assessment / Measuring energy sufficiency: A state of being neither in energy poverty nor energy extravagance / What can be done with one tonne of CO2 emissions?: Reconsidering fair carbon emissions for households in relation to the use of domestic energy services / Measuring energy sufficiency: A state of being in neither energy poverty nor energy extravagance / How to evaluate energy sufficiency: A direct measurement approach / Energy Poverty in Japan: Current Trends and Future Challenges / 公平なエネルギー転換：気候正義とエネルギー正義の観点から / Regional energy poverty reevaluated: A direct measurement approach applied to France and Japan / Energy poor need more energy, but do they need more carbon?: Evaluation of people’s basic carbon needs / Prevalence of energy poverty in Japan: A comprehensive analysis of energy poverty vulnerabilities / Energy poor need more energy, but do they need more carbon? / Engendering an inclusive low-carbon energy transition in Japan: Considering the perspectives and awareness of the energy poor / Understanding regional energy poverty in Japan: a direct measurement approach / Measuring Energy Poverty via Energy Service Usage: The Japanese case / 「エネルギー貧困」・「エネルギー脆弱性」・「エネルギー正義」：日本における現状と課題 / 「エネルギー正義」について / Gauging Energy Poverty: A Multidimensional Approach / Measuring Energy Poverty in Japan, 2004-2013 / How Can We Gauge Energy Poverty? A Multidimensional Approach</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>中国の排出量取引制度がグリーン投資に与える影響 / 再生可能エネルギー促進のための課題ー全国トラブル発生データを用いた考察ー / 中国の「費改税」が製造業に与える影響</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>経済政策 ; 環境政策・環境社会システム ; マッチング理論・ゲーム理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 環境工学 ; 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>経済政策
 環境政策・環境社会システム
@@ -7619,7 +7824,7 @@
 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>中国の排出量取引制度がグリーン投資に与える影響
 再生可能エネルギー促進のための課題ー全国トラブル発生データを用いた考察ー
@@ -7688,6 +7893,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>民主主義における利益誘導と経済発展への影響
 政策立案のための衛星データ利用法の探索：社会工学的アプローチ
 社会工学分野での衛星画像の利用促進に向けた探索的研究
@@ -7725,42 +7935,42 @@
 School Choice and Student Sorting: Evidence from Adachi City in Japan</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>民主主義における利益誘導と経済発展への影響 / 政策立案のための衛星データ利用法の探索：社会工学的アプローチ / 社会工学分野での衛星画像の利用促進に向けた探索的研究 / 衛星情報を利用した物流における大気環境改善の評価 / 反実仮想で測る公的資源配分の依怙贔屓と非効率 / 交通と環境に関する新経済地理学的基盤研究 / 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年 / 都市における環境リスクの軽減の経済効果に関する研究 / 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>経済政策</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>開発経済学、教育の経済学、健康の経済学、応用計量経済学</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand / The Impact of a High-speed Railway on Residential Land Prices / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan / School Choice and Student Sorting: Evidence from Adachi Ward in Japan / オリンピック・パラリンピックにはどんな経済効果があるのか / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward / Building an Administrative Database of Children / 高速鉄道の建設が居住地価格に与えた影響 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 / 学校の質と地価－足立区の地価データを用いた検証 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ / 子どもについての行政データベースの構築 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から / 区立小学校での補習の効果：足立区のケース / ヘドニック・アプローチにおける因果識別 / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand / School Choice and Student Sorting: Evidence from Adachi City in Japan</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>選挙制度と資源配分のゆがみ－昭和前期の事例－ / 都市の住みやすさランキングによる居住地選択への影響 / 個人競技における チームメイトの影響 / 農産物直売所が​地域農業に与える影響 / 夜間光リモートセンシング画像を用いた​高速鉄道建設の四川省経済発展に対する影響 / エネルギー会社に対する省エネ基準が、エネルギー消費に与える影響の分析 / 有名作品の舞台地になることによる地方創生への可能性 / 新型農村協同医療制度が中国農村女性の健康格差に与える影響</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>経済政策 ; 都市・地域政策 ; 交通・モビリティ ; 機械学習 ; 画像・視覚情報処理 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>経済政策
 開発経済学、教育の経済学、健康の経済学、応用計量経済学
@@ -7802,7 +8012,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>選挙制度と資源配分のゆがみ－昭和前期の事例－
 都市の住みやすさランキングによる居住地選択への影響
@@ -7876,6 +8086,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>行動経済学の知見を利用した進化ゲーム理論による均衡選択分析
 社会選択問題への進化ゲーム理論的アプローチ
 マルチタスク環境および協力ゲームにおける進化ゲーム理論の研究
@@ -7902,42 +8117,42 @@
 CG を用いたマシンの3 次元構造進化システム</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>行動経済学の知見を利用した進化ゲーム理論による均衡選択分析 / 社会選択問題への進化ゲーム理論的アプローチ / マルチタスク環境および協力ゲームにおける進化ゲーム理論の研究</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>理論経済学 / 社会システム工学・安全システム</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>ゲーム理論; 進化ゲーム理論;</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>The evolution of collective choice under majority rules / Statistical inference in evolutionary dynamics / 研究室の選好と学生の成績を考慮した研究室配属法の分析 / 有限オートマトンを用いた私的観測繰り返しゲームにおける進化的安定戦略分析 / A stochastic stability analysis with observation errors in normal form games / Stochastic stability in the large population and small mutation limits for coordination games / oTreeを用いた配属システムの設計・構築とその運用 / A prospect theory Nash bargaining solution and its stochastic stability / 複利型強化学習を用いたポートフォリオ選択手法についての研究 / Evolutionary dynamics in multitasking environments / Stochastic stability under logit choice in coalitional bargaining problems / Prospect dynamics and loss dominance / Reference-dependent preferences, super-dominance and stochastic stability / A one-shot deviation principle for stability in matching problems / Evolutionary imitative dynamics with population-varying aspiration levels / Coalitional stochastic stability in games, networks and markets / Mutation rates and equilibrium selection under stochastic evolutionary dynamics / CG を用いたマシンの3 次元構造進化システム</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>不完全観測下における損失回避性が均衡の安定性に及ぼす影響 / 不確実性の存在する公共財提供問題における近視眼的プレイヤーによる持続的協力行動の進化分析 / 品質選択がクラウドファンディングを行う企業の資金募集形式および利潤に与える影響の分析 / 企業の不祥事における隠蔽のゲーム理論 / 就活市場における企業の内定通知がマッチングの安定性に与える影響の分析 / 非線形公共財ゲームにおけるプレイヤーの関係性を利用したグループ形成手法の考察 / Stochastic stability analysis on the tragedy of climate change via agents’ psychological dynamics / ソーシャルメディア上の炎上現象の分析と対策 / 感情表現と表現に対する反応の共進化 / 通貨競争モデルによる仮想通貨の普及に関する分析 / 多数決による準公益施設の立地分析 / プロ野球現役ドラフト制度における改善 / オークションモデルによる官製談合の分析</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>理論経済学 ; 社会システム工学・安全システム ; マッチング理論・ゲーム理論 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 学習分析 ; 計算社会科学 ; 行動科学</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>理論経済学
 社会システム工学・安全システム
@@ -7961,7 +8176,7 @@
 行動科学</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>不完全観測下における損失回避性が均衡の安定性に及ぼす影響
 不確実性の存在する公共財提供問題における近視眼的プレイヤーによる持続的協力行動の進化分析
@@ -8019,23 +8234,28 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>researchmap_not_found</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>researchmap</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
 グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築
@@ -8075,6 +8295,11 @@
         </is>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>リーマン多様体上の制約付き最適化問題に対する汎用アルゴリズムの理論と実装
 リーマン多様体上の最適化理論に基づく新たなデータコラボレーション手法の開発
@@ -8114,42 +8339,42 @@
 ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成―</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>リーマン多様体上の制約付き最適化問題に対する汎用アルゴリズムの理論と実装 / リーマン多様体上の最適化理論に基づく新たなデータコラボレーション手法の開発 / ガソリンスタンドにおけるスタッフ最適配置編成アプリケーションの開発 / コネクティッドカーのサービス開発を目的とした走行データのデータクレンジング手法に係る研究 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / 半正定値基を用いた錐最適化問題の近似解法の開発 / 地域未来創生共同研究講座 / 次世代社会システムとモビリティの新価値研究 / 購買データに基づく顧客行動分析</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>数理情報学 / 数学基礎・応用数学 / 社会システム工学・安全システム / 計算科学</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>数理最適化 / 数理計画 / オペレーションズ・リサーチ / サービス工学</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Data Collaboration Analysis with Orthonormal Basis Selection and Alignment / Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning / 正循環制約を考慮したナーススケジューリング / Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices / Post-Processing with Projection and Rescaling Algorithms for Semidefinite Programming / Riemannian Interior Point Methods for Constrained Optimization on Manifolds / A new extension of Chubanov's method to symmetric cones / 射影- 再スケーリング法を用いた 対称錐計画問題に対する後処理アルゴリズム / On the Global Convergence of Riemannian Interior Point Method / Completely positive factorization by a Riemannian smoothing method / Evaluating approximations of the semidefinite cone with trace normalized distance / Completely Positive Factorization in Orthogonality Optimization via Smoothing Method / Scenario-based CVaR Approach to Strategic Decision Support in One-way Station-based Carsharing Systems / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach / Polyhedral approximations of the semidefinite cone and their application / Centering ADMM for the Semidefinite Relaxation of the QAP / QAPの半正定値緩和問題を解くためのセンタリングADMM / SD基に基づく半正定値行列錐の凸多面錐近似 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成―</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>ロード・プライシング政策を考慮したNLSUEモデルとその解法の提案 / 未達率指標を用いた生産計画手法のSC能力設計への応用の研究 / 予約制乗合タクシーのルート最適化 / スマートキャンパスバス運行計画 / 救急医療サービスの効率化に向けた患者の医療機関割り当てに関するオフラインアルゴリズムの開発 / 一般消費財業界における未達率指標を用いた生産計画手法のSC能力設計への応用の研究 / 多死社会における在宅看取りに関する一考察 －茨城県の医療・介護に関する地域分析と実際の看取りをふまえて－ / バックトゥバック数を考慮したNBAの2018-2019シーズンスケジュールの作成 / 健康診断センターの勤務表作成におけるスケジューリング問題 / メタヒューリスティクスを用いた予約制乗合タクシーの配車スケジュール作成 / 乗客満足度を考慮した乗合タクシーの路線最適化モデル / ファストフード店の勤務スケジュールの作成 / リーマン多様体上の統合解析関数最適化 / 社会工学学位プログラムにおける修論発表会のスケジューリングについて / Traveling umpire problem におけるチーム間の公平性が高い解の探求 / 多要素ランキング法の上で正確性と多様性のトレードオフを考慮したモデルによる推薦システム / A Modification of Representing Linear Programs by Graph Neural Network / つくば市における予約制乗合タクシーの配車スケジューリング作成 / マイクログリッドにおける災害対策を考慮した最適化シミュレーション / 大学入試における屋内連絡員の人員配置最適化ツール開発 / 実運用を考慮した予約制乗合タクシーの配車スケジューリング作成</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>数理情報学 ; 数学基礎・応用数学 ; 社会システム工学・安全システム ; 計算科学 ; 都市・地域政策 ; オペレーションズリサーチ ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 学習分析 ; 物流最適化</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>数理情報学
 数学基礎・応用数学
@@ -8174,7 +8399,7 @@
 物流最適化</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>ロード・プライシング政策を考慮したNLSUEモデルとその解法の提案
 未達率指標を用いた生産計画手法のSC能力設計への応用の研究
@@ -8256,6 +8481,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>人工知能に基づく非線形高次元小標本データ解析とその社会的応用
 ３元型時系列高次元小標本データの解析とその社会的応用
 高次計量による高次元小標本型ビックデータ解析とその社会的応用
@@ -8296,42 +8526,42 @@
 区間組成データに対する重み付き回帰分析</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>人工知能に基づく非線形高次元小標本データ解析とその社会的応用 / ３元型時系列高次元小標本データの解析とその社会的応用 / 高次計量による高次元小標本型ビックデータ解析とその社会的応用 / 多次元クラスター尺度構成法によるビックデータ解析とその社会的応用 / 高次シンボリックデータに対するクラスターワイズ手法の開発とその応用 / Data Mining and Machine Learning Techniques / Development of Decision Fusion Architecture for Complex Scenarios / 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 / 高次元データの理論と方法論の総合的研究 / 高次Aggregation Operatorの開発とクラスタリングモデルへの適用</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>統計科学 / ソフトコンピューティング</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>統計科学 / ソフトコンピューティング / データマイニング / 多次元データ解析</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Simultaneous visualization method for mixed HDLSS data and its application for education / Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design / Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey / Difference on Evaluation Scores Considering Image Descriptions for Autocoding / ファジィクラスタリングの信頼度について / Hierarchical Support Vector Machine based Classifier for Autocoding / Fuzzy Cluster-Scaled Principal Component Analysis for Mixed Data and Its Application of Educational Effect based on Device Selection / A Fuzzy Cluster-Scaled Principal Component Analysis for Mixed High-Dimension and Low-Sample Size Data / Principal component analysis for mixed high-dimension low-sample size data based on fuzzy-cluster scale / Improvement of Training Data for Autocoding on "The National Survey of Family Income, Consumption and Wealth" and "The Family Income and Expenditure Survey" / Fuzzy Clustering based Autocoding Methods for Family Income and Expenditure Surveys / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding / Fuzzy Clustering based Classifier for Extraction of Individualities from High Dimension Low Sample Size Data / Individuality-based Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results / Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling / Cluster-based Analysis for Discrimination of Individuality （招待講演） / クラスター尺度に基づくデータ間差異の検出と市場データへの応用 / ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 / Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data / Clustering and Multidimensional Scaling for Individual Difference Extraction / 多次元尺度法による計算効率を考慮したディープラーニング手法 / Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means / 区間組成データに対する重み付き回帰分析</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>TLPCMの評価および欠損値処理手法 / 区間組成データに対する 回帰分析 / 歌詞テキストデータの感情分類 / 区間データに対するPCA手法の提案と従来法との比較 / ファジィクラスタリングを用いた欠損値補完法について / T-normを用いたクラスター尺度による顧客分類法</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>統計科学 ; ソフトコンピューティング ; 労働経済・就職マッチング ; 都市・地域政策 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 公共政策・社会工学 ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 行政データ分析 ; センサデータ解析 ; 社会ネットワーク分析 ; 計算社会科学</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>統計科学
 ソフトコンピューティング
@@ -8365,7 +8595,7 @@
 計算社会科学</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>TLPCMの評価および欠損値処理手法
 区間組成データに対する 回帰分析
@@ -8437,6 +8667,11 @@
         </is>
       </c>
       <c r="F8" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究
 アカウンティング・インフォマティクス（会計情報科学）の基盤研究
@@ -8483,42 +8718,42 @@
 Configuration model for correlation matrices preserving the node strength</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究 / アカウンティング・インフォマティクス（会計情報科学）の基盤研究 / 学際的エビデンスに基づく超高齢社会のモビリティ支援とアクティブ・エイジングの推進 / 多層ネットワークを用いたワクチン忌避に対する実証的研究 / 想起効果を内在する集合的記憶モデルの開発 / International School and Conference on Network Science (NetSciX 2020) / 勤労世代における風疹ワクチン接種の決定要因に関する研究 / 乳幼児の活動量を測定するウェアラブル機器の開発 / 乳幼児の活動量を測定するウェアラブルデバイスの開発 / サイバー社会ネットワークにおける噂の伝播の検出と制御</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>数理物理・物性基礎 / ウェブ情報学・サービス情報学</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>経済物理学 / ネットワーク科学 / 社会物理学 / 計算社会科学 / ウェブサイエンス / ビッグデータ</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis / コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 / Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan / Quantifying Collective Emotions: Japan’s Societal Trends Through Enhanced Sentiment Index Using POMS2 and SNS / Quantifying collective attention and fan engagement: a case study of the Japanese professional baseball league / News coverage of older drivers' fatal car crashes: is it over-represented? / Burstiness of human physical activities and their characterisation / 12-year observation of tweets about rubella in Japan: A retrospective infodemiology study / A two-phase model of collective memory decay with a dynamical switching point / SNSデータを用いた情報拡散シミュレーション / SNSにおける情報伝播ネットワークの構造 / Music Roles Affect the Selection of Consumption Means: A Questionnaire Survey of People’s Expectations for Music and Exploratory Factor Analysis / Dataset of identified scholars mentioned in acknowledgement statements / Classification of endogenous and exogenous bursts in collective emotions based on Weibo comments during COVID-19 / 日本におけるオンライン・ハラスメントの現状と対策：Twitterでの女性記者のツイート「炎上」を例に / 日本における自治体報道発表のCOVID-19発生状況を用いた感染者遷移状況の記録と可視化 / Simulation of information spreading on Twitter concerning radiation after the Fukushima nuclear power plant accident / 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― / サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して / Fake news propagates differently from real news even at early stages of spreading / 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 / Identifying long-term periodic cycles and memories of collective emotion in online social media / Correlations and fluctuations in the word sets of collective emotions / Configuration model for correlation matrices preserving the node strength</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>高齢運転者に関する報道とウェブ上の世論の可視化 / SNSから抽出した感情と実社会の関連性に関する研究 / Wikipedia閲覧数を用いた集合的記憶の減衰モデル / 保育現場への顔認証システム導入と運用の実証研究 / The identification of acknowledged scholars and their interdisciplinarity / Empirical studies on user-generated content and behavior of Southeast Asia community in Reddit / 日本プロ野球における集合的熱狂とファンの関与 / 仲値決定時近傍における板情報の非対称性の定量化 / 福島原発事故後のSNSにおける情報拡散シミュレーション / インターネットテレビにおけるコンテンツカテゴリ間の視聴数流動予測 / SNSを用いた新型コロナ禍における日本の空気感分析 / ソーシャルメディアを通した日本の高齢運転者に対する言論の定量化 / シラバスのテキストマイニングによる学生の主体性を育む科目の研究 / Wikipedia閲覧数を用いた集合的記憶の想起</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>数理物理・物性基礎 ; ウェブ情報学・サービス情報学 ; 社会政策・福祉 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 政策評価・計量分析 ; 会計・ファイナンス ; テキスト分析・NLP ; 医療・ヘルスデータ ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 社会ネットワーク分析 ; 計算社会科学 ; 行政データ分析 ; 学習分析</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>数理物理・物性基礎
 ウェブ情報学・サービス情報学
@@ -8570,7 +8805,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>高齢運転者に関する報道とウェブ上の世論の可視化
 SNSから抽出した感情と実社会の関連性に関する研究
@@ -8652,6 +8887,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>中小企業の雇用・技術と日本経済の再生
 経済環境の激変と中小企業の役割
 縮小経済のもとでの中小企業と企業家活動
@@ -8686,38 +8926,38 @@
 SNA統計を用いた民間法人企業ベースの「トービンのｑ」と投資関数</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>中小企業の雇用・技術と日本経済の再生 / 経済環境の激変と中小企業の役割 / 縮小経済のもとでの中小企業と企業家活動 / 中小企業の資金調達環境と政策のあり方</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>経済政策 / 財政・公共経済 / 経済統計</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Number of positive lymph nodes and lymphatic invasion are significant prognostic factors after pancreaticoduodenectomy for distal cholangiocarcinoma. / 開業と廃業 / 中小企業の知的財産 / Bankruptcy dynamics in Japan / 開業のダイナミクス－開業研究の展望と法人設立登記にもとづく実証分析－ / Which firms exit and why? An analysis of small firm exits in Japan / Video game demand in Japan: a household data analysis / 新企業の人材確保--事業所・企業統計調査と新企業調査の個票分析 / SME policy, financial structure and firm growth: Evidence from japan / Does the creative business promotion law enhance SMEs' capital investments? Evidence from a panel dataset of unlisted SMEs in Japan / Potential entrepreneurship in Japan / Consumption-leisure preference structure: A new explanation of the Evans-Jovanovic results for entrepreneurial choice / Consumption-Leisure Preference Structure: A New Explanation of the Evans-Jovanovic Results for Entrepreneurial Choice(Erratum, 24, 423-427, 2005) / Does the Creative Business Promotion Law Enhance SMEs' Capital Investment? Evidence from a Panel Dataset of Unlisted SMEs in Japan / The IT revolution and productivity growth in Japan / Small Business Owner-Managers as Latent Informal Investors in Japan: Evidence from a Country with a Bank-based Financial System / 企業家の労働時間－実証分析－ / 景況感とアンケート調査－変化方向と水準は異曲同工か？－ / Productivity and Entrepreneurial Characteristics in New Japanese Firms / Who Succeeds as an Entrepreneur? An Analysis of the Post-Entry Performance of New Firms in Japan / 少子・高齢化と日本の消費フロンティア / SNA統計を用いた「トービンのｑ」の計測結果の違いについて / 潜在的開業者の実証分析 / 起業の意思決定における所得・余暇の代替と流動性制約 / SNA統計を用いた民間法人企業ベースの「トービンのｑ」と投資関数</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>中小企業における労働力の質的不足の影響要因 / 企業の情報開示と株価</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>経済政策 ; 財政・公共経済 ; 経済統計 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 経営工学 ; 行政データ分析 ; 政策評価 ; マーケティング分析</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>経済政策
 財政・公共経済
@@ -8735,7 +8975,7 @@
 マーケティング分析</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>中小企業における労働力の質的不足の影響要因
 企業の情報開示と株価
@@ -8798,6 +9038,11 @@
         </is>
       </c>
       <c r="F10" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>大規模な両面市場に対する公平性を考慮した取引促進施策の包括的最適化
 混合整数最適化による次元縮約法の最良スパース推定
@@ -8864,42 +9109,42 @@
 混合整数2次錐計画法による回帰式の変数選択</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>大規模な両面市場に対する公平性を考慮した取引促進施策の包括的最適化 / 混合整数最適化による次元縮約法の最良スパース推定 / 混合整数最適化を用いた制約付き変数選択による高精度パラメータ推定 / ノンパラメトリック推定に基づくテスト理論モデルの研究 / カーネル法と制御ポリシーを用いた中長期的投資戦略最適化 / 取引コストを考慮した多期間ポートフォリオの最適化</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム / 数理情報学 / 統計科学 / 知能情報学</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>数理最適化 / 金融工学 / 機械学習</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Robust personalized pricing under uncertainty of purchase probabilities / Privacy-preserving recommender system using the data collaboration analysis for distributed datasets / 最適モデル多分木による価格需要曲線の推定 / Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times / DC algorithm for estimation of sparse Gaussian graphical models / Robust Portfolio Optimization for Recommender Systems Considering Uncertainty of Estimated Statistics / Fast Solution to the Fair Ranking Problem Using the Sinkhorn Algorithm / Mixed-Integer Linear Optimization Formulations for Feature Subset Selection in Kernel SVM Classification / Robust portfolio optimization model for electronic coupon allocation / 混合整数最適化による相続工程の長期化リスク採点システム / ECサイトにおける利用者属性データの欠損値補完 / Prescriptive price optimization using optimal regression trees / 構造的正則化処方分析による旅行パックの価格最適化 / Predicting Online Item-Choice Behavior: A Shape-Restricted Regression Approach / Cardinality-constrained distributionally robust portfolio optimization / Cutting-plane algorithm for estimation of sparse Cox proportional hazards models / Branch-and-bound algorithm for optimal sparse canonical correlation analysis / Dynamic portfolio selection with linear control policies for coherent risk minimization / Linear control policies for online vehicle relocation in shared mobility systems / 出産前後の情報検索の分析：数理最適化による検索日の確率分布推定 / ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析) / Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach / Sparse Poisson regression via mixed-integer optimization / 時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析 / データコラボレーション解析における統合関数の最適化 / A Design Method of the Joint Venture Formation in EPC Projects / 形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待) / サポートベクトルマシンとカーネル法 (特集 機械学習の手法と役割期待) / Smoothness-constrained model for nonparametric item response theory / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― / LDPC符号に対するタブー探索法に基づく勾配降下ビット反転復号法 / A Resource Flow Based Multistage Dynamic Scheduling Method for the State-Dependent Work / 数理最適化による学生のプロジェクト配属の決定 / 整数最適化復号法の性能評価 / 多重共線性を考慮した回帰式の変数選択問題の定式化 / A Simulation-Based Dynamic Scheduling Method in Project Cost Estimation Process / キークレーン間干渉を考慮したコンテナ事前配列問題 / 混合整数最適化による階層的変数選択を用いた店舗選択要因の分析 / ZIMPL言語とSCIPによる数理最適化 / 複数の販売チャネルでの購入を促進するための商品推薦手法 / Mathematical Optimization Models for Nonparametric Item Response Theory / 時系列モデルによる商品販促効果の分析 / 整数計画法による変数選択を用いた店舗選択モデル / 競争入札戦略と決定理論モデル / アドネットワークにおけるバナー広告入札戦略決定フレームワークの有効性の検証 / 確率計画法の理論と応用 / ECサイトの商品特性を考慮した2次元確率表による購買予測 / A Heuristic Bidding Price Decision Algorithm Based on Cost Estimation Accuracy under Limited Engineering Man-Hours in EPC Projects / 混合整数2次錐計画法による回帰式の変数選択</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>データ統合解析におけるアンカーデータ作成方法の提案 / 切除平面法による比例ハザードモデルの特徴選択 / 線形制御政策によるロング・ショートポートフォリオ最適化 / データコラボレーション解析における統合関数最適化問題の定式化と解法 / 多値型ノンパラメトリック項目反応理論の形状制約推定モデル / 最適化手法を用いた事例・変数統合型の欠損値補完 / 縮小推定を用いた平均・分散モデルによる推薦システム / 多重共線性を考慮した変数選択問題に対する切除平面法 / 2値分類の採点システムに対するbAUC最大化 / ロバスト平均・分散モデルを用いた推薦アルゴリズム / 確率制約付き最適化問題に対するDCアルゴリズム / シンクホーンアルゴリズムを用いた公平ランキング問題の高速求解 / 多重共線性を考慮した変数選択問題に対する高速厳密解法 / 深層学習を用いた巡回セールスマン問題の高速求解 / 強化学習を用いた競争入札戦略 / 予測評価値の不確実性を考慮した推薦商品集合の分布的ロバスト最適化 / 複数クーポンの効果推定と配布最適化 / コールセンターにおける会話データの分析 / 出産・子育てQ&amp;Aサイトにおける検索クエリの予測と分析 / 疎なWEB解答データの多次元項目反応理論分析</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム ; 数理情報学 ; 統計科学 ; 知能情報学 ; 保険・金融行動 ; オペレーションズリサーチ ; 機械学習 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 物流最適化 ; 最適化</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム
 数理情報学
@@ -8927,7 +9172,7 @@
 最適化</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>データ統合解析におけるアンカーデータ作成方法の提案
 切除平面法による比例ハザードモデルの特徴選択
@@ -9036,6 +9281,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>KPI工学教育研究の推進
 包摂的コミュニティプラットフォームの構築
 健康にやさしいまちづくりのための環境整備に係る実証事業
@@ -9079,42 +9329,42 @@
 Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>KPI工学教育研究の推進 / 包摂的コミュニティプラットフォームの構築 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 統合型ヘルスケアシステムの構築 / 文書生成AIサービス工学に関する研究 / 文書生成AIの企業内利活用における最適化の研究 / 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>会計学 / ウェブ情報学・サービス情報学 / 社会システム工学・安全システム / 経営学 / 商学</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>ビジネスインテリジェンス / 会計情報科学 / サービス工学 / ソーシャル・データサイエンス / 社会工学</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment / Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients / Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach / Estimation of conditional average treatment effects on distributed confidential data / Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support / Data collaboration for causal inference from limited medical testing and medication data / Generating Synthetic Journal-Entry Data Using Variational Autoencoder / Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data / An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises / Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 / pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis / 会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 / Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data / 分散機密データを想定した 処置効果の推定手法の開発 / 英文学術雑誌における近年の簿記研究 / Collaborative causal inference on distributed data / Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach / Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation / Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data / Knowledge sharing among coaches: expert power and social cognitive theory perspectives / Positive effect of proactive personality on customer orientation in service context / Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data / Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>個人の能動的先手行動がチームに与える影響に関する時系列分析 / 若者のエシカル消費の阻害要因に関する実証分析 / チーム全体の能動的先手行動を強化するチーム構成の実証分析 / 中小サービス企業における業績管理会計の効果的な実践に関する実証分析 / 地域健康政策のためのベイジアンネットワークを用いた推論モデルの研究 / シングルサイロを想定した解釈可能なデータコラボレーション解析の応用研究 / 傾向スコアを用いた特定健診・特定保健指導の効果検証 / 価値共創を活性化する店員の音声模倣スキルに関する実験的研究 / 糖尿病の予防政策のためのデータコラボレーション解析の応用可能性 / ベイジアンネットワークを用いたフレイルの発症予測モデリング：健康関心度の違いに着目して / マルチレベルモデルを用いたフレイルの地域および個人要因分析 / 糖尿病の因果構造の推定におけるLingamの応用可能性 / 営業部門の上司と部下の顧客意識が提案行動に与える影響 / 小売店の接客サービス中に生じる頷きの模倣に関する実験的研究 / データコラボレーション解析による地域中小企業の資金ニーズ予測 / NavigatorⅢの開発と実証分析 / 分散データに対する統合的クラスタリングの提案 / 営業チームにおける人事異動が能動的先手行動に与える影響 / 非接触呼吸識別技術によるコンサート観客の呼吸同期分析 / 若者の選挙投票に着目したアカウンタビリティの実験的研究 / 確率的潜在意味解析による擬人情報作成方法の提案 / 社会参加が主観的幸福感に及ぼす効果の疑似実験による検証 / GPSデータを用いた陸運の誤配送検知手法の提案 / 仕訳とビジネスプロセスの月次変化とキャッシュフローに関する研究 / 複式簿記の相互参照性情報を学習した業績予測モデルに関する研究 / 高齢者の運動習慣とメンタルヘルスとの関係の実証分析 / 中小企業の財務難予測モデルを解釈する反事実的説明手法の研究 / 非接触計測による生理指標を用いた患者のマルチモーダル感情認識の研究 / 孤独の選好と身体的・精神的健康状態との関係の実証分析 / 分散生存時間データに対するDC因果推論の拡張 / 能動的先手行動の形成プロセスについての縦断的研究 / 標準年限卒業予測における大学間転移学習の研究 / NavigatorIIIのパイロット企業における実証実験</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>会計学 ; ウェブ情報学・サービス情報学 ; 社会システム工学・安全システム ; 経営学 ; 商学 ; 社会政策・福祉 ; オペレーションズリサーチ ; 政策評価・計量分析 ; 会計・ファイナンス ; 医療・ヘルスデータ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 経営工学 ; 環境工学 ; 社会ネットワーク分析 ; 学習分析</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>会計学
 ウェブ情報学・サービス情報学
@@ -9165,7 +9415,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>個人の能動的先手行動がチームに与える影響に関する時系列分析
 若者のエシカル消費の阻害要因に関する実証分析
@@ -9262,6 +9512,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>ESG、開示とパフォーマンス：ノンパラメトリック手法を用いて
 CSRの実証研究：ノンパラメトリック推計アプローチ
 社会的責任活動の実証研究：企業のミクロ経済学的行動と政策分析
@@ -9276,34 +9531,34 @@
 Nonnegative Bias Reduction Methods for Density Estimation Using Asymmetric Kernels</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>ESG、開示とパフォーマンス：ノンパラメトリック手法を用いて / CSRの実証研究：ノンパラメトリック推計アプローチ / 社会的責任活動の実証研究：企業のミクロ経済学的行動と政策分析</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Subjective probabilistic expectations, household air pollution, and health: Evidence from cooking fuel use patterns in West Bengal, India / Seemingly Unrelated Interventions: Environmental Management Systems in the Workplace and Energy Saving Practices at Home / Cooking Fuel Choices --Analysis of Socio-economic and Demographic Factors in Rural India-- / Another Bias Correction for Asymmetric Kernel Density Estimation with a Parametric Start / Functional-Coefficient Cointegration Models in the Presence of Deterministic Trends / Do Social Norms Matter to Energy Saving Behavior?: Endogenous Social and Correlated Effects / Testing Symmetry of Unknown Densities via Smoothing with the Generalized Gamma Kernels / Family of the Generalised Gamma Kernels: A Generator of Asymmetric Kernels for Nonnegative Data / Nonnegative Bias Reduction Methods for Density Estimation Using Asymmetric Kernels</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>交通ネットワークと都市の成長ー西日本における高速道路建設が地方都市に与えた影響ー / 中国における結婚が健康に及ぼす影響 / 日本の賃金分布に対する反実仮想的要因分解 / ESGに関するSNS上での評判と企業パフォーマンス / 駅の開業が大気汚染に与えた影響の分析</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>保険・金融行動 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; マーケティング分析 ; 社会ネットワーク分析 ; 経営工学</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>保険・金融行動
 政策評価・計量分析
@@ -9322,7 +9577,7 @@
 経営工学</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>交通ネットワークと都市の成長ー西日本における高速道路建設が地方都市に与えた影響ー
 中国における結婚が健康に及ぼす影響
@@ -9371,6 +9626,11 @@
         </is>
       </c>
       <c r="F13" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析
 新規投資家の継続的な参入が価格形成・価格変動に与える影響
@@ -9410,42 +9670,42 @@
 A quantitative easing experiment</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析 / 新規投資家の継続的な参入が価格形成・価格変動に与える影響 / ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響 / 信用スコア社会に対応可能な評判管理システムの設計 / 験財消費のための情報収集行動とその支援情報提供システム / 市場参加者の価格予測の異質性と市場の振る舞いの関係について / 情報の非対称性と多様な期待形成がもたらす金融市場への影響とその安定化政策について / 国家の規模とガバナンスの学際的分析 / 情報コストゼロ社会における過剰懲罰とリスク軽減のための社会制度設計 / 新しい肺移植制度の構築と評価：ドナー交換移植の可能性</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>社会的ジレンマ、資産市場実験</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>検索連動型広告における循環的な入札額変動の発生機構の解明 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Bubbles in Asset Markets and the Heterogeneity of Beliefs. / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 / 進化ゲーム理論の進化 — マルチエージェントシミュレーション，実験室実験と，LLM の行動経済学— / 発話量と発話内容に基づく集団間のコミュニケーション円滑化システムの提案 / ソーシャルメディア上のアジェンダ設定がエコーチェンバーの発生に与える影響について / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. / Emergence of echo chambers in social media communication involving multiple topics / 進化ゲーム理論の進化：マルチエージェントシミュレーション, 実験室実験と，LLMの行動経済学 / 重みが動的なネットワークにおいてネットワーク構造が協力の進化に与える影響 / 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ / Individuals reciprocate negative actions revealing negative upstream reciprocity / SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. / Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement / Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim / パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 / 群淘汰状況下における罰則・報酬の進化 / Self-organized Speculation Game for the spontaneous emergence of financial stylized facts / 情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ / 時間制約を導入したゴミ箱モデル / Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment / 協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 / A quantitative easing experiment</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>条件付き協力のためのコストの存在が、ネットワーク上での協力の進化に与える影響 / 自動運転配車サービスが東京中心部の交通形態に与える影響の分析 / 問題の難易度と意思決定数の関係に双曲志向が与える影響-ゴミ箱モデルによるアプローチ- / 多重ネットワーク上での協力の進化 〜相互作用ネットワークと戦略更新ネットワークの非対称性が協力の進化に与える影響〜 / 重みが動的なネットワークにおいてネットワークトポロジーが協力の進化に与える影響 / リンク重みの異質性と情報開示率が協力の進化に与える影響 / ソーシャルメディア上での複数のトピックにわたるコミュニケーションが意見の分極化とエコーチェンバーの発生に与える影響 / 純粋リスク下において他者の選択がリスク態度に与える影響：経済実験によるアプローチ / 間接互恵による協力進化に記憶の減衰が与える影響 / 歩行者ラウンドアバウトによる整流効果-駅構内の混雑緩和- / 投機的リスク下でのピア効果がリスク態度に与える影響 / 懲罰に関する社会規範が間接互恵の進化に与える影響について:シミュレーションによるアプローチ</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム ; 保険・金融行動 ; 意思決定分析 ; マッチング理論・ゲーム理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 学習分析 ; マーケティング分析</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム
 社会的ジレンマ、資産市場実験
@@ -9477,7 +9737,7 @@
 マーケティング分析</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>条件付き協力のためのコストの存在が、ネットワーク上での協力の進化に与える影響
 自動運転配車サービスが東京中心部の交通形態に与える影響の分析
@@ -9556,6 +9816,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>「もう一つのモダニズム」による地域性の再構築 フェルナン・プイヨンの生涯業績
 中東・北アフリカ地域におけるヘレニズム基盤の継承に関する都市文献史的研究
 西アジア地域の都市空間の重層性に関する計画論的研究
@@ -9602,42 +9867,42 @@
 ビルマ王都マンダレーの城内および城外市街地の空間構造に関する研究</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>「もう一つのモダニズム」による地域性の再構築 フェルナン・プイヨンの生涯業績 / 中東・北アフリカ地域におけるヘレニズム基盤の継承に関する都市文献史的研究 / 西アジア地域の都市空間の重層性に関する計画論的研究 / 日本の貢献を踏まえた中東・北アフリカ地域の都市計画史-「イスラム都市」論を越えて / チュニジア－日本シンポジウム「イノベーティブ社会構築に向けたマネジメント戦略」 / アレッポの戦災状況調査と戦災復興都市計画原案の策定 / 多様性と共生の知恵を育む中東・北アフリカ地域の都市計画史 / 国際交流を背景とした中東都市計画史研究と都市保全プロジェクトへの還元 / モロッコの歴史都市 フェスの保全と近代化 / 現代イスラーム都市の多元的成り立ちに関する研究</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>都市計画・建築計画 / 建築史・意匠 / 地域研究</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>建築・都市計画史 / 地中海都市 / ヘレニズム基盤 / 歴史文化保全 / 国際協力 / 中東・北アフリカ</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” / フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― / 吉田正春使節団が見た19世紀テヘラン都市改造 / ジスカール・デスタン政権下のパリ歩行者空間整備 / 1960 年アガディール地震とその震災復興都市計画に関する研究 / フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 / フェルナン・プイヨンのベルカステル村修復に関する研究 ─城と村の一体性に着目して─ / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス / 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 / フェス 積み重なる寄進が形成した迷宮都市 / ガルダイア 丘の上の城塞とオアシス渓谷の集落 / Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development / The Urban Forming History of Dubrovnik During the 12th Until 17th Century / Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning / Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration / カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- / Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris / Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille / The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel / アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 / 19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 / 商業都市カサブランカにおけるトラム導入による社会空間変容 / ビルマ王都マンダレーの城内および城外市街地の空間構造に関する研究</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>ポルトガル植民地期におけるリオ・デ・ジャネイロの都市空間変容 / 戦後パリ郊外におけるフェルナン・プイヨンの住宅地計画 -アルジェ及びマルセイユの作品との比較から- / 中国・杭州市における近代宗教建築の展開 –1840〜1949年に建設されたキリスト教建築を対象に– / メキシコシティ旧水路空間の変遷に見る水都空間の重層性 / アンナバ新市街における伝統的商業空間の形成 / カイロ中心市街地の都市空間変容-イギリス統治下から共和制移行期に着目して / 乾燥地域における伝統的水利システムの洪水抑制効果―アルジェリア国ガルダイア県の事例― / 現チェコ共和国の諸地域におけるカミロ・ジッテの都市計画実作 / フェルナン・プイヨンのベルカステル村修復に関する研究-城と村の一体性に着目して- / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス / 上海・上生新所の都市イノベーション-歴史保全と現代的開発の融合- / 海上シルクロード都市ザイトゥーン（中国・泉州）における遺産の保全と活用 / A Historical Survey of Spatial Customisation in the Modern Planned City of Abuja, Nigeria</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>都市計画・建築計画 ; 建築史・意匠 ; 地域研究 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 都市計画 ; 社会ネットワーク分析 ; 人間中心設計 ; 災害分析</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>都市計画・建築計画
 建築史・意匠
@@ -9672,7 +9937,7 @@
 災害分析</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>ポルトガル植民地期におけるリオ・デ・ジャネイロの都市空間変容
 戦後パリ郊外におけるフェルナン・プイヨンの住宅地計画 -アルジェ及びマルセイユの作品との比較から-
@@ -9752,6 +10017,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>衛星情報を利用した物流における大気環境改善の評価
 独占的競争下での環境オフセットの自発的供給に関する研究
 都市における環境リスクの軽減の経済効果に関する研究
@@ -9789,42 +10059,42 @@
 東京都心部における賃貸集合住宅価格の付加価値要因に関する研究</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>衛星情報を利用した物流における大気環境改善の評価 / 独占的競争下での環境オフセットの自発的供給に関する研究 / 都市における環境リスクの軽減の経済効果に関する研究 / Radon測度上の動的システムの研究と都市構造遷移モデルへの応用 / 新たな集積効果関数を用いた都市一般均衡モデルの構築 / 通信技術の発達と住宅地地価の都市経済的分析 / 通信技術革新と都市空間構造の自己組織化 / 海外における中間財生産による国内都市空間構造の変化に関する研究 / 都市内立地の内生的決定に関する数値計算的アプローチ / 都市内情報流を考慮した空間構造の自己組織化</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>経済政策 / 理論経済学</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>都市構造</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Dual Chalcogen-Bonding Interactions for the Conformational Control of Urea / Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone / Life Cycle Analysis and Cost–Benefit Assessment of the Waste Collection System in Anyama, Cote d’Ivoire / Green Markets, Free Riders, and Monopolistic Competition / Relationship between urban population growth and utility level of workers with heterogeneity of labor efficiency / Environmental offsets and production externalities under monopolistic competition / Implications of urbanization and Impact of Population Growth on Abidjan City, Cote d’Ivoire / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― / 通信技術革新と企業内立地行動の変化に関する研究-通信の固定費用を考慮して- / 通信技術革新と企業内立地行動の変化に関する研究 / Communication technologies and spatial organization of multi-unit firms in metropolitan areas / 企業の分離立地にともなう副都心成立の均衡土地利用分析 / The Influence of the Great Hanshin-Awaji Earthquake on Housing Market of the Area / 東京大都市圏の効用分布の推計と住居選択モデルの応用可能性に関する研究 / テレコミューティングの普及と都市構造に関する研究 / 複数都心を持つ都市構造の動的安定性に関する研究 / 首都圏における通勤家計の居住地選択モデル / 2種類の企業による都市の均衡形状に関する研究 / 大都市圏における近年のテレコミューティング（在宅勤務）と都市構造の均衡分析 / 東京都心部における賃貸集合住宅価格の付加価値要因に関する研究</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>広域行政が自治体の財政に与える影響 / 長時間労働が中国人の健康に与える影響に関する研究 / 中国・広州市における高齢者施設の空間的アクセシビリティ評価 / 羽田空港の新飛行経路の騒音は周辺住宅価格への影響 / 中国の住宅資産と負債が高等教育進学率への影響と性別差異 / ネット・口コミが消費者行動に与える影響に関する研究～丸亀製麵を例として～ / 地方都市の駅まち空間再構築事業による地価変化の計量分析 / 地方都市におけるスマートシティ事業の実装が地価に与える影響 / 鉄道廃線敷のBRT化が地域に与える影響について / 中国における農村金融の格差に関する影響要因分析及び政策分析。ー中国“十二五”計画を中心に / 「国立公園満喫プロジェクト」が関連地域の地価に与える影響ー先行８公園を対象としてー / ハイテク企業のイノベーションが地価に与える影響 / 中国におけるライブコマースが農村振興に与える影響に関する分析 / 国際スポーツ大会の開催決定がスタジアム周辺地域に与える影響についての研究―地価の変化に注目して― / Park-PFIによる公園整備が商業地域の地価に与える影響 / ウォーカブル向上による関連地域の地価変化に関する研究 / 水害についてのリスク認識の変化が地価に及ぼす影響 / 高速鉄道が沿線地域に与える影響の実証研究―徐蘭高速鉄道を例として― / 中国における子供性別が家計の資産配分に与える影響―不動産を研究対象として― / LRT導入による地価への影響―宇都宮ライトレールを事例として―</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>経済政策 ; 理論経済学 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 画像・視覚情報処理 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 物流最適化 ; 災害分析 ; 社会ネットワーク分析 ; 行政データ分析</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>経済政策
 理論経済学
@@ -9874,7 +10144,7 @@
 行政データ分析</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>広域行政が自治体の財政に与える影響
 長時間労働が中国人の健康に与える影響に関する研究
@@ -9959,6 +10229,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>ジェネレーティブデザインを通じて敷地計画における創造力はどこまで拡張できるか
 創造性の論理的・ 技術的探求に基づくデザイン共創環境の構築と教育プログラムの開発
 コンパクトシティを目指した都市デザイン戦略のための都市構造評価指標の探究
@@ -9998,42 +10273,42 @@
 土地利用の混在指標を用いたわが国の都市圏の形態分析 ―埼玉県東部を対象としたMetropolitan Form Analysis― Land-Use Mixの適用―</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>ジェネレーティブデザインを通じて敷地計画における創造力はどこまで拡張できるか / 創造性の論理的・ 技術的探求に基づくデザイン共創環境の構築と教育プログラムの開発 / コンパクトシティを目指した都市デザイン戦略のための都市構造評価指標の探究 / 伝統的市街地の景観形成支援手法の研究 / 博士課程「短期在学コース」の創設に関わる課題等に関する調査研究 / 伝統的都市の現代化における空間制御を支援する情報技術の開発 / 伝統的都市の現代化における空間制御技術に関する研究 / 「建築情報モデラーに関する研究」に対する / ポスト定住化社会における時空を超えたアクティビティの流動化実態に関する実証的研究 / 拡張現実技術を利用した実空間景観シミュレーションシステムの開発</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>都市計画・建築計画 / 社会システム工学・安全システム</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>情報化・ネットワーク社会における建築計画・都市計画</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>歩行者の空間学習を支援するナビゲーション手法に関する研究 / 超一線都市の若者向けマンションの立地分析：広州を例にして / 街路網の広がりから見た城下町の空間構成の変容に関する研究 / 総合設計制度による建築物が街路景観の印象に与える影響に関する研究 ―3D都市モデルPLATEAU及びVR を用いて― / 都市の集約化が分散型エネルギーシステム導入に与える影響について / デザイン共創環境を用いた集合住宅設計支援ツールの開発 / An analysis on urban shrinkage trends of all Japanese cities by detecting relative densely inhabited districts - Changes in urban form of Japanese cities in an era of shrinking population, part 2 / モビリティ技術活用による新しい児童通学スタイルの検証 / デザインパターンの列挙に関する一考察 / 相対的な人口集中地区の抽出を通じた全国市町村の都市縮小傾向の分析 －人口減少時代を迎えるわが国の都市圏の形態変化に関する研究（その2）－ / Exploring the Panel Exercises in the Modulor as presented by Le Corbusier / 歩行空間ネットワークを用いた駅周辺の回遊性に関する研究 －埼玉県大宮駅周辺を事例として－ / ル・コルビュジエが提示したモデュロールによる羽目板遊びの探求 / 中国安慶市の敬老院における整備実態の居住者の満足度に関する研究 / BIMと修繕記録を用いた既存建物の部位等の更新間隔算出 / 共育 ～ともに育て、ともに育つ保育園～ / ソーシャルメディアの投稿写真からみた地域特性に関する考察 / 媒介中心性を用いた歩行者の回遊行動に関する検討 - Walkability 指標の計測へ向けて - / 情報量損失最小化法を応用した相対的人口集中地区の抽出; 都市縮小・拡大市町村数の経年変化分析 / 上海中心市街地におけるGated Communityが飲食店への徒歩到達アクセシ ビリティに与える影響 / デジタル・モデュロール３ / AN ANALYSIS OF MIXED LAND USE TOWARD DESIGNING THE COMPACT CITY / 都市のWalkabilityに関する研究 ―Urban Network Analysisを用いた評価指標計算に向けて― / 土地利用の混在指標を用いたわが国の都市圏の形態分析 ―埼玉県東部を対象としたMetropolitan Form Analysis― Land-Use Mixの適用―</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>市民の屋外公共空間活用に対する自治体の支援実態とその在り方ー市民の屋外空間における音楽活動支援に着目してー / 景観計画下での屋外広告物等の実態と伝統的都市景観に対する若者の景観認識—京都市を事例に— / 発達障害者の空間認知からみたナビゲーションのあり方に関する研究 / 中国における大学城の土地用途変遷と利用者の満足度について—呼蘭、下沙、広州大学城を対象にして— / デザイン共創環境を用いた集合住宅設計支援ツールの提案 / 中国旧市街地のゲーテッドコミュニティの再生に関する研究 ー河南省鄭州市を事例としてー / 都市の集約化と分散型エネルギーの導入適性に関する研究 / 総合設計制度による建築物が都市空間に与える圧迫感に関する研究-3D都市モデルPLATEAU及びVRを用いて- / 歩行者の空間学習に関する研究－ナビゲーション手法と環境的特徴に着目して－ / 超一線都市の若者向けマンションの立地分析と最適化－広州を例にして－</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>都市計画・建築計画 ; 社会システム工学・安全システム ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 都市計画 ; 数理最適化 ; 環境工学 ; 強化学習</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>都市計画・建築計画
 社会システム工学・安全システム
@@ -10072,7 +10347,7 @@
 強化学習</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>市民の屋外公共空間活用に対する自治体の支援実態とその在り方ー市民の屋外空間における音楽活動支援に着目してー
 景観計画下での屋外広告物等の実態と伝統的都市景観に対する若者の景観認識—京都市を事例に—
@@ -10149,6 +10424,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>まちづくりを含む不動産開発に関する指導
 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究
 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会
@@ -10195,42 +10475,42 @@
 地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>まちづくりを含む不動産開発に関する指導 / 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 超高層住宅の二重の老いの潜在的課題に関する研究 / 社会的孤独の解消モデル事例のプロセス分析及び検証手法の検討 / つくば市みどりの分譲地のまちづくり提案について / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築 / 超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>都市計画・建築計画</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>都市計画 / 地区計画 / まちづくり / カナダの都市計画 / 団地再生 / 住環境整備 / 産官学民連携 / 地域活性化 / コミュニティビジネス</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として / わがまちのSDGs / 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ / 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 / 京都市東松ノ木市営住宅 / 国勢調査分析からみる外国人集住団地の実態 / 増加する外国人の受け皿としての住宅団地 / 住宅団地の外国人集住：特集の趣旨 / 住宅地における地区計画や認可協定の今後 / 区分所有マンションを含む市街地再開発事業の有効空地を考える / 社会的包摂とデザイン─「つながる場」15事例の実践から / 外国人住民との共存・共生: 海外の事例からの示唆 / 首都圏郊外におけるリノベーションまちづくりの成果と課題に関する研究 / 住宅建替えと一体的に再整備された街区公園の維持管理活動を通じたコミュニティ形成に関する研究 / 計画的戸建住宅地における駐車場シェアの導入意向と活用可能性に関する研究 / 多様な主体が関わる出産祝いプロジェクトの成立経緯と参加主体にもたらす変化に関する研究 / 職員の活躍を願う市長の思いと取り組み / 今後の地域づくりへの期待 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea / 転換期にある筑波研究学園都市の地区計画が空間資源継承に果たす役割と課題 / 1980年以降、40年の「つくば」の変化と現状 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea, Urban Planning / Living Lab Participants’ Knowledge Change about Inclusive Smart Cities: An Urban Living Lab in Seongdaegol, Seoul, South Korea / 地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>計画的戸建住宅地におけるスペース・シェアリングの展開可能性と受け入れ条件の検討 / 転換期にある筑波研究学園都市の地区計画が地域資源継承に果たす役割と実態 / 地域課題解決に取り組む空き家の活用過程の課題に関する研究―茨城県常総市水海道地区を対象にー / 筑波研究学園都市における市民に向けたサイエンスコミュニケーションの実態と課題 / 絶対高さ型高度地区導入後の展開と課題 / 高齢者情報格差の実態と対応策の検討：つくば市スーパーシティモデル地区を対象に / 民俗芸能の継承と観光活用意向に関する研究―岩手県北上市に着目してー / スペースシェアリングを活用した計画的戸建住宅団地の再生方策に関する研究 / 人材育成事業を契機とした地域活動拡大に関する研究 / 大都市郊外住宅団地における多世代交流活動の展開に関する研究 / 工業地帯の土地利用転換による知識集約型産業集積の実態と課題 －スペイン・バルセロナ市22＠プロジェクトを対象として－ / ごちゃまぜを理念とする多機能型福祉拠点の成立要因と意義に関する研究 －石川県社会福祉法人佛子園「三草二木 西圓寺」を対象として－ / 移住増加地域における遊休不動産を活用した新規事業の成立要因に関する研究 －長野県小諸市中心市街地を対象として－ / 超高層住宅集積地における利活用・維持管理の実態を踏まえた公開空地等の課題に関する研究 －東京都中央区第3ゾーンを対象として－</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>都市計画・建築計画 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 都市計画 ; 社会ネットワーク分析 ; 人間中心設計 ; 行政データ分析</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>都市計画・建築計画
 都市計画
@@ -10271,7 +10551,7 @@
 行政データ分析</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>計画的戸建住宅地におけるスペース・シェアリングの展開可能性と受け入れ条件の検討
 転換期にある筑波研究学園都市の地区計画が地域資源継承に果たす役割と実態
@@ -10352,6 +10632,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発
 ネットワーク上の時間軸をもった最適化問題とその応用
 スタッフスケジューリングに関する研究
@@ -10390,38 +10675,38 @@
 A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 / ネットワーク上の時間軸をもった最適化問題とその応用 / スタッフスケジューリングに関する研究 / 組合せ最適化，ネットワーク最適化のアルゴリズム開発 / ネットワーク構造解析アルゴリズムの開発とネットワークアルゴリズムの総合的展開 / ネットワーク理論の基盤整備と伸張 / データの精度を考慮した組合せ最適化問題に対する問題構造とアルゴリズムの研究 / 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
         <is>
           <t>最適化 / 組合せ最適化 / アルゴリズム</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs / Break maximization for round-robin tournaments without consecutive breaks / Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm / Height Estimation for Abrasive Grain of Synthetic Diamonds on Microscope Images by Conditional Adversarial Networks / Designing of OTN/WDM networks withrecovery methods for multiple failures / Restaurant Sales forecasting with feature interaction-learning mechanism based neural network model,IEEE International Conference on Big Data / A Discrete JAYA Algorithm for Long-Term Carpooling Problem / Carry-over Effect Values Minimization under Circle Method and Binary Factorization Based on Jaya Algorithm / Application of Data Anonymization to Smartphone Apps Usage Logs / 数理最適化を用いたサービス工学の事例―通勤カープールの実証実験― / Four-level knowledge graph contrastive learning structure for smart-phone application recommendation / A New Approach to Market Segmentation Based on 2-Dimensional Tables / Challenges of commuter carpooling with adapting to Japanese customs and regulations: A pilot study / Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model / Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan / Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament / 交換移植制度におけるドミナントマッチングの適用可能性 / Network Design Models with Partial Protection Schemes against Multiple Failures under Optical- Channel Data Unit Constraints / ILP models and improved methods for the problem of routing and spectrum allocation / A novel channel-based model for the problem of routing, space, and spectrum assignment / NASH EQUILIBRIA FOR INFORMATION DIFFUSION GAMES ON WEIGHTED CYCLES AND PATHS / Strongly separable matrices for nonadaptive combinatorial group testing / Modeling and Evaluating Taxi Ride-sharing for Event Trips / 不均衡データに対する多段階学習を用いた アンサンブルモデルによる2 クラス分類アルゴリズムの提案 / A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>外国人居住者向けWebサイトのアクセスログ解析による主要な遷移の特定 / 並列機械バッチスケジューチング問題に対するヒューリスティックアルゴリズム / ネットワーク拡張ゲームの均衡解を求める一解法 / 市場分析における遺伝的アルゴリズムを用いたサンプルデータ抽出 / 光通信ネットワークの耐故障二層モデルの比較と評価 / 深層学習を用いた平面画像上の物体の高さ推定 / ブレークに関する公平性を考慮した総当たり戦スケジューリング / プラスチック製部品製造工場における成形工程の生産スケジューリングモデル化と実応用 / 実応用にむけた多品種少量生産スケジューリング / byesを用いたスポーツスケジューリングの移動距離に関する検討 / ジョブショップスケジューリングの実応用へ向けた二つのアプローチ / 欠勤者を考慮した通勤カープールモデルの提案 / 2部グラフ上のポピュラーマッチングの要素数に着目した特徴づけ / スポーツ競技のスケジュール作成における Carry-Over Effect 値最小化に関する検討 / 次世代光伝送網における資源割り当てIPモデルとヒューリスティックアルゴリズム / 深層学習を用いたレストラン売り上げの予測モデルの構築と実応用 / 安全性と日本の法規制を考慮した通勤カープールモデルの提案と評価 / テクスチャ解析手法による2次元画像の砥粒群の形状分類 / 飲食店におけるスタッフのスキルを考慮したシフト作成のモデル構築と自動化 / 耐故障性を持つ二層光ネットワーク設計問題 / 飲食店の業務標準化に向けた最適な調理手順モデリング / 並列機械スケジューリング問題における多様な解の生成 / 空間分割多重光伝送網における通信保護を考慮した資源割当問題の効率的計算方法の検討 / ジョブショップスケジューリング問題に対する深層学習を用いたヒューリスティックアルゴリズム / A Contrastive Learning Structure for Prediction of smartphone applications to use next / 知識グラフの対照学習におけるグラフサンプリング手法の検討 / 大規模なカープーリング問題に対するK-medoidsクラスタリングを用いた二段階アルゴリズム / データ匿名加工手法のスマートフォンアプリ利用ログへの適用可能性 / 光通信ネットワークにおけるスプリットスペクトルを取り入れた資源割当モデルの提案 / ネットワーク上の耐故障性のある centdian 配置問題 / スマホアプリデータにおける推薦システムの活用 / 動的最短経路阻止モデルの拡張と観察 / 総当たり戦における試合間隔差の最小化問題 / 双曲空間とグラフニューラルネットワークを用いたCross-Domain推薦システムモデル / 高次元データに対するクラスタリングアプローチ / 高齢者通所介護施設における訪問時刻幅を持つ送迎サービスモデル / 訪問介護における訪問順序の最適化 / 待ち時間を考慮した通勤カープールモデル / 試合間隔の公平性を考慮した同時制約を持つ対戦表作成 / 飲食店の調理スケジューリング問題に対するメタヒューリスティクスの適用 / 光ネットワーク上の資源割当問題における候補パスの選択 / Pointer Networksを用いた飲食店における調理スケジューリング</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 社会ネットワーク分析 ; ネットワーク科学</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>最適化
 組合せ最適化
@@ -10440,7 +10725,7 @@
 ネットワーク科学</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>外国人居住者向けWebサイトのアクセスログ解析による主要な遷移の特定
 並列機械バッチスケジューチング問題に対するヒューリスティックアルゴリズム
@@ -10548,6 +10833,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>特殊詐欺に「騙されても被害に至らない」社会システムの構築に向けた実証研究
 情報提供と環境手がかりによる行動変容：ナッジ犯罪予防の定式化とその効果検証
 日本における農村犯罪学の創成に向けた萌芽研究：窃盗犯を事例とする実態分析
@@ -10592,42 +10882,42 @@
 サイバー・フィジカル空間上の社会的交流と居住地の近隣環境</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>特殊詐欺に「騙されても被害に至らない」社会システムの構築に向けた実証研究 / 情報提供と環境手がかりによる行動変容：ナッジ犯罪予防の定式化とその効果検証 / 日本における農村犯罪学の創成に向けた萌芽研究：窃盗犯を事例とする実態分析 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / 安全と身体活動を両立するActive School Travelの探究と都市計画・デザイン手法の確立 / 地理空間ビッグデータを用いた犯罪の時空間分析と社会実験への展開 / 警察の情報発信における「信頼」－行動科学・倫理学・政策科学からの学際的問題解決 / 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究 / 集合住宅における子ども・女性に対する犯罪の実態分析と対策立案 / 地理的犯罪予測の手法構築‐学際研究と産官学連携による学術基盤の確立とシステム開発</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム / 都市計画・建築計画 / 環境農学（含ランドスケープ科学）</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>都市計画 / 犯罪科学 / 空間情報科学 / 環境心理学</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて / 都市公園における逸脱行為に関する縦断的研究 / 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 / Mechanisms contributing to road network growth in volunteered street view imagery data / 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して / 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として / 人口低密度地域における人々の活動から見た「都市の活力」の計測 / 全国のJAを対象とする果物盗被害に関するアンケート調査報告 / Regional variations in key factors of children's independent mobility across Japan / 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 / Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives / Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) / Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning / 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 / GPSロガーを用いた官民による果樹盗パトロールの計測 / 子供の前兆事案被害情報の主体間共有の実態 / 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 / Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) / 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して / GPSログに基づく行動推定データを用いた人々の社会的接触可能性の時空間的把握 / サイバー・フィジカル空間上の社会的交流と居住地の近隣環境</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>COVID-19緊急事態宣言に伴う社会変化と犯罪の関連 / 小規模公園の廃止プロセスの実態と評価：社会受容と地域活性化の視点から / Methodology for applying a crowdsourced street view imagery data to evaluate street-level greenness / 留学生の帯同家族におけるソーシャルサポートの実態 / 子供を対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因 / 余暇歩行と近隣の土地利用の配置及び道路構成パターンとの関連 - GULPデータを用いて - / 地方部におけるSNSを介した観光関連情報の授受と観光行動や旅行地に対する愛着の関係 / 子どもを対象とする前兆事案に関する保護者・警察・学校の情報共有の実態と要因 / 自主防犯行動促進の観点から見た警察SNSの評価 / 新たな防犯活動としての「ながら見守り」の実態と評価 / 多拠点生活者の特徴からみた地域への参入可能性の解明 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 / 刑務所出所者の地域生活定着に向けた訪問支援制度の実態と評価 / 若年層のサイバー・フィジカル空間におけるパーソナルネットワークと個人・居住地特性 / 筑波研究学園都市における公務員宿舎の廃止・再開発が人口移動・住民構成・コミュニティ活動に与える影響 / 人々の社会的接触可能性の時空間的把握とその要因：人口低密地域での検討 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム ; 都市計画・建築計画 ; 環境農学（含ランドスケープ科学） ; 意思決定分析 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 建築・空間設計 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 農業情報学 ; 災害分析 ; 環境工学</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム
 都市計画・建築計画
@@ -10680,7 +10970,7 @@
 環境工学</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>COVID-19緊急事態宣言に伴う社会変化と犯罪の関連
 小規模公園の廃止プロセスの実態と評価：社会受容と地域活性化の視点から
@@ -10763,6 +11053,11 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として―
 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討
 リアルタイム場面におけるサービス・インタラクション理論の構築と実証
@@ -10803,42 +11098,42 @@
 Analogical decision making in career choice</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として― / 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討 / リアルタイム場面におけるサービス・インタラクション理論の構築と実証 / 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 / 慢性ストレスがヒトの生理心理状態に与える影響とその対処法 / 犯罪不安に関する認知・感情プロセスのモデル化とその応用 / 逸脱行動が生起するプロセスと矯正方法に関する研究 / 進路意思決定における認知・感情過程のモデル化 / 教師教育教材を事例としたマルチメディア教材設計・評価手法の開発</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>社会心理学 / 実験心理学</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>意思決定 / 認知心理学 / 社会心理学 / 感情</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Factors that foster individual willingness to serve in rehabilitation-oriented penal sector volunteer roles in Japan / 後悔を力に変える / Exploring the Relationship Between Different Consumer Behaviors and Subjective Well-Being in Japan: A Focus on Prosocial, Sustainable, Experiential, and Conspicuous Consumption / The Effect of General Trust on Willingness to Communicate in English among Japanese individuals across various situations. / Factors influencing behavioral intentions in livestream shopping: A cross-cultural study / Does macro-level general trust influence second language communication? :targeting prefectural capitals. / The influence of online multiplayer games on social capital and interdependent well-being in Japan / オンライン入試の実施と問題点 / 一般市民の更生支援に対する認知および参加意向の向上にむけた検討 / Understanding confidence in the human papillomavirus vaccine in Japan: a web-based survey of mothers, female adolescents, and healthcare professionals / Simulation of Outpatient Flow at the University of Tsukuba Hospital / Frequency of grooming the eyebrows and cosmetic consciousness in men. / The relationship between quantity of information contact and public evaluation of volunteer probation officers to promote understanding for social reintegration support. / Factors influencing differences between useful and useless regret. / The relationships between a metacognition scale and adaptive behavior in the regret situations: A comparison between junior high-school and university students. / Understanding confidence in human papillomavirus vaccine in Japan: A web-based questionnaire survey of mothers, female adolescents, and health care professionals. / 裁判員参加意向を規定する要因および意思決定プロセスの差異：制度施行前後の比較 / 市民の生態系サービスへの認知が保全行動意図に及ぼす影響：全国アンケートを用いた社会心理学的分析 / どのようにリスクを伝えればよいか：よりよいリスクコミュニケーションのために必要なこと / 意思決定から見たギャンブル行動 / Change of decision-making processes in repeated risk-taking behavior in a complex dynamic situation / The neural networks model of decision-making including feedback processes / Research on the gaps between students' expectation and satisfaction for universities / Analogical decision making in career choice</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>中学生の達成目標志向が学業成績に影響を及ぼすプロセスの検討：社会的比較感情・行動を媒介にして / ブランドのSNS活動における製品カテゴリが消費者のSNS使用に与える影響 / 中国人大学生におけるダイエット行動に関連する心理・社会的要因についての検討ー身体不満足感とやせ願望に着目してー / ユーザー生成コンテンツがアプリの粘着性と消費者の購買意図に与える影響に関する研究 / 在日中国人留学生の異文化適応に関する研究 / 個人差要因およびマンガ作品内の表現がマンガ読書行動に与える影響 / 福祉・介護サービス従事者のコミュニティ感覚とメンタルヘルスの関連性について / 新しいメディア環境におけるライブコマースが消費者心理と行動に影響を及ぼす要因の検討 / 中国人大学生のとりあえず進学に関する研究―個人差要因と学校適応感に着目して / 看護師支援における共感疲労に影響を及ぼす要因 / 読書状況が変えるネタバレ選好 / グリーン購入における他者の影響 / An Investigation of the Factors Influencing college student Volunteering motivation - In Perspectives on prosocial behaviour</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>社会心理学 ; 実験心理学 ; 労働経済・就職マッチング ; 意思決定分析 ; 都市・地域政策 ; 政策評価・計量分析 ; テキスト分析・NLP ; 医療・ヘルスデータ ; 公共政策・社会工学 ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 社会ネットワーク分析 ; マーケティング分析 ; 学習分析</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>社会心理学
 実験心理学
@@ -10882,7 +11177,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>中学生の達成目標志向が学業成績に影響を及ぼすプロセスの検討：社会的比較感情・行動を媒介にして
 ブランドのSNS活動における製品カテゴリが消費者のSNS使用に与える影響
@@ -10961,6 +11256,11 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>持続可能な観光のための戦略的オーバーツーリズム対処療法の構築
 持続可能な観光地形成に向けた複雑系モデルとそれを用いた合意形成ツールの開発
 意識分析にもとづく国外旅行意向の国際比較研究
@@ -11008,42 +11308,42 @@
 観光地における地域ブランド構築の内部関係者による資源活用パターンと課題構造に関する研究 - 関東・甲信越地域の市町村を対象として -</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>持続可能な観光のための戦略的オーバーツーリズム対処療法の構築 / 持続可能な観光地形成に向けた複雑系モデルとそれを用いた合意形成ツールの開発 / 意識分析にもとづく国外旅行意向の国際比較研究 / 観光振興のためのマーケットデザインに関する研究－効果的な日本型DMO構築に向けて / 複数の観光交通データの融合的活用方法の開発と政策評価への展開 / 道路インフラマネジメントサイクルの展開と国内外への実装を目指した統括的研究 / 交通関連調査体系の再構築と政策評価への展開 / 道路パフォーマンス指標の開発 / コンテナ港湾機能配分に関する研究 / 観光交通の需要分析</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>土木計画学・交通工学 / 観光学</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>交通 / 観光 / 社会資本 / プロジェクト評価 / 港湾 / 物流 / オーバーツーリズム / 都市計画 / 費用便益分析</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>人口分布とネットワークを考慮したコミュニティバス運営負担に関する実証分析 ～茨城県の自治体を対象として～ / Analysis of Changes in Demand before and after the Restructuring of “Tsukubus” / Simulation Analysis of Tsunami Evacuation Behavior for Residents and Seabathers Under Mixed Pedestrian-Automobile / A Study of Recovery from Shocks Lead by Crisis in the Field of Tourism / Examination of A Risk Management Through Technical Transitions in The Railway ATS System / バス利用に影響を与える要因の検討－利用者意識調査とマクロ分析に基づいて－ / Consciousness Analysis on Travel Behavior and Intention of People in Mainland China / 道路ネットワーク上の交通荷重情報収集を目的とした車重計の配置方法 / つくば市における宅配便の利用実態と再配達依頼の規定因―配達人とのコミュニケーションに着目してー / 渡航回数に着目した中国人の旅行意向形成に関する研究 / 観光流行現象の変遷に関する基礎的考察 / 茨城県内の市町村における橋梁維持管理の実態に関する研究 / 英国を事例とした我が国の空港運営政策に関する一考察 / GPSログデータを用いた訪日外国人旅行者の訪問パターンの分析手法の開発 / 東京近郊観光地におけるインバウンド観光プロモーション施策の考察 / 人口分布統計データを活用した観光地の特性把握 / 高齢者の交通環境改善に向けた新たな交通手段の利用可能性に関する研究 / ガソリンスタンドの経営収支と需要を考慮した存続可能性に関する研究 / 効果的な鉄道の安全対策が新たな課題を惹起する―「安全の 4M」と「リスク」の体系化による考察とマネジメントの重要性― / 地域鉄道の維持に関する考察-時 系列データによる検討- / 都市高速道路における交通状態推定問題およびセンサー配置問題に対するデータ同化アプローチ / 橋梁および高速道路上の横断構造物に対する維持管理の実態と課題 / 国内旅行におけるリピーターの行動特性及び醸成要因に関する研究 / 観光地における地域ブランド構築の内部関係者による資源活用パターンと課題構造に関する研究 - 関東・甲信越地域の市町村を対象として -</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>鉄道の運行支障時における駅周辺道路の交通実態に関する研究 / 自動車の走行距離課税制度に対する社会的受容性に関する研究 / 公共交通のネットワーク形態が自治体の負担に与える影響に関する研究 / 高速交通ネットワークの発展に伴う基幹交通の組合せ利用に関する研究 / つくば市における公共交通に対する住民満足度の要因分析 / 地方誘導型インバウンド政策がもたらす経済的影響に関する研究 / 国内旅行実態の経年的変化に関する基礎的研究 / 津波避難シミュレーションを用いた海水浴場の危険性評価 / 地域公共交通に関する利用者意識調査の活用方法の検討 / Difference of tourists‘ behavior by transportation mode in Kamakura City / TX開通による沿線エリアの交通需要とアクセシビリティ変化に関する研究</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>土木計画学・交通工学 ; 観光学 ; 交通・モビリティ ; 政策評価・計量分析 ; 観光・マーケティング ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 観光情報学 ; 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>土木計画学・交通工学
 観光学
@@ -11079,7 +11379,7 @@
 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>鉄道の運行支障時における駅周辺道路の交通実態に関する研究
 自動車の走行距離課税制度に対する社会的受容性に関する研究
@@ -11157,6 +11457,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>津波で失われた景観の再現による記憶の抽出と日常生活に結びついた場の解析
 低環境負荷型住まい方の実践とソーシャル・キャピタル向上の相乗効果を誘発する都市デザイン－インドネシア・ジャカルタの中層住宅における建築空間・住民行動・コミュニティの関係分析
 津波で失われた景観のデジタル再現と記憶の分析によるコミュニティが共有する場の解析
@@ -11192,38 +11497,38 @@
 地域・土地との関係性の希薄化</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>津波で失われた景観の再現による記憶の抽出と日常生活に結びついた場の解析 / 低環境負荷型住まい方の実践とソーシャル・キャピタル向上の相乗効果を誘発する都市デザイン－インドネシア・ジャカルタの中層住宅における建築空間・住民行動・コミュニティの関係分析 / 津波で失われた景観のデジタル再現と記憶の分析によるコミュニティが共有する場の解析 / 量から質へのシフトを実現するための緑地の計画制度・設計手法・運用方法の研究 / 樹冠表面温度を利用した都市気温分布図の作成と緑地の気候緩和機能の分析 / リモートセンシングを活用した生物季節学図の作成と都市微気候の評価</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
         <is>
           <t>都市農村計画 / 緑地計画</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>グリーンインフラ整備を支える緑化技術研究 / 熱的快適性が屋外空間における滞在状態に与える影響に関する研究 / グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例 / 2023年度一般公開シンポジウム開催報告 / 座談会 「緑の基本計画」のこれからを考える座談会 : 制度創設30年目を迎えて / 量から質への転換 / 人と土地の関係を創造するよろこび / 「働くクルマと社会」特集にあたって / GPSデータを用いたスポーツイベント来場者の行動分析 / 企業のIR情報に見る都市緑地に関する第三者認証制度の取り扱いに関する研究 / 熱赤外域リモートセンシングデータを活用した市街地の土地被覆に関する研究 / 熱的快適性が屋外空間における滞在に与える影響に関する研究 / 可視化された温熱環境情報が屋外空間の利用に与える影響に関する研究 / An Empirical Study on Using Green Spaces Around an Office as Workplace in Summer: Considerations Based on Office Employees’ Trait Anxiety Tendencies / グリーンインフラと緑の基本計画 / これからの自律的な民間緑地整備に関する考察 / ノルウェーにおける地表面での雨水管理策に関する法改正における議論の特徴 / ランドスケープ分野におけるDX / グリーンインフラとしての平地林による防災機能 －災害現場で確認された農業気象災害軽減事例－ / 移動の体験と景観 / 企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ / 屋外空間利用がオフィスワーカーに与える心理・生理的影響とその要因に関する研究 / 人流ビッグデータを用いた「Natural Cities」と温熱環境の関係分析についての研究 / 季節の違いが緑化に対する支払意思額に与える影響 / 地域・土地との関係性の希薄化</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>温熱環境がランナーの深部体温に及ぼす影響の把握と都市緑道の暑熱対策の検討 / 屋外温熱環境の違いが来訪者の空間利用に与える影響に関する研究 / 地域の持続可能性に資する非住宅木造建築の実現における関係主体の役割と課題 〜大崎市鳴子こども園を事例として〜 / 温熱環境情報の提示が空間利用に与える影響に関する研究 / 総合設計制度により創出された公開空地の緑化の実態に関する研究 / 北京市におけるヒートアイランド現象の時空間特性の分析 / オフィス街における来街者の滞留行動の季節変化に関する研究ー丸の内仲通りを対象としてー / 屋外空間利用がオフィスワーカーに与える心理的・生理的影響とその要因に関する研究 / 都市住民と農家の都市農地保全に対する意識の乖離とその要因に関する研究 / GPSログデータを用いたCOVID-19流行下の都市公園利用と公園利用前後の行動パターンに関する研究 / 日常の生活行動と温熱環境が深部体温に与える影響に関する基礎的研究 / 歩行時の空間認識と歩行の快適性の関係に関する研究</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 災害分析 ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>都市農村計画
 緑地計画
@@ -11276,7 +11581,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>温熱環境がランナーの深部体温に及ぼす影響の把握と都市緑道の暑熱対策の検討
 屋外温熱環境の違いが来訪者の空間利用に与える影響に関する研究
@@ -11352,6 +11657,11 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>AI時代の省エネ型データセンター性能の数理的解明
 省電力データセンターの協調機構の性能評価
 省電力サーバ群の性能評価と負荷分散に関する数理モデル
@@ -11391,42 +11701,42 @@
 Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>AI時代の省エネ型データセンター性能の数理的解明 / 省電力データセンターの協調機構の性能評価 / 省電力サーバ群の性能評価と負荷分散に関する数理モデル / 処理能力可変型待ち行列モデルの理論的発展と大規模省エネデータセンターへの応用 / 複数車両・複数道路橋を対象とした移動センシング技術の基盤的研究 / 処理能力可変型待ち行列システムの理論的深化と省エネデータセンターへの応用 / 起動時間を有するシステムの理論解析と省エネ型データセンター性能評価への応用 / 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化 / 顧客の再試行と途中放棄を考慮したコールセンターのモデル化と性能解析 / 再試行型待ち行列によるコールセンターの性能解析とサービス科学への応用</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>数理情報学 / 社会システム工学・安全システム</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>応用確率論、 確率モデル、 待ち行列理論、 性能評価、 オペレーションズ・リサーチ、確率システム</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Performance Analysis of Energy-efficient Reliable AIoT System Architectures / Queueing Model with Alternating Service for Zipper Merging / A simulation study of the sojourn time in queueing systems with stochastically delayed information / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers / Performance Analysis of Blockchain with Rollups / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times / Analysis of a Batch Arrival Queue with Power Saving Mode / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory / Analytical Modelling of Asymmetric Multi-core Servers / Energy-performance tradeoffs in server farms with batch services and setup times / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers / Queueing Analysis of an Ensemble Machine Learning System / Performance analysis of a collision channel with abandonments / Empirical architecture comparison of two-input machine learning systems for vision tasks / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes / Modeling and performance analysis of hybrid systems by queues with setup time / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing / To wait or not to wait: Strategic behaviors in an observable batch-service queueing system / A Two-Population Game in Observable Double-Ended Queueing Systems / Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>集団サービス型無限サーバ待ち行列の解析 / 客とサーバの性質が異なるシステムにおける待ち現象の解析 / Modelling social media load through a birth-death-batch-immigration process / マルコフ連鎖を用いたレンタカーとオンデマンド交通の融合システムの性能評価 / 混雑度に依存するサービス速度変化を考慮した待ち行列モデルの分析と交通流への応用 / Sojourn time analysis for m/m/c/setup queues / 異なる省電力モードを導入した集団到着型複数サーバモデルの解析 / Retrial queues with two-way communication for cognitive networks</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>数理情報学 ; 社会システム工学・安全システム ; オペレーションズリサーチ ; 交通・モビリティ ; サービス・待ち行列 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 待ち行列理論 ; サービス工学 ; システム性能評価 ; 学習分析 ; 物流最適化</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>数理情報学
 社会システム工学・安全システム
@@ -11451,7 +11761,7 @@
 物流最適化</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>集団サービス型無限サーバ待ち行列の解析
 客とサーバの性質が異なるシステムにおける待ち現象の解析
@@ -11526,6 +11836,11 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>「協働型都市開発と公共貢献手法に係る今後の展開可能性に関する研究」に対する研究助成
 「今後の都市再生におけるインセンティヴ制度のあり方に関連する研究」に対する研究助成
 自治体保有資産の有効活用を目的とした公民共創プロセスに関する研究
@@ -11567,42 +11882,42 @@
 マイナンバー導入事例に見る政府情報システム調達の現状に関する研究</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>「協働型都市開発と公共貢献手法に係る今後の展開可能性に関する研究」に対する研究助成 / 「今後の都市再生におけるインセンティヴ制度のあり方に関連する研究」に対する研究助成 / 自治体保有資産の有効活用を目的とした公民共創プロセスに関する研究 / 公的不動産の有効活用実現のための公民連携促進策とアセットマネジメント戦略のあり方 / 中古住宅市場における空き家・空き地の流通促進のための公民連携体制のあり方に関する研究 / 既成市街地における不動産流通促進を通じた地域再生に資する土地利用制度に関する研究 / イギリスの都市計画プランナーの職能団体による実務研修等を支えるシステムに関する研究 / オープンデータを踏まえた市民セクター主体のICT協働まちづくりに関する研究 / 豪雨災害から避難弱者を守る共助的な避難行動計画づくりシステムに関する学際的研究</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>都市計画・建築計画 / 経済政策</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Industrial Location / 産業集積 / 都市・地域政策 / 都市計画制度</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで / 新しい時代の都市再生と公共貢献のあり方 / 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 / 都市再開発のこれからの「必要性」と「可能性」 / 農村集落における区域区分制度を前提とした土地利用調整手法の実態と活用可能性に関する研究 / 土地建物一体型市街地整備の「必要性」と「可能性」 : これまでとこれから / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に / つくば市による心肺停止傷病者発生位置情報の最寄AED管理者との共有が生み出す協働による救命効果に関する研究 / 地方自治体におけるオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 / 東京都区部における開発実態の評価を踏まえた開発拠点誘導政策の課題に関する研究 / 公民連携による空き家・空き地対策組織の展開と運営実態 / 避難行動要支援者名簿活用に向けた制度設計・運用プロセスにおける課題に関する研究 / オープンデータ施策に総合的に取り組む地方自治体の動因に関する研究 / 地方都市中心市街地における商店街の連続性を踏まえた空間整備の変遷と課題に関する研究 / 地方自治体のオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 / 世界からみた銀座のルールとガバナンス (特集 銀座と都市計画) -- (都市計画と銀座のルール) / 11027 地区スケールの賑わい空間構造の定量分析に関する研究 歩行空間と周辺土地利用に着目して / “Planning transparency and public involvement in pre-application discussions,” / 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 / 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) / 集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ / マイナンバー導入に伴う自治体業務情報システム改修事例に見るオープン化・標準化及び共同化の現状に関する研究 / マイナンバー導入事例に見る政府情報システム調達の現状に関する研究</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>地方都市の法定再開発における持続的運営の課題に関する研究ー権利変換手法に着目してー / 改正個人情報保護法を受けた避難行動要支援者名簿情報の提供方策に関する研究 / 管理型まちづくりへの転換における公民連携の地域管理体制に関する研究-組織の成立プロセスに着目して- / 民間業務範囲を拡大させた PFI 事業における事業実現過程の課題に関する研究 / 人口減少社会における土地利用調整手法の実態と活用可能性に関する研究 －茨城県桜川市を事例として－ / 都市公園における官民連携事業の課題に関する研究 / 公的不動産の有効活用を促進する民間提案プラットフォームにおける課題に関する研究 / 実効性のある個別避難計画に向けた作成プロセスについて / 外国資本による国内不動産投資の増加が周辺地域に与える影響についての考察 / 公的不動産の利活用に向けた情報発信と官民の対話に関する研究 / 公的不動産の有効活用に関する研究 ―自治体に着目して― / 神社更新に伴う分譲マンション開発の実態と課題に関する研究ー東京都区部の神社を対象としてー</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>都市計画・建築計画 ; 経済政策 ; 保険・金融行動 ; 都市・地域政策 ; 建築・空間設計 ; 災害・防災研究 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 行政データ分析 ; 都市計画 ; 意思決定支援 ; 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>都市計画・建築計画
 経済政策
@@ -11639,7 +11954,7 @@
 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>地方都市の法定再開発における持続的運営の課題に関する研究ー権利変換手法に着目してー
 改正個人情報保護法を受けた避難行動要支援者名簿情報の提供方策に関する研究
@@ -11717,6 +12032,11 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>形態・材料に着目した近代町家の地域性とその形成要因
 モビリティーイノベーションの社会応用と未来社会工学研究5
 モビリティーイノベーションの社会応用と未来社会工学研究3
@@ -11761,42 +12081,42 @@
 「清代新疆の地域構造と都市群の立地 -軍政中心地イリを対象に- 」</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>形態・材料に着目した近代町家の地域性とその形成要因 / モビリティーイノベーションの社会応用と未来社会工学研究5 / モビリティーイノベーションの社会応用と未来社会工学研究3 / モビリティーイノベーションの社会応用と未来社会工学研究4 / 石岡市歴史的景観及び里山景観調査研究 / 大火からの復興を通してみた近代の町並みの再評価 / 江戸武家地の成熟過程に関する建築史・都市史的研究 / 江戸武家地の空間変容に関する文理統合的研究 / 北関東の町並みの建築的構成とその展開過程に関する研究 / 常陸太田市鯨が丘歴史的建造物調査</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>建築史・意匠 / 都市計画・建築計画 / 日本史</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>建築史 / 都市史 / 保全型都市計画 / 居住環境史</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>近代中国青島市における「雑院一覧表 二十四年夏季」について / 五台山行宮座落地盤圖 からみた清代白雲寺行宮 / 嵩山史跡群における建物の空間構成および登封県の建立の経緯 / 近代の町並み景観の多様性：大火からの復興を通してみた近代の町並みに関する研究 その 1 / 戦後昭和期の横浜中華街における商住空間の分布と特徴：中区明細地図の考察から / 清代福州における住宅の類型とその特徴 古絵図 De Stud Hockzieuw en de stad Nanta を中心とした分析 / 明清時代漕運と大運河沿いの都市空間特性との関係 その 2： 済寧を例として / 「白川郷における駐車空間の分布と交通整備の経緯：重要伝統的建造物群保存地区における駐車空間に関する研究」 / 『大日本職業別明細図之内』の空間表現 千葉県北部の地図を対象に / 観光開発を目的とした窯業集落の保全の実態とその課題： 中国陝西省澄城県の伝統村落・堯頭村を事例に / 「清代蘇州の屋外空間における商人達の「自発的な居場所」 のパターン： 「姑蘇繁華図」の分析」 / 新刊紹介『リスボン』 / 明清時代における漕河沿い城・鎮の空間構成に関する研究（その1）：漕運システムと漕河沿岸空間の構成要素との関係 / 清代福州における住宅の三類型 / 大正期から戦前までの山下町における中国系事業所と公共施設の立地と特徴–Japan Directory、商工案内の分析から– / 清代福建省における「舗」の分布とその特性－連江県城を事例として－ / 清代五台山顕通寺の火災と修復工程 / 明清時代漕運と京杭大運河沿い都市の空間特性との関係－臨清を例として－ / 中国における団地構内の小規模野菜市場の空間利用－街商と住民の共存モデル－ / 新刊紹介『明暦の大火』 / 五台山塔院寺の建築の構成とその変容 / 「奈良県橿原市今井町における駐車場の出現パターン：重要伝統的建造物群保存地区の駐車空間に関する研究 その2」 / 「真壁のこれから：過去・現在・未来」 / 「商店街アーケードの空間の変容:十条銀座商店街を対象に」 / 「清代新疆の地域構造と都市群の立地 -軍政中心地イリを対象に- 」</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>東京都区部における銭湯の存続要因とその周辺環境に関する研究－江東区を事例として－ / 幕末の海防に伴う都市空間の変容-江戸沿岸部地域に着目して- / 旧軍用地が地域空間形成に与えた影響について―茨城県ひたちなか市を対象として― / 中国鉄鋼業の発達が都市空間に与えた影響ー近代の武漢を事例にー / 近代中国における鉄道交通基盤の導入と歴史的都市空間との関係—1888〜1958年の京津・津浦鉄道沿線都市を対象に— / 清代駅道の変遷と沿道集落・駅建築の特徴－山東省済南府地域を事例として / 華僑の投資・建設活動が新たな都市空間の形成に果たした役割ー清末〜民国期の広州市東山区を例としてー / 戦後における商店街の業態と空間の変容—高円寺、北千住、巣鴨を事例として— / 観光開発を目的とした窯業集落の保全・修景に関する研究—中国陝西省澄城県の伝統村落・堯頭村を事例に— / 近代中国における民間主導の計画的市街地「漢口模範区」の形成と変容 / 明清期陝西省における都市時報建築の立地と形態 / 近代の繊維都市の形成に模範撚糸工事が果たした役割 / 中国の近代化において交通システムの変容が在郷町の機能・空間に与えた影響 ～四川省資中県を事例として～ / 建設時期・地域による相違に着目した清代満城の都市形態に関する研究 / 農村地域における短路型集落の特徴と近代以降の変容ー茨城県の集落を対象にー / 中国天童寺の寺域及び構成施設の変遷：晋代の創建から近現代の保護まで / 明清時代の役人住宅における職階制度と建築様式の関係—陳氏の住宅を例に / 北京市歴史文化保護区におけるジェントリフィケーションの実態とメカニズム―南鑼鼓巷を事例に</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>建築史・意匠 ; 都市計画・建築計画 ; 日本史 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 都市計画 ; 人間中心設計 ; 社会ネットワーク分析 ; 環境工学</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>建築史・意匠
 都市計画・建築計画
@@ -11829,7 +12149,7 @@
 環境工学</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>東京都区部における銭湯の存続要因とその周辺環境に関する研究－江東区を事例として－
 幕末の海防に伴う都市空間の変容-江戸沿岸部地域に着目して-
@@ -11915,6 +12235,11 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化
 ワークライフバランスに貢献するサイバー・フィジカル製造業
 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配
@@ -11952,42 +12277,42 @@
 Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化 / ワークライフバランスに貢献するサイバー・フィジカル製造業 / 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配 / 半導体・液晶製造の良品スループット向上とコスト低減の両立を目指してQ-time制約の遵守と装置の生産性向上とを同時に実現する実時間最適オペレーション管理手法の研究 / ＱＣＤＲモデルに基づいて革新的な総合設備効率の向上と生産期間の短縮を実現する工場・設備の運用管理システム / ＱＣＤモデルに基づくマルチチャンバ装置および生産ラインの運用・設計方法 / 共創ビジョンに基づく半導体産業のビジネスモデル進化と、知財・人材の組織的流動化</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>制御・システム工学</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>生産システム工学 / オペレーション管理 / 地域活性化</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>"INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH / Robust Classifications of WBM Defect Patterns / Due dates assignment based on customer changeability classifications in Make-to-order productoins / Pipeline production model and sensitivity analysis of Engineering-to-Order products using system dynamics / PRODUCTION AND JOB ROTATION PLANNING CONSIDERING DISABILITIES AND HEALTH CONDITIONS / Classification of Multivariate Time Series Signals Using Self-Supervised Representation Learning / Multi-factory Scheduling Considering the Trade-offs between Production Efficiency and Risks / Analysis of Resilience Factors and Satisfaction in Life-line Charts for Life Career Developments / Interaction Modeling for High-Dimensional Mixed Data with Numerical and Categorical Features / Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL / MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION / Mixed-type Defect Pattern Classifications / Interaction Modelling of High Dimensional Production Data / DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS / MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN / Data-driven Modeling for Production Dynamics / Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption / MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - / Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - / Interaction Modelings for Industrial Data - for final quality estimation and proess integration / スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 / 従属需要の予測手法の構築と検証 / Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>多目的ハイブリッドフローショップスケジューリングの実証研究 / QR決済ヘビーユーザーの内外特徴の分析と活用 ～ キャンペーンと多種アプリ利用状況を考慮して / 保全時間を考慮した自律搬送ロボットのスケジューリング / n工程・多目的ハイブリッドフローショップスケジューリングの高速化～タブーリストと解構造の活用 / 生産リスクと段取りを考慮したMulti-factoryスケジューリング / 高次元交互作用モデリングにおける構造導入アプローチの効果検証 / 上流工場と処理単位の変化を考慮した投入制御ルールと多目的スケジューリングの融合 / 大規模データに対する変化検出と因果分析 / 多重共線性と因子効果ギャップを考慮した高次元交互作用モデリング / エネルギー消費量と納期遅れペナルティのトレードオフを考慮したセルフチューニングバッチ編成と多目的スケジューリング / 建設現場の多様性への対応する360度撮像と画像認識技術 / データ駆動プロセスインテグレーションのための高相関高次元データモデリング / ネットワーク理論に基づく高齢者福祉施設の最適化配置計画～茨城県通所型高齢者福祉施設の事例 / 相関関係を内包した多次元時系列データの予測モデリング / 高相関データの高因子効果比モデル推定 / 多品種繰り返し大規模生産システムのモデリングと最適スケジューリング～半導体Testbedを対象として / 自己教師あり学習を用いた多変量時系列信号の状態分類 / 料理アプリに着目したスマホ起動履歴の解析と情報推薦 / 高次元混合データの交互作用モデリング / 生産効率・人間工学リスク・エネルギーを考慮したジョブローテーションスケジューリング / 工場間搬送を考慮した並列分散型マルチファクトリー・スケジューリング / 営業コストを考慮したサプライチェーンにおける企業間多段階納期交渉 / エネルギー消費と待ち時間制約のトレードオフを考慮したサプライチェーン・スケジューリング / 画像マルチモーダル学習による半導体不良パターンの解析 / 時空間情報を用いた画像マルチモーダル学習による半導体不良パターンの高精度分類 / 資源・エネルギーロスを最小化する生産フロー制御つきマルチファクトリー・スケジューリング / 因果推論と機械学習による車載半導体需要予測 / 推薦システムによる多様なアプリの利用促進 / 高次元データの交互作用モデリング-Adaptive SFMとSafe Pruningによる高精度化 / 多様な建設現場の部材の検出と分類</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>制御・システム工学 ; 都市・地域政策 ; オペレーションズリサーチ ; 機械学習 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 物流最適化 ; 最適化</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>制御・システム工学
 生産システム工学
@@ -12013,7 +12338,7 @@
 最適化</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>多目的ハイブリッドフローショップスケジューリングの実証研究
 QR決済ヘビーユーザーの内外特徴の分析と活用 ～ キャンペーンと多種アプリ利用状況を考慮して
@@ -12107,6 +12432,11 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>地方での生活空間データ連携
 Hack My Tsukuba 2018
 Hack My Tsukuba 2019
@@ -12154,42 +12484,42 @@
 自治体会計情報のオープンデータ化の促進―国際基準COFOGによる費目分類に着目して―</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>地方での生活空間データ連携 / Hack My Tsukuba 2018 / Hack My Tsukuba 2019 / 豪雨災害から避難弱者を守る共助的な避難行動計画づくりシステムに関する学際的研究 / 茨城県AEDデータベース / 犯罪情報オープン化の犯罪抑止効果研究 / つくば市AEDデータベース / 公共サービスの革新に関する研究 / 医療相談アプリ「LEBER」を用いた医療費削減効果のデータ解析に関する学術指導 / 日本政府のオープンデータ政策評価</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム / 都市計画・建築計画 / ウェブ情報学・サービス情報学 / 図書館情報学・人文社会情報学 / 財政・公共経済 / 持続可能システム / 経営学 / 地域研究 / 環境影響評価</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>オープンデータ、公共データ分析、自治体経営、地域情報化政策、国際協力</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>在宅医療におけるD to P with Nの臨床的役割：訪問診療との比較による診療内容および受療パターンのケーススタディ / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 / 筑波大学理工学群におけるデータサイエンス応用基礎教育 / 水害時における市民の避難行動に関する意識の分析 / Asian Cities Connecting through Communities / 排水再利用設備に係る建築行政の現状と今後の動向 / 建設省--インテリジェントビルへの構図 / ペンシルバニア通り2121番地(第1便)「世界銀行」ってどんなところ? / 世界銀行の都市開発分野における日本の情報発信の方向性 / CIOの視点/INTERVIEW 人と人をつなげて進む川島流地域活性化のビジョン / 地方自治体における業務改革と情報システム構築の実際--佐賀県を事例として / 佐賀県 台帳記録管理システムによる業務改革 / 大きな社会システムのアーキテクチャ再構築を / 世界の潮流 : オープンデータ : エンドユーザーの視点に立ち便益が明確な事業の推進を / 事実証拠を根拠とした政策策定 : オープンデータ推進の効果 / オープンデータの最新動向と公共データ市場に関する考察 / 電子自治体と公共イノベーション / オープンデータの5W1H : 今、自治体は「オープンデータ」にどのように取り組むべきか / オープンデータからソーシャルイノベーションへ : 公共データ×ICT×市民力で社会課題を自ら解決する社会ヘ / 自治体がオープンデータに取り組む際の留意点 オープンデータの活用において自治体が成果を出すための5原則 / Society 5.0実現に向けて必要となる教育の方向性 / オープンガバナンス推進に求められる政府・自治体職員の能力 / VUCA時代の政策形成にデジタルをどう活かすか / 自治体会計情報のオープンデータ化の促進―国際基準COFOGによる費目分類に着目して―</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>地方自治体・企業におけるワーケーション関連の取り組み実態に関する研究 / 個別避難計画の作成促進方策に関する研究～常総市・つくばみらい市を対象として～ / 現代における茅葺き屋根保存に関する課題と適切な支援施策に関する研究 ―茨城県石岡市を事例として― / 避難支援関係主体の参画に着目した実効性のある個別避難計画作成プロセスに関する研究 ―令和２年７月豪雨による球磨川氾濫周辺地区を対象として― / ナッジメッセージを用いた地震に対する世帯備蓄促進に向けた社会実験 ―茨城県つくば市内の世帯を対象として― / 医療過疎地域におけるD to P with Nと訪問診療との代替・補完可能性に関する研究 ~ 長野県伊那市のモバイルクリニック運用を例に ~ / 認知症等行方不明者の発生記録を用いた捜索時間の短縮効果に関する研究 / 最寄AED急搬送システムの社会実装過程における不確実性を考慮したAED選定モデル / 地方の先進社会課題の解決に取り組んでいる若者起業家の成功要因に関する研究～修正エフェクチュエーション・モデルの検証～ / 高経年区分所有住宅の耐震性能を向上する建替え推進に向けた法制度設計上の課題に関する研究 ー台湾と日本の法制度の比較を通じてー</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム ; 都市計画・建築計画 ; ウェブ情報学・サービス情報学 ; 図書館情報学・人文社会情報学 ; 財政・公共経済 ; 持続可能システム ; 経営学 ; 地域研究 ; 環境影響評価 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 災害・防災研究 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 行政データ分析 ; 災害分析 ; 推薦システム ; 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>社会システム工学・安全システム
 都市計画・建築計画
@@ -12246,7 +12576,7 @@
 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>地方自治体・企業におけるワーケーション関連の取り組み実態に関する研究
 個別避難計画の作成促進方策に関する研究～常総市・つくばみらい市を対象として～
@@ -12324,6 +12654,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>オルタナティブデータを用いたオフィス不動産市場分析の可能性
 オフィス賃貸マーケットに関する研究
 地方自治体における情報の利活用方策の導入
@@ -12366,42 +12701,42 @@
 モバイル端末の活用による地方自治体の道路維持業務支援の検討</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>オルタナティブデータを用いたオフィス不動産市場分析の可能性 / オフィス賃貸マーケットに関する研究 / 地方自治体における情報の利活用方策の導入 / 地方自治体における道路維持管理業務のため / 空間計量経済学における最重要課題への挑戦と新たな展開 / 道路台帳を活かした道路アセットマネジメントに関する研究</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>土木計画学・交通工学</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>道路維持管理 / 空間計量経済学 / 地理情報システム / 空間データ / 空間統計 / 不動産 / 不動産価格 / 不動産賃料 / 土地利用 / 立地分析</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ / 東京23区における賃貸オフィスビルストックの地域性と経年変化 / The Impact of the Flight to Quality on Office Rents and Vacancy / Spillover Effect of Large Building Construction on Neighborhood Office Rents / 地域属性と産業振興政策に着目した新設会社の立地に関する考察 / 実用性を考慮したローカルな不動産価格指数の理論と実証. / デジタル化と立地がコロナ禍における私立中学校選択に与える影響. / 大規模オフィスビルの竣工が近隣のオフィス賃料に与える影響：アメニティ効果 vs 供給効果. / 東京オフィス市場における 集積の経済・不経済とその時間的変化 / Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics / Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market / ビッグデータのためのローカルなオフィス賃料指数の開発 / オフィス空室率の時空間変動に関する探索的小地域分析 / 北陸新幹線開通による大学選択への影響に関する実証的研究 / 計量テキスト分析による道路橋を維持管理する技術力の解明の試み / 土木技術者の経験と学習 ―地方整備局職員の研究所出向と道路構造物を維持管理する技術力に着目して― / 空室率データで見る東京オフィス市場の空間的特性 / インフラの維持管理に関する研修による技術力向上効果の評価 ―道路橋の点検に着目して― / 東京オフィス市場における集積の経済・不経済とその時間的変化 / 携帯位置情報データを用いた東京23区内における“オフィス出社”の時空間分析 / 改訂版ブルーム・タキソノミーを用いた道路橋を維持管理する技術力の解明の試み / 交通アクセシビリティの変化が 中学受験における学校選択に与える影響 / モバイル端末の活用による地方自治体の道路維持業務支援の検討</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>自然災害発生による学校選択行動への影響ー首都圏私立中学を対象としてー / 東京オフィス市場における賃料調整過程の異質性と非対称性 / 非労働環境におけるライフキャリア形成プロセス / The Effect of the Housing Prices on the Household Savings in Urban China Under the Trend of Aging Society / The Determinants of China’s crude birth rate and regional difference ——Under the effect of two child policy / 中国における個人用固定資産税改革の効果分析 / 物流企業を考慮した応用都市経済モデルの開発に向けて / 国内政策の普及の実態 ～マイナンバーカードを事例として～ / 地域おこし協力隊の受け入れをめぐる自治体間競争に関する考察 / 大阪市における学力テストスコアと賃料の関係 ～小学校学校選択制の導入から～ / サービス付き高齢者向け住宅の賃料と立地選択の影響要因に関する研究</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>土木計画学・交通工学 ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; マーケティング分析 ; 災害分析 ; 都市計画</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>土木計画学・交通工学
 道路維持管理
@@ -12448,7 +12783,7 @@
 都市計画</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>自然災害発生による学校選択行動への影響ー首都圏私立中学を対象としてー
 東京オフィス市場における賃料調整過程の異質性と非対称性
@@ -12521,6 +12856,11 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>「クルマ」と「自動化するクルマ」の社会的受容の包括的理解に向けた学際研究
 ナラティブで編まれる地域交通コミュニティ形成と人材プログラムの研究開発
 健康にやさしい環境整備に係る実証事業
@@ -12560,42 +12900,42 @@
 奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>「クルマ」と「自動化するクルマ」の社会的受容の包括的理解に向けた学際研究 / ナラティブで編まれる地域交通コミュニティ形成と人材プログラムの研究開発 / 健康にやさしい環境整備に係る実証事業 / 高速道路における渋滞吸収走行の社会的受容に関する研究 / 技術の倫理的・法制度的・社会的課題(ELSI)への包括的実線研究開発プログラム / 「クルマ」と「自動化するクルマ」に対する社会的受容の包括的理解に向けた学際研究 / 「高齢運転者向け認知機能検査の負の効用とその緩和策の検討」 / ASEAN諸国におけるモビリティ・マネジメントの実行可能性に関する実証分析 / 道路上の異モード間コミュニケーションの生起と社会的受容 / 健康に配慮した交通行動誘発のための学際的研究</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>土木計画学・交通工学</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>交通計画 / 都市計画における態度・行動変容研究 / リスク･コミュニケーション</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo / Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt / 高齢運転者向け認知機能検査における制度変更の影響評価 / Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour / おつかい行動に見る子どもの移動自由性の世代変化と要因分析 / 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 / 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 / 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― / 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― / モビリティのイノベーションに，モビリティ･マネジメントをどう活かすか？ / モビリティ・マネジメントと健康福祉・教育 / 日米の車両生成データ制作の現状とEUのData Actの波及可能性 / SWC首長研究会への加盟有無(健康都市づくりに対する首長の意識)と公共交通分担率が住民の心身の健康に与える影響 / 「報復の空白」と「運」が交通事故時の道徳的判断に与える影響－自動運転と手動運転の比較分析－ / 東京都区部の電動キックボードシェア利用実態と利用体験・交通手段別視点による比較分析 / 米国における自動運転タクシーの社会的受容とその要因分析－人身事故経験を有する二都市に着目して / おつかい行動に見る子どもの移動自由性の世代変化とその要因分析，最近の調査研究から / 新たなモビリティの規制緩和－思考停止の日本人，大丈夫？ / モビリティ・マネジメントとの出会いと今後 / 基礎自治体における電動キックボードビジネス のガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― / 米国の自動運転車両の事故発生後の 社会的受容の比較分析 / 奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>電動キックボードの社会的受容 －国内外専門家の懸念と東京都区部への影響 / EUデータ政策を事例にしたわが国の自動車産業における課題の調査研究 / 高速道路での渋滞吸収走行普及に向けた情報提供と先導車種によるドライバーの心理変化 / 俯瞰的整理を通じた「地域の公共交通向上の担い手人材」育成に向けた取組みの現状と課題</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>土木計画学・交通工学 ; 都市・地域政策 ; 社会政策・福祉 ; 交通・モビリティ ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 計算社会科学 ; 学習分析</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>土木計画学・交通工学
 交通計画
@@ -12634,7 +12974,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>電動キックボードの社会的受容 －国内外専門家の懸念と東京都区部への影響
 EUデータ政策を事例にしたわが国の自動車産業における課題の調査研究
@@ -12703,6 +13043,11 @@
         </is>
       </c>
       <c r="F30" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>トポロジー的組合せ論と組合せ論におけるトポロジー的手法
 組合せ的構造に関する研究
@@ -12748,42 +13093,42 @@
 核付アフィン点配置の根付サーキット系の性質について</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>トポロジー的組合せ論と組合せ論におけるトポロジー的手法 / 組合せ的構造に関する研究 / Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求 / デジタル指紋符号、多重接続通信路、及び組合せ探索問題 / 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / 部分構造への等質性を基軸とする単体的複体の構造解析 / ネットワーク上の時間軸をもった最適化問題とその応用 / 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化 / 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>数学基礎・応用数学</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>組合せ論 / トポロジー的組合せ論 / シェラビリティー / 単体的複体 / 離散構造 / 離散幾何</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>The average expected value of a rooted graph, Monte Carlo calculation, and a power index for the voting game / Coloring zonotopal quadrangulations of the projective space / Several minimality concepts related to Frankl's conjecture / Some computational studies of the root distribution of Ehrhart polynomials / The root distributions of Ehrhart polynomials of free sums of reflexive polytopes / Sequential Partitions of Nonpure Simplicial Complexes / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting / Pure-strategy Nash equilibria on competitive diffusion games / Hereditary properties and obstructions of simplicial complexes / A comment on pure-strategy Nash equilibria in competitive diffusion games / Obstructions to shellability, partitionability, and sequential Cohen-Macaulayness / Decompositions of two-dimensional simplicial complexes / A note on shellability and acyclic orientations / On the topology of the free complexes of convex geometries / A factorization theorem of characteristic polynomials of convex geometries / The max-flow min-cut property of two-dimensional affine convex geometries / h-Assignments of simplicial complexes and reverse search / Tangle sum and constructible spheres / Deciding constructibility of 3-balls with at most two interior vertices / Non-constructible complexes and the bridge index / Decompositions of balls and spheres with knots consisting of few edges / Nonconstructible balls and a way of testing constructibility / Constructible complexes and recursive division of posets / セル複体に付随するグラフの向き付けとその最適解 / 核付アフィン点配置の根付サーキット系の性質について</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>飛行禁止空域のある空間におけるドローンを用いた監視経路決定 / グラフ理論における再構成問題及び再構成数に関する一考察 / 最大次数が4以下のグラフにおける1-2 Conjectureについて / 低discrepancy点集合の構成における数独超方格の応用 / 繰り返し離散ボロノイゲームのヒューリスティック解法の検討 / 特定の形をした直径が6の木グラフに対するGraceful Labeling</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>数学基礎・応用数学 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; ネットワーク科学 ; 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>数学基礎・応用数学
 組合せ論
@@ -12808,7 +13153,7 @@
 社会ネットワーク分析</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>飛行禁止空域のある空間におけるドローンを用いた監視経路決定
 グラフ理論における再構成問題及び再構成数に関する一考察
@@ -12882,6 +13227,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>不正者追跡アルゴリズムの開発とその応用
 デジタル指紋符号、多重接続通信路、及び組合せ探索問題
 スパースな結合行列を持つ組合せ的構造の分析と構成
@@ -12923,42 +13273,42 @@
 Zero-difference balanced functions with new parameters and their applications</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>不正者追跡アルゴリズムの開発とその応用 / デジタル指紋符号、多重接続通信路、及び組合せ探索問題 / スパースな結合行列を持つ組合せ的構造の分析と構成 / デジタル指紋及びグループ検査に共通する組合せ構造とアルゴリズムに関する研究 / 組合せ論的マルチメディア指紋符号とその不正者追跡アルゴリズムの研究 / 完全差集合族とそのレーダー配列への応用に関する研究 / 組合せ的デザイン理論を用いた周波数ホッピング系列の構成に関する研究 / 組合せ的デザイン理論を用いた光直交符号の構成に関する研究 / 組合せ的デザインとその符号・暗号への応用</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>数学基礎・応用数学</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>組合せ論 / 符号理論 / 情報セキュリティ / グループ検査</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) / A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) / Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) / Repairing Schemes for Tamo-Barg Codes / A Construction of Optimal One-Coincidence Frequency-Hopping Sequences via Generalized Cyclotomy / Secure Codes With List Decoding / Codes for Exact Support Recovery of Sparse Vectors from Inaccurate Linear Measurements and Their Decoding / Optimal Locally Repairable Codes: An Improved Bound and Constructions / On the Information-Theoretic Security of Combinatorial All-or-Nothing Transforms / A Construction of Maximally Recoverable Codes With Order-Optimal Field Size / Capacity-Achieving Private Information Retrieval Schemes From Uncoded Storage Constrained Servers With Low Sub-Packetization / BCH codes with minimum distance proportional to code length / Existence and Construction of Complete Traceability Multimedia Fingerprinting Codes Resistant to Averaging Attack and Adversarial Noise / Strongly separable matrices for nonadaptive combinatorial group testing / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting / Algebraic manipulation detection codes via highly nonlinear functions / On Optimal Locally Repairable Codes With Super-Linear Length / On optimal weak algebraic manipulation detection codes and weighted external difference families / On Optimal Locally Repairable Codes With Multiple Disjoint Repair Sets / Improved Bounds for Separable Codes and B-2 Codes / Probabilistic Existence Results for Parent-Identifying Schemes / Non-adaptive group testing on graphs with connectivity / Bounds on Traceability Schemes / New Bounds for Frameproof Codes / Zero-difference balanced functions with new parameters and their applications</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>An improved algorithm to identify the cardinality of a coalition in multimedia fingerprinting / Group Testing with List Decoding</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>数学基礎・応用数学 ; 機械学習</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 組合せ最適化 ; 社会ネットワーク分析 ; 学習分析 ; 数理最適化</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>数学基礎・応用数学
 組合せ論
@@ -12975,7 +13325,7 @@
 数理最適化</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>An improved algorithm to identify the cardinality of a coalition in multimedia fingerprinting
 Group Testing with List Decoding
@@ -13043,6 +13393,11 @@
         </is>
       </c>
       <c r="F32" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>気候変動緩和に貢献する新興大都市におけるデータ駆動型の動的交通マネジメントに関する研究
 高速車両連結技術を前提とした都市鉄道の近未来型運行スキーム
@@ -13083,42 +13438,42 @@
 Trading mechanisms for bottleneck permits with multiple purchase opportunities</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>気候変動緩和に貢献する新興大都市におけるデータ駆動型の動的交通マネジメントに関する研究 / 高速車両連結技術を前提とした都市鉄道の近未来型運行スキーム / 高速道路単路部の交通流理論の検証と交通制御システムの戦略的デザイン / 限定合理的個人を仮定した大規模社会システムの動的制度設計 / 交通・物流システム効率化のための市場型マッチング・システムの設計・評価法構築 / MaaS＋CV時代の次世代交通システムに向けたインフラと制度の設計 / 交通渋滞マネジメントのためのビリーフデザインアプローチ / バイオミメティックスに学ぶスマートな都市退化マネジメント / AI計算リソースとしての実交通ダイナミクスの活用技術の開発 / 走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>土木計画学・交通工学</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks / A second order model of capacity drop at expressway lane-drop bottlenecks / 都市鉄道整備推進に向けた事業制度に関する研究 / Stability analysis of a departure time choice problem with atomic vehicle models / 自動運転車両の速度制御を考慮した系統信号制御に関する考察 / 追従モデルによる高速道路サグ部のCapacity Drop現象の再現 / 連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析 / テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル / Predicting traffic breakdown in expressways using linear combination of vehicle detector data / Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 / 連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析 / Dynamic traffic assignment in a corridor network: Optimum versus equilibrium / 高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム / 需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡 / Fundamental diagram of urban rail transit considering train-passenger interaction / 高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム / 高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動 / Dynamic system optimal traffic assignment with atomic users: Convergence and stability / A new look at departure time choice equilibrium models with heterogeneous users / 動的交通均衡配分理論の近年の進展 / Continuum car-following model of capacity drop at sag and tunnel bottlenecks / Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" / Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach / Trading mechanisms for bottleneck permits with multiple purchase opportunities</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>ボトルネック渋滞と都市人口分布の相互依存関係の解析 / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 / 多種別連結運行スキームにおける鉄道システムの安定性解析 / 市場型混雑管理システム下における自動運転サービスの運用方法 / 需要の時間的・空間的異質性を考慮した多種別連結運行スキームの分析 / 路線分割に基づく系統制御評価とオフセット設計 / 小規模シェアサイクルにおける再配置の効果分析と改善策の提案―茨城県つくば市「つくチャリ」を対象として―</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>土木計画学・交通工学 ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; 交通・モビリティ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 社会ネットワーク分析 ; 学習分析 ; 災害分析</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>土木計画学・交通工学
 交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム
@@ -13152,7 +13507,7 @@
 災害分析</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>ボトルネック渋滞と都市人口分布の相互依存関係の解析
 音声による速度回復情報提供の交通性能改善メカニズムの実証分析
@@ -13226,6 +13581,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>非線形・非正規状態空間モデルと多変量・高次元経済金融時系列分析
 統計的学習を用いた非線形計量経済モデルの新展開と金融・経済リスク評価への応用
 多変量／高次元の潜在変数をもつ時系列モデルの効率的ベイズ推測
@@ -13242,42 +13602,42 @@
 Bayesian Analysis of Time-Varying Quantiles Using a Smoothing Spline</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>非線形・非正規状態空間モデルと多変量・高次元経済金融時系列分析 / 統計的学習を用いた非線形計量経済モデルの新展開と金融・経済リスク評価への応用 / 多変量／高次元の潜在変数をもつ時系列モデルの効率的ベイズ推測 / 高次元データモデリングの新展開と統計的リスク分析 / 経済・金融多変量データのベイズモデリングと政策・行動の確率的評価</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>統計科学 / 経済統計</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>ベイズ統計学, 状態空間モデル</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Simulation of truncated and unimodal gamma distributions / Bayesian GARCH modeling for return and range / 時間変動する相関と確率的ボラティリティモデル / Multiple-block dynamic equicorrelations with realized measures, leverage and endogeneity / Dynamic equicorrelation stochastic volatility / Bayesian Analysis of Time-Varying Quantiles Using a Smoothing Spline</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>階層ディリクレ多項モデルの効率的な変分推論</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>統計科学 ; 経済統計 ; 保険・金融行動 ; GIS・空間分析 ; 建築・空間設計 ; 機械学習 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 学習分析 ; 統計学 ; 行政データ分析 ; 数理最適化</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>統計科学
 経済統計
@@ -13315,7 +13675,7 @@
 数理最適化</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>階層ディリクレ多項モデルの効率的な変分推論
 非線形・非正規状態空間モデルと多変量・高次元経済金融時系列分析
@@ -13359,6 +13719,11 @@
         </is>
       </c>
       <c r="F34" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>歩行からみた都市空間の評価とインフラ適正配置に関する数理的・実証的研究
 輸送モードの多様化と地域性・広域性を両立する公共交通網設計
@@ -13407,42 +13772,42 @@
 沿道電柱密度の地域別・道路種別比較</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>歩行からみた都市空間の評価とインフラ適正配置に関する数理的・実証的研究 / 輸送モードの多様化と地域性・広域性を両立する公共交通網設計 / 人口の年齢構成の変遷パターンと市街地構造・生活利便施設アクセシビリティとの関連性分析 / 位置情報ビッグデータを活用した人の移動パターンと都市施設・土地利用・交通網の関係性の分析 / 都市拠点の人流パターン解析と市街地構造変容の モデル分析研究 / デジタル時代の施設配置の理論－自己完結，個人情報保護，民主的決定による非効率性－ / 水害時の住民避難をより安全にする広域避難対策の社会的実装を図る計画技術の構築 / 都市の拠点集約と拠点間ネットワークの空間分析 / 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>都市計画・建築計画 / 社会システム工学・安全システム / 人文地理学 / 地理学 / 土木計画学・交通工学</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>都市解析 / 地域施設計画 / 立地科学 / 地域公共交通 / 地理情報科学 / 都市リスク分析</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>起伏を考慮した低炭素都市交通施策の評価 / 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関 / 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析 / 東京区部における年齢構成類型の変化と生活利便施設へのアクシセビリティ分析 / 電柱広告の空間的配置に関する研究―筑波研究学園都市中心部を対象に― / Exploring Network Scale Separation Strategies for Car-Bicycle Integration / 都市条件に応じた複数公共交通モード併用によるネットワーク設計 / 全国鉄道駅周辺地域における地域分断による移動制約の定量評価 / 小地域人口の年齢構成類型とその遷移から見た安定性分析 / 東京区部における業種構成・滞在パターンに基づく商業集積地の類型化と滞在移動特性の分析 / 東京区部におけるGPSデータに基づく街区レベル発生集中・滞在移動特性と建物用途構成 / 人口分布の集積性と鉄道網との連携度の変化動向に関する研究 / 東京区部における人口年齢構成と土地利用遷移の関連性分析 / 東京区部における交通量密度・移動速度に基づく交通軸と移動効率性評価 / 鉄道網による移動時間短縮を考慮した都市の人口分布の集積性の評価 / 人流データによる滞在者平均年齢の時空間分析 ―昼や休日に若返る自治体はどこか？― / 通学距離最小化と安定マッチングによる学校割当 / Preference-based jogging route selection in Downtown Tokyo / Effect of Speed Control for Travel Time and Emission Reduction in Connected Vehicle Environment / Exploring Separation Strategies for Car-Bicycle Integration / アジア地域の都市における鉄道・道路と人口分布構造 / 建物主要用途・トリップチェーンに着目した人流データによる街区間トリップ特性 / 人流データによる街区レベル時間帯別発生集中の時空間分布 / 人口重心に着目した人流分析 / 沿道電柱密度の地域別・道路種別比較</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>人口の年齢構成遷移と市街地構造・生活利便施設アクセシビリティとの関連性分析</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>都市計画・建築計画 ; 社会システム工学・安全システム ; 人文地理学 ; 地理学 ; 土木計画学・交通工学 ; 家族・人口政策 ; 都市・地域政策 ; GIS・空間分析 ; オペレーションズリサーチ ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析 ; 都市計画</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>都市計画・建築計画
 社会システム工学・安全システム
@@ -13504,7 +13869,7 @@
 都市計画</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>人口の年齢構成遷移と市街地構造・生活利便施設アクセシビリティとの関連性分析
 歩行からみた都市空間の評価とインフラ適正配置に関する数理的・実証的研究
@@ -13571,6 +13936,11 @@
         </is>
       </c>
       <c r="F35" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>世界測地系の構築
 合成開口レーダー解析ソフトウェアの開発
@@ -13614,30 +13984,30 @@
 Preceding, coseismic, and postseismic slips of the 2011 Tohoku earthquake, Japan</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>世界測地系の構築 / 合成開口レーダー解析ソフトウェアの開発 / 測地基準系の座標変換 / 地下水位と地盤上下変動に関する研究 / 地殻変動解析</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
         <is>
           <t>測地学 / 空間情報科学 / 測量学 / 地球観測 / リモートセンシング / 宇宙測地学 / 合成開口レーダー / 干渉法 / データサイエンス / 基準座標系</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>2011年東北地方太平洋沖地震後の余効変動の時空間関数モデリング / Spatiotemporal functional modeling of postseismic deformations after the 2011 Tohoku-Oki earthquake / Ground deformation in the Kobe-Osaka area during 22 years after the Kobe earthquake / 兵庫県南部地震以後の22年間の京阪神の地盤変動 / JERS-1/InSAR再解析：1995年兵庫県南部地震後の地殻変動の検出 / 兵庫県南部地震以降，六甲山は高くなったのか？ / Volcanic deformation of Atosanupuri volcanic complex in the Kussharo caldera, Japan, from 1993 to 2016 revealed by JERS-1, ALOS, and ALOS-2 radar interferometry / 宇宙測地技術により検出された1995年兵庫県南部地震の余効変動 / A possible restart of an interplate slow slip adjacent to the Tokai seismic gap in Japan / Combined logarithmic and exponential function model for fitting postseismic GNSS time series after 2011 Tohoku-Oki earthquake / だいち2号SAR干渉解析により捉えられた平成26年（2014年）長野県北部の地震に伴う地殻変動と地表変形 / だいち2号SAR干渉解析による御嶽山噴火に伴う地表変位の検出 (小特集 御嶽山噴火への対応) / P47 ALOS-2干渉SARにより捉えられた2015年箱根山・大涌谷火山活動に伴う地殻変動(ポスターセッション) / 2014年11月22日長野県北部の地震におけるSAR干渉画像に基づく地表変形現地調査結果 / 干渉SARで捉えた2014年11月22日長野県北部を震源とする地震に伴う地表変位 / Continuous gps observations on mindanao / 無人航空機(UAV)による西之島の空中写真撮影と高精度地形計測 / SAR干渉解析のための数値気象モデルを用いた大気遅延誤差の低減処理ツールの開発 / 無人航空機による西之島空中写真の撮影とその分析 / 無人機による西之島地形計測の高精度化 / Landform Monitoring in Active Volcano by UAV and SFM-MVS Technique / Spatial and temporal evolution of the long-term slow slip in the Bungo Channel, Japan / InSAR-derived Coseismic Deformation of the 2010 Southeastern Iran Earthquake (M6.5) and its Relationship with the Tectonic Background in the South of Lut Block / 新潟—神戸ひずみ集中帯越後平野付近の詳細地殻変動分布 / Preceding, coseismic, and postseismic slips of the 2011 Tohoku earthquake, Japan</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
         <is>
           <t>センサデータ解析 ; 災害分析 ; 環境工学 ; 行政データ分析</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>測地学
 空間情報科学
@@ -13655,7 +14025,7 @@
 行政データ分析</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>世界測地系の構築
 合成開口レーダー解析ソフトウェアの開発
@@ -13717,6 +14087,11 @@
         </is>
       </c>
       <c r="F36" t="inlineStr">
+        <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>災害時交通網の動学的設計にむけた不確かさ回避行動の評価手法の構築
 ネットワークリスクの動的変化と避難行動チェインの解明
@@ -13755,34 +14130,34 @@
 「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>災害時交通網の動学的設計にむけた不確かさ回避行動の評価手法の構築 / ネットワークリスクの動的変化と避難行動チェインの解明 / 次世代モビリティ導入を想定した交通・土地利用モデルの開発とその不確実性分析 / 災害時の他者支援行動を考慮した動的制御シミュレータの開発 / MaaS＋CV時代の次世代交通システムに向けたインフラと制度の設計 / 相乗型豪雨災害時の交通マネジメントの理論再構築と社会への実装 / 量子コンピューティングによる他者相互作用型の行動モデルの発展 / マルチスケールな拠点空間計画のための新たな行動モデル研究 / 災害時都市継続計画にむけた即応型需要予測の信頼性向上のためのデータフロー / 災害時都市活動支援のためのsoftware2.0型シミュレータの構築</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
         <is>
           <t>避難行動 / 交通需要 / 交通シミュレーション / 災害復旧 / 相互作用</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ / EVユーザーの充電場所選択問題に対するゲーム理論的考察 / 災害復旧期における個々人の移動パターン変化の特徴分析 / メタ分析による災害時の避難開始選択要因の評価 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 / 相互作用下での多肢選択行動の量子計算による求解 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— / 筑波大学理工学群におけるデータサイエンス応用基礎教育 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 / 選択肢の不確実性を考慮した動的離散選択モデル / LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること / 日本の復興計画の研究動向と今後の展望 -1995年以降の建築・都市・土木の計画分野を中心に- / LET'S GO ABROAD!(第77回)シンガポール、パキスタン、アフガニスタン、ベトナム、カンボジア 地域建設業の海外展開と見据える未来—A regional construction company looks to overseas expansion and their future—特集 土木と地政学 / 「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
         <is>
           <t>都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 観光・マーケティング ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 災害社会学 ; 防災政策 ; リスク評価 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 災害分析 ; 社会ネットワーク分析 ; 学習分析</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>避難行動
 交通需要
@@ -13832,7 +14207,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>災害時交通網の動学的設計にむけた不確かさ回避行動の評価手法の構築
 ネットワークリスクの動的変化と避難行動チェインの解明
@@ -13895,6 +14270,11 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>trios</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発
 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証
 Service Engineering
@@ -13911,34 +14291,34 @@
 Manufacturer’s strategy in a sharing economy</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発 / 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
         <is>
           <t>Service Engineering / Experimental economics</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 / What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews / Mystery shopping considering lifestyle heterogeneity / 経験効用モデルに基づくサービス継続利用を促すリマインダーの最適間隔 / Effects of Incentivized Fake Reviews on E-commerce Markets / Platform in manufacturing for enhancement of product value by sharing / Interpreting value creation model by case-based decision theory / Service switching in case-based decisions following bad experiences: Online reviews data of Japanese hairdressing salons / Multi-agent simulation for the manufacturer’s decision making in sharing markets / Manufacturer’s strategy in a sharing economy</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
         <is>
           <t>意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 推薦システム ; 政策評価 ; 学習分析</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Service Engineering
 Experimental economics
@@ -13953,7 +14333,7 @@
 学習分析</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発
 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -1067,10 +1067,14 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://researchmap.jp/new_accounts</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>researchmap_not_found</t>
+          <t>researchmap_profile_empty</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -8231,10 +8235,14 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://researchmap.jp/new_accounts</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>researchmap_not_found</t>
+          <t>researchmap_profile_empty</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -1067,14 +1067,10 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://researchmap.jp/new_accounts</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>researchmap_profile_empty</t>
+          <t>researchmap_error</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -8235,14 +8231,10 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://researchmap.jp/new_accounts</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>researchmap_profile_empty</t>
+          <t>researchmap_error</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -4530,7 +4530,7 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-%HPM&lt;F&lt;HD^miNFgONPFP=&lt;g&lt;&gt;gEKt
+2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -4567,7 +4567,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / %HPM&lt;F&lt;HD^miNFgONPFP=&lt;g&lt;&gt;gEKt</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; %HPM&lt;F&lt;HD^miNFgONPFP=&lt;g&lt;&gt;gEKt ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^ ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4608,7 +4608,7 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-%HPM&lt;F&lt;HD^miNFgONPFP=&lt;g&lt;&gt;gEKt
+2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^
 都市農村計画
 緑地計画
 都市・地域政策
@@ -7593,7 +7593,7 @@
 URL
 https://sites.google.com/view/hirokitakahashi/
 eメール
-+I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E
+)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
 研究室
 3F1236
 電話
@@ -7619,7 +7619,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / +I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -7635,7 +7635,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; +I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -7662,7 +7662,7 @@
 URL
 https://sites.google.com/view/hirokitakahashi/
 eメール
-+I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E
+)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
 研究室
 3F1236
 電話
@@ -11615,7 +11615,7 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-%HPM&lt;F&lt;HD^miNFgONPFP=&lt;g&lt;&gt;gEKt
+2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -11652,7 +11652,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / %HPM&lt;F&lt;HD^miNFgONPFP=&lt;g&lt;&gt;gEKt</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; %HPM&lt;F&lt;HD^miNFgONPFP=&lt;g&lt;&gt;gEKt ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^ ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -11693,7 +11693,7 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-%HPM&lt;F&lt;HD^miNFgONPFP=&lt;g&lt;&gt;gEKt
+2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^
 都市農村計画
 緑地計画
 都市・地域政策
@@ -14484,7 +14484,7 @@
 URL
 https://sites.google.com/view/hirokitakahashi/
 eメール
-+I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E
+)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
 研究室
 3F1236
 電話
@@ -14510,7 +14510,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / +I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -14526,7 +14526,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; +I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -14553,7 +14553,7 @@
 URL
 https://sites.google.com/view/hirokitakahashi/
 eメール
-+I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E
+)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
 研究室
 3F1236
 電話

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -3686,7 +3686,7 @@
 職名
 教授
 eメール
-)D8@BFZieJBcKJLBL98c8:cAG
+2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5
 最適化
 組合せ最適化
 アルゴリズム
@@ -3724,7 +3724,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / )D8@BFZieJBcKJLBL98c8:cAG</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / 2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; )D8@BFZieJBcKJLBL98c8:cAG ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; 2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3763,7 +3763,7 @@
 職名
 教授
 eメール
-)D8@BFZieJBcKJLBL98c8:cAG
+2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5
 最適化
 組合せ最適化
 アルゴリズム
@@ -4530,7 +4530,7 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^
+I$,)v"v$ :IE*"C+*,",wvCvxC!'P
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -4567,7 +4567,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / I$,)v"v$ :IE*"C+*,",wvCvxC!'P</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^ ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; I$,)v"v$ :IE*"C+*,",wvCvxC!'P ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4608,7 +4608,7 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^
+I$,)v"v$ :IE*"C+*,",wvCvxC!'P
 都市農村計画
 緑地計画
 都市・地域政策
@@ -10771,7 +10771,7 @@
 職名
 教授
 eメール
-)D8@BFZieJBcKJLBL98c8:cAG
+2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5
 最適化
 組合せ最適化
 アルゴリズム
@@ -10809,7 +10809,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / )D8@BFZieJBcKJLBL98c8:cAG</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / 2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; )D8@BFZieJBcKJLBL98c8:cAG ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; 2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -10848,7 +10848,7 @@
 職名
 教授
 eメール
-)D8@BFZieJBcKJLBL98c8:cAG
+2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5
 最適化
 組合せ最適化
 アルゴリズム
@@ -11615,7 +11615,7 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^
+I$,)v"v$ :IE*"C+*,",wvCvxC!'P
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -11652,7 +11652,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / I$,)v"v$ :IE*"C+*,",wvCvxC!'P</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^ ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; I$,)v"v$ :IE*"C+*,",wvCvxC!'P ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -11693,7 +11693,7 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q/5^
+I$,)v"v$ :IE*"C+*,",wvCvxC!'P
 都市農村計画
 緑地計画
 都市・地域政策

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -3686,7 +3686,8 @@
 職名
 教授
 eメール
-2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5
+/&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
+A
 最適化
 組合せ最適化
 アルゴリズム
@@ -3724,7 +3725,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / 2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / /&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] / A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3744,7 +3745,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; 2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; /&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] ; A ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3763,7 +3764,8 @@
 職名
 教授
 eメール
-2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5
+/&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
+A
 最適化
 組合せ最適化
 アルゴリズム
@@ -4530,7 +4532,7 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-I$,)v"v$ :IE*"C+*,",wvCvxC!'P
++BJG6@6B&gt;XgcH@aIHJ@J76a68a?En
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -4567,7 +4569,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / I$,)v"v$ :IE*"C+*,",wvCvxC!'P</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / +BJG6@6B&gt;XgcH@aIHJ@J76a68a?En</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4587,7 +4589,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; I$,)v"v$ :IE*"C+*,",wvCvxC!'P ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; +BJG6@6B&gt;XgcH@aIHJ@J76a68a?En ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4608,7 +4610,7 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-I$,)v"v$ :IE*"C+*,",wvCvxC!'P
++BJG6@6B&gt;XgcH@aIHJ@J76a68a?En
 都市農村計画
 緑地計画
 都市・地域政策
@@ -7593,7 +7595,12 @@
 URL
 https://sites.google.com/view/hirokitakahashi/
 eメール
-)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
+C1
+(
+%
+0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2}
+I
+I'-
 研究室
 3F1236
 電話
@@ -7619,7 +7626,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / C1 / ( / % / 0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2} / I / I'- / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -7635,7 +7642,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; C1 ; ( ; % ; 0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2} ; I ; I'- ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -7662,7 +7669,12 @@
 URL
 https://sites.google.com/view/hirokitakahashi/
 eメール
-)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
+C1
+(
+%
+0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2}
+I
+I'-
 研究室
 3F1236
 電話
@@ -10771,7 +10783,8 @@
 職名
 教授
 eメール
-2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5
+/&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
+A
 最適化
 組合せ最適化
 アルゴリズム
@@ -10809,7 +10822,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / 2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / /&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] / A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -10829,7 +10842,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; 2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; /&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] ; A ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -10848,7 +10861,8 @@
 職名
 教授
 eメール
-2&amp;.04HWS80Q98:0:'&amp;Q&amp;(Q/5
+/&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
+A
 最適化
 組合せ最適化
 アルゴリズム
@@ -11615,7 +11629,7 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-I$,)v"v$ :IE*"C+*,",wvCvxC!'P
++BJG6@6B&gt;XgcH@aIHJ@J76a68a?En
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -11652,7 +11666,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / I$,)v"v$ :IE*"C+*,",wvCvxC!'P</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / +BJG6@6B&gt;XgcH@aIHJ@J76a68a?En</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11672,7 +11686,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; I$,)v"v$ :IE*"C+*,",wvCvxC!'P ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; +BJG6@6B&gt;XgcH@aIHJ@J76a68a?En ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -11693,7 +11707,7 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-I$,)v"v$ :IE*"C+*,",wvCvxC!'P
++BJG6@6B&gt;XgcH@aIHJ@J76a68a?En
 都市農村計画
 緑地計画
 都市・地域政策
@@ -14484,7 +14498,12 @@
 URL
 https://sites.google.com/view/hirokitakahashi/
 eメール
-)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
+C1
+(
+%
+0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2}
+I
+I'-
 研究室
 3F1236
 電話
@@ -14510,7 +14529,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / C1 / ( / % / 0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2} / I / I'- / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -14526,7 +14545,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; C1 ; ( ; % ; 0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2} ; I ; I'- ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -14553,7 +14572,12 @@
 URL
 https://sites.google.com/view/hirokitakahashi/
 eメール
-)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
+C1
+(
+%
+0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2}
+I
+I'-
 研究室
 3F1236
 電話

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -3686,8 +3686,7 @@
 職名
 教授
 eメール
-/&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
-A
+58,46:N]Y&gt;6W?&gt;@6@-,W,.W5
 最適化
 組合せ最適化
 アルゴリズム
@@ -3725,7 +3724,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / /&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] / A</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / 58,46:N]Y&gt;6W?&gt;@6@-,W,.W5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3745,7 +3744,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; /&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] ; A ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; 58,46:N]Y&gt;6W?&gt;@6@-,W,.W5 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3764,8 +3763,7 @@
 職名
 教授
 eメール
-/&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
-A
+58,46:N]Y&gt;6W?&gt;@6@-,W,.W5
 最適化
 組合せ最適化
 アルゴリズム
@@ -4532,7 +4530,8 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-+BJG6@6B&gt;XgcH@aIHJ@J76a68a?En
+/&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
+Aj
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -4569,7 +4568,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / +BJG6@6B&gt;XgcH@aIHJ@J76a68a?En</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / /&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] / Aj</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4589,7 +4588,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; +BJG6@6B&gt;XgcH@aIHJ@J76a68a?En ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; /&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] ; Aj ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4610,7 +4609,8 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-+BJG6@6B&gt;XgcH@aIHJ@J76a68a?En
+/&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
+Aj
 都市農村計画
 緑地計画
 都市・地域政策
@@ -7595,12 +7595,7 @@
 URL
 https://sites.google.com/view/hirokitakahashi/
 eメール
-C1
-(
-%
-0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2}
-I
-I'-
+5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5
 研究室
 3F1236
 電話
@@ -7626,7 +7621,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / C1 / ( / % / 0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2} / I / I'- / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -7642,7 +7637,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; C1 ; ( ; % ; 0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2} ; I ; I'- ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -7669,12 +7664,7 @@
 URL
 https://sites.google.com/view/hirokitakahashi/
 eメール
-C1
-(
-%
-0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2}
-I
-I'-
+5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5
 研究室
 3F1236
 電話
@@ -10783,8 +10773,7 @@
 職名
 教授
 eメール
-/&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
-A
+58,46:N]Y&gt;6W?&gt;@6@-,W,.W5
 最適化
 組合せ最適化
 アルゴリズム
@@ -10822,7 +10811,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / /&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] / A</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / 58,46:N]Y&gt;6W?&gt;@6@-,W,.W5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -10842,7 +10831,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; /&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] ; A ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; 58,46:N]Y&gt;6W?&gt;@6@-,W,.W5 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -10861,8 +10850,7 @@
 職名
 教授
 eメール
-/&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
-A
+58,46:N]Y&gt;6W?&gt;@6@-,W,.W5
 最適化
 組合せ最適化
 アルゴリズム
@@ -11629,7 +11617,8 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-+BJG6@6B&gt;XgcH@aIHJ@J76a68a?En
+/&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
+Aj
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -11666,7 +11655,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / +BJG6@6B&gt;XgcH@aIHJ@J76a68a?En</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / /&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] / Aj</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11686,7 +11675,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; +BJG6@6B&gt;XgcH@aIHJ@J76a68a?En ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; /&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] ; Aj ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -11707,7 +11696,8 @@
 URL
 https://tsukubalandscapela.wixsite.com/landscape-lab
 eメール
-+BJG6@6B&gt;XgcH@aIHJ@J76a68a?En
+/&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
+Aj
 都市農村計画
 緑地計画
 都市・地域政策
@@ -14498,12 +14488,7 @@
 URL
 https://sites.google.com/view/hirokitakahashi/
 eメール
-C1
-(
-%
-0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2}
-I
-I'-
+5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5
 研究室
 3F1236
 電話
@@ -14529,7 +14514,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / C1 / ( / % / 0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2} / I / I'- / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -14545,7 +14530,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; C1 ; ( ; % ; 0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2} ; I ; I'- ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -14572,12 +14557,7 @@
 URL
 https://sites.google.com/view/hirokitakahashi/
 eメール
-C1
-(
-%
-0%&amp;I%&amp;/,(&amp;I$+@OK2I102(2}
-I
-I'-
+5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5
 研究室
 3F1236
 電話

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -1064,10 +1064,14 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=200901029857148130</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jglobal_not_found</t>
+          <t>ok_jglobal_direct</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1075,19 +1079,110 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
+超混雑環境における群集ナビゲーションに関する研究
+救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
+大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
+データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
+救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
+仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
+障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
+認知科学
+, 知能ロボティクス
+, 知覚情報処理
+, 知能情報学
+, ヒューマンインタフェース
+インタラクション
+, データベース
+知能ロボット
+, 映像処理
+Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
+Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
+一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
+Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
+Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究 / 超混雑環境における群集ナビゲーションに関する研究 / 救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上 / 大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成 / データ同化手法を用いた身体障害者の共創的衣服作製に関する研究 / 救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究 / 仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究 / 障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>認知科学 / , 知能ロボティクス / , 知覚情報処理 / , 知能情報学 / , ヒューマンインタフェース / インタラクション / , データベース</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>知能ロボット / , 映像処理</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718 / Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600 / 一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235 / Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376 / Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>認知科学 ; , 知能ロボティクス ; , 知覚情報処理 ; , 知能情報学 ; , ヒューマンインタフェース ; インタラクション ; , データベース ; GIS・空間分析 ; 建築・空間設計 ; スポーツデータ分析 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>認知科学
+, 知能ロボティクス
+, 知覚情報処理
+, 知能情報学
+, ヒューマンインタフェース
+インタラクション
+, データベース
+知能ロボット
+, 映像処理
+GIS・空間分析
+建築・空間設計
+スポーツデータ分析
+政策評価・計量分析
+医療・ヘルスデータ
+環境・エネルギー
+AI・データサイエンス
+GIS
+空間計量
+地理情報分析
+立地分析
+建築計画
+空間レイアウト生成
+居住空間設計
+都市空間デザイン
+スポーツアナリティクス
+戦術分析
+パフォーマンス分析
+政策評価
+計量経済学
+統計的因果推論
+実証分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
@@ -1097,7 +1192,20 @@
 大規模イベントにおける歩行者モデルの拡張と群集制御最適化
 多目的最適化による地下動線を活用した避難誘導効果の検証
 実時間で動作する音響イベント検出の大規模事前学習
-超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
+超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案
+超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
+超混雑環境における群集ナビゲーションに関する研究
+救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
+大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
+データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
+救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
+仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
+障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
+Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
+Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
+一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
+Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
+Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3794,8 @@
 職名
 教授
 eメール
-58,46:N]Y&gt;6W?&gt;@6@-,W,.W5
+&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
+A
 最適化
 組合せ最適化
 アルゴリズム
@@ -3724,7 +3833,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / 58,46:N]Y&gt;6W?&gt;@6@-,W,.W5</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / &gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] / A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3744,7 +3853,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; 58,46:N]Y&gt;6W?&gt;@6@-,W,.W5 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; &gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] ; A ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3763,7 +3872,8 @@
 職名
 教授
 eメール
-58,46:N]Y&gt;6W?&gt;@6@-,W,.W5
+&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
+A
 最適化
 組合せ最適化
 アルゴリズム
@@ -4528,10 +4638,11 @@
 職名
 教授
 URL
-https://tsukubalandscapela.wixsite.com/landscape-lab
+https:
+tsukubalandscapela.wixsite.com
+landscape-lab
 eメール
-/&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
-Aj
+G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -4568,7 +4679,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / /&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] / Aj</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4588,7 +4699,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; /&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] ; Aj ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4607,10 +4718,11 @@
 職名
 教授
 URL
-https://tsukubalandscapela.wixsite.com/landscape-lab
+https:
+tsukubalandscapela.wixsite.com
+landscape-lab
 eメール
-/&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
-Aj
+G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R
 都市農村計画
 緑地計画
 都市・地域政策
@@ -7380,8 +7492,10 @@
 ORCID
 0000-0003-4594-7436
 URL
-https://uratalab.net/
-http://junji-urata.net/
+https:
+uratalab.net
+http:
+junji-urata.net
 避難行動
 交通需要
 交通シミュレーション
@@ -7420,7 +7534,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 浦田 淳司(ウラタ ジュンジ) / 所属 / システム情報系 / 職名 / 准教授 / ORCID / 0000-0003-4594-7436 / URL / https://uratalab.net/ / http://junji-urata.net/</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 浦田 淳司(ウラタ ジュンジ) / 所属 / システム情報系 / 職名 / 准教授 / ORCID / 0000-0003-4594-7436 / URL / https: / uratalab.net / http: / junji-urata.net</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -7436,7 +7550,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 浦田 淳司(ウラタ ジュンジ) ; 所属 ; システム情報系 ; 職名 ; 准教授 ; ORCID ; 0000-0003-4594-7436 ; URL ; https://uratalab.net/ ; http://junji-urata.net/ ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 観光・マーケティング ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 浦田 淳司(ウラタ ジュンジ) ; 所属 ; システム情報系 ; 職名 ; 准教授 ; ORCID ; 0000-0003-4594-7436 ; URL ; https: ; uratalab.net ; http: ; junji-urata.net ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 観光・マーケティング ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -7457,8 +7571,10 @@
 ORCID
 0000-0003-4594-7436
 URL
-https://uratalab.net/
-http://junji-urata.net/
+https:
+uratalab.net
+http:
+junji-urata.net
 避難行動
 交通需要
 交通シミュレーション
@@ -7593,7 +7709,10 @@
 生年月
 1993-06
 URL
-https://sites.google.com/view/hirokitakahashi/
+https:
+sites.google.com
+view
+hirokitakahashi
 eメール
 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5
 研究室
@@ -7621,7 +7740,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -7637,7 +7756,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -7662,7 +7781,10 @@
 生年月
 1993-06
 URL
-https://sites.google.com/view/hirokitakahashi/
+https:
+sites.google.com
+view
+hirokitakahashi
 eメール
 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5
 研究室
@@ -8345,10 +8467,14 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=200901029857148130</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jglobal_not_found</t>
+          <t>ok_jglobal_direct</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -8356,19 +8482,110 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
+超混雑環境における群集ナビゲーションに関する研究
+救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
+大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
+データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
+救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
+仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
+障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
+認知科学
+, 知能ロボティクス
+, 知覚情報処理
+, 知能情報学
+, ヒューマンインタフェース
+インタラクション
+, データベース
+知能ロボット
+, 映像処理
+Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
+Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
+一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
+Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
+Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究 / 超混雑環境における群集ナビゲーションに関する研究 / 救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上 / 大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成 / データ同化手法を用いた身体障害者の共創的衣服作製に関する研究 / 救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究 / 仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究 / 障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>認知科学 / , 知能ロボティクス / , 知覚情報処理 / , 知能情報学 / , ヒューマンインタフェース / インタラクション / , データベース</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>知能ロボット / , 映像処理</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718 / Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600 / 一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235 / Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376 / Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>認知科学 ; , 知能ロボティクス ; , 知覚情報処理 ; , 知能情報学 ; , ヒューマンインタフェース ; インタラクション ; , データベース ; GIS・空間分析 ; 建築・空間設計 ; スポーツデータ分析 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>認知科学
+, 知能ロボティクス
+, 知覚情報処理
+, 知能情報学
+, ヒューマンインタフェース
+インタラクション
+, データベース
+知能ロボット
+, 映像処理
+GIS・空間分析
+建築・空間設計
+スポーツデータ分析
+政策評価・計量分析
+医療・ヘルスデータ
+環境・エネルギー
+AI・データサイエンス
+GIS
+空間計量
+地理情報分析
+立地分析
+建築計画
+空間レイアウト生成
+居住空間設計
+都市空間デザイン
+スポーツアナリティクス
+戦術分析
+パフォーマンス分析
+政策評価
+計量経済学
+統計的因果推論
+実証分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
@@ -8378,7 +8595,20 @@
 大規模イベントにおける歩行者モデルの拡張と群集制御最適化
 多目的最適化による地下動線を活用した避難誘導効果の検証
 実時間で動作する音響イベント検出の大規模事前学習
-超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
+超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案
+超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
+超混雑環境における群集ナビゲーションに関する研究
+救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
+大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
+データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
+救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
+仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
+障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
+Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
+Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
+一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
+Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
+Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
         </is>
       </c>
     </row>
@@ -10773,7 +11003,8 @@
 職名
 教授
 eメール
-58,46:N]Y&gt;6W?&gt;@6@-,W,.W5
+&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
+A
 最適化
 組合せ最適化
 アルゴリズム
@@ -10811,7 +11042,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / 58,46:N]Y&gt;6W?&gt;@6@-,W,.W5</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / &gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] / A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -10831,7 +11062,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; 58,46:N]Y&gt;6W?&gt;@6@-,W,.W5 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; &gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] ; A ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -10850,7 +11081,8 @@
 職名
 教授
 eメール
-58,46:N]Y&gt;6W?&gt;@6@-,W,.W5
+&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
+A
 最適化
 組合せ最適化
 アルゴリズム
@@ -11615,10 +11847,11 @@
 職名
 教授
 URL
-https://tsukubalandscapela.wixsite.com/landscape-lab
+https:
+tsukubalandscapela.wixsite.com
+landscape-lab
 eメール
-/&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
-Aj
+G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -11655,7 +11888,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https://tsukubalandscapela.wixsite.com/landscape-lab / eメール / /&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] / Aj</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11675,7 +11908,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https://tsukubalandscapela.wixsite.com/landscape-lab ; eメール ; /&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] ; Aj ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -11694,10 +11927,11 @@
 職名
 教授
 URL
-https://tsukubalandscapela.wixsite.com/landscape-lab
+https:
+tsukubalandscapela.wixsite.com
+landscape-lab
 eメール
-/&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
-Aj
+G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R
 都市農村計画
 緑地計画
 都市・地域政策
@@ -14273,8 +14507,10 @@
 ORCID
 0000-0003-4594-7436
 URL
-https://uratalab.net/
-http://junji-urata.net/
+https:
+uratalab.net
+http:
+junji-urata.net
 避難行動
 交通需要
 交通シミュレーション
@@ -14313,7 +14549,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 浦田 淳司(ウラタ ジュンジ) / 所属 / システム情報系 / 職名 / 准教授 / ORCID / 0000-0003-4594-7436 / URL / https://uratalab.net/ / http://junji-urata.net/</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 浦田 淳司(ウラタ ジュンジ) / 所属 / システム情報系 / 職名 / 准教授 / ORCID / 0000-0003-4594-7436 / URL / https: / uratalab.net / http: / junji-urata.net</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -14329,7 +14565,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 浦田 淳司(ウラタ ジュンジ) ; 所属 ; システム情報系 ; 職名 ; 准教授 ; ORCID ; 0000-0003-4594-7436 ; URL ; https://uratalab.net/ ; http://junji-urata.net/ ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 観光・マーケティング ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 浦田 淳司(ウラタ ジュンジ) ; 所属 ; システム情報系 ; 職名 ; 准教授 ; ORCID ; 0000-0003-4594-7436 ; URL ; https: ; uratalab.net ; http: ; junji-urata.net ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計 ; ネットワーク・グラフ理論 ; 災害・防災研究 ; 観光・マーケティング ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -14350,8 +14586,10 @@
 ORCID
 0000-0003-4594-7436
 URL
-https://uratalab.net/
-http://junji-urata.net/
+https:
+uratalab.net
+http:
+junji-urata.net
 避難行動
 交通需要
 交通シミュレーション
@@ -14486,7 +14724,10 @@
 生年月
 1993-06
 URL
-https://sites.google.com/view/hirokitakahashi/
+https:
+sites.google.com
+view
+hirokitakahashi
 eメール
 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5
 研究室
@@ -14514,7 +14755,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https://sites.google.com/view/hirokitakahashi/ / eメール / 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -14530,7 +14771,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https://sites.google.com/view/hirokitakahashi/ ; eメール ; 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -14555,7 +14796,10 @@
 生年月
 1993-06
 URL
-https://sites.google.com/view/hirokitakahashi/
+https:
+sites.google.com
+view
+hirokitakahashi
 eメール
 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5
 研究室

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -1064,14 +1064,10 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=200901029857148130</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ok_jglobal_direct</t>
+          <t>jglobal_not_found</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1079,110 +1075,19 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
-超混雑環境における群集ナビゲーションに関する研究
-救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
-大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
-データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
-救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
-仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
-障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
-認知科学
-, 知能ロボティクス
-, 知覚情報処理
-, 知能情報学
-, ヒューマンインタフェース
-インタラクション
-, データベース
-知能ロボット
-, 映像処理
-Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
-Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
-一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
-Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
-Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究 / 超混雑環境における群集ナビゲーションに関する研究 / 救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上 / 大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成 / データ同化手法を用いた身体障害者の共創的衣服作製に関する研究 / 救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究 / 仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究 / 障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>認知科学 / , 知能ロボティクス / , 知覚情報処理 / , 知能情報学 / , ヒューマンインタフェース / インタラクション / , データベース</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>知能ロボット / , 映像処理</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718 / Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600 / 一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235 / Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376 / Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>認知科学 ; , 知能ロボティクス ; , 知覚情報処理 ; , 知能情報学 ; , ヒューマンインタフェース ; インタラクション ; , データベース ; GIS・空間分析 ; 建築・空間設計 ; スポーツデータ分析 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>認知科学
-, 知能ロボティクス
-, 知覚情報処理
-, 知能情報学
-, ヒューマンインタフェース
-インタラクション
-, データベース
-知能ロボット
-, 映像処理
-GIS・空間分析
-建築・空間設計
-スポーツデータ分析
-政策評価・計量分析
-医療・ヘルスデータ
-環境・エネルギー
-AI・データサイエンス
-GIS
-空間計量
-地理情報分析
-立地分析
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
-政策評価
-計量経済学
-統計的因果推論
-実証分析
-医療データ分析
-生体情報解析
-ヘルスデータサイエンス
-統計解析
-環境政策
-エネルギーシステム
-脱炭素分析
-持続可能性評価</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
@@ -1192,20 +1097,7 @@
 大規模イベントにおける歩行者モデルの拡張と群集制御最適化
 多目的最適化による地下動線を活用した避難誘導効果の検証
 実時間で動作する音響イベント検出の大規模事前学習
-超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案
-超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
-超混雑環境における群集ナビゲーションに関する研究
-救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
-大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
-データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
-救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
-仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
-障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
-Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
-Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
-一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
-Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
-Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
     </row>
@@ -3794,8 +3686,7 @@
 職名
 教授
 eメール
-&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
-A
+=0$,.2FUQ6.O768.8%$O$&amp;O-3
 最適化
 組合せ最適化
 アルゴリズム
@@ -3833,7 +3724,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / &gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] / A</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / =0$,.2FUQ6.O768.8%$O$&amp;O-3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3853,7 +3744,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; &gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] ; A ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; =0$,.2FUQ6.O768.8%$O$&amp;O-3 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3872,8 +3763,7 @@
 職名
 教授
 eメール
-&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
-A
+=0$,.2FUQ6.O768.8%$O$&amp;O-3
 最適化
 組合せ最適化
 アルゴリズム
@@ -4642,7 +4532,8 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R
+&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
+Aj
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -4679,7 +4570,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] / Aj</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4699,7 +4590,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] ; Aj ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4722,7 +4613,8 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R
+&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
+Aj
 都市農村計画
 緑地計画
 都市・地域政策
@@ -7714,7 +7606,7 @@
 view
 hirokitakahashi
 eメール
-5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5
++I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E
 研究室
 3F1236
 電話
@@ -7740,7 +7632,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / +I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -7756,7 +7648,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; +I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -7786,7 +7678,7 @@
 view
 hirokitakahashi
 eメール
-5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5
++I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E
 研究室
 3F1236
 電話
@@ -8467,14 +8359,10 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=200901029857148130</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ok_jglobal_direct</t>
+          <t>jglobal_not_found</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -8482,110 +8370,19 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
-超混雑環境における群集ナビゲーションに関する研究
-救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
-大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
-データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
-救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
-仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
-障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
-認知科学
-, 知能ロボティクス
-, 知覚情報処理
-, 知能情報学
-, ヒューマンインタフェース
-インタラクション
-, データベース
-知能ロボット
-, 映像処理
-Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
-Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
-一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
-Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
-Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究 / 超混雑環境における群集ナビゲーションに関する研究 / 救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上 / 大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成 / データ同化手法を用いた身体障害者の共創的衣服作製に関する研究 / 救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究 / 仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究 / 障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>認知科学 / , 知能ロボティクス / , 知覚情報処理 / , 知能情報学 / , ヒューマンインタフェース / インタラクション / , データベース</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>知能ロボット / , 映像処理</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718 / Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600 / 一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235 / Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376 / Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>認知科学 ; , 知能ロボティクス ; , 知覚情報処理 ; , 知能情報学 ; , ヒューマンインタフェース ; インタラクション ; , データベース ; GIS・空間分析 ; 建築・空間設計 ; スポーツデータ分析 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>認知科学
-, 知能ロボティクス
-, 知覚情報処理
-, 知能情報学
-, ヒューマンインタフェース
-インタラクション
-, データベース
-知能ロボット
-, 映像処理
-GIS・空間分析
-建築・空間設計
-スポーツデータ分析
-政策評価・計量分析
-医療・ヘルスデータ
-環境・エネルギー
-AI・データサイエンス
-GIS
-空間計量
-地理情報分析
-立地分析
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
-政策評価
-計量経済学
-統計的因果推論
-実証分析
-医療データ分析
-生体情報解析
-ヘルスデータサイエンス
-統計解析
-環境政策
-エネルギーシステム
-脱炭素分析
-持続可能性評価</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
@@ -8595,20 +8392,7 @@
 大規模イベントにおける歩行者モデルの拡張と群集制御最適化
 多目的最適化による地下動線を活用した避難誘導効果の検証
 実時間で動作する音響イベント検出の大規模事前学習
-超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案
-超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
-超混雑環境における群集ナビゲーションに関する研究
-救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
-大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
-データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
-救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
-仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
-障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
-Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
-Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
-一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
-Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
-Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
     </row>
@@ -11003,8 +10787,7 @@
 職名
 教授
 eメール
-&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
-A
+=0$,.2FUQ6.O768.8%$O$&amp;O-3
 最適化
 組合せ最適化
 アルゴリズム
@@ -11042,7 +10825,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / &gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] / A</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / =0$,.2FUQ6.O768.8%$O$&amp;O-3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -11062,7 +10845,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; &gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24] ; A ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; =0$,.2FUQ6.O768.8%$O$&amp;O-3 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -11081,8 +10864,7 @@
 職名
 教授
 eメール
-&gt;2:&lt;@Tc_D&lt;]EDF&lt;F32]24]
-A
+=0$,.2FUQ6.O768.8%$O$&amp;O-3
 最適化
 組合せ最適化
 アルゴリズム
@@ -11851,7 +11633,8 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R
+&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
+Aj
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -11888,7 +11671,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] / Aj</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11908,7 +11691,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] ; Aj ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -11931,7 +11714,8 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-G&amp;.+x$x&amp;"&lt;KG,$E-,.$.yxExzE#)R
+&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
+Aj
 都市農村計画
 緑地計画
 都市・地域政策
@@ -14729,7 +14513,7 @@
 view
 hirokitakahashi
 eメール
-5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5
++I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E
 研究室
 3F1236
 電話
@@ -14755,7 +14539,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / +I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -14771,7 +14555,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; 5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; +I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -14801,7 +14585,7 @@
 view
 hirokitakahashi
 eメール
-5?,6,3,&gt;34W34=:64W29N]Y@W?&gt;@6@-,W,.W5
++I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E
 研究室
 3F1236
 電話

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -1064,10 +1064,14 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=200901029857148130</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jglobal_not_found</t>
+          <t>ok_jglobal_fallback</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1075,19 +1079,110 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
+超混雑環境における群集ナビゲーションに関する研究
+救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
+大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
+データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
+救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
+仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
+障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
+認知科学
+, 知能ロボティクス
+, 知覚情報処理
+, 知能情報学
+, ヒューマンインタフェース
+インタラクション
+, データベース
+知能ロボット
+, 映像処理
+Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
+Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
+一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
+Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
+Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究 / 超混雑環境における群集ナビゲーションに関する研究 / 救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上 / 大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成 / データ同化手法を用いた身体障害者の共創的衣服作製に関する研究 / 救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究 / 仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究 / 障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>認知科学 / , 知能ロボティクス / , 知覚情報処理 / , 知能情報学 / , ヒューマンインタフェース / インタラクション / , データベース</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>知能ロボット / , 映像処理</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718 / Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600 / 一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235 / Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376 / Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>認知科学 ; , 知能ロボティクス ; , 知覚情報処理 ; , 知能情報学 ; , ヒューマンインタフェース ; インタラクション ; , データベース ; GIS・空間分析 ; 建築・空間設計 ; スポーツデータ分析 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>認知科学
+, 知能ロボティクス
+, 知覚情報処理
+, 知能情報学
+, ヒューマンインタフェース
+インタラクション
+, データベース
+知能ロボット
+, 映像処理
+GIS・空間分析
+建築・空間設計
+スポーツデータ分析
+政策評価・計量分析
+医療・ヘルスデータ
+環境・エネルギー
+AI・データサイエンス
+GIS
+空間計量
+地理情報分析
+立地分析
+建築計画
+空間レイアウト生成
+居住空間設計
+都市空間デザイン
+スポーツアナリティクス
+戦術分析
+パフォーマンス分析
+政策評価
+計量経済学
+統計的因果推論
+実証分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
@@ -1097,7 +1192,20 @@
 大規模イベントにおける歩行者モデルの拡張と群集制御最適化
 多目的最適化による地下動線を活用した避難誘導効果の検証
 実時間で動作する音響イベント検出の大規模事前学習
-超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
+超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案
+超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
+超混雑環境における群集ナビゲーションに関する研究
+救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
+大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
+データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
+救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
+仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
+障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
+Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
+Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
+一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
+Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
+Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3794,10 @@
 職名
 教授
 eメール
-=0$,.2FUQ6.O768.8%$O$&amp;O-3
+C*
+&amp;(,@OK0(I102(2}
+I
+I'-
 最適化
 組合せ最適化
 アルゴリズム
@@ -3724,7 +3835,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / =0$,.2FUQ6.O768.8%$O$&amp;O-3</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / C* / &amp;(,@OK0(I102(2} / I / I'-</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3744,7 +3855,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; =0$,.2FUQ6.O768.8%$O$&amp;O-3 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; C* ; &amp;(,@OK0(I102(2} ; I ; I'- ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3763,7 +3874,10 @@
 職名
 教授
 eメール
-=0$,.2FUQ6.O768.8%$O$&amp;O-3
+C*
+&amp;(,@OK0(I102(2}
+I
+I'-
 最適化
 組合せ最適化
 アルゴリズム
@@ -4532,8 +4646,11 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
-Aj
+C*2
+(
+*&amp;@OK0(I102(2}
+I
+I'-V
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -4570,7 +4687,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] / Aj</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / C*2 / ( / *&amp;@OK0(I102(2} / I / I'-V</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4590,7 +4707,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] ; Aj ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; C*2 ; ( ; *&amp;@OK0(I102(2} ; I ; I'-V ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4613,8 +4730,11 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
-Aj
+C*2
+(
+*&amp;@OK0(I102(2}
+I
+I'-V
 都市農村計画
 緑地計画
 都市・地域政策
@@ -7606,7 +7726,7 @@
 view
 hirokitakahashi
 eメール
-+I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E
+=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
 研究室
 3F1236
 電話
@@ -7632,7 +7752,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / +I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -7648,7 +7768,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; +I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -7678,7 +7798,7 @@
 view
 hirokitakahashi
 eメール
-+I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E
+=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
 研究室
 3F1236
 電話
@@ -8359,10 +8479,14 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=200901029857148130</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jglobal_not_found</t>
+          <t>ok_jglobal_fallback</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -8370,19 +8494,110 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
+超混雑環境における群集ナビゲーションに関する研究
+救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
+大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
+データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
+救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
+仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
+障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
+認知科学
+, 知能ロボティクス
+, 知覚情報処理
+, 知能情報学
+, ヒューマンインタフェース
+インタラクション
+, データベース
+知能ロボット
+, 映像処理
+Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
+Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
+一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
+Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
+Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究 / 超混雑環境における群集ナビゲーションに関する研究 / 救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上 / 大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成 / データ同化手法を用いた身体障害者の共創的衣服作製に関する研究 / 救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究 / 仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究 / 障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>認知科学 / , 知能ロボティクス / , 知覚情報処理 / , 知能情報学 / , ヒューマンインタフェース / インタラクション / , データベース</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>知能ロボット / , 映像処理</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718 / Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600 / 一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235 / Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376 / Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>認知科学 ; , 知能ロボティクス ; , 知覚情報処理 ; , 知能情報学 ; , ヒューマンインタフェース ; インタラクション ; , データベース ; GIS・空間分析 ; 建築・空間設計 ; スポーツデータ分析 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; AI・データサイエンス</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>認知科学
+, 知能ロボティクス
+, 知覚情報処理
+, 知能情報学
+, ヒューマンインタフェース
+インタラクション
+, データベース
+知能ロボット
+, 映像処理
+GIS・空間分析
+建築・空間設計
+スポーツデータ分析
+政策評価・計量分析
+医療・ヘルスデータ
+環境・エネルギー
+AI・データサイエンス
+GIS
+空間計量
+地理情報分析
+立地分析
+建築計画
+空間レイアウト生成
+居住空間設計
+都市空間デザイン
+スポーツアナリティクス
+戦術分析
+パフォーマンス分析
+政策評価
+計量経済学
+統計的因果推論
+実証分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
@@ -8392,7 +8607,20 @@
 大規模イベントにおける歩行者モデルの拡張と群集制御最適化
 多目的最適化による地下動線を活用した避難誘導効果の検証
 実時間で動作する音響イベント検出の大規模事前学習
-超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
+超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案
+超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
+超混雑環境における群集ナビゲーションに関する研究
+救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
+大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
+データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
+救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
+仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
+障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
+Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
+Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
+一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
+Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
+Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
         </is>
       </c>
     </row>
@@ -10787,7 +11015,10 @@
 職名
 教授
 eメール
-=0$,.2FUQ6.O768.8%$O$&amp;O-3
+C*
+&amp;(,@OK0(I102(2}
+I
+I'-
 最適化
 組合せ最適化
 アルゴリズム
@@ -10825,7 +11056,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / =0$,.2FUQ6.O768.8%$O$&amp;O-3</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / C* / &amp;(,@OK0(I102(2} / I / I'-</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -10845,7 +11076,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; =0$,.2FUQ6.O768.8%$O$&amp;O-3 ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; C* ; &amp;(,@OK0(I102(2} ; I ; I'- ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -10864,7 +11095,10 @@
 職名
 教授
 eメール
-=0$,.2FUQ6.O768.8%$O$&amp;O-3
+C*
+&amp;(,@OK0(I102(2}
+I
+I'-
 最適化
 組合せ最適化
 アルゴリズム
@@ -11633,8 +11867,11 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
-Aj
+C*2
+(
+*&amp;@OK0(I102(2}
+I
+I'-V
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -11671,7 +11908,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] / Aj</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / C*2 / ( / *&amp;@OK0(I102(2} / I / I'-V</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11691,7 +11928,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] ; Aj ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; C*2 ; ( ; *&amp;@OK0(I102(2} ; I ; I'-V ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -11714,8 +11951,11 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
-Aj
+C*2
+(
+*&amp;@OK0(I102(2}
+I
+I'-V
 都市農村計画
 緑地計画
 都市・地域政策
@@ -14513,7 +14753,7 @@
 view
 hirokitakahashi
 eメール
-+I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E
+=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
 研究室
 3F1236
 電話
@@ -14539,7 +14779,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / +I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -14555,7 +14795,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; +I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -14585,7 +14825,7 @@
 view
 hirokitakahashi
 eメール
-+I6@6=6H=&gt;a=&gt;GD@&gt;a&lt;CXgcJaIHJ@J76a68a?E
+=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
 研究室
 3F1236
 電話

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -3794,10 +3794,7 @@
 職名
 教授
 eメール
-C*
-&amp;(,@OK0(I102(2}
-I
-I'-
+G&amp;x"$(&lt;KG,$E-,.$.yxExzE#)
 最適化
 組合せ最適化
 アルゴリズム
@@ -3835,7 +3832,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / C* / &amp;(,@OK0(I102(2} / I / I'-</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / G&amp;x"$(&lt;KG,$E-,.$.yxExzE#)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3855,7 +3852,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; C* ; &amp;(,@OK0(I102(2} ; I ; I'- ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; G&amp;x"$(&lt;KG,$E-,.$.yxExzE#) ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3874,10 +3871,7 @@
 職名
 教授
 eメール
-C*
-&amp;(,@OK0(I102(2}
-I
-I'-
+G&amp;x"$(&lt;KG,$E-,.$.yxExzE#)
 最適化
 組合せ最適化
 アルゴリズム
@@ -4646,11 +4640,7 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-C*2
-(
-*&amp;@OK0(I102(2}
-I
-I'-V
+=085$.$0,FUQ6.O768.8%$O$&amp;O-3\
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -4687,7 +4677,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / C*2 / ( / *&amp;@OK0(I102(2} / I / I'-V</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / =085$.$0,FUQ6.O768.8%$O$&amp;O-3\</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4707,7 +4697,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; C*2 ; ( ; *&amp;@OK0(I102(2} ; I ; I'-V ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; =085$.$0,FUQ6.O768.8%$O$&amp;O-3\ ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4730,11 +4720,7 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-C*2
-(
-*&amp;@OK0(I102(2}
-I
-I'-V
+=085$.$0,FUQ6.O768.8%$O$&amp;O-3\
 都市農村計画
 緑地計画
 都市・地域政策
@@ -7726,7 +7712,8 @@
 view
 hirokitakahashi
 eメール
-=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
+9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q
+5
 研究室
 3F1236
 電話
@@ -7752,7 +7739,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / 9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q / 5 / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -7768,7 +7755,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; 9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q ; 5 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -7798,7 +7785,8 @@
 view
 hirokitakahashi
 eメール
-=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
+9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q
+5
 研究室
 3F1236
 電話
@@ -11015,10 +11003,7 @@
 職名
 教授
 eメール
-C*
-&amp;(,@OK0(I102(2}
-I
-I'-
+G&amp;x"$(&lt;KG,$E-,.$.yxExzE#)
 最適化
 組合せ最適化
 アルゴリズム
@@ -11056,7 +11041,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / C* / &amp;(,@OK0(I102(2} / I / I'-</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / G&amp;x"$(&lt;KG,$E-,.$.yxExzE#)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -11076,7 +11061,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; C* ; &amp;(,@OK0(I102(2} ; I ; I'- ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; G&amp;x"$(&lt;KG,$E-,.$.yxExzE#) ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -11095,10 +11080,7 @@
 職名
 教授
 eメール
-C*
-&amp;(,@OK0(I102(2}
-I
-I'-
+G&amp;x"$(&lt;KG,$E-,.$.yxExzE#)
 最適化
 組合せ最適化
 アルゴリズム
@@ -11867,11 +11849,7 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-C*2
-(
-*&amp;@OK0(I102(2}
-I
-I'-V
+=085$.$0,FUQ6.O768.8%$O$&amp;O-3\
 都市農村計画
 緑地計画
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
@@ -11908,7 +11886,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / C*2 / ( / *&amp;@OK0(I102(2} / I / I'-V</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / =085$.$0,FUQ6.O768.8%$O$&amp;O-3\</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11928,7 +11906,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; C*2 ; ( ; *&amp;@OK0(I102(2} ; I ; I'-V ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; =085$.$0,FUQ6.O768.8%$O$&amp;O-3\ ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -11951,11 +11929,7 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-C*2
-(
-*&amp;@OK0(I102(2}
-I
-I'-V
+=085$.$0,FUQ6.O768.8%$O$&amp;O-3\
 都市農村計画
 緑地計画
 都市・地域政策
@@ -14753,7 +14727,8 @@
 view
 hirokitakahashi
 eメール
-=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
+9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q
+5
 研究室
 3F1236
 電話
@@ -14779,7 +14754,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / 9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q / 5 / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -14795,7 +14770,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; 9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q ; 5 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -14825,7 +14800,8 @@
 view
 hirokitakahashi
 eメール
-=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
+9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q
+5
 研究室
 3F1236
 電話

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -747,6 +747,7 @@
 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―
 経済政策
 開発経済学、教育の経済学、健康の経済学、応用計量経済学
+非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
 Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05
 Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020
 The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04
@@ -770,8 +771,7 @@
 ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 牛島 光一 応用地域学研究/(18)/pp.62-63, 2014-09
 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 牛島 光一 住宅土地経済/(2010年秋季)/pp.36-39, 2010-10
 The Impact of a High-speed Railway on Residential Land Prices Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1344), 2016-03
-The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10
-School Choice and Student Sorting: Evidence from Adachi City in Japan Ushijima Koichi Department of Social Systems and Management, University of Tsukuba, 2007-03</t>
+The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05 / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020 / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04 / The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/p.1305, 2017 Tsukuba Repository / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... JAPAN AND THE WORLD ECONOMY/50/pp.36-46, 2019-06 / School Choice and Student Sorting: Evidence from Adachi Ward in Japan 牛島 光一 Japanese Economic Review/60(4)/pp.446-472, 2009-12 / オリンピック・パラリンピックにはどんな経済効果があるのか 牛島 光一 経済セミナー 2019年4・5月号, 2019-03 / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi Public Policy Review, 2020-09 / Building an Administrative Database of Children Bessho Shun-ichiro; Noguchi Haruko; 牛島 光一; Kawamura Akir... Public Policy Review, 2020-09 / 高速鉄道の建設が居住地価格に与えた影響 牛島 光一 季刊 住宅土地経済/pp.24-31, 2019-07 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... IZA Discussion Papers, 2020-04 / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ 香川涼亮; 小倉利仁; 太田 充; 牛島光一 都市住宅学/97/pp.126-135, 2017-04 CiNii / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― 姜 哲敏; 太田 充; 牛島光一 応用地域学研究/20/pp.67-77, 2016-09 / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 牛島 光一 応用地域学研究/(14)/pp.37-47, 2009-12 / 学校の質と地価－足立区の地価データを用いた検証 牛島 光一 住宅土地経済/(68)/pp.10-18, 2008-04 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ 牛島 光一 フィナンシャルレビュー/(141)/pp.65-85, 2019-12 / 子どもについての行政データベースの構築 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.106-119, 2019-12 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.120-140, 2019-12 / 区立小学校での補習の効果：足立区のケース 別所俊一郎; 川村顕; 野口晴子; 田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.141-159, 2019-12 / ヘドニック・アプローチにおける因果識別 牛島 光一 都市住宅学/2016(92)/pp.25-30, 2016-01 CiNii / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 牛島 光一 応用地域学研究/(18)/pp.62-63, 2014-09 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 牛島 光一 住宅土地経済/(2010年秋季)/pp.36-39, 2010-10 / The Impact of a High-speed Railway on Residential Land Prices Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1344), 2016-03 / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10 / School Choice and Student Sorting: Evidence from Adachi City in Japan Ushijima Koichi Department of Social Systems and Management, University of Tsukuba, 2007-03</t>
+          <t>非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17 / Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05 / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020 / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04 / The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/p.1305, 2017 Tsukuba Repository / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... JAPAN AND THE WORLD ECONOMY/50/pp.36-46, 2019-06 / School Choice and Student Sorting: Evidence from Adachi Ward in Japan 牛島 光一 Japanese Economic Review/60(4)/pp.446-472, 2009-12 / オリンピック・パラリンピックにはどんな経済効果があるのか 牛島 光一 経済セミナー 2019年4・5月号, 2019-03 / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi Public Policy Review, 2020-09 / Building an Administrative Database of Children Bessho Shun-ichiro; Noguchi Haruko; 牛島 光一; Kawamura Akir... Public Policy Review, 2020-09 / 高速鉄道の建設が居住地価格に与えた影響 牛島 光一 季刊 住宅土地経済/pp.24-31, 2019-07 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... IZA Discussion Papers, 2020-04 / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ 香川涼亮; 小倉利仁; 太田 充; 牛島光一 都市住宅学/97/pp.126-135, 2017-04 CiNii / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― 姜 哲敏; 太田 充; 牛島光一 応用地域学研究/20/pp.67-77, 2016-09 / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 牛島 光一 応用地域学研究/(14)/pp.37-47, 2009-12 / 学校の質と地価－足立区の地価データを用いた検証 牛島 光一 住宅土地経済/(68)/pp.10-18, 2008-04 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ 牛島 光一 フィナンシャルレビュー/(141)/pp.65-85, 2019-12 / 子どもについての行政データベースの構築 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.106-119, 2019-12 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.120-140, 2019-12 / 区立小学校での補習の効果：足立区のケース 別所俊一郎; 川村顕; 野口晴子; 田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.141-159, 2019-12 / ヘドニック・アプローチにおける因果識別 牛島 光一 都市住宅学/2016(92)/pp.25-30, 2016-01 CiNii / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 牛島 光一 応用地域学研究/(18)/pp.62-63, 2014-09 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 牛島 光一 住宅土地経済/(2010年秋季)/pp.36-39, 2010-10 / The Impact of a High-speed Railway on Residential Land Prices Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1344), 2016-03 / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -867,6 +867,7 @@
 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年
 都市における環境リスクの軽減の経済効果に関する研究
 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―
+非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
 Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05
 Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020
 The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04
@@ -890,8 +891,7 @@
 ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 牛島 光一 応用地域学研究/(18)/pp.62-63, 2014-09
 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 牛島 光一 住宅土地経済/(2010年秋季)/pp.36-39, 2010-10
 The Impact of a High-speed Railway on Residential Land Prices Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1344), 2016-03
-The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10
-School Choice and Student Sorting: Evidence from Adachi City in Japan Ushijima Koichi Department of Social Systems and Management, University of Tsukuba, 2007-03</t>
+The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10</t>
         </is>
       </c>
     </row>
@@ -934,6 +934,8 @@
 理論経済学
 社会システム工学・安全システム
 ゲーム理論; 進化ゲーム理論;
+Pairwise Imitation and Tournament Graphs Hwang Sung-ha; Neary Philip R.; Newton Jonathan; Sawa ... INTERNATIONAL ECONOMIC REVIEW, 2026-02-04
+Conventions in large games with randomly drawn payoffs Newton Jonathan; Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/157/pp.50-70, 2026-03
 The evolution of collective choice under majority rules Okada Akira; Sawa Ryoji JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/225/pp.290-304, 2024-09
 Statistical inference in evolutionary dynamics Sawa Ryoji; Wu Jiabin GAMES AND ECONOMIC BEHAVIOR/137/pp.294-316, 2023-01
 研究室の選好と学生の成績を考慮した研究室配属法の分析 杉浦 有輝; 澤 亮治 情報処理学会論文誌/64(3)/pp.698-707, 2023-03
@@ -971,7 +973,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The evolution of collective choice under majority rules Okada Akira; Sawa Ryoji JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/225/pp.290-304, 2024-09 / Statistical inference in evolutionary dynamics Sawa Ryoji; Wu Jiabin GAMES AND ECONOMIC BEHAVIOR/137/pp.294-316, 2023-01 / 研究室の選好と学生の成績を考慮した研究室配属法の分析 杉浦 有輝; 澤 亮治 情報処理学会論文誌/64(3)/pp.698-707, 2023-03 / 有限オートマトンを用いた私的観測繰り返しゲームにおける進化的安定戦略分析 小池 淳平; 澤 亮治 情報処理学会論文誌/63(3)/pp.773-786, 2022-03 / A stochastic stability analysis with observation errors in normal form games Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/129/pp.570-589, 2021-09 / Stochastic stability in the large population and small mutation limits for coordination games Sawa Ryoji Journal of Dynamics and Games, 2021 / oTreeを用いた配属システムの設計・構築とその運用 島田 夏美; 吉田 真聖人; 澤 亮治 情報処理学会論文誌/62(3)/pp.849-859, 2021-03 CiNii / A prospect theory Nash bargaining solution and its stochastic stability Sawa Ryoji JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/184/pp.692-711, 2021-04 / 複利型強化学習を用いたポートフォリオ選択手法についての研究 畠山 卓; 澤 亮治 情報処理学会論文誌/60(10)/pp.1631-1640, 2019-10 / Evolutionary dynamics in multitasking environments Sawa Ryoji; Zusai Dai JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/166/pp.288-308, 2019-10 / Stochastic stability under logit choice in coalitional bargaining problems Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/113/pp.633-650, 2019-01 Tsukuba Repository / Prospect dynamics and loss dominance Sawa Ryoji; Wu Jiabin GAMES AND ECONOMIC BEHAVIOR/112/pp.98-124, 2018-11 Tsukuba Repository / Reference-dependent preferences, super-dominance and stochastic stability Sawa Ryoji; Wu Jiabin JOURNAL OF MATHEMATICAL ECONOMICS/78/pp.96-104, 2018-10 Tsukuba Repository / A one-shot deviation principle for stability in matching problems Newton Jonathan; Sawa Ryoji JOURNAL OF ECONOMIC THEORY/157/pp.1-27, 2015-05 / Evolutionary imitative dynamics with population-varying aspiration levels Sawa Ryoji JOURNAL OF ECONOMIC THEORY/154/pp.562-577, 2014-11 / Coalitional stochastic stability in games, networks and markets Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/88/pp.90-111, 2014-11 / Mutation rates and equilibrium selection under stochastic evolutionary dynamics Sawa Ryoji INTERNATIONAL JOURNAL OF GAME THEORY/41(3)/pp.489-496, 2012-08 / CG を用いたマシンの3 次元構造進化システム 澤 亮治 電気学会論文誌. C, 電子・情報・システム部門誌 = The transactions of the Institute of Electrical Engineers of Japan. C, A publication of Electronics, Information and System Society/121(2)/pp.461-467, 2001-02</t>
+          <t>Pairwise Imitation and Tournament Graphs Hwang Sung-ha; Neary Philip R.; Newton Jonathan; Sawa ... INTERNATIONAL ECONOMIC REVIEW, 2026-02-04 / Conventions in large games with randomly drawn payoffs Newton Jonathan; Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/157/pp.50-70, 2026-03 / The evolution of collective choice under majority rules Okada Akira; Sawa Ryoji JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/225/pp.290-304, 2024-09 / Statistical inference in evolutionary dynamics Sawa Ryoji; Wu Jiabin GAMES AND ECONOMIC BEHAVIOR/137/pp.294-316, 2023-01 / 研究室の選好と学生の成績を考慮した研究室配属法の分析 杉浦 有輝; 澤 亮治 情報処理学会論文誌/64(3)/pp.698-707, 2023-03 / 有限オートマトンを用いた私的観測繰り返しゲームにおける進化的安定戦略分析 小池 淳平; 澤 亮治 情報処理学会論文誌/63(3)/pp.773-786, 2022-03 / A stochastic stability analysis with observation errors in normal form games Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/129/pp.570-589, 2021-09 / Stochastic stability in the large population and small mutation limits for coordination games Sawa Ryoji Journal of Dynamics and Games, 2021 / oTreeを用いた配属システムの設計・構築とその運用 島田 夏美; 吉田 真聖人; 澤 亮治 情報処理学会論文誌/62(3)/pp.849-859, 2021-03 CiNii / A prospect theory Nash bargaining solution and its stochastic stability Sawa Ryoji JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/184/pp.692-711, 2021-04 / 複利型強化学習を用いたポートフォリオ選択手法についての研究 畠山 卓; 澤 亮治 情報処理学会論文誌/60(10)/pp.1631-1640, 2019-10 / Evolutionary dynamics in multitasking environments Sawa Ryoji; Zusai Dai JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/166/pp.288-308, 2019-10 / Stochastic stability under logit choice in coalitional bargaining problems Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/113/pp.633-650, 2019-01 Tsukuba Repository / Prospect dynamics and loss dominance Sawa Ryoji; Wu Jiabin GAMES AND ECONOMIC BEHAVIOR/112/pp.98-124, 2018-11 Tsukuba Repository / Reference-dependent preferences, super-dominance and stochastic stability Sawa Ryoji; Wu Jiabin JOURNAL OF MATHEMATICAL ECONOMICS/78/pp.96-104, 2018-10 Tsukuba Repository / A one-shot deviation principle for stability in matching problems Newton Jonathan; Sawa Ryoji JOURNAL OF ECONOMIC THEORY/157/pp.1-27, 2015-05 / Evolutionary imitative dynamics with population-varying aspiration levels Sawa Ryoji JOURNAL OF ECONOMIC THEORY/154/pp.562-577, 2014-11 / Coalitional stochastic stability in games, networks and markets Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/88/pp.90-111, 2014-11 / Mutation rates and equilibrium selection under stochastic evolutionary dynamics Sawa Ryoji INTERNATIONAL JOURNAL OF GAME THEORY/41(3)/pp.489-496, 2012-08 / CG を用いたマシンの3 次元構造進化システム 澤 亮治 電気学会論文誌. C, 電子・情報・システム部門誌 = The transactions of the Institute of Electrical Engineers of Japan. C, A publication of Electronics, Information and System Society/121(2)/pp.461-467, 2001-02</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1027,6 +1029,8 @@
 行動経済学の知見を利用した進化ゲーム理論による均衡選択分析
 社会選択問題への進化ゲーム理論的アプローチ
 マルチタスク環境および協力ゲームにおける進化ゲーム理論の研究
+Pairwise Imitation and Tournament Graphs Hwang Sung-ha; Neary Philip R.; Newton Jonathan; Sawa ... INTERNATIONAL ECONOMIC REVIEW, 2026-02-04
+Conventions in large games with randomly drawn payoffs Newton Jonathan; Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/157/pp.50-70, 2026-03
 The evolution of collective choice under majority rules Okada Akira; Sawa Ryoji JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/225/pp.290-304, 2024-09
 Statistical inference in evolutionary dynamics Sawa Ryoji; Wu Jiabin GAMES AND ECONOMIC BEHAVIOR/137/pp.294-316, 2023-01
 研究室の選好と学生の成績を考慮した研究室配属法の分析 杉浦 有輝; 澤 亮治 情報処理学会論文誌/64(3)/pp.698-707, 2023-03
@@ -1259,7 +1263,8 @@
 数理計画
 オペレーションズ・リサーチ
 サービス工学
-Data Collaboration Analysis with Orthonormal Basis Selection and Alignment Nosaka Keiyu; Takano Yuichi; YOSHISE Akiko arXiv Preprint/pp.1-28, 2024-12
+Data collaboration analysis with orthonormal basis selection and alignment Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... Computers and Electrical Engineering/pp.1-28, 2026-06
+Data Collaboration Analysis with Orthonormal Basis Selection and Alignment (v6) Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... arXiv Preprint/pp.1-44, 2025-12
 Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning Nosaka Keiyu; Yoshise Akiko 2023 IEEE 3rd International Conference on Electronic Communications, Internet of Things and Big Data (ICEIB)/pp.180-185, 2023-07
 正循環制約を考慮したナーススケジューリング 本村力希; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.214-215, 2024-03
 Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices 野坂桂悠; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.50-51, 2024-03
@@ -1282,8 +1287,7 @@
 QAPの半正定値緩和問題を解くためのセンタリングADMM 加納 伸一; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.114-129, 2020-03
 SD基に基づく半正定値行列錐の凸多面錐近似 汪 玉柱; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.106-113, 2020-03
 ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― 高橋 直希; 高野 祐一; 吉瀬 章子 オペレーションズ・リサーチ/68(8)/pp.453-459, 2019-08
-Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Discussion Paper Series/1368, 2020-01
-Polyhedral approximations of the semidefinite cone and their application Yuzhu Wang; Akihiro Tanaka; 吉瀬 章子 Discussion Paper Series/1359, 2019-05</t>
+Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Discussion Paper Series/1368, 2020-01</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1303,7 +1307,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Data Collaboration Analysis with Orthonormal Basis Selection and Alignment Nosaka Keiyu; Takano Yuichi; YOSHISE Akiko arXiv Preprint/pp.1-28, 2024-12 / Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning Nosaka Keiyu; Yoshise Akiko 2023 IEEE 3rd International Conference on Electronic Communications, Internet of Things and Big Data (ICEIB)/pp.180-185, 2023-07 / 正循環制約を考慮したナーススケジューリング 本村力希; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.214-215, 2024-03 / Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices 野坂桂悠; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.50-51, 2024-03 / Post-Processing with Projection and Rescaling Algorithms for Semidefinite Programming Kanoh Shin-ichi; Yoshise Akiko arXiv preprint, 2024-01 / Riemannian Interior Point Methods for Constrained Optimization on Manifolds Lai Zhijian; Yoshise Akiko arXiv preprint, 2022-02 / A new extension of Chubanov's method to symmetric cones Kanoh Shin-ichi; Yoshise Akiko Mathematical Programming/205(1)/pp.773-812, 2024-05 / 射影- 再スケーリング法を用いた 対称錐計画問題に対する後処理アルゴリズム 加納伸一; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2023年春季研究発表会アブストラクト集/pp.12-13, 2023-03 / Riemannian Interior Point Methods for Constrained Optimization on Manifolds 頼志堅; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2023年春季研究発表会アブストラクト集/pp.10-11, 2023-03 / On the Global Convergence of Riemannian Interior Point Method 頼志堅; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2022年秋季研究発表会アブストラクト集/pp.194-195, 2022-09 / Completely positive factorization by a Riemannian smoothing method Lai Zhijian; Yoshise Akiko COMPUTATIONAL OPTIMIZATION AND APPLICATIONS/83(3)/pp.933-966, 2022-10 / Evaluating approximations of the semidefinite cone with trace normalized distance Yuzhu Wang; 吉瀬 章子 arXiv preprint, 2021-05 / Evaluating approximations of the semidefinite cone with trace normalized distance Yuzhu Wang; 吉瀬 章子 OPTIMIZATION LETTERS/Epub, 2022-07 / A New Extension of Chubanov's Method to Symmetric Cones Kanoh Shin-ichi; Yoshise Akiko arXiv preprint, 2021-10 / Riemannian Interior Point Methods for Constrained Optimization on Manifolds Lai Zhijian; Yoshise Akiko Journal of Optimization Theory and Applications/201(1)/pp.433-469, 2024-03 / Completely Positive Factorization in Orthogonality Optimization via Smoothing Method Lai Zhijian; Yoshise Akiko arXiv preprint, 2021-07 / Scenario-based CVaR Approach to Strategic Decision Support in One-way Station-based Carsharing Systems Kai Zhang; 高野祐一; 吉瀬 章子 SIAM News Blog, 2021-12 / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach Zhang Kai; Takano Yuichi; Wang Yuzhu; Yoshise Akiko IEEE Access/9/pp.79816-79828, 2021-06 / Polyhedral approximations of the semidefinite cone and their application Yuzhu Wang; Akihiro Tanaka; 吉瀬 章子 Computational Optimization and Applications/78/pp.893-913, 2021-01 / Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Peoceedings of NACA-ICOTA2019/1/pp.197-213, 2021-09 / QAPの半正定値緩和問題を解くためのセンタリングADMM 加納 伸一; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.114-129, 2020-03 / SD基に基づく半正定値行列錐の凸多面錐近似 汪 玉柱; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.106-113, 2020-03 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― 高橋 直希; 高野 祐一; 吉瀬 章子 オペレーションズ・リサーチ/68(8)/pp.453-459, 2019-08 / Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Discussion Paper Series/1368, 2020-01 / Polyhedral approximations of the semidefinite cone and their application Yuzhu Wang; Akihiro Tanaka; 吉瀬 章子 Discussion Paper Series/1359, 2019-05</t>
+          <t>Data collaboration analysis with orthonormal basis selection and alignment Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... Computers and Electrical Engineering/pp.1-28, 2026-06 / Data Collaboration Analysis with Orthonormal Basis Selection and Alignment (v6) Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... arXiv Preprint/pp.1-44, 2025-12 / Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning Nosaka Keiyu; Yoshise Akiko 2023 IEEE 3rd International Conference on Electronic Communications, Internet of Things and Big Data (ICEIB)/pp.180-185, 2023-07 / 正循環制約を考慮したナーススケジューリング 本村力希; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.214-215, 2024-03 / Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices 野坂桂悠; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.50-51, 2024-03 / Post-Processing with Projection and Rescaling Algorithms for Semidefinite Programming Kanoh Shin-ichi; Yoshise Akiko arXiv preprint, 2024-01 / Riemannian Interior Point Methods for Constrained Optimization on Manifolds Lai Zhijian; Yoshise Akiko arXiv preprint, 2022-02 / A new extension of Chubanov's method to symmetric cones Kanoh Shin-ichi; Yoshise Akiko Mathematical Programming/205(1)/pp.773-812, 2024-05 / 射影- 再スケーリング法を用いた 対称錐計画問題に対する後処理アルゴリズム 加納伸一; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2023年春季研究発表会アブストラクト集/pp.12-13, 2023-03 / Riemannian Interior Point Methods for Constrained Optimization on Manifolds 頼志堅; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2023年春季研究発表会アブストラクト集/pp.10-11, 2023-03 / On the Global Convergence of Riemannian Interior Point Method 頼志堅; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2022年秋季研究発表会アブストラクト集/pp.194-195, 2022-09 / Completely positive factorization by a Riemannian smoothing method Lai Zhijian; Yoshise Akiko COMPUTATIONAL OPTIMIZATION AND APPLICATIONS/83(3)/pp.933-966, 2022-10 / Evaluating approximations of the semidefinite cone with trace normalized distance Yuzhu Wang; 吉瀬 章子 arXiv preprint, 2021-05 / Evaluating approximations of the semidefinite cone with trace normalized distance Yuzhu Wang; 吉瀬 章子 OPTIMIZATION LETTERS/Epub, 2022-07 / A New Extension of Chubanov's Method to Symmetric Cones Kanoh Shin-ichi; Yoshise Akiko arXiv preprint, 2021-10 / Riemannian Interior Point Methods for Constrained Optimization on Manifolds Lai Zhijian; Yoshise Akiko Journal of Optimization Theory and Applications/201(1)/pp.433-469, 2024-03 / Completely Positive Factorization in Orthogonality Optimization via Smoothing Method Lai Zhijian; Yoshise Akiko arXiv preprint, 2021-07 / Scenario-based CVaR Approach to Strategic Decision Support in One-way Station-based Carsharing Systems Kai Zhang; 高野祐一; 吉瀬 章子 SIAM News Blog, 2021-12 / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach Zhang Kai; Takano Yuichi; Wang Yuzhu; Yoshise Akiko IEEE Access/9/pp.79816-79828, 2021-06 / Polyhedral approximations of the semidefinite cone and their application Yuzhu Wang; Akihiro Tanaka; 吉瀬 章子 Computational Optimization and Applications/78/pp.893-913, 2021-01 / Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Peoceedings of NACA-ICOTA2019/1/pp.197-213, 2021-09 / QAPの半正定値緩和問題を解くためのセンタリングADMM 加納 伸一; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.114-129, 2020-03 / SD基に基づく半正定値行列錐の凸多面錐近似 汪 玉柱; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.106-113, 2020-03 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― 高橋 直希; 高野 祐一; 吉瀬 章子 オペレーションズ・リサーチ/68(8)/pp.453-459, 2019-08 / Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Discussion Paper Series/1368, 2020-01</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1376,7 +1380,8 @@
 地域未来創生共同研究講座
 次世代社会システムとモビリティの新価値研究
 購買データに基づく顧客行動分析
-Data Collaboration Analysis with Orthonormal Basis Selection and Alignment Nosaka Keiyu; Takano Yuichi; YOSHISE Akiko arXiv Preprint/pp.1-28, 2024-12
+Data collaboration analysis with orthonormal basis selection and alignment Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... Computers and Electrical Engineering/pp.1-28, 2026-06
+Data Collaboration Analysis with Orthonormal Basis Selection and Alignment (v6) Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... arXiv Preprint/pp.1-44, 2025-12
 Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning Nosaka Keiyu; Yoshise Akiko 2023 IEEE 3rd International Conference on Electronic Communications, Internet of Things and Big Data (ICEIB)/pp.180-185, 2023-07
 正循環制約を考慮したナーススケジューリング 本村力希; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.214-215, 2024-03
 Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices 野坂桂悠; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.50-51, 2024-03
@@ -1399,8 +1404,7 @@
 QAPの半正定値緩和問題を解くためのセンタリングADMM 加納 伸一; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.114-129, 2020-03
 SD基に基づく半正定値行列錐の凸多面錐近似 汪 玉柱; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.106-113, 2020-03
 ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― 高橋 直希; 高野 祐一; 吉瀬 章子 オペレーションズ・リサーチ/68(8)/pp.453-459, 2019-08
-Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Discussion Paper Series/1368, 2020-01
-Polyhedral approximations of the semidefinite cone and their application Yuzhu Wang; Akihiro Tanaka; 吉瀬 章子 Discussion Paper Series/1359, 2019-05</t>
+Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Discussion Paper Series/1368, 2020-01</t>
         </is>
       </c>
     </row>
@@ -1451,6 +1455,12 @@
 ソフトコンピューティング
 データマイニング
 多次元データ解析
+Reliability of clustering methods-based uncertainty SATO-ILIC Mika 65th ISI World Statistics Congress, 2025-10
+混合データを用いたファジィクラスタリングに基づくハイブリッド識別法 山本薫; イリチュ 美佳 2025年度日本分類学会シンポジウム予稿集/pp.1-4, 2025-12
+Fuzzy clustering-based weighted principal component analysis for mixed data SATO-ILIC Mika IEEE International Conference on Fuzzy Systems, 2025-07
+Dimensionality Reduction Method for Fuzzy Interval Data Using Deep Learning SUGIURA Gakuei; SATO-ILIC Mika Procedia Computer Science, Elsevier/270/pp.2247-2256, 2025-09
+収支項目分類符号に対する効率的な自動格付に関する研究 床 裕佳子; イリチュ 美佳 リサーチペーパー第 63 号/pp.1-26, 2025-06
+Explainable dimensionality reduction for mixed data considering uncertainty of dynamic classification boundaries (accepted) SATO-ILIC Mika Procedia Computer Science, Elsevier, 2026-03
 Simultaneous visualization method for mixed HDLSS data and its application for education SATO-ILIC Mika; ILIC Peter Procedia Computer Science/246/pp.5036-5045, 2024-09
 Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design ILIC Peter; SATO-ILIC Mika Smart Innovation, Systems and Technologies/399/pp.141-150, 2024-06
 Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey TOKO Yukako; SATO-ILIC Mika Procedia Computer Science/246/pp.1820-1829, 2024-09
@@ -1469,13 +1479,7 @@
 Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results Toko Yukako; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.43-44, 2022-12
 Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling Takamura Shojiro; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.45-46, 2022-12
 Cluster-based Analysis for Discrimination of Individuality （招待講演） Sato-Ilic Mika Global Summit and Expo on Robot Intelligence Technology and Applications2022, 2022/09/19
-クラスター尺度に基づくデータ間差異の検出と市場データへの応用 本多 拓朗; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.788-790, 2022-09
-ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 加藤 優友; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.431-434, 2022-09
-Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data Sato-Ilic Mika The 24th International Conference on Computational Statistics, 2022-08-23
-Clustering and Multidimensional Scaling for Individual Difference Extraction Sato-Ilic Mika The 4th International Conference on Statistics: Theory and Applications/pp.162-1-162-8, 2022-07
-多次元尺度法による計算効率を考慮したディープラーニング手法 高村 昇二郎; イリチユ 美佳 ⽇本分類学会第41回⼤会予稿集/pp.54-57, 2022-06
-Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means Yukako Toko; Sato-Ilic Mika ROMANIAN STATISTICAL REVIEW/1/pp.27-39, 2022-03
-区間組成データに対する重み付き回帰分析 藤本 聖; イリチユ 美佳 日本分類学会シンポジウム予稿集/pp.19, 1-19, 4, 2021-12</t>
+クラスター尺度に基づくデータ間差異の検出と市場データへの応用 本多 拓朗; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.788-790, 2022-09</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1495,7 +1499,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Simultaneous visualization method for mixed HDLSS data and its application for education SATO-ILIC Mika; ILIC Peter Procedia Computer Science/246/pp.5036-5045, 2024-09 / Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design ILIC Peter; SATO-ILIC Mika Smart Innovation, Systems and Technologies/399/pp.141-150, 2024-06 / Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey TOKO Yukako; SATO-ILIC Mika Procedia Computer Science/246/pp.1820-1829, 2024-09 / Difference on Evaluation Scores Considering Image Descriptions for Autocoding Toko Yukako; Sato-Ilic Mika ROMANIAN STATISTICAL REVIEW/1/pp.27-42, 2024 / ファジィクラスタリングの信頼度について イリチュ 美佳 本分類学会第４３回大会予稿集/pp.45-48, 2024-06 / Hierarchical Support Vector Machine based Classifier for Autocoding Toko Yukako; Sato-Ilic Mika Procedia Computer Science, Elsevier/225/pp.2733-2742, 2023-09 / Fuzzy Cluster-Scaled Principal Component Analysis for Mixed Data and Its Application of Educational Effect based on Device Selection Sato-Ilic Mika; Ilic Peter Procedia Computer Science, Elsevier/225/pp.2402-2411, 2023-09 / A Fuzzy Cluster-Scaled Principal Component Analysis for Mixed High-Dimension and Low-Sample Size Data SATO-ILIC Mika 25th International Conference on Computational Statistics, 2023 / Principal component analysis for mixed high-dimension low-sample size data based on fuzzy-cluster scale SATO-ILIC Mika 16th International Conference of the ERCIM WG on Computational and Methodological Statistics and 17th International Conference on Computational and Financial Econometrics, 2023 / Improvement of Training Data for Autocoding on "The National Survey of Family Income, Consumption and Wealth" and "The Family Income and Expenditure Survey" Toko Yukako; Sato-Ilic Mika 日本分類学会第42回大会予稿集/pp.49-52, 2023 / Fuzzy Clustering based Autocoding Methods for Family Income and Expenditure Surveys Toko Yukako; Sato-Ilic Mika Conference on New Techniques and Technologies for Official Statistics/pp.404-408, 2023 / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding Toko Yukako; Sato-Ilic Mika; Takayuki Sasajima ROMANIAN STATISTICAL REVIEW/1(1)/pp.34-48, 2023 / Fuzzy Clustering based Classifier for Extraction of Individualities from High Dimension Low Sample Size Data Sato-Ilic Mika INTELLIGENT DECISION TECHNOLOGIES-NETHERLANDS/17(1)/pp.127-138, 2023 / Individuality-based Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data Sato-Ilic Mika 15th International Conference of the ERCIM WG on Computational and Methodological Statistics and 16th International Conference on Computational and Financial Econometrics, 2022-12-17 / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding Toko Yukako; Sato-Ilic Mika The Annual Conference on the Use of R in Official Statistics (10th International Conference: uRos2022), 2022-12-06 / Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results Toko Yukako; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.43-44, 2022-12 / Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling Takamura Shojiro; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.45-46, 2022-12 / Cluster-based Analysis for Discrimination of Individuality （招待講演） Sato-Ilic Mika Global Summit and Expo on Robot Intelligence Technology and Applications2022, 2022/09/19 / クラスター尺度に基づくデータ間差異の検出と市場データへの応用 本多 拓朗; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.788-790, 2022-09 / ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 加藤 優友; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.431-434, 2022-09 / Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data Sato-Ilic Mika The 24th International Conference on Computational Statistics, 2022-08-23 / Clustering and Multidimensional Scaling for Individual Difference Extraction Sato-Ilic Mika The 4th International Conference on Statistics: Theory and Applications/pp.162-1-162-8, 2022-07 / 多次元尺度法による計算効率を考慮したディープラーニング手法 高村 昇二郎; イリチユ 美佳 ⽇本分類学会第41回⼤会予稿集/pp.54-57, 2022-06 / Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means Yukako Toko; Sato-Ilic Mika ROMANIAN STATISTICAL REVIEW/1/pp.27-39, 2022-03 / 区間組成データに対する重み付き回帰分析 藤本 聖; イリチユ 美佳 日本分類学会シンポジウム予稿集/pp.19, 1-19, 4, 2021-12</t>
+          <t>Reliability of clustering methods-based uncertainty SATO-ILIC Mika 65th ISI World Statistics Congress, 2025-10 / 混合データを用いたファジィクラスタリングに基づくハイブリッド識別法 山本薫; イリチュ 美佳 2025年度日本分類学会シンポジウム予稿集/pp.1-4, 2025-12 / Fuzzy clustering-based weighted principal component analysis for mixed data SATO-ILIC Mika IEEE International Conference on Fuzzy Systems, 2025-07 / Dimensionality Reduction Method for Fuzzy Interval Data Using Deep Learning SUGIURA Gakuei; SATO-ILIC Mika Procedia Computer Science, Elsevier/270/pp.2247-2256, 2025-09 / 収支項目分類符号に対する効率的な自動格付に関する研究 床 裕佳子; イリチュ 美佳 リサーチペーパー第 63 号/pp.1-26, 2025-06 / Explainable dimensionality reduction for mixed data considering uncertainty of dynamic classification boundaries (accepted) SATO-ILIC Mika Procedia Computer Science, Elsevier, 2026-03 / Simultaneous visualization method for mixed HDLSS data and its application for education SATO-ILIC Mika; ILIC Peter Procedia Computer Science/246/pp.5036-5045, 2024-09 / Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design ILIC Peter; SATO-ILIC Mika Smart Innovation, Systems and Technologies/399/pp.141-150, 2024-06 / Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey TOKO Yukako; SATO-ILIC Mika Procedia Computer Science/246/pp.1820-1829, 2024-09 / Difference on Evaluation Scores Considering Image Descriptions for Autocoding Toko Yukako; Sato-Ilic Mika ROMANIAN STATISTICAL REVIEW/1/pp.27-42, 2024 / ファジィクラスタリングの信頼度について イリチュ 美佳 本分類学会第４３回大会予稿集/pp.45-48, 2024-06 / Hierarchical Support Vector Machine based Classifier for Autocoding Toko Yukako; Sato-Ilic Mika Procedia Computer Science, Elsevier/225/pp.2733-2742, 2023-09 / Fuzzy Cluster-Scaled Principal Component Analysis for Mixed Data and Its Application of Educational Effect based on Device Selection Sato-Ilic Mika; Ilic Peter Procedia Computer Science, Elsevier/225/pp.2402-2411, 2023-09 / A Fuzzy Cluster-Scaled Principal Component Analysis for Mixed High-Dimension and Low-Sample Size Data SATO-ILIC Mika 25th International Conference on Computational Statistics, 2023 / Principal component analysis for mixed high-dimension low-sample size data based on fuzzy-cluster scale SATO-ILIC Mika 16th International Conference of the ERCIM WG on Computational and Methodological Statistics and 17th International Conference on Computational and Financial Econometrics, 2023 / Improvement of Training Data for Autocoding on "The National Survey of Family Income, Consumption and Wealth" and "The Family Income and Expenditure Survey" Toko Yukako; Sato-Ilic Mika 日本分類学会第42回大会予稿集/pp.49-52, 2023 / Fuzzy Clustering based Autocoding Methods for Family Income and Expenditure Surveys Toko Yukako; Sato-Ilic Mika Conference on New Techniques and Technologies for Official Statistics/pp.404-408, 2023 / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding Toko Yukako; Sato-Ilic Mika; Takayuki Sasajima ROMANIAN STATISTICAL REVIEW/1(1)/pp.34-48, 2023 / Fuzzy Clustering based Classifier for Extraction of Individualities from High Dimension Low Sample Size Data Sato-Ilic Mika INTELLIGENT DECISION TECHNOLOGIES-NETHERLANDS/17(1)/pp.127-138, 2023 / Individuality-based Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data Sato-Ilic Mika 15th International Conference of the ERCIM WG on Computational and Methodological Statistics and 16th International Conference on Computational and Financial Econometrics, 2022-12-17 / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding Toko Yukako; Sato-Ilic Mika The Annual Conference on the Use of R in Official Statistics (10th International Conference: uRos2022), 2022-12-06 / Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results Toko Yukako; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.43-44, 2022-12 / Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling Takamura Shojiro; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.45-46, 2022-12 / Cluster-based Analysis for Discrimination of Individuality （招待講演） Sato-Ilic Mika Global Summit and Expo on Robot Intelligence Technology and Applications2022, 2022/09/19 / クラスター尺度に基づくデータ間差異の検出と市場データへの応用 本多 拓朗; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.788-790, 2022-09</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1561,6 +1565,12 @@
 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学
 高次元データの理論と方法論の総合的研究
 高次Aggregation Operatorの開発とクラスタリングモデルへの適用
+Reliability of clustering methods-based uncertainty SATO-ILIC Mika 65th ISI World Statistics Congress, 2025-10
+混合データを用いたファジィクラスタリングに基づくハイブリッド識別法 山本薫; イリチュ 美佳 2025年度日本分類学会シンポジウム予稿集/pp.1-4, 2025-12
+Fuzzy clustering-based weighted principal component analysis for mixed data SATO-ILIC Mika IEEE International Conference on Fuzzy Systems, 2025-07
+Dimensionality Reduction Method for Fuzzy Interval Data Using Deep Learning SUGIURA Gakuei; SATO-ILIC Mika Procedia Computer Science, Elsevier/270/pp.2247-2256, 2025-09
+収支項目分類符号に対する効率的な自動格付に関する研究 床 裕佳子; イリチュ 美佳 リサーチペーパー第 63 号/pp.1-26, 2025-06
+Explainable dimensionality reduction for mixed data considering uncertainty of dynamic classification boundaries (accepted) SATO-ILIC Mika Procedia Computer Science, Elsevier, 2026-03
 Simultaneous visualization method for mixed HDLSS data and its application for education SATO-ILIC Mika; ILIC Peter Procedia Computer Science/246/pp.5036-5045, 2024-09
 Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design ILIC Peter; SATO-ILIC Mika Smart Innovation, Systems and Technologies/399/pp.141-150, 2024-06
 Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey TOKO Yukako; SATO-ILIC Mika Procedia Computer Science/246/pp.1820-1829, 2024-09
@@ -1579,13 +1589,7 @@
 Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results Toko Yukako; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.43-44, 2022-12
 Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling Takamura Shojiro; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.45-46, 2022-12
 Cluster-based Analysis for Discrimination of Individuality （招待講演） Sato-Ilic Mika Global Summit and Expo on Robot Intelligence Technology and Applications2022, 2022/09/19
-クラスター尺度に基づくデータ間差異の検出と市場データへの応用 本多 拓朗; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.788-790, 2022-09
-ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 加藤 優友; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.431-434, 2022-09
-Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data Sato-Ilic Mika The 24th International Conference on Computational Statistics, 2022-08-23
-Clustering and Multidimensional Scaling for Individual Difference Extraction Sato-Ilic Mika The 4th International Conference on Statistics: Theory and Applications/pp.162-1-162-8, 2022-07
-多次元尺度法による計算効率を考慮したディープラーニング手法 高村 昇二郎; イリチユ 美佳 ⽇本分類学会第41回⼤会予稿集/pp.54-57, 2022-06
-Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means Yukako Toko; Sato-Ilic Mika ROMANIAN STATISTICAL REVIEW/1/pp.27-39, 2022-03
-区間組成データに対する重み付き回帰分析 藤本 聖; イリチユ 美佳 日本分類学会シンポジウム予稿集/pp.19, 1-19, 4, 2021-12</t>
+クラスター尺度に基づくデータ間差異の検出と市場データへの応用 本多 拓朗; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.788-790, 2022-09</t>
         </is>
       </c>
     </row>
@@ -1640,6 +1644,8 @@
 計算社会科学
 ウェブサイエンス
 ビッグデータ
+Linking Opinion Dynamics and Emotional Expression in Online Communities: a Case Study of Covid-19 Vaccination Discourse in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako The 10th International Workshop on Application of Big Data for Computational Social Science (ABCSS2025)/pp.5876-5883, 2025-12-09
+SNSにおける日本の高齢運転者に対する言論の定量化 佐野幸恵; 中西映人; 吉田光男; 市川政雄 情報処理学会 第88回全国大会, 2026-03
 Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-04-01
 コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 呉 潜雲; 佐野 幸恵; 高安 秀樹; Havlin Shlomo; 高安 美佐子 人工知能学会全国大会論文集/JSAI2024/pp.2I4OS1b05-2I4OS1b05, 2024-05-28
 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19
@@ -1662,9 +1668,7 @@
 サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して 浅野 翔; 雨宮 護; 佐野 幸恵 オペレーションズリサーチ/66(4)/pp.240(44)-245(49), 2021-04
 Fake news propagates differently from real news even at early stages of spreading Zhao Zilong; Zhao Jichang; Sano Yukie; Levy Orr; Takayasu... EPJ Data Science/9/p.7, 2020-04
 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii
-Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository
-Correlations and fluctuations in the word sets of collective emotions Sano Yukie Nonlinear Theory and Its Applications, IEICE/9(3)/pp.382-390, 2018-07 CiNii Tsukuba Repository
-Configuration model for correlation matrices preserving the node strength Masuda Naoki; Kojaku Sadamori; Sano Yukie Physical Review E/98(1)/p.012312, 2018-07 PubMed</t>
+Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1684,7 +1688,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-04-01 / コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 呉 潜雲; 佐野 幸恵; 高安 秀樹; Havlin Shlomo; 高安 美佐子 人工知能学会全国大会論文集/JSAI2024/pp.2I4OS1b05-2I4OS1b05, 2024-05-28 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19 / Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Havlin Shlom... Scientific Reports/15(1)/p.11716, 2025-04 / Quantifying Collective Emotions: Japan’s Societal Trends Through Enhanced Sentiment Index Using POMS2 and SNS TAMURA Koutarou; SANO Yukie; SHIOZAKI Junichi 2024 IEEE International Conference on Big Data (BigData)/pp.3082-3087, 2024-12 / Quantifying collective attention and fan engagement: a case study of the Japanese professional baseball league Otomo Naofumi; Sasahara Kazutoshi; Mizuno Makoto; Sano... Journal of Computational Social Science/8(2), 2025-03 / News coverage of older drivers' fatal car crashes: is it over-represented? Ichikawa Masao; Tanaka Rie; Nakanishi Akito; Sano Yukie JOURNAL OF EPIDEMIOLOGY/Epub, 2024-10-26 / Burstiness of human physical activities and their characterisation Takeuchi Makoto; Sano Yukie Journal of Computational Social Science/7/pp.625-641, 2024-03 / 12-year observation of tweets about rubella in Japan: A retrospective infodemiology study Sano Yukie; Hori Ai PLOS ONE/18(5)/p.e0285101, 2023-05 PubMed / A two-phase model of collective memory decay with a dynamical switching point Igarashi Naoki; Okada Yukihiko; Sayama Hiroki; Sano Y... SCIENTIFIC REPORTS/12(1), 2022-12 / SNSデータを用いた情報拡散シミュレーション 佐野 幸恵; 鳥居 寛之 シミュレーション = Journal of the Japan Society for Simulation Technology / 日本シミュレーション学会 編/40(3)/pp.137-143, 2021-09 CiNii / SNSにおける情報伝播ネットワークの構造 佐野 幸恵; 高安 秀樹; 高安 美佐子 日本物理学会誌/77(7)/pp.458-463, 2022-07-05 / Music Roles Affect the Selection of Consumption Means: A Questionnaire Survey of People’s Expectations for Music and Exploratory Factor Analysis Takeuchi Makoto; Morishita Soichiro; Sano Yukie REVIEW OF SOCIONETWORK STRATEGIES/16(2:SI)/pp.453-464, 2022-09 / Dataset of identified scholars mentioned in acknowledgement statements Kusumegi Keigo; Sano Yukie Scientific data/9(1)/p.461, 2022-08 / Classification of endogenous and exogenous bursts in collective emotions based on Weibo comments during COVID-19 Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako Scientific Reports/12(1)/p.3120, 2022-02 / 日本におけるオンライン・ハラスメントの現状と対策：Twitterでの女性記者のツイート「炎上」を例に 礪波 亜希; 吉田 光男; 佐野 幸恵 F1000Research/10, 2022-02 / 日本における自治体報道発表のCOVID-19発生状況を用いた感染者遷移状況の記録と可視化 渡辺 知恵美; 佐野 幸恵; 岡田幸彦; 天笠 俊之 研究報告ドキュメントコミュニケーション（DC）/2020-DC-117(4)/pp.1-7, 2020-07 / Simulation of information spreading on Twitter concerning radiation after the Fukushima nuclear power plant accident Sano Yukie; Torii Hiroyuki A; Onoue Yosuke; Uno Kazuko Frontiers in Physics/9, 2021-06 / 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― 水野 誠; 佐野 幸恵; 笹原 和俊 マーケティングジャーナル/40(4)/pp.6-18, 2021 CiNii / サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して 浅野 翔; 雨宮 護; 佐野 幸恵 オペレーションズリサーチ/66(4)/pp.240(44)-245(49), 2021-04 / Fake news propagates differently from real news even at early stages of spreading Zhao Zilong; Zhao Jichang; Sano Yukie; Levy Orr; Takayasu... EPJ Data Science/9/p.7, 2020-04 / 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii / Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository / Correlations and fluctuations in the word sets of collective emotions Sano Yukie Nonlinear Theory and Its Applications, IEICE/9(3)/pp.382-390, 2018-07 CiNii Tsukuba Repository / Configuration model for correlation matrices preserving the node strength Masuda Naoki; Kojaku Sadamori; Sano Yukie Physical Review E/98(1)/p.012312, 2018-07 PubMed</t>
+          <t>Linking Opinion Dynamics and Emotional Expression in Online Communities: a Case Study of Covid-19 Vaccination Discourse in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako The 10th International Workshop on Application of Big Data for Computational Social Science (ABCSS2025)/pp.5876-5883, 2025-12-09 / SNSにおける日本の高齢運転者に対する言論の定量化 佐野幸恵; 中西映人; 吉田光男; 市川政雄 情報処理学会 第88回全国大会, 2026-03 / Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-04-01 / コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 呉 潜雲; 佐野 幸恵; 高安 秀樹; Havlin Shlomo; 高安 美佐子 人工知能学会全国大会論文集/JSAI2024/pp.2I4OS1b05-2I4OS1b05, 2024-05-28 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19 / Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Havlin Shlom... Scientific Reports/15(1)/p.11716, 2025-04 / Quantifying Collective Emotions: Japan’s Societal Trends Through Enhanced Sentiment Index Using POMS2 and SNS TAMURA Koutarou; SANO Yukie; SHIOZAKI Junichi 2024 IEEE International Conference on Big Data (BigData)/pp.3082-3087, 2024-12 / Quantifying collective attention and fan engagement: a case study of the Japanese professional baseball league Otomo Naofumi; Sasahara Kazutoshi; Mizuno Makoto; Sano... Journal of Computational Social Science/8(2), 2025-03 / News coverage of older drivers' fatal car crashes: is it over-represented? Ichikawa Masao; Tanaka Rie; Nakanishi Akito; Sano Yukie JOURNAL OF EPIDEMIOLOGY/Epub, 2024-10-26 / Burstiness of human physical activities and their characterisation Takeuchi Makoto; Sano Yukie Journal of Computational Social Science/7/pp.625-641, 2024-03 / 12-year observation of tweets about rubella in Japan: A retrospective infodemiology study Sano Yukie; Hori Ai PLOS ONE/18(5)/p.e0285101, 2023-05 PubMed / A two-phase model of collective memory decay with a dynamical switching point Igarashi Naoki; Okada Yukihiko; Sayama Hiroki; Sano Y... SCIENTIFIC REPORTS/12(1), 2022-12 / SNSデータを用いた情報拡散シミュレーション 佐野 幸恵; 鳥居 寛之 シミュレーション = Journal of the Japan Society for Simulation Technology / 日本シミュレーション学会 編/40(3)/pp.137-143, 2021-09 CiNii / SNSにおける情報伝播ネットワークの構造 佐野 幸恵; 高安 秀樹; 高安 美佐子 日本物理学会誌/77(7)/pp.458-463, 2022-07-05 / Music Roles Affect the Selection of Consumption Means: A Questionnaire Survey of People’s Expectations for Music and Exploratory Factor Analysis Takeuchi Makoto; Morishita Soichiro; Sano Yukie REVIEW OF SOCIONETWORK STRATEGIES/16(2:SI)/pp.453-464, 2022-09 / Dataset of identified scholars mentioned in acknowledgement statements Kusumegi Keigo; Sano Yukie Scientific data/9(1)/p.461, 2022-08 / Classification of endogenous and exogenous bursts in collective emotions based on Weibo comments during COVID-19 Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako Scientific Reports/12(1)/p.3120, 2022-02 / 日本におけるオンライン・ハラスメントの現状と対策：Twitterでの女性記者のツイート「炎上」を例に 礪波 亜希; 吉田 光男; 佐野 幸恵 F1000Research/10, 2022-02 / 日本における自治体報道発表のCOVID-19発生状況を用いた感染者遷移状況の記録と可視化 渡辺 知恵美; 佐野 幸恵; 岡田幸彦; 天笠 俊之 研究報告ドキュメントコミュニケーション（DC）/2020-DC-117(4)/pp.1-7, 2020-07 / Simulation of information spreading on Twitter concerning radiation after the Fukushima nuclear power plant accident Sano Yukie; Torii Hiroyuki A; Onoue Yosuke; Uno Kazuko Frontiers in Physics/9, 2021-06 / 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― 水野 誠; 佐野 幸恵; 笹原 和俊 マーケティングジャーナル/40(4)/pp.6-18, 2021 CiNii / サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して 浅野 翔; 雨宮 護; 佐野 幸恵 オペレーションズリサーチ/66(4)/pp.240(44)-245(49), 2021-04 / Fake news propagates differently from real news even at early stages of spreading Zhao Zilong; Zhao Jichang; Sano Yukie; Levy Orr; Takayasu... EPJ Data Science/9/p.7, 2020-04 / 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii / Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1777,6 +1781,8 @@
 乳幼児の活動量を測定するウェアラブル機器の開発
 乳幼児の活動量を測定するウェアラブルデバイスの開発
 サイバー社会ネットワークにおける噂の伝播の検出と制御
+Linking Opinion Dynamics and Emotional Expression in Online Communities: a Case Study of Covid-19 Vaccination Discourse in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako The 10th International Workshop on Application of Big Data for Computational Social Science (ABCSS2025)/pp.5876-5883, 2025-12-09
+SNSにおける日本の高齢運転者に対する言論の定量化 佐野幸恵; 中西映人; 吉田光男; 市川政雄 情報処理学会 第88回全国大会, 2026-03
 Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-04-01
 コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 呉 潜雲; 佐野 幸恵; 高安 秀樹; Havlin Shlomo; 高安 美佐子 人工知能学会全国大会論文集/JSAI2024/pp.2I4OS1b05-2I4OS1b05, 2024-05-28
 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19
@@ -1799,9 +1805,7 @@
 サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して 浅野 翔; 雨宮 護; 佐野 幸恵 オペレーションズリサーチ/66(4)/pp.240(44)-245(49), 2021-04
 Fake news propagates differently from real news even at early stages of spreading Zhao Zilong; Zhao Jichang; Sano Yukie; Levy Orr; Takayasu... EPJ Data Science/9/p.7, 2020-04
 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii
-Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository
-Correlations and fluctuations in the word sets of collective emotions Sano Yukie Nonlinear Theory and Its Applications, IEICE/9(3)/pp.382-390, 2018-07 CiNii Tsukuba Repository
-Configuration model for correlation matrices preserving the node strength Masuda Naoki; Kojaku Sadamori; Sano Yukie Physical Review E/98(1)/p.012312, 2018-07 PubMed</t>
+Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository</t>
         </is>
       </c>
     </row>
@@ -1999,7 +2003,13 @@
 数理最適化
 金融工学
 機械学習
+Data collaboration analysis with orthonormal basis selection and alignment Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... Computers and Electrical Engineering/pp.1-28, 2026-06
+Mean–variance portfolio optimization with shrinkage estimation for recommender systems YANAGI Tomoya; YASUMOTO Yuta; TAKANO Yuichi Proceedings of the 15th International Conference on Operations Research and Enterprise Systems (ICORES 2026)/pp.265-272, 2026-03
+最適多分木による解釈可能な市場細分化 深谷 悠人; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 菊池 明飛; 武井 柊悟; 竹内 崇貴; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/71(2)/pp.61-69, 2026-02
+New solutions based on the generalized eigenvalue problem for the data collaboration analysis Kawakami Yuta; Takano Yuichi; Imakura Akira INFORMATION SCIENCES/723, 2026-01
+Subset Selection for Stratified Sampling in Online Controlled Experiments MOMOZU Haru; UEHARA Yuki; NISHIMURA Naoki; OHASHI Koy... Proceedings of the 22nd Pacific Rim International Conference on Artificial Intelligence (PRICAI 2025)/(Part II)/pp.600-613, 2025-11
 Robust personalized pricing under uncertainty of purchase probabilities Ikeda Shunnosuke; Nishimura Naoki; Sukegawa Noriyoshi; ... EURO Journal on Computational Optimization/13, 2025-08
+Missing Value Imputation via Mathematical Optimization with Instance-and-feature Neighborhoods Kawakami Yuta; Matsumoto Takumi; Takano Yuichi Journal of Information Processing/33(0)/pp.410-418, 2025
 Privacy-preserving recommender system using the data collaboration analysis for distributed datasets Yanagi Tomoya; Ikeda Shunnosuke; Sukegawa Noriyoshi; T... PLoS ONE/20(4), 2025-04
 最適モデル多分木による価格需要曲線の推定 菊池 明飛; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 武井 柊悟; 竹内 崇貴; 深谷 悠人; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/70(2)/pp.61-68, 2025-02
 Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times Ikuma Daiki; Ikeda Shunnosuke; Sukegawa Noriyoshi; Tak... Journal of Japan Industrial Management Association/75(4E)/pp.172-182, 2025-01
@@ -2018,12 +2028,6 @@
 Branch-and-bound algorithm for optimal sparse canonical correlation analysis Watanabe Akihisa; Tamura Ryuta; Takano Yuichi; Miyashi... EXPERT SYSTEMS WITH APPLICATIONS/217, 2023-05
 Dynamic portfolio selection with linear control policies for coherent risk minimization Takano Yuichi; Gotoh Jun-ya OPERATIONS RESEARCH PERSPECTIVES/10, 2023
 Linear control policies for online vehicle relocation in shared mobility systems Yoshida Yasuhiro; Takano Yuichi EXPERT SYSTEMS WITH APPLICATIONS/210, 2022-12
-出産前後の情報検索の分析：数理最適化による検索日の確率分布推定 岩永 二郎; 西村 直樹; 鮏川 矩義; 高野 祐一 人工知能学会論文誌/37(3)/pp.D-L74_1-11, 2022-05-01
-ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析) 河上 佳太; 工藤 晃太; 川瀬 元暉; 最首 大輝; 山田 直輝; 吉田 晏大; 岩永 二郎; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/67(2)/pp.73-80, 2022-02 CiNii
-Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization Kobayashi Ken; Takano Yuichi; Nakata Kazuhide JOURNAL OF GLOBAL OPTIMIZATION/81(2)/pp.493-528, 2021-10
-Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach Zhang Kai; Takano Yuichi; Wang Yuzhu; Yoshise Akiko IEEE Access/9/pp.79816-79828, 2021-06
-Sparse Poisson regression via mixed-integer optimization Saishu Hiroki; Kudo Kota; Takano Yuichi PloS one/16(4), 2021-04 PubMed
-時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析 河上 佳太; 西村 直樹; 白鳥 友風; 工藤 晃太; 松岡 雄大; 最首 大輝; 渡邊 彰久; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/66(4)/pp.246-254, 2021-04 CiNii
 データコラボレーション解析における統合関数の最適化 川上 雄大; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(6)/pp.297-302, 2024-06
 A Design Method of the Joint Venture Formation in EPC Projects Ishi Nobuaki; Takano Yuichi; Muraki Masaaki Intelligent Engineering and Management for Industry 4.0/pp.137-146, 2022-06
 形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待) 西村 直樹; 鮏川 矩義; 高野 祐一; 岩永 二郎 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/65(6)/pp.328-333, 2020-06 CiNii
@@ -2068,7 +2072,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Robust personalized pricing under uncertainty of purchase probabilities Ikeda Shunnosuke; Nishimura Naoki; Sukegawa Noriyoshi; ... EURO Journal on Computational Optimization/13, 2025-08 / Privacy-preserving recommender system using the data collaboration analysis for distributed datasets Yanagi Tomoya; Ikeda Shunnosuke; Sukegawa Noriyoshi; T... PLoS ONE/20(4), 2025-04 / 最適モデル多分木による価格需要曲線の推定 菊池 明飛; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 武井 柊悟; 竹内 崇貴; 深谷 悠人; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/70(2)/pp.61-68, 2025-02 / Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times Ikuma Daiki; Ikeda Shunnosuke; Sukegawa Noriyoshi; Tak... Journal of Japan Industrial Management Association/75(4E)/pp.172-182, 2025-01 / DC algorithm for estimation of sparse Gaussian graphical models Shiratori Tomokaze; Takano Yuichi PLOS ONE/19(12), 2024-12-23 / Robust Portfolio Optimization for Recommender Systems Considering Uncertainty of Estimated Statistics Yanagi Tomoya; Ikeda Shunnosuke; Takano Yuichi Proceedings of Pacific rim international conference on artificial intelligence/pp.429-440, 2024-11 / Fast Solution to the Fair Ranking Problem Using the Sinkhorn Algorithm Uehara Yuki; Ikeda Shunnosuke; Nishimura Naoki; Ohashi... Proceedings of Pacific rim international conference on artificial intelligence/pp.207-215, 2024-11 / Mixed-Integer Linear Optimization Formulations for Feature Subset Selection in Kernel SVM Classification Tamura Ryuta; Takano Yuichi; Miyashiro Ryuhei IEICE TRANSACTIONS ON FUNDAMENTALS OF ELECTRONICS COMMUNICATIONS AND COMPUTER SCIENCES/E107A(8)/pp.1151-1162, 2024-08 / Robust portfolio optimization model for electronic coupon allocation Uehara Yuki; Nishimura Naoki; Li Yilin; Yang Jie; Job... INFOR/Epub, 2024-07-29 / 混合整数最適化による相続工程の長期化リスク採点システム 椎名 萌; 高野 祐一; 宇佐美 朋香; 山西 康孝; 藤巻 米隆 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(4)/pp.219-224, 2024-04 / ECサイトにおける利用者属性データの欠損値補完 川上 雄大; 奈良岡 勇; 松本 拓見; 安元 優太; 朝倉 希美; 椎名 萌; 守屋 恵瑠萌; 鮏... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(2)/pp.82-88, 2024-02 / Prescriptive price optimization using optimal regression trees Ikeda Shunnosuke; Nishimura Naoki; Sukegawa Noriyoshi; ... OPERATIONS RESEARCH PERSPECTIVES/11, 2023-12 / 構造的正則化処方分析による旅行パックの価格最適化 池田 春之介; 朝倉 希美; 西村 直樹; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/68(9)/pp.485-490, 2023-09 / Predicting Online Item-Choice Behavior: A Shape-Restricted Regression Approach Nishimura Naoki; Sukegawa Noriyoshi; Takano Yuichi; Iw... ALGORITHMS/16(9), 2023-09 / Cardinality-constrained distributionally robust portfolio optimization Kobayashi Ken; Takano Yuichi; Nakata Kazuhide EUROPEAN JOURNAL OF OPERATIONAL RESEARCH/309(3)/pp.1173-1182, 2023-09 / Cutting-plane algorithm for estimation of sparse Cox proportional hazards models Saishu Hiroki; Kudo Kota; Takano Yuichi TOP/Epub, 2023-07-21 / Branch-and-bound algorithm for optimal sparse canonical correlation analysis Watanabe Akihisa; Tamura Ryuta; Takano Yuichi; Miyashi... EXPERT SYSTEMS WITH APPLICATIONS/217, 2023-05 / Dynamic portfolio selection with linear control policies for coherent risk minimization Takano Yuichi; Gotoh Jun-ya OPERATIONS RESEARCH PERSPECTIVES/10, 2023 / Linear control policies for online vehicle relocation in shared mobility systems Yoshida Yasuhiro; Takano Yuichi EXPERT SYSTEMS WITH APPLICATIONS/210, 2022-12 / 出産前後の情報検索の分析：数理最適化による検索日の確率分布推定 岩永 二郎; 西村 直樹; 鮏川 矩義; 高野 祐一 人工知能学会論文誌/37(3)/pp.D-L74_1-11, 2022-05-01 / ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析) 河上 佳太; 工藤 晃太; 川瀬 元暉; 最首 大輝; 山田 直輝; 吉田 晏大; 岩永 二郎; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/67(2)/pp.73-80, 2022-02 CiNii / Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization Kobayashi Ken; Takano Yuichi; Nakata Kazuhide JOURNAL OF GLOBAL OPTIMIZATION/81(2)/pp.493-528, 2021-10 / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach Zhang Kai; Takano Yuichi; Wang Yuzhu; Yoshise Akiko IEEE Access/9/pp.79816-79828, 2021-06 / Sparse Poisson regression via mixed-integer optimization Saishu Hiroki; Kudo Kota; Takano Yuichi PloS one/16(4), 2021-04 PubMed / 時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析 河上 佳太; 西村 直樹; 白鳥 友風; 工藤 晃太; 松岡 雄大; 最首 大輝; 渡邊 彰久; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/66(4)/pp.246-254, 2021-04 CiNii / データコラボレーション解析における統合関数の最適化 川上 雄大; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(6)/pp.297-302, 2024-06 / A Design Method of the Joint Venture Formation in EPC Projects Ishi Nobuaki; Takano Yuichi; Muraki Masaaki Intelligent Engineering and Management for Industry 4.0/pp.137-146, 2022-06 / 形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待) 西村 直樹; 鮏川 矩義; 高野 祐一; 岩永 二郎 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/65(6)/pp.328-333, 2020-06 CiNii / サポートベクトルマシンとカーネル法 (特集 機械学習の手法と役割期待) 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/65(6)/pp.304-309, 2020-06 CiNii / Smoothness-constrained model for nonparametric item response theory Sato Toshiki; Takano Yuichi Information Science and Applied Mathematics/27/pp.1-20, 2020-03 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― 高橋 直希; 高野 祐一; 吉瀬 章子 オペレーションズ・リサーチ/68(8)/pp.453-459, 2019-08 / LDPC符号に対するタブー探索法に基づく勾配降下ビット反転復号法 高橋 良介; 高野 祐一 情報科学研究/39/pp.51-59, 2019-03 / A Resource Flow Based Multistage Dynamic Scheduling Method for the State-Dependent Work Ishii Nobuaki; Takano Yuichi; Muraki Masaaki Advances in Intelligent Systems and Computing/873/pp.300-316, 2019-01 / 数理最適化による学生のプロジェクト配属の決定 橋本 莉奈; 高野 祐一 専修ネットワーク＆インフォメーション/26/pp.27-31, 2018-03 / 整数最適化復号法の性能評価 柿沼 美希; 高野 祐一 情報科学研究/38/pp.17-24, 2018-03 / 多重共線性を考慮した回帰式の変数選択問題の定式化 田村 隆太; 小林 健; 高野 祐一; 宮代 隆平; 中田 和秀; 松井 知己 オペレーションズ・リサーチ：経営の科学/63(3)/pp.128-133, 2018-03 / A Simulation-Based Dynamic Scheduling Method in Project Cost Estimation Process Ishii Nobuaki; Takano Yuichi; Muraki Masaaki Advances in Intelligent Systems and Computing/676/pp.261-279, 2018-01 / キークレーン間干渉を考慮したコンテナ事前配列問題 宮崎 晃年; 鮏川 矩義; 高野 祐一; 水野 眞治 情報科学研究/37/pp.1-11, 2017-03 / 混合整数最適化による階層的変数選択を用いた店舗選択要因の分析 佐藤 俊樹; 高野 祐一; 中原 孝信 情報科学技術フォーラム講演論文集/15(2)/pp.23-30, 2016-09 / ZIMPL言語とSCIPによる数理最適化 高野 祐一 専修ネットワーク＆インフォメーション/24/pp.9-14, 2016-03 / 複数の販売チャネルでの購入を促進するための商品推薦手法 志甫 有真; 谷川 奈穂; 馬場 隆; 菊地 宏治; 片山翔太; 高野 祐一; 中田 和秀 情報科学研究/36/pp.1-10, 2016-03 / Mathematical Optimization Models for Nonparametric Item Response Theory Takano Yuichi; Tsunoda Shintaro; Muraki Masaaki Information Science and Applied Mathematics/23/pp.1-18, 2016-03 / 時系列モデルによる商品販促効果の分析 山根 智之; 菅原 光太郎; 西村 直樹; 小林 健; 吉田 佑輔; 高野 祐一; 中田 和秀 オペレーションズ・リサーチ：経営の科学/61(2)/pp.65-70, 2016-02 / 整数計画法による変数選択を用いた店舗選択モデル 佐藤 俊樹; 高野 祐一; 中原 孝信 情報科学技術フォーラム講演論文集/14(2)/pp.53-58, 2015-08 CiNii / 競争入札戦略と決定理論モデル 高野 祐一 オペレーションズ・リサーチ：経営の科学/60(7)/pp.369-373, 2015-07 / アドネットワークにおけるバナー広告入札戦略決定フレームワークの有効性の検証 高野 祐一; 和田 悠太郎; 生田目 崇; 村木 正昭 情報科学研究/35/pp.1-17, 2015-03 / 確率計画法の理論と応用 高野 祐一 専修ネットワーク＆インフォメーション/23/pp.14-21, 2015-03 / ECサイトの商品特性を考慮した2次元確率表による購買予測 西村 直樹; 鮏川矩義; 高野 祐一; 岩永 二郎; 水野 眞治 オペレーションズ・リサーチ：経営の科学/60(2)/pp.69-74, 2015-02 / A Heuristic Bidding Price Decision Algorithm Based on Cost Estimation Accuracy under Limited Engineering Man-Hours in EPC Projects Ishii Nobuaki; Takano Yuichi; Muraki Masaaki Advances in Intelligent Systems and Computing/319/pp.101-118, 2015-01 / 混合整数2次錐計画法による回帰式の変数選択 宮代 隆平; 高野 祐一 オペレーションズ・リサーチ：経営の科学/59(12)/pp.732-738, 2014-12</t>
+          <t>Data collaboration analysis with orthonormal basis selection and alignment Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... Computers and Electrical Engineering/pp.1-28, 2026-06 / Mean–variance portfolio optimization with shrinkage estimation for recommender systems YANAGI Tomoya; YASUMOTO Yuta; TAKANO Yuichi Proceedings of the 15th International Conference on Operations Research and Enterprise Systems (ICORES 2026)/pp.265-272, 2026-03 / 最適多分木による解釈可能な市場細分化 深谷 悠人; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 菊池 明飛; 武井 柊悟; 竹内 崇貴; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/71(2)/pp.61-69, 2026-02 / New solutions based on the generalized eigenvalue problem for the data collaboration analysis Kawakami Yuta; Takano Yuichi; Imakura Akira INFORMATION SCIENCES/723, 2026-01 / Subset Selection for Stratified Sampling in Online Controlled Experiments MOMOZU Haru; UEHARA Yuki; NISHIMURA Naoki; OHASHI Koy... Proceedings of the 22nd Pacific Rim International Conference on Artificial Intelligence (PRICAI 2025)/(Part II)/pp.600-613, 2025-11 / Robust personalized pricing under uncertainty of purchase probabilities Ikeda Shunnosuke; Nishimura Naoki; Sukegawa Noriyoshi; ... EURO Journal on Computational Optimization/13, 2025-08 / Missing Value Imputation via Mathematical Optimization with Instance-and-feature Neighborhoods Kawakami Yuta; Matsumoto Takumi; Takano Yuichi Journal of Information Processing/33(0)/pp.410-418, 2025 / Privacy-preserving recommender system using the data collaboration analysis for distributed datasets Yanagi Tomoya; Ikeda Shunnosuke; Sukegawa Noriyoshi; T... PLoS ONE/20(4), 2025-04 / 最適モデル多分木による価格需要曲線の推定 菊池 明飛; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 武井 柊悟; 竹内 崇貴; 深谷 悠人; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/70(2)/pp.61-68, 2025-02 / Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times Ikuma Daiki; Ikeda Shunnosuke; Sukegawa Noriyoshi; Tak... Journal of Japan Industrial Management Association/75(4E)/pp.172-182, 2025-01 / DC algorithm for estimation of sparse Gaussian graphical models Shiratori Tomokaze; Takano Yuichi PLOS ONE/19(12), 2024-12-23 / Robust Portfolio Optimization for Recommender Systems Considering Uncertainty of Estimated Statistics Yanagi Tomoya; Ikeda Shunnosuke; Takano Yuichi Proceedings of Pacific rim international conference on artificial intelligence/pp.429-440, 2024-11 / Fast Solution to the Fair Ranking Problem Using the Sinkhorn Algorithm Uehara Yuki; Ikeda Shunnosuke; Nishimura Naoki; Ohashi... Proceedings of Pacific rim international conference on artificial intelligence/pp.207-215, 2024-11 / Mixed-Integer Linear Optimization Formulations for Feature Subset Selection in Kernel SVM Classification Tamura Ryuta; Takano Yuichi; Miyashiro Ryuhei IEICE TRANSACTIONS ON FUNDAMENTALS OF ELECTRONICS COMMUNICATIONS AND COMPUTER SCIENCES/E107A(8)/pp.1151-1162, 2024-08 / Robust portfolio optimization model for electronic coupon allocation Uehara Yuki; Nishimura Naoki; Li Yilin; Yang Jie; Job... INFOR/Epub, 2024-07-29 / 混合整数最適化による相続工程の長期化リスク採点システム 椎名 萌; 高野 祐一; 宇佐美 朋香; 山西 康孝; 藤巻 米隆 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(4)/pp.219-224, 2024-04 / ECサイトにおける利用者属性データの欠損値補完 川上 雄大; 奈良岡 勇; 松本 拓見; 安元 優太; 朝倉 希美; 椎名 萌; 守屋 恵瑠萌; 鮏... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(2)/pp.82-88, 2024-02 / Prescriptive price optimization using optimal regression trees Ikeda Shunnosuke; Nishimura Naoki; Sukegawa Noriyoshi; ... OPERATIONS RESEARCH PERSPECTIVES/11, 2023-12 / 構造的正則化処方分析による旅行パックの価格最適化 池田 春之介; 朝倉 希美; 西村 直樹; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/68(9)/pp.485-490, 2023-09 / Predicting Online Item-Choice Behavior: A Shape-Restricted Regression Approach Nishimura Naoki; Sukegawa Noriyoshi; Takano Yuichi; Iw... ALGORITHMS/16(9), 2023-09 / Cardinality-constrained distributionally robust portfolio optimization Kobayashi Ken; Takano Yuichi; Nakata Kazuhide EUROPEAN JOURNAL OF OPERATIONAL RESEARCH/309(3)/pp.1173-1182, 2023-09 / Cutting-plane algorithm for estimation of sparse Cox proportional hazards models Saishu Hiroki; Kudo Kota; Takano Yuichi TOP/Epub, 2023-07-21 / Branch-and-bound algorithm for optimal sparse canonical correlation analysis Watanabe Akihisa; Tamura Ryuta; Takano Yuichi; Miyashi... EXPERT SYSTEMS WITH APPLICATIONS/217, 2023-05 / Dynamic portfolio selection with linear control policies for coherent risk minimization Takano Yuichi; Gotoh Jun-ya OPERATIONS RESEARCH PERSPECTIVES/10, 2023 / Linear control policies for online vehicle relocation in shared mobility systems Yoshida Yasuhiro; Takano Yuichi EXPERT SYSTEMS WITH APPLICATIONS/210, 2022-12 / データコラボレーション解析における統合関数の最適化 川上 雄大; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(6)/pp.297-302, 2024-06 / A Design Method of the Joint Venture Formation in EPC Projects Ishi Nobuaki; Takano Yuichi; Muraki Masaaki Intelligent Engineering and Management for Industry 4.0/pp.137-146, 2022-06 / 形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待) 西村 直樹; 鮏川 矩義; 高野 祐一; 岩永 二郎 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/65(6)/pp.328-333, 2020-06 CiNii / サポートベクトルマシンとカーネル法 (特集 機械学習の手法と役割期待) 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/65(6)/pp.304-309, 2020-06 CiNii / Smoothness-constrained model for nonparametric item response theory Sato Toshiki; Takano Yuichi Information Science and Applied Mathematics/27/pp.1-20, 2020-03 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― 高橋 直希; 高野 祐一; 吉瀬 章子 オペレーションズ・リサーチ/68(8)/pp.453-459, 2019-08 / LDPC符号に対するタブー探索法に基づく勾配降下ビット反転復号法 高橋 良介; 高野 祐一 情報科学研究/39/pp.51-59, 2019-03 / A Resource Flow Based Multistage Dynamic Scheduling Method for the State-Dependent Work Ishii Nobuaki; Takano Yuichi; Muraki Masaaki Advances in Intelligent Systems and Computing/873/pp.300-316, 2019-01 / 数理最適化による学生のプロジェクト配属の決定 橋本 莉奈; 高野 祐一 専修ネットワーク＆インフォメーション/26/pp.27-31, 2018-03 / 整数最適化復号法の性能評価 柿沼 美希; 高野 祐一 情報科学研究/38/pp.17-24, 2018-03 / 多重共線性を考慮した回帰式の変数選択問題の定式化 田村 隆太; 小林 健; 高野 祐一; 宮代 隆平; 中田 和秀; 松井 知己 オペレーションズ・リサーチ：経営の科学/63(3)/pp.128-133, 2018-03 / A Simulation-Based Dynamic Scheduling Method in Project Cost Estimation Process Ishii Nobuaki; Takano Yuichi; Muraki Masaaki Advances in Intelligent Systems and Computing/676/pp.261-279, 2018-01 / キークレーン間干渉を考慮したコンテナ事前配列問題 宮崎 晃年; 鮏川 矩義; 高野 祐一; 水野 眞治 情報科学研究/37/pp.1-11, 2017-03 / 混合整数最適化による階層的変数選択を用いた店舗選択要因の分析 佐藤 俊樹; 高野 祐一; 中原 孝信 情報科学技術フォーラム講演論文集/15(2)/pp.23-30, 2016-09 / ZIMPL言語とSCIPによる数理最適化 高野 祐一 専修ネットワーク＆インフォメーション/24/pp.9-14, 2016-03 / 複数の販売チャネルでの購入を促進するための商品推薦手法 志甫 有真; 谷川 奈穂; 馬場 隆; 菊地 宏治; 片山翔太; 高野 祐一; 中田 和秀 情報科学研究/36/pp.1-10, 2016-03 / Mathematical Optimization Models for Nonparametric Item Response Theory Takano Yuichi; Tsunoda Shintaro; Muraki Masaaki Information Science and Applied Mathematics/23/pp.1-18, 2016-03 / 時系列モデルによる商品販促効果の分析 山根 智之; 菅原 光太郎; 西村 直樹; 小林 健; 吉田 佑輔; 高野 祐一; 中田 和秀 オペレーションズ・リサーチ：経営の科学/61(2)/pp.65-70, 2016-02 / 整数計画法による変数選択を用いた店舗選択モデル 佐藤 俊樹; 高野 祐一; 中原 孝信 情報科学技術フォーラム講演論文集/14(2)/pp.53-58, 2015-08 CiNii / 競争入札戦略と決定理論モデル 高野 祐一 オペレーションズ・リサーチ：経営の科学/60(7)/pp.369-373, 2015-07 / アドネットワークにおけるバナー広告入札戦略決定フレームワークの有効性の検証 高野 祐一; 和田 悠太郎; 生田目 崇; 村木 正昭 情報科学研究/35/pp.1-17, 2015-03 / 確率計画法の理論と応用 高野 祐一 専修ネットワーク＆インフォメーション/23/pp.14-21, 2015-03 / ECサイトの商品特性を考慮した2次元確率表による購買予測 西村 直樹; 鮏川矩義; 高野 祐一; 岩永 二郎; 水野 眞治 オペレーションズ・リサーチ：経営の科学/60(2)/pp.69-74, 2015-02 / A Heuristic Bidding Price Decision Algorithm Based on Cost Estimation Accuracy under Limited Engineering Man-Hours in EPC Projects Ishii Nobuaki; Takano Yuichi; Muraki Masaaki Advances in Intelligent Systems and Computing/319/pp.101-118, 2015-01 / 混合整数2次錐計画法による回帰式の変数選択 宮代 隆平; 高野 祐一 オペレーションズ・リサーチ：経営の科学/59(12)/pp.732-738, 2014-12</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2140,7 +2144,13 @@
 ノンパラメトリック推定に基づくテスト理論モデルの研究
 カーネル法と制御ポリシーを用いた中長期的投資戦略最適化
 取引コストを考慮した多期間ポートフォリオの最適化
+Data collaboration analysis with orthonormal basis selection and alignment Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... Computers and Electrical Engineering/pp.1-28, 2026-06
+Mean–variance portfolio optimization with shrinkage estimation for recommender systems YANAGI Tomoya; YASUMOTO Yuta; TAKANO Yuichi Proceedings of the 15th International Conference on Operations Research and Enterprise Systems (ICORES 2026)/pp.265-272, 2026-03
+最適多分木による解釈可能な市場細分化 深谷 悠人; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 菊池 明飛; 武井 柊悟; 竹内 崇貴; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/71(2)/pp.61-69, 2026-02
+New solutions based on the generalized eigenvalue problem for the data collaboration analysis Kawakami Yuta; Takano Yuichi; Imakura Akira INFORMATION SCIENCES/723, 2026-01
+Subset Selection for Stratified Sampling in Online Controlled Experiments MOMOZU Haru; UEHARA Yuki; NISHIMURA Naoki; OHASHI Koy... Proceedings of the 22nd Pacific Rim International Conference on Artificial Intelligence (PRICAI 2025)/(Part II)/pp.600-613, 2025-11
 Robust personalized pricing under uncertainty of purchase probabilities Ikeda Shunnosuke; Nishimura Naoki; Sukegawa Noriyoshi; ... EURO Journal on Computational Optimization/13, 2025-08
+Missing Value Imputation via Mathematical Optimization with Instance-and-feature Neighborhoods Kawakami Yuta; Matsumoto Takumi; Takano Yuichi Journal of Information Processing/33(0)/pp.410-418, 2025
 Privacy-preserving recommender system using the data collaboration analysis for distributed datasets Yanagi Tomoya; Ikeda Shunnosuke; Sukegawa Noriyoshi; T... PLoS ONE/20(4), 2025-04
 最適モデル多分木による価格需要曲線の推定 菊池 明飛; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 武井 柊悟; 竹内 崇貴; 深谷 悠人; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/70(2)/pp.61-68, 2025-02
 Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times Ikuma Daiki; Ikeda Shunnosuke; Sukegawa Noriyoshi; Tak... Journal of Japan Industrial Management Association/75(4E)/pp.172-182, 2025-01
@@ -2159,12 +2169,6 @@
 Branch-and-bound algorithm for optimal sparse canonical correlation analysis Watanabe Akihisa; Tamura Ryuta; Takano Yuichi; Miyashi... EXPERT SYSTEMS WITH APPLICATIONS/217, 2023-05
 Dynamic portfolio selection with linear control policies for coherent risk minimization Takano Yuichi; Gotoh Jun-ya OPERATIONS RESEARCH PERSPECTIVES/10, 2023
 Linear control policies for online vehicle relocation in shared mobility systems Yoshida Yasuhiro; Takano Yuichi EXPERT SYSTEMS WITH APPLICATIONS/210, 2022-12
-出産前後の情報検索の分析：数理最適化による検索日の確率分布推定 岩永 二郎; 西村 直樹; 鮏川 矩義; 高野 祐一 人工知能学会論文誌/37(3)/pp.D-L74_1-11, 2022-05-01
-ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析) 河上 佳太; 工藤 晃太; 川瀬 元暉; 最首 大輝; 山田 直輝; 吉田 晏大; 岩永 二郎; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/67(2)/pp.73-80, 2022-02 CiNii
-Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization Kobayashi Ken; Takano Yuichi; Nakata Kazuhide JOURNAL OF GLOBAL OPTIMIZATION/81(2)/pp.493-528, 2021-10
-Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach Zhang Kai; Takano Yuichi; Wang Yuzhu; Yoshise Akiko IEEE Access/9/pp.79816-79828, 2021-06
-Sparse Poisson regression via mixed-integer optimization Saishu Hiroki; Kudo Kota; Takano Yuichi PloS one/16(4), 2021-04 PubMed
-時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析 河上 佳太; 西村 直樹; 白鳥 友風; 工藤 晃太; 松岡 雄大; 最首 大輝; 渡邊 彰久; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/66(4)/pp.246-254, 2021-04 CiNii
 データコラボレーション解析における統合関数の最適化 川上 雄大; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(6)/pp.297-302, 2024-06
 A Design Method of the Joint Venture Formation in EPC Projects Ishi Nobuaki; Takano Yuichi; Muraki Masaaki Intelligent Engineering and Management for Industry 4.0/pp.137-146, 2022-06
 形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待) 西村 直樹; 鮏川 矩義; 高野 祐一; 岩永 二郎 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/65(6)/pp.328-333, 2020-06 CiNii
@@ -2226,13 +2230,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>KPI工学教育研究の推進
+          <t>サービスLAD:人間とAIエージェントの協働によるサービス設計基盤の構築
+仮想3PLにおける在庫移動最適化
+LMS利用行動ログと学習指標に関する調査
+健康にやさしいまちづくりのための環境整備に係る実証事業
 包摂的コミュニティプラットフォームの構築
-健康にやさしいまちづくりのための環境整備に係る実証事業
-統合型ヘルスケアシステムの構築
-文書生成AIサービス工学に関する研究
-文書生成AIの企業内利活用における最適化の研究
-包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究
+中小企業価値評価の実践的研究の発展
+デジタルガバメント／スマートシティ連携モデル研究の 防災分野への発展
+経営における組織・人事ソリューションの基盤研究
+KPI工学教育研究の推進
 会計学
 ウェブ情報学・サービス情報学
 社会システム工学・安全システム
@@ -2243,36 +2249,36 @@
 サービス工学
 ソーシャル・データサイエンス
 社会工学
+Single-Round Clustered Federated Learning via Data Collaboration Analysis for Non-IID Data SUGAWARA Sota; KAWAMATA Yuji; TOYODA Akihiro; NAKAYAMA... Proceedings of International Joint Conferences on Artificial Intelligence (IJCAI-ECAI2026), 2026-08
+Differential Effects of Soft and Hard Hindrance Demands on Job Satisfaction: An Analysis of Interactions with Job Resources Using Latent Moderated Structural Equations TAMURA Aoba; TAMARI Yuki; TAKAZONO Tadasuke; OKADA Yu... Proceedings of The Association for Psychological Science (APS), 2026-05
+Covariance-Based Structural Equation Modeling in Small-Sample Settings with p&gt;n HASEGAWA Hiroki; TAMURA Aoba; OKADA Yukihiko arXiv, 2026-04
+Re-presenting Physiological Synchrony as Non-Interpretive Haptic Cues in Dyadic Dialogue Higashiyama Yuki; Wang Zhaolong; Alhalabi Hajar; Okada... Proceedings of the Augmented Humans International Conference 2026 (AHs '26), 2026-03
 Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment TOYODA Akihiro; KAWAMATA Yuji; NAKAYAMA Tomoru; IMAKUR... Scientific Reports/16(1), 2026-01
+Estimation of conditional average treatment effects on distributed confidential data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; IMAKURA A... Expert Systems with Applications/296(C)/p.129066, 2026-01
+Interaction Tensor SHAP HASEGAWA Hiroki; OKADA Yukihiko arXiv, 2025-12
+アカウンティング・インフォマティクスの可能性：ディテクター機能と会計情報 岡田 幸彦 會計/208(1)/pp.57-68, 2025-12
 Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients Ashitomi Y.; Kawamura H.; Kubo E.; Kosugi K. H.; Kosh... ANNALS OF ONCOLOGY/36(4), 2025-12
 Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach Mashiko Sota; Kawamata Yuji; Nakayama Tomoru; Sakurai ... SCIENTIFIC REPORTS/15(1), 2025-11-26
-Estimation of conditional average treatment effects on distributed confidential data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; IMAKURA A... Expert Systems with Applications/296(C)/p.129066, 2026-01
+A Reliable Decision Support Framework for SME Default Prediction Using Uncertainty-Aware Bayesian GEV Regression TERADA Kaito; ABE Keiji; TAKEDA Toshihiko; KAWAMATA Y... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.2268-2273, 2025-11
+DC-CP: Data Collaboration Conformal Prediction from Model Training to Conformal Prediction in Single-Round Communication While Preserving Privacy NAKAYAMA Tomoru; KAWAMATA Yuji; IMAKURA Akira; OKADA ... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.1474-1479, 2025-11
+Cash-Flow Prediction Model Using Graph Neural Networks and Spatiotemporal Information from Double-Entry Bookkeeping Data MOTAI Ryoki; KAMEBUCHI Masato; WATANABE Sora; MATSUMOT... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.2425-2433, 2025-11
+A new type of federated clustering: A non-model-sharing approach KAWAMATA Yuji; KAMIJO Kaoru; KIHIRA Masateru; TOYODA ... arXiv, 2025-06
+A Robust and Non-Iterative Tensor Decomposition Method with Automatic Thresholding HASEGAWA Hiroki; OKADA Yukihiko arXiv, 2025-05
+Designing Undetectable Morphing Speech: How Morph Rate and Discrete/Continuous Changes Influences Change Detection Thresholds Okano Hiiro; Wakatsuki Naoto; Okada Yukihiko; ZEMPO K... Proceedings of the Augmented Humans International Conference 2025/pp.409-412, 2025-05
 Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support Kawamura Homura; Miura Tomofumi; Maeda Yuka; Okada Yu... IEEE ACCESS/13/pp.99490-99508, 2025-05
 Data collaboration for causal inference from limited medical testing and medication data NAKAYAMA Tomoru; KAWAMATA Yuji; TOYODA Akihiro; IMAKUR... Scientific Reports/15(1), 2025-03
 Generating Synthetic Journal-Entry Data Using Variational Autoencoder MOTAI Ryoki; MASHIKO Sota; KAWAMATA Yuji; SHIN Ryota; ... Intelligent Systems in Accounting, Finance and Management/32(1), 2025-03
-Anomaly Detection in Double-entry Bookkeeping Data by Federated Learning System with Non-model Sharing Approach MASHIKO Sota; KAWAMATA Yuji; NAKAYAMA Tomoru; SAKURAI ... arXiv, 2025-01
 Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data MOTAI Ryoki; MASHIKO Sota; KAMEBUCHI Masato; WATANABE ... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2360-2364, 2024-12
 An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises ANDO Renon; KAWAMATA Yuji; TAKEDA Toshihiko; OKADA Yu... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2269-2274, 2024-12
 Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data HASEGAWA Hiroki; YATA Kazuyoshi; OKADA Yukihiko; KUNIM... Prceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.34-43, 2024-12
 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19
 pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis Kawamura Homura; Wang Zhaolong; Harima Kotone; Yamanis... Companion of the 2024 ACM International Joint Conference on Pervasive and Ubiquitous Computing (UbiComp '24), 2024-10-07
-会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 山矢 和輝; 罇 涼稀; 岡田 幸彦 帝京経済学研究/58(1)/pp.7-23, 2024-10
-Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data Hasegawa Hiroki; Kawamura Homura; Shin Ryota; Yata Ka... Proceedings of the 6th International Conference on Statistics: Theory and Applications, 2024-8
-分散機密データを想定した 処置効果の推定手法の開発 河又裕士; 岡田 幸彦 オペレーションズ・リサーチ, 2024-06
-英文学術雑誌における近年の簿記研究 中村亮介; 罇 涼稀; 松下真也; 岡田 幸彦 簿記研究/7(1)/pp.1-14, 2024-06
-Collaborative causal inference on distributed data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; Imakura A... EXPERT SYSTEMS WITH APPLICATIONS/244, 2024-06
-Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach Kawamata Yuji; Motai Ryoki; Okada Yukihiko; Imakura A... arXiv, 2024-02
-Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation Tanabe Kai; Sugawara Yuki; Sakurai Eiichi; Motomura Y... PloS one/19(2), 2024-02 PubMed
-Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data Mudahemuka Eugene; 宮城昌竜; 秦涼太; 金子直樹; 岡田幸彦; Yamamoto Kyosuke Sensors/24(4), 2024-02
-Knowledge sharing among coaches: expert power and social cognitive theory perspectives Funasaki Kohei; Inoue Yuhei; Takahashi Yoshio; Shirai ... EUROPEAN SPORT MANAGEMENT QUARTERLY/Epub/pp.1-20, 2024-01
-Positive effect of proactive personality on customer orientation in service context Takashima Ryota; Ueda Natsuki; Hashimoto Tatsuya; Okad... INTERNATIONAL JOURNAL OF PSYCHOLOGY/58(1)/pp.818-818, 2023-12
-Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data Yanagiura Takeshi; Yano Shiho; Kihira Masateru; Okada ... Journal of Educational Data Mining/15(3)/pp.1-25, 2023-12
-Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis Sugawara Yuki; Sakurai Eiichi; Motomura Yoichi; Okada ... Proceedings of 2023 IEEE International Conference on Big Data (BigData)/pp.2726-2734, 2023-12</t>
+会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 山矢 和輝; 罇 涼稀; 岡田 幸彦 帝京経済学研究/58(1)/pp.7-23, 2024-10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KPI工学教育研究の推進 / 包摂的コミュニティプラットフォームの構築 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 統合型ヘルスケアシステムの構築 / 文書生成AIサービス工学に関する研究 / 文書生成AIの企業内利活用における最適化の研究 / 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究</t>
+          <t>サービスLAD:人間とAIエージェントの協働によるサービス設計基盤の構築 / 仮想3PLにおける在庫移動最適化 / LMS利用行動ログと学習指標に関する調査 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 包摂的コミュニティプラットフォームの構築 / 中小企業価値評価の実践的研究の発展 / デジタルガバメント／スマートシティ連携モデル研究の 防災分野への発展 / 経営における組織・人事ソリューションの基盤研究 / KPI工学教育研究の推進</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2287,7 +2293,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment TOYODA Akihiro; KAWAMATA Yuji; NAKAYAMA Tomoru; IMAKUR... Scientific Reports/16(1), 2026-01 / Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients Ashitomi Y.; Kawamura H.; Kubo E.; Kosugi K. H.; Kosh... ANNALS OF ONCOLOGY/36(4), 2025-12 / Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach Mashiko Sota; Kawamata Yuji; Nakayama Tomoru; Sakurai ... SCIENTIFIC REPORTS/15(1), 2025-11-26 / Estimation of conditional average treatment effects on distributed confidential data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; IMAKURA A... Expert Systems with Applications/296(C)/p.129066, 2026-01 / Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support Kawamura Homura; Miura Tomofumi; Maeda Yuka; Okada Yu... IEEE ACCESS/13/pp.99490-99508, 2025-05 / Data collaboration for causal inference from limited medical testing and medication data NAKAYAMA Tomoru; KAWAMATA Yuji; TOYODA Akihiro; IMAKUR... Scientific Reports/15(1), 2025-03 / Generating Synthetic Journal-Entry Data Using Variational Autoencoder MOTAI Ryoki; MASHIKO Sota; KAWAMATA Yuji; SHIN Ryota; ... Intelligent Systems in Accounting, Finance and Management/32(1), 2025-03 / Anomaly Detection in Double-entry Bookkeeping Data by Federated Learning System with Non-model Sharing Approach MASHIKO Sota; KAWAMATA Yuji; NAKAYAMA Tomoru; SAKURAI ... arXiv, 2025-01 / Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data MOTAI Ryoki; MASHIKO Sota; KAMEBUCHI Masato; WATANABE ... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2360-2364, 2024-12 / An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises ANDO Renon; KAWAMATA Yuji; TAKEDA Toshihiko; OKADA Yu... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2269-2274, 2024-12 / Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data HASEGAWA Hiroki; YATA Kazuyoshi; OKADA Yukihiko; KUNIM... Prceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.34-43, 2024-12 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19 / pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis Kawamura Homura; Wang Zhaolong; Harima Kotone; Yamanis... Companion of the 2024 ACM International Joint Conference on Pervasive and Ubiquitous Computing (UbiComp '24), 2024-10-07 / 会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 山矢 和輝; 罇 涼稀; 岡田 幸彦 帝京経済学研究/58(1)/pp.7-23, 2024-10 / Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data Hasegawa Hiroki; Kawamura Homura; Shin Ryota; Yata Ka... Proceedings of the 6th International Conference on Statistics: Theory and Applications, 2024-8 / 分散機密データを想定した 処置効果の推定手法の開発 河又裕士; 岡田 幸彦 オペレーションズ・リサーチ, 2024-06 / 英文学術雑誌における近年の簿記研究 中村亮介; 罇 涼稀; 松下真也; 岡田 幸彦 簿記研究/7(1)/pp.1-14, 2024-06 / Collaborative causal inference on distributed data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; Imakura A... EXPERT SYSTEMS WITH APPLICATIONS/244, 2024-06 / Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach Kawamata Yuji; Motai Ryoki; Okada Yukihiko; Imakura A... arXiv, 2024-02 / Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation Tanabe Kai; Sugawara Yuki; Sakurai Eiichi; Motomura Y... PloS one/19(2), 2024-02 PubMed / Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data Mudahemuka Eugene; 宮城昌竜; 秦涼太; 金子直樹; 岡田幸彦; Yamamoto Kyosuke Sensors/24(4), 2024-02 / Knowledge sharing among coaches: expert power and social cognitive theory perspectives Funasaki Kohei; Inoue Yuhei; Takahashi Yoshio; Shirai ... EUROPEAN SPORT MANAGEMENT QUARTERLY/Epub/pp.1-20, 2024-01 / Positive effect of proactive personality on customer orientation in service context Takashima Ryota; Ueda Natsuki; Hashimoto Tatsuya; Okad... INTERNATIONAL JOURNAL OF PSYCHOLOGY/58(1)/pp.818-818, 2023-12 / Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data Yanagiura Takeshi; Yano Shiho; Kihira Masateru; Okada ... Journal of Educational Data Mining/15(3)/pp.1-25, 2023-12 / Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis Sugawara Yuki; Sakurai Eiichi; Motomura Yoichi; Okada ... Proceedings of 2023 IEEE International Conference on Big Data (BigData)/pp.2726-2734, 2023-12</t>
+          <t>Single-Round Clustered Federated Learning via Data Collaboration Analysis for Non-IID Data SUGAWARA Sota; KAWAMATA Yuji; TOYODA Akihiro; NAKAYAMA... Proceedings of International Joint Conferences on Artificial Intelligence (IJCAI-ECAI2026), 2026-08 / Differential Effects of Soft and Hard Hindrance Demands on Job Satisfaction: An Analysis of Interactions with Job Resources Using Latent Moderated Structural Equations TAMURA Aoba; TAMARI Yuki; TAKAZONO Tadasuke; OKADA Yu... Proceedings of The Association for Psychological Science (APS), 2026-05 / Covariance-Based Structural Equation Modeling in Small-Sample Settings with p&gt;n HASEGAWA Hiroki; TAMURA Aoba; OKADA Yukihiko arXiv, 2026-04 / Re-presenting Physiological Synchrony as Non-Interpretive Haptic Cues in Dyadic Dialogue Higashiyama Yuki; Wang Zhaolong; Alhalabi Hajar; Okada... Proceedings of the Augmented Humans International Conference 2026 (AHs '26), 2026-03 / Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment TOYODA Akihiro; KAWAMATA Yuji; NAKAYAMA Tomoru; IMAKUR... Scientific Reports/16(1), 2026-01 / Estimation of conditional average treatment effects on distributed confidential data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; IMAKURA A... Expert Systems with Applications/296(C)/p.129066, 2026-01 / Interaction Tensor SHAP HASEGAWA Hiroki; OKADA Yukihiko arXiv, 2025-12 / アカウンティング・インフォマティクスの可能性：ディテクター機能と会計情報 岡田 幸彦 會計/208(1)/pp.57-68, 2025-12 / Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients Ashitomi Y.; Kawamura H.; Kubo E.; Kosugi K. H.; Kosh... ANNALS OF ONCOLOGY/36(4), 2025-12 / Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach Mashiko Sota; Kawamata Yuji; Nakayama Tomoru; Sakurai ... SCIENTIFIC REPORTS/15(1), 2025-11-26 / A Reliable Decision Support Framework for SME Default Prediction Using Uncertainty-Aware Bayesian GEV Regression TERADA Kaito; ABE Keiji; TAKEDA Toshihiko; KAWAMATA Y... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.2268-2273, 2025-11 / DC-CP: Data Collaboration Conformal Prediction from Model Training to Conformal Prediction in Single-Round Communication While Preserving Privacy NAKAYAMA Tomoru; KAWAMATA Yuji; IMAKURA Akira; OKADA ... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.1474-1479, 2025-11 / Cash-Flow Prediction Model Using Graph Neural Networks and Spatiotemporal Information from Double-Entry Bookkeeping Data MOTAI Ryoki; KAMEBUCHI Masato; WATANABE Sora; MATSUMOT... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.2425-2433, 2025-11 / A new type of federated clustering: A non-model-sharing approach KAWAMATA Yuji; KAMIJO Kaoru; KIHIRA Masateru; TOYODA ... arXiv, 2025-06 / A Robust and Non-Iterative Tensor Decomposition Method with Automatic Thresholding HASEGAWA Hiroki; OKADA Yukihiko arXiv, 2025-05 / Designing Undetectable Morphing Speech: How Morph Rate and Discrete/Continuous Changes Influences Change Detection Thresholds Okano Hiiro; Wakatsuki Naoto; Okada Yukihiko; ZEMPO K... Proceedings of the Augmented Humans International Conference 2025/pp.409-412, 2025-05 / Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support Kawamura Homura; Miura Tomofumi; Maeda Yuka; Okada Yu... IEEE ACCESS/13/pp.99490-99508, 2025-05 / Data collaboration for causal inference from limited medical testing and medication data NAKAYAMA Tomoru; KAWAMATA Yuji; TOYODA Akihiro; IMAKUR... Scientific Reports/15(1), 2025-03 / Generating Synthetic Journal-Entry Data Using Variational Autoencoder MOTAI Ryoki; MASHIKO Sota; KAWAMATA Yuji; SHIN Ryota; ... Intelligent Systems in Accounting, Finance and Management/32(1), 2025-03 / Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data MOTAI Ryoki; MASHIKO Sota; KAMEBUCHI Masato; WATANABE ... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2360-2364, 2024-12 / An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises ANDO Renon; KAWAMATA Yuji; TAKEDA Toshihiko; OKADA Yu... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2269-2274, 2024-12 / Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data HASEGAWA Hiroki; YATA Kazuyoshi; OKADA Yukihiko; KUNIM... Prceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.34-43, 2024-12 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19 / pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis Kawamura Homura; Wang Zhaolong; Harima Kotone; Yamanis... Companion of the 2024 ACM International Joint Conference on Pervasive and Ubiquitous Computing (UbiComp '24), 2024-10-07 / 会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 山矢 和輝; 罇 涼稀; 岡田 幸彦 帝京経済学研究/58(1)/pp.7-23, 2024-10</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2297,12 +2303,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>会計学 ; ウェブ情報学・サービス情報学 ; 社会システム工学・安全システム ; 経営学 ; 商学 ; 社会政策・福祉 ; オペレーションズリサーチ ; 政策評価・計量分析 ; 会計・ファイナンス ; 医療・ヘルスデータ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>会計学 ; ウェブ情報学・サービス情報学 ; 社会システム工学・安全システム ; 経営学 ; 商学 ; 社会政策・福祉 ; オペレーションズリサーチ ; 災害・防災研究 ; 政策評価・計量分析 ; 会計・ファイナンス ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
+          <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2319,9 +2325,9 @@
 社会工学
 社会政策・福祉
 オペレーションズリサーチ
+災害・防災研究
 政策評価・計量分析
 会計・ファイナンス
-医療・ヘルスデータ
 環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
@@ -2334,6 +2340,9 @@
 数理最適化
 組合せ最適化
 計画・スケジューリング
+災害社会学
+防災政策
+リスク評価
 政策評価
 計量経済学
 統計的因果推論
@@ -2342,10 +2351,6 @@
 財務会計
 管理会計
 会計情報システム
-医療データ分析
-生体情報解析
-ヘルスデータサイエンス
-統計解析
 環境政策
 エネルギーシステム
 脱炭素分析
@@ -2387,38 +2392,40 @@
 能動的先手行動の形成プロセスについての縦断的研究
 標準年限卒業予測における大学間転移学習の研究
 NavigatorIIIのパイロット企業における実証実験
+サービスLAD:人間とAIエージェントの協働によるサービス設計基盤の構築
+仮想3PLにおける在庫移動最適化
+LMS利用行動ログと学習指標に関する調査
+健康にやさしいまちづくりのための環境整備に係る実証事業
+包摂的コミュニティプラットフォームの構築
+中小企業価値評価の実践的研究の発展
+デジタルガバメント／スマートシティ連携モデル研究の 防災分野への発展
+経営における組織・人事ソリューションの基盤研究
 KPI工学教育研究の推進
-包摂的コミュニティプラットフォームの構築
-健康にやさしいまちづくりのための環境整備に係る実証事業
-統合型ヘルスケアシステムの構築
-文書生成AIサービス工学に関する研究
-文書生成AIの企業内利活用における最適化の研究
-包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究
+Single-Round Clustered Federated Learning via Data Collaboration Analysis for Non-IID Data SUGAWARA Sota; KAWAMATA Yuji; TOYODA Akihiro; NAKAYAMA... Proceedings of International Joint Conferences on Artificial Intelligence (IJCAI-ECAI2026), 2026-08
+Differential Effects of Soft and Hard Hindrance Demands on Job Satisfaction: An Analysis of Interactions with Job Resources Using Latent Moderated Structural Equations TAMURA Aoba; TAMARI Yuki; TAKAZONO Tadasuke; OKADA Yu... Proceedings of The Association for Psychological Science (APS), 2026-05
+Covariance-Based Structural Equation Modeling in Small-Sample Settings with p&gt;n HASEGAWA Hiroki; TAMURA Aoba; OKADA Yukihiko arXiv, 2026-04
+Re-presenting Physiological Synchrony as Non-Interpretive Haptic Cues in Dyadic Dialogue Higashiyama Yuki; Wang Zhaolong; Alhalabi Hajar; Okada... Proceedings of the Augmented Humans International Conference 2026 (AHs '26), 2026-03
 Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment TOYODA Akihiro; KAWAMATA Yuji; NAKAYAMA Tomoru; IMAKUR... Scientific Reports/16(1), 2026-01
+Estimation of conditional average treatment effects on distributed confidential data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; IMAKURA A... Expert Systems with Applications/296(C)/p.129066, 2026-01
+Interaction Tensor SHAP HASEGAWA Hiroki; OKADA Yukihiko arXiv, 2025-12
+アカウンティング・インフォマティクスの可能性：ディテクター機能と会計情報 岡田 幸彦 會計/208(1)/pp.57-68, 2025-12
 Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients Ashitomi Y.; Kawamura H.; Kubo E.; Kosugi K. H.; Kosh... ANNALS OF ONCOLOGY/36(4), 2025-12
 Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach Mashiko Sota; Kawamata Yuji; Nakayama Tomoru; Sakurai ... SCIENTIFIC REPORTS/15(1), 2025-11-26
-Estimation of conditional average treatment effects on distributed confidential data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; IMAKURA A... Expert Systems with Applications/296(C)/p.129066, 2026-01
+A Reliable Decision Support Framework for SME Default Prediction Using Uncertainty-Aware Bayesian GEV Regression TERADA Kaito; ABE Keiji; TAKEDA Toshihiko; KAWAMATA Y... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.2268-2273, 2025-11
+DC-CP: Data Collaboration Conformal Prediction from Model Training to Conformal Prediction in Single-Round Communication While Preserving Privacy NAKAYAMA Tomoru; KAWAMATA Yuji; IMAKURA Akira; OKADA ... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.1474-1479, 2025-11
+Cash-Flow Prediction Model Using Graph Neural Networks and Spatiotemporal Information from Double-Entry Bookkeeping Data MOTAI Ryoki; KAMEBUCHI Masato; WATANABE Sora; MATSUMOT... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.2425-2433, 2025-11
+A new type of federated clustering: A non-model-sharing approach KAWAMATA Yuji; KAMIJO Kaoru; KIHIRA Masateru; TOYODA ... arXiv, 2025-06
+A Robust and Non-Iterative Tensor Decomposition Method with Automatic Thresholding HASEGAWA Hiroki; OKADA Yukihiko arXiv, 2025-05
+Designing Undetectable Morphing Speech: How Morph Rate and Discrete/Continuous Changes Influences Change Detection Thresholds Okano Hiiro; Wakatsuki Naoto; Okada Yukihiko; ZEMPO K... Proceedings of the Augmented Humans International Conference 2025/pp.409-412, 2025-05
 Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support Kawamura Homura; Miura Tomofumi; Maeda Yuka; Okada Yu... IEEE ACCESS/13/pp.99490-99508, 2025-05
 Data collaboration for causal inference from limited medical testing and medication data NAKAYAMA Tomoru; KAWAMATA Yuji; TOYODA Akihiro; IMAKUR... Scientific Reports/15(1), 2025-03
 Generating Synthetic Journal-Entry Data Using Variational Autoencoder MOTAI Ryoki; MASHIKO Sota; KAWAMATA Yuji; SHIN Ryota; ... Intelligent Systems in Accounting, Finance and Management/32(1), 2025-03
-Anomaly Detection in Double-entry Bookkeeping Data by Federated Learning System with Non-model Sharing Approach MASHIKO Sota; KAWAMATA Yuji; NAKAYAMA Tomoru; SAKURAI ... arXiv, 2025-01
 Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data MOTAI Ryoki; MASHIKO Sota; KAMEBUCHI Masato; WATANABE ... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2360-2364, 2024-12
 An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises ANDO Renon; KAWAMATA Yuji; TAKEDA Toshihiko; OKADA Yu... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2269-2274, 2024-12
 Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data HASEGAWA Hiroki; YATA Kazuyoshi; OKADA Yukihiko; KUNIM... Prceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.34-43, 2024-12
 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19
 pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis Kawamura Homura; Wang Zhaolong; Harima Kotone; Yamanis... Companion of the 2024 ACM International Joint Conference on Pervasive and Ubiquitous Computing (UbiComp '24), 2024-10-07
-会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 山矢 和輝; 罇 涼稀; 岡田 幸彦 帝京経済学研究/58(1)/pp.7-23, 2024-10
-Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data Hasegawa Hiroki; Kawamura Homura; Shin Ryota; Yata Ka... Proceedings of the 6th International Conference on Statistics: Theory and Applications, 2024-8
-分散機密データを想定した 処置効果の推定手法の開発 河又裕士; 岡田 幸彦 オペレーションズ・リサーチ, 2024-06
-英文学術雑誌における近年の簿記研究 中村亮介; 罇 涼稀; 松下真也; 岡田 幸彦 簿記研究/7(1)/pp.1-14, 2024-06
-Collaborative causal inference on distributed data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; Imakura A... EXPERT SYSTEMS WITH APPLICATIONS/244, 2024-06
-Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach Kawamata Yuji; Motai Ryoki; Okada Yukihiko; Imakura A... arXiv, 2024-02
-Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation Tanabe Kai; Sugawara Yuki; Sakurai Eiichi; Motomura Y... PloS one/19(2), 2024-02 PubMed
-Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data Mudahemuka Eugene; 宮城昌竜; 秦涼太; 金子直樹; 岡田幸彦; Yamamoto Kyosuke Sensors/24(4), 2024-02
-Knowledge sharing among coaches: expert power and social cognitive theory perspectives Funasaki Kohei; Inoue Yuhei; Takahashi Yoshio; Shirai ... EUROPEAN SPORT MANAGEMENT QUARTERLY/Epub/pp.1-20, 2024-01
-Positive effect of proactive personality on customer orientation in service context Takashima Ryota; Ueda Natsuki; Hashimoto Tatsuya; Okad... INTERNATIONAL JOURNAL OF PSYCHOLOGY/58(1)/pp.818-818, 2023-12
-Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data Yanagiura Takeshi; Yano Shiho; Kihira Masateru; Okada ... Journal of Educational Data Mining/15(3)/pp.1-25, 2023-12
-Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis Sugawara Yuki; Sakurai Eiichi; Motomura Yoichi; Okada ... Proceedings of 2023 IEEE International Conference on Big Data (BigData)/pp.2726-2734, 2023-12</t>
+会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 山矢 和輝; 罇 涼稀; 岡田 幸彦 帝京経済学研究/58(1)/pp.7-23, 2024-10</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2594,9 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析
+          <t>金融資産市場・リスク状況と社会的ジレンマ下での人間とAIの意思決定
+グリーン投資の意思決定メカニズムの実験的検証
+人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析
 新規投資家の継続的な参入が価格形成・価格変動に与える影響
 ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響
 信用スコア社会に対応可能な評判管理システムの設計
@@ -2595,10 +2604,17 @@
 市場参加者の価格予測の異質性と市場の振る舞いの関係について
 情報の非対称性と多様な期待形成がもたらす金融市場への影響とその安定化政策について
 国家の規模とガバナンスの学際的分析
-情報コストゼロ社会における過剰懲罰とリスク軽減のための社会制度設計
-新しい肺移植制度の構築と評価：ドナー交換移植の可能性
 社会システム工学・安全システム
 社会的ジレンマ、資産市場実験
+ジレンマ状況における表情計測に基づく人の協力行動の分析. 小菅雷太朗; 秋山 英三; 山本仁志; 栗原聡 社会システムと情報技術研究ウィーク（WSSIT2026）, 2026
+Effects of a “Topic Diversification System” facilitating diverse topic exposure on topic interest and social media engage behavior. Nagura Takuya; AKIYAMA Eizo In Proceedings of the 2025 IEEE International Conference on Big Data (IEEE BigData 2025), 2025
+Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. Inaba Masaaki; AKIYAMA Eizo PLOS Complex Systems/2(4), 2025
+Emergence of echo chambers in social media communication involving multiple topics. Nagura Takuya; AKIYAMA Eizo Information, Communication &amp; Society/28(6)/pp. 1099- 1120, 2025
+Partner selection biases induced by resource inequality. Umetani Ryohei; Yamamoto Hitoshi; AKIYAMA Eizo Social Sciences &amp; Humanities Open/12, 2025
+Influence of agent social and network segregation on fake news diffusion. Kitagawa Yuta; Akiyama Eizo In Proceedings of the 2025 IEEE International Conference on Big Data (IEEE BigData 2025), 2025-12
+発話量と発話内容分析に基づく分断された集団間のコミュニケーション円滑化システムの提案 筒井律稀; 小菅雷太朗; 秋山 英三; 山本仁志; 荒牧大樹; 伊藤千輝; 栗原聡 2025年度人工知能学会全国大会（第39回）論文集, 2025/5
+Effect of Network Homophily and Partisanship on Social Media to "Oil Spill" Polarizations Nagura Takuya; Akiyama Eizo JASSS-THE JOURNAL OF ARTIFICIAL SOCIETIES AND SOCIAL SIMULATION/29(1), 2026-01-31
+Evolution of cooperation among migrating resource-oriented agents under environmental variability Inaba Masaaki; Akiyama Eizo CHAOS SOLITONS &amp; FRACTALS/202(2), 2026-01
 検索連動型広告における循環的な入札額変動の発生機構の解明 河又 裕士; 张 晓泉; 秋山 英三 経営情報学会 全国研究発表大会要旨集/201906/pp.117-120, 2019
 ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07
 Bubbles in Asset Markets and the Heterogeneity of Beliefs. AKIYAMA Eizo; Funaki Yukihiko; Ishikawa Ryuichiro; Lah... Journal of Economic Behavior and Organization/236, 2025-08
@@ -2614,21 +2630,12 @@
 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ 秋山 英三; 石橋 裕 第66回土木計画学研究発表会・講演集, 2022-11
 Individuals reciprocate negative actions revealing negative upstream reciprocity Umetani Ryohei; Yamamoto Hitoshi; Goto Akira; Okada I... PLOS ONE/18(7), 2023-07-05
 SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. 名倉 卓弥; 秋山 英三 人工知能学会論文誌/38(4)/pp.B-N11_1-B-N11_9, 2023
-Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement Masaaki Inaba; 秋山 英三 SCIENTIFIC REPORTS/13(1), 2023-06-17
-Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim Ishibashi Yutaka; Akiyama Eizo 2022 IEEE International Conference on Big Data (Big Data), 2022-12
-パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 栗栖慶太; 秋山英三 シミュレーション＆ゲーミング/33(1)/pp.11-22, 2023
-群淘汰状況下における罰則・報酬の進化 秋山 英三 信学技報/122(421)/pp.36-41, 2023-03
-Self-organized Speculation Game for the spontaneous emergence of financial stylized facts Katahira K.; Chen Y.; Akiyama Eizo Physica A/582, 2021-11
-情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ 秋山 英三; 謝凡 人工知能学会論文, 2021-10
-時間制約を導入したゴミ箱モデル 秋山 英三; 石田雄大 人工知能学会論文, 2021-10
-Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment Akiyama Eizo; Okada I.; Yamamoto H.; Toriumi F. Scientific Reports/11(1), 2021-04
-協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 米納 弘渡; 秋山英三 JAWS2014, 2014-10
-A quantitative easing experiment Penalver Adrian; Hanaki Nobuyuki; Akiyama Eizo; Funaki... Journal of economic dynamics &amp; control/119, 2020-10 PubMed</t>
+Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement Masaaki Inaba; 秋山 英三 SCIENTIFIC REPORTS/13(1), 2023-06-17</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析 / 新規投資家の継続的な参入が価格形成・価格変動に与える影響 / ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響 / 信用スコア社会に対応可能な評判管理システムの設計 / 験財消費のための情報収集行動とその支援情報提供システム / 市場参加者の価格予測の異質性と市場の振る舞いの関係について / 情報の非対称性と多様な期待形成がもたらす金融市場への影響とその安定化政策について / 国家の規模とガバナンスの学際的分析 / 情報コストゼロ社会における過剰懲罰とリスク軽減のための社会制度設計 / 新しい肺移植制度の構築と評価：ドナー交換移植の可能性</t>
+          <t>金融資産市場・リスク状況と社会的ジレンマ下での人間とAIの意思決定 / グリーン投資の意思決定メカニズムの実験的検証 / 人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析 / 新規投資家の継続的な参入が価格形成・価格変動に与える影響 / ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響 / 信用スコア社会に対応可能な評判管理システムの設計 / 験財消費のための情報収集行動とその支援情報提供システム / 市場参加者の価格予測の異質性と市場の振る舞いの関係について / 情報の非対称性と多様な期待形成がもたらす金融市場への影響とその安定化政策について / 国家の規模とガバナンスの学際的分析</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2643,7 +2650,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>検索連動型広告における循環的な入札額変動の発生機構の解明 河又 裕士; 张 晓泉; 秋山 英三 経営情報学会 全国研究発表大会要旨集/201906/pp.117-120, 2019 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07 / Bubbles in Asset Markets and the Heterogeneity of Beliefs. AKIYAMA Eizo; Funaki Yukihiko; Ishikawa Ryuichiro; Lah... Journal of Economic Behavior and Organization/236, 2025-08 / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 小菅雷太朗; 若林直希; 山本仁志; 秋山 英三; 栗原聡 行動変容と社会システム/10, 2024 / 進化ゲーム理論の進化 — マルチエージェントシミュレーション，実験室実験と，LLM の行動経済学— 秋山 英三 人工知能/39(3)/pp.323-329, 2024 / 発話量と発話内容に基づく集団間のコミュニケーション円滑化システムの提案 筒井律稀; 小菅雷太朗; 秋山 英三; 山本仁志; 荒牧大樹; 伊藤千輝; 栗原 聡 行動変容と社会システム/11, 2024 / ソーシャルメディア上のアジェンダ設定がエコーチェンバーの発生に与える影響について 名倉 卓弥; 秋山 英三 人工知能学会論文誌/39(6)/pp.p. AG24-A_1-8, 2024-11-1 / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. Inaba Masaaki; Akiyama Eizo PLOS Complex Systems/2(4), 2025-04 / Emergence of echo chambers in social media communication involving multiple topics Nagura Takuya; Akiyama Eizo INFORMATION COMMUNICATION &amp; SOCIETY/Epub/pp.1099-1120, 2025-01-28 / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 小菅雷太郎; 若林直希; 山本仁志; 栗原聡; 秋山 英三 行動変容と社会システム/10, 2024-3 / 進化ゲーム理論の進化：マルチエージェントシミュレーション, 実験室実験と，LLMの行動経済学 秋山 英三 人工知能学会論文誌/39(3)/pp.323-330, 2024-5 / 重みが動的なネットワークにおいてネットワーク構造が協力の進化に与える影響 栗栖 慶太; 秋山 英三 情報処理学会論文誌/65(1)/pp.61-68, 2024-1 / 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ 秋山 英三; 石橋 裕 第66回土木計画学研究発表会・講演集, 2022-11 / Individuals reciprocate negative actions revealing negative upstream reciprocity Umetani Ryohei; Yamamoto Hitoshi; Goto Akira; Okada I... PLOS ONE/18(7), 2023-07-05 / SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. 名倉 卓弥; 秋山 英三 人工知能学会論文誌/38(4)/pp.B-N11_1-B-N11_9, 2023 / Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement Masaaki Inaba; 秋山 英三 SCIENTIFIC REPORTS/13(1), 2023-06-17 / Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim Ishibashi Yutaka; Akiyama Eizo 2022 IEEE International Conference on Big Data (Big Data), 2022-12 / パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 栗栖慶太; 秋山英三 シミュレーション＆ゲーミング/33(1)/pp.11-22, 2023 / 群淘汰状況下における罰則・報酬の進化 秋山 英三 信学技報/122(421)/pp.36-41, 2023-03 / Self-organized Speculation Game for the spontaneous emergence of financial stylized facts Katahira K.; Chen Y.; Akiyama Eizo Physica A/582, 2021-11 / 情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ 秋山 英三; 謝凡 人工知能学会論文, 2021-10 / 時間制約を導入したゴミ箱モデル 秋山 英三; 石田雄大 人工知能学会論文, 2021-10 / Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment Akiyama Eizo; Okada I.; Yamamoto H.; Toriumi F. Scientific Reports/11(1), 2021-04 / 協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 米納 弘渡; 秋山英三 JAWS2014, 2014-10 / A quantitative easing experiment Penalver Adrian; Hanaki Nobuyuki; Akiyama Eizo; Funaki... Journal of economic dynamics &amp; control/119, 2020-10 PubMed</t>
+          <t>ジレンマ状況における表情計測に基づく人の協力行動の分析. 小菅雷太朗; 秋山 英三; 山本仁志; 栗原聡 社会システムと情報技術研究ウィーク（WSSIT2026）, 2026 / Effects of a “Topic Diversification System” facilitating diverse topic exposure on topic interest and social media engage behavior. Nagura Takuya; AKIYAMA Eizo In Proceedings of the 2025 IEEE International Conference on Big Data (IEEE BigData 2025), 2025 / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. Inaba Masaaki; AKIYAMA Eizo PLOS Complex Systems/2(4), 2025 / Emergence of echo chambers in social media communication involving multiple topics. Nagura Takuya; AKIYAMA Eizo Information, Communication &amp; Society/28(6)/pp. 1099- 1120, 2025 / Partner selection biases induced by resource inequality. Umetani Ryohei; Yamamoto Hitoshi; AKIYAMA Eizo Social Sciences &amp; Humanities Open/12, 2025 / Influence of agent social and network segregation on fake news diffusion. Kitagawa Yuta; Akiyama Eizo In Proceedings of the 2025 IEEE International Conference on Big Data (IEEE BigData 2025), 2025-12 / 発話量と発話内容分析に基づく分断された集団間のコミュニケーション円滑化システムの提案 筒井律稀; 小菅雷太朗; 秋山 英三; 山本仁志; 荒牧大樹; 伊藤千輝; 栗原聡 2025年度人工知能学会全国大会（第39回）論文集, 2025/5 / Effect of Network Homophily and Partisanship on Social Media to "Oil Spill" Polarizations Nagura Takuya; Akiyama Eizo JASSS-THE JOURNAL OF ARTIFICIAL SOCIETIES AND SOCIAL SIMULATION/29(1), 2026-01-31 / Evolution of cooperation among migrating resource-oriented agents under environmental variability Inaba Masaaki; Akiyama Eizo CHAOS SOLITONS &amp; FRACTALS/202(2), 2026-01 / 検索連動型広告における循環的な入札額変動の発生機構の解明 河又 裕士; 张 晓泉; 秋山 英三 経営情報学会 全国研究発表大会要旨集/201906/pp.117-120, 2019 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07 / Bubbles in Asset Markets and the Heterogeneity of Beliefs. AKIYAMA Eizo; Funaki Yukihiko; Ishikawa Ryuichiro; Lah... Journal of Economic Behavior and Organization/236, 2025-08 / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 小菅雷太朗; 若林直希; 山本仁志; 秋山 英三; 栗原聡 行動変容と社会システム/10, 2024 / 進化ゲーム理論の進化 — マルチエージェントシミュレーション，実験室実験と，LLM の行動経済学— 秋山 英三 人工知能/39(3)/pp.323-329, 2024 / 発話量と発話内容に基づく集団間のコミュニケーション円滑化システムの提案 筒井律稀; 小菅雷太朗; 秋山 英三; 山本仁志; 荒牧大樹; 伊藤千輝; 栗原 聡 行動変容と社会システム/11, 2024 / ソーシャルメディア上のアジェンダ設定がエコーチェンバーの発生に与える影響について 名倉 卓弥; 秋山 英三 人工知能学会論文誌/39(6)/pp.p. AG24-A_1-8, 2024-11-1 / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. Inaba Masaaki; Akiyama Eizo PLOS Complex Systems/2(4), 2025-04 / Emergence of echo chambers in social media communication involving multiple topics Nagura Takuya; Akiyama Eizo INFORMATION COMMUNICATION &amp; SOCIETY/Epub/pp.1099-1120, 2025-01-28 / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 小菅雷太郎; 若林直希; 山本仁志; 栗原聡; 秋山 英三 行動変容と社会システム/10, 2024-3 / 進化ゲーム理論の進化：マルチエージェントシミュレーション, 実験室実験と，LLMの行動経済学 秋山 英三 人工知能学会論文誌/39(3)/pp.323-330, 2024-5 / 重みが動的なネットワークにおいてネットワーク構造が協力の進化に与える影響 栗栖 慶太; 秋山 英三 情報処理学会論文誌/65(1)/pp.61-68, 2024-1 / 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ 秋山 英三; 石橋 裕 第66回土木計画学研究発表会・講演集, 2022-11 / Individuals reciprocate negative actions revealing negative upstream reciprocity Umetani Ryohei; Yamamoto Hitoshi; Goto Akira; Okada I... PLOS ONE/18(7), 2023-07-05 / SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. 名倉 卓弥; 秋山 英三 人工知能学会論文誌/38(4)/pp.B-N11_1-B-N11_9, 2023 / Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement Masaaki Inaba; 秋山 英三 SCIENTIFIC REPORTS/13(1), 2023-06-17</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2653,12 +2660,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>社会システム工学・安全システム ; 保険・金融行動 ; 意思決定分析 ; マッチング理論・ゲーム理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
+          <t>社会システム工学・安全システム ; 保険・金融行動 ; 意思決定分析 ; マッチング理論・ゲーム理論 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2669,6 +2676,7 @@
 意思決定分析
 マッチング理論・ゲーム理論
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
@@ -2687,7 +2695,11 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2704,6 +2716,8 @@
 歩行者ラウンドアバウトによる整流効果-駅構内の混雑緩和-
 投機的リスク下でのピア効果がリスク態度に与える影響
 懲罰に関する社会規範が間接互恵の進化に与える影響について:シミュレーションによるアプローチ
+金融資産市場・リスク状況と社会的ジレンマ下での人間とAIの意思決定
+グリーン投資の意思決定メカニズムの実験的検証
 人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析
 新規投資家の継続的な参入が価格形成・価格変動に与える影響
 ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響
@@ -2712,8 +2726,15 @@
 市場参加者の価格予測の異質性と市場の振る舞いの関係について
 情報の非対称性と多様な期待形成がもたらす金融市場への影響とその安定化政策について
 国家の規模とガバナンスの学際的分析
-情報コストゼロ社会における過剰懲罰とリスク軽減のための社会制度設計
-新しい肺移植制度の構築と評価：ドナー交換移植の可能性
+ジレンマ状況における表情計測に基づく人の協力行動の分析. 小菅雷太朗; 秋山 英三; 山本仁志; 栗原聡 社会システムと情報技術研究ウィーク（WSSIT2026）, 2026
+Effects of a “Topic Diversification System” facilitating diverse topic exposure on topic interest and social media engage behavior. Nagura Takuya; AKIYAMA Eizo In Proceedings of the 2025 IEEE International Conference on Big Data (IEEE BigData 2025), 2025
+Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. Inaba Masaaki; AKIYAMA Eizo PLOS Complex Systems/2(4), 2025
+Emergence of echo chambers in social media communication involving multiple topics. Nagura Takuya; AKIYAMA Eizo Information, Communication &amp; Society/28(6)/pp. 1099- 1120, 2025
+Partner selection biases induced by resource inequality. Umetani Ryohei; Yamamoto Hitoshi; AKIYAMA Eizo Social Sciences &amp; Humanities Open/12, 2025
+Influence of agent social and network segregation on fake news diffusion. Kitagawa Yuta; Akiyama Eizo In Proceedings of the 2025 IEEE International Conference on Big Data (IEEE BigData 2025), 2025-12
+発話量と発話内容分析に基づく分断された集団間のコミュニケーション円滑化システムの提案 筒井律稀; 小菅雷太朗; 秋山 英三; 山本仁志; 荒牧大樹; 伊藤千輝; 栗原聡 2025年度人工知能学会全国大会（第39回）論文集, 2025/5
+Effect of Network Homophily and Partisanship on Social Media to "Oil Spill" Polarizations Nagura Takuya; Akiyama Eizo JASSS-THE JOURNAL OF ARTIFICIAL SOCIETIES AND SOCIAL SIMULATION/29(1), 2026-01-31
+Evolution of cooperation among migrating resource-oriented agents under environmental variability Inaba Masaaki; Akiyama Eizo CHAOS SOLITONS &amp; FRACTALS/202(2), 2026-01
 検索連動型広告における循環的な入札額変動の発生機構の解明 河又 裕士; 张 晓泉; 秋山 英三 経営情報学会 全国研究発表大会要旨集/201906/pp.117-120, 2019
 ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07
 Bubbles in Asset Markets and the Heterogeneity of Beliefs. AKIYAMA Eizo; Funaki Yukihiko; Ishikawa Ryuichiro; Lah... Journal of Economic Behavior and Organization/236, 2025-08
@@ -2729,16 +2750,7 @@
 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ 秋山 英三; 石橋 裕 第66回土木計画学研究発表会・講演集, 2022-11
 Individuals reciprocate negative actions revealing negative upstream reciprocity Umetani Ryohei; Yamamoto Hitoshi; Goto Akira; Okada I... PLOS ONE/18(7), 2023-07-05
 SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. 名倉 卓弥; 秋山 英三 人工知能学会論文誌/38(4)/pp.B-N11_1-B-N11_9, 2023
-Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement Masaaki Inaba; 秋山 英三 SCIENTIFIC REPORTS/13(1), 2023-06-17
-Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim Ishibashi Yutaka; Akiyama Eizo 2022 IEEE International Conference on Big Data (Big Data), 2022-12
-パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 栗栖慶太; 秋山英三 シミュレーション＆ゲーミング/33(1)/pp.11-22, 2023
-群淘汰状況下における罰則・報酬の進化 秋山 英三 信学技報/122(421)/pp.36-41, 2023-03
-Self-organized Speculation Game for the spontaneous emergence of financial stylized facts Katahira K.; Chen Y.; Akiyama Eizo Physica A/582, 2021-11
-情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ 秋山 英三; 謝凡 人工知能学会論文, 2021-10
-時間制約を導入したゴミ箱モデル 秋山 英三; 石田雄大 人工知能学会論文, 2021-10
-Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment Akiyama Eizo; Okada I.; Yamamoto H.; Toriumi F. Scientific Reports/11(1), 2021-04
-協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 米納 弘渡; 秋山英三 JAWS2014, 2014-10
-A quantitative easing experiment Penalver Adrian; Hanaki Nobuyuki; Akiyama Eizo; Funaki... Journal of economic dynamics &amp; control/119, 2020-10 PubMed</t>
+Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement Masaaki Inaba; 秋山 英三 SCIENTIFIC REPORTS/13(1), 2023-06-17</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2803,19 @@
 建築・都市計画史
 地中海都市
 ヘレニズム基盤
+イスラーム的都市形成
+西アジア
+中東・北アフリカ
 歴史文化保全
 国際協力
-中東・北アフリカ
-Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026
+Modernist Master Planning and Resident Adaptation in Abuja, Nigeria: a Historical Geography of Imposed Spatial Order,1976-2024 AKINKUNMI Priscilla; MATSUBARA Kosuke Planning Perspectives, 2026-04
+Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026-04
 フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― 戸田 理香子; 松原 康介 日本建築学会計画系論文集/91(840)/pp.351-362, 2026-02
 吉田正春使節団が見た19世紀テヘラン都市改造 松原 康介 都市計画論文集/60(3)/pp.532-539, 2025-10
+Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08
+Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08
+Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08
+The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08
 ジスカール・デスタン政権下のパリ歩行者空間整備 家城悠紀; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.415-416, 2025-08
 1960 年アガディール地震とその震災復興都市計画に関する研究 根岸美空; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.427-428, 2025-08
 フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 三重野馨; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.207-208, 2025-08
@@ -2805,20 +2824,15 @@
 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 瀨古希; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.541-542, 2025-08
 フェス 積み重なる寄進が形成した迷宮都市 松原 康介 建築知識/2025(7)/pp.84-85, 2025-6
 ガルダイア 丘の上の城塞とオアシス渓谷の集落 松原 康介 建築知識/2025(7)/pp.82-83, 2025-6
-Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08
-The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08
-Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08
-Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08
 カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- 渡邊 智也; 松原 康介 都市計画論文集/59(3)/pp.892-899, 2024-10
+The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10
 Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris FURUICHI Manako; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-15-6-1-D-15-6-4, 2024-09
 Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille YOSHIDA Yuno; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-5-5-1-D-5-5-4, 2024-09
-The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10
 アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 和田 夏音; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.321-322, 2024-08
+商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08
+19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08
 カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08
-カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08
-19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08
-商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08
-ビルマ王都マンダレーの城内および城外市街地の空間構造に関する研究 山田 耕治; 松原 康介 2023年度 日本建築学会大会［近畿］学術講演梗概集/pp.29-30, 2023-09</t>
+カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2833,12 +2847,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>建築・都市計画史 / 地中海都市 / ヘレニズム基盤 / 歴史文化保全 / 国際協力 / 中東・北アフリカ</t>
+          <t>建築・都市計画史 / 地中海都市 / ヘレニズム基盤 / イスラーム的都市形成 / 西アジア / 中東・北アフリカ / 歴史文化保全 / 国際協力</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026 / フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― 戸田 理香子; 松原 康介 日本建築学会計画系論文集/91(840)/pp.351-362, 2026-02 / 吉田正春使節団が見た19世紀テヘラン都市改造 松原 康介 都市計画論文集/60(3)/pp.532-539, 2025-10 / ジスカール・デスタン政権下のパリ歩行者空間整備 家城悠紀; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.415-416, 2025-08 / 1960 年アガディール地震とその震災復興都市計画に関する研究 根岸美空; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.427-428, 2025-08 / フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 三重野馨; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.207-208, 2025-08 / フェルナン・プイヨンのベルカステル村修復に関する研究 ─城と村の一体性に着目して─ 古市麻菜子; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.205-206, 2025-08 / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス 吉田悠乃; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.203-204, 2025-08 / 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 瀨古希; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.541-542, 2025-08 / フェス 積み重なる寄進が形成した迷宮都市 松原 康介 建築知識/2025(7)/pp.84-85, 2025-6 / ガルダイア 丘の上の城塞とオアシス渓谷の集落 松原 康介 建築知識/2025(7)/pp.82-83, 2025-6 / Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08 / The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08 / Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08 / Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08 / カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- 渡邊 智也; 松原 康介 都市計画論文集/59(3)/pp.892-899, 2024-10 / Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris FURUICHI Manako; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-15-6-1-D-15-6-4, 2024-09 / Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille YOSHIDA Yuno; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-5-5-1-D-5-5-4, 2024-09 / The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10 / アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 和田 夏音; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.321-322, 2024-08 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08 / 19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08 / 商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08 / ビルマ王都マンダレーの城内および城外市街地の空間構造に関する研究 山田 耕治; 松原 康介 2023年度 日本建築学会大会［近畿］学術講演梗概集/pp.29-30, 2023-09</t>
+          <t>Modernist Master Planning and Resident Adaptation in Abuja, Nigeria: a Historical Geography of Imposed Spatial Order,1976-2024 AKINKUNMI Priscilla; MATSUBARA Kosuke Planning Perspectives, 2026-04 / Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026-04 / フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― 戸田 理香子; 松原 康介 日本建築学会計画系論文集/91(840)/pp.351-362, 2026-02 / 吉田正春使節団が見た19世紀テヘラン都市改造 松原 康介 都市計画論文集/60(3)/pp.532-539, 2025-10 / Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08 / Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08 / Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08 / The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08 / ジスカール・デスタン政権下のパリ歩行者空間整備 家城悠紀; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.415-416, 2025-08 / 1960 年アガディール地震とその震災復興都市計画に関する研究 根岸美空; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.427-428, 2025-08 / フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 三重野馨; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.207-208, 2025-08 / フェルナン・プイヨンのベルカステル村修復に関する研究 ─城と村の一体性に着目して─ 古市麻菜子; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.205-206, 2025-08 / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス 吉田悠乃; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.203-204, 2025-08 / 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 瀨古希; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.541-542, 2025-08 / フェス 積み重なる寄進が形成した迷宮都市 松原 康介 建築知識/2025(7)/pp.84-85, 2025-6 / ガルダイア 丘の上の城塞とオアシス渓谷の集落 松原 康介 建築知識/2025(7)/pp.82-83, 2025-6 / カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- 渡邊 智也; 松原 康介 都市計画論文集/59(3)/pp.892-899, 2024-10 / The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10 / Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris FURUICHI Manako; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-15-6-1-D-15-6-4, 2024-09 / Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille YOSHIDA Yuno; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-5-5-1-D-5-5-4, 2024-09 / アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 和田 夏音; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.321-322, 2024-08 / 商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08 / 19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2864,9 +2878,11 @@
 建築・都市計画史
 地中海都市
 ヘレニズム基盤
+イスラーム的都市形成
+西アジア
+中東・北アフリカ
 歴史文化保全
 国際協力
-中東・北アフリカ
 都市・地域政策
 GIS・空間分析
 建築・空間設計
@@ -2912,9 +2928,14 @@
 国際交流を背景とした中東都市計画史研究と都市保全プロジェクトへの還元
 モロッコの歴史都市 フェスの保全と近代化
 現代イスラーム都市の多元的成り立ちに関する研究
-Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026
+Modernist Master Planning and Resident Adaptation in Abuja, Nigeria: a Historical Geography of Imposed Spatial Order,1976-2024 AKINKUNMI Priscilla; MATSUBARA Kosuke Planning Perspectives, 2026-04
+Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026-04
 フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― 戸田 理香子; 松原 康介 日本建築学会計画系論文集/91(840)/pp.351-362, 2026-02
 吉田正春使節団が見た19世紀テヘラン都市改造 松原 康介 都市計画論文集/60(3)/pp.532-539, 2025-10
+Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08
+Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08
+Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08
+The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08
 ジスカール・デスタン政権下のパリ歩行者空間整備 家城悠紀; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.415-416, 2025-08
 1960 年アガディール地震とその震災復興都市計画に関する研究 根岸美空; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.427-428, 2025-08
 フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 三重野馨; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.207-208, 2025-08
@@ -2923,20 +2944,15 @@
 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 瀨古希; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.541-542, 2025-08
 フェス 積み重なる寄進が形成した迷宮都市 松原 康介 建築知識/2025(7)/pp.84-85, 2025-6
 ガルダイア 丘の上の城塞とオアシス渓谷の集落 松原 康介 建築知識/2025(7)/pp.82-83, 2025-6
-Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08
-The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08
-Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08
-Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08
 カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- 渡邊 智也; 松原 康介 都市計画論文集/59(3)/pp.892-899, 2024-10
+The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10
 Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris FURUICHI Manako; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-15-6-1-D-15-6-4, 2024-09
 Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille YOSHIDA Yuno; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-5-5-1-D-5-5-4, 2024-09
-The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10
 アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 和田 夏音; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.321-322, 2024-08
+商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08
+19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08
 カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08
-カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08
-19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08
-商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08
-ビルマ王都マンダレーの城内および城外市街地の空間構造に関する研究 山田 耕治; 松原 康介 2023年度 日本建築学会大会［近畿］学術講演梗概集/pp.29-30, 2023-09</t>
+カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3394,8 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>まちづくりを含む不動産開発に関する指導
+          <t>外国人材との共生策と空間整備を組み合わせる都市計画手法の提言～少子高齢化・人口減少で生まれる空き空間の有効再活用～
+まちづくりを含む不動産開発に関する指導
 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究
 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会
 超高層住宅の二重の老いの潜在的課題に関する研究
@@ -3386,7 +3403,6 @@
 つくば市みどりの分譲地のまちづくり提案について
 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性
 スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築
-超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究
 都市計画・建築計画
 都市計画
 地区計画
@@ -3397,8 +3413,21 @@
 産官学民連携
 地域活性化
 コミュニティビジネス
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
+外国人集住と地域の受入れ支援 藤井 さやか 都市計画/373/pp.56-59, 2025-09
+外国人居住を考える：特集の趣旨 藤井 さやか 住宅/74(9)/pp.2-2, 2025-09
+地方創生と外国人受け入れの取組み(北海道東川町) 藤井 さやか 住宅/74(9)/pp.46-48, 2025-09
+外国人研究者受入れの取り組み(JST・二の宮ハウス) 藤井 さやか 住宅/74(9)/pp.30-33, 2025-09
+多様化する外国人の住まい 藤井 さやか 住宅/74(9)/pp.3-10, 2025-09
+複合的な福祉支援を要するペット多頭飼育崩壊解決に向けた多機関連携支援体制に関する研究 渡邊優樹; 藤井 さやか 2025福祉のまちづくり学会要旨集/pp.272-273, 2025-09-26
+工場立地法敷地外緑地制度の活用実態と課題に関する研究 飛田晴哉; 藤井 さやか 都市計画報告集/24(2)/pp.294-301, 2025-09
+滞留空間整備及び参加型WSによる公共空間の利用促進効果に関する研究 岩崎真由子; 藤井 さやか 都市計画報告集/24(2)/pp.370-376, 2025-09
+地方小都市中心市街地における遊休不動産の特性に応じた新規事業の成立要因に関する研究 根岸龍宏; 鳩貝優太; 藤井 さやか 都市計画論文集/60(3)/pp.961-968, 2025-10
+地域に開かれた福祉施設がケアラーに与える影響 篠原百合; 武田侑哉; 梁イェリム; 中島弘貴; 新雄太; 井上拓央; 渡部一郎; 古賀千絵; 藤井 さやか; ... 都市計画論文集/60(3)/pp.854-861, 2025-10
+ごちゃまぜを理念とする多機能型福祉拠点の利用実態と課題に関する研究 武田侑哉; 藤井 さやか 都市計画論文集/60(3)/pp.814-821, 2025-10
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10
+A framework for analyzing the role of living labs in smart cities: insights from a case study in Japan Park Jooho; Watanabe Kentaro; Akasaka Fumiya; Fujii S... DISCOVER SUSTAINABILITY/6(1), 2025-08-11
 わがまちのSDGs 小出 譲治; 田中 幹夫; 松尾 勝利; 小長井 義正; 藤井 さやか 市政/73(5)/pp.6-13, 2023-05
 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ 吉田 啓助; 吉武 麻子; 荒 昌史; 藤井 さやか; 柴田 建; 益田 信也; 池添 昌幸 都市住宅学/119・120/pp.126-144, 2024-12
 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 原科 幸彦; 藤井 さやか; 阿部 くらん; 大澤 義明; 大島 弘至; 山西 康孝; 森川 晶; ... 日本不動産学会誌/38(1)/pp.26-49, 2024-06
@@ -3408,25 +3437,12 @@
 住宅団地の外国人集住：特集の趣旨 藤井 さやか 住宅/73(5)/p.2, 2024-05
 住宅地における地区計画や認可協定の今後 藤井 さやか 家とまちなみ/43(1)/pp.8-13, 2024-05
 区分所有マンションを含む市街地再開発事業の有効空地を考える 藤井 さやか 再開発コーディネーター/234/pp.31-31, 2025-03
-社会的包摂とデザイン─「つながる場」15事例の実践から 藤井 さやか; 後藤智香子 都市計画/373/pp.54-57, 2025-03
-外国人住民との共存・共生: 海外の事例からの示唆 藤井 さやか 都市問題/115(12)/pp.11-16, 2024-12
-首都圏郊外におけるリノベーションまちづくりの成果と課題に関する研究 鳩貝優太; 藤井 さやか 都市計画論文集/59(3)/pp.1391-1398, 2024-10
-住宅建替えと一体的に再整備された街区公園の維持管理活動を通じたコミュニティ形成に関する研究 大森聡; 藤井 さやか 都市計画論文集/59(3)/pp.714-721, 2024-10
-計画的戸建住宅地における駐車場シェアの導入意向と活用可能性に関する研究 佐藤 耀; 根岸 龍宏; 藤井 さやか 都市計画論文集/59(3)/pp.752-759, 2024-10
-多様な主体が関わる出産祝いプロジェクトの成立経緯と参加主体にもたらす変化に関する研究 石川夏帆; 藤井 さやか 都市計画論文集/59(3)/pp.1383-1388, 2024-10
-職員の活躍を願う市長の思いと取り組み 品川萬里; 北村 正平; 瀧澤智子; 玉井敏久; 藤井 さやか 市政/72(5)/pp.6-11, 2023-05
-今後の地域づくりへの期待 藤井 さやか 人と国土21/49(5)/pp.44-44, 2024-01
-Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea Park Jooho; Fujii Sayaka Urban Planning/8(2)/pp.93-107, 2023-04
-転換期にある筑波研究学園都市の地区計画が空間資源継承に果たす役割と課題 瀬川遥子; 島田由美子; 藤井 さやか 都市計画論文集/58(3)/pp.1187-1192, 2023-10
-1980年以降、40年の「つくば」の変化と現状 藤井 さやか 建築ジャーナル/1334/pp.15-18, 2022-09
-Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea, Urban Planning Park Jooho; Fujii Sayaka URBAN PLANNING/8(2)/pp.93-107, 2023-04
-Living Lab Participants’ Knowledge Change about Inclusive Smart Cities: An Urban Living Lab in Seongdaegol, Seoul, South Korea Park Jooho; Fujii Sayaka Smart Cities/5(4)/pp.1376-1388, 2022-10
-地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究 板橋奈央; 藤井 さやか; 島田由美子 都市計画論文集/57(3)/pp.1347-1354, 2022-11</t>
+社会的包摂とデザイン─「つながる場」15事例の実践から 藤井 さやか; 後藤智香子 都市計画/373/pp.54-57, 2025-03</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>まちづくりを含む不動産開発に関する指導 / 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 超高層住宅の二重の老いの潜在的課題に関する研究 / 社会的孤独の解消モデル事例のプロセス分析及び検証手法の検討 / つくば市みどりの分譲地のまちづくり提案について / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築 / 超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究</t>
+          <t>外国人材との共生策と空間整備を組み合わせる都市計画手法の提言～少子高齢化・人口減少で生まれる空き空間の有効再活用～ / まちづくりを含む不動産開発に関する指導 / 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 超高層住宅の二重の老いの潜在的課題に関する研究 / 社会的孤独の解消モデル事例のプロセス分析及び検証手法の検討 / つくば市みどりの分譲地のまちづくり提案について / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3441,7 +3457,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10 / わがまちのSDGs 小出 譲治; 田中 幹夫; 松尾 勝利; 小長井 義正; 藤井 さやか 市政/73(5)/pp.6-13, 2023-05 / 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ 吉田 啓助; 吉武 麻子; 荒 昌史; 藤井 さやか; 柴田 建; 益田 信也; 池添 昌幸 都市住宅学/119・120/pp.126-144, 2024-12 / 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 原科 幸彦; 藤井 さやか; 阿部 くらん; 大澤 義明; 大島 弘至; 山西 康孝; 森川 晶; ... 日本不動産学会誌/38(1)/pp.26-49, 2024-06 / 京都市東松ノ木市営住宅 村木美都子; 藤井 さやか 住宅/73(5)/pp.13-19, 2024-05 / 国勢調査分析からみる外国人集住団地の実態 藤井 さやか; 王爽 住宅/73(5)/pp.9-12, 2024-05 / 増加する外国人の受け皿としての住宅団地 藤井 さやか 住宅/73(5)/pp.3-8, 2024-05 / 住宅団地の外国人集住：特集の趣旨 藤井 さやか 住宅/73(5)/p.2, 2024-05 / 住宅地における地区計画や認可協定の今後 藤井 さやか 家とまちなみ/43(1)/pp.8-13, 2024-05 / 区分所有マンションを含む市街地再開発事業の有効空地を考える 藤井 さやか 再開発コーディネーター/234/pp.31-31, 2025-03 / 社会的包摂とデザイン─「つながる場」15事例の実践から 藤井 さやか; 後藤智香子 都市計画/373/pp.54-57, 2025-03 / 外国人住民との共存・共生: 海外の事例からの示唆 藤井 さやか 都市問題/115(12)/pp.11-16, 2024-12 / 首都圏郊外におけるリノベーションまちづくりの成果と課題に関する研究 鳩貝優太; 藤井 さやか 都市計画論文集/59(3)/pp.1391-1398, 2024-10 / 住宅建替えと一体的に再整備された街区公園の維持管理活動を通じたコミュニティ形成に関する研究 大森聡; 藤井 さやか 都市計画論文集/59(3)/pp.714-721, 2024-10 / 計画的戸建住宅地における駐車場シェアの導入意向と活用可能性に関する研究 佐藤 耀; 根岸 龍宏; 藤井 さやか 都市計画論文集/59(3)/pp.752-759, 2024-10 / 多様な主体が関わる出産祝いプロジェクトの成立経緯と参加主体にもたらす変化に関する研究 石川夏帆; 藤井 さやか 都市計画論文集/59(3)/pp.1383-1388, 2024-10 / 職員の活躍を願う市長の思いと取り組み 品川萬里; 北村 正平; 瀧澤智子; 玉井敏久; 藤井 さやか 市政/72(5)/pp.6-11, 2023-05 / 今後の地域づくりへの期待 藤井 さやか 人と国土21/49(5)/pp.44-44, 2024-01 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea Park Jooho; Fujii Sayaka Urban Planning/8(2)/pp.93-107, 2023-04 / 転換期にある筑波研究学園都市の地区計画が空間資源継承に果たす役割と課題 瀬川遥子; 島田由美子; 藤井 さやか 都市計画論文集/58(3)/pp.1187-1192, 2023-10 / 1980年以降、40年の「つくば」の変化と現状 藤井 さやか 建築ジャーナル/1334/pp.15-18, 2022-09 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea, Urban Planning Park Jooho; Fujii Sayaka URBAN PLANNING/8(2)/pp.93-107, 2023-04 / Living Lab Participants’ Knowledge Change about Inclusive Smart Cities: An Urban Living Lab in Seongdaegol, Seoul, South Korea Park Jooho; Fujii Sayaka Smart Cities/5(4)/pp.1376-1388, 2022-10 / 地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究 板橋奈央; 藤井 さやか; 島田由美子 都市計画論文集/57(3)/pp.1347-1354, 2022-11</t>
+          <t>大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / 外国人集住と地域の受入れ支援 藤井 さやか 都市計画/373/pp.56-59, 2025-09 / 外国人居住を考える：特集の趣旨 藤井 さやか 住宅/74(9)/pp.2-2, 2025-09 / 地方創生と外国人受け入れの取組み(北海道東川町) 藤井 さやか 住宅/74(9)/pp.46-48, 2025-09 / 外国人研究者受入れの取り組み(JST・二の宮ハウス) 藤井 さやか 住宅/74(9)/pp.30-33, 2025-09 / 多様化する外国人の住まい 藤井 さやか 住宅/74(9)/pp.3-10, 2025-09 / 複合的な福祉支援を要するペット多頭飼育崩壊解決に向けた多機関連携支援体制に関する研究 渡邊優樹; 藤井 さやか 2025福祉のまちづくり学会要旨集/pp.272-273, 2025-09-26 / 工場立地法敷地外緑地制度の活用実態と課題に関する研究 飛田晴哉; 藤井 さやか 都市計画報告集/24(2)/pp.294-301, 2025-09 / 滞留空間整備及び参加型WSによる公共空間の利用促進効果に関する研究 岩崎真由子; 藤井 さやか 都市計画報告集/24(2)/pp.370-376, 2025-09 / 地方小都市中心市街地における遊休不動産の特性に応じた新規事業の成立要因に関する研究 根岸龍宏; 鳩貝優太; 藤井 さやか 都市計画論文集/60(3)/pp.961-968, 2025-10 / 地域に開かれた福祉施設がケアラーに与える影響 篠原百合; 武田侑哉; 梁イェリム; 中島弘貴; 新雄太; 井上拓央; 渡部一郎; 古賀千絵; 藤井 さやか; ... 都市計画論文集/60(3)/pp.854-861, 2025-10 / ごちゃまぜを理念とする多機能型福祉拠点の利用実態と課題に関する研究 武田侑哉; 藤井 さやか 都市計画論文集/60(3)/pp.814-821, 2025-10 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10 / A framework for analyzing the role of living labs in smart cities: insights from a case study in Japan Park Jooho; Watanabe Kentaro; Akasaka Fumiya; Fujii S... DISCOVER SUSTAINABILITY/6(1), 2025-08-11 / わがまちのSDGs 小出 譲治; 田中 幹夫; 松尾 勝利; 小長井 義正; 藤井 さやか 市政/73(5)/pp.6-13, 2023-05 / 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ 吉田 啓助; 吉武 麻子; 荒 昌史; 藤井 さやか; 柴田 建; 益田 信也; 池添 昌幸 都市住宅学/119・120/pp.126-144, 2024-12 / 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 原科 幸彦; 藤井 さやか; 阿部 くらん; 大澤 義明; 大島 弘至; 山西 康孝; 森川 晶; ... 日本不動産学会誌/38(1)/pp.26-49, 2024-06 / 京都市東松ノ木市営住宅 村木美都子; 藤井 さやか 住宅/73(5)/pp.13-19, 2024-05 / 国勢調査分析からみる外国人集住団地の実態 藤井 さやか; 王爽 住宅/73(5)/pp.9-12, 2024-05 / 増加する外国人の受け皿としての住宅団地 藤井 さやか 住宅/73(5)/pp.3-8, 2024-05 / 住宅団地の外国人集住：特集の趣旨 藤井 さやか 住宅/73(5)/p.2, 2024-05 / 住宅地における地区計画や認可協定の今後 藤井 さやか 家とまちなみ/43(1)/pp.8-13, 2024-05 / 区分所有マンションを含む市街地再開発事業の有効空地を考える 藤井 さやか 再開発コーディネーター/234/pp.31-31, 2025-03 / 社会的包摂とデザイン─「つながる場」15事例の実践から 藤井 さやか; 後藤智香子 都市計画/373/pp.54-57, 2025-03</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -3451,12 +3467,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>都市計画・建築計画 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>都市計画・建築計画 ; 家族・人口政策 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -3471,6 +3487,7 @@
 産官学民連携
 地域活性化
 コミュニティビジネス
+家族・人口政策
 都市・地域政策
 GIS・空間分析
 建築・空間設計
@@ -3479,6 +3496,10 @@
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
+家族の経済学
+少子化対策
+人口政策
+家計意思決定
 都市経済
 地域政策
 土地利用
@@ -3513,6 +3534,7 @@
 ごちゃまぜを理念とする多機能型福祉拠点の成立要因と意義に関する研究 －石川県社会福祉法人佛子園「三草二木 西圓寺」を対象として－
 移住増加地域における遊休不動産を活用した新規事業の成立要因に関する研究 －長野県小諸市中心市街地を対象として－
 超高層住宅集積地における利活用・維持管理の実態を踏まえた公開空地等の課題に関する研究 －東京都中央区第3ゾーンを対象として－
+外国人材との共生策と空間整備を組み合わせる都市計画手法の提言～少子高齢化・人口減少で生まれる空き空間の有効再活用～
 まちづくりを含む不動産開発に関する指導
 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究
 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会
@@ -3521,9 +3543,21 @@
 つくば市みどりの分譲地のまちづくり提案について
 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性
 スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築
-超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
+外国人集住と地域の受入れ支援 藤井 さやか 都市計画/373/pp.56-59, 2025-09
+外国人居住を考える：特集の趣旨 藤井 さやか 住宅/74(9)/pp.2-2, 2025-09
+地方創生と外国人受け入れの取組み(北海道東川町) 藤井 さやか 住宅/74(9)/pp.46-48, 2025-09
+外国人研究者受入れの取り組み(JST・二の宮ハウス) 藤井 さやか 住宅/74(9)/pp.30-33, 2025-09
+多様化する外国人の住まい 藤井 さやか 住宅/74(9)/pp.3-10, 2025-09
+複合的な福祉支援を要するペット多頭飼育崩壊解決に向けた多機関連携支援体制に関する研究 渡邊優樹; 藤井 さやか 2025福祉のまちづくり学会要旨集/pp.272-273, 2025-09-26
+工場立地法敷地外緑地制度の活用実態と課題に関する研究 飛田晴哉; 藤井 さやか 都市計画報告集/24(2)/pp.294-301, 2025-09
+滞留空間整備及び参加型WSによる公共空間の利用促進効果に関する研究 岩崎真由子; 藤井 さやか 都市計画報告集/24(2)/pp.370-376, 2025-09
+地方小都市中心市街地における遊休不動産の特性に応じた新規事業の成立要因に関する研究 根岸龍宏; 鳩貝優太; 藤井 さやか 都市計画論文集/60(3)/pp.961-968, 2025-10
+地域に開かれた福祉施設がケアラーに与える影響 篠原百合; 武田侑哉; 梁イェリム; 中島弘貴; 新雄太; 井上拓央; 渡部一郎; 古賀千絵; 藤井 さやか; ... 都市計画論文集/60(3)/pp.854-861, 2025-10
+ごちゃまぜを理念とする多機能型福祉拠点の利用実態と課題に関する研究 武田侑哉; 藤井 さやか 都市計画論文集/60(3)/pp.814-821, 2025-10
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10
+A framework for analyzing the role of living labs in smart cities: insights from a case study in Japan Park Jooho; Watanabe Kentaro; Akasaka Fumiya; Fujii S... DISCOVER SUSTAINABILITY/6(1), 2025-08-11
 わがまちのSDGs 小出 譲治; 田中 幹夫; 松尾 勝利; 小長井 義正; 藤井 さやか 市政/73(5)/pp.6-13, 2023-05
 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ 吉田 啓助; 吉武 麻子; 荒 昌史; 藤井 さやか; 柴田 建; 益田 信也; 池添 昌幸 都市住宅学/119・120/pp.126-144, 2024-12
 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 原科 幸彦; 藤井 さやか; 阿部 くらん; 大澤 義明; 大島 弘至; 山西 康孝; 森川 晶; ... 日本不動産学会誌/38(1)/pp.26-49, 2024-06
@@ -3533,20 +3567,7 @@
 住宅団地の外国人集住：特集の趣旨 藤井 さやか 住宅/73(5)/p.2, 2024-05
 住宅地における地区計画や認可協定の今後 藤井 さやか 家とまちなみ/43(1)/pp.8-13, 2024-05
 区分所有マンションを含む市街地再開発事業の有効空地を考える 藤井 さやか 再開発コーディネーター/234/pp.31-31, 2025-03
-社会的包摂とデザイン─「つながる場」15事例の実践から 藤井 さやか; 後藤智香子 都市計画/373/pp.54-57, 2025-03
-外国人住民との共存・共生: 海外の事例からの示唆 藤井 さやか 都市問題/115(12)/pp.11-16, 2024-12
-首都圏郊外におけるリノベーションまちづくりの成果と課題に関する研究 鳩貝優太; 藤井 さやか 都市計画論文集/59(3)/pp.1391-1398, 2024-10
-住宅建替えと一体的に再整備された街区公園の維持管理活動を通じたコミュニティ形成に関する研究 大森聡; 藤井 さやか 都市計画論文集/59(3)/pp.714-721, 2024-10
-計画的戸建住宅地における駐車場シェアの導入意向と活用可能性に関する研究 佐藤 耀; 根岸 龍宏; 藤井 さやか 都市計画論文集/59(3)/pp.752-759, 2024-10
-多様な主体が関わる出産祝いプロジェクトの成立経緯と参加主体にもたらす変化に関する研究 石川夏帆; 藤井 さやか 都市計画論文集/59(3)/pp.1383-1388, 2024-10
-職員の活躍を願う市長の思いと取り組み 品川萬里; 北村 正平; 瀧澤智子; 玉井敏久; 藤井 さやか 市政/72(5)/pp.6-11, 2023-05
-今後の地域づくりへの期待 藤井 さやか 人と国土21/49(5)/pp.44-44, 2024-01
-Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea Park Jooho; Fujii Sayaka Urban Planning/8(2)/pp.93-107, 2023-04
-転換期にある筑波研究学園都市の地区計画が空間資源継承に果たす役割と課題 瀬川遥子; 島田由美子; 藤井 さやか 都市計画論文集/58(3)/pp.1187-1192, 2023-10
-1980年以降、40年の「つくば」の変化と現状 藤井 さやか 建築ジャーナル/1334/pp.15-18, 2022-09
-Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea, Urban Planning Park Jooho; Fujii Sayaka URBAN PLANNING/8(2)/pp.93-107, 2023-04
-Living Lab Participants’ Knowledge Change about Inclusive Smart Cities: An Urban Living Lab in Seongdaegol, Seoul, South Korea Park Jooho; Fujii Sayaka Smart Cities/5(4)/pp.1376-1388, 2022-10
-地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究 板橋奈央; 藤井 さやか; 島田由美子 都市計画論文集/57(3)/pp.1347-1354, 2022-11</t>
+社会的包摂とデザイン─「つながる場」15事例の実践から 藤井 さやか; 後藤智香子 都市計画/373/pp.54-57, 2025-03</t>
         </is>
       </c>
     </row>
@@ -3600,6 +3621,19 @@
 空き家
 廃校
 地域組織
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
+現代板倉構法の普及実態と木材生産・供給体制に関する研究 その２−木材生産・供給体制の事例分析及びコスト分析− 岡原 玄八; 石井 裕樹; 山本 幸子 日本建築学会大会学術講演梗概集/pp.1025-1026, 2025-09
+現代板倉構法の普及実態と木材生産・供給体制に関する研究 その１−板倉の実績調査結果より− 石井 裕樹; 岡原 玄八; 山本 幸子 日本建築学会大会学術講演梗概集/pp.1023-1024, 2025-09
+農村移住者の宿泊滞在施設の運営と地域交流活動の実態―全国のゲストハウスを対象として― 山本 幸子; 大庭 知子 日本建築学会大会学術講演梗概集/pp.85-86, 2025-09
+離島における若者移住者の定住プロセスと要因に関する研究 伊豆大島を対象としたヒアリングに基づく分析 朝賀 史織; 山本 幸子 2025年度農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.49-50, 2025-11
+太陽光パネルに関する条例内容とパネル設置状況・地域的特徴との関連分析 石井 裕樹; 山本 幸子 2025年度農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.27-28, 2025-11
+農村地域の民泊の背景と動向 山本 幸子 住宅/pp.29-34, 2019-11
+空き家相談会記録から見る空家活用阻害要因 山本 幸子 JIR NEWS/pp.10-13, 2025-08
+茨城県利根町の戸建住宅地空き家の日本語学校寄宿舎への転用 廣谷 泰斗; 山本 幸子 住宅/pp.34-30, 2025-09
+座談会：近接分野からみた造園・ランドスケープ分野の見え方と期待 村山 顕人; 寺田 徹; 三輪 隆; 真田 純子; 山本 幸子; 曽我 昌史; 吉永 明弘 ランドスケープ研究/89(1)/pp.50-53, 2025-05-01
+戸建て住宅空き家を活用した外国人留学生寄宿舎の整備手法と地域への影響 廣谷 泰斗; 山本 幸子 日本建築学会住宅系研究報告会論文集/(20)/pp.287-296, 2025-12
+木造民家を活用した高齢者通所介護施設の空間用途構成に関する研究（その２）：主用途が１室で行われる施設の空間構成と使われ方 三島 幸子; 山本 幸子; 細田 智久; 中園 眞人 日本建築学会計画系論文集/91(841)/pp.544-555, 2026-03-01
+地域組織による移住・定住支援の運営体制と効果 齊藤 啓誠; 山本 幸子 日本建築学会計画系論文集/91(843)/pp.1031-1040, 2026-05-01
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 農山村地域に立地するゲストハウスの地域活性化に向けた取り組み 九州・中国・四国地方の基礎調査 牛見佳乃子; 大庭知子; 山本 幸子 日本建築学会九州支部研究報告/(64)/pp.53-56, 2025-3
 地域おこし協力隊の任期終了後の定住率と進路及び地域特性との関連分析 全国の自治体データを対象として 小林 正英; 山本 幸子 農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.55-56, 2024-11-30
@@ -3611,20 +3645,7 @@
 農村地域の宿泊滞在施設における地域交流活動の実態調査−九州・中国・四国地方のシェアハウスを対象として− 大庭 知子; 山本 幸子 日本建築学会大会学術講演梗概集/pp.25-26, 2024/8
 北関東地域における高齢者通所介護サービスの需給構造と将来推計（その1）：利用者数と供給量の推移を指標とした県別市場特性分析（2000～2019） 陳 星; 山本 幸子; 中園 眞人 日本建築学会計画系論文集/89(815)/pp.76-86, 2024-01-01
 農村集落の電力オフグリッド化の可能性に関する研究―石岡市上山集落を対象として― 石井 裕樹; 山本 幸子 農村計画学会秋季大会/p.8, 2023-12-10
-市町村合併により生じた旧市街地の振興における行政支援の手法について－つくば市周辺市街地振興における地域運営組織と外部人材との協働支援を事例として－ 吉岡誠生; 山本 幸子 都市計画報告集/21(2)/pp.153-159, 2022-12
-関係人口の居住地と訪問先との距離が地域とのかかわり方に与える影響－茨城県を対象として－ 古屋昂; 山本 幸子 日本建築学会大会学術講演梗概集（計画系）/pp.69-77, 2022-07
-多様な主体が連携する「新しい内発的発展」を支える地方自治体の取り組みについて－つくば市周辺市街地振興を事例として－ 吉岡誠生; 山本 幸子 日本建築学会大会学術講演梗概集（計画系）/pp.1055-1056, 2022-07
-木造民家を活用した高齢者通所介護施設の空間用途構成に関する研究（その1）：民家の平面構成と主用途の空間配置 山本 幸子; 三島 幸子; 中園 眞人 日本建築学会計画系論文集/87(793)/pp.521-532, 2022-03-01 CiNii
-現代建築への茅葺きの導入可能性に関する研究 福山 夏映; 山本 幸子 日本建築学会技術報告集/28(68)/pp.380-384, 2022-02-20 CiNii
-木造公共建築の用途と建築規模による特徴把握と実現手法の分析 新建築掲載事例を対象として 歌代 友哉; 山本 幸子 日本建築学会大会（東海）学術講演会梗概集/pp.399-400, 2021-9
-現代の茅葺き構法に関する研究−兵庫県神戸市の事例を対象として− 福山 夏映; 山本 幸子 日本建築学会大会（東海）学術講演会梗概集/pp.447-448, 2021-9
-既存建築を活用した自立高齢者地域支援拠点の運営形態と平面構成—土浦市「生きがい対応型デイサービス事業」を対象として— 稲石 渓太; 山本 幸子 日本建築学会大会（東海）学術講演会梗概集/pp.765-766, 2021-9
-大規模高齢者通所介護施設における主室の用途構成と使われ方 中園眞人; 三島幸子; 山本 幸子 日本建築学会計画系論文集/(782)/pp.1212-1223, 2021-04
-萩市における医療法人による高齢者福祉施設の整備運営に関する事例研究（その２）：木造民家を改修した通所介護・介護予防施設の使われ方 中園 眞人; 三島 幸子; 瀬戸口 佳奈美; 山本 幸子 日本建築学会計画系論文集/781/pp.717-726, 2021-03
-食堂兼機能訓練室と和室が一体的に構成された小規模高齢者通所介護施設の使われ方 中園 眞人; 三島 幸子; 山本 幸子 日本建築学会計画系論文集/780/pp.403-412, 2021-02
-社会福祉協議会による中山間地域における高齢者福祉施設の整備運営の取組み（その２）：下関市社会福祉協議会による中山間地域における高齢者福祉施設の整備プロセス 三島 幸子; 中園眞人; 山本 幸子 日本建築学会計画系論文集/778/pp.2573-2581, 2020-12
-農村系長屋門の利用の変遷と利活用実態 茨城県つくば市桜地区を対象として 山根 知; 山本 幸子 日本建築学会大会学術講演梗概集/(E-2分冊)/pp.111-112, 2020-09
-既存建築ストックを活用したサテライトオフィスの誘致プロセスとその実態 福井県鯖江市を対象として 齊藤啓誠; 山本 幸子 日本建築学会大会学術講演梗概集/(E-2分冊)/pp.57-58, 2020-09</t>
+市町村合併により生じた旧市街地の振興における行政支援の手法について－つくば市周辺市街地振興における地域運営組織と外部人材との協働支援を事例として－ 吉岡誠生; 山本 幸子 都市計画報告集/21(2)/pp.153-159, 2022-12</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3644,7 +3665,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 農山村地域に立地するゲストハウスの地域活性化に向けた取り組み 九州・中国・四国地方の基礎調査 牛見佳乃子; 大庭知子; 山本 幸子 日本建築学会九州支部研究報告/(64)/pp.53-56, 2025-3 / 地域おこし協力隊の任期終了後の定住率と進路及び地域特性との関連分析 全国の自治体データを対象として 小林 正英; 山本 幸子 農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.55-56, 2024-11-30 / 農地における規模別の太陽光パネル設置要因の分析 石井 裕樹; 山本 幸子 農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.41-42, 2024-11-30 / 自治体担当課による地域コミュニティ活動のフォローアップと施策立案に関する研究 都市的地域と農村地域が合併した自治体を対象として 吉岡 誠生; 山本 幸子 農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.27-28, 2024-11-30 / 北関東地域における高齢者通所介護サービスの需給構造と将来推計(その2)：市場均衡条件を組込んだ需要供給量推計（2020～2045） 陳 星; 山本 幸子; 中園眞人 日本建築学会計画系論文集/(824)/pp.1942-1951, 2024/10 / 木造板倉仮設住宅の再利用事例における平面構成の変化と住まい方 小野寺 七海; 山本 幸子 日本建築学会大会学術講演梗概集, 2024/8 / 移住者主体による交流の場の形成過程と効果−茨城県石岡市八郷地域を事例として− 関 梢子; 山本 幸子 日本建築学会大会学術講演梗概集/pp.121-122, 2024/8 / 農村地域の宿泊滞在施設における地域交流活動の実態調査−九州・中国・四国地方のシェアハウスを対象として− 大庭 知子; 山本 幸子 日本建築学会大会学術講演梗概集/pp.25-26, 2024/8 / 北関東地域における高齢者通所介護サービスの需給構造と将来推計（その1）：利用者数と供給量の推移を指標とした県別市場特性分析（2000～2019） 陳 星; 山本 幸子; 中園 眞人 日本建築学会計画系論文集/89(815)/pp.76-86, 2024-01-01 / 農村集落の電力オフグリッド化の可能性に関する研究―石岡市上山集落を対象として― 石井 裕樹; 山本 幸子 農村計画学会秋季大会/p.8, 2023-12-10 / 市町村合併により生じた旧市街地の振興における行政支援の手法について－つくば市周辺市街地振興における地域運営組織と外部人材との協働支援を事例として－ 吉岡誠生; 山本 幸子 都市計画報告集/21(2)/pp.153-159, 2022-12 / 関係人口の居住地と訪問先との距離が地域とのかかわり方に与える影響－茨城県を対象として－ 古屋昂; 山本 幸子 日本建築学会大会学術講演梗概集（計画系）/pp.69-77, 2022-07 / 多様な主体が連携する「新しい内発的発展」を支える地方自治体の取り組みについて－つくば市周辺市街地振興を事例として－ 吉岡誠生; 山本 幸子 日本建築学会大会学術講演梗概集（計画系）/pp.1055-1056, 2022-07 / 木造民家を活用した高齢者通所介護施設の空間用途構成に関する研究（その1）：民家の平面構成と主用途の空間配置 山本 幸子; 三島 幸子; 中園 眞人 日本建築学会計画系論文集/87(793)/pp.521-532, 2022-03-01 CiNii / 現代建築への茅葺きの導入可能性に関する研究 福山 夏映; 山本 幸子 日本建築学会技術報告集/28(68)/pp.380-384, 2022-02-20 CiNii / 木造公共建築の用途と建築規模による特徴把握と実現手法の分析 新建築掲載事例を対象として 歌代 友哉; 山本 幸子 日本建築学会大会（東海）学術講演会梗概集/pp.399-400, 2021-9 / 現代の茅葺き構法に関する研究−兵庫県神戸市の事例を対象として− 福山 夏映; 山本 幸子 日本建築学会大会（東海）学術講演会梗概集/pp.447-448, 2021-9 / 既存建築を活用した自立高齢者地域支援拠点の運営形態と平面構成—土浦市「生きがい対応型デイサービス事業」を対象として— 稲石 渓太; 山本 幸子 日本建築学会大会（東海）学術講演会梗概集/pp.765-766, 2021-9 / 大規模高齢者通所介護施設における主室の用途構成と使われ方 中園眞人; 三島幸子; 山本 幸子 日本建築学会計画系論文集/(782)/pp.1212-1223, 2021-04 / 萩市における医療法人による高齢者福祉施設の整備運営に関する事例研究（その２）：木造民家を改修した通所介護・介護予防施設の使われ方 中園 眞人; 三島 幸子; 瀬戸口 佳奈美; 山本 幸子 日本建築学会計画系論文集/781/pp.717-726, 2021-03 / 食堂兼機能訓練室と和室が一体的に構成された小規模高齢者通所介護施設の使われ方 中園 眞人; 三島 幸子; 山本 幸子 日本建築学会計画系論文集/780/pp.403-412, 2021-02 / 社会福祉協議会による中山間地域における高齢者福祉施設の整備運営の取組み（その２）：下関市社会福祉協議会による中山間地域における高齢者福祉施設の整備プロセス 三島 幸子; 中園眞人; 山本 幸子 日本建築学会計画系論文集/778/pp.2573-2581, 2020-12 / 農村系長屋門の利用の変遷と利活用実態 茨城県つくば市桜地区を対象として 山根 知; 山本 幸子 日本建築学会大会学術講演梗概集/(E-2分冊)/pp.111-112, 2020-09 / 既存建築ストックを活用したサテライトオフィスの誘致プロセスとその実態 福井県鯖江市を対象として 齊藤啓誠; 山本 幸子 日本建築学会大会学術講演梗概集/(E-2分冊)/pp.57-58, 2020-09</t>
+          <t>大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / 現代板倉構法の普及実態と木材生産・供給体制に関する研究 その２−木材生産・供給体制の事例分析及びコスト分析− 岡原 玄八; 石井 裕樹; 山本 幸子 日本建築学会大会学術講演梗概集/pp.1025-1026, 2025-09 / 現代板倉構法の普及実態と木材生産・供給体制に関する研究 その１−板倉の実績調査結果より− 石井 裕樹; 岡原 玄八; 山本 幸子 日本建築学会大会学術講演梗概集/pp.1023-1024, 2025-09 / 農村移住者の宿泊滞在施設の運営と地域交流活動の実態―全国のゲストハウスを対象として― 山本 幸子; 大庭 知子 日本建築学会大会学術講演梗概集/pp.85-86, 2025-09 / 離島における若者移住者の定住プロセスと要因に関する研究 伊豆大島を対象としたヒアリングに基づく分析 朝賀 史織; 山本 幸子 2025年度農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.49-50, 2025-11 / 太陽光パネルに関する条例内容とパネル設置状況・地域的特徴との関連分析 石井 裕樹; 山本 幸子 2025年度農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.27-28, 2025-11 / 農村地域の民泊の背景と動向 山本 幸子 住宅/pp.29-34, 2019-11 / 空き家相談会記録から見る空家活用阻害要因 山本 幸子 JIR NEWS/pp.10-13, 2025-08 / 茨城県利根町の戸建住宅地空き家の日本語学校寄宿舎への転用 廣谷 泰斗; 山本 幸子 住宅/pp.34-30, 2025-09 / 座談会：近接分野からみた造園・ランドスケープ分野の見え方と期待 村山 顕人; 寺田 徹; 三輪 隆; 真田 純子; 山本 幸子; 曽我 昌史; 吉永 明弘 ランドスケープ研究/89(1)/pp.50-53, 2025-05-01 / 戸建て住宅空き家を活用した外国人留学生寄宿舎の整備手法と地域への影響 廣谷 泰斗; 山本 幸子 日本建築学会住宅系研究報告会論文集/(20)/pp.287-296, 2025-12 / 木造民家を活用した高齢者通所介護施設の空間用途構成に関する研究（その２）：主用途が１室で行われる施設の空間構成と使われ方 三島 幸子; 山本 幸子; 細田 智久; 中園 眞人 日本建築学会計画系論文集/91(841)/pp.544-555, 2026-03-01 / 地域組織による移住・定住支援の運営体制と効果 齊藤 啓誠; 山本 幸子 日本建築学会計画系論文集/91(843)/pp.1031-1040, 2026-05-01 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 農山村地域に立地するゲストハウスの地域活性化に向けた取り組み 九州・中国・四国地方の基礎調査 牛見佳乃子; 大庭知子; 山本 幸子 日本建築学会九州支部研究報告/(64)/pp.53-56, 2025-3 / 地域おこし協力隊の任期終了後の定住率と進路及び地域特性との関連分析 全国の自治体データを対象として 小林 正英; 山本 幸子 農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.55-56, 2024-11-30 / 農地における規模別の太陽光パネル設置要因の分析 石井 裕樹; 山本 幸子 農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.41-42, 2024-11-30 / 自治体担当課による地域コミュニティ活動のフォローアップと施策立案に関する研究 都市的地域と農村地域が合併した自治体を対象として 吉岡 誠生; 山本 幸子 農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.27-28, 2024-11-30 / 北関東地域における高齢者通所介護サービスの需給構造と将来推計(その2)：市場均衡条件を組込んだ需要供給量推計（2020～2045） 陳 星; 山本 幸子; 中園眞人 日本建築学会計画系論文集/(824)/pp.1942-1951, 2024/10 / 木造板倉仮設住宅の再利用事例における平面構成の変化と住まい方 小野寺 七海; 山本 幸子 日本建築学会大会学術講演梗概集, 2024/8 / 移住者主体による交流の場の形成過程と効果−茨城県石岡市八郷地域を事例として− 関 梢子; 山本 幸子 日本建築学会大会学術講演梗概集/pp.121-122, 2024/8 / 農村地域の宿泊滞在施設における地域交流活動の実態調査−九州・中国・四国地方のシェアハウスを対象として− 大庭 知子; 山本 幸子 日本建築学会大会学術講演梗概集/pp.25-26, 2024/8 / 北関東地域における高齢者通所介護サービスの需給構造と将来推計（その1）：利用者数と供給量の推移を指標とした県別市場特性分析（2000～2019） 陳 星; 山本 幸子; 中園 眞人 日本建築学会計画系論文集/89(815)/pp.76-86, 2024-01-01 / 農村集落の電力オフグリッド化の可能性に関する研究―石岡市上山集落を対象として― 石井 裕樹; 山本 幸子 農村計画学会秋季大会/p.8, 2023-12-10 / 市町村合併により生じた旧市街地の振興における行政支援の手法について－つくば市周辺市街地振興における地域運営組織と外部人材との協働支援を事例として－ 吉岡誠生; 山本 幸子 都市計画報告集/21(2)/pp.153-159, 2022-12</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -3716,6 +3737,19 @@
 茨城版ＳＤＧｓを推進する産学研究
 次世代の茅葺きの再生・導入に関する共同研究拠点の形成
 相続工学に関する共同研究
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
+現代板倉構法の普及実態と木材生産・供給体制に関する研究 その２−木材生産・供給体制の事例分析及びコスト分析− 岡原 玄八; 石井 裕樹; 山本 幸子 日本建築学会大会学術講演梗概集/pp.1025-1026, 2025-09
+現代板倉構法の普及実態と木材生産・供給体制に関する研究 その１−板倉の実績調査結果より− 石井 裕樹; 岡原 玄八; 山本 幸子 日本建築学会大会学術講演梗概集/pp.1023-1024, 2025-09
+農村移住者の宿泊滞在施設の運営と地域交流活動の実態―全国のゲストハウスを対象として― 山本 幸子; 大庭 知子 日本建築学会大会学術講演梗概集/pp.85-86, 2025-09
+離島における若者移住者の定住プロセスと要因に関する研究 伊豆大島を対象としたヒアリングに基づく分析 朝賀 史織; 山本 幸子 2025年度農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.49-50, 2025-11
+太陽光パネルに関する条例内容とパネル設置状況・地域的特徴との関連分析 石井 裕樹; 山本 幸子 2025年度農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.27-28, 2025-11
+農村地域の民泊の背景と動向 山本 幸子 住宅/pp.29-34, 2019-11
+空き家相談会記録から見る空家活用阻害要因 山本 幸子 JIR NEWS/pp.10-13, 2025-08
+茨城県利根町の戸建住宅地空き家の日本語学校寄宿舎への転用 廣谷 泰斗; 山本 幸子 住宅/pp.34-30, 2025-09
+座談会：近接分野からみた造園・ランドスケープ分野の見え方と期待 村山 顕人; 寺田 徹; 三輪 隆; 真田 純子; 山本 幸子; 曽我 昌史; 吉永 明弘 ランドスケープ研究/89(1)/pp.50-53, 2025-05-01
+戸建て住宅空き家を活用した外国人留学生寄宿舎の整備手法と地域への影響 廣谷 泰斗; 山本 幸子 日本建築学会住宅系研究報告会論文集/(20)/pp.287-296, 2025-12
+木造民家を活用した高齢者通所介護施設の空間用途構成に関する研究（その２）：主用途が１室で行われる施設の空間構成と使われ方 三島 幸子; 山本 幸子; 細田 智久; 中園 眞人 日本建築学会計画系論文集/91(841)/pp.544-555, 2026-03-01
+地域組織による移住・定住支援の運営体制と効果 齊藤 啓誠; 山本 幸子 日本建築学会計画系論文集/91(843)/pp.1031-1040, 2026-05-01
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 農山村地域に立地するゲストハウスの地域活性化に向けた取り組み 九州・中国・四国地方の基礎調査 牛見佳乃子; 大庭知子; 山本 幸子 日本建築学会九州支部研究報告/(64)/pp.53-56, 2025-3
 地域おこし協力隊の任期終了後の定住率と進路及び地域特性との関連分析 全国の自治体データを対象として 小林 正英; 山本 幸子 農村計画学会全国大会（秋季大会）学術研究発表会梗概集/pp.55-56, 2024-11-30
@@ -3727,20 +3761,7 @@
 農村地域の宿泊滞在施設における地域交流活動の実態調査−九州・中国・四国地方のシェアハウスを対象として− 大庭 知子; 山本 幸子 日本建築学会大会学術講演梗概集/pp.25-26, 2024/8
 北関東地域における高齢者通所介護サービスの需給構造と将来推計（その1）：利用者数と供給量の推移を指標とした県別市場特性分析（2000～2019） 陳 星; 山本 幸子; 中園 眞人 日本建築学会計画系論文集/89(815)/pp.76-86, 2024-01-01
 農村集落の電力オフグリッド化の可能性に関する研究―石岡市上山集落を対象として― 石井 裕樹; 山本 幸子 農村計画学会秋季大会/p.8, 2023-12-10
-市町村合併により生じた旧市街地の振興における行政支援の手法について－つくば市周辺市街地振興における地域運営組織と外部人材との協働支援を事例として－ 吉岡誠生; 山本 幸子 都市計画報告集/21(2)/pp.153-159, 2022-12
-関係人口の居住地と訪問先との距離が地域とのかかわり方に与える影響－茨城県を対象として－ 古屋昂; 山本 幸子 日本建築学会大会学術講演梗概集（計画系）/pp.69-77, 2022-07
-多様な主体が連携する「新しい内発的発展」を支える地方自治体の取り組みについて－つくば市周辺市街地振興を事例として－ 吉岡誠生; 山本 幸子 日本建築学会大会学術講演梗概集（計画系）/pp.1055-1056, 2022-07
-木造民家を活用した高齢者通所介護施設の空間用途構成に関する研究（その1）：民家の平面構成と主用途の空間配置 山本 幸子; 三島 幸子; 中園 眞人 日本建築学会計画系論文集/87(793)/pp.521-532, 2022-03-01 CiNii
-現代建築への茅葺きの導入可能性に関する研究 福山 夏映; 山本 幸子 日本建築学会技術報告集/28(68)/pp.380-384, 2022-02-20 CiNii
-木造公共建築の用途と建築規模による特徴把握と実現手法の分析 新建築掲載事例を対象として 歌代 友哉; 山本 幸子 日本建築学会大会（東海）学術講演会梗概集/pp.399-400, 2021-9
-現代の茅葺き構法に関する研究−兵庫県神戸市の事例を対象として− 福山 夏映; 山本 幸子 日本建築学会大会（東海）学術講演会梗概集/pp.447-448, 2021-9
-既存建築を活用した自立高齢者地域支援拠点の運営形態と平面構成—土浦市「生きがい対応型デイサービス事業」を対象として— 稲石 渓太; 山本 幸子 日本建築学会大会（東海）学術講演会梗概集/pp.765-766, 2021-9
-大規模高齢者通所介護施設における主室の用途構成と使われ方 中園眞人; 三島幸子; 山本 幸子 日本建築学会計画系論文集/(782)/pp.1212-1223, 2021-04
-萩市における医療法人による高齢者福祉施設の整備運営に関する事例研究（その２）：木造民家を改修した通所介護・介護予防施設の使われ方 中園 眞人; 三島 幸子; 瀬戸口 佳奈美; 山本 幸子 日本建築学会計画系論文集/781/pp.717-726, 2021-03
-食堂兼機能訓練室と和室が一体的に構成された小規模高齢者通所介護施設の使われ方 中園 眞人; 三島 幸子; 山本 幸子 日本建築学会計画系論文集/780/pp.403-412, 2021-02
-社会福祉協議会による中山間地域における高齢者福祉施設の整備運営の取組み（その２）：下関市社会福祉協議会による中山間地域における高齢者福祉施設の整備プロセス 三島 幸子; 中園眞人; 山本 幸子 日本建築学会計画系論文集/778/pp.2573-2581, 2020-12
-農村系長屋門の利用の変遷と利活用実態 茨城県つくば市桜地区を対象として 山根 知; 山本 幸子 日本建築学会大会学術講演梗概集/(E-2分冊)/pp.111-112, 2020-09
-既存建築ストックを活用したサテライトオフィスの誘致プロセスとその実態 福井県鯖江市を対象として 齊藤啓誠; 山本 幸子 日本建築学会大会学術講演梗概集/(E-2分冊)/pp.57-58, 2020-09</t>
+市町村合併により生じた旧市街地の振興における行政支援の手法について－つくば市周辺市街地振興における地域運営組織と外部人材との協働支援を事例として－ 吉岡誠生; 山本 幸子 都市計画報告集/21(2)/pp.153-159, 2022-12</t>
         </is>
       </c>
     </row>
@@ -3794,10 +3815,18 @@
 職名
 教授
 eメール
-G&amp;x"$(&lt;KG,$E-,.$.yxExzE#)
++B6&gt;@DXgcH@aIHJ@J76a68a?E
 最適化
 組合せ最適化
 アルゴリズム
+Hgformer: Hyperbolic Graph Transformer for Collaborative Filtering Yang Xin; Li Xingrun; Chang Heng; Jinze Yang; Yang X... Proceedings of the 42nd International Conference on Machine Learning/pp.70813-70832, 2025-11
+Graph-Topological Deep Detector for Cross-Platform Forest Point Clouds Yiliu Tan; Yang Xin; Xu Xin; Zhang Jingyi; Cao Yunji... Proceedings of the 2025 8th International Conference on Computational Intelligence and Intelligent Systems/pp.15-22, 2026-02
+Locker-based Drone Delivery with Battery Swapping Stations: A Joint Routing-Recharging Optimization Wushuang Wang; Yiliu Tan; Yu Li; 繁野 麻衣子 Proceedings of the 2025 8th International Conference on Computational Intelligence and Intelligent Systems/pp.88-95, 2026-02
+EONにおける通信要求の保持時間を考慮した予約種別リソース割り当て戦略の提案 李 宗晟; 繁野 麻衣子 信学技報,/125(146)/pp.27-32, 2025-08
+TLNet : A deep learning framework for tree detection in forest point clouds using multi-layered forest structure Tan Yiliu; Yang Xin; Zhang Jingyi; Xu Xin; Cao Yunji... ISPRS JOURNAL OF PHOTOGRAMMETRY AND REMOTE SENSING/234/pp.227-241, 2026-04
+Transformer-pointer DRL model for static resource allocation problems in SDM-EONs Chen Sibo; Wang Jiading; Shigeno Maiko JOURNAL OF OPTICAL COMMUNICATIONS AND NETWORKING/18(3)/pp.315-328, 2026-03
+Selection of candidate paths based on diversity in resource allocation problems on optical networks Mori Yuta; Shigeno Maiko OPTICAL SWITCHING AND NETWORKING/58, 2025-12
+Mathematical models for carpooling considering driver absence: Comparative analysis and heuristic strategies Wang Wushuang; Li Yu; Tan Yiliu; Kobayashi Ryotaro; H... COMPUTERS &amp; INDUSTRIAL ENGINEERING/210, 2025-12
 A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs Chen Sibo; Wang Jiading; SHIGENO Maiko 2024 IEEE Opto-Electronics and Communications Conference (OECC)/pp.1-3, 2024-6
 Break maximization for round-robin tournaments without consecutive breaks Xue Fei; Ma Hajunfu; Shigeno Maiko OPERATIONS RESEARCH LETTERS/57, 2024-11
 Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm Li Yu; Wang Wushuang; Hashikami Hidenobu; Shigeno Maiko COMPUTERS &amp; INDUSTRIAL ENGINEERING/198, 2024-12
@@ -3814,15 +3843,7 @@
 Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model Wang Jiading; Chen Sibo; Wu Qian; Tan Yiliu; Shigeno ... SENSORS/22(24), 2022-12
 Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan Hashikami Hidenobu; Kobayashi Ryotaro; Li Yu; Nakano ... IEEE TRANSACTIONS ON SYSTEMS MAN CYBERNETICS-SYSTEMS/53(7)/pp.4239-4250, 2023-07
 Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament Xue Fei; Ma Haijunfu; Shigeno Maiko JOURNAL OF ADVANCED MECHANICAL DESIGN SYSTEMS AND MANUFACTURING/16(4), 2022
-交換移植制度におけるドミナントマッチングの適用可能性 臼井 颯汰; 栗野 盛光; 大藤 剛宏; 繁野 麻衣子 日本オペレーションズ・リサーチ学会和文論文誌/pp.1-21, 2022
-Network Design Models with Partial Protection Schemes against Multiple Failures under Optical- Channel Data Unit Constraints Yiliu Tan; Qian Wu; Yoshiki Nakano; Jiading Wang; Shigeno... Proceedings of 2021 IEEE 6th Optoelectronics Global Conference/pp.38-46, 2021
-ILP models and improved methods for the problem of routing and spectrum allocation Wang Jiading; Shigeno Maiko; Wu Qian Optical Switching and Networking/45/pp.100675-100675, 2022
-A novel channel-based model for the problem of routing, space, and spectrum assignment Wu Qian; Wang Jiading; Shigeno Maiko OPTICAL SWITCHING AND NETWORKING/43, 2022-02
-NASH EQUILIBRIA FOR INFORMATION DIFFUSION GAMES ON WEIGHTED CYCLES AND PATHS Li Tianyang; Shigeno Maiko 日本オペレーションズ・リサーチ学会論文誌/64(1)/pp.1-11, 2021 CiNii
-Strongly separable matrices for nonadaptive combinatorial group testing Fan Jinping; Fu Hung-Lin; Gu Yujie; Miao Ying; Shigen... DISCRETE APPLIED MATHEMATICS/291/pp.180-187, 2021-03
-Modeling and Evaluating Taxi Ride-sharing for Event Trips Yoshida Taketo; Yano Masaki; Horikawa Kenichiro; Sato Ke... IPSJ Transactions on Mathematical Modeling and Its Applications/12/pp.10-11, 2019
-不均衡データに対する多段階学習を用いた アンサンブルモデルによる2 クラス分類アルゴリズムの提案 藤原和樹; 繁野 麻衣子; 住田潮 情報処理学会論文誌，数理モデル化と応用（TOM）/12(3)/pp.10-17, 2019
-A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data Fujiwara Kazuki; Shigeno Maiko; Sumita Ushio IEEE ACCESS/7/pp.82970-82977, 2019</t>
+交換移植制度におけるドミナントマッチングの適用可能性 臼井 颯汰; 栗野 盛光; 大藤 剛宏; 繁野 麻衣子 日本オペレーションズ・リサーチ学会和文論文誌/pp.1-21, 2022</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3832,7 +3853,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / G&amp;x"$(&lt;KG,$E-,.$.yxExzE#)</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / +B6&gt;@DXgcH@aIHJ@J76a68a?E</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3842,7 +3863,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs Chen Sibo; Wang Jiading; SHIGENO Maiko 2024 IEEE Opto-Electronics and Communications Conference (OECC)/pp.1-3, 2024-6 / Break maximization for round-robin tournaments without consecutive breaks Xue Fei; Ma Hajunfu; Shigeno Maiko OPERATIONS RESEARCH LETTERS/57, 2024-11 / Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm Li Yu; Wang Wushuang; Hashikami Hidenobu; Shigeno Maiko COMPUTERS &amp; INDUSTRIAL ENGINEERING/198, 2024-12 / Height Estimation for Abrasive Grain of Synthetic Diamonds on Microscope Images by Conditional Adversarial Networks Joe Brinton; Shota Oki; Xin Yang; SHIGENO Maiko Proceedings of the IEA/AIE 2022: Advances and Trends in Artificial Intelligence. Theory and Practices in Artificial Intelligence/pp.797-804, 2022 / Designing of OTN/WDM networks withrecovery methods for multiple failures Yiliu Tan; Yoshiki Nakano; Jiading Wang; SHIGENO Maiko Proceedings of the 27th OptoElectronics and CommunicationsConference (OECC) and 2022 International Conference on Photonics in Switching andComputing (PSC)/pp.1-3, 2022 / Restaurant Sales forecasting with feature interaction-learning mechanism based neural network model,IEEE International Conference on Big Data Xin Yang; Tetsuya Tsuboi; Keisuke Kimura; Keitarou Ha... Proceedings of IEEE International Conference on Big Data, Big Data 2022/pp.4166-4172, 2023 / A Discrete JAYA Algorithm for Long-Term Carpooling Problem Wushuang Wang; Yu Li; Hidenobu Hashikami; SHIGENO Maiko Proceedings of the 2023 IEEE 12th Global Conference on Consumer Electronics (GCCE 2023)/pp.1075-1076, 2023 / Carry-over Effect Values Minimization under Circle Method and Binary Factorization Based on Jaya Algorithm Wushuang Wang; Fei Xue; Toshiki Mitsui; Zhiyuan Shang... Proceedings of the 2024 8th International Conference on Control Engineering and Artificial Intelligence/pp.44-51, 2024 / Application of Data Anonymization to Smartphone Apps Usage Logs Tabata Naoya; SHIGENO Maiko Proceedings of the 2024 9th International Conference on Big Data Analytics (ICBDA)/pp.60-69, 2024 / 数理最適化を用いたサービス工学の事例―通勤カープールの実証実験― 橋上英宜; 繁野 麻衣子 オペレーションズ・リサーチ：経営の科学/68/pp.161-168, 2024 / Four-level knowledge graph contrastive learning structure for smart-phone application recommendation Xin Yang; Yu Li; Wenhui Ai; SHIGENO Maiko Proceedings of 2023 International Wireless Communications and Mobile Computing/pp.1340-1345, 2023 / A New Approach to Market Segmentation Based on 2-Dimensional Tables Naoya Tabata; Rin Itoshiya; Hideshi Narita; SHIGENO M... Proceedings of 10th International Conference on Computing and Data Engineering, 2024 / Challenges of commuter carpooling with adapting to Japanese customs and regulations: A pilot study Hashikami Hidenobu; Li Yu; Kobayashi Ryotaro; Shigeno ... TRANSPORTATION RESEARCH INTERDISCIPLINARY PERSPECTIVES/22, 2023-11 / Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model Wang Jiading; Chen Sibo; Wu Qian; Tan Yiliu; Shigeno ... SENSORS/22(24), 2022-12 / Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan Hashikami Hidenobu; Kobayashi Ryotaro; Li Yu; Nakano ... IEEE TRANSACTIONS ON SYSTEMS MAN CYBERNETICS-SYSTEMS/53(7)/pp.4239-4250, 2023-07 / Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament Xue Fei; Ma Haijunfu; Shigeno Maiko JOURNAL OF ADVANCED MECHANICAL DESIGN SYSTEMS AND MANUFACTURING/16(4), 2022 / 交換移植制度におけるドミナントマッチングの適用可能性 臼井 颯汰; 栗野 盛光; 大藤 剛宏; 繁野 麻衣子 日本オペレーションズ・リサーチ学会和文論文誌/pp.1-21, 2022 / Network Design Models with Partial Protection Schemes against Multiple Failures under Optical- Channel Data Unit Constraints Yiliu Tan; Qian Wu; Yoshiki Nakano; Jiading Wang; Shigeno... Proceedings of 2021 IEEE 6th Optoelectronics Global Conference/pp.38-46, 2021 / ILP models and improved methods for the problem of routing and spectrum allocation Wang Jiading; Shigeno Maiko; Wu Qian Optical Switching and Networking/45/pp.100675-100675, 2022 / A novel channel-based model for the problem of routing, space, and spectrum assignment Wu Qian; Wang Jiading; Shigeno Maiko OPTICAL SWITCHING AND NETWORKING/43, 2022-02 / NASH EQUILIBRIA FOR INFORMATION DIFFUSION GAMES ON WEIGHTED CYCLES AND PATHS Li Tianyang; Shigeno Maiko 日本オペレーションズ・リサーチ学会論文誌/64(1)/pp.1-11, 2021 CiNii / Strongly separable matrices for nonadaptive combinatorial group testing Fan Jinping; Fu Hung-Lin; Gu Yujie; Miao Ying; Shigen... DISCRETE APPLIED MATHEMATICS/291/pp.180-187, 2021-03 / Modeling and Evaluating Taxi Ride-sharing for Event Trips Yoshida Taketo; Yano Masaki; Horikawa Kenichiro; Sato Ke... IPSJ Transactions on Mathematical Modeling and Its Applications/12/pp.10-11, 2019 / 不均衡データに対する多段階学習を用いた アンサンブルモデルによる2 クラス分類アルゴリズムの提案 藤原和樹; 繁野 麻衣子; 住田潮 情報処理学会論文誌，数理モデル化と応用（TOM）/12(3)/pp.10-17, 2019 / A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data Fujiwara Kazuki; Shigeno Maiko; Sumita Ushio IEEE ACCESS/7/pp.82970-82977, 2019</t>
+          <t>Hgformer: Hyperbolic Graph Transformer for Collaborative Filtering Yang Xin; Li Xingrun; Chang Heng; Jinze Yang; Yang X... Proceedings of the 42nd International Conference on Machine Learning/pp.70813-70832, 2025-11 / Graph-Topological Deep Detector for Cross-Platform Forest Point Clouds Yiliu Tan; Yang Xin; Xu Xin; Zhang Jingyi; Cao Yunji... Proceedings of the 2025 8th International Conference on Computational Intelligence and Intelligent Systems/pp.15-22, 2026-02 / Locker-based Drone Delivery with Battery Swapping Stations: A Joint Routing-Recharging Optimization Wushuang Wang; Yiliu Tan; Yu Li; 繁野 麻衣子 Proceedings of the 2025 8th International Conference on Computational Intelligence and Intelligent Systems/pp.88-95, 2026-02 / EONにおける通信要求の保持時間を考慮した予約種別リソース割り当て戦略の提案 李 宗晟; 繁野 麻衣子 信学技報,/125(146)/pp.27-32, 2025-08 / TLNet : A deep learning framework for tree detection in forest point clouds using multi-layered forest structure Tan Yiliu; Yang Xin; Zhang Jingyi; Xu Xin; Cao Yunji... ISPRS JOURNAL OF PHOTOGRAMMETRY AND REMOTE SENSING/234/pp.227-241, 2026-04 / Transformer-pointer DRL model for static resource allocation problems in SDM-EONs Chen Sibo; Wang Jiading; Shigeno Maiko JOURNAL OF OPTICAL COMMUNICATIONS AND NETWORKING/18(3)/pp.315-328, 2026-03 / Selection of candidate paths based on diversity in resource allocation problems on optical networks Mori Yuta; Shigeno Maiko OPTICAL SWITCHING AND NETWORKING/58, 2025-12 / Mathematical models for carpooling considering driver absence: Comparative analysis and heuristic strategies Wang Wushuang; Li Yu; Tan Yiliu; Kobayashi Ryotaro; H... COMPUTERS &amp; INDUSTRIAL ENGINEERING/210, 2025-12 / A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs Chen Sibo; Wang Jiading; SHIGENO Maiko 2024 IEEE Opto-Electronics and Communications Conference (OECC)/pp.1-3, 2024-6 / Break maximization for round-robin tournaments without consecutive breaks Xue Fei; Ma Hajunfu; Shigeno Maiko OPERATIONS RESEARCH LETTERS/57, 2024-11 / Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm Li Yu; Wang Wushuang; Hashikami Hidenobu; Shigeno Maiko COMPUTERS &amp; INDUSTRIAL ENGINEERING/198, 2024-12 / Height Estimation for Abrasive Grain of Synthetic Diamonds on Microscope Images by Conditional Adversarial Networks Joe Brinton; Shota Oki; Xin Yang; SHIGENO Maiko Proceedings of the IEA/AIE 2022: Advances and Trends in Artificial Intelligence. Theory and Practices in Artificial Intelligence/pp.797-804, 2022 / Designing of OTN/WDM networks withrecovery methods for multiple failures Yiliu Tan; Yoshiki Nakano; Jiading Wang; SHIGENO Maiko Proceedings of the 27th OptoElectronics and CommunicationsConference (OECC) and 2022 International Conference on Photonics in Switching andComputing (PSC)/pp.1-3, 2022 / Restaurant Sales forecasting with feature interaction-learning mechanism based neural network model,IEEE International Conference on Big Data Xin Yang; Tetsuya Tsuboi; Keisuke Kimura; Keitarou Ha... Proceedings of IEEE International Conference on Big Data, Big Data 2022/pp.4166-4172, 2023 / A Discrete JAYA Algorithm for Long-Term Carpooling Problem Wushuang Wang; Yu Li; Hidenobu Hashikami; SHIGENO Maiko Proceedings of the 2023 IEEE 12th Global Conference on Consumer Electronics (GCCE 2023)/pp.1075-1076, 2023 / Carry-over Effect Values Minimization under Circle Method and Binary Factorization Based on Jaya Algorithm Wushuang Wang; Fei Xue; Toshiki Mitsui; Zhiyuan Shang... Proceedings of the 2024 8th International Conference on Control Engineering and Artificial Intelligence/pp.44-51, 2024 / Application of Data Anonymization to Smartphone Apps Usage Logs Tabata Naoya; SHIGENO Maiko Proceedings of the 2024 9th International Conference on Big Data Analytics (ICBDA)/pp.60-69, 2024 / 数理最適化を用いたサービス工学の事例―通勤カープールの実証実験― 橋上英宜; 繁野 麻衣子 オペレーションズ・リサーチ：経営の科学/68/pp.161-168, 2024 / Four-level knowledge graph contrastive learning structure for smart-phone application recommendation Xin Yang; Yu Li; Wenhui Ai; SHIGENO Maiko Proceedings of 2023 International Wireless Communications and Mobile Computing/pp.1340-1345, 2023 / A New Approach to Market Segmentation Based on 2-Dimensional Tables Naoya Tabata; Rin Itoshiya; Hideshi Narita; SHIGENO M... Proceedings of 10th International Conference on Computing and Data Engineering, 2024 / Challenges of commuter carpooling with adapting to Japanese customs and regulations: A pilot study Hashikami Hidenobu; Li Yu; Kobayashi Ryotaro; Shigeno ... TRANSPORTATION RESEARCH INTERDISCIPLINARY PERSPECTIVES/22, 2023-11 / Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model Wang Jiading; Chen Sibo; Wu Qian; Tan Yiliu; Shigeno ... SENSORS/22(24), 2022-12 / Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan Hashikami Hidenobu; Kobayashi Ryotaro; Li Yu; Nakano ... IEEE TRANSACTIONS ON SYSTEMS MAN CYBERNETICS-SYSTEMS/53(7)/pp.4239-4250, 2023-07 / Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament Xue Fei; Ma Haijunfu; Shigeno Maiko JOURNAL OF ADVANCED MECHANICAL DESIGN SYSTEMS AND MANUFACTURING/16(4), 2022 / 交換移植制度におけるドミナントマッチングの適用可能性 臼井 颯汰; 栗野 盛光; 大藤 剛宏; 繁野 麻衣子 日本オペレーションズ・リサーチ学会和文論文誌/pp.1-21, 2022</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -3852,7 +3873,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; G&amp;x"$(&lt;KG,$E-,.$.yxExzE#) ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; +B6&gt;@DXgcH@aIHJ@J76a68a?E ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3871,7 +3892,7 @@
 職名
 教授
 eメール
-G&amp;x"$(&lt;KG,$E-,.$.yxExzE#)
++B6&gt;@DXgcH@aIHJ@J76a68a?E
 最適化
 組合せ最適化
 アルゴリズム
@@ -3939,6 +3960,14 @@
 ネットワーク理論の基盤整備と伸張
 データの精度を考慮した組合せ最適化問題に対する問題構造とアルゴリズムの研究
 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開
+Hgformer: Hyperbolic Graph Transformer for Collaborative Filtering Yang Xin; Li Xingrun; Chang Heng; Jinze Yang; Yang X... Proceedings of the 42nd International Conference on Machine Learning/pp.70813-70832, 2025-11
+Graph-Topological Deep Detector for Cross-Platform Forest Point Clouds Yiliu Tan; Yang Xin; Xu Xin; Zhang Jingyi; Cao Yunji... Proceedings of the 2025 8th International Conference on Computational Intelligence and Intelligent Systems/pp.15-22, 2026-02
+Locker-based Drone Delivery with Battery Swapping Stations: A Joint Routing-Recharging Optimization Wushuang Wang; Yiliu Tan; Yu Li; 繁野 麻衣子 Proceedings of the 2025 8th International Conference on Computational Intelligence and Intelligent Systems/pp.88-95, 2026-02
+EONにおける通信要求の保持時間を考慮した予約種別リソース割り当て戦略の提案 李 宗晟; 繁野 麻衣子 信学技報,/125(146)/pp.27-32, 2025-08
+TLNet : A deep learning framework for tree detection in forest point clouds using multi-layered forest structure Tan Yiliu; Yang Xin; Zhang Jingyi; Xu Xin; Cao Yunji... ISPRS JOURNAL OF PHOTOGRAMMETRY AND REMOTE SENSING/234/pp.227-241, 2026-04
+Transformer-pointer DRL model for static resource allocation problems in SDM-EONs Chen Sibo; Wang Jiading; Shigeno Maiko JOURNAL OF OPTICAL COMMUNICATIONS AND NETWORKING/18(3)/pp.315-328, 2026-03
+Selection of candidate paths based on diversity in resource allocation problems on optical networks Mori Yuta; Shigeno Maiko OPTICAL SWITCHING AND NETWORKING/58, 2025-12
+Mathematical models for carpooling considering driver absence: Comparative analysis and heuristic strategies Wang Wushuang; Li Yu; Tan Yiliu; Kobayashi Ryotaro; H... COMPUTERS &amp; INDUSTRIAL ENGINEERING/210, 2025-12
 A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs Chen Sibo; Wang Jiading; SHIGENO Maiko 2024 IEEE Opto-Electronics and Communications Conference (OECC)/pp.1-3, 2024-6
 Break maximization for round-robin tournaments without consecutive breaks Xue Fei; Ma Hajunfu; Shigeno Maiko OPERATIONS RESEARCH LETTERS/57, 2024-11
 Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm Li Yu; Wang Wushuang; Hashikami Hidenobu; Shigeno Maiko COMPUTERS &amp; INDUSTRIAL ENGINEERING/198, 2024-12
@@ -3955,15 +3984,7 @@
 Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model Wang Jiading; Chen Sibo; Wu Qian; Tan Yiliu; Shigeno ... SENSORS/22(24), 2022-12
 Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan Hashikami Hidenobu; Kobayashi Ryotaro; Li Yu; Nakano ... IEEE TRANSACTIONS ON SYSTEMS MAN CYBERNETICS-SYSTEMS/53(7)/pp.4239-4250, 2023-07
 Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament Xue Fei; Ma Haijunfu; Shigeno Maiko JOURNAL OF ADVANCED MECHANICAL DESIGN SYSTEMS AND MANUFACTURING/16(4), 2022
-交換移植制度におけるドミナントマッチングの適用可能性 臼井 颯汰; 栗野 盛光; 大藤 剛宏; 繁野 麻衣子 日本オペレーションズ・リサーチ学会和文論文誌/pp.1-21, 2022
-Network Design Models with Partial Protection Schemes against Multiple Failures under Optical- Channel Data Unit Constraints Yiliu Tan; Qian Wu; Yoshiki Nakano; Jiading Wang; Shigeno... Proceedings of 2021 IEEE 6th Optoelectronics Global Conference/pp.38-46, 2021
-ILP models and improved methods for the problem of routing and spectrum allocation Wang Jiading; Shigeno Maiko; Wu Qian Optical Switching and Networking/45/pp.100675-100675, 2022
-A novel channel-based model for the problem of routing, space, and spectrum assignment Wu Qian; Wang Jiading; Shigeno Maiko OPTICAL SWITCHING AND NETWORKING/43, 2022-02
-NASH EQUILIBRIA FOR INFORMATION DIFFUSION GAMES ON WEIGHTED CYCLES AND PATHS Li Tianyang; Shigeno Maiko 日本オペレーションズ・リサーチ学会論文誌/64(1)/pp.1-11, 2021 CiNii
-Strongly separable matrices for nonadaptive combinatorial group testing Fan Jinping; Fu Hung-Lin; Gu Yujie; Miao Ying; Shigen... DISCRETE APPLIED MATHEMATICS/291/pp.180-187, 2021-03
-Modeling and Evaluating Taxi Ride-sharing for Event Trips Yoshida Taketo; Yano Masaki; Horikawa Kenichiro; Sato Ke... IPSJ Transactions on Mathematical Modeling and Its Applications/12/pp.10-11, 2019
-不均衡データに対する多段階学習を用いた アンサンブルモデルによる2 クラス分類アルゴリズムの提案 藤原和樹; 繁野 麻衣子; 住田潮 情報処理学会論文誌，数理モデル化と応用（TOM）/12(3)/pp.10-17, 2019
-A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data Fujiwara Kazuki; Shigeno Maiko; Sumita Ushio IEEE ACCESS/7/pp.82970-82977, 2019</t>
+交換移植制度におけるドミナントマッチングの適用可能性 臼井 颯汰; 栗野 盛光; 大藤 剛宏; 繁野 麻衣子 日本オペレーションズ・リサーチ学会和文論文誌/pp.1-21, 2022</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4038,8 @@
 犯罪科学
 空間情報科学
 環境心理学
+非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06
 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06
@@ -4039,9 +4062,7 @@
 子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10
 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10
 Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10
-筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10
-GPSログに基づく行動推定データを用いた人々の社会的接触可能性の時空間的把握 米田 有希; 雨宮 護 地理情報システム学会講演論文集/33, 2024-10
-サイバー・フィジカル空間上の社会的交流と居住地の近隣環境 尾藤 皓太朗; 雨宮 護; 島田 貴仁 MERA Journal=人間・環境学会誌/27(1)/pp.101-101, 2024-09-30</t>
+筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4061,7 +4082,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06 / 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06 / 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 雨宮 護; 鈴木 あい; 田村 孝浩; 御田 成顕; 島田 貴仁; 栗田 英治 2025年度農村計画学会全国大会学術研究発表会企画セッション梗概集/pp.70-71, 2025-11-29 / Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09 / 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して 井上 皓介; 雨宮 護; 大山 智也; 中野 裕貴 都市計画論文集/60(3)/pp.1604-1611, 2025-10 / 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 高橋 南織; 雨宮 護 都市計画論文集/60(3)/pp.650-656, 2025-10 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10 / 人口低密度地域における人々の活動から見た「都市の活力」の計測 米田 有希; 雨宮 護; 森山 拓洋 都市計画論文集/60(3)/pp.1658-1665, 2025-10 / 全国のJAを対象とする果物盗被害に関するアンケート調査報告 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 都市計画報告集/24(2)/pp.318-321, 2025-09 / Regional variations in key factors of children's independent mobility across Japan HINO Kimihiro; AMEMIYA Mamoru; YOSHIKI Syuji; ZHENG Erli Journal of Transport &amp; Health/44, 2025-09 / 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 佐光 未帆; 雨宮 護 環境心理学研究/13(1)/pp.48-48, 2025-05-28 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 李 超群; 雨宮 護 環境心理学研究/13(1)/pp.44-44, 2025-05-28 / Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives SUZUKI Ai; AMEMIYA Mamoru; KURITA Hideharu; SHIMADA T... International Journal of Rural Criminology/9(1)/pp.77-104, 2025-04 / Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05 / Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits Zheng Xinrui; Amemiya Mamoru TRANSACTIONS IN GIS/29(1), 2025-02 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya Ohyama 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12 / 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 市川 はるひ; 雨宮 護 IPA日本支部研究集会発表要旨集/pp.４-4, 2024-12 / GPSロガーを用いた官民による果樹盗パトロールの計測 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 Research Abstracts on Spatial Information Science CSIS DAYS 2024/D13, 2024-11-15 / 子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10 / 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10 / Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10 / 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10 / GPSログに基づく行動推定データを用いた人々の社会的接触可能性の時空間的把握 米田 有希; 雨宮 護 地理情報システム学会講演論文集/33, 2024-10 / サイバー・フィジカル空間上の社会的交流と居住地の近隣環境 尾藤 皓太朗; 雨宮 護; 島田 貴仁 MERA Journal=人間・環境学会誌/27(1)/pp.101-101, 2024-09-30</t>
+          <t>非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17 / 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06 / 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06 / 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 雨宮 護; 鈴木 あい; 田村 孝浩; 御田 成顕; 島田 貴仁; 栗田 英治 2025年度農村計画学会全国大会学術研究発表会企画セッション梗概集/pp.70-71, 2025-11-29 / Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09 / 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して 井上 皓介; 雨宮 護; 大山 智也; 中野 裕貴 都市計画論文集/60(3)/pp.1604-1611, 2025-10 / 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 高橋 南織; 雨宮 護 都市計画論文集/60(3)/pp.650-656, 2025-10 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10 / 人口低密度地域における人々の活動から見た「都市の活力」の計測 米田 有希; 雨宮 護; 森山 拓洋 都市計画論文集/60(3)/pp.1658-1665, 2025-10 / 全国のJAを対象とする果物盗被害に関するアンケート調査報告 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 都市計画報告集/24(2)/pp.318-321, 2025-09 / Regional variations in key factors of children's independent mobility across Japan HINO Kimihiro; AMEMIYA Mamoru; YOSHIKI Syuji; ZHENG Erli Journal of Transport &amp; Health/44, 2025-09 / 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 佐光 未帆; 雨宮 護 環境心理学研究/13(1)/pp.48-48, 2025-05-28 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 李 超群; 雨宮 護 環境心理学研究/13(1)/pp.44-44, 2025-05-28 / Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives SUZUKI Ai; AMEMIYA Mamoru; KURITA Hideharu; SHIMADA T... International Journal of Rural Criminology/9(1)/pp.77-104, 2025-04 / Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05 / Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits Zheng Xinrui; Amemiya Mamoru TRANSACTIONS IN GIS/29(1), 2025-02 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya Ohyama 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12 / 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 市川 はるひ; 雨宮 護 IPA日本支部研究集会発表要旨集/pp.４-4, 2024-12 / GPSロガーを用いた官民による果樹盗パトロールの計測 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 Research Abstracts on Spatial Information Science CSIS DAYS 2024/D13, 2024-11-15 / 子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10 / 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10 / Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10 / 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -4157,6 +4178,8 @@
 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究
 集合住宅における子ども・女性に対する犯罪の実態分析と対策立案
 地理的犯罪予測の手法構築‐学際研究と産官学連携による学術基盤の確立とシステム開発
+非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06
 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06
@@ -4179,9 +4202,7 @@
 子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10
 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10
 Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10
-筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10
-GPSログに基づく行動推定データを用いた人々の社会的接触可能性の時空間的把握 米田 有希; 雨宮 護 地理情報システム学会講演論文集/33, 2024-10
-サイバー・フィジカル空間上の社会的交流と居住地の近隣環境 尾藤 皓太朗; 雨宮 護; 島田 貴仁 MERA Journal=人間・環境学会誌/27(1)/pp.101-101, 2024-09-30</t>
+筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4239,8 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として―
+          <t>更生支援者への支援および地域住民の誤解・偏見の是正と参加・協力促進のモデル化
+過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として―
 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討
 リアルタイム場面におけるサービス・インタラクション理論の構築と実証
 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学
@@ -4261,7 +4283,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として― / 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討 / リアルタイム場面におけるサービス・インタラクション理論の構築と実証 / 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 / 慢性ストレスがヒトの生理心理状態に与える影響とその対処法 / 犯罪不安に関する認知・感情プロセスのモデル化とその応用 / 逸脱行動が生起するプロセスと矯正方法に関する研究 / 進路意思決定における認知・感情過程のモデル化 / 教師教育教材を事例としたマルチメディア教材設計・評価手法の開発</t>
+          <t>更生支援者への支援および地域住民の誤解・偏見の是正と参加・協力促進のモデル化 / 過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として― / 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討 / リアルタイム場面におけるサービス・インタラクション理論の構築と実証 / 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 / 慢性ストレスがヒトの生理心理状態に与える影響とその対処法 / 犯罪不安に関する認知・感情プロセスのモデル化とその応用 / 逸脱行動が生起するプロセスと矯正方法に関する研究 / 進路意思決定における認知・感情過程のモデル化 / 教師教育教材を事例としたマルチメディア教材設計・評価手法の開発</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -4350,6 +4372,7 @@
 読書状況が変えるネタバレ選好
 グリーン購入における他者の影響
 An Investigation of the Factors Influencing college student Volunteering motivation - In Perspectives on prosocial behaviour
+更生支援者への支援および地域住民の誤解・偏見の是正と参加・協力促進のモデル化
 過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として―
 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討
 リアルタイム場面におけるサービス・インタラクション理論の構築と実証
@@ -4640,9 +4663,14 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-=085$.$0,FUQ6.O768.8%$O$&amp;O-3\
+2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q
+5^
 都市農村計画
 緑地計画
+Memorable Places on Campuses Across Generations Janpathompong Dalin; Anantsuksomsri Sutee; MURAKAMI Ak... Journal of Architectural/Planning Research and Studies (JARS)/23(1)/pp.278-289, 2026-01
+企業の情報開示における企業緑地に関する第三者認証取得事実の取り扱いに関する研究 斎藤 すみれ; 植田 直樹; 村上 暁信 都市計画論文集/60(3)/pp.735-742, 2025-04-30
+グリーンをインフラたらしめる 村上 暁信 都市計画 = City planning review / 日本都市計画学会 編/74(6)/pp.16-19, 2025-11
+優良緑地確保計画認定制度（TSUNAG）における緑地の機能評価手法と今後の展望 村上 暁信; 柳井 重人; 小笠原 奨悟; 増澤 直; 守谷 修; 福塚 祐子 ランドスケープ研究/89(3)/pp.238-241, 2025-11-01
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
 熱的快適性が屋外空間における滞在状態に与える影響に関する研究 クワン グエン ヒュー; 村上 暁信 ランドスケープ研究/88(5)/pp.545-550, 2024
 グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所研究報告 = Report of the National Research Institute for Earth Science and Disaster Resilience / 防災科学技術研究所編集委員会 編/(86-88)/pp.33-44, 2024-06
@@ -4663,11 +4691,7 @@
 ランドスケープ分野におけるDX 村上 暁信 ランドスケープ研究 : 日本造園学会会誌 : journal of the Japanese Institute of Landscape Architecture/87(3)/pp.188-193, 2023-11
 グリーンインフラとしての平地林による防災機能 －災害現場で確認された農業気象災害軽減事例－ 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所 研究報告/(88)/pp.33-44, 2023-12-08
 移動の体験と景観 村上 暁信 IATSS Review（国際交通安全学会誌）/48(3)/p.149, 2024-02-29
-企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ 植田 直樹; 菊池 佐智子; 村上 暁信 都市計画報告集/22(4)/pp.586-591, 2024-03-11
-屋外空間利用がオフィスワーカーに与える心理・生理的影響とその要因に関する研究 池田 千紘; 村上 暁信 環境情報科学/53(1)/pp.128-128, 2024-04-15
-人流ビッグデータを用いた「Natural Cities」と温熱環境の関係分析についての研究 QUANG Nguyen Huu; 村上 暁信 環境情報科学/53(1)/pp.131-131, 2024-04-15
-季節の違いが緑化に対する支払意思額に与える影響 花田 大地; 村上 暁信 環境情報科学/53(1)/pp.115-115, 2024-04-15
-地域・土地との関係性の希薄化 村上 暁信 IATSS Review（国際交通安全学会誌）/49(1)/pp.106-107, 2024-06-30</t>
+企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ 植田 直樹; 菊池 佐智子; 村上 暁信 都市計画報告集/22(4)/pp.586-591, 2024-03-11</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4677,7 +4701,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / =085$.$0,FUQ6.O768.8%$O$&amp;O-3\</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q / 5^</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4687,7 +4711,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024 / 熱的快適性が屋外空間における滞在状態に与える影響に関する研究 クワン グエン ヒュー; 村上 暁信 ランドスケープ研究/88(5)/pp.545-550, 2024 / グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所研究報告 = Report of the National Research Institute for Earth Science and Disaster Resilience / 防災科学技術研究所編集委員会 編/(86-88)/pp.33-44, 2024-06 / 2023年度一般公開シンポジウム開催報告 上田 康治; 村上 暁信; 堀井 亮; 小谷 幸司; 村山 武彦; 大倉 紀彰 環境情報科学/53(2)/pp.65-73, 2024-07-15 / 座談会 「緑の基本計画」のこれからを考える座談会 : 制度創設30年目を迎えて 村上 暁信; 飯田 晶子; 根岸 勇太; 山田 順之; 永井 淳一; 望月 一彦; 古澤 達也 公園緑地 = Parks and open space/85(3)/pp.29-36, 2024-11 / 量から質への転換 村上 暁信 グリーン・エージ = Green age/52(1)/pp.26-29, 2025-01 / 人と土地の関係を創造するよろこび 村上 暁信 ランドスケープ研究/88(4)/pp.338-339, 2025-02-01 / 「働くクルマと社会」特集にあたって 村上 暁信 IATSS Review（国際交通安全学会誌）/49(3)/pp.278-279, 2025-02-28 / GPSデータを用いたスポーツイベント来場者の行動分析 上山 滉介; 村上 暁信; Sunyong Eom 環境情報科学/54(1)/p.122, 2025-04-30 / 企業のIR情報に見る都市緑地に関する第三者認証制度の取り扱いに関する研究 斎藤 すみれ; 植田 直樹; 村上 暁信 環境情報科学/54(1)/p.104, 2025-04-30 / 熱赤外域リモートセンシングデータを活用した市街地の土地被覆に関する研究 徐 伍華; 村上 暁信 環境情報科学/54(1)/p.113, 2025-04-30 / 熱的快適性が屋外空間における滞在に与える影響に関する研究 QUANG Nguyen Huu; 村上 暁信 環境情報科学/54(1)/p.102, 2025-04-30 / 可視化された温熱環境情報が屋外空間の利用に与える影響に関する研究 深谷恭平; 村上 暁信 都市計画論文集/58(3)/pp.1439-1445, 2023-10 / An Empirical Study on Using Green Spaces Around an Office as Workplace in Summer: Considerations Based on Office Employees’ Trait Anxiety Tendencies Umehara Mizuki; Arai Naomi; Komori Misaki; Takeda Eri... Journal of the Human-Environment System/26(1)/pp.1-10, 2024-03 / グリーンインフラと緑の基本計画 村上 暁信 公園緑地 = Parks and open space/84(2)/pp.36-39, 2023-08 / これからの自律的な民間緑地整備に関する考察 植田 直樹; 村上 暁信; 横張 真 都市計画報告集/22(2)/pp.194-197, 2023-09-07 / ノルウェーにおける地表面での雨水管理策に関する法改正における議論の特徴 木藤 健二郎; 村上 暁信 都市計画論文集/58(3)/pp.1485-1492, 2023-10-25 / ランドスケープ分野におけるDX 村上 暁信 ランドスケープ研究 : 日本造園学会会誌 : journal of the Japanese Institute of Landscape Architecture/87(3)/pp.188-193, 2023-11 / グリーンインフラとしての平地林による防災機能 －災害現場で確認された農業気象災害軽減事例－ 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所 研究報告/(88)/pp.33-44, 2023-12-08 / 移動の体験と景観 村上 暁信 IATSS Review（国際交通安全学会誌）/48(3)/p.149, 2024-02-29 / 企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ 植田 直樹; 菊池 佐智子; 村上 暁信 都市計画報告集/22(4)/pp.586-591, 2024-03-11 / 屋外空間利用がオフィスワーカーに与える心理・生理的影響とその要因に関する研究 池田 千紘; 村上 暁信 環境情報科学/53(1)/pp.128-128, 2024-04-15 / 人流ビッグデータを用いた「Natural Cities」と温熱環境の関係分析についての研究 QUANG Nguyen Huu; 村上 暁信 環境情報科学/53(1)/pp.131-131, 2024-04-15 / 季節の違いが緑化に対する支払意思額に与える影響 花田 大地; 村上 暁信 環境情報科学/53(1)/pp.115-115, 2024-04-15 / 地域・土地との関係性の希薄化 村上 暁信 IATSS Review（国際交通安全学会誌）/49(1)/pp.106-107, 2024-06-30</t>
+          <t>Memorable Places on Campuses Across Generations Janpathompong Dalin; Anantsuksomsri Sutee; MURAKAMI Ak... Journal of Architectural/Planning Research and Studies (JARS)/23(1)/pp.278-289, 2026-01 / 企業の情報開示における企業緑地に関する第三者認証取得事実の取り扱いに関する研究 斎藤 すみれ; 植田 直樹; 村上 暁信 都市計画論文集/60(3)/pp.735-742, 2025-04-30 / グリーンをインフラたらしめる 村上 暁信 都市計画 = City planning review / 日本都市計画学会 編/74(6)/pp.16-19, 2025-11 / 優良緑地確保計画認定制度（TSUNAG）における緑地の機能評価手法と今後の展望 村上 暁信; 柳井 重人; 小笠原 奨悟; 増澤 直; 守谷 修; 福塚 祐子 ランドスケープ研究/89(3)/pp.238-241, 2025-11-01 / グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024 / 熱的快適性が屋外空間における滞在状態に与える影響に関する研究 クワン グエン ヒュー; 村上 暁信 ランドスケープ研究/88(5)/pp.545-550, 2024 / グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所研究報告 = Report of the National Research Institute for Earth Science and Disaster Resilience / 防災科学技術研究所編集委員会 編/(86-88)/pp.33-44, 2024-06 / 2023年度一般公開シンポジウム開催報告 上田 康治; 村上 暁信; 堀井 亮; 小谷 幸司; 村山 武彦; 大倉 紀彰 環境情報科学/53(2)/pp.65-73, 2024-07-15 / 座談会 「緑の基本計画」のこれからを考える座談会 : 制度創設30年目を迎えて 村上 暁信; 飯田 晶子; 根岸 勇太; 山田 順之; 永井 淳一; 望月 一彦; 古澤 達也 公園緑地 = Parks and open space/85(3)/pp.29-36, 2024-11 / 量から質への転換 村上 暁信 グリーン・エージ = Green age/52(1)/pp.26-29, 2025-01 / 人と土地の関係を創造するよろこび 村上 暁信 ランドスケープ研究/88(4)/pp.338-339, 2025-02-01 / 「働くクルマと社会」特集にあたって 村上 暁信 IATSS Review（国際交通安全学会誌）/49(3)/pp.278-279, 2025-02-28 / GPSデータを用いたスポーツイベント来場者の行動分析 上山 滉介; 村上 暁信; Sunyong Eom 環境情報科学/54(1)/p.122, 2025-04-30 / 企業のIR情報に見る都市緑地に関する第三者認証制度の取り扱いに関する研究 斎藤 すみれ; 植田 直樹; 村上 暁信 環境情報科学/54(1)/p.104, 2025-04-30 / 熱赤外域リモートセンシングデータを活用した市街地の土地被覆に関する研究 徐 伍華; 村上 暁信 環境情報科学/54(1)/p.113, 2025-04-30 / 熱的快適性が屋外空間における滞在に与える影響に関する研究 QUANG Nguyen Huu; 村上 暁信 環境情報科学/54(1)/p.102, 2025-04-30 / 可視化された温熱環境情報が屋外空間の利用に与える影響に関する研究 深谷恭平; 村上 暁信 都市計画論文集/58(3)/pp.1439-1445, 2023-10 / An Empirical Study on Using Green Spaces Around an Office as Workplace in Summer: Considerations Based on Office Employees’ Trait Anxiety Tendencies Umehara Mizuki; Arai Naomi; Komori Misaki; Takeda Eri... Journal of the Human-Environment System/26(1)/pp.1-10, 2024-03 / グリーンインフラと緑の基本計画 村上 暁信 公園緑地 = Parks and open space/84(2)/pp.36-39, 2023-08 / これからの自律的な民間緑地整備に関する考察 植田 直樹; 村上 暁信; 横張 真 都市計画報告集/22(2)/pp.194-197, 2023-09-07 / ノルウェーにおける地表面での雨水管理策に関する法改正における議論の特徴 木藤 健二郎; 村上 暁信 都市計画論文集/58(3)/pp.1485-1492, 2023-10-25 / ランドスケープ分野におけるDX 村上 暁信 ランドスケープ研究 : 日本造園学会会誌 : journal of the Japanese Institute of Landscape Architecture/87(3)/pp.188-193, 2023-11 / グリーンインフラとしての平地林による防災機能 －災害現場で確認された農業気象災害軽減事例－ 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所 研究報告/(88)/pp.33-44, 2023-12-08 / 移動の体験と景観 村上 暁信 IATSS Review（国際交通安全学会誌）/48(3)/p.149, 2024-02-29 / 企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ 植田 直樹; 菊池 佐智子; 村上 暁信 都市計画報告集/22(4)/pp.586-591, 2024-03-11</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -4697,7 +4721,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; =085$.$0,FUQ6.O768.8%$O$&amp;O-3\ ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q ; 5^ ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4720,7 +4744,8 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-=085$.$0,FUQ6.O768.8%$O$&amp;O-3\
+2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q
+5^
 都市農村計画
 緑地計画
 都市・地域政策
@@ -4788,6 +4813,10 @@
 量から質へのシフトを実現するための緑地の計画制度・設計手法・運用方法の研究
 樹冠表面温度を利用した都市気温分布図の作成と緑地の気候緩和機能の分析
 リモートセンシングを活用した生物季節学図の作成と都市微気候の評価
+Memorable Places on Campuses Across Generations Janpathompong Dalin; Anantsuksomsri Sutee; MURAKAMI Ak... Journal of Architectural/Planning Research and Studies (JARS)/23(1)/pp.278-289, 2026-01
+企業の情報開示における企業緑地に関する第三者認証取得事実の取り扱いに関する研究 斎藤 すみれ; 植田 直樹; 村上 暁信 都市計画論文集/60(3)/pp.735-742, 2025-04-30
+グリーンをインフラたらしめる 村上 暁信 都市計画 = City planning review / 日本都市計画学会 編/74(6)/pp.16-19, 2025-11
+優良緑地確保計画認定制度（TSUNAG）における緑地の機能評価手法と今後の展望 村上 暁信; 柳井 重人; 小笠原 奨悟; 増澤 直; 守谷 修; 福塚 祐子 ランドスケープ研究/89(3)/pp.238-241, 2025-11-01
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
 熱的快適性が屋外空間における滞在状態に与える影響に関する研究 クワン グエン ヒュー; 村上 暁信 ランドスケープ研究/88(5)/pp.545-550, 2024
 グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所研究報告 = Report of the National Research Institute for Earth Science and Disaster Resilience / 防災科学技術研究所編集委員会 編/(86-88)/pp.33-44, 2024-06
@@ -4808,11 +4837,7 @@
 ランドスケープ分野におけるDX 村上 暁信 ランドスケープ研究 : 日本造園学会会誌 : journal of the Japanese Institute of Landscape Architecture/87(3)/pp.188-193, 2023-11
 グリーンインフラとしての平地林による防災機能 －災害現場で確認された農業気象災害軽減事例－ 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所 研究報告/(88)/pp.33-44, 2023-12-08
 移動の体験と景観 村上 暁信 IATSS Review（国際交通安全学会誌）/48(3)/p.149, 2024-02-29
-企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ 植田 直樹; 菊池 佐智子; 村上 暁信 都市計画報告集/22(4)/pp.586-591, 2024-03-11
-屋外空間利用がオフィスワーカーに与える心理・生理的影響とその要因に関する研究 池田 千紘; 村上 暁信 環境情報科学/53(1)/pp.128-128, 2024-04-15
-人流ビッグデータを用いた「Natural Cities」と温熱環境の関係分析についての研究 QUANG Nguyen Huu; 村上 暁信 環境情報科学/53(1)/pp.131-131, 2024-04-15
-季節の違いが緑化に対する支払意思額に与える影響 花田 大地; 村上 暁信 環境情報科学/53(1)/pp.115-115, 2024-04-15
-地域・土地との関係性の希薄化 村上 暁信 IATSS Review（国際交通安全学会誌）/49(1)/pp.106-107, 2024-06-30</t>
+企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ 植田 直樹; 菊池 佐智子; 村上 暁信 都市計画報告集/22(4)/pp.586-591, 2024-03-11</t>
         </is>
       </c>
     </row>
@@ -4862,8 +4887,11 @@
 数理情報学
 社会システム工学・安全システム
 応用確率論、 確率モデル、 待ち行列理論、 性能評価、 オペレーションズ・リサーチ、確率システム
-Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03
-Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03
+Retrial Queues: Scaling Limits Tuan Phung-Duc Journal of Systems Scalability/1(2)/pp.39-42, 2026-04
+Analysis of Multiserver Queues with Batch Arrivals and Setup Times Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.128-137, 2026-02
+Multi-Server Queues with s-staggered Setup: A Faster Computational Approach Thu Le-Anh; Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.118-127, 2026-02
+Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03 Tsukuba Repository
+Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03 Tsukuba Repository
 A simulation study of the sojourn time in queueing systems with stochastically delayed information Kazuma Abe; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering, 2025-12
 Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Proceedings of 2025 International Symposium on Nonlinear Theory and Its Applications (Nolta 2025)/pp.526-529, 2025-10
 Performance Analysis of Blockchain with Rollups Yusei Funahashi; Tuan Phung-Duc Proceedings of Asia-Pacific Conference on Communications (APCC) 2025, 2025-11 Tsukuba Repository
@@ -4883,10 +4911,7 @@
 Modeling and performance analysis of hybrid systems by queues with setup time Mitsuki Sato; Kohei Kawamura; Ken’ichi Kawanishi; Tuan... PERFORMANCE EVALUATION/162(102366), 2023-11
 Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis Yi Ren; Tuan Phung-Duc; Jyh-Cheng Chen; Frank Y. Li IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY/72(6)/pp.7743-7756, 2023-01
 Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04
-To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository
-A Two-Population Game in Observable Double-Ended Queueing Systems Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(4)/pp.407-414, 2022-07 Tsukuba Repository
-Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems Hung Quoc Nguyen; Tuan Phung-Duc COMPUTERS &amp; INDUSTRIAL ENGINEERING/170, 2022-08
-Analysis of a Batch Arrival Queue with Power Saving Mode Yuta Sakai; Tuan Phung-Duc Proceedings of 24th International Conference on INFORMATION TECHNOLOGIES AND MATHEMATICAL MODELLING (IТММ – 2025)/pp.70-75, 2024-10</t>
+To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4906,7 +4931,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03 / Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03 / A simulation study of the sojourn time in queueing systems with stochastically delayed information Kazuma Abe; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering, 2025-12 / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Proceedings of 2025 International Symposium on Nonlinear Theory and Its Applications (Nolta 2025)/pp.526-529, 2025-10 / Performance Analysis of Blockchain with Rollups Yusei Funahashi; Tuan Phung-Duc Proceedings of Asia-Pacific Conference on Communications (APCC) 2025, 2025-11 Tsukuba Repository / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times Nguyen Hung Q.; Phung-Duc Tuan Operations Research Letters/63(107362), 2025-11 Tsukuba Repository / Analysis of a Batch Arrival Queue with Power Saving Mode Yuta Sakai; Tuan Phung-Duc Communications in Computer and Information Science/2472/pp.181-192, 2025-05 / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes Thu Le-Anh; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering/663/pp.142-157, 2026-01 Tsukuba Repository / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes Thu Le-Anh; Tuan Phung-Duc Proceedings of 36th International Teletraffic Congress, 2025-06 Tsukuba Repository / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory Koki Inami; Tuan Phung-Duc Mathematics/13(6)/pp.1010-1-1010-18, 2025-03 Tsukuba Repository / Analytical Modelling of Asymmetric Multi-core Servers Marco Gribaudo; Tuan Phung-Duc Lecture Notes in Computer Science/15454/pp.121-136, 2025-02 / Energy-performance tradeoffs in server farms with batch services and setup times Le-Anh Thu; Phung-Duc Tuan PERFORMANCE EVALUATION/168, 2025-06 Tsukuba Repository / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers Nakamura Ayane; Phung-Duc Tuan TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/171, 2025-02 Tsukuba Repository / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Mathematics/12(18)/pp.2820-1-2820-27, 2024-09 / Queueing Analysis of an Ensemble Machine Learning System Keishin Tsutsumi; Tuan Phung-Duc; Hong-Linh Truong Lecture Notes in Computer Science/14826/pp.97-111, 2024-09 / Performance analysis of a collision channel with abandonments Fiems Dieter; Tuan Phung-Duc PERFORMANCE EVALUATION/165(102424), 2024-08 / Empirical architecture comparison of two-input machine learning systems for vision tasks Kazuya Wakigami; Fumio Machida; Tuan Phung-Duc Formal Aspects of Computing/36(4), 2024-06 / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes Ayane Nakamura; Tuan Phung-Duc QUEUEING SYSTEMS/106(1-2)/pp.129-158, 2023-11 / Modeling and performance analysis of hybrid systems by queues with setup time Mitsuki Sato; Kohei Kawamura; Ken’ichi Kawanishi; Tuan... PERFORMANCE EVALUATION/162(102366), 2023-11 / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis Yi Ren; Tuan Phung-Duc; Jyh-Cheng Chen; Frank Y. Li IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY/72(6)/pp.7743-7756, 2023-01 / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04 / To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository / A Two-Population Game in Observable Double-Ended Queueing Systems Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(4)/pp.407-414, 2022-07 Tsukuba Repository / Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems Hung Quoc Nguyen; Tuan Phung-Duc COMPUTERS &amp; INDUSTRIAL ENGINEERING/170, 2022-08 / Analysis of a Batch Arrival Queue with Power Saving Mode Yuta Sakai; Tuan Phung-Duc Proceedings of 24th International Conference on INFORMATION TECHNOLOGIES AND MATHEMATICAL MODELLING (IТММ – 2025)/pp.70-75, 2024-10</t>
+          <t>Retrial Queues: Scaling Limits Tuan Phung-Duc Journal of Systems Scalability/1(2)/pp.39-42, 2026-04 / Analysis of Multiserver Queues with Batch Arrivals and Setup Times Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.128-137, 2026-02 / Multi-Server Queues with s-staggered Setup: A Faster Computational Approach Thu Le-Anh; Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.118-127, 2026-02 / Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03 Tsukuba Repository / Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03 Tsukuba Repository / A simulation study of the sojourn time in queueing systems with stochastically delayed information Kazuma Abe; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering, 2025-12 / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Proceedings of 2025 International Symposium on Nonlinear Theory and Its Applications (Nolta 2025)/pp.526-529, 2025-10 / Performance Analysis of Blockchain with Rollups Yusei Funahashi; Tuan Phung-Duc Proceedings of Asia-Pacific Conference on Communications (APCC) 2025, 2025-11 Tsukuba Repository / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times Nguyen Hung Q.; Phung-Duc Tuan Operations Research Letters/63(107362), 2025-11 Tsukuba Repository / Analysis of a Batch Arrival Queue with Power Saving Mode Yuta Sakai; Tuan Phung-Duc Communications in Computer and Information Science/2472/pp.181-192, 2025-05 / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes Thu Le-Anh; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering/663/pp.142-157, 2026-01 Tsukuba Repository / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes Thu Le-Anh; Tuan Phung-Duc Proceedings of 36th International Teletraffic Congress, 2025-06 Tsukuba Repository / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory Koki Inami; Tuan Phung-Duc Mathematics/13(6)/pp.1010-1-1010-18, 2025-03 Tsukuba Repository / Analytical Modelling of Asymmetric Multi-core Servers Marco Gribaudo; Tuan Phung-Duc Lecture Notes in Computer Science/15454/pp.121-136, 2025-02 / Energy-performance tradeoffs in server farms with batch services and setup times Le-Anh Thu; Phung-Duc Tuan PERFORMANCE EVALUATION/168, 2025-06 Tsukuba Repository / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers Nakamura Ayane; Phung-Duc Tuan TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/171, 2025-02 Tsukuba Repository / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Mathematics/12(18)/pp.2820-1-2820-27, 2024-09 / Queueing Analysis of an Ensemble Machine Learning System Keishin Tsutsumi; Tuan Phung-Duc; Hong-Linh Truong Lecture Notes in Computer Science/14826/pp.97-111, 2024-09 / Performance analysis of a collision channel with abandonments Fiems Dieter; Tuan Phung-Duc PERFORMANCE EVALUATION/165(102424), 2024-08 / Empirical architecture comparison of two-input machine learning systems for vision tasks Kazuya Wakigami; Fumio Machida; Tuan Phung-Duc Formal Aspects of Computing/36(4), 2024-06 / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes Ayane Nakamura; Tuan Phung-Duc QUEUEING SYSTEMS/106(1-2)/pp.129-158, 2023-11 / Modeling and performance analysis of hybrid systems by queues with setup time Mitsuki Sato; Kohei Kawamura; Ken’ichi Kawanishi; Tuan... PERFORMANCE EVALUATION/162(102366), 2023-11 / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis Yi Ren; Tuan Phung-Duc; Jyh-Cheng Chen; Frank Y. Li IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY/72(6)/pp.7743-7756, 2023-01 / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04 / To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -4967,8 +4992,11 @@
 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化
 顧客の再試行と途中放棄を考慮したコールセンターのモデル化と性能解析
 再試行型待ち行列によるコールセンターの性能解析とサービス科学への応用
-Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03
-Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03
+Retrial Queues: Scaling Limits Tuan Phung-Duc Journal of Systems Scalability/1(2)/pp.39-42, 2026-04
+Analysis of Multiserver Queues with Batch Arrivals and Setup Times Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.128-137, 2026-02
+Multi-Server Queues with s-staggered Setup: A Faster Computational Approach Thu Le-Anh; Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.118-127, 2026-02
+Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03 Tsukuba Repository
+Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03 Tsukuba Repository
 A simulation study of the sojourn time in queueing systems with stochastically delayed information Kazuma Abe; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering, 2025-12
 Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Proceedings of 2025 International Symposium on Nonlinear Theory and Its Applications (Nolta 2025)/pp.526-529, 2025-10
 Performance Analysis of Blockchain with Rollups Yusei Funahashi; Tuan Phung-Duc Proceedings of Asia-Pacific Conference on Communications (APCC) 2025, 2025-11 Tsukuba Repository
@@ -4988,10 +5016,7 @@
 Modeling and performance analysis of hybrid systems by queues with setup time Mitsuki Sato; Kohei Kawamura; Ken’ichi Kawanishi; Tuan... PERFORMANCE EVALUATION/162(102366), 2023-11
 Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis Yi Ren; Tuan Phung-Duc; Jyh-Cheng Chen; Frank Y. Li IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY/72(6)/pp.7743-7756, 2023-01
 Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04
-To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository
-A Two-Population Game in Observable Double-Ended Queueing Systems Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(4)/pp.407-414, 2022-07 Tsukuba Repository
-Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems Hung Quoc Nguyen; Tuan Phung-Duc COMPUTERS &amp; INDUSTRIAL ENGINEERING/170, 2022-08
-Analysis of a Batch Arrival Queue with Power Saving Mode Yuta Sakai; Tuan Phung-Duc Proceedings of 24th International Conference on INFORMATION TECHNOLOGIES AND MATHEMATICAL MODELLING (IТММ – 2025)/pp.70-75, 2024-10</t>
+To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository</t>
         </is>
       </c>
     </row>
@@ -5043,6 +5068,8 @@
 産業集積
 都市・地域政策
 都市計画制度
+パネルディスカッション 未来志向のまちづくり 有田 智一; 坂井 文; 田中 仁; 山下 裕子; 大村 謙二郎 再開発コーディネーター/(240)/pp.15-28, 2026
+東京の集積の質的向上と多様性の高度化へ─土地・建物の高度利用を超えて 有田 智一 都市計画/75-3(380)/pp.18-21, 2026-05
 土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで 有田 智一 区画整理士会報/235/pp.48-52, 2025-07
 新しい時代の都市再生と公共貢献のあり方 有田 智一 新都市/79(9)/pp.13-17, 2025-09
 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 有田 智一 都市計画/pp.44-47, 2024-11
@@ -5065,9 +5092,7 @@
 “Planning transparency and public involvement in pre-application discussions,” Arita Tomokazu; Parker Gavin Journal of Town &amp; Country Planning/pp.66-70, 2019-02
 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 有田 智一 ビルディングレター/pp.16-17, 2018-05
 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) 有田 智一 都市問題/109(11)/pp.84-97, 2018-11
-集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ 梶塚 真良; 有田 智一 日本建築学会環境系論文集/83(751)/pp.791-799, 2018 CiNii Tsukuba Repository
-マイナンバー導入に伴う自治体業務情報システム改修事例に見るオープン化・標準化及び共同化の現状に関する研究 金崎健太郎; 川島宏一; 有田智一 情報システム学会誌/13(2), 2018-03
-マイナンバー導入事例に見る政府情報システム調達の現状に関する研究 金崎健太郎; 川島宏一; 有田智一 情報システム学会誌/14(1), 2018-09</t>
+集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ 梶塚 真良; 有田 智一 日本建築学会環境系論文集/83(751)/pp.791-799, 2018 CiNii Tsukuba Repository</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -5087,7 +5112,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで 有田 智一 区画整理士会報/235/pp.48-52, 2025-07 / 新しい時代の都市再生と公共貢献のあり方 有田 智一 新都市/79(9)/pp.13-17, 2025-09 / 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 有田 智一 都市計画/pp.44-47, 2024-11 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 川島 宏一; 石井樹; 有田 智一 地域安全学会論文集/(43)/pp.79-86, 2023-11 / 都市再開発のこれからの「必要性」と「可能性」 有田 智一 土地総合研究/pp.38-46, 2024-05 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 有田 智一 地域安全学会論文集 地域安全学会/43/pp.79-86, 2023-11 / 農村集落における区域区分制度を前提とした土地利用調整手法の実態と活用可能性に関する研究 有田 智一 都市計画論文集/58(3)/pp.1211-1218, 2023-10 / 土地建物一体型市街地整備の「必要性」と「可能性」 : これまでとこれから 有田 智一 区画整理/66(5)/pp.6-14, 2023-05 / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に 川島 宏一; 李珠善; 有田智一 情報処理学会研究報告, 2018-03 / つくば市による心肺停止傷病者発生位置情報の最寄AED管理者との共有が生み出す協働による救命効果に関する研究 川島 宏一; 有田 智一; 鈴木良介 計画行政/43(1)/pp.26-26, 2020-02-15 / 地方自治体におけるオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 川島 宏一; 有田智一 情報通信学会誌, 2021-09 / 東京都区部における開発実態の評価を踏まえた開発拠点誘導政策の課題に関する研究 鈴木 賢人; 有田 智一 都市計画論文集/56(3)/pp.881-888, 2021-10-25 CiNii / 公民連携による空き家・空き地対策組織の展開と運営実態 阿部 俊介; 有田 智一 都市計画論文集/56(3)/pp.1268-1274, 2021-10-25 CiNii / 避難行動要支援者名簿活用に向けた制度設計・運用プロセスにおける課題に関する研究 藤田 修平; 川島 宏一; 有田 智一; 岡本 正 地域安全学会論文集/39(0)/pp.145-153, 2021-11-01 / オープンデータ施策に総合的に取り組む地方自治体の動因に関する研究 川島 宏一; 有田智一; 野村敦子 自治体学/35(2), 2022-03 / 地方都市中心市街地における商店街の連続性を踏まえた空間整備の変遷と課題に関する研究 杉田 光; 有田 智一 都市計画報告集/21(1)/pp.57-63, 2022-06-08 / 地方自治体のオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 川島 宏一; 野村敦子; 有田智一 情報通信学会誌, 2021-09 / 世界からみた銀座のルールとガバナンス (特集 銀座と都市計画) -- (都市計画と銀座のルール) 有田 智一 都市計画 = City planning review/68(4)/pp.42-45, 2019-07-15 CiNii / 11027 地区スケールの賑わい空間構造の定量分析に関する研究 歩行空間と周辺土地利用に着目して 鈴木 賢人; 有田 智一 情報システム技術/(2019)/pp.53-54, 2019-07-20 CiNii / “Planning transparency and public involvement in pre-application discussions,” Arita Tomokazu; Parker Gavin Journal of Town &amp; Country Planning/pp.66-70, 2019-02 / 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 有田 智一 ビルディングレター/pp.16-17, 2018-05 / 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) 有田 智一 都市問題/109(11)/pp.84-97, 2018-11 / 集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ 梶塚 真良; 有田 智一 日本建築学会環境系論文集/83(751)/pp.791-799, 2018 CiNii Tsukuba Repository / マイナンバー導入に伴う自治体業務情報システム改修事例に見るオープン化・標準化及び共同化の現状に関する研究 金崎健太郎; 川島宏一; 有田智一 情報システム学会誌/13(2), 2018-03 / マイナンバー導入事例に見る政府情報システム調達の現状に関する研究 金崎健太郎; 川島宏一; 有田智一 情報システム学会誌/14(1), 2018-09</t>
+          <t>パネルディスカッション 未来志向のまちづくり 有田 智一; 坂井 文; 田中 仁; 山下 裕子; 大村 謙二郎 再開発コーディネーター/(240)/pp.15-28, 2026 / 東京の集積の質的向上と多様性の高度化へ─土地・建物の高度利用を超えて 有田 智一 都市計画/75-3(380)/pp.18-21, 2026-05 / 土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで 有田 智一 区画整理士会報/235/pp.48-52, 2025-07 / 新しい時代の都市再生と公共貢献のあり方 有田 智一 新都市/79(9)/pp.13-17, 2025-09 / 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 有田 智一 都市計画/pp.44-47, 2024-11 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 川島 宏一; 石井樹; 有田 智一 地域安全学会論文集/(43)/pp.79-86, 2023-11 / 都市再開発のこれからの「必要性」と「可能性」 有田 智一 土地総合研究/pp.38-46, 2024-05 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 有田 智一 地域安全学会論文集 地域安全学会/43/pp.79-86, 2023-11 / 農村集落における区域区分制度を前提とした土地利用調整手法の実態と活用可能性に関する研究 有田 智一 都市計画論文集/58(3)/pp.1211-1218, 2023-10 / 土地建物一体型市街地整備の「必要性」と「可能性」 : これまでとこれから 有田 智一 区画整理/66(5)/pp.6-14, 2023-05 / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に 川島 宏一; 李珠善; 有田智一 情報処理学会研究報告, 2018-03 / つくば市による心肺停止傷病者発生位置情報の最寄AED管理者との共有が生み出す協働による救命効果に関する研究 川島 宏一; 有田 智一; 鈴木良介 計画行政/43(1)/pp.26-26, 2020-02-15 / 地方自治体におけるオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 川島 宏一; 有田智一 情報通信学会誌, 2021-09 / 東京都区部における開発実態の評価を踏まえた開発拠点誘導政策の課題に関する研究 鈴木 賢人; 有田 智一 都市計画論文集/56(3)/pp.881-888, 2021-10-25 CiNii / 公民連携による空き家・空き地対策組織の展開と運営実態 阿部 俊介; 有田 智一 都市計画論文集/56(3)/pp.1268-1274, 2021-10-25 CiNii / 避難行動要支援者名簿活用に向けた制度設計・運用プロセスにおける課題に関する研究 藤田 修平; 川島 宏一; 有田 智一; 岡本 正 地域安全学会論文集/39(0)/pp.145-153, 2021-11-01 / オープンデータ施策に総合的に取り組む地方自治体の動因に関する研究 川島 宏一; 有田智一; 野村敦子 自治体学/35(2), 2022-03 / 地方都市中心市街地における商店街の連続性を踏まえた空間整備の変遷と課題に関する研究 杉田 光; 有田 智一 都市計画報告集/21(1)/pp.57-63, 2022-06-08 / 地方自治体のオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 川島 宏一; 野村敦子; 有田智一 情報通信学会誌, 2021-09 / 世界からみた銀座のルールとガバナンス (特集 銀座と都市計画) -- (都市計画と銀座のルール) 有田 智一 都市計画 = City planning review/68(4)/pp.42-45, 2019-07-15 CiNii / 11027 地区スケールの賑わい空間構造の定量分析に関する研究 歩行空間と周辺土地利用に着目して 鈴木 賢人; 有田 智一 情報システム技術/(2019)/pp.53-54, 2019-07-20 CiNii / “Planning transparency and public involvement in pre-application discussions,” Arita Tomokazu; Parker Gavin Journal of Town &amp; Country Planning/pp.66-70, 2019-02 / 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 有田 智一 ビルディングレター/pp.16-17, 2018-05 / 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) 有田 智一 都市問題/109(11)/pp.84-97, 2018-11 / 集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ 梶塚 真良; 有田 智一 日本建築学会環境系論文集/83(751)/pp.791-799, 2018 CiNii Tsukuba Repository</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -5161,6 +5186,8 @@
 イギリスの都市計画プランナーの職能団体による実務研修等を支えるシステムに関する研究
 オープンデータを踏まえた市民セクター主体のICT協働まちづくりに関する研究
 豪雨災害から避難弱者を守る共助的な避難行動計画づくりシステムに関する学際的研究
+パネルディスカッション 未来志向のまちづくり 有田 智一; 坂井 文; 田中 仁; 山下 裕子; 大村 謙二郎 再開発コーディネーター/(240)/pp.15-28, 2026
+東京の集積の質的向上と多様性の高度化へ─土地・建物の高度利用を超えて 有田 智一 都市計画/75-3(380)/pp.18-21, 2026-05
 土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで 有田 智一 区画整理士会報/235/pp.48-52, 2025-07
 新しい時代の都市再生と公共貢献のあり方 有田 智一 新都市/79(9)/pp.13-17, 2025-09
 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 有田 智一 都市計画/pp.44-47, 2024-11
@@ -5183,9 +5210,7 @@
 “Planning transparency and public involvement in pre-application discussions,” Arita Tomokazu; Parker Gavin Journal of Town &amp; Country Planning/pp.66-70, 2019-02
 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 有田 智一 ビルディングレター/pp.16-17, 2018-05
 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) 有田 智一 都市問題/109(11)/pp.84-97, 2018-11
-集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ 梶塚 真良; 有田 智一 日本建築学会環境系論文集/83(751)/pp.791-799, 2018 CiNii Tsukuba Repository
-マイナンバー導入に伴う自治体業務情報システム改修事例に見るオープン化・標準化及び共同化の現状に関する研究 金崎健太郎; 川島宏一; 有田智一 情報システム学会誌/13(2), 2018-03
-マイナンバー導入事例に見る政府情報システム調達の現状に関する研究 金崎健太郎; 川島宏一; 有田智一 情報システム学会誌/14(1), 2018-09</t>
+集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ 梶塚 真良; 有田 智一 日本建築学会環境系論文集/83(751)/pp.791-799, 2018 CiNii Tsukuba Repository</t>
         </is>
       </c>
     </row>
@@ -5223,6 +5248,7 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>形態・材料に着目した近代町家の地域性とその形成要因
+都市・住宅・クルマの相互関係比較史
 モビリティーイノベーションの社会応用と未来社会工学研究5
 モビリティーイノベーションの社会応用と未来社会工学研究3
 モビリティーイノベーションの社会応用と未来社会工学研究4
@@ -5231,7 +5257,6 @@
 江戸武家地の成熟過程に関する建築史・都市史的研究
 江戸武家地の空間変容に関する文理統合的研究
 北関東の町並みの建築的構成とその展開過程に関する研究
-常陸太田市鯨が丘歴史的建造物調査
 建築史・意匠
 都市計画・建築計画
 日本史
@@ -5239,6 +5264,14 @@
 都市史
 保全型都市計画
 居住環境史
+『盛世滋生図』に見られる清代蘇州城の商業区域と販売形態 呂 志裕; 藤川 昌樹 日本建築学会計画系論文集/91(840)/pp.500-511, 2026-02-01
+南宋蘇州城における商・工・流通業の空間の配置 藤川 昌樹; 呂 志裕 日本建築学会大会講演梗概集/pp.617-618, 2025-09
+明治初期の横浜居留地における外国人の土地賃借と利用状況：中国人の集住との関係に着目して 藤川 昌樹; 呂 夢琦 日本建築学会大会講演梗概集/pp.511-512, 2025-09
+2020年代に開発された郊外住宅地における住宅と駐車スペースの関係：茨城県 X 市の景観協定締結区域を事例に 藤川 昌樹; 宋 宇辰 日本建築学会大会講演梗概集/pp.617-618, 2025-09
+香取神宮参道の変遷 江戸時代から現在にかけて 藤川 昌樹; 渡辺 唯斗 日本建築学会大会講演梗概集/pp.631-632, 2025-09
+嵩山における四本の登拝道の成立とその位置づけ 藤川 昌樹; 楊 佳楽 日本建築学会大会講演梗概集/pp.477-478, 2025-09
+北京歴史文化保護区におけるシェントリフィケーションの実態とその形成過程：南鑼鼓巷を事例に 藤川 昌樹; 劉 嘉恵 日本建築学会大会講演梗概集/pp.499-500, 2025-09
+『乾隆南巡駐蹕図』から見た江蘇地域の南巡行宮の立地と構造 藤川 昌樹; 張 宇星 日本建築学会大会学術講演梗概集/pp.479-480, 2025-09
 近代中国青島市における「雑院一覧表 二十四年夏季」について 徐 暢; 藤川 昌樹 日本建築学会技術報告集/30(75)/pp.1062-1067, 2024-06-20
 五台山行宮座落地盤圖 からみた清代白雲寺行宮 余思奇; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.843-844, 2023-9
 嵩山史跡群における建物の空間構成および登封県の建立の経緯 楊 佳楽; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.841-842, 2023-9
@@ -5255,20 +5288,12 @@
 清代福州における住宅の三類型 陳穎; 藤川 昌樹 日本建築学会計画系論文集/(810)/pp.pp.2,436-2,443, 2023-8
 大正期から戦前までの山下町における中国系事業所と公共施設の立地と特徴–Japan Directory、商工案内の分析から– 呂夢琦; 藤川 昌樹 日本建築学会大会/建築史・意匠/pp.569-570, 2022-09
 清代福建省における「舗」の分布とその特性－連江県城を事例として－ 陳穎; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.503-504, 2022-09
-清代五台山顕通寺の火災と修復工程 余思奇; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.425-426, 2022-09
-明清時代漕運と京杭大運河沿い都市の空間特性との関係－臨清を例として－ 宋宇辰; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.423-424, 2022-09
-中国における団地構内の小規模野菜市場の空間利用－街商と住民の共存モデル－ 呂志裕; 藤川 昌樹 日本建築学会大会術講演梗概集/建築計画/pp.195-196, 2022-09
-新刊紹介『明暦の大火』 藤川 昌樹 都市史研究/(9)/pp.112-112, 2022-10
-五台山塔院寺の建築の構成とその変容 余思奇; 藤川 昌樹 日本建築学会計画系論文集/(799)/pp.1010-1020, 2022-09
-「奈良県橿原市今井町における駐車場の出現パターン：重要伝統的建造物群保存地区の駐車空間に関する研究 その2」 劉一辰・李雪・藤川 昌樹 『日本建築学会計画系論文報告集』/796/pp.1010-1020, 2022-6
-「真壁のこれから：過去・現在・未来」 藤川 昌樹 『かわら版』（ディスカバー真壁）/(21), 2021-12
-「商店街アーケードの空間の変容:十条銀座商店街を対象に」 酒巻裕作・藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.147-148, 2021-09
-「清代新疆の地域構造と都市群の立地 -軍政中心地イリを対象に- 」 シャキラ、藤川 昌樹 アリミナ 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.525-516, 2021-09</t>
+清代五台山顕通寺の火災と修復工程 余思奇; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.425-426, 2022-09</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>形態・材料に着目した近代町家の地域性とその形成要因 / モビリティーイノベーションの社会応用と未来社会工学研究5 / モビリティーイノベーションの社会応用と未来社会工学研究3 / モビリティーイノベーションの社会応用と未来社会工学研究4 / 石岡市歴史的景観及び里山景観調査研究 / 大火からの復興を通してみた近代の町並みの再評価 / 江戸武家地の成熟過程に関する建築史・都市史的研究 / 江戸武家地の空間変容に関する文理統合的研究 / 北関東の町並みの建築的構成とその展開過程に関する研究 / 常陸太田市鯨が丘歴史的建造物調査</t>
+          <t>形態・材料に着目した近代町家の地域性とその形成要因 / 都市・住宅・クルマの相互関係比較史 / モビリティーイノベーションの社会応用と未来社会工学研究5 / モビリティーイノベーションの社会応用と未来社会工学研究3 / モビリティーイノベーションの社会応用と未来社会工学研究4 / 石岡市歴史的景観及び里山景観調査研究 / 大火からの復興を通してみた近代の町並みの再評価 / 江戸武家地の成熟過程に関する建築史・都市史的研究 / 江戸武家地の空間変容に関する文理統合的研究 / 北関東の町並みの建築的構成とその展開過程に関する研究</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -5283,7 +5308,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>近代中国青島市における「雑院一覧表 二十四年夏季」について 徐 暢; 藤川 昌樹 日本建築学会技術報告集/30(75)/pp.1062-1067, 2024-06-20 / 五台山行宮座落地盤圖 からみた清代白雲寺行宮 余思奇; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.843-844, 2023-9 / 嵩山史跡群における建物の空間構成および登封県の建立の経緯 楊 佳楽; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.841-842, 2023-9 / 近代の町並み景観の多様性：大火からの復興を通してみた近代の町並みに関する研究 その 1 藤川 昌樹; 呂志裕; 楊 佳楽 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.167-168, 2023-9 / 戦後昭和期の横浜中華街における商住空間の分布と特徴：中区明細地図の考察から 呂夢琦; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.65-66, 2023-9 / 清代福州における住宅の類型とその特徴 古絵図 De Stud Hockzieuw en de stad Nanta を中心とした分析 陳穎; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp. 3-4, 2023-9 / 明清時代漕運と大運河沿いの都市空間特性との関係 その 2： 済寧を例として 宋宇辰; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp. 1-2, 2023-9 / 「白川郷における駐車空間の分布と交通整備の経緯：重要伝統的建造物群保存地区における駐車空間に関する研究」 芦澤美月; 劉一辰; 李雪; 藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.pp.739-740, 2023-9 / 『大日本職業別明細図之内』の空間表現 千葉県北部の地図を対象に 渡辺莉緒; 藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.pp. 157-158, 2023-9 / 観光開発を目的とした窯業集落の保全の実態とその課題： 中国陝西省澄城県の伝統村落・堯頭村を事例に 艾思思; 藤川 昌樹 日本建築学会大会学術講演梗概集/pp.pp.213-214, 2023-9 / 「清代蘇州の屋外空間における商人達の「自発的な居場所」 のパターン： 「姑蘇繁華図」の分析」 呂志裕; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築計画/pp.pp.1397-1398, 2023-9 / 新刊紹介『リスボン』 藤川 昌樹 建築史学/(81)/pp.p.223-226, 2023-9 / 明清時代における漕河沿い城・鎮の空間構成に関する研究（その1）：漕運システムと漕河沿岸空間の構成要素との関係 宋宇辰; 藤川 昌樹 日本建築学会計画系論文集/(814)/pp.3,416-3,425, 2023-12 / 清代福州における住宅の三類型 陳穎; 藤川 昌樹 日本建築学会計画系論文集/(810)/pp.pp.2,436-2,443, 2023-8 / 大正期から戦前までの山下町における中国系事業所と公共施設の立地と特徴–Japan Directory、商工案内の分析から– 呂夢琦; 藤川 昌樹 日本建築学会大会/建築史・意匠/pp.569-570, 2022-09 / 清代福建省における「舗」の分布とその特性－連江県城を事例として－ 陳穎; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.503-504, 2022-09 / 清代五台山顕通寺の火災と修復工程 余思奇; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.425-426, 2022-09 / 明清時代漕運と京杭大運河沿い都市の空間特性との関係－臨清を例として－ 宋宇辰; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.423-424, 2022-09 / 中国における団地構内の小規模野菜市場の空間利用－街商と住民の共存モデル－ 呂志裕; 藤川 昌樹 日本建築学会大会術講演梗概集/建築計画/pp.195-196, 2022-09 / 新刊紹介『明暦の大火』 藤川 昌樹 都市史研究/(9)/pp.112-112, 2022-10 / 五台山塔院寺の建築の構成とその変容 余思奇; 藤川 昌樹 日本建築学会計画系論文集/(799)/pp.1010-1020, 2022-09 / 「奈良県橿原市今井町における駐車場の出現パターン：重要伝統的建造物群保存地区の駐車空間に関する研究 その2」 劉一辰・李雪・藤川 昌樹 『日本建築学会計画系論文報告集』/796/pp.1010-1020, 2022-6 / 「真壁のこれから：過去・現在・未来」 藤川 昌樹 『かわら版』（ディスカバー真壁）/(21), 2021-12 / 「商店街アーケードの空間の変容:十条銀座商店街を対象に」 酒巻裕作・藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.147-148, 2021-09 / 「清代新疆の地域構造と都市群の立地 -軍政中心地イリを対象に- 」 シャキラ、藤川 昌樹 アリミナ 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.525-516, 2021-09</t>
+          <t>『盛世滋生図』に見られる清代蘇州城の商業区域と販売形態 呂 志裕; 藤川 昌樹 日本建築学会計画系論文集/91(840)/pp.500-511, 2026-02-01 / 南宋蘇州城における商・工・流通業の空間の配置 藤川 昌樹; 呂 志裕 日本建築学会大会講演梗概集/pp.617-618, 2025-09 / 明治初期の横浜居留地における外国人の土地賃借と利用状況：中国人の集住との関係に着目して 藤川 昌樹; 呂 夢琦 日本建築学会大会講演梗概集/pp.511-512, 2025-09 / 2020年代に開発された郊外住宅地における住宅と駐車スペースの関係：茨城県 X 市の景観協定締結区域を事例に 藤川 昌樹; 宋 宇辰 日本建築学会大会講演梗概集/pp.617-618, 2025-09 / 香取神宮参道の変遷 江戸時代から現在にかけて 藤川 昌樹; 渡辺 唯斗 日本建築学会大会講演梗概集/pp.631-632, 2025-09 / 嵩山における四本の登拝道の成立とその位置づけ 藤川 昌樹; 楊 佳楽 日本建築学会大会講演梗概集/pp.477-478, 2025-09 / 北京歴史文化保護区におけるシェントリフィケーションの実態とその形成過程：南鑼鼓巷を事例に 藤川 昌樹; 劉 嘉恵 日本建築学会大会講演梗概集/pp.499-500, 2025-09 / 『乾隆南巡駐蹕図』から見た江蘇地域の南巡行宮の立地と構造 藤川 昌樹; 張 宇星 日本建築学会大会学術講演梗概集/pp.479-480, 2025-09 / 近代中国青島市における「雑院一覧表 二十四年夏季」について 徐 暢; 藤川 昌樹 日本建築学会技術報告集/30(75)/pp.1062-1067, 2024-06-20 / 五台山行宮座落地盤圖 からみた清代白雲寺行宮 余思奇; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.843-844, 2023-9 / 嵩山史跡群における建物の空間構成および登封県の建立の経緯 楊 佳楽; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.841-842, 2023-9 / 近代の町並み景観の多様性：大火からの復興を通してみた近代の町並みに関する研究 その 1 藤川 昌樹; 呂志裕; 楊 佳楽 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.167-168, 2023-9 / 戦後昭和期の横浜中華街における商住空間の分布と特徴：中区明細地図の考察から 呂夢琦; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.65-66, 2023-9 / 清代福州における住宅の類型とその特徴 古絵図 De Stud Hockzieuw en de stad Nanta を中心とした分析 陳穎; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp. 3-4, 2023-9 / 明清時代漕運と大運河沿いの都市空間特性との関係 その 2： 済寧を例として 宋宇辰; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp. 1-2, 2023-9 / 「白川郷における駐車空間の分布と交通整備の経緯：重要伝統的建造物群保存地区における駐車空間に関する研究」 芦澤美月; 劉一辰; 李雪; 藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.pp.739-740, 2023-9 / 『大日本職業別明細図之内』の空間表現 千葉県北部の地図を対象に 渡辺莉緒; 藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.pp. 157-158, 2023-9 / 観光開発を目的とした窯業集落の保全の実態とその課題： 中国陝西省澄城県の伝統村落・堯頭村を事例に 艾思思; 藤川 昌樹 日本建築学会大会学術講演梗概集/pp.pp.213-214, 2023-9 / 「清代蘇州の屋外空間における商人達の「自発的な居場所」 のパターン： 「姑蘇繁華図」の分析」 呂志裕; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築計画/pp.pp.1397-1398, 2023-9 / 新刊紹介『リスボン』 藤川 昌樹 建築史学/(81)/pp.p.223-226, 2023-9 / 明清時代における漕河沿い城・鎮の空間構成に関する研究（その1）：漕運システムと漕河沿岸空間の構成要素との関係 宋宇辰; 藤川 昌樹 日本建築学会計画系論文集/(814)/pp.3,416-3,425, 2023-12 / 清代福州における住宅の三類型 陳穎; 藤川 昌樹 日本建築学会計画系論文集/(810)/pp.pp.2,436-2,443, 2023-8 / 大正期から戦前までの山下町における中国系事業所と公共施設の立地と特徴–Japan Directory、商工案内の分析から– 呂夢琦; 藤川 昌樹 日本建築学会大会/建築史・意匠/pp.569-570, 2022-09 / 清代福建省における「舗」の分布とその特性－連江県城を事例として－ 陳穎; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.503-504, 2022-09 / 清代五台山顕通寺の火災と修復工程 余思奇; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.425-426, 2022-09</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -5351,6 +5376,7 @@
 明清時代の役人住宅における職階制度と建築様式の関係—陳氏の住宅を例に
 北京市歴史文化保護区におけるジェントリフィケーションの実態とメカニズム―南鑼鼓巷を事例に
 形態・材料に着目した近代町家の地域性とその形成要因
+都市・住宅・クルマの相互関係比較史
 モビリティーイノベーションの社会応用と未来社会工学研究5
 モビリティーイノベーションの社会応用と未来社会工学研究3
 モビリティーイノベーションの社会応用と未来社会工学研究4
@@ -5359,7 +5385,14 @@
 江戸武家地の成熟過程に関する建築史・都市史的研究
 江戸武家地の空間変容に関する文理統合的研究
 北関東の町並みの建築的構成とその展開過程に関する研究
-常陸太田市鯨が丘歴史的建造物調査
+『盛世滋生図』に見られる清代蘇州城の商業区域と販売形態 呂 志裕; 藤川 昌樹 日本建築学会計画系論文集/91(840)/pp.500-511, 2026-02-01
+南宋蘇州城における商・工・流通業の空間の配置 藤川 昌樹; 呂 志裕 日本建築学会大会講演梗概集/pp.617-618, 2025-09
+明治初期の横浜居留地における外国人の土地賃借と利用状況：中国人の集住との関係に着目して 藤川 昌樹; 呂 夢琦 日本建築学会大会講演梗概集/pp.511-512, 2025-09
+2020年代に開発された郊外住宅地における住宅と駐車スペースの関係：茨城県 X 市の景観協定締結区域を事例に 藤川 昌樹; 宋 宇辰 日本建築学会大会講演梗概集/pp.617-618, 2025-09
+香取神宮参道の変遷 江戸時代から現在にかけて 藤川 昌樹; 渡辺 唯斗 日本建築学会大会講演梗概集/pp.631-632, 2025-09
+嵩山における四本の登拝道の成立とその位置づけ 藤川 昌樹; 楊 佳楽 日本建築学会大会講演梗概集/pp.477-478, 2025-09
+北京歴史文化保護区におけるシェントリフィケーションの実態とその形成過程：南鑼鼓巷を事例に 藤川 昌樹; 劉 嘉恵 日本建築学会大会講演梗概集/pp.499-500, 2025-09
+『乾隆南巡駐蹕図』から見た江蘇地域の南巡行宮の立地と構造 藤川 昌樹; 張 宇星 日本建築学会大会学術講演梗概集/pp.479-480, 2025-09
 近代中国青島市における「雑院一覧表 二十四年夏季」について 徐 暢; 藤川 昌樹 日本建築学会技術報告集/30(75)/pp.1062-1067, 2024-06-20
 五台山行宮座落地盤圖 からみた清代白雲寺行宮 余思奇; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.843-844, 2023-9
 嵩山史跡群における建物の空間構成および登封県の建立の経緯 楊 佳楽; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.841-842, 2023-9
@@ -5376,15 +5409,7 @@
 清代福州における住宅の三類型 陳穎; 藤川 昌樹 日本建築学会計画系論文集/(810)/pp.pp.2,436-2,443, 2023-8
 大正期から戦前までの山下町における中国系事業所と公共施設の立地と特徴–Japan Directory、商工案内の分析から– 呂夢琦; 藤川 昌樹 日本建築学会大会/建築史・意匠/pp.569-570, 2022-09
 清代福建省における「舗」の分布とその特性－連江県城を事例として－ 陳穎; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.503-504, 2022-09
-清代五台山顕通寺の火災と修復工程 余思奇; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.425-426, 2022-09
-明清時代漕運と京杭大運河沿い都市の空間特性との関係－臨清を例として－ 宋宇辰; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.423-424, 2022-09
-中国における団地構内の小規模野菜市場の空間利用－街商と住民の共存モデル－ 呂志裕; 藤川 昌樹 日本建築学会大会術講演梗概集/建築計画/pp.195-196, 2022-09
-新刊紹介『明暦の大火』 藤川 昌樹 都市史研究/(9)/pp.112-112, 2022-10
-五台山塔院寺の建築の構成とその変容 余思奇; 藤川 昌樹 日本建築学会計画系論文集/(799)/pp.1010-1020, 2022-09
-「奈良県橿原市今井町における駐車場の出現パターン：重要伝統的建造物群保存地区の駐車空間に関する研究 その2」 劉一辰・李雪・藤川 昌樹 『日本建築学会計画系論文報告集』/796/pp.1010-1020, 2022-6
-「真壁のこれから：過去・現在・未来」 藤川 昌樹 『かわら版』（ディスカバー真壁）/(21), 2021-12
-「商店街アーケードの空間の変容:十条銀座商店街を対象に」 酒巻裕作・藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.147-148, 2021-09
-「清代新疆の地域構造と都市群の立地 -軍政中心地イリを対象に- 」 シャキラ、藤川 昌樹 アリミナ 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.525-516, 2021-09</t>
+清代五台山顕通寺の火災と修復工程 余思奇; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.425-426, 2022-09</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5446,10 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化
+          <t>半導体撮像テスト結果を認識し、良・不良の判断を行うモデルに関する研究
+仮想3PLにおける在庫移動最適化
+安全モニタリング生成機能開発
+遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化
 ワークライフバランスに貢献するサイバー・フィジカル製造業
 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配
 半導体・液晶製造の良品スループット向上とコスト低減の両立を目指してQ-time制約の遵守と装置の生産性向上とを同時に実現する実時間最適オペレーション管理手法の研究
@@ -5432,6 +5460,18 @@
 生産システム工学
 オペレーション管理
 地域活性化
+建設現場部材の自動計数システム その2：物体判別と計数のための機械学習 金原壮汰; 髙田大右; 有馬 澄佳 日本建築学会2025梗概集/pp.１-2, 2025-09
+建設現場部材の自動計数システム その1：360°画像に基づく多種計器の計数 有馬 澄佳; 髙田大右; 金原壮汰; 岡本崇利; 本多花帆 日本建築学会2025梗概集/pp.1-2, 2025-09
+Data-Driven Modeling of Multi-Factory Production Systems with Tran, Product-mix and Re-entrant flows Sakurai Shuntaro; 有馬 澄佳 Proceedings of The Asia Pacific Industrial Engineering &amp; Management Systems Conference 2025 (APIEMS2025)/pp.1-6, 2025-11-07
+Automated Cause-Effect Discovery on Multivariate Time-series Data -Semiconductor production dynamics and process anomaly MAO Chendin; LI Ke; Xu X.; ARIMA Sumika Proceedings of The Semiconductor Wafer Test Asia Conference 2025 (SWTest Asia2025)/pp.1-2, 2025-11-20
+Multi-criteria Parameter Optimization for Complex Systems - Multi-Objective Scheduling Case AKIZUKI Hiroto; MAO Chendin; SUZUKI Yurika; LI Ke; YO... Proceedings of The Semiconductor Wafer Test Asia Conference 2025 (SWTest Asia2025)/pp.1-2, 2025-11-20
+Supply Chain Operation Coordination Optimization Based on Multi-objective Scheduling Lin Jia; ARIMA Sumika Proceedings of The 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07-14
+Masked Invariant Information Clustering for Visualized Multivariate Time-Series Data Sumiya Koichi; ARIMA Sumika Proceedings of The 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07-14
+Extended VAR-LinGAM Methods for Modeling Production System Dynamics Xu X.; Mao Chendin; Sakurai Shuntaro; ARIMA Sumika Proceedings of The proceedings of the 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07
+Detection and Localization of Defects Using Masked Image Modeling Yasuda Akira; Shishido Hayato; Nagai Kosuke; Sumiya K... Proceedings of Advanced Equipment Control/Advanced Process Control Symposium Asia 2025/pp.1-2, 2025-11
+Multi-Objective Multi-Factory Scheduling with Robust Optimization for Inter-Factory Routing Suzuki Yurika; 有馬 澄佳 Proceedings of International Conference on Operations Research and Enterprise Systems (ICORES) 2026/pp.1-7, 2026-03
+Interaction Modeling for High-Dimensional Mixed Data Considering Distribution and Correlation Ito Taiki; Matsuzawa Takuya; ARIMA Sumika Procedia Computer Science/270/pp.752-761, 2025-09
+The reduction of false positives in Sparse Factorization Machines Matsuzawa Takuya; Ito Taiki; ARIMA Sumika Procedia Computer Science/270/pp.802-811, 2025-09
 "INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH Ozawa H.; ITO T.; Matsuzawa T.; Hoshino S.; Watanabe ... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10
 Robust Classifications of WBM Defect Patterns ARIMA Sumika; AI T.; MAEDA T.; SUMIYA K.; ITO T.; TA... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10
 Due dates assignment based on customer changeability classifications in Make-to-order productoins Shishido I.; Sakurai S.; 有馬 澄佳 Proceedings of the Asia Pacific Industrial Engineering &amp; Management Systems Conference 2024/2024/pp.1-6, 2024-11
@@ -5444,24 +5484,12 @@
 Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL Ozawa H.; Hoshino S.; ARIMA Sumika Procedia Computer Science/246/pp.2953-2963, 2024-09
 MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION Lin Jia; MAO Chending; Arima Sumika Proceedings of International Symposium on Scheduling 2023/2023/pp.1-6, 2023-06-23
 Mixed-type Defect Pattern Classifications Maeda Takumi; Takada Daisuke; Arima Sumika Proceedings of AEC/APC Symposium Asia 2023/2023/pp.1-2, 2023-11-02
-Interaction Modelling of High Dimensional Production Data Hoshino Sara; Watanabe Kyo; Arima Sumika Procedia Computer Science/225/pp.4055-4064, 2023-12
-DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS Arima Sumika; Takahashi Haruki; Shishido Ibuki The Journal ACTA TECHNICA NAPOCENSIS - Series: APPLIED MATHEMATICS, MECHANICS, and ENGINEERING/66(1S)/pp.55-60, 2023-11
-MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN Arima Sumika; Tahara Yusaku; Nagai Kosuke The Journal ACTA TECHNICA NAPOCENSIS - Series: APPLIED MATHEMATICS, MECHANICS, and ENGINEERING/66(SI)/pp.105-112, 2023-11
-Data-driven Modeling for Production Dynamics Arima Sumika; Y. SASAKI; MORIE S.; KATAOKA Y.; MAO C.; LIN... Proceesings of IEEE International Symposium on Semiconductor Manufacturing 2022/pp.1-4, 2022-12-12
-Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption Arima Sumika; MAO C.; LIN J. Proceedings of IEEE International Symposium on Semiconductor Manufacturing 2022/pp.1-4, 2022-12
-MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - Arima Sumika; JIA Lin; Ohno Tomoki; MAO Chending; MORIE ... Proceedings of the 2022 International Symposium on Flexible Automation/(ISFA2022)/pp.1-8, 2022-07
-Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - Arima Sumika; BU Huizhen; NAGATA Takuya; ONODERA Kakeru The Journal of the Japan Industrial Management Association/pp.1-10, 2022-07
-Interaction Modelings for Industrial Data - for final quality estimation and proess integration Arima Sumika; Limin Qin; Nagata Takuya; Handa Kotaro; Wat... Proceeding of AEC/APC symposium Asia 2021/pp.1-4, 2021-11
-スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 有馬 澄佳; 半田滉太朗 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-スマートフォンアプリの起動順序に着目したユーザーセグメント分析 大野智暉; 有馬 澄佳 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-従属需要の予測手法の構築と検証 有馬 澄佳; 小川陽平 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-スマートフォンアプリの起動順序に着目したユーザーセグメント分析 有馬 澄佳; 大野智暉 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling J. LIN; Tomoki ONO; Sho MORIE; Qingxin ZHU; Yu SASAKI; Su... Proceedings of The International Symposium on Semiconductor Manufacturing 2020 (ISSM2020)/pp.1-4, 2020-12</t>
+Interaction Modelling of High Dimensional Production Data Hoshino Sara; Watanabe Kyo; Arima Sumika Procedia Computer Science/225/pp.4055-4064, 2023-12</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化 / ワークライフバランスに貢献するサイバー・フィジカル製造業 / 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配 / 半導体・液晶製造の良品スループット向上とコスト低減の両立を目指してQ-time制約の遵守と装置の生産性向上とを同時に実現する実時間最適オペレーション管理手法の研究 / ＱＣＤＲモデルに基づいて革新的な総合設備効率の向上と生産期間の短縮を実現する工場・設備の運用管理システム / ＱＣＤモデルに基づくマルチチャンバ装置および生産ラインの運用・設計方法 / 共創ビジョンに基づく半導体産業のビジネスモデル進化と、知財・人材の組織的流動化</t>
+          <t>半導体撮像テスト結果を認識し、良・不良の判断を行うモデルに関する研究 / 仮想3PLにおける在庫移動最適化 / 安全モニタリング生成機能開発 / 遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化 / ワークライフバランスに貢献するサイバー・フィジカル製造業 / 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配 / 半導体・液晶製造の良品スループット向上とコスト低減の両立を目指してQ-time制約の遵守と装置の生産性向上とを同時に実現する実時間最適オペレーション管理手法の研究 / ＱＣＤＲモデルに基づいて革新的な総合設備効率の向上と生産期間の短縮を実現する工場・設備の運用管理システム / ＱＣＤモデルに基づくマルチチャンバ装置および生産ラインの運用・設計方法 / 共創ビジョンに基づく半導体産業のビジネスモデル進化と、知財・人材の組織的流動化</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -5476,7 +5504,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>"INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH Ozawa H.; ITO T.; Matsuzawa T.; Hoshino S.; Watanabe ... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10 / Robust Classifications of WBM Defect Patterns ARIMA Sumika; AI T.; MAEDA T.; SUMIYA K.; ITO T.; TA... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10 / Due dates assignment based on customer changeability classifications in Make-to-order productoins Shishido I.; Sakurai S.; 有馬 澄佳 Proceedings of the Asia Pacific Industrial Engineering &amp; Management Systems Conference 2024/2024/pp.1-6, 2024-11 / Pipeline production model and sensitivity analysis of Engineering-to-Order products using system dynamics Nagai K.; 有馬 澄佳 Proceedings of the Asia Pacific Industrial Engineering &amp; Management Systems Conference 2024/2024/pp.1-6, 2024-11 / PRODUCTION AND JOB ROTATION PLANNING CONSIDERING DISABILITIES AND HEALTH CONDITIONS Watanabe Y.; Kashimoto N.; 有馬 澄佳 Proceedings of the 51st International Conference on Computers and Industrial Engineering (CIE51)/pp.1-10, 2024-12 / Classification of Multivariate Time Series Signals Using Self-Supervised Representation Learning Suzuki Y.; ARIMA Sumika Proceedings of International Symposium on Semiconductor Manufacturing/2024/pp.1-4, 2024-12 / Multi-factory Scheduling Considering the Trade-offs between Production Efficiency and Risks Suzuki Y.; ARIMA Sumika Proceedings of International Symposium on Semiconductor Manufacturing/2024/pp.1-4, 2024-12 / Analysis of Resilience Factors and Satisfaction in Life-line Charts for Life Career Developments ARIMA Sumika; Morita Sayuri; Yasuda Akira Proceedings of the 11th International Symposium on Affective Science and Engineering (ISASE2025)/pp.1-4, 2025-03 / Interaction Modeling for High-Dimensional Mixed Data with Numerical and Categorical Features Hoshino S.; Ito T.; Matsuzawa T.; ARIMA Sumika Procedia Computer Science/246/pp.2964-2973, 2024-09 / Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL Ozawa H.; Hoshino S.; ARIMA Sumika Procedia Computer Science/246/pp.2953-2963, 2024-09 / MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION Lin Jia; MAO Chending; Arima Sumika Proceedings of International Symposium on Scheduling 2023/2023/pp.1-6, 2023-06-23 / Mixed-type Defect Pattern Classifications Maeda Takumi; Takada Daisuke; Arima Sumika Proceedings of AEC/APC Symposium Asia 2023/2023/pp.1-2, 2023-11-02 / Interaction Modelling of High Dimensional Production Data Hoshino Sara; Watanabe Kyo; Arima Sumika Procedia Computer Science/225/pp.4055-4064, 2023-12 / DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS Arima Sumika; Takahashi Haruki; Shishido Ibuki The Journal ACTA TECHNICA NAPOCENSIS - Series: APPLIED MATHEMATICS, MECHANICS, and ENGINEERING/66(1S)/pp.55-60, 2023-11 / MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN Arima Sumika; Tahara Yusaku; Nagai Kosuke The Journal ACTA TECHNICA NAPOCENSIS - Series: APPLIED MATHEMATICS, MECHANICS, and ENGINEERING/66(SI)/pp.105-112, 2023-11 / Data-driven Modeling for Production Dynamics Arima Sumika; Y. SASAKI; MORIE S.; KATAOKA Y.; MAO C.; LIN... Proceesings of IEEE International Symposium on Semiconductor Manufacturing 2022/pp.1-4, 2022-12-12 / Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption Arima Sumika; MAO C.; LIN J. Proceedings of IEEE International Symposium on Semiconductor Manufacturing 2022/pp.1-4, 2022-12 / MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - Arima Sumika; JIA Lin; Ohno Tomoki; MAO Chending; MORIE ... Proceedings of the 2022 International Symposium on Flexible Automation/(ISFA2022)/pp.1-8, 2022-07 / Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - Arima Sumika; BU Huizhen; NAGATA Takuya; ONODERA Kakeru The Journal of the Japan Industrial Management Association/pp.1-10, 2022-07 / Interaction Modelings for Industrial Data - for final quality estimation and proess integration Arima Sumika; Limin Qin; Nagata Takuya; Handa Kotaro; Wat... Proceeding of AEC/APC symposium Asia 2021/pp.1-4, 2021-11 / スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 有馬 澄佳; 半田滉太朗 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 大野智暉; 有馬 澄佳 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10 / 従属需要の予測手法の構築と検証 有馬 澄佳; 小川陽平 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 有馬 澄佳; 大野智暉 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10 / Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling J. LIN; Tomoki ONO; Sho MORIE; Qingxin ZHU; Yu SASAKI; Su... Proceedings of The International Symposium on Semiconductor Manufacturing 2020 (ISSM2020)/pp.1-4, 2020-12</t>
+          <t>建設現場部材の自動計数システム その2：物体判別と計数のための機械学習 金原壮汰; 髙田大右; 有馬 澄佳 日本建築学会2025梗概集/pp.１-2, 2025-09 / 建設現場部材の自動計数システム その1：360°画像に基づく多種計器の計数 有馬 澄佳; 髙田大右; 金原壮汰; 岡本崇利; 本多花帆 日本建築学会2025梗概集/pp.1-2, 2025-09 / Data-Driven Modeling of Multi-Factory Production Systems with Tran, Product-mix and Re-entrant flows Sakurai Shuntaro; 有馬 澄佳 Proceedings of The Asia Pacific Industrial Engineering &amp; Management Systems Conference 2025 (APIEMS2025)/pp.1-6, 2025-11-07 / Automated Cause-Effect Discovery on Multivariate Time-series Data -Semiconductor production dynamics and process anomaly MAO Chendin; LI Ke; Xu X.; ARIMA Sumika Proceedings of The Semiconductor Wafer Test Asia Conference 2025 (SWTest Asia2025)/pp.1-2, 2025-11-20 / Multi-criteria Parameter Optimization for Complex Systems - Multi-Objective Scheduling Case AKIZUKI Hiroto; MAO Chendin; SUZUKI Yurika; LI Ke; YO... Proceedings of The Semiconductor Wafer Test Asia Conference 2025 (SWTest Asia2025)/pp.1-2, 2025-11-20 / Supply Chain Operation Coordination Optimization Based on Multi-objective Scheduling Lin Jia; ARIMA Sumika Proceedings of The 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07-14 / Masked Invariant Information Clustering for Visualized Multivariate Time-Series Data Sumiya Koichi; ARIMA Sumika Proceedings of The 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07-14 / Extended VAR-LinGAM Methods for Modeling Production System Dynamics Xu X.; Mao Chendin; Sakurai Shuntaro; ARIMA Sumika Proceedings of The proceedings of the 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07 / Detection and Localization of Defects Using Masked Image Modeling Yasuda Akira; Shishido Hayato; Nagai Kosuke; Sumiya K... Proceedings of Advanced Equipment Control/Advanced Process Control Symposium Asia 2025/pp.1-2, 2025-11 / Multi-Objective Multi-Factory Scheduling with Robust Optimization for Inter-Factory Routing Suzuki Yurika; 有馬 澄佳 Proceedings of International Conference on Operations Research and Enterprise Systems (ICORES) 2026/pp.1-7, 2026-03 / Interaction Modeling for High-Dimensional Mixed Data Considering Distribution and Correlation Ito Taiki; Matsuzawa Takuya; ARIMA Sumika Procedia Computer Science/270/pp.752-761, 2025-09 / The reduction of false positives in Sparse Factorization Machines Matsuzawa Takuya; Ito Taiki; ARIMA Sumika Procedia Computer Science/270/pp.802-811, 2025-09 / "INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH Ozawa H.; ITO T.; Matsuzawa T.; Hoshino S.; Watanabe ... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10 / Robust Classifications of WBM Defect Patterns ARIMA Sumika; AI T.; MAEDA T.; SUMIYA K.; ITO T.; TA... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10 / Due dates assignment based on customer changeability classifications in Make-to-order productoins Shishido I.; Sakurai S.; 有馬 澄佳 Proceedings of the Asia Pacific Industrial Engineering &amp; Management Systems Conference 2024/2024/pp.1-6, 2024-11 / Pipeline production model and sensitivity analysis of Engineering-to-Order products using system dynamics Nagai K.; 有馬 澄佳 Proceedings of the Asia Pacific Industrial Engineering &amp; Management Systems Conference 2024/2024/pp.1-6, 2024-11 / PRODUCTION AND JOB ROTATION PLANNING CONSIDERING DISABILITIES AND HEALTH CONDITIONS Watanabe Y.; Kashimoto N.; 有馬 澄佳 Proceedings of the 51st International Conference on Computers and Industrial Engineering (CIE51)/pp.1-10, 2024-12 / Classification of Multivariate Time Series Signals Using Self-Supervised Representation Learning Suzuki Y.; ARIMA Sumika Proceedings of International Symposium on Semiconductor Manufacturing/2024/pp.1-4, 2024-12 / Multi-factory Scheduling Considering the Trade-offs between Production Efficiency and Risks Suzuki Y.; ARIMA Sumika Proceedings of International Symposium on Semiconductor Manufacturing/2024/pp.1-4, 2024-12 / Analysis of Resilience Factors and Satisfaction in Life-line Charts for Life Career Developments ARIMA Sumika; Morita Sayuri; Yasuda Akira Proceedings of the 11th International Symposium on Affective Science and Engineering (ISASE2025)/pp.1-4, 2025-03 / Interaction Modeling for High-Dimensional Mixed Data with Numerical and Categorical Features Hoshino S.; Ito T.; Matsuzawa T.; ARIMA Sumika Procedia Computer Science/246/pp.2964-2973, 2024-09 / Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL Ozawa H.; Hoshino S.; ARIMA Sumika Procedia Computer Science/246/pp.2953-2963, 2024-09 / MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION Lin Jia; MAO Chending; Arima Sumika Proceedings of International Symposium on Scheduling 2023/2023/pp.1-6, 2023-06-23 / Mixed-type Defect Pattern Classifications Maeda Takumi; Takada Daisuke; Arima Sumika Proceedings of AEC/APC Symposium Asia 2023/2023/pp.1-2, 2023-11-02 / Interaction Modelling of High Dimensional Production Data Hoshino Sara; Watanabe Kyo; Arima Sumika Procedia Computer Science/225/pp.4055-4064, 2023-12</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -5486,12 +5514,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>制御・システム工学 ; 都市・地域政策 ; オペレーションズリサーチ ; 機械学習 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>制御・システム工学 ; 都市・地域政策 ; オペレーションズリサーチ ; 機械学習 ; 画像・視覚情報処理 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -5503,6 +5531,7 @@
 都市・地域政策
 オペレーションズリサーチ
 機械学習
+画像・視覚情報処理
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
@@ -5515,7 +5544,11 @@
 計画・スケジューリング
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+コンピュータビジョン
+画像認識
+行動認識
+マルチモーダル解析</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -5550,6 +5583,9 @@
 推薦システムによる多様なアプリの利用促進
 高次元データの交互作用モデリング-Adaptive SFMとSafe Pruningによる高精度化
 多様な建設現場の部材の検出と分類
+半導体撮像テスト結果を認識し、良・不良の判断を行うモデルに関する研究
+仮想3PLにおける在庫移動最適化
+安全モニタリング生成機能開発
 遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化
 ワークライフバランスに貢献するサイバー・フィジカル製造業
 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配
@@ -5557,6 +5593,18 @@
 ＱＣＤＲモデルに基づいて革新的な総合設備効率の向上と生産期間の短縮を実現する工場・設備の運用管理システム
 ＱＣＤモデルに基づくマルチチャンバ装置および生産ラインの運用・設計方法
 共創ビジョンに基づく半導体産業のビジネスモデル進化と、知財・人材の組織的流動化
+建設現場部材の自動計数システム その2：物体判別と計数のための機械学習 金原壮汰; 髙田大右; 有馬 澄佳 日本建築学会2025梗概集/pp.１-2, 2025-09
+建設現場部材の自動計数システム その1：360°画像に基づく多種計器の計数 有馬 澄佳; 髙田大右; 金原壮汰; 岡本崇利; 本多花帆 日本建築学会2025梗概集/pp.1-2, 2025-09
+Data-Driven Modeling of Multi-Factory Production Systems with Tran, Product-mix and Re-entrant flows Sakurai Shuntaro; 有馬 澄佳 Proceedings of The Asia Pacific Industrial Engineering &amp; Management Systems Conference 2025 (APIEMS2025)/pp.1-6, 2025-11-07
+Automated Cause-Effect Discovery on Multivariate Time-series Data -Semiconductor production dynamics and process anomaly MAO Chendin; LI Ke; Xu X.; ARIMA Sumika Proceedings of The Semiconductor Wafer Test Asia Conference 2025 (SWTest Asia2025)/pp.1-2, 2025-11-20
+Multi-criteria Parameter Optimization for Complex Systems - Multi-Objective Scheduling Case AKIZUKI Hiroto; MAO Chendin; SUZUKI Yurika; LI Ke; YO... Proceedings of The Semiconductor Wafer Test Asia Conference 2025 (SWTest Asia2025)/pp.1-2, 2025-11-20
+Supply Chain Operation Coordination Optimization Based on Multi-objective Scheduling Lin Jia; ARIMA Sumika Proceedings of The 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07-14
+Masked Invariant Information Clustering for Visualized Multivariate Time-Series Data Sumiya Koichi; ARIMA Sumika Proceedings of The 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07-14
+Extended VAR-LinGAM Methods for Modeling Production System Dynamics Xu X.; Mao Chendin; Sakurai Shuntaro; ARIMA Sumika Proceedings of The proceedings of the 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07
+Detection and Localization of Defects Using Masked Image Modeling Yasuda Akira; Shishido Hayato; Nagai Kosuke; Sumiya K... Proceedings of Advanced Equipment Control/Advanced Process Control Symposium Asia 2025/pp.1-2, 2025-11
+Multi-Objective Multi-Factory Scheduling with Robust Optimization for Inter-Factory Routing Suzuki Yurika; 有馬 澄佳 Proceedings of International Conference on Operations Research and Enterprise Systems (ICORES) 2026/pp.1-7, 2026-03
+Interaction Modeling for High-Dimensional Mixed Data Considering Distribution and Correlation Ito Taiki; Matsuzawa Takuya; ARIMA Sumika Procedia Computer Science/270/pp.752-761, 2025-09
+The reduction of false positives in Sparse Factorization Machines Matsuzawa Takuya; Ito Taiki; ARIMA Sumika Procedia Computer Science/270/pp.802-811, 2025-09
 "INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH Ozawa H.; ITO T.; Matsuzawa T.; Hoshino S.; Watanabe ... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10
 Robust Classifications of WBM Defect Patterns ARIMA Sumika; AI T.; MAEDA T.; SUMIYA K.; ITO T.; TA... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10
 Due dates assignment based on customer changeability classifications in Make-to-order productoins Shishido I.; Sakurai S.; 有馬 澄佳 Proceedings of the Asia Pacific Industrial Engineering &amp; Management Systems Conference 2024/2024/pp.1-6, 2024-11
@@ -5569,19 +5617,7 @@
 Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL Ozawa H.; Hoshino S.; ARIMA Sumika Procedia Computer Science/246/pp.2953-2963, 2024-09
 MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION Lin Jia; MAO Chending; Arima Sumika Proceedings of International Symposium on Scheduling 2023/2023/pp.1-6, 2023-06-23
 Mixed-type Defect Pattern Classifications Maeda Takumi; Takada Daisuke; Arima Sumika Proceedings of AEC/APC Symposium Asia 2023/2023/pp.1-2, 2023-11-02
-Interaction Modelling of High Dimensional Production Data Hoshino Sara; Watanabe Kyo; Arima Sumika Procedia Computer Science/225/pp.4055-4064, 2023-12
-DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS Arima Sumika; Takahashi Haruki; Shishido Ibuki The Journal ACTA TECHNICA NAPOCENSIS - Series: APPLIED MATHEMATICS, MECHANICS, and ENGINEERING/66(1S)/pp.55-60, 2023-11
-MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN Arima Sumika; Tahara Yusaku; Nagai Kosuke The Journal ACTA TECHNICA NAPOCENSIS - Series: APPLIED MATHEMATICS, MECHANICS, and ENGINEERING/66(SI)/pp.105-112, 2023-11
-Data-driven Modeling for Production Dynamics Arima Sumika; Y. SASAKI; MORIE S.; KATAOKA Y.; MAO C.; LIN... Proceesings of IEEE International Symposium on Semiconductor Manufacturing 2022/pp.1-4, 2022-12-12
-Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption Arima Sumika; MAO C.; LIN J. Proceedings of IEEE International Symposium on Semiconductor Manufacturing 2022/pp.1-4, 2022-12
-MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - Arima Sumika; JIA Lin; Ohno Tomoki; MAO Chending; MORIE ... Proceedings of the 2022 International Symposium on Flexible Automation/(ISFA2022)/pp.1-8, 2022-07
-Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - Arima Sumika; BU Huizhen; NAGATA Takuya; ONODERA Kakeru The Journal of the Japan Industrial Management Association/pp.1-10, 2022-07
-Interaction Modelings for Industrial Data - for final quality estimation and proess integration Arima Sumika; Limin Qin; Nagata Takuya; Handa Kotaro; Wat... Proceeding of AEC/APC symposium Asia 2021/pp.1-4, 2021-11
-スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 有馬 澄佳; 半田滉太朗 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-スマートフォンアプリの起動順序に着目したユーザーセグメント分析 大野智暉; 有馬 澄佳 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-従属需要の予測手法の構築と検証 有馬 澄佳; 小川陽平 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-スマートフォンアプリの起動順序に着目したユーザーセグメント分析 有馬 澄佳; 大野智暉 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling J. LIN; Tomoki ONO; Sho MORIE; Qingxin ZHU; Yu SASAKI; Su... Proceedings of The International Symposium on Semiconductor Manufacturing 2020 (ISSM2020)/pp.1-4, 2020-12</t>
+Interaction Modelling of High Dimensional Production Data Hoshino Sara; Watanabe Kyo; Arima Sumika Procedia Computer Science/225/pp.4055-4064, 2023-12</t>
         </is>
       </c>
     </row>
@@ -5853,6 +5889,18 @@
 不動産賃料
 土地利用
 立地分析
+マニラ首都圏における洪水リスクが不動産賃料に与える影響の分析 釜谷 紘生; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.91-91, 2025-12
+立地アメニティとオフィス賃料 －オフィスビルにおける交通利便性の再考－ 青木 日花; 松尾 和史; 今関 豊和; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.89-89, 2025-12
+東京国際空港新飛行経路による不動産価値への影響分析のための広域騒音推計 早坂 遼; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.101-101, 2025-12
+金融機関店舗の跡地利用についての考察 西原 梨沙子; 堤 盛人 地理情報システム学会 予稿集/p.P2-40, 2025-11-01
+地方自治体のマイナンバーカード普及の空間分析 伊柳 佑康; 堤 盛人 地理情報システム学会 予稿集/p.P2-36, 2025-11-01
+立地アメニティとオフィス賃料 －オフィスビルにおける交通利便性の再考－ 青木 日花; 堤 盛人 地理情報システム学会 予稿集/p.D1-04, 2025-11-01
+マニラ首都圏における洪水リスクが不動産賃料に与える影響の分析 ― 賃料帯の異質性に着目して ― 釜谷 紘生; 堤 盛人 地理情報システム学会 予稿集/p.D4-04, 2025-11-01
+東京国際空港新飛行経路による不動産価値への影響分析のための広域騒音推計 早坂 遼; 堤 盛人 地理情報システム学会 予稿集/p.D6-04, 2025-11-01
+地籍調査の進捗に関する地理空間分析－市区町村の担当部署に着目して－ 佐藤 佳乃; 堤 盛人 地理情報システム学会 予稿集/p.P2-26, 2025-11-01
+物流を明示的に考慮した 応用都市経済モデルの開発の試み 久保 拓也; 堤 盛人 土木計画学研究・講演集/71/p.P02-35, 2025-06-07
+茨城県における金融機関跡地の地理空間分布とその利用状況についての考察 西原 梨沙子; 堤 盛人; 松尾 和史 第土木計画学研究・講演集/71/p.P01-15, 2025-06-07
+オフィスビルアメニティの概念整理と実態分析 青木日花; 松尾 和史; 今関 豊和; 堤 盛人 土木計画学研究・講演集/71/p.P02-18, 2025-06
 立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ 松尾和史; 瀬谷創; 堤 盛人; 今関豊和 土木計画学研究・講演集/69, 2024-05
 東京23区における賃貸オフィスビルストックの地域性と経年変化 松尾和史; 堤 盛人; 今関豊和 第33回地理情報システム学会研究発表大会 講演論文集, 2024-10
 The Impact of the Flight to Quality on Office Rents and Vacancy Matsuo Kazushi; TSUTSUMI Morito; IMAZEKI Toyokazu; KUD... Real Estate Management and Valuation/32(3)/pp.77-86, 2024-04
@@ -5865,19 +5913,7 @@
 Spillover Effect of Large Building Construction on Neighborhood Office Rents Matsuo Kazushi; Tsutsumi Morito Journal of Real Estate Portfolio Management, 2024-02
 Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics Sakuma Makoto; Matsuo Kazushi; Tsutsumi Morito; Imazek... ASIA-PACIFIC JOURNAL OF REGIONAL SCIENCE/8(1)/pp.185-237, 2024-01
 Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market Matsuo Kazushi; Tsutsumi Morito; Imazeki Toyokazu INTERNATIONAL REAL ESTATE REVIEW/26(1)/pp.1-41, 2023-04
-ビッグデータのためのローカルなオフィス賃料指数の開発 松尾和史; 村上大輔; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/30, 2022-10
-オフィス空室率の時空間変動に関する探索的小地域分析 松尾和史; 堤 盛人; 今関豊和 ジャレフ・ジャーナル/13/pp.e11-e14, 2021-10
-東京オフィス市場における 集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木学会論文集D3（土木計画学研究・論文集）/78(5)/pp.I_263-I_274, 2023-05
-北陸新幹線開通による大学選択への影響に関する実証的研究 西村大希; 松尾和史; 堤 盛人 土木計画学研究・講演集(CD-ROM)/66, 2022-11-6
-計量テキスト分析による道路橋を維持管理する技術力の解明の試み 宮原 史; 堤 盛人 土木学会論文集D3（土木計画学）/78(3)/pp.137-149, 2022
-土木技術者の経験と学習 ―地方整備局職員の研究所出向と道路構造物を維持管理する技術力に着目して― 宮原史; 堤 盛人 土木学会論文集H（教育）/78(1)/pp.20-37, 2022
-空室率データで見る東京オフィス市場の空間的特性 松尾和史; 堤 盛人; 今関豊和 GIS理論と応用/30(1)/pp.51-63, 2022-06
-インフラの維持管理に関する研修による技術力向上効果の評価 ―道路橋の点検に着目して― 宮原史; 堤 盛人 土木学会論文集/79(1)/p.22-00132, 2023-04
-東京オフィス市場における集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木計画学研究発表会・講演集/65/pp.PS2-PS23, 2022-06-04
-携帯位置情報データを用いた東京23区内における“オフィス出社”の時空間分析 松尾和史; 佐久間誠; 堤 盛人; 今関豊和 土木計画学研究・講演集(CD-ROM)/64, 2021-12-03
-改訂版ブルーム・タキソノミーを用いた道路橋を維持管理する技術力の解明の試み 宮原史; 堤 盛人 日本教育工学会全国大会講演論文集, 2021-10-16
-交通アクセシビリティの変化が 中学受験における学校選択に与える影響 馬場優樹; 堤 盛人 土木計画学研究・講演集, 2021-06-05
-モバイル端末の活用による地方自治体の道路維持業務支援の検討 由井貴大; 堤 盛人; 新井千乃 土木計画学研究・講演集/63, 2021-06-05</t>
+ビッグデータのためのローカルなオフィス賃料指数の開発 松尾和史; 村上大輔; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/30, 2022-10</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5897,7 +5933,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ 松尾和史; 瀬谷創; 堤 盛人; 今関豊和 土木計画学研究・講演集/69, 2024-05 / 東京23区における賃貸オフィスビルストックの地域性と経年変化 松尾和史; 堤 盛人; 今関豊和 第33回地理情報システム学会研究発表大会 講演論文集, 2024-10 / The Impact of the Flight to Quality on Office Rents and Vacancy Matsuo Kazushi; TSUTSUMI Morito; IMAZEKI Toyokazu; KUD... Real Estate Management and Valuation/32(3)/pp.77-86, 2024-04 / Spillover Effect of Large Building Construction on Neighborhood Office Rents Matsuo Kazushi; TSUTSUMI Morito; IMAZEKI Toyokazu Journal of Real Estate Portfolio Management/30(2)/pp.103-120, 2024-02 / 地域属性と産業振興政策に着目した新設会社の立地に関する考察 堤 盛人; 木﨑拓真 土木計画学研究・講演集(CD-ROM)/67/p.P01-43, 2023 / 実用性を考慮したローカルな不動産価格指数の理論と実証. 松尾和史; 村上大輔; 堤 盛人; 今関豊和 土木計画学研究・講演集(CD-ROM)/67/p.P02-19, 2023 / デジタル化と立地がコロナ禍における私立中学校選択に与える影響. 馬場優樹; 伊柳佑康; 松尾和史; 堤 盛人 地理情報システム学会講演論文集/32/p.F1-03, 2023 / 大規模オフィスビルの竣工が近隣のオフィス賃料に与える影響：アメニティ効果 vs 供給効果. 松尾和史; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/32/pp.P1-P32, 2023 / 東京オフィス市場における 集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木学会論文集 D3 （土木計画学）/78/pp. I_263-I_274, 2023 / Spillover Effect of Large Building Construction on Neighborhood Office Rents Matsuo Kazushi; Tsutsumi Morito Journal of Real Estate Portfolio Management, 2024-02 / Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics Sakuma Makoto; Matsuo Kazushi; Tsutsumi Morito; Imazek... ASIA-PACIFIC JOURNAL OF REGIONAL SCIENCE/8(1)/pp.185-237, 2024-01 / Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market Matsuo Kazushi; Tsutsumi Morito; Imazeki Toyokazu INTERNATIONAL REAL ESTATE REVIEW/26(1)/pp.1-41, 2023-04 / ビッグデータのためのローカルなオフィス賃料指数の開発 松尾和史; 村上大輔; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/30, 2022-10 / オフィス空室率の時空間変動に関する探索的小地域分析 松尾和史; 堤 盛人; 今関豊和 ジャレフ・ジャーナル/13/pp.e11-e14, 2021-10 / 東京オフィス市場における 集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木学会論文集D3（土木計画学研究・論文集）/78(5)/pp.I_263-I_274, 2023-05 / 北陸新幹線開通による大学選択への影響に関する実証的研究 西村大希; 松尾和史; 堤 盛人 土木計画学研究・講演集(CD-ROM)/66, 2022-11-6 / 計量テキスト分析による道路橋を維持管理する技術力の解明の試み 宮原 史; 堤 盛人 土木学会論文集D3（土木計画学）/78(3)/pp.137-149, 2022 / 土木技術者の経験と学習 ―地方整備局職員の研究所出向と道路構造物を維持管理する技術力に着目して― 宮原史; 堤 盛人 土木学会論文集H（教育）/78(1)/pp.20-37, 2022 / 空室率データで見る東京オフィス市場の空間的特性 松尾和史; 堤 盛人; 今関豊和 GIS理論と応用/30(1)/pp.51-63, 2022-06 / インフラの維持管理に関する研修による技術力向上効果の評価 ―道路橋の点検に着目して― 宮原史; 堤 盛人 土木学会論文集/79(1)/p.22-00132, 2023-04 / 東京オフィス市場における集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木計画学研究発表会・講演集/65/pp.PS2-PS23, 2022-06-04 / 携帯位置情報データを用いた東京23区内における“オフィス出社”の時空間分析 松尾和史; 佐久間誠; 堤 盛人; 今関豊和 土木計画学研究・講演集(CD-ROM)/64, 2021-12-03 / 改訂版ブルーム・タキソノミーを用いた道路橋を維持管理する技術力の解明の試み 宮原史; 堤 盛人 日本教育工学会全国大会講演論文集, 2021-10-16 / 交通アクセシビリティの変化が 中学受験における学校選択に与える影響 馬場優樹; 堤 盛人 土木計画学研究・講演集, 2021-06-05 / モバイル端末の活用による地方自治体の道路維持業務支援の検討 由井貴大; 堤 盛人; 新井千乃 土木計画学研究・講演集/63, 2021-06-05</t>
+          <t>マニラ首都圏における洪水リスクが不動産賃料に与える影響の分析 釜谷 紘生; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.91-91, 2025-12 / 立地アメニティとオフィス賃料 －オフィスビルにおける交通利便性の再考－ 青木 日花; 松尾 和史; 今関 豊和; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.89-89, 2025-12 / 東京国際空港新飛行経路による不動産価値への影響分析のための広域騒音推計 早坂 遼; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.101-101, 2025-12 / 金融機関店舗の跡地利用についての考察 西原 梨沙子; 堤 盛人 地理情報システム学会 予稿集/p.P2-40, 2025-11-01 / 地方自治体のマイナンバーカード普及の空間分析 伊柳 佑康; 堤 盛人 地理情報システム学会 予稿集/p.P2-36, 2025-11-01 / 立地アメニティとオフィス賃料 －オフィスビルにおける交通利便性の再考－ 青木 日花; 堤 盛人 地理情報システム学会 予稿集/p.D1-04, 2025-11-01 / マニラ首都圏における洪水リスクが不動産賃料に与える影響の分析 ― 賃料帯の異質性に着目して ― 釜谷 紘生; 堤 盛人 地理情報システム学会 予稿集/p.D4-04, 2025-11-01 / 東京国際空港新飛行経路による不動産価値への影響分析のための広域騒音推計 早坂 遼; 堤 盛人 地理情報システム学会 予稿集/p.D6-04, 2025-11-01 / 地籍調査の進捗に関する地理空間分析－市区町村の担当部署に着目して－ 佐藤 佳乃; 堤 盛人 地理情報システム学会 予稿集/p.P2-26, 2025-11-01 / 物流を明示的に考慮した 応用都市経済モデルの開発の試み 久保 拓也; 堤 盛人 土木計画学研究・講演集/71/p.P02-35, 2025-06-07 / 茨城県における金融機関跡地の地理空間分布とその利用状況についての考察 西原 梨沙子; 堤 盛人; 松尾 和史 第土木計画学研究・講演集/71/p.P01-15, 2025-06-07 / オフィスビルアメニティの概念整理と実態分析 青木日花; 松尾 和史; 今関 豊和; 堤 盛人 土木計画学研究・講演集/71/p.P02-18, 2025-06 / 立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ 松尾和史; 瀬谷創; 堤 盛人; 今関豊和 土木計画学研究・講演集/69, 2024-05 / 東京23区における賃貸オフィスビルストックの地域性と経年変化 松尾和史; 堤 盛人; 今関豊和 第33回地理情報システム学会研究発表大会 講演論文集, 2024-10 / The Impact of the Flight to Quality on Office Rents and Vacancy Matsuo Kazushi; TSUTSUMI Morito; IMAZEKI Toyokazu; KUD... Real Estate Management and Valuation/32(3)/pp.77-86, 2024-04 / Spillover Effect of Large Building Construction on Neighborhood Office Rents Matsuo Kazushi; TSUTSUMI Morito; IMAZEKI Toyokazu Journal of Real Estate Portfolio Management/30(2)/pp.103-120, 2024-02 / 地域属性と産業振興政策に着目した新設会社の立地に関する考察 堤 盛人; 木﨑拓真 土木計画学研究・講演集(CD-ROM)/67/p.P01-43, 2023 / 実用性を考慮したローカルな不動産価格指数の理論と実証. 松尾和史; 村上大輔; 堤 盛人; 今関豊和 土木計画学研究・講演集(CD-ROM)/67/p.P02-19, 2023 / デジタル化と立地がコロナ禍における私立中学校選択に与える影響. 馬場優樹; 伊柳佑康; 松尾和史; 堤 盛人 地理情報システム学会講演論文集/32/p.F1-03, 2023 / 大規模オフィスビルの竣工が近隣のオフィス賃料に与える影響：アメニティ効果 vs 供給効果. 松尾和史; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/32/pp.P1-P32, 2023 / 東京オフィス市場における 集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木学会論文集 D3 （土木計画学）/78/pp. I_263-I_274, 2023 / Spillover Effect of Large Building Construction on Neighborhood Office Rents Matsuo Kazushi; Tsutsumi Morito Journal of Real Estate Portfolio Management, 2024-02 / Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics Sakuma Makoto; Matsuo Kazushi; Tsutsumi Morito; Imazek... ASIA-PACIFIC JOURNAL OF REGIONAL SCIENCE/8(1)/pp.185-237, 2024-01 / Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market Matsuo Kazushi; Tsutsumi Morito; Imazeki Toyokazu INTERNATIONAL REAL ESTATE REVIEW/26(1)/pp.1-41, 2023-04 / ビッグデータのためのローカルなオフィス賃料指数の開発 松尾和史; 村上大輔; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/30, 2022-10</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -5977,6 +6013,18 @@
 地方自治体における道路維持管理業務のため
 空間計量経済学における最重要課題への挑戦と新たな展開
 道路台帳を活かした道路アセットマネジメントに関する研究
+マニラ首都圏における洪水リスクが不動産賃料に与える影響の分析 釜谷 紘生; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.91-91, 2025-12
+立地アメニティとオフィス賃料 －オフィスビルにおける交通利便性の再考－ 青木 日花; 松尾 和史; 今関 豊和; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.89-89, 2025-12
+東京国際空港新飛行経路による不動産価値への影響分析のための広域騒音推計 早坂 遼; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.101-101, 2025-12
+金融機関店舗の跡地利用についての考察 西原 梨沙子; 堤 盛人 地理情報システム学会 予稿集/p.P2-40, 2025-11-01
+地方自治体のマイナンバーカード普及の空間分析 伊柳 佑康; 堤 盛人 地理情報システム学会 予稿集/p.P2-36, 2025-11-01
+立地アメニティとオフィス賃料 －オフィスビルにおける交通利便性の再考－ 青木 日花; 堤 盛人 地理情報システム学会 予稿集/p.D1-04, 2025-11-01
+マニラ首都圏における洪水リスクが不動産賃料に与える影響の分析 ― 賃料帯の異質性に着目して ― 釜谷 紘生; 堤 盛人 地理情報システム学会 予稿集/p.D4-04, 2025-11-01
+東京国際空港新飛行経路による不動産価値への影響分析のための広域騒音推計 早坂 遼; 堤 盛人 地理情報システム学会 予稿集/p.D6-04, 2025-11-01
+地籍調査の進捗に関する地理空間分析－市区町村の担当部署に着目して－ 佐藤 佳乃; 堤 盛人 地理情報システム学会 予稿集/p.P2-26, 2025-11-01
+物流を明示的に考慮した 応用都市経済モデルの開発の試み 久保 拓也; 堤 盛人 土木計画学研究・講演集/71/p.P02-35, 2025-06-07
+茨城県における金融機関跡地の地理空間分布とその利用状況についての考察 西原 梨沙子; 堤 盛人; 松尾 和史 第土木計画学研究・講演集/71/p.P01-15, 2025-06-07
+オフィスビルアメニティの概念整理と実態分析 青木日花; 松尾 和史; 今関 豊和; 堤 盛人 土木計画学研究・講演集/71/p.P02-18, 2025-06
 立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ 松尾和史; 瀬谷創; 堤 盛人; 今関豊和 土木計画学研究・講演集/69, 2024-05
 東京23区における賃貸オフィスビルストックの地域性と経年変化 松尾和史; 堤 盛人; 今関豊和 第33回地理情報システム学会研究発表大会 講演論文集, 2024-10
 The Impact of the Flight to Quality on Office Rents and Vacancy Matsuo Kazushi; TSUTSUMI Morito; IMAZEKI Toyokazu; KUD... Real Estate Management and Valuation/32(3)/pp.77-86, 2024-04
@@ -5989,19 +6037,7 @@
 Spillover Effect of Large Building Construction on Neighborhood Office Rents Matsuo Kazushi; Tsutsumi Morito Journal of Real Estate Portfolio Management, 2024-02
 Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics Sakuma Makoto; Matsuo Kazushi; Tsutsumi Morito; Imazek... ASIA-PACIFIC JOURNAL OF REGIONAL SCIENCE/8(1)/pp.185-237, 2024-01
 Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market Matsuo Kazushi; Tsutsumi Morito; Imazeki Toyokazu INTERNATIONAL REAL ESTATE REVIEW/26(1)/pp.1-41, 2023-04
-ビッグデータのためのローカルなオフィス賃料指数の開発 松尾和史; 村上大輔; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/30, 2022-10
-オフィス空室率の時空間変動に関する探索的小地域分析 松尾和史; 堤 盛人; 今関豊和 ジャレフ・ジャーナル/13/pp.e11-e14, 2021-10
-東京オフィス市場における 集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木学会論文集D3（土木計画学研究・論文集）/78(5)/pp.I_263-I_274, 2023-05
-北陸新幹線開通による大学選択への影響に関する実証的研究 西村大希; 松尾和史; 堤 盛人 土木計画学研究・講演集(CD-ROM)/66, 2022-11-6
-計量テキスト分析による道路橋を維持管理する技術力の解明の試み 宮原 史; 堤 盛人 土木学会論文集D3（土木計画学）/78(3)/pp.137-149, 2022
-土木技術者の経験と学習 ―地方整備局職員の研究所出向と道路構造物を維持管理する技術力に着目して― 宮原史; 堤 盛人 土木学会論文集H（教育）/78(1)/pp.20-37, 2022
-空室率データで見る東京オフィス市場の空間的特性 松尾和史; 堤 盛人; 今関豊和 GIS理論と応用/30(1)/pp.51-63, 2022-06
-インフラの維持管理に関する研修による技術力向上効果の評価 ―道路橋の点検に着目して― 宮原史; 堤 盛人 土木学会論文集/79(1)/p.22-00132, 2023-04
-東京オフィス市場における集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木計画学研究発表会・講演集/65/pp.PS2-PS23, 2022-06-04
-携帯位置情報データを用いた東京23区内における“オフィス出社”の時空間分析 松尾和史; 佐久間誠; 堤 盛人; 今関豊和 土木計画学研究・講演集(CD-ROM)/64, 2021-12-03
-改訂版ブルーム・タキソノミーを用いた道路橋を維持管理する技術力の解明の試み 宮原史; 堤 盛人 日本教育工学会全国大会講演論文集, 2021-10-16
-交通アクセシビリティの変化が 中学受験における学校選択に与える影響 馬場優樹; 堤 盛人 土木計画学研究・講演集, 2021-06-05
-モバイル端末の活用による地方自治体の道路維持業務支援の検討 由井貴大; 堤 盛人; 新井千乃 土木計画学研究・講演集/63, 2021-06-05</t>
+ビッグデータのためのローカルなオフィス賃料指数の開発 松尾和史; 村上大輔; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/30, 2022-10</t>
         </is>
       </c>
     </row>
@@ -6052,22 +6088,24 @@
 社会心理学
 環境心理学
 人間と環境の相互作用
-環境価値観・意識
+価値観・態度
 環境配慮行動
 気候関連行動
 場所愛着
+Drivers of plastic waste reduction in island communities in Central Vietnam: An application of the extended theory of planned behavior Nguyen Hue Thi Dang; KAIDA Naoko; Tamura Makoto Resources, Conservation &amp; Recycling Advances/29, 2026-03
 Validating the dragons of inaction psychological barriers (DIPB) scale in Japan and China: cross-cultural insights on climate change mitigation behaviors Liu Xun; Kaida Naoko Climatic Change/179(3), 2026-02-18
+出身地域の都市化度と景観認識の関係性：回復感・場所感覚・景観選好に着目して 及川智也; 甲斐田 直子 環境情報科学論文集/39/pp.334-341, 2025-12
+信仰と文化にもとづく環境観とプラスチック汚染緩和行動の関係性：マレーシアを対象に 糸井風音; 甲斐田 直子; Azrina Sobian; Norhayati Abdullah 環境情報科学論文集/39/pp.83-89, 2025-12
 Potentials of No Single-Use Plastic Initiatives for Plastic Waste Management in Island Communities in Central Vietnam: Insights from Local Stakeholder Interviews Nguyen Hue Thi Dang; KAIDA Naoko; Tamura Makoto Journal of Environmental Information Science/2025(1)/pp.10-20, 2025-12
-Drivers of plastic waste reduction in island communities in Central Vietnam: An application of the extended theory of planned behavior Nguyen Hue Thi Dang; KAIDA Naoko; Tamura Makoto Resources, Conservation &amp; Recycling Advances/29, 2026-03
 景観特性と心理的要因が回復環境形成に与える影響：都市・歴史文化・自然環境の比較 及川智也; 甲斐田 直子 都市計画論文集/60(3)/pp.1092-1099, 2025-10
 航空移動に対する環境負荷認識と相殺行動・主観的幸福感の関係性：日本国内航空会社マイレージ会員調査にもとづく検証 小濱幸平; KAIDA Naoko 環境情報科学論文集/38(2024)/pp.128-133, 2024-12
 騒音源公共施設の受容促進における情報提示の効果：質問紙実験による検証 森下陽平; KAIDA Naoko; 甲斐田幸佐; 近井学; 佐藤洋 環境情報科学論文集/38(2024)/pp.91-96, 2024-12
 Children’s Pro-Environmental Attitudes and Behaviors in Climate Change Mitigation: Findings from Japan and China Liu Xun; KAIDA Naoko 環境情報科学論文集/38(2024)/pp.134-140, 2024-12
 Parent-Child Intergenerational Associations of Environmental Attitudes, Psychological Barriers, and Pro-Environmental Behaviors in Japan and China Liu Xun; Kaida Naoko SUSTAINABILITY/16(23), 2024-12
+Relevance of faith and its positive associations with plastic pollution mitigation behaviors : Findings from Japan and Malaysia Itoi Kazane; KAIDA Naoko; Sobian Azrina; Abdullah Nor... Journal of Environmental Information Science/2924(1)/pp.23-34, 2024-10
+Psychological determinants of waste-related pro-environmental behavior by recreational anglers in inland waters in the Kanto region, Japan Shirato Kazuki; KAIDA Naoko Journal of Environmental Information Science/2924(1)/pp.13-22, 2024-10
 The function of REM and NREM sleep on memory distortion and consolidation Kaida Kosuke; Mori Ikue; Kihara Ken; Kaida Naoko INTERNATIONAL JOURNAL OF PSYCHOLOGY/59(1)/pp.152-153, 2024-08
 Health versus environment in alternative meat adoption: An experiment of communication strategies Obama Kohei; Itoi Kazane; Kaida Naoko INTERNATIONAL JOURNAL OF PSYCHOLOGY/59(1)/pp.301-301, 2024-08
-Relevance of faith and its positive associations with plastic pollution mitigation behaviors : Findings from Japan and Malaysia Itoi Kazane; KAIDA Naoko; Sobian Azrina; Abdullah Nor... Journal of Environmental Information Science/2924(1)/pp.23-34, 2024-10
-Psychological determinants of waste-related pro-environmental behavior by recreational anglers in inland waters in the Kanto region, Japan Shirato Kazuki; KAIDA Naoko Journal of Environmental Information Science/2924(1)/pp.13-22, 2024-10
 Opportunities and challenges for circular economy in the Maldives: A stakeholder analysis of informal E-waste management in the Greater Malé Region Mohammed Sumaa; Kaida Naoko Journal of Environmental Management/358/p.120944, 2024-05
 肉類消費抑制と代替肉普及のためのコミュニケーション方策の効果検証 小濱 幸平; 甲斐田 直子 環境情報科学学術研究論文集/37/pp.86-91, 2023-12
 The function of REM and NREM sleep on memory distortion and consolidation Kaida Kosuke; Mori Ikue; Kihara Ken; Kaida Naoko NEUROBIOLOGY OF LEARNING AND MEMORY/204, 2023-10
@@ -6078,9 +6116,7 @@
 環境問題を意識し始めた過去のきっかけと現在の環境配慮行動の関係：大学生を対象に 杉田真緒; 甲斐田 直子 環境情報科学論文集/36/pp.197-202, 2022-12
 路上ポイ捨ての理由と解決方策に関する認識比較分析：日本・マレーシア大学生を対象に 糸井 風音; 甲斐田 直子; 岩本 浩二; Azrina Sobian; Norhayati Abdullah; ... 環境情報科学論文集/36/pp.256-261, 2022-11
 Linking environmental knowledge, attitude, and behavior with place: a case study for strategic environmental education planning in Saint Lucia Kanada Momoe; Norman Paul; Kaida Naoko; Carver Steve Environmental Education Research, 2022-05
-環境問題を意識し始める契機と環境配慮行動の関係：大学生を対象に 杉田 真緒; 甲斐田 直子 環境心理学研究/p.14, 2022-04
-夜間屋外光環境に対する主観的評価と屋外行動の関係 王 童語; 山﨑 海; 甲斐田 直子; 甲斐田 幸佐 環境心理学研究/p.16, 2022-04
-Discrepancies between beliefs and practices on sleep as a factor of insomnia and negative feelings Kaida Kosuke; Kaida Naoko Psychological reports, 2021-05-26 PubMed</t>
+環境問題を意識し始める契機と環境配慮行動の関係：大学生を対象に 杉田 真緒; 甲斐田 直子 環境心理学研究/p.14, 2022-04</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6095,12 +6131,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>環境心理学 / 人間と環境の相互作用 / 環境価値観・意識 / 環境配慮行動 / 気候関連行動 / 場所愛着</t>
+          <t>環境心理学 / 人間と環境の相互作用 / 価値観・態度 / 環境配慮行動 / 気候関連行動 / 場所愛着</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Validating the dragons of inaction psychological barriers (DIPB) scale in Japan and China: cross-cultural insights on climate change mitigation behaviors Liu Xun; Kaida Naoko Climatic Change/179(3), 2026-02-18 / Potentials of No Single-Use Plastic Initiatives for Plastic Waste Management in Island Communities in Central Vietnam: Insights from Local Stakeholder Interviews Nguyen Hue Thi Dang; KAIDA Naoko; Tamura Makoto Journal of Environmental Information Science/2025(1)/pp.10-20, 2025-12 / Drivers of plastic waste reduction in island communities in Central Vietnam: An application of the extended theory of planned behavior Nguyen Hue Thi Dang; KAIDA Naoko; Tamura Makoto Resources, Conservation &amp; Recycling Advances/29, 2026-03 / 景観特性と心理的要因が回復環境形成に与える影響：都市・歴史文化・自然環境の比較 及川智也; 甲斐田 直子 都市計画論文集/60(3)/pp.1092-1099, 2025-10 / 航空移動に対する環境負荷認識と相殺行動・主観的幸福感の関係性：日本国内航空会社マイレージ会員調査にもとづく検証 小濱幸平; KAIDA Naoko 環境情報科学論文集/38(2024)/pp.128-133, 2024-12 / 騒音源公共施設の受容促進における情報提示の効果：質問紙実験による検証 森下陽平; KAIDA Naoko; 甲斐田幸佐; 近井学; 佐藤洋 環境情報科学論文集/38(2024)/pp.91-96, 2024-12 / Children’s Pro-Environmental Attitudes and Behaviors in Climate Change Mitigation: Findings from Japan and China Liu Xun; KAIDA Naoko 環境情報科学論文集/38(2024)/pp.134-140, 2024-12 / Parent-Child Intergenerational Associations of Environmental Attitudes, Psychological Barriers, and Pro-Environmental Behaviors in Japan and China Liu Xun; Kaida Naoko SUSTAINABILITY/16(23), 2024-12 / The function of REM and NREM sleep on memory distortion and consolidation Kaida Kosuke; Mori Ikue; Kihara Ken; Kaida Naoko INTERNATIONAL JOURNAL OF PSYCHOLOGY/59(1)/pp.152-153, 2024-08 / Health versus environment in alternative meat adoption: An experiment of communication strategies Obama Kohei; Itoi Kazane; Kaida Naoko INTERNATIONAL JOURNAL OF PSYCHOLOGY/59(1)/pp.301-301, 2024-08 / Relevance of faith and its positive associations with plastic pollution mitigation behaviors : Findings from Japan and Malaysia Itoi Kazane; KAIDA Naoko; Sobian Azrina; Abdullah Nor... Journal of Environmental Information Science/2924(1)/pp.23-34, 2024-10 / Psychological determinants of waste-related pro-environmental behavior by recreational anglers in inland waters in the Kanto region, Japan Shirato Kazuki; KAIDA Naoko Journal of Environmental Information Science/2924(1)/pp.13-22, 2024-10 / Opportunities and challenges for circular economy in the Maldives: A stakeholder analysis of informal E-waste management in the Greater Malé Region Mohammed Sumaa; Kaida Naoko Journal of Environmental Management/358/p.120944, 2024-05 / 肉類消費抑制と代替肉普及のためのコミュニケーション方策の効果検証 小濱 幸平; 甲斐田 直子 環境情報科学学術研究論文集/37/pp.86-91, 2023-12 / The function of REM and NREM sleep on memory distortion and consolidation Kaida Kosuke; Mori Ikue; Kihara Ken; Kaida Naoko NEUROBIOLOGY OF LEARNING AND MEMORY/204, 2023-10 / Associations of Positive and Negative Perceptions of Outdoor Artificial Light at Night with Nighttime Outdoor Behaviors and Health: Self-Reported Data Analyses on Urban and Suburban Residents in Japan Wang Tongyu; Kaida Naoko; Kaida Kosuke SUSTAINABILITY/15(17), 2023-09 / 容器包装プラスチック分別の社会的受容性：住民の納得感に着目して 川又豪士; 長谷川美紅; 甲斐田 直子 環境心理学研究/p.16, 2023-04 / Memory load of information encoded amplifies the magnitude of hindsight bias Kaida Kosuke; Kaida Naoko PLOS ONE/18(4)/p.e0283969, 2023-04 / Effects of outdoor artificial light at night on human health and behavior: A literature review Wang Tongyu; Kaida Naoko; Kaida Kosuke ENVIRONMENTAL POLLUTION/323/p.121321, 2023-04 / 環境問題を意識し始めた過去のきっかけと現在の環境配慮行動の関係：大学生を対象に 杉田真緒; 甲斐田 直子 環境情報科学論文集/36/pp.197-202, 2022-12 / 路上ポイ捨ての理由と解決方策に関する認識比較分析：日本・マレーシア大学生を対象に 糸井 風音; 甲斐田 直子; 岩本 浩二; Azrina Sobian; Norhayati Abdullah; ... 環境情報科学論文集/36/pp.256-261, 2022-11 / Linking environmental knowledge, attitude, and behavior with place: a case study for strategic environmental education planning in Saint Lucia Kanada Momoe; Norman Paul; Kaida Naoko; Carver Steve Environmental Education Research, 2022-05 / 環境問題を意識し始める契機と環境配慮行動の関係：大学生を対象に 杉田 真緒; 甲斐田 直子 環境心理学研究/p.14, 2022-04 / 夜間屋外光環境に対する主観的評価と屋外行動の関係 王 童語; 山﨑 海; 甲斐田 直子; 甲斐田 幸佐 環境心理学研究/p.16, 2022-04 / Discrepancies between beliefs and practices on sleep as a factor of insomnia and negative feelings Kaida Kosuke; Kaida Naoko Psychological reports, 2021-05-26 PubMed</t>
+          <t>Drivers of plastic waste reduction in island communities in Central Vietnam: An application of the extended theory of planned behavior Nguyen Hue Thi Dang; KAIDA Naoko; Tamura Makoto Resources, Conservation &amp; Recycling Advances/29, 2026-03 / Validating the dragons of inaction psychological barriers (DIPB) scale in Japan and China: cross-cultural insights on climate change mitigation behaviors Liu Xun; Kaida Naoko Climatic Change/179(3), 2026-02-18 / 出身地域の都市化度と景観認識の関係性：回復感・場所感覚・景観選好に着目して 及川智也; 甲斐田 直子 環境情報科学論文集/39/pp.334-341, 2025-12 / 信仰と文化にもとづく環境観とプラスチック汚染緩和行動の関係性：マレーシアを対象に 糸井風音; 甲斐田 直子; Azrina Sobian; Norhayati Abdullah 環境情報科学論文集/39/pp.83-89, 2025-12 / Potentials of No Single-Use Plastic Initiatives for Plastic Waste Management in Island Communities in Central Vietnam: Insights from Local Stakeholder Interviews Nguyen Hue Thi Dang; KAIDA Naoko; Tamura Makoto Journal of Environmental Information Science/2025(1)/pp.10-20, 2025-12 / 景観特性と心理的要因が回復環境形成に与える影響：都市・歴史文化・自然環境の比較 及川智也; 甲斐田 直子 都市計画論文集/60(3)/pp.1092-1099, 2025-10 / 航空移動に対する環境負荷認識と相殺行動・主観的幸福感の関係性：日本国内航空会社マイレージ会員調査にもとづく検証 小濱幸平; KAIDA Naoko 環境情報科学論文集/38(2024)/pp.128-133, 2024-12 / 騒音源公共施設の受容促進における情報提示の効果：質問紙実験による検証 森下陽平; KAIDA Naoko; 甲斐田幸佐; 近井学; 佐藤洋 環境情報科学論文集/38(2024)/pp.91-96, 2024-12 / Children’s Pro-Environmental Attitudes and Behaviors in Climate Change Mitigation: Findings from Japan and China Liu Xun; KAIDA Naoko 環境情報科学論文集/38(2024)/pp.134-140, 2024-12 / Parent-Child Intergenerational Associations of Environmental Attitudes, Psychological Barriers, and Pro-Environmental Behaviors in Japan and China Liu Xun; Kaida Naoko SUSTAINABILITY/16(23), 2024-12 / Relevance of faith and its positive associations with plastic pollution mitigation behaviors : Findings from Japan and Malaysia Itoi Kazane; KAIDA Naoko; Sobian Azrina; Abdullah Nor... Journal of Environmental Information Science/2924(1)/pp.23-34, 2024-10 / Psychological determinants of waste-related pro-environmental behavior by recreational anglers in inland waters in the Kanto region, Japan Shirato Kazuki; KAIDA Naoko Journal of Environmental Information Science/2924(1)/pp.13-22, 2024-10 / The function of REM and NREM sleep on memory distortion and consolidation Kaida Kosuke; Mori Ikue; Kihara Ken; Kaida Naoko INTERNATIONAL JOURNAL OF PSYCHOLOGY/59(1)/pp.152-153, 2024-08 / Health versus environment in alternative meat adoption: An experiment of communication strategies Obama Kohei; Itoi Kazane; Kaida Naoko INTERNATIONAL JOURNAL OF PSYCHOLOGY/59(1)/pp.301-301, 2024-08 / Opportunities and challenges for circular economy in the Maldives: A stakeholder analysis of informal E-waste management in the Greater Malé Region Mohammed Sumaa; Kaida Naoko Journal of Environmental Management/358/p.120944, 2024-05 / 肉類消費抑制と代替肉普及のためのコミュニケーション方策の効果検証 小濱 幸平; 甲斐田 直子 環境情報科学学術研究論文集/37/pp.86-91, 2023-12 / The function of REM and NREM sleep on memory distortion and consolidation Kaida Kosuke; Mori Ikue; Kihara Ken; Kaida Naoko NEUROBIOLOGY OF LEARNING AND MEMORY/204, 2023-10 / Associations of Positive and Negative Perceptions of Outdoor Artificial Light at Night with Nighttime Outdoor Behaviors and Health: Self-Reported Data Analyses on Urban and Suburban Residents in Japan Wang Tongyu; Kaida Naoko; Kaida Kosuke SUSTAINABILITY/15(17), 2023-09 / 容器包装プラスチック分別の社会的受容性：住民の納得感に着目して 川又豪士; 長谷川美紅; 甲斐田 直子 環境心理学研究/p.16, 2023-04 / Memory load of information encoded amplifies the magnitude of hindsight bias Kaida Kosuke; Kaida Naoko PLOS ONE/18(4)/p.e0283969, 2023-04 / Effects of outdoor artificial light at night on human health and behavior: A literature review Wang Tongyu; Kaida Naoko; Kaida Kosuke ENVIRONMENTAL POLLUTION/323/p.121321, 2023-04 / 環境問題を意識し始めた過去のきっかけと現在の環境配慮行動の関係：大学生を対象に 杉田真緒; 甲斐田 直子 環境情報科学論文集/36/pp.197-202, 2022-12 / 路上ポイ捨ての理由と解決方策に関する認識比較分析：日本・マレーシア大学生を対象に 糸井 風音; 甲斐田 直子; 岩本 浩二; Azrina Sobian; Norhayati Abdullah; ... 環境情報科学論文集/36/pp.256-261, 2022-11 / Linking environmental knowledge, attitude, and behavior with place: a case study for strategic environmental education planning in Saint Lucia Kanada Momoe; Norman Paul; Kaida Naoko; Carver Steve Environmental Education Research, 2022-05 / 環境問題を意識し始める契機と環境配慮行動の関係：大学生を対象に 杉田 真緒; 甲斐田 直子 環境心理学研究/p.14, 2022-04</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -6126,7 +6162,7 @@
 社会心理学
 環境心理学
 人間と環境の相互作用
-環境価値観・意識
+価値観・態度
 環境配慮行動
 気候関連行動
 場所愛着
@@ -6171,18 +6207,20 @@
 環境配慮行動と充足感のポジティブな連鎖に関する縦断的研究
 環境政策が市民の環境意識と省エネルギー行動に及ぼす波及効果
 新たな持続的開発指標にもとづく国際環境協力政策評価に関する研究
+Drivers of plastic waste reduction in island communities in Central Vietnam: An application of the extended theory of planned behavior Nguyen Hue Thi Dang; KAIDA Naoko; Tamura Makoto Resources, Conservation &amp; Recycling Advances/29, 2026-03
 Validating the dragons of inaction psychological barriers (DIPB) scale in Japan and China: cross-cultural insights on climate change mitigation behaviors Liu Xun; Kaida Naoko Climatic Change/179(3), 2026-02-18
+出身地域の都市化度と景観認識の関係性：回復感・場所感覚・景観選好に着目して 及川智也; 甲斐田 直子 環境情報科学論文集/39/pp.334-341, 2025-12
+信仰と文化にもとづく環境観とプラスチック汚染緩和行動の関係性：マレーシアを対象に 糸井風音; 甲斐田 直子; Azrina Sobian; Norhayati Abdullah 環境情報科学論文集/39/pp.83-89, 2025-12
 Potentials of No Single-Use Plastic Initiatives for Plastic Waste Management in Island Communities in Central Vietnam: Insights from Local Stakeholder Interviews Nguyen Hue Thi Dang; KAIDA Naoko; Tamura Makoto Journal of Environmental Information Science/2025(1)/pp.10-20, 2025-12
-Drivers of plastic waste reduction in island communities in Central Vietnam: An application of the extended theory of planned behavior Nguyen Hue Thi Dang; KAIDA Naoko; Tamura Makoto Resources, Conservation &amp; Recycling Advances/29, 2026-03
 景観特性と心理的要因が回復環境形成に与える影響：都市・歴史文化・自然環境の比較 及川智也; 甲斐田 直子 都市計画論文集/60(3)/pp.1092-1099, 2025-10
 航空移動に対する環境負荷認識と相殺行動・主観的幸福感の関係性：日本国内航空会社マイレージ会員調査にもとづく検証 小濱幸平; KAIDA Naoko 環境情報科学論文集/38(2024)/pp.128-133, 2024-12
 騒音源公共施設の受容促進における情報提示の効果：質問紙実験による検証 森下陽平; KAIDA Naoko; 甲斐田幸佐; 近井学; 佐藤洋 環境情報科学論文集/38(2024)/pp.91-96, 2024-12
 Children’s Pro-Environmental Attitudes and Behaviors in Climate Change Mitigation: Findings from Japan and China Liu Xun; KAIDA Naoko 環境情報科学論文集/38(2024)/pp.134-140, 2024-12
 Parent-Child Intergenerational Associations of Environmental Attitudes, Psychological Barriers, and Pro-Environmental Behaviors in Japan and China Liu Xun; Kaida Naoko SUSTAINABILITY/16(23), 2024-12
+Relevance of faith and its positive associations with plastic pollution mitigation behaviors : Findings from Japan and Malaysia Itoi Kazane; KAIDA Naoko; Sobian Azrina; Abdullah Nor... Journal of Environmental Information Science/2924(1)/pp.23-34, 2024-10
+Psychological determinants of waste-related pro-environmental behavior by recreational anglers in inland waters in the Kanto region, Japan Shirato Kazuki; KAIDA Naoko Journal of Environmental Information Science/2924(1)/pp.13-22, 2024-10
 The function of REM and NREM sleep on memory distortion and consolidation Kaida Kosuke; Mori Ikue; Kihara Ken; Kaida Naoko INTERNATIONAL JOURNAL OF PSYCHOLOGY/59(1)/pp.152-153, 2024-08
 Health versus environment in alternative meat adoption: An experiment of communication strategies Obama Kohei; Itoi Kazane; Kaida Naoko INTERNATIONAL JOURNAL OF PSYCHOLOGY/59(1)/pp.301-301, 2024-08
-Relevance of faith and its positive associations with plastic pollution mitigation behaviors : Findings from Japan and Malaysia Itoi Kazane; KAIDA Naoko; Sobian Azrina; Abdullah Nor... Journal of Environmental Information Science/2924(1)/pp.23-34, 2024-10
-Psychological determinants of waste-related pro-environmental behavior by recreational anglers in inland waters in the Kanto region, Japan Shirato Kazuki; KAIDA Naoko Journal of Environmental Information Science/2924(1)/pp.13-22, 2024-10
 Opportunities and challenges for circular economy in the Maldives: A stakeholder analysis of informal E-waste management in the Greater Malé Region Mohammed Sumaa; Kaida Naoko Journal of Environmental Management/358/p.120944, 2024-05
 肉類消費抑制と代替肉普及のためのコミュニケーション方策の効果検証 小濱 幸平; 甲斐田 直子 環境情報科学学術研究論文集/37/pp.86-91, 2023-12
 The function of REM and NREM sleep on memory distortion and consolidation Kaida Kosuke; Mori Ikue; Kihara Ken; Kaida Naoko NEUROBIOLOGY OF LEARNING AND MEMORY/204, 2023-10
@@ -6193,9 +6231,7 @@
 環境問題を意識し始めた過去のきっかけと現在の環境配慮行動の関係：大学生を対象に 杉田真緒; 甲斐田 直子 環境情報科学論文集/36/pp.197-202, 2022-12
 路上ポイ捨ての理由と解決方策に関する認識比較分析：日本・マレーシア大学生を対象に 糸井 風音; 甲斐田 直子; 岩本 浩二; Azrina Sobian; Norhayati Abdullah; ... 環境情報科学論文集/36/pp.256-261, 2022-11
 Linking environmental knowledge, attitude, and behavior with place: a case study for strategic environmental education planning in Saint Lucia Kanada Momoe; Norman Paul; Kaida Naoko; Carver Steve Environmental Education Research, 2022-05
-環境問題を意識し始める契機と環境配慮行動の関係：大学生を対象に 杉田 真緒; 甲斐田 直子 環境心理学研究/p.14, 2022-04
-夜間屋外光環境に対する主観的評価と屋外行動の関係 王 童語; 山﨑 海; 甲斐田 直子; 甲斐田 幸佐 環境心理学研究/p.16, 2022-04
-Discrepancies between beliefs and practices on sleep as a factor of insomnia and negative feelings Kaida Kosuke; Kaida Naoko Psychological reports, 2021-05-26 PubMed</t>
+環境問題を意識し始める契機と環境配慮行動の関係：大学生を対象に 杉田 真緒; 甲斐田 直子 環境心理学研究/p.14, 2022-04</t>
         </is>
       </c>
     </row>
@@ -6246,31 +6282,31 @@
 交通計画
 都市計画における態度・行動変容研究
 リスク･コミュニケーション
+自動運転バスのエクステリアへの印象評価と配慮行動意図に関する研究 星野明日美; 谷口 綾子; 河合英直 土木学会論文集D3(土木計画学(政策と実践)）, 2026
+一般市民の自動運転受容度の評価に向けた標準指標の提案 -複数都市への適用結果より- 前川凜; 谷口 綾子; 淺見知秀; 倉谷昌臣; 大井元揮; 金貞姫 土木学会論文集D3(土木計画学(政策と実践), 2026
+Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo Dibaj Samira; Keiichi Hizaki; Goto Rie; Taniguchi Aya... TRAVEL BEHAVIOUR AND SOCIETY/39, 2025-04
 ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07
-Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo Dibaj Samira; Keiichi Hizaki; Goto Rie; Taniguchi Aya... TRAVEL BEHAVIOUR AND SOCIETY/39, 2025-04
-Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt Miyadai Kasumi; Taniguchi Ayako INTERNATIONAL JOURNAL OF PSYCHOLOGY/58(1)/pp.403-403, 2023-12
-Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo TANIGUCHI Ayako Travel Behaviour and Society/39, 2025-04
-高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 交通工学, 2025-03
+高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 交通工学/11(3)/pp.11-21, 2025-03
+自動運転技術についての情報提供によるモラル・ハザード意識醸成可能性の基礎的実証研究 田中皓介; 中尾聡史; 谷口 綾子 実践政策学/10(2)/pp.149-154, 2024
+基礎自治体における電動キックボードビジネスのガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― 後藤りえ; 谷口 綾子; 樋崎恵一 交通工学論文集/10(2)/pp.10-18, 2024
+「東京2020オリパラ輸送チーム物語」の構築と，読者の態度変容－シビックプライドに着目して－ 中川権人; 谷口 綾子; 片桐暁 土木学会論文集D3（土木計画学（政策と実践））/80(3), 2024
+自動運転システムが地域のシビックプライドに与える影響 岩田剛弥; 谷口 綾子; 渡辺健太郎 実践政策学（Policy and Practice Studies）/9(2)/pp.217-225, 2024
+海外都市の専門家が懸念する電動キックボードシェアリング導入・運用の課題と助言 後藤りえ; 谷口 綾子; 樋崎恵一; 本間雄太 土木学会論文集D3（土木計画学（政策と実践）, 2023
 Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour Asumi Hoshino; TANIGUCHI Ayako; Kawai Terunao Proceeding of European Transport Conference held at Antwerp, 2024-09
+米国サンフランシスコ都市圏における自動運転タクシー普及に伴う社会的受容の変化―2時点のアンケート調査比較より― 谷口 綾子; 藤枝碧斗 第73回土木計画学研究・講演集(CD-ROM), 2026
+バス運転士不足問題に着目した自動運転技術の導入目的に関する新聞報道分析 織田渚颯; 谷口 綾子; 中尾聡史 第73回土木計画学研究・講演集(CD-ROM), 2026
+大学生の自転車ヘルメット着用阻害要因分析と官学連携による普及啓発策の提案 宗岡禾子; 植村菖太郎; 吉田歩加; 林凜太郎; 谷口 綾子; 平根英一; 安島結夏 第73回土木計画学研究・講演集(CD-ROM), 2026
+Mobility Communityの成長プロセスとReadiness Levelの指標化に関する試論 石部颯己; 神田佑亮; 竹口祐二; 土崎伸; 諸星賢治; 𠮷川令; 大井元揮; 東徹; 谷口 綾子 第73回土木計画学研究・講演集(CD-ROM), 2026
+米国サンフランシスコ都市圏における自動運転タクシーの社会的受容 -州政府との対話と市民意識調査結果より 谷口 綾子; 藤枝碧斗; 中川由賀; 鈴沖陽子; 岩月泰頼; 森田岳人; 宮木由貴子; 久保達弘 第72回土木計画学研究・講演集(CD-ROM), 2025
+超高齢社会体験ゲームが地域活動への態度に与える効果 吉田泰基; 谷口 綾子 第72回土木計画学研究・講演集(CD-ROM), 2025
+ドライブレコーダー映像を用いた自動運転バスの社会的受容評価に向けた基礎的集計 星野明日美; 谷口 綾子; 藤枝碧斗 第72回土木計画学研究・講演集(CD-ROM), 2025
+奥入瀬渓流利活用のあり方をめぐる関係主体の語りの質的分析 真谷健悟; 谷口 綾子; 倉谷昌臣 第72回土木計画学研究・講演集(CD-ROM), 2025
 おつかい行動に見る子どもの移動自由性の世代変化と要因分析 中尾聡史; 谷口 綾子; 山下知華; 新井優輔 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 真谷健悟; 谷口 綾子; 岩田剛弥 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 星野明日美; 谷口 綾子; 倉谷昌臣; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― 大月崇義; 谷口 綾子; 片桐暁; 吉田泰基 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― 織田渚颯; 谷口 綾子; 吉田泰基; 淺見知秀; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06
-モビリティのイノベーションに，モビリティ･マネジメントをどう活かすか？ 谷口 綾子 環境情報科学(特集：持続可能なモビリティシフト), 2025-04
-モビリティ・マネジメントと健康福祉・教育 谷口 綾子 都市住宅学(特集：健康に過ごせる都市・住宅づくり最前線)/(72), 2025-01
-日米の車両生成データ制作の現状とEUのData Actの波及可能性 齋木亮作; 谷口 綾子 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-SWC首長研究会への加盟有無(健康都市づくりに対する首長の意識)と公共交通分担率が住民の心身の健康に与える影響 内田海; 谷口 綾子; 田邉解; 久野譜也 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-「報復の空白」と「運」が交通事故時の道徳的判断に与える影響－自動運転と手動運転の比較分析－ 大野弘佑起; 谷口 綾子; 久木田水生 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-東京都区部の電動キックボードシェア利用実態と利用体験・交通手段別視点による比較分析 樋崎恵一; 谷口 綾子; 後藤りえ 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-米国における自動運転タクシーの社会的受容とその要因分析－人身事故経験を有する二都市に着目して 前川凜; 谷口 綾子 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-おつかい行動に見る子どもの移動自由性の世代変化とその要因分析，最近の調査研究から 谷口 綾子 日本交通政策研究会, 2024-11
-新たなモビリティの規制緩和－思考停止の日本人，大丈夫？ 谷口 綾子 都市計画/(371), 2024-10
-モビリティ・マネジメントとの出会いと今後 谷口 綾子; 淺見知秀 アーバン・アドバンス/82/pp.13-24, 2024-09
-基礎自治体における電動キックボードビジネス のガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― 後藤りえ; 谷口 綾子; 樋崎恵一 第69回土木計画学研究・講演集(CD-ROM), 2024-05
-高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 第69回土木計画学研究・講演集(CD-ROM), 2024-05
-米国の自動運転車両の事故発生後の 社会的受容の比較分析 前川凜; 谷口 綾子 第69回土木計画学研究・講演集(CD-ROM), 2024-05
-奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討 真谷健悟; 谷口 綾子; 倉谷昌臣 第69回土木計画学研究・講演集(CD-ROM), 2024-05</t>
+モビリティの潜在価値を最大化するプラットフォームや人材の要件に関する研究 山原けい; 神田佑亮; 竹口祐二; 大井元揮; 土崎伸; 𠮷川令; 東徹; 諸星賢治; 谷口 綾子 第71回土木計画学研究・講演集(CD-ROM), 2025</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6290,7 +6326,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07 / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo Dibaj Samira; Keiichi Hizaki; Goto Rie; Taniguchi Aya... TRAVEL BEHAVIOUR AND SOCIETY/39, 2025-04 / Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt Miyadai Kasumi; Taniguchi Ayako INTERNATIONAL JOURNAL OF PSYCHOLOGY/58(1)/pp.403-403, 2023-12 / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo TANIGUCHI Ayako Travel Behaviour and Society/39, 2025-04 / 高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 交通工学, 2025-03 / Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour Asumi Hoshino; TANIGUCHI Ayako; Kawai Terunao Proceeding of European Transport Conference held at Antwerp, 2024-09 / おつかい行動に見る子どもの移動自由性の世代変化と要因分析 中尾聡史; 谷口 綾子; 山下知華; 新井優輔 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 真谷健悟; 谷口 綾子; 岩田剛弥 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 星野明日美; 谷口 綾子; 倉谷昌臣; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― 大月崇義; 谷口 綾子; 片桐暁; 吉田泰基 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― 織田渚颯; 谷口 綾子; 吉田泰基; 淺見知秀; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / モビリティのイノベーションに，モビリティ･マネジメントをどう活かすか？ 谷口 綾子 環境情報科学(特集：持続可能なモビリティシフト), 2025-04 / モビリティ・マネジメントと健康福祉・教育 谷口 綾子 都市住宅学(特集：健康に過ごせる都市・住宅づくり最前線)/(72), 2025-01 / 日米の車両生成データ制作の現状とEUのData Actの波及可能性 齋木亮作; 谷口 綾子 第70回土木計画学研究・講演集(CD-ROM), 2024-11 / SWC首長研究会への加盟有無(健康都市づくりに対する首長の意識)と公共交通分担率が住民の心身の健康に与える影響 内田海; 谷口 綾子; 田邉解; 久野譜也 第70回土木計画学研究・講演集(CD-ROM), 2024-11 / 「報復の空白」と「運」が交通事故時の道徳的判断に与える影響－自動運転と手動運転の比較分析－ 大野弘佑起; 谷口 綾子; 久木田水生 第70回土木計画学研究・講演集(CD-ROM), 2024-11 / 東京都区部の電動キックボードシェア利用実態と利用体験・交通手段別視点による比較分析 樋崎恵一; 谷口 綾子; 後藤りえ 第70回土木計画学研究・講演集(CD-ROM), 2024-11 / 米国における自動運転タクシーの社会的受容とその要因分析－人身事故経験を有する二都市に着目して 前川凜; 谷口 綾子 第70回土木計画学研究・講演集(CD-ROM), 2024-11 / おつかい行動に見る子どもの移動自由性の世代変化とその要因分析，最近の調査研究から 谷口 綾子 日本交通政策研究会, 2024-11 / 新たなモビリティの規制緩和－思考停止の日本人，大丈夫？ 谷口 綾子 都市計画/(371), 2024-10 / モビリティ・マネジメントとの出会いと今後 谷口 綾子; 淺見知秀 アーバン・アドバンス/82/pp.13-24, 2024-09 / 基礎自治体における電動キックボードビジネス のガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― 後藤りえ; 谷口 綾子; 樋崎恵一 第69回土木計画学研究・講演集(CD-ROM), 2024-05 / 高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 第69回土木計画学研究・講演集(CD-ROM), 2024-05 / 米国の自動運転車両の事故発生後の 社会的受容の比較分析 前川凜; 谷口 綾子 第69回土木計画学研究・講演集(CD-ROM), 2024-05 / 奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討 真谷健悟; 谷口 綾子; 倉谷昌臣 第69回土木計画学研究・講演集(CD-ROM), 2024-05</t>
+          <t>自動運転バスのエクステリアへの印象評価と配慮行動意図に関する研究 星野明日美; 谷口 綾子; 河合英直 土木学会論文集D3(土木計画学(政策と実践)）, 2026 / 一般市民の自動運転受容度の評価に向けた標準指標の提案 -複数都市への適用結果より- 前川凜; 谷口 綾子; 淺見知秀; 倉谷昌臣; 大井元揮; 金貞姫 土木学会論文集D3(土木計画学(政策と実践), 2026 / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo Dibaj Samira; Keiichi Hizaki; Goto Rie; Taniguchi Aya... TRAVEL BEHAVIOUR AND SOCIETY/39, 2025-04 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07 / 高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 交通工学/11(3)/pp.11-21, 2025-03 / 自動運転技術についての情報提供によるモラル・ハザード意識醸成可能性の基礎的実証研究 田中皓介; 中尾聡史; 谷口 綾子 実践政策学/10(2)/pp.149-154, 2024 / 基礎自治体における電動キックボードビジネスのガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― 後藤りえ; 谷口 綾子; 樋崎恵一 交通工学論文集/10(2)/pp.10-18, 2024 / 「東京2020オリパラ輸送チーム物語」の構築と，読者の態度変容－シビックプライドに着目して－ 中川権人; 谷口 綾子; 片桐暁 土木学会論文集D3（土木計画学（政策と実践））/80(3), 2024 / 自動運転システムが地域のシビックプライドに与える影響 岩田剛弥; 谷口 綾子; 渡辺健太郎 実践政策学（Policy and Practice Studies）/9(2)/pp.217-225, 2024 / 海外都市の専門家が懸念する電動キックボードシェアリング導入・運用の課題と助言 後藤りえ; 谷口 綾子; 樋崎恵一; 本間雄太 土木学会論文集D3（土木計画学（政策と実践）, 2023 / Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour Asumi Hoshino; TANIGUCHI Ayako; Kawai Terunao Proceeding of European Transport Conference held at Antwerp, 2024-09 / 米国サンフランシスコ都市圏における自動運転タクシー普及に伴う社会的受容の変化―2時点のアンケート調査比較より― 谷口 綾子; 藤枝碧斗 第73回土木計画学研究・講演集(CD-ROM), 2026 / バス運転士不足問題に着目した自動運転技術の導入目的に関する新聞報道分析 織田渚颯; 谷口 綾子; 中尾聡史 第73回土木計画学研究・講演集(CD-ROM), 2026 / 大学生の自転車ヘルメット着用阻害要因分析と官学連携による普及啓発策の提案 宗岡禾子; 植村菖太郎; 吉田歩加; 林凜太郎; 谷口 綾子; 平根英一; 安島結夏 第73回土木計画学研究・講演集(CD-ROM), 2026 / Mobility Communityの成長プロセスとReadiness Levelの指標化に関する試論 石部颯己; 神田佑亮; 竹口祐二; 土崎伸; 諸星賢治; 𠮷川令; 大井元揮; 東徹; 谷口 綾子 第73回土木計画学研究・講演集(CD-ROM), 2026 / 米国サンフランシスコ都市圏における自動運転タクシーの社会的受容 -州政府との対話と市民意識調査結果より 谷口 綾子; 藤枝碧斗; 中川由賀; 鈴沖陽子; 岩月泰頼; 森田岳人; 宮木由貴子; 久保達弘 第72回土木計画学研究・講演集(CD-ROM), 2025 / 超高齢社会体験ゲームが地域活動への態度に与える効果 吉田泰基; 谷口 綾子 第72回土木計画学研究・講演集(CD-ROM), 2025 / ドライブレコーダー映像を用いた自動運転バスの社会的受容評価に向けた基礎的集計 星野明日美; 谷口 綾子; 藤枝碧斗 第72回土木計画学研究・講演集(CD-ROM), 2025 / 奥入瀬渓流利活用のあり方をめぐる関係主体の語りの質的分析 真谷健悟; 谷口 綾子; 倉谷昌臣 第72回土木計画学研究・講演集(CD-ROM), 2025 / おつかい行動に見る子どもの移動自由性の世代変化と要因分析 中尾聡史; 谷口 綾子; 山下知華; 新井優輔 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 真谷健悟; 谷口 綾子; 岩田剛弥 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 星野明日美; 谷口 綾子; 倉谷昌臣; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― 大月崇義; 谷口 綾子; 片桐暁; 吉田泰基 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― 織田渚颯; 谷口 綾子; 吉田泰基; 淺見知秀; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / モビリティの潜在価値を最大化するプラットフォームや人材の要件に関する研究 山原けい; 神田佑亮; 竹口祐二; 大井元揮; 土崎伸; 𠮷川令; 東徹; 諸星賢治; 谷口 綾子 第71回土木計画学研究・講演集(CD-ROM), 2025</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -6360,31 +6396,31 @@
 ASEAN諸国におけるモビリティ・マネジメントの実行可能性に関する実証分析
 道路上の異モード間コミュニケーションの生起と社会的受容
 健康に配慮した交通行動誘発のための学際的研究
+自動運転バスのエクステリアへの印象評価と配慮行動意図に関する研究 星野明日美; 谷口 綾子; 河合英直 土木学会論文集D3(土木計画学(政策と実践)）, 2026
+一般市民の自動運転受容度の評価に向けた標準指標の提案 -複数都市への適用結果より- 前川凜; 谷口 綾子; 淺見知秀; 倉谷昌臣; 大井元揮; 金貞姫 土木学会論文集D3(土木計画学(政策と実践), 2026
+Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo Dibaj Samira; Keiichi Hizaki; Goto Rie; Taniguchi Aya... TRAVEL BEHAVIOUR AND SOCIETY/39, 2025-04
 ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07
-Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo Dibaj Samira; Keiichi Hizaki; Goto Rie; Taniguchi Aya... TRAVEL BEHAVIOUR AND SOCIETY/39, 2025-04
-Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt Miyadai Kasumi; Taniguchi Ayako INTERNATIONAL JOURNAL OF PSYCHOLOGY/58(1)/pp.403-403, 2023-12
-Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo TANIGUCHI Ayako Travel Behaviour and Society/39, 2025-04
-高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 交通工学, 2025-03
+高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 交通工学/11(3)/pp.11-21, 2025-03
+自動運転技術についての情報提供によるモラル・ハザード意識醸成可能性の基礎的実証研究 田中皓介; 中尾聡史; 谷口 綾子 実践政策学/10(2)/pp.149-154, 2024
+基礎自治体における電動キックボードビジネスのガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― 後藤りえ; 谷口 綾子; 樋崎恵一 交通工学論文集/10(2)/pp.10-18, 2024
+「東京2020オリパラ輸送チーム物語」の構築と，読者の態度変容－シビックプライドに着目して－ 中川権人; 谷口 綾子; 片桐暁 土木学会論文集D3（土木計画学（政策と実践））/80(3), 2024
+自動運転システムが地域のシビックプライドに与える影響 岩田剛弥; 谷口 綾子; 渡辺健太郎 実践政策学（Policy and Practice Studies）/9(2)/pp.217-225, 2024
+海外都市の専門家が懸念する電動キックボードシェアリング導入・運用の課題と助言 後藤りえ; 谷口 綾子; 樋崎恵一; 本間雄太 土木学会論文集D3（土木計画学（政策と実践）, 2023
 Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour Asumi Hoshino; TANIGUCHI Ayako; Kawai Terunao Proceeding of European Transport Conference held at Antwerp, 2024-09
+米国サンフランシスコ都市圏における自動運転タクシー普及に伴う社会的受容の変化―2時点のアンケート調査比較より― 谷口 綾子; 藤枝碧斗 第73回土木計画学研究・講演集(CD-ROM), 2026
+バス運転士不足問題に着目した自動運転技術の導入目的に関する新聞報道分析 織田渚颯; 谷口 綾子; 中尾聡史 第73回土木計画学研究・講演集(CD-ROM), 2026
+大学生の自転車ヘルメット着用阻害要因分析と官学連携による普及啓発策の提案 宗岡禾子; 植村菖太郎; 吉田歩加; 林凜太郎; 谷口 綾子; 平根英一; 安島結夏 第73回土木計画学研究・講演集(CD-ROM), 2026
+Mobility Communityの成長プロセスとReadiness Levelの指標化に関する試論 石部颯己; 神田佑亮; 竹口祐二; 土崎伸; 諸星賢治; 𠮷川令; 大井元揮; 東徹; 谷口 綾子 第73回土木計画学研究・講演集(CD-ROM), 2026
+米国サンフランシスコ都市圏における自動運転タクシーの社会的受容 -州政府との対話と市民意識調査結果より 谷口 綾子; 藤枝碧斗; 中川由賀; 鈴沖陽子; 岩月泰頼; 森田岳人; 宮木由貴子; 久保達弘 第72回土木計画学研究・講演集(CD-ROM), 2025
+超高齢社会体験ゲームが地域活動への態度に与える効果 吉田泰基; 谷口 綾子 第72回土木計画学研究・講演集(CD-ROM), 2025
+ドライブレコーダー映像を用いた自動運転バスの社会的受容評価に向けた基礎的集計 星野明日美; 谷口 綾子; 藤枝碧斗 第72回土木計画学研究・講演集(CD-ROM), 2025
+奥入瀬渓流利活用のあり方をめぐる関係主体の語りの質的分析 真谷健悟; 谷口 綾子; 倉谷昌臣 第72回土木計画学研究・講演集(CD-ROM), 2025
 おつかい行動に見る子どもの移動自由性の世代変化と要因分析 中尾聡史; 谷口 綾子; 山下知華; 新井優輔 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 真谷健悟; 谷口 綾子; 岩田剛弥 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 星野明日美; 谷口 綾子; 倉谷昌臣; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― 大月崇義; 谷口 綾子; 片桐暁; 吉田泰基 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― 織田渚颯; 谷口 綾子; 吉田泰基; 淺見知秀; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06
-モビリティのイノベーションに，モビリティ･マネジメントをどう活かすか？ 谷口 綾子 環境情報科学(特集：持続可能なモビリティシフト), 2025-04
-モビリティ・マネジメントと健康福祉・教育 谷口 綾子 都市住宅学(特集：健康に過ごせる都市・住宅づくり最前線)/(72), 2025-01
-日米の車両生成データ制作の現状とEUのData Actの波及可能性 齋木亮作; 谷口 綾子 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-SWC首長研究会への加盟有無(健康都市づくりに対する首長の意識)と公共交通分担率が住民の心身の健康に与える影響 内田海; 谷口 綾子; 田邉解; 久野譜也 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-「報復の空白」と「運」が交通事故時の道徳的判断に与える影響－自動運転と手動運転の比較分析－ 大野弘佑起; 谷口 綾子; 久木田水生 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-東京都区部の電動キックボードシェア利用実態と利用体験・交通手段別視点による比較分析 樋崎恵一; 谷口 綾子; 後藤りえ 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-米国における自動運転タクシーの社会的受容とその要因分析－人身事故経験を有する二都市に着目して 前川凜; 谷口 綾子 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-おつかい行動に見る子どもの移動自由性の世代変化とその要因分析，最近の調査研究から 谷口 綾子 日本交通政策研究会, 2024-11
-新たなモビリティの規制緩和－思考停止の日本人，大丈夫？ 谷口 綾子 都市計画/(371), 2024-10
-モビリティ・マネジメントとの出会いと今後 谷口 綾子; 淺見知秀 アーバン・アドバンス/82/pp.13-24, 2024-09
-基礎自治体における電動キックボードビジネス のガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― 後藤りえ; 谷口 綾子; 樋崎恵一 第69回土木計画学研究・講演集(CD-ROM), 2024-05
-高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 第69回土木計画学研究・講演集(CD-ROM), 2024-05
-米国の自動運転車両の事故発生後の 社会的受容の比較分析 前川凜; 谷口 綾子 第69回土木計画学研究・講演集(CD-ROM), 2024-05
-奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討 真谷健悟; 谷口 綾子; 倉谷昌臣 第69回土木計画学研究・講演集(CD-ROM), 2024-05</t>
+モビリティの潜在価値を最大化するプラットフォームや人材の要件に関する研究 山原けい; 神田佑亮; 竹口祐二; 大井元揮; 土崎伸; 𠮷川令; 東徹; 諸星賢治; 谷口 綾子 第71回土木計画学研究・講演集(CD-ROM), 2025</t>
         </is>
       </c>
     </row>
@@ -6423,6 +6459,7 @@
         <is>
           <t>トポロジー的組合せ論と組合せ論におけるトポロジー的手法
 組合せ的構造に関する研究
+単体的複体のシェラビリティーおよび関連概念、極小反例の視点による研究
 Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求
 デジタル指紋符号、多重接続通信路、及び組合せ探索問題
 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発
@@ -6430,7 +6467,6 @@
 部分構造への等質性を基軸とする単体的複体の構造解析
 ネットワーク上の時間軸をもった最適化問題とその応用
 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化
-実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開
 数学基礎・応用数学
 組合せ論
 トポロジー的組合せ論
@@ -6467,7 +6503,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>トポロジー的組合せ論と組合せ論におけるトポロジー的手法 / 組合せ的構造に関する研究 / Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求 / デジタル指紋符号、多重接続通信路、及び組合せ探索問題 / 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / 部分構造への等質性を基軸とする単体的複体の構造解析 / ネットワーク上の時間軸をもった最適化問題とその応用 / 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化 / 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開</t>
+          <t>トポロジー的組合せ論と組合せ論におけるトポロジー的手法 / 組合せ的構造に関する研究 / 単体的複体のシェラビリティーおよび関連概念、極小反例の視点による研究 / Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求 / デジタル指紋符号、多重接続通信路、及び組合せ探索問題 / 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / 部分構造への等質性を基軸とする単体的複体の構造解析 / ネットワーク上の時間軸をもった最適化問題とその応用 / 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -6533,6 +6569,7 @@
 特定の形をした直径が6の木グラフに対するGraceful Labeling
 トポロジー的組合せ論と組合せ論におけるトポロジー的手法
 組合せ的構造に関する研究
+単体的複体のシェラビリティーおよび関連概念、極小反例の視点による研究
 Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求
 デジタル指紋符号、多重接続通信路、及び組合せ探索問題
 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発
@@ -6540,7 +6577,6 @@
 部分構造への等質性を基軸とする単体的複体の構造解析
 ネットワーク上の時間軸をもった最適化問題とその応用
 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化
-実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開
 The average expected value of a rooted graph, Monte Carlo calculation, and a power index for the voting game Hachimori Masahiro Discrete Applied Mathematics/377/pp.74-86, 2025-12
 Coloring zonotopal quadrangulations of the projective space Masahiro Hachimori; Atsuhiro Nakamoto; Kenta Ozeki EUROPEAN JOURNAL OF COMBINATORICS/125/p.104089, 2025-03
 Several minimality concepts related to Frankl's conjecture Masahiro Hachimori; Kenji Kashiwabara Graphs and Combinatorics/40(6), 2024-11
@@ -6616,6 +6652,7 @@
 符号理論
 情報セキュリティ
 グループ検査
+FRACTAL DIMENSION OF SUBSTITUTION TREE NETWORKS Zeng Qingcheng; Xue Yumei; Wang Daohua; Miao Ying FRACTALS-COMPLEX GEOMETRY PATTERNS AND SCALING IN NATURE AND SOCIETY, 2025-10-28
 版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) MIAO Ying 中国科学数学, 2023
 A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) MIAO Ying 2022 IEEE International Multi-Conference on Engineering, Computer and Information Sciences (SIBIRCON), 2022/11
 Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) MIAO Ying Problems of Information Transmission/59(1)/pp.14-21, 2023/1
@@ -6639,8 +6676,7 @@
 Probabilistic Existence Results for Parent-Identifying Schemes Gu Yujie; Cheng Minquan; Kabatiansky Grigory; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/65(10)/pp.6160-6170, 2019-10
 Non-adaptive group testing on graphs with connectivity Luo S.; Matsuura Y.; Miao Ying; Shigeno Maiko Journal of Combinatorial Optimization/38(1)/pp.278-291, 2019
 Bounds on Traceability Schemes Gu Yujie; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/64(5)/pp.3450-3460, 2018-05
-New Bounds for Frameproof Codes Shangguan Chong; Wang Xin; Ge Gennian; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/63(11)/pp.7247-7252, 2017-11
-Zero-difference balanced functions with new parameters and their applications Cai H.; Zhou Z.; Tang X; Miao Ying IEEE Transactions on Information Theory/63(7)/pp.4379-4387, 2017-06</t>
+New Bounds for Frameproof Codes Shangguan Chong; Wang Xin; Ge Gennian; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/63(11)/pp.7247-7252, 2017-11</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6660,7 +6696,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) MIAO Ying 中国科学数学, 2023 / A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) MIAO Ying 2022 IEEE International Multi-Conference on Engineering, Computer and Information Sciences (SIBIRCON), 2022/11 / Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) MIAO Ying Problems of Information Transmission/59(1)/pp.14-21, 2023/1 / Repairing Schemes for Tamo-Barg Codes Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/71(1)/pp.227-243, 2025-01 / A Construction of Optimal One-Coincidence Frequency-Hopping Sequences via Generalized Cyclotomy Shao Minfeng; Miao Ying ENTROPY/26(11), 2024-11 / Secure Codes With List Decoding Gu Yujie; Vorobyev Ilya; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/70(4)/pp.2430-2442, 2024-04 / Codes for Exact Support Recovery of Sparse Vectors from Inaccurate Linear Measurements and Their Decoding Fernandez M.; Kabatiansky G. A.; Kruglik S. A.; Miao Y. PROBLEMS OF INFORMATION TRANSMISSION/59(1)/pp.14-21, 2023-01 / Optimal Locally Repairable Codes: An Improved Bound and Constructions Cai Han; Fan Cuiling; Miao Ying; Schwartz Moshe; Tang... IEEE TRANSACTIONS ON INFORMATION THEORY/68(8)/pp.5060-5074, 2022-08 / On the Information-Theoretic Security of Combinatorial All-or-Nothing Transforms Gu Yujie; Akao Sonata; Esfahani Navid Nasr; Miao Ying... IEEE TRANSACTIONS ON INFORMATION THEORY/68(10)/pp.6904-6914, 2022-10 / A Construction of Maximally Recoverable Codes With Order-Optimal Field Size Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/68(1)/pp.204-212, 2022-01 / Capacity-Achieving Private Information Retrieval Schemes From Uncoded Storage Constrained Servers With Low Sub-Packetization Zhu Jinbao; Yan Qifa; Tang Xiaohu; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/67(8)/pp.5370-5386, 2021-08 / BCH codes with minimum distance proportional to code length Noguchi Satoshi; Lu Xiao-Nan; Jimbo Masakazu; Miao Ying SIAM Journal on Discrete Mathematics/35(1)/pp.179-193, 2021-02 / Existence and Construction of Complete Traceability Multimedia Fingerprinting Codes Resistant to Averaging Attack and Adversarial Noise Egorova E. E.; Fernandez M.; Kabatiansky G. A.; Miao Y. PROBLEMS OF INFORMATION TRANSMISSION/56(4)/pp.388-398, 2020-12 / Strongly separable matrices for nonadaptive combinatorial group testing Fan Jinping; Fu Hung-Lin; Gu Yujie; Miao Ying; Shigen... DISCRETE APPLIED MATHEMATICS/291/pp.180-187, 2021-03 / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting Fan Jinping; Gu Yujie; Hachimori Masahiro; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/67(1)/pp.200-216, 2021-01 / Algebraic manipulation detection codes via highly nonlinear functions Shao Minfeng; Miao Ying CRYPTOGRAPHY AND COMMUNICATIONS-DISCRETE-STRUCTURES BOOLEAN FUNCTIONS AND SEQUENCES/Epub, 2021-02 / On Optimal Locally Repairable Codes With Super-Linear Length Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/66(8)/pp.4853-4868, 2020-08 / On optimal weak algebraic manipulation detection codes and weighted external difference families Shao Minfeng; Miao Ying DESIGNS CODES AND CRYPTOGRAPHY/Epub, 2020-04 / On Optimal Locally Repairable Codes With Multiple Disjoint Repair Sets Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/66(4)/pp.2402-2416, 2020-04 / Improved Bounds for Separable Codes and B-2 Codes Gu Yujie; Fan Jinping; Miao Ying IEEE COMMUNICATIONS LETTERS/24(1)/pp.15-19, 2020-01 / Probabilistic Existence Results for Parent-Identifying Schemes Gu Yujie; Cheng Minquan; Kabatiansky Grigory; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/65(10)/pp.6160-6170, 2019-10 / Non-adaptive group testing on graphs with connectivity Luo S.; Matsuura Y.; Miao Ying; Shigeno Maiko Journal of Combinatorial Optimization/38(1)/pp.278-291, 2019 / Bounds on Traceability Schemes Gu Yujie; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/64(5)/pp.3450-3460, 2018-05 / New Bounds for Frameproof Codes Shangguan Chong; Wang Xin; Ge Gennian; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/63(11)/pp.7247-7252, 2017-11 / Zero-difference balanced functions with new parameters and their applications Cai H.; Zhou Z.; Tang X; Miao Ying IEEE Transactions on Information Theory/63(7)/pp.4379-4387, 2017-06</t>
+          <t>FRACTAL DIMENSION OF SUBSTITUTION TREE NETWORKS Zeng Qingcheng; Xue Yumei; Wang Daohua; Miao Ying FRACTALS-COMPLEX GEOMETRY PATTERNS AND SCALING IN NATURE AND SOCIETY, 2025-10-28 / 版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) MIAO Ying 中国科学数学, 2023 / A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) MIAO Ying 2022 IEEE International Multi-Conference on Engineering, Computer and Information Sciences (SIBIRCON), 2022/11 / Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) MIAO Ying Problems of Information Transmission/59(1)/pp.14-21, 2023/1 / Repairing Schemes for Tamo-Barg Codes Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/71(1)/pp.227-243, 2025-01 / A Construction of Optimal One-Coincidence Frequency-Hopping Sequences via Generalized Cyclotomy Shao Minfeng; Miao Ying ENTROPY/26(11), 2024-11 / Secure Codes With List Decoding Gu Yujie; Vorobyev Ilya; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/70(4)/pp.2430-2442, 2024-04 / Codes for Exact Support Recovery of Sparse Vectors from Inaccurate Linear Measurements and Their Decoding Fernandez M.; Kabatiansky G. A.; Kruglik S. A.; Miao Y. PROBLEMS OF INFORMATION TRANSMISSION/59(1)/pp.14-21, 2023-01 / Optimal Locally Repairable Codes: An Improved Bound and Constructions Cai Han; Fan Cuiling; Miao Ying; Schwartz Moshe; Tang... IEEE TRANSACTIONS ON INFORMATION THEORY/68(8)/pp.5060-5074, 2022-08 / On the Information-Theoretic Security of Combinatorial All-or-Nothing Transforms Gu Yujie; Akao Sonata; Esfahani Navid Nasr; Miao Ying... IEEE TRANSACTIONS ON INFORMATION THEORY/68(10)/pp.6904-6914, 2022-10 / A Construction of Maximally Recoverable Codes With Order-Optimal Field Size Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/68(1)/pp.204-212, 2022-01 / Capacity-Achieving Private Information Retrieval Schemes From Uncoded Storage Constrained Servers With Low Sub-Packetization Zhu Jinbao; Yan Qifa; Tang Xiaohu; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/67(8)/pp.5370-5386, 2021-08 / BCH codes with minimum distance proportional to code length Noguchi Satoshi; Lu Xiao-Nan; Jimbo Masakazu; Miao Ying SIAM Journal on Discrete Mathematics/35(1)/pp.179-193, 2021-02 / Existence and Construction of Complete Traceability Multimedia Fingerprinting Codes Resistant to Averaging Attack and Adversarial Noise Egorova E. E.; Fernandez M.; Kabatiansky G. A.; Miao Y. PROBLEMS OF INFORMATION TRANSMISSION/56(4)/pp.388-398, 2020-12 / Strongly separable matrices for nonadaptive combinatorial group testing Fan Jinping; Fu Hung-Lin; Gu Yujie; Miao Ying; Shigen... DISCRETE APPLIED MATHEMATICS/291/pp.180-187, 2021-03 / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting Fan Jinping; Gu Yujie; Hachimori Masahiro; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/67(1)/pp.200-216, 2021-01 / Algebraic manipulation detection codes via highly nonlinear functions Shao Minfeng; Miao Ying CRYPTOGRAPHY AND COMMUNICATIONS-DISCRETE-STRUCTURES BOOLEAN FUNCTIONS AND SEQUENCES/Epub, 2021-02 / On Optimal Locally Repairable Codes With Super-Linear Length Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/66(8)/pp.4853-4868, 2020-08 / On optimal weak algebraic manipulation detection codes and weighted external difference families Shao Minfeng; Miao Ying DESIGNS CODES AND CRYPTOGRAPHY/Epub, 2020-04 / On Optimal Locally Repairable Codes With Multiple Disjoint Repair Sets Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/66(4)/pp.2402-2416, 2020-04 / Improved Bounds for Separable Codes and B-2 Codes Gu Yujie; Fan Jinping; Miao Ying IEEE COMMUNICATIONS LETTERS/24(1)/pp.15-19, 2020-01 / Probabilistic Existence Results for Parent-Identifying Schemes Gu Yujie; Cheng Minquan; Kabatiansky Grigory; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/65(10)/pp.6160-6170, 2019-10 / Non-adaptive group testing on graphs with connectivity Luo S.; Matsuura Y.; Miao Ying; Shigeno Maiko Journal of Combinatorial Optimization/38(1)/pp.278-291, 2019 / Bounds on Traceability Schemes Gu Yujie; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/64(5)/pp.3450-3460, 2018-05 / New Bounds for Frameproof Codes Shangguan Chong; Wang Xin; Ge Gennian; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/63(11)/pp.7247-7252, 2017-11</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -6704,6 +6740,7 @@
 組合せ的デザイン理論を用いた周波数ホッピング系列の構成に関する研究
 組合せ的デザイン理論を用いた光直交符号の構成に関する研究
 組合せ的デザインとその符号・暗号への応用
+FRACTAL DIMENSION OF SUBSTITUTION TREE NETWORKS Zeng Qingcheng; Xue Yumei; Wang Daohua; Miao Ying FRACTALS-COMPLEX GEOMETRY PATTERNS AND SCALING IN NATURE AND SOCIETY, 2025-10-28
 版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) MIAO Ying 中国科学数学, 2023
 A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) MIAO Ying 2022 IEEE International Multi-Conference on Engineering, Computer and Information Sciences (SIBIRCON), 2022/11
 Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) MIAO Ying Problems of Information Transmission/59(1)/pp.14-21, 2023/1
@@ -6727,8 +6764,7 @@
 Probabilistic Existence Results for Parent-Identifying Schemes Gu Yujie; Cheng Minquan; Kabatiansky Grigory; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/65(10)/pp.6160-6170, 2019-10
 Non-adaptive group testing on graphs with connectivity Luo S.; Matsuura Y.; Miao Ying; Shigeno Maiko Journal of Combinatorial Optimization/38(1)/pp.278-291, 2019
 Bounds on Traceability Schemes Gu Yujie; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/64(5)/pp.3450-3460, 2018-05
-New Bounds for Frameproof Codes Shangguan Chong; Wang Xin; Ge Gennian; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/63(11)/pp.7247-7252, 2017-11
-Zero-difference balanced functions with new parameters and their applications Cai H.; Zhou Z.; Tang X; Miao Ying IEEE Transactions on Information Theory/63(7)/pp.4379-4387, 2017-06</t>
+New Bounds for Frameproof Codes Shangguan Chong; Wang Xin; Ge Gennian; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/63(11)/pp.7247-7252, 2017-11</t>
         </is>
       </c>
     </row>
@@ -6777,8 +6813,8 @@
 走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー
 土木計画学・交通工学
 交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム
-Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/p.in press, 2026-01
-A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/p.in press, 2025-12
+Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/24/pp.250-264, 2026-04
+A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/24/pp.216-225, 2026-04
 都市鉄道整備推進に向けた事業制度に関する研究 石丸 真也; 森田 泰智; 浅井 遼馬; 和田 健太郎; 日比野 直彦 運輸政策研究/28/pp.6-16, 2026-02
 Stability analysis of a departure time choice problem with atomic vehicle models Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/189/p.103039, 2024-11
 自動運転車両の速度制御を考慮した系統信号制御に関する考察 梅村 悠生; 和田 健太郎 交通工学論文集/10(1)/pp.A_10-A_17, 2024-02
@@ -6821,7 +6857,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/p.in press, 2026-01 / A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/p.in press, 2025-12 / 都市鉄道整備推進に向けた事業制度に関する研究 石丸 真也; 森田 泰智; 浅井 遼馬; 和田 健太郎; 日比野 直彦 運輸政策研究/28/pp.6-16, 2026-02 / Stability analysis of a departure time choice problem with atomic vehicle models Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/189/p.103039, 2024-11 / 自動運転車両の速度制御を考慮した系統信号制御に関する考察 梅村 悠生; 和田 健太郎 交通工学論文集/10(1)/pp.A_10-A_17, 2024-02 / 追従モデルによる高速道路サグ部のCapacity Drop現象の再現 甲斐 慎一朗; 和田 健太郎; 堀口 良太 土木学会論文集D3（土木計画学）/78(5)/pp.I_963-I_971, 2023-05 / 連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析 金﨑 圭吾; 和田 健太郎 土木学会論文集D3（土木計画学）/78(5)/pp.I_911-I_918, 2023-05 / テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル 和田 健太郎; 岩見 悠太郎 土木学会論文集D3（土木計画学）/78(5)/pp.I_899-I_909, 2023-05 / Predicting traffic breakdown in expressways using linear combination of vehicle detector data Shigemi Rikuto; Ando Hiroyasu; Wada Kentaro; Mukai Risa Nonlinear Theory and Its Applications, IEICE/14(2)/pp.416-427, 2023-04 / Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals Zhang Jiahua; Wada Kentaro; Oguchi Takashi TRANSPORTMETRICA B-TRANSPORT DYNAMICS/11(1)/pp.1256-1280, 2023-03 / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 和田 健太郎; 金﨑 圭吾; 西田 匡志; 平井 章一 交通工学論文集/9(2)/pp.A_326-A_334, 2023-02 / 連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析 甲斐 慎一朗; 和田 健太郎; 堀口 良太; 邢 健 交通工学論文集/9(2)/pp.A_280-A_287, 2023-02 / Dynamic traffic assignment in a corridor network: Optimum versus equilibrium Haoran Fu; Takashi Akamatsu; Koki Satsukawa; Kentaro Wada Transportation Research Part B: Methodological/161/pp.218-246, 2022-07 / 高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム 岸川 知樹; 和田 健太郎 土木学会論文集D3（土木計画学）/77(5)/pp.I_1109-I_1119, 2022-05 / 需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡 板橋 昂汰; 和田 健太郎 土木学会論文集D3（土木計画学）/77(5)/pp.I_1045-I_1055, 2022-05 / Fundamental diagram of urban rail transit considering train-passenger interaction Seo Toru; Wada Kentaro; Fukuda Daisuke Transportation/Epub(50)/pp.1399-1424, 2023-08 / 高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム 和田 健太郎; 邢 健; 大口 敬 交通工学論文集/8(3)/pp.1-10, 2022-04 / 高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動 和田 健太郎; 甲斐 慎一朗; 堀口 良太 交通工学論文集/8(2)/pp.A_1-A_8, 2022-02 Tsukuba Repository / Dynamic system optimal traffic assignment with atomic users: Convergence and stability Satsukawa Koki; Wada Kentaro; Watling David Transportation Research Part B: Methodological/155/pp.188-209, 2022-01 / A new look at departure time choice equilibrium models with heterogeneous users Akamatsu Takashi; Wada Kentaro; Iryo Takamasa; Hayashi S... Transportation Research Part B: Methodological/148/pp.152-182, 2021-06 / 動的交通均衡配分理論の近年の進展 和田 健太郎 土木学会論文集D3（土木計画学）/76(5)/pp.I_21-I_39, 2021-04 / Continuum car-following model of capacity drop at sag and tunnel bottlenecks Wada Kentaro; Martínez Irene; Jin Wen-Long Transportation Research Part C: Emerging Technologies/113/pp.260-276, 2020-04 / Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/132(SI)/pp.117-135, 2020-02 / Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/125/pp.229-247, 2019-05 Tsukuba Repository / Trading mechanisms for bottleneck permits with multiple purchase opportunities Wang Pengfei; Wada Kentaro; Akamatsu Takashi; Nagae Takeshi Transportation Research Part C: Emerging Technologies/95/pp.414-430, 2018-10</t>
+          <t>Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/24/pp.250-264, 2026-04 / A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/24/pp.216-225, 2026-04 / 都市鉄道整備推進に向けた事業制度に関する研究 石丸 真也; 森田 泰智; 浅井 遼馬; 和田 健太郎; 日比野 直彦 運輸政策研究/28/pp.6-16, 2026-02 / Stability analysis of a departure time choice problem with atomic vehicle models Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/189/p.103039, 2024-11 / 自動運転車両の速度制御を考慮した系統信号制御に関する考察 梅村 悠生; 和田 健太郎 交通工学論文集/10(1)/pp.A_10-A_17, 2024-02 / 追従モデルによる高速道路サグ部のCapacity Drop現象の再現 甲斐 慎一朗; 和田 健太郎; 堀口 良太 土木学会論文集D3（土木計画学）/78(5)/pp.I_963-I_971, 2023-05 / 連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析 金﨑 圭吾; 和田 健太郎 土木学会論文集D3（土木計画学）/78(5)/pp.I_911-I_918, 2023-05 / テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル 和田 健太郎; 岩見 悠太郎 土木学会論文集D3（土木計画学）/78(5)/pp.I_899-I_909, 2023-05 / Predicting traffic breakdown in expressways using linear combination of vehicle detector data Shigemi Rikuto; Ando Hiroyasu; Wada Kentaro; Mukai Risa Nonlinear Theory and Its Applications, IEICE/14(2)/pp.416-427, 2023-04 / Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals Zhang Jiahua; Wada Kentaro; Oguchi Takashi TRANSPORTMETRICA B-TRANSPORT DYNAMICS/11(1)/pp.1256-1280, 2023-03 / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 和田 健太郎; 金﨑 圭吾; 西田 匡志; 平井 章一 交通工学論文集/9(2)/pp.A_326-A_334, 2023-02 / 連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析 甲斐 慎一朗; 和田 健太郎; 堀口 良太; 邢 健 交通工学論文集/9(2)/pp.A_280-A_287, 2023-02 / Dynamic traffic assignment in a corridor network: Optimum versus equilibrium Haoran Fu; Takashi Akamatsu; Koki Satsukawa; Kentaro Wada Transportation Research Part B: Methodological/161/pp.218-246, 2022-07 / 高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム 岸川 知樹; 和田 健太郎 土木学会論文集D3（土木計画学）/77(5)/pp.I_1109-I_1119, 2022-05 / 需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡 板橋 昂汰; 和田 健太郎 土木学会論文集D3（土木計画学）/77(5)/pp.I_1045-I_1055, 2022-05 / Fundamental diagram of urban rail transit considering train-passenger interaction Seo Toru; Wada Kentaro; Fukuda Daisuke Transportation/Epub(50)/pp.1399-1424, 2023-08 / 高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム 和田 健太郎; 邢 健; 大口 敬 交通工学論文集/8(3)/pp.1-10, 2022-04 / 高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動 和田 健太郎; 甲斐 慎一朗; 堀口 良太 交通工学論文集/8(2)/pp.A_1-A_8, 2022-02 Tsukuba Repository / Dynamic system optimal traffic assignment with atomic users: Convergence and stability Satsukawa Koki; Wada Kentaro; Watling David Transportation Research Part B: Methodological/155/pp.188-209, 2022-01 / A new look at departure time choice equilibrium models with heterogeneous users Akamatsu Takashi; Wada Kentaro; Iryo Takamasa; Hayashi S... Transportation Research Part B: Methodological/148/pp.152-182, 2021-06 / 動的交通均衡配分理論の近年の進展 和田 健太郎 土木学会論文集D3（土木計画学）/76(5)/pp.I_21-I_39, 2021-04 / Continuum car-following model of capacity drop at sag and tunnel bottlenecks Wada Kentaro; Martínez Irene; Jin Wen-Long Transportation Research Part C: Emerging Technologies/113/pp.260-276, 2020-04 / Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/132(SI)/pp.117-135, 2020-02 / Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/125/pp.229-247, 2019-05 Tsukuba Repository / Trading mechanisms for bottleneck permits with multiple purchase opportunities Wang Pengfei; Wada Kentaro; Akamatsu Takashi; Nagae Takeshi Transportation Research Part C: Emerging Technologies/95/pp.414-430, 2018-10</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -6889,8 +6925,8 @@
 バイオミメティックスに学ぶスマートな都市退化マネジメント
 AI計算リソースとしての実交通ダイナミクスの活用技術の開発
 走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー
-Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/p.in press, 2026-01
-A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/p.in press, 2025-12
+Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/24/pp.250-264, 2026-04
+A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/24/pp.216-225, 2026-04
 都市鉄道整備推進に向けた事業制度に関する研究 石丸 真也; 森田 泰智; 浅井 遼馬; 和田 健太郎; 日比野 直彦 運輸政策研究/28/pp.6-16, 2026-02
 Stability analysis of a departure time choice problem with atomic vehicle models Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/189/p.103039, 2024-11
 自動運転車両の速度制御を考慮した系統信号制御に関する考察 梅村 悠生; 和田 健太郎 交通工学論文集/10(1)/pp.A_10-A_17, 2024-02
@@ -7105,6 +7141,8 @@
 地域公共交通
 地理情報科学
 都市リスク分析
+A Semi-Supervised Framework for Road Condition Assessment: From Minor Surface Distress to Post-Disaster Failures Tsujimoto Eda; Eom Sunyong; Suzuki Tsutomu IEEE Open Journal of Intelligent Transportation Systems/7/pp.1244-1263, 2026-05
+GPSデータに基づく都市内移動効率の計測と交通軸の抽出 竹内真雄; 嚴先鏞; 鈴木勉 都市計画論文集/61(1)/pp.149-158, 2026-04
 起伏を考慮した低炭素都市交通施策の評価 Luo Linyan; 鈴木 勉 地理情報システム学会講演論文集, 2025-10
 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2025-10
 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析 飛松涼太; 石井儀光; 鈴木勉 都市計画報告集/24(4)/pp.567-570, 2026-03
@@ -7127,9 +7165,7 @@
 Exploring Separation Strategies for Car-Bicycle Integration Liu Liling; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
 アジア地域の都市における鉄道・道路と人口分布構造 神﨑達也; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
 建物主要用途・トリップチェーンに着目した人流データによる街区間トリップ特性 早坂遼; 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
-人流データによる街区レベル時間帯別発生集中の時空間分布 竹内真雄; 早坂遼; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
-人口重心に着目した人流分析 一井直人; 鈴木 勉; 大澤義明 地理情報システム学会講演論文集, 2022
-沿道電柱密度の地域別・道路種別比較 欧陽君顔; 大澤義明; 鈴木 勉 地理情報システム学会講演論文集, 2022</t>
+人流データによる街区レベル時間帯別発生集中の時空間分布 竹内真雄; 早坂遼; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -7149,7 +7185,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>起伏を考慮した低炭素都市交通施策の評価 Luo Linyan; 鈴木 勉 地理情報システム学会講演論文集, 2025-10 / 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2025-10 / 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析 飛松涼太; 石井儀光; 鈴木勉 都市計画報告集/24(4)/pp.567-570, 2026-03 / 東京区部における年齢構成類型の変化と生活利便施設へのアクシセビリティ分析 飛松涼太; 石井儀光; 鈴木勉 都市計画報告集/24(3)/pp.391-397, 2025-12 / 電柱広告の空間的配置に関する研究―筑波研究学園都市中心部を対象に― 竹内真雄; 鈴木脩矢; 田所達也; 池澤隼映; 大川駿介; 安部桂佑; 熊野喬元; 廣田陽香; 田畑優希; 塩野目... 都市計画報告集/24(4)/pp.515-520, 2026-03 / Exploring Network Scale Separation Strategies for Car-Bicycle Integration Liu Liling; Eom Sunyong; Suzuki Tsutomu Transportation Research Interdisciplinary Perspectives/36, 2026-03 / 都市条件に応じた複数公共交通モード併用によるネットワーク設計 竹内真雄; 鈴木勉 都市計画論文集/60(3)/pp.1535-1542, 2025-11 / 全国鉄道駅周辺地域における地域分断による移動制約の定量評価 北口立大; 嚴先鏞; 鈴木勉 都市計画論文集/60(2)/pp.248-255, 2025-08 / 小地域人口の年齢構成類型とその遷移から見た安定性分析 飛松涼太; 嚴先鏞; 鈴木勉 都市計画論文集/59(3)/pp.1232-1239, 2024-11 / 東京区部における業種構成・滞在パターンに基づく商業集積地の類型化と滞在移動特性の分析 竹内真雄; 嚴先鏞; 鈴木勉 都市計画論文集/59(3)/pp.555-562, 2024-11 / 東京区部におけるGPSデータに基づく街区レベル発生集中・滞在移動特性と建物用途構成 竹内真雄; 早坂遼; 嚴先鏞; 鈴木勉 都市計画論文集/59(2)/pp.177-188, 2024-11 / 人口分布の集積性と鉄道網との連携度の変化動向に関する研究 神﨑達也; 嚴先鏞; 鈴木勉 都市計画報告集/23(4), 2025-03 / 東京区部における人口年齢構成と土地利用遷移の関連性分析 飛松涼太; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2024-10 / 東京区部における交通量密度・移動速度に基づく交通軸と移動効率性評価 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2024-10 / 鉄道網による移動時間短縮を考慮した都市の人口分布の集積性の評価 神﨑達也; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2024-10 / 人流データによる滞在者平均年齢の時空間分析 ―昼や休日に若返る自治体はどこか？― 田村侑介; 鈴木 勉; 大澤義明 地理情報システム学会講演論文集, 2024-10 / 通学距離最小化と安定マッチングによる学校割当 神﨑達也; 嚴先鏞; 鈴木 勉 オペレーションズ・リサーチ/69(7)/pp.355-360, 2024-07 / Preference-based jogging route selection in Downtown Tokyo Huang Yumeng; Eom Sunyong; Suzuki Tsutomu Cities &amp; Health/pp.1-15, 2024-02 / Effect of Speed Control for Travel Time and Emission Reduction in Connected Vehicle Environment Liu Yuheng; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / Exploring Separation Strategies for Car-Bicycle Integration Liu Liling; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / アジア地域の都市における鉄道・道路と人口分布構造 神﨑達也; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / 建物主要用途・トリップチェーンに着目した人流データによる街区間トリップ特性 早坂遼; 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / 人流データによる街区レベル時間帯別発生集中の時空間分布 竹内真雄; 早坂遼; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / 人口重心に着目した人流分析 一井直人; 鈴木 勉; 大澤義明 地理情報システム学会講演論文集, 2022 / 沿道電柱密度の地域別・道路種別比較 欧陽君顔; 大澤義明; 鈴木 勉 地理情報システム学会講演論文集, 2022</t>
+          <t>A Semi-Supervised Framework for Road Condition Assessment: From Minor Surface Distress to Post-Disaster Failures Tsujimoto Eda; Eom Sunyong; Suzuki Tsutomu IEEE Open Journal of Intelligent Transportation Systems/7/pp.1244-1263, 2026-05 / GPSデータに基づく都市内移動効率の計測と交通軸の抽出 竹内真雄; 嚴先鏞; 鈴木勉 都市計画論文集/61(1)/pp.149-158, 2026-04 / 起伏を考慮した低炭素都市交通施策の評価 Luo Linyan; 鈴木 勉 地理情報システム学会講演論文集, 2025-10 / 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2025-10 / 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析 飛松涼太; 石井儀光; 鈴木勉 都市計画報告集/24(4)/pp.567-570, 2026-03 / 東京区部における年齢構成類型の変化と生活利便施設へのアクシセビリティ分析 飛松涼太; 石井儀光; 鈴木勉 都市計画報告集/24(3)/pp.391-397, 2025-12 / 電柱広告の空間的配置に関する研究―筑波研究学園都市中心部を対象に― 竹内真雄; 鈴木脩矢; 田所達也; 池澤隼映; 大川駿介; 安部桂佑; 熊野喬元; 廣田陽香; 田畑優希; 塩野目... 都市計画報告集/24(4)/pp.515-520, 2026-03 / Exploring Network Scale Separation Strategies for Car-Bicycle Integration Liu Liling; Eom Sunyong; Suzuki Tsutomu Transportation Research Interdisciplinary Perspectives/36, 2026-03 / 都市条件に応じた複数公共交通モード併用によるネットワーク設計 竹内真雄; 鈴木勉 都市計画論文集/60(3)/pp.1535-1542, 2025-11 / 全国鉄道駅周辺地域における地域分断による移動制約の定量評価 北口立大; 嚴先鏞; 鈴木勉 都市計画論文集/60(2)/pp.248-255, 2025-08 / 小地域人口の年齢構成類型とその遷移から見た安定性分析 飛松涼太; 嚴先鏞; 鈴木勉 都市計画論文集/59(3)/pp.1232-1239, 2024-11 / 東京区部における業種構成・滞在パターンに基づく商業集積地の類型化と滞在移動特性の分析 竹内真雄; 嚴先鏞; 鈴木勉 都市計画論文集/59(3)/pp.555-562, 2024-11 / 東京区部におけるGPSデータに基づく街区レベル発生集中・滞在移動特性と建物用途構成 竹内真雄; 早坂遼; 嚴先鏞; 鈴木勉 都市計画論文集/59(2)/pp.177-188, 2024-11 / 人口分布の集積性と鉄道網との連携度の変化動向に関する研究 神﨑達也; 嚴先鏞; 鈴木勉 都市計画報告集/23(4), 2025-03 / 東京区部における人口年齢構成と土地利用遷移の関連性分析 飛松涼太; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2024-10 / 東京区部における交通量密度・移動速度に基づく交通軸と移動効率性評価 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2024-10 / 鉄道網による移動時間短縮を考慮した都市の人口分布の集積性の評価 神﨑達也; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2024-10 / 人流データによる滞在者平均年齢の時空間分析 ―昼や休日に若返る自治体はどこか？― 田村侑介; 鈴木 勉; 大澤義明 地理情報システム学会講演論文集, 2024-10 / 通学距離最小化と安定マッチングによる学校割当 神﨑達也; 嚴先鏞; 鈴木 勉 オペレーションズ・リサーチ/69(7)/pp.355-360, 2024-07 / Preference-based jogging route selection in Downtown Tokyo Huang Yumeng; Eom Sunyong; Suzuki Tsutomu Cities &amp; Health/pp.1-15, 2024-02 / Effect of Speed Control for Travel Time and Emission Reduction in Connected Vehicle Environment Liu Yuheng; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / Exploring Separation Strategies for Car-Bicycle Integration Liu Liling; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / アジア地域の都市における鉄道・道路と人口分布構造 神﨑達也; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / 建物主要用途・トリップチェーンに着目した人流データによる街区間トリップ特性 早坂遼; 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / 人流データによる街区レベル時間帯別発生集中の時空間分布 竹内真雄; 早坂遼; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -7237,6 +7273,8 @@
 水害時の住民避難をより安全にする広域避難対策の社会的実装を図る計画技術の構築
 都市の拠点集約と拠点間ネットワークの空間分析
 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究
+A Semi-Supervised Framework for Road Condition Assessment: From Minor Surface Distress to Post-Disaster Failures Tsujimoto Eda; Eom Sunyong; Suzuki Tsutomu IEEE Open Journal of Intelligent Transportation Systems/7/pp.1244-1263, 2026-05
+GPSデータに基づく都市内移動効率の計測と交通軸の抽出 竹内真雄; 嚴先鏞; 鈴木勉 都市計画論文集/61(1)/pp.149-158, 2026-04
 起伏を考慮した低炭素都市交通施策の評価 Luo Linyan; 鈴木 勉 地理情報システム学会講演論文集, 2025-10
 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2025-10
 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析 飛松涼太; 石井儀光; 鈴木勉 都市計画報告集/24(4)/pp.567-570, 2026-03
@@ -7259,9 +7297,7 @@
 Exploring Separation Strategies for Car-Bicycle Integration Liu Liling; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
 アジア地域の都市における鉄道・道路と人口分布構造 神﨑達也; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
 建物主要用途・トリップチェーンに着目した人流データによる街区間トリップ特性 早坂遼; 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
-人流データによる街区レベル時間帯別発生集中の時空間分布 竹内真雄; 早坂遼; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
-人口重心に着目した人流分析 一井直人; 鈴木 勉; 大澤義明 地理情報システム学会講演論文集, 2022
-沿道電柱密度の地域別・道路種別比較 欧陽君顔; 大澤義明; 鈴木 勉 地理情報システム学会講演論文集, 2022</t>
+人流データによる街区レベル時間帯別発生集中の時空間分布 竹内真雄; 早坂遼; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023</t>
         </is>
       </c>
     </row>
@@ -7499,6 +7535,11 @@
 交通シミュレーション
 災害復旧
 相互作用
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
+Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12
+A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12
+Robust OD matrix estimation method under low sampling rate by utilizing multiscale information of questionnaire data Mochizuki Y.; Pel A.J.; Hinsbergen C.; URATA Junji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06
+Developing an Estimation Algorithm for Generalizing the Parameters of the network-GEV model in Destination Choice URATA Junji; KANEDA Yudai; ISHII Ryoji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06
 通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ 上杉 朋花; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11
 EVユーザーの充電場所選択問題に対するゲーム理論的考察 大野 隆輔; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11
 災害復旧期における個々人の移動パターン変化の特徴分析 村上 智仁; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11
@@ -7517,12 +7558,7 @@
 Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository
 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02
 選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02
-LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09
-日本の復興計画の研究動向と今後の展望 -1995年以降の建築・都市・土木の計画分野を中心に- 小野 悠; 井本 佐保里; 浦田 淳司; 萩原 拓也; 羽藤 英二 日本建築学会計画系論文集/87(799), 2022-09
-選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 第42回交通工学研究発表会論文報告集/42/pp.381-388, 2022-08
-災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 第42回交通工学研究発表会論文報告集/42/pp.389-396, 2022-08
-LET'S GO ABROAD!(第77回)シンガポール、パキスタン、アフガニスタン、ベトナム、カンボジア 地域建設業の海外展開と見据える未来—A regional construction company looks to overseas expansion and their future—特集 土木と地政学 才田 善之; 金子 辰生; 浦田 淳司 土木学会誌/107(5)/pp.38-40, 2022-05
-「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学 浦田 淳司; 森 弘継; 高松 俊介; 西村 俊亮 土木学会誌/107(5)/pp.41-43, 2022-05</t>
+LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -7542,7 +7578,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ 上杉 朋花; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / EVユーザーの充電場所選択問題に対するゲーム理論的考察 大野 隆輔; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / 災害復旧期における個々人の移動パターン変化の特徴分析 村上 智仁; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / メタ分析による災害時の避難開始選択要因の評価 柴田 龍聖; 浦田 淳司; 大東 延幸 第72回土木計画学研究発表会・講演集, 2025-11 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction URATA Junji; NAKAZAWA Ruka THE 29TH INTERNATIONAL CONFERENCE OF HONG KONG SOCIETY FOR TRANSPORTATION STUDIES, 2025-12 / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging Mochizuki Y.; 浦田 淳司; Hato E. 2024 IEEE 27th International Conference on Intelligent Transportation Systems (ITSC)/pp.653-660, 2025-03 / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 田村 侑介; 浦田 淳司 都市計画論文集/60(3)/pp.1543-1550, 2025-10 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 相互作用下での多肢選択行動の量子計算による求解 中澤瑠河; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- 中嶋 駿; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- 中山 凛空; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— 河瀬理貴; 井料隆雅; 浦田 淳司 土木学会論文集, 2024-12 / Object-oriented Bayesian Networks for Activity-based Model with deep generative graph averaging URATA Junji; Mochizuki Y.; Hato E. IEEE 27th International Conference on Intelligent Transportation Systems, 2024-09 / 筑波大学理工学群におけるデータサイエンス応用基礎教育 浦田 淳司; オム ソンヨン; 川島 宏一 大学教育と情報, 2024-03 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02 / 選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02 / LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09 / 日本の復興計画の研究動向と今後の展望 -1995年以降の建築・都市・土木の計画分野を中心に- 小野 悠; 井本 佐保里; 浦田 淳司; 萩原 拓也; 羽藤 英二 日本建築学会計画系論文集/87(799), 2022-09 / 選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 第42回交通工学研究発表会論文報告集/42/pp.381-388, 2022-08 / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 第42回交通工学研究発表会論文報告集/42/pp.389-396, 2022-08 / LET'S GO ABROAD!(第77回)シンガポール、パキスタン、アフガニスタン、ベトナム、カンボジア 地域建設業の海外展開と見据える未来—A regional construction company looks to overseas expansion and their future—特集 土木と地政学 才田 善之; 金子 辰生; 浦田 淳司 土木学会誌/107(5)/pp.38-40, 2022-05 / 「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学 浦田 淳司; 森 弘継; 高松 俊介; 西村 俊亮 土木学会誌/107(5)/pp.41-43, 2022-05</t>
+          <t>大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12 / A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12 / Robust OD matrix estimation method under low sampling rate by utilizing multiscale information of questionnaire data Mochizuki Y.; Pel A.J.; Hinsbergen C.; URATA Junji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06 / Developing an Estimation Algorithm for Generalizing the Parameters of the network-GEV model in Destination Choice URATA Junji; KANEDA Yudai; ISHII Ryoji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06 / 通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ 上杉 朋花; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / EVユーザーの充電場所選択問題に対するゲーム理論的考察 大野 隆輔; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / 災害復旧期における個々人の移動パターン変化の特徴分析 村上 智仁; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / メタ分析による災害時の避難開始選択要因の評価 柴田 龍聖; 浦田 淳司; 大東 延幸 第72回土木計画学研究発表会・講演集, 2025-11 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction URATA Junji; NAKAZAWA Ruka THE 29TH INTERNATIONAL CONFERENCE OF HONG KONG SOCIETY FOR TRANSPORTATION STUDIES, 2025-12 / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging Mochizuki Y.; 浦田 淳司; Hato E. 2024 IEEE 27th International Conference on Intelligent Transportation Systems (ITSC)/pp.653-660, 2025-03 / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 田村 侑介; 浦田 淳司 都市計画論文集/60(3)/pp.1543-1550, 2025-10 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 相互作用下での多肢選択行動の量子計算による求解 中澤瑠河; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- 中嶋 駿; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- 中山 凛空; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— 河瀬理貴; 井料隆雅; 浦田 淳司 土木学会論文集, 2024-12 / Object-oriented Bayesian Networks for Activity-based Model with deep generative graph averaging URATA Junji; Mochizuki Y.; Hato E. IEEE 27th International Conference on Intelligent Transportation Systems, 2024-09 / 筑波大学理工学群におけるデータサイエンス応用基礎教育 浦田 淳司; オム ソンヨン; 川島 宏一 大学教育と情報, 2024-03 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02 / 選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02 / LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -7630,6 +7666,11 @@
 マルチスケールな拠点空間計画のための新たな行動モデル研究
 災害時都市継続計画にむけた即応型需要予測の信頼性向上のためのデータフロー
 災害時都市活動支援のためのsoftware2.0型シミュレータの構築
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
+Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12
+A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12
+Robust OD matrix estimation method under low sampling rate by utilizing multiscale information of questionnaire data Mochizuki Y.; Pel A.J.; Hinsbergen C.; URATA Junji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06
+Developing an Estimation Algorithm for Generalizing the Parameters of the network-GEV model in Destination Choice URATA Junji; KANEDA Yudai; ISHII Ryoji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06
 通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ 上杉 朋花; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11
 EVユーザーの充電場所選択問題に対するゲーム理論的考察 大野 隆輔; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11
 災害復旧期における個々人の移動パターン変化の特徴分析 村上 智仁; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11
@@ -7648,12 +7689,7 @@
 Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository
 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02
 選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02
-LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09
-日本の復興計画の研究動向と今後の展望 -1995年以降の建築・都市・土木の計画分野を中心に- 小野 悠; 井本 佐保里; 浦田 淳司; 萩原 拓也; 羽藤 英二 日本建築学会計画系論文集/87(799), 2022-09
-選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 第42回交通工学研究発表会論文報告集/42/pp.381-388, 2022-08
-災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 第42回交通工学研究発表会論文報告集/42/pp.389-396, 2022-08
-LET'S GO ABROAD!(第77回)シンガポール、パキスタン、アフガニスタン、ベトナム、カンボジア 地域建設業の海外展開と見据える未来—A regional construction company looks to overseas expansion and their future—特集 土木と地政学 才田 善之; 金子 辰生; 浦田 淳司 土木学会誌/107(5)/pp.38-40, 2022-05
-「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学 浦田 淳司; 森 弘継; 高松 俊介; 西村 俊亮 土木学会誌/107(5)/pp.41-43, 2022-05</t>
+LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09</t>
         </is>
       </c>
     </row>
@@ -7712,14 +7748,15 @@
 view
 hirokitakahashi
 eメール
-9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q
-5
+)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
 研究室
 3F1236
 電話
 5379
 Service Engineering
 Experimental economics
+Incentive Mechanism for Continuous Consumption under Habit Formation and Satiation Utility Model LEE Sangjic; XU Yitao; TAKAHASHI Hiroki; NISHINO Nariaki Procedia CIRP/138/pp.13-18, 2026-02
+Balancing profitability and resilience to earthquake-induced isolation: A multi-objective optimization for drone depot location TAKAHASHI Yusuke; TAKAHASHI Hiroki Socio-Economic Planning Sciences/105(102482), 2026-06
 主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 長谷川 弘貴; 信夫 咲希; 髙橋 裕紀 サービソロジー論文誌/9(3)/pp.1-14, 2025-08
 What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews 髙橋 裕紀 PLoS ONE/19(12), 2024-12
 Mystery shopping considering lifestyle heterogeneity Takahashi Hiroki; Kawasaki Shohei; Takenaka Takeshi; N... International Journal of Services and Operations Management, 2024-03
@@ -7739,7 +7776,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / 9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q / 5 / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -7749,13 +7786,13 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 長谷川 弘貴; 信夫 咲希; 髙橋 裕紀 サービソロジー論文誌/9(3)/pp.1-14, 2025-08 / What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews 髙橋 裕紀 PLoS ONE/19(12), 2024-12 / Mystery shopping considering lifestyle heterogeneity Takahashi Hiroki; Kawasaki Shohei; Takenaka Takeshi; N... International Journal of Services and Operations Management, 2024-03 / 経験効用モデルに基づくサービス継続利用を促すリマインダーの最適間隔 徐 亦陶; 髙橋 裕紀; 木見田 康治; 西野 成昭 サービソロジー/6(2)/pp.29-42, 2022-08 / Effects of Incentivized Fake Reviews on E-commerce Markets Okamoto Shotaro; Takahashi Hiroki; Kimita Koji; Nishino ... The Human Side of Service Engineering/62/pp.8-15, 2022-07 / Platform in manufacturing for enhancement of product value by sharing Nishino Nariaki; Takahashi Hiroki; Takenaka Takeshi; Inou... Procedia CIRP/99/pp.574-579, 2020-01 / Interpreting value creation model by case-based decision theory Takahashi Hiroki; Nishino Nariaki; Takenaka Takeshi; Ishi... Procedia CIRP/88/pp.584-588, 2020-01 / Service switching in case-based decisions following bad experiences: Online reviews data of Japanese hairdressing salons Takahashi Hiroki; Nishino Nariaki; Ishikawa Ryuichiro The 27th International Conference on Case-Based Reasoning (ICCBR 2019) Workshop Proceedings/pp.74-82, 2019-09 / Multi-agent simulation for the manufacturer’s decision making in sharing markets Takahashi Hiroki; Nishino Nariaki; Takenaka Takeshi Procedia CIRP/67/pp.546-551, 2018-01 / Manufacturer’s strategy in a sharing economy Nishino Nariaki; Takenaka Takeshi; Takahashi Hiroki CIRP Annals/66(1)/pp.409-412, 2017-04</t>
+          <t>Incentive Mechanism for Continuous Consumption under Habit Formation and Satiation Utility Model LEE Sangjic; XU Yitao; TAKAHASHI Hiroki; NISHINO Nariaki Procedia CIRP/138/pp.13-18, 2026-02 / Balancing profitability and resilience to earthquake-induced isolation: A multi-objective optimization for drone depot location TAKAHASHI Yusuke; TAKAHASHI Hiroki Socio-Economic Planning Sciences/105(102482), 2026-06 / 主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 長谷川 弘貴; 信夫 咲希; 髙橋 裕紀 サービソロジー論文誌/9(3)/pp.1-14, 2025-08 / What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews 髙橋 裕紀 PLoS ONE/19(12), 2024-12 / Mystery shopping considering lifestyle heterogeneity Takahashi Hiroki; Kawasaki Shohei; Takenaka Takeshi; N... International Journal of Services and Operations Management, 2024-03 / 経験効用モデルに基づくサービス継続利用を促すリマインダーの最適間隔 徐 亦陶; 髙橋 裕紀; 木見田 康治; 西野 成昭 サービソロジー/6(2)/pp.29-42, 2022-08 / Effects of Incentivized Fake Reviews on E-commerce Markets Okamoto Shotaro; Takahashi Hiroki; Kimita Koji; Nishino ... The Human Side of Service Engineering/62/pp.8-15, 2022-07 / Platform in manufacturing for enhancement of product value by sharing Nishino Nariaki; Takahashi Hiroki; Takenaka Takeshi; Inou... Procedia CIRP/99/pp.574-579, 2020-01 / Interpreting value creation model by case-based decision theory Takahashi Hiroki; Nishino Nariaki; Takenaka Takeshi; Ishi... Procedia CIRP/88/pp.584-588, 2020-01 / Service switching in case-based decisions following bad experiences: Online reviews data of Japanese hairdressing salons Takahashi Hiroki; Nishino Nariaki; Ishikawa Ryuichiro The 27th International Conference on Case-Based Reasoning (ICCBR 2019) Workshop Proceedings/pp.74-82, 2019-09 / Multi-agent simulation for the manufacturer’s decision making in sharing markets Takahashi Hiroki; Nishino Nariaki; Takenaka Takeshi Procedia CIRP/67/pp.546-551, 2018-01 / Manufacturer’s strategy in a sharing economy Nishino Nariaki; Takenaka Takeshi; Takahashi Hiroki CIRP Annals/66(1)/pp.409-412, 2017-04</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; 9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q ; 5 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -7785,8 +7822,7 @@
 view
 hirokitakahashi
 eメール
-9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q
-5
+)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
 研究室
 3F1236
 電話
@@ -7805,6 +7841,8 @@
         <is>
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発
 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証
+Incentive Mechanism for Continuous Consumption under Habit Formation and Satiation Utility Model LEE Sangjic; XU Yitao; TAKAHASHI Hiroki; NISHINO Nariaki Procedia CIRP/138/pp.13-18, 2026-02
+Balancing profitability and resilience to earthquake-induced isolation: A multi-objective optimization for drone depot location TAKAHASHI Yusuke; TAKAHASHI Hiroki Socio-Economic Planning Sciences/105(102482), 2026-06
 主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 長谷川 弘貴; 信夫 咲希; 髙橋 裕紀 サービソロジー論文誌/9(3)/pp.1-14, 2025-08
 What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews 髙橋 裕紀 PLoS ONE/19(12), 2024-12
 Mystery shopping considering lifestyle heterogeneity Takahashi Hiroki; Kawasaki Shohei; Takenaka Takeshi; N... International Journal of Services and Operations Management, 2024-03
@@ -8150,6 +8188,7 @@
 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―
 経済政策
 開発経済学、教育の経済学、健康の経済学、応用計量経済学
+非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
 Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05
 Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020
 The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04
@@ -8173,8 +8212,7 @@
 ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 牛島 光一 応用地域学研究/(18)/pp.62-63, 2014-09
 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 牛島 光一 住宅土地経済/(2010年秋季)/pp.36-39, 2010-10
 The Impact of a High-speed Railway on Residential Land Prices Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1344), 2016-03
-The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10
-School Choice and Student Sorting: Evidence from Adachi City in Japan Ushijima Koichi Department of Social Systems and Management, University of Tsukuba, 2007-03</t>
+The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -8194,7 +8232,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05 / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020 / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04 / The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/p.1305, 2017 Tsukuba Repository / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... JAPAN AND THE WORLD ECONOMY/50/pp.36-46, 2019-06 / School Choice and Student Sorting: Evidence from Adachi Ward in Japan 牛島 光一 Japanese Economic Review/60(4)/pp.446-472, 2009-12 / オリンピック・パラリンピックにはどんな経済効果があるのか 牛島 光一 経済セミナー 2019年4・5月号, 2019-03 / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi Public Policy Review, 2020-09 / Building an Administrative Database of Children Bessho Shun-ichiro; Noguchi Haruko; 牛島 光一; Kawamura Akir... Public Policy Review, 2020-09 / 高速鉄道の建設が居住地価格に与えた影響 牛島 光一 季刊 住宅土地経済/pp.24-31, 2019-07 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... IZA Discussion Papers, 2020-04 / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ 香川涼亮; 小倉利仁; 太田 充; 牛島光一 都市住宅学/97/pp.126-135, 2017-04 CiNii / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― 姜 哲敏; 太田 充; 牛島光一 応用地域学研究/20/pp.67-77, 2016-09 / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 牛島 光一 応用地域学研究/(14)/pp.37-47, 2009-12 / 学校の質と地価－足立区の地価データを用いた検証 牛島 光一 住宅土地経済/(68)/pp.10-18, 2008-04 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ 牛島 光一 フィナンシャルレビュー/(141)/pp.65-85, 2019-12 / 子どもについての行政データベースの構築 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.106-119, 2019-12 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.120-140, 2019-12 / 区立小学校での補習の効果：足立区のケース 別所俊一郎; 川村顕; 野口晴子; 田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.141-159, 2019-12 / ヘドニック・アプローチにおける因果識別 牛島 光一 都市住宅学/2016(92)/pp.25-30, 2016-01 CiNii / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 牛島 光一 応用地域学研究/(18)/pp.62-63, 2014-09 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 牛島 光一 住宅土地経済/(2010年秋季)/pp.36-39, 2010-10 / The Impact of a High-speed Railway on Residential Land Prices Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1344), 2016-03 / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10 / School Choice and Student Sorting: Evidence from Adachi City in Japan Ushijima Koichi Department of Social Systems and Management, University of Tsukuba, 2007-03</t>
+          <t>非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17 / Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05 / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020 / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04 / The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/p.1305, 2017 Tsukuba Repository / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... JAPAN AND THE WORLD ECONOMY/50/pp.36-46, 2019-06 / School Choice and Student Sorting: Evidence from Adachi Ward in Japan 牛島 光一 Japanese Economic Review/60(4)/pp.446-472, 2009-12 / オリンピック・パラリンピックにはどんな経済効果があるのか 牛島 光一 経済セミナー 2019年4・5月号, 2019-03 / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi Public Policy Review, 2020-09 / Building an Administrative Database of Children Bessho Shun-ichiro; Noguchi Haruko; 牛島 光一; Kawamura Akir... Public Policy Review, 2020-09 / 高速鉄道の建設が居住地価格に与えた影響 牛島 光一 季刊 住宅土地経済/pp.24-31, 2019-07 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... IZA Discussion Papers, 2020-04 / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ 香川涼亮; 小倉利仁; 太田 充; 牛島光一 都市住宅学/97/pp.126-135, 2017-04 CiNii / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― 姜 哲敏; 太田 充; 牛島光一 応用地域学研究/20/pp.67-77, 2016-09 / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 牛島 光一 応用地域学研究/(14)/pp.37-47, 2009-12 / 学校の質と地価－足立区の地価データを用いた検証 牛島 光一 住宅土地経済/(68)/pp.10-18, 2008-04 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ 牛島 光一 フィナンシャルレビュー/(141)/pp.65-85, 2019-12 / 子どもについての行政データベースの構築 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.106-119, 2019-12 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.120-140, 2019-12 / 区立小学校での補習の効果：足立区のケース 別所俊一郎; 川村顕; 野口晴子; 田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.141-159, 2019-12 / ヘドニック・アプローチにおける因果識別 牛島 光一 都市住宅学/2016(92)/pp.25-30, 2016-01 CiNii / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 牛島 光一 応用地域学研究/(18)/pp.62-63, 2014-09 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 牛島 光一 住宅土地経済/(2010年秋季)/pp.36-39, 2010-10 / The Impact of a High-speed Railway on Residential Land Prices Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1344), 2016-03 / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -8270,6 +8308,7 @@
 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年
 都市における環境リスクの軽減の経済効果に関する研究
 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―
+非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
 Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05
 Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020
 The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04
@@ -8293,8 +8332,7 @@
 ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 牛島 光一 応用地域学研究/(18)/pp.62-63, 2014-09
 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 牛島 光一 住宅土地経済/(2010年秋季)/pp.36-39, 2010-10
 The Impact of a High-speed Railway on Residential Land Prices Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1344), 2016-03
-The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10
-School Choice and Student Sorting: Evidence from Adachi City in Japan Ushijima Koichi Department of Social Systems and Management, University of Tsukuba, 2007-03</t>
+The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10</t>
         </is>
       </c>
     </row>
@@ -8337,6 +8375,8 @@
 理論経済学
 社会システム工学・安全システム
 ゲーム理論; 進化ゲーム理論;
+Pairwise Imitation and Tournament Graphs Hwang Sung-ha; Neary Philip R.; Newton Jonathan; Sawa ... INTERNATIONAL ECONOMIC REVIEW, 2026-02-04
+Conventions in large games with randomly drawn payoffs Newton Jonathan; Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/157/pp.50-70, 2026-03
 The evolution of collective choice under majority rules Okada Akira; Sawa Ryoji JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/225/pp.290-304, 2024-09
 Statistical inference in evolutionary dynamics Sawa Ryoji; Wu Jiabin GAMES AND ECONOMIC BEHAVIOR/137/pp.294-316, 2023-01
 研究室の選好と学生の成績を考慮した研究室配属法の分析 杉浦 有輝; 澤 亮治 情報処理学会論文誌/64(3)/pp.698-707, 2023-03
@@ -8374,7 +8414,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The evolution of collective choice under majority rules Okada Akira; Sawa Ryoji JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/225/pp.290-304, 2024-09 / Statistical inference in evolutionary dynamics Sawa Ryoji; Wu Jiabin GAMES AND ECONOMIC BEHAVIOR/137/pp.294-316, 2023-01 / 研究室の選好と学生の成績を考慮した研究室配属法の分析 杉浦 有輝; 澤 亮治 情報処理学会論文誌/64(3)/pp.698-707, 2023-03 / 有限オートマトンを用いた私的観測繰り返しゲームにおける進化的安定戦略分析 小池 淳平; 澤 亮治 情報処理学会論文誌/63(3)/pp.773-786, 2022-03 / A stochastic stability analysis with observation errors in normal form games Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/129/pp.570-589, 2021-09 / Stochastic stability in the large population and small mutation limits for coordination games Sawa Ryoji Journal of Dynamics and Games, 2021 / oTreeを用いた配属システムの設計・構築とその運用 島田 夏美; 吉田 真聖人; 澤 亮治 情報処理学会論文誌/62(3)/pp.849-859, 2021-03 CiNii / A prospect theory Nash bargaining solution and its stochastic stability Sawa Ryoji JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/184/pp.692-711, 2021-04 / 複利型強化学習を用いたポートフォリオ選択手法についての研究 畠山 卓; 澤 亮治 情報処理学会論文誌/60(10)/pp.1631-1640, 2019-10 / Evolutionary dynamics in multitasking environments Sawa Ryoji; Zusai Dai JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/166/pp.288-308, 2019-10 / Stochastic stability under logit choice in coalitional bargaining problems Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/113/pp.633-650, 2019-01 Tsukuba Repository / Prospect dynamics and loss dominance Sawa Ryoji; Wu Jiabin GAMES AND ECONOMIC BEHAVIOR/112/pp.98-124, 2018-11 Tsukuba Repository / Reference-dependent preferences, super-dominance and stochastic stability Sawa Ryoji; Wu Jiabin JOURNAL OF MATHEMATICAL ECONOMICS/78/pp.96-104, 2018-10 Tsukuba Repository / A one-shot deviation principle for stability in matching problems Newton Jonathan; Sawa Ryoji JOURNAL OF ECONOMIC THEORY/157/pp.1-27, 2015-05 / Evolutionary imitative dynamics with population-varying aspiration levels Sawa Ryoji JOURNAL OF ECONOMIC THEORY/154/pp.562-577, 2014-11 / Coalitional stochastic stability in games, networks and markets Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/88/pp.90-111, 2014-11 / Mutation rates and equilibrium selection under stochastic evolutionary dynamics Sawa Ryoji INTERNATIONAL JOURNAL OF GAME THEORY/41(3)/pp.489-496, 2012-08 / CG を用いたマシンの3 次元構造進化システム 澤 亮治 電気学会論文誌. C, 電子・情報・システム部門誌 = The transactions of the Institute of Electrical Engineers of Japan. C, A publication of Electronics, Information and System Society/121(2)/pp.461-467, 2001-02</t>
+          <t>Pairwise Imitation and Tournament Graphs Hwang Sung-ha; Neary Philip R.; Newton Jonathan; Sawa ... INTERNATIONAL ECONOMIC REVIEW, 2026-02-04 / Conventions in large games with randomly drawn payoffs Newton Jonathan; Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/157/pp.50-70, 2026-03 / The evolution of collective choice under majority rules Okada Akira; Sawa Ryoji JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/225/pp.290-304, 2024-09 / Statistical inference in evolutionary dynamics Sawa Ryoji; Wu Jiabin GAMES AND ECONOMIC BEHAVIOR/137/pp.294-316, 2023-01 / 研究室の選好と学生の成績を考慮した研究室配属法の分析 杉浦 有輝; 澤 亮治 情報処理学会論文誌/64(3)/pp.698-707, 2023-03 / 有限オートマトンを用いた私的観測繰り返しゲームにおける進化的安定戦略分析 小池 淳平; 澤 亮治 情報処理学会論文誌/63(3)/pp.773-786, 2022-03 / A stochastic stability analysis with observation errors in normal form games Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/129/pp.570-589, 2021-09 / Stochastic stability in the large population and small mutation limits for coordination games Sawa Ryoji Journal of Dynamics and Games, 2021 / oTreeを用いた配属システムの設計・構築とその運用 島田 夏美; 吉田 真聖人; 澤 亮治 情報処理学会論文誌/62(3)/pp.849-859, 2021-03 CiNii / A prospect theory Nash bargaining solution and its stochastic stability Sawa Ryoji JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/184/pp.692-711, 2021-04 / 複利型強化学習を用いたポートフォリオ選択手法についての研究 畠山 卓; 澤 亮治 情報処理学会論文誌/60(10)/pp.1631-1640, 2019-10 / Evolutionary dynamics in multitasking environments Sawa Ryoji; Zusai Dai JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/166/pp.288-308, 2019-10 / Stochastic stability under logit choice in coalitional bargaining problems Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/113/pp.633-650, 2019-01 Tsukuba Repository / Prospect dynamics and loss dominance Sawa Ryoji; Wu Jiabin GAMES AND ECONOMIC BEHAVIOR/112/pp.98-124, 2018-11 Tsukuba Repository / Reference-dependent preferences, super-dominance and stochastic stability Sawa Ryoji; Wu Jiabin JOURNAL OF MATHEMATICAL ECONOMICS/78/pp.96-104, 2018-10 Tsukuba Repository / A one-shot deviation principle for stability in matching problems Newton Jonathan; Sawa Ryoji JOURNAL OF ECONOMIC THEORY/157/pp.1-27, 2015-05 / Evolutionary imitative dynamics with population-varying aspiration levels Sawa Ryoji JOURNAL OF ECONOMIC THEORY/154/pp.562-577, 2014-11 / Coalitional stochastic stability in games, networks and markets Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/88/pp.90-111, 2014-11 / Mutation rates and equilibrium selection under stochastic evolutionary dynamics Sawa Ryoji INTERNATIONAL JOURNAL OF GAME THEORY/41(3)/pp.489-496, 2012-08 / CG を用いたマシンの3 次元構造進化システム 澤 亮治 電気学会論文誌. C, 電子・情報・システム部門誌 = The transactions of the Institute of Electrical Engineers of Japan. C, A publication of Electronics, Information and System Society/121(2)/pp.461-467, 2001-02</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -8430,6 +8470,8 @@
 行動経済学の知見を利用した進化ゲーム理論による均衡選択分析
 社会選択問題への進化ゲーム理論的アプローチ
 マルチタスク環境および協力ゲームにおける進化ゲーム理論の研究
+Pairwise Imitation and Tournament Graphs Hwang Sung-ha; Neary Philip R.; Newton Jonathan; Sawa ... INTERNATIONAL ECONOMIC REVIEW, 2026-02-04
+Conventions in large games with randomly drawn payoffs Newton Jonathan; Sawa Ryoji GAMES AND ECONOMIC BEHAVIOR/157/pp.50-70, 2026-03
 The evolution of collective choice under majority rules Okada Akira; Sawa Ryoji JOURNAL OF ECONOMIC BEHAVIOR &amp; ORGANIZATION/225/pp.290-304, 2024-09
 Statistical inference in evolutionary dynamics Sawa Ryoji; Wu Jiabin GAMES AND ECONOMIC BEHAVIOR/137/pp.294-316, 2023-01
 研究室の選好と学生の成績を考慮した研究室配属法の分析 杉浦 有輝; 澤 亮治 情報処理学会論文誌/64(3)/pp.698-707, 2023-03
@@ -8662,7 +8704,8 @@
 数理計画
 オペレーションズ・リサーチ
 サービス工学
-Data Collaboration Analysis with Orthonormal Basis Selection and Alignment Nosaka Keiyu; Takano Yuichi; YOSHISE Akiko arXiv Preprint/pp.1-28, 2024-12
+Data collaboration analysis with orthonormal basis selection and alignment Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... Computers and Electrical Engineering/pp.1-28, 2026-06
+Data Collaboration Analysis with Orthonormal Basis Selection and Alignment (v6) Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... arXiv Preprint/pp.1-44, 2025-12
 Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning Nosaka Keiyu; Yoshise Akiko 2023 IEEE 3rd International Conference on Electronic Communications, Internet of Things and Big Data (ICEIB)/pp.180-185, 2023-07
 正循環制約を考慮したナーススケジューリング 本村力希; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.214-215, 2024-03
 Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices 野坂桂悠; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.50-51, 2024-03
@@ -8685,8 +8728,7 @@
 QAPの半正定値緩和問題を解くためのセンタリングADMM 加納 伸一; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.114-129, 2020-03
 SD基に基づく半正定値行列錐の凸多面錐近似 汪 玉柱; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.106-113, 2020-03
 ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― 高橋 直希; 高野 祐一; 吉瀬 章子 オペレーションズ・リサーチ/68(8)/pp.453-459, 2019-08
-Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Discussion Paper Series/1368, 2020-01
-Polyhedral approximations of the semidefinite cone and their application Yuzhu Wang; Akihiro Tanaka; 吉瀬 章子 Discussion Paper Series/1359, 2019-05</t>
+Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Discussion Paper Series/1368, 2020-01</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8706,7 +8748,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Data Collaboration Analysis with Orthonormal Basis Selection and Alignment Nosaka Keiyu; Takano Yuichi; YOSHISE Akiko arXiv Preprint/pp.1-28, 2024-12 / Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning Nosaka Keiyu; Yoshise Akiko 2023 IEEE 3rd International Conference on Electronic Communications, Internet of Things and Big Data (ICEIB)/pp.180-185, 2023-07 / 正循環制約を考慮したナーススケジューリング 本村力希; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.214-215, 2024-03 / Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices 野坂桂悠; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.50-51, 2024-03 / Post-Processing with Projection and Rescaling Algorithms for Semidefinite Programming Kanoh Shin-ichi; Yoshise Akiko arXiv preprint, 2024-01 / Riemannian Interior Point Methods for Constrained Optimization on Manifolds Lai Zhijian; Yoshise Akiko arXiv preprint, 2022-02 / A new extension of Chubanov's method to symmetric cones Kanoh Shin-ichi; Yoshise Akiko Mathematical Programming/205(1)/pp.773-812, 2024-05 / 射影- 再スケーリング法を用いた 対称錐計画問題に対する後処理アルゴリズム 加納伸一; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2023年春季研究発表会アブストラクト集/pp.12-13, 2023-03 / Riemannian Interior Point Methods for Constrained Optimization on Manifolds 頼志堅; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2023年春季研究発表会アブストラクト集/pp.10-11, 2023-03 / On the Global Convergence of Riemannian Interior Point Method 頼志堅; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2022年秋季研究発表会アブストラクト集/pp.194-195, 2022-09 / Completely positive factorization by a Riemannian smoothing method Lai Zhijian; Yoshise Akiko COMPUTATIONAL OPTIMIZATION AND APPLICATIONS/83(3)/pp.933-966, 2022-10 / Evaluating approximations of the semidefinite cone with trace normalized distance Yuzhu Wang; 吉瀬 章子 arXiv preprint, 2021-05 / Evaluating approximations of the semidefinite cone with trace normalized distance Yuzhu Wang; 吉瀬 章子 OPTIMIZATION LETTERS/Epub, 2022-07 / A New Extension of Chubanov's Method to Symmetric Cones Kanoh Shin-ichi; Yoshise Akiko arXiv preprint, 2021-10 / Riemannian Interior Point Methods for Constrained Optimization on Manifolds Lai Zhijian; Yoshise Akiko Journal of Optimization Theory and Applications/201(1)/pp.433-469, 2024-03 / Completely Positive Factorization in Orthogonality Optimization via Smoothing Method Lai Zhijian; Yoshise Akiko arXiv preprint, 2021-07 / Scenario-based CVaR Approach to Strategic Decision Support in One-way Station-based Carsharing Systems Kai Zhang; 高野祐一; 吉瀬 章子 SIAM News Blog, 2021-12 / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach Zhang Kai; Takano Yuichi; Wang Yuzhu; Yoshise Akiko IEEE Access/9/pp.79816-79828, 2021-06 / Polyhedral approximations of the semidefinite cone and their application Yuzhu Wang; Akihiro Tanaka; 吉瀬 章子 Computational Optimization and Applications/78/pp.893-913, 2021-01 / Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Peoceedings of NACA-ICOTA2019/1/pp.197-213, 2021-09 / QAPの半正定値緩和問題を解くためのセンタリングADMM 加納 伸一; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.114-129, 2020-03 / SD基に基づく半正定値行列錐の凸多面錐近似 汪 玉柱; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.106-113, 2020-03 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― 高橋 直希; 高野 祐一; 吉瀬 章子 オペレーションズ・リサーチ/68(8)/pp.453-459, 2019-08 / Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Discussion Paper Series/1368, 2020-01 / Polyhedral approximations of the semidefinite cone and their application Yuzhu Wang; Akihiro Tanaka; 吉瀬 章子 Discussion Paper Series/1359, 2019-05</t>
+          <t>Data collaboration analysis with orthonormal basis selection and alignment Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... Computers and Electrical Engineering/pp.1-28, 2026-06 / Data Collaboration Analysis with Orthonormal Basis Selection and Alignment (v6) Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... arXiv Preprint/pp.1-44, 2025-12 / Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning Nosaka Keiyu; Yoshise Akiko 2023 IEEE 3rd International Conference on Electronic Communications, Internet of Things and Big Data (ICEIB)/pp.180-185, 2023-07 / 正循環制約を考慮したナーススケジューリング 本村力希; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.214-215, 2024-03 / Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices 野坂桂悠; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.50-51, 2024-03 / Post-Processing with Projection and Rescaling Algorithms for Semidefinite Programming Kanoh Shin-ichi; Yoshise Akiko arXiv preprint, 2024-01 / Riemannian Interior Point Methods for Constrained Optimization on Manifolds Lai Zhijian; Yoshise Akiko arXiv preprint, 2022-02 / A new extension of Chubanov's method to symmetric cones Kanoh Shin-ichi; Yoshise Akiko Mathematical Programming/205(1)/pp.773-812, 2024-05 / 射影- 再スケーリング法を用いた 対称錐計画問題に対する後処理アルゴリズム 加納伸一; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2023年春季研究発表会アブストラクト集/pp.12-13, 2023-03 / Riemannian Interior Point Methods for Constrained Optimization on Manifolds 頼志堅; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2023年春季研究発表会アブストラクト集/pp.10-11, 2023-03 / On the Global Convergence of Riemannian Interior Point Method 頼志堅; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2022年秋季研究発表会アブストラクト集/pp.194-195, 2022-09 / Completely positive factorization by a Riemannian smoothing method Lai Zhijian; Yoshise Akiko COMPUTATIONAL OPTIMIZATION AND APPLICATIONS/83(3)/pp.933-966, 2022-10 / Evaluating approximations of the semidefinite cone with trace normalized distance Yuzhu Wang; 吉瀬 章子 arXiv preprint, 2021-05 / Evaluating approximations of the semidefinite cone with trace normalized distance Yuzhu Wang; 吉瀬 章子 OPTIMIZATION LETTERS/Epub, 2022-07 / A New Extension of Chubanov's Method to Symmetric Cones Kanoh Shin-ichi; Yoshise Akiko arXiv preprint, 2021-10 / Riemannian Interior Point Methods for Constrained Optimization on Manifolds Lai Zhijian; Yoshise Akiko Journal of Optimization Theory and Applications/201(1)/pp.433-469, 2024-03 / Completely Positive Factorization in Orthogonality Optimization via Smoothing Method Lai Zhijian; Yoshise Akiko arXiv preprint, 2021-07 / Scenario-based CVaR Approach to Strategic Decision Support in One-way Station-based Carsharing Systems Kai Zhang; 高野祐一; 吉瀬 章子 SIAM News Blog, 2021-12 / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach Zhang Kai; Takano Yuichi; Wang Yuzhu; Yoshise Akiko IEEE Access/9/pp.79816-79828, 2021-06 / Polyhedral approximations of the semidefinite cone and their application Yuzhu Wang; Akihiro Tanaka; 吉瀬 章子 Computational Optimization and Applications/78/pp.893-913, 2021-01 / Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Peoceedings of NACA-ICOTA2019/1/pp.197-213, 2021-09 / QAPの半正定値緩和問題を解くためのセンタリングADMM 加納 伸一; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.114-129, 2020-03 / SD基に基づく半正定値行列錐の凸多面錐近似 汪 玉柱; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.106-113, 2020-03 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― 高橋 直希; 高野 祐一; 吉瀬 章子 オペレーションズ・リサーチ/68(8)/pp.453-459, 2019-08 / Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Discussion Paper Series/1368, 2020-01</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -8779,7 +8821,8 @@
 地域未来創生共同研究講座
 次世代社会システムとモビリティの新価値研究
 購買データに基づく顧客行動分析
-Data Collaboration Analysis with Orthonormal Basis Selection and Alignment Nosaka Keiyu; Takano Yuichi; YOSHISE Akiko arXiv Preprint/pp.1-28, 2024-12
+Data collaboration analysis with orthonormal basis selection and alignment Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... Computers and Electrical Engineering/pp.1-28, 2026-06
+Data Collaboration Analysis with Orthonormal Basis Selection and Alignment (v6) Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... arXiv Preprint/pp.1-44, 2025-12
 Creating Collaborative Data Representations Using Matrix Manifold Optimal Computation and Automated Hyperparameter Tuning Nosaka Keiyu; Yoshise Akiko 2023 IEEE 3rd International Conference on Electronic Communications, Internet of Things and Big Data (ICEIB)/pp.180-185, 2023-07
 正循環制約を考慮したナーススケジューリング 本村力希; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.214-215, 2024-03
 Data Collaboration Analysis for Distributed Datasets With Orthogonal Integration Matrices 野坂桂悠; 吉瀬 章子 日本オペレーションズ・リサーチ学会 2024年春季研究発表会アブストラクト集/pp.50-51, 2024-03
@@ -8802,8 +8845,7 @@
 QAPの半正定値緩和問題を解くためのセンタリングADMM 加納 伸一; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.114-129, 2020-03
 SD基に基づく半正定値行列錐の凸多面錐近似 汪 玉柱; 吉瀬 章子 統計数理研究所共同研究リポート「最適化：モデリングとアルゴリズム」/428/pp.106-113, 2020-03
 ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― 高橋 直希; 高野 祐一; 吉瀬 章子 オペレーションズ・リサーチ/68(8)/pp.453-459, 2019-08
-Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Discussion Paper Series/1368, 2020-01
-Polyhedral approximations of the semidefinite cone and their application Yuzhu Wang; Akihiro Tanaka; 吉瀬 章子 Discussion Paper Series/1359, 2019-05</t>
+Centering ADMM for the Semidefinite Relaxation of the QAP Kanoh Shin-ichi; Yoshise Akiko Discussion Paper Series/1368, 2020-01</t>
         </is>
       </c>
     </row>
@@ -8854,6 +8896,12 @@
 ソフトコンピューティング
 データマイニング
 多次元データ解析
+Reliability of clustering methods-based uncertainty SATO-ILIC Mika 65th ISI World Statistics Congress, 2025-10
+混合データを用いたファジィクラスタリングに基づくハイブリッド識別法 山本薫; イリチュ 美佳 2025年度日本分類学会シンポジウム予稿集/pp.1-4, 2025-12
+Fuzzy clustering-based weighted principal component analysis for mixed data SATO-ILIC Mika IEEE International Conference on Fuzzy Systems, 2025-07
+Dimensionality Reduction Method for Fuzzy Interval Data Using Deep Learning SUGIURA Gakuei; SATO-ILIC Mika Procedia Computer Science, Elsevier/270/pp.2247-2256, 2025-09
+収支項目分類符号に対する効率的な自動格付に関する研究 床 裕佳子; イリチュ 美佳 リサーチペーパー第 63 号/pp.1-26, 2025-06
+Explainable dimensionality reduction for mixed data considering uncertainty of dynamic classification boundaries (accepted) SATO-ILIC Mika Procedia Computer Science, Elsevier, 2026-03
 Simultaneous visualization method for mixed HDLSS data and its application for education SATO-ILIC Mika; ILIC Peter Procedia Computer Science/246/pp.5036-5045, 2024-09
 Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design ILIC Peter; SATO-ILIC Mika Smart Innovation, Systems and Technologies/399/pp.141-150, 2024-06
 Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey TOKO Yukako; SATO-ILIC Mika Procedia Computer Science/246/pp.1820-1829, 2024-09
@@ -8872,13 +8920,7 @@
 Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results Toko Yukako; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.43-44, 2022-12
 Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling Takamura Shojiro; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.45-46, 2022-12
 Cluster-based Analysis for Discrimination of Individuality （招待講演） Sato-Ilic Mika Global Summit and Expo on Robot Intelligence Technology and Applications2022, 2022/09/19
-クラスター尺度に基づくデータ間差異の検出と市場データへの応用 本多 拓朗; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.788-790, 2022-09
-ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 加藤 優友; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.431-434, 2022-09
-Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data Sato-Ilic Mika The 24th International Conference on Computational Statistics, 2022-08-23
-Clustering and Multidimensional Scaling for Individual Difference Extraction Sato-Ilic Mika The 4th International Conference on Statistics: Theory and Applications/pp.162-1-162-8, 2022-07
-多次元尺度法による計算効率を考慮したディープラーニング手法 高村 昇二郎; イリチユ 美佳 ⽇本分類学会第41回⼤会予稿集/pp.54-57, 2022-06
-Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means Yukako Toko; Sato-Ilic Mika ROMANIAN STATISTICAL REVIEW/1/pp.27-39, 2022-03
-区間組成データに対する重み付き回帰分析 藤本 聖; イリチユ 美佳 日本分類学会シンポジウム予稿集/pp.19, 1-19, 4, 2021-12</t>
+クラスター尺度に基づくデータ間差異の検出と市場データへの応用 本多 拓朗; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.788-790, 2022-09</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8898,7 +8940,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Simultaneous visualization method for mixed HDLSS data and its application for education SATO-ILIC Mika; ILIC Peter Procedia Computer Science/246/pp.5036-5045, 2024-09 / Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design ILIC Peter; SATO-ILIC Mika Smart Innovation, Systems and Technologies/399/pp.141-150, 2024-06 / Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey TOKO Yukako; SATO-ILIC Mika Procedia Computer Science/246/pp.1820-1829, 2024-09 / Difference on Evaluation Scores Considering Image Descriptions for Autocoding Toko Yukako; Sato-Ilic Mika ROMANIAN STATISTICAL REVIEW/1/pp.27-42, 2024 / ファジィクラスタリングの信頼度について イリチュ 美佳 本分類学会第４３回大会予稿集/pp.45-48, 2024-06 / Hierarchical Support Vector Machine based Classifier for Autocoding Toko Yukako; Sato-Ilic Mika Procedia Computer Science, Elsevier/225/pp.2733-2742, 2023-09 / Fuzzy Cluster-Scaled Principal Component Analysis for Mixed Data and Its Application of Educational Effect based on Device Selection Sato-Ilic Mika; Ilic Peter Procedia Computer Science, Elsevier/225/pp.2402-2411, 2023-09 / A Fuzzy Cluster-Scaled Principal Component Analysis for Mixed High-Dimension and Low-Sample Size Data SATO-ILIC Mika 25th International Conference on Computational Statistics, 2023 / Principal component analysis for mixed high-dimension low-sample size data based on fuzzy-cluster scale SATO-ILIC Mika 16th International Conference of the ERCIM WG on Computational and Methodological Statistics and 17th International Conference on Computational and Financial Econometrics, 2023 / Improvement of Training Data for Autocoding on "The National Survey of Family Income, Consumption and Wealth" and "The Family Income and Expenditure Survey" Toko Yukako; Sato-Ilic Mika 日本分類学会第42回大会予稿集/pp.49-52, 2023 / Fuzzy Clustering based Autocoding Methods for Family Income and Expenditure Surveys Toko Yukako; Sato-Ilic Mika Conference on New Techniques and Technologies for Official Statistics/pp.404-408, 2023 / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding Toko Yukako; Sato-Ilic Mika; Takayuki Sasajima ROMANIAN STATISTICAL REVIEW/1(1)/pp.34-48, 2023 / Fuzzy Clustering based Classifier for Extraction of Individualities from High Dimension Low Sample Size Data Sato-Ilic Mika INTELLIGENT DECISION TECHNOLOGIES-NETHERLANDS/17(1)/pp.127-138, 2023 / Individuality-based Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data Sato-Ilic Mika 15th International Conference of the ERCIM WG on Computational and Methodological Statistics and 16th International Conference on Computational and Financial Econometrics, 2022-12-17 / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding Toko Yukako; Sato-Ilic Mika The Annual Conference on the Use of R in Official Statistics (10th International Conference: uRos2022), 2022-12-06 / Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results Toko Yukako; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.43-44, 2022-12 / Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling Takamura Shojiro; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.45-46, 2022-12 / Cluster-based Analysis for Discrimination of Individuality （招待講演） Sato-Ilic Mika Global Summit and Expo on Robot Intelligence Technology and Applications2022, 2022/09/19 / クラスター尺度に基づくデータ間差異の検出と市場データへの応用 本多 拓朗; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.788-790, 2022-09 / ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 加藤 優友; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.431-434, 2022-09 / Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data Sato-Ilic Mika The 24th International Conference on Computational Statistics, 2022-08-23 / Clustering and Multidimensional Scaling for Individual Difference Extraction Sato-Ilic Mika The 4th International Conference on Statistics: Theory and Applications/pp.162-1-162-8, 2022-07 / 多次元尺度法による計算効率を考慮したディープラーニング手法 高村 昇二郎; イリチユ 美佳 ⽇本分類学会第41回⼤会予稿集/pp.54-57, 2022-06 / Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means Yukako Toko; Sato-Ilic Mika ROMANIAN STATISTICAL REVIEW/1/pp.27-39, 2022-03 / 区間組成データに対する重み付き回帰分析 藤本 聖; イリチユ 美佳 日本分類学会シンポジウム予稿集/pp.19, 1-19, 4, 2021-12</t>
+          <t>Reliability of clustering methods-based uncertainty SATO-ILIC Mika 65th ISI World Statistics Congress, 2025-10 / 混合データを用いたファジィクラスタリングに基づくハイブリッド識別法 山本薫; イリチュ 美佳 2025年度日本分類学会シンポジウム予稿集/pp.1-4, 2025-12 / Fuzzy clustering-based weighted principal component analysis for mixed data SATO-ILIC Mika IEEE International Conference on Fuzzy Systems, 2025-07 / Dimensionality Reduction Method for Fuzzy Interval Data Using Deep Learning SUGIURA Gakuei; SATO-ILIC Mika Procedia Computer Science, Elsevier/270/pp.2247-2256, 2025-09 / 収支項目分類符号に対する効率的な自動格付に関する研究 床 裕佳子; イリチュ 美佳 リサーチペーパー第 63 号/pp.1-26, 2025-06 / Explainable dimensionality reduction for mixed data considering uncertainty of dynamic classification boundaries (accepted) SATO-ILIC Mika Procedia Computer Science, Elsevier, 2026-03 / Simultaneous visualization method for mixed HDLSS data and its application for education SATO-ILIC Mika; ILIC Peter Procedia Computer Science/246/pp.5036-5045, 2024-09 / Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design ILIC Peter; SATO-ILIC Mika Smart Innovation, Systems and Technologies/399/pp.141-150, 2024-06 / Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey TOKO Yukako; SATO-ILIC Mika Procedia Computer Science/246/pp.1820-1829, 2024-09 / Difference on Evaluation Scores Considering Image Descriptions for Autocoding Toko Yukako; Sato-Ilic Mika ROMANIAN STATISTICAL REVIEW/1/pp.27-42, 2024 / ファジィクラスタリングの信頼度について イリチュ 美佳 本分類学会第４３回大会予稿集/pp.45-48, 2024-06 / Hierarchical Support Vector Machine based Classifier for Autocoding Toko Yukako; Sato-Ilic Mika Procedia Computer Science, Elsevier/225/pp.2733-2742, 2023-09 / Fuzzy Cluster-Scaled Principal Component Analysis for Mixed Data and Its Application of Educational Effect based on Device Selection Sato-Ilic Mika; Ilic Peter Procedia Computer Science, Elsevier/225/pp.2402-2411, 2023-09 / A Fuzzy Cluster-Scaled Principal Component Analysis for Mixed High-Dimension and Low-Sample Size Data SATO-ILIC Mika 25th International Conference on Computational Statistics, 2023 / Principal component analysis for mixed high-dimension low-sample size data based on fuzzy-cluster scale SATO-ILIC Mika 16th International Conference of the ERCIM WG on Computational and Methodological Statistics and 17th International Conference on Computational and Financial Econometrics, 2023 / Improvement of Training Data for Autocoding on "The National Survey of Family Income, Consumption and Wealth" and "The Family Income and Expenditure Survey" Toko Yukako; Sato-Ilic Mika 日本分類学会第42回大会予稿集/pp.49-52, 2023 / Fuzzy Clustering based Autocoding Methods for Family Income and Expenditure Surveys Toko Yukako; Sato-Ilic Mika Conference on New Techniques and Technologies for Official Statistics/pp.404-408, 2023 / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding Toko Yukako; Sato-Ilic Mika; Takayuki Sasajima ROMANIAN STATISTICAL REVIEW/1(1)/pp.34-48, 2023 / Fuzzy Clustering based Classifier for Extraction of Individualities from High Dimension Low Sample Size Data Sato-Ilic Mika INTELLIGENT DECISION TECHNOLOGIES-NETHERLANDS/17(1)/pp.127-138, 2023 / Individuality-based Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data Sato-Ilic Mika 15th International Conference of the ERCIM WG on Computational and Methodological Statistics and 16th International Conference on Computational and Financial Econometrics, 2022-12-17 / Improvement of Model Construction based on Reliability Scores of Objects for Autocoding Toko Yukako; Sato-Ilic Mika The Annual Conference on the Use of R in Official Statistics (10th International Conference: uRos2022), 2022-12-06 / Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results Toko Yukako; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.43-44, 2022-12 / Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling Takamura Shojiro; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.45-46, 2022-12 / Cluster-based Analysis for Discrimination of Individuality （招待講演） Sato-Ilic Mika Global Summit and Expo on Robot Intelligence Technology and Applications2022, 2022/09/19 / クラスター尺度に基づくデータ間差異の検出と市場データへの応用 本多 拓朗; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.788-790, 2022-09</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -8964,6 +9006,12 @@
 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学
 高次元データの理論と方法論の総合的研究
 高次Aggregation Operatorの開発とクラスタリングモデルへの適用
+Reliability of clustering methods-based uncertainty SATO-ILIC Mika 65th ISI World Statistics Congress, 2025-10
+混合データを用いたファジィクラスタリングに基づくハイブリッド識別法 山本薫; イリチュ 美佳 2025年度日本分類学会シンポジウム予稿集/pp.1-4, 2025-12
+Fuzzy clustering-based weighted principal component analysis for mixed data SATO-ILIC Mika IEEE International Conference on Fuzzy Systems, 2025-07
+Dimensionality Reduction Method for Fuzzy Interval Data Using Deep Learning SUGIURA Gakuei; SATO-ILIC Mika Procedia Computer Science, Elsevier/270/pp.2247-2256, 2025-09
+収支項目分類符号に対する効率的な自動格付に関する研究 床 裕佳子; イリチュ 美佳 リサーチペーパー第 63 号/pp.1-26, 2025-06
+Explainable dimensionality reduction for mixed data considering uncertainty of dynamic classification boundaries (accepted) SATO-ILIC Mika Procedia Computer Science, Elsevier, 2026-03
 Simultaneous visualization method for mixed HDLSS data and its application for education SATO-ILIC Mika; ILIC Peter Procedia Computer Science/246/pp.5036-5045, 2024-09
 Mapping Students’ Digital Eco-system Usage Patterns Using Kernel-Based Principal Component Analysis to Inform Course Design ILIC Peter; SATO-ILIC Mika Smart Innovation, Systems and Technologies/399/pp.141-150, 2024-06
 Comparison of fuzzy clustering based SVM with reinforcement learning based SVM for autocoding of the Family Income and Expenditure Survey TOKO Yukako; SATO-ILIC Mika Procedia Computer Science/246/pp.1820-1829, 2024-09
@@ -8982,13 +9030,7 @@
 Fuzzy Clustering based Support Vector Machine for Autocoding and Interpretation of Results Toko Yukako; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.43-44, 2022-12
 Deep Learning Method for Imbalanced Image Data Considering Reduction of Dimensionality by Multidimensional Scaling Takamura Shojiro; Sato-Ilic Mika IASC-ARS Interim Conference 2022 - The Interplay between Statistical Computing and Artificial Intelligence/pp.45-46, 2022-12
 Cluster-based Analysis for Discrimination of Individuality （招待講演） Sato-Ilic Mika Global Summit and Expo on Robot Intelligence Technology and Applications2022, 2022/09/19
-クラスター尺度に基づくデータ間差異の検出と市場データへの応用 本多 拓朗; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.788-790, 2022-09
-ファジィクラスタリングに基づくサポートベクターマシンを用いたがん種類の識別 加藤 優友; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.431-434, 2022-09
-Fuzzy Cluster-Scaled Principal Component Analysis for High-Dimension Low-Sample Data Sato-Ilic Mika The 24th International Conference on Computational Statistics, 2022-08-23
-Clustering and Multidimensional Scaling for Individual Difference Extraction Sato-Ilic Mika The 4th International Conference on Statistics: Theory and Applications/pp.162-1-162-8, 2022-07
-多次元尺度法による計算効率を考慮したディープラーニング手法 高村 昇二郎; イリチユ 美佳 ⽇本分類学会第41回⼤会予稿集/pp.54-57, 2022-06
-Autocoding based Multi-Class Support Vector Machine by Fuzzy c-Means Yukako Toko; Sato-Ilic Mika ROMANIAN STATISTICAL REVIEW/1/pp.27-39, 2022-03
-区間組成データに対する重み付き回帰分析 藤本 聖; イリチユ 美佳 日本分類学会シンポジウム予稿集/pp.19, 1-19, 4, 2021-12</t>
+クラスター尺度に基づくデータ間差異の検出と市場データへの応用 本多 拓朗; イリチユ 美佳 第38回ファジィシステムシンポジウム講演論文集/pp.788-790, 2022-09</t>
         </is>
       </c>
     </row>
@@ -9043,6 +9085,8 @@
 計算社会科学
 ウェブサイエンス
 ビッグデータ
+Linking Opinion Dynamics and Emotional Expression in Online Communities: a Case Study of Covid-19 Vaccination Discourse in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako The 10th International Workshop on Application of Big Data for Computational Social Science (ABCSS2025)/pp.5876-5883, 2025-12-09
+SNSにおける日本の高齢運転者に対する言論の定量化 佐野幸恵; 中西映人; 吉田光男; 市川政雄 情報処理学会 第88回全国大会, 2026-03
 Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-04-01
 コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 呉 潜雲; 佐野 幸恵; 高安 秀樹; Havlin Shlomo; 高安 美佐子 人工知能学会全国大会論文集/JSAI2024/pp.2I4OS1b05-2I4OS1b05, 2024-05-28
 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19
@@ -9065,9 +9109,7 @@
 サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して 浅野 翔; 雨宮 護; 佐野 幸恵 オペレーションズリサーチ/66(4)/pp.240(44)-245(49), 2021-04
 Fake news propagates differently from real news even at early stages of spreading Zhao Zilong; Zhao Jichang; Sano Yukie; Levy Orr; Takayasu... EPJ Data Science/9/p.7, 2020-04
 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii
-Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository
-Correlations and fluctuations in the word sets of collective emotions Sano Yukie Nonlinear Theory and Its Applications, IEICE/9(3)/pp.382-390, 2018-07 CiNii Tsukuba Repository
-Configuration model for correlation matrices preserving the node strength Masuda Naoki; Kojaku Sadamori; Sano Yukie Physical Review E/98(1)/p.012312, 2018-07 PubMed</t>
+Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9087,7 +9129,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-04-01 / コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 呉 潜雲; 佐野 幸恵; 高安 秀樹; Havlin Shlomo; 高安 美佐子 人工知能学会全国大会論文集/JSAI2024/pp.2I4OS1b05-2I4OS1b05, 2024-05-28 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19 / Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Havlin Shlom... Scientific Reports/15(1)/p.11716, 2025-04 / Quantifying Collective Emotions: Japan’s Societal Trends Through Enhanced Sentiment Index Using POMS2 and SNS TAMURA Koutarou; SANO Yukie; SHIOZAKI Junichi 2024 IEEE International Conference on Big Data (BigData)/pp.3082-3087, 2024-12 / Quantifying collective attention and fan engagement: a case study of the Japanese professional baseball league Otomo Naofumi; Sasahara Kazutoshi; Mizuno Makoto; Sano... Journal of Computational Social Science/8(2), 2025-03 / News coverage of older drivers' fatal car crashes: is it over-represented? Ichikawa Masao; Tanaka Rie; Nakanishi Akito; Sano Yukie JOURNAL OF EPIDEMIOLOGY/Epub, 2024-10-26 / Burstiness of human physical activities and their characterisation Takeuchi Makoto; Sano Yukie Journal of Computational Social Science/7/pp.625-641, 2024-03 / 12-year observation of tweets about rubella in Japan: A retrospective infodemiology study Sano Yukie; Hori Ai PLOS ONE/18(5)/p.e0285101, 2023-05 PubMed / A two-phase model of collective memory decay with a dynamical switching point Igarashi Naoki; Okada Yukihiko; Sayama Hiroki; Sano Y... SCIENTIFIC REPORTS/12(1), 2022-12 / SNSデータを用いた情報拡散シミュレーション 佐野 幸恵; 鳥居 寛之 シミュレーション = Journal of the Japan Society for Simulation Technology / 日本シミュレーション学会 編/40(3)/pp.137-143, 2021-09 CiNii / SNSにおける情報伝播ネットワークの構造 佐野 幸恵; 高安 秀樹; 高安 美佐子 日本物理学会誌/77(7)/pp.458-463, 2022-07-05 / Music Roles Affect the Selection of Consumption Means: A Questionnaire Survey of People’s Expectations for Music and Exploratory Factor Analysis Takeuchi Makoto; Morishita Soichiro; Sano Yukie REVIEW OF SOCIONETWORK STRATEGIES/16(2:SI)/pp.453-464, 2022-09 / Dataset of identified scholars mentioned in acknowledgement statements Kusumegi Keigo; Sano Yukie Scientific data/9(1)/p.461, 2022-08 / Classification of endogenous and exogenous bursts in collective emotions based on Weibo comments during COVID-19 Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako Scientific Reports/12(1)/p.3120, 2022-02 / 日本におけるオンライン・ハラスメントの現状と対策：Twitterでの女性記者のツイート「炎上」を例に 礪波 亜希; 吉田 光男; 佐野 幸恵 F1000Research/10, 2022-02 / 日本における自治体報道発表のCOVID-19発生状況を用いた感染者遷移状況の記録と可視化 渡辺 知恵美; 佐野 幸恵; 岡田幸彦; 天笠 俊之 研究報告ドキュメントコミュニケーション（DC）/2020-DC-117(4)/pp.1-7, 2020-07 / Simulation of information spreading on Twitter concerning radiation after the Fukushima nuclear power plant accident Sano Yukie; Torii Hiroyuki A; Onoue Yosuke; Uno Kazuko Frontiers in Physics/9, 2021-06 / 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― 水野 誠; 佐野 幸恵; 笹原 和俊 マーケティングジャーナル/40(4)/pp.6-18, 2021 CiNii / サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して 浅野 翔; 雨宮 護; 佐野 幸恵 オペレーションズリサーチ/66(4)/pp.240(44)-245(49), 2021-04 / Fake news propagates differently from real news even at early stages of spreading Zhao Zilong; Zhao Jichang; Sano Yukie; Levy Orr; Takayasu... EPJ Data Science/9/p.7, 2020-04 / 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii / Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository / Correlations and fluctuations in the word sets of collective emotions Sano Yukie Nonlinear Theory and Its Applications, IEICE/9(3)/pp.382-390, 2018-07 CiNii Tsukuba Repository / Configuration model for correlation matrices preserving the node strength Masuda Naoki; Kojaku Sadamori; Sano Yukie Physical Review E/98(1)/p.012312, 2018-07 PubMed</t>
+          <t>Linking Opinion Dynamics and Emotional Expression in Online Communities: a Case Study of Covid-19 Vaccination Discourse in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako The 10th International Workshop on Application of Big Data for Computational Social Science (ABCSS2025)/pp.5876-5883, 2025-12-09 / SNSにおける日本の高齢運転者に対する言論の定量化 佐野幸恵; 中西映人; 吉田光男; 市川政雄 情報処理学会 第88回全国大会, 2026-03 / Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-04-01 / コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 呉 潜雲; 佐野 幸恵; 高安 秀樹; Havlin Shlomo; 高安 美佐子 人工知能学会全国大会論文集/JSAI2024/pp.2I4OS1b05-2I4OS1b05, 2024-05-28 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19 / Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Havlin Shlom... Scientific Reports/15(1)/p.11716, 2025-04 / Quantifying Collective Emotions: Japan’s Societal Trends Through Enhanced Sentiment Index Using POMS2 and SNS TAMURA Koutarou; SANO Yukie; SHIOZAKI Junichi 2024 IEEE International Conference on Big Data (BigData)/pp.3082-3087, 2024-12 / Quantifying collective attention and fan engagement: a case study of the Japanese professional baseball league Otomo Naofumi; Sasahara Kazutoshi; Mizuno Makoto; Sano... Journal of Computational Social Science/8(2), 2025-03 / News coverage of older drivers' fatal car crashes: is it over-represented? Ichikawa Masao; Tanaka Rie; Nakanishi Akito; Sano Yukie JOURNAL OF EPIDEMIOLOGY/Epub, 2024-10-26 / Burstiness of human physical activities and their characterisation Takeuchi Makoto; Sano Yukie Journal of Computational Social Science/7/pp.625-641, 2024-03 / 12-year observation of tweets about rubella in Japan: A retrospective infodemiology study Sano Yukie; Hori Ai PLOS ONE/18(5)/p.e0285101, 2023-05 PubMed / A two-phase model of collective memory decay with a dynamical switching point Igarashi Naoki; Okada Yukihiko; Sayama Hiroki; Sano Y... SCIENTIFIC REPORTS/12(1), 2022-12 / SNSデータを用いた情報拡散シミュレーション 佐野 幸恵; 鳥居 寛之 シミュレーション = Journal of the Japan Society for Simulation Technology / 日本シミュレーション学会 編/40(3)/pp.137-143, 2021-09 CiNii / SNSにおける情報伝播ネットワークの構造 佐野 幸恵; 高安 秀樹; 高安 美佐子 日本物理学会誌/77(7)/pp.458-463, 2022-07-05 / Music Roles Affect the Selection of Consumption Means: A Questionnaire Survey of People’s Expectations for Music and Exploratory Factor Analysis Takeuchi Makoto; Morishita Soichiro; Sano Yukie REVIEW OF SOCIONETWORK STRATEGIES/16(2:SI)/pp.453-464, 2022-09 / Dataset of identified scholars mentioned in acknowledgement statements Kusumegi Keigo; Sano Yukie Scientific data/9(1)/p.461, 2022-08 / Classification of endogenous and exogenous bursts in collective emotions based on Weibo comments during COVID-19 Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako Scientific Reports/12(1)/p.3120, 2022-02 / 日本におけるオンライン・ハラスメントの現状と対策：Twitterでの女性記者のツイート「炎上」を例に 礪波 亜希; 吉田 光男; 佐野 幸恵 F1000Research/10, 2022-02 / 日本における自治体報道発表のCOVID-19発生状況を用いた感染者遷移状況の記録と可視化 渡辺 知恵美; 佐野 幸恵; 岡田幸彦; 天笠 俊之 研究報告ドキュメントコミュニケーション（DC）/2020-DC-117(4)/pp.1-7, 2020-07 / Simulation of information spreading on Twitter concerning radiation after the Fukushima nuclear power plant accident Sano Yukie; Torii Hiroyuki A; Onoue Yosuke; Uno Kazuko Frontiers in Physics/9, 2021-06 / 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― 水野 誠; 佐野 幸恵; 笹原 和俊 マーケティングジャーナル/40(4)/pp.6-18, 2021 CiNii / サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して 浅野 翔; 雨宮 護; 佐野 幸恵 オペレーションズリサーチ/66(4)/pp.240(44)-245(49), 2021-04 / Fake news propagates differently from real news even at early stages of spreading Zhao Zilong; Zhao Jichang; Sano Yukie; Levy Orr; Takayasu... EPJ Data Science/9/p.7, 2020-04 / 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii / Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -9180,6 +9222,8 @@
 乳幼児の活動量を測定するウェアラブル機器の開発
 乳幼児の活動量を測定するウェアラブルデバイスの開発
 サイバー社会ネットワークにおける噂の伝播の検出と制御
+Linking Opinion Dynamics and Emotional Expression in Online Communities: a Case Study of Covid-19 Vaccination Discourse in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako The 10th International Workshop on Application of Big Data for Computational Social Science (ABCSS2025)/pp.5876-5883, 2025-12-09
+SNSにおける日本の高齢運転者に対する言論の定量化 佐野幸恵; 中西映人; 吉田光男; 市川政雄 情報処理学会 第88回全国大会, 2026-03
 Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-04-01
 コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 呉 潜雲; 佐野 幸恵; 高安 秀樹; Havlin Shlomo; 高安 美佐子 人工知能学会全国大会論文集/JSAI2024/pp.2I4OS1b05-2I4OS1b05, 2024-05-28
 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19
@@ -9202,9 +9246,7 @@
 サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して 浅野 翔; 雨宮 護; 佐野 幸恵 オペレーションズリサーチ/66(4)/pp.240(44)-245(49), 2021-04
 Fake news propagates differently from real news even at early stages of spreading Zhao Zilong; Zhao Jichang; Sano Yukie; Levy Orr; Takayasu... EPJ Data Science/9/p.7, 2020-04
 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii
-Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository
-Correlations and fluctuations in the word sets of collective emotions Sano Yukie Nonlinear Theory and Its Applications, IEICE/9(3)/pp.382-390, 2018-07 CiNii Tsukuba Repository
-Configuration model for correlation matrices preserving the node strength Masuda Naoki; Kojaku Sadamori; Sano Yukie Physical Review E/98(1)/p.012312, 2018-07 PubMed</t>
+Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9444,13 @@
 数理最適化
 金融工学
 機械学習
+Data collaboration analysis with orthonormal basis selection and alignment Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... Computers and Electrical Engineering/pp.1-28, 2026-06
+Mean–variance portfolio optimization with shrinkage estimation for recommender systems YANAGI Tomoya; YASUMOTO Yuta; TAKANO Yuichi Proceedings of the 15th International Conference on Operations Research and Enterprise Systems (ICORES 2026)/pp.265-272, 2026-03
+最適多分木による解釈可能な市場細分化 深谷 悠人; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 菊池 明飛; 武井 柊悟; 竹内 崇貴; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/71(2)/pp.61-69, 2026-02
+New solutions based on the generalized eigenvalue problem for the data collaboration analysis Kawakami Yuta; Takano Yuichi; Imakura Akira INFORMATION SCIENCES/723, 2026-01
+Subset Selection for Stratified Sampling in Online Controlled Experiments MOMOZU Haru; UEHARA Yuki; NISHIMURA Naoki; OHASHI Koy... Proceedings of the 22nd Pacific Rim International Conference on Artificial Intelligence (PRICAI 2025)/(Part II)/pp.600-613, 2025-11
 Robust personalized pricing under uncertainty of purchase probabilities Ikeda Shunnosuke; Nishimura Naoki; Sukegawa Noriyoshi; ... EURO Journal on Computational Optimization/13, 2025-08
+Missing Value Imputation via Mathematical Optimization with Instance-and-feature Neighborhoods Kawakami Yuta; Matsumoto Takumi; Takano Yuichi Journal of Information Processing/33(0)/pp.410-418, 2025
 Privacy-preserving recommender system using the data collaboration analysis for distributed datasets Yanagi Tomoya; Ikeda Shunnosuke; Sukegawa Noriyoshi; T... PLoS ONE/20(4), 2025-04
 最適モデル多分木による価格需要曲線の推定 菊池 明飛; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 武井 柊悟; 竹内 崇貴; 深谷 悠人; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/70(2)/pp.61-68, 2025-02
 Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times Ikuma Daiki; Ikeda Shunnosuke; Sukegawa Noriyoshi; Tak... Journal of Japan Industrial Management Association/75(4E)/pp.172-182, 2025-01
@@ -9421,12 +9469,6 @@
 Branch-and-bound algorithm for optimal sparse canonical correlation analysis Watanabe Akihisa; Tamura Ryuta; Takano Yuichi; Miyashi... EXPERT SYSTEMS WITH APPLICATIONS/217, 2023-05
 Dynamic portfolio selection with linear control policies for coherent risk minimization Takano Yuichi; Gotoh Jun-ya OPERATIONS RESEARCH PERSPECTIVES/10, 2023
 Linear control policies for online vehicle relocation in shared mobility systems Yoshida Yasuhiro; Takano Yuichi EXPERT SYSTEMS WITH APPLICATIONS/210, 2022-12
-出産前後の情報検索の分析：数理最適化による検索日の確率分布推定 岩永 二郎; 西村 直樹; 鮏川 矩義; 高野 祐一 人工知能学会論文誌/37(3)/pp.D-L74_1-11, 2022-05-01
-ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析) 河上 佳太; 工藤 晃太; 川瀬 元暉; 最首 大輝; 山田 直輝; 吉田 晏大; 岩永 二郎; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/67(2)/pp.73-80, 2022-02 CiNii
-Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization Kobayashi Ken; Takano Yuichi; Nakata Kazuhide JOURNAL OF GLOBAL OPTIMIZATION/81(2)/pp.493-528, 2021-10
-Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach Zhang Kai; Takano Yuichi; Wang Yuzhu; Yoshise Akiko IEEE Access/9/pp.79816-79828, 2021-06
-Sparse Poisson regression via mixed-integer optimization Saishu Hiroki; Kudo Kota; Takano Yuichi PloS one/16(4), 2021-04 PubMed
-時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析 河上 佳太; 西村 直樹; 白鳥 友風; 工藤 晃太; 松岡 雄大; 最首 大輝; 渡邊 彰久; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/66(4)/pp.246-254, 2021-04 CiNii
 データコラボレーション解析における統合関数の最適化 川上 雄大; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(6)/pp.297-302, 2024-06
 A Design Method of the Joint Venture Formation in EPC Projects Ishi Nobuaki; Takano Yuichi; Muraki Masaaki Intelligent Engineering and Management for Industry 4.0/pp.137-146, 2022-06
 形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待) 西村 直樹; 鮏川 矩義; 高野 祐一; 岩永 二郎 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/65(6)/pp.328-333, 2020-06 CiNii
@@ -9471,7 +9513,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Robust personalized pricing under uncertainty of purchase probabilities Ikeda Shunnosuke; Nishimura Naoki; Sukegawa Noriyoshi; ... EURO Journal on Computational Optimization/13, 2025-08 / Privacy-preserving recommender system using the data collaboration analysis for distributed datasets Yanagi Tomoya; Ikeda Shunnosuke; Sukegawa Noriyoshi; T... PLoS ONE/20(4), 2025-04 / 最適モデル多分木による価格需要曲線の推定 菊池 明飛; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 武井 柊悟; 竹内 崇貴; 深谷 悠人; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/70(2)/pp.61-68, 2025-02 / Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times Ikuma Daiki; Ikeda Shunnosuke; Sukegawa Noriyoshi; Tak... Journal of Japan Industrial Management Association/75(4E)/pp.172-182, 2025-01 / DC algorithm for estimation of sparse Gaussian graphical models Shiratori Tomokaze; Takano Yuichi PLOS ONE/19(12), 2024-12-23 / Robust Portfolio Optimization for Recommender Systems Considering Uncertainty of Estimated Statistics Yanagi Tomoya; Ikeda Shunnosuke; Takano Yuichi Proceedings of Pacific rim international conference on artificial intelligence/pp.429-440, 2024-11 / Fast Solution to the Fair Ranking Problem Using the Sinkhorn Algorithm Uehara Yuki; Ikeda Shunnosuke; Nishimura Naoki; Ohashi... Proceedings of Pacific rim international conference on artificial intelligence/pp.207-215, 2024-11 / Mixed-Integer Linear Optimization Formulations for Feature Subset Selection in Kernel SVM Classification Tamura Ryuta; Takano Yuichi; Miyashiro Ryuhei IEICE TRANSACTIONS ON FUNDAMENTALS OF ELECTRONICS COMMUNICATIONS AND COMPUTER SCIENCES/E107A(8)/pp.1151-1162, 2024-08 / Robust portfolio optimization model for electronic coupon allocation Uehara Yuki; Nishimura Naoki; Li Yilin; Yang Jie; Job... INFOR/Epub, 2024-07-29 / 混合整数最適化による相続工程の長期化リスク採点システム 椎名 萌; 高野 祐一; 宇佐美 朋香; 山西 康孝; 藤巻 米隆 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(4)/pp.219-224, 2024-04 / ECサイトにおける利用者属性データの欠損値補完 川上 雄大; 奈良岡 勇; 松本 拓見; 安元 優太; 朝倉 希美; 椎名 萌; 守屋 恵瑠萌; 鮏... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(2)/pp.82-88, 2024-02 / Prescriptive price optimization using optimal regression trees Ikeda Shunnosuke; Nishimura Naoki; Sukegawa Noriyoshi; ... OPERATIONS RESEARCH PERSPECTIVES/11, 2023-12 / 構造的正則化処方分析による旅行パックの価格最適化 池田 春之介; 朝倉 希美; 西村 直樹; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/68(9)/pp.485-490, 2023-09 / Predicting Online Item-Choice Behavior: A Shape-Restricted Regression Approach Nishimura Naoki; Sukegawa Noriyoshi; Takano Yuichi; Iw... ALGORITHMS/16(9), 2023-09 / Cardinality-constrained distributionally robust portfolio optimization Kobayashi Ken; Takano Yuichi; Nakata Kazuhide EUROPEAN JOURNAL OF OPERATIONAL RESEARCH/309(3)/pp.1173-1182, 2023-09 / Cutting-plane algorithm for estimation of sparse Cox proportional hazards models Saishu Hiroki; Kudo Kota; Takano Yuichi TOP/Epub, 2023-07-21 / Branch-and-bound algorithm for optimal sparse canonical correlation analysis Watanabe Akihisa; Tamura Ryuta; Takano Yuichi; Miyashi... EXPERT SYSTEMS WITH APPLICATIONS/217, 2023-05 / Dynamic portfolio selection with linear control policies for coherent risk minimization Takano Yuichi; Gotoh Jun-ya OPERATIONS RESEARCH PERSPECTIVES/10, 2023 / Linear control policies for online vehicle relocation in shared mobility systems Yoshida Yasuhiro; Takano Yuichi EXPERT SYSTEMS WITH APPLICATIONS/210, 2022-12 / 出産前後の情報検索の分析：数理最適化による検索日の確率分布推定 岩永 二郎; 西村 直樹; 鮏川 矩義; 高野 祐一 人工知能学会論文誌/37(3)/pp.D-L74_1-11, 2022-05-01 / ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析) 河上 佳太; 工藤 晃太; 川瀬 元暉; 最首 大輝; 山田 直輝; 吉田 晏大; 岩永 二郎; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/67(2)/pp.73-80, 2022-02 CiNii / Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization Kobayashi Ken; Takano Yuichi; Nakata Kazuhide JOURNAL OF GLOBAL OPTIMIZATION/81(2)/pp.493-528, 2021-10 / Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach Zhang Kai; Takano Yuichi; Wang Yuzhu; Yoshise Akiko IEEE Access/9/pp.79816-79828, 2021-06 / Sparse Poisson regression via mixed-integer optimization Saishu Hiroki; Kudo Kota; Takano Yuichi PloS one/16(4), 2021-04 PubMed / 時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析 河上 佳太; 西村 直樹; 白鳥 友風; 工藤 晃太; 松岡 雄大; 最首 大輝; 渡邊 彰久; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/66(4)/pp.246-254, 2021-04 CiNii / データコラボレーション解析における統合関数の最適化 川上 雄大; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(6)/pp.297-302, 2024-06 / A Design Method of the Joint Venture Formation in EPC Projects Ishi Nobuaki; Takano Yuichi; Muraki Masaaki Intelligent Engineering and Management for Industry 4.0/pp.137-146, 2022-06 / 形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待) 西村 直樹; 鮏川 矩義; 高野 祐一; 岩永 二郎 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/65(6)/pp.328-333, 2020-06 CiNii / サポートベクトルマシンとカーネル法 (特集 機械学習の手法と役割期待) 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/65(6)/pp.304-309, 2020-06 CiNii / Smoothness-constrained model for nonparametric item response theory Sato Toshiki; Takano Yuichi Information Science and Applied Mathematics/27/pp.1-20, 2020-03 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― 高橋 直希; 高野 祐一; 吉瀬 章子 オペレーションズ・リサーチ/68(8)/pp.453-459, 2019-08 / LDPC符号に対するタブー探索法に基づく勾配降下ビット反転復号法 高橋 良介; 高野 祐一 情報科学研究/39/pp.51-59, 2019-03 / A Resource Flow Based Multistage Dynamic Scheduling Method for the State-Dependent Work Ishii Nobuaki; Takano Yuichi; Muraki Masaaki Advances in Intelligent Systems and Computing/873/pp.300-316, 2019-01 / 数理最適化による学生のプロジェクト配属の決定 橋本 莉奈; 高野 祐一 専修ネットワーク＆インフォメーション/26/pp.27-31, 2018-03 / 整数最適化復号法の性能評価 柿沼 美希; 高野 祐一 情報科学研究/38/pp.17-24, 2018-03 / 多重共線性を考慮した回帰式の変数選択問題の定式化 田村 隆太; 小林 健; 高野 祐一; 宮代 隆平; 中田 和秀; 松井 知己 オペレーションズ・リサーチ：経営の科学/63(3)/pp.128-133, 2018-03 / A Simulation-Based Dynamic Scheduling Method in Project Cost Estimation Process Ishii Nobuaki; Takano Yuichi; Muraki Masaaki Advances in Intelligent Systems and Computing/676/pp.261-279, 2018-01 / キークレーン間干渉を考慮したコンテナ事前配列問題 宮崎 晃年; 鮏川 矩義; 高野 祐一; 水野 眞治 情報科学研究/37/pp.1-11, 2017-03 / 混合整数最適化による階層的変数選択を用いた店舗選択要因の分析 佐藤 俊樹; 高野 祐一; 中原 孝信 情報科学技術フォーラム講演論文集/15(2)/pp.23-30, 2016-09 / ZIMPL言語とSCIPによる数理最適化 高野 祐一 専修ネットワーク＆インフォメーション/24/pp.9-14, 2016-03 / 複数の販売チャネルでの購入を促進するための商品推薦手法 志甫 有真; 谷川 奈穂; 馬場 隆; 菊地 宏治; 片山翔太; 高野 祐一; 中田 和秀 情報科学研究/36/pp.1-10, 2016-03 / Mathematical Optimization Models for Nonparametric Item Response Theory Takano Yuichi; Tsunoda Shintaro; Muraki Masaaki Information Science and Applied Mathematics/23/pp.1-18, 2016-03 / 時系列モデルによる商品販促効果の分析 山根 智之; 菅原 光太郎; 西村 直樹; 小林 健; 吉田 佑輔; 高野 祐一; 中田 和秀 オペレーションズ・リサーチ：経営の科学/61(2)/pp.65-70, 2016-02 / 整数計画法による変数選択を用いた店舗選択モデル 佐藤 俊樹; 高野 祐一; 中原 孝信 情報科学技術フォーラム講演論文集/14(2)/pp.53-58, 2015-08 CiNii / 競争入札戦略と決定理論モデル 高野 祐一 オペレーションズ・リサーチ：経営の科学/60(7)/pp.369-373, 2015-07 / アドネットワークにおけるバナー広告入札戦略決定フレームワークの有効性の検証 高野 祐一; 和田 悠太郎; 生田目 崇; 村木 正昭 情報科学研究/35/pp.1-17, 2015-03 / 確率計画法の理論と応用 高野 祐一 専修ネットワーク＆インフォメーション/23/pp.14-21, 2015-03 / ECサイトの商品特性を考慮した2次元確率表による購買予測 西村 直樹; 鮏川矩義; 高野 祐一; 岩永 二郎; 水野 眞治 オペレーションズ・リサーチ：経営の科学/60(2)/pp.69-74, 2015-02 / A Heuristic Bidding Price Decision Algorithm Based on Cost Estimation Accuracy under Limited Engineering Man-Hours in EPC Projects Ishii Nobuaki; Takano Yuichi; Muraki Masaaki Advances in Intelligent Systems and Computing/319/pp.101-118, 2015-01 / 混合整数2次錐計画法による回帰式の変数選択 宮代 隆平; 高野 祐一 オペレーションズ・リサーチ：経営の科学/59(12)/pp.732-738, 2014-12</t>
+          <t>Data collaboration analysis with orthonormal basis selection and alignment Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... Computers and Electrical Engineering/pp.1-28, 2026-06 / Mean–variance portfolio optimization with shrinkage estimation for recommender systems YANAGI Tomoya; YASUMOTO Yuta; TAKANO Yuichi Proceedings of the 15th International Conference on Operations Research and Enterprise Systems (ICORES 2026)/pp.265-272, 2026-03 / 最適多分木による解釈可能な市場細分化 深谷 悠人; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 菊池 明飛; 武井 柊悟; 竹内 崇貴; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/71(2)/pp.61-69, 2026-02 / New solutions based on the generalized eigenvalue problem for the data collaboration analysis Kawakami Yuta; Takano Yuichi; Imakura Akira INFORMATION SCIENCES/723, 2026-01 / Subset Selection for Stratified Sampling in Online Controlled Experiments MOMOZU Haru; UEHARA Yuki; NISHIMURA Naoki; OHASHI Koy... Proceedings of the 22nd Pacific Rim International Conference on Artificial Intelligence (PRICAI 2025)/(Part II)/pp.600-613, 2025-11 / Robust personalized pricing under uncertainty of purchase probabilities Ikeda Shunnosuke; Nishimura Naoki; Sukegawa Noriyoshi; ... EURO Journal on Computational Optimization/13, 2025-08 / Missing Value Imputation via Mathematical Optimization with Instance-and-feature Neighborhoods Kawakami Yuta; Matsumoto Takumi; Takano Yuichi Journal of Information Processing/33(0)/pp.410-418, 2025 / Privacy-preserving recommender system using the data collaboration analysis for distributed datasets Yanagi Tomoya; Ikeda Shunnosuke; Sukegawa Noriyoshi; T... PLoS ONE/20(4), 2025-04 / 最適モデル多分木による価格需要曲線の推定 菊池 明飛; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 武井 柊悟; 竹内 崇貴; 深谷 悠人; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/70(2)/pp.61-68, 2025-02 / Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times Ikuma Daiki; Ikeda Shunnosuke; Sukegawa Noriyoshi; Tak... Journal of Japan Industrial Management Association/75(4E)/pp.172-182, 2025-01 / DC algorithm for estimation of sparse Gaussian graphical models Shiratori Tomokaze; Takano Yuichi PLOS ONE/19(12), 2024-12-23 / Robust Portfolio Optimization for Recommender Systems Considering Uncertainty of Estimated Statistics Yanagi Tomoya; Ikeda Shunnosuke; Takano Yuichi Proceedings of Pacific rim international conference on artificial intelligence/pp.429-440, 2024-11 / Fast Solution to the Fair Ranking Problem Using the Sinkhorn Algorithm Uehara Yuki; Ikeda Shunnosuke; Nishimura Naoki; Ohashi... Proceedings of Pacific rim international conference on artificial intelligence/pp.207-215, 2024-11 / Mixed-Integer Linear Optimization Formulations for Feature Subset Selection in Kernel SVM Classification Tamura Ryuta; Takano Yuichi; Miyashiro Ryuhei IEICE TRANSACTIONS ON FUNDAMENTALS OF ELECTRONICS COMMUNICATIONS AND COMPUTER SCIENCES/E107A(8)/pp.1151-1162, 2024-08 / Robust portfolio optimization model for electronic coupon allocation Uehara Yuki; Nishimura Naoki; Li Yilin; Yang Jie; Job... INFOR/Epub, 2024-07-29 / 混合整数最適化による相続工程の長期化リスク採点システム 椎名 萌; 高野 祐一; 宇佐美 朋香; 山西 康孝; 藤巻 米隆 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(4)/pp.219-224, 2024-04 / ECサイトにおける利用者属性データの欠損値補完 川上 雄大; 奈良岡 勇; 松本 拓見; 安元 優太; 朝倉 希美; 椎名 萌; 守屋 恵瑠萌; 鮏... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(2)/pp.82-88, 2024-02 / Prescriptive price optimization using optimal regression trees Ikeda Shunnosuke; Nishimura Naoki; Sukegawa Noriyoshi; ... OPERATIONS RESEARCH PERSPECTIVES/11, 2023-12 / 構造的正則化処方分析による旅行パックの価格最適化 池田 春之介; 朝倉 希美; 西村 直樹; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/68(9)/pp.485-490, 2023-09 / Predicting Online Item-Choice Behavior: A Shape-Restricted Regression Approach Nishimura Naoki; Sukegawa Noriyoshi; Takano Yuichi; Iw... ALGORITHMS/16(9), 2023-09 / Cardinality-constrained distributionally robust portfolio optimization Kobayashi Ken; Takano Yuichi; Nakata Kazuhide EUROPEAN JOURNAL OF OPERATIONAL RESEARCH/309(3)/pp.1173-1182, 2023-09 / Cutting-plane algorithm for estimation of sparse Cox proportional hazards models Saishu Hiroki; Kudo Kota; Takano Yuichi TOP/Epub, 2023-07-21 / Branch-and-bound algorithm for optimal sparse canonical correlation analysis Watanabe Akihisa; Tamura Ryuta; Takano Yuichi; Miyashi... EXPERT SYSTEMS WITH APPLICATIONS/217, 2023-05 / Dynamic portfolio selection with linear control policies for coherent risk minimization Takano Yuichi; Gotoh Jun-ya OPERATIONS RESEARCH PERSPECTIVES/10, 2023 / Linear control policies for online vehicle relocation in shared mobility systems Yoshida Yasuhiro; Takano Yuichi EXPERT SYSTEMS WITH APPLICATIONS/210, 2022-12 / データコラボレーション解析における統合関数の最適化 川上 雄大; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(6)/pp.297-302, 2024-06 / A Design Method of the Joint Venture Formation in EPC Projects Ishi Nobuaki; Takano Yuichi; Muraki Masaaki Intelligent Engineering and Management for Industry 4.0/pp.137-146, 2022-06 / 形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待) 西村 直樹; 鮏川 矩義; 高野 祐一; 岩永 二郎 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/65(6)/pp.328-333, 2020-06 CiNii / サポートベクトルマシンとカーネル法 (特集 機械学習の手法と役割期待) 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/65(6)/pp.304-309, 2020-06 CiNii / Smoothness-constrained model for nonparametric item response theory Sato Toshiki; Takano Yuichi Information Science and Applied Mathematics/27/pp.1-20, 2020-03 / ラストマイル・モビリティシェアリング ―シナリオモデルに基づく運用計画案の作成― 高橋 直希; 高野 祐一; 吉瀬 章子 オペレーションズ・リサーチ/68(8)/pp.453-459, 2019-08 / LDPC符号に対するタブー探索法に基づく勾配降下ビット反転復号法 高橋 良介; 高野 祐一 情報科学研究/39/pp.51-59, 2019-03 / A Resource Flow Based Multistage Dynamic Scheduling Method for the State-Dependent Work Ishii Nobuaki; Takano Yuichi; Muraki Masaaki Advances in Intelligent Systems and Computing/873/pp.300-316, 2019-01 / 数理最適化による学生のプロジェクト配属の決定 橋本 莉奈; 高野 祐一 専修ネットワーク＆インフォメーション/26/pp.27-31, 2018-03 / 整数最適化復号法の性能評価 柿沼 美希; 高野 祐一 情報科学研究/38/pp.17-24, 2018-03 / 多重共線性を考慮した回帰式の変数選択問題の定式化 田村 隆太; 小林 健; 高野 祐一; 宮代 隆平; 中田 和秀; 松井 知己 オペレーションズ・リサーチ：経営の科学/63(3)/pp.128-133, 2018-03 / A Simulation-Based Dynamic Scheduling Method in Project Cost Estimation Process Ishii Nobuaki; Takano Yuichi; Muraki Masaaki Advances in Intelligent Systems and Computing/676/pp.261-279, 2018-01 / キークレーン間干渉を考慮したコンテナ事前配列問題 宮崎 晃年; 鮏川 矩義; 高野 祐一; 水野 眞治 情報科学研究/37/pp.1-11, 2017-03 / 混合整数最適化による階層的変数選択を用いた店舗選択要因の分析 佐藤 俊樹; 高野 祐一; 中原 孝信 情報科学技術フォーラム講演論文集/15(2)/pp.23-30, 2016-09 / ZIMPL言語とSCIPによる数理最適化 高野 祐一 専修ネットワーク＆インフォメーション/24/pp.9-14, 2016-03 / 複数の販売チャネルでの購入を促進するための商品推薦手法 志甫 有真; 谷川 奈穂; 馬場 隆; 菊地 宏治; 片山翔太; 高野 祐一; 中田 和秀 情報科学研究/36/pp.1-10, 2016-03 / Mathematical Optimization Models for Nonparametric Item Response Theory Takano Yuichi; Tsunoda Shintaro; Muraki Masaaki Information Science and Applied Mathematics/23/pp.1-18, 2016-03 / 時系列モデルによる商品販促効果の分析 山根 智之; 菅原 光太郎; 西村 直樹; 小林 健; 吉田 佑輔; 高野 祐一; 中田 和秀 オペレーションズ・リサーチ：経営の科学/61(2)/pp.65-70, 2016-02 / 整数計画法による変数選択を用いた店舗選択モデル 佐藤 俊樹; 高野 祐一; 中原 孝信 情報科学技術フォーラム講演論文集/14(2)/pp.53-58, 2015-08 CiNii / 競争入札戦略と決定理論モデル 高野 祐一 オペレーションズ・リサーチ：経営の科学/60(7)/pp.369-373, 2015-07 / アドネットワークにおけるバナー広告入札戦略決定フレームワークの有効性の検証 高野 祐一; 和田 悠太郎; 生田目 崇; 村木 正昭 情報科学研究/35/pp.1-17, 2015-03 / 確率計画法の理論と応用 高野 祐一 専修ネットワーク＆インフォメーション/23/pp.14-21, 2015-03 / ECサイトの商品特性を考慮した2次元確率表による購買予測 西村 直樹; 鮏川矩義; 高野 祐一; 岩永 二郎; 水野 眞治 オペレーションズ・リサーチ：経営の科学/60(2)/pp.69-74, 2015-02 / A Heuristic Bidding Price Decision Algorithm Based on Cost Estimation Accuracy under Limited Engineering Man-Hours in EPC Projects Ishii Nobuaki; Takano Yuichi; Muraki Masaaki Advances in Intelligent Systems and Computing/319/pp.101-118, 2015-01 / 混合整数2次錐計画法による回帰式の変数選択 宮代 隆平; 高野 祐一 オペレーションズ・リサーチ：経営の科学/59(12)/pp.732-738, 2014-12</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -9543,7 +9585,13 @@
 ノンパラメトリック推定に基づくテスト理論モデルの研究
 カーネル法と制御ポリシーを用いた中長期的投資戦略最適化
 取引コストを考慮した多期間ポートフォリオの最適化
+Data collaboration analysis with orthonormal basis selection and alignment Nosaka Keiyu; Suetake Yamato; Takano Yuichi; YOSHISE ... Computers and Electrical Engineering/pp.1-28, 2026-06
+Mean–variance portfolio optimization with shrinkage estimation for recommender systems YANAGI Tomoya; YASUMOTO Yuta; TAKANO Yuichi Proceedings of the 15th International Conference on Operations Research and Enterprise Systems (ICORES 2026)/pp.265-272, 2026-03
+最適多分木による解釈可能な市場細分化 深谷 悠人; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 菊池 明飛; 武井 柊悟; 竹内 崇貴; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/71(2)/pp.61-69, 2026-02
+New solutions based on the generalized eigenvalue problem for the data collaboration analysis Kawakami Yuta; Takano Yuichi; Imakura Akira INFORMATION SCIENCES/723, 2026-01
+Subset Selection for Stratified Sampling in Online Controlled Experiments MOMOZU Haru; UEHARA Yuki; NISHIMURA Naoki; OHASHI Koy... Proceedings of the 22nd Pacific Rim International Conference on Artificial Intelligence (PRICAI 2025)/(Part II)/pp.600-613, 2025-11
 Robust personalized pricing under uncertainty of purchase probabilities Ikeda Shunnosuke; Nishimura Naoki; Sukegawa Noriyoshi; ... EURO Journal on Computational Optimization/13, 2025-08
+Missing Value Imputation via Mathematical Optimization with Instance-and-feature Neighborhoods Kawakami Yuta; Matsumoto Takumi; Takano Yuichi Journal of Information Processing/33(0)/pp.410-418, 2025
 Privacy-preserving recommender system using the data collaboration analysis for distributed datasets Yanagi Tomoya; Ikeda Shunnosuke; Sukegawa Noriyoshi; T... PLoS ONE/20(4), 2025-04
 最適モデル多分木による価格需要曲線の推定 菊池 明飛; 伊熊 大貴; 板山 咲穂; 上原 祐輝; 武井 柊悟; 竹内 崇貴; 深谷 悠人; 柳... オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/70(2)/pp.61-68, 2025-02
 Container Pre-marshalling Problem Minimizing CV@R under Uncertainty of Ship Arrival Times Ikuma Daiki; Ikeda Shunnosuke; Sukegawa Noriyoshi; Tak... Journal of Japan Industrial Management Association/75(4E)/pp.172-182, 2025-01
@@ -9562,12 +9610,6 @@
 Branch-and-bound algorithm for optimal sparse canonical correlation analysis Watanabe Akihisa; Tamura Ryuta; Takano Yuichi; Miyashi... EXPERT SYSTEMS WITH APPLICATIONS/217, 2023-05
 Dynamic portfolio selection with linear control policies for coherent risk minimization Takano Yuichi; Gotoh Jun-ya OPERATIONS RESEARCH PERSPECTIVES/10, 2023
 Linear control policies for online vehicle relocation in shared mobility systems Yoshida Yasuhiro; Takano Yuichi EXPERT SYSTEMS WITH APPLICATIONS/210, 2022-12
-出産前後の情報検索の分析：数理最適化による検索日の確率分布推定 岩永 二郎; 西村 直樹; 鮏川 矩義; 高野 祐一 人工知能学会論文誌/37(3)/pp.D-L74_1-11, 2022-05-01
-ランキング手法を用いたフィットネスクラブの分析 (特集 データ解析コンペティション : 大規模アンケートデータの分析) 河上 佳太; 工藤 晃太; 川瀬 元暉; 最首 大輝; 山田 直輝; 吉田 晏大; 岩永 二郎; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/67(2)/pp.73-80, 2022-02 CiNii
-Bilevel cutting-plane algorithm for cardinality-constrained mean-CVaR portfolio optimization Kobayashi Ken; Takano Yuichi; Nakata Kazuhide JOURNAL OF GLOBAL OPTIMIZATION/81(2)/pp.493-528, 2021-10
-Optimizing the strategic decisions for one-way station-based carsharing systems: A mean-CVaR approach Zhang Kai; Takano Yuichi; Wang Yuzhu; Yoshise Akiko IEEE Access/9/pp.79816-79828, 2021-06
-Sparse Poisson regression via mixed-integer optimization Saishu Hiroki; Kudo Kota; Takano Yuichi PloS one/16(4), 2021-04 PubMed
-時間付加グラフのベクトル表現を用いたタクシー軌跡データの解析 河上 佳太; 西村 直樹; 白鳥 友風; 工藤 晃太; 松岡 雄大; 最首 大輝; 渡邊 彰久; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/66(4)/pp.246-254, 2021-04 CiNii
 データコラボレーション解析における統合関数の最適化 川上 雄大; 高野 祐一 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/69(6)/pp.297-302, 2024-06
 A Design Method of the Joint Venture Formation in EPC Projects Ishi Nobuaki; Takano Yuichi; Muraki Masaaki Intelligent Engineering and Management for Industry 4.0/pp.137-146, 2022-06
 形状制約モデルによる顧客の商品選択行動の予測 (特集 機械学習の手法と役割期待) 西村 直樹; 鮏川 矩義; 高野 祐一; 岩永 二郎 オペレーションズ・リサーチ = Communications of the Operations Research Society of Japan : 経営の科学/65(6)/pp.328-333, 2020-06 CiNii
@@ -9629,13 +9671,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>KPI工学教育研究の推進
+          <t>サービスLAD:人間とAIエージェントの協働によるサービス設計基盤の構築
+仮想3PLにおける在庫移動最適化
+LMS利用行動ログと学習指標に関する調査
+健康にやさしいまちづくりのための環境整備に係る実証事業
 包摂的コミュニティプラットフォームの構築
-健康にやさしいまちづくりのための環境整備に係る実証事業
-統合型ヘルスケアシステムの構築
-文書生成AIサービス工学に関する研究
-文書生成AIの企業内利活用における最適化の研究
-包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究
+中小企業価値評価の実践的研究の発展
+デジタルガバメント／スマートシティ連携モデル研究の 防災分野への発展
+経営における組織・人事ソリューションの基盤研究
+KPI工学教育研究の推進
 会計学
 ウェブ情報学・サービス情報学
 社会システム工学・安全システム
@@ -9646,36 +9690,36 @@
 サービス工学
 ソーシャル・データサイエンス
 社会工学
+Single-Round Clustered Federated Learning via Data Collaboration Analysis for Non-IID Data SUGAWARA Sota; KAWAMATA Yuji; TOYODA Akihiro; NAKAYAMA... Proceedings of International Joint Conferences on Artificial Intelligence (IJCAI-ECAI2026), 2026-08
+Differential Effects of Soft and Hard Hindrance Demands on Job Satisfaction: An Analysis of Interactions with Job Resources Using Latent Moderated Structural Equations TAMURA Aoba; TAMARI Yuki; TAKAZONO Tadasuke; OKADA Yu... Proceedings of The Association for Psychological Science (APS), 2026-05
+Covariance-Based Structural Equation Modeling in Small-Sample Settings with p&gt;n HASEGAWA Hiroki; TAMURA Aoba; OKADA Yukihiko arXiv, 2026-04
+Re-presenting Physiological Synchrony as Non-Interpretive Haptic Cues in Dyadic Dialogue Higashiyama Yuki; Wang Zhaolong; Alhalabi Hajar; Okada... Proceedings of the Augmented Humans International Conference 2026 (AHs '26), 2026-03
 Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment TOYODA Akihiro; KAWAMATA Yuji; NAKAYAMA Tomoru; IMAKUR... Scientific Reports/16(1), 2026-01
+Estimation of conditional average treatment effects on distributed confidential data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; IMAKURA A... Expert Systems with Applications/296(C)/p.129066, 2026-01
+Interaction Tensor SHAP HASEGAWA Hiroki; OKADA Yukihiko arXiv, 2025-12
+アカウンティング・インフォマティクスの可能性：ディテクター機能と会計情報 岡田 幸彦 會計/208(1)/pp.57-68, 2025-12
 Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients Ashitomi Y.; Kawamura H.; Kubo E.; Kosugi K. H.; Kosh... ANNALS OF ONCOLOGY/36(4), 2025-12
 Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach Mashiko Sota; Kawamata Yuji; Nakayama Tomoru; Sakurai ... SCIENTIFIC REPORTS/15(1), 2025-11-26
-Estimation of conditional average treatment effects on distributed confidential data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; IMAKURA A... Expert Systems with Applications/296(C)/p.129066, 2026-01
+A Reliable Decision Support Framework for SME Default Prediction Using Uncertainty-Aware Bayesian GEV Regression TERADA Kaito; ABE Keiji; TAKEDA Toshihiko; KAWAMATA Y... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.2268-2273, 2025-11
+DC-CP: Data Collaboration Conformal Prediction from Model Training to Conformal Prediction in Single-Round Communication While Preserving Privacy NAKAYAMA Tomoru; KAWAMATA Yuji; IMAKURA Akira; OKADA ... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.1474-1479, 2025-11
+Cash-Flow Prediction Model Using Graph Neural Networks and Spatiotemporal Information from Double-Entry Bookkeeping Data MOTAI Ryoki; KAMEBUCHI Masato; WATANABE Sora; MATSUMOT... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.2425-2433, 2025-11
+A new type of federated clustering: A non-model-sharing approach KAWAMATA Yuji; KAMIJO Kaoru; KIHIRA Masateru; TOYODA ... arXiv, 2025-06
+A Robust and Non-Iterative Tensor Decomposition Method with Automatic Thresholding HASEGAWA Hiroki; OKADA Yukihiko arXiv, 2025-05
+Designing Undetectable Morphing Speech: How Morph Rate and Discrete/Continuous Changes Influences Change Detection Thresholds Okano Hiiro; Wakatsuki Naoto; Okada Yukihiko; ZEMPO K... Proceedings of the Augmented Humans International Conference 2025/pp.409-412, 2025-05
 Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support Kawamura Homura; Miura Tomofumi; Maeda Yuka; Okada Yu... IEEE ACCESS/13/pp.99490-99508, 2025-05
 Data collaboration for causal inference from limited medical testing and medication data NAKAYAMA Tomoru; KAWAMATA Yuji; TOYODA Akihiro; IMAKUR... Scientific Reports/15(1), 2025-03
 Generating Synthetic Journal-Entry Data Using Variational Autoencoder MOTAI Ryoki; MASHIKO Sota; KAWAMATA Yuji; SHIN Ryota; ... Intelligent Systems in Accounting, Finance and Management/32(1), 2025-03
-Anomaly Detection in Double-entry Bookkeeping Data by Federated Learning System with Non-model Sharing Approach MASHIKO Sota; KAWAMATA Yuji; NAKAYAMA Tomoru; SAKURAI ... arXiv, 2025-01
 Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data MOTAI Ryoki; MASHIKO Sota; KAMEBUCHI Masato; WATANABE ... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2360-2364, 2024-12
 An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises ANDO Renon; KAWAMATA Yuji; TAKEDA Toshihiko; OKADA Yu... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2269-2274, 2024-12
 Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data HASEGAWA Hiroki; YATA Kazuyoshi; OKADA Yukihiko; KUNIM... Prceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.34-43, 2024-12
 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19
 pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis Kawamura Homura; Wang Zhaolong; Harima Kotone; Yamanis... Companion of the 2024 ACM International Joint Conference on Pervasive and Ubiquitous Computing (UbiComp '24), 2024-10-07
-会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 山矢 和輝; 罇 涼稀; 岡田 幸彦 帝京経済学研究/58(1)/pp.7-23, 2024-10
-Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data Hasegawa Hiroki; Kawamura Homura; Shin Ryota; Yata Ka... Proceedings of the 6th International Conference on Statistics: Theory and Applications, 2024-8
-分散機密データを想定した 処置効果の推定手法の開発 河又裕士; 岡田 幸彦 オペレーションズ・リサーチ, 2024-06
-英文学術雑誌における近年の簿記研究 中村亮介; 罇 涼稀; 松下真也; 岡田 幸彦 簿記研究/7(1)/pp.1-14, 2024-06
-Collaborative causal inference on distributed data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; Imakura A... EXPERT SYSTEMS WITH APPLICATIONS/244, 2024-06
-Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach Kawamata Yuji; Motai Ryoki; Okada Yukihiko; Imakura A... arXiv, 2024-02
-Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation Tanabe Kai; Sugawara Yuki; Sakurai Eiichi; Motomura Y... PloS one/19(2), 2024-02 PubMed
-Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data Mudahemuka Eugene; 宮城昌竜; 秦涼太; 金子直樹; 岡田幸彦; Yamamoto Kyosuke Sensors/24(4), 2024-02
-Knowledge sharing among coaches: expert power and social cognitive theory perspectives Funasaki Kohei; Inoue Yuhei; Takahashi Yoshio; Shirai ... EUROPEAN SPORT MANAGEMENT QUARTERLY/Epub/pp.1-20, 2024-01
-Positive effect of proactive personality on customer orientation in service context Takashima Ryota; Ueda Natsuki; Hashimoto Tatsuya; Okad... INTERNATIONAL JOURNAL OF PSYCHOLOGY/58(1)/pp.818-818, 2023-12
-Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data Yanagiura Takeshi; Yano Shiho; Kihira Masateru; Okada ... Journal of Educational Data Mining/15(3)/pp.1-25, 2023-12
-Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis Sugawara Yuki; Sakurai Eiichi; Motomura Yoichi; Okada ... Proceedings of 2023 IEEE International Conference on Big Data (BigData)/pp.2726-2734, 2023-12</t>
+会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 山矢 和輝; 罇 涼稀; 岡田 幸彦 帝京経済学研究/58(1)/pp.7-23, 2024-10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KPI工学教育研究の推進 / 包摂的コミュニティプラットフォームの構築 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 統合型ヘルスケアシステムの構築 / 文書生成AIサービス工学に関する研究 / 文書生成AIの企業内利活用における最適化の研究 / 包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究</t>
+          <t>サービスLAD:人間とAIエージェントの協働によるサービス設計基盤の構築 / 仮想3PLにおける在庫移動最適化 / LMS利用行動ログと学習指標に関する調査 / 健康にやさしいまちづくりのための環境整備に係る実証事業 / 包摂的コミュニティプラットフォームの構築 / 中小企業価値評価の実践的研究の発展 / デジタルガバメント／スマートシティ連携モデル研究の 防災分野への発展 / 経営における組織・人事ソリューションの基盤研究 / KPI工学教育研究の推進</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9690,7 +9734,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment TOYODA Akihiro; KAWAMATA Yuji; NAKAYAMA Tomoru; IMAKUR... Scientific Reports/16(1), 2026-01 / Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients Ashitomi Y.; Kawamura H.; Kubo E.; Kosugi K. H.; Kosh... ANNALS OF ONCOLOGY/36(4), 2025-12 / Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach Mashiko Sota; Kawamata Yuji; Nakayama Tomoru; Sakurai ... SCIENTIFIC REPORTS/15(1), 2025-11-26 / Estimation of conditional average treatment effects on distributed confidential data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; IMAKURA A... Expert Systems with Applications/296(C)/p.129066, 2026-01 / Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support Kawamura Homura; Miura Tomofumi; Maeda Yuka; Okada Yu... IEEE ACCESS/13/pp.99490-99508, 2025-05 / Data collaboration for causal inference from limited medical testing and medication data NAKAYAMA Tomoru; KAWAMATA Yuji; TOYODA Akihiro; IMAKUR... Scientific Reports/15(1), 2025-03 / Generating Synthetic Journal-Entry Data Using Variational Autoencoder MOTAI Ryoki; MASHIKO Sota; KAWAMATA Yuji; SHIN Ryota; ... Intelligent Systems in Accounting, Finance and Management/32(1), 2025-03 / Anomaly Detection in Double-entry Bookkeeping Data by Federated Learning System with Non-model Sharing Approach MASHIKO Sota; KAWAMATA Yuji; NAKAYAMA Tomoru; SAKURAI ... arXiv, 2025-01 / Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data MOTAI Ryoki; MASHIKO Sota; KAMEBUCHI Masato; WATANABE ... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2360-2364, 2024-12 / An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises ANDO Renon; KAWAMATA Yuji; TAKEDA Toshihiko; OKADA Yu... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2269-2274, 2024-12 / Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data HASEGAWA Hiroki; YATA Kazuyoshi; OKADA Yukihiko; KUNIM... Prceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.34-43, 2024-12 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19 / pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis Kawamura Homura; Wang Zhaolong; Harima Kotone; Yamanis... Companion of the 2024 ACM International Joint Conference on Pervasive and Ubiquitous Computing (UbiComp '24), 2024-10-07 / 会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 山矢 和輝; 罇 涼稀; 岡田 幸彦 帝京経済学研究/58(1)/pp.7-23, 2024-10 / Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data Hasegawa Hiroki; Kawamura Homura; Shin Ryota; Yata Ka... Proceedings of the 6th International Conference on Statistics: Theory and Applications, 2024-8 / 分散機密データを想定した 処置効果の推定手法の開発 河又裕士; 岡田 幸彦 オペレーションズ・リサーチ, 2024-06 / 英文学術雑誌における近年の簿記研究 中村亮介; 罇 涼稀; 松下真也; 岡田 幸彦 簿記研究/7(1)/pp.1-14, 2024-06 / Collaborative causal inference on distributed data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; Imakura A... EXPERT SYSTEMS WITH APPLICATIONS/244, 2024-06 / Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach Kawamata Yuji; Motai Ryoki; Okada Yukihiko; Imakura A... arXiv, 2024-02 / Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation Tanabe Kai; Sugawara Yuki; Sakurai Eiichi; Motomura Y... PloS one/19(2), 2024-02 PubMed / Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data Mudahemuka Eugene; 宮城昌竜; 秦涼太; 金子直樹; 岡田幸彦; Yamamoto Kyosuke Sensors/24(4), 2024-02 / Knowledge sharing among coaches: expert power and social cognitive theory perspectives Funasaki Kohei; Inoue Yuhei; Takahashi Yoshio; Shirai ... EUROPEAN SPORT MANAGEMENT QUARTERLY/Epub/pp.1-20, 2024-01 / Positive effect of proactive personality on customer orientation in service context Takashima Ryota; Ueda Natsuki; Hashimoto Tatsuya; Okad... INTERNATIONAL JOURNAL OF PSYCHOLOGY/58(1)/pp.818-818, 2023-12 / Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data Yanagiura Takeshi; Yano Shiho; Kihira Masateru; Okada ... Journal of Educational Data Mining/15(3)/pp.1-25, 2023-12 / Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis Sugawara Yuki; Sakurai Eiichi; Motomura Yoichi; Okada ... Proceedings of 2023 IEEE International Conference on Big Data (BigData)/pp.2726-2734, 2023-12</t>
+          <t>Single-Round Clustered Federated Learning via Data Collaboration Analysis for Non-IID Data SUGAWARA Sota; KAWAMATA Yuji; TOYODA Akihiro; NAKAYAMA... Proceedings of International Joint Conferences on Artificial Intelligence (IJCAI-ECAI2026), 2026-08 / Differential Effects of Soft and Hard Hindrance Demands on Job Satisfaction: An Analysis of Interactions with Job Resources Using Latent Moderated Structural Equations TAMURA Aoba; TAMARI Yuki; TAKAZONO Tadasuke; OKADA Yu... Proceedings of The Association for Psychological Science (APS), 2026-05 / Covariance-Based Structural Equation Modeling in Small-Sample Settings with p&gt;n HASEGAWA Hiroki; TAMURA Aoba; OKADA Yukihiko arXiv, 2026-04 / Re-presenting Physiological Synchrony as Non-Interpretive Haptic Cues in Dyadic Dialogue Higashiyama Yuki; Wang Zhaolong; Alhalabi Hajar; Okada... Proceedings of the Augmented Humans International Conference 2026 (AHs '26), 2026-03 / Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment TOYODA Akihiro; KAWAMATA Yuji; NAKAYAMA Tomoru; IMAKUR... Scientific Reports/16(1), 2026-01 / Estimation of conditional average treatment effects on distributed confidential data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; IMAKURA A... Expert Systems with Applications/296(C)/p.129066, 2026-01 / Interaction Tensor SHAP HASEGAWA Hiroki; OKADA Yukihiko arXiv, 2025-12 / アカウンティング・インフォマティクスの可能性：ディテクター機能と会計情報 岡田 幸彦 會計/208(1)/pp.57-68, 2025-12 / Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients Ashitomi Y.; Kawamura H.; Kubo E.; Kosugi K. H.; Kosh... ANNALS OF ONCOLOGY/36(4), 2025-12 / Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach Mashiko Sota; Kawamata Yuji; Nakayama Tomoru; Sakurai ... SCIENTIFIC REPORTS/15(1), 2025-11-26 / A Reliable Decision Support Framework for SME Default Prediction Using Uncertainty-Aware Bayesian GEV Regression TERADA Kaito; ABE Keiji; TAKEDA Toshihiko; KAWAMATA Y... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.2268-2273, 2025-11 / DC-CP: Data Collaboration Conformal Prediction from Model Training to Conformal Prediction in Single-Round Communication While Preserving Privacy NAKAYAMA Tomoru; KAWAMATA Yuji; IMAKURA Akira; OKADA ... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.1474-1479, 2025-11 / Cash-Flow Prediction Model Using Graph Neural Networks and Spatiotemporal Information from Double-Entry Bookkeeping Data MOTAI Ryoki; KAMEBUCHI Masato; WATANABE Sora; MATSUMOT... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.2425-2433, 2025-11 / A new type of federated clustering: A non-model-sharing approach KAWAMATA Yuji; KAMIJO Kaoru; KIHIRA Masateru; TOYODA ... arXiv, 2025-06 / A Robust and Non-Iterative Tensor Decomposition Method with Automatic Thresholding HASEGAWA Hiroki; OKADA Yukihiko arXiv, 2025-05 / Designing Undetectable Morphing Speech: How Morph Rate and Discrete/Continuous Changes Influences Change Detection Thresholds Okano Hiiro; Wakatsuki Naoto; Okada Yukihiko; ZEMPO K... Proceedings of the Augmented Humans International Conference 2025/pp.409-412, 2025-05 / Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support Kawamura Homura; Miura Tomofumi; Maeda Yuka; Okada Yu... IEEE ACCESS/13/pp.99490-99508, 2025-05 / Data collaboration for causal inference from limited medical testing and medication data NAKAYAMA Tomoru; KAWAMATA Yuji; TOYODA Akihiro; IMAKUR... Scientific Reports/15(1), 2025-03 / Generating Synthetic Journal-Entry Data Using Variational Autoencoder MOTAI Ryoki; MASHIKO Sota; KAWAMATA Yuji; SHIN Ryota; ... Intelligent Systems in Accounting, Finance and Management/32(1), 2025-03 / Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data MOTAI Ryoki; MASHIKO Sota; KAMEBUCHI Masato; WATANABE ... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2360-2364, 2024-12 / An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises ANDO Renon; KAWAMATA Yuji; TAKEDA Toshihiko; OKADA Yu... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2269-2274, 2024-12 / Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data HASEGAWA Hiroki; YATA Kazuyoshi; OKADA Yukihiko; KUNIM... Prceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.34-43, 2024-12 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19 / pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis Kawamura Homura; Wang Zhaolong; Harima Kotone; Yamanis... Companion of the 2024 ACM International Joint Conference on Pervasive and Ubiquitous Computing (UbiComp '24), 2024-10-07 / 会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 山矢 和輝; 罇 涼稀; 岡田 幸彦 帝京経済学研究/58(1)/pp.7-23, 2024-10</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -9700,12 +9744,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>会計学 ; ウェブ情報学・サービス情報学 ; 社会システム工学・安全システム ; 経営学 ; 商学 ; 社会政策・福祉 ; オペレーションズリサーチ ; 政策評価・計量分析 ; 会計・ファイナンス ; 医療・ヘルスデータ ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>会計学 ; ウェブ情報学・サービス情報学 ; 社会システム工学・安全システム ; 経営学 ; 商学 ; 社会政策・福祉 ; オペレーションズリサーチ ; 災害・防災研究 ; 政策評価・計量分析 ; 会計・ファイナンス ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
+          <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -9722,9 +9766,9 @@
 社会工学
 社会政策・福祉
 オペレーションズリサーチ
+災害・防災研究
 政策評価・計量分析
 会計・ファイナンス
-医療・ヘルスデータ
 環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
@@ -9737,6 +9781,9 @@
 数理最適化
 組合せ最適化
 計画・スケジューリング
+災害社会学
+防災政策
+リスク評価
 政策評価
 計量経済学
 統計的因果推論
@@ -9745,10 +9792,6 @@
 財務会計
 管理会計
 会計情報システム
-医療データ分析
-生体情報解析
-ヘルスデータサイエンス
-統計解析
 環境政策
 エネルギーシステム
 脱炭素分析
@@ -9790,38 +9833,40 @@
 能動的先手行動の形成プロセスについての縦断的研究
 標準年限卒業予測における大学間転移学習の研究
 NavigatorIIIのパイロット企業における実証実験
+サービスLAD:人間とAIエージェントの協働によるサービス設計基盤の構築
+仮想3PLにおける在庫移動最適化
+LMS利用行動ログと学習指標に関する調査
+健康にやさしいまちづくりのための環境整備に係る実証事業
+包摂的コミュニティプラットフォームの構築
+中小企業価値評価の実践的研究の発展
+デジタルガバメント／スマートシティ連携モデル研究の 防災分野への発展
+経営における組織・人事ソリューションの基盤研究
 KPI工学教育研究の推進
-包摂的コミュニティプラットフォームの構築
-健康にやさしいまちづくりのための環境整備に係る実証事業
-統合型ヘルスケアシステムの構築
-文書生成AIサービス工学に関する研究
-文書生成AIの企業内利活用における最適化の研究
-包摂的コミュニティ創生のためのデータ駆動型数理基盤の研究
+Single-Round Clustered Federated Learning via Data Collaboration Analysis for Non-IID Data SUGAWARA Sota; KAWAMATA Yuji; TOYODA Akihiro; NAKAYAMA... Proceedings of International Joint Conferences on Artificial Intelligence (IJCAI-ECAI2026), 2026-08
+Differential Effects of Soft and Hard Hindrance Demands on Job Satisfaction: An Analysis of Interactions with Job Resources Using Latent Moderated Structural Equations TAMURA Aoba; TAMARI Yuki; TAKAZONO Tadasuke; OKADA Yu... Proceedings of The Association for Psychological Science (APS), 2026-05
+Covariance-Based Structural Equation Modeling in Small-Sample Settings with p&gt;n HASEGAWA Hiroki; TAMURA Aoba; OKADA Yukihiko arXiv, 2026-04
+Re-presenting Physiological Synchrony as Non-Interpretive Haptic Cues in Dyadic Dialogue Higashiyama Yuki; Wang Zhaolong; Alhalabi Hajar; Okada... Proceedings of the Augmented Humans International Conference 2026 (AHs '26), 2026-03
 Estimating covariate-balanced survival curve in distributed data environment using data collaboration quasi-experiment TOYODA Akihiro; KAWAMATA Yuji; NAKAYAMA Tomoru; IMAKUR... Scientific Reports/16(1), 2026-01
+Estimation of conditional average treatment effects on distributed confidential data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; IMAKURA A... Expert Systems with Applications/296(C)/p.129066, 2026-01
+Interaction Tensor SHAP HASEGAWA Hiroki; OKADA Yukihiko arXiv, 2025-12
+アカウンティング・インフォマティクスの可能性：ディテクター機能と会計情報 岡田 幸彦 會計/208(1)/pp.57-68, 2025-12
 Exploring the mechanisms underlying the effectiveness of a communication skills training program in interactions with cancer patients Ashitomi Y.; Kawamura H.; Kubo E.; Kosugi K. H.; Kosh... ANNALS OF ONCOLOGY/36(4), 2025-12
 Anomaly detection in double-entry bookkeeping data by federated learning system with non-model sharing approach Mashiko Sota; Kawamata Yuji; Nakayama Tomoru; Sakurai ... SCIENTIFIC REPORTS/15(1), 2025-11-26
-Estimation of conditional average treatment effects on distributed confidential data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; IMAKURA A... Expert Systems with Applications/296(C)/p.129066, 2026-01
+A Reliable Decision Support Framework for SME Default Prediction Using Uncertainty-Aware Bayesian GEV Regression TERADA Kaito; ABE Keiji; TAKEDA Toshihiko; KAWAMATA Y... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.2268-2273, 2025-11
+DC-CP: Data Collaboration Conformal Prediction from Model Training to Conformal Prediction in Single-Round Communication While Preserving Privacy NAKAYAMA Tomoru; KAWAMATA Yuji; IMAKURA Akira; OKADA ... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.1474-1479, 2025-11
+Cash-Flow Prediction Model Using Graph Neural Networks and Spatiotemporal Information from Double-Entry Bookkeeping Data MOTAI Ryoki; KAMEBUCHI Masato; WATANABE Sora; MATSUMOT... Prceedings of 2025 IEEE International Conference on Big Data (BigData)/pp.2425-2433, 2025-11
+A new type of federated clustering: A non-model-sharing approach KAWAMATA Yuji; KAMIJO Kaoru; KIHIRA Masateru; TOYODA ... arXiv, 2025-06
+A Robust and Non-Iterative Tensor Decomposition Method with Automatic Thresholding HASEGAWA Hiroki; OKADA Yukihiko arXiv, 2025-05
+Designing Undetectable Morphing Speech: How Morph Rate and Discrete/Continuous Changes Influences Change Detection Thresholds Okano Hiiro; Wakatsuki Naoto; Okada Yukihiko; ZEMPO K... Proceedings of the Augmented Humans International Conference 2025/pp.409-412, 2025-05
 Framework for Emotion Recognition Using Cross-Modal Transformers With Non-Contact Multimodal Signals Aiming Clinical Service Support Kawamura Homura; Miura Tomofumi; Maeda Yuka; Okada Yu... IEEE ACCESS/13/pp.99490-99508, 2025-05
 Data collaboration for causal inference from limited medical testing and medication data NAKAYAMA Tomoru; KAWAMATA Yuji; TOYODA Akihiro; IMAKUR... Scientific Reports/15(1), 2025-03
 Generating Synthetic Journal-Entry Data Using Variational Autoencoder MOTAI Ryoki; MASHIKO Sota; KAWAMATA Yuji; SHIN Ryota; ... Intelligent Systems in Accounting, Finance and Management/32(1), 2025-03
-Anomaly Detection in Double-entry Bookkeeping Data by Federated Learning System with Non-model Sharing Approach MASHIKO Sota; KAWAMATA Yuji; NAKAYAMA Tomoru; SAKURAI ... arXiv, 2025-01
 Practical Experiment of Predicting Cash Flows with LSTM and Double-entry Bookkeeping Data MOTAI Ryoki; MASHIKO Sota; KAMEBUCHI Masato; WATANABE ... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2360-2364, 2024-12
 An explainable framework based on counterfactual explanations for multi-class financial distress prediction of small and medium enterprises ANDO Renon; KAWAMATA Yuji; TAKEDA Toshihiko; OKADA Yu... Proceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.2269-2274, 2024-12
 Proposing a Low-Rank Approximation Method with Mathematical Guarantees for High-Dimensional Tensor Data HASEGAWA Hiroki; YATA Kazuyoshi; OKADA Yukihiko; KUNIM... Prceedings of 2024 IEEE International Conference on Big Data (BigData)/pp.34-43, 2024-12
 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19
 pSCOUTER: Time-Series Emotion Classification Using Contactless Measured Multimodal Biosignals in Medical Diagnosis Kawamura Homura; Wang Zhaolong; Harima Kotone; Yamanis... Companion of the 2024 ACM International Joint Conference on Pervasive and Ubiquitous Computing (UbiComp '24), 2024-10-07
-会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 山矢 和輝; 罇 涼稀; 岡田 幸彦 帝京経済学研究/58(1)/pp.7-23, 2024-10
-Noise Reduced Common PCA for High-Dimensional, Low-Sample Size Multi-View Data Hasegawa Hiroki; Kawamura Homura; Shin Ryota; Yata Ka... Proceedings of the 6th International Conference on Statistics: Theory and Applications, 2024-8
-分散機密データを想定した 処置効果の推定手法の開発 河又裕士; 岡田 幸彦 オペレーションズ・リサーチ, 2024-06
-英文学術雑誌における近年の簿記研究 中村亮介; 罇 涼稀; 松下真也; 岡田 幸彦 簿記研究/7(1)/pp.1-14, 2024-06
-Collaborative causal inference on distributed data Kawamata Yuji; Motai Ryoki; Okada Yukihiko; Imakura A... EXPERT SYSTEMS WITH APPLICATIONS/244, 2024-06
-Estimation of conditional average treatment effects on distributed data: A privacy-preserving approach Kawamata Yuji; Motai Ryoki; Okada Yukihiko; Imakura A... arXiv, 2024-02
-Impact of subjective well-being on physical frailty in middle-aged and elderly Japanese with high social isolation Tanabe Kai; Sugawara Yuki; Sakurai Eiichi; Motomura Y... PloS one/19(2), 2024-02 PubMed
-Estimating Bridge Natural Frequencies Based on Modal Analysis of Vehicle–Bridge Synchronized Vibration Data Mudahemuka Eugene; 宮城昌竜; 秦涼太; 金子直樹; 岡田幸彦; Yamamoto Kyosuke Sensors/24(4), 2024-02
-Knowledge sharing among coaches: expert power and social cognitive theory perspectives Funasaki Kohei; Inoue Yuhei; Takahashi Yoshio; Shirai ... EUROPEAN SPORT MANAGEMENT QUARTERLY/Epub/pp.1-20, 2024-01
-Positive effect of proactive personality on customer orientation in service context Takashima Ryota; Ueda Natsuki; Hashimoto Tatsuya; Okad... INTERNATIONAL JOURNAL OF PSYCHOLOGY/58(1)/pp.818-818, 2023-12
-Examining Algorithmic Fairness for First-Term College Grade Prediction Models Relying on Pre-matriculation Data Yanagiura Takeshi; Yano Shiho; Kihira Masateru; Okada ... Journal of Educational Data Mining/15(3)/pp.1-25, 2023-12
-Method for creating privacy-preserving information using Probabilistic Latent Semantic Analysis Sugawara Yuki; Sakurai Eiichi; Motomura Yoichi; Okada ... Proceedings of 2023 IEEE International Conference on Big Data (BigData)/pp.2726-2734, 2023-12</t>
+会計情報システムとマネジメント・コントロールとの関係性に関する実証的研究の潮流と将来の発展方向 山矢 和輝; 罇 涼稀; 岡田 幸彦 帝京経済学研究/58(1)/pp.7-23, 2024-10</t>
         </is>
       </c>
     </row>
@@ -9990,7 +10035,9 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析
+          <t>金融資産市場・リスク状況と社会的ジレンマ下での人間とAIの意思決定
+グリーン投資の意思決定メカニズムの実験的検証
+人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析
 新規投資家の継続的な参入が価格形成・価格変動に与える影響
 ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響
 信用スコア社会に対応可能な評判管理システムの設計
@@ -9998,10 +10045,17 @@
 市場参加者の価格予測の異質性と市場の振る舞いの関係について
 情報の非対称性と多様な期待形成がもたらす金融市場への影響とその安定化政策について
 国家の規模とガバナンスの学際的分析
-情報コストゼロ社会における過剰懲罰とリスク軽減のための社会制度設計
-新しい肺移植制度の構築と評価：ドナー交換移植の可能性
 社会システム工学・安全システム
 社会的ジレンマ、資産市場実験
+ジレンマ状況における表情計測に基づく人の協力行動の分析. 小菅雷太朗; 秋山 英三; 山本仁志; 栗原聡 社会システムと情報技術研究ウィーク（WSSIT2026）, 2026
+Effects of a “Topic Diversification System” facilitating diverse topic exposure on topic interest and social media engage behavior. Nagura Takuya; AKIYAMA Eizo In Proceedings of the 2025 IEEE International Conference on Big Data (IEEE BigData 2025), 2025
+Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. Inaba Masaaki; AKIYAMA Eizo PLOS Complex Systems/2(4), 2025
+Emergence of echo chambers in social media communication involving multiple topics. Nagura Takuya; AKIYAMA Eizo Information, Communication &amp; Society/28(6)/pp. 1099- 1120, 2025
+Partner selection biases induced by resource inequality. Umetani Ryohei; Yamamoto Hitoshi; AKIYAMA Eizo Social Sciences &amp; Humanities Open/12, 2025
+Influence of agent social and network segregation on fake news diffusion. Kitagawa Yuta; Akiyama Eizo In Proceedings of the 2025 IEEE International Conference on Big Data (IEEE BigData 2025), 2025-12
+発話量と発話内容分析に基づく分断された集団間のコミュニケーション円滑化システムの提案 筒井律稀; 小菅雷太朗; 秋山 英三; 山本仁志; 荒牧大樹; 伊藤千輝; 栗原聡 2025年度人工知能学会全国大会（第39回）論文集, 2025/5
+Effect of Network Homophily and Partisanship on Social Media to "Oil Spill" Polarizations Nagura Takuya; Akiyama Eizo JASSS-THE JOURNAL OF ARTIFICIAL SOCIETIES AND SOCIAL SIMULATION/29(1), 2026-01-31
+Evolution of cooperation among migrating resource-oriented agents under environmental variability Inaba Masaaki; Akiyama Eizo CHAOS SOLITONS &amp; FRACTALS/202(2), 2026-01
 検索連動型広告における循環的な入札額変動の発生機構の解明 河又 裕士; 张 晓泉; 秋山 英三 経営情報学会 全国研究発表大会要旨集/201906/pp.117-120, 2019
 ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07
 Bubbles in Asset Markets and the Heterogeneity of Beliefs. AKIYAMA Eizo; Funaki Yukihiko; Ishikawa Ryuichiro; Lah... Journal of Economic Behavior and Organization/236, 2025-08
@@ -10017,21 +10071,12 @@
 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ 秋山 英三; 石橋 裕 第66回土木計画学研究発表会・講演集, 2022-11
 Individuals reciprocate negative actions revealing negative upstream reciprocity Umetani Ryohei; Yamamoto Hitoshi; Goto Akira; Okada I... PLOS ONE/18(7), 2023-07-05
 SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. 名倉 卓弥; 秋山 英三 人工知能学会論文誌/38(4)/pp.B-N11_1-B-N11_9, 2023
-Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement Masaaki Inaba; 秋山 英三 SCIENTIFIC REPORTS/13(1), 2023-06-17
-Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim Ishibashi Yutaka; Akiyama Eizo 2022 IEEE International Conference on Big Data (Big Data), 2022-12
-パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 栗栖慶太; 秋山英三 シミュレーション＆ゲーミング/33(1)/pp.11-22, 2023
-群淘汰状況下における罰則・報酬の進化 秋山 英三 信学技報/122(421)/pp.36-41, 2023-03
-Self-organized Speculation Game for the spontaneous emergence of financial stylized facts Katahira K.; Chen Y.; Akiyama Eizo Physica A/582, 2021-11
-情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ 秋山 英三; 謝凡 人工知能学会論文, 2021-10
-時間制約を導入したゴミ箱モデル 秋山 英三; 石田雄大 人工知能学会論文, 2021-10
-Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment Akiyama Eizo; Okada I.; Yamamoto H.; Toriumi F. Scientific Reports/11(1), 2021-04
-協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 米納 弘渡; 秋山英三 JAWS2014, 2014-10
-A quantitative easing experiment Penalver Adrian; Hanaki Nobuyuki; Akiyama Eizo; Funaki... Journal of economic dynamics &amp; control/119, 2020-10 PubMed</t>
+Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement Masaaki Inaba; 秋山 英三 SCIENTIFIC REPORTS/13(1), 2023-06-17</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析 / 新規投資家の継続的な参入が価格形成・価格変動に与える影響 / ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響 / 信用スコア社会に対応可能な評判管理システムの設計 / 験財消費のための情報収集行動とその支援情報提供システム / 市場参加者の価格予測の異質性と市場の振る舞いの関係について / 情報の非対称性と多様な期待形成がもたらす金融市場への影響とその安定化政策について / 国家の規模とガバナンスの学際的分析 / 情報コストゼロ社会における過剰懲罰とリスク軽減のための社会制度設計 / 新しい肺移植制度の構築と評価：ドナー交換移植の可能性</t>
+          <t>金融資産市場・リスク状況と社会的ジレンマ下での人間とAIの意思決定 / グリーン投資の意思決定メカニズムの実験的検証 / 人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析 / 新規投資家の継続的な参入が価格形成・価格変動に与える影響 / ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響 / 信用スコア社会に対応可能な評判管理システムの設計 / 験財消費のための情報収集行動とその支援情報提供システム / 市場参加者の価格予測の異質性と市場の振る舞いの関係について / 情報の非対称性と多様な期待形成がもたらす金融市場への影響とその安定化政策について / 国家の規模とガバナンスの学際的分析</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10046,7 +10091,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>検索連動型広告における循環的な入札額変動の発生機構の解明 河又 裕士; 张 晓泉; 秋山 英三 経営情報学会 全国研究発表大会要旨集/201906/pp.117-120, 2019 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07 / Bubbles in Asset Markets and the Heterogeneity of Beliefs. AKIYAMA Eizo; Funaki Yukihiko; Ishikawa Ryuichiro; Lah... Journal of Economic Behavior and Organization/236, 2025-08 / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 小菅雷太朗; 若林直希; 山本仁志; 秋山 英三; 栗原聡 行動変容と社会システム/10, 2024 / 進化ゲーム理論の進化 — マルチエージェントシミュレーション，実験室実験と，LLM の行動経済学— 秋山 英三 人工知能/39(3)/pp.323-329, 2024 / 発話量と発話内容に基づく集団間のコミュニケーション円滑化システムの提案 筒井律稀; 小菅雷太朗; 秋山 英三; 山本仁志; 荒牧大樹; 伊藤千輝; 栗原 聡 行動変容と社会システム/11, 2024 / ソーシャルメディア上のアジェンダ設定がエコーチェンバーの発生に与える影響について 名倉 卓弥; 秋山 英三 人工知能学会論文誌/39(6)/pp.p. AG24-A_1-8, 2024-11-1 / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. Inaba Masaaki; Akiyama Eizo PLOS Complex Systems/2(4), 2025-04 / Emergence of echo chambers in social media communication involving multiple topics Nagura Takuya; Akiyama Eizo INFORMATION COMMUNICATION &amp; SOCIETY/Epub/pp.1099-1120, 2025-01-28 / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 小菅雷太郎; 若林直希; 山本仁志; 栗原聡; 秋山 英三 行動変容と社会システム/10, 2024-3 / 進化ゲーム理論の進化：マルチエージェントシミュレーション, 実験室実験と，LLMの行動経済学 秋山 英三 人工知能学会論文誌/39(3)/pp.323-330, 2024-5 / 重みが動的なネットワークにおいてネットワーク構造が協力の進化に与える影響 栗栖 慶太; 秋山 英三 情報処理学会論文誌/65(1)/pp.61-68, 2024-1 / 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ 秋山 英三; 石橋 裕 第66回土木計画学研究発表会・講演集, 2022-11 / Individuals reciprocate negative actions revealing negative upstream reciprocity Umetani Ryohei; Yamamoto Hitoshi; Goto Akira; Okada I... PLOS ONE/18(7), 2023-07-05 / SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. 名倉 卓弥; 秋山 英三 人工知能学会論文誌/38(4)/pp.B-N11_1-B-N11_9, 2023 / Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement Masaaki Inaba; 秋山 英三 SCIENTIFIC REPORTS/13(1), 2023-06-17 / Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim Ishibashi Yutaka; Akiyama Eizo 2022 IEEE International Conference on Big Data (Big Data), 2022-12 / パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 栗栖慶太; 秋山英三 シミュレーション＆ゲーミング/33(1)/pp.11-22, 2023 / 群淘汰状況下における罰則・報酬の進化 秋山 英三 信学技報/122(421)/pp.36-41, 2023-03 / Self-organized Speculation Game for the spontaneous emergence of financial stylized facts Katahira K.; Chen Y.; Akiyama Eizo Physica A/582, 2021-11 / 情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ 秋山 英三; 謝凡 人工知能学会論文, 2021-10 / 時間制約を導入したゴミ箱モデル 秋山 英三; 石田雄大 人工知能学会論文, 2021-10 / Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment Akiyama Eizo; Okada I.; Yamamoto H.; Toriumi F. Scientific Reports/11(1), 2021-04 / 協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 米納 弘渡; 秋山英三 JAWS2014, 2014-10 / A quantitative easing experiment Penalver Adrian; Hanaki Nobuyuki; Akiyama Eizo; Funaki... Journal of economic dynamics &amp; control/119, 2020-10 PubMed</t>
+          <t>ジレンマ状況における表情計測に基づく人の協力行動の分析. 小菅雷太朗; 秋山 英三; 山本仁志; 栗原聡 社会システムと情報技術研究ウィーク（WSSIT2026）, 2026 / Effects of a “Topic Diversification System” facilitating diverse topic exposure on topic interest and social media engage behavior. Nagura Takuya; AKIYAMA Eizo In Proceedings of the 2025 IEEE International Conference on Big Data (IEEE BigData 2025), 2025 / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. Inaba Masaaki; AKIYAMA Eizo PLOS Complex Systems/2(4), 2025 / Emergence of echo chambers in social media communication involving multiple topics. Nagura Takuya; AKIYAMA Eizo Information, Communication &amp; Society/28(6)/pp. 1099- 1120, 2025 / Partner selection biases induced by resource inequality. Umetani Ryohei; Yamamoto Hitoshi; AKIYAMA Eizo Social Sciences &amp; Humanities Open/12, 2025 / Influence of agent social and network segregation on fake news diffusion. Kitagawa Yuta; Akiyama Eizo In Proceedings of the 2025 IEEE International Conference on Big Data (IEEE BigData 2025), 2025-12 / 発話量と発話内容分析に基づく分断された集団間のコミュニケーション円滑化システムの提案 筒井律稀; 小菅雷太朗; 秋山 英三; 山本仁志; 荒牧大樹; 伊藤千輝; 栗原聡 2025年度人工知能学会全国大会（第39回）論文集, 2025/5 / Effect of Network Homophily and Partisanship on Social Media to "Oil Spill" Polarizations Nagura Takuya; Akiyama Eizo JASSS-THE JOURNAL OF ARTIFICIAL SOCIETIES AND SOCIAL SIMULATION/29(1), 2026-01-31 / Evolution of cooperation among migrating resource-oriented agents under environmental variability Inaba Masaaki; Akiyama Eizo CHAOS SOLITONS &amp; FRACTALS/202(2), 2026-01 / 検索連動型広告における循環的な入札額変動の発生機構の解明 河又 裕士; 张 晓泉; 秋山 英三 経営情報学会 全国研究発表大会要旨集/201906/pp.117-120, 2019 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07 / Bubbles in Asset Markets and the Heterogeneity of Beliefs. AKIYAMA Eizo; Funaki Yukihiko; Ishikawa Ryuichiro; Lah... Journal of Economic Behavior and Organization/236, 2025-08 / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 小菅雷太朗; 若林直希; 山本仁志; 秋山 英三; 栗原聡 行動変容と社会システム/10, 2024 / 進化ゲーム理論の進化 — マルチエージェントシミュレーション，実験室実験と，LLM の行動経済学— 秋山 英三 人工知能/39(3)/pp.323-329, 2024 / 発話量と発話内容に基づく集団間のコミュニケーション円滑化システムの提案 筒井律稀; 小菅雷太朗; 秋山 英三; 山本仁志; 荒牧大樹; 伊藤千輝; 栗原 聡 行動変容と社会システム/11, 2024 / ソーシャルメディア上のアジェンダ設定がエコーチェンバーの発生に与える影響について 名倉 卓弥; 秋山 英三 人工知能学会論文誌/39(6)/pp.p. AG24-A_1-8, 2024-11-1 / Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. Inaba Masaaki; Akiyama Eizo PLOS Complex Systems/2(4), 2025-04 / Emergence of echo chambers in social media communication involving multiple topics Nagura Takuya; Akiyama Eizo INFORMATION COMMUNICATION &amp; SOCIETY/Epub/pp.1099-1120, 2025-01-28 / 繰り返し囚人のジレンマゲームにおける表情センシングを活用した人の感情と行動の分析 小菅雷太郎; 若林直希; 山本仁志; 栗原聡; 秋山 英三 行動変容と社会システム/10, 2024-3 / 進化ゲーム理論の進化：マルチエージェントシミュレーション, 実験室実験と，LLMの行動経済学 秋山 英三 人工知能学会論文誌/39(3)/pp.323-330, 2024-5 / 重みが動的なネットワークにおいてネットワーク構造が協力の進化に与える影響 栗栖 慶太; 秋山 英三 情報処理学会論文誌/65(1)/pp.61-68, 2024-1 / 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ 秋山 英三; 石橋 裕 第66回土木計画学研究発表会・講演集, 2022-11 / Individuals reciprocate negative actions revealing negative upstream reciprocity Umetani Ryohei; Yamamoto Hitoshi; Goto Akira; Okada I... PLOS ONE/18(7), 2023-07-05 / SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. 名倉 卓弥; 秋山 英三 人工知能学会論文誌/38(4)/pp.B-N11_1-B-N11_9, 2023 / Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement Masaaki Inaba; 秋山 英三 SCIENTIFIC REPORTS/13(1), 2023-06-17</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -10056,12 +10101,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>社会システム工学・安全システム ; 保険・金融行動 ; 意思決定分析 ; マッチング理論・ゲーム理論 ; 政策評価・計量分析 ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
+          <t>社会システム工学・安全システム ; 保険・金融行動 ; 意思決定分析 ; マッチング理論・ゲーム理論 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -10072,6 +10117,7 @@
 意思決定分析
 マッチング理論・ゲーム理論
 政策評価・計量分析
+環境・エネルギー
 公共政策・社会工学
 経済・ファイナンス
 数理最適化・OR
@@ -10090,7 +10136,11 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -10107,6 +10157,8 @@
 歩行者ラウンドアバウトによる整流効果-駅構内の混雑緩和-
 投機的リスク下でのピア効果がリスク態度に与える影響
 懲罰に関する社会規範が間接互恵の進化に与える影響について:シミュレーションによるアプローチ
+金融資産市場・リスク状況と社会的ジレンマ下での人間とAIの意思決定
+グリーン投資の意思決定メカニズムの実験的検証
 人間とAIの共生社会を支える意思決定プロセスの行動経済学的分析
 新規投資家の継続的な参入が価格形成・価格変動に与える影響
 ゲーム理論・意思決定理論への理性制約・準理性制約の導入とその影響
@@ -10115,8 +10167,15 @@
 市場参加者の価格予測の異質性と市場の振る舞いの関係について
 情報の非対称性と多様な期待形成がもたらす金融市場への影響とその安定化政策について
 国家の規模とガバナンスの学際的分析
-情報コストゼロ社会における過剰懲罰とリスク軽減のための社会制度設計
-新しい肺移植制度の構築と評価：ドナー交換移植の可能性
+ジレンマ状況における表情計測に基づく人の協力行動の分析. 小菅雷太朗; 秋山 英三; 山本仁志; 栗原聡 社会システムと情報技術研究ウィーク（WSSIT2026）, 2026
+Effects of a “Topic Diversification System” facilitating diverse topic exposure on topic interest and social media engage behavior. Nagura Takuya; AKIYAMA Eizo In Proceedings of the 2025 IEEE International Conference on Big Data (IEEE BigData 2025), 2025
+Environmental variability promotes the evolution of cooperation among geographically dispersed groups on dynamic networks. Inaba Masaaki; AKIYAMA Eizo PLOS Complex Systems/2(4), 2025
+Emergence of echo chambers in social media communication involving multiple topics. Nagura Takuya; AKIYAMA Eizo Information, Communication &amp; Society/28(6)/pp. 1099- 1120, 2025
+Partner selection biases induced by resource inequality. Umetani Ryohei; Yamamoto Hitoshi; AKIYAMA Eizo Social Sciences &amp; Humanities Open/12, 2025
+Influence of agent social and network segregation on fake news diffusion. Kitagawa Yuta; Akiyama Eizo In Proceedings of the 2025 IEEE International Conference on Big Data (IEEE BigData 2025), 2025-12
+発話量と発話内容分析に基づく分断された集団間のコミュニケーション円滑化システムの提案 筒井律稀; 小菅雷太朗; 秋山 英三; 山本仁志; 荒牧大樹; 伊藤千輝; 栗原聡 2025年度人工知能学会全国大会（第39回）論文集, 2025/5
+Effect of Network Homophily and Partisanship on Social Media to "Oil Spill" Polarizations Nagura Takuya; Akiyama Eizo JASSS-THE JOURNAL OF ARTIFICIAL SOCIETIES AND SOCIAL SIMULATION/29(1), 2026-01-31
+Evolution of cooperation among migrating resource-oriented agents under environmental variability Inaba Masaaki; Akiyama Eizo CHAOS SOLITONS &amp; FRACTALS/202(2), 2026-01
 検索連動型広告における循環的な入札額変動の発生機構の解明 河又 裕士; 张 晓泉; 秋山 英三 経営情報学会 全国研究発表大会要旨集/201906/pp.117-120, 2019
 ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07
 Bubbles in Asset Markets and the Heterogeneity of Beliefs. AKIYAMA Eizo; Funaki Yukihiko; Ishikawa Ryuichiro; Lah... Journal of Economic Behavior and Organization/236, 2025-08
@@ -10132,16 +10191,7 @@
 自動運転配車サービス（SAVs）の導入が東京都中心部に与える影響 ～マルチエージェント交通シミュレータ“MATSim”を用いて～ 秋山 英三; 石橋 裕 第66回土木計画学研究発表会・講演集, 2022-11
 Individuals reciprocate negative actions revealing negative upstream reciprocity Umetani Ryohei; Yamamoto Hitoshi; Goto Akira; Okada I... PLOS ONE/18(7), 2023-07-05
 SNS におけるトピックス数の増加が意見の分極化とエコーチェンバーに与える影響. 名倉 卓弥; 秋山 英三 人工知能学会論文誌/38(4)/pp.B-N11_1-B-N11_9, 2023
-Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement Masaaki Inaba; 秋山 英三 SCIENTIFIC REPORTS/13(1), 2023-06-17
-Predicting the Impact of Shared Autonomous Vehicles on Tokyo Transportation Using MATSim Ishibashi Yutaka; Akiyama Eizo 2022 IEEE International Conference on Big Data (Big Data), 2022-12
-パンデミックにおける感染者数と経済ダメージの抑制に最適な人的移動制限率の検討 栗栖慶太; 秋山英三 シミュレーション＆ゲーミング/33(1)/pp.11-22, 2023
-群淘汰状況下における罰則・報酬の進化 秋山 英三 信学技報/122(421)/pp.36-41, 2023-03
-Self-organized Speculation Game for the spontaneous emergence of financial stylized facts Katahira K.; Chen Y.; Akiyama Eizo Physica A/582, 2021-11
-情報入手時間の差異がある市場の振る舞いに値幅制限が与える影響：人工市場によるアプローチ 秋山 英三; 謝凡 人工知能学会論文, 2021-10
-時間制約を導入したゴミ箱モデル 秋山 英三; 石田雄大 人工知能学会論文, 2021-10
-Cooperation in spatial public good games depends on the locality effects of game, adaptation, and punishment Akiyama Eizo; Okada I.; Yamamoto H.; Toriumi F. Scientific Reports/11(1), 2021-04
-協力者が裏切者とのリンクを切断する動的ネットワーク上での協力とネットワーク構造の進化 米納 弘渡; 秋山英三 JAWS2014, 2014-10
-A quantitative easing experiment Penalver Adrian; Hanaki Nobuyuki; Akiyama Eizo; Funaki... Journal of economic dynamics &amp; control/119, 2020-10 PubMed</t>
+Evolution of cooperation in multiplex networks through asymmetry between interaction and replacement Masaaki Inaba; 秋山 英三 SCIENTIFIC REPORTS/13(1), 2023-06-17</t>
         </is>
       </c>
     </row>
@@ -10194,12 +10244,19 @@
 建築・都市計画史
 地中海都市
 ヘレニズム基盤
+イスラーム的都市形成
+西アジア
+中東・北アフリカ
 歴史文化保全
 国際協力
-中東・北アフリカ
-Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026
+Modernist Master Planning and Resident Adaptation in Abuja, Nigeria: a Historical Geography of Imposed Spatial Order,1976-2024 AKINKUNMI Priscilla; MATSUBARA Kosuke Planning Perspectives, 2026-04
+Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026-04
 フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― 戸田 理香子; 松原 康介 日本建築学会計画系論文集/91(840)/pp.351-362, 2026-02
 吉田正春使節団が見た19世紀テヘラン都市改造 松原 康介 都市計画論文集/60(3)/pp.532-539, 2025-10
+Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08
+Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08
+Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08
+The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08
 ジスカール・デスタン政権下のパリ歩行者空間整備 家城悠紀; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.415-416, 2025-08
 1960 年アガディール地震とその震災復興都市計画に関する研究 根岸美空; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.427-428, 2025-08
 フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 三重野馨; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.207-208, 2025-08
@@ -10208,20 +10265,15 @@
 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 瀨古希; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.541-542, 2025-08
 フェス 積み重なる寄進が形成した迷宮都市 松原 康介 建築知識/2025(7)/pp.84-85, 2025-6
 ガルダイア 丘の上の城塞とオアシス渓谷の集落 松原 康介 建築知識/2025(7)/pp.82-83, 2025-6
-Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08
-The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08
-Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08
-Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08
 カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- 渡邊 智也; 松原 康介 都市計画論文集/59(3)/pp.892-899, 2024-10
+The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10
 Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris FURUICHI Manako; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-15-6-1-D-15-6-4, 2024-09
 Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille YOSHIDA Yuno; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-5-5-1-D-5-5-4, 2024-09
-The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10
 アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 和田 夏音; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.321-322, 2024-08
+商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08
+19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08
 カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08
-カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08
-19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08
-商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08
-ビルマ王都マンダレーの城内および城外市街地の空間構造に関する研究 山田 耕治; 松原 康介 2023年度 日本建築学会大会［近畿］学術講演梗概集/pp.29-30, 2023-09</t>
+カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10236,12 +10288,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>建築・都市計画史 / 地中海都市 / ヘレニズム基盤 / 歴史文化保全 / 国際協力 / 中東・北アフリカ</t>
+          <t>建築・都市計画史 / 地中海都市 / ヘレニズム基盤 / イスラーム的都市形成 / 西アジア / 中東・北アフリカ / 歴史文化保全 / 国際協力</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026 / フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― 戸田 理香子; 松原 康介 日本建築学会計画系論文集/91(840)/pp.351-362, 2026-02 / 吉田正春使節団が見た19世紀テヘラン都市改造 松原 康介 都市計画論文集/60(3)/pp.532-539, 2025-10 / ジスカール・デスタン政権下のパリ歩行者空間整備 家城悠紀; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.415-416, 2025-08 / 1960 年アガディール地震とその震災復興都市計画に関する研究 根岸美空; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.427-428, 2025-08 / フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 三重野馨; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.207-208, 2025-08 / フェルナン・プイヨンのベルカステル村修復に関する研究 ─城と村の一体性に着目して─ 古市麻菜子; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.205-206, 2025-08 / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス 吉田悠乃; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.203-204, 2025-08 / 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 瀨古希; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.541-542, 2025-08 / フェス 積み重なる寄進が形成した迷宮都市 松原 康介 建築知識/2025(7)/pp.84-85, 2025-6 / ガルダイア 丘の上の城塞とオアシス渓谷の集落 松原 康介 建築知識/2025(7)/pp.82-83, 2025-6 / Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08 / The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08 / Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08 / Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08 / カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- 渡邊 智也; 松原 康介 都市計画論文集/59(3)/pp.892-899, 2024-10 / Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris FURUICHI Manako; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-15-6-1-D-15-6-4, 2024-09 / Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille YOSHIDA Yuno; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-5-5-1-D-5-5-4, 2024-09 / The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10 / アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 和田 夏音; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.321-322, 2024-08 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08 / 19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08 / 商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08 / ビルマ王都マンダレーの城内および城外市街地の空間構造に関する研究 山田 耕治; 松原 康介 2023年度 日本建築学会大会［近畿］学術講演梗概集/pp.29-30, 2023-09</t>
+          <t>Modernist Master Planning and Resident Adaptation in Abuja, Nigeria: a Historical Geography of Imposed Spatial Order,1976-2024 AKINKUNMI Priscilla; MATSUBARA Kosuke Planning Perspectives, 2026-04 / Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026-04 / フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― 戸田 理香子; 松原 康介 日本建築学会計画系論文集/91(840)/pp.351-362, 2026-02 / 吉田正春使節団が見た19世紀テヘラン都市改造 松原 康介 都市計画論文集/60(3)/pp.532-539, 2025-10 / Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08 / Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08 / Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08 / The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08 / ジスカール・デスタン政権下のパリ歩行者空間整備 家城悠紀; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.415-416, 2025-08 / 1960 年アガディール地震とその震災復興都市計画に関する研究 根岸美空; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.427-428, 2025-08 / フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 三重野馨; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.207-208, 2025-08 / フェルナン・プイヨンのベルカステル村修復に関する研究 ─城と村の一体性に着目して─ 古市麻菜子; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.205-206, 2025-08 / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス 吉田悠乃; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.203-204, 2025-08 / 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 瀨古希; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.541-542, 2025-08 / フェス 積み重なる寄進が形成した迷宮都市 松原 康介 建築知識/2025(7)/pp.84-85, 2025-6 / ガルダイア 丘の上の城塞とオアシス渓谷の集落 松原 康介 建築知識/2025(7)/pp.82-83, 2025-6 / カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- 渡邊 智也; 松原 康介 都市計画論文集/59(3)/pp.892-899, 2024-10 / The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10 / Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris FURUICHI Manako; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-15-6-1-D-15-6-4, 2024-09 / Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille YOSHIDA Yuno; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-5-5-1-D-5-5-4, 2024-09 / アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 和田 夏音; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.321-322, 2024-08 / 商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08 / 19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -10267,9 +10319,11 @@
 建築・都市計画史
 地中海都市
 ヘレニズム基盤
+イスラーム的都市形成
+西アジア
+中東・北アフリカ
 歴史文化保全
 国際協力
-中東・北アフリカ
 都市・地域政策
 GIS・空間分析
 建築・空間設計
@@ -10315,9 +10369,14 @@
 国際交流を背景とした中東都市計画史研究と都市保全プロジェクトへの還元
 モロッコの歴史都市 フェスの保全と近代化
 現代イスラーム都市の多元的成り立ちに関する研究
-Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026
+Modernist Master Planning and Resident Adaptation in Abuja, Nigeria: a Historical Geography of Imposed Spatial Order,1976-2024 AKINKUNMI Priscilla; MATSUBARA Kosuke Planning Perspectives, 2026-04
+Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026-04
 フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― 戸田 理香子; 松原 康介 日本建築学会計画系論文集/91(840)/pp.351-362, 2026-02
 吉田正春使節団が見た19世紀テヘラン都市改造 松原 康介 都市計画論文集/60(3)/pp.532-539, 2025-10
+Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08
+Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08
+Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08
+The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08
 ジスカール・デスタン政権下のパリ歩行者空間整備 家城悠紀; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.415-416, 2025-08
 1960 年アガディール地震とその震災復興都市計画に関する研究 根岸美空; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.427-428, 2025-08
 フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 三重野馨; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.207-208, 2025-08
@@ -10326,20 +10385,15 @@
 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 瀨古希; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.541-542, 2025-08
 フェス 積み重なる寄進が形成した迷宮都市 松原 康介 建築知識/2025(7)/pp.84-85, 2025-6
 ガルダイア 丘の上の城塞とオアシス渓谷の集落 松原 康介 建築知識/2025(7)/pp.82-83, 2025-6
-Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08
-The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08
-Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08
-Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08
 カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- 渡邊 智也; 松原 康介 都市計画論文集/59(3)/pp.892-899, 2024-10
+The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10
 Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris FURUICHI Manako; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-15-6-1-D-15-6-4, 2024-09
 Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille YOSHIDA Yuno; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-5-5-1-D-5-5-4, 2024-09
-The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10
 アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 和田 夏音; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.321-322, 2024-08
+商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08
+19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08
 カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08
-カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08
-19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08
-商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08
-ビルマ王都マンダレーの城内および城外市街地の空間構造に関する研究 山田 耕治; 松原 康介 2023年度 日本建築学会大会［近畿］学術講演梗概集/pp.29-30, 2023-09</t>
+カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10835,8 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>まちづくりを含む不動産開発に関する指導
+          <t>外国人材との共生策と空間整備を組み合わせる都市計画手法の提言～少子高齢化・人口減少で生まれる空き空間の有効再活用～
+まちづくりを含む不動産開発に関する指導
 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究
 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会
 超高層住宅の二重の老いの潜在的課題に関する研究
@@ -10789,7 +10844,6 @@
 つくば市みどりの分譲地のまちづくり提案について
 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性
 スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築
-超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究
 都市計画・建築計画
 都市計画
 地区計画
@@ -10800,8 +10854,21 @@
 産官学民連携
 地域活性化
 コミュニティビジネス
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
+外国人集住と地域の受入れ支援 藤井 さやか 都市計画/373/pp.56-59, 2025-09
+外国人居住を考える：特集の趣旨 藤井 さやか 住宅/74(9)/pp.2-2, 2025-09
+地方創生と外国人受け入れの取組み(北海道東川町) 藤井 さやか 住宅/74(9)/pp.46-48, 2025-09
+外国人研究者受入れの取り組み(JST・二の宮ハウス) 藤井 さやか 住宅/74(9)/pp.30-33, 2025-09
+多様化する外国人の住まい 藤井 さやか 住宅/74(9)/pp.3-10, 2025-09
+複合的な福祉支援を要するペット多頭飼育崩壊解決に向けた多機関連携支援体制に関する研究 渡邊優樹; 藤井 さやか 2025福祉のまちづくり学会要旨集/pp.272-273, 2025-09-26
+工場立地法敷地外緑地制度の活用実態と課題に関する研究 飛田晴哉; 藤井 さやか 都市計画報告集/24(2)/pp.294-301, 2025-09
+滞留空間整備及び参加型WSによる公共空間の利用促進効果に関する研究 岩崎真由子; 藤井 さやか 都市計画報告集/24(2)/pp.370-376, 2025-09
+地方小都市中心市街地における遊休不動産の特性に応じた新規事業の成立要因に関する研究 根岸龍宏; 鳩貝優太; 藤井 さやか 都市計画論文集/60(3)/pp.961-968, 2025-10
+地域に開かれた福祉施設がケアラーに与える影響 篠原百合; 武田侑哉; 梁イェリム; 中島弘貴; 新雄太; 井上拓央; 渡部一郎; 古賀千絵; 藤井 さやか; ... 都市計画論文集/60(3)/pp.854-861, 2025-10
+ごちゃまぜを理念とする多機能型福祉拠点の利用実態と課題に関する研究 武田侑哉; 藤井 さやか 都市計画論文集/60(3)/pp.814-821, 2025-10
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10
+A framework for analyzing the role of living labs in smart cities: insights from a case study in Japan Park Jooho; Watanabe Kentaro; Akasaka Fumiya; Fujii S... DISCOVER SUSTAINABILITY/6(1), 2025-08-11
 わがまちのSDGs 小出 譲治; 田中 幹夫; 松尾 勝利; 小長井 義正; 藤井 さやか 市政/73(5)/pp.6-13, 2023-05
 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ 吉田 啓助; 吉武 麻子; 荒 昌史; 藤井 さやか; 柴田 建; 益田 信也; 池添 昌幸 都市住宅学/119・120/pp.126-144, 2024-12
 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 原科 幸彦; 藤井 さやか; 阿部 くらん; 大澤 義明; 大島 弘至; 山西 康孝; 森川 晶; ... 日本不動産学会誌/38(1)/pp.26-49, 2024-06
@@ -10811,25 +10878,12 @@
 住宅団地の外国人集住：特集の趣旨 藤井 さやか 住宅/73(5)/p.2, 2024-05
 住宅地における地区計画や認可協定の今後 藤井 さやか 家とまちなみ/43(1)/pp.8-13, 2024-05
 区分所有マンションを含む市街地再開発事業の有効空地を考える 藤井 さやか 再開発コーディネーター/234/pp.31-31, 2025-03
-社会的包摂とデザイン─「つながる場」15事例の実践から 藤井 さやか; 後藤智香子 都市計画/373/pp.54-57, 2025-03
-外国人住民との共存・共生: 海外の事例からの示唆 藤井 さやか 都市問題/115(12)/pp.11-16, 2024-12
-首都圏郊外におけるリノベーションまちづくりの成果と課題に関する研究 鳩貝優太; 藤井 さやか 都市計画論文集/59(3)/pp.1391-1398, 2024-10
-住宅建替えと一体的に再整備された街区公園の維持管理活動を通じたコミュニティ形成に関する研究 大森聡; 藤井 さやか 都市計画論文集/59(3)/pp.714-721, 2024-10
-計画的戸建住宅地における駐車場シェアの導入意向と活用可能性に関する研究 佐藤 耀; 根岸 龍宏; 藤井 さやか 都市計画論文集/59(3)/pp.752-759, 2024-10
-多様な主体が関わる出産祝いプロジェクトの成立経緯と参加主体にもたらす変化に関する研究 石川夏帆; 藤井 さやか 都市計画論文集/59(3)/pp.1383-1388, 2024-10
-職員の活躍を願う市長の思いと取り組み 品川萬里; 北村 正平; 瀧澤智子; 玉井敏久; 藤井 さやか 市政/72(5)/pp.6-11, 2023-05
-今後の地域づくりへの期待 藤井 さやか 人と国土21/49(5)/pp.44-44, 2024-01
-Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea Park Jooho; Fujii Sayaka Urban Planning/8(2)/pp.93-107, 2023-04
-転換期にある筑波研究学園都市の地区計画が空間資源継承に果たす役割と課題 瀬川遥子; 島田由美子; 藤井 さやか 都市計画論文集/58(3)/pp.1187-1192, 2023-10
-1980年以降、40年の「つくば」の変化と現状 藤井 さやか 建築ジャーナル/1334/pp.15-18, 2022-09
-Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea, Urban Planning Park Jooho; Fujii Sayaka URBAN PLANNING/8(2)/pp.93-107, 2023-04
-Living Lab Participants’ Knowledge Change about Inclusive Smart Cities: An Urban Living Lab in Seongdaegol, Seoul, South Korea Park Jooho; Fujii Sayaka Smart Cities/5(4)/pp.1376-1388, 2022-10
-地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究 板橋奈央; 藤井 さやか; 島田由美子 都市計画論文集/57(3)/pp.1347-1354, 2022-11</t>
+社会的包摂とデザイン─「つながる場」15事例の実践から 藤井 さやか; 後藤智香子 都市計画/373/pp.54-57, 2025-03</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>まちづくりを含む不動産開発に関する指導 / 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 超高層住宅の二重の老いの潜在的課題に関する研究 / 社会的孤独の解消モデル事例のプロセス分析及び検証手法の検討 / つくば市みどりの分譲地のまちづくり提案について / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築 / 超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究</t>
+          <t>外国人材との共生策と空間整備を組み合わせる都市計画手法の提言～少子高齢化・人口減少で生まれる空き空間の有効再活用～ / まちづくりを含む不動産開発に関する指導 / 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究 / 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会 / 超高層住宅の二重の老いの潜在的課題に関する研究 / 社会的孤独の解消モデル事例のプロセス分析及び検証手法の検討 / つくば市みどりの分譲地のまちづくり提案について / 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性 / スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10844,7 +10898,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10 / わがまちのSDGs 小出 譲治; 田中 幹夫; 松尾 勝利; 小長井 義正; 藤井 さやか 市政/73(5)/pp.6-13, 2023-05 / 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ 吉田 啓助; 吉武 麻子; 荒 昌史; 藤井 さやか; 柴田 建; 益田 信也; 池添 昌幸 都市住宅学/119・120/pp.126-144, 2024-12 / 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 原科 幸彦; 藤井 さやか; 阿部 くらん; 大澤 義明; 大島 弘至; 山西 康孝; 森川 晶; ... 日本不動産学会誌/38(1)/pp.26-49, 2024-06 / 京都市東松ノ木市営住宅 村木美都子; 藤井 さやか 住宅/73(5)/pp.13-19, 2024-05 / 国勢調査分析からみる外国人集住団地の実態 藤井 さやか; 王爽 住宅/73(5)/pp.9-12, 2024-05 / 増加する外国人の受け皿としての住宅団地 藤井 さやか 住宅/73(5)/pp.3-8, 2024-05 / 住宅団地の外国人集住：特集の趣旨 藤井 さやか 住宅/73(5)/p.2, 2024-05 / 住宅地における地区計画や認可協定の今後 藤井 さやか 家とまちなみ/43(1)/pp.8-13, 2024-05 / 区分所有マンションを含む市街地再開発事業の有効空地を考える 藤井 さやか 再開発コーディネーター/234/pp.31-31, 2025-03 / 社会的包摂とデザイン─「つながる場」15事例の実践から 藤井 さやか; 後藤智香子 都市計画/373/pp.54-57, 2025-03 / 外国人住民との共存・共生: 海外の事例からの示唆 藤井 さやか 都市問題/115(12)/pp.11-16, 2024-12 / 首都圏郊外におけるリノベーションまちづくりの成果と課題に関する研究 鳩貝優太; 藤井 さやか 都市計画論文集/59(3)/pp.1391-1398, 2024-10 / 住宅建替えと一体的に再整備された街区公園の維持管理活動を通じたコミュニティ形成に関する研究 大森聡; 藤井 さやか 都市計画論文集/59(3)/pp.714-721, 2024-10 / 計画的戸建住宅地における駐車場シェアの導入意向と活用可能性に関する研究 佐藤 耀; 根岸 龍宏; 藤井 さやか 都市計画論文集/59(3)/pp.752-759, 2024-10 / 多様な主体が関わる出産祝いプロジェクトの成立経緯と参加主体にもたらす変化に関する研究 石川夏帆; 藤井 さやか 都市計画論文集/59(3)/pp.1383-1388, 2024-10 / 職員の活躍を願う市長の思いと取り組み 品川萬里; 北村 正平; 瀧澤智子; 玉井敏久; 藤井 さやか 市政/72(5)/pp.6-11, 2023-05 / 今後の地域づくりへの期待 藤井 さやか 人と国土21/49(5)/pp.44-44, 2024-01 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea Park Jooho; Fujii Sayaka Urban Planning/8(2)/pp.93-107, 2023-04 / 転換期にある筑波研究学園都市の地区計画が空間資源継承に果たす役割と課題 瀬川遥子; 島田由美子; 藤井 さやか 都市計画論文集/58(3)/pp.1187-1192, 2023-10 / 1980年以降、40年の「つくば」の変化と現状 藤井 さやか 建築ジャーナル/1334/pp.15-18, 2022-09 / Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea, Urban Planning Park Jooho; Fujii Sayaka URBAN PLANNING/8(2)/pp.93-107, 2023-04 / Living Lab Participants’ Knowledge Change about Inclusive Smart Cities: An Urban Living Lab in Seongdaegol, Seoul, South Korea Park Jooho; Fujii Sayaka Smart Cities/5(4)/pp.1376-1388, 2022-10 / 地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究 板橋奈央; 藤井 さやか; 島田由美子 都市計画論文集/57(3)/pp.1347-1354, 2022-11</t>
+          <t>大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / 外国人集住と地域の受入れ支援 藤井 さやか 都市計画/373/pp.56-59, 2025-09 / 外国人居住を考える：特集の趣旨 藤井 さやか 住宅/74(9)/pp.2-2, 2025-09 / 地方創生と外国人受け入れの取組み(北海道東川町) 藤井 さやか 住宅/74(9)/pp.46-48, 2025-09 / 外国人研究者受入れの取り組み(JST・二の宮ハウス) 藤井 さやか 住宅/74(9)/pp.30-33, 2025-09 / 多様化する外国人の住まい 藤井 さやか 住宅/74(9)/pp.3-10, 2025-09 / 複合的な福祉支援を要するペット多頭飼育崩壊解決に向けた多機関連携支援体制に関する研究 渡邊優樹; 藤井 さやか 2025福祉のまちづくり学会要旨集/pp.272-273, 2025-09-26 / 工場立地法敷地外緑地制度の活用実態と課題に関する研究 飛田晴哉; 藤井 さやか 都市計画報告集/24(2)/pp.294-301, 2025-09 / 滞留空間整備及び参加型WSによる公共空間の利用促進効果に関する研究 岩崎真由子; 藤井 さやか 都市計画報告集/24(2)/pp.370-376, 2025-09 / 地方小都市中心市街地における遊休不動産の特性に応じた新規事業の成立要因に関する研究 根岸龍宏; 鳩貝優太; 藤井 さやか 都市計画論文集/60(3)/pp.961-968, 2025-10 / 地域に開かれた福祉施設がケアラーに与える影響 篠原百合; 武田侑哉; 梁イェリム; 中島弘貴; 新雄太; 井上拓央; 渡部一郎; 古賀千絵; 藤井 さやか; ... 都市計画論文集/60(3)/pp.854-861, 2025-10 / ごちゃまぜを理念とする多機能型福祉拠点の利用実態と課題に関する研究 武田侑哉; 藤井 さやか 都市計画論文集/60(3)/pp.814-821, 2025-10 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10 / A framework for analyzing the role of living labs in smart cities: insights from a case study in Japan Park Jooho; Watanabe Kentaro; Akasaka Fumiya; Fujii S... DISCOVER SUSTAINABILITY/6(1), 2025-08-11 / わがまちのSDGs 小出 譲治; 田中 幹夫; 松尾 勝利; 小長井 義正; 藤井 さやか 市政/73(5)/pp.6-13, 2023-05 / 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ 吉田 啓助; 吉武 麻子; 荒 昌史; 藤井 さやか; 柴田 建; 益田 信也; 池添 昌幸 都市住宅学/119・120/pp.126-144, 2024-12 / 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 原科 幸彦; 藤井 さやか; 阿部 くらん; 大澤 義明; 大島 弘至; 山西 康孝; 森川 晶; ... 日本不動産学会誌/38(1)/pp.26-49, 2024-06 / 京都市東松ノ木市営住宅 村木美都子; 藤井 さやか 住宅/73(5)/pp.13-19, 2024-05 / 国勢調査分析からみる外国人集住団地の実態 藤井 さやか; 王爽 住宅/73(5)/pp.9-12, 2024-05 / 増加する外国人の受け皿としての住宅団地 藤井 さやか 住宅/73(5)/pp.3-8, 2024-05 / 住宅団地の外国人集住：特集の趣旨 藤井 さやか 住宅/73(5)/p.2, 2024-05 / 住宅地における地区計画や認可協定の今後 藤井 さやか 家とまちなみ/43(1)/pp.8-13, 2024-05 / 区分所有マンションを含む市街地再開発事業の有効空地を考える 藤井 さやか 再開発コーディネーター/234/pp.31-31, 2025-03 / 社会的包摂とデザイン─「つながる場」15事例の実践から 藤井 さやか; 後藤智香子 都市計画/373/pp.54-57, 2025-03</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -10854,12 +10908,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>都市計画・建築計画 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>都市計画・建築計画 ; 家族・人口政策 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -10874,6 +10928,7 @@
 産官学民連携
 地域活性化
 コミュニティビジネス
+家族・人口政策
 都市・地域政策
 GIS・空間分析
 建築・空間設計
@@ -10882,6 +10937,10 @@
 数理最適化・OR
 AI・データサイエンス
 都市・空間・交通
+家族の経済学
+少子化対策
+人口政策
+家計意思決定
 都市経済
 地域政策
 土地利用
@@ -10916,6 +10975,7 @@
 ごちゃまぜを理念とする多機能型福祉拠点の成立要因と意義に関する研究 －石川県社会福祉法人佛子園「三草二木 西圓寺」を対象として－
 移住増加地域における遊休不動産を活用した新規事業の成立要因に関する研究 －長野県小諸市中心市街地を対象として－
 超高層住宅集積地における利活用・維持管理の実態を踏まえた公開空地等の課題に関する研究 －東京都中央区第3ゾーンを対象として－
+外国人材との共生策と空間整備を組み合わせる都市計画手法の提言～少子高齢化・人口減少で生まれる空き空間の有効再活用～
 まちづくりを含む不動産開発に関する指導
 教育研究環境の改善に向けた、第三エリアを中心としたキャンパス空間の再構築に関する研究
 空き空間を活用した社会的孤立を解消・予防する「つながる場」に関する研究会
@@ -10924,9 +10984,21 @@
 つくば市みどりの分譲地のまちづくり提案について
 空き空間を活用した社会的孤立を解消・予防する「つながる場」の形成実態と展開可能性
 スペース・シェアリングを活用した高経年戸建住宅地再生・継承モデルの構築
-超高層住宅の「二重の老い」の乗り越えを目指す学際的・国際的研究
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
+外国人集住と地域の受入れ支援 藤井 さやか 都市計画/373/pp.56-59, 2025-09
+外国人居住を考える：特集の趣旨 藤井 さやか 住宅/74(9)/pp.2-2, 2025-09
+地方創生と外国人受け入れの取組み(北海道東川町) 藤井 さやか 住宅/74(9)/pp.46-48, 2025-09
+外国人研究者受入れの取り組み(JST・二の宮ハウス) 藤井 さやか 住宅/74(9)/pp.30-33, 2025-09
+多様化する外国人の住まい 藤井 さやか 住宅/74(9)/pp.3-10, 2025-09
+複合的な福祉支援を要するペット多頭飼育崩壊解決に向けた多機関連携支援体制に関する研究 渡邊優樹; 藤井 さやか 2025福祉のまちづくり学会要旨集/pp.272-273, 2025-09-26
+工場立地法敷地外緑地制度の活用実態と課題に関する研究 飛田晴哉; 藤井 さやか 都市計画報告集/24(2)/pp.294-301, 2025-09
+滞留空間整備及び参加型WSによる公共空間の利用促進効果に関する研究 岩崎真由子; 藤井 さやか 都市計画報告集/24(2)/pp.370-376, 2025-09
+地方小都市中心市街地における遊休不動産の特性に応じた新規事業の成立要因に関する研究 根岸龍宏; 鳩貝優太; 藤井 さやか 都市計画論文集/60(3)/pp.961-968, 2025-10
+地域に開かれた福祉施設がケアラーに与える影響 篠原百合; 武田侑哉; 梁イェリム; 中島弘貴; 新雄太; 井上拓央; 渡部一郎; 古賀千絵; 藤井 さやか; ... 都市計画論文集/60(3)/pp.854-861, 2025-10
+ごちゃまぜを理念とする多機能型福祉拠点の利用実態と課題に関する研究 武田侑哉; 藤井 さやか 都市計画論文集/60(3)/pp.814-821, 2025-10
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10
+A framework for analyzing the role of living labs in smart cities: insights from a case study in Japan Park Jooho; Watanabe Kentaro; Akasaka Fumiya; Fujii S... DISCOVER SUSTAINABILITY/6(1), 2025-08-11
 わがまちのSDGs 小出 譲治; 田中 幹夫; 松尾 勝利; 小長井 義正; 藤井 さやか 市政/73(5)/pp.6-13, 2023-05
 2022年度第30回学術講演会メインシンポジウム 郊外居住の新たな価値 : 日の里団地再生のセカンドステージ 吉田 啓助; 吉武 麻子; 荒 昌史; 藤井 さやか; 柴田 建; 益田 信也; 池添 昌幸 都市住宅学/119・120/pp.126-144, 2024-12
 日本不動産学会シンポジウム(令和5年度科学研究費助成事業) 危険な空き家の解決から始めるまちづくり : 行政・事業者・市民の連携による取り組みと知恵 原科 幸彦; 藤井 さやか; 阿部 くらん; 大澤 義明; 大島 弘至; 山西 康孝; 森川 晶; ... 日本不動産学会誌/38(1)/pp.26-49, 2024-06
@@ -10936,20 +11008,7 @@
 住宅団地の外国人集住：特集の趣旨 藤井 さやか 住宅/73(5)/p.2, 2024-05
 住宅地における地区計画や認可協定の今後 藤井 さやか 家とまちなみ/43(1)/pp.8-13, 2024-05
 区分所有マンションを含む市街地再開発事業の有効空地を考える 藤井 さやか 再開発コーディネーター/234/pp.31-31, 2025-03
-社会的包摂とデザイン─「つながる場」15事例の実践から 藤井 さやか; 後藤智香子 都市計画/373/pp.54-57, 2025-03
-外国人住民との共存・共生: 海外の事例からの示唆 藤井 さやか 都市問題/115(12)/pp.11-16, 2024-12
-首都圏郊外におけるリノベーションまちづくりの成果と課題に関する研究 鳩貝優太; 藤井 さやか 都市計画論文集/59(3)/pp.1391-1398, 2024-10
-住宅建替えと一体的に再整備された街区公園の維持管理活動を通じたコミュニティ形成に関する研究 大森聡; 藤井 さやか 都市計画論文集/59(3)/pp.714-721, 2024-10
-計画的戸建住宅地における駐車場シェアの導入意向と活用可能性に関する研究 佐藤 耀; 根岸 龍宏; 藤井 さやか 都市計画論文集/59(3)/pp.752-759, 2024-10
-多様な主体が関わる出産祝いプロジェクトの成立経緯と参加主体にもたらす変化に関する研究 石川夏帆; 藤井 さやか 都市計画論文集/59(3)/pp.1383-1388, 2024-10
-職員の活躍を願う市長の思いと取り組み 品川萬里; 北村 正平; 瀧澤智子; 玉井敏久; 藤井 さやか 市政/72(5)/pp.6-11, 2023-05
-今後の地域づくりへの期待 藤井 さやか 人と国土21/49(5)/pp.44-44, 2024-01
-Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea Park Jooho; Fujii Sayaka Urban Planning/8(2)/pp.93-107, 2023-04
-転換期にある筑波研究学園都市の地区計画が空間資源継承に果たす役割と課題 瀬川遥子; 島田由美子; 藤井 さやか 都市計画論文集/58(3)/pp.1187-1192, 2023-10
-1980年以降、40年の「つくば」の変化と現状 藤井 さやか 建築ジャーナル/1334/pp.15-18, 2022-09
-Civic Engagement in a Citizen-Led Living Lab for Smart Cities: Evidence From South Korea, Urban Planning Park Jooho; Fujii Sayaka URBAN PLANNING/8(2)/pp.93-107, 2023-04
-Living Lab Participants’ Knowledge Change about Inclusive Smart Cities: An Urban Living Lab in Seongdaegol, Seoul, South Korea Park Jooho; Fujii Sayaka Smart Cities/5(4)/pp.1376-1388, 2022-10
-地方都市における市民提案型まちづくり活動助成制度の市民活動育成機能に関する研究 板橋奈央; 藤井 さやか; 島田由美子 都市計画論文集/57(3)/pp.1347-1354, 2022-11</t>
+社会的包摂とデザイン─「つながる場」15事例の実践から 藤井 さやか; 後藤智香子 都市計画/373/pp.54-57, 2025-03</t>
         </is>
       </c>
     </row>
@@ -11003,10 +11062,18 @@
 職名
 教授
 eメール
-G&amp;x"$(&lt;KG,$E-,.$.yxExzE#)
++B6&gt;@DXgcH@aIHJ@J76a68a?E
 最適化
 組合せ最適化
 アルゴリズム
+Hgformer: Hyperbolic Graph Transformer for Collaborative Filtering Yang Xin; Li Xingrun; Chang Heng; Jinze Yang; Yang X... Proceedings of the 42nd International Conference on Machine Learning/pp.70813-70832, 2025-11
+Graph-Topological Deep Detector for Cross-Platform Forest Point Clouds Yiliu Tan; Yang Xin; Xu Xin; Zhang Jingyi; Cao Yunji... Proceedings of the 2025 8th International Conference on Computational Intelligence and Intelligent Systems/pp.15-22, 2026-02
+Locker-based Drone Delivery with Battery Swapping Stations: A Joint Routing-Recharging Optimization Wushuang Wang; Yiliu Tan; Yu Li; 繁野 麻衣子 Proceedings of the 2025 8th International Conference on Computational Intelligence and Intelligent Systems/pp.88-95, 2026-02
+EONにおける通信要求の保持時間を考慮した予約種別リソース割り当て戦略の提案 李 宗晟; 繁野 麻衣子 信学技報,/125(146)/pp.27-32, 2025-08
+TLNet : A deep learning framework for tree detection in forest point clouds using multi-layered forest structure Tan Yiliu; Yang Xin; Zhang Jingyi; Xu Xin; Cao Yunji... ISPRS JOURNAL OF PHOTOGRAMMETRY AND REMOTE SENSING/234/pp.227-241, 2026-04
+Transformer-pointer DRL model for static resource allocation problems in SDM-EONs Chen Sibo; Wang Jiading; Shigeno Maiko JOURNAL OF OPTICAL COMMUNICATIONS AND NETWORKING/18(3)/pp.315-328, 2026-03
+Selection of candidate paths based on diversity in resource allocation problems on optical networks Mori Yuta; Shigeno Maiko OPTICAL SWITCHING AND NETWORKING/58, 2025-12
+Mathematical models for carpooling considering driver absence: Comparative analysis and heuristic strategies Wang Wushuang; Li Yu; Tan Yiliu; Kobayashi Ryotaro; H... COMPUTERS &amp; INDUSTRIAL ENGINEERING/210, 2025-12
 A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs Chen Sibo; Wang Jiading; SHIGENO Maiko 2024 IEEE Opto-Electronics and Communications Conference (OECC)/pp.1-3, 2024-6
 Break maximization for round-robin tournaments without consecutive breaks Xue Fei; Ma Hajunfu; Shigeno Maiko OPERATIONS RESEARCH LETTERS/57, 2024-11
 Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm Li Yu; Wang Wushuang; Hashikami Hidenobu; Shigeno Maiko COMPUTERS &amp; INDUSTRIAL ENGINEERING/198, 2024-12
@@ -11023,15 +11090,7 @@
 Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model Wang Jiading; Chen Sibo; Wu Qian; Tan Yiliu; Shigeno ... SENSORS/22(24), 2022-12
 Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan Hashikami Hidenobu; Kobayashi Ryotaro; Li Yu; Nakano ... IEEE TRANSACTIONS ON SYSTEMS MAN CYBERNETICS-SYSTEMS/53(7)/pp.4239-4250, 2023-07
 Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament Xue Fei; Ma Haijunfu; Shigeno Maiko JOURNAL OF ADVANCED MECHANICAL DESIGN SYSTEMS AND MANUFACTURING/16(4), 2022
-交換移植制度におけるドミナントマッチングの適用可能性 臼井 颯汰; 栗野 盛光; 大藤 剛宏; 繁野 麻衣子 日本オペレーションズ・リサーチ学会和文論文誌/pp.1-21, 2022
-Network Design Models with Partial Protection Schemes against Multiple Failures under Optical- Channel Data Unit Constraints Yiliu Tan; Qian Wu; Yoshiki Nakano; Jiading Wang; Shigeno... Proceedings of 2021 IEEE 6th Optoelectronics Global Conference/pp.38-46, 2021
-ILP models and improved methods for the problem of routing and spectrum allocation Wang Jiading; Shigeno Maiko; Wu Qian Optical Switching and Networking/45/pp.100675-100675, 2022
-A novel channel-based model for the problem of routing, space, and spectrum assignment Wu Qian; Wang Jiading; Shigeno Maiko OPTICAL SWITCHING AND NETWORKING/43, 2022-02
-NASH EQUILIBRIA FOR INFORMATION DIFFUSION GAMES ON WEIGHTED CYCLES AND PATHS Li Tianyang; Shigeno Maiko 日本オペレーションズ・リサーチ学会論文誌/64(1)/pp.1-11, 2021 CiNii
-Strongly separable matrices for nonadaptive combinatorial group testing Fan Jinping; Fu Hung-Lin; Gu Yujie; Miao Ying; Shigen... DISCRETE APPLIED MATHEMATICS/291/pp.180-187, 2021-03
-Modeling and Evaluating Taxi Ride-sharing for Event Trips Yoshida Taketo; Yano Masaki; Horikawa Kenichiro; Sato Ke... IPSJ Transactions on Mathematical Modeling and Its Applications/12/pp.10-11, 2019
-不均衡データに対する多段階学習を用いた アンサンブルモデルによる2 クラス分類アルゴリズムの提案 藤原和樹; 繁野 麻衣子; 住田潮 情報処理学会論文誌，数理モデル化と応用（TOM）/12(3)/pp.10-17, 2019
-A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data Fujiwara Kazuki; Shigeno Maiko; Sumita Ushio IEEE ACCESS/7/pp.82970-82977, 2019</t>
+交換移植制度におけるドミナントマッチングの適用可能性 臼井 颯汰; 栗野 盛光; 大藤 剛宏; 繁野 麻衣子 日本オペレーションズ・リサーチ学会和文論文誌/pp.1-21, 2022</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11041,7 +11100,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / G&amp;x"$(&lt;KG,$E-,.$.yxExzE#)</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / +B6&gt;@DXgcH@aIHJ@J76a68a?E</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -11051,7 +11110,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs Chen Sibo; Wang Jiading; SHIGENO Maiko 2024 IEEE Opto-Electronics and Communications Conference (OECC)/pp.1-3, 2024-6 / Break maximization for round-robin tournaments without consecutive breaks Xue Fei; Ma Hajunfu; Shigeno Maiko OPERATIONS RESEARCH LETTERS/57, 2024-11 / Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm Li Yu; Wang Wushuang; Hashikami Hidenobu; Shigeno Maiko COMPUTERS &amp; INDUSTRIAL ENGINEERING/198, 2024-12 / Height Estimation for Abrasive Grain of Synthetic Diamonds on Microscope Images by Conditional Adversarial Networks Joe Brinton; Shota Oki; Xin Yang; SHIGENO Maiko Proceedings of the IEA/AIE 2022: Advances and Trends in Artificial Intelligence. Theory and Practices in Artificial Intelligence/pp.797-804, 2022 / Designing of OTN/WDM networks withrecovery methods for multiple failures Yiliu Tan; Yoshiki Nakano; Jiading Wang; SHIGENO Maiko Proceedings of the 27th OptoElectronics and CommunicationsConference (OECC) and 2022 International Conference on Photonics in Switching andComputing (PSC)/pp.1-3, 2022 / Restaurant Sales forecasting with feature interaction-learning mechanism based neural network model,IEEE International Conference on Big Data Xin Yang; Tetsuya Tsuboi; Keisuke Kimura; Keitarou Ha... Proceedings of IEEE International Conference on Big Data, Big Data 2022/pp.4166-4172, 2023 / A Discrete JAYA Algorithm for Long-Term Carpooling Problem Wushuang Wang; Yu Li; Hidenobu Hashikami; SHIGENO Maiko Proceedings of the 2023 IEEE 12th Global Conference on Consumer Electronics (GCCE 2023)/pp.1075-1076, 2023 / Carry-over Effect Values Minimization under Circle Method and Binary Factorization Based on Jaya Algorithm Wushuang Wang; Fei Xue; Toshiki Mitsui; Zhiyuan Shang... Proceedings of the 2024 8th International Conference on Control Engineering and Artificial Intelligence/pp.44-51, 2024 / Application of Data Anonymization to Smartphone Apps Usage Logs Tabata Naoya; SHIGENO Maiko Proceedings of the 2024 9th International Conference on Big Data Analytics (ICBDA)/pp.60-69, 2024 / 数理最適化を用いたサービス工学の事例―通勤カープールの実証実験― 橋上英宜; 繁野 麻衣子 オペレーションズ・リサーチ：経営の科学/68/pp.161-168, 2024 / Four-level knowledge graph contrastive learning structure for smart-phone application recommendation Xin Yang; Yu Li; Wenhui Ai; SHIGENO Maiko Proceedings of 2023 International Wireless Communications and Mobile Computing/pp.1340-1345, 2023 / A New Approach to Market Segmentation Based on 2-Dimensional Tables Naoya Tabata; Rin Itoshiya; Hideshi Narita; SHIGENO M... Proceedings of 10th International Conference on Computing and Data Engineering, 2024 / Challenges of commuter carpooling with adapting to Japanese customs and regulations: A pilot study Hashikami Hidenobu; Li Yu; Kobayashi Ryotaro; Shigeno ... TRANSPORTATION RESEARCH INTERDISCIPLINARY PERSPECTIVES/22, 2023-11 / Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model Wang Jiading; Chen Sibo; Wu Qian; Tan Yiliu; Shigeno ... SENSORS/22(24), 2022-12 / Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan Hashikami Hidenobu; Kobayashi Ryotaro; Li Yu; Nakano ... IEEE TRANSACTIONS ON SYSTEMS MAN CYBERNETICS-SYSTEMS/53(7)/pp.4239-4250, 2023-07 / Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament Xue Fei; Ma Haijunfu; Shigeno Maiko JOURNAL OF ADVANCED MECHANICAL DESIGN SYSTEMS AND MANUFACTURING/16(4), 2022 / 交換移植制度におけるドミナントマッチングの適用可能性 臼井 颯汰; 栗野 盛光; 大藤 剛宏; 繁野 麻衣子 日本オペレーションズ・リサーチ学会和文論文誌/pp.1-21, 2022 / Network Design Models with Partial Protection Schemes against Multiple Failures under Optical- Channel Data Unit Constraints Yiliu Tan; Qian Wu; Yoshiki Nakano; Jiading Wang; Shigeno... Proceedings of 2021 IEEE 6th Optoelectronics Global Conference/pp.38-46, 2021 / ILP models and improved methods for the problem of routing and spectrum allocation Wang Jiading; Shigeno Maiko; Wu Qian Optical Switching and Networking/45/pp.100675-100675, 2022 / A novel channel-based model for the problem of routing, space, and spectrum assignment Wu Qian; Wang Jiading; Shigeno Maiko OPTICAL SWITCHING AND NETWORKING/43, 2022-02 / NASH EQUILIBRIA FOR INFORMATION DIFFUSION GAMES ON WEIGHTED CYCLES AND PATHS Li Tianyang; Shigeno Maiko 日本オペレーションズ・リサーチ学会論文誌/64(1)/pp.1-11, 2021 CiNii / Strongly separable matrices for nonadaptive combinatorial group testing Fan Jinping; Fu Hung-Lin; Gu Yujie; Miao Ying; Shigen... DISCRETE APPLIED MATHEMATICS/291/pp.180-187, 2021-03 / Modeling and Evaluating Taxi Ride-sharing for Event Trips Yoshida Taketo; Yano Masaki; Horikawa Kenichiro; Sato Ke... IPSJ Transactions on Mathematical Modeling and Its Applications/12/pp.10-11, 2019 / 不均衡データに対する多段階学習を用いた アンサンブルモデルによる2 クラス分類アルゴリズムの提案 藤原和樹; 繁野 麻衣子; 住田潮 情報処理学会論文誌，数理モデル化と応用（TOM）/12(3)/pp.10-17, 2019 / A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data Fujiwara Kazuki; Shigeno Maiko; Sumita Ushio IEEE ACCESS/7/pp.82970-82977, 2019</t>
+          <t>Hgformer: Hyperbolic Graph Transformer for Collaborative Filtering Yang Xin; Li Xingrun; Chang Heng; Jinze Yang; Yang X... Proceedings of the 42nd International Conference on Machine Learning/pp.70813-70832, 2025-11 / Graph-Topological Deep Detector for Cross-Platform Forest Point Clouds Yiliu Tan; Yang Xin; Xu Xin; Zhang Jingyi; Cao Yunji... Proceedings of the 2025 8th International Conference on Computational Intelligence and Intelligent Systems/pp.15-22, 2026-02 / Locker-based Drone Delivery with Battery Swapping Stations: A Joint Routing-Recharging Optimization Wushuang Wang; Yiliu Tan; Yu Li; 繁野 麻衣子 Proceedings of the 2025 8th International Conference on Computational Intelligence and Intelligent Systems/pp.88-95, 2026-02 / EONにおける通信要求の保持時間を考慮した予約種別リソース割り当て戦略の提案 李 宗晟; 繁野 麻衣子 信学技報,/125(146)/pp.27-32, 2025-08 / TLNet : A deep learning framework for tree detection in forest point clouds using multi-layered forest structure Tan Yiliu; Yang Xin; Zhang Jingyi; Xu Xin; Cao Yunji... ISPRS JOURNAL OF PHOTOGRAMMETRY AND REMOTE SENSING/234/pp.227-241, 2026-04 / Transformer-pointer DRL model for static resource allocation problems in SDM-EONs Chen Sibo; Wang Jiading; Shigeno Maiko JOURNAL OF OPTICAL COMMUNICATIONS AND NETWORKING/18(3)/pp.315-328, 2026-03 / Selection of candidate paths based on diversity in resource allocation problems on optical networks Mori Yuta; Shigeno Maiko OPTICAL SWITCHING AND NETWORKING/58, 2025-12 / Mathematical models for carpooling considering driver absence: Comparative analysis and heuristic strategies Wang Wushuang; Li Yu; Tan Yiliu; Kobayashi Ryotaro; H... COMPUTERS &amp; INDUSTRIAL ENGINEERING/210, 2025-12 / A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs Chen Sibo; Wang Jiading; SHIGENO Maiko 2024 IEEE Opto-Electronics and Communications Conference (OECC)/pp.1-3, 2024-6 / Break maximization for round-robin tournaments without consecutive breaks Xue Fei; Ma Hajunfu; Shigeno Maiko OPERATIONS RESEARCH LETTERS/57, 2024-11 / Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm Li Yu; Wang Wushuang; Hashikami Hidenobu; Shigeno Maiko COMPUTERS &amp; INDUSTRIAL ENGINEERING/198, 2024-12 / Height Estimation for Abrasive Grain of Synthetic Diamonds on Microscope Images by Conditional Adversarial Networks Joe Brinton; Shota Oki; Xin Yang; SHIGENO Maiko Proceedings of the IEA/AIE 2022: Advances and Trends in Artificial Intelligence. Theory and Practices in Artificial Intelligence/pp.797-804, 2022 / Designing of OTN/WDM networks withrecovery methods for multiple failures Yiliu Tan; Yoshiki Nakano; Jiading Wang; SHIGENO Maiko Proceedings of the 27th OptoElectronics and CommunicationsConference (OECC) and 2022 International Conference on Photonics in Switching andComputing (PSC)/pp.1-3, 2022 / Restaurant Sales forecasting with feature interaction-learning mechanism based neural network model,IEEE International Conference on Big Data Xin Yang; Tetsuya Tsuboi; Keisuke Kimura; Keitarou Ha... Proceedings of IEEE International Conference on Big Data, Big Data 2022/pp.4166-4172, 2023 / A Discrete JAYA Algorithm for Long-Term Carpooling Problem Wushuang Wang; Yu Li; Hidenobu Hashikami; SHIGENO Maiko Proceedings of the 2023 IEEE 12th Global Conference on Consumer Electronics (GCCE 2023)/pp.1075-1076, 2023 / Carry-over Effect Values Minimization under Circle Method and Binary Factorization Based on Jaya Algorithm Wushuang Wang; Fei Xue; Toshiki Mitsui; Zhiyuan Shang... Proceedings of the 2024 8th International Conference on Control Engineering and Artificial Intelligence/pp.44-51, 2024 / Application of Data Anonymization to Smartphone Apps Usage Logs Tabata Naoya; SHIGENO Maiko Proceedings of the 2024 9th International Conference on Big Data Analytics (ICBDA)/pp.60-69, 2024 / 数理最適化を用いたサービス工学の事例―通勤カープールの実証実験― 橋上英宜; 繁野 麻衣子 オペレーションズ・リサーチ：経営の科学/68/pp.161-168, 2024 / Four-level knowledge graph contrastive learning structure for smart-phone application recommendation Xin Yang; Yu Li; Wenhui Ai; SHIGENO Maiko Proceedings of 2023 International Wireless Communications and Mobile Computing/pp.1340-1345, 2023 / A New Approach to Market Segmentation Based on 2-Dimensional Tables Naoya Tabata; Rin Itoshiya; Hideshi Narita; SHIGENO M... Proceedings of 10th International Conference on Computing and Data Engineering, 2024 / Challenges of commuter carpooling with adapting to Japanese customs and regulations: A pilot study Hashikami Hidenobu; Li Yu; Kobayashi Ryotaro; Shigeno ... TRANSPORTATION RESEARCH INTERDISCIPLINARY PERSPECTIVES/22, 2023-11 / Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model Wang Jiading; Chen Sibo; Wu Qian; Tan Yiliu; Shigeno ... SENSORS/22(24), 2022-12 / Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan Hashikami Hidenobu; Kobayashi Ryotaro; Li Yu; Nakano ... IEEE TRANSACTIONS ON SYSTEMS MAN CYBERNETICS-SYSTEMS/53(7)/pp.4239-4250, 2023-07 / Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament Xue Fei; Ma Haijunfu; Shigeno Maiko JOURNAL OF ADVANCED MECHANICAL DESIGN SYSTEMS AND MANUFACTURING/16(4), 2022 / 交換移植制度におけるドミナントマッチングの適用可能性 臼井 颯汰; 栗野 盛光; 大藤 剛宏; 繁野 麻衣子 日本オペレーションズ・リサーチ学会和文論文誌/pp.1-21, 2022</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -11061,7 +11120,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; G&amp;x"$(&lt;KG,$E-,.$.yxExzE#) ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; +B6&gt;@DXgcH@aIHJ@J76a68a?E ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -11080,7 +11139,7 @@
 職名
 教授
 eメール
-G&amp;x"$(&lt;KG,$E-,.$.yxExzE#)
++B6&gt;@DXgcH@aIHJ@J76a68a?E
 最適化
 組合せ最適化
 アルゴリズム
@@ -11148,6 +11207,14 @@
 ネットワーク理論の基盤整備と伸張
 データの精度を考慮した組合せ最適化問題に対する問題構造とアルゴリズムの研究
 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開
+Hgformer: Hyperbolic Graph Transformer for Collaborative Filtering Yang Xin; Li Xingrun; Chang Heng; Jinze Yang; Yang X... Proceedings of the 42nd International Conference on Machine Learning/pp.70813-70832, 2025-11
+Graph-Topological Deep Detector for Cross-Platform Forest Point Clouds Yiliu Tan; Yang Xin; Xu Xin; Zhang Jingyi; Cao Yunji... Proceedings of the 2025 8th International Conference on Computational Intelligence and Intelligent Systems/pp.15-22, 2026-02
+Locker-based Drone Delivery with Battery Swapping Stations: A Joint Routing-Recharging Optimization Wushuang Wang; Yiliu Tan; Yu Li; 繁野 麻衣子 Proceedings of the 2025 8th International Conference on Computational Intelligence and Intelligent Systems/pp.88-95, 2026-02
+EONにおける通信要求の保持時間を考慮した予約種別リソース割り当て戦略の提案 李 宗晟; 繁野 麻衣子 信学技報,/125(146)/pp.27-32, 2025-08
+TLNet : A deep learning framework for tree detection in forest point clouds using multi-layered forest structure Tan Yiliu; Yang Xin; Zhang Jingyi; Xu Xin; Cao Yunji... ISPRS JOURNAL OF PHOTOGRAMMETRY AND REMOTE SENSING/234/pp.227-241, 2026-04
+Transformer-pointer DRL model for static resource allocation problems in SDM-EONs Chen Sibo; Wang Jiading; Shigeno Maiko JOURNAL OF OPTICAL COMMUNICATIONS AND NETWORKING/18(3)/pp.315-328, 2026-03
+Selection of candidate paths based on diversity in resource allocation problems on optical networks Mori Yuta; Shigeno Maiko OPTICAL SWITCHING AND NETWORKING/58, 2025-12
+Mathematical models for carpooling considering driver absence: Comparative analysis and heuristic strategies Wang Wushuang; Li Yu; Tan Yiliu; Kobayashi Ryotaro; H... COMPUTERS &amp; INDUSTRIAL ENGINEERING/210, 2025-12
 A Deep Reinforcement Learning Approach with Pointer Networks for Resource Allocation Problems in SDM-EONs Chen Sibo; Wang Jiading; SHIGENO Maiko 2024 IEEE Opto-Electronics and Communications Conference (OECC)/pp.1-3, 2024-6
 Break maximization for round-robin tournaments without consecutive breaks Xue Fei; Ma Hajunfu; Shigeno Maiko OPERATIONS RESEARCH LETTERS/57, 2024-11
 Optimizing long-term carpooling with fairness: A collaborative Jaya algorithm Li Yu; Wang Wushuang; Hashikami Hidenobu; Shigeno Maiko COMPUTERS &amp; INDUSTRIAL ENGINEERING/198, 2024-12
@@ -11164,15 +11231,7 @@
 Solving the Static Resource-Allocation Problem in SDM-EONs via a Node-Type ILP Model Wang Jiading; Chen Sibo; Wu Qian; Tan Yiliu; Shigeno ... SENSORS/22(24), 2022-12
 Safe Route Carpooling to Avoid Accident Locations and Small-Scale Proof of Concept in Japan Hashikami Hidenobu; Kobayashi Ryotaro; Li Yu; Nakano ... IEEE TRANSACTIONS ON SYSTEMS MAN CYBERNETICS-SYSTEMS/53(7)/pp.4239-4250, 2023-07
 Home away table classification and carry-over effect values minimization under restricted breaks for round-robin tournament Xue Fei; Ma Haijunfu; Shigeno Maiko JOURNAL OF ADVANCED MECHANICAL DESIGN SYSTEMS AND MANUFACTURING/16(4), 2022
-交換移植制度におけるドミナントマッチングの適用可能性 臼井 颯汰; 栗野 盛光; 大藤 剛宏; 繁野 麻衣子 日本オペレーションズ・リサーチ学会和文論文誌/pp.1-21, 2022
-Network Design Models with Partial Protection Schemes against Multiple Failures under Optical- Channel Data Unit Constraints Yiliu Tan; Qian Wu; Yoshiki Nakano; Jiading Wang; Shigeno... Proceedings of 2021 IEEE 6th Optoelectronics Global Conference/pp.38-46, 2021
-ILP models and improved methods for the problem of routing and spectrum allocation Wang Jiading; Shigeno Maiko; Wu Qian Optical Switching and Networking/45/pp.100675-100675, 2022
-A novel channel-based model for the problem of routing, space, and spectrum assignment Wu Qian; Wang Jiading; Shigeno Maiko OPTICAL SWITCHING AND NETWORKING/43, 2022-02
-NASH EQUILIBRIA FOR INFORMATION DIFFUSION GAMES ON WEIGHTED CYCLES AND PATHS Li Tianyang; Shigeno Maiko 日本オペレーションズ・リサーチ学会論文誌/64(1)/pp.1-11, 2021 CiNii
-Strongly separable matrices for nonadaptive combinatorial group testing Fan Jinping; Fu Hung-Lin; Gu Yujie; Miao Ying; Shigen... DISCRETE APPLIED MATHEMATICS/291/pp.180-187, 2021-03
-Modeling and Evaluating Taxi Ride-sharing for Event Trips Yoshida Taketo; Yano Masaki; Horikawa Kenichiro; Sato Ke... IPSJ Transactions on Mathematical Modeling and Its Applications/12/pp.10-11, 2019
-不均衡データに対する多段階学習を用いた アンサンブルモデルによる2 クラス分類アルゴリズムの提案 藤原和樹; 繁野 麻衣子; 住田潮 情報処理学会論文誌，数理モデル化と応用（TOM）/12(3)/pp.10-17, 2019
-A New Approach for Developing Segmentation Algorithms for Strongly Imbalanced Data Fujiwara Kazuki; Shigeno Maiko; Sumita Ushio IEEE ACCESS/7/pp.82970-82977, 2019</t>
+交換移植制度におけるドミナントマッチングの適用可能性 臼井 颯汰; 栗野 盛光; 大藤 剛宏; 繁野 麻衣子 日本オペレーションズ・リサーチ学会和文論文誌/pp.1-21, 2022</t>
         </is>
       </c>
     </row>
@@ -11226,6 +11285,8 @@
 犯罪科学
 空間情報科学
 環境心理学
+非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06
 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06
@@ -11248,9 +11309,7 @@
 子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10
 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10
 Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10
-筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10
-GPSログに基づく行動推定データを用いた人々の社会的接触可能性の時空間的把握 米田 有希; 雨宮 護 地理情報システム学会講演論文集/33, 2024-10
-サイバー・フィジカル空間上の社会的交流と居住地の近隣環境 尾藤 皓太朗; 雨宮 護; 島田 貴仁 MERA Journal=人間・環境学会誌/27(1)/pp.101-101, 2024-09-30</t>
+筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11270,7 +11329,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06 / 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06 / 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 雨宮 護; 鈴木 あい; 田村 孝浩; 御田 成顕; 島田 貴仁; 栗田 英治 2025年度農村計画学会全国大会学術研究発表会企画セッション梗概集/pp.70-71, 2025-11-29 / Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09 / 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して 井上 皓介; 雨宮 護; 大山 智也; 中野 裕貴 都市計画論文集/60(3)/pp.1604-1611, 2025-10 / 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 高橋 南織; 雨宮 護 都市計画論文集/60(3)/pp.650-656, 2025-10 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10 / 人口低密度地域における人々の活動から見た「都市の活力」の計測 米田 有希; 雨宮 護; 森山 拓洋 都市計画論文集/60(3)/pp.1658-1665, 2025-10 / 全国のJAを対象とする果物盗被害に関するアンケート調査報告 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 都市計画報告集/24(2)/pp.318-321, 2025-09 / Regional variations in key factors of children's independent mobility across Japan HINO Kimihiro; AMEMIYA Mamoru; YOSHIKI Syuji; ZHENG Erli Journal of Transport &amp; Health/44, 2025-09 / 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 佐光 未帆; 雨宮 護 環境心理学研究/13(1)/pp.48-48, 2025-05-28 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 李 超群; 雨宮 護 環境心理学研究/13(1)/pp.44-44, 2025-05-28 / Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives SUZUKI Ai; AMEMIYA Mamoru; KURITA Hideharu; SHIMADA T... International Journal of Rural Criminology/9(1)/pp.77-104, 2025-04 / Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05 / Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits Zheng Xinrui; Amemiya Mamoru TRANSACTIONS IN GIS/29(1), 2025-02 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya Ohyama 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12 / 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 市川 はるひ; 雨宮 護 IPA日本支部研究集会発表要旨集/pp.４-4, 2024-12 / GPSロガーを用いた官民による果樹盗パトロールの計測 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 Research Abstracts on Spatial Information Science CSIS DAYS 2024/D13, 2024-11-15 / 子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10 / 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10 / Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10 / 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10 / GPSログに基づく行動推定データを用いた人々の社会的接触可能性の時空間的把握 米田 有希; 雨宮 護 地理情報システム学会講演論文集/33, 2024-10 / サイバー・フィジカル空間上の社会的交流と居住地の近隣環境 尾藤 皓太朗; 雨宮 護; 島田 貴仁 MERA Journal=人間・環境学会誌/27(1)/pp.101-101, 2024-09-30</t>
+          <t>非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17 / 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06 / 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06 / 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 雨宮 護; 鈴木 あい; 田村 孝浩; 御田 成顕; 島田 貴仁; 栗田 英治 2025年度農村計画学会全国大会学術研究発表会企画セッション梗概集/pp.70-71, 2025-11-29 / Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09 / 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して 井上 皓介; 雨宮 護; 大山 智也; 中野 裕貴 都市計画論文集/60(3)/pp.1604-1611, 2025-10 / 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 高橋 南織; 雨宮 護 都市計画論文集/60(3)/pp.650-656, 2025-10 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10 / 人口低密度地域における人々の活動から見た「都市の活力」の計測 米田 有希; 雨宮 護; 森山 拓洋 都市計画論文集/60(3)/pp.1658-1665, 2025-10 / 全国のJAを対象とする果物盗被害に関するアンケート調査報告 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 都市計画報告集/24(2)/pp.318-321, 2025-09 / Regional variations in key factors of children's independent mobility across Japan HINO Kimihiro; AMEMIYA Mamoru; YOSHIKI Syuji; ZHENG Erli Journal of Transport &amp; Health/44, 2025-09 / 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 佐光 未帆; 雨宮 護 環境心理学研究/13(1)/pp.48-48, 2025-05-28 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 李 超群; 雨宮 護 環境心理学研究/13(1)/pp.44-44, 2025-05-28 / Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives SUZUKI Ai; AMEMIYA Mamoru; KURITA Hideharu; SHIMADA T... International Journal of Rural Criminology/9(1)/pp.77-104, 2025-04 / Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05 / Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits Zheng Xinrui; Amemiya Mamoru TRANSACTIONS IN GIS/29(1), 2025-02 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya Ohyama 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12 / 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 市川 はるひ; 雨宮 護 IPA日本支部研究集会発表要旨集/pp.４-4, 2024-12 / GPSロガーを用いた官民による果樹盗パトロールの計測 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 Research Abstracts on Spatial Information Science CSIS DAYS 2024/D13, 2024-11-15 / 子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10 / 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10 / Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10 / 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -11366,6 +11425,8 @@
 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究
 集合住宅における子ども・女性に対する犯罪の実態分析と対策立案
 地理的犯罪予測の手法構築‐学際研究と産官学連携による学術基盤の確立とシステム開発
+非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06
 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06
@@ -11388,9 +11449,7 @@
 子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10
 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10
 Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10
-筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10
-GPSログに基づく行動推定データを用いた人々の社会的接触可能性の時空間的把握 米田 有希; 雨宮 護 地理情報システム学会講演論文集/33, 2024-10
-サイバー・フィジカル空間上の社会的交流と居住地の近隣環境 尾藤 皓太朗; 雨宮 護; 島田 貴仁 MERA Journal=人間・環境学会誌/27(1)/pp.101-101, 2024-09-30</t>
+筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11486,8 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として―
+          <t>更生支援者への支援および地域住民の誤解・偏見の是正と参加・協力促進のモデル化
+過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として―
 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討
 リアルタイム場面におけるサービス・インタラクション理論の構築と実証
 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学
@@ -11470,7 +11530,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として― / 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討 / リアルタイム場面におけるサービス・インタラクション理論の構築と実証 / 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 / 慢性ストレスがヒトの生理心理状態に与える影響とその対処法 / 犯罪不安に関する認知・感情プロセスのモデル化とその応用 / 逸脱行動が生起するプロセスと矯正方法に関する研究 / 進路意思決定における認知・感情過程のモデル化 / 教師教育教材を事例としたマルチメディア教材設計・評価手法の開発</t>
+          <t>更生支援者への支援および地域住民の誤解・偏見の是正と参加・協力促進のモデル化 / 過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として― / 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討 / リアルタイム場面におけるサービス・インタラクション理論の構築と実証 / 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 / 慢性ストレスがヒトの生理心理状態に与える影響とその対処法 / 犯罪不安に関する認知・感情プロセスのモデル化とその応用 / 逸脱行動が生起するプロセスと矯正方法に関する研究 / 進路意思決定における認知・感情過程のモデル化 / 教師教育教材を事例としたマルチメディア教材設計・評価手法の開発</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -11559,6 +11619,7 @@
 読書状況が変えるネタバレ選好
 グリーン購入における他者の影響
 An Investigation of the Factors Influencing college student Volunteering motivation - In Perspectives on prosocial behaviour
+更生支援者への支援および地域住民の誤解・偏見の是正と参加・協力促進のモデル化
 過剰接客サービス存在時のIT活用―小売業でのRFID動線を対象として―
 慢性ストレスが生体リズムに影響を与えるまでのタイムラグの検討
 リアルタイム場面におけるサービス・インタラクション理論の構築と実証
@@ -11849,9 +11910,14 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-=085$.$0,FUQ6.O768.8%$O$&amp;O-3\
+2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q
+5^
 都市農村計画
 緑地計画
+Memorable Places on Campuses Across Generations Janpathompong Dalin; Anantsuksomsri Sutee; MURAKAMI Ak... Journal of Architectural/Planning Research and Studies (JARS)/23(1)/pp.278-289, 2026-01
+企業の情報開示における企業緑地に関する第三者認証取得事実の取り扱いに関する研究 斎藤 すみれ; 植田 直樹; 村上 暁信 都市計画論文集/60(3)/pp.735-742, 2025-04-30
+グリーンをインフラたらしめる 村上 暁信 都市計画 = City planning review / 日本都市計画学会 編/74(6)/pp.16-19, 2025-11
+優良緑地確保計画認定制度（TSUNAG）における緑地の機能評価手法と今後の展望 村上 暁信; 柳井 重人; 小笠原 奨悟; 増澤 直; 守谷 修; 福塚 祐子 ランドスケープ研究/89(3)/pp.238-241, 2025-11-01
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
 熱的快適性が屋外空間における滞在状態に与える影響に関する研究 クワン グエン ヒュー; 村上 暁信 ランドスケープ研究/88(5)/pp.545-550, 2024
 グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所研究報告 = Report of the National Research Institute for Earth Science and Disaster Resilience / 防災科学技術研究所編集委員会 編/(86-88)/pp.33-44, 2024-06
@@ -11872,11 +11938,7 @@
 ランドスケープ分野におけるDX 村上 暁信 ランドスケープ研究 : 日本造園学会会誌 : journal of the Japanese Institute of Landscape Architecture/87(3)/pp.188-193, 2023-11
 グリーンインフラとしての平地林による防災機能 －災害現場で確認された農業気象災害軽減事例－ 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所 研究報告/(88)/pp.33-44, 2023-12-08
 移動の体験と景観 村上 暁信 IATSS Review（国際交通安全学会誌）/48(3)/p.149, 2024-02-29
-企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ 植田 直樹; 菊池 佐智子; 村上 暁信 都市計画報告集/22(4)/pp.586-591, 2024-03-11
-屋外空間利用がオフィスワーカーに与える心理・生理的影響とその要因に関する研究 池田 千紘; 村上 暁信 環境情報科学/53(1)/pp.128-128, 2024-04-15
-人流ビッグデータを用いた「Natural Cities」と温熱環境の関係分析についての研究 QUANG Nguyen Huu; 村上 暁信 環境情報科学/53(1)/pp.131-131, 2024-04-15
-季節の違いが緑化に対する支払意思額に与える影響 花田 大地; 村上 暁信 環境情報科学/53(1)/pp.115-115, 2024-04-15
-地域・土地との関係性の希薄化 村上 暁信 IATSS Review（国際交通安全学会誌）/49(1)/pp.106-107, 2024-06-30</t>
+企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ 植田 直樹; 菊池 佐智子; 村上 暁信 都市計画報告集/22(4)/pp.586-591, 2024-03-11</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -11886,7 +11948,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / =085$.$0,FUQ6.O768.8%$O$&amp;O-3\</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q / 5^</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11896,7 +11958,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024 / 熱的快適性が屋外空間における滞在状態に与える影響に関する研究 クワン グエン ヒュー; 村上 暁信 ランドスケープ研究/88(5)/pp.545-550, 2024 / グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所研究報告 = Report of the National Research Institute for Earth Science and Disaster Resilience / 防災科学技術研究所編集委員会 編/(86-88)/pp.33-44, 2024-06 / 2023年度一般公開シンポジウム開催報告 上田 康治; 村上 暁信; 堀井 亮; 小谷 幸司; 村山 武彦; 大倉 紀彰 環境情報科学/53(2)/pp.65-73, 2024-07-15 / 座談会 「緑の基本計画」のこれからを考える座談会 : 制度創設30年目を迎えて 村上 暁信; 飯田 晶子; 根岸 勇太; 山田 順之; 永井 淳一; 望月 一彦; 古澤 達也 公園緑地 = Parks and open space/85(3)/pp.29-36, 2024-11 / 量から質への転換 村上 暁信 グリーン・エージ = Green age/52(1)/pp.26-29, 2025-01 / 人と土地の関係を創造するよろこび 村上 暁信 ランドスケープ研究/88(4)/pp.338-339, 2025-02-01 / 「働くクルマと社会」特集にあたって 村上 暁信 IATSS Review（国際交通安全学会誌）/49(3)/pp.278-279, 2025-02-28 / GPSデータを用いたスポーツイベント来場者の行動分析 上山 滉介; 村上 暁信; Sunyong Eom 環境情報科学/54(1)/p.122, 2025-04-30 / 企業のIR情報に見る都市緑地に関する第三者認証制度の取り扱いに関する研究 斎藤 すみれ; 植田 直樹; 村上 暁信 環境情報科学/54(1)/p.104, 2025-04-30 / 熱赤外域リモートセンシングデータを活用した市街地の土地被覆に関する研究 徐 伍華; 村上 暁信 環境情報科学/54(1)/p.113, 2025-04-30 / 熱的快適性が屋外空間における滞在に与える影響に関する研究 QUANG Nguyen Huu; 村上 暁信 環境情報科学/54(1)/p.102, 2025-04-30 / 可視化された温熱環境情報が屋外空間の利用に与える影響に関する研究 深谷恭平; 村上 暁信 都市計画論文集/58(3)/pp.1439-1445, 2023-10 / An Empirical Study on Using Green Spaces Around an Office as Workplace in Summer: Considerations Based on Office Employees’ Trait Anxiety Tendencies Umehara Mizuki; Arai Naomi; Komori Misaki; Takeda Eri... Journal of the Human-Environment System/26(1)/pp.1-10, 2024-03 / グリーンインフラと緑の基本計画 村上 暁信 公園緑地 = Parks and open space/84(2)/pp.36-39, 2023-08 / これからの自律的な民間緑地整備に関する考察 植田 直樹; 村上 暁信; 横張 真 都市計画報告集/22(2)/pp.194-197, 2023-09-07 / ノルウェーにおける地表面での雨水管理策に関する法改正における議論の特徴 木藤 健二郎; 村上 暁信 都市計画論文集/58(3)/pp.1485-1492, 2023-10-25 / ランドスケープ分野におけるDX 村上 暁信 ランドスケープ研究 : 日本造園学会会誌 : journal of the Japanese Institute of Landscape Architecture/87(3)/pp.188-193, 2023-11 / グリーンインフラとしての平地林による防災機能 －災害現場で確認された農業気象災害軽減事例－ 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所 研究報告/(88)/pp.33-44, 2023-12-08 / 移動の体験と景観 村上 暁信 IATSS Review（国際交通安全学会誌）/48(3)/p.149, 2024-02-29 / 企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ 植田 直樹; 菊池 佐智子; 村上 暁信 都市計画報告集/22(4)/pp.586-591, 2024-03-11 / 屋外空間利用がオフィスワーカーに与える心理・生理的影響とその要因に関する研究 池田 千紘; 村上 暁信 環境情報科学/53(1)/pp.128-128, 2024-04-15 / 人流ビッグデータを用いた「Natural Cities」と温熱環境の関係分析についての研究 QUANG Nguyen Huu; 村上 暁信 環境情報科学/53(1)/pp.131-131, 2024-04-15 / 季節の違いが緑化に対する支払意思額に与える影響 花田 大地; 村上 暁信 環境情報科学/53(1)/pp.115-115, 2024-04-15 / 地域・土地との関係性の希薄化 村上 暁信 IATSS Review（国際交通安全学会誌）/49(1)/pp.106-107, 2024-06-30</t>
+          <t>Memorable Places on Campuses Across Generations Janpathompong Dalin; Anantsuksomsri Sutee; MURAKAMI Ak... Journal of Architectural/Planning Research and Studies (JARS)/23(1)/pp.278-289, 2026-01 / 企業の情報開示における企業緑地に関する第三者認証取得事実の取り扱いに関する研究 斎藤 すみれ; 植田 直樹; 村上 暁信 都市計画論文集/60(3)/pp.735-742, 2025-04-30 / グリーンをインフラたらしめる 村上 暁信 都市計画 = City planning review / 日本都市計画学会 編/74(6)/pp.16-19, 2025-11 / 優良緑地確保計画認定制度（TSUNAG）における緑地の機能評価手法と今後の展望 村上 暁信; 柳井 重人; 小笠原 奨悟; 増澤 直; 守谷 修; 福塚 祐子 ランドスケープ研究/89(3)/pp.238-241, 2025-11-01 / グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024 / 熱的快適性が屋外空間における滞在状態に与える影響に関する研究 クワン グエン ヒュー; 村上 暁信 ランドスケープ研究/88(5)/pp.545-550, 2024 / グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所研究報告 = Report of the National Research Institute for Earth Science and Disaster Resilience / 防災科学技術研究所編集委員会 編/(86-88)/pp.33-44, 2024-06 / 2023年度一般公開シンポジウム開催報告 上田 康治; 村上 暁信; 堀井 亮; 小谷 幸司; 村山 武彦; 大倉 紀彰 環境情報科学/53(2)/pp.65-73, 2024-07-15 / 座談会 「緑の基本計画」のこれからを考える座談会 : 制度創設30年目を迎えて 村上 暁信; 飯田 晶子; 根岸 勇太; 山田 順之; 永井 淳一; 望月 一彦; 古澤 達也 公園緑地 = Parks and open space/85(3)/pp.29-36, 2024-11 / 量から質への転換 村上 暁信 グリーン・エージ = Green age/52(1)/pp.26-29, 2025-01 / 人と土地の関係を創造するよろこび 村上 暁信 ランドスケープ研究/88(4)/pp.338-339, 2025-02-01 / 「働くクルマと社会」特集にあたって 村上 暁信 IATSS Review（国際交通安全学会誌）/49(3)/pp.278-279, 2025-02-28 / GPSデータを用いたスポーツイベント来場者の行動分析 上山 滉介; 村上 暁信; Sunyong Eom 環境情報科学/54(1)/p.122, 2025-04-30 / 企業のIR情報に見る都市緑地に関する第三者認証制度の取り扱いに関する研究 斎藤 すみれ; 植田 直樹; 村上 暁信 環境情報科学/54(1)/p.104, 2025-04-30 / 熱赤外域リモートセンシングデータを活用した市街地の土地被覆に関する研究 徐 伍華; 村上 暁信 環境情報科学/54(1)/p.113, 2025-04-30 / 熱的快適性が屋外空間における滞在に与える影響に関する研究 QUANG Nguyen Huu; 村上 暁信 環境情報科学/54(1)/p.102, 2025-04-30 / 可視化された温熱環境情報が屋外空間の利用に与える影響に関する研究 深谷恭平; 村上 暁信 都市計画論文集/58(3)/pp.1439-1445, 2023-10 / An Empirical Study on Using Green Spaces Around an Office as Workplace in Summer: Considerations Based on Office Employees’ Trait Anxiety Tendencies Umehara Mizuki; Arai Naomi; Komori Misaki; Takeda Eri... Journal of the Human-Environment System/26(1)/pp.1-10, 2024-03 / グリーンインフラと緑の基本計画 村上 暁信 公園緑地 = Parks and open space/84(2)/pp.36-39, 2023-08 / これからの自律的な民間緑地整備に関する考察 植田 直樹; 村上 暁信; 横張 真 都市計画報告集/22(2)/pp.194-197, 2023-09-07 / ノルウェーにおける地表面での雨水管理策に関する法改正における議論の特徴 木藤 健二郎; 村上 暁信 都市計画論文集/58(3)/pp.1485-1492, 2023-10-25 / ランドスケープ分野におけるDX 村上 暁信 ランドスケープ研究 : 日本造園学会会誌 : journal of the Japanese Institute of Landscape Architecture/87(3)/pp.188-193, 2023-11 / グリーンインフラとしての平地林による防災機能 －災害現場で確認された農業気象災害軽減事例－ 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所 研究報告/(88)/pp.33-44, 2023-12-08 / 移動の体験と景観 村上 暁信 IATSS Review（国際交通安全学会誌）/48(3)/p.149, 2024-02-29 / 企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ 植田 直樹; 菊池 佐智子; 村上 暁信 都市計画報告集/22(4)/pp.586-591, 2024-03-11</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -11906,7 +11968,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; =085$.$0,FUQ6.O768.8%$O$&amp;O-3\ ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q ; 5^ ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -11929,7 +11991,8 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-=085$.$0,FUQ6.O768.8%$O$&amp;O-3\
+2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q
+5^
 都市農村計画
 緑地計画
 都市・地域政策
@@ -11997,6 +12060,10 @@
 量から質へのシフトを実現するための緑地の計画制度・設計手法・運用方法の研究
 樹冠表面温度を利用した都市気温分布図の作成と緑地の気候緩和機能の分析
 リモートセンシングを活用した生物季節学図の作成と都市微気候の評価
+Memorable Places on Campuses Across Generations Janpathompong Dalin; Anantsuksomsri Sutee; MURAKAMI Ak... Journal of Architectural/Planning Research and Studies (JARS)/23(1)/pp.278-289, 2026-01
+企業の情報開示における企業緑地に関する第三者認証取得事実の取り扱いに関する研究 斎藤 すみれ; 植田 直樹; 村上 暁信 都市計画論文集/60(3)/pp.735-742, 2025-04-30
+グリーンをインフラたらしめる 村上 暁信 都市計画 = City planning review / 日本都市計画学会 編/74(6)/pp.16-19, 2025-11
+優良緑地確保計画認定制度（TSUNAG）における緑地の機能評価手法と今後の展望 村上 暁信; 柳井 重人; 小笠原 奨悟; 増澤 直; 守谷 修; 福塚 祐子 ランドスケープ研究/89(3)/pp.238-241, 2025-11-01
 グリーンインフラ整備を支える緑化技術研究 村上 暁信 都市緑化技術/(127)/p.1, 2024
 熱的快適性が屋外空間における滞在状態に与える影響に関する研究 クワン グエン ヒュー; 村上 暁信 ランドスケープ研究/88(5)/pp.545-550, 2024
 グリーンインフラとしての平地林による防災機能 : 災害現場で確認された農業気象災害軽減事例 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所研究報告 = Report of the National Research Institute for Earth Science and Disaster Resilience / 防災科学技術研究所編集委員会 編/(86-88)/pp.33-44, 2024-06
@@ -12017,11 +12084,7 @@
 ランドスケープ分野におけるDX 村上 暁信 ランドスケープ研究 : 日本造園学会会誌 : journal of the Japanese Institute of Landscape Architecture/87(3)/pp.188-193, 2023-11
 グリーンインフラとしての平地林による防災機能 －災害現場で確認された農業気象災害軽減事例－ 横山 仁; 鈴木 真一; 飯塚 聡; 内山 庄一郎; 岩波 越; 村上 暁信 防災科学技術研究所 研究報告/(88)/pp.33-44, 2023-12-08
 移動の体験と景観 村上 暁信 IATSS Review（国際交通安全学会誌）/48(3)/p.149, 2024-02-29
-企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ 植田 直樹; 菊池 佐智子; 村上 暁信 都市計画報告集/22(4)/pp.586-591, 2024-03-11
-屋外空間利用がオフィスワーカーに与える心理・生理的影響とその要因に関する研究 池田 千紘; 村上 暁信 環境情報科学/53(1)/pp.128-128, 2024-04-15
-人流ビッグデータを用いた「Natural Cities」と温熱環境の関係分析についての研究 QUANG Nguyen Huu; 村上 暁信 環境情報科学/53(1)/pp.131-131, 2024-04-15
-季節の違いが緑化に対する支払意思額に与える影響 花田 大地; 村上 暁信 環境情報科学/53(1)/pp.115-115, 2024-04-15
-地域・土地との関係性の希薄化 村上 暁信 IATSS Review（国際交通安全学会誌）/49(1)/pp.106-107, 2024-06-30</t>
+企業の緑地創出と維持管理に関する第三者認証取得行動に関する研究 －SEGESとABINCを題材に－ 植田 直樹; 菊池 佐智子; 村上 暁信 都市計画報告集/22(4)/pp.586-591, 2024-03-11</t>
         </is>
       </c>
     </row>
@@ -12071,8 +12134,11 @@
 数理情報学
 社会システム工学・安全システム
 応用確率論、 確率モデル、 待ち行列理論、 性能評価、 オペレーションズ・リサーチ、確率システム
-Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03
-Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03
+Retrial Queues: Scaling Limits Tuan Phung-Duc Journal of Systems Scalability/1(2)/pp.39-42, 2026-04
+Analysis of Multiserver Queues with Batch Arrivals and Setup Times Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.128-137, 2026-02
+Multi-Server Queues with s-staggered Setup: A Faster Computational Approach Thu Le-Anh; Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.118-127, 2026-02
+Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03 Tsukuba Repository
+Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03 Tsukuba Repository
 A simulation study of the sojourn time in queueing systems with stochastically delayed information Kazuma Abe; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering, 2025-12
 Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Proceedings of 2025 International Symposium on Nonlinear Theory and Its Applications (Nolta 2025)/pp.526-529, 2025-10
 Performance Analysis of Blockchain with Rollups Yusei Funahashi; Tuan Phung-Duc Proceedings of Asia-Pacific Conference on Communications (APCC) 2025, 2025-11 Tsukuba Repository
@@ -12092,10 +12158,7 @@
 Modeling and performance analysis of hybrid systems by queues with setup time Mitsuki Sato; Kohei Kawamura; Ken’ichi Kawanishi; Tuan... PERFORMANCE EVALUATION/162(102366), 2023-11
 Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis Yi Ren; Tuan Phung-Duc; Jyh-Cheng Chen; Frank Y. Li IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY/72(6)/pp.7743-7756, 2023-01
 Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04
-To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository
-A Two-Population Game in Observable Double-Ended Queueing Systems Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(4)/pp.407-414, 2022-07 Tsukuba Repository
-Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems Hung Quoc Nguyen; Tuan Phung-Duc COMPUTERS &amp; INDUSTRIAL ENGINEERING/170, 2022-08
-Analysis of a Batch Arrival Queue with Power Saving Mode Yuta Sakai; Tuan Phung-Duc Proceedings of 24th International Conference on INFORMATION TECHNOLOGIES AND MATHEMATICAL MODELLING (IТММ – 2025)/pp.70-75, 2024-10</t>
+To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -12115,7 +12178,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03 / Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03 / A simulation study of the sojourn time in queueing systems with stochastically delayed information Kazuma Abe; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering, 2025-12 / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Proceedings of 2025 International Symposium on Nonlinear Theory and Its Applications (Nolta 2025)/pp.526-529, 2025-10 / Performance Analysis of Blockchain with Rollups Yusei Funahashi; Tuan Phung-Duc Proceedings of Asia-Pacific Conference on Communications (APCC) 2025, 2025-11 Tsukuba Repository / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times Nguyen Hung Q.; Phung-Duc Tuan Operations Research Letters/63(107362), 2025-11 Tsukuba Repository / Analysis of a Batch Arrival Queue with Power Saving Mode Yuta Sakai; Tuan Phung-Duc Communications in Computer and Information Science/2472/pp.181-192, 2025-05 / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes Thu Le-Anh; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering/663/pp.142-157, 2026-01 Tsukuba Repository / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes Thu Le-Anh; Tuan Phung-Duc Proceedings of 36th International Teletraffic Congress, 2025-06 Tsukuba Repository / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory Koki Inami; Tuan Phung-Duc Mathematics/13(6)/pp.1010-1-1010-18, 2025-03 Tsukuba Repository / Analytical Modelling of Asymmetric Multi-core Servers Marco Gribaudo; Tuan Phung-Duc Lecture Notes in Computer Science/15454/pp.121-136, 2025-02 / Energy-performance tradeoffs in server farms with batch services and setup times Le-Anh Thu; Phung-Duc Tuan PERFORMANCE EVALUATION/168, 2025-06 Tsukuba Repository / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers Nakamura Ayane; Phung-Duc Tuan TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/171, 2025-02 Tsukuba Repository / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Mathematics/12(18)/pp.2820-1-2820-27, 2024-09 / Queueing Analysis of an Ensemble Machine Learning System Keishin Tsutsumi; Tuan Phung-Duc; Hong-Linh Truong Lecture Notes in Computer Science/14826/pp.97-111, 2024-09 / Performance analysis of a collision channel with abandonments Fiems Dieter; Tuan Phung-Duc PERFORMANCE EVALUATION/165(102424), 2024-08 / Empirical architecture comparison of two-input machine learning systems for vision tasks Kazuya Wakigami; Fumio Machida; Tuan Phung-Duc Formal Aspects of Computing/36(4), 2024-06 / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes Ayane Nakamura; Tuan Phung-Duc QUEUEING SYSTEMS/106(1-2)/pp.129-158, 2023-11 / Modeling and performance analysis of hybrid systems by queues with setup time Mitsuki Sato; Kohei Kawamura; Ken’ichi Kawanishi; Tuan... PERFORMANCE EVALUATION/162(102366), 2023-11 / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis Yi Ren; Tuan Phung-Duc; Jyh-Cheng Chen; Frank Y. Li IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY/72(6)/pp.7743-7756, 2023-01 / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04 / To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository / A Two-Population Game in Observable Double-Ended Queueing Systems Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(4)/pp.407-414, 2022-07 Tsukuba Repository / Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems Hung Quoc Nguyen; Tuan Phung-Duc COMPUTERS &amp; INDUSTRIAL ENGINEERING/170, 2022-08 / Analysis of a Batch Arrival Queue with Power Saving Mode Yuta Sakai; Tuan Phung-Duc Proceedings of 24th International Conference on INFORMATION TECHNOLOGIES AND MATHEMATICAL MODELLING (IТММ – 2025)/pp.70-75, 2024-10</t>
+          <t>Retrial Queues: Scaling Limits Tuan Phung-Duc Journal of Systems Scalability/1(2)/pp.39-42, 2026-04 / Analysis of Multiserver Queues with Batch Arrivals and Setup Times Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.128-137, 2026-02 / Multi-Server Queues with s-staggered Setup: A Faster Computational Approach Thu Le-Anh; Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.118-127, 2026-02 / Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03 Tsukuba Repository / Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03 Tsukuba Repository / A simulation study of the sojourn time in queueing systems with stochastically delayed information Kazuma Abe; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering, 2025-12 / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Proceedings of 2025 International Symposium on Nonlinear Theory and Its Applications (Nolta 2025)/pp.526-529, 2025-10 / Performance Analysis of Blockchain with Rollups Yusei Funahashi; Tuan Phung-Duc Proceedings of Asia-Pacific Conference on Communications (APCC) 2025, 2025-11 Tsukuba Repository / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times Nguyen Hung Q.; Phung-Duc Tuan Operations Research Letters/63(107362), 2025-11 Tsukuba Repository / Analysis of a Batch Arrival Queue with Power Saving Mode Yuta Sakai; Tuan Phung-Duc Communications in Computer and Information Science/2472/pp.181-192, 2025-05 / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes Thu Le-Anh; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering/663/pp.142-157, 2026-01 Tsukuba Repository / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes Thu Le-Anh; Tuan Phung-Duc Proceedings of 36th International Teletraffic Congress, 2025-06 Tsukuba Repository / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory Koki Inami; Tuan Phung-Duc Mathematics/13(6)/pp.1010-1-1010-18, 2025-03 Tsukuba Repository / Analytical Modelling of Asymmetric Multi-core Servers Marco Gribaudo; Tuan Phung-Duc Lecture Notes in Computer Science/15454/pp.121-136, 2025-02 / Energy-performance tradeoffs in server farms with batch services and setup times Le-Anh Thu; Phung-Duc Tuan PERFORMANCE EVALUATION/168, 2025-06 Tsukuba Repository / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers Nakamura Ayane; Phung-Duc Tuan TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/171, 2025-02 Tsukuba Repository / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Mathematics/12(18)/pp.2820-1-2820-27, 2024-09 / Queueing Analysis of an Ensemble Machine Learning System Keishin Tsutsumi; Tuan Phung-Duc; Hong-Linh Truong Lecture Notes in Computer Science/14826/pp.97-111, 2024-09 / Performance analysis of a collision channel with abandonments Fiems Dieter; Tuan Phung-Duc PERFORMANCE EVALUATION/165(102424), 2024-08 / Empirical architecture comparison of two-input machine learning systems for vision tasks Kazuya Wakigami; Fumio Machida; Tuan Phung-Duc Formal Aspects of Computing/36(4), 2024-06 / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes Ayane Nakamura; Tuan Phung-Duc QUEUEING SYSTEMS/106(1-2)/pp.129-158, 2023-11 / Modeling and performance analysis of hybrid systems by queues with setup time Mitsuki Sato; Kohei Kawamura; Ken’ichi Kawanishi; Tuan... PERFORMANCE EVALUATION/162(102366), 2023-11 / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis Yi Ren; Tuan Phung-Duc; Jyh-Cheng Chen; Frank Y. Li IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY/72(6)/pp.7743-7756, 2023-01 / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04 / To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -12176,8 +12239,11 @@
 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化
 顧客の再試行と途中放棄を考慮したコールセンターのモデル化と性能解析
 再試行型待ち行列によるコールセンターの性能解析とサービス科学への応用
-Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03
-Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03
+Retrial Queues: Scaling Limits Tuan Phung-Duc Journal of Systems Scalability/1(2)/pp.39-42, 2026-04
+Analysis of Multiserver Queues with Batch Arrivals and Setup Times Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.128-137, 2026-02
+Multi-Server Queues with s-staggered Setup: A Faster Computational Approach Thu Le-Anh; Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.118-127, 2026-02
+Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03 Tsukuba Repository
+Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03 Tsukuba Repository
 A simulation study of the sojourn time in queueing systems with stochastically delayed information Kazuma Abe; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering, 2025-12
 Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Proceedings of 2025 International Symposium on Nonlinear Theory and Its Applications (Nolta 2025)/pp.526-529, 2025-10
 Performance Analysis of Blockchain with Rollups Yusei Funahashi; Tuan Phung-Duc Proceedings of Asia-Pacific Conference on Communications (APCC) 2025, 2025-11 Tsukuba Repository
@@ -12197,10 +12263,7 @@
 Modeling and performance analysis of hybrid systems by queues with setup time Mitsuki Sato; Kohei Kawamura; Ken’ichi Kawanishi; Tuan... PERFORMANCE EVALUATION/162(102366), 2023-11
 Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis Yi Ren; Tuan Phung-Duc; Jyh-Cheng Chen; Frank Y. Li IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY/72(6)/pp.7743-7756, 2023-01
 Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04
-To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository
-A Two-Population Game in Observable Double-Ended Queueing Systems Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(4)/pp.407-414, 2022-07 Tsukuba Repository
-Supply-Demand Equilibria and Multivariate Optimization of Social Welfare in Double-Ended Queueing Systems Hung Quoc Nguyen; Tuan Phung-Duc COMPUTERS &amp; INDUSTRIAL ENGINEERING/170, 2022-08
-Analysis of a Batch Arrival Queue with Power Saving Mode Yuta Sakai; Tuan Phung-Duc Proceedings of 24th International Conference on INFORMATION TECHNOLOGIES AND MATHEMATICAL MODELLING (IТММ – 2025)/pp.70-75, 2024-10</t>
+To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository</t>
         </is>
       </c>
     </row>
@@ -12252,6 +12315,8 @@
 産業集積
 都市・地域政策
 都市計画制度
+パネルディスカッション 未来志向のまちづくり 有田 智一; 坂井 文; 田中 仁; 山下 裕子; 大村 謙二郎 再開発コーディネーター/(240)/pp.15-28, 2026
+東京の集積の質的向上と多様性の高度化へ─土地・建物の高度利用を超えて 有田 智一 都市計画/75-3(380)/pp.18-21, 2026-05
 土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで 有田 智一 区画整理士会報/235/pp.48-52, 2025-07
 新しい時代の都市再生と公共貢献のあり方 有田 智一 新都市/79(9)/pp.13-17, 2025-09
 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 有田 智一 都市計画/pp.44-47, 2024-11
@@ -12274,9 +12339,7 @@
 “Planning transparency and public involvement in pre-application discussions,” Arita Tomokazu; Parker Gavin Journal of Town &amp; Country Planning/pp.66-70, 2019-02
 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 有田 智一 ビルディングレター/pp.16-17, 2018-05
 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) 有田 智一 都市問題/109(11)/pp.84-97, 2018-11
-集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ 梶塚 真良; 有田 智一 日本建築学会環境系論文集/83(751)/pp.791-799, 2018 CiNii Tsukuba Repository
-マイナンバー導入に伴う自治体業務情報システム改修事例に見るオープン化・標準化及び共同化の現状に関する研究 金崎健太郎; 川島宏一; 有田智一 情報システム学会誌/13(2), 2018-03
-マイナンバー導入事例に見る政府情報システム調達の現状に関する研究 金崎健太郎; 川島宏一; 有田智一 情報システム学会誌/14(1), 2018-09</t>
+集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ 梶塚 真良; 有田 智一 日本建築学会環境系論文集/83(751)/pp.791-799, 2018 CiNii Tsukuba Repository</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -12296,7 +12359,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで 有田 智一 区画整理士会報/235/pp.48-52, 2025-07 / 新しい時代の都市再生と公共貢献のあり方 有田 智一 新都市/79(9)/pp.13-17, 2025-09 / 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 有田 智一 都市計画/pp.44-47, 2024-11 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 川島 宏一; 石井樹; 有田 智一 地域安全学会論文集/(43)/pp.79-86, 2023-11 / 都市再開発のこれからの「必要性」と「可能性」 有田 智一 土地総合研究/pp.38-46, 2024-05 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 有田 智一 地域安全学会論文集 地域安全学会/43/pp.79-86, 2023-11 / 農村集落における区域区分制度を前提とした土地利用調整手法の実態と活用可能性に関する研究 有田 智一 都市計画論文集/58(3)/pp.1211-1218, 2023-10 / 土地建物一体型市街地整備の「必要性」と「可能性」 : これまでとこれから 有田 智一 区画整理/66(5)/pp.6-14, 2023-05 / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に 川島 宏一; 李珠善; 有田智一 情報処理学会研究報告, 2018-03 / つくば市による心肺停止傷病者発生位置情報の最寄AED管理者との共有が生み出す協働による救命効果に関する研究 川島 宏一; 有田 智一; 鈴木良介 計画行政/43(1)/pp.26-26, 2020-02-15 / 地方自治体におけるオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 川島 宏一; 有田智一 情報通信学会誌, 2021-09 / 東京都区部における開発実態の評価を踏まえた開発拠点誘導政策の課題に関する研究 鈴木 賢人; 有田 智一 都市計画論文集/56(3)/pp.881-888, 2021-10-25 CiNii / 公民連携による空き家・空き地対策組織の展開と運営実態 阿部 俊介; 有田 智一 都市計画論文集/56(3)/pp.1268-1274, 2021-10-25 CiNii / 避難行動要支援者名簿活用に向けた制度設計・運用プロセスにおける課題に関する研究 藤田 修平; 川島 宏一; 有田 智一; 岡本 正 地域安全学会論文集/39(0)/pp.145-153, 2021-11-01 / オープンデータ施策に総合的に取り組む地方自治体の動因に関する研究 川島 宏一; 有田智一; 野村敦子 自治体学/35(2), 2022-03 / 地方都市中心市街地における商店街の連続性を踏まえた空間整備の変遷と課題に関する研究 杉田 光; 有田 智一 都市計画報告集/21(1)/pp.57-63, 2022-06-08 / 地方自治体のオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 川島 宏一; 野村敦子; 有田智一 情報通信学会誌, 2021-09 / 世界からみた銀座のルールとガバナンス (特集 銀座と都市計画) -- (都市計画と銀座のルール) 有田 智一 都市計画 = City planning review/68(4)/pp.42-45, 2019-07-15 CiNii / 11027 地区スケールの賑わい空間構造の定量分析に関する研究 歩行空間と周辺土地利用に着目して 鈴木 賢人; 有田 智一 情報システム技術/(2019)/pp.53-54, 2019-07-20 CiNii / “Planning transparency and public involvement in pre-application discussions,” Arita Tomokazu; Parker Gavin Journal of Town &amp; Country Planning/pp.66-70, 2019-02 / 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 有田 智一 ビルディングレター/pp.16-17, 2018-05 / 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) 有田 智一 都市問題/109(11)/pp.84-97, 2018-11 / 集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ 梶塚 真良; 有田 智一 日本建築学会環境系論文集/83(751)/pp.791-799, 2018 CiNii Tsukuba Repository / マイナンバー導入に伴う自治体業務情報システム改修事例に見るオープン化・標準化及び共同化の現状に関する研究 金崎健太郎; 川島宏一; 有田智一 情報システム学会誌/13(2), 2018-03 / マイナンバー導入事例に見る政府情報システム調達の現状に関する研究 金崎健太郎; 川島宏一; 有田智一 情報システム学会誌/14(1), 2018-09</t>
+          <t>パネルディスカッション 未来志向のまちづくり 有田 智一; 坂井 文; 田中 仁; 山下 裕子; 大村 謙二郎 再開発コーディネーター/(240)/pp.15-28, 2026 / 東京の集積の質的向上と多様性の高度化へ─土地・建物の高度利用を超えて 有田 智一 都市計画/75-3(380)/pp.18-21, 2026-05 / 土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで 有田 智一 区画整理士会報/235/pp.48-52, 2025-07 / 新しい時代の都市再生と公共貢献のあり方 有田 智一 新都市/79(9)/pp.13-17, 2025-09 / 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 有田 智一 都市計画/pp.44-47, 2024-11 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 川島 宏一; 石井樹; 有田 智一 地域安全学会論文集/(43)/pp.79-86, 2023-11 / 都市再開発のこれからの「必要性」と「可能性」 有田 智一 土地総合研究/pp.38-46, 2024-05 / 実効性のある避難支援実現に向けた個別避難計画作成における方針と課題に関する研究 有田 智一 地域安全学会論文集 地域安全学会/43/pp.79-86, 2023-11 / 農村集落における区域区分制度を前提とした土地利用調整手法の実態と活用可能性に関する研究 有田 智一 都市計画論文集/58(3)/pp.1211-1218, 2023-10 / 土地建物一体型市街地整備の「必要性」と「可能性」 : これまでとこれから 有田 智一 区画整理/66(5)/pp.6-14, 2023-05 / 教育統計情報調査システムの構築方案に関する研究：中等教育を中心に 川島 宏一; 李珠善; 有田智一 情報処理学会研究報告, 2018-03 / つくば市による心肺停止傷病者発生位置情報の最寄AED管理者との共有が生み出す協働による救命効果に関する研究 川島 宏一; 有田 智一; 鈴木良介 計画行政/43(1)/pp.26-26, 2020-02-15 / 地方自治体におけるオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 川島 宏一; 有田智一 情報通信学会誌, 2021-09 / 東京都区部における開発実態の評価を踏まえた開発拠点誘導政策の課題に関する研究 鈴木 賢人; 有田 智一 都市計画論文集/56(3)/pp.881-888, 2021-10-25 CiNii / 公民連携による空き家・空き地対策組織の展開と運営実態 阿部 俊介; 有田 智一 都市計画論文集/56(3)/pp.1268-1274, 2021-10-25 CiNii / 避難行動要支援者名簿活用に向けた制度設計・運用プロセスにおける課題に関する研究 藤田 修平; 川島 宏一; 有田 智一; 岡本 正 地域安全学会論文集/39(0)/pp.145-153, 2021-11-01 / オープンデータ施策に総合的に取り組む地方自治体の動因に関する研究 川島 宏一; 有田智一; 野村敦子 自治体学/35(2), 2022-03 / 地方都市中心市街地における商店街の連続性を踏まえた空間整備の変遷と課題に関する研究 杉田 光; 有田 智一 都市計画報告集/21(1)/pp.57-63, 2022-06-08 / 地方自治体のオープンデータ施策の実態と取り組み内容に影響を与える要因に関する研究 川島 宏一; 野村敦子; 有田智一 情報通信学会誌, 2021-09 / 世界からみた銀座のルールとガバナンス (特集 銀座と都市計画) -- (都市計画と銀座のルール) 有田 智一 都市計画 = City planning review/68(4)/pp.42-45, 2019-07-15 CiNii / 11027 地区スケールの賑わい空間構造の定量分析に関する研究 歩行空間と周辺土地利用に着目して 鈴木 賢人; 有田 智一 情報システム技術/(2019)/pp.53-54, 2019-07-20 CiNii / “Planning transparency and public involvement in pre-application discussions,” Arita Tomokazu; Parker Gavin Journal of Town &amp; Country Planning/pp.66-70, 2019-02 / 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 有田 智一 ビルディングレター/pp.16-17, 2018-05 / 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) 有田 智一 都市問題/109(11)/pp.84-97, 2018-11 / 集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ 梶塚 真良; 有田 智一 日本建築学会環境系論文集/83(751)/pp.791-799, 2018 CiNii Tsukuba Repository</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -12370,6 +12433,8 @@
 イギリスの都市計画プランナーの職能団体による実務研修等を支えるシステムに関する研究
 オープンデータを踏まえた市民セクター主体のICT協働まちづくりに関する研究
 豪雨災害から避難弱者を守る共助的な避難行動計画づくりシステムに関する学際的研究
+パネルディスカッション 未来志向のまちづくり 有田 智一; 坂井 文; 田中 仁; 山下 裕子; 大村 謙二郎 再開発コーディネーター/(240)/pp.15-28, 2026
+東京の集積の質的向上と多様性の高度化へ─土地・建物の高度利用を超えて 有田 智一 都市計画/75-3(380)/pp.18-21, 2026-05
 土地建物一体型市街地整備の系譜：立体換地から市街地 再開発事業、区画整理・再開発の一体的施行まで 有田 智一 区画整理士会報/235/pp.48-52, 2025-07
 新しい時代の都市再生と公共貢献のあり方 有田 智一 新都市/79(9)/pp.13-17, 2025-09
 都市再生特別措置法と都市再生特別地区─日本型公民協働の課題 有田 智一 都市計画/pp.44-47, 2024-11
@@ -12392,9 +12457,7 @@
 “Planning transparency and public involvement in pre-application discussions,” Arita Tomokazu; Parker Gavin Journal of Town &amp; Country Planning/pp.66-70, 2019-02
 市街地建築物法・建築基準法と建築学会 はじめに：日本建築学会建築法制委員会近代建築法制100周年記念活動支援小委員会 有田 智一 ビルディングレター/pp.16-17, 2018-05
 今後の土地・建物ストック活用型社会を踏まえた用途地域制の課題 (特集 50年目を迎えた都市計画法) 有田 智一 都市問題/109(11)/pp.84-97, 2018-11
-集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ 梶塚 真良; 有田 智一 日本建築学会環境系論文集/83(751)/pp.791-799, 2018 CiNii Tsukuba Repository
-マイナンバー導入に伴う自治体業務情報システム改修事例に見るオープン化・標準化及び共同化の現状に関する研究 金崎健太郎; 川島宏一; 有田智一 情報システム学会誌/13(2), 2018-03
-マイナンバー導入事例に見る政府情報システム調達の現状に関する研究 金崎健太郎; 川島宏一; 有田智一 情報システム学会誌/14(1), 2018-09</t>
+集合住宅の環境性能における消費者重要度と不動産価格の関連性に関する研究:－自治体版CASBEEの評価結果を用いた実証分析－ 梶塚 真良; 有田 智一 日本建築学会環境系論文集/83(751)/pp.791-799, 2018 CiNii Tsukuba Repository</t>
         </is>
       </c>
     </row>
@@ -12432,6 +12495,7 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>形態・材料に着目した近代町家の地域性とその形成要因
+都市・住宅・クルマの相互関係比較史
 モビリティーイノベーションの社会応用と未来社会工学研究5
 モビリティーイノベーションの社会応用と未来社会工学研究3
 モビリティーイノベーションの社会応用と未来社会工学研究4
@@ -12440,7 +12504,6 @@
 江戸武家地の成熟過程に関する建築史・都市史的研究
 江戸武家地の空間変容に関する文理統合的研究
 北関東の町並みの建築的構成とその展開過程に関する研究
-常陸太田市鯨が丘歴史的建造物調査
 建築史・意匠
 都市計画・建築計画
 日本史
@@ -12448,6 +12511,14 @@
 都市史
 保全型都市計画
 居住環境史
+『盛世滋生図』に見られる清代蘇州城の商業区域と販売形態 呂 志裕; 藤川 昌樹 日本建築学会計画系論文集/91(840)/pp.500-511, 2026-02-01
+南宋蘇州城における商・工・流通業の空間の配置 藤川 昌樹; 呂 志裕 日本建築学会大会講演梗概集/pp.617-618, 2025-09
+明治初期の横浜居留地における外国人の土地賃借と利用状況：中国人の集住との関係に着目して 藤川 昌樹; 呂 夢琦 日本建築学会大会講演梗概集/pp.511-512, 2025-09
+2020年代に開発された郊外住宅地における住宅と駐車スペースの関係：茨城県 X 市の景観協定締結区域を事例に 藤川 昌樹; 宋 宇辰 日本建築学会大会講演梗概集/pp.617-618, 2025-09
+香取神宮参道の変遷 江戸時代から現在にかけて 藤川 昌樹; 渡辺 唯斗 日本建築学会大会講演梗概集/pp.631-632, 2025-09
+嵩山における四本の登拝道の成立とその位置づけ 藤川 昌樹; 楊 佳楽 日本建築学会大会講演梗概集/pp.477-478, 2025-09
+北京歴史文化保護区におけるシェントリフィケーションの実態とその形成過程：南鑼鼓巷を事例に 藤川 昌樹; 劉 嘉恵 日本建築学会大会講演梗概集/pp.499-500, 2025-09
+『乾隆南巡駐蹕図』から見た江蘇地域の南巡行宮の立地と構造 藤川 昌樹; 張 宇星 日本建築学会大会学術講演梗概集/pp.479-480, 2025-09
 近代中国青島市における「雑院一覧表 二十四年夏季」について 徐 暢; 藤川 昌樹 日本建築学会技術報告集/30(75)/pp.1062-1067, 2024-06-20
 五台山行宮座落地盤圖 からみた清代白雲寺行宮 余思奇; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.843-844, 2023-9
 嵩山史跡群における建物の空間構成および登封県の建立の経緯 楊 佳楽; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.841-842, 2023-9
@@ -12464,20 +12535,12 @@
 清代福州における住宅の三類型 陳穎; 藤川 昌樹 日本建築学会計画系論文集/(810)/pp.pp.2,436-2,443, 2023-8
 大正期から戦前までの山下町における中国系事業所と公共施設の立地と特徴–Japan Directory、商工案内の分析から– 呂夢琦; 藤川 昌樹 日本建築学会大会/建築史・意匠/pp.569-570, 2022-09
 清代福建省における「舗」の分布とその特性－連江県城を事例として－ 陳穎; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.503-504, 2022-09
-清代五台山顕通寺の火災と修復工程 余思奇; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.425-426, 2022-09
-明清時代漕運と京杭大運河沿い都市の空間特性との関係－臨清を例として－ 宋宇辰; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.423-424, 2022-09
-中国における団地構内の小規模野菜市場の空間利用－街商と住民の共存モデル－ 呂志裕; 藤川 昌樹 日本建築学会大会術講演梗概集/建築計画/pp.195-196, 2022-09
-新刊紹介『明暦の大火』 藤川 昌樹 都市史研究/(9)/pp.112-112, 2022-10
-五台山塔院寺の建築の構成とその変容 余思奇; 藤川 昌樹 日本建築学会計画系論文集/(799)/pp.1010-1020, 2022-09
-「奈良県橿原市今井町における駐車場の出現パターン：重要伝統的建造物群保存地区の駐車空間に関する研究 その2」 劉一辰・李雪・藤川 昌樹 『日本建築学会計画系論文報告集』/796/pp.1010-1020, 2022-6
-「真壁のこれから：過去・現在・未来」 藤川 昌樹 『かわら版』（ディスカバー真壁）/(21), 2021-12
-「商店街アーケードの空間の変容:十条銀座商店街を対象に」 酒巻裕作・藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.147-148, 2021-09
-「清代新疆の地域構造と都市群の立地 -軍政中心地イリを対象に- 」 シャキラ、藤川 昌樹 アリミナ 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.525-516, 2021-09</t>
+清代五台山顕通寺の火災と修復工程 余思奇; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.425-426, 2022-09</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>形態・材料に着目した近代町家の地域性とその形成要因 / モビリティーイノベーションの社会応用と未来社会工学研究5 / モビリティーイノベーションの社会応用と未来社会工学研究3 / モビリティーイノベーションの社会応用と未来社会工学研究4 / 石岡市歴史的景観及び里山景観調査研究 / 大火からの復興を通してみた近代の町並みの再評価 / 江戸武家地の成熟過程に関する建築史・都市史的研究 / 江戸武家地の空間変容に関する文理統合的研究 / 北関東の町並みの建築的構成とその展開過程に関する研究 / 常陸太田市鯨が丘歴史的建造物調査</t>
+          <t>形態・材料に着目した近代町家の地域性とその形成要因 / 都市・住宅・クルマの相互関係比較史 / モビリティーイノベーションの社会応用と未来社会工学研究5 / モビリティーイノベーションの社会応用と未来社会工学研究3 / モビリティーイノベーションの社会応用と未来社会工学研究4 / 石岡市歴史的景観及び里山景観調査研究 / 大火からの復興を通してみた近代の町並みの再評価 / 江戸武家地の成熟過程に関する建築史・都市史的研究 / 江戸武家地の空間変容に関する文理統合的研究 / 北関東の町並みの建築的構成とその展開過程に関する研究</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12492,7 +12555,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>近代中国青島市における「雑院一覧表 二十四年夏季」について 徐 暢; 藤川 昌樹 日本建築学会技術報告集/30(75)/pp.1062-1067, 2024-06-20 / 五台山行宮座落地盤圖 からみた清代白雲寺行宮 余思奇; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.843-844, 2023-9 / 嵩山史跡群における建物の空間構成および登封県の建立の経緯 楊 佳楽; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.841-842, 2023-9 / 近代の町並み景観の多様性：大火からの復興を通してみた近代の町並みに関する研究 その 1 藤川 昌樹; 呂志裕; 楊 佳楽 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.167-168, 2023-9 / 戦後昭和期の横浜中華街における商住空間の分布と特徴：中区明細地図の考察から 呂夢琦; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.65-66, 2023-9 / 清代福州における住宅の類型とその特徴 古絵図 De Stud Hockzieuw en de stad Nanta を中心とした分析 陳穎; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp. 3-4, 2023-9 / 明清時代漕運と大運河沿いの都市空間特性との関係 その 2： 済寧を例として 宋宇辰; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp. 1-2, 2023-9 / 「白川郷における駐車空間の分布と交通整備の経緯：重要伝統的建造物群保存地区における駐車空間に関する研究」 芦澤美月; 劉一辰; 李雪; 藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.pp.739-740, 2023-9 / 『大日本職業別明細図之内』の空間表現 千葉県北部の地図を対象に 渡辺莉緒; 藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.pp. 157-158, 2023-9 / 観光開発を目的とした窯業集落の保全の実態とその課題： 中国陝西省澄城県の伝統村落・堯頭村を事例に 艾思思; 藤川 昌樹 日本建築学会大会学術講演梗概集/pp.pp.213-214, 2023-9 / 「清代蘇州の屋外空間における商人達の「自発的な居場所」 のパターン： 「姑蘇繁華図」の分析」 呂志裕; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築計画/pp.pp.1397-1398, 2023-9 / 新刊紹介『リスボン』 藤川 昌樹 建築史学/(81)/pp.p.223-226, 2023-9 / 明清時代における漕河沿い城・鎮の空間構成に関する研究（その1）：漕運システムと漕河沿岸空間の構成要素との関係 宋宇辰; 藤川 昌樹 日本建築学会計画系論文集/(814)/pp.3,416-3,425, 2023-12 / 清代福州における住宅の三類型 陳穎; 藤川 昌樹 日本建築学会計画系論文集/(810)/pp.pp.2,436-2,443, 2023-8 / 大正期から戦前までの山下町における中国系事業所と公共施設の立地と特徴–Japan Directory、商工案内の分析から– 呂夢琦; 藤川 昌樹 日本建築学会大会/建築史・意匠/pp.569-570, 2022-09 / 清代福建省における「舗」の分布とその特性－連江県城を事例として－ 陳穎; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.503-504, 2022-09 / 清代五台山顕通寺の火災と修復工程 余思奇; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.425-426, 2022-09 / 明清時代漕運と京杭大運河沿い都市の空間特性との関係－臨清を例として－ 宋宇辰; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.423-424, 2022-09 / 中国における団地構内の小規模野菜市場の空間利用－街商と住民の共存モデル－ 呂志裕; 藤川 昌樹 日本建築学会大会術講演梗概集/建築計画/pp.195-196, 2022-09 / 新刊紹介『明暦の大火』 藤川 昌樹 都市史研究/(9)/pp.112-112, 2022-10 / 五台山塔院寺の建築の構成とその変容 余思奇; 藤川 昌樹 日本建築学会計画系論文集/(799)/pp.1010-1020, 2022-09 / 「奈良県橿原市今井町における駐車場の出現パターン：重要伝統的建造物群保存地区の駐車空間に関する研究 その2」 劉一辰・李雪・藤川 昌樹 『日本建築学会計画系論文報告集』/796/pp.1010-1020, 2022-6 / 「真壁のこれから：過去・現在・未来」 藤川 昌樹 『かわら版』（ディスカバー真壁）/(21), 2021-12 / 「商店街アーケードの空間の変容:十条銀座商店街を対象に」 酒巻裕作・藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.147-148, 2021-09 / 「清代新疆の地域構造と都市群の立地 -軍政中心地イリを対象に- 」 シャキラ、藤川 昌樹 アリミナ 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.525-516, 2021-09</t>
+          <t>『盛世滋生図』に見られる清代蘇州城の商業区域と販売形態 呂 志裕; 藤川 昌樹 日本建築学会計画系論文集/91(840)/pp.500-511, 2026-02-01 / 南宋蘇州城における商・工・流通業の空間の配置 藤川 昌樹; 呂 志裕 日本建築学会大会講演梗概集/pp.617-618, 2025-09 / 明治初期の横浜居留地における外国人の土地賃借と利用状況：中国人の集住との関係に着目して 藤川 昌樹; 呂 夢琦 日本建築学会大会講演梗概集/pp.511-512, 2025-09 / 2020年代に開発された郊外住宅地における住宅と駐車スペースの関係：茨城県 X 市の景観協定締結区域を事例に 藤川 昌樹; 宋 宇辰 日本建築学会大会講演梗概集/pp.617-618, 2025-09 / 香取神宮参道の変遷 江戸時代から現在にかけて 藤川 昌樹; 渡辺 唯斗 日本建築学会大会講演梗概集/pp.631-632, 2025-09 / 嵩山における四本の登拝道の成立とその位置づけ 藤川 昌樹; 楊 佳楽 日本建築学会大会講演梗概集/pp.477-478, 2025-09 / 北京歴史文化保護区におけるシェントリフィケーションの実態とその形成過程：南鑼鼓巷を事例に 藤川 昌樹; 劉 嘉恵 日本建築学会大会講演梗概集/pp.499-500, 2025-09 / 『乾隆南巡駐蹕図』から見た江蘇地域の南巡行宮の立地と構造 藤川 昌樹; 張 宇星 日本建築学会大会学術講演梗概集/pp.479-480, 2025-09 / 近代中国青島市における「雑院一覧表 二十四年夏季」について 徐 暢; 藤川 昌樹 日本建築学会技術報告集/30(75)/pp.1062-1067, 2024-06-20 / 五台山行宮座落地盤圖 からみた清代白雲寺行宮 余思奇; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.843-844, 2023-9 / 嵩山史跡群における建物の空間構成および登封県の建立の経緯 楊 佳楽; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.841-842, 2023-9 / 近代の町並み景観の多様性：大火からの復興を通してみた近代の町並みに関する研究 その 1 藤川 昌樹; 呂志裕; 楊 佳楽 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.167-168, 2023-9 / 戦後昭和期の横浜中華街における商住空間の分布と特徴：中区明細地図の考察から 呂夢琦; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.65-66, 2023-9 / 清代福州における住宅の類型とその特徴 古絵図 De Stud Hockzieuw en de stad Nanta を中心とした分析 陳穎; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp. 3-4, 2023-9 / 明清時代漕運と大運河沿いの都市空間特性との関係 その 2： 済寧を例として 宋宇辰; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp. 1-2, 2023-9 / 「白川郷における駐車空間の分布と交通整備の経緯：重要伝統的建造物群保存地区における駐車空間に関する研究」 芦澤美月; 劉一辰; 李雪; 藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.pp.739-740, 2023-9 / 『大日本職業別明細図之内』の空間表現 千葉県北部の地図を対象に 渡辺莉緒; 藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.pp. 157-158, 2023-9 / 観光開発を目的とした窯業集落の保全の実態とその課題： 中国陝西省澄城県の伝統村落・堯頭村を事例に 艾思思; 藤川 昌樹 日本建築学会大会学術講演梗概集/pp.pp.213-214, 2023-9 / 「清代蘇州の屋外空間における商人達の「自発的な居場所」 のパターン： 「姑蘇繁華図」の分析」 呂志裕; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築計画/pp.pp.1397-1398, 2023-9 / 新刊紹介『リスボン』 藤川 昌樹 建築史学/(81)/pp.p.223-226, 2023-9 / 明清時代における漕河沿い城・鎮の空間構成に関する研究（その1）：漕運システムと漕河沿岸空間の構成要素との関係 宋宇辰; 藤川 昌樹 日本建築学会計画系論文集/(814)/pp.3,416-3,425, 2023-12 / 清代福州における住宅の三類型 陳穎; 藤川 昌樹 日本建築学会計画系論文集/(810)/pp.pp.2,436-2,443, 2023-8 / 大正期から戦前までの山下町における中国系事業所と公共施設の立地と特徴–Japan Directory、商工案内の分析から– 呂夢琦; 藤川 昌樹 日本建築学会大会/建築史・意匠/pp.569-570, 2022-09 / 清代福建省における「舗」の分布とその特性－連江県城を事例として－ 陳穎; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.503-504, 2022-09 / 清代五台山顕通寺の火災と修復工程 余思奇; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.425-426, 2022-09</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -12560,6 +12623,7 @@
 明清時代の役人住宅における職階制度と建築様式の関係—陳氏の住宅を例に
 北京市歴史文化保護区におけるジェントリフィケーションの実態とメカニズム―南鑼鼓巷を事例に
 形態・材料に着目した近代町家の地域性とその形成要因
+都市・住宅・クルマの相互関係比較史
 モビリティーイノベーションの社会応用と未来社会工学研究5
 モビリティーイノベーションの社会応用と未来社会工学研究3
 モビリティーイノベーションの社会応用と未来社会工学研究4
@@ -12568,7 +12632,14 @@
 江戸武家地の成熟過程に関する建築史・都市史的研究
 江戸武家地の空間変容に関する文理統合的研究
 北関東の町並みの建築的構成とその展開過程に関する研究
-常陸太田市鯨が丘歴史的建造物調査
+『盛世滋生図』に見られる清代蘇州城の商業区域と販売形態 呂 志裕; 藤川 昌樹 日本建築学会計画系論文集/91(840)/pp.500-511, 2026-02-01
+南宋蘇州城における商・工・流通業の空間の配置 藤川 昌樹; 呂 志裕 日本建築学会大会講演梗概集/pp.617-618, 2025-09
+明治初期の横浜居留地における外国人の土地賃借と利用状況：中国人の集住との関係に着目して 藤川 昌樹; 呂 夢琦 日本建築学会大会講演梗概集/pp.511-512, 2025-09
+2020年代に開発された郊外住宅地における住宅と駐車スペースの関係：茨城県 X 市の景観協定締結区域を事例に 藤川 昌樹; 宋 宇辰 日本建築学会大会講演梗概集/pp.617-618, 2025-09
+香取神宮参道の変遷 江戸時代から現在にかけて 藤川 昌樹; 渡辺 唯斗 日本建築学会大会講演梗概集/pp.631-632, 2025-09
+嵩山における四本の登拝道の成立とその位置づけ 藤川 昌樹; 楊 佳楽 日本建築学会大会講演梗概集/pp.477-478, 2025-09
+北京歴史文化保護区におけるシェントリフィケーションの実態とその形成過程：南鑼鼓巷を事例に 藤川 昌樹; 劉 嘉恵 日本建築学会大会講演梗概集/pp.499-500, 2025-09
+『乾隆南巡駐蹕図』から見た江蘇地域の南巡行宮の立地と構造 藤川 昌樹; 張 宇星 日本建築学会大会学術講演梗概集/pp.479-480, 2025-09
 近代中国青島市における「雑院一覧表 二十四年夏季」について 徐 暢; 藤川 昌樹 日本建築学会技術報告集/30(75)/pp.1062-1067, 2024-06-20
 五台山行宮座落地盤圖 からみた清代白雲寺行宮 余思奇; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.843-844, 2023-9
 嵩山史跡群における建物の空間構成および登封県の建立の経緯 楊 佳楽; 藤川 昌樹 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.pp.841-842, 2023-9
@@ -12585,15 +12656,7 @@
 清代福州における住宅の三類型 陳穎; 藤川 昌樹 日本建築学会計画系論文集/(810)/pp.pp.2,436-2,443, 2023-8
 大正期から戦前までの山下町における中国系事業所と公共施設の立地と特徴–Japan Directory、商工案内の分析から– 呂夢琦; 藤川 昌樹 日本建築学会大会/建築史・意匠/pp.569-570, 2022-09
 清代福建省における「舗」の分布とその特性－連江県城を事例として－ 陳穎; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.503-504, 2022-09
-清代五台山顕通寺の火災と修復工程 余思奇; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.425-426, 2022-09
-明清時代漕運と京杭大運河沿い都市の空間特性との関係－臨清を例として－ 宋宇辰; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.423-424, 2022-09
-中国における団地構内の小規模野菜市場の空間利用－街商と住民の共存モデル－ 呂志裕; 藤川 昌樹 日本建築学会大会術講演梗概集/建築計画/pp.195-196, 2022-09
-新刊紹介『明暦の大火』 藤川 昌樹 都市史研究/(9)/pp.112-112, 2022-10
-五台山塔院寺の建築の構成とその変容 余思奇; 藤川 昌樹 日本建築学会計画系論文集/(799)/pp.1010-1020, 2022-09
-「奈良県橿原市今井町における駐車場の出現パターン：重要伝統的建造物群保存地区の駐車空間に関する研究 その2」 劉一辰・李雪・藤川 昌樹 『日本建築学会計画系論文報告集』/796/pp.1010-1020, 2022-6
-「真壁のこれから：過去・現在・未来」 藤川 昌樹 『かわら版』（ディスカバー真壁）/(21), 2021-12
-「商店街アーケードの空間の変容:十条銀座商店街を対象に」 酒巻裕作・藤川 昌樹 『日本建築学会大会学術講演梗概集』都市計画/pp.147-148, 2021-09
-「清代新疆の地域構造と都市群の立地 -軍政中心地イリを対象に- 」 シャキラ、藤川 昌樹 アリミナ 『日本建築学会大会学術講演梗概集』建築史・意匠/pp.525-516, 2021-09</t>
+清代五台山顕通寺の火災と修復工程 余思奇; 藤川 昌樹 日本建築学会大会学術講演梗概集/建築史・意匠/pp.425-426, 2022-09</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12693,10 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化
+          <t>半導体撮像テスト結果を認識し、良・不良の判断を行うモデルに関する研究
+仮想3PLにおける在庫移動最適化
+安全モニタリング生成機能開発
+遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化
 ワークライフバランスに貢献するサイバー・フィジカル製造業
 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配
 半導体・液晶製造の良品スループット向上とコスト低減の両立を目指してQ-time制約の遵守と装置の生産性向上とを同時に実現する実時間最適オペレーション管理手法の研究
@@ -12641,6 +12707,18 @@
 生産システム工学
 オペレーション管理
 地域活性化
+建設現場部材の自動計数システム その2：物体判別と計数のための機械学習 金原壮汰; 髙田大右; 有馬 澄佳 日本建築学会2025梗概集/pp.１-2, 2025-09
+建設現場部材の自動計数システム その1：360°画像に基づく多種計器の計数 有馬 澄佳; 髙田大右; 金原壮汰; 岡本崇利; 本多花帆 日本建築学会2025梗概集/pp.1-2, 2025-09
+Data-Driven Modeling of Multi-Factory Production Systems with Tran, Product-mix and Re-entrant flows Sakurai Shuntaro; 有馬 澄佳 Proceedings of The Asia Pacific Industrial Engineering &amp; Management Systems Conference 2025 (APIEMS2025)/pp.1-6, 2025-11-07
+Automated Cause-Effect Discovery on Multivariate Time-series Data -Semiconductor production dynamics and process anomaly MAO Chendin; LI Ke; Xu X.; ARIMA Sumika Proceedings of The Semiconductor Wafer Test Asia Conference 2025 (SWTest Asia2025)/pp.1-2, 2025-11-20
+Multi-criteria Parameter Optimization for Complex Systems - Multi-Objective Scheduling Case AKIZUKI Hiroto; MAO Chendin; SUZUKI Yurika; LI Ke; YO... Proceedings of The Semiconductor Wafer Test Asia Conference 2025 (SWTest Asia2025)/pp.1-2, 2025-11-20
+Supply Chain Operation Coordination Optimization Based on Multi-objective Scheduling Lin Jia; ARIMA Sumika Proceedings of The 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07-14
+Masked Invariant Information Clustering for Visualized Multivariate Time-Series Data Sumiya Koichi; ARIMA Sumika Proceedings of The 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07-14
+Extended VAR-LinGAM Methods for Modeling Production System Dynamics Xu X.; Mao Chendin; Sakurai Shuntaro; ARIMA Sumika Proceedings of The proceedings of the 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07
+Detection and Localization of Defects Using Masked Image Modeling Yasuda Akira; Shishido Hayato; Nagai Kosuke; Sumiya K... Proceedings of Advanced Equipment Control/Advanced Process Control Symposium Asia 2025/pp.1-2, 2025-11
+Multi-Objective Multi-Factory Scheduling with Robust Optimization for Inter-Factory Routing Suzuki Yurika; 有馬 澄佳 Proceedings of International Conference on Operations Research and Enterprise Systems (ICORES) 2026/pp.1-7, 2026-03
+Interaction Modeling for High-Dimensional Mixed Data Considering Distribution and Correlation Ito Taiki; Matsuzawa Takuya; ARIMA Sumika Procedia Computer Science/270/pp.752-761, 2025-09
+The reduction of false positives in Sparse Factorization Machines Matsuzawa Takuya; Ito Taiki; ARIMA Sumika Procedia Computer Science/270/pp.802-811, 2025-09
 "INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH Ozawa H.; ITO T.; Matsuzawa T.; Hoshino S.; Watanabe ... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10
 Robust Classifications of WBM Defect Patterns ARIMA Sumika; AI T.; MAEDA T.; SUMIYA K.; ITO T.; TA... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10
 Due dates assignment based on customer changeability classifications in Make-to-order productoins Shishido I.; Sakurai S.; 有馬 澄佳 Proceedings of the Asia Pacific Industrial Engineering &amp; Management Systems Conference 2024/2024/pp.1-6, 2024-11
@@ -12653,24 +12731,12 @@
 Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL Ozawa H.; Hoshino S.; ARIMA Sumika Procedia Computer Science/246/pp.2953-2963, 2024-09
 MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION Lin Jia; MAO Chending; Arima Sumika Proceedings of International Symposium on Scheduling 2023/2023/pp.1-6, 2023-06-23
 Mixed-type Defect Pattern Classifications Maeda Takumi; Takada Daisuke; Arima Sumika Proceedings of AEC/APC Symposium Asia 2023/2023/pp.1-2, 2023-11-02
-Interaction Modelling of High Dimensional Production Data Hoshino Sara; Watanabe Kyo; Arima Sumika Procedia Computer Science/225/pp.4055-4064, 2023-12
-DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS Arima Sumika; Takahashi Haruki; Shishido Ibuki The Journal ACTA TECHNICA NAPOCENSIS - Series: APPLIED MATHEMATICS, MECHANICS, and ENGINEERING/66(1S)/pp.55-60, 2023-11
-MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN Arima Sumika; Tahara Yusaku; Nagai Kosuke The Journal ACTA TECHNICA NAPOCENSIS - Series: APPLIED MATHEMATICS, MECHANICS, and ENGINEERING/66(SI)/pp.105-112, 2023-11
-Data-driven Modeling for Production Dynamics Arima Sumika; Y. SASAKI; MORIE S.; KATAOKA Y.; MAO C.; LIN... Proceesings of IEEE International Symposium on Semiconductor Manufacturing 2022/pp.1-4, 2022-12-12
-Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption Arima Sumika; MAO C.; LIN J. Proceedings of IEEE International Symposium on Semiconductor Manufacturing 2022/pp.1-4, 2022-12
-MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - Arima Sumika; JIA Lin; Ohno Tomoki; MAO Chending; MORIE ... Proceedings of the 2022 International Symposium on Flexible Automation/(ISFA2022)/pp.1-8, 2022-07
-Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - Arima Sumika; BU Huizhen; NAGATA Takuya; ONODERA Kakeru The Journal of the Japan Industrial Management Association/pp.1-10, 2022-07
-Interaction Modelings for Industrial Data - for final quality estimation and proess integration Arima Sumika; Limin Qin; Nagata Takuya; Handa Kotaro; Wat... Proceeding of AEC/APC symposium Asia 2021/pp.1-4, 2021-11
-スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 有馬 澄佳; 半田滉太朗 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-スマートフォンアプリの起動順序に着目したユーザーセグメント分析 大野智暉; 有馬 澄佳 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-従属需要の予測手法の構築と検証 有馬 澄佳; 小川陽平 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-スマートフォンアプリの起動順序に着目したユーザーセグメント分析 有馬 澄佳; 大野智暉 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling J. LIN; Tomoki ONO; Sho MORIE; Qingxin ZHU; Yu SASAKI; Su... Proceedings of The International Symposium on Semiconductor Manufacturing 2020 (ISSM2020)/pp.1-4, 2020-12</t>
+Interaction Modelling of High Dimensional Production Data Hoshino Sara; Watanabe Kyo; Arima Sumika Procedia Computer Science/225/pp.4055-4064, 2023-12</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化 / ワークライフバランスに貢献するサイバー・フィジカル製造業 / 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配 / 半導体・液晶製造の良品スループット向上とコスト低減の両立を目指してQ-time制約の遵守と装置の生産性向上とを同時に実現する実時間最適オペレーション管理手法の研究 / ＱＣＤＲモデルに基づいて革新的な総合設備効率の向上と生産期間の短縮を実現する工場・設備の運用管理システム / ＱＣＤモデルに基づくマルチチャンバ装置および生産ラインの運用・設計方法 / 共創ビジョンに基づく半導体産業のビジネスモデル進化と、知財・人材の組織的流動化</t>
+          <t>半導体撮像テスト結果を認識し、良・不良の判断を行うモデルに関する研究 / 仮想3PLにおける在庫移動最適化 / 安全モニタリング生成機能開発 / 遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化 / ワークライフバランスに貢献するサイバー・フィジカル製造業 / 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配 / 半導体・液晶製造の良品スループット向上とコスト低減の両立を目指してQ-time制約の遵守と装置の生産性向上とを同時に実現する実時間最適オペレーション管理手法の研究 / ＱＣＤＲモデルに基づいて革新的な総合設備効率の向上と生産期間の短縮を実現する工場・設備の運用管理システム / ＱＣＤモデルに基づくマルチチャンバ装置および生産ラインの運用・設計方法 / 共創ビジョンに基づく半導体産業のビジネスモデル進化と、知財・人材の組織的流動化</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12685,7 +12751,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>"INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH Ozawa H.; ITO T.; Matsuzawa T.; Hoshino S.; Watanabe ... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10 / Robust Classifications of WBM Defect Patterns ARIMA Sumika; AI T.; MAEDA T.; SUMIYA K.; ITO T.; TA... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10 / Due dates assignment based on customer changeability classifications in Make-to-order productoins Shishido I.; Sakurai S.; 有馬 澄佳 Proceedings of the Asia Pacific Industrial Engineering &amp; Management Systems Conference 2024/2024/pp.1-6, 2024-11 / Pipeline production model and sensitivity analysis of Engineering-to-Order products using system dynamics Nagai K.; 有馬 澄佳 Proceedings of the Asia Pacific Industrial Engineering &amp; Management Systems Conference 2024/2024/pp.1-6, 2024-11 / PRODUCTION AND JOB ROTATION PLANNING CONSIDERING DISABILITIES AND HEALTH CONDITIONS Watanabe Y.; Kashimoto N.; 有馬 澄佳 Proceedings of the 51st International Conference on Computers and Industrial Engineering (CIE51)/pp.1-10, 2024-12 / Classification of Multivariate Time Series Signals Using Self-Supervised Representation Learning Suzuki Y.; ARIMA Sumika Proceedings of International Symposium on Semiconductor Manufacturing/2024/pp.1-4, 2024-12 / Multi-factory Scheduling Considering the Trade-offs between Production Efficiency and Risks Suzuki Y.; ARIMA Sumika Proceedings of International Symposium on Semiconductor Manufacturing/2024/pp.1-4, 2024-12 / Analysis of Resilience Factors and Satisfaction in Life-line Charts for Life Career Developments ARIMA Sumika; Morita Sayuri; Yasuda Akira Proceedings of the 11th International Symposium on Affective Science and Engineering (ISASE2025)/pp.1-4, 2025-03 / Interaction Modeling for High-Dimensional Mixed Data with Numerical and Categorical Features Hoshino S.; Ito T.; Matsuzawa T.; ARIMA Sumika Procedia Computer Science/246/pp.2964-2973, 2024-09 / Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL Ozawa H.; Hoshino S.; ARIMA Sumika Procedia Computer Science/246/pp.2953-2963, 2024-09 / MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION Lin Jia; MAO Chending; Arima Sumika Proceedings of International Symposium on Scheduling 2023/2023/pp.1-6, 2023-06-23 / Mixed-type Defect Pattern Classifications Maeda Takumi; Takada Daisuke; Arima Sumika Proceedings of AEC/APC Symposium Asia 2023/2023/pp.1-2, 2023-11-02 / Interaction Modelling of High Dimensional Production Data Hoshino Sara; Watanabe Kyo; Arima Sumika Procedia Computer Science/225/pp.4055-4064, 2023-12 / DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS Arima Sumika; Takahashi Haruki; Shishido Ibuki The Journal ACTA TECHNICA NAPOCENSIS - Series: APPLIED MATHEMATICS, MECHANICS, and ENGINEERING/66(1S)/pp.55-60, 2023-11 / MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN Arima Sumika; Tahara Yusaku; Nagai Kosuke The Journal ACTA TECHNICA NAPOCENSIS - Series: APPLIED MATHEMATICS, MECHANICS, and ENGINEERING/66(SI)/pp.105-112, 2023-11 / Data-driven Modeling for Production Dynamics Arima Sumika; Y. SASAKI; MORIE S.; KATAOKA Y.; MAO C.; LIN... Proceesings of IEEE International Symposium on Semiconductor Manufacturing 2022/pp.1-4, 2022-12-12 / Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption Arima Sumika; MAO C.; LIN J. Proceedings of IEEE International Symposium on Semiconductor Manufacturing 2022/pp.1-4, 2022-12 / MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - Arima Sumika; JIA Lin; Ohno Tomoki; MAO Chending; MORIE ... Proceedings of the 2022 International Symposium on Flexible Automation/(ISFA2022)/pp.1-8, 2022-07 / Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - Arima Sumika; BU Huizhen; NAGATA Takuya; ONODERA Kakeru The Journal of the Japan Industrial Management Association/pp.1-10, 2022-07 / Interaction Modelings for Industrial Data - for final quality estimation and proess integration Arima Sumika; Limin Qin; Nagata Takuya; Handa Kotaro; Wat... Proceeding of AEC/APC symposium Asia 2021/pp.1-4, 2021-11 / スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 有馬 澄佳; 半田滉太朗 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 大野智暉; 有馬 澄佳 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10 / 従属需要の予測手法の構築と検証 有馬 澄佳; 小川陽平 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10 / スマートフォンアプリの起動順序に着目したユーザーセグメント分析 有馬 澄佳; 大野智暉 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10 / Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling J. LIN; Tomoki ONO; Sho MORIE; Qingxin ZHU; Yu SASAKI; Su... Proceedings of The International Symposium on Semiconductor Manufacturing 2020 (ISSM2020)/pp.1-4, 2020-12</t>
+          <t>建設現場部材の自動計数システム その2：物体判別と計数のための機械学習 金原壮汰; 髙田大右; 有馬 澄佳 日本建築学会2025梗概集/pp.１-2, 2025-09 / 建設現場部材の自動計数システム その1：360°画像に基づく多種計器の計数 有馬 澄佳; 髙田大右; 金原壮汰; 岡本崇利; 本多花帆 日本建築学会2025梗概集/pp.1-2, 2025-09 / Data-Driven Modeling of Multi-Factory Production Systems with Tran, Product-mix and Re-entrant flows Sakurai Shuntaro; 有馬 澄佳 Proceedings of The Asia Pacific Industrial Engineering &amp; Management Systems Conference 2025 (APIEMS2025)/pp.1-6, 2025-11-07 / Automated Cause-Effect Discovery on Multivariate Time-series Data -Semiconductor production dynamics and process anomaly MAO Chendin; LI Ke; Xu X.; ARIMA Sumika Proceedings of The Semiconductor Wafer Test Asia Conference 2025 (SWTest Asia2025)/pp.1-2, 2025-11-20 / Multi-criteria Parameter Optimization for Complex Systems - Multi-Objective Scheduling Case AKIZUKI Hiroto; MAO Chendin; SUZUKI Yurika; LI Ke; YO... Proceedings of The Semiconductor Wafer Test Asia Conference 2025 (SWTest Asia2025)/pp.1-2, 2025-11-20 / Supply Chain Operation Coordination Optimization Based on Multi-objective Scheduling Lin Jia; ARIMA Sumika Proceedings of The 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07-14 / Masked Invariant Information Clustering for Visualized Multivariate Time-Series Data Sumiya Koichi; ARIMA Sumika Proceedings of The 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07-14 / Extended VAR-LinGAM Methods for Modeling Production System Dynamics Xu X.; Mao Chendin; Sakurai Shuntaro; ARIMA Sumika Proceedings of The proceedings of the 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07 / Detection and Localization of Defects Using Masked Image Modeling Yasuda Akira; Shishido Hayato; Nagai Kosuke; Sumiya K... Proceedings of Advanced Equipment Control/Advanced Process Control Symposium Asia 2025/pp.1-2, 2025-11 / Multi-Objective Multi-Factory Scheduling with Robust Optimization for Inter-Factory Routing Suzuki Yurika; 有馬 澄佳 Proceedings of International Conference on Operations Research and Enterprise Systems (ICORES) 2026/pp.1-7, 2026-03 / Interaction Modeling for High-Dimensional Mixed Data Considering Distribution and Correlation Ito Taiki; Matsuzawa Takuya; ARIMA Sumika Procedia Computer Science/270/pp.752-761, 2025-09 / The reduction of false positives in Sparse Factorization Machines Matsuzawa Takuya; Ito Taiki; ARIMA Sumika Procedia Computer Science/270/pp.802-811, 2025-09 / "INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH Ozawa H.; ITO T.; Matsuzawa T.; Hoshino S.; Watanabe ... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10 / Robust Classifications of WBM Defect Patterns ARIMA Sumika; AI T.; MAEDA T.; SUMIYA K.; ITO T.; TA... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10 / Due dates assignment based on customer changeability classifications in Make-to-order productoins Shishido I.; Sakurai S.; 有馬 澄佳 Proceedings of the Asia Pacific Industrial Engineering &amp; Management Systems Conference 2024/2024/pp.1-6, 2024-11 / Pipeline production model and sensitivity analysis of Engineering-to-Order products using system dynamics Nagai K.; 有馬 澄佳 Proceedings of the Asia Pacific Industrial Engineering &amp; Management Systems Conference 2024/2024/pp.1-6, 2024-11 / PRODUCTION AND JOB ROTATION PLANNING CONSIDERING DISABILITIES AND HEALTH CONDITIONS Watanabe Y.; Kashimoto N.; 有馬 澄佳 Proceedings of the 51st International Conference on Computers and Industrial Engineering (CIE51)/pp.1-10, 2024-12 / Classification of Multivariate Time Series Signals Using Self-Supervised Representation Learning Suzuki Y.; ARIMA Sumika Proceedings of International Symposium on Semiconductor Manufacturing/2024/pp.1-4, 2024-12 / Multi-factory Scheduling Considering the Trade-offs between Production Efficiency and Risks Suzuki Y.; ARIMA Sumika Proceedings of International Symposium on Semiconductor Manufacturing/2024/pp.1-4, 2024-12 / Analysis of Resilience Factors and Satisfaction in Life-line Charts for Life Career Developments ARIMA Sumika; Morita Sayuri; Yasuda Akira Proceedings of the 11th International Symposium on Affective Science and Engineering (ISASE2025)/pp.1-4, 2025-03 / Interaction Modeling for High-Dimensional Mixed Data with Numerical and Categorical Features Hoshino S.; Ito T.; Matsuzawa T.; ARIMA Sumika Procedia Computer Science/246/pp.2964-2973, 2024-09 / Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL Ozawa H.; Hoshino S.; ARIMA Sumika Procedia Computer Science/246/pp.2953-2963, 2024-09 / MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION Lin Jia; MAO Chending; Arima Sumika Proceedings of International Symposium on Scheduling 2023/2023/pp.1-6, 2023-06-23 / Mixed-type Defect Pattern Classifications Maeda Takumi; Takada Daisuke; Arima Sumika Proceedings of AEC/APC Symposium Asia 2023/2023/pp.1-2, 2023-11-02 / Interaction Modelling of High Dimensional Production Data Hoshino Sara; Watanabe Kyo; Arima Sumika Procedia Computer Science/225/pp.4055-4064, 2023-12</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -12695,12 +12761,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>制御・システム工学 ; 都市・地域政策 ; オペレーションズリサーチ ; 機械学習 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>制御・システム工学 ; 都市・地域政策 ; オペレーションズリサーチ ; 機械学習 ; 画像・視覚情報処理 ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12712,6 +12778,7 @@
 都市・地域政策
 オペレーションズリサーチ
 機械学習
+画像・視覚情報処理
 公共政策・社会工学
 数理最適化・OR
 AI・データサイエンス
@@ -12724,7 +12791,11 @@
 計画・スケジューリング
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+コンピュータビジョン
+画像認識
+行動認識
+マルチモーダル解析</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -12759,6 +12830,9 @@
 推薦システムによる多様なアプリの利用促進
 高次元データの交互作用モデリング-Adaptive SFMとSafe Pruningによる高精度化
 多様な建設現場の部材の検出と分類
+半導体撮像テスト結果を認識し、良・不良の判断を行うモデルに関する研究
+仮想3PLにおける在庫移動最適化
+安全モニタリング生成機能開発
 遠隔保守情報を統合活用した高速印刷機械の異常予測と保全計画最適化
 ワークライフバランスに貢献するサイバー・フィジカル製造業
 地域協働情報プラットフォームの構築と評価、資源余剰の最適割付けと社会合理的分配
@@ -12766,6 +12840,18 @@
 ＱＣＤＲモデルに基づいて革新的な総合設備効率の向上と生産期間の短縮を実現する工場・設備の運用管理システム
 ＱＣＤモデルに基づくマルチチャンバ装置および生産ラインの運用・設計方法
 共創ビジョンに基づく半導体産業のビジネスモデル進化と、知財・人材の組織的流動化
+建設現場部材の自動計数システム その2：物体判別と計数のための機械学習 金原壮汰; 髙田大右; 有馬 澄佳 日本建築学会2025梗概集/pp.１-2, 2025-09
+建設現場部材の自動計数システム その1：360°画像に基づく多種計器の計数 有馬 澄佳; 髙田大右; 金原壮汰; 岡本崇利; 本多花帆 日本建築学会2025梗概集/pp.1-2, 2025-09
+Data-Driven Modeling of Multi-Factory Production Systems with Tran, Product-mix and Re-entrant flows Sakurai Shuntaro; 有馬 澄佳 Proceedings of The Asia Pacific Industrial Engineering &amp; Management Systems Conference 2025 (APIEMS2025)/pp.1-6, 2025-11-07
+Automated Cause-Effect Discovery on Multivariate Time-series Data -Semiconductor production dynamics and process anomaly MAO Chendin; LI Ke; Xu X.; ARIMA Sumika Proceedings of The Semiconductor Wafer Test Asia Conference 2025 (SWTest Asia2025)/pp.1-2, 2025-11-20
+Multi-criteria Parameter Optimization for Complex Systems - Multi-Objective Scheduling Case AKIZUKI Hiroto; MAO Chendin; SUZUKI Yurika; LI Ke; YO... Proceedings of The Semiconductor Wafer Test Asia Conference 2025 (SWTest Asia2025)/pp.1-2, 2025-11-20
+Supply Chain Operation Coordination Optimization Based on Multi-objective Scheduling Lin Jia; ARIMA Sumika Proceedings of The 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07-14
+Masked Invariant Information Clustering for Visualized Multivariate Time-Series Data Sumiya Koichi; ARIMA Sumika Proceedings of The 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07-14
+Extended VAR-LinGAM Methods for Modeling Production System Dynamics Xu X.; Mao Chendin; Sakurai Shuntaro; ARIMA Sumika Proceedings of The proceedings of the 28th International Conference on Production Research (ICPR 28)/pp.1-4, 2025-07
+Detection and Localization of Defects Using Masked Image Modeling Yasuda Akira; Shishido Hayato; Nagai Kosuke; Sumiya K... Proceedings of Advanced Equipment Control/Advanced Process Control Symposium Asia 2025/pp.1-2, 2025-11
+Multi-Objective Multi-Factory Scheduling with Robust Optimization for Inter-Factory Routing Suzuki Yurika; 有馬 澄佳 Proceedings of International Conference on Operations Research and Enterprise Systems (ICORES) 2026/pp.1-7, 2026-03
+Interaction Modeling for High-Dimensional Mixed Data Considering Distribution and Correlation Ito Taiki; Matsuzawa Takuya; ARIMA Sumika Procedia Computer Science/270/pp.752-761, 2025-09
+The reduction of false positives in Sparse Factorization Machines Matsuzawa Takuya; Ito Taiki; ARIMA Sumika Procedia Computer Science/270/pp.802-811, 2025-09
 "INTERACTION MODELING OF HIGH-DIMENSIONAL DATA WITH THE BIAS AND HIGH CORRELATION- SPARSE FACTORIZATION MACHINES APPROACH Ozawa H.; ITO T.; Matsuzawa T.; Hoshino S.; Watanabe ... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10
 Robust Classifications of WBM Defect Patterns ARIMA Sumika; AI T.; MAEDA T.; SUMIYA K.; ITO T.; TA... Proceedings of the Semiconductor Wafer Test Conference Asia (SWTest Asia 2024), 2024-10
 Due dates assignment based on customer changeability classifications in Make-to-order productoins Shishido I.; Sakurai S.; 有馬 澄佳 Proceedings of the Asia Pacific Industrial Engineering &amp; Management Systems Conference 2024/2024/pp.1-6, 2024-11
@@ -12778,19 +12864,7 @@
 Interaction modeling of high-correlated data based on Sparse Factorization Machines and CHANOL Ozawa H.; Hoshino S.; ARIMA Sumika Procedia Computer Science/246/pp.2953-2963, 2024-09
 MULTI-OBJECTIVE N-STEP HYBRID FLOW-SHOP SCHEDULING IN THE CONSTRAINT TRANSFORMATION FORM WITH MULTI-PARAMETER OPTIMIZATION Lin Jia; MAO Chending; Arima Sumika Proceedings of International Symposium on Scheduling 2023/2023/pp.1-6, 2023-06-23
 Mixed-type Defect Pattern Classifications Maeda Takumi; Takada Daisuke; Arima Sumika Proceedings of AEC/APC Symposium Asia 2023/2023/pp.1-2, 2023-11-02
-Interaction Modelling of High Dimensional Production Data Hoshino Sara; Watanabe Kyo; Arima Sumika Procedia Computer Science/225/pp.4055-4064, 2023-12
-DUE DATE ASSIGNMENT OF MULTI-PRODUCT IN MAKE-TO-ORDER SUPPLY CHAINS Arima Sumika; Takahashi Haruki; Shishido Ibuki The Journal ACTA TECHNICA NAPOCENSIS - Series: APPLIED MATHEMATICS, MECHANICS, and ENGINEERING/66(1S)/pp.55-60, 2023-11
-MULTI-FACTORY SCHEDULING FOR A CORPORATED SUPPLY CHAIN Arima Sumika; Tahara Yusaku; Nagai Kosuke The Journal ACTA TECHNICA NAPOCENSIS - Series: APPLIED MATHEMATICS, MECHANICS, and ENGINEERING/66(SI)/pp.105-112, 2023-11
-Data-driven Modeling for Production Dynamics Arima Sumika; Y. SASAKI; MORIE S.; KATAOKA Y.; MAO C.; LIN... Proceesings of IEEE International Symposium on Semiconductor Manufacturing 2022/pp.1-4, 2022-12-12
-Self-tuning Optimization to Compatible the Delivery and Low Energy Consumption Arima Sumika; MAO C.; LIN J. Proceedings of IEEE International Symposium on Semiconductor Manufacturing 2022/pp.1-4, 2022-12
-MULTI-CRITERIA OPTIMIZATION OF N-STEP HYBRID FLOW-SHOP SCHEDULING - MAKE-TO-ORDER CASES WITH BATCH PROCESS - Arima Sumika; JIA Lin; Ohno Tomoki; MAO Chending; MORIE ... Proceedings of the 2022 International Symposium on Flexible Automation/(ISFA2022)/pp.1-8, 2022-07
-Sparse reluctant interaction modelling with Convex Hull Approximation - For accurate modelling of highly correlated variables based on diverse nearly optimal solutions - Arima Sumika; BU Huizhen; NAGATA Takuya; ONODERA Kakeru The Journal of the Japan Industrial Management Association/pp.1-10, 2022-07
-Interaction Modelings for Industrial Data - for final quality estimation and proess integration Arima Sumika; Limin Qin; Nagata Takuya; Handa Kotaro; Wat... Proceeding of AEC/APC symposium Asia 2021/pp.1-4, 2021-11
-スマホアプリ市場におけるヘビーユーザーのアプリ所持パターンと次期インストール数の関係 有馬 澄佳; 半田滉太朗 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-スマートフォンアプリの起動順序に着目したユーザーセグメント分析 大野智暉; 有馬 澄佳 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-従属需要の予測手法の構築と検証 有馬 澄佳; 小川陽平 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-スマートフォンアプリの起動順序に着目したユーザーセグメント分析 有馬 澄佳; 大野智暉 日本経営工学会秋季大会2020要綱集/pp.1-4, 2020-10
-Optimization of Multi-objective Function of n-step Hybrid Flowshop Scheduling J. LIN; Tomoki ONO; Sho MORIE; Qingxin ZHU; Yu SASAKI; Su... Proceedings of The International Symposium on Semiconductor Manufacturing 2020 (ISSM2020)/pp.1-4, 2020-12</t>
+Interaction Modelling of High Dimensional Production Data Hoshino Sara; Watanabe Kyo; Arima Sumika Procedia Computer Science/225/pp.4055-4064, 2023-12</t>
         </is>
       </c>
     </row>
@@ -13062,6 +13136,18 @@
 不動産賃料
 土地利用
 立地分析
+マニラ首都圏における洪水リスクが不動産賃料に与える影響の分析 釜谷 紘生; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.91-91, 2025-12
+立地アメニティとオフィス賃料 －オフィスビルにおける交通利便性の再考－ 青木 日花; 松尾 和史; 今関 豊和; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.89-89, 2025-12
+東京国際空港新飛行経路による不動産価値への影響分析のための広域騒音推計 早坂 遼; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.101-101, 2025-12
+金融機関店舗の跡地利用についての考察 西原 梨沙子; 堤 盛人 地理情報システム学会 予稿集/p.P2-40, 2025-11-01
+地方自治体のマイナンバーカード普及の空間分析 伊柳 佑康; 堤 盛人 地理情報システム学会 予稿集/p.P2-36, 2025-11-01
+立地アメニティとオフィス賃料 －オフィスビルにおける交通利便性の再考－ 青木 日花; 堤 盛人 地理情報システム学会 予稿集/p.D1-04, 2025-11-01
+マニラ首都圏における洪水リスクが不動産賃料に与える影響の分析 ― 賃料帯の異質性に着目して ― 釜谷 紘生; 堤 盛人 地理情報システム学会 予稿集/p.D4-04, 2025-11-01
+東京国際空港新飛行経路による不動産価値への影響分析のための広域騒音推計 早坂 遼; 堤 盛人 地理情報システム学会 予稿集/p.D6-04, 2025-11-01
+地籍調査の進捗に関する地理空間分析－市区町村の担当部署に着目して－ 佐藤 佳乃; 堤 盛人 地理情報システム学会 予稿集/p.P2-26, 2025-11-01
+物流を明示的に考慮した 応用都市経済モデルの開発の試み 久保 拓也; 堤 盛人 土木計画学研究・講演集/71/p.P02-35, 2025-06-07
+茨城県における金融機関跡地の地理空間分布とその利用状況についての考察 西原 梨沙子; 堤 盛人; 松尾 和史 第土木計画学研究・講演集/71/p.P01-15, 2025-06-07
+オフィスビルアメニティの概念整理と実態分析 青木日花; 松尾 和史; 今関 豊和; 堤 盛人 土木計画学研究・講演集/71/p.P02-18, 2025-06
 立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ 松尾和史; 瀬谷創; 堤 盛人; 今関豊和 土木計画学研究・講演集/69, 2024-05
 東京23区における賃貸オフィスビルストックの地域性と経年変化 松尾和史; 堤 盛人; 今関豊和 第33回地理情報システム学会研究発表大会 講演論文集, 2024-10
 The Impact of the Flight to Quality on Office Rents and Vacancy Matsuo Kazushi; TSUTSUMI Morito; IMAZEKI Toyokazu; KUD... Real Estate Management and Valuation/32(3)/pp.77-86, 2024-04
@@ -13074,19 +13160,7 @@
 Spillover Effect of Large Building Construction on Neighborhood Office Rents Matsuo Kazushi; Tsutsumi Morito Journal of Real Estate Portfolio Management, 2024-02
 Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics Sakuma Makoto; Matsuo Kazushi; Tsutsumi Morito; Imazek... ASIA-PACIFIC JOURNAL OF REGIONAL SCIENCE/8(1)/pp.185-237, 2024-01
 Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market Matsuo Kazushi; Tsutsumi Morito; Imazeki Toyokazu INTERNATIONAL REAL ESTATE REVIEW/26(1)/pp.1-41, 2023-04
-ビッグデータのためのローカルなオフィス賃料指数の開発 松尾和史; 村上大輔; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/30, 2022-10
-オフィス空室率の時空間変動に関する探索的小地域分析 松尾和史; 堤 盛人; 今関豊和 ジャレフ・ジャーナル/13/pp.e11-e14, 2021-10
-東京オフィス市場における 集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木学会論文集D3（土木計画学研究・論文集）/78(5)/pp.I_263-I_274, 2023-05
-北陸新幹線開通による大学選択への影響に関する実証的研究 西村大希; 松尾和史; 堤 盛人 土木計画学研究・講演集(CD-ROM)/66, 2022-11-6
-計量テキスト分析による道路橋を維持管理する技術力の解明の試み 宮原 史; 堤 盛人 土木学会論文集D3（土木計画学）/78(3)/pp.137-149, 2022
-土木技術者の経験と学習 ―地方整備局職員の研究所出向と道路構造物を維持管理する技術力に着目して― 宮原史; 堤 盛人 土木学会論文集H（教育）/78(1)/pp.20-37, 2022
-空室率データで見る東京オフィス市場の空間的特性 松尾和史; 堤 盛人; 今関豊和 GIS理論と応用/30(1)/pp.51-63, 2022-06
-インフラの維持管理に関する研修による技術力向上効果の評価 ―道路橋の点検に着目して― 宮原史; 堤 盛人 土木学会論文集/79(1)/p.22-00132, 2023-04
-東京オフィス市場における集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木計画学研究発表会・講演集/65/pp.PS2-PS23, 2022-06-04
-携帯位置情報データを用いた東京23区内における“オフィス出社”の時空間分析 松尾和史; 佐久間誠; 堤 盛人; 今関豊和 土木計画学研究・講演集(CD-ROM)/64, 2021-12-03
-改訂版ブルーム・タキソノミーを用いた道路橋を維持管理する技術力の解明の試み 宮原史; 堤 盛人 日本教育工学会全国大会講演論文集, 2021-10-16
-交通アクセシビリティの変化が 中学受験における学校選択に与える影響 馬場優樹; 堤 盛人 土木計画学研究・講演集, 2021-06-05
-モバイル端末の活用による地方自治体の道路維持業務支援の検討 由井貴大; 堤 盛人; 新井千乃 土木計画学研究・講演集/63, 2021-06-05</t>
+ビッグデータのためのローカルなオフィス賃料指数の開発 松尾和史; 村上大輔; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/30, 2022-10</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -13106,7 +13180,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ 松尾和史; 瀬谷創; 堤 盛人; 今関豊和 土木計画学研究・講演集/69, 2024-05 / 東京23区における賃貸オフィスビルストックの地域性と経年変化 松尾和史; 堤 盛人; 今関豊和 第33回地理情報システム学会研究発表大会 講演論文集, 2024-10 / The Impact of the Flight to Quality on Office Rents and Vacancy Matsuo Kazushi; TSUTSUMI Morito; IMAZEKI Toyokazu; KUD... Real Estate Management and Valuation/32(3)/pp.77-86, 2024-04 / Spillover Effect of Large Building Construction on Neighborhood Office Rents Matsuo Kazushi; TSUTSUMI Morito; IMAZEKI Toyokazu Journal of Real Estate Portfolio Management/30(2)/pp.103-120, 2024-02 / 地域属性と産業振興政策に着目した新設会社の立地に関する考察 堤 盛人; 木﨑拓真 土木計画学研究・講演集(CD-ROM)/67/p.P01-43, 2023 / 実用性を考慮したローカルな不動産価格指数の理論と実証. 松尾和史; 村上大輔; 堤 盛人; 今関豊和 土木計画学研究・講演集(CD-ROM)/67/p.P02-19, 2023 / デジタル化と立地がコロナ禍における私立中学校選択に与える影響. 馬場優樹; 伊柳佑康; 松尾和史; 堤 盛人 地理情報システム学会講演論文集/32/p.F1-03, 2023 / 大規模オフィスビルの竣工が近隣のオフィス賃料に与える影響：アメニティ効果 vs 供給効果. 松尾和史; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/32/pp.P1-P32, 2023 / 東京オフィス市場における 集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木学会論文集 D3 （土木計画学）/78/pp. I_263-I_274, 2023 / Spillover Effect of Large Building Construction on Neighborhood Office Rents Matsuo Kazushi; Tsutsumi Morito Journal of Real Estate Portfolio Management, 2024-02 / Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics Sakuma Makoto; Matsuo Kazushi; Tsutsumi Morito; Imazek... ASIA-PACIFIC JOURNAL OF REGIONAL SCIENCE/8(1)/pp.185-237, 2024-01 / Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market Matsuo Kazushi; Tsutsumi Morito; Imazeki Toyokazu INTERNATIONAL REAL ESTATE REVIEW/26(1)/pp.1-41, 2023-04 / ビッグデータのためのローカルなオフィス賃料指数の開発 松尾和史; 村上大輔; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/30, 2022-10 / オフィス空室率の時空間変動に関する探索的小地域分析 松尾和史; 堤 盛人; 今関豊和 ジャレフ・ジャーナル/13/pp.e11-e14, 2021-10 / 東京オフィス市場における 集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木学会論文集D3（土木計画学研究・論文集）/78(5)/pp.I_263-I_274, 2023-05 / 北陸新幹線開通による大学選択への影響に関する実証的研究 西村大希; 松尾和史; 堤 盛人 土木計画学研究・講演集(CD-ROM)/66, 2022-11-6 / 計量テキスト分析による道路橋を維持管理する技術力の解明の試み 宮原 史; 堤 盛人 土木学会論文集D3（土木計画学）/78(3)/pp.137-149, 2022 / 土木技術者の経験と学習 ―地方整備局職員の研究所出向と道路構造物を維持管理する技術力に着目して― 宮原史; 堤 盛人 土木学会論文集H（教育）/78(1)/pp.20-37, 2022 / 空室率データで見る東京オフィス市場の空間的特性 松尾和史; 堤 盛人; 今関豊和 GIS理論と応用/30(1)/pp.51-63, 2022-06 / インフラの維持管理に関する研修による技術力向上効果の評価 ―道路橋の点検に着目して― 宮原史; 堤 盛人 土木学会論文集/79(1)/p.22-00132, 2023-04 / 東京オフィス市場における集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木計画学研究発表会・講演集/65/pp.PS2-PS23, 2022-06-04 / 携帯位置情報データを用いた東京23区内における“オフィス出社”の時空間分析 松尾和史; 佐久間誠; 堤 盛人; 今関豊和 土木計画学研究・講演集(CD-ROM)/64, 2021-12-03 / 改訂版ブルーム・タキソノミーを用いた道路橋を維持管理する技術力の解明の試み 宮原史; 堤 盛人 日本教育工学会全国大会講演論文集, 2021-10-16 / 交通アクセシビリティの変化が 中学受験における学校選択に与える影響 馬場優樹; 堤 盛人 土木計画学研究・講演集, 2021-06-05 / モバイル端末の活用による地方自治体の道路維持業務支援の検討 由井貴大; 堤 盛人; 新井千乃 土木計画学研究・講演集/63, 2021-06-05</t>
+          <t>マニラ首都圏における洪水リスクが不動産賃料に与える影響の分析 釜谷 紘生; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.91-91, 2025-12 / 立地アメニティとオフィス賃料 －オフィスビルにおける交通利便性の再考－ 青木 日花; 松尾 和史; 今関 豊和; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.89-89, 2025-12 / 東京国際空港新飛行経路による不動産価値への影響分析のための広域騒音推計 早坂 遼; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.101-101, 2025-12 / 金融機関店舗の跡地利用についての考察 西原 梨沙子; 堤 盛人 地理情報システム学会 予稿集/p.P2-40, 2025-11-01 / 地方自治体のマイナンバーカード普及の空間分析 伊柳 佑康; 堤 盛人 地理情報システム学会 予稿集/p.P2-36, 2025-11-01 / 立地アメニティとオフィス賃料 －オフィスビルにおける交通利便性の再考－ 青木 日花; 堤 盛人 地理情報システム学会 予稿集/p.D1-04, 2025-11-01 / マニラ首都圏における洪水リスクが不動産賃料に与える影響の分析 ― 賃料帯の異質性に着目して ― 釜谷 紘生; 堤 盛人 地理情報システム学会 予稿集/p.D4-04, 2025-11-01 / 東京国際空港新飛行経路による不動産価値への影響分析のための広域騒音推計 早坂 遼; 堤 盛人 地理情報システム学会 予稿集/p.D6-04, 2025-11-01 / 地籍調査の進捗に関する地理空間分析－市区町村の担当部署に着目して－ 佐藤 佳乃; 堤 盛人 地理情報システム学会 予稿集/p.P2-26, 2025-11-01 / 物流を明示的に考慮した 応用都市経済モデルの開発の試み 久保 拓也; 堤 盛人 土木計画学研究・講演集/71/p.P02-35, 2025-06-07 / 茨城県における金融機関跡地の地理空間分布とその利用状況についての考察 西原 梨沙子; 堤 盛人; 松尾 和史 第土木計画学研究・講演集/71/p.P01-15, 2025-06-07 / オフィスビルアメニティの概念整理と実態分析 青木日花; 松尾 和史; 今関 豊和; 堤 盛人 土木計画学研究・講演集/71/p.P02-18, 2025-06 / 立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ 松尾和史; 瀬谷創; 堤 盛人; 今関豊和 土木計画学研究・講演集/69, 2024-05 / 東京23区における賃貸オフィスビルストックの地域性と経年変化 松尾和史; 堤 盛人; 今関豊和 第33回地理情報システム学会研究発表大会 講演論文集, 2024-10 / The Impact of the Flight to Quality on Office Rents and Vacancy Matsuo Kazushi; TSUTSUMI Morito; IMAZEKI Toyokazu; KUD... Real Estate Management and Valuation/32(3)/pp.77-86, 2024-04 / Spillover Effect of Large Building Construction on Neighborhood Office Rents Matsuo Kazushi; TSUTSUMI Morito; IMAZEKI Toyokazu Journal of Real Estate Portfolio Management/30(2)/pp.103-120, 2024-02 / 地域属性と産業振興政策に着目した新設会社の立地に関する考察 堤 盛人; 木﨑拓真 土木計画学研究・講演集(CD-ROM)/67/p.P01-43, 2023 / 実用性を考慮したローカルな不動産価格指数の理論と実証. 松尾和史; 村上大輔; 堤 盛人; 今関豊和 土木計画学研究・講演集(CD-ROM)/67/p.P02-19, 2023 / デジタル化と立地がコロナ禍における私立中学校選択に与える影響. 馬場優樹; 伊柳佑康; 松尾和史; 堤 盛人 地理情報システム学会講演論文集/32/p.F1-03, 2023 / 大規模オフィスビルの竣工が近隣のオフィス賃料に与える影響：アメニティ効果 vs 供給効果. 松尾和史; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/32/pp.P1-P32, 2023 / 東京オフィス市場における 集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木学会論文集 D3 （土木計画学）/78/pp. I_263-I_274, 2023 / Spillover Effect of Large Building Construction on Neighborhood Office Rents Matsuo Kazushi; Tsutsumi Morito Journal of Real Estate Portfolio Management, 2024-02 / Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics Sakuma Makoto; Matsuo Kazushi; Tsutsumi Morito; Imazek... ASIA-PACIFIC JOURNAL OF REGIONAL SCIENCE/8(1)/pp.185-237, 2024-01 / Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market Matsuo Kazushi; Tsutsumi Morito; Imazeki Toyokazu INTERNATIONAL REAL ESTATE REVIEW/26(1)/pp.1-41, 2023-04 / ビッグデータのためのローカルなオフィス賃料指数の開発 松尾和史; 村上大輔; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/30, 2022-10</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -13186,6 +13260,18 @@
 地方自治体における道路維持管理業務のため
 空間計量経済学における最重要課題への挑戦と新たな展開
 道路台帳を活かした道路アセットマネジメントに関する研究
+マニラ首都圏における洪水リスクが不動産賃料に与える影響の分析 釜谷 紘生; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.91-91, 2025-12
+立地アメニティとオフィス賃料 －オフィスビルにおける交通利便性の再考－ 青木 日花; 松尾 和史; 今関 豊和; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.89-89, 2025-12
+東京国際空港新飛行経路による不動産価値への影響分析のための広域騒音推計 早坂 遼; 堤 盛人 ＧＩＳ‐理論と応用/33(2)/pp.101-101, 2025-12
+金融機関店舗の跡地利用についての考察 西原 梨沙子; 堤 盛人 地理情報システム学会 予稿集/p.P2-40, 2025-11-01
+地方自治体のマイナンバーカード普及の空間分析 伊柳 佑康; 堤 盛人 地理情報システム学会 予稿集/p.P2-36, 2025-11-01
+立地アメニティとオフィス賃料 －オフィスビルにおける交通利便性の再考－ 青木 日花; 堤 盛人 地理情報システム学会 予稿集/p.D1-04, 2025-11-01
+マニラ首都圏における洪水リスクが不動産賃料に与える影響の分析 ― 賃料帯の異質性に着目して ― 釜谷 紘生; 堤 盛人 地理情報システム学会 予稿集/p.D4-04, 2025-11-01
+東京国際空港新飛行経路による不動産価値への影響分析のための広域騒音推計 早坂 遼; 堤 盛人 地理情報システム学会 予稿集/p.D6-04, 2025-11-01
+地籍調査の進捗に関する地理空間分析－市区町村の担当部署に着目して－ 佐藤 佳乃; 堤 盛人 地理情報システム学会 予稿集/p.P2-26, 2025-11-01
+物流を明示的に考慮した 応用都市経済モデルの開発の試み 久保 拓也; 堤 盛人 土木計画学研究・講演集/71/p.P02-35, 2025-06-07
+茨城県における金融機関跡地の地理空間分布とその利用状況についての考察 西原 梨沙子; 堤 盛人; 松尾 和史 第土木計画学研究・講演集/71/p.P01-15, 2025-06-07
+オフィスビルアメニティの概念整理と実態分析 青木日花; 松尾 和史; 今関 豊和; 堤 盛人 土木計画学研究・講演集/71/p.P02-18, 2025-06
 立地の魅力とその変遷～賃料と空室率で見るオフィス立地選好の定量分析～ 松尾和史; 瀬谷創; 堤 盛人; 今関豊和 土木計画学研究・講演集/69, 2024-05
 東京23区における賃貸オフィスビルストックの地域性と経年変化 松尾和史; 堤 盛人; 今関豊和 第33回地理情報システム学会研究発表大会 講演論文集, 2024-10
 The Impact of the Flight to Quality on Office Rents and Vacancy Matsuo Kazushi; TSUTSUMI Morito; IMAZEKI Toyokazu; KUD... Real Estate Management and Valuation/32(3)/pp.77-86, 2024-04
@@ -13198,19 +13284,7 @@
 Spillover Effect of Large Building Construction on Neighborhood Office Rents Matsuo Kazushi; Tsutsumi Morito Journal of Real Estate Portfolio Management, 2024-02
 Measuring office attendance during the COVID-19 pandemic with mobility data to quantify local trends and characteristics Sakuma Makoto; Matsuo Kazushi; Tsutsumi Morito; Imazek... ASIA-PACIFIC JOURNAL OF REGIONAL SCIENCE/8(1)/pp.185-237, 2024-01
 Asymmetric Dynamics of Rent and Vacancy Rates in the Tokyo Office Market Matsuo Kazushi; Tsutsumi Morito; Imazeki Toyokazu INTERNATIONAL REAL ESTATE REVIEW/26(1)/pp.1-41, 2023-04
-ビッグデータのためのローカルなオフィス賃料指数の開発 松尾和史; 村上大輔; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/30, 2022-10
-オフィス空室率の時空間変動に関する探索的小地域分析 松尾和史; 堤 盛人; 今関豊和 ジャレフ・ジャーナル/13/pp.e11-e14, 2021-10
-東京オフィス市場における 集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木学会論文集D3（土木計画学研究・論文集）/78(5)/pp.I_263-I_274, 2023-05
-北陸新幹線開通による大学選択への影響に関する実証的研究 西村大希; 松尾和史; 堤 盛人 土木計画学研究・講演集(CD-ROM)/66, 2022-11-6
-計量テキスト分析による道路橋を維持管理する技術力の解明の試み 宮原 史; 堤 盛人 土木学会論文集D3（土木計画学）/78(3)/pp.137-149, 2022
-土木技術者の経験と学習 ―地方整備局職員の研究所出向と道路構造物を維持管理する技術力に着目して― 宮原史; 堤 盛人 土木学会論文集H（教育）/78(1)/pp.20-37, 2022
-空室率データで見る東京オフィス市場の空間的特性 松尾和史; 堤 盛人; 今関豊和 GIS理論と応用/30(1)/pp.51-63, 2022-06
-インフラの維持管理に関する研修による技術力向上効果の評価 ―道路橋の点検に着目して― 宮原史; 堤 盛人 土木学会論文集/79(1)/p.22-00132, 2023-04
-東京オフィス市場における集積の経済・不経済とその時間的変化 松尾和史; 堤 盛人; 今関豊和 土木計画学研究発表会・講演集/65/pp.PS2-PS23, 2022-06-04
-携帯位置情報データを用いた東京23区内における“オフィス出社”の時空間分析 松尾和史; 佐久間誠; 堤 盛人; 今関豊和 土木計画学研究・講演集(CD-ROM)/64, 2021-12-03
-改訂版ブルーム・タキソノミーを用いた道路橋を維持管理する技術力の解明の試み 宮原史; 堤 盛人 日本教育工学会全国大会講演論文集, 2021-10-16
-交通アクセシビリティの変化が 中学受験における学校選択に与える影響 馬場優樹; 堤 盛人 土木計画学研究・講演集, 2021-06-05
-モバイル端末の活用による地方自治体の道路維持業務支援の検討 由井貴大; 堤 盛人; 新井千乃 土木計画学研究・講演集/63, 2021-06-05</t>
+ビッグデータのためのローカルなオフィス賃料指数の開発 松尾和史; 村上大輔; 堤 盛人; 今関豊和 地理情報システム学会講演論文集/30, 2022-10</t>
         </is>
       </c>
     </row>
@@ -13261,31 +13335,31 @@
 交通計画
 都市計画における態度・行動変容研究
 リスク･コミュニケーション
+自動運転バスのエクステリアへの印象評価と配慮行動意図に関する研究 星野明日美; 谷口 綾子; 河合英直 土木学会論文集D3(土木計画学(政策と実践)）, 2026
+一般市民の自動運転受容度の評価に向けた標準指標の提案 -複数都市への適用結果より- 前川凜; 谷口 綾子; 淺見知秀; 倉谷昌臣; 大井元揮; 金貞姫 土木学会論文集D3(土木計画学(政策と実践), 2026
+Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo Dibaj Samira; Keiichi Hizaki; Goto Rie; Taniguchi Aya... TRAVEL BEHAVIOUR AND SOCIETY/39, 2025-04
 ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07
-Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo Dibaj Samira; Keiichi Hizaki; Goto Rie; Taniguchi Aya... TRAVEL BEHAVIOUR AND SOCIETY/39, 2025-04
-Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt Miyadai Kasumi; Taniguchi Ayako INTERNATIONAL JOURNAL OF PSYCHOLOGY/58(1)/pp.403-403, 2023-12
-Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo TANIGUCHI Ayako Travel Behaviour and Society/39, 2025-04
-高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 交通工学, 2025-03
+高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 交通工学/11(3)/pp.11-21, 2025-03
+自動運転技術についての情報提供によるモラル・ハザード意識醸成可能性の基礎的実証研究 田中皓介; 中尾聡史; 谷口 綾子 実践政策学/10(2)/pp.149-154, 2024
+基礎自治体における電動キックボードビジネスのガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― 後藤りえ; 谷口 綾子; 樋崎恵一 交通工学論文集/10(2)/pp.10-18, 2024
+「東京2020オリパラ輸送チーム物語」の構築と，読者の態度変容－シビックプライドに着目して－ 中川権人; 谷口 綾子; 片桐暁 土木学会論文集D3（土木計画学（政策と実践））/80(3), 2024
+自動運転システムが地域のシビックプライドに与える影響 岩田剛弥; 谷口 綾子; 渡辺健太郎 実践政策学（Policy and Practice Studies）/9(2)/pp.217-225, 2024
+海外都市の専門家が懸念する電動キックボードシェアリング導入・運用の課題と助言 後藤りえ; 谷口 綾子; 樋崎恵一; 本間雄太 土木学会論文集D3（土木計画学（政策と実践）, 2023
 Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour Asumi Hoshino; TANIGUCHI Ayako; Kawai Terunao Proceeding of European Transport Conference held at Antwerp, 2024-09
+米国サンフランシスコ都市圏における自動運転タクシー普及に伴う社会的受容の変化―2時点のアンケート調査比較より― 谷口 綾子; 藤枝碧斗 第73回土木計画学研究・講演集(CD-ROM), 2026
+バス運転士不足問題に着目した自動運転技術の導入目的に関する新聞報道分析 織田渚颯; 谷口 綾子; 中尾聡史 第73回土木計画学研究・講演集(CD-ROM), 2026
+大学生の自転車ヘルメット着用阻害要因分析と官学連携による普及啓発策の提案 宗岡禾子; 植村菖太郎; 吉田歩加; 林凜太郎; 谷口 綾子; 平根英一; 安島結夏 第73回土木計画学研究・講演集(CD-ROM), 2026
+Mobility Communityの成長プロセスとReadiness Levelの指標化に関する試論 石部颯己; 神田佑亮; 竹口祐二; 土崎伸; 諸星賢治; 𠮷川令; 大井元揮; 東徹; 谷口 綾子 第73回土木計画学研究・講演集(CD-ROM), 2026
+米国サンフランシスコ都市圏における自動運転タクシーの社会的受容 -州政府との対話と市民意識調査結果より 谷口 綾子; 藤枝碧斗; 中川由賀; 鈴沖陽子; 岩月泰頼; 森田岳人; 宮木由貴子; 久保達弘 第72回土木計画学研究・講演集(CD-ROM), 2025
+超高齢社会体験ゲームが地域活動への態度に与える効果 吉田泰基; 谷口 綾子 第72回土木計画学研究・講演集(CD-ROM), 2025
+ドライブレコーダー映像を用いた自動運転バスの社会的受容評価に向けた基礎的集計 星野明日美; 谷口 綾子; 藤枝碧斗 第72回土木計画学研究・講演集(CD-ROM), 2025
+奥入瀬渓流利活用のあり方をめぐる関係主体の語りの質的分析 真谷健悟; 谷口 綾子; 倉谷昌臣 第72回土木計画学研究・講演集(CD-ROM), 2025
 おつかい行動に見る子どもの移動自由性の世代変化と要因分析 中尾聡史; 谷口 綾子; 山下知華; 新井優輔 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 真谷健悟; 谷口 綾子; 岩田剛弥 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 星野明日美; 谷口 綾子; 倉谷昌臣; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― 大月崇義; 谷口 綾子; 片桐暁; 吉田泰基 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― 織田渚颯; 谷口 綾子; 吉田泰基; 淺見知秀; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06
-モビリティのイノベーションに，モビリティ･マネジメントをどう活かすか？ 谷口 綾子 環境情報科学(特集：持続可能なモビリティシフト), 2025-04
-モビリティ・マネジメントと健康福祉・教育 谷口 綾子 都市住宅学(特集：健康に過ごせる都市・住宅づくり最前線)/(72), 2025-01
-日米の車両生成データ制作の現状とEUのData Actの波及可能性 齋木亮作; 谷口 綾子 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-SWC首長研究会への加盟有無(健康都市づくりに対する首長の意識)と公共交通分担率が住民の心身の健康に与える影響 内田海; 谷口 綾子; 田邉解; 久野譜也 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-「報復の空白」と「運」が交通事故時の道徳的判断に与える影響－自動運転と手動運転の比較分析－ 大野弘佑起; 谷口 綾子; 久木田水生 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-東京都区部の電動キックボードシェア利用実態と利用体験・交通手段別視点による比較分析 樋崎恵一; 谷口 綾子; 後藤りえ 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-米国における自動運転タクシーの社会的受容とその要因分析－人身事故経験を有する二都市に着目して 前川凜; 谷口 綾子 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-おつかい行動に見る子どもの移動自由性の世代変化とその要因分析，最近の調査研究から 谷口 綾子 日本交通政策研究会, 2024-11
-新たなモビリティの規制緩和－思考停止の日本人，大丈夫？ 谷口 綾子 都市計画/(371), 2024-10
-モビリティ・マネジメントとの出会いと今後 谷口 綾子; 淺見知秀 アーバン・アドバンス/82/pp.13-24, 2024-09
-基礎自治体における電動キックボードビジネス のガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― 後藤りえ; 谷口 綾子; 樋崎恵一 第69回土木計画学研究・講演集(CD-ROM), 2024-05
-高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 第69回土木計画学研究・講演集(CD-ROM), 2024-05
-米国の自動運転車両の事故発生後の 社会的受容の比較分析 前川凜; 谷口 綾子 第69回土木計画学研究・講演集(CD-ROM), 2024-05
-奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討 真谷健悟; 谷口 綾子; 倉谷昌臣 第69回土木計画学研究・講演集(CD-ROM), 2024-05</t>
+モビリティの潜在価値を最大化するプラットフォームや人材の要件に関する研究 山原けい; 神田佑亮; 竹口祐二; 大井元揮; 土崎伸; 𠮷川令; 東徹; 諸星賢治; 谷口 綾子 第71回土木計画学研究・講演集(CD-ROM), 2025</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -13305,7 +13379,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07 / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo Dibaj Samira; Keiichi Hizaki; Goto Rie; Taniguchi Aya... TRAVEL BEHAVIOUR AND SOCIETY/39, 2025-04 / Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt Miyadai Kasumi; Taniguchi Ayako INTERNATIONAL JOURNAL OF PSYCHOLOGY/58(1)/pp.403-403, 2023-12 / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo TANIGUCHI Ayako Travel Behaviour and Society/39, 2025-04 / 高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 交通工学, 2025-03 / Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour Asumi Hoshino; TANIGUCHI Ayako; Kawai Terunao Proceeding of European Transport Conference held at Antwerp, 2024-09 / おつかい行動に見る子どもの移動自由性の世代変化と要因分析 中尾聡史; 谷口 綾子; 山下知華; 新井優輔 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 真谷健悟; 谷口 綾子; 岩田剛弥 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 星野明日美; 谷口 綾子; 倉谷昌臣; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― 大月崇義; 谷口 綾子; 片桐暁; 吉田泰基 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― 織田渚颯; 谷口 綾子; 吉田泰基; 淺見知秀; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / モビリティのイノベーションに，モビリティ･マネジメントをどう活かすか？ 谷口 綾子 環境情報科学(特集：持続可能なモビリティシフト), 2025-04 / モビリティ・マネジメントと健康福祉・教育 谷口 綾子 都市住宅学(特集：健康に過ごせる都市・住宅づくり最前線)/(72), 2025-01 / 日米の車両生成データ制作の現状とEUのData Actの波及可能性 齋木亮作; 谷口 綾子 第70回土木計画学研究・講演集(CD-ROM), 2024-11 / SWC首長研究会への加盟有無(健康都市づくりに対する首長の意識)と公共交通分担率が住民の心身の健康に与える影響 内田海; 谷口 綾子; 田邉解; 久野譜也 第70回土木計画学研究・講演集(CD-ROM), 2024-11 / 「報復の空白」と「運」が交通事故時の道徳的判断に与える影響－自動運転と手動運転の比較分析－ 大野弘佑起; 谷口 綾子; 久木田水生 第70回土木計画学研究・講演集(CD-ROM), 2024-11 / 東京都区部の電動キックボードシェア利用実態と利用体験・交通手段別視点による比較分析 樋崎恵一; 谷口 綾子; 後藤りえ 第70回土木計画学研究・講演集(CD-ROM), 2024-11 / 米国における自動運転タクシーの社会的受容とその要因分析－人身事故経験を有する二都市に着目して 前川凜; 谷口 綾子 第70回土木計画学研究・講演集(CD-ROM), 2024-11 / おつかい行動に見る子どもの移動自由性の世代変化とその要因分析，最近の調査研究から 谷口 綾子 日本交通政策研究会, 2024-11 / 新たなモビリティの規制緩和－思考停止の日本人，大丈夫？ 谷口 綾子 都市計画/(371), 2024-10 / モビリティ・マネジメントとの出会いと今後 谷口 綾子; 淺見知秀 アーバン・アドバンス/82/pp.13-24, 2024-09 / 基礎自治体における電動キックボードビジネス のガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― 後藤りえ; 谷口 綾子; 樋崎恵一 第69回土木計画学研究・講演集(CD-ROM), 2024-05 / 高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 第69回土木計画学研究・講演集(CD-ROM), 2024-05 / 米国の自動運転車両の事故発生後の 社会的受容の比較分析 前川凜; 谷口 綾子 第69回土木計画学研究・講演集(CD-ROM), 2024-05 / 奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討 真谷健悟; 谷口 綾子; 倉谷昌臣 第69回土木計画学研究・講演集(CD-ROM), 2024-05</t>
+          <t>自動運転バスのエクステリアへの印象評価と配慮行動意図に関する研究 星野明日美; 谷口 綾子; 河合英直 土木学会論文集D3(土木計画学(政策と実践)）, 2026 / 一般市民の自動運転受容度の評価に向けた標準指標の提案 -複数都市への適用結果より- 前川凜; 谷口 綾子; 淺見知秀; 倉谷昌臣; 大井元揮; 金貞姫 土木学会論文集D3(土木計画学(政策と実践), 2026 / Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo Dibaj Samira; Keiichi Hizaki; Goto Rie; Taniguchi Aya... TRAVEL BEHAVIOUR AND SOCIETY/39, 2025-04 / ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07 / 高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 交通工学/11(3)/pp.11-21, 2025-03 / 自動運転技術についての情報提供によるモラル・ハザード意識醸成可能性の基礎的実証研究 田中皓介; 中尾聡史; 谷口 綾子 実践政策学/10(2)/pp.149-154, 2024 / 基礎自治体における電動キックボードビジネスのガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― 後藤りえ; 谷口 綾子; 樋崎恵一 交通工学論文集/10(2)/pp.10-18, 2024 / 「東京2020オリパラ輸送チーム物語」の構築と，読者の態度変容－シビックプライドに着目して－ 中川権人; 谷口 綾子; 片桐暁 土木学会論文集D3（土木計画学（政策と実践））/80(3), 2024 / 自動運転システムが地域のシビックプライドに与える影響 岩田剛弥; 谷口 綾子; 渡辺健太郎 実践政策学（Policy and Practice Studies）/9(2)/pp.217-225, 2024 / 海外都市の専門家が懸念する電動キックボードシェアリング導入・運用の課題と助言 後藤りえ; 谷口 綾子; 樋崎恵一; 本間雄太 土木学会論文集D3（土木計画学（政策と実践）, 2023 / Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour Asumi Hoshino; TANIGUCHI Ayako; Kawai Terunao Proceeding of European Transport Conference held at Antwerp, 2024-09 / 米国サンフランシスコ都市圏における自動運転タクシー普及に伴う社会的受容の変化―2時点のアンケート調査比較より― 谷口 綾子; 藤枝碧斗 第73回土木計画学研究・講演集(CD-ROM), 2026 / バス運転士不足問題に着目した自動運転技術の導入目的に関する新聞報道分析 織田渚颯; 谷口 綾子; 中尾聡史 第73回土木計画学研究・講演集(CD-ROM), 2026 / 大学生の自転車ヘルメット着用阻害要因分析と官学連携による普及啓発策の提案 宗岡禾子; 植村菖太郎; 吉田歩加; 林凜太郎; 谷口 綾子; 平根英一; 安島結夏 第73回土木計画学研究・講演集(CD-ROM), 2026 / Mobility Communityの成長プロセスとReadiness Levelの指標化に関する試論 石部颯己; 神田佑亮; 竹口祐二; 土崎伸; 諸星賢治; 𠮷川令; 大井元揮; 東徹; 谷口 綾子 第73回土木計画学研究・講演集(CD-ROM), 2026 / 米国サンフランシスコ都市圏における自動運転タクシーの社会的受容 -州政府との対話と市民意識調査結果より 谷口 綾子; 藤枝碧斗; 中川由賀; 鈴沖陽子; 岩月泰頼; 森田岳人; 宮木由貴子; 久保達弘 第72回土木計画学研究・講演集(CD-ROM), 2025 / 超高齢社会体験ゲームが地域活動への態度に与える効果 吉田泰基; 谷口 綾子 第72回土木計画学研究・講演集(CD-ROM), 2025 / ドライブレコーダー映像を用いた自動運転バスの社会的受容評価に向けた基礎的集計 星野明日美; 谷口 綾子; 藤枝碧斗 第72回土木計画学研究・講演集(CD-ROM), 2025 / 奥入瀬渓流利活用のあり方をめぐる関係主体の語りの質的分析 真谷健悟; 谷口 綾子; 倉谷昌臣 第72回土木計画学研究・講演集(CD-ROM), 2025 / おつかい行動に見る子どもの移動自由性の世代変化と要因分析 中尾聡史; 谷口 綾子; 山下知華; 新井優輔 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 真谷健悟; 谷口 綾子; 岩田剛弥 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 星野明日美; 谷口 綾子; 倉谷昌臣; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― 大月崇義; 谷口 綾子; 片桐暁; 吉田泰基 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― 織田渚颯; 谷口 綾子; 吉田泰基; 淺見知秀; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06 / モビリティの潜在価値を最大化するプラットフォームや人材の要件に関する研究 山原けい; 神田佑亮; 竹口祐二; 大井元揮; 土崎伸; 𠮷川令; 東徹; 諸星賢治; 谷口 綾子 第71回土木計画学研究・講演集(CD-ROM), 2025</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -13375,31 +13449,31 @@
 ASEAN諸国におけるモビリティ・マネジメントの実行可能性に関する実証分析
 道路上の異モード間コミュニケーションの生起と社会的受容
 健康に配慮した交通行動誘発のための学際的研究
+自動運転バスのエクステリアへの印象評価と配慮行動意図に関する研究 星野明日美; 谷口 綾子; 河合英直 土木学会論文集D3(土木計画学(政策と実践)）, 2026
+一般市民の自動運転受容度の評価に向けた標準指標の提案 -複数都市への適用結果より- 前川凜; 谷口 綾子; 淺見知秀; 倉谷昌臣; 大井元揮; 金貞姫 土木学会論文集D3(土木計画学(政策と実践), 2026
+Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo Dibaj Samira; Keiichi Hizaki; Goto Rie; Taniguchi Aya... TRAVEL BEHAVIOUR AND SOCIETY/39, 2025-04
 ゲーム理論の枠組みを援用した交通すごろくの効果検証と戦略分析 前川 凜; 谷口 綾子; 秋山 英三 土木学会論文集(土木計画学)/80(20), 2025-07
-Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo Dibaj Samira; Keiichi Hizaki; Goto Rie; Taniguchi Aya... TRAVEL BEHAVIOUR AND SOCIETY/39, 2025-04
-Psychological process model to ease home-redelivery problems in Japan - Focusing on customer guilt Miyadai Kasumi; Taniguchi Ayako INTERNATIONAL JOURNAL OF PSYCHOLOGY/58(1)/pp.403-403, 2023-12
-Latent class approach to classify e-scooter non-users: A comparative study of Helsinki and Tokyo TANIGUCHI Ayako Travel Behaviour and Society/39, 2025-04
-高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 交通工学, 2025-03
+高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 交通工学/11(3)/pp.11-21, 2025-03
+自動運転技術についての情報提供によるモラル・ハザード意識醸成可能性の基礎的実証研究 田中皓介; 中尾聡史; 谷口 綾子 実践政策学/10(2)/pp.149-154, 2024
+基礎自治体における電動キックボードビジネスのガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― 後藤りえ; 谷口 綾子; 樋崎恵一 交通工学論文集/10(2)/pp.10-18, 2024
+「東京2020オリパラ輸送チーム物語」の構築と，読者の態度変容－シビックプライドに着目して－ 中川権人; 谷口 綾子; 片桐暁 土木学会論文集D3（土木計画学（政策と実践））/80(3), 2024
+自動運転システムが地域のシビックプライドに与える影響 岩田剛弥; 谷口 綾子; 渡辺健太郎 実践政策学（Policy and Practice Studies）/9(2)/pp.217-225, 2024
+海外都市の専門家が懸念する電動キックボードシェアリング導入・運用の課題と助言 後藤りえ; 谷口 綾子; 樋崎恵一; 本間雄太 土木学会論文集D3（土木計画学（政策と実践）, 2023
 Evaluation of the Impression of the Exterior of Autonomous Buses and How This Impression Elicits Cooperative Behaviour Asumi Hoshino; TANIGUCHI Ayako; Kawai Terunao Proceeding of European Transport Conference held at Antwerp, 2024-09
+米国サンフランシスコ都市圏における自動運転タクシー普及に伴う社会的受容の変化―2時点のアンケート調査比較より― 谷口 綾子; 藤枝碧斗 第73回土木計画学研究・講演集(CD-ROM), 2026
+バス運転士不足問題に着目した自動運転技術の導入目的に関する新聞報道分析 織田渚颯; 谷口 綾子; 中尾聡史 第73回土木計画学研究・講演集(CD-ROM), 2026
+大学生の自転車ヘルメット着用阻害要因分析と官学連携による普及啓発策の提案 宗岡禾子; 植村菖太郎; 吉田歩加; 林凜太郎; 谷口 綾子; 平根英一; 安島結夏 第73回土木計画学研究・講演集(CD-ROM), 2026
+Mobility Communityの成長プロセスとReadiness Levelの指標化に関する試論 石部颯己; 神田佑亮; 竹口祐二; 土崎伸; 諸星賢治; 𠮷川令; 大井元揮; 東徹; 谷口 綾子 第73回土木計画学研究・講演集(CD-ROM), 2026
+米国サンフランシスコ都市圏における自動運転タクシーの社会的受容 -州政府との対話と市民意識調査結果より 谷口 綾子; 藤枝碧斗; 中川由賀; 鈴沖陽子; 岩月泰頼; 森田岳人; 宮木由貴子; 久保達弘 第72回土木計画学研究・講演集(CD-ROM), 2025
+超高齢社会体験ゲームが地域活動への態度に与える効果 吉田泰基; 谷口 綾子 第72回土木計画学研究・講演集(CD-ROM), 2025
+ドライブレコーダー映像を用いた自動運転バスの社会的受容評価に向けた基礎的集計 星野明日美; 谷口 綾子; 藤枝碧斗 第72回土木計画学研究・講演集(CD-ROM), 2025
+奥入瀬渓流利活用のあり方をめぐる関係主体の語りの質的分析 真谷健悟; 谷口 綾子; 倉谷昌臣 第72回土木計画学研究・講演集(CD-ROM), 2025
 おつかい行動に見る子どもの移動自由性の世代変化と要因分析 中尾聡史; 谷口 綾子; 山下知華; 新井優輔 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 高速道路利用者の渋滞情報提供媒体の利用実態と出発時間変更意図に関する分析 真谷健悟; 谷口 綾子; 岩田剛弥 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 奥入瀬渓流における自動運転バスのラッピング検討のプロセスと観光客の評価 星野明日美; 谷口 綾子; 倉谷昌臣; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 地域モビリティ人材育成団体「再生塾」の物語構築とその態度変容効果－職業コミットメントに着目して― 大月崇義; 谷口 綾子; 片桐暁; 吉田泰基 第71回土木計画学研究・講演集(CD-ROM), 2025-06
 脱炭素先行地域でのモビリティ・マネジメントにおける動機付け効果の検証－太陽光発電・地域公共交通への態度に着目して― 織田渚颯; 谷口 綾子; 吉田泰基; 淺見知秀; 齋藤綾 第71回土木計画学研究・講演集(CD-ROM), 2025-06
-モビリティのイノベーションに，モビリティ･マネジメントをどう活かすか？ 谷口 綾子 環境情報科学(特集：持続可能なモビリティシフト), 2025-04
-モビリティ・マネジメントと健康福祉・教育 谷口 綾子 都市住宅学(特集：健康に過ごせる都市・住宅づくり最前線)/(72), 2025-01
-日米の車両生成データ制作の現状とEUのData Actの波及可能性 齋木亮作; 谷口 綾子 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-SWC首長研究会への加盟有無(健康都市づくりに対する首長の意識)と公共交通分担率が住民の心身の健康に与える影響 内田海; 谷口 綾子; 田邉解; 久野譜也 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-「報復の空白」と「運」が交通事故時の道徳的判断に与える影響－自動運転と手動運転の比較分析－ 大野弘佑起; 谷口 綾子; 久木田水生 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-東京都区部の電動キックボードシェア利用実態と利用体験・交通手段別視点による比較分析 樋崎恵一; 谷口 綾子; 後藤りえ 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-米国における自動運転タクシーの社会的受容とその要因分析－人身事故経験を有する二都市に着目して 前川凜; 谷口 綾子 第70回土木計画学研究・講演集(CD-ROM), 2024-11
-おつかい行動に見る子どもの移動自由性の世代変化とその要因分析，最近の調査研究から 谷口 綾子 日本交通政策研究会, 2024-11
-新たなモビリティの規制緩和－思考停止の日本人，大丈夫？ 谷口 綾子 都市計画/(371), 2024-10
-モビリティ・マネジメントとの出会いと今後 谷口 綾子; 淺見知秀 アーバン・アドバンス/82/pp.13-24, 2024-09
-基礎自治体における電動キックボードビジネス のガバナンス方法とその課題 ―ヘルシンキの事例と日本への示唆― 後藤りえ; 谷口 綾子; 樋崎恵一 第69回土木計画学研究・講演集(CD-ROM), 2024-05
-高齢運転者向け認知機能検査における制度変更の影響評価 渡邊芳樹; 谷口 綾子; 張詠皓 第69回土木計画学研究・講演集(CD-ROM), 2024-05
-米国の自動運転車両の事故発生後の 社会的受容の比較分析 前川凜; 谷口 綾子 第69回土木計画学研究・講演集(CD-ROM), 2024-05
-奥入瀬渓流の観光の質向上に向けた小中学生向けエコツアーの効果計測と普及促進への検討 真谷健悟; 谷口 綾子; 倉谷昌臣 第69回土木計画学研究・講演集(CD-ROM), 2024-05</t>
+モビリティの潜在価値を最大化するプラットフォームや人材の要件に関する研究 山原けい; 神田佑亮; 竹口祐二; 大井元揮; 土崎伸; 𠮷川令; 東徹; 諸星賢治; 谷口 綾子 第71回土木計画学研究・講演集(CD-ROM), 2025</t>
         </is>
       </c>
     </row>
@@ -13438,6 +13512,7 @@
         <is>
           <t>トポロジー的組合せ論と組合せ論におけるトポロジー的手法
 組合せ的構造に関する研究
+単体的複体のシェラビリティーおよび関連概念、極小反例の視点による研究
 Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求
 デジタル指紋符号、多重接続通信路、及び組合せ探索問題
 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発
@@ -13445,7 +13520,6 @@
 部分構造への等質性を基軸とする単体的複体の構造解析
 ネットワーク上の時間軸をもった最適化問題とその応用
 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化
-実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開
 数学基礎・応用数学
 組合せ論
 トポロジー的組合せ論
@@ -13482,7 +13556,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>トポロジー的組合せ論と組合せ論におけるトポロジー的手法 / 組合せ的構造に関する研究 / Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求 / デジタル指紋符号、多重接続通信路、及び組合せ探索問題 / 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / 部分構造への等質性を基軸とする単体的複体の構造解析 / ネットワーク上の時間軸をもった最適化問題とその応用 / 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化 / 実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開</t>
+          <t>トポロジー的組合せ論と組合せ論におけるトポロジー的手法 / 組合せ的構造に関する研究 / 単体的複体のシェラビリティーおよび関連概念、極小反例の視点による研究 / Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求 / デジタル指紋符号、多重接続通信路、及び組合せ探索問題 / 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発 / 錐最適化における半正定値錐の多面錐近似の理論の構築とその応用 / 部分構造への等質性を基軸とする単体的複体の構造解析 / ネットワーク上の時間軸をもった最適化問題とその応用 / 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -13548,6 +13622,7 @@
 特定の形をした直径が6の木グラフに対するGraceful Labeling
 トポロジー的組合せ論と組合せ論におけるトポロジー的手法
 組合せ的構造に関する研究
+単体的複体のシェラビリティーおよび関連概念、極小反例の視点による研究
 Nonpure複体の分割構造を軸とした単体的複体の組合せ構造の探求
 デジタル指紋符号、多重接続通信路、及び組合せ探索問題
 大規模データ時代のネットワーク最適化に対する実応用に向けた説明力のある手法開発
@@ -13555,7 +13630,6 @@
 部分構造への等質性を基軸とする単体的複体の構造解析
 ネットワーク上の時間軸をもった最適化問題とその応用
 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化
-実問題への適応能力のあるネットワーク最適化アルゴリズムと構造解析手法の発展的展開
 The average expected value of a rooted graph, Monte Carlo calculation, and a power index for the voting game Hachimori Masahiro Discrete Applied Mathematics/377/pp.74-86, 2025-12
 Coloring zonotopal quadrangulations of the projective space Masahiro Hachimori; Atsuhiro Nakamoto; Kenta Ozeki EUROPEAN JOURNAL OF COMBINATORICS/125/p.104089, 2025-03
 Several minimality concepts related to Frankl's conjecture Masahiro Hachimori; Kenji Kashiwabara Graphs and Combinatorics/40(6), 2024-11
@@ -13631,6 +13705,7 @@
 符号理論
 情報セキュリティ
 グループ検査
+FRACTAL DIMENSION OF SUBSTITUTION TREE NETWORKS Zeng Qingcheng; Xue Yumei; Wang Daohua; Miao Ying FRACTALS-COMPLEX GEOMETRY PATTERNS AND SCALING IN NATURE AND SOCIETY, 2025-10-28
 版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) MIAO Ying 中国科学数学, 2023
 A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) MIAO Ying 2022 IEEE International Multi-Conference on Engineering, Computer and Information Sciences (SIBIRCON), 2022/11
 Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) MIAO Ying Problems of Information Transmission/59(1)/pp.14-21, 2023/1
@@ -13654,8 +13729,7 @@
 Probabilistic Existence Results for Parent-Identifying Schemes Gu Yujie; Cheng Minquan; Kabatiansky Grigory; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/65(10)/pp.6160-6170, 2019-10
 Non-adaptive group testing on graphs with connectivity Luo S.; Matsuura Y.; Miao Ying; Shigeno Maiko Journal of Combinatorial Optimization/38(1)/pp.278-291, 2019
 Bounds on Traceability Schemes Gu Yujie; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/64(5)/pp.3450-3460, 2018-05
-New Bounds for Frameproof Codes Shangguan Chong; Wang Xin; Ge Gennian; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/63(11)/pp.7247-7252, 2017-11
-Zero-difference balanced functions with new parameters and their applications Cai H.; Zhou Z.; Tang X; Miao Ying IEEE Transactions on Information Theory/63(7)/pp.4379-4387, 2017-06</t>
+New Bounds for Frameproof Codes Shangguan Chong; Wang Xin; Ge Gennian; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/63(11)/pp.7247-7252, 2017-11</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -13675,7 +13749,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) MIAO Ying 中国科学数学, 2023 / A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) MIAO Ying 2022 IEEE International Multi-Conference on Engineering, Computer and Information Sciences (SIBIRCON), 2022/11 / Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) MIAO Ying Problems of Information Transmission/59(1)/pp.14-21, 2023/1 / Repairing Schemes for Tamo-Barg Codes Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/71(1)/pp.227-243, 2025-01 / A Construction of Optimal One-Coincidence Frequency-Hopping Sequences via Generalized Cyclotomy Shao Minfeng; Miao Ying ENTROPY/26(11), 2024-11 / Secure Codes With List Decoding Gu Yujie; Vorobyev Ilya; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/70(4)/pp.2430-2442, 2024-04 / Codes for Exact Support Recovery of Sparse Vectors from Inaccurate Linear Measurements and Their Decoding Fernandez M.; Kabatiansky G. A.; Kruglik S. A.; Miao Y. PROBLEMS OF INFORMATION TRANSMISSION/59(1)/pp.14-21, 2023-01 / Optimal Locally Repairable Codes: An Improved Bound and Constructions Cai Han; Fan Cuiling; Miao Ying; Schwartz Moshe; Tang... IEEE TRANSACTIONS ON INFORMATION THEORY/68(8)/pp.5060-5074, 2022-08 / On the Information-Theoretic Security of Combinatorial All-or-Nothing Transforms Gu Yujie; Akao Sonata; Esfahani Navid Nasr; Miao Ying... IEEE TRANSACTIONS ON INFORMATION THEORY/68(10)/pp.6904-6914, 2022-10 / A Construction of Maximally Recoverable Codes With Order-Optimal Field Size Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/68(1)/pp.204-212, 2022-01 / Capacity-Achieving Private Information Retrieval Schemes From Uncoded Storage Constrained Servers With Low Sub-Packetization Zhu Jinbao; Yan Qifa; Tang Xiaohu; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/67(8)/pp.5370-5386, 2021-08 / BCH codes with minimum distance proportional to code length Noguchi Satoshi; Lu Xiao-Nan; Jimbo Masakazu; Miao Ying SIAM Journal on Discrete Mathematics/35(1)/pp.179-193, 2021-02 / Existence and Construction of Complete Traceability Multimedia Fingerprinting Codes Resistant to Averaging Attack and Adversarial Noise Egorova E. E.; Fernandez M.; Kabatiansky G. A.; Miao Y. PROBLEMS OF INFORMATION TRANSMISSION/56(4)/pp.388-398, 2020-12 / Strongly separable matrices for nonadaptive combinatorial group testing Fan Jinping; Fu Hung-Lin; Gu Yujie; Miao Ying; Shigen... DISCRETE APPLIED MATHEMATICS/291/pp.180-187, 2021-03 / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting Fan Jinping; Gu Yujie; Hachimori Masahiro; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/67(1)/pp.200-216, 2021-01 / Algebraic manipulation detection codes via highly nonlinear functions Shao Minfeng; Miao Ying CRYPTOGRAPHY AND COMMUNICATIONS-DISCRETE-STRUCTURES BOOLEAN FUNCTIONS AND SEQUENCES/Epub, 2021-02 / On Optimal Locally Repairable Codes With Super-Linear Length Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/66(8)/pp.4853-4868, 2020-08 / On optimal weak algebraic manipulation detection codes and weighted external difference families Shao Minfeng; Miao Ying DESIGNS CODES AND CRYPTOGRAPHY/Epub, 2020-04 / On Optimal Locally Repairable Codes With Multiple Disjoint Repair Sets Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/66(4)/pp.2402-2416, 2020-04 / Improved Bounds for Separable Codes and B-2 Codes Gu Yujie; Fan Jinping; Miao Ying IEEE COMMUNICATIONS LETTERS/24(1)/pp.15-19, 2020-01 / Probabilistic Existence Results for Parent-Identifying Schemes Gu Yujie; Cheng Minquan; Kabatiansky Grigory; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/65(10)/pp.6160-6170, 2019-10 / Non-adaptive group testing on graphs with connectivity Luo S.; Matsuura Y.; Miao Ying; Shigeno Maiko Journal of Combinatorial Optimization/38(1)/pp.278-291, 2019 / Bounds on Traceability Schemes Gu Yujie; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/64(5)/pp.3450-3460, 2018-05 / New Bounds for Frameproof Codes Shangguan Chong; Wang Xin; Ge Gennian; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/63(11)/pp.7247-7252, 2017-11 / Zero-difference balanced functions with new parameters and their applications Cai H.; Zhou Z.; Tang X; Miao Ying IEEE Transactions on Information Theory/63(7)/pp.4379-4387, 2017-06</t>
+          <t>FRACTAL DIMENSION OF SUBSTITUTION TREE NETWORKS Zeng Qingcheng; Xue Yumei; Wang Daohua; Miao Ying FRACTALS-COMPLEX GEOMETRY PATTERNS AND SCALING IN NATURE AND SOCIETY, 2025-10-28 / 版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) MIAO Ying 中国科学数学, 2023 / A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) MIAO Ying 2022 IEEE International Multi-Conference on Engineering, Computer and Information Sciences (SIBIRCON), 2022/11 / Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) MIAO Ying Problems of Information Transmission/59(1)/pp.14-21, 2023/1 / Repairing Schemes for Tamo-Barg Codes Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/71(1)/pp.227-243, 2025-01 / A Construction of Optimal One-Coincidence Frequency-Hopping Sequences via Generalized Cyclotomy Shao Minfeng; Miao Ying ENTROPY/26(11), 2024-11 / Secure Codes With List Decoding Gu Yujie; Vorobyev Ilya; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/70(4)/pp.2430-2442, 2024-04 / Codes for Exact Support Recovery of Sparse Vectors from Inaccurate Linear Measurements and Their Decoding Fernandez M.; Kabatiansky G. A.; Kruglik S. A.; Miao Y. PROBLEMS OF INFORMATION TRANSMISSION/59(1)/pp.14-21, 2023-01 / Optimal Locally Repairable Codes: An Improved Bound and Constructions Cai Han; Fan Cuiling; Miao Ying; Schwartz Moshe; Tang... IEEE TRANSACTIONS ON INFORMATION THEORY/68(8)/pp.5060-5074, 2022-08 / On the Information-Theoretic Security of Combinatorial All-or-Nothing Transforms Gu Yujie; Akao Sonata; Esfahani Navid Nasr; Miao Ying... IEEE TRANSACTIONS ON INFORMATION THEORY/68(10)/pp.6904-6914, 2022-10 / A Construction of Maximally Recoverable Codes With Order-Optimal Field Size Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/68(1)/pp.204-212, 2022-01 / Capacity-Achieving Private Information Retrieval Schemes From Uncoded Storage Constrained Servers With Low Sub-Packetization Zhu Jinbao; Yan Qifa; Tang Xiaohu; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/67(8)/pp.5370-5386, 2021-08 / BCH codes with minimum distance proportional to code length Noguchi Satoshi; Lu Xiao-Nan; Jimbo Masakazu; Miao Ying SIAM Journal on Discrete Mathematics/35(1)/pp.179-193, 2021-02 / Existence and Construction of Complete Traceability Multimedia Fingerprinting Codes Resistant to Averaging Attack and Adversarial Noise Egorova E. E.; Fernandez M.; Kabatiansky G. A.; Miao Y. PROBLEMS OF INFORMATION TRANSMISSION/56(4)/pp.388-398, 2020-12 / Strongly separable matrices for nonadaptive combinatorial group testing Fan Jinping; Fu Hung-Lin; Gu Yujie; Miao Ying; Shigen... DISCRETE APPLIED MATHEMATICS/291/pp.180-187, 2021-03 / Signature Codes for Weighted Binary Adder Channel and Multimedia Fingerprinting Fan Jinping; Gu Yujie; Hachimori Masahiro; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/67(1)/pp.200-216, 2021-01 / Algebraic manipulation detection codes via highly nonlinear functions Shao Minfeng; Miao Ying CRYPTOGRAPHY AND COMMUNICATIONS-DISCRETE-STRUCTURES BOOLEAN FUNCTIONS AND SEQUENCES/Epub, 2021-02 / On Optimal Locally Repairable Codes With Super-Linear Length Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/66(8)/pp.4853-4868, 2020-08 / On optimal weak algebraic manipulation detection codes and weighted external difference families Shao Minfeng; Miao Ying DESIGNS CODES AND CRYPTOGRAPHY/Epub, 2020-04 / On Optimal Locally Repairable Codes With Multiple Disjoint Repair Sets Cai Han; Miao Ying; Schwartz Moshe; Tang Xiaohu IEEE TRANSACTIONS ON INFORMATION THEORY/66(4)/pp.2402-2416, 2020-04 / Improved Bounds for Separable Codes and B-2 Codes Gu Yujie; Fan Jinping; Miao Ying IEEE COMMUNICATIONS LETTERS/24(1)/pp.15-19, 2020-01 / Probabilistic Existence Results for Parent-Identifying Schemes Gu Yujie; Cheng Minquan; Kabatiansky Grigory; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/65(10)/pp.6160-6170, 2019-10 / Non-adaptive group testing on graphs with connectivity Luo S.; Matsuura Y.; Miao Ying; Shigeno Maiko Journal of Combinatorial Optimization/38(1)/pp.278-291, 2019 / Bounds on Traceability Schemes Gu Yujie; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/64(5)/pp.3450-3460, 2018-05 / New Bounds for Frameproof Codes Shangguan Chong; Wang Xin; Ge Gennian; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/63(11)/pp.7247-7252, 2017-11</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -13719,6 +13793,7 @@
 組合せ的デザイン理論を用いた周波数ホッピング系列の構成に関する研究
 組合せ的デザイン理論を用いた光直交符号の構成に関する研究
 組合せ的デザインとその符号・暗号への応用
+FRACTAL DIMENSION OF SUBSTITUTION TREE NETWORKS Zeng Qingcheng; Xue Yumei; Wang Daohua; Miao Ying FRACTALS-COMPLEX GEOMETRY PATTERNS AND SCALING IN NATURE AND SOCIETY, 2025-10-28
 版权保护中的组合安全码及相关问题 (范金萍, 顾玉杰, 缪莹) MIAO Ying 中国科学数学, 2023
 A Novel Support Recovery Algorithms and Its Applications to Multiple-Access Channels (M Fernandez, G Kabatiansky, Y Miao) MIAO Ying 2022 IEEE International Multi-Conference on Engineering, Computer and Information Sciences (SIBIRCON), 2022/11
 Codes for exact support recovery of sparse vectors from inaccurate linear measurements and their decoding (M Fernandez, GA Kabatiansky, SA Kruglik, Y Miao) MIAO Ying Problems of Information Transmission/59(1)/pp.14-21, 2023/1
@@ -13742,8 +13817,7 @@
 Probabilistic Existence Results for Parent-Identifying Schemes Gu Yujie; Cheng Minquan; Kabatiansky Grigory; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/65(10)/pp.6160-6170, 2019-10
 Non-adaptive group testing on graphs with connectivity Luo S.; Matsuura Y.; Miao Ying; Shigeno Maiko Journal of Combinatorial Optimization/38(1)/pp.278-291, 2019
 Bounds on Traceability Schemes Gu Yujie; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/64(5)/pp.3450-3460, 2018-05
-New Bounds for Frameproof Codes Shangguan Chong; Wang Xin; Ge Gennian; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/63(11)/pp.7247-7252, 2017-11
-Zero-difference balanced functions with new parameters and their applications Cai H.; Zhou Z.; Tang X; Miao Ying IEEE Transactions on Information Theory/63(7)/pp.4379-4387, 2017-06</t>
+New Bounds for Frameproof Codes Shangguan Chong; Wang Xin; Ge Gennian; Miao Ying IEEE TRANSACTIONS ON INFORMATION THEORY/63(11)/pp.7247-7252, 2017-11</t>
         </is>
       </c>
     </row>
@@ -13792,8 +13866,8 @@
 走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー
 土木計画学・交通工学
 交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム
-Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/p.in press, 2026-01
-A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/p.in press, 2025-12
+Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/24/pp.250-264, 2026-04
+A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/24/pp.216-225, 2026-04
 都市鉄道整備推進に向けた事業制度に関する研究 石丸 真也; 森田 泰智; 浅井 遼馬; 和田 健太郎; 日比野 直彦 運輸政策研究/28/pp.6-16, 2026-02
 Stability analysis of a departure time choice problem with atomic vehicle models Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/189/p.103039, 2024-11
 自動運転車両の速度制御を考慮した系統信号制御に関する考察 梅村 悠生; 和田 健太郎 交通工学論文集/10(1)/pp.A_10-A_17, 2024-02
@@ -13836,7 +13910,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/p.in press, 2026-01 / A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/p.in press, 2025-12 / 都市鉄道整備推進に向けた事業制度に関する研究 石丸 真也; 森田 泰智; 浅井 遼馬; 和田 健太郎; 日比野 直彦 運輸政策研究/28/pp.6-16, 2026-02 / Stability analysis of a departure time choice problem with atomic vehicle models Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/189/p.103039, 2024-11 / 自動運転車両の速度制御を考慮した系統信号制御に関する考察 梅村 悠生; 和田 健太郎 交通工学論文集/10(1)/pp.A_10-A_17, 2024-02 / 追従モデルによる高速道路サグ部のCapacity Drop現象の再現 甲斐 慎一朗; 和田 健太郎; 堀口 良太 土木学会論文集D3（土木計画学）/78(5)/pp.I_963-I_971, 2023-05 / 連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析 金﨑 圭吾; 和田 健太郎 土木学会論文集D3（土木計画学）/78(5)/pp.I_911-I_918, 2023-05 / テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル 和田 健太郎; 岩見 悠太郎 土木学会論文集D3（土木計画学）/78(5)/pp.I_899-I_909, 2023-05 / Predicting traffic breakdown in expressways using linear combination of vehicle detector data Shigemi Rikuto; Ando Hiroyasu; Wada Kentaro; Mukai Risa Nonlinear Theory and Its Applications, IEICE/14(2)/pp.416-427, 2023-04 / Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals Zhang Jiahua; Wada Kentaro; Oguchi Takashi TRANSPORTMETRICA B-TRANSPORT DYNAMICS/11(1)/pp.1256-1280, 2023-03 / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 和田 健太郎; 金﨑 圭吾; 西田 匡志; 平井 章一 交通工学論文集/9(2)/pp.A_326-A_334, 2023-02 / 連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析 甲斐 慎一朗; 和田 健太郎; 堀口 良太; 邢 健 交通工学論文集/9(2)/pp.A_280-A_287, 2023-02 / Dynamic traffic assignment in a corridor network: Optimum versus equilibrium Haoran Fu; Takashi Akamatsu; Koki Satsukawa; Kentaro Wada Transportation Research Part B: Methodological/161/pp.218-246, 2022-07 / 高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム 岸川 知樹; 和田 健太郎 土木学会論文集D3（土木計画学）/77(5)/pp.I_1109-I_1119, 2022-05 / 需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡 板橋 昂汰; 和田 健太郎 土木学会論文集D3（土木計画学）/77(5)/pp.I_1045-I_1055, 2022-05 / Fundamental diagram of urban rail transit considering train-passenger interaction Seo Toru; Wada Kentaro; Fukuda Daisuke Transportation/Epub(50)/pp.1399-1424, 2023-08 / 高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム 和田 健太郎; 邢 健; 大口 敬 交通工学論文集/8(3)/pp.1-10, 2022-04 / 高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動 和田 健太郎; 甲斐 慎一朗; 堀口 良太 交通工学論文集/8(2)/pp.A_1-A_8, 2022-02 Tsukuba Repository / Dynamic system optimal traffic assignment with atomic users: Convergence and stability Satsukawa Koki; Wada Kentaro; Watling David Transportation Research Part B: Methodological/155/pp.188-209, 2022-01 / A new look at departure time choice equilibrium models with heterogeneous users Akamatsu Takashi; Wada Kentaro; Iryo Takamasa; Hayashi S... Transportation Research Part B: Methodological/148/pp.152-182, 2021-06 / 動的交通均衡配分理論の近年の進展 和田 健太郎 土木学会論文集D3（土木計画学）/76(5)/pp.I_21-I_39, 2021-04 / Continuum car-following model of capacity drop at sag and tunnel bottlenecks Wada Kentaro; Martínez Irene; Jin Wen-Long Transportation Research Part C: Emerging Technologies/113/pp.260-276, 2020-04 / Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/132(SI)/pp.117-135, 2020-02 / Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/125/pp.229-247, 2019-05 Tsukuba Repository / Trading mechanisms for bottleneck permits with multiple purchase opportunities Wang Pengfei; Wada Kentaro; Akamatsu Takashi; Nagae Takeshi Transportation Research Part C: Emerging Technologies/95/pp.414-430, 2018-10</t>
+          <t>Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/24/pp.250-264, 2026-04 / A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/24/pp.216-225, 2026-04 / 都市鉄道整備推進に向けた事業制度に関する研究 石丸 真也; 森田 泰智; 浅井 遼馬; 和田 健太郎; 日比野 直彦 運輸政策研究/28/pp.6-16, 2026-02 / Stability analysis of a departure time choice problem with atomic vehicle models Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/189/p.103039, 2024-11 / 自動運転車両の速度制御を考慮した系統信号制御に関する考察 梅村 悠生; 和田 健太郎 交通工学論文集/10(1)/pp.A_10-A_17, 2024-02 / 追従モデルによる高速道路サグ部のCapacity Drop現象の再現 甲斐 慎一朗; 和田 健太郎; 堀口 良太 土木学会論文集D3（土木計画学）/78(5)/pp.I_963-I_971, 2023-05 / 連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析 金﨑 圭吾; 和田 健太郎 土木学会論文集D3（土木計画学）/78(5)/pp.I_911-I_918, 2023-05 / テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル 和田 健太郎; 岩見 悠太郎 土木学会論文集D3（土木計画学）/78(5)/pp.I_899-I_909, 2023-05 / Predicting traffic breakdown in expressways using linear combination of vehicle detector data Shigemi Rikuto; Ando Hiroyasu; Wada Kentaro; Mukai Risa Nonlinear Theory and Its Applications, IEICE/14(2)/pp.416-427, 2023-04 / Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals Zhang Jiahua; Wada Kentaro; Oguchi Takashi TRANSPORTMETRICA B-TRANSPORT DYNAMICS/11(1)/pp.1256-1280, 2023-03 / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 和田 健太郎; 金﨑 圭吾; 西田 匡志; 平井 章一 交通工学論文集/9(2)/pp.A_326-A_334, 2023-02 / 連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析 甲斐 慎一朗; 和田 健太郎; 堀口 良太; 邢 健 交通工学論文集/9(2)/pp.A_280-A_287, 2023-02 / Dynamic traffic assignment in a corridor network: Optimum versus equilibrium Haoran Fu; Takashi Akamatsu; Koki Satsukawa; Kentaro Wada Transportation Research Part B: Methodological/161/pp.218-246, 2022-07 / 高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム 岸川 知樹; 和田 健太郎 土木学会論文集D3（土木計画学）/77(5)/pp.I_1109-I_1119, 2022-05 / 需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡 板橋 昂汰; 和田 健太郎 土木学会論文集D3（土木計画学）/77(5)/pp.I_1045-I_1055, 2022-05 / Fundamental diagram of urban rail transit considering train-passenger interaction Seo Toru; Wada Kentaro; Fukuda Daisuke Transportation/Epub(50)/pp.1399-1424, 2023-08 / 高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム 和田 健太郎; 邢 健; 大口 敬 交通工学論文集/8(3)/pp.1-10, 2022-04 / 高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動 和田 健太郎; 甲斐 慎一朗; 堀口 良太 交通工学論文集/8(2)/pp.A_1-A_8, 2022-02 Tsukuba Repository / Dynamic system optimal traffic assignment with atomic users: Convergence and stability Satsukawa Koki; Wada Kentaro; Watling David Transportation Research Part B: Methodological/155/pp.188-209, 2022-01 / A new look at departure time choice equilibrium models with heterogeneous users Akamatsu Takashi; Wada Kentaro; Iryo Takamasa; Hayashi S... Transportation Research Part B: Methodological/148/pp.152-182, 2021-06 / 動的交通均衡配分理論の近年の進展 和田 健太郎 土木学会論文集D3（土木計画学）/76(5)/pp.I_21-I_39, 2021-04 / Continuum car-following model of capacity drop at sag and tunnel bottlenecks Wada Kentaro; Martínez Irene; Jin Wen-Long Transportation Research Part C: Emerging Technologies/113/pp.260-276, 2020-04 / Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/132(SI)/pp.117-135, 2020-02 / Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/125/pp.229-247, 2019-05 Tsukuba Repository / Trading mechanisms for bottleneck permits with multiple purchase opportunities Wang Pengfei; Wada Kentaro; Akamatsu Takashi; Nagae Takeshi Transportation Research Part C: Emerging Technologies/95/pp.414-430, 2018-10</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -13904,8 +13978,8 @@
 バイオミメティックスに学ぶスマートな都市退化マネジメント
 AI計算リソースとしての実交通ダイナミクスの活用技術の開発
 走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー
-Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/p.in press, 2026-01
-A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/p.in press, 2025-12
+Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/24/pp.250-264, 2026-04
+A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/24/pp.216-225, 2026-04
 都市鉄道整備推進に向けた事業制度に関する研究 石丸 真也; 森田 泰智; 浅井 遼馬; 和田 健太郎; 日比野 直彦 運輸政策研究/28/pp.6-16, 2026-02
 Stability analysis of a departure time choice problem with atomic vehicle models Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/189/p.103039, 2024-11
 自動運転車両の速度制御を考慮した系統信号制御に関する考察 梅村 悠生; 和田 健太郎 交通工学論文集/10(1)/pp.A_10-A_17, 2024-02
@@ -14120,6 +14194,8 @@
 地域公共交通
 地理情報科学
 都市リスク分析
+A Semi-Supervised Framework for Road Condition Assessment: From Minor Surface Distress to Post-Disaster Failures Tsujimoto Eda; Eom Sunyong; Suzuki Tsutomu IEEE Open Journal of Intelligent Transportation Systems/7/pp.1244-1263, 2026-05
+GPSデータに基づく都市内移動効率の計測と交通軸の抽出 竹内真雄; 嚴先鏞; 鈴木勉 都市計画論文集/61(1)/pp.149-158, 2026-04
 起伏を考慮した低炭素都市交通施策の評価 Luo Linyan; 鈴木 勉 地理情報システム学会講演論文集, 2025-10
 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2025-10
 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析 飛松涼太; 石井儀光; 鈴木勉 都市計画報告集/24(4)/pp.567-570, 2026-03
@@ -14142,9 +14218,7 @@
 Exploring Separation Strategies for Car-Bicycle Integration Liu Liling; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
 アジア地域の都市における鉄道・道路と人口分布構造 神﨑達也; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
 建物主要用途・トリップチェーンに着目した人流データによる街区間トリップ特性 早坂遼; 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
-人流データによる街区レベル時間帯別発生集中の時空間分布 竹内真雄; 早坂遼; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
-人口重心に着目した人流分析 一井直人; 鈴木 勉; 大澤義明 地理情報システム学会講演論文集, 2022
-沿道電柱密度の地域別・道路種別比較 欧陽君顔; 大澤義明; 鈴木 勉 地理情報システム学会講演論文集, 2022</t>
+人流データによる街区レベル時間帯別発生集中の時空間分布 竹内真雄; 早坂遼; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -14164,7 +14238,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>起伏を考慮した低炭素都市交通施策の評価 Luo Linyan; 鈴木 勉 地理情報システム学会講演論文集, 2025-10 / 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2025-10 / 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析 飛松涼太; 石井儀光; 鈴木勉 都市計画報告集/24(4)/pp.567-570, 2026-03 / 東京区部における年齢構成類型の変化と生活利便施設へのアクシセビリティ分析 飛松涼太; 石井儀光; 鈴木勉 都市計画報告集/24(3)/pp.391-397, 2025-12 / 電柱広告の空間的配置に関する研究―筑波研究学園都市中心部を対象に― 竹内真雄; 鈴木脩矢; 田所達也; 池澤隼映; 大川駿介; 安部桂佑; 熊野喬元; 廣田陽香; 田畑優希; 塩野目... 都市計画報告集/24(4)/pp.515-520, 2026-03 / Exploring Network Scale Separation Strategies for Car-Bicycle Integration Liu Liling; Eom Sunyong; Suzuki Tsutomu Transportation Research Interdisciplinary Perspectives/36, 2026-03 / 都市条件に応じた複数公共交通モード併用によるネットワーク設計 竹内真雄; 鈴木勉 都市計画論文集/60(3)/pp.1535-1542, 2025-11 / 全国鉄道駅周辺地域における地域分断による移動制約の定量評価 北口立大; 嚴先鏞; 鈴木勉 都市計画論文集/60(2)/pp.248-255, 2025-08 / 小地域人口の年齢構成類型とその遷移から見た安定性分析 飛松涼太; 嚴先鏞; 鈴木勉 都市計画論文集/59(3)/pp.1232-1239, 2024-11 / 東京区部における業種構成・滞在パターンに基づく商業集積地の類型化と滞在移動特性の分析 竹内真雄; 嚴先鏞; 鈴木勉 都市計画論文集/59(3)/pp.555-562, 2024-11 / 東京区部におけるGPSデータに基づく街区レベル発生集中・滞在移動特性と建物用途構成 竹内真雄; 早坂遼; 嚴先鏞; 鈴木勉 都市計画論文集/59(2)/pp.177-188, 2024-11 / 人口分布の集積性と鉄道網との連携度の変化動向に関する研究 神﨑達也; 嚴先鏞; 鈴木勉 都市計画報告集/23(4), 2025-03 / 東京区部における人口年齢構成と土地利用遷移の関連性分析 飛松涼太; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2024-10 / 東京区部における交通量密度・移動速度に基づく交通軸と移動効率性評価 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2024-10 / 鉄道網による移動時間短縮を考慮した都市の人口分布の集積性の評価 神﨑達也; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2024-10 / 人流データによる滞在者平均年齢の時空間分析 ―昼や休日に若返る自治体はどこか？― 田村侑介; 鈴木 勉; 大澤義明 地理情報システム学会講演論文集, 2024-10 / 通学距離最小化と安定マッチングによる学校割当 神﨑達也; 嚴先鏞; 鈴木 勉 オペレーションズ・リサーチ/69(7)/pp.355-360, 2024-07 / Preference-based jogging route selection in Downtown Tokyo Huang Yumeng; Eom Sunyong; Suzuki Tsutomu Cities &amp; Health/pp.1-15, 2024-02 / Effect of Speed Control for Travel Time and Emission Reduction in Connected Vehicle Environment Liu Yuheng; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / Exploring Separation Strategies for Car-Bicycle Integration Liu Liling; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / アジア地域の都市における鉄道・道路と人口分布構造 神﨑達也; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / 建物主要用途・トリップチェーンに着目した人流データによる街区間トリップ特性 早坂遼; 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / 人流データによる街区レベル時間帯別発生集中の時空間分布 竹内真雄; 早坂遼; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / 人口重心に着目した人流分析 一井直人; 鈴木 勉; 大澤義明 地理情報システム学会講演論文集, 2022 / 沿道電柱密度の地域別・道路種別比較 欧陽君顔; 大澤義明; 鈴木 勉 地理情報システム学会講演論文集, 2022</t>
+          <t>A Semi-Supervised Framework for Road Condition Assessment: From Minor Surface Distress to Post-Disaster Failures Tsujimoto Eda; Eom Sunyong; Suzuki Tsutomu IEEE Open Journal of Intelligent Transportation Systems/7/pp.1244-1263, 2026-05 / GPSデータに基づく都市内移動効率の計測と交通軸の抽出 竹内真雄; 嚴先鏞; 鈴木勉 都市計画論文集/61(1)/pp.149-158, 2026-04 / 起伏を考慮した低炭素都市交通施策の評価 Luo Linyan; 鈴木 勉 地理情報システム学会講演論文集, 2025-10 / 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2025-10 / 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析 飛松涼太; 石井儀光; 鈴木勉 都市計画報告集/24(4)/pp.567-570, 2026-03 / 東京区部における年齢構成類型の変化と生活利便施設へのアクシセビリティ分析 飛松涼太; 石井儀光; 鈴木勉 都市計画報告集/24(3)/pp.391-397, 2025-12 / 電柱広告の空間的配置に関する研究―筑波研究学園都市中心部を対象に― 竹内真雄; 鈴木脩矢; 田所達也; 池澤隼映; 大川駿介; 安部桂佑; 熊野喬元; 廣田陽香; 田畑優希; 塩野目... 都市計画報告集/24(4)/pp.515-520, 2026-03 / Exploring Network Scale Separation Strategies for Car-Bicycle Integration Liu Liling; Eom Sunyong; Suzuki Tsutomu Transportation Research Interdisciplinary Perspectives/36, 2026-03 / 都市条件に応じた複数公共交通モード併用によるネットワーク設計 竹内真雄; 鈴木勉 都市計画論文集/60(3)/pp.1535-1542, 2025-11 / 全国鉄道駅周辺地域における地域分断による移動制約の定量評価 北口立大; 嚴先鏞; 鈴木勉 都市計画論文集/60(2)/pp.248-255, 2025-08 / 小地域人口の年齢構成類型とその遷移から見た安定性分析 飛松涼太; 嚴先鏞; 鈴木勉 都市計画論文集/59(3)/pp.1232-1239, 2024-11 / 東京区部における業種構成・滞在パターンに基づく商業集積地の類型化と滞在移動特性の分析 竹内真雄; 嚴先鏞; 鈴木勉 都市計画論文集/59(3)/pp.555-562, 2024-11 / 東京区部におけるGPSデータに基づく街区レベル発生集中・滞在移動特性と建物用途構成 竹内真雄; 早坂遼; 嚴先鏞; 鈴木勉 都市計画論文集/59(2)/pp.177-188, 2024-11 / 人口分布の集積性と鉄道網との連携度の変化動向に関する研究 神﨑達也; 嚴先鏞; 鈴木勉 都市計画報告集/23(4), 2025-03 / 東京区部における人口年齢構成と土地利用遷移の関連性分析 飛松涼太; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2024-10 / 東京区部における交通量密度・移動速度に基づく交通軸と移動効率性評価 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2024-10 / 鉄道網による移動時間短縮を考慮した都市の人口分布の集積性の評価 神﨑達也; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2024-10 / 人流データによる滞在者平均年齢の時空間分析 ―昼や休日に若返る自治体はどこか？― 田村侑介; 鈴木 勉; 大澤義明 地理情報システム学会講演論文集, 2024-10 / 通学距離最小化と安定マッチングによる学校割当 神﨑達也; 嚴先鏞; 鈴木 勉 オペレーションズ・リサーチ/69(7)/pp.355-360, 2024-07 / Preference-based jogging route selection in Downtown Tokyo Huang Yumeng; Eom Sunyong; Suzuki Tsutomu Cities &amp; Health/pp.1-15, 2024-02 / Effect of Speed Control for Travel Time and Emission Reduction in Connected Vehicle Environment Liu Yuheng; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / Exploring Separation Strategies for Car-Bicycle Integration Liu Liling; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / アジア地域の都市における鉄道・道路と人口分布構造 神﨑達也; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / 建物主要用途・トリップチェーンに着目した人流データによる街区間トリップ特性 早坂遼; 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023 / 人流データによる街区レベル時間帯別発生集中の時空間分布 竹内真雄; 早坂遼; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -14252,6 +14326,8 @@
 水害時の住民避難をより安全にする広域避難対策の社会的実装を図る計画技術の構築
 都市の拠点集約と拠点間ネットワークの空間分析
 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究
+A Semi-Supervised Framework for Road Condition Assessment: From Minor Surface Distress to Post-Disaster Failures Tsujimoto Eda; Eom Sunyong; Suzuki Tsutomu IEEE Open Journal of Intelligent Transportation Systems/7/pp.1244-1263, 2026-05
+GPSデータに基づく都市内移動効率の計測と交通軸の抽出 竹内真雄; 嚴先鏞; 鈴木勉 都市計画論文集/61(1)/pp.149-158, 2026-04
 起伏を考慮した低炭素都市交通施策の評価 Luo Linyan; 鈴木 勉 地理情報システム学会講演論文集, 2025-10
 多世代の位置情報に基づく滞在集積の時空間分布と年代間相関 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2025-10
 東京区部における土地利用遷移と年齢構成・高齢化率変化の関連分析 飛松涼太; 石井儀光; 鈴木勉 都市計画報告集/24(4)/pp.567-570, 2026-03
@@ -14274,9 +14350,7 @@
 Exploring Separation Strategies for Car-Bicycle Integration Liu Liling; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
 アジア地域の都市における鉄道・道路と人口分布構造 神﨑達也; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
 建物主要用途・トリップチェーンに着目した人流データによる街区間トリップ特性 早坂遼; 竹内真雄; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
-人流データによる街区レベル時間帯別発生集中の時空間分布 竹内真雄; 早坂遼; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023
-人口重心に着目した人流分析 一井直人; 鈴木 勉; 大澤義明 地理情報システム学会講演論文集, 2022
-沿道電柱密度の地域別・道路種別比較 欧陽君顔; 大澤義明; 鈴木 勉 地理情報システム学会講演論文集, 2022</t>
+人流データによる街区レベル時間帯別発生集中の時空間分布 竹内真雄; 早坂遼; 嚴先鏞; 鈴木 勉 地理情報システム学会講演論文集, 2023</t>
         </is>
       </c>
     </row>
@@ -14514,6 +14588,11 @@
 交通シミュレーション
 災害復旧
 相互作用
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
+Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12
+A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12
+Robust OD matrix estimation method under low sampling rate by utilizing multiscale information of questionnaire data Mochizuki Y.; Pel A.J.; Hinsbergen C.; URATA Junji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06
+Developing an Estimation Algorithm for Generalizing the Parameters of the network-GEV model in Destination Choice URATA Junji; KANEDA Yudai; ISHII Ryoji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06
 通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ 上杉 朋花; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11
 EVユーザーの充電場所選択問題に対するゲーム理論的考察 大野 隆輔; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11
 災害復旧期における個々人の移動パターン変化の特徴分析 村上 智仁; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11
@@ -14532,12 +14611,7 @@
 Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository
 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02
 選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02
-LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09
-日本の復興計画の研究動向と今後の展望 -1995年以降の建築・都市・土木の計画分野を中心に- 小野 悠; 井本 佐保里; 浦田 淳司; 萩原 拓也; 羽藤 英二 日本建築学会計画系論文集/87(799), 2022-09
-選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 第42回交通工学研究発表会論文報告集/42/pp.381-388, 2022-08
-災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 第42回交通工学研究発表会論文報告集/42/pp.389-396, 2022-08
-LET'S GO ABROAD!(第77回)シンガポール、パキスタン、アフガニスタン、ベトナム、カンボジア 地域建設業の海外展開と見据える未来—A regional construction company looks to overseas expansion and their future—特集 土木と地政学 才田 善之; 金子 辰生; 浦田 淳司 土木学会誌/107(5)/pp.38-40, 2022-05
-「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学 浦田 淳司; 森 弘継; 高松 俊介; 西村 俊亮 土木学会誌/107(5)/pp.41-43, 2022-05</t>
+LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -14557,7 +14631,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ 上杉 朋花; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / EVユーザーの充電場所選択問題に対するゲーム理論的考察 大野 隆輔; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / 災害復旧期における個々人の移動パターン変化の特徴分析 村上 智仁; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / メタ分析による災害時の避難開始選択要因の評価 柴田 龍聖; 浦田 淳司; 大東 延幸 第72回土木計画学研究発表会・講演集, 2025-11 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction URATA Junji; NAKAZAWA Ruka THE 29TH INTERNATIONAL CONFERENCE OF HONG KONG SOCIETY FOR TRANSPORTATION STUDIES, 2025-12 / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging Mochizuki Y.; 浦田 淳司; Hato E. 2024 IEEE 27th International Conference on Intelligent Transportation Systems (ITSC)/pp.653-660, 2025-03 / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 田村 侑介; 浦田 淳司 都市計画論文集/60(3)/pp.1543-1550, 2025-10 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 相互作用下での多肢選択行動の量子計算による求解 中澤瑠河; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- 中嶋 駿; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- 中山 凛空; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— 河瀬理貴; 井料隆雅; 浦田 淳司 土木学会論文集, 2024-12 / Object-oriented Bayesian Networks for Activity-based Model with deep generative graph averaging URATA Junji; Mochizuki Y.; Hato E. IEEE 27th International Conference on Intelligent Transportation Systems, 2024-09 / 筑波大学理工学群におけるデータサイエンス応用基礎教育 浦田 淳司; オム ソンヨン; 川島 宏一 大学教育と情報, 2024-03 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02 / 選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02 / LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09 / 日本の復興計画の研究動向と今後の展望 -1995年以降の建築・都市・土木の計画分野を中心に- 小野 悠; 井本 佐保里; 浦田 淳司; 萩原 拓也; 羽藤 英二 日本建築学会計画系論文集/87(799), 2022-09 / 選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 第42回交通工学研究発表会論文報告集/42/pp.381-388, 2022-08 / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 第42回交通工学研究発表会論文報告集/42/pp.389-396, 2022-08 / LET'S GO ABROAD!(第77回)シンガポール、パキスタン、アフガニスタン、ベトナム、カンボジア 地域建設業の海外展開と見据える未来—A regional construction company looks to overseas expansion and their future—特集 土木と地政学 才田 善之; 金子 辰生; 浦田 淳司 土木学会誌/107(5)/pp.38-40, 2022-05 / 「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学 浦田 淳司; 森 弘継; 高松 俊介; 西村 俊亮 土木学会誌/107(5)/pp.41-43, 2022-05</t>
+          <t>大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12 / A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12 / Robust OD matrix estimation method under low sampling rate by utilizing multiscale information of questionnaire data Mochizuki Y.; Pel A.J.; Hinsbergen C.; URATA Junji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06 / Developing an Estimation Algorithm for Generalizing the Parameters of the network-GEV model in Destination Choice URATA Junji; KANEDA Yudai; ISHII Ryoji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06 / 通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ 上杉 朋花; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / EVユーザーの充電場所選択問題に対するゲーム理論的考察 大野 隆輔; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / 災害復旧期における個々人の移動パターン変化の特徴分析 村上 智仁; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / メタ分析による災害時の避難開始選択要因の評価 柴田 龍聖; 浦田 淳司; 大東 延幸 第72回土木計画学研究発表会・講演集, 2025-11 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction URATA Junji; NAKAZAWA Ruka THE 29TH INTERNATIONAL CONFERENCE OF HONG KONG SOCIETY FOR TRANSPORTATION STUDIES, 2025-12 / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging Mochizuki Y.; 浦田 淳司; Hato E. 2024 IEEE 27th International Conference on Intelligent Transportation Systems (ITSC)/pp.653-660, 2025-03 / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 田村 侑介; 浦田 淳司 都市計画論文集/60(3)/pp.1543-1550, 2025-10 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 相互作用下での多肢選択行動の量子計算による求解 中澤瑠河; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- 中嶋 駿; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- 中山 凛空; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— 河瀬理貴; 井料隆雅; 浦田 淳司 土木学会論文集, 2024-12 / Object-oriented Bayesian Networks for Activity-based Model with deep generative graph averaging URATA Junji; Mochizuki Y.; Hato E. IEEE 27th International Conference on Intelligent Transportation Systems, 2024-09 / 筑波大学理工学群におけるデータサイエンス応用基礎教育 浦田 淳司; オム ソンヨン; 川島 宏一 大学教育と情報, 2024-03 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02 / 選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02 / LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -14645,6 +14719,11 @@
 マルチスケールな拠点空間計画のための新たな行動モデル研究
 災害時都市継続計画にむけた即応型需要予測の信頼性向上のためのデータフロー
 災害時都市活動支援のためのsoftware2.0型シミュレータの構築
+大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
+Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12
+A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12
+Robust OD matrix estimation method under low sampling rate by utilizing multiscale information of questionnaire data Mochizuki Y.; Pel A.J.; Hinsbergen C.; URATA Junji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06
+Developing an Estimation Algorithm for Generalizing the Parameters of the network-GEV model in Destination Choice URATA Junji; KANEDA Yudai; ISHII Ryoji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06
 通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ 上杉 朋花; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11
 EVユーザーの充電場所選択問題に対するゲーム理論的考察 大野 隆輔; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11
 災害復旧期における個々人の移動パターン変化の特徴分析 村上 智仁; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11
@@ -14663,12 +14742,7 @@
 Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository
 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02
 選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02
-LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09
-日本の復興計画の研究動向と今後の展望 -1995年以降の建築・都市・土木の計画分野を中心に- 小野 悠; 井本 佐保里; 浦田 淳司; 萩原 拓也; 羽藤 英二 日本建築学会計画系論文集/87(799), 2022-09
-選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 第42回交通工学研究発表会論文報告集/42/pp.381-388, 2022-08
-災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 第42回交通工学研究発表会論文報告集/42/pp.389-396, 2022-08
-LET'S GO ABROAD!(第77回)シンガポール、パキスタン、アフガニスタン、ベトナム、カンボジア 地域建設業の海外展開と見据える未来—A regional construction company looks to overseas expansion and their future—特集 土木と地政学 才田 善之; 金子 辰生; 浦田 淳司 土木学会誌/107(5)/pp.38-40, 2022-05
-「土木と地政学」を通じて学んだこと—Afterword : What we learn through editing work for "Civil Engineering and Geopolitics"—特集 土木と地政学 浦田 淳司; 森 弘継; 高松 俊介; 西村 俊亮 土木学会誌/107(5)/pp.41-43, 2022-05</t>
+LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09</t>
         </is>
       </c>
     </row>
@@ -14727,14 +14801,15 @@
 view
 hirokitakahashi
 eメール
-9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q
-5
+)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
 研究室
 3F1236
 電話
 5379
 Service Engineering
 Experimental economics
+Incentive Mechanism for Continuous Consumption under Habit Formation and Satiation Utility Model LEE Sangjic; XU Yitao; TAKAHASHI Hiroki; NISHINO Nariaki Procedia CIRP/138/pp.13-18, 2026-02
+Balancing profitability and resilience to earthquake-induced isolation: A multi-objective optimization for drone depot location TAKAHASHI Yusuke; TAKAHASHI Hiroki Socio-Economic Planning Sciences/105(102482), 2026-06
 主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 長谷川 弘貴; 信夫 咲希; 髙橋 裕紀 サービソロジー論文誌/9(3)/pp.1-14, 2025-08
 What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews 髙橋 裕紀 PLoS ONE/19(12), 2024-12
 Mystery shopping considering lifestyle heterogeneity Takahashi Hiroki; Kawasaki Shohei; Takenaka Takeshi; N... International Journal of Services and Operations Management, 2024-03
@@ -14754,7 +14829,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / 9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q / 5 / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -14764,13 +14839,13 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 長谷川 弘貴; 信夫 咲希; 髙橋 裕紀 サービソロジー論文誌/9(3)/pp.1-14, 2025-08 / What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews 髙橋 裕紀 PLoS ONE/19(12), 2024-12 / Mystery shopping considering lifestyle heterogeneity Takahashi Hiroki; Kawasaki Shohei; Takenaka Takeshi; N... International Journal of Services and Operations Management, 2024-03 / 経験効用モデルに基づくサービス継続利用を促すリマインダーの最適間隔 徐 亦陶; 髙橋 裕紀; 木見田 康治; 西野 成昭 サービソロジー/6(2)/pp.29-42, 2022-08 / Effects of Incentivized Fake Reviews on E-commerce Markets Okamoto Shotaro; Takahashi Hiroki; Kimita Koji; Nishino ... The Human Side of Service Engineering/62/pp.8-15, 2022-07 / Platform in manufacturing for enhancement of product value by sharing Nishino Nariaki; Takahashi Hiroki; Takenaka Takeshi; Inou... Procedia CIRP/99/pp.574-579, 2020-01 / Interpreting value creation model by case-based decision theory Takahashi Hiroki; Nishino Nariaki; Takenaka Takeshi; Ishi... Procedia CIRP/88/pp.584-588, 2020-01 / Service switching in case-based decisions following bad experiences: Online reviews data of Japanese hairdressing salons Takahashi Hiroki; Nishino Nariaki; Ishikawa Ryuichiro The 27th International Conference on Case-Based Reasoning (ICCBR 2019) Workshop Proceedings/pp.74-82, 2019-09 / Multi-agent simulation for the manufacturer’s decision making in sharing markets Takahashi Hiroki; Nishino Nariaki; Takenaka Takeshi Procedia CIRP/67/pp.546-551, 2018-01 / Manufacturer’s strategy in a sharing economy Nishino Nariaki; Takenaka Takeshi; Takahashi Hiroki CIRP Annals/66(1)/pp.409-412, 2017-04</t>
+          <t>Incentive Mechanism for Continuous Consumption under Habit Formation and Satiation Utility Model LEE Sangjic; XU Yitao; TAKAHASHI Hiroki; NISHINO Nariaki Procedia CIRP/138/pp.13-18, 2026-02 / Balancing profitability and resilience to earthquake-induced isolation: A multi-objective optimization for drone depot location TAKAHASHI Yusuke; TAKAHASHI Hiroki Socio-Economic Planning Sciences/105(102482), 2026-06 / 主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 長谷川 弘貴; 信夫 咲希; 髙橋 裕紀 サービソロジー論文誌/9(3)/pp.1-14, 2025-08 / What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews 髙橋 裕紀 PLoS ONE/19(12), 2024-12 / Mystery shopping considering lifestyle heterogeneity Takahashi Hiroki; Kawasaki Shohei; Takenaka Takeshi; N... International Journal of Services and Operations Management, 2024-03 / 経験効用モデルに基づくサービス継続利用を促すリマインダーの最適間隔 徐 亦陶; 髙橋 裕紀; 木見田 康治; 西野 成昭 サービソロジー/6(2)/pp.29-42, 2022-08 / Effects of Incentivized Fake Reviews on E-commerce Markets Okamoto Shotaro; Takahashi Hiroki; Kimita Koji; Nishino ... The Human Side of Service Engineering/62/pp.8-15, 2022-07 / Platform in manufacturing for enhancement of product value by sharing Nishino Nariaki; Takahashi Hiroki; Takenaka Takeshi; Inou... Procedia CIRP/99/pp.574-579, 2020-01 / Interpreting value creation model by case-based decision theory Takahashi Hiroki; Nishino Nariaki; Takenaka Takeshi; Ishi... Procedia CIRP/88/pp.584-588, 2020-01 / Service switching in case-based decisions following bad experiences: Online reviews data of Japanese hairdressing salons Takahashi Hiroki; Nishino Nariaki; Ishikawa Ryuichiro The 27th International Conference on Case-Based Reasoning (ICCBR 2019) Workshop Proceedings/pp.74-82, 2019-09 / Multi-agent simulation for the manufacturer’s decision making in sharing markets Takahashi Hiroki; Nishino Nariaki; Takenaka Takeshi Procedia CIRP/67/pp.546-551, 2018-01 / Manufacturer’s strategy in a sharing economy Nishino Nariaki; Takenaka Takeshi; Takahashi Hiroki CIRP Annals/66(1)/pp.409-412, 2017-04</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; 9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q ; 5 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -14800,8 +14875,7 @@
 view
 hirokitakahashi
 eメール
-9&amp;0&amp;-&amp;8-.Q-.740.Q,3HWS:Q98:0:'&amp;Q&amp;(Q
-5
+)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
 研究室
 3F1236
 電話
@@ -14820,6 +14894,8 @@
         <is>
           <t>サービス産業における従業員へのシステム化可能な顧客満足度フィードバック方法の開発
 帰納的意思決定モデルを用いたサービス評価プラットフォームの理論分析と実検証
+Incentive Mechanism for Continuous Consumption under Habit Formation and Satiation Utility Model LEE Sangjic; XU Yitao; TAKAHASHI Hiroki; NISHINO Nariaki Procedia CIRP/138/pp.13-18, 2026-02
+Balancing profitability and resilience to earthquake-induced isolation: A multi-objective optimization for drone depot location TAKAHASHI Yusuke; TAKAHASHI Hiroki Socio-Economic Planning Sciences/105(102482), 2026-06
 主体的で協働的な学びの実現に向けたICT教育サービスの価値共創モデルの提案 長谷川 弘貴; 信夫 咲希; 髙橋 裕紀 サービソロジー論文誌/9(3)/pp.1-14, 2025-08
 What do part-time employees in Japanese chain restaurants talk about when dissatisfied? Applying Structural Topic Modeling to employee reviews 髙橋 裕紀 PLoS ONE/19(12), 2024-12
 Mystery shopping considering lifestyle heterogeneity Takahashi Hiroki; Kawasaki Shohei; Takenaka Takeshi; N... International Journal of Services and Operations Management, 2024-03

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -4663,8 +4663,8 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q
-5^
+&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
+Aj
 都市農村計画
 緑地計画
 Memorable Places on Campuses Across Generations Janpathompong Dalin; Anantsuksomsri Sutee; MURAKAMI Ak... Journal of Architectural/Planning Research and Studies (JARS)/23(1)/pp.278-289, 2026-01
@@ -4701,7 +4701,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q / 5^</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] / Aj</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q ; 5^ ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] ; Aj ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4744,8 +4744,8 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q
-5^
+&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
+Aj
 都市農村計画
 緑地計画
 都市・地域政策
@@ -7748,7 +7748,7 @@
 view
 hirokitakahashi
 eメール
-)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
+=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
 研究室
 3F1236
 電話
@@ -7776,7 +7776,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -7792,7 +7792,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -7822,7 +7822,7 @@
 view
 hirokitakahashi
 eメール
-)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
+=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
 研究室
 3F1236
 電話
@@ -11910,8 +11910,8 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q
-5^
+&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
+Aj
 都市農村計画
 緑地計画
 Memorable Places on Campuses Across Generations Janpathompong Dalin; Anantsuksomsri Sutee; MURAKAMI Ak... Journal of Architectural/Planning Research and Studies (JARS)/23(1)/pp.278-289, 2026-01
@@ -11948,7 +11948,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q / 5^</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] / Aj</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; 2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q ; 5^ ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] ; Aj ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -11991,8 +11991,8 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-2:7&amp;0&amp;2.HWS80Q98:0:'&amp;Q&amp;(Q
-5^
+&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
+Aj
 都市農村計画
 緑地計画
 都市・地域政策
@@ -14801,7 +14801,7 @@
 view
 hirokitakahashi
 eメール
-)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
+=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
 研究室
 3F1236
 電話
@@ -14829,7 +14829,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -14845,7 +14845,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; )K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -14875,7 +14875,7 @@
 view
 hirokitakahashi
 eメール
-)K8B8?8J?@c?@IFB@c&gt;EZieLcKJLBL98c8:cAG
+=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
 研究室
 3F1236
 電話

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -1068,14 +1068,10 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=200901029857148130</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ok_jglobal_fallback</t>
+          <t>jglobal_not_found</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1083,110 +1079,19 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
-超混雑環境における群集ナビゲーションに関する研究
-救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
-大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
-データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
-救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
-仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
-障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
-認知科学
-, 知能ロボティクス
-, 知覚情報処理
-, 知能情報学
-, ヒューマンインタフェース
-インタラクション
-, データベース
-知能ロボット
-, 映像処理
-Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
-Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
-一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
-Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
-Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究 / 超混雑環境における群集ナビゲーションに関する研究 / 救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上 / 大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成 / データ同化手法を用いた身体障害者の共創的衣服作製に関する研究 / 救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究 / 仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究 / 障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>認知科学 / , 知能ロボティクス / , 知覚情報処理 / , 知能情報学 / , ヒューマンインタフェース / インタラクション / , データベース</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>知能ロボット / , 映像処理</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718 / Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600 / 一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235 / Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376 / Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>認知科学 ; , 知能ロボティクス ; , 知覚情報処理 ; , 知能情報学 ; , ヒューマンインタフェース ; インタラクション ; , データベース ; GIS・空間分析 ; 建築・空間設計 ; スポーツデータ分析 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>認知科学
-, 知能ロボティクス
-, 知覚情報処理
-, 知能情報学
-, ヒューマンインタフェース
-インタラクション
-, データベース
-知能ロボット
-, 映像処理
-GIS・空間分析
-建築・空間設計
-スポーツデータ分析
-政策評価・計量分析
-医療・ヘルスデータ
-環境・エネルギー
-AI・データサイエンス
-GIS
-空間計量
-地理情報分析
-立地分析
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
-政策評価
-計量経済学
-統計的因果推論
-実証分析
-医療データ分析
-生体情報解析
-ヘルスデータサイエンス
-統計解析
-環境政策
-エネルギーシステム
-脱炭素分析
-持続可能性評価</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
@@ -1196,20 +1101,7 @@
 大規模イベントにおける歩行者モデルの拡張と群集制御最適化
 多目的最適化による地下動線を活用した避難誘導効果の検証
 実時間で動作する音響イベント検出の大規模事前学習
-超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案
-超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
-超混雑環境における群集ナビゲーションに関する研究
-救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
-大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
-データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
-救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
-仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
-障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
-Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
-Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
-一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
-Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
-Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3707,7 @@
 職名
 教授
 eメール
-+B6&gt;@DXgcH@aIHJ@J76a68a?E
+)D8@BFZieJBcKJLBL98c8:cAG
 最適化
 組合せ最適化
 アルゴリズム
@@ -3853,7 +3745,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / +B6&gt;@DXgcH@aIHJ@J76a68a?E</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / )D8@BFZieJBcKJLBL98c8:cAG</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3873,7 +3765,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; +B6&gt;@DXgcH@aIHJ@J76a68a?E ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; )D8@BFZieJBcKJLBL98c8:cAG ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3892,7 +3784,7 @@
 職名
 教授
 eメール
-+B6&gt;@DXgcH@aIHJ@J76a68a?E
+)D8@BFZieJBcKJLBL98c8:cAG
 最適化
 組合せ最適化
 アルゴリズム
@@ -4663,8 +4555,7 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
-Aj
+I$,)v"v$ :IE*"C+*,",wvCvxC!'P
 都市農村計画
 緑地計画
 Memorable Places on Campuses Across Generations Janpathompong Dalin; Anantsuksomsri Sutee; MURAKAMI Ak... Journal of Architectural/Planning Research and Studies (JARS)/23(1)/pp.278-289, 2026-01
@@ -4701,7 +4592,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] / Aj</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / I$,)v"v$ :IE*"C+*,",wvCvxC!'P</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4721,7 +4612,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] ; Aj ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; I$,)v"v$ :IE*"C+*,",wvCvxC!'P ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4744,8 +4635,7 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
-Aj
+I$,)v"v$ :IE*"C+*,",wvCvxC!'P
 都市農村計画
 緑地計画
 都市・地域政策
@@ -7748,7 +7638,13 @@
 view
 hirokitakahashi
 eメール
-=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
+C1
+(
+%
+0%&amp;I%&amp;
+,(&amp;I$+@OK2I102(2}
+I
+I'-
 研究室
 3F1236
 電話
@@ -7776,7 +7672,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / C1 / ( / % / 0%&amp;I%&amp; / ,(&amp;I$+@OK2I102(2} / I / I'- / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -7792,7 +7688,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; C1 ; ( ; % ; 0%&amp;I%&amp; ; ,(&amp;I$+@OK2I102(2} ; I ; I'- ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -7822,7 +7718,13 @@
 view
 hirokitakahashi
 eメール
-=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
+C1
+(
+%
+0%&amp;I%&amp;
+,(&amp;I$+@OK2I102(2}
+I
+I'-
 研究室
 3F1236
 電話
@@ -8509,14 +8411,10 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=200901029857148130</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ok_jglobal_fallback</t>
+          <t>jglobal_not_found</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -8524,110 +8422,19 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
-超混雑環境における群集ナビゲーションに関する研究
-救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
-大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
-データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
-救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
-仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
-障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
-認知科学
-, 知能ロボティクス
-, 知覚情報処理
-, 知能情報学
-, ヒューマンインタフェース
-インタラクション
-, データベース
-知能ロボット
-, 映像処理
-Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
-Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
-一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
-Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
-Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究 / 超混雑環境における群集ナビゲーションに関する研究 / 救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上 / 大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成 / データ同化手法を用いた身体障害者の共創的衣服作製に関する研究 / 救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究 / 仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究 / 障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>認知科学 / , 知能ロボティクス / , 知覚情報処理 / , 知能情報学 / , ヒューマンインタフェース / インタラクション / , データベース</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>知能ロボット / , 映像処理</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718 / Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600 / 一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235 / Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376 / Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>認知科学 ; , 知能ロボティクス ; , 知覚情報処理 ; , 知能情報学 ; , ヒューマンインタフェース ; インタラクション ; , データベース ; GIS・空間分析 ; 建築・空間設計 ; スポーツデータ分析 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>認知科学
-, 知能ロボティクス
-, 知覚情報処理
-, 知能情報学
-, ヒューマンインタフェース
-インタラクション
-, データベース
-知能ロボット
-, 映像処理
-GIS・空間分析
-建築・空間設計
-スポーツデータ分析
-政策評価・計量分析
-医療・ヘルスデータ
-環境・エネルギー
-AI・データサイエンス
-GIS
-空間計量
-地理情報分析
-立地分析
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
-政策評価
-計量経済学
-統計的因果推論
-実証分析
-医療データ分析
-生体情報解析
-ヘルスデータサイエンス
-統計解析
-環境政策
-エネルギーシステム
-脱炭素分析
-持続可能性評価</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
@@ -8637,20 +8444,7 @@
 大規模イベントにおける歩行者モデルの拡張と群集制御最適化
 多目的最適化による地下動線を活用した避難誘導効果の検証
 実時間で動作する音響イベント検出の大規模事前学習
-超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案
-超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
-超混雑環境における群集ナビゲーションに関する研究
-救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
-大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
-データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
-救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
-仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
-障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
-Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
-Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
-一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
-Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
-Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
     </row>
@@ -11062,7 +10856,7 @@
 職名
 教授
 eメール
-+B6&gt;@DXgcH@aIHJ@J76a68a?E
+)D8@BFZieJBcKJLBL98c8:cAG
 最適化
 組合せ最適化
 アルゴリズム
@@ -11100,7 +10894,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / +B6&gt;@DXgcH@aIHJ@J76a68a?E</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / )D8@BFZieJBcKJLBL98c8:cAG</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -11120,7 +10914,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; +B6&gt;@DXgcH@aIHJ@J76a68a?E ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; )D8@BFZieJBcKJLBL98c8:cAG ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -11139,7 +10933,7 @@
 職名
 教授
 eメール
-+B6&gt;@DXgcH@aIHJ@J76a68a?E
+)D8@BFZieJBcKJLBL98c8:cAG
 最適化
 組合せ最適化
 アルゴリズム
@@ -11910,8 +11704,7 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
-Aj
+I$,)v"v$ :IE*"C+*,",wvCvxC!'P
 都市農村計画
 緑地計画
 Memorable Places on Campuses Across Generations Janpathompong Dalin; Anantsuksomsri Sutee; MURAKAMI Ak... Journal of Architectural/Planning Research and Studies (JARS)/23(1)/pp.278-289, 2026-01
@@ -11948,7 +11741,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] / Aj</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / I$,)v"v$ :IE*"C+*,",wvCvxC!'P</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11968,7 +11761,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; &gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24] ; Aj ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; I$,)v"v$ :IE*"C+*,",wvCvxC!'P ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -11991,8 +11784,7 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-&gt;FC2&lt;2&gt;:Tc_D&lt;]EDF&lt;F32]24]
-Aj
+I$,)v"v$ :IE*"C+*,",wvCvxC!'P
 都市農村計画
 緑地計画
 都市・地域政策
@@ -14801,7 +14593,13 @@
 view
 hirokitakahashi
 eメール
-=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
+C1
+(
+%
+0%&amp;I%&amp;
+,(&amp;I$+@OK2I102(2}
+I
+I'-
 研究室
 3F1236
 電話
@@ -14829,7 +14627,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / C1 / ( / % / 0%&amp;I%&amp; / ,(&amp;I$+@OK2I102(2} / I / I'- / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -14845,7 +14643,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; =7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3 ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; C1 ; ( ; % ; 0%&amp;I%&amp; ; ,(&amp;I$+@OK2I102(2} ; I ; I'- ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -14875,7 +14673,13 @@
 view
 hirokitakahashi
 eメール
-=7$.$+$6+,O+,52.,O*1FUQ8O768.8%$O$&amp;O-3
+C1
+(
+%
+0%&amp;I%&amp;
+,(&amp;I$+@OK2I102(2}
+I
+I'-
 研究室
 3F1236
 電話

--- a/generated/teachers_enriched.xlsx
+++ b/generated/teachers_enriched.xlsx
@@ -754,29 +754,29 @@
 犯罪科学
 空間情報科学
 環境心理学
+Plural policing in rural contexts: a GPS-based evaluation of multi-entity patrols against fruit theft AMEMIYA Mamoru; SUZUMI Ai; SHIMADA Takahito; KURITA H... Security Journal/39, 2026-05
+公園を「負動産」にしないために：茨城県笠間市の挑戦 雨宮 護 日造協ニュース/(626)/pp.2-2, 2026-05
+共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
-共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06
 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06
 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 雨宮 護; 鈴木 あい; 田村 孝浩; 御田 成顕; 島田 貴仁; 栗田 英治 2025年度農村計画学会全国大会学術研究発表会企画セッション梗概集/pp.70-71, 2025-11-29
-Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09
 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して 井上 皓介; 雨宮 護; 大山 智也; 中野 裕貴 都市計画論文集/60(3)/pp.1604-1611, 2025-10
 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 高橋 南織; 雨宮 護 都市計画論文集/60(3)/pp.650-656, 2025-10
 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10
 人口低密度地域における人々の活動から見た「都市の活力」の計測 米田 有希; 雨宮 護; 森山 拓洋 都市計画論文集/60(3)/pp.1658-1665, 2025-10
+Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09
 全国のJAを対象とする果物盗被害に関するアンケート調査報告 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 都市計画報告集/24(2)/pp.318-321, 2025-09
 Regional variations in key factors of children's independent mobility across Japan HINO Kimihiro; AMEMIYA Mamoru; YOSHIKI Syuji; ZHENG Erli Journal of Transport &amp; Health/44, 2025-09
 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 佐光 未帆; 雨宮 護 環境心理学研究/13(1)/pp.48-48, 2025-05-28
 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 李 超群; 雨宮 護 環境心理学研究/13(1)/pp.44-44, 2025-05-28
 Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives SUZUKI Ai; AMEMIYA Mamoru; KURITA Hideharu; SHIMADA T... International Journal of Rural Criminology/9(1)/pp.77-104, 2025-04
-Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05
 Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits Zheng Xinrui; Amemiya Mamoru TRANSACTIONS IN GIS/29(1), 2025-02
-Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya Ohyama 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12
+Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya ... 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12
 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 市川 はるひ; 雨宮 護 IPA日本支部研究集会発表要旨集/pp.４-4, 2024-12
 GPSロガーを用いた官民による果樹盗パトロールの計測 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 Research Abstracts on Spatial Information Science CSIS DAYS 2024/D13, 2024-11-15
-子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10
-時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10
+Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05
 Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10
 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
         </is>
@@ -798,7 +798,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17 / 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06 / 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06 / 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 雨宮 護; 鈴木 あい; 田村 孝浩; 御田 成顕; 島田 貴仁; 栗田 英治 2025年度農村計画学会全国大会学術研究発表会企画セッション梗概集/pp.70-71, 2025-11-29 / Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09 / 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して 井上 皓介; 雨宮 護; 大山 智也; 中野 裕貴 都市計画論文集/60(3)/pp.1604-1611, 2025-10 / 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 高橋 南織; 雨宮 護 都市計画論文集/60(3)/pp.650-656, 2025-10 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10 / 人口低密度地域における人々の活動から見た「都市の活力」の計測 米田 有希; 雨宮 護; 森山 拓洋 都市計画論文集/60(3)/pp.1658-1665, 2025-10 / 全国のJAを対象とする果物盗被害に関するアンケート調査報告 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 都市計画報告集/24(2)/pp.318-321, 2025-09 / Regional variations in key factors of children's independent mobility across Japan HINO Kimihiro; AMEMIYA Mamoru; YOSHIKI Syuji; ZHENG Erli Journal of Transport &amp; Health/44, 2025-09 / 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 佐光 未帆; 雨宮 護 環境心理学研究/13(1)/pp.48-48, 2025-05-28 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 李 超群; 雨宮 護 環境心理学研究/13(1)/pp.44-44, 2025-05-28 / Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives SUZUKI Ai; AMEMIYA Mamoru; KURITA Hideharu; SHIMADA T... International Journal of Rural Criminology/9(1)/pp.77-104, 2025-04 / Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05 / Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits Zheng Xinrui; Amemiya Mamoru TRANSACTIONS IN GIS/29(1), 2025-02 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya Ohyama 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12 / 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 市川 はるひ; 雨宮 護 IPA日本支部研究集会発表要旨集/pp.４-4, 2024-12 / GPSロガーを用いた官民による果樹盗パトロールの計測 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 Research Abstracts on Spatial Information Science CSIS DAYS 2024/D13, 2024-11-15 / 子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10 / 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10 / Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10 / 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
+          <t>Plural policing in rural contexts: a GPS-based evaluation of multi-entity patrols against fruit theft AMEMIYA Mamoru; SUZUMI Ai; SHIMADA Takahito; KURITA H... Security Journal/39, 2026-05 / 公園を「負動産」にしないために：茨城県笠間市の挑戦 雨宮 護 日造協ニュース/(626)/pp.2-2, 2026-05 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17 / 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06 / 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06 / 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 雨宮 護; 鈴木 あい; 田村 孝浩; 御田 成顕; 島田 貴仁; 栗田 英治 2025年度農村計画学会全国大会学術研究発表会企画セッション梗概集/pp.70-71, 2025-11-29 / 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して 井上 皓介; 雨宮 護; 大山 智也; 中野 裕貴 都市計画論文集/60(3)/pp.1604-1611, 2025-10 / 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 高橋 南織; 雨宮 護 都市計画論文集/60(3)/pp.650-656, 2025-10 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10 / 人口低密度地域における人々の活動から見た「都市の活力」の計測 米田 有希; 雨宮 護; 森山 拓洋 都市計画論文集/60(3)/pp.1658-1665, 2025-10 / Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09 / 全国のJAを対象とする果物盗被害に関するアンケート調査報告 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 都市計画報告集/24(2)/pp.318-321, 2025-09 / Regional variations in key factors of children's independent mobility across Japan HINO Kimihiro; AMEMIYA Mamoru; YOSHIKI Syuji; ZHENG Erli Journal of Transport &amp; Health/44, 2025-09 / 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 佐光 未帆; 雨宮 護 環境心理学研究/13(1)/pp.48-48, 2025-05-28 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 李 超群; 雨宮 護 環境心理学研究/13(1)/pp.44-44, 2025-05-28 / Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives SUZUKI Ai; AMEMIYA Mamoru; KURITA Hideharu; SHIMADA T... International Journal of Rural Criminology/9(1)/pp.77-104, 2025-04 / Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits Zheng Xinrui; Amemiya Mamoru TRANSACTIONS IN GIS/29(1), 2025-02 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya ... 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12 / 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 市川 はるひ; 雨宮 護 IPA日本支部研究集会発表要旨集/pp.４-4, 2024-12 / GPSロガーを用いた官民による果樹盗パトロールの計測 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 Research Abstracts on Spatial Information Science CSIS DAYS 2024/D13, 2024-11-15 / Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05 / Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10 / 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -894,29 +894,29 @@
 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究
 集合住宅における子ども・女性に対する犯罪の実態分析と対策立案
 地理的犯罪予測の手法構築‐学際研究と産官学連携による学術基盤の確立とシステム開発
+Plural policing in rural contexts: a GPS-based evaluation of multi-entity patrols against fruit theft AMEMIYA Mamoru; SUZUMI Ai; SHIMADA Takahito; KURITA H... Security Journal/39, 2026-05
+公園を「負動産」にしないために：茨城県笠間市の挑戦 雨宮 護 日造協ニュース/(626)/pp.2-2, 2026-05
+共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
-共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06
 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06
 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 雨宮 護; 鈴木 あい; 田村 孝浩; 御田 成顕; 島田 貴仁; 栗田 英治 2025年度農村計画学会全国大会学術研究発表会企画セッション梗概集/pp.70-71, 2025-11-29
-Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09
 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して 井上 皓介; 雨宮 護; 大山 智也; 中野 裕貴 都市計画論文集/60(3)/pp.1604-1611, 2025-10
 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 高橋 南織; 雨宮 護 都市計画論文集/60(3)/pp.650-656, 2025-10
 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10
 人口低密度地域における人々の活動から見た「都市の活力」の計測 米田 有希; 雨宮 護; 森山 拓洋 都市計画論文集/60(3)/pp.1658-1665, 2025-10
+Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09
 全国のJAを対象とする果物盗被害に関するアンケート調査報告 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 都市計画報告集/24(2)/pp.318-321, 2025-09
 Regional variations in key factors of children's independent mobility across Japan HINO Kimihiro; AMEMIYA Mamoru; YOSHIKI Syuji; ZHENG Erli Journal of Transport &amp; Health/44, 2025-09
 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 佐光 未帆; 雨宮 護 環境心理学研究/13(1)/pp.48-48, 2025-05-28
 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 李 超群; 雨宮 護 環境心理学研究/13(1)/pp.44-44, 2025-05-28
 Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives SUZUKI Ai; AMEMIYA Mamoru; KURITA Hideharu; SHIMADA T... International Journal of Rural Criminology/9(1)/pp.77-104, 2025-04
-Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05
 Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits Zheng Xinrui; Amemiya Mamoru TRANSACTIONS IN GIS/29(1), 2025-02
-Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya Ohyama 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12
+Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya ... 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12
 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 市川 はるひ; 雨宮 護 IPA日本支部研究集会発表要旨集/pp.４-4, 2024-12
 GPSロガーを用いた官民による果樹盗パトロールの計測 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 Research Abstracts on Spatial Information Science CSIS DAYS 2024/D13, 2024-11-15
-子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10
-時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10
+Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05
 Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10
 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
         </is>
@@ -1340,14 +1340,10 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=201301045848886763</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ok_jglobal_fallback</t>
+          <t>jglobal_not_found</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1355,89 +1351,19 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>公平な複数財配分の研究
-複数財割当問題の理論的研究
-マッチング市場の理論的研究
-肝臓・肺生体交換移植ネットワークの構築
-誘因両立的かつ効率的な資源配分ルールの設計に関する理論的研究
-戦略的操作不可能な社会的選択ルールの設計
-戦略的操作不可能かつ次善効率的資源配分ルールの設計
-Design of strategy-proof rules in public goods economies
-Design of strategy-proof and second-best efficienct resource allocation rules
-理論経済学
-マッチング理論
-, 社会的選択理論
-, ミクロ経済学
-Hidekazu Anno. Note on Gale's conjecture in one-sided matching problems. International Journal of Game Theory. 2025. 54
-Hidekazu Anno, Sui Takahashi. A unified approach to strategy-proofness of the deferred-acceptance rule and the top-trading cycles rule. Review of Economic Design. 2023. 27. 133-137
-Hidekazu Anno, Sui Takahashi. A decomposition of strategy-proofness in discrete resource allocation problems. Economics Bulletin. 2022. 42. 49-59
-Hidekazu Anno, Morimitsu Kurino. On the operation of multiple matching markets. Games and Economic Behavior. 2016. 100. 166-185
-Hidekazu Anno. A short proof for the characterization of the core in housing markets. Economics Letters. 2015. 126. 66-67</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>公平な複数財配分の研究 / 複数財割当問題の理論的研究 / マッチング市場の理論的研究 / 肝臓・肺生体交換移植ネットワークの構築 / 誘因両立的かつ効率的な資源配分ルールの設計に関する理論的研究 / 戦略的操作不可能な社会的選択ルールの設計 / 戦略的操作不可能かつ次善効率的資源配分ルールの設計 / Design of strategy-proof rules in public goods economies / Design of strategy-proof and second-best efficienct resource allocation rules</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>理論経済学</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>マッチング理論 / , 社会的選択理論 / , ミクロ経済学</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Hidekazu Anno. Note on Gale's conjecture in one-sided matching problems. International Journal of Game Theory. 2025. 54 / Hidekazu Anno, Sui Takahashi. A unified approach to strategy-proofness of the deferred-acceptance rule and the top-trading cycles rule. Review of Economic Design. 2023. 27. 133-137 / Hidekazu Anno, Sui Takahashi. A decomposition of strategy-proofness in discrete resource allocation problems. Economics Bulletin. 2022. 42. 49-59 / Hidekazu Anno, Morimitsu Kurino. On the operation of multiple matching markets. Games and Economic Behavior. 2016. 100. 166-185 / Hidekazu Anno. A short proof for the characterization of the core in housing markets. Economics Letters. 2015. 126. 66-67</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>個人間および部局間公平な非分割財配分について / 結婚市場において仲介業者が一部参加者を名簿から 削除するインセンティブを持たないメカニズムの設計 / 抽選独裁制とcardinal invarianceについて / プロ野球現役ドラフトにおける耐戦略的メカニズムの設計 / 複数並列市場における耐戦略的ルールの効率性に関する研究 / 不確実性下の同質財割当におけるrandomized uniform ruleの非効率性について</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>理論経済学 ; マッチング理論・ゲーム理論 ; ネットワーク・グラフ理論 ; 医療・ヘルスデータ ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>理論経済学
-マッチング理論
-, 社会的選択理論
-, ミクロ経済学
-マッチング理論・ゲーム理論
-ネットワーク・グラフ理論
-医療・ヘルスデータ
-公共政策・社会工学
-経済・ファイナンス
-数理最適化・OR
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-医療データ分析
-生体情報解析
-ヘルスデータサイエンス
-統計解析</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>個人間および部局間公平な非分割財配分について
@@ -1445,21 +1371,7 @@
 抽選独裁制とcardinal invarianceについて
 プロ野球現役ドラフトにおける耐戦略的メカニズムの設計
 複数並列市場における耐戦略的ルールの効率性に関する研究
-不確実性下の同質財割当におけるrandomized uniform ruleの非効率性について
-公平な複数財配分の研究
-複数財割当問題の理論的研究
-マッチング市場の理論的研究
-肝臓・肺生体交換移植ネットワークの構築
-誘因両立的かつ効率的な資源配分ルールの設計に関する理論的研究
-戦略的操作不可能な社会的選択ルールの設計
-戦略的操作不可能かつ次善効率的資源配分ルールの設計
-Design of strategy-proof rules in public goods economies
-Design of strategy-proof and second-best efficienct resource allocation rules
-Hidekazu Anno. Note on Gale's conjecture in one-sided matching problems. International Journal of Game Theory. 2025. 54
-Hidekazu Anno, Sui Takahashi. A unified approach to strategy-proofness of the deferred-acceptance rule and the top-trading cycles rule. Review of Economic Design. 2023. 27. 133-137
-Hidekazu Anno, Sui Takahashi. A decomposition of strategy-proofness in discrete resource allocation problems. Economics Bulletin. 2022. 42. 49-59
-Hidekazu Anno, Morimitsu Kurino. On the operation of multiple matching markets. Games and Economic Behavior. 2016. 100. 166-185
-Hidekazu Anno. A short proof for the characterization of the core in housing markets. Economics Letters. 2015. 126. 66-67</t>
+不確実性下の同質財割当におけるrandomized uniform ruleの非効率性について</t>
         </is>
       </c>
     </row>
@@ -1894,17 +1806,18 @@
 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年
 都市における環境リスクの軽減の経済効果に関する研究
 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―
+環境衛生リスク改善の経済的価値
 経済政策
 開発経済学、教育の経済学、健康の経済学、応用計量経済学
 非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
 Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05
 Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020
-The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04
-The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/p.1305, 2017 Tsukuba Repository
+The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/69(3)/pp.1203-1237, 2021-04
+The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/pp.1305-1336, 2017 Tsukuba Repository
 Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... JAPAN AND THE WORLD ECONOMY/50/pp.36-46, 2019-06
 School Choice and Student Sorting: Evidence from Adachi Ward in Japan 牛島 光一 Japanese Economic Review/60(4)/pp.446-472, 2009-12
 オリンピック・パラリンピックにはどんな経済効果があるのか 牛島 光一 経済セミナー 2019年4・5月号, 2019-03
-Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi Public Policy Review, 2020-09
+Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi; Tanaka H. Noguchi、S. Bessho、A. Kawamur... Public Policy Review, 2020-09
 Building an Administrative Database of Children Bessho Shun-ichiro; Noguchi Haruko; 牛島 光一; Kawamura Akir... Public Policy Review, 2020-09
 高速鉄道の建設が居住地価格に与えた影響 牛島 光一 季刊 住宅土地経済/pp.24-31, 2019-07
 Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... IZA Discussion Papers, 2020-04
@@ -1925,7 +1838,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>民主主義における利益誘導と経済発展への影響 / 政策立案のための衛星データ利用法の探索：社会工学的アプローチ / 社会工学分野での衛星画像の利用促進に向けた探索的研究 / 衛星情報を利用した物流における大気環境改善の評価 / 反実仮想で測る公的資源配分の依怙贔屓と非効率 / 交通と環境に関する新経済地理学的基盤研究 / 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年 / 都市における環境リスクの軽減の経済効果に関する研究 / 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―</t>
+          <t>民主主義における利益誘導と経済発展への影響 / 政策立案のための衛星データ利用法の探索：社会工学的アプローチ / 社会工学分野での衛星画像の利用促進に向けた探索的研究 / 衛星情報を利用した物流における大気環境改善の評価 / 反実仮想で測る公的資源配分の依怙贔屓と非効率 / 交通と環境に関する新経済地理学的基盤研究 / 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年 / 都市における環境リスクの軽減の経済効果に関する研究 / 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に― / 環境衛生リスク改善の経済的価値</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1940,7 +1853,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17 / Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05 / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020 / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04 / The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/p.1305, 2017 Tsukuba Repository / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... JAPAN AND THE WORLD ECONOMY/50/pp.36-46, 2019-06 / School Choice and Student Sorting: Evidence from Adachi Ward in Japan 牛島 光一 Japanese Economic Review/60(4)/pp.446-472, 2009-12 / オリンピック・パラリンピックにはどんな経済効果があるのか 牛島 光一 経済セミナー 2019年4・5月号, 2019-03 / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi Public Policy Review, 2020-09 / Building an Administrative Database of Children Bessho Shun-ichiro; Noguchi Haruko; 牛島 光一; Kawamura Akir... Public Policy Review, 2020-09 / 高速鉄道の建設が居住地価格に与えた影響 牛島 光一 季刊 住宅土地経済/pp.24-31, 2019-07 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... IZA Discussion Papers, 2020-04 / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ 香川涼亮; 小倉利仁; 太田 充; 牛島光一 都市住宅学/97/pp.126-135, 2017-04 CiNii / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― 姜 哲敏; 太田 充; 牛島光一 応用地域学研究/20/pp.67-77, 2016-09 / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 牛島 光一 応用地域学研究/(14)/pp.37-47, 2009-12 / 学校の質と地価－足立区の地価データを用いた検証 牛島 光一 住宅土地経済/(68)/pp.10-18, 2008-04 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ 牛島 光一 フィナンシャルレビュー/(141)/pp.65-85, 2019-12 / 子どもについての行政データベースの構築 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.106-119, 2019-12 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.120-140, 2019-12 / 区立小学校での補習の効果：足立区のケース 別所俊一郎; 川村顕; 野口晴子; 田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.141-159, 2019-12 / ヘドニック・アプローチにおける因果識別 牛島 光一 都市住宅学/2016(92)/pp.25-30, 2016-01 CiNii / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 牛島 光一 応用地域学研究/(18)/pp.62-63, 2014-09 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 牛島 光一 住宅土地経済/(2010年秋季)/pp.36-39, 2010-10 / The Impact of a High-speed Railway on Residential Land Prices Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1344), 2016-03 / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10</t>
+          <t>非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17 / Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05 / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020 / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/69(3)/pp.1203-1237, 2021-04 / The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/pp.1305-1336, 2017 Tsukuba Repository / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... JAPAN AND THE WORLD ECONOMY/50/pp.36-46, 2019-06 / School Choice and Student Sorting: Evidence from Adachi Ward in Japan 牛島 光一 Japanese Economic Review/60(4)/pp.446-472, 2009-12 / オリンピック・パラリンピックにはどんな経済効果があるのか 牛島 光一 経済セミナー 2019年4・5月号, 2019-03 / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi; Tanaka H. Noguchi、S. Bessho、A. Kawamur... Public Policy Review, 2020-09 / Building an Administrative Database of Children Bessho Shun-ichiro; Noguchi Haruko; 牛島 光一; Kawamura Akir... Public Policy Review, 2020-09 / 高速鉄道の建設が居住地価格に与えた影響 牛島 光一 季刊 住宅土地経済/pp.24-31, 2019-07 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... IZA Discussion Papers, 2020-04 / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ 香川涼亮; 小倉利仁; 太田 充; 牛島光一 都市住宅学/97/pp.126-135, 2017-04 CiNii / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― 姜 哲敏; 太田 充; 牛島光一 応用地域学研究/20/pp.67-77, 2016-09 / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 牛島 光一 応用地域学研究/(14)/pp.37-47, 2009-12 / 学校の質と地価－足立区の地価データを用いた検証 牛島 光一 住宅土地経済/(68)/pp.10-18, 2008-04 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ 牛島 光一 フィナンシャルレビュー/(141)/pp.65-85, 2019-12 / 子どもについての行政データベースの構築 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.106-119, 2019-12 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.120-140, 2019-12 / 区立小学校での補習の効果：足立区のケース 別所俊一郎; 川村顕; 野口晴子; 田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.141-159, 2019-12 / ヘドニック・アプローチにおける因果識別 牛島 光一 都市住宅学/2016(92)/pp.25-30, 2016-01 CiNii / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 牛島 光一 応用地域学研究/(18)/pp.62-63, 2014-09 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 牛島 光一 住宅土地経済/(2010年秋季)/pp.36-39, 2010-10 / The Impact of a High-speed Railway on Residential Land Prices Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1344), 2016-03 / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2016,15 +1929,16 @@
 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年
 都市における環境リスクの軽減の経済効果に関する研究
 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―
+環境衛生リスク改善の経済的価値
 非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
 Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05
 Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020
-The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04
-The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/p.1305, 2017 Tsukuba Repository
+The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/69(3)/pp.1203-1237, 2021-04
+The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/pp.1305-1336, 2017 Tsukuba Repository
 Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... JAPAN AND THE WORLD ECONOMY/50/pp.36-46, 2019-06
 School Choice and Student Sorting: Evidence from Adachi Ward in Japan 牛島 光一 Japanese Economic Review/60(4)/pp.446-472, 2009-12
 オリンピック・パラリンピックにはどんな経済効果があるのか 牛島 光一 経済セミナー 2019年4・5月号, 2019-03
-Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi Public Policy Review, 2020-09
+Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi; Tanaka H. Noguchi、S. Bessho、A. Kawamur... Public Policy Review, 2020-09
 Building an Administrative Database of Children Bessho Shun-ichiro; Noguchi Haruko; 牛島 光一; Kawamura Akir... Public Policy Review, 2020-09
 高速鉄道の建設が居住地価格に与えた影響 牛島 光一 季刊 住宅土地経済/pp.24-31, 2019-07
 Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... IZA Discussion Papers, 2020-04
@@ -2282,6 +2196,8 @@
 交通シミュレーション
 災害復旧
 相互作用
+神経発達過程を模した幹線・フィーダー型バスネットワーク最適化 出本大起; 浦田 淳司 第73回土木計画学研究発表会・講演集, 2026-06
+Data-centric AIにむけたプローブデータの欠測検知手法の開発 中山凛空; 浦田 淳司; 鵜飼誠治 第73回土木計画学研究発表会・講演集, 2026-06
 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
 Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12
 A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12
@@ -2303,9 +2219,7 @@
 筑波大学理工学群におけるデータサイエンス応用基礎教育 浦田 淳司; オム ソンヨン; 川島 宏一 大学教育と情報, 2024-03
 Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01
 Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository
-災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02
-選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02
-LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09</t>
+災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2325,7 +2239,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12 / A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12 / Robust OD matrix estimation method under low sampling rate by utilizing multiscale information of questionnaire data Mochizuki Y.; Pel A.J.; Hinsbergen C.; URATA Junji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06 / Developing an Estimation Algorithm for Generalizing the Parameters of the network-GEV model in Destination Choice URATA Junji; KANEDA Yudai; ISHII Ryoji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06 / 通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ 上杉 朋花; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / EVユーザーの充電場所選択問題に対するゲーム理論的考察 大野 隆輔; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / 災害復旧期における個々人の移動パターン変化の特徴分析 村上 智仁; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / メタ分析による災害時の避難開始選択要因の評価 柴田 龍聖; 浦田 淳司; 大東 延幸 第72回土木計画学研究発表会・講演集, 2025-11 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction URATA Junji; NAKAZAWA Ruka THE 29TH INTERNATIONAL CONFERENCE OF HONG KONG SOCIETY FOR TRANSPORTATION STUDIES, 2025-12 / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging Mochizuki Y.; 浦田 淳司; Hato E. 2024 IEEE 27th International Conference on Intelligent Transportation Systems (ITSC)/pp.653-660, 2025-03 / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 田村 侑介; 浦田 淳司 都市計画論文集/60(3)/pp.1543-1550, 2025-10 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 相互作用下での多肢選択行動の量子計算による求解 中澤瑠河; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- 中嶋 駿; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- 中山 凛空; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— 河瀬理貴; 井料隆雅; 浦田 淳司 土木学会論文集, 2024-12 / Object-oriented Bayesian Networks for Activity-based Model with deep generative graph averaging URATA Junji; Mochizuki Y.; Hato E. IEEE 27th International Conference on Intelligent Transportation Systems, 2024-09 / 筑波大学理工学群におけるデータサイエンス応用基礎教育 浦田 淳司; オム ソンヨン; 川島 宏一 大学教育と情報, 2024-03 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02 / 選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02 / LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09</t>
+          <t>神経発達過程を模した幹線・フィーダー型バスネットワーク最適化 出本大起; 浦田 淳司 第73回土木計画学研究発表会・講演集, 2026-06 / Data-centric AIにむけたプローブデータの欠測検知手法の開発 中山凛空; 浦田 淳司; 鵜飼誠治 第73回土木計画学研究発表会・講演集, 2026-06 / 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12 / A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12 / Robust OD matrix estimation method under low sampling rate by utilizing multiscale information of questionnaire data Mochizuki Y.; Pel A.J.; Hinsbergen C.; URATA Junji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06 / Developing an Estimation Algorithm for Generalizing the Parameters of the network-GEV model in Destination Choice URATA Junji; KANEDA Yudai; ISHII Ryoji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06 / 通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ 上杉 朋花; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / EVユーザーの充電場所選択問題に対するゲーム理論的考察 大野 隆輔; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / 災害復旧期における個々人の移動パターン変化の特徴分析 村上 智仁; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / メタ分析による災害時の避難開始選択要因の評価 柴田 龍聖; 浦田 淳司; 大東 延幸 第72回土木計画学研究発表会・講演集, 2025-11 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction URATA Junji; NAKAZAWA Ruka THE 29TH INTERNATIONAL CONFERENCE OF HONG KONG SOCIETY FOR TRANSPORTATION STUDIES, 2025-12 / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging Mochizuki Y.; 浦田 淳司; Hato E. 2024 IEEE 27th International Conference on Intelligent Transportation Systems (ITSC)/pp.653-660, 2025-03 / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 田村 侑介; 浦田 淳司 都市計画論文集/60(3)/pp.1543-1550, 2025-10 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 相互作用下での多肢選択行動の量子計算による求解 中澤瑠河; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- 中嶋 駿; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- 中山 凛空; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— 河瀬理貴; 井料隆雅; 浦田 淳司 土木学会論文集, 2024-12 / Object-oriented Bayesian Networks for Activity-based Model with deep generative graph averaging URATA Junji; Mochizuki Y.; Hato E. IEEE 27th International Conference on Intelligent Transportation Systems, 2024-09 / 筑波大学理工学群におけるデータサイエンス応用基礎教育 浦田 淳司; オム ソンヨン; 川島 宏一 大学教育と情報, 2024-03 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -2413,6 +2327,8 @@
 マルチスケールな拠点空間計画のための新たな行動モデル研究
 災害時都市継続計画にむけた即応型需要予測の信頼性向上のためのデータフロー
 災害時都市活動支援のためのsoftware2.0型シミュレータの構築
+神経発達過程を模した幹線・フィーダー型バスネットワーク最適化 出本大起; 浦田 淳司 第73回土木計画学研究発表会・講演集, 2026-06
+Data-centric AIにむけたプローブデータの欠測検知手法の開発 中山凛空; 浦田 淳司; 鵜飼誠治 第73回土木計画学研究発表会・講演集, 2026-06
 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
 Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12
 A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12
@@ -2434,9 +2350,7 @@
 筑波大学理工学群におけるデータサイエンス応用基礎教育 浦田 淳司; オム ソンヨン; 川島 宏一 大学教育と情報, 2024-03
 Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01
 Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository
-災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02
-選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02
-LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09</t>
+災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2404,7 @@
 職名
 准教授
 eメール
-G($.y(B&lt;IOx-&lt;IPB,$E-,.$.yxExzE#)
++D@J7D^Xek6IXel^H@aIHJ@J76a68a?E
 マクロ経済学
 計量経済学
 Model uncertainty, economic development, and welfare costs of business cycles Okubo Masakatsu JOURNAL OF MACROECONOMICS/76, 2023-06
@@ -2515,7 +2429,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 大久保 正勝(オオクボ マサカツ) / 所属 / システム情報系 / 職名 / 准教授 / eメール / G($.y(B&lt;IOx-&lt;IPB,$E-,.$.yxExzE#)</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 大久保 正勝(オオクボ マサカツ) / 所属 / システム情報系 / 職名 / 准教授 / eメール / +D@J7D^Xek6IXel^H@aIHJ@J76a68a?E</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2531,7 +2445,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 大久保 正勝(オオクボ マサカツ) ; 所属 ; システム情報系 ; 職名 ; 准教授 ; eメール ; G($.y(B&lt;IOx-&lt;IPB,$E-,.$.yxExzE#) ; 労働経済・就職マッチング ; 保険・金融行動 ; 意思決定分析 ; 政策評価・計量分析 ; 経済・ファイナンス ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 大久保 正勝(オオクボ マサカツ) ; 所属 ; システム情報系 ; 職名 ; 准教授 ; eメール ; +D@J7D^Xek6IXel^H@aIHJ@J76a68a?E ; 労働経済・就職マッチング ; 保険・金融行動 ; 意思決定分析 ; 政策評価・計量分析 ; 経済・ファイナンス ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2550,7 +2464,7 @@
 職名
 准教授
 eメール
-G($.y(B&lt;IOx-&lt;IPB,$E-,.$.yxExzE#)
++D@J7D^Xek6IXel^H@aIHJ@J76a68a?E
 マクロ経済学
 計量経済学
 労働経済・就職マッチング
@@ -3089,9 +3003,10 @@
 衛生学・公衆衛生学
 健康政策
 社会政策
-健康経済学
+医療経済学
 国際保健
-Financial burden of menstrual and menopausal symptoms: Productivity loss from absenteeism and presenteeism among working age women KASAHARA Shingo; GOTO Rei; SUZUKI Shu; SAKAMOTO Haruk... Reproductive Health/p.(in press), 2026-04
+Spousal bereavement and mental health among older Japanese adults Iida Masumi; Sugawara Ikuko; Kobayashi Erika; Okamoto ... Research on Aging, 2026-06
+Financial burden of menstrual and menopausal symptoms: Productivity loss from absenteeism and presenteeism among working age women KASAHARA Shingo; GOTO Rei; SUZUKI Shu; SAKAMOTO Haruk... Reproductive Health, 2026-05
 Comparison income and subjective well-being: Evidence from a nationwide panel survey in Japan Shiraishi Kenichi; Sumita Kazuto; Kamimura Kazuki; Oka... Economics Bulletin/p.(in press), 2026-04
 Reversed loneliness development after age 65 for men and women: Modeling of the age trajectories of loneliness using national cohorts in Taiwan and Japan Chiu Ching-Ju; Hou Szu-Yu; Kobayashi Erika; Lin Yu-Ch... Geriatrics &amp; Gerontology International/25(4)/pp.620-627, 2025-04-01 PubMed
 Socioeconomic inequity in access to medical and long-term care among older people Okamoto Shohei; Yamada Atsuhiro; Kobayashi Erika; Lian... International Journal for Equity in Health/24(1)/p.28, 2025-01-23 PubMed
@@ -3115,7 +3030,6 @@
 Age trajectories of disability development after 65: A comparison between Japan and Taiwan Chiu Ching-Ju; Chen Yun-An; Kobayashi Erika; Murayama ... Archives of Gerontology and Geriatrics/96, 2021-04-01 PubMed
 Age, gender, and financial literacy in Japan Okamoto Shohei; Komamura Kohei PLoS ONE/16(11), 2021-04-01 PubMed
 Increase in suicide following an initial decline during the COVID-19 pandemic in Japan Tanaka Takanao; Okamoto Shohei Nature Human Behaviour/5(2)/pp.229-238, 2021-02-01 PubMed
-Decomposition of gender differences in cognitive functioning: National Survey of the Japanese elderly Okamoto Shohei; Kobayashi Erika; Murayama Hiroshi; Lia... BMC Geriatrics/21(1)/p.38, 2021-01-10 PubMed
 Box 5. Catastrophic health spending and unmet need among households with older persons in Japan. Okamoto Shohei Global monitoring report on financial protection in heath 2021, 2021-12
 新型コロナウイルス感染症拡⼤下における自殺者数の推移 岡本 翔平; 田中 孝直 精神科治療学/pp.869-874, 2021-08
 新型コロナウイルス感染症拡大のもう一つの脅威 : 感染症対策による非感染性疾患リスクへの影響 岡本 翔平 生活経済政策/294/pp.20-27, 2021-07
@@ -3135,12 +3049,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>健康政策 / 社会政策 / 健康経済学 / 国際保健</t>
+          <t>健康政策 / 社会政策 / 医療経済学 / 国際保健</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Financial burden of menstrual and menopausal symptoms: Productivity loss from absenteeism and presenteeism among working age women KASAHARA Shingo; GOTO Rei; SUZUKI Shu; SAKAMOTO Haruk... Reproductive Health/p.(in press), 2026-04 / Comparison income and subjective well-being: Evidence from a nationwide panel survey in Japan Shiraishi Kenichi; Sumita Kazuto; Kamimura Kazuki; Oka... Economics Bulletin/p.(in press), 2026-04 / Reversed loneliness development after age 65 for men and women: Modeling of the age trajectories of loneliness using national cohorts in Taiwan and Japan Chiu Ching-Ju; Hou Szu-Yu; Kobayashi Erika; Lin Yu-Ch... Geriatrics &amp; Gerontology International/25(4)/pp.620-627, 2025-04-01 PubMed / Socioeconomic inequity in access to medical and long-term care among older people Okamoto Shohei; Yamada Atsuhiro; Kobayashi Erika; Lian... International Journal for Equity in Health/24(1)/p.28, 2025-01-23 PubMed / The importance of examining both the amount and balance of social support: A study on the relationship between social support and subjective well-being of older Japanese adults Tham Yukari Jessica; Okamoto Shohei; Kobayashi Erika Journal of Community &amp; Applied Social Psychology/34(2), 2024-03 / Universal health coverage in the context of population ageing: catastrophic health expenditure and unmet need for healthcare Okamoto Shohei; Sata Mizuki; Rosenberg Megumi; Nakagos... Health Economics Review/14(1)/p.8, 2024-01-30 PubMed / Better data on unmet healthcare need can strengthen global monitoring of universal health coverage Rosenberg Megumi; Kowal Paul; Rahman Md Mizanur; Okamo... BMJ/382, 2023-09-05 PubMed / Economic effects of healthy ageing: functional limitation, forgone wages, and medical and long-term care costs Okamoto Shohei; Sakamoto Haruka; Kamimura Kazuki; Koma... Health Economics Review/13(1)/p.28, 2023-05-10 PubMed / An overview of systems for providing integrated and comprehensive care for older people in Japan Sano Junko; Hirazawa Yuzuki; Komamura Kohei; Okamoto ... Archives of Public Health/81(1)/p.81, 2023-05-04 PubMed / Living alone and depressive symptoms among older Japanese: Do urbanization and time period matter? Kobayashi Erika; Harada Ken; Okamoto Shohei; Liang Je... The Journals of Gerontology. Series B, Psychological Sciences and Social Sciences/78(4)/pp.718-729, 2023-04-01 PubMed / Financial incentives for exercise and medical care costs Kamimura Kazuki; Okamoto Shohei; Shiraishi Kenichi; Su... The International Journal of Economic Policy Studies/17(1)/pp.95-116, 2023-02 / The retirement-health puzzle: A sigh of relief at retirement? Okamoto Shohei; Kobayashi Erika; Komamura Kohei The Journals of Gerontology. Series B, Psychological Sciences and Social Sciences/78(1)/pp.167-178, 2023-01-28 PubMed / Effect of diabetes and prediabetes on the development of disability and mortality among middle-aged Japanese adults: A 22-year follow up of NIPPON DATA90 Tran Ngoc Hoang Phap; Kadota Aya; Yano Yuichiro; Harad... Journal of Diabetes Investigation/13(11)/pp.1897-1904, 2022-11-01 PubMed / Towards universal health coverage in the context of population ageing: a narrative review on the implications from the long-term care system in Japan Okamoto Shohei; Komamura Kohei Archives of Public Health/80(1)/p.210, 2022-09-21 PubMed / State of emergency and human mobility during the COVID-19 pandemic in Japan Okamoto Shohei Journal of Transport and Health/26, 2022-09-01 PubMed / COVID-19 vaccine hesitancy and vaccine passports: a cross-sectional conjoint experiment in Japan Okamoto Shohei; Kamimura Kazuki; Komamura Kohei BMJ Open/12(6), 2022-06-16 PubMed / National Health Spending, Health-Care Resources, Service Utilization, and Health Outcomes Tanaka Takanao; Okamoto Shohei; Canning David American Journal of Epidemiology/191(3)/pp.386-396, 2022-02-19 PubMed / Retirement and Social Activities in Japan: Does Age Moderate the Association? Kobayashi Erika; Sugawara Ikuko; Fukaya Taro; Okamoto ... Research on Aging/44(2)/pp.144-155, 2022-02-01 PubMed / Social isolation and cognitive functioning: A quasi-experimental approach Okamoto Shohei; Kobayashi Erika The Journals of Gerontology. Series B, Psychological Sciences and Social Sciences/76(7)/pp.1441-1451, 2021-08-13 PubMed / Daily steps and healthcare costs in Japanese communities Okamoto Shohei; Kamimura Kazuki; Shiraishi Kenichi; Su... Scientific Reports/11(1), 2021-07 PubMed / Parental socioeconomic status and adolescent health in Japan Okamoto Shohei Scientific reports/11(1), 2021-06-08 PubMed / Age trajectories of disability development after 65: A comparison between Japan and Taiwan Chiu Ching-Ju; Chen Yun-An; Kobayashi Erika; Murayama ... Archives of Gerontology and Geriatrics/96, 2021-04-01 PubMed / Age, gender, and financial literacy in Japan Okamoto Shohei; Komamura Kohei PLoS ONE/16(11), 2021-04-01 PubMed / Increase in suicide following an initial decline during the COVID-19 pandemic in Japan Tanaka Takanao; Okamoto Shohei Nature Human Behaviour/5(2)/pp.229-238, 2021-02-01 PubMed / Decomposition of gender differences in cognitive functioning: National Survey of the Japanese elderly Okamoto Shohei; Kobayashi Erika; Murayama Hiroshi; Lia... BMC Geriatrics/21(1)/p.38, 2021-01-10 PubMed / Box 5. Catastrophic health spending and unmet need among households with older persons in Japan. Okamoto Shohei Global monitoring report on financial protection in heath 2021, 2021-12 / 新型コロナウイルス感染症拡⼤下における自殺者数の推移 岡本 翔平; 田中 孝直 精神科治療学/pp.869-874, 2021-08 / 新型コロナウイルス感染症拡大のもう一つの脅威 : 感染症対策による非感染性疾患リスクへの影響 岡本 翔平 生活経済政策/294/pp.20-27, 2021-07 / 高齢期の就労と健康 岡本 翔平 健康長寿ネット, 2019-12 / わが国の栄養・食事と関連する健康施策の現状 岡本 翔平; 栗原 綾子; 岡村 智教 動脈硬化予防/pp.40-45, 2017-03</t>
+          <t>Spousal bereavement and mental health among older Japanese adults Iida Masumi; Sugawara Ikuko; Kobayashi Erika; Okamoto ... Research on Aging, 2026-06 / Financial burden of menstrual and menopausal symptoms: Productivity loss from absenteeism and presenteeism among working age women KASAHARA Shingo; GOTO Rei; SUZUKI Shu; SAKAMOTO Haruk... Reproductive Health, 2026-05 / Comparison income and subjective well-being: Evidence from a nationwide panel survey in Japan Shiraishi Kenichi; Sumita Kazuto; Kamimura Kazuki; Oka... Economics Bulletin/p.(in press), 2026-04 / Reversed loneliness development after age 65 for men and women: Modeling of the age trajectories of loneliness using national cohorts in Taiwan and Japan Chiu Ching-Ju; Hou Szu-Yu; Kobayashi Erika; Lin Yu-Ch... Geriatrics &amp; Gerontology International/25(4)/pp.620-627, 2025-04-01 PubMed / Socioeconomic inequity in access to medical and long-term care among older people Okamoto Shohei; Yamada Atsuhiro; Kobayashi Erika; Lian... International Journal for Equity in Health/24(1)/p.28, 2025-01-23 PubMed / The importance of examining both the amount and balance of social support: A study on the relationship between social support and subjective well-being of older Japanese adults Tham Yukari Jessica; Okamoto Shohei; Kobayashi Erika Journal of Community &amp; Applied Social Psychology/34(2), 2024-03 / Universal health coverage in the context of population ageing: catastrophic health expenditure and unmet need for healthcare Okamoto Shohei; Sata Mizuki; Rosenberg Megumi; Nakagos... Health Economics Review/14(1)/p.8, 2024-01-30 PubMed / Better data on unmet healthcare need can strengthen global monitoring of universal health coverage Rosenberg Megumi; Kowal Paul; Rahman Md Mizanur; Okamo... BMJ/382, 2023-09-05 PubMed / Economic effects of healthy ageing: functional limitation, forgone wages, and medical and long-term care costs Okamoto Shohei; Sakamoto Haruka; Kamimura Kazuki; Koma... Health Economics Review/13(1)/p.28, 2023-05-10 PubMed / An overview of systems for providing integrated and comprehensive care for older people in Japan Sano Junko; Hirazawa Yuzuki; Komamura Kohei; Okamoto ... Archives of Public Health/81(1)/p.81, 2023-05-04 PubMed / Living alone and depressive symptoms among older Japanese: Do urbanization and time period matter? Kobayashi Erika; Harada Ken; Okamoto Shohei; Liang Je... The Journals of Gerontology. Series B, Psychological Sciences and Social Sciences/78(4)/pp.718-729, 2023-04-01 PubMed / Financial incentives for exercise and medical care costs Kamimura Kazuki; Okamoto Shohei; Shiraishi Kenichi; Su... The International Journal of Economic Policy Studies/17(1)/pp.95-116, 2023-02 / The retirement-health puzzle: A sigh of relief at retirement? Okamoto Shohei; Kobayashi Erika; Komamura Kohei The Journals of Gerontology. Series B, Psychological Sciences and Social Sciences/78(1)/pp.167-178, 2023-01-28 PubMed / Effect of diabetes and prediabetes on the development of disability and mortality among middle-aged Japanese adults: A 22-year follow up of NIPPON DATA90 Tran Ngoc Hoang Phap; Kadota Aya; Yano Yuichiro; Harad... Journal of Diabetes Investigation/13(11)/pp.1897-1904, 2022-11-01 PubMed / Towards universal health coverage in the context of population ageing: a narrative review on the implications from the long-term care system in Japan Okamoto Shohei; Komamura Kohei Archives of Public Health/80(1)/p.210, 2022-09-21 PubMed / State of emergency and human mobility during the COVID-19 pandemic in Japan Okamoto Shohei Journal of Transport and Health/26, 2022-09-01 PubMed / COVID-19 vaccine hesitancy and vaccine passports: a cross-sectional conjoint experiment in Japan Okamoto Shohei; Kamimura Kazuki; Komamura Kohei BMJ Open/12(6), 2022-06-16 PubMed / National Health Spending, Health-Care Resources, Service Utilization, and Health Outcomes Tanaka Takanao; Okamoto Shohei; Canning David American Journal of Epidemiology/191(3)/pp.386-396, 2022-02-19 PubMed / Retirement and Social Activities in Japan: Does Age Moderate the Association? Kobayashi Erika; Sugawara Ikuko; Fukaya Taro; Okamoto ... Research on Aging/44(2)/pp.144-155, 2022-02-01 PubMed / Social isolation and cognitive functioning: A quasi-experimental approach Okamoto Shohei; Kobayashi Erika The Journals of Gerontology. Series B, Psychological Sciences and Social Sciences/76(7)/pp.1441-1451, 2021-08-13 PubMed / Daily steps and healthcare costs in Japanese communities Okamoto Shohei; Kamimura Kazuki; Shiraishi Kenichi; Su... Scientific Reports/11(1), 2021-07 PubMed / Parental socioeconomic status and adolescent health in Japan Okamoto Shohei Scientific reports/11(1), 2021-06-08 PubMed / Age trajectories of disability development after 65: A comparison between Japan and Taiwan Chiu Ching-Ju; Chen Yun-An; Kobayashi Erika; Murayama ... Archives of Gerontology and Geriatrics/96, 2021-04-01 PubMed / Age, gender, and financial literacy in Japan Okamoto Shohei; Komamura Kohei PLoS ONE/16(11), 2021-04-01 PubMed / Increase in suicide following an initial decline during the COVID-19 pandemic in Japan Tanaka Takanao; Okamoto Shohei Nature Human Behaviour/5(2)/pp.229-238, 2021-02-01 PubMed / Box 5. Catastrophic health spending and unmet need among households with older persons in Japan. Okamoto Shohei Global monitoring report on financial protection in heath 2021, 2021-12 / 新型コロナウイルス感染症拡⼤下における自殺者数の推移 岡本 翔平; 田中 孝直 精神科治療学/pp.869-874, 2021-08 / 新型コロナウイルス感染症拡大のもう一つの脅威 : 感染症対策による非感染性疾患リスクへの影響 岡本 翔平 生活経済政策/294/pp.20-27, 2021-07 / 高齢期の就労と健康 岡本 翔平 健康長寿ネット, 2019-12 / わが国の栄養・食事と関連する健康施策の現状 岡本 翔平; 栗原 綾子; 岡村 智教 動脈硬化予防/pp.40-45, 2017-03</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -3160,7 +3074,7 @@
 衛生学・公衆衛生学
 健康政策
 社会政策
-健康経済学
+医療経済学
 国際保健
 家族・人口政策
 政策評価・計量分析
@@ -3189,7 +3103,8 @@
 高齢期の就労と健康：メカニズムの解明と社会経済への影響に関する研究
 人口高齢化と疾病構造の変化に対応したユニバーサルヘルスカバレッジに関する研究
 疫学転換に対応したuniversal health coverageモニタリング指標の開発
-Financial burden of menstrual and menopausal symptoms: Productivity loss from absenteeism and presenteeism among working age women KASAHARA Shingo; GOTO Rei; SUZUKI Shu; SAKAMOTO Haruk... Reproductive Health/p.(in press), 2026-04
+Spousal bereavement and mental health among older Japanese adults Iida Masumi; Sugawara Ikuko; Kobayashi Erika; Okamoto ... Research on Aging, 2026-06
+Financial burden of menstrual and menopausal symptoms: Productivity loss from absenteeism and presenteeism among working age women KASAHARA Shingo; GOTO Rei; SUZUKI Shu; SAKAMOTO Haruk... Reproductive Health, 2026-05
 Comparison income and subjective well-being: Evidence from a nationwide panel survey in Japan Shiraishi Kenichi; Sumita Kazuto; Kamimura Kazuki; Oka... Economics Bulletin/p.(in press), 2026-04
 Reversed loneliness development after age 65 for men and women: Modeling of the age trajectories of loneliness using national cohorts in Taiwan and Japan Chiu Ching-Ju; Hou Szu-Yu; Kobayashi Erika; Lin Yu-Ch... Geriatrics &amp; Gerontology International/25(4)/pp.620-627, 2025-04-01 PubMed
 Socioeconomic inequity in access to medical and long-term care among older people Okamoto Shohei; Yamada Atsuhiro; Kobayashi Erika; Lian... International Journal for Equity in Health/24(1)/p.28, 2025-01-23 PubMed
@@ -3213,7 +3128,6 @@
 Age trajectories of disability development after 65: A comparison between Japan and Taiwan Chiu Ching-Ju; Chen Yun-An; Kobayashi Erika; Murayama ... Archives of Gerontology and Geriatrics/96, 2021-04-01 PubMed
 Age, gender, and financial literacy in Japan Okamoto Shohei; Komamura Kohei PLoS ONE/16(11), 2021-04-01 PubMed
 Increase in suicide following an initial decline during the COVID-19 pandemic in Japan Tanaka Takanao; Okamoto Shohei Nature Human Behaviour/5(2)/pp.229-238, 2021-02-01 PubMed
-Decomposition of gender differences in cognitive functioning: National Survey of the Japanese elderly Okamoto Shohei; Kobayashi Erika; Murayama Hiroshi; Lia... BMC Geriatrics/21(1)/p.38, 2021-01-10 PubMed
 Box 5. Catastrophic health spending and unmet need among households with older persons in Japan. Okamoto Shohei Global monitoring report on financial protection in heath 2021, 2021-12
 新型コロナウイルス感染症拡⼤下における自殺者数の推移 岡本 翔平; 田中 孝直 精神科治療学/pp.869-874, 2021-08
 新型コロナウイルス感染症拡大のもう一つの脅威 : 感染症対策による非感染性疾患リスクへの影響 岡本 翔平 生活経済政策/294/pp.20-27, 2021-07
@@ -4850,9 +4764,10 @@
 計算社会科学
 ウェブサイエンス
 ビッグデータ
+Fluctuation scaling in online social media Sano Yukie; Takayasu Hideki; Takayasu Misako Proceedings of 2015 International Conference on Noise and Fluctuations (ICNF)/pp.1-5, 2015-06
 Linking Opinion Dynamics and Emotional Expression in Online Communities: a Case Study of Covid-19 Vaccination Discourse in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako The 10th International Workshop on Application of Big Data for Computational Social Science (ABCSS2025)/pp.5876-5883, 2025-12-09
 SNSにおける日本の高齢運転者に対する言論の定量化 佐野幸恵; 中西映人; 吉田光男; 市川政雄 情報処理学会 第88回全国大会, 2026-03
-Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-04-01
+Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-06
 コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 呉 潜雲; 佐野 幸恵; 高安 秀樹; Havlin Shlomo; 高安 美佐子 人工知能学会全国大会論文集/JSAI2024/pp.2I4OS1b05-2I4OS1b05, 2024-05-28
 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19
 Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Havlin Shlom... Scientific Reports/15(1)/p.11716, 2025-04
@@ -4873,8 +4788,7 @@
 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― 水野 誠; 佐野 幸恵; 笹原 和俊 マーケティングジャーナル/40(4)/pp.6-18, 2021 CiNii
 サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して 浅野 翔; 雨宮 護; 佐野 幸恵 オペレーションズリサーチ/66(4)/pp.240(44)-245(49), 2021-04
 Fake news propagates differently from real news even at early stages of spreading Zhao Zilong; Zhao Jichang; Sano Yukie; Levy Orr; Takayasu... EPJ Data Science/9/p.7, 2020-04
-連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii
-Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository</t>
+連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4894,7 +4808,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Linking Opinion Dynamics and Emotional Expression in Online Communities: a Case Study of Covid-19 Vaccination Discourse in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako The 10th International Workshop on Application of Big Data for Computational Social Science (ABCSS2025)/pp.5876-5883, 2025-12-09 / SNSにおける日本の高齢運転者に対する言論の定量化 佐野幸恵; 中西映人; 吉田光男; 市川政雄 情報処理学会 第88回全国大会, 2026-03 / Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-04-01 / コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 呉 潜雲; 佐野 幸恵; 高安 秀樹; Havlin Shlomo; 高安 美佐子 人工知能学会全国大会論文集/JSAI2024/pp.2I4OS1b05-2I4OS1b05, 2024-05-28 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19 / Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Havlin Shlom... Scientific Reports/15(1)/p.11716, 2025-04 / Quantifying Collective Emotions: Japan’s Societal Trends Through Enhanced Sentiment Index Using POMS2 and SNS TAMURA Koutarou; SANO Yukie; SHIOZAKI Junichi 2024 IEEE International Conference on Big Data (BigData)/pp.3082-3087, 2024-12 / Quantifying collective attention and fan engagement: a case study of the Japanese professional baseball league Otomo Naofumi; Sasahara Kazutoshi; Mizuno Makoto; Sano... Journal of Computational Social Science/8(2), 2025-03 / News coverage of older drivers' fatal car crashes: is it over-represented? Ichikawa Masao; Tanaka Rie; Nakanishi Akito; Sano Yukie JOURNAL OF EPIDEMIOLOGY/Epub, 2024-10-26 / Burstiness of human physical activities and their characterisation Takeuchi Makoto; Sano Yukie Journal of Computational Social Science/7/pp.625-641, 2024-03 / 12-year observation of tweets about rubella in Japan: A retrospective infodemiology study Sano Yukie; Hori Ai PLOS ONE/18(5)/p.e0285101, 2023-05 PubMed / A two-phase model of collective memory decay with a dynamical switching point Igarashi Naoki; Okada Yukihiko; Sayama Hiroki; Sano Y... SCIENTIFIC REPORTS/12(1), 2022-12 / SNSデータを用いた情報拡散シミュレーション 佐野 幸恵; 鳥居 寛之 シミュレーション = Journal of the Japan Society for Simulation Technology / 日本シミュレーション学会 編/40(3)/pp.137-143, 2021-09 CiNii / SNSにおける情報伝播ネットワークの構造 佐野 幸恵; 高安 秀樹; 高安 美佐子 日本物理学会誌/77(7)/pp.458-463, 2022-07-05 / Music Roles Affect the Selection of Consumption Means: A Questionnaire Survey of People’s Expectations for Music and Exploratory Factor Analysis Takeuchi Makoto; Morishita Soichiro; Sano Yukie REVIEW OF SOCIONETWORK STRATEGIES/16(2:SI)/pp.453-464, 2022-09 / Dataset of identified scholars mentioned in acknowledgement statements Kusumegi Keigo; Sano Yukie Scientific data/9(1)/p.461, 2022-08 / Classification of endogenous and exogenous bursts in collective emotions based on Weibo comments during COVID-19 Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako Scientific Reports/12(1)/p.3120, 2022-02 / 日本におけるオンライン・ハラスメントの現状と対策：Twitterでの女性記者のツイート「炎上」を例に 礪波 亜希; 吉田 光男; 佐野 幸恵 F1000Research/10, 2022-02 / 日本における自治体報道発表のCOVID-19発生状況を用いた感染者遷移状況の記録と可視化 渡辺 知恵美; 佐野 幸恵; 岡田幸彦; 天笠 俊之 研究報告ドキュメントコミュニケーション（DC）/2020-DC-117(4)/pp.1-7, 2020-07 / Simulation of information spreading on Twitter concerning radiation after the Fukushima nuclear power plant accident Sano Yukie; Torii Hiroyuki A; Onoue Yosuke; Uno Kazuko Frontiers in Physics/9, 2021-06 / 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― 水野 誠; 佐野 幸恵; 笹原 和俊 マーケティングジャーナル/40(4)/pp.6-18, 2021 CiNii / サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して 浅野 翔; 雨宮 護; 佐野 幸恵 オペレーションズリサーチ/66(4)/pp.240(44)-245(49), 2021-04 / Fake news propagates differently from real news even at early stages of spreading Zhao Zilong; Zhao Jichang; Sano Yukie; Levy Orr; Takayasu... EPJ Data Science/9/p.7, 2020-04 / 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii / Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository</t>
+          <t>Fluctuation scaling in online social media Sano Yukie; Takayasu Hideki; Takayasu Misako Proceedings of 2015 International Conference on Noise and Fluctuations (ICNF)/pp.1-5, 2015-06 / Linking Opinion Dynamics and Emotional Expression in Online Communities: a Case Study of Covid-19 Vaccination Discourse in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako The 10th International Workshop on Application of Big Data for Computational Social Science (ABCSS2025)/pp.5876-5883, 2025-12-09 / SNSにおける日本の高齢運転者に対する言論の定量化 佐野幸恵; 中西映人; 吉田光男; 市川政雄 情報処理学会 第88回全国大会, 2026-03 / Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-06 / コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 呉 潜雲; 佐野 幸恵; 高安 秀樹; Havlin Shlomo; 高安 美佐子 人工知能学会全国大会論文集/JSAI2024/pp.2I4OS1b05-2I4OS1b05, 2024-05-28 / 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19 / Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Havlin Shlom... Scientific Reports/15(1)/p.11716, 2025-04 / Quantifying Collective Emotions: Japan’s Societal Trends Through Enhanced Sentiment Index Using POMS2 and SNS TAMURA Koutarou; SANO Yukie; SHIOZAKI Junichi 2024 IEEE International Conference on Big Data (BigData)/pp.3082-3087, 2024-12 / Quantifying collective attention and fan engagement: a case study of the Japanese professional baseball league Otomo Naofumi; Sasahara Kazutoshi; Mizuno Makoto; Sano... Journal of Computational Social Science/8(2), 2025-03 / News coverage of older drivers' fatal car crashes: is it over-represented? Ichikawa Masao; Tanaka Rie; Nakanishi Akito; Sano Yukie JOURNAL OF EPIDEMIOLOGY/Epub, 2024-10-26 / Burstiness of human physical activities and their characterisation Takeuchi Makoto; Sano Yukie Journal of Computational Social Science/7/pp.625-641, 2024-03 / 12-year observation of tweets about rubella in Japan: A retrospective infodemiology study Sano Yukie; Hori Ai PLOS ONE/18(5)/p.e0285101, 2023-05 PubMed / A two-phase model of collective memory decay with a dynamical switching point Igarashi Naoki; Okada Yukihiko; Sayama Hiroki; Sano Y... SCIENTIFIC REPORTS/12(1), 2022-12 / SNSデータを用いた情報拡散シミュレーション 佐野 幸恵; 鳥居 寛之 シミュレーション = Journal of the Japan Society for Simulation Technology / 日本シミュレーション学会 編/40(3)/pp.137-143, 2021-09 CiNii / SNSにおける情報伝播ネットワークの構造 佐野 幸恵; 高安 秀樹; 高安 美佐子 日本物理学会誌/77(7)/pp.458-463, 2022-07-05 / Music Roles Affect the Selection of Consumption Means: A Questionnaire Survey of People’s Expectations for Music and Exploratory Factor Analysis Takeuchi Makoto; Morishita Soichiro; Sano Yukie REVIEW OF SOCIONETWORK STRATEGIES/16(2:SI)/pp.453-464, 2022-09 / Dataset of identified scholars mentioned in acknowledgement statements Kusumegi Keigo; Sano Yukie Scientific data/9(1)/p.461, 2022-08 / Classification of endogenous and exogenous bursts in collective emotions based on Weibo comments during COVID-19 Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako Scientific Reports/12(1)/p.3120, 2022-02 / 日本におけるオンライン・ハラスメントの現状と対策：Twitterでの女性記者のツイート「炎上」を例に 礪波 亜希; 吉田 光男; 佐野 幸恵 F1000Research/10, 2022-02 / 日本における自治体報道発表のCOVID-19発生状況を用いた感染者遷移状況の記録と可視化 渡辺 知恵美; 佐野 幸恵; 岡田幸彦; 天笠 俊之 研究報告ドキュメントコミュニケーション（DC）/2020-DC-117(4)/pp.1-7, 2020-07 / Simulation of information spreading on Twitter concerning radiation after the Fukushima nuclear power plant accident Sano Yukie; Torii Hiroyuki A; Onoue Yosuke; Uno Kazuko Frontiers in Physics/9, 2021-06 / 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― 水野 誠; 佐野 幸恵; 笹原 和俊 マーケティングジャーナル/40(4)/pp.6-18, 2021 CiNii / サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して 浅野 翔; 雨宮 護; 佐野 幸恵 オペレーションズリサーチ/66(4)/pp.240(44)-245(49), 2021-04 / Fake news propagates differently from real news even at early stages of spreading Zhao Zilong; Zhao Jichang; Sano Yukie; Levy Orr; Takayasu... EPJ Data Science/9/p.7, 2020-04 / 連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4987,9 +4901,10 @@
 乳幼児の活動量を測定するウェアラブル機器の開発
 乳幼児の活動量を測定するウェアラブルデバイスの開発
 サイバー社会ネットワークにおける噂の伝播の検出と制御
+Fluctuation scaling in online social media Sano Yukie; Takayasu Hideki; Takayasu Misako Proceedings of 2015 International Conference on Noise and Fluctuations (ICNF)/pp.1-5, 2015-06
 Linking Opinion Dynamics and Emotional Expression in Online Communities: a Case Study of Covid-19 Vaccination Discourse in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Takayasu Misako The 10th International Workshop on Application of Big Data for Computational Social Science (ABCSS2025)/pp.5876-5883, 2025-12-09
 SNSにおける日本の高齢運転者に対する言論の定量化 佐野幸恵; 中西映人; 吉田光男; 市川政雄 情報処理学会 第88回全国大会, 2026-03
-Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-04-01
+Public Discourse Toward Older Drivers in Japan Using Social Media Data From 2010 to 2022: Longitudinal Analysis Nakanishi Akito; Ichikawa Masao; Sano Yukie JMIR INFODEMIOLOGY/5, 2025-06
 コロナワクチンに関するTwitter上の意見の変化：動的ネットワークコミュニティ検出と意見混在の分析 呉 潜雲; 佐野 幸恵; 高安 秀樹; Havlin Shlomo; 高安 美佐子 人工知能学会全国大会論文集/JSAI2024/pp.2I4OS1b05-2I4OS1b05, 2024-05-28
 有価証券報告書のテキストから得られる多次元感情と株式リターンの分析 冨樫 歩大; 佐野 幸恵; 岡田 幸彦 人工知能学会第二種研究会資料/2024(FIN-033)/pp.185-191, 2024-10-19
 Twitter communities are associated with changing user’s opinion towards COVID-19 vaccine in Japan Wu Qianyun; Sano Yukie; Takayasu Hideki; Havlin Shlom... Scientific Reports/15(1)/p.11716, 2025-04
@@ -5010,8 +4925,7 @@
 熱狂するファンダム:― プロ野球ファンのツイートを分析する ― 水野 誠; 佐野 幸恵; 笹原 和俊 マーケティングジャーナル/40(4)/pp.6-18, 2021 CiNii
 サイバー空間における情報拡散のフィジカル空間表現：大阪府警察本部Twitterに注目して 浅野 翔; 雨宮 護; 佐野 幸恵 オペレーションズリサーチ/66(4)/pp.240(44)-245(49), 2021-04
 Fake news propagates differently from real news even at early stages of spreading Zhao Zilong; Zhao Jichang; Sano Yukie; Levy Orr; Takayasu... EPJ Data Science/9/p.7, 2020-04
-連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii
-Identifying long-term periodic cycles and memories of collective emotion in online social media Sano Yukie; Takayasu Hideki; Havlin Shlomo; Takayasu Misako PLoS ONE/14(3)/p.e0213843, 2019-03 PubMed Tsukuba Repository</t>
+連載：情報を計測し，法則化する～今に活かせる計量情報学の経験則: Zipf則・Heaps則とその周辺 佐野 幸恵 情報の科学と技術/70(2)/pp.87-89, 2020-02 CiNii</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5136,7 @@
 職名
 教授
 eメール
-I$v "&amp;:IE*"C+*,",wvCvxC!'
+)D8@BFZieJBcKJLBL98c8:cAG
 最適化
 組合せ最適化
 アルゴリズム
@@ -5260,7 +5174,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / I$v "&amp;:IE*"C+*,",wvCvxC!'</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 繁野 麻衣子(シゲノ マイコ) / 所属 / システム情報系 / 職名 / 教授 / eメール / )D8@BFZieJBcKJLBL98c8:cAG</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -5280,7 +5194,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; I$v "&amp;:IE*"C+*,",wvCvxC!' ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 繁野 麻衣子(シゲノ マイコ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; eメール ; )D8@BFZieJBcKJLBL98c8:cAG ; オペレーションズリサーチ ; ネットワーク・グラフ理論 ; 数理最適化・OR ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -5299,7 +5213,7 @@
 職名
 教授
 eメール
-I$v "&amp;:IE*"C+*,",wvCvxC!'
+)D8@BFZieJBcKJLBL98c8:cAG
 最適化
 組合せ最適化
 アルゴリズム
@@ -6042,7 +5956,8 @@
 view
 hirokitakahashi
 eメール
-G-x$x!x,!"E!"+($"E '&lt;KG.E-,.$.yxExzE#)
+I+v"v}v*} C} )&amp;" C
+%:IE,C+*,",wvCvxC!'
 研究室
 3F1236
 電話
@@ -6070,7 +5985,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / G-x$x!x,!"E!"+($"E '&lt;KG.E-,.$.yxExzE#) / 研究室 / 3F1236 / 電話 / 5379</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 髙橋 裕紀(タカハシ ヒロキ) / 所属 / システム情報系 / 職名 / 助教 / ORCID / 0000-0003-1356-1467 / 性別 / 男性 / 生年月 / 1993-06 / URL / https: / sites.google.com / view / hirokitakahashi / eメール / I+v"v}v*} C} )&amp;" C / %:IE,C+*,",wvCvxC!' / 研究室 / 3F1236 / 電話 / 5379</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -6086,7 +6001,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; G-x$x!x,!"E!"+($"E '&lt;KG.E-,.$.yxExzE#) ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 髙橋 裕紀(タカハシ ヒロキ) ; 所属 ; システム情報系 ; 職名 ; 助教 ; ORCID ; 0000-0003-1356-1467 ; 性別 ; 男性 ; 生年月 ; 1993-06 ; URL ; https: ; sites.google.com ; view ; hirokitakahashi ; eメール ; I+v"v}v*} C} )&amp;" C ; %:IE,C+*,",wvCvxC!' ; 研究室 ; 3F1236 ; 電話 ; 5379 ; 意思決定分析 ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -6116,7 +6031,8 @@
 view
 hirokitakahashi
 eメール
-G-x$x!x,!"E!"+($"E '&lt;KG.E-,.$.yxExzE#)
+I+v"v}v*} C} )&amp;" C
+%:IE,C+*,",wvCvxC!'
 研究室
 3F1236
 電話
@@ -6664,14 +6580,10 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=200901054428620829</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ok_jglobal_fallback</t>
+          <t>jglobal_not_found</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6679,113 +6591,19 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>次世代無線通信網での高速データ通信手法と適応能力をもつネットワーク構築手法の開発
-患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学
-無線メッシュネットワークにおけるスループットの最大化とフローの公平性に関する研究
-準天頂衛星および無線メッシュLANを利用した被災情報伝送法の開発
-無線ネットワークにおける電波資源の有効利用に関する研究
-資源の動的最適配分法の理論とその無線周波数帯域割当て及びサービス科学への応用
-産学連携による実践型人材育成事業-サービス・イノベーション人材育成-
-文理融合型サービス・イノベーション研究教育拠点形成のための研究ネットワーク基盤構築
-Web技術に基づくWi-Fiタグを用いた大規模位置検知システムの開発
-広帯域無線ネットワークにおけるサービス品質保証の研究
-文部省「先進的大学改革推進委託事業」博士課程「短期在学コース」の創設に係わる課題などに関する調査研究
-次世代情報通信ネットワークにおける経路制御方式に関する研究
-移動体無線通信網におけるサービス品質の評価と通信資源の最適配分に関する理論的研究
-Wireless Communication Networks
-品質保証を可能にするマルチサービス光ネットワークアーキテクチャに関する研究
-インターネットのトラヒック源のモデル化と測定による検証
-シームレス情報通信網の設計と性能評価のための通信トラヒック解析
-実時間データベースシステムにおけるトランザクションスケジューリングに関する研究
-複合通信ネットワークの性能評価と管理の確率モデル
-分散コンピュータシステムにおける最適な動的資源配分に関する研究
-移動通信システムにおける周波数資源の最適割り当て方式に関する研究
-移動エージントによる分散処理システムの構築
-WDM光通信ネットワークにおけるルーティング方式
-Optimal routing in power-aware senor networks
-通信工学
-Zheng, Weichang, Yang, Mingcong, Zheng, Yu, ZHANG, Yongbing, Yang, Kun. Joint routing, band, and spectrum assignment in C+L band elastic optical network towards ultra-broadband era. Computer Networks. 2025. 267. 111373
-Zheng, Weichang, Ke, Ming, Li, Jinke, Yang, Mingcong, Zheng, Yu, Zhang, Yongbing, Yang, Kun. Improved ILP Models and Heuristics for Solving Routing and Resource Allocation Problems in Optical Networks. JOURNAL OF LIGHTWAVE TECHNOLOGY. 2025. 43. 7. 3016-3033
-Jin, Cheng, Zheng, Yu, Yang, Mingcong, ZHANG, Yongbing. Efficient Optical Line Terminal Placement for Passive Optical Network Deployment. IEEE ACCESS. 2025. 13. 38794
-Zheng, Yu, Zheng, Weichang, Yang, Mingcong, ZHANG, Yongbing. Shared Rerouting Backup Path Protection (SRBPP) Technology Based on Elastic Optical Networks. Proc. Int. Conf. Information Networking (ICOIN 2025). 2025
-Zheng, Yu, Zheng, W., Yang, M., Jin, C., Zhang, C., ZHANG, Yongbing. Dynamic Routing, Spatial Channel, and Spectrum Assignment (RSCSA) in Spatial Channel Networks (SCNs) based on Granularity Switching Threshold. JOURNAL OF OPTICAL COMMUNICATIONS AND NETWORKING. 2024. 16. 9. 905-917</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>次世代無線通信網での高速データ通信手法と適応能力をもつネットワーク構築手法の開発 / 患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学 / 無線メッシュネットワークにおけるスループットの最大化とフローの公平性に関する研究 / 準天頂衛星および無線メッシュLANを利用した被災情報伝送法の開発 / 無線ネットワークにおける電波資源の有効利用に関する研究 / 資源の動的最適配分法の理論とその無線周波数帯域割当て及びサービス科学への応用 / 産学連携による実践型人材育成事業-サービス・イノベーション人材育成- / 文理融合型サービス・イノベーション研究教育拠点形成のための研究ネットワーク基盤構築 / Web技術に基づくWi-Fiタグを用いた大規模位置検知システムの開発 / 広帯域無線ネットワークにおけるサービス品質保証の研究 / 文部省「先進的大学改革推進委託事業」博士課程「短期在学コース」の創設に係わる課題などに関する調査研究 / 次世代情報通信ネットワークにおける経路制御方式に関する研究 / 移動体無線通信網におけるサービス品質の評価と通信資源の最適配分に関する理論的研究 / Wireless Communication Networks / 品質保証を可能にするマルチサービス光ネットワークアーキテクチャに関する研究 / インターネットのトラヒック源のモデル化と測定による検証 / シームレス情報通信網の設計と性能評価のための通信トラヒック解析 / 実時間データベースシステムにおけるトランザクションスケジューリングに関する研究 / 複合通信ネットワークの性能評価と管理の確率モデル / 分散コンピュータシステムにおける最適な動的資源配分に関する研究 / 移動通信システムにおける周波数資源の最適割り当て方式に関する研究 / 移動エージントによる分散処理システムの構築 / WDM光通信ネットワークにおけるルーティング方式 / Optimal routing in power-aware senor networks</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>通信工学</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Zheng, Weichang, Yang, Mingcong, Zheng, Yu, ZHANG, Yongbing, Yang, Kun. Joint routing, band, and spectrum assignment in C+L band elastic optical network towards ultra-broadband era. Computer Networks. 2025. 267. 111373 / Zheng, Weichang, Ke, Ming, Li, Jinke, Yang, Mingcong, Zheng, Yu, Zhang, Yongbing, Yang, Kun. Improved ILP Models and Heuristics for Solving Routing and Resource Allocation Problems in Optical Networks. JOURNAL OF LIGHTWAVE TECHNOLOGY. 2025. 43. 7. 3016-3033 / Jin, Cheng, Zheng, Yu, Yang, Mingcong, ZHANG, Yongbing. Efficient Optical Line Terminal Placement for Passive Optical Network Deployment. IEEE ACCESS. 2025. 13. 38794 / Zheng, Yu, Zheng, Weichang, Yang, Mingcong, ZHANG, Yongbing. Shared Rerouting Backup Path Protection (SRBPP) Technology Based on Elastic Optical Networks. Proc. Int. Conf. Information Networking (ICOIN 2025). 2025 / Zheng, Yu, Zheng, W., Yang, M., Jin, C., Zhang, C., ZHANG, Yongbing. Dynamic Routing, Spatial Channel, and Spectrum Assignment (RSCSA) in Spatial Channel Networks (SCNs) based on Granularity Switching Threshold. JOURNAL OF OPTICAL COMMUNICATIONS AND NETWORKING. 2024. 16. 9. 905-917</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>スマートメーターデータを用いたエネルギー消費パターンの分析 / Time and QoS aware Machine Learning-based traffic classification / QoS routing protocols in ad hoc networks / Edge caching schemes over PON-based mobile cellular networks / A comprehensive test and assessment of an under studying Japanese TTS system / Routing and spectrum assignmnet in MCF-SDM networks / A blockchain construction approach for edge computing applications / Routing and Spectrum Assignment for Dual Failure Path Proteced MCF-SDM networks / 次世代無線LANにおける効率的なリソース割当に関する研究 / 深層強化学習手法を用いた通信ネットワークにおける高信頼性ルーティングに関する研究 / Routing and spectrum assignment using a packing approach in elastic optical networks / 強化学習手法を用いた光ネットワークにおける動的ルーティングとスペクトル割当法に関する研究</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>通信工学 ; 労働経済・就職マッチング ; マッチング理論・ゲーム理論 ; 都市・地域政策 ; オペレーションズリサーチ ; 画像・視覚情報処理 ; ネットワーク・グラフ理論 ; 医療・ヘルスデータ ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>通信工学
-労働経済・就職マッチング
-マッチング理論・ゲーム理論
-都市・地域政策
-オペレーションズリサーチ
-画像・視覚情報処理
-ネットワーク・グラフ理論
-医療・ヘルスデータ
-公共政策・社会工学
-数理最適化・OR
-AI・データサイエンス
-労働経済
-人的資本
-就職マッチング
-採用市場設計
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
-都市経済
-地域政策
-土地利用
-公共政策評価
-数理最適化
-組合せ最適化
-計画・スケジューリング
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-医療データ分析
-生体情報解析
-ヘルスデータサイエンス
-統計解析</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>スマートメーターデータを用いたエネルギー消費パターンの分析
@@ -6799,36 +6617,7 @@
 次世代無線LANにおける効率的なリソース割当に関する研究
 深層強化学習手法を用いた通信ネットワークにおける高信頼性ルーティングに関する研究
 Routing and spectrum assignment using a packing approach in elastic optical networks
-強化学習手法を用いた光ネットワークにおける動的ルーティングとスペクトル割当法に関する研究
-次世代無線通信網での高速データ通信手法と適応能力をもつネットワーク構築手法の開発
-患者の満足とスタッフの適正労働を実現する地域基幹病院の医療サービス科学
-無線メッシュネットワークにおけるスループットの最大化とフローの公平性に関する研究
-準天頂衛星および無線メッシュLANを利用した被災情報伝送法の開発
-無線ネットワークにおける電波資源の有効利用に関する研究
-資源の動的最適配分法の理論とその無線周波数帯域割当て及びサービス科学への応用
-産学連携による実践型人材育成事業-サービス・イノベーション人材育成-
-文理融合型サービス・イノベーション研究教育拠点形成のための研究ネットワーク基盤構築
-Web技術に基づくWi-Fiタグを用いた大規模位置検知システムの開発
-広帯域無線ネットワークにおけるサービス品質保証の研究
-文部省「先進的大学改革推進委託事業」博士課程「短期在学コース」の創設に係わる課題などに関する調査研究
-次世代情報通信ネットワークにおける経路制御方式に関する研究
-移動体無線通信網におけるサービス品質の評価と通信資源の最適配分に関する理論的研究
-Wireless Communication Networks
-品質保証を可能にするマルチサービス光ネットワークアーキテクチャに関する研究
-インターネットのトラヒック源のモデル化と測定による検証
-シームレス情報通信網の設計と性能評価のための通信トラヒック解析
-実時間データベースシステムにおけるトランザクションスケジューリングに関する研究
-複合通信ネットワークの性能評価と管理の確率モデル
-分散コンピュータシステムにおける最適な動的資源配分に関する研究
-移動通信システムにおける周波数資源の最適割り当て方式に関する研究
-移動エージントによる分散処理システムの構築
-WDM光通信ネットワークにおけるルーティング方式
-Optimal routing in power-aware senor networks
-Zheng, Weichang, Yang, Mingcong, Zheng, Yu, ZHANG, Yongbing, Yang, Kun. Joint routing, band, and spectrum assignment in C+L band elastic optical network towards ultra-broadband era. Computer Networks. 2025. 267. 111373
-Zheng, Weichang, Ke, Ming, Li, Jinke, Yang, Mingcong, Zheng, Yu, Zhang, Yongbing, Yang, Kun. Improved ILP Models and Heuristics for Solving Routing and Resource Allocation Problems in Optical Networks. JOURNAL OF LIGHTWAVE TECHNOLOGY. 2025. 43. 7. 3016-3033
-Jin, Cheng, Zheng, Yu, Yang, Mingcong, ZHANG, Yongbing. Efficient Optical Line Terminal Placement for Passive Optical Network Deployment. IEEE ACCESS. 2025. 13. 38794
-Zheng, Yu, Zheng, Weichang, Yang, Mingcong, ZHANG, Yongbing. Shared Rerouting Backup Path Protection (SRBPP) Technology Based on Elastic Optical Networks. Proc. Int. Conf. Information Networking (ICOIN 2025). 2025
-Zheng, Yu, Zheng, W., Yang, M., Jin, C., Zhang, C., ZHANG, Yongbing. Dynamic Routing, Spatial Channel, and Spectrum Assignment (RSCSA) in Spatial Channel Networks (SCNs) based on Granularity Switching Threshold. JOURNAL OF OPTICAL COMMUNICATIONS AND NETWORKING. 2024. 16. 9. 905-917</t>
+強化学習手法を用いた光ネットワークにおける動的ルーティングとスペクトル割当法に関する研究</t>
         </is>
       </c>
     </row>
@@ -7080,6 +6869,7 @@
 数理情報学
 社会システム工学・安全システム
 応用確率論、 確率モデル、 待ち行列理論、 性能評価、 オペレーションズ・リサーチ、確率システム
+Energy-Efficient Controls for M/M/c/Setup Queues with Threshold-Based Policies Taiga Kawano; Tuan Phung-Duc Lecture Notes in Computer Science/16629/pp.33-48, 2026-06 Tsukuba Repository
 Retrial Queues: Scaling Limits Tuan Phung-Duc Journal of Systems Scalability/1(2)/pp.39-42, 2026-04
 Analysis of Multiserver Queues with Batch Arrivals and Setup Times Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.128-137, 2026-02
 Multi-Server Queues with s-staggered Setup: A Faster Computational Approach Thu Le-Anh; Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.118-127, 2026-02
@@ -7103,8 +6893,7 @@
 Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes Ayane Nakamura; Tuan Phung-Duc QUEUEING SYSTEMS/106(1-2)/pp.129-158, 2023-11
 Modeling and performance analysis of hybrid systems by queues with setup time Mitsuki Sato; Kohei Kawamura; Ken’ichi Kawanishi; Tuan... PERFORMANCE EVALUATION/162(102366), 2023-11
 Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis Yi Ren; Tuan Phung-Duc; Jyh-Cheng Chen; Frank Y. Li IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY/72(6)/pp.7743-7756, 2023-01
-Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04
-To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository</t>
+Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -7124,7 +6913,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Retrial Queues: Scaling Limits Tuan Phung-Duc Journal of Systems Scalability/1(2)/pp.39-42, 2026-04 / Analysis of Multiserver Queues with Batch Arrivals and Setup Times Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.128-137, 2026-02 / Multi-Server Queues with s-staggered Setup: A Faster Computational Approach Thu Le-Anh; Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.118-127, 2026-02 / Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03 Tsukuba Repository / Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03 Tsukuba Repository / A simulation study of the sojourn time in queueing systems with stochastically delayed information Kazuma Abe; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering, 2025-12 / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Proceedings of 2025 International Symposium on Nonlinear Theory and Its Applications (Nolta 2025)/pp.526-529, 2025-10 / Performance Analysis of Blockchain with Rollups Yusei Funahashi; Tuan Phung-Duc Proceedings of Asia-Pacific Conference on Communications (APCC) 2025, 2025-11 Tsukuba Repository / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times Nguyen Hung Q.; Phung-Duc Tuan Operations Research Letters/63(107362), 2025-11 Tsukuba Repository / Analysis of a Batch Arrival Queue with Power Saving Mode Yuta Sakai; Tuan Phung-Duc Communications in Computer and Information Science/2472/pp.181-192, 2025-05 / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes Thu Le-Anh; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering/663/pp.142-157, 2026-01 Tsukuba Repository / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes Thu Le-Anh; Tuan Phung-Duc Proceedings of 36th International Teletraffic Congress, 2025-06 Tsukuba Repository / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory Koki Inami; Tuan Phung-Duc Mathematics/13(6)/pp.1010-1-1010-18, 2025-03 Tsukuba Repository / Analytical Modelling of Asymmetric Multi-core Servers Marco Gribaudo; Tuan Phung-Duc Lecture Notes in Computer Science/15454/pp.121-136, 2025-02 / Energy-performance tradeoffs in server farms with batch services and setup times Le-Anh Thu; Phung-Duc Tuan PERFORMANCE EVALUATION/168, 2025-06 Tsukuba Repository / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers Nakamura Ayane; Phung-Duc Tuan TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/171, 2025-02 Tsukuba Repository / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Mathematics/12(18)/pp.2820-1-2820-27, 2024-09 / Queueing Analysis of an Ensemble Machine Learning System Keishin Tsutsumi; Tuan Phung-Duc; Hong-Linh Truong Lecture Notes in Computer Science/14826/pp.97-111, 2024-09 / Performance analysis of a collision channel with abandonments Fiems Dieter; Tuan Phung-Duc PERFORMANCE EVALUATION/165(102424), 2024-08 / Empirical architecture comparison of two-input machine learning systems for vision tasks Kazuya Wakigami; Fumio Machida; Tuan Phung-Duc Formal Aspects of Computing/36(4), 2024-06 / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes Ayane Nakamura; Tuan Phung-Duc QUEUEING SYSTEMS/106(1-2)/pp.129-158, 2023-11 / Modeling and performance analysis of hybrid systems by queues with setup time Mitsuki Sato; Kohei Kawamura; Ken’ichi Kawanishi; Tuan... PERFORMANCE EVALUATION/162(102366), 2023-11 / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis Yi Ren; Tuan Phung-Duc; Jyh-Cheng Chen; Frank Y. Li IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY/72(6)/pp.7743-7756, 2023-01 / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04 / To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository</t>
+          <t>Energy-Efficient Controls for M/M/c/Setup Queues with Threshold-Based Policies Taiga Kawano; Tuan Phung-Duc Lecture Notes in Computer Science/16629/pp.33-48, 2026-06 Tsukuba Repository / Retrial Queues: Scaling Limits Tuan Phung-Duc Journal of Systems Scalability/1(2)/pp.39-42, 2026-04 / Analysis of Multiserver Queues with Batch Arrivals and Setup Times Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.128-137, 2026-02 / Multi-Server Queues with s-staggered Setup: A Faster Computational Approach Thu Le-Anh; Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.118-127, 2026-02 / Performance Analysis of Energy-efficient Reliable AIoT System Architectures Shoma Nishio; Yuta Makino; Tuan Phung-Duc; Fumio Machida Journal of Systems Scalability/1(1)/pp.6-22, 2026-03 Tsukuba Repository / Queueing Model with Alternating Service for Zipper Merging Yuki Goto; Tuan Phung-Duc Proceedings of the 15th International Conference on Operations Research and Enterprise Systems - ICORES, 2026-03 Tsukuba Repository / A simulation study of the sojourn time in queueing systems with stochastically delayed information Kazuma Abe; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering, 2025-12 / Queueing Analysis of Mode Selection Problem Between Solo/Shared Services with Strategic Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Proceedings of 2025 International Symposium on Nonlinear Theory and Its Applications (Nolta 2025)/pp.526-529, 2025-10 / Performance Analysis of Blockchain with Rollups Yusei Funahashi; Tuan Phung-Duc Proceedings of Asia-Pacific Conference on Communications (APCC) 2025, 2025-11 Tsukuba Repository / Subgame perfect Nash equilibrium analysis in a two-population strategic matching queue with nonzero matching times Nguyen Hung Q.; Phung-Duc Tuan Operations Research Letters/63(107362), 2025-11 Tsukuba Repository / Analysis of a Batch Arrival Queue with Power Saving Mode Yuta Sakai; Tuan Phung-Duc Communications in Computer and Information Science/2472/pp.181-192, 2025-05 / Analysis of Multi-server Queueing Systems with Setup Times and Power-saving Modes Thu Le-Anh; Tuan Phung-Duc Lecture Notes of the Institute for Computer Sciences, Social Informatics and Telecommunications Engineering/663/pp.142-157, 2026-01 Tsukuba Repository / A Fast Algorithm for Multiserver Queueing Systems with Setup Times and Power-saving Modes Thu Le-Anh; Tuan Phung-Duc Proceedings of 36th International Teletraffic Congress, 2025-06 Tsukuba Repository / Analysis of Dynamic Transaction Fee Blockchain using Queueing Theory Koki Inami; Tuan Phung-Duc Mathematics/13(6)/pp.1010-1-1010-18, 2025-03 Tsukuba Repository / Analytical Modelling of Asymmetric Multi-core Servers Marco Gribaudo; Tuan Phung-Duc Lecture Notes in Computer Science/15454/pp.121-136, 2025-02 / Energy-performance tradeoffs in server farms with batch services and setup times Le-Anh Thu; Phung-Duc Tuan PERFORMANCE EVALUATION/168, 2025-06 Tsukuba Repository / Fair and efficient sharing: Dynamic pricing control for batch service system with strategic customers Nakamura Ayane; Phung-Duc Tuan TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/171, 2025-02 Tsukuba Repository / Sojourn Time Analysis of a Single-Server Queue with Single- and Batch-Service Customers Yusei Koyama; Ayane Nakamura; Tuan Phung-Duc Mathematics/12(18)/pp.2820-1-2820-27, 2024-09 / Queueing Analysis of an Ensemble Machine Learning System Keishin Tsutsumi; Tuan Phung-Duc; Hong-Linh Truong Lecture Notes in Computer Science/14826/pp.97-111, 2024-09 / Performance analysis of a collision channel with abandonments Fiems Dieter; Tuan Phung-Duc PERFORMANCE EVALUATION/165(102424), 2024-08 / Empirical architecture comparison of two-input machine learning systems for vision tasks Kazuya Wakigami; Fumio Machida; Tuan Phung-Duc Formal Aspects of Computing/36(4), 2024-06 / Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes Ayane Nakamura; Tuan Phung-Duc QUEUEING SYSTEMS/106(1-2)/pp.129-158, 2023-11 / Modeling and performance analysis of hybrid systems by queues with setup time Mitsuki Sato; Kohei Kawamura; Ken’ichi Kawanishi; Tuan... PERFORMANCE EVALUATION/162(102366), 2023-11 / Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis Yi Ren; Tuan Phung-Duc; Jyh-Cheng Chen; Frank Y. Li IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY/72(6)/pp.7743-7756, 2023-01 / Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -7185,6 +6974,7 @@
 錐最適化技術の実社会における利活用を加速させる基礎理論の整備と深化
 顧客の再試行と途中放棄を考慮したコールセンターのモデル化と性能解析
 再試行型待ち行列によるコールセンターの性能解析とサービス科学への応用
+Energy-Efficient Controls for M/M/c/Setup Queues with Threshold-Based Policies Taiga Kawano; Tuan Phung-Duc Lecture Notes in Computer Science/16629/pp.33-48, 2026-06 Tsukuba Repository
 Retrial Queues: Scaling Limits Tuan Phung-Duc Journal of Systems Scalability/1(2)/pp.39-42, 2026-04
 Analysis of Multiserver Queues with Batch Arrivals and Setup Times Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.128-137, 2026-02
 Multi-Server Queues with s-staggered Setup: A Faster Computational Approach Thu Le-Anh; Tuan Phung-Duc RIMS Kôkyûroku/2336/pp.118-127, 2026-02
@@ -7208,8 +6998,7 @@
 Exact and Asymptotic Analysis of Infinite Server Batch Service Queues with Random Batch Sizes Ayane Nakamura; Tuan Phung-Duc QUEUEING SYSTEMS/106(1-2)/pp.129-158, 2023-11
 Modeling and performance analysis of hybrid systems by queues with setup time Mitsuki Sato; Kohei Kawamura; Ken’ichi Kawanishi; Tuan... PERFORMANCE EVALUATION/162(102366), 2023-11
 Enabling Dynamic Autoscaling for NFV in a Non-Standalone Virtual EPC: Design and Analysis Yi Ren; Tuan Phung-Duc; Jyh-Cheng Chen; Frank Y. Li IEEE TRANSACTIONS ON VEHICULAR TECHNOLOGY/72(6)/pp.7743-7756, 2023-01
-Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04
-To wait or not to wait: Strategic behaviors in an observable batch-service queueing system Hung Quoc Nguyen; Tuan Phung-Duc Operations Research Letters/50(3)/pp.343-346, 2022-05 Tsukuba Repository</t>
+Design and Analysis of Dynamic Block-setup Reservation Algorithm for 5G Network Slicing Cheng-Ying Hsieh; Tuan Phung-Duc; Yi Ren; Jyh-Cheng Chen IEEE TRANSACTIONS ON MOBILE COMPUTING/22(9)/pp.5140-5154, 2022-04</t>
         </is>
       </c>
     </row>
@@ -8271,16 +8060,13 @@
 都市計画・建築計画
 建築史・意匠
 地域研究
-建築・都市計画史
 地中海都市
-ヘレニズム基盤
-イスラーム的都市形成
-西アジア
 中東・北アフリカ
 歴史文化保全
 国際協力
+Formation and change of an international exchange organization ATBAT: A study on the history of international and regional exchange activity of ATBAT(Atelier des Bâtisseurs), part 1 MATSUBARA Kosuke JAPAN ARCHITECTURAL REVIEW, 2026-07
 Modernist Master Planning and Resident Adaptation in Abuja, Nigeria: a Historical Geography of Imposed Spatial Order,1976-2024 AKINKUNMI Priscilla; MATSUBARA Kosuke Planning Perspectives, 2026-04
-Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026-04
+Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review/9(1), 2026-04
 フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― 戸田 理香子; 松原 康介 日本建築学会計画系論文集/91(840)/pp.351-362, 2026-02
 吉田正春使節団が見た19世紀テヘラン都市改造 松原 康介 都市計画論文集/60(3)/pp.532-539, 2025-10
 Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08
@@ -8302,8 +8088,7 @@
 アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 和田 夏音; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.321-322, 2024-08
 商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08
 19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08
-カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08
-カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08</t>
+カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -8318,12 +8103,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>建築・都市計画史 / 地中海都市 / ヘレニズム基盤 / イスラーム的都市形成 / 西アジア / 中東・北アフリカ / 歴史文化保全 / 国際協力</t>
+          <t>地中海都市 / 中東・北アフリカ / 歴史文化保全 / 国際協力</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Modernist Master Planning and Resident Adaptation in Abuja, Nigeria: a Historical Geography of Imposed Spatial Order,1976-2024 AKINKUNMI Priscilla; MATSUBARA Kosuke Planning Perspectives, 2026-04 / Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026-04 / フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― 戸田 理香子; 松原 康介 日本建築学会計画系論文集/91(840)/pp.351-362, 2026-02 / 吉田正春使節団が見た19世紀テヘラン都市改造 松原 康介 都市計画論文集/60(3)/pp.532-539, 2025-10 / Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08 / Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08 / Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08 / The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08 / ジスカール・デスタン政権下のパリ歩行者空間整備 家城悠紀; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.415-416, 2025-08 / 1960 年アガディール地震とその震災復興都市計画に関する研究 根岸美空; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.427-428, 2025-08 / フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 三重野馨; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.207-208, 2025-08 / フェルナン・プイヨンのベルカステル村修復に関する研究 ─城と村の一体性に着目して─ 古市麻菜子; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.205-206, 2025-08 / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス 吉田悠乃; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.203-204, 2025-08 / 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 瀨古希; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.541-542, 2025-08 / フェス 積み重なる寄進が形成した迷宮都市 松原 康介 建築知識/2025(7)/pp.84-85, 2025-6 / ガルダイア 丘の上の城塞とオアシス渓谷の集落 松原 康介 建築知識/2025(7)/pp.82-83, 2025-6 / カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- 渡邊 智也; 松原 康介 都市計画論文集/59(3)/pp.892-899, 2024-10 / The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10 / Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris FURUICHI Manako; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-15-6-1-D-15-6-4, 2024-09 / Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille YOSHIDA Yuno; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-5-5-1-D-5-5-4, 2024-09 / アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 和田 夏音; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.321-322, 2024-08 / 商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08 / 19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08</t>
+          <t>Formation and change of an international exchange organization ATBAT: A study on the history of international and regional exchange activity of ATBAT(Atelier des Bâtisseurs), part 1 MATSUBARA Kosuke JAPAN ARCHITECTURAL REVIEW, 2026-07 / Modernist Master Planning and Resident Adaptation in Abuja, Nigeria: a Historical Geography of Imposed Spatial Order,1976-2024 AKINKUNMI Priscilla; MATSUBARA Kosuke Planning Perspectives, 2026-04 / Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review/9(1), 2026-04 / フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― 戸田 理香子; 松原 康介 日本建築学会計画系論文集/91(840)/pp.351-362, 2026-02 / 吉田正春使節団が見た19世紀テヘラン都市改造 松原 康介 都市計画論文集/60(3)/pp.532-539, 2025-10 / Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08 / Reconciling Modernist Planning and Lived Realities: Lessons from Abuja for Sustainable Urban Development AKINKUNMI Priscilla; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.508-512, 2025-08 / Study on the 1960 Agadir Earthquake and its Earthquake Reconstruction Urban Planning NEGISHI Misora; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.598-602, 2025-08 / The Urban Forming History of Dubrovnik During the 12th Until 17th Century SEKO Nozomi; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.593-597, 2025-08 / ジスカール・デスタン政権下のパリ歩行者空間整備 家城悠紀; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.415-416, 2025-08 / 1960 年アガディール地震とその震災復興都市計画に関する研究 根岸美空; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.427-428, 2025-08 / フェルナン・プイヨンのアルジェリアにおける観光施設の現地調査報告 三重野馨; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.207-208, 2025-08 / フェルナン・プイヨンのベルカステル村修復に関する研究 ─城と村の一体性に着目して─ 古市麻菜子; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.205-206, 2025-08 / フェルナン・プイヨンのパリ郊外四地区におけるオルドナンス 吉田悠乃; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.203-204, 2025-08 / 12 世紀から17 世紀にかけてのドゥブロヴニク都市形成史 瀨古希; 松原 康介 2025年度 日本建築学会大会［九州］学術講演梗概集/pp.541-542, 2025-08 / フェス 積み重なる寄進が形成した迷宮都市 松原 康介 建築知識/2025(7)/pp.84-85, 2025-6 / ガルダイア 丘の上の城塞とオアシス渓谷の集落 松原 康介 建築知識/2025(7)/pp.82-83, 2025-6 / カミロ・ジッテの思想的変遷に関する研究 -「芸術性」から「実用性」への展開を中心に- 渡邊 智也; 松原 康介 都市計画論文集/59(3)/pp.892-899, 2024-10 / The Influence of Ibadi Architecture on Le Corbusier’s Ronchamp Chapel MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.B-1-2-1-B-1-2-4, 2024-09-10 / Political Philosophy and the Cultural Transformation of Urban Space in the Grands Projets of Paris FURUICHI Manako; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-15-6-1-D-15-6-4, 2024-09 / Multicultural Characteristics of Urban Space Development in Marseille A Case Study of the Saint-Mauront Urban Renewal Project in the 3rd Arrondissement of Marseille YOSHIDA Yuno; MATSUBARA Kosuke Proceedings of the 14th International Symposium on Architectural Interchanges in Asia (ISAIA)/pp.D-5-5-1-D-5-5-4, 2024-09 / アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 和田 夏音; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.321-322, 2024-08 / 商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08 / 19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08 / カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -8346,11 +8131,7 @@
           <t>都市計画・建築計画
 建築史・意匠
 地域研究
-建築・都市計画史
 地中海都市
-ヘレニズム基盤
-イスラーム的都市形成
-西アジア
 中東・北アフリカ
 歴史文化保全
 国際協力
@@ -8399,8 +8180,9 @@
 国際交流を背景とした中東都市計画史研究と都市保全プロジェクトへの還元
 モロッコの歴史都市 フェスの保全と近代化
 現代イスラーム都市の多元的成り立ちに関する研究
+Formation and change of an international exchange organization ATBAT: A study on the history of international and regional exchange activity of ATBAT(Atelier des Bâtisseurs), part 1 MATSUBARA Kosuke JAPAN ARCHITECTURAL REVIEW, 2026-07
 Modernist Master Planning and Resident Adaptation in Abuja, Nigeria: a Historical Geography of Imposed Spatial Order,1976-2024 AKINKUNMI Priscilla; MATSUBARA Kosuke Planning Perspectives, 2026-04
-Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review, 2026-04
+Fernand Pouillon's Symbiotic Spaces in Suburban Housing Complex in Paris—From the Perspective of Continuity with the “Three Districts of Algiers” TODA Rikako; MATSUBARA Kosuke Japan Architectural Review/9(1), 2026-04
 フェルナン・プイヨンのパリ郊外団地地区における共生空間 ―「アルジェ三地区」との連続性の視点から― 戸田 理香子; 松原 康介 日本建築学会計画系論文集/91(840)/pp.351-362, 2026-02
 吉田正春使節団が見た19世紀テヘラン都市改造 松原 康介 都市計画論文集/60(3)/pp.532-539, 2025-10
 Development of Pedestrian Spaces in Paris under Giscard d’Estaing Administration IEKI Yuki; MATSUBARA Kosuke Proceedings of the 2025 International Conference of Asia-Pacific Planning Societies/pp.713-717, 2025-08
@@ -8422,8 +8204,7 @@
 アルジェリア・ムザブの谷のオアシスにおける伝統的水利システムの形成と変容 和田 夏音; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.321-322, 2024-08
 商業都市カサブランカにおけるトラム導入による社会空間変容 三重野 馨; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.323-324, 2024-08
 19世紀後半から20世紀初頭にかけてのブリュッセル旧市街の空間変容 田村 駿介; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.325-326, 2024-08
-カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08
-カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その1 松原 康介; 渡邊 智也 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.587-588, 2024-08</t>
+カミロ・ジッテの都市計画実作に関する研究 -現チェコ共和国の諸地域を対象として-その2 渡邊 智也; 松原 康介 2024年度 日本建築学会大会［関東］学術講演梗概集/pp.589-590, 2024-08</t>
         </is>
       </c>
     </row>
@@ -8766,11 +8547,8 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-C*2
-(
-*&amp;@OK0(I102(2}
-I
-I'-V
+58@=,6,84N]Y&gt;6W?&gt;@6@-,W,.W5
+d
 都市農村計画
 緑地計画
 Memorable Places on Campuses Across Generations Janpathompong Dalin; Anantsuksomsri Sutee; MURAKAMI Ak... Journal of Architectural/Planning Research and Studies (JARS)/23(1)/pp.278-289, 2026-01
@@ -8807,7 +8585,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / C*2 / ( / *&amp;@OK0(I102(2} / I / I'-V</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 村上 暁信(ムラカミ アキノブ) / 所属 / システム情報系 / 職名 / 教授 / URL / https: / tsukubalandscapela.wixsite.com / landscape-lab / eメール / 58@=,6,84N]Y&gt;6W?&gt;@6@-,W,.W5 / d</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -8827,7 +8605,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; C*2 ; ( ; *&amp;@OK0(I102(2} ; I ; I'-V ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 村上 暁信(ムラカミ アキノブ) ; 所属 ; システム情報系 ; 職名 ; 教授 ; URL ; https: ; tsukubalandscapela.wixsite.com ; landscape-lab ; eメール ; 58@=,6,84N]Y&gt;6W?&gt;@6@-,W,.W5 ; d ; 都市・地域政策 ; GIS・空間分析 ; 社会政策・福祉 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 数理最適化・OR ; AI・データサイエンス ; 都市・空間・交通</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -8850,11 +8628,8 @@
 tsukubalandscapela.wixsite.com
 landscape-lab
 eメール
-C*2
-(
-*&amp;@OK0(I102(2}
-I
-I'-V
+58@=,6,84N]Y&gt;6W?&gt;@6@-,W,.W5
+d
 都市農村計画
 緑地計画
 都市・地域政策
@@ -9497,8 +9272,10 @@
 走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー
 土木計画学・交通工学
 交通制御・マネジメント，交通ネットワーク，交通流，高度交通システム
-Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/24/pp.250-264, 2026-04
-A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/24/pp.216-225, 2026-04
+連続体交通流理論に基づく自発光ペースメーカーライトによる渋滞対策の持続効果分析 中林 悠; 甲斐 慎一朗; 和田 健太郎; 外山 敬祐; 加藤 寛道; 石田 貴志 土木学会論文集/81(20)/p.25-20044, 2025-12
+連続体交通流理論と機械学習の融合による高速道路単路部の追従モデルパラメータ推定手法 山田 圭祐; 甲斐 慎一朗; 和田 健太郎 土木学会論文集/81(20)/p.25-20030, 2025-12
+Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks Kai Shin-ichiro; Horiguchi Ryota; Xing Jian; Wada Ken... International Journal of Intelligent Transportation Systems Research/24/pp.250-264, 2026-04
+A second order model of capacity drop at expressway lane-drop bottlenecks Hattori Fuminori; Wada Kentaro International Journal of Intelligent Transportation Systems Research/24/pp.216-225, 2026-04
 都市鉄道整備推進に向けた事業制度に関する研究 石丸 真也; 森田 泰智; 浅井 遼馬; 和田 健太郎; 日比野 直彦 運輸政策研究/28/pp.6-16, 2026-02
 Stability analysis of a departure time choice problem with atomic vehicle models Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/189/p.103039, 2024-11
 自動運転車両の速度制御を考慮した系統信号制御に関する考察 梅村 悠生; 和田 健太郎 交通工学論文集/10(1)/pp.A_10-A_17, 2024-02
@@ -9519,9 +9296,7 @@
 A new look at departure time choice equilibrium models with heterogeneous users Akamatsu Takashi; Wada Kentaro; Iryo Takamasa; Hayashi S... Transportation Research Part B: Methodological/148/pp.152-182, 2021-06
 動的交通均衡配分理論の近年の進展 和田 健太郎 土木学会論文集D3（土木計画学）/76(5)/pp.I_21-I_39, 2021-04
 Continuum car-following model of capacity drop at sag and tunnel bottlenecks Wada Kentaro; Martínez Irene; Jin Wen-Long Transportation Research Part C: Emerging Technologies/113/pp.260-276, 2020-04
-Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/132(SI)/pp.117-135, 2020-02
-Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/125/pp.229-247, 2019-05 Tsukuba Repository
-Trading mechanisms for bottleneck permits with multiple purchase opportunities Wang Pengfei; Wada Kentaro; Akamatsu Takashi; Nagae Takeshi Transportation Research Part C: Emerging Technologies/95/pp.414-430, 2018-10</t>
+Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/132(SI)/pp.117-135, 2020-02</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -9541,7 +9316,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/24/pp.250-264, 2026-04 / A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/24/pp.216-225, 2026-04 / 都市鉄道整備推進に向けた事業制度に関する研究 石丸 真也; 森田 泰智; 浅井 遼馬; 和田 健太郎; 日比野 直彦 運輸政策研究/28/pp.6-16, 2026-02 / Stability analysis of a departure time choice problem with atomic vehicle models Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/189/p.103039, 2024-11 / 自動運転車両の速度制御を考慮した系統信号制御に関する考察 梅村 悠生; 和田 健太郎 交通工学論文集/10(1)/pp.A_10-A_17, 2024-02 / 追従モデルによる高速道路サグ部のCapacity Drop現象の再現 甲斐 慎一朗; 和田 健太郎; 堀口 良太 土木学会論文集D3（土木計画学）/78(5)/pp.I_963-I_971, 2023-05 / 連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析 金﨑 圭吾; 和田 健太郎 土木学会論文集D3（土木計画学）/78(5)/pp.I_911-I_918, 2023-05 / テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル 和田 健太郎; 岩見 悠太郎 土木学会論文集D3（土木計画学）/78(5)/pp.I_899-I_909, 2023-05 / Predicting traffic breakdown in expressways using linear combination of vehicle detector data Shigemi Rikuto; Ando Hiroyasu; Wada Kentaro; Mukai Risa Nonlinear Theory and Its Applications, IEICE/14(2)/pp.416-427, 2023-04 / Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals Zhang Jiahua; Wada Kentaro; Oguchi Takashi TRANSPORTMETRICA B-TRANSPORT DYNAMICS/11(1)/pp.1256-1280, 2023-03 / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 和田 健太郎; 金﨑 圭吾; 西田 匡志; 平井 章一 交通工学論文集/9(2)/pp.A_326-A_334, 2023-02 / 連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析 甲斐 慎一朗; 和田 健太郎; 堀口 良太; 邢 健 交通工学論文集/9(2)/pp.A_280-A_287, 2023-02 / Dynamic traffic assignment in a corridor network: Optimum versus equilibrium Haoran Fu; Takashi Akamatsu; Koki Satsukawa; Kentaro Wada Transportation Research Part B: Methodological/161/pp.218-246, 2022-07 / 高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム 岸川 知樹; 和田 健太郎 土木学会論文集D3（土木計画学）/77(5)/pp.I_1109-I_1119, 2022-05 / 需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡 板橋 昂汰; 和田 健太郎 土木学会論文集D3（土木計画学）/77(5)/pp.I_1045-I_1055, 2022-05 / Fundamental diagram of urban rail transit considering train-passenger interaction Seo Toru; Wada Kentaro; Fukuda Daisuke Transportation/Epub(50)/pp.1399-1424, 2023-08 / 高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム 和田 健太郎; 邢 健; 大口 敬 交通工学論文集/8(3)/pp.1-10, 2022-04 / 高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動 和田 健太郎; 甲斐 慎一朗; 堀口 良太 交通工学論文集/8(2)/pp.A_1-A_8, 2022-02 Tsukuba Repository / Dynamic system optimal traffic assignment with atomic users: Convergence and stability Satsukawa Koki; Wada Kentaro; Watling David Transportation Research Part B: Methodological/155/pp.188-209, 2022-01 / A new look at departure time choice equilibrium models with heterogeneous users Akamatsu Takashi; Wada Kentaro; Iryo Takamasa; Hayashi S... Transportation Research Part B: Methodological/148/pp.152-182, 2021-06 / 動的交通均衡配分理論の近年の進展 和田 健太郎 土木学会論文集D3（土木計画学）/76(5)/pp.I_21-I_39, 2021-04 / Continuum car-following model of capacity drop at sag and tunnel bottlenecks Wada Kentaro; Martínez Irene; Jin Wen-Long Transportation Research Part C: Emerging Technologies/113/pp.260-276, 2020-04 / Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/132(SI)/pp.117-135, 2020-02 / Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/125/pp.229-247, 2019-05 Tsukuba Repository / Trading mechanisms for bottleneck permits with multiple purchase opportunities Wang Pengfei; Wada Kentaro; Akamatsu Takashi; Nagae Takeshi Transportation Research Part C: Emerging Technologies/95/pp.414-430, 2018-10</t>
+          <t>連続体交通流理論に基づく自発光ペースメーカーライトによる渋滞対策の持続効果分析 中林 悠; 甲斐 慎一朗; 和田 健太郎; 外山 敬祐; 加藤 寛道; 石田 貴志 土木学会論文集/81(20)/p.25-20044, 2025-12 / 連続体交通流理論と機械学習の融合による高速道路単路部の追従モデルパラメータ推定手法 山田 圭祐; 甲斐 慎一朗; 和田 健太郎 土木学会論文集/81(20)/p.25-20030, 2025-12 / Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks Kai Shin-ichiro; Horiguchi Ryota; Xing Jian; Wada Ken... International Journal of Intelligent Transportation Systems Research/24/pp.250-264, 2026-04 / A second order model of capacity drop at expressway lane-drop bottlenecks Hattori Fuminori; Wada Kentaro International Journal of Intelligent Transportation Systems Research/24/pp.216-225, 2026-04 / 都市鉄道整備推進に向けた事業制度に関する研究 石丸 真也; 森田 泰智; 浅井 遼馬; 和田 健太郎; 日比野 直彦 運輸政策研究/28/pp.6-16, 2026-02 / Stability analysis of a departure time choice problem with atomic vehicle models Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/189/p.103039, 2024-11 / 自動運転車両の速度制御を考慮した系統信号制御に関する考察 梅村 悠生; 和田 健太郎 交通工学論文集/10(1)/pp.A_10-A_17, 2024-02 / 追従モデルによる高速道路サグ部のCapacity Drop現象の再現 甲斐 慎一朗; 和田 健太郎; 堀口 良太 土木学会論文集D3（土木計画学）/78(5)/pp.I_963-I_971, 2023-05 / 連続体交通流モデルに基づく高速道路サグ・トンネル部における渋滞発生確率の解析 金﨑 圭吾; 和田 健太郎 土木学会論文集D3（土木計画学）/78(5)/pp.I_911-I_918, 2023-05 / テレワークおよび時間集積の経済・不経済を考慮した通勤均衡モデル 和田 健太郎; 岩見 悠太郎 土木学会論文集D3（土木計画学）/78(5)/pp.I_899-I_909, 2023-05 / Predicting traffic breakdown in expressways using linear combination of vehicle detector data Shigemi Rikuto; Ando Hiroyasu; Wada Kentaro; Mukai Risa Nonlinear Theory and Its Applications, IEICE/14(2)/pp.416-427, 2023-04 / Morning commute in congested urban rail transit system: a macroscopic model for equilibrium distribution of passenger arrivals Zhang Jiahua; Wada Kentaro; Oguchi Takashi TRANSPORTMETRICA B-TRANSPORT DYNAMICS/11(1)/pp.1256-1280, 2023-03 / 音声による速度回復情報提供の交通性能改善メカニズムの実証分析 和田 健太郎; 金﨑 圭吾; 西田 匡志; 平井 章一 交通工学論文集/9(2)/pp.A_326-A_334, 2023-02 / 連続体交通流理論に基づく国内複数のサグ・トンネルにおける交通容量低下の実証分析 甲斐 慎一朗; 和田 健太郎; 堀口 良太; 邢 健 交通工学論文集/9(2)/pp.A_280-A_287, 2023-02 / Dynamic traffic assignment in a corridor network: Optimum versus equilibrium Haoran Fu; Takashi Akamatsu; Koki Satsukawa; Kentaro Wada Transportation Research Part B: Methodological/161/pp.218-246, 2022-07 / 高速な連結・解結を前提とした新たな高頻度鉄道運行スキーム 岸川 知樹; 和田 健太郎 土木学会論文集D3（土木計画学）/77(5)/pp.I_1109-I_1119, 2022-05 / 需要分布を内生化したタンデムボトルネックにおける出発時刻選択均衡 板橋 昂汰; 和田 健太郎 土木学会論文集D3（土木計画学）/77(5)/pp.I_1045-I_1055, 2022-05 / Fundamental diagram of urban rail transit considering train-passenger interaction Seo Toru; Wada Kentaro; Fukuda Daisuke Transportation/Epub(50)/pp.1399-1424, 2023-08 / 高速道路サグ・トンネル部における渋滞発生後捌け交通量の低下メカニズム 和田 健太郎; 邢 健; 大口 敬 交通工学論文集/8(3)/pp.1-10, 2022-04 / 高速道路サグ・トンネル部における渋滞発生後捌け交通量を改善する走行挙動 和田 健太郎; 甲斐 慎一朗; 堀口 良太 交通工学論文集/8(2)/pp.A_1-A_8, 2022-02 Tsukuba Repository / Dynamic system optimal traffic assignment with atomic users: Convergence and stability Satsukawa Koki; Wada Kentaro; Watling David Transportation Research Part B: Methodological/155/pp.188-209, 2022-01 / A new look at departure time choice equilibrium models with heterogeneous users Akamatsu Takashi; Wada Kentaro; Iryo Takamasa; Hayashi S... Transportation Research Part B: Methodological/148/pp.152-182, 2021-06 / 動的交通均衡配分理論の近年の進展 和田 健太郎 土木学会論文集D3（土木計画学）/76(5)/pp.I_21-I_39, 2021-04 / Continuum car-following model of capacity drop at sag and tunnel bottlenecks Wada Kentaro; Martínez Irene; Jin Wen-Long Transportation Research Part C: Emerging Technologies/113/pp.260-276, 2020-04 / Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/132(SI)/pp.117-135, 2020-02</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -9609,8 +9384,10 @@
 バイオミメティックスに学ぶスマートな都市退化マネジメント
 AI計算リソースとしての実交通ダイナミクスの活用技術の開発
 走行税課金による道路インフラ維持管理ーEV化と車両認証のデジタル時代を迎えてー
-Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks KAI Shin-ichiro; HORIGUCHI Ryota; XING Jian; WADA Ken... International Journal of Intelligent Transportation Systems Research/24/pp.250-264, 2026-04
-A second order model of capacity drop at expressway lane-drop bottlenecks HATTORI Fuminori; WADA Kentaro International Journal of Intelligent Transportation Systems Research/24/pp.216-225, 2026-04
+連続体交通流理論に基づく自発光ペースメーカーライトによる渋滞対策の持続効果分析 中林 悠; 甲斐 慎一朗; 和田 健太郎; 外山 敬祐; 加藤 寛道; 石田 貴志 土木学会論文集/81(20)/p.25-20044, 2025-12
+連続体交通流理論と機械学習の融合による高速道路単路部の追従モデルパラメータ推定手法 山田 圭祐; 甲斐 慎一朗; 和田 健太郎 土木学会論文集/81(20)/p.25-20030, 2025-12
+Empirical validation of continuum traffic flow model of capacity drop at sag and tunnel bottlenecks Kai Shin-ichiro; Horiguchi Ryota; Xing Jian; Wada Ken... International Journal of Intelligent Transportation Systems Research/24/pp.250-264, 2026-04
+A second order model of capacity drop at expressway lane-drop bottlenecks Hattori Fuminori; Wada Kentaro International Journal of Intelligent Transportation Systems Research/24/pp.216-225, 2026-04
 都市鉄道整備推進に向けた事業制度に関する研究 石丸 真也; 森田 泰智; 浅井 遼馬; 和田 健太郎; 日比野 直彦 運輸政策研究/28/pp.6-16, 2026-02
 Stability analysis of a departure time choice problem with atomic vehicle models Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/189/p.103039, 2024-11
 自動運転車両の速度制御を考慮した系統信号制御に関する考察 梅村 悠生; 和田 健太郎 交通工学論文集/10(1)/pp.A_10-A_17, 2024-02
@@ -9631,9 +9408,7 @@
 A new look at departure time choice equilibrium models with heterogeneous users Akamatsu Takashi; Wada Kentaro; Iryo Takamasa; Hayashi S... Transportation Research Part B: Methodological/148/pp.152-182, 2021-06
 動的交通均衡配分理論の近年の進展 和田 健太郎 土木学会論文集D3（土木計画学）/76(5)/pp.I_21-I_39, 2021-04
 Continuum car-following model of capacity drop at sag and tunnel bottlenecks Wada Kentaro; Martínez Irene; Jin Wen-Long Transportation Research Part C: Emerging Technologies/113/pp.260-276, 2020-04
-Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/132(SI)/pp.117-135, 2020-02
-Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/125/pp.229-247, 2019-05 Tsukuba Repository
-Trading mechanisms for bottleneck permits with multiple purchase opportunities Wang Pengfei; Wada Kentaro; Akamatsu Takashi; Nagae Takeshi Transportation Research Part C: Emerging Technologies/95/pp.414-430, 2018-10</t>
+Reprint of "Stochastic stability of dynamic user equilibrium in unidirectional networks: Weakly acyclic game approach" Satsukawa Koki; Wada Kentaro; Iryo Takamasa Transportation Research Part B: Methodological/132(SI)/pp.117-135, 2020-02</t>
         </is>
       </c>
     </row>
@@ -9849,213 +9624,23 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ok_researchmap_fallback</t>
+          <t>jglobal_not_found</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>researchmap</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>大分類
-指定なし --
-ライフサイエンス
-情報通信
-環境・農学
-ナノテク・材料
-エネルギー
-ものづくり技術（機械・電気電子・化学工学）
-社会基盤（土木・建築・防災）
-フロンティア（航空・船舶）
-人文・社会
-自然科学一般
-その他
-小分類
-機関タイプ
-国立研究機関
-独立行政法人・国立研究開発法人等
-大学共同利用機関法人
-公設試験研究機関
-学校機関
-公益法人等
-企業研究施設
-その他機関
-研究者番号
-エリア
-すべて
-北海道
-東北
-関東
-中部
-近畿
-中国
-四国
-九州・沖縄
-青森県
-岩手県
-宮城県
-秋田県
-山形県
-福島県
-茨城県
-栃木県
-群馬県
-埼玉県
-千葉県
-東京都
-神奈川県
-新潟県
-富山県
-石川県
-福井県
-山梨県
-長野県
-岐阜県
-静岡県
-愛知県
-三重県
-滋賀県
-京都府
-大阪府
-兵庫県
-奈良県
-和歌山県
-鳥取県
-島根県
-岡山県
-広島県
-山口県
-徳島県
-香川県
-愛媛県
-高知県
-福岡県
-佐賀県
-長崎県
-熊本県
-大分県
-宮崎県
-鹿児島県
-沖縄県
-最終更新日
-1週間以内
-2週間以内
-1ヶ月以内
-2ヶ月以内
-3ヶ月以内
-検索
-2017 researchmap</t>
-        </is>
-      </c>
+          <t>jglobal</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>大分類 / 指定なし -- / ライフサイエンス / 情報通信 / 環境・農学 / ナノテク・材料 / エネルギー / ものづくり技術（機械・電気電子・化学工学） / 社会基盤（土木・建築・防災） / フロンティア（航空・船舶） / 人文・社会 / 自然科学一般 / その他 / 小分類 / 機関タイプ / 国立研究機関 / 独立行政法人・国立研究開発法人等 / 大学共同利用機関法人 / 公設試験研究機関 / 学校機関 / 公益法人等 / 企業研究施設 / その他機関 / 研究者番号 / エリア / すべて / 北海道 / 東北 / 関東 / 中部 / 近畿 / 中国 / 四国 / 九州・沖縄 / 青森県 / 岩手県 / 宮城県 / 秋田県 / 山形県 / 福島県 / 茨城県 / 栃木県 / 群馬県 / 埼玉県 / 千葉県 / 東京都 / 神奈川県 / 新潟県 / 富山県 / 石川県 / 福井県 / 山梨県 / 長野県 / 岐阜県 / 静岡県 / 愛知県 / 三重県 / 滋賀県 / 京都府 / 大阪府 / 兵庫県 / 奈良県 / 和歌山県 / 鳥取県 / 島根県 / 岡山県 / 広島県 / 山口県 / 徳島県 / 香川県 / 愛媛県 / 高知県 / 福岡県 / 佐賀県 / 長崎県 / 熊本県 / 大分県 / 宮崎県 / 鹿児島県 / 沖縄県 / 最終更新日 / 1週間以内 / 2週間以内 / 1ヶ月以内 / 2ヶ月以内 / 3ヶ月以内 / 検索 / 2017 researchmap</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>大分類 ; 指定なし -- ; ライフサイエンス ; 情報通信 ; 環境・農学 ; ナノテク・材料 ; エネルギー ; ものづくり技術（機械・電気電子・化学工学） ; 社会基盤（土木・建築・防災） ; フロンティア（航空・船舶） ; 人文・社会 ; 自然科学一般 ; その他 ; 小分類 ; 機関タイプ ; 国立研究機関 ; 独立行政法人・国立研究開発法人等 ; 大学共同利用機関法人 ; 公設試験研究機関 ; 学校機関 ; 公益法人等 ; 企業研究施設 ; その他機関 ; 研究者番号 ; エリア ; すべて ; 北海道 ; 東北 ; 関東 ; 中部 ; 近畿 ; 中国 ; 四国 ; 九州・沖縄 ; 青森県 ; 岩手県 ; 宮城県 ; 秋田県 ; 山形県 ; 福島県 ; 茨城県 ; 栃木県 ; 群馬県 ; 埼玉県 ; 千葉県 ; 東京都 ; 神奈川県 ; 新潟県 ; 富山県 ; 石川県 ; 福井県 ; 山梨県 ; 長野県 ; 岐阜県 ; 静岡県 ; 愛知県 ; 三重県 ; 滋賀県 ; 京都府 ; 大阪府 ; 兵庫県 ; 奈良県 ; 和歌山県 ; 鳥取県 ; 島根県 ; 岡山県 ; 広島県 ; 山口県 ; 徳島県 ; 香川県 ; 愛媛県 ; 高知県 ; 福岡県 ; 佐賀県 ; 長崎県 ; 熊本県 ; 大分県 ; 宮崎県 ; 鹿児島県 ; 沖縄県 ; 最終更新日 ; 1週間以内 ; 2週間以内 ; 1ヶ月以内 ; 2ヶ月以内 ; 3ヶ月以内 ; 検索 ; 2017 researchmap</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>大分類
-指定なし --
-ライフサイエンス
-情報通信
-環境・農学
-ナノテク・材料
-エネルギー
-ものづくり技術（機械・電気電子・化学工学）
-社会基盤（土木・建築・防災）
-フロンティア（航空・船舶）
-人文・社会
-自然科学一般
-その他
-小分類
-機関タイプ
-国立研究機関
-独立行政法人・国立研究開発法人等
-大学共同利用機関法人
-公設試験研究機関
-学校機関
-公益法人等
-企業研究施設
-その他機関
-研究者番号
-エリア
-すべて
-北海道
-東北
-関東
-中部
-近畿
-中国
-四国
-九州・沖縄
-青森県
-岩手県
-宮城県
-秋田県
-山形県
-福島県
-茨城県
-栃木県
-群馬県
-埼玉県
-千葉県
-東京都
-神奈川県
-新潟県
-富山県
-石川県
-福井県
-山梨県
-長野県
-岐阜県
-静岡県
-愛知県
-三重県
-滋賀県
-京都府
-大阪府
-兵庫県
-奈良県
-和歌山県
-鳥取県
-島根県
-岡山県
-広島県
-山口県
-徳島県
-香川県
-愛媛県
-高知県
-福岡県
-佐賀県
-長崎県
-熊本県
-大分県
-宮崎県
-鹿児島県
-沖縄県
-最終更新日
-1週間以内
-2週間以内
-1ヶ月以内
-2ヶ月以内
-3ヶ月以内
-検索
-2017 researchmap</t>
-        </is>
-      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -10074,14 +9659,10 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=200901029857148130</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ok_jglobal_fallback</t>
+          <t>jglobal_not_found</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10089,110 +9670,19 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
-超混雑環境における群集ナビゲーションに関する研究
-救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
-大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
-データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
-救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
-仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
-障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
-認知科学
-, 知能ロボティクス
-, 知覚情報処理
-, 知能情報学
-, ヒューマンインタフェース
-インタラクション
-, データベース
-知能ロボット
-, 映像処理
-Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
-Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
-一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
-Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
-Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究 / 超混雑環境における群集ナビゲーションに関する研究 / 救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上 / 大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成 / データ同化手法を用いた身体障害者の共創的衣服作製に関する研究 / 救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究 / 仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究 / 障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>認知科学 / , 知能ロボティクス / , 知覚情報処理 / , 知能情報学 / , ヒューマンインタフェース / インタラクション / , データベース</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>知能ロボット / , 映像処理</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718 / Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600 / 一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235 / Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376 / Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化 / グラフニューラルネットワークを用いた高精度な人流シミュレーションモデルの構築 / 中断時系列デザインを用いた人流抑制の効果推定 / 実世界への応用のためのNeural Architecture Searchの多目的最適化 / 大規模イベントにおける歩行者モデルの拡張と群集制御最適化 / 多目的最適化による地下動線を活用した避難誘導効果の検証 / 実時間で動作する音響イベント検出の大規模事前学習 / 超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>認知科学 ; , 知能ロボティクス ; , 知覚情報処理 ; , 知能情報学 ; , ヒューマンインタフェース ; インタラクション ; , データベース ; GIS・空間分析 ; 建築・空間設計 ; スポーツデータ分析 ; 政策評価・計量分析 ; 医療・ヘルスデータ ; 環境・エネルギー ; AI・データサイエンス</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>認知科学
-, 知能ロボティクス
-, 知覚情報処理
-, 知能情報学
-, ヒューマンインタフェース
-インタラクション
-, データベース
-知能ロボット
-, 映像処理
-GIS・空間分析
-建築・空間設計
-スポーツデータ分析
-政策評価・計量分析
-医療・ヘルスデータ
-環境・エネルギー
-AI・データサイエンス
-GIS
-空間計量
-地理情報分析
-立地分析
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-スポーツアナリティクス
-戦術分析
-パフォーマンス分析
-政策評価
-計量経済学
-統計的因果推論
-実証分析
-医療データ分析
-生体情報解析
-ヘルスデータサイエンス
-統計解析
-環境政策
-エネルギーシステム
-脱炭素分析
-持続可能性評価</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>歩行者シミュレーションを用いた群集誘導のmulti-fidelity最適化
@@ -10202,20 +9692,7 @@
 大規模イベントにおける歩行者モデルの拡張と群集制御最適化
 多目的最適化による地下動線を活用した避難誘導効果の検証
 実時間で動作する音響イベント検出の大規模事前学習
-超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案
-超混雑環境における群集移動モデルの構築と安全なナビゲーションに関する研究
-超混雑環境における群集ナビゲーションに関する研究
-救急医療現場での動線分析と会話分析の融合によるチーム医療の評価と教育効果の向上
-大規模空間における避難訓練の科学的解析に基づく屋内避難経路ピクトグラムの作成
-データ同化手法を用いた身体障害者の共創的衣服作製に関する研究
-救急初期診療の可視化に基づいたチーム医療のシミュレーション教育システムの研究
-仮想空間の情報が実空間の人の流れに伝播する様子のモデル化と分析に関する研究
-障害者の座位姿勢における衣服作製のための3次元計測とバーチャル着装の研究
-Yuta Irisawa, Tomoaki Yamazaki, Seiya Ito, Shuhei Kurita, Ryota Akasaka, Masaki Onishi, Kouzou Ohara, Ken Sakurada. Low-Latency Privacy-Aware Robot Behavior guided by Automatically Generated Text Datasets. IROS. 2025. 17711-17718
-Qiong Chang, Aolong Zha, Weimin Wang 0007, Xin Liu 0020, Masaki Onishi, Tsutomu Maruyama. Z2-ZNCC: ZigZag Scanning based Zero-means Normalized Cross Correlation for Fast and Accurate Stereo Matching on Embedded GPU. 38th IEEE International Conference on Computer Design(ICCD). 2020. 597-600
-一刈 良介, 三浦 貴大, 尾形 邦裕, 大西 正輝, 蔵田 武志. 車いす利用者向けバーチャル着装アプリの社会実装に向けた検証~パラリンピックアスリートのユニフォーム製作への活用とアンケート調査を通して~. 日本バーチャルリアリティ学会論文誌. 2020. 25. 3. 232-235
-Qiong Chang, Aolong Zha, Onishi Masaki, Tsutomu Maruyama. A GPU accelerator for domain transformation-based stereo matching. ACM International Conference Proceeding Series. 2019. 370-376
-Qiong Chang, Masaki Onishi, Tsutomu Maruyama. Fast convolution Kernels on Pascal GPU with high memory efficiency. Simulation Series. 2018. 50. 4. 24-35</t>
+超低遅延なLiDAR3次元物体検出のためのネットワークアーキテクチャの提案</t>
         </is>
       </c>
     </row>
@@ -10235,14 +9712,10 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=200901023079327687</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ok_jglobal_fallback</t>
+          <t>jglobal_not_found</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10250,143 +9723,16 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>環境とヒトの相互構築史:汎太平洋の比較研究による文理統合的研究(人間と環境班)
-脆弱な世界を生きる-ポリネシア極リモート環礁における環境機能分化と環境限界の研究
-グローバル経済の成長に潜む資源利用の不平等・格差の計測と可視化
-人新世の新しいサンゴ礁保全:浅場-深場間の鉛直群集構造、機能と将来予測
-オセアニア環礁社会を支えるタロイモ栽培の天水田景観と気象災害のジオアーケオロジー
-資源消費が誘発する地球改変量:影響の原因者である消費国が果たすべき役割
-温帯性サンゴ骨格から検証する日本周辺の地球環境変動
-世界の231の国・地域を対象とした国際貿易に伴う金属資源の移動量と需給構造の解析
-サンゴ礁学-人と生態系の共生・共存のための未来戦略-
-ストレスとサンゴ礁の歴史的変化
-小笠原諸島における十脚目甲殻類のインベントリ作成および保全に関する基礎的研究
-熱帯海草藻場における堆積物撹乱の影響評価:津波と局所的環境変動の複合効果
-モーリシャスサンゴ礁の白化の特異性:ミクロ生態系と物質循環の調査
-環境と生態系の時空間変動、特にサンゴ礁の環境史・モニタリング・将来予測
-Remote Sensing of Environments
-環境動態解析
-, 地理学
-サンゴ礁
-, 自然地理
-, リモートセンシング
-, Grassland
-, Coral Reef
-, Physical Geography
-, Remote Sensing
-Akihiko Nonaka, Yoshimitsu Tajima, Tatsuhito Kono, Hiroya Yamano, Tomonori Orita, Hajime Kayanne. Nature-based Solutions (NbS) for Sustainable Coastal Communities in the Pacific Island Countries and Territories. Sustainable Development Across Pacific Islands. 2024. 227-253
-Hajime Kayanne, Takeshi Hara, Nobuaki Arai, Hiroya Yamano, Hiroyuki Matsuda. Trajectory to local extinction of an isolated dugong population near Okinawa Island, Japan. SCIENTIFIC REPORTS. 2022. 12. 1
-Asahi Sakuma, Hiroya Abe, Hiroya Yamano. Short-term sediment plume event in the coral reef area of a small island captured by the Planet Dove satellite constellation. Remote Sensing Letters. 2021. 12. 10. 1038-1048
-Hiroya Abe, Naoki H. Kumagai, Hiroya Yamano, Yosuke Kuramoto. Coupling high-resolution coral bleaching modeling with management practices to identify areas for conservation in a warming climate: Keramashoto National Park (Okinawa Prefecture, Japan). SCIENCE OF THE TOTAL ENVIRONMENT. 2021. 790
-Hiroya Abe, Haruka Suzuki, Yuko F. Kitano, Naoki H. Kumagai, Satomi Mitsui, Hiroya Yamano. Climate-induced species range shift and local adaptation strategies in a temperate marine protected area, Ashizuri-Uwakai National Park, Shikoku Island, western Japan. OCEAN &amp; COASTAL MANAGEMENT. 2021. 210</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>環境とヒトの相互構築史:汎太平洋の比較研究による文理統合的研究(人間と環境班) / 脆弱な世界を生きる-ポリネシア極リモート環礁における環境機能分化と環境限界の研究 / グローバル経済の成長に潜む資源利用の不平等・格差の計測と可視化 / 人新世の新しいサンゴ礁保全:浅場-深場間の鉛直群集構造、機能と将来予測 / オセアニア環礁社会を支えるタロイモ栽培の天水田景観と気象災害のジオアーケオロジー / 資源消費が誘発する地球改変量:影響の原因者である消費国が果たすべき役割 / 温帯性サンゴ骨格から検証する日本周辺の地球環境変動 / 世界の231の国・地域を対象とした国際貿易に伴う金属資源の移動量と需給構造の解析 / サンゴ礁学-人と生態系の共生・共存のための未来戦略- / ストレスとサンゴ礁の歴史的変化 / 小笠原諸島における十脚目甲殻類のインベントリ作成および保全に関する基礎的研究 / 熱帯海草藻場における堆積物撹乱の影響評価:津波と局所的環境変動の複合効果 / モーリシャスサンゴ礁の白化の特異性:ミクロ生態系と物質循環の調査 / 環境と生態系の時空間変動、特にサンゴ礁の環境史・モニタリング・将来予測 / Remote Sensing of Environments</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>環境動態解析 / , 地理学</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>サンゴ礁 / , 自然地理 / , リモートセンシング / , Grassland / , Coral Reef / , Physical Geography / , Remote Sensing</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Akihiko Nonaka, Yoshimitsu Tajima, Tatsuhito Kono, Hiroya Yamano, Tomonori Orita, Hajime Kayanne. Nature-based Solutions (NbS) for Sustainable Coastal Communities in the Pacific Island Countries and Territories. Sustainable Development Across Pacific Islands. 2024. 227-253 / Hajime Kayanne, Takeshi Hara, Nobuaki Arai, Hiroya Yamano, Hiroyuki Matsuda. Trajectory to local extinction of an isolated dugong population near Okinawa Island, Japan. SCIENTIFIC REPORTS. 2022. 12. 1 / Asahi Sakuma, Hiroya Abe, Hiroya Yamano. Short-term sediment plume event in the coral reef area of a small island captured by the Planet Dove satellite constellation. Remote Sensing Letters. 2021. 12. 10. 1038-1048 / Hiroya Abe, Naoki H. Kumagai, Hiroya Yamano, Yosuke Kuramoto. Coupling high-resolution coral bleaching modeling with management practices to identify areas for conservation in a warming climate: Keramashoto National Park (Okinawa Prefecture, Japan). SCIENCE OF THE TOTAL ENVIRONMENT. 2021. 790 / Hiroya Abe, Haruka Suzuki, Yuko F. Kitano, Naoki H. Kumagai, Satomi Mitsui, Hiroya Yamano. Climate-induced species range shift and local adaptation strategies in a temperate marine protected area, Ashizuri-Uwakai National Park, Shikoku Island, western Japan. OCEAN &amp; COASTAL MANAGEMENT. 2021. 210</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>環境動態解析 ; , 地理学 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計 ; 画像・視覚情報処理 ; 災害・防災研究 ; 政策評価・計量分析 ; 環境・エネルギー ; 公共政策・社会工学 ; 経済・ファイナンス</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>環境動態解析
-, 地理学
-サンゴ礁
-, 自然地理
-, リモートセンシング
-, Grassland
-, Coral Reef
-, Physical Geography
-, Remote Sensing
-都市・地域政策
-GIS・空間分析
-建築・空間設計
-画像・視覚情報処理
-災害・防災研究
-政策評価・計量分析
-環境・エネルギー
-公共政策・社会工学
-経済・ファイナンス
-都市経済
-地域政策
-土地利用
-公共政策評価
-GIS
-空間計量
-地理情報分析
-立地分析
-建築計画
-空間レイアウト生成
-居住空間設計
-都市空間デザイン
-コンピュータビジョン
-画像認識
-行動認識
-マルチモーダル解析
-災害社会学
-防災政策
-リスク評価
-政策評価
-計量経済学
-統計的因果推論
-実証分析
-環境政策
-エネルギーシステム
-脱炭素分析
-持続可能性評価</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>環境とヒトの相互構築史:汎太平洋の比較研究による文理統合的研究(人間と環境班)
-脆弱な世界を生きる-ポリネシア極リモート環礁における環境機能分化と環境限界の研究
-グローバル経済の成長に潜む資源利用の不平等・格差の計測と可視化
-人新世の新しいサンゴ礁保全:浅場-深場間の鉛直群集構造、機能と将来予測
-オセアニア環礁社会を支えるタロイモ栽培の天水田景観と気象災害のジオアーケオロジー
-資源消費が誘発する地球改変量:影響の原因者である消費国が果たすべき役割
-温帯性サンゴ骨格から検証する日本周辺の地球環境変動
-世界の231の国・地域を対象とした国際貿易に伴う金属資源の移動量と需給構造の解析
-サンゴ礁学-人と生態系の共生・共存のための未来戦略-
-ストレスとサンゴ礁の歴史的変化
-小笠原諸島における十脚目甲殻類のインベントリ作成および保全に関する基礎的研究
-熱帯海草藻場における堆積物撹乱の影響評価:津波と局所的環境変動の複合効果
-モーリシャスサンゴ礁の白化の特異性:ミクロ生態系と物質循環の調査
-環境と生態系の時空間変動、特にサンゴ礁の環境史・モニタリング・将来予測
-Remote Sensing of Environments
-Akihiko Nonaka, Yoshimitsu Tajima, Tatsuhito Kono, Hiroya Yamano, Tomonori Orita, Hajime Kayanne. Nature-based Solutions (NbS) for Sustainable Coastal Communities in the Pacific Island Countries and Territories. Sustainable Development Across Pacific Islands. 2024. 227-253
-Hajime Kayanne, Takeshi Hara, Nobuaki Arai, Hiroya Yamano, Hiroyuki Matsuda. Trajectory to local extinction of an isolated dugong population near Okinawa Island, Japan. SCIENTIFIC REPORTS. 2022. 12. 1
-Asahi Sakuma, Hiroya Abe, Hiroya Yamano. Short-term sediment plume event in the coral reef area of a small island captured by the Planet Dove satellite constellation. Remote Sensing Letters. 2021. 12. 10. 1038-1048
-Hiroya Abe, Naoki H. Kumagai, Hiroya Yamano, Yosuke Kuramoto. Coupling high-resolution coral bleaching modeling with management practices to identify areas for conservation in a warming climate: Keramashoto National Park (Okinawa Prefecture, Japan). SCIENCE OF THE TOTAL ENVIRONMENT. 2021. 790
-Hiroya Abe, Haruka Suzuki, Yuko F. Kitano, Naoki H. Kumagai, Satomi Mitsui, Hiroya Yamano. Climate-induced species range shift and local adaptation strategies in a temperate marine protected area, Ashizuri-Uwakai National Park, Shikoku Island, western Japan. OCEAN &amp; COASTAL MANAGEMENT. 2021. 210</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10727,29 +10073,29 @@
 犯罪科学
 空間情報科学
 環境心理学
+Plural policing in rural contexts: a GPS-based evaluation of multi-entity patrols against fruit theft AMEMIYA Mamoru; SUZUMI Ai; SHIMADA Takahito; KURITA H... Security Journal/39, 2026-05
+公園を「負動産」にしないために：茨城県笠間市の挑戦 雨宮 護 日造協ニュース/(626)/pp.2-2, 2026-05
+共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
-共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06
 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06
 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 雨宮 護; 鈴木 あい; 田村 孝浩; 御田 成顕; 島田 貴仁; 栗田 英治 2025年度農村計画学会全国大会学術研究発表会企画セッション梗概集/pp.70-71, 2025-11-29
-Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09
 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して 井上 皓介; 雨宮 護; 大山 智也; 中野 裕貴 都市計画論文集/60(3)/pp.1604-1611, 2025-10
 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 高橋 南織; 雨宮 護 都市計画論文集/60(3)/pp.650-656, 2025-10
 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10
 人口低密度地域における人々の活動から見た「都市の活力」の計測 米田 有希; 雨宮 護; 森山 拓洋 都市計画論文集/60(3)/pp.1658-1665, 2025-10
+Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09
 全国のJAを対象とする果物盗被害に関するアンケート調査報告 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 都市計画報告集/24(2)/pp.318-321, 2025-09
 Regional variations in key factors of children's independent mobility across Japan HINO Kimihiro; AMEMIYA Mamoru; YOSHIKI Syuji; ZHENG Erli Journal of Transport &amp; Health/44, 2025-09
 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 佐光 未帆; 雨宮 護 環境心理学研究/13(1)/pp.48-48, 2025-05-28
 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 李 超群; 雨宮 護 環境心理学研究/13(1)/pp.44-44, 2025-05-28
 Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives SUZUKI Ai; AMEMIYA Mamoru; KURITA Hideharu; SHIMADA T... International Journal of Rural Criminology/9(1)/pp.77-104, 2025-04
-Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05
 Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits Zheng Xinrui; Amemiya Mamoru TRANSACTIONS IN GIS/29(1), 2025-02
-Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya Ohyama 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12
+Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya ... 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12
 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 市川 はるひ; 雨宮 護 IPA日本支部研究集会発表要旨集/pp.４-4, 2024-12
 GPSロガーを用いた官民による果樹盗パトロールの計測 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 Research Abstracts on Spatial Information Science CSIS DAYS 2024/D13, 2024-11-15
-子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10
-時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10
+Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05
 Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10
 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
         </is>
@@ -10771,7 +10117,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17 / 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06 / 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06 / 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 雨宮 護; 鈴木 あい; 田村 孝浩; 御田 成顕; 島田 貴仁; 栗田 英治 2025年度農村計画学会全国大会学術研究発表会企画セッション梗概集/pp.70-71, 2025-11-29 / Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09 / 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して 井上 皓介; 雨宮 護; 大山 智也; 中野 裕貴 都市計画論文集/60(3)/pp.1604-1611, 2025-10 / 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 高橋 南織; 雨宮 護 都市計画論文集/60(3)/pp.650-656, 2025-10 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10 / 人口低密度地域における人々の活動から見た「都市の活力」の計測 米田 有希; 雨宮 護; 森山 拓洋 都市計画論文集/60(3)/pp.1658-1665, 2025-10 / 全国のJAを対象とする果物盗被害に関するアンケート調査報告 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 都市計画報告集/24(2)/pp.318-321, 2025-09 / Regional variations in key factors of children's independent mobility across Japan HINO Kimihiro; AMEMIYA Mamoru; YOSHIKI Syuji; ZHENG Erli Journal of Transport &amp; Health/44, 2025-09 / 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 佐光 未帆; 雨宮 護 環境心理学研究/13(1)/pp.48-48, 2025-05-28 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 李 超群; 雨宮 護 環境心理学研究/13(1)/pp.44-44, 2025-05-28 / Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives SUZUKI Ai; AMEMIYA Mamoru; KURITA Hideharu; SHIMADA T... International Journal of Rural Criminology/9(1)/pp.77-104, 2025-04 / Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05 / Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits Zheng Xinrui; Amemiya Mamoru TRANSACTIONS IN GIS/29(1), 2025-02 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya Ohyama 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12 / 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 市川 はるひ; 雨宮 護 IPA日本支部研究集会発表要旨集/pp.４-4, 2024-12 / GPSロガーを用いた官民による果樹盗パトロールの計測 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 Research Abstracts on Spatial Information Science CSIS DAYS 2024/D13, 2024-11-15 / 子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10 / 時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10 / Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10 / 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
+          <t>Plural policing in rural contexts: a GPS-based evaluation of multi-entity patrols against fruit theft AMEMIYA Mamoru; SUZUMI Ai; SHIMADA Takahito; KURITA H... Security Journal/39, 2026-05 / 公園を「負動産」にしないために：茨城県笠間市の挑戦 雨宮 護 日造協ニュース/(626)/pp.2-2, 2026-05 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17 / 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06 / 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06 / 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 雨宮 護; 鈴木 あい; 田村 孝浩; 御田 成顕; 島田 貴仁; 栗田 英治 2025年度農村計画学会全国大会学術研究発表会企画セッション梗概集/pp.70-71, 2025-11-29 / 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して 井上 皓介; 雨宮 護; 大山 智也; 中野 裕貴 都市計画論文集/60(3)/pp.1604-1611, 2025-10 / 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 高橋 南織; 雨宮 護 都市計画論文集/60(3)/pp.650-656, 2025-10 / 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10 / 人口低密度地域における人々の活動から見た「都市の活力」の計測 米田 有希; 雨宮 護; 森山 拓洋 都市計画論文集/60(3)/pp.1658-1665, 2025-10 / Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09 / 全国のJAを対象とする果物盗被害に関するアンケート調査報告 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 都市計画報告集/24(2)/pp.318-321, 2025-09 / Regional variations in key factors of children's independent mobility across Japan HINO Kimihiro; AMEMIYA Mamoru; YOSHIKI Syuji; ZHENG Erli Journal of Transport &amp; Health/44, 2025-09 / 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 佐光 未帆; 雨宮 護 環境心理学研究/13(1)/pp.48-48, 2025-05-28 / 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 李 超群; 雨宮 護 環境心理学研究/13(1)/pp.44-44, 2025-05-28 / Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives SUZUKI Ai; AMEMIYA Mamoru; KURITA Hideharu; SHIMADA T... International Journal of Rural Criminology/9(1)/pp.77-104, 2025-04 / Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits Zheng Xinrui; Amemiya Mamoru TRANSACTIONS IN GIS/29(1), 2025-02 / Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya ... 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12 / 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 市川 はるひ; 雨宮 護 IPA日本支部研究集会発表要旨集/pp.４-4, 2024-12 / GPSロガーを用いた官民による果樹盗パトロールの計測 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 Research Abstracts on Spatial Information Science CSIS DAYS 2024/D13, 2024-11-15 / Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05 / Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10 / 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -10867,29 +10213,29 @@
 空間移動・輸送ルート設計の最適戦略に関する理論・応用研究
 集合住宅における子ども・女性に対する犯罪の実態分析と対策立案
 地理的犯罪予測の手法構築‐学際研究と産官学連携による学術基盤の確立とシステム開発
+Plural policing in rural contexts: a GPS-based evaluation of multi-entity patrols against fruit theft AMEMIYA Mamoru; SUZUMI Ai; SHIMADA Takahito; KURITA H... Security Journal/39, 2026-05
+公園を「負動産」にしないために：茨城県笠間市の挑戦 雨宮 護 日造協ニュース/(626)/pp.2-2, 2026-05
+共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
-共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03
 冒険遊び場における犯罪被害と防犯対策の実態に関する研究：自由な遊びと防犯性の両立に向けて 市川 はるひ; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.64-65, 2025-12-06
 都市公園における逸脱行為に関する縦断的研究 宮村 悠太; 寺田 徹; 雨宮 護 日本造園学会関東支部大会梗概集/事例研究報告集/(43)/pp.22-23, 2025-12-06
 日本における「農村犯罪学」の可能性：農山村地域における犯罪と対策の実態報告 雨宮 護; 鈴木 あい; 田村 孝浩; 御田 成顕; 島田 貴仁; 栗田 英治 2025年度農村計画学会全国大会学術研究発表会企画セッション梗概集/pp.70-71, 2025-11-29
-Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09
 夜間帰宅時の「ラストワンマイル」における男女差の実態解明：歩行ルートの移動特性と都市的要素に着目して 井上 皓介; 雨宮 護; 大山 智也; 中野 裕貴 都市計画論文集/60(3)/pp.1604-1611, 2025-10
 街歩きガイドツアー中の写真撮影行動が参加者のシーン記憶・エピソード記憶に及ぼす影響 高橋 南織; 雨宮 護 都市計画論文集/60(3)/pp.650-656, 2025-10
 高齢者を対象とする電動アシスト自転車購入費補助事業の効果検証：茨城県つくば市の補助事業を事例として 尾藤 皓太朗; 雨宮 護; 澤田 学; 松尾 智美; 藤井 さやか 都市計画論文集/60(3)/pp.1551-1558, 2025-10
 人口低密度地域における人々の活動から見た「都市の活力」の計測 米田 有希; 雨宮 護; 森山 拓洋 都市計画論文集/60(3)/pp.1658-1665, 2025-10
+Mechanisms contributing to road network growth in volunteered street view imagery data ZHENG Xinrui; AMEMIYA Mamoru The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences/XLVIII-4(W16)/pp.143-148, 2025-09
 全国のJAを対象とする果物盗被害に関するアンケート調査報告 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 都市計画報告集/24(2)/pp.318-321, 2025-09
 Regional variations in key factors of children's independent mobility across Japan HINO Kimihiro; AMEMIYA Mamoru; YOSHIKI Syuji; ZHENG Erli Journal of Transport &amp; Health/44, 2025-09
 大学敷地内における学生の被害実態と報告行動の現状：インタビュー調査を通じた分析 佐光 未帆; 雨宮 護 環境心理学研究/13(1)/pp.48-48, 2025-05-28
 留学生の帯同家族におけるソーシャル・サポートの実態に関する研究 李 超群; 雨宮 護 環境心理学研究/13(1)/pp.44-44, 2025-05-28
 Investigating Agricultural Theft in Japan: A Qualitative Study of Japan Agricultural Cooperatives SUZUKI Ai; AMEMIYA Mamoru; KURITA Hideharu; SHIMADA T... International Journal of Rural Criminology/9(1)/pp.77-104, 2025-04
-Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05
 Does Linus' Law Apply to Data Quality in Volunteered Street View Imagery (VSVI)? Mechanisms Contributing to VSVI Data Quality Improvement for Environmental Audits Zheng Xinrui; Amemiya Mamoru TRANSACTIONS IN GIS/29(1), 2025-02
-Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya Ohyama 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12
+Downscaling of Crime Counts from City Level into Neighborhood Level Based on Machine Learning Chen Zhang; Mamoru Amemiya; Daisuke Murakami; Tomoya ... 「都市のOR」ワークショップ2024アブストラクト集/pp.17-17, 2024-12
 運営者・プレイリーダーへのインタビューに基づく冒険遊び場における犯罪被害の事例調査 市川 はるひ; 雨宮 護 IPA日本支部研究集会発表要旨集/pp.４-4, 2024-12
 GPSロガーを用いた官民による果樹盗パトロールの計測 雨宮 護; 鈴木 あい; 島田 貴仁; 栗田 英治 Research Abstracts on Spatial Information Science CSIS DAYS 2024/D13, 2024-11-15
-子供の前兆事案被害情報の主体間共有の実態 今井 巧; 雨宮 護; 島田 貴仁; 樋野 公宏; 柴田 久 都市計画論文集/59(3)/pp.1549-1556, 2024-10
-時空間データにみる新たな地域防犯活動としての「ながら見守り」の特性 香嶋 愛美; 雨宮 護; 樋野 公宏 都市計画論文集/59(3)/pp.547-554, 2024-10
+Possibility of capturing behavior patterns of park users using Volunteered Street View Imagery (VSVI) ZHENG Xinrui; AMEMIYA Mamoru 17th Asian Planning School Association Congress, Proceedings book/pp.242-242, 2024-11-05
 Possibility of capturing behavior patterns of park users usin Volunteered Street View Imagery (VSVI) Zheng Xinrui; Amemniya Mamoru 地理情報システム学会講演論文集/33, 2024-10
 筑波研究学園都市における国家公務員宿舎の廃止・再開発と社会変化の関連：宿舎住民の人口移動に着目して 広兼 靖也; 雨宮 護; 澤田 学 地理情報システム学会講演論文集/33, 2024-10</t>
         </is>
@@ -11313,14 +10659,10 @@
           <t>MPPS / MSE</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://jglobal.jst.go.jp/detail?JGLOBAL_ID=201301045848886763</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ok_jglobal_fallback</t>
+          <t>jglobal_not_found</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -11328,89 +10670,19 @@
           <t>jglobal</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>公平な複数財配分の研究
-複数財割当問題の理論的研究
-マッチング市場の理論的研究
-肝臓・肺生体交換移植ネットワークの構築
-誘因両立的かつ効率的な資源配分ルールの設計に関する理論的研究
-戦略的操作不可能な社会的選択ルールの設計
-戦略的操作不可能かつ次善効率的資源配分ルールの設計
-Design of strategy-proof rules in public goods economies
-Design of strategy-proof and second-best efficienct resource allocation rules
-理論経済学
-マッチング理論
-, 社会的選択理論
-, ミクロ経済学
-Hidekazu Anno. Note on Gale's conjecture in one-sided matching problems. International Journal of Game Theory. 2025. 54
-Hidekazu Anno, Sui Takahashi. A unified approach to strategy-proofness of the deferred-acceptance rule and the top-trading cycles rule. Review of Economic Design. 2023. 27. 133-137
-Hidekazu Anno, Sui Takahashi. A decomposition of strategy-proofness in discrete resource allocation problems. Economics Bulletin. 2022. 42. 49-59
-Hidekazu Anno, Morimitsu Kurino. On the operation of multiple matching markets. Games and Economic Behavior. 2016. 100. 166-185
-Hidekazu Anno. A short proof for the characterization of the core in housing markets. Economics Letters. 2015. 126. 66-67</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>公平な複数財配分の研究 / 複数財割当問題の理論的研究 / マッチング市場の理論的研究 / 肝臓・肺生体交換移植ネットワークの構築 / 誘因両立的かつ効率的な資源配分ルールの設計に関する理論的研究 / 戦略的操作不可能な社会的選択ルールの設計 / 戦略的操作不可能かつ次善効率的資源配分ルールの設計 / Design of strategy-proof rules in public goods economies / Design of strategy-proof and second-best efficienct resource allocation rules</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>理論経済学</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>マッチング理論 / , 社会的選択理論 / , ミクロ経済学</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Hidekazu Anno. Note on Gale's conjecture in one-sided matching problems. International Journal of Game Theory. 2025. 54 / Hidekazu Anno, Sui Takahashi. A unified approach to strategy-proofness of the deferred-acceptance rule and the top-trading cycles rule. Review of Economic Design. 2023. 27. 133-137 / Hidekazu Anno, Sui Takahashi. A decomposition of strategy-proofness in discrete resource allocation problems. Economics Bulletin. 2022. 42. 49-59 / Hidekazu Anno, Morimitsu Kurino. On the operation of multiple matching markets. Games and Economic Behavior. 2016. 100. 166-185 / Hidekazu Anno. A short proof for the characterization of the core in housing markets. Economics Letters. 2015. 126. 66-67</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>個人間および部局間公平な非分割財配分について / 結婚市場において仲介業者が一部参加者を名簿から 削除するインセンティブを持たないメカニズムの設計 / 抽選独裁制とcardinal invarianceについて / プロ野球現役ドラフトにおける耐戦略的メカニズムの設計 / 複数並列市場における耐戦略的ルールの効率性に関する研究 / 不確実性下の同質財割当におけるrandomized uniform ruleの非効率性について</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>理論経済学 ; マッチング理論・ゲーム理論 ; ネットワーク・グラフ理論 ; 医療・ヘルスデータ ; 公共政策・社会工学 ; 経済・ファイナンス ; 数理最適化・OR</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>理論経済学
-マッチング理論
-, 社会的選択理論
-, ミクロ経済学
-マッチング理論・ゲーム理論
-ネットワーク・グラフ理論
-医療・ヘルスデータ
-公共政策・社会工学
-経済・ファイナンス
-数理最適化・OR
-安定マッチング
-資源配分
-メカニズムデザイン
-協力ゲーム・非協力ゲーム
-グラフ理論
-離散数学
-ネットワーク最適化
-組合せ構造
-医療データ分析
-生体情報解析
-ヘルスデータサイエンス
-統計解析</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>個人間および部局間公平な非分割財配分について
@@ -11418,21 +10690,7 @@
 抽選独裁制とcardinal invarianceについて
 プロ野球現役ドラフトにおける耐戦略的メカニズムの設計
 複数並列市場における耐戦略的ルールの効率性に関する研究
-不確実性下の同質財割当におけるrandomized uniform ruleの非効率性について
-公平な複数財配分の研究
-複数財割当問題の理論的研究
-マッチング市場の理論的研究
-肝臓・肺生体交換移植ネットワークの構築
-誘因両立的かつ効率的な資源配分ルールの設計に関する理論的研究
-戦略的操作不可能な社会的選択ルールの設計
-戦略的操作不可能かつ次善効率的資源配分ルールの設計
-Design of strategy-proof rules in public goods economies
-Design of strategy-proof and second-best efficienct resource allocation rules
-Hidekazu Anno. Note on Gale's conjecture in one-sided matching problems. International Journal of Game Theory. 2025. 54
-Hidekazu Anno, Sui Takahashi. A unified approach to strategy-proofness of the deferred-acceptance rule and the top-trading cycles rule. Review of Economic Design. 2023. 27. 133-137
-Hidekazu Anno, Sui Takahashi. A decomposition of strategy-proofness in discrete resource allocation problems. Economics Bulletin. 2022. 42. 49-59
-Hidekazu Anno, Morimitsu Kurino. On the operation of multiple matching markets. Games and Economic Behavior. 2016. 100. 166-185
-Hidekazu Anno. A short proof for the characterization of the core in housing markets. Economics Letters. 2015. 126. 66-67</t>
+不確実性下の同質財割当におけるrandomized uniform ruleの非効率性について</t>
         </is>
       </c>
     </row>
@@ -11867,17 +11125,18 @@
 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年
 都市における環境リスクの軽減の経済効果に関する研究
 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―
+環境衛生リスク改善の経済的価値
 経済政策
 開発経済学、教育の経済学、健康の経済学、応用計量経済学
 非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
 Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05
 Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020
-The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04
-The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/p.1305, 2017 Tsukuba Repository
+The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/69(3)/pp.1203-1237, 2021-04
+The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/pp.1305-1336, 2017 Tsukuba Repository
 Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... JAPAN AND THE WORLD ECONOMY/50/pp.36-46, 2019-06
 School Choice and Student Sorting: Evidence from Adachi Ward in Japan 牛島 光一 Japanese Economic Review/60(4)/pp.446-472, 2009-12
 オリンピック・パラリンピックにはどんな経済効果があるのか 牛島 光一 経済セミナー 2019年4・5月号, 2019-03
-Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi Public Policy Review, 2020-09
+Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi; Tanaka H. Noguchi、S. Bessho、A. Kawamur... Public Policy Review, 2020-09
 Building an Administrative Database of Children Bessho Shun-ichiro; Noguchi Haruko; 牛島 光一; Kawamura Akir... Public Policy Review, 2020-09
 高速鉄道の建設が居住地価格に与えた影響 牛島 光一 季刊 住宅土地経済/pp.24-31, 2019-07
 Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... IZA Discussion Papers, 2020-04
@@ -11898,7 +11157,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>民主主義における利益誘導と経済発展への影響 / 政策立案のための衛星データ利用法の探索：社会工学的アプローチ / 社会工学分野での衛星画像の利用促進に向けた探索的研究 / 衛星情報を利用した物流における大気環境改善の評価 / 反実仮想で測る公的資源配分の依怙贔屓と非効率 / 交通と環境に関する新経済地理学的基盤研究 / 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年 / 都市における環境リスクの軽減の経済効果に関する研究 / 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―</t>
+          <t>民主主義における利益誘導と経済発展への影響 / 政策立案のための衛星データ利用法の探索：社会工学的アプローチ / 社会工学分野での衛星画像の利用促進に向けた探索的研究 / 衛星情報を利用した物流における大気環境改善の評価 / 反実仮想で測る公的資源配分の依怙贔屓と非効率 / 交通と環境に関する新経済地理学的基盤研究 / 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年 / 都市における環境リスクの軽減の経済効果に関する研究 / 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に― / 環境衛生リスク改善の経済的価値</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -11913,7 +11172,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17 / Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05 / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020 / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04 / The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/p.1305, 2017 Tsukuba Repository / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... JAPAN AND THE WORLD ECONOMY/50/pp.36-46, 2019-06 / School Choice and Student Sorting: Evidence from Adachi Ward in Japan 牛島 光一 Japanese Economic Review/60(4)/pp.446-472, 2009-12 / オリンピック・パラリンピックにはどんな経済効果があるのか 牛島 光一 経済セミナー 2019年4・5月号, 2019-03 / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi Public Policy Review, 2020-09 / Building an Administrative Database of Children Bessho Shun-ichiro; Noguchi Haruko; 牛島 光一; Kawamura Akir... Public Policy Review, 2020-09 / 高速鉄道の建設が居住地価格に与えた影響 牛島 光一 季刊 住宅土地経済/pp.24-31, 2019-07 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... IZA Discussion Papers, 2020-04 / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ 香川涼亮; 小倉利仁; 太田 充; 牛島光一 都市住宅学/97/pp.126-135, 2017-04 CiNii / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― 姜 哲敏; 太田 充; 牛島光一 応用地域学研究/20/pp.67-77, 2016-09 / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 牛島 光一 応用地域学研究/(14)/pp.37-47, 2009-12 / 学校の質と地価－足立区の地価データを用いた検証 牛島 光一 住宅土地経済/(68)/pp.10-18, 2008-04 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ 牛島 光一 フィナンシャルレビュー/(141)/pp.65-85, 2019-12 / 子どもについての行政データベースの構築 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.106-119, 2019-12 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.120-140, 2019-12 / 区立小学校での補習の効果：足立区のケース 別所俊一郎; 川村顕; 野口晴子; 田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.141-159, 2019-12 / ヘドニック・アプローチにおける因果識別 牛島 光一 都市住宅学/2016(92)/pp.25-30, 2016-01 CiNii / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 牛島 光一 応用地域学研究/(18)/pp.62-63, 2014-09 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 牛島 光一 住宅土地経済/(2010年秋季)/pp.36-39, 2010-10 / The Impact of a High-speed Railway on Residential Land Prices Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1344), 2016-03 / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10</t>
+          <t>非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17 / Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05 / Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020 / The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/69(3)/pp.1203-1237, 2021-04 / The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/pp.1305-1336, 2017 Tsukuba Repository / Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... JAPAN AND THE WORLD ECONOMY/50/pp.36-46, 2019-06 / School Choice and Student Sorting: Evidence from Adachi Ward in Japan 牛島 光一 Japanese Economic Review/60(4)/pp.446-472, 2009-12 / オリンピック・パラリンピックにはどんな経済効果があるのか 牛島 光一 経済セミナー 2019年4・5月号, 2019-03 / Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi; Tanaka H. Noguchi、S. Bessho、A. Kawamur... Public Policy Review, 2020-09 / Building an Administrative Database of Children Bessho Shun-ichiro; Noguchi Haruko; 牛島 光一; Kawamura Akir... Public Policy Review, 2020-09 / 高速鉄道の建設が居住地価格に与えた影響 牛島 光一 季刊 住宅土地経済/pp.24-31, 2019-07 / Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... IZA Discussion Papers, 2020-04 / 東京オリンピック・パラリンピックの開催決定で住宅地地価は上昇するか？ 香川涼亮; 小倉利仁; 太田 充; 牛島光一 都市住宅学/97/pp.126-135, 2017-04 CiNii / 大気環境が地価に与える影響―東京都特別区の地価データを用いた検証― 姜 哲敏; 太田 充; 牛島光一 応用地域学研究/20/pp.67-77, 2016-09 / 小学校における学校の質は地価に影響するか？－東京都特別区の地価データを用いた検証 牛島 光一 応用地域学研究/(14)/pp.37-47, 2009-12 / 学校の質と地価－足立区の地価データを用いた検証 牛島 光一 住宅土地経済/(68)/pp.10-18, 2008-04 / 自然災害による就業機会の減少と人的資本投資－東日本大震災の事例－ 牛島 光一 フィナンシャルレビュー/(141)/pp.65-85, 2019-12 / 子どもについての行政データベースの構築 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.106-119, 2019-12 / 就学援助と学力の関連性について：足立区におけるパネルデータ分析結果から 別所俊一郎、川村顕、野口晴子、田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.120-140, 2019-12 / 区立小学校での補習の効果：足立区のケース 別所俊一郎; 川村顕; 野口晴子; 田中隆一; 牛島 光一 フィナンシャルレビュー/(141)/pp.141-159, 2019-12 / ヘドニック・アプローチにおける因果識別 牛島 光一 都市住宅学/2016(92)/pp.25-30, 2016-01 CiNii / ＜書評＞「柿崎一郎『鉄道と道路の政治経済学 タイの交通政策と商品流通1935～1975年』（京都大学学術出版会 2009年）」 牛島 光一 応用地域学研究/(18)/pp.62-63, 2014-09 / 海外論文紹介「子供の健康と近隣環境：無作為住宅バウチャー実験の結果-- Fortson J. G. and L. Sanbonmatsu, "Child health and neighborhood conditions: results from a randomized housing voucher experiment," Journal of human resources, forthcoming」 牛島 光一 住宅土地経済/(2010年秋季)/pp.36-39, 2010-10 / The Impact of a High-speed Railway on Residential Land Prices Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1344), 2016-03 / The Impact of a Universal Health Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi University of Tsukuba, Discussion Paper Series/(No.1321), 2014-10</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -11989,15 +11248,16 @@
 衛星画像と機械学習で描くサブサハラ・アフリカの民族優遇と交通インフラ整備の20年
 都市における環境リスクの軽減の経済効果に関する研究
 経済学の実証研究における衛星画像と機械学習の応用―アフリカの開発政策を事例に―
+環境衛生リスク改善の経済的価値
 非罰則的介入の犯罪抑止効果：渋谷区路上飲酒禁止条例を事例として 山縣 力也; 雨宮 護; 牛島 光一 環境心理学研究/14(1)/pp.33-33, 2026-05-17
 Benefits of Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Kang C.; Ota Mitsuru JOURNAL OF ENVIRONMENTAL ECONOMICS AND MANAGEMENT/125, 2024-05
 Benefits of Heavy-Duty Diesel Emission Regulations: Evidence from the World’s Largest Low Emission Zone Ushijima Koichi; Ota Mitsuru; Kang Choelmin 筑波大学 Department of Policy and Planning Sciences Discussion Paper Series, 2020
-The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/Ahead of Print, 2021-04
-The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/p.1305, 2017 Tsukuba Repository
+The Impact of a Universal Health Coverage Scheme on Precautionary Savings: Evidence from Thailand Ushijima Koichi ECONOMIC DEVELOPMENT AND CULTURAL CHANGE/69(3)/pp.1203-1237, 2021-04
+The Impact of a High-speed Railway on Residential Land Prices Kanasugi Hiroshi; Ushijima Koichi Papers in Regional Science/97(4)/pp.1305-1336, 2017 Tsukuba Repository
 Evaluating remedial education in elementary schools: Administrative data from a municipality in Japan Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... JAPAN AND THE WORLD ECONOMY/50/pp.36-46, 2019-06
 School Choice and Student Sorting: Evidence from Adachi Ward in Japan 牛島 光一 Japanese Economic Review/60(4)/pp.446-472, 2009-12
 オリンピック・パラリンピックにはどんな経済効果があるのか 牛島 光一 経済セミナー 2019年4・5月号, 2019-03
-Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi Public Policy Review, 2020-09
+Relationship between School Attendance Support and Academic Performance:An Analysis of Panel Data from Adachi Ward Ushijima Koichi; Tanaka H. Noguchi、S. Bessho、A. Kawamur... Public Policy Review, 2020-09
 Building an Administrative Database of Children Bessho Shun-ichiro; Noguchi Haruko; 牛島 光一; Kawamura Akir... Public Policy Review, 2020-09
 高速鉄道の建設が居住地価格に与えた影響 牛島 光一 季刊 住宅土地経済/pp.24-31, 2019-07
 Determinants of Teacher Value-added in Public Primary Schools: Evidence from Administrative Panel Data Bessho Shun-ichiro; Noguchi Haruko; Kawamura Akira; Tanak... IZA Discussion Papers, 2020-04
@@ -12255,6 +11515,8 @@
 交通シミュレーション
 災害復旧
 相互作用
+神経発達過程を模した幹線・フィーダー型バスネットワーク最適化 出本大起; 浦田 淳司 第73回土木計画学研究発表会・講演集, 2026-06
+Data-centric AIにむけたプローブデータの欠測検知手法の開発 中山凛空; 浦田 淳司; 鵜飼誠治 第73回土木計画学研究発表会・講演集, 2026-06
 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
 Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12
 A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12
@@ -12276,9 +11538,7 @@
 筑波大学理工学群におけるデータサイエンス応用基礎教育 浦田 淳司; オム ソンヨン; 川島 宏一 大学教育と情報, 2024-03
 Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01
 Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository
-災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02
-選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02
-LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09</t>
+災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -12298,7 +11558,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12 / A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12 / Robust OD matrix estimation method under low sampling rate by utilizing multiscale information of questionnaire data Mochizuki Y.; Pel A.J.; Hinsbergen C.; URATA Junji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06 / Developing an Estimation Algorithm for Generalizing the Parameters of the network-GEV model in Destination Choice URATA Junji; KANEDA Yudai; ISHII Ryoji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06 / 通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ 上杉 朋花; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / EVユーザーの充電場所選択問題に対するゲーム理論的考察 大野 隆輔; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / 災害復旧期における個々人の移動パターン変化の特徴分析 村上 智仁; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / メタ分析による災害時の避難開始選択要因の評価 柴田 龍聖; 浦田 淳司; 大東 延幸 第72回土木計画学研究発表会・講演集, 2025-11 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction URATA Junji; NAKAZAWA Ruka THE 29TH INTERNATIONAL CONFERENCE OF HONG KONG SOCIETY FOR TRANSPORTATION STUDIES, 2025-12 / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging Mochizuki Y.; 浦田 淳司; Hato E. 2024 IEEE 27th International Conference on Intelligent Transportation Systems (ITSC)/pp.653-660, 2025-03 / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 田村 侑介; 浦田 淳司 都市計画論文集/60(3)/pp.1543-1550, 2025-10 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 相互作用下での多肢選択行動の量子計算による求解 中澤瑠河; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- 中嶋 駿; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- 中山 凛空; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— 河瀬理貴; 井料隆雅; 浦田 淳司 土木学会論文集, 2024-12 / Object-oriented Bayesian Networks for Activity-based Model with deep generative graph averaging URATA Junji; Mochizuki Y.; Hato E. IEEE 27th International Conference on Intelligent Transportation Systems, 2024-09 / 筑波大学理工学群におけるデータサイエンス応用基礎教育 浦田 淳司; オム ソンヨン; 川島 宏一 大学教育と情報, 2024-03 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02 / 選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02 / LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09</t>
+          <t>神経発達過程を模した幹線・フィーダー型バスネットワーク最適化 出本大起; 浦田 淳司 第73回土木計画学研究発表会・講演集, 2026-06 / Data-centric AIにむけたプローブデータの欠測検知手法の開発 中山凛空; 浦田 淳司; 鵜飼誠治 第73回土木計画学研究発表会・講演集, 2026-06 / 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17 / Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12 / A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12 / Robust OD matrix estimation method under low sampling rate by utilizing multiscale information of questionnaire data Mochizuki Y.; Pel A.J.; Hinsbergen C.; URATA Junji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06 / Developing an Estimation Algorithm for Generalizing the Parameters of the network-GEV model in Destination Choice URATA Junji; KANEDA Yudai; ISHII Ryoji International Symposium on Transportation Data &amp; Modelling (ISTDM2023), 2023-06 / 通学自転車の経路・駐輪場選択モデルの構築～大学構内を対象として～ 上杉 朋花; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / EVユーザーの充電場所選択問題に対するゲーム理論的考察 大野 隆輔; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / 災害復旧期における個々人の移動パターン変化の特徴分析 村上 智仁; 浦田 淳司 第72回土木計画学研究発表会・講演集, 2025-11 / メタ分析による災害時の避難開始選択要因の評価 柴田 龍聖; 浦田 淳司; 大東 延幸 第72回土木計画学研究発表会・講演集, 2025-11 / Quantum Computation for Solving Multi-Choice Decision-Making Under Interaction URATA Junji; NAKAZAWA Ruka THE 29TH INTERNATIONAL CONFERENCE OF HONG KONG SOCIETY FOR TRANSPORTATION STUDIES, 2025-12 / Object-Oriented Bayesian Networks for Activity-Based Model with Deep Generative Graph Averaging Mochizuki Y.; 浦田 淳司; Hato E. 2024 IEEE 27th International Conference on Intelligent Transportation Systems (ITSC)/pp.653-660, 2025-03 / 集合住宅における充電器設置の合意形成ルールとEV普及の関係 田村 侑介; 浦田 淳司 都市計画論文集/60(3)/pp.1543-1550, 2025-10 / 共創型スマートプランニングによるキャンパス屋外空間のリデザイン：筑波大学第3エリアスマートキャンパスプロジェクト社会実験の事例報告 藤井 さやか; 浦田 淳司; 雨宮 護; 山本 幸子; 鈴木 健嗣; 槙枝 順一; 山崎 貴大; 永... 都市計画報告集/24(4)/pp.767-772, 2026-03 / 相互作用下での多肢選択行動の量子計算による求解 中澤瑠河; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 半構造化SP調査のためのwebアプリの開発-避難生活場所選択を対象として- 中嶋 駿; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 活動シミュレーションにむけた移動軌跡データへの都市活動ラベリング-能登半島での実装- 中山 凛空; 浦田 淳司 第71回土木計画学研究発表会, 2025-06 / 人道支援ロジスティクスにおける在庫モデルのレビューと展望—商業分野の理論研究を踏まえて— 河瀬理貴; 井料隆雅; 浦田 淳司 土木学会論文集, 2024-12 / Object-oriented Bayesian Networks for Activity-based Model with deep generative graph averaging URATA Junji; Mochizuki Y.; Hato E. IEEE 27th International Conference on Intelligent Transportation Systems, 2024-09 / 筑波大学理工学群におけるデータサイエンス応用基礎教育 浦田 淳司; オム ソンヨン; 川島 宏一 大学教育と情報, 2024-03 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 / Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository / 災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -12386,6 +11646,8 @@
 マルチスケールな拠点空間計画のための新たな行動モデル研究
 災害時都市継続計画にむけた即応型需要予測の信頼性向上のためのデータフロー
 災害時都市活動支援のためのsoftware2.0型シミュレータの構築
+神経発達過程を模した幹線・フィーダー型バスネットワーク最適化 出本大起; 浦田 淳司 第73回土木計画学研究発表会・講演集, 2026-06
+Data-centric AIにむけたプローブデータの欠測検知手法の開発 中山凛空; 浦田 淳司; 鵜飼誠治 第73回土木計画学研究発表会・講演集, 2026-06
 大学キャンパスにおける自転車の通行・駐輪規制とストリートファニチャ設置による利用者の意識・行動の変化：筑波大学第3エリアスマートキャンパスプロジェクトを対象に 舩戸 祐汰; 雨宮 護; 藤井 さやか; 浦田 淳司; 山本 幸子 環境心理学研究/14(1)/pp.43-43, 2026-05-17
 Activity Chain Generation with Dynamic Object-Oriented Bayesian Networks URATA Junji; Mochizuki Y.; Hato E. The Conference in Emerging Technologies in Transportation Systems, 2023-12
 A tri-level optimization model to design transit routes for public buses and privately owned commercial vehicles with elastic passenger demand Zeeshan M.; URATA Junji; Hato E. The 26th international conference of Hong Kong society for transportation studies, 2023-12
@@ -12407,9 +11669,7 @@
 筑波大学理工学群におけるデータサイエンス応用基礎教育 浦田 淳司; オム ソンヨン; 川島 宏一 大学教育と情報, 2024-03
 Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01
 Dynamic discrete choice model and its estimation algorithm with dynamic inconsistent expected utility in an uncertain situation 浦田 淳司; Hato Eiji TRANSPORTATION RESEARCH PART C-EMERGING TECHNOLOGIES/158, 2024-01 Tsukuba Repository
-災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02
-選択肢の不確実性を考慮した動的離散選択モデル 近藤 愛子; 浦田 淳司; 羽藤 英二 交通工学論文集/9(2)/pp.A_197-A_204, 2023-02
-LET'S GO ABROAD!(第81回)座談会 連載7年を迎えて、これからの土木国際人材育成に本連載ができること 吉見 昌宏; 橋本 純; スレン ソッキアン; 浦田 淳司; 森 弘継 土木学会誌/107(9)/pp.40-43, 2022-09</t>
+災害復旧期の交通需要予測のための時間変化するパラメータのリアルタイム推定手法 望月 陽介; 浦田 淳司 交通工学論文集/9(2)/pp.A_19-A_27, 2023-02</t>
         </is>
       </c>
     </row>
@@ -12463,7 +11723,7 @@
 職名
 准教授
 eメール
-G($.y(B&lt;IOx-&lt;IPB,$E-,.$.yxExzE#)
++D@J7D^Xek6IXel^H@aIHJ@J76a68a?E
 マクロ経済学
 計量経済学
 Model uncertainty, economic development, and welfare costs of business cycles Okubo Masakatsu JOURNAL OF MACROECONOMICS/76, 2023-06
@@ -12488,7 +11748,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>詳細検索 / 使い方 / お問い合わせ / 大久保 正勝(オオクボ マサカツ) / 所属 / システム情報系 / 職名 / 准教授 / eメール / G($.y(B&lt;IOx-&lt;IPB,$E-,.$.yxExzE#)</t>
+          <t>詳細検索 / 使い方 / お問い合わせ / 大久保 正勝(オオクボ マサカツ) / 所属 / システム情報系 / 職名 / 准教授 / eメール / +D@J7D^Xek6IXel^H@aIHJ@J76a68a?E</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -12504,7 +11764,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>詳細検索 ; 使い方 ; お問い合わせ ; 大久保 正勝(オオクボ マサカツ) ; 所属 ; システム情報系 ; 職名 ; 准教授 ; eメール ; G($.y(B&lt;IOx-&lt;IPB,$E-,.$.yxExzE#) ; 労働経済・就職マッチング ; 保険・金融行動 ; 意思決定分析 ; 政策評価・計量分析 ; 経済・ファイナンス ; AI・データサイエンス</t>
+          <t>詳細検索 ; 使い方 ; お問い合わせ ; 大久保 正勝(オオクボ マサカツ) ; 所属 ; システム情報系 ; 職名 ; 准教授 ; eメール ; +D@J7D^Xek6IXel^H@aIHJ@J76a68a?E ; 労働経済・就職マッチング ; 保険・金融行動 ; 意思決定分析 ; 政策評価・計量分析 ; 経済・ファイナンス ; AI・データサイエンス</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -12523,7 +11783,7 @@
 職名
 准教授
 eメール
-G($.y(B&lt;IOx-&lt;IPB,$E-,.$.yxExzE#)
++D@J7D^Xek6IXel^H@aIHJ@J76a68a?E
 マクロ経済学
 計量経済学
 労働経済・就職マッチング
@@ -13062,9 +12322,10 @@
 衛生学・公衆衛生学
 健康政策
 社会政策
-健康経済学
+医療経済学
 国際保健
-Financial burden of menstrual and menopausal symptoms: Productivity loss from absenteeism and presenteeism among working age women KASAHARA Shingo; GOTO Rei; SUZUKI Shu; SAKAMOTO Haruk... Reproductive Health/p.(in press), 2026-04
+Spousal bereavement and mental health among older Japanese adults Iida Masumi; Sugawara Ikuko; Kobayashi Erika; Okamoto ... Research on Aging, 2026-06
+Financial burden of menstrual and menopausal symptoms: Productivity loss from absenteeism and presenteeism among working age women KASAHARA Shingo; GOTO Rei; SUZUKI Shu; SAKAMOTO Haruk... Reproductive Health, 2026-05
 Comparison income and subjective well-being: Evidence from a nationwide panel survey in Japan Shiraishi Kenichi; Sumita Kazuto; Kamimura Kazuki; Oka... Economics Bulletin/p.(in press), 2026-04
 Reversed loneliness development after age 65 for men and women: Modeling of the age trajectories of loneliness using national cohorts in Taiwan and Japan Chiu Ching-Ju; Hou Szu-Yu; Kobayashi Erika; Lin Yu-Ch... Geriatrics &amp; Gerontology International/25(4)/pp.620-627, 2025-04-01 PubMed
 Socioeconomic inequity in access to medical and long-term care among older people Okamoto Shohei; Yamada Atsuhiro; Kobayashi Erika; Lian... International Journal for Equity in Health/24(1)/p.28, 2025-01-23 PubMed
@@ -13088,7 +12349,6 @@
 Age trajectories of disability development after 65: A comparison between Japan and Taiwan Chiu Ching-Ju; Chen Yun-An; Kobayashi Erika; Murayama ... Archives of Gerontology and Geriatrics/96, 2021-04-01 PubMed
 Age, gender, and financial literacy in Japan Okamoto Shohei; Komamura Kohei PLoS ONE/16(11), 2021-04-01 PubMed
 Increase in suicide following an initial decline during the COVID-19 pandemic in Japan Tanaka Takanao; Okamoto Shohei Nature Human Behaviour/5(2)/pp.229-238, 2021-02-01 PubMed
-Decomposition of gender differences in cognitive functioning: National Survey of the Japanese elderly Okamoto Shohei; Kobayashi Erika; Murayama Hiroshi; Lia... BMC Geriatrics/21(1)/p.38, 2021-01-10 PubMed
 Box 5. Catastrophic health spending and unmet need among households with older persons in Japan. Okamoto Shohei Global monitoring report on financial protection in heath 2021, 2021-12
 新型コロナウイルス感染症拡⼤下における自殺者数の推移 岡本 翔平; 田中 孝直 精神科治療学/pp.869-874, 2021-08
 新型コロナウイルス感染症拡大のもう一つの脅威 : 感染症対策による非感染性疾患リスクへの影響 岡本 翔平 生活経済政策/294/pp.20-27, 2021-07
@@ -13108,12 +12368,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>健康政策 / 社会政策 / 健康経済学 / 国際保健</t>
+          <t>健康政策 / 社会政策 / 医療経済学 / 国際保健</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Financial burden of menstrual and menopausal symptoms: Productivity loss from absenteeism and presenteeism among working age women KASAHARA Shingo; GOTO Rei; SUZUKI Shu; SAKAMOTO Haruk... Reproductive Health/p.(in press), 2026-04 / Comparison income and subjective well-being: Evidence from a nationwide panel survey in Japan Shiraishi Kenichi; Sumita Kazuto; Kamimura Kazuki; Oka... Economics Bulletin/p.(in press), 2026-04 / Reversed loneliness development after age 65 for men and women: Modeling of the age trajectories of loneliness using national cohorts in Taiwan and Japan Chiu Ching-Ju; Hou Szu-Yu; Kobayashi Erika; Lin Yu-Ch... Geriatrics &amp; Gerontology International/25(4)/pp.620-627, 2025-04-01 PubMed / Socioeconomic inequity in access to medical and long-term care among older people Okamoto Shohei; Yamada Atsuhiro; Kobayashi Erika; Lian... International Journal for Equity in Health/24(1)/p.28, 2025-01-23 PubMed / The importance of examining both the amount and balance of social support: A study on the relationship between social support and subjective well-being of older Japanese adults Tham Yukari Jessica; Okamoto Shohei; Kobayashi Erika Journal of Community &amp; Applied Social Psychology/34(2), 2024-03 / Universal health coverage in the context of population ageing: catastrophic health expenditure and unmet need for healthcare Okamoto Shohei; Sata Mizuki; Rosenberg Megumi; Nakagos... Health Economics Review/14(1)/p.8, 2024-01-30 PubMed / Better data on unmet healthcare need can strengthen global monitoring of universal health coverage Rosenberg Megumi; Kowal Paul; Rahman Md Mizanur; Okamo... BMJ/382, 2023-09-05 PubMed / Economic effects of healthy ageing: functional limitation, forgone wages, and medical and long-term care costs Okamoto Shohei; Sakamoto Haruka; Kamimura Kazuki; Koma... Health Economics Review/13(1)/p.28, 2023-05-10 PubMed / An overview of systems for providing integrated and comprehensive care for older people in Japan Sano Junko; Hirazawa Yuzuki; Komamura Kohei; Okamoto ... Archives of Public Health/81(1)/p.81, 2023-05-04 PubMed / Living alone and depressive symptoms among older Japanese: Do urbanization and time period matter? Kobayashi Erika; Harada Ken; Okamoto Shohei; Liang Je... The Journals of Gerontology. Series B, Psychological Sciences and Social Sciences/78(4)/pp.718-729, 2023-04-01 PubMed / Financial incentives for exercise and medical care costs Kamimura Kazuki; Okamoto Shohei; Shiraishi Kenichi; Su... The International Journal of Economic Policy Studies/17(1)/pp.95-116, 2023-02 / The retirement-health puzzle: A sigh of relief at retirement? Okamoto Shohei; Kobayashi Erika; Komamura Kohei The Journals of Gerontology. Series B, Psychological Sciences and Social Sciences/78(1)/pp.167-178, 2023-01-28 PubMed / Effect of diabetes and prediabetes on the development of disability and mortality among middle-aged Japanese adults: A 22-year follow up of NIPPON DATA90 Tran Ngoc Hoang Phap; Kadota Aya; Yano Yuichiro; Harad... Journal of Diabetes Investigation/13(11)/pp.1897-1904, 2022-11-01 PubMed / Towards universal health coverage in the context of population ageing: a narrative review on the implications from the long-term care system in Japan Okamoto Shohei; Komamura Kohei Archives of Public Health/80(1)/p.210, 2022-09-21 PubMed / State of emergency and human mobility during the COVID-19 pandemic in Japan Okamoto Shohei Journal of Transport and Health/26, 2022-09-01 PubMed / COVID-19 vaccine hesitancy and vaccine passports: a cross-sectional conjoint experiment in Japan Okamoto Shohei; Kamimura Kazuki; Komamura Kohei BMJ Open/12(6), 2022-06-16 PubMed / National Health Spending, Health-Care Resources, Service Utilization, and Health Outcomes Tanaka Takanao; Okamoto Shohei; Canning David American Journal of Epidemiology/191(3)/pp.386-396, 2022-02-19 PubMed / Retirement and Social Activities in Japan: Does Age Moderate the Association? Kobayashi Erika; Sugawara Ikuko; Fukaya Taro; Okamoto ... Research on Aging/44(2)/pp.144-155, 2022-02-01 PubMed / Social isolation and cognitive functioning: A quasi-experimental approach Okamoto Shohei; Kobayashi Erika The Journals of Gerontology. Series B, Psychological Sciences and Social Sciences/76(7)/pp.1441-1451, 2021-08-13 PubMed / Daily steps and healthcare costs in Japanese communities Okamoto Shohei; Kamimura Kazuki; Shiraishi Kenichi; Su... Scientific Reports/11(1), 2021-07 PubMed / Parental socioeconomic status and adolescent health in Japan Okamoto Shohei Scientific reports/11(1), 2021-06-08 PubMed / Age trajectories of disability development after 65: A comparison between Japan and Taiwan Chiu Ching-Ju; Chen Yun-An; Kobayashi Erika; Murayama ... Archives of Gerontology and Geriatrics/96, 2021-04-01 PubMed / Age, gender, and financial literacy in Japan Okamoto Shohei; Komamura Kohei PLoS ONE/16(11), 2021-04-01 PubMed / Increase in suicide following an initial decline during the COVID-19 pandemic in Japan Tanaka Takanao; Okamoto Shohei Nature Human Behaviour/5(2)/pp.229-238, 2021-02-01 PubMed / Decomposition of gender differences in cognitive functioning: National Survey of the Japanese elderly Okamoto Shohei; Kobayashi Erika; Murayama Hiroshi; Lia... BMC Geriatrics/21(1)/p.38, 2021-01-10 PubMed / Box 5. Catastrophic health spending and unmet need among households with older persons in Japan. Okamoto Shohei Global monitoring report on financial protection in heath 2021, 2021-12 / 新型コロナウイルス感染症拡⼤下における自殺者数の推移 岡本 翔平; 田中 孝直 精神科治療学/pp.869-874, 2021-08 / 新型コロナウイルス感染症拡大のもう一つの脅威 : 感染症対策による非感染性疾患リスクへの影響 岡本 翔平 生活経済政策/294/pp.20-27, 2021-07 / 高齢期の就労と健康 岡本 翔平 健康長寿ネット, 2019-12 / わが国の栄養・食事と関連する健康施策の現状 岡本 翔平; 栗原 綾子; 岡村 智教 動脈硬化予防/pp.40-45, 2017-03</t>
+          <t>Spousal bereavement and mental health among older Japanese adults Iida Masumi; Sugawara Ikuko; Kobayashi Erika; Okamoto ... Research on Aging, 2026-06 / Financial burden of menstrual and menopausal symptoms: Productivity loss from absenteeism and presenteeism among working age women KASAHARA Shingo; GOTO Rei; SUZUKI Shu; SAKAMOTO Haruk... Reproductive Health, 2026-05 / Comparison income and subjective well-being: Evidence from a nationwide panel survey in Japan Shiraishi Kenichi; Sumita Kazuto; Kamimura Kazuki; Oka... Economics Bulletin/p.(in press), 2026-04 / Reversed loneliness development after age 65 for men and women: Modeling of the age trajectories of loneliness using national cohorts in Taiwan and Japan Chiu Ching-Ju; Hou Szu-Yu; Kobayashi Erika; Lin Yu-Ch... Geriatrics &amp; Gerontology International/25(4)/pp.620-627, 2025-04-01 PubMed / Socioeconomic inequity in access to medical and long-term care among older people Okamoto Shohei; Yamada Atsuhiro; Kobayashi Erika; Lian... International Journal for Equity in Health/24(1)/p.28, 2025-01-23 PubMed / The importance of examining both the amount and balance of social support: A study on the relationship between social support and subjective well-being of older Japanese adults Tham Yukari Jessica; Okamoto Shohei; Kobayashi Erika Journal of Community &amp; Applied Social Psychology/34(2), 2024-03 / Universal health coverage in the context of population ageing: catastrophic health expenditure and unmet need for healthcare Okamoto Shohei; Sata Mizuki; Rosenberg Megumi; Nakagos... Health Economics Review/14(1)/p.8, 2024-01-30 PubMed / Better data on unmet healthcare need can strengthen global monitoring of universal health coverage Rosenberg Megumi; Kowal Paul; Rahman Md Mizanur; Okamo... BMJ/382, 2023-09-05 PubMed / Economic effects of healthy ageing: functional limitation, forgone wages, and medical and long-term care costs Okamoto Shohei; Sakamoto Haruka; Kamimura Kazuki; Koma... Health Economics Review/13(1)/p.28, 2023-05-10 PubMed / An overview of systems for providing integrated and comprehensive care for older people in Japan Sano Junko; Hirazawa Yuzuki; Komamura Kohei; Okamoto ... Archives of Public Health/81(1)/p.81, 2023-05-04 PubMed / Living alone and depressive symptoms among older Japanese: Do urbanization and time period matter? Kobayashi Erika; Harada Ken; Okamoto Shohei; Liang Je... The Journals of Gerontology. Series B, Psychological Sciences and Social Sciences/78(4)/pp.718-729, 2023-04-01 PubMed / Financial incentives for exercise and medical care costs Kamimura Kazuki; Okamoto Shohei; Shiraishi Kenichi; Su... The International Journal of Economic Policy Studies/17(1)/pp.95-116, 2023-02 / The retirement-health puzzle: A sigh of relief at retirement? Okamoto Shohei; Kobayashi Erika; Komamura Kohei The Journals of Gerontology. Series B, Psychological Sciences and Social Sciences/78(1)/pp.167-178, 2023-01-28 PubMed / Effect of diabetes and prediabetes on the development of disability and mortality among middle-aged Japanese adults: A 22-year follow up of NIPPON DATA90 Tran Ngoc Hoang Phap; Kadota Aya; Yano Yuichiro; Harad... Journal of Diabetes Investigation/13(11)/pp.1897-1904, 2022-11-01 PubMed / Towards universal health coverage in the context of population ageing: a narrative review on the implications from the long-term care system in Japan Okamoto Shohei; Komamura Kohei Archives of Public Health/80(1)/p.210, 2022-09-21 PubMed / State of emergency and human mobility during the COVID-19 pandemic in Japan Okamoto Shohei Journal of Transport and Health/26, 2022-09-01 PubMed / COVID-19 vaccine hesitancy and vaccine passports: a cross-sectional conjoint experiment in Japan Okamoto Shohei; Kamimura Kazuki; Komamura Kohei BMJ Open/12(6), 2022-06-16 PubMed / National Health Spending, Health-Care Resources, Service Utilization, and Health Outcomes Tanaka Takanao; Okamoto Shohei; Canning David American Journal of Epidemiology/191(3)/pp.386-396, 2022-02-19 PubMed / Retirement and Social Activities in Japan: Does Age Moderate the Association? Kobayashi Erika; Sugawara Ikuko; Fukaya Taro; Okamoto ... Research on Aging/44(2)/pp.144-155, 2022-02-01 PubMed / Social isolation and cognitive functioning: A quasi-experimental approach Okamoto Shohei; Kobayashi Erika The Journals of Gerontology. Series B, Psychological Sciences and Social Sciences/76(7)/pp.1441-1451, 2021-08-13 PubMed / Daily steps and healthcare costs in Japanese communities Okamoto Shohei; Kamimura Kazuki; Shiraishi Kenichi; Su... Scientific Reports/11(1), 2021-07 PubMed / Parental socioeconomic status and adolescent health in Japan Okamoto Shohei Scientific reports/11(1), 2021-06-08 PubMed / Age trajectories of disability development after 65: A comparison between Japan and Taiwan Chiu Ching-Ju; Chen Yun-An; Kobayashi Erika; Murayama ... Archives of Gerontology and Geriatrics/96, 2021-04-01 PubMed / Age, gender, and financial literacy in Japan Okamoto Shohei; Komamura Kohei PLoS ONE/16(11), 2021-04-01 PubMed / Increase in suicide following an initial decline during the COVID-19 pandemic in Japan Tanaka Takanao; Okamoto Shohei Nature Human Behaviour/5(2)/pp.229-238, 2021-02-01 PubMed / Box 5. Catastrophic health spending and unmet need among households with older persons in Japan. Okamoto Shohei Global monitoring report on financial protection in heath 2021, 2021-12 / 新型コロナウイルス感染症拡⼤下における自殺者数の推移 岡本 翔平; 田中 孝直 精神科治療学/pp.869-874, 2021-08 / 新型コロナウイルス感染症拡大のもう一つの脅威 : 感染症対策による非感染性疾患リスクへの影響 岡本 翔平 生活経済政策/294/pp.20-27, 2021-07 / 高齢期の就労と健康 岡本 翔平 健康長寿ネット, 2019-12 / わが国の栄養・食事と関連する健康施策の現状 岡本 翔平; 栗原 綾子; 岡村 智教 動脈硬化予防/pp.40-45, 2017-03</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -13133,7 +12393,7 @@
 衛生学・公衆衛生学
 健康政策
 社会政策
-健康経済学
+医療経済学
 国際保健
 家族・人口政策
 政策評価・計量分析
@@ -13162,7 +12422,8 @@
 高齢期の就労と健康：メカニズムの解明と社会経済への影響に関する研究
 人口高齢化と疾病構造の変化に対応したユニバーサルヘルスカバレッジに関する研究
 疫学転換に対応したuniversal health coverageモニタリング指標の開発
-Financial burden of menstrual and menopausal symptoms: Productivity loss from absenteeism and presenteeism among working age women KASAHARA Shingo; GOTO Rei; SUZUKI Shu; SAKAMOTO Haruk... Reproductive Health/p.(in press), 2026-04
+Spousal bereavement and mental health among older Japanese adults Iida Masumi; Sugawara Ikuko; Kobayashi Erika; Okamoto ... Research on Aging, 2026-06
+Financial burden of menstrual and menopausal symptoms: Productivity loss from absenteeism and presenteeism among working age women KASAHARA Shingo; GOTO Rei; SUZUKI Shu; SAKAMOTO Haruk... Reproductive Health, 2026-05
 Comparison income and subjective well-being: Evidence from a nationwide panel survey in Japan Shiraishi Kenichi; Sumita Kazuto; Kamimura Kazuki; Oka... Economics Bulletin/p.(in press), 2026-04
 Reversed loneliness development after age 65 for men and women: Modeling of the age trajectories of loneliness using national cohorts in Taiwan and Japan Chiu Ching-Ju; Hou Szu-Yu; Kobayashi Erika; Lin Yu-Ch... Geriatrics &amp; Gerontology International/25(4)/pp.620-627, 2025-04-01 PubMed
 Socioeconomic inequity in access to medical and long-term care among older people Okamoto Shohei; Yamada Atsuhiro; Kobayashi Erika; Lian... International Journal for Equity in Health/24(1)/p.28, 2025-01-23 PubMed
@@ -13186,7 +12447,6 @@
 Age trajectories of disability development after 65: A comparison between Japan and Taiwan Chiu Ching-Ju; Chen Yun-An; Kobayashi Erika; Murayama ... Archives of Gerontology and Geriatrics/96, 2021-04-01 PubMed
 Age, gender, and financial literacy in Japan Okamoto Shohei; Komamura Kohei PLoS ONE/16(11), 2021-04-01 PubMed
 Increase in suicide following an initial decline during the COVID-19 pandemic in Japan Tanaka Takanao; Okamoto Shohei Nature Human Behaviour/5(2)/pp.229-238, 2021-02-01 PubMed
-Decomposition of gender differences in cognitive functioning: National Survey of the Japanese elderly Okamoto Shohei; Kobayashi Erika; Murayama Hiroshi; Lia... BMC Geriatrics/21(1)/p.38, 2021-01-10 PubMed
 Box 5. Catastrophic health spending and unmet need among households with older persons in Japan. Okamoto Shohei Global monitoring report on financial protection in heath 2021, 2021-12
 新型コロナウイルス感染症拡⼤下における自殺者数の推移 岡本 翔平; 田中 孝直 精神科治療学/pp.869-874, 2021-08
 新型コロナウイルス感染症拡大のもう一つの脅威 : 感染症対策による非感染性疾患リスクへの影響 岡本 翔平 生活経済政策/294/pp.20-27, 2021-07
@@ -14823,9 +14083,10 @@
 計算社会科学
 ウェブサイエンス
 ビッグデータ
+Fluctuation scaling in online social media Sano Yu